--- a/reports/investment_dashboard.xlsx
+++ b/reports/investment_dashboard.xlsx
@@ -525,16 +525,16 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>MU</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Micron Technology, Inc.</t>
+          <t>Taiwan Semiconductor Manufacturing Company Limited</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>57.27</v>
+        <v>55.66</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>966.780029296875</v>
+        <v>418.9500122070312</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -550,24 +550,19 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>84.2</v>
+        <v>100</v>
       </c>
       <c r="I2" t="n">
-        <v>88.2</v>
+        <v>100</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Revenue Growth; Earnings Fcf; Balance Sheet</t>
+          <t>Revenue Growth; Earnings Fcf; Balance Sheet; Valuation</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
           <t>Industry Growth; Competitive Advantage; Catalysts; Inflation Resilience</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>High market sensitivity / beta</t>
         </is>
       </c>
     </row>
@@ -577,16 +572,16 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>MU</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Taiwan Semiconductor Manufacturing Company Limited</t>
+          <t>Micron Technology, Inc.</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>55.66</v>
+        <v>55.05</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -594,7 +589,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>418.9500122070312</v>
+        <v>966.780029296875</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -602,19 +597,24 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="I3" t="n">
         <v>100</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Revenue Growth; Earnings Fcf; Balance Sheet; Valuation</t>
+          <t>Revenue Growth; Earnings Fcf; Balance Sheet</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
           <t>Industry Growth; Competitive Advantage; Catalysts; Inflation Resilience</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>High market sensitivity / beta</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>MongoDB, Inc. Class A Common Stock</t>
+          <t>MongoDB, Inc.</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1426,11 +1426,11 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>ACM Research, Inc. Class A Common Stock</t>
+          <t>ACM Research, Inc.</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>42.73</v>
+        <v>42.76</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -2115,7 +2115,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>MU</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -2128,19 +2128,19 @@
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>9.02</v>
+        <v>8.84</v>
       </c>
       <c r="F2" t="n">
-        <v>7.04</v>
+        <v>8.67</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>7.71</v>
+        <v>5.46</v>
       </c>
       <c r="I2" t="n">
-        <v>3.5</v>
+        <v>2.69</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -2149,13 +2149,13 @@
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>57.27</v>
+        <v>55.66</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>MU</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -2168,19 +2168,19 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>8.84</v>
+        <v>9.02</v>
       </c>
       <c r="F3" t="n">
-        <v>8.67</v>
+        <v>4.82</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>5.46</v>
+        <v>7.71</v>
       </c>
       <c r="I3" t="n">
-        <v>2.69</v>
+        <v>3.5</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -2189,7 +2189,7 @@
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>55.66</v>
+        <v>55.05</v>
       </c>
     </row>
     <row r="4">
@@ -2851,7 +2851,7 @@
         <v>4.02</v>
       </c>
       <c r="F20" t="n">
-        <v>6.86</v>
+        <v>6.89</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -2869,7 +2869,7 @@
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>42.73</v>
+        <v>42.76</v>
       </c>
     </row>
     <row r="21">
@@ -3343,7 +3343,7 @@
     <col width="15" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="18" customWidth="1" min="16" max="16"/>
-    <col width="11" customWidth="1" min="17" max="17"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
     <col width="16" customWidth="1" min="18" max="18"/>
     <col width="19" customWidth="1" min="19" max="19"/>
     <col width="23" customWidth="1" min="20" max="20"/>
@@ -3514,12 +3514,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>MU</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Micron Technology, Inc.</t>
+          <t>Taiwan Semiconductor Manufacturing Company Limited</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -3532,60 +3532,69 @@
           <t>Semiconductors</t>
         </is>
       </c>
+      <c r="E2" t="n">
+        <v>2172873342976</v>
+      </c>
       <c r="F2" t="n">
-        <v>966.780029296875</v>
+        <v>418.9500122070312</v>
       </c>
       <c r="G2" t="n">
-        <v>90273996800</v>
+        <v>4440492343296</v>
       </c>
       <c r="H2" t="n">
-        <v>3.457</v>
+        <v>0.36</v>
       </c>
       <c r="I2" t="n">
-        <v>44.23</v>
+        <v>13.4</v>
       </c>
       <c r="J2" t="n">
-        <v>13.685</v>
+        <v>0.774</v>
       </c>
       <c r="K2" t="n">
-        <v>7639499776</v>
+        <v>730826014720</v>
       </c>
       <c r="M2" t="n">
-        <v>26022000640</v>
+        <v>3518010228736</v>
       </c>
       <c r="N2" t="n">
-        <v>6376000000</v>
+        <v>1068558516224</v>
       </c>
       <c r="O2" t="n">
-        <v>0.7256899999999999</v>
+        <v>0.6423</v>
       </c>
       <c r="P2" t="n">
-        <v>0.80370003</v>
+        <v>0.60344005</v>
       </c>
       <c r="Q2" t="n">
-        <v>21.858015</v>
+        <v>31.264927</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0.48933163</v>
+      </c>
+      <c r="S2" t="n">
+        <v>2.97317459861974</v>
       </c>
       <c r="T2" t="n">
-        <v>0.007608338867642228</v>
+        <v>-0.005365445487747644</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2875215850577266</v>
+        <v>0.03809732083456407</v>
       </c>
       <c r="V2" t="n">
-        <v>1.317802614597143</v>
+        <v>0.1684963370842598</v>
       </c>
       <c r="W2" t="n">
-        <v>7.362826824630407</v>
+        <v>0.8632972961454419</v>
       </c>
       <c r="X2" t="n">
-        <v>0.00243</v>
+        <v>0.00013</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.79989</v>
+        <v>0.155</v>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>2026-08-22T00:21:04.075142+00:00</t>
+          <t>2026-08-22T01:53:26.879198+00:00</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
@@ -3597,12 +3606,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>MU</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Taiwan Semiconductor Manufacturing Company Limited</t>
+          <t>Micron Technology, Inc.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -3616,68 +3625,68 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2172873342976</v>
+        <v>1091874717696</v>
       </c>
       <c r="F3" t="n">
-        <v>418.9500122070312</v>
+        <v>966.780029296875</v>
       </c>
       <c r="G3" t="n">
-        <v>4440492343296</v>
+        <v>90273996800</v>
       </c>
       <c r="H3" t="n">
-        <v>0.36</v>
+        <v>3.457</v>
       </c>
       <c r="I3" t="n">
-        <v>13.4</v>
+        <v>44.23</v>
       </c>
       <c r="J3" t="n">
-        <v>0.774</v>
+        <v>13.685</v>
       </c>
       <c r="K3" t="n">
-        <v>730826014720</v>
+        <v>7639499776</v>
       </c>
       <c r="M3" t="n">
-        <v>3518010228736</v>
+        <v>26022000640</v>
       </c>
       <c r="N3" t="n">
-        <v>1068558516224</v>
+        <v>6376000000</v>
       </c>
       <c r="O3" t="n">
-        <v>0.6423</v>
+        <v>0.7256899999999999</v>
       </c>
       <c r="P3" t="n">
-        <v>0.60344005</v>
+        <v>0.80370003</v>
       </c>
       <c r="Q3" t="n">
-        <v>31.264927</v>
+        <v>21.858015</v>
       </c>
       <c r="R3" t="n">
-        <v>0.48933163</v>
+        <v>12.0951185</v>
       </c>
       <c r="S3" t="n">
-        <v>2.97317459861974</v>
+        <v>142.924896879531</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.005365445487747644</v>
+        <v>0.007608338867642228</v>
       </c>
       <c r="U3" t="n">
-        <v>0.03809732083456407</v>
+        <v>0.2875215850577266</v>
       </c>
       <c r="V3" t="n">
-        <v>0.1684963370842598</v>
+        <v>1.317802614597143</v>
       </c>
       <c r="W3" t="n">
-        <v>0.8632971696944793</v>
+        <v>7.362827376540883</v>
       </c>
       <c r="X3" t="n">
-        <v>0.00013</v>
+        <v>0.00243</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.155</v>
+        <v>0.79989</v>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>2026-08-22T00:21:10.763980+00:00</t>
+          <t>2026-08-22T01:53:19.227481+00:00</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
@@ -3720,7 +3729,7 @@
         <v>1.57</v>
       </c>
       <c r="I4" t="n">
-        <v>2.5</v>
+        <v>2.49</v>
       </c>
       <c r="J4" t="n">
         <v>3.432</v>
@@ -3741,7 +3750,7 @@
         <v>0.35661998</v>
       </c>
       <c r="Q4" t="n">
-        <v>92.228004</v>
+        <v>92.5984</v>
       </c>
       <c r="R4" t="n">
         <v>32.2041</v>
@@ -3769,7 +3778,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>2026-08-22T00:21:05.194232+00:00</t>
+          <t>2026-08-22T01:53:20.671246+00:00</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
@@ -3812,7 +3821,7 @@
         <v>0.377</v>
       </c>
       <c r="I5" t="n">
-        <v>3.16</v>
+        <v>3.24</v>
       </c>
       <c r="J5" t="n">
         <v>0.357</v>
@@ -3833,7 +3842,7 @@
         <v>0.45393002</v>
       </c>
       <c r="Q5" t="n">
-        <v>59.699364</v>
+        <v>58.225307</v>
       </c>
       <c r="R5" t="n">
         <v>22.572294</v>
@@ -3861,7 +3870,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>2026-08-22T00:21:13.253617+00:00</t>
+          <t>2026-08-22T01:53:30.555881+00:00</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
@@ -3904,7 +3913,7 @@
         <v>0.928</v>
       </c>
       <c r="I6" t="n">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="J6" t="n">
         <v>2.154</v>
@@ -3925,7 +3934,7 @@
         <v>0.47120997</v>
       </c>
       <c r="Q6" t="n">
-        <v>153.79488</v>
+        <v>148.71074</v>
       </c>
       <c r="R6" t="n">
         <v>70.24212</v>
@@ -3953,7 +3962,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>2026-08-22T00:21:01.534381+00:00</t>
+          <t>2026-08-22T01:53:15.596545+00:00</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr">
@@ -3996,7 +4005,7 @@
         <v>1.039</v>
       </c>
       <c r="I7" t="n">
-        <v>7.28</v>
+        <v>7.14</v>
       </c>
       <c r="J7" t="n">
         <v>3.858</v>
@@ -4017,7 +4026,7 @@
         <v>0.33161</v>
       </c>
       <c r="Q7" t="n">
-        <v>51.612633</v>
+        <v>52.62465</v>
       </c>
       <c r="R7" t="n">
         <v>13.159287</v>
@@ -4035,7 +4044,7 @@
         <v>0.1898762435729664</v>
       </c>
       <c r="W7" t="n">
-        <v>2.446494647256825</v>
+        <v>2.446494406067634</v>
       </c>
       <c r="X7" t="n">
         <v>0.00202</v>
@@ -4045,7 +4054,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>2026-08-22T00:21:05.798638+00:00</t>
+          <t>2026-08-22T01:53:21.315292+00:00</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr">
@@ -4137,7 +4146,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>2026-08-22T00:21:13.873489+00:00</t>
+          <t>2026-08-22T01:53:31.303419+00:00</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr">
@@ -4219,7 +4228,7 @@
         <v>0.144129303232654</v>
       </c>
       <c r="W9" t="n">
-        <v>0.2287460719461247</v>
+        <v>0.2287461792392489</v>
       </c>
       <c r="X9" t="n">
         <v>0.03991</v>
@@ -4229,7 +4238,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>2026-08-22T00:21:00.977695+00:00</t>
+          <t>2026-08-22T01:53:14.711548+00:00</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr">
@@ -4318,7 +4327,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>2026-08-22T00:21:18.824707+00:00</t>
+          <t>2026-08-22T01:53:38.699827+00:00</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr">
@@ -4361,7 +4370,7 @@
         <v>0.501</v>
       </c>
       <c r="I11" t="n">
-        <v>3.94</v>
+        <v>3.98</v>
       </c>
       <c r="J11" t="n">
         <v>1.595</v>
@@ -4382,7 +4391,7 @@
         <v>0.1725</v>
       </c>
       <c r="Q11" t="n">
-        <v>120.11421</v>
+        <v>118.907036</v>
       </c>
       <c r="R11" t="n">
         <v>18.704</v>
@@ -4410,7 +4419,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>2026-08-22T00:21:02.096565+00:00</t>
+          <t>2026-08-22T01:53:16.403972+00:00</t>
         </is>
       </c>
       <c r="AD11" t="inlineStr">
@@ -4492,7 +4501,7 @@
         <v>0.1400655521483041</v>
       </c>
       <c r="W12" t="n">
-        <v>0.7311824950356518</v>
+        <v>0.731182362414351</v>
       </c>
       <c r="X12" t="n">
         <v>0.01596</v>
@@ -4502,7 +4511,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>2026-08-22T00:21:08.181398+00:00</t>
+          <t>2026-08-22T01:53:23.947831+00:00</t>
         </is>
       </c>
       <c r="AD12" t="inlineStr">
@@ -4584,7 +4593,7 @@
         <v>0.3342865245955684</v>
       </c>
       <c r="W13" t="n">
-        <v>2.097116106946919</v>
+        <v>2.097116404241915</v>
       </c>
       <c r="X13" t="n">
         <v>0.00331</v>
@@ -4594,7 +4603,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>2026-08-22T00:21:03.400143+00:00</t>
+          <t>2026-08-22T01:53:18.234976+00:00</t>
         </is>
       </c>
       <c r="AD13" t="inlineStr">
@@ -4637,7 +4646,7 @@
         <v>0.356</v>
       </c>
       <c r="I14" t="n">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="J14" t="n">
         <v>14.985</v>
@@ -4658,7 +4667,7 @@
         <v>0.00666</v>
       </c>
       <c r="Q14" t="n">
-        <v>462</v>
+        <v>453.1154</v>
       </c>
       <c r="R14" t="n">
         <v>21.328741</v>
@@ -4686,7 +4695,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>2026-08-22T00:21:16.396404+00:00</t>
+          <t>2026-08-22T01:53:34.535792+00:00</t>
         </is>
       </c>
       <c r="AD14" t="inlineStr">
@@ -4729,7 +4738,7 @@
         <v>0.479</v>
       </c>
       <c r="I15" t="n">
-        <v>6.01</v>
+        <v>6.08</v>
       </c>
       <c r="J15" t="n">
         <v>0.854</v>
@@ -4750,7 +4759,7 @@
         <v>0.48988</v>
       </c>
       <c r="Q15" t="n">
-        <v>61.306156</v>
+        <v>60.60033</v>
       </c>
       <c r="R15" t="n">
         <v>23.22839</v>
@@ -4765,7 +4774,7 @@
         <v>-0.1089169343844046</v>
       </c>
       <c r="V15" t="n">
-        <v>0.1072406716938052</v>
+        <v>0.1072405701495147</v>
       </c>
       <c r="W15" t="n">
         <v>0.2815942361128876</v>
@@ -4778,7 +4787,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>2026-08-22T00:21:02.710452+00:00</t>
+          <t>2026-08-22T01:53:17.275059+00:00</t>
         </is>
       </c>
       <c r="AD15" t="inlineStr">
@@ -4864,7 +4873,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>2026-08-22T00:21:15.802810+00:00</t>
+          <t>2026-08-22T01:53:33.581729+00:00</t>
         </is>
       </c>
       <c r="AD16" t="inlineStr">
@@ -4956,7 +4965,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>2026-08-22T00:21:08.903136+00:00</t>
+          <t>2026-08-22T01:53:24.330842+00:00</t>
         </is>
       </c>
       <c r="AD17" t="inlineStr">
@@ -4973,7 +4982,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>MongoDB, Inc. Class A Common Stock</t>
+          <t>MongoDB, Inc.</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -5042,7 +5051,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>2026-08-22T00:21:18.242316+00:00</t>
+          <t>2026-08-22T01:53:37.699969+00:00</t>
         </is>
       </c>
       <c r="AD18" t="inlineStr">
@@ -5128,7 +5137,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>2026-08-22T00:21:17.008833+00:00</t>
+          <t>2026-08-22T01:53:35.482358+00:00</t>
         </is>
       </c>
       <c r="AD19" t="inlineStr">
@@ -5145,7 +5154,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>ACM Research, Inc. Class A Common Stock</t>
+          <t>ACM Research, Inc.</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -5171,7 +5180,7 @@
         <v>0.36</v>
       </c>
       <c r="I20" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="J20" t="n">
         <v>1.806</v>
@@ -5192,7 +5201,7 @@
         <v>0.16982001</v>
       </c>
       <c r="Q20" t="n">
-        <v>37.45755</v>
+        <v>37.107475</v>
       </c>
       <c r="R20" t="n">
         <v>5.329536</v>
@@ -5217,7 +5226,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>2026-08-22T00:21:04.613522+00:00</t>
+          <t>2026-08-22T01:53:20.063957+00:00</t>
         </is>
       </c>
       <c r="AD20" t="inlineStr">
@@ -5309,7 +5318,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>2026-08-22T00:21:14.515160+00:00</t>
+          <t>2026-08-22T01:53:31.988027+00:00</t>
         </is>
       </c>
       <c r="AD21" t="inlineStr">
@@ -5401,7 +5410,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>2026-08-22T00:21:11.443345+00:00</t>
+          <t>2026-08-22T01:53:27.631839+00:00</t>
         </is>
       </c>
       <c r="AD22" t="inlineStr">
@@ -5490,7 +5499,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>2026-08-22T00:21:15.196451+00:00</t>
+          <t>2026-08-22T01:53:32.771618+00:00</t>
         </is>
       </c>
       <c r="AD23" t="inlineStr">
@@ -5533,7 +5542,7 @@
         <v>0.177</v>
       </c>
       <c r="I24" t="n">
-        <v>17.95</v>
+        <v>18.02</v>
       </c>
       <c r="J24" t="n">
         <v>0.317</v>
@@ -5554,7 +5563,7 @@
         <v>0.45111</v>
       </c>
       <c r="Q24" t="n">
-        <v>26.921446</v>
+        <v>26.81687</v>
       </c>
       <c r="R24" t="n">
         <v>10.813438</v>
@@ -5582,7 +5591,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>2026-08-22T00:21:07.555990+00:00</t>
+          <t>2026-08-22T01:53:23.183402+00:00</t>
         </is>
       </c>
       <c r="AD24" t="inlineStr">
@@ -5671,7 +5680,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>2026-08-22T00:21:06.945375+00:00</t>
+          <t>2026-08-22T01:53:22.351936+00:00</t>
         </is>
       </c>
       <c r="AD25" t="inlineStr">
@@ -5763,7 +5772,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>2026-08-22T00:21:11.995875+00:00</t>
+          <t>2026-08-22T01:53:28.756466+00:00</t>
         </is>
       </c>
       <c r="AD26" t="inlineStr">
@@ -5849,7 +5858,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>2026-08-22T00:21:06.372514+00:00</t>
+          <t>2026-08-22T01:53:21.832209+00:00</t>
         </is>
       </c>
       <c r="AD27" t="inlineStr">
@@ -5931,7 +5940,7 @@
         <v>-0.1456296261876776</v>
       </c>
       <c r="W28" t="n">
-        <v>-0.253548447765114</v>
+        <v>-0.2535483859208238</v>
       </c>
       <c r="X28" t="n">
         <v>0.00148</v>
@@ -5941,7 +5950,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>2026-08-22T00:21:09.467259+00:00</t>
+          <t>2026-08-22T01:53:25.278066+00:00</t>
         </is>
       </c>
       <c r="AD28" t="inlineStr">
@@ -6033,7 +6042,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>2026-08-22T00:21:12.703551+00:00</t>
+          <t>2026-08-22T01:53:29.696687+00:00</t>
         </is>
       </c>
       <c r="AD29" t="inlineStr">
@@ -6076,7 +6085,7 @@
         <v>0.24</v>
       </c>
       <c r="I30" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="J30" t="n">
         <v>-0.219</v>
@@ -6097,7 +6106,7 @@
         <v>0.04063</v>
       </c>
       <c r="Q30" t="n">
-        <v>80.299995</v>
+        <v>81.31645</v>
       </c>
       <c r="R30" t="n">
         <v>9.016465999999999</v>
@@ -6125,7 +6134,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>2026-08-22T00:21:17.551468+00:00</t>
+          <t>2026-08-22T01:53:36.630899+00:00</t>
         </is>
       </c>
       <c r="AD30" t="inlineStr">
@@ -6204,7 +6213,7 @@
         <v>-0.05779410309686361</v>
       </c>
       <c r="W31" t="n">
-        <v>-0.3646448121864612</v>
+        <v>-0.3646447701327261</v>
       </c>
       <c r="X31" t="n">
         <v>0.40498</v>
@@ -6214,7 +6223,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>2026-08-22T00:21:10.135137+00:00</t>
+          <t>2026-08-22T01:53:26.086204+00:00</t>
         </is>
       </c>
       <c r="AD31" t="inlineStr">
@@ -6242,7 +6251,7 @@
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
@@ -6299,27 +6308,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>MU</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>84.2</v>
+        <v>100</v>
       </c>
       <c r="C2" t="n">
-        <v>88.2</v>
+        <v>100</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>MODERATE</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>price_to_sales, price_to_fcf</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -6333,11 +6337,11 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>MU</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="C3" t="n">
         <v>100</v>
@@ -6348,7 +6352,7 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -7285,11 +7289,11 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>MU</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>57.27</v>
+        <v>55.66</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -7302,7 +7306,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>84.2</v>
+        <v>100</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>

--- a/reports/investment_dashboard.xlsx
+++ b/reports/investment_dashboard.xlsx
@@ -525,16 +525,16 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>MU</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Taiwan Semiconductor Manufacturing Company Limited</t>
+          <t>Micron Technology, Inc.</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>55.66</v>
+        <v>57.27</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>418.9500122070312</v>
+        <v>966.780029296875</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -550,19 +550,24 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>100</v>
+        <v>84.2</v>
       </c>
       <c r="I2" t="n">
-        <v>100</v>
+        <v>88.2</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Revenue Growth; Earnings Fcf; Balance Sheet; Valuation</t>
+          <t>Revenue Growth; Earnings Fcf; Balance Sheet</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
           <t>Industry Growth; Competitive Advantage; Catalysts; Inflation Resilience</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>High market sensitivity / beta</t>
         </is>
       </c>
     </row>
@@ -572,16 +577,16 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>MU</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Micron Technology, Inc.</t>
+          <t>Taiwan Semiconductor Manufacturing Company Limited</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>55.05</v>
+        <v>55.66</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -589,7 +594,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>966.780029296875</v>
+        <v>418.9500122070312</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -597,24 +602,19 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="I3" t="n">
         <v>100</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Revenue Growth; Earnings Fcf; Balance Sheet</t>
+          <t>Revenue Growth; Earnings Fcf; Balance Sheet; Valuation</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
           <t>Industry Growth; Competitive Advantage; Catalysts; Inflation Resilience</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>High market sensitivity / beta</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>MongoDB, Inc.</t>
+          <t>MongoDB, Inc. Class A Common Stock</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1426,7 +1426,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>ACM Research, Inc.</t>
+          <t>ACM Research, Inc. Class A Common Stock</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -2115,7 +2115,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>MU</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -2128,19 +2128,19 @@
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>8.84</v>
+        <v>9.02</v>
       </c>
       <c r="F2" t="n">
-        <v>8.67</v>
+        <v>7.04</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>5.46</v>
+        <v>7.71</v>
       </c>
       <c r="I2" t="n">
-        <v>2.69</v>
+        <v>3.5</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -2149,13 +2149,13 @@
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>55.66</v>
+        <v>57.27</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>MU</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -2168,19 +2168,19 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>9.02</v>
+        <v>8.84</v>
       </c>
       <c r="F3" t="n">
-        <v>4.82</v>
+        <v>8.67</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>7.71</v>
+        <v>5.46</v>
       </c>
       <c r="I3" t="n">
-        <v>3.5</v>
+        <v>2.69</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -2189,7 +2189,7 @@
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>55.05</v>
+        <v>55.66</v>
       </c>
     </row>
     <row r="4">
@@ -3514,12 +3514,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>MU</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Taiwan Semiconductor Manufacturing Company Limited</t>
+          <t>Micron Technology, Inc.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -3532,69 +3532,60 @@
           <t>Semiconductors</t>
         </is>
       </c>
-      <c r="E2" t="n">
-        <v>2172873342976</v>
-      </c>
       <c r="F2" t="n">
-        <v>418.9500122070312</v>
+        <v>966.780029296875</v>
       </c>
       <c r="G2" t="n">
-        <v>4440492343296</v>
+        <v>90273996800</v>
       </c>
       <c r="H2" t="n">
-        <v>0.36</v>
+        <v>3.457</v>
       </c>
       <c r="I2" t="n">
-        <v>13.4</v>
+        <v>44.23</v>
       </c>
       <c r="J2" t="n">
-        <v>0.774</v>
+        <v>13.685</v>
       </c>
       <c r="K2" t="n">
-        <v>730826014720</v>
+        <v>7639499776</v>
       </c>
       <c r="M2" t="n">
-        <v>3518010228736</v>
+        <v>26022000640</v>
       </c>
       <c r="N2" t="n">
-        <v>1068558516224</v>
+        <v>6376000000</v>
       </c>
       <c r="O2" t="n">
-        <v>0.6423</v>
+        <v>0.7256899999999999</v>
       </c>
       <c r="P2" t="n">
-        <v>0.60344005</v>
+        <v>0.80370003</v>
       </c>
       <c r="Q2" t="n">
-        <v>31.264927</v>
-      </c>
-      <c r="R2" t="n">
-        <v>0.48933163</v>
-      </c>
-      <c r="S2" t="n">
-        <v>2.97317459861974</v>
+        <v>21.858015</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.005365445487747644</v>
+        <v>0.007608338867642228</v>
       </c>
       <c r="U2" t="n">
-        <v>0.03809732083456407</v>
+        <v>0.2875215850577266</v>
       </c>
       <c r="V2" t="n">
-        <v>0.1684963370842598</v>
+        <v>1.317802614597143</v>
       </c>
       <c r="W2" t="n">
-        <v>0.8632972961454419</v>
+        <v>7.362826824630407</v>
       </c>
       <c r="X2" t="n">
-        <v>0.00013</v>
+        <v>0.00243</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.155</v>
+        <v>0.79989</v>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>2026-08-22T01:53:26.879198+00:00</t>
+          <t>2026-08-22T01:55:30.546663+00:00</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
@@ -3606,12 +3597,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>MU</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Micron Technology, Inc.</t>
+          <t>Taiwan Semiconductor Manufacturing Company Limited</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -3625,68 +3616,68 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1091874717696</v>
+        <v>2172873342976</v>
       </c>
       <c r="F3" t="n">
-        <v>966.780029296875</v>
+        <v>418.9500122070312</v>
       </c>
       <c r="G3" t="n">
-        <v>90273996800</v>
+        <v>4440492343296</v>
       </c>
       <c r="H3" t="n">
-        <v>3.457</v>
+        <v>0.36</v>
       </c>
       <c r="I3" t="n">
-        <v>44.23</v>
+        <v>13.4</v>
       </c>
       <c r="J3" t="n">
-        <v>13.685</v>
+        <v>0.774</v>
       </c>
       <c r="K3" t="n">
-        <v>7639499776</v>
+        <v>730826014720</v>
       </c>
       <c r="M3" t="n">
-        <v>26022000640</v>
+        <v>3518010228736</v>
       </c>
       <c r="N3" t="n">
-        <v>6376000000</v>
+        <v>1068558516224</v>
       </c>
       <c r="O3" t="n">
-        <v>0.7256899999999999</v>
+        <v>0.6423</v>
       </c>
       <c r="P3" t="n">
-        <v>0.80370003</v>
+        <v>0.60344005</v>
       </c>
       <c r="Q3" t="n">
-        <v>21.858015</v>
+        <v>31.264927</v>
       </c>
       <c r="R3" t="n">
-        <v>12.0951185</v>
+        <v>0.48933163</v>
       </c>
       <c r="S3" t="n">
-        <v>142.924896879531</v>
+        <v>2.97317459861974</v>
       </c>
       <c r="T3" t="n">
-        <v>0.007608338867642228</v>
+        <v>-0.005365445487747644</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2875215850577266</v>
+        <v>0.03809732083456407</v>
       </c>
       <c r="V3" t="n">
-        <v>1.317802614597143</v>
+        <v>0.1684963370842598</v>
       </c>
       <c r="W3" t="n">
-        <v>7.362827376540883</v>
+        <v>0.8632972961454419</v>
       </c>
       <c r="X3" t="n">
-        <v>0.00243</v>
+        <v>0.00013</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.79989</v>
+        <v>0.155</v>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>2026-08-22T01:53:19.227481+00:00</t>
+          <t>2026-08-22T01:55:37.579631+00:00</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
@@ -3778,7 +3769,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>2026-08-22T01:53:20.671246+00:00</t>
+          <t>2026-08-22T01:55:31.630454+00:00</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
@@ -3870,7 +3861,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>2026-08-22T01:53:30.555881+00:00</t>
+          <t>2026-08-22T01:55:40.131293+00:00</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
@@ -3962,7 +3953,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>2026-08-22T01:53:15.596545+00:00</t>
+          <t>2026-08-22T01:55:27.969972+00:00</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr">
@@ -4054,7 +4045,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>2026-08-22T01:53:21.315292+00:00</t>
+          <t>2026-08-22T01:55:32.228498+00:00</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr">
@@ -4146,7 +4137,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>2026-08-22T01:53:31.303419+00:00</t>
+          <t>2026-08-22T01:55:40.801803+00:00</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr">
@@ -4238,7 +4229,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>2026-08-22T01:53:14.711548+00:00</t>
+          <t>2026-08-22T01:55:27.434170+00:00</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr">
@@ -4327,7 +4318,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>2026-08-22T01:53:38.699827+00:00</t>
+          <t>2026-08-22T01:55:45.491511+00:00</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr">
@@ -4419,7 +4410,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>2026-08-22T01:53:16.403972+00:00</t>
+          <t>2026-08-22T01:55:28.690883+00:00</t>
         </is>
       </c>
       <c r="AD11" t="inlineStr">
@@ -4501,7 +4492,7 @@
         <v>0.1400655521483041</v>
       </c>
       <c r="W12" t="n">
-        <v>0.731182362414351</v>
+        <v>0.7311824950356518</v>
       </c>
       <c r="X12" t="n">
         <v>0.01596</v>
@@ -4511,7 +4502,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>2026-08-22T01:53:23.947831+00:00</t>
+          <t>2026-08-22T01:55:34.994696+00:00</t>
         </is>
       </c>
       <c r="AD12" t="inlineStr">
@@ -4593,7 +4584,7 @@
         <v>0.3342865245955684</v>
       </c>
       <c r="W13" t="n">
-        <v>2.097116404241915</v>
+        <v>2.097116106946919</v>
       </c>
       <c r="X13" t="n">
         <v>0.00331</v>
@@ -4603,7 +4594,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>2026-08-22T01:53:18.234976+00:00</t>
+          <t>2026-08-22T01:55:29.907213+00:00</t>
         </is>
       </c>
       <c r="AD13" t="inlineStr">
@@ -4695,7 +4686,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>2026-08-22T01:53:34.535792+00:00</t>
+          <t>2026-08-22T01:55:43.292697+00:00</t>
         </is>
       </c>
       <c r="AD14" t="inlineStr">
@@ -4774,10 +4765,10 @@
         <v>-0.1089169343844046</v>
       </c>
       <c r="V15" t="n">
-        <v>0.1072405701495147</v>
+        <v>0.1072406716938052</v>
       </c>
       <c r="W15" t="n">
-        <v>0.2815942361128876</v>
+        <v>0.2815941000710358</v>
       </c>
       <c r="X15" t="n">
         <v>0.01948</v>
@@ -4787,7 +4778,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>2026-08-22T01:53:17.275059+00:00</t>
+          <t>2026-08-22T01:55:29.288749+00:00</t>
         </is>
       </c>
       <c r="AD15" t="inlineStr">
@@ -4873,7 +4864,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>2026-08-22T01:53:33.581729+00:00</t>
+          <t>2026-08-22T01:55:42.781069+00:00</t>
         </is>
       </c>
       <c r="AD16" t="inlineStr">
@@ -4965,7 +4956,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>2026-08-22T01:53:24.330842+00:00</t>
+          <t>2026-08-22T01:55:35.667747+00:00</t>
         </is>
       </c>
       <c r="AD17" t="inlineStr">
@@ -4982,7 +4973,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>MongoDB, Inc.</t>
+          <t>MongoDB, Inc. Class A Common Stock</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -5051,7 +5042,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>2026-08-22T01:53:37.699969+00:00</t>
+          <t>2026-08-22T01:55:44.953565+00:00</t>
         </is>
       </c>
       <c r="AD18" t="inlineStr">
@@ -5137,7 +5128,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>2026-08-22T01:53:35.482358+00:00</t>
+          <t>2026-08-22T01:55:43.875257+00:00</t>
         </is>
       </c>
       <c r="AD19" t="inlineStr">
@@ -5154,7 +5145,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>ACM Research, Inc.</t>
+          <t>ACM Research, Inc. Class A Common Stock</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -5226,7 +5217,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>2026-08-22T01:53:20.063957+00:00</t>
+          <t>2026-08-22T01:55:31.101925+00:00</t>
         </is>
       </c>
       <c r="AD20" t="inlineStr">
@@ -5308,7 +5299,7 @@
         <v>0.07819827777494104</v>
       </c>
       <c r="W21" t="n">
-        <v>1.071721934408579</v>
+        <v>1.071721809401515</v>
       </c>
       <c r="X21" t="n">
         <v>0.00269</v>
@@ -5318,7 +5309,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>2026-08-22T01:53:31.988027+00:00</t>
+          <t>2026-08-22T01:55:41.450937+00:00</t>
         </is>
       </c>
       <c r="AD21" t="inlineStr">
@@ -5400,7 +5391,7 @@
         <v>0.2131482647002914</v>
       </c>
       <c r="W22" t="n">
-        <v>1.414165201818253</v>
+        <v>1.414165403503707</v>
       </c>
       <c r="X22" t="n">
         <v>0.00016000001</v>
@@ -5410,7 +5401,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>2026-08-22T01:53:27.631839+00:00</t>
+          <t>2026-08-22T01:55:38.398667+00:00</t>
         </is>
       </c>
       <c r="AD22" t="inlineStr">
@@ -5499,7 +5490,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>2026-08-22T01:53:32.771618+00:00</t>
+          <t>2026-08-22T01:55:42.119808+00:00</t>
         </is>
       </c>
       <c r="AD23" t="inlineStr">
@@ -5591,7 +5582,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>2026-08-22T01:53:23.183402+00:00</t>
+          <t>2026-08-22T01:55:34.296088+00:00</t>
         </is>
       </c>
       <c r="AD24" t="inlineStr">
@@ -5680,7 +5671,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>2026-08-22T01:53:22.351936+00:00</t>
+          <t>2026-08-22T01:55:33.418108+00:00</t>
         </is>
       </c>
       <c r="AD25" t="inlineStr">
@@ -5772,7 +5763,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>2026-08-22T01:53:28.756466+00:00</t>
+          <t>2026-08-22T01:55:38.984220+00:00</t>
         </is>
       </c>
       <c r="AD26" t="inlineStr">
@@ -5858,7 +5849,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>2026-08-22T01:53:21.832209+00:00</t>
+          <t>2026-08-22T01:55:32.817977+00:00</t>
         </is>
       </c>
       <c r="AD27" t="inlineStr">
@@ -5950,7 +5941,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>2026-08-22T01:53:25.278066+00:00</t>
+          <t>2026-08-22T01:55:36.388843+00:00</t>
         </is>
       </c>
       <c r="AD28" t="inlineStr">
@@ -6032,7 +6023,7 @@
         <v>1.979740667578479</v>
       </c>
       <c r="W29" t="n">
-        <v>2.335838148861586</v>
+        <v>2.335837790700546</v>
       </c>
       <c r="X29" t="n">
         <v>0.00494</v>
@@ -6042,7 +6033,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>2026-08-22T01:53:29.696687+00:00</t>
+          <t>2026-08-22T01:55:39.574602+00:00</t>
         </is>
       </c>
       <c r="AD29" t="inlineStr">
@@ -6134,7 +6125,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>2026-08-22T01:53:36.630899+00:00</t>
+          <t>2026-08-22T01:55:44.421940+00:00</t>
         </is>
       </c>
       <c r="AD30" t="inlineStr">
@@ -6213,7 +6204,7 @@
         <v>-0.05779410309686361</v>
       </c>
       <c r="W31" t="n">
-        <v>-0.3646447701327261</v>
+        <v>-0.3646448121864612</v>
       </c>
       <c r="X31" t="n">
         <v>0.40498</v>
@@ -6223,7 +6214,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>2026-08-22T01:53:26.086204+00:00</t>
+          <t>2026-08-22T01:55:36.982692+00:00</t>
         </is>
       </c>
       <c r="AD31" t="inlineStr">
@@ -6251,7 +6242,7 @@
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
@@ -6308,22 +6299,27 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>MU</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>100</v>
+        <v>84.2</v>
       </c>
       <c r="C2" t="n">
-        <v>100</v>
+        <v>88.2</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MODERATE</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>price_to_sales, price_to_fcf</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -6337,11 +6333,11 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>MU</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="C3" t="n">
         <v>100</v>
@@ -6352,7 +6348,7 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -7289,11 +7285,11 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>MU</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>55.66</v>
+        <v>57.27</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -7306,7 +7302,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>100</v>
+        <v>84.2</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>

--- a/reports/investment_dashboard.xlsx
+++ b/reports/investment_dashboard.xlsx
@@ -586,7 +586,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>55.66</v>
+        <v>55.67</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -883,7 +883,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>50.09</v>
+        <v>50.06</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>48.25</v>
+        <v>48.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>45.8</v>
+        <v>45.78</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -1775,16 +1775,16 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>CRWD</t>
+          <t>META</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>CrowdStrike Holdings, Inc.</t>
+          <t>Meta Platforms, Inc.</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>39.29</v>
+        <v>39.3</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -1792,7 +1792,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>191.9499969482422</v>
+        <v>549.9000244140625</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1800,24 +1800,19 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>88.2</v>
+        <v>100</v>
       </c>
       <c r="I27" t="n">
-        <v>88.2</v>
+        <v>100</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Balance Sheet</t>
+          <t>Revenue Growth</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>Industry Growth; Valuation; Competitive Advantage; Catalysts; Inflation Resilience</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>Excessive price-to-sales valuation</t>
+          <t>Industry Growth; Competitive Advantage; Momentum; Catalysts; Inflation Resilience</t>
         </is>
       </c>
     </row>
@@ -1827,12 +1822,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>META</t>
+          <t>CRWD</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Meta Platforms, Inc.</t>
+          <t>CrowdStrike Holdings, Inc.</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1844,7 +1839,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>549.9000244140625</v>
+        <v>191.9499969482422</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1852,19 +1847,24 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>100</v>
+        <v>88.2</v>
       </c>
       <c r="I28" t="n">
-        <v>100</v>
+        <v>88.2</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Revenue Growth</t>
+          <t>Balance Sheet</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>Industry Growth; Competitive Advantage; Momentum; Catalysts; Inflation Resilience</t>
+          <t>Industry Growth; Valuation; Competitive Advantage; Catalysts; Inflation Resilience</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>Excessive price-to-sales valuation</t>
         </is>
       </c>
     </row>
@@ -1977,7 +1977,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>30.87</v>
+        <v>30.94</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -2171,7 +2171,7 @@
         <v>8.84</v>
       </c>
       <c r="F3" t="n">
-        <v>8.67</v>
+        <v>8.68</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -2189,7 +2189,7 @@
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>55.66</v>
+        <v>55.67</v>
       </c>
     </row>
     <row r="4">
@@ -2411,7 +2411,7 @@
         <v>9.029999999999999</v>
       </c>
       <c r="F9" t="n">
-        <v>3.15</v>
+        <v>3.12</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -2429,7 +2429,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>50.09</v>
+        <v>50.06</v>
       </c>
     </row>
     <row r="10">
@@ -2451,7 +2451,7 @@
         <v>9.699999999999999</v>
       </c>
       <c r="F10" t="n">
-        <v>7.12</v>
+        <v>7.17</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -2469,7 +2469,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>48.25</v>
+        <v>48.3</v>
       </c>
     </row>
     <row r="11">
@@ -2571,7 +2571,7 @@
         <v>7.93</v>
       </c>
       <c r="F13" t="n">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -2589,7 +2589,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>45.8</v>
+        <v>45.78</v>
       </c>
     </row>
     <row r="14">
@@ -3115,32 +3115,32 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>CRWD</t>
+          <t>META</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>11.47</v>
+        <v>12.38</v>
       </c>
       <c r="C27" t="n">
-        <v>7.5</v>
+        <v>10</v>
       </c>
       <c r="D27" t="n">
         <v>0</v>
       </c>
       <c r="E27" t="n">
-        <v>9.24</v>
+        <v>7.23</v>
       </c>
       <c r="F27" t="n">
-        <v>0.44</v>
+        <v>5.82</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>7.16</v>
+        <v>0.38</v>
       </c>
       <c r="I27" t="n">
-        <v>3.48</v>
+        <v>3.49</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3149,38 +3149,38 @@
         <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>39.29</v>
+        <v>39.3</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>META</t>
+          <t>CRWD</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>12.38</v>
+        <v>11.47</v>
       </c>
       <c r="C28" t="n">
-        <v>10</v>
+        <v>7.5</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>7.23</v>
+        <v>9.24</v>
       </c>
       <c r="F28" t="n">
-        <v>5.81</v>
+        <v>0.44</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>0.38</v>
+        <v>7.16</v>
       </c>
       <c r="I28" t="n">
-        <v>3.49</v>
+        <v>3.48</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3291,7 +3291,7 @@
         <v>0.8</v>
       </c>
       <c r="F31" t="n">
-        <v>6.5</v>
+        <v>6.57</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -3309,7 +3309,7 @@
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>30.87</v>
+        <v>30.94</v>
       </c>
     </row>
   </sheetData>
@@ -3349,7 +3349,7 @@
     <col width="23" customWidth="1" min="20" max="20"/>
     <col width="23" customWidth="1" min="21" max="21"/>
     <col width="22" customWidth="1" min="22" max="22"/>
-    <col width="22" customWidth="1" min="23" max="23"/>
+    <col width="21" customWidth="1" min="23" max="23"/>
     <col width="18" customWidth="1" min="24" max="24"/>
     <col width="24" customWidth="1" min="25" max="25"/>
     <col width="17" customWidth="1" min="26" max="26"/>
@@ -3585,7 +3585,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>2026-08-22T01:55:30.546663+00:00</t>
+          <t>2026-08-22T03:04:50.376213+00:00</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
@@ -3628,7 +3628,7 @@
         <v>0.36</v>
       </c>
       <c r="I3" t="n">
-        <v>13.4</v>
+        <v>13.49</v>
       </c>
       <c r="J3" t="n">
         <v>0.774</v>
@@ -3649,7 +3649,7 @@
         <v>0.60344005</v>
       </c>
       <c r="Q3" t="n">
-        <v>31.264927</v>
+        <v>31.05634</v>
       </c>
       <c r="R3" t="n">
         <v>0.48933163</v>
@@ -3677,7 +3677,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>2026-08-22T01:55:37.579631+00:00</t>
+          <t>2026-08-22T03:04:55.466331+00:00</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
@@ -3769,7 +3769,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>2026-08-22T01:55:31.630454+00:00</t>
+          <t>2026-08-22T03:04:51.236273+00:00</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
@@ -3861,7 +3861,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>2026-08-22T01:55:40.131293+00:00</t>
+          <t>2026-08-22T03:04:57.379424+00:00</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
@@ -3953,7 +3953,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>2026-08-22T01:55:27.969972+00:00</t>
+          <t>2026-08-22T03:04:48.453435+00:00</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr">
@@ -4035,7 +4035,7 @@
         <v>0.1898762435729664</v>
       </c>
       <c r="W7" t="n">
-        <v>2.446494406067634</v>
+        <v>2.446494647256825</v>
       </c>
       <c r="X7" t="n">
         <v>0.00202</v>
@@ -4045,7 +4045,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>2026-08-22T01:55:32.228498+00:00</t>
+          <t>2026-08-22T03:04:51.711790+00:00</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr">
@@ -4137,7 +4137,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>2026-08-22T01:55:40.801803+00:00</t>
+          <t>2026-08-22T03:04:57.913429+00:00</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr">
@@ -4180,7 +4180,7 @@
         <v>0.852</v>
       </c>
       <c r="I9" t="n">
-        <v>6.53</v>
+        <v>6.46</v>
       </c>
       <c r="J9" t="n">
         <v>2.145</v>
@@ -4201,7 +4201,7 @@
         <v>0.65596</v>
       </c>
       <c r="Q9" t="n">
-        <v>32.88208</v>
+        <v>33.23839</v>
       </c>
       <c r="R9" t="n">
         <v>20.51644</v>
@@ -4219,7 +4219,7 @@
         <v>0.144129303232654</v>
       </c>
       <c r="W9" t="n">
-        <v>0.2287461792392489</v>
+        <v>0.2287460719461247</v>
       </c>
       <c r="X9" t="n">
         <v>0.03991</v>
@@ -4229,7 +4229,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>2026-08-22T01:55:27.434170+00:00</t>
+          <t>2026-08-22T03:04:48.008883+00:00</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr">
@@ -4272,7 +4272,7 @@
         <v>0.173</v>
       </c>
       <c r="I10" t="n">
-        <v>0.6</v>
+        <v>0.62</v>
       </c>
       <c r="K10" t="n">
         <v>511553632</v>
@@ -4290,7 +4290,7 @@
         <v>0.07274</v>
       </c>
       <c r="Q10" t="n">
-        <v>27.316664</v>
+        <v>26.435482</v>
       </c>
       <c r="R10" t="n">
         <v>5.0779395</v>
@@ -4318,7 +4318,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>2026-08-22T01:55:45.491511+00:00</t>
+          <t>2026-08-22T03:05:01.590514+00:00</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr">
@@ -4410,7 +4410,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>2026-08-22T01:55:28.690883+00:00</t>
+          <t>2026-08-22T03:04:48.908506+00:00</t>
         </is>
       </c>
       <c r="AD11" t="inlineStr">
@@ -4502,7 +4502,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>2026-08-22T01:55:34.994696+00:00</t>
+          <t>2026-08-22T03:04:53.508576+00:00</t>
         </is>
       </c>
       <c r="AD12" t="inlineStr">
@@ -4545,7 +4545,7 @@
         <v>0.248</v>
       </c>
       <c r="I13" t="n">
-        <v>11.61</v>
+        <v>11.52</v>
       </c>
       <c r="J13" t="n">
         <v>0.428</v>
@@ -4566,7 +4566,7 @@
         <v>0.33736</v>
       </c>
       <c r="Q13" t="n">
-        <v>42.404827</v>
+        <v>42.73611</v>
       </c>
       <c r="R13" t="n">
         <v>12.67575</v>
@@ -4584,7 +4584,7 @@
         <v>0.3342865245955684</v>
       </c>
       <c r="W13" t="n">
-        <v>2.097116106946919</v>
+        <v>2.097116404241915</v>
       </c>
       <c r="X13" t="n">
         <v>0.00331</v>
@@ -4594,7 +4594,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>2026-08-22T01:55:29.907213+00:00</t>
+          <t>2026-08-22T03:04:49.893426+00:00</t>
         </is>
       </c>
       <c r="AD13" t="inlineStr">
@@ -4686,7 +4686,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>2026-08-22T01:55:43.292697+00:00</t>
+          <t>2026-08-22T03:04:59.785497+00:00</t>
         </is>
       </c>
       <c r="AD14" t="inlineStr">
@@ -4768,7 +4768,7 @@
         <v>0.1072406716938052</v>
       </c>
       <c r="W15" t="n">
-        <v>0.2815941000710358</v>
+        <v>0.2815942361128876</v>
       </c>
       <c r="X15" t="n">
         <v>0.01948</v>
@@ -4778,7 +4778,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>2026-08-22T01:55:29.288749+00:00</t>
+          <t>2026-08-22T03:04:49.385929+00:00</t>
         </is>
       </c>
       <c r="AD15" t="inlineStr">
@@ -4864,7 +4864,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>2026-08-22T01:55:42.781069+00:00</t>
+          <t>2026-08-22T03:04:59.316950+00:00</t>
         </is>
       </c>
       <c r="AD16" t="inlineStr">
@@ -4956,7 +4956,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>2026-08-22T01:55:35.667747+00:00</t>
+          <t>2026-08-22T03:04:53.947014+00:00</t>
         </is>
       </c>
       <c r="AD17" t="inlineStr">
@@ -4999,7 +4999,7 @@
         <v>0.252</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.38</v>
+        <v>-0.39</v>
       </c>
       <c r="K18" t="n">
         <v>517605376</v>
@@ -5042,7 +5042,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>2026-08-22T01:55:44.953565+00:00</t>
+          <t>2026-08-22T03:05:01.155223+00:00</t>
         </is>
       </c>
       <c r="AD18" t="inlineStr">
@@ -5128,7 +5128,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>2026-08-22T01:55:43.875257+00:00</t>
+          <t>2026-08-22T03:05:00.284167+00:00</t>
         </is>
       </c>
       <c r="AD19" t="inlineStr">
@@ -5217,7 +5217,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>2026-08-22T01:55:31.101925+00:00</t>
+          <t>2026-08-22T03:04:50.804877+00:00</t>
         </is>
       </c>
       <c r="AD20" t="inlineStr">
@@ -5299,7 +5299,7 @@
         <v>0.07819827777494104</v>
       </c>
       <c r="W21" t="n">
-        <v>1.071721809401515</v>
+        <v>1.071721934408579</v>
       </c>
       <c r="X21" t="n">
         <v>0.00269</v>
@@ -5309,7 +5309,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>2026-08-22T01:55:41.450937+00:00</t>
+          <t>2026-08-22T03:04:58.386499+00:00</t>
         </is>
       </c>
       <c r="AD21" t="inlineStr">
@@ -5401,7 +5401,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>2026-08-22T01:55:38.398667+00:00</t>
+          <t>2026-08-22T03:04:55.956103+00:00</t>
         </is>
       </c>
       <c r="AD22" t="inlineStr">
@@ -5490,7 +5490,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>2026-08-22T01:55:42.119808+00:00</t>
+          <t>2026-08-22T03:04:58.841227+00:00</t>
         </is>
       </c>
       <c r="AD23" t="inlineStr">
@@ -5572,7 +5572,7 @@
         <v>0.2176838288473297</v>
       </c>
       <c r="W24" t="n">
-        <v>-0.03376181497550057</v>
+        <v>-0.0337617560157526</v>
       </c>
       <c r="X24" t="n">
         <v>0.00090000004</v>
@@ -5582,7 +5582,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>2026-08-22T01:55:34.296088+00:00</t>
+          <t>2026-08-22T03:04:53.043803+00:00</t>
         </is>
       </c>
       <c r="AD24" t="inlineStr">
@@ -5671,7 +5671,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>2026-08-22T01:55:33.418108+00:00</t>
+          <t>2026-08-22T03:04:52.563908+00:00</t>
         </is>
       </c>
       <c r="AD25" t="inlineStr">
@@ -5714,7 +5714,7 @@
         <v>0.224</v>
       </c>
       <c r="I26" t="n">
-        <v>0.98</v>
+        <v>0.95</v>
       </c>
       <c r="J26" t="n">
         <v>1.083</v>
@@ -5735,7 +5735,7 @@
         <v>0.07603</v>
       </c>
       <c r="Q26" t="n">
-        <v>248.28572</v>
+        <v>256.1263</v>
       </c>
       <c r="R26" t="n">
         <v>50.40059</v>
@@ -5763,7 +5763,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>2026-08-22T01:55:38.984220+00:00</t>
+          <t>2026-08-22T03:04:56.473920+00:00</t>
         </is>
       </c>
       <c r="AD26" t="inlineStr">
@@ -5775,81 +5775,87 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>CRWD</t>
+          <t>META</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>CrowdStrike Holdings, Inc.</t>
+          <t>Meta Platforms, Inc.</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Software - Infrastructure</t>
+          <t>Internet Content &amp; Information</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>195454861312</v>
+        <v>1400873680896</v>
       </c>
       <c r="F27" t="n">
-        <v>191.9499969482422</v>
+        <v>549.9000244140625</v>
       </c>
       <c r="G27" t="n">
-        <v>5094199808</v>
+        <v>228246994944</v>
       </c>
       <c r="H27" t="n">
-        <v>0.256</v>
+        <v>0.28</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.04</v>
+        <v>26.73</v>
+      </c>
+      <c r="J27" t="n">
+        <v>-0.134</v>
       </c>
       <c r="K27" t="n">
-        <v>1926365056</v>
+        <v>21553625088</v>
       </c>
       <c r="M27" t="n">
-        <v>4552800768</v>
+        <v>90259996672</v>
       </c>
       <c r="N27" t="n">
-        <v>821342976</v>
+        <v>112317997056</v>
       </c>
       <c r="O27" t="n">
-        <v>0.75136</v>
+        <v>0.81747</v>
       </c>
       <c r="P27" t="n">
-        <v>-0.022079999</v>
+        <v>0.34827</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>20.572392</v>
       </c>
       <c r="R27" t="n">
-        <v>38.36812</v>
+        <v>6.137534</v>
       </c>
       <c r="S27" t="n">
-        <v>101.4630434160035</v>
+        <v>64.99480598629961</v>
       </c>
       <c r="T27" t="n">
-        <v>0.01873473523830382</v>
+        <v>-0.1232041720771622</v>
       </c>
       <c r="U27" t="n">
-        <v>0.1572663949066291</v>
+        <v>-0.09807350747934629</v>
       </c>
       <c r="V27" t="n">
-        <v>0.8188277849765093</v>
+        <v>-0.1456296261876776</v>
       </c>
       <c r="W27" t="n">
-        <v>0.8543206113126569</v>
+        <v>-0.2535483859208238</v>
       </c>
       <c r="X27" t="n">
-        <v>0.0147</v>
+        <v>0.00148</v>
       </c>
       <c r="Y27" t="n">
-        <v>0.76635003</v>
+        <v>0.79107004</v>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>2026-08-22T01:55:32.817977+00:00</t>
+          <t>2026-08-22T03:04:54.403651+00:00</t>
         </is>
       </c>
       <c r="AD27" t="inlineStr">
@@ -5861,87 +5867,81 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>META</t>
+          <t>CRWD</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Meta Platforms, Inc.</t>
+          <t>CrowdStrike Holdings, Inc.</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Internet Content &amp; Information</t>
+          <t>Software - Infrastructure</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1400873680896</v>
+        <v>195454861312</v>
       </c>
       <c r="F28" t="n">
-        <v>549.9000244140625</v>
+        <v>191.9499969482422</v>
       </c>
       <c r="G28" t="n">
-        <v>228246994944</v>
+        <v>5094199808</v>
       </c>
       <c r="H28" t="n">
-        <v>0.28</v>
+        <v>0.256</v>
       </c>
       <c r="I28" t="n">
-        <v>26.53</v>
-      </c>
-      <c r="J28" t="n">
-        <v>-0.134</v>
+        <v>-0.04</v>
       </c>
       <c r="K28" t="n">
-        <v>21553625088</v>
+        <v>1926365056</v>
       </c>
       <c r="M28" t="n">
-        <v>90259996672</v>
+        <v>4552800768</v>
       </c>
       <c r="N28" t="n">
-        <v>112317997056</v>
+        <v>821342976</v>
       </c>
       <c r="O28" t="n">
-        <v>0.81747</v>
+        <v>0.75136</v>
       </c>
       <c r="P28" t="n">
-        <v>0.34827</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>20.727478</v>
+        <v>-0.022079999</v>
       </c>
       <c r="R28" t="n">
-        <v>6.137534</v>
+        <v>38.36812</v>
       </c>
       <c r="S28" t="n">
-        <v>64.99480598629961</v>
+        <v>101.4630434160035</v>
       </c>
       <c r="T28" t="n">
-        <v>-0.1232041720771622</v>
+        <v>0.01873473523830382</v>
       </c>
       <c r="U28" t="n">
-        <v>-0.09807350747934629</v>
+        <v>0.1572663949066291</v>
       </c>
       <c r="V28" t="n">
-        <v>-0.1456296261876776</v>
+        <v>0.8188277849765093</v>
       </c>
       <c r="W28" t="n">
-        <v>-0.2535483859208238</v>
+        <v>0.8543206113126569</v>
       </c>
       <c r="X28" t="n">
-        <v>0.00148</v>
+        <v>0.0147</v>
       </c>
       <c r="Y28" t="n">
-        <v>0.79107004</v>
+        <v>0.76635003</v>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>2026-08-22T01:55:36.388843+00:00</t>
+          <t>2026-08-22T03:04:52.146198+00:00</t>
         </is>
       </c>
       <c r="AD28" t="inlineStr">
@@ -6033,7 +6033,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>2026-08-22T01:55:39.574602+00:00</t>
+          <t>2026-08-22T03:04:56.951179+00:00</t>
         </is>
       </c>
       <c r="AD29" t="inlineStr">
@@ -6125,7 +6125,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>2026-08-22T01:55:44.421940+00:00</t>
+          <t>2026-08-22T03:05:00.719477+00:00</t>
         </is>
       </c>
       <c r="AD30" t="inlineStr">
@@ -6168,7 +6168,7 @@
         <v>0.206</v>
       </c>
       <c r="I31" t="n">
-        <v>5.82</v>
+        <v>6.01</v>
       </c>
       <c r="J31" t="n">
         <v>0.219</v>
@@ -6189,7 +6189,7 @@
         <v>0.36202</v>
       </c>
       <c r="Q31" t="n">
-        <v>25.166666</v>
+        <v>24.371048</v>
       </c>
       <c r="R31" t="n">
         <v>6.2636786</v>
@@ -6214,7 +6214,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>2026-08-22T01:55:36.982692+00:00</t>
+          <t>2026-08-22T03:04:54.895466+00:00</t>
         </is>
       </c>
       <c r="AD31" t="inlineStr">
@@ -7064,23 +7064,18 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>CRWD</t>
+          <t>META</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>88.2</v>
+        <v>100</v>
       </c>
       <c r="C27" t="n">
-        <v>88.2</v>
+        <v>100</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
           <t>HIGH</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>eps_growth, pe_ratio</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -7098,18 +7093,23 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>META</t>
+          <t>CRWD</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>100</v>
+        <v>88.2</v>
       </c>
       <c r="C28" t="n">
-        <v>100</v>
+        <v>88.2</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
           <t>HIGH</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>eps_growth, pe_ratio</t>
         </is>
       </c>
       <c r="G28" t="n">

--- a/reports/investment_dashboard.xlsx
+++ b/reports/investment_dashboard.xlsx
@@ -525,16 +525,16 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>MU</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Micron Technology, Inc.</t>
+          <t>Taiwan Semiconductor Manufacturing Company Limited</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>57.27</v>
+        <v>55.67</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>966.780029296875</v>
+        <v>418.9500122070312</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -550,24 +550,19 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>84.2</v>
+        <v>100</v>
       </c>
       <c r="I2" t="n">
-        <v>88.2</v>
+        <v>100</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Revenue Growth; Earnings Fcf; Balance Sheet</t>
+          <t>Revenue Growth; Earnings Fcf; Balance Sheet; Valuation</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
           <t>Industry Growth; Competitive Advantage; Catalysts; Inflation Resilience</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>High market sensitivity / beta</t>
         </is>
       </c>
     </row>
@@ -577,16 +572,16 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>MU</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Taiwan Semiconductor Manufacturing Company Limited</t>
+          <t>Micron Technology, Inc.</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>55.67</v>
+        <v>55.05</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -594,7 +589,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>418.9500122070312</v>
+        <v>966.780029296875</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -602,19 +597,24 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="I3" t="n">
         <v>100</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Revenue Growth; Earnings Fcf; Balance Sheet; Valuation</t>
+          <t>Revenue Growth; Earnings Fcf; Balance Sheet</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
           <t>Industry Growth; Competitive Advantage; Catalysts; Inflation Resilience</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>High market sensitivity / beta</t>
         </is>
       </c>
     </row>
@@ -883,7 +883,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>50.06</v>
+        <v>50.09</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -2115,7 +2115,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>MU</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -2128,19 +2128,19 @@
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>9.02</v>
+        <v>8.84</v>
       </c>
       <c r="F2" t="n">
-        <v>7.04</v>
+        <v>8.68</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>7.71</v>
+        <v>5.46</v>
       </c>
       <c r="I2" t="n">
-        <v>3.5</v>
+        <v>2.69</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -2149,13 +2149,13 @@
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>57.27</v>
+        <v>55.67</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>MU</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -2168,19 +2168,19 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>8.84</v>
+        <v>9.02</v>
       </c>
       <c r="F3" t="n">
-        <v>8.68</v>
+        <v>4.82</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>5.46</v>
+        <v>7.71</v>
       </c>
       <c r="I3" t="n">
-        <v>2.69</v>
+        <v>3.5</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -2189,7 +2189,7 @@
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>55.67</v>
+        <v>55.05</v>
       </c>
     </row>
     <row r="4">
@@ -2411,7 +2411,7 @@
         <v>9.029999999999999</v>
       </c>
       <c r="F9" t="n">
-        <v>3.12</v>
+        <v>3.15</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -2429,7 +2429,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>50.06</v>
+        <v>50.09</v>
       </c>
     </row>
     <row r="10">
@@ -3349,7 +3349,7 @@
     <col width="23" customWidth="1" min="20" max="20"/>
     <col width="23" customWidth="1" min="21" max="21"/>
     <col width="22" customWidth="1" min="22" max="22"/>
-    <col width="21" customWidth="1" min="23" max="23"/>
+    <col width="22" customWidth="1" min="23" max="23"/>
     <col width="18" customWidth="1" min="24" max="24"/>
     <col width="24" customWidth="1" min="25" max="25"/>
     <col width="17" customWidth="1" min="26" max="26"/>
@@ -3514,12 +3514,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>MU</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Micron Technology, Inc.</t>
+          <t>Taiwan Semiconductor Manufacturing Company Limited</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -3532,60 +3532,69 @@
           <t>Semiconductors</t>
         </is>
       </c>
+      <c r="E2" t="n">
+        <v>2172873342976</v>
+      </c>
       <c r="F2" t="n">
-        <v>966.780029296875</v>
+        <v>418.9500122070312</v>
       </c>
       <c r="G2" t="n">
-        <v>90273996800</v>
+        <v>4440492343296</v>
       </c>
       <c r="H2" t="n">
-        <v>3.457</v>
+        <v>0.36</v>
       </c>
       <c r="I2" t="n">
-        <v>44.23</v>
+        <v>13.49</v>
       </c>
       <c r="J2" t="n">
-        <v>13.685</v>
+        <v>0.774</v>
       </c>
       <c r="K2" t="n">
-        <v>7639499776</v>
+        <v>730826014720</v>
       </c>
       <c r="M2" t="n">
-        <v>26022000640</v>
+        <v>3518010228736</v>
       </c>
       <c r="N2" t="n">
-        <v>6376000000</v>
+        <v>1068558516224</v>
       </c>
       <c r="O2" t="n">
-        <v>0.7256899999999999</v>
+        <v>0.6423</v>
       </c>
       <c r="P2" t="n">
-        <v>0.80370003</v>
+        <v>0.60344005</v>
       </c>
       <c r="Q2" t="n">
-        <v>21.858015</v>
+        <v>31.05634</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0.48933163</v>
+      </c>
+      <c r="S2" t="n">
+        <v>2.97317459861974</v>
       </c>
       <c r="T2" t="n">
-        <v>0.007608338867642228</v>
+        <v>-0.005365445487747644</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2875215850577266</v>
+        <v>0.03809732083456407</v>
       </c>
       <c r="V2" t="n">
-        <v>1.317802614597143</v>
+        <v>0.1684963370842598</v>
       </c>
       <c r="W2" t="n">
-        <v>7.362826824630407</v>
+        <v>0.8632971696944793</v>
       </c>
       <c r="X2" t="n">
-        <v>0.00243</v>
+        <v>0.00013</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.79989</v>
+        <v>0.155</v>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>2026-08-22T03:04:50.376213+00:00</t>
+          <t>2026-08-22T03:14:28.746216+00:00</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
@@ -3597,12 +3606,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>MU</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Taiwan Semiconductor Manufacturing Company Limited</t>
+          <t>Micron Technology, Inc.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -3616,68 +3625,68 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2172873342976</v>
+        <v>1091874717696</v>
       </c>
       <c r="F3" t="n">
-        <v>418.9500122070312</v>
+        <v>966.780029296875</v>
       </c>
       <c r="G3" t="n">
-        <v>4440492343296</v>
+        <v>90273996800</v>
       </c>
       <c r="H3" t="n">
-        <v>0.36</v>
+        <v>3.457</v>
       </c>
       <c r="I3" t="n">
-        <v>13.49</v>
+        <v>44.23</v>
       </c>
       <c r="J3" t="n">
-        <v>0.774</v>
+        <v>13.685</v>
       </c>
       <c r="K3" t="n">
-        <v>730826014720</v>
+        <v>7639499776</v>
       </c>
       <c r="M3" t="n">
-        <v>3518010228736</v>
+        <v>26022000640</v>
       </c>
       <c r="N3" t="n">
-        <v>1068558516224</v>
+        <v>6376000000</v>
       </c>
       <c r="O3" t="n">
-        <v>0.6423</v>
+        <v>0.7256899999999999</v>
       </c>
       <c r="P3" t="n">
-        <v>0.60344005</v>
+        <v>0.80370003</v>
       </c>
       <c r="Q3" t="n">
-        <v>31.05634</v>
+        <v>21.858015</v>
       </c>
       <c r="R3" t="n">
-        <v>0.48933163</v>
+        <v>12.0951185</v>
       </c>
       <c r="S3" t="n">
-        <v>2.97317459861974</v>
+        <v>142.924896879531</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.005365445487747644</v>
+        <v>0.007608338867642228</v>
       </c>
       <c r="U3" t="n">
-        <v>0.03809732083456407</v>
+        <v>0.2875215850577266</v>
       </c>
       <c r="V3" t="n">
-        <v>0.1684963370842598</v>
+        <v>1.317802614597143</v>
       </c>
       <c r="W3" t="n">
-        <v>0.8632972961454419</v>
+        <v>7.362826824630407</v>
       </c>
       <c r="X3" t="n">
-        <v>0.00013</v>
+        <v>0.00243</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.155</v>
+        <v>0.79989</v>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>2026-08-22T03:04:55.466331+00:00</t>
+          <t>2026-08-22T03:14:26.573946+00:00</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
@@ -3769,7 +3778,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>2026-08-22T03:04:51.236273+00:00</t>
+          <t>2026-08-22T03:14:26.929380+00:00</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
@@ -3861,7 +3870,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>2026-08-22T03:04:57.379424+00:00</t>
+          <t>2026-08-22T03:14:29.585984+00:00</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
@@ -3953,7 +3962,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>2026-08-22T03:04:48.453435+00:00</t>
+          <t>2026-08-22T03:14:25.630813+00:00</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr">
@@ -4045,7 +4054,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>2026-08-22T03:04:51.711790+00:00</t>
+          <t>2026-08-22T03:14:27.127952+00:00</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr">
@@ -4137,7 +4146,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>2026-08-22T03:04:57.913429+00:00</t>
+          <t>2026-08-22T03:14:29.784099+00:00</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr">
@@ -4180,7 +4189,7 @@
         <v>0.852</v>
       </c>
       <c r="I9" t="n">
-        <v>6.46</v>
+        <v>6.53</v>
       </c>
       <c r="J9" t="n">
         <v>2.145</v>
@@ -4201,7 +4210,7 @@
         <v>0.65596</v>
       </c>
       <c r="Q9" t="n">
-        <v>33.23839</v>
+        <v>32.88208</v>
       </c>
       <c r="R9" t="n">
         <v>20.51644</v>
@@ -4229,7 +4238,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>2026-08-22T03:04:48.008883+00:00</t>
+          <t>2026-08-22T03:14:25.450160+00:00</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr">
@@ -4318,7 +4327,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>2026-08-22T03:05:01.590514+00:00</t>
+          <t>2026-08-22T03:14:31.234763+00:00</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr">
@@ -4410,7 +4419,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>2026-08-22T03:04:48.908506+00:00</t>
+          <t>2026-08-22T03:14:25.812936+00:00</t>
         </is>
       </c>
       <c r="AD11" t="inlineStr">
@@ -4492,7 +4501,7 @@
         <v>0.1400655521483041</v>
       </c>
       <c r="W12" t="n">
-        <v>0.7311824950356518</v>
+        <v>0.731182362414351</v>
       </c>
       <c r="X12" t="n">
         <v>0.01596</v>
@@ -4502,7 +4511,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>2026-08-22T03:04:53.508576+00:00</t>
+          <t>2026-08-22T03:14:27.913224+00:00</t>
         </is>
       </c>
       <c r="AD12" t="inlineStr">
@@ -4584,7 +4593,7 @@
         <v>0.3342865245955684</v>
       </c>
       <c r="W13" t="n">
-        <v>2.097116404241915</v>
+        <v>2.09711580965198</v>
       </c>
       <c r="X13" t="n">
         <v>0.00331</v>
@@ -4594,7 +4603,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>2026-08-22T03:04:49.893426+00:00</t>
+          <t>2026-08-22T03:14:26.302811+00:00</t>
         </is>
       </c>
       <c r="AD13" t="inlineStr">
@@ -4686,7 +4695,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>2026-08-22T03:04:59.785497+00:00</t>
+          <t>2026-08-22T03:14:30.531611+00:00</t>
         </is>
       </c>
       <c r="AD14" t="inlineStr">
@@ -4778,7 +4787,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>2026-08-22T03:04:49.385929+00:00</t>
+          <t>2026-08-22T03:14:26.043247+00:00</t>
         </is>
       </c>
       <c r="AD15" t="inlineStr">
@@ -4864,7 +4873,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>2026-08-22T03:04:59.316950+00:00</t>
+          <t>2026-08-22T03:14:30.349718+00:00</t>
         </is>
       </c>
       <c r="AD16" t="inlineStr">
@@ -4956,7 +4965,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>2026-08-22T03:04:53.947014+00:00</t>
+          <t>2026-08-22T03:14:28.093214+00:00</t>
         </is>
       </c>
       <c r="AD17" t="inlineStr">
@@ -5042,7 +5051,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>2026-08-22T03:05:01.155223+00:00</t>
+          <t>2026-08-22T03:14:31.054273+00:00</t>
         </is>
       </c>
       <c r="AD18" t="inlineStr">
@@ -5128,7 +5137,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>2026-08-22T03:05:00.284167+00:00</t>
+          <t>2026-08-22T03:14:30.704245+00:00</t>
         </is>
       </c>
       <c r="AD19" t="inlineStr">
@@ -5217,7 +5226,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>2026-08-22T03:04:50.804877+00:00</t>
+          <t>2026-08-22T03:14:26.754309+00:00</t>
         </is>
       </c>
       <c r="AD20" t="inlineStr">
@@ -5309,7 +5318,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>2026-08-22T03:04:58.386499+00:00</t>
+          <t>2026-08-22T03:14:29.983721+00:00</t>
         </is>
       </c>
       <c r="AD21" t="inlineStr">
@@ -5401,7 +5410,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>2026-08-22T03:04:55.956103+00:00</t>
+          <t>2026-08-22T03:14:28.994127+00:00</t>
         </is>
       </c>
       <c r="AD22" t="inlineStr">
@@ -5490,7 +5499,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>2026-08-22T03:04:58.841227+00:00</t>
+          <t>2026-08-22T03:14:30.172067+00:00</t>
         </is>
       </c>
       <c r="AD23" t="inlineStr">
@@ -5572,7 +5581,7 @@
         <v>0.2176838288473297</v>
       </c>
       <c r="W24" t="n">
-        <v>-0.0337617560157526</v>
+        <v>-0.03376181497550057</v>
       </c>
       <c r="X24" t="n">
         <v>0.00090000004</v>
@@ -5582,7 +5591,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>2026-08-22T03:04:53.043803+00:00</t>
+          <t>2026-08-22T03:14:27.715414+00:00</t>
         </is>
       </c>
       <c r="AD24" t="inlineStr">
@@ -5671,7 +5680,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>2026-08-22T03:04:52.563908+00:00</t>
+          <t>2026-08-22T03:14:27.484444+00:00</t>
         </is>
       </c>
       <c r="AD25" t="inlineStr">
@@ -5763,7 +5772,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>2026-08-22T03:04:56.473920+00:00</t>
+          <t>2026-08-22T03:14:29.203156+00:00</t>
         </is>
       </c>
       <c r="AD26" t="inlineStr">
@@ -5845,7 +5854,7 @@
         <v>-0.1456296261876776</v>
       </c>
       <c r="W27" t="n">
-        <v>-0.2535483859208238</v>
+        <v>-0.253548447765114</v>
       </c>
       <c r="X27" t="n">
         <v>0.00148</v>
@@ -5855,7 +5864,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>2026-08-22T03:04:54.403651+00:00</t>
+          <t>2026-08-22T03:14:28.288018+00:00</t>
         </is>
       </c>
       <c r="AD27" t="inlineStr">
@@ -5941,7 +5950,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>2026-08-22T03:04:52.146198+00:00</t>
+          <t>2026-08-22T03:14:27.302041+00:00</t>
         </is>
       </c>
       <c r="AD28" t="inlineStr">
@@ -6023,7 +6032,7 @@
         <v>1.979740667578479</v>
       </c>
       <c r="W29" t="n">
-        <v>2.335837790700546</v>
+        <v>2.335838148861586</v>
       </c>
       <c r="X29" t="n">
         <v>0.00494</v>
@@ -6033,7 +6042,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>2026-08-22T03:04:56.951179+00:00</t>
+          <t>2026-08-22T03:14:29.401623+00:00</t>
         </is>
       </c>
       <c r="AD29" t="inlineStr">
@@ -6125,7 +6134,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>2026-08-22T03:05:00.719477+00:00</t>
+          <t>2026-08-22T03:14:30.882803+00:00</t>
         </is>
       </c>
       <c r="AD30" t="inlineStr">
@@ -6204,7 +6213,7 @@
         <v>-0.05779410309686361</v>
       </c>
       <c r="W31" t="n">
-        <v>-0.3646448121864612</v>
+        <v>-0.3646448542401906</v>
       </c>
       <c r="X31" t="n">
         <v>0.40498</v>
@@ -6214,7 +6223,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>2026-08-22T03:04:54.895466+00:00</t>
+          <t>2026-08-22T03:14:28.520889+00:00</t>
         </is>
       </c>
       <c r="AD31" t="inlineStr">
@@ -6242,7 +6251,7 @@
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
@@ -6299,27 +6308,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>MU</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>84.2</v>
+        <v>100</v>
       </c>
       <c r="C2" t="n">
-        <v>88.2</v>
+        <v>100</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>MODERATE</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>price_to_sales, price_to_fcf</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -6333,11 +6337,11 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>MU</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="C3" t="n">
         <v>100</v>
@@ -6348,7 +6352,7 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -7285,11 +7289,11 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>MU</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>57.27</v>
+        <v>55.67</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -7302,7 +7306,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>84.2</v>
+        <v>100</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>

--- a/reports/investment_dashboard.xlsx
+++ b/reports/investment_dashboard.xlsx
@@ -3594,7 +3594,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>2026-08-22T03:14:28.746216+00:00</t>
+          <t>2026-08-22T03:18:17.357579+00:00</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
@@ -3676,7 +3676,7 @@
         <v>1.317802614597143</v>
       </c>
       <c r="W3" t="n">
-        <v>7.362826824630407</v>
+        <v>7.362826272720001</v>
       </c>
       <c r="X3" t="n">
         <v>0.00243</v>
@@ -3686,7 +3686,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>2026-08-22T03:14:26.573946+00:00</t>
+          <t>2026-08-22T03:18:14.083925+00:00</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
@@ -3778,7 +3778,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>2026-08-22T03:14:26.929380+00:00</t>
+          <t>2026-08-22T03:18:14.619724+00:00</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
@@ -3870,7 +3870,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>2026-08-22T03:14:29.585984+00:00</t>
+          <t>2026-08-22T03:18:18.544411+00:00</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
@@ -3962,7 +3962,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>2026-08-22T03:14:25.630813+00:00</t>
+          <t>2026-08-22T03:18:12.810467+00:00</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr">
@@ -4044,7 +4044,7 @@
         <v>0.1898762435729664</v>
       </c>
       <c r="W7" t="n">
-        <v>2.446494647256825</v>
+        <v>2.446494406067634</v>
       </c>
       <c r="X7" t="n">
         <v>0.00202</v>
@@ -4054,7 +4054,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>2026-08-22T03:14:27.127952+00:00</t>
+          <t>2026-08-22T03:18:14.930623+00:00</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>2026-08-22T03:14:29.784099+00:00</t>
+          <t>2026-08-22T03:18:18.811915+00:00</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr">
@@ -4228,7 +4228,7 @@
         <v>0.144129303232654</v>
       </c>
       <c r="W9" t="n">
-        <v>0.2287460719461247</v>
+        <v>0.2287461792392489</v>
       </c>
       <c r="X9" t="n">
         <v>0.03991</v>
@@ -4238,7 +4238,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>2026-08-22T03:14:25.450160+00:00</t>
+          <t>2026-08-22T03:18:12.544404+00:00</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr">
@@ -4327,7 +4327,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>2026-08-22T03:14:31.234763+00:00</t>
+          <t>2026-08-22T03:18:21.166229+00:00</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr">
@@ -4419,7 +4419,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>2026-08-22T03:14:25.812936+00:00</t>
+          <t>2026-08-22T03:18:13.056644+00:00</t>
         </is>
       </c>
       <c r="AD11" t="inlineStr">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>2026-08-22T03:14:27.913224+00:00</t>
+          <t>2026-08-22T03:18:16.069649+00:00</t>
         </is>
       </c>
       <c r="AD12" t="inlineStr">
@@ -4593,7 +4593,7 @@
         <v>0.3342865245955684</v>
       </c>
       <c r="W13" t="n">
-        <v>2.09711580965198</v>
+        <v>2.097116404241915</v>
       </c>
       <c r="X13" t="n">
         <v>0.00331</v>
@@ -4603,7 +4603,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>2026-08-22T03:14:26.302811+00:00</t>
+          <t>2026-08-22T03:18:13.724578+00:00</t>
         </is>
       </c>
       <c r="AD13" t="inlineStr">
@@ -4695,7 +4695,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>2026-08-22T03:14:30.531611+00:00</t>
+          <t>2026-08-22T03:18:20.045192+00:00</t>
         </is>
       </c>
       <c r="AD14" t="inlineStr">
@@ -4774,7 +4774,7 @@
         <v>-0.1089169343844046</v>
       </c>
       <c r="V15" t="n">
-        <v>0.1072406716938052</v>
+        <v>0.1072405701495147</v>
       </c>
       <c r="W15" t="n">
         <v>0.2815942361128876</v>
@@ -4787,7 +4787,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>2026-08-22T03:14:26.043247+00:00</t>
+          <t>2026-08-22T03:18:13.415914+00:00</t>
         </is>
       </c>
       <c r="AD15" t="inlineStr">
@@ -4873,7 +4873,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>2026-08-22T03:14:30.349718+00:00</t>
+          <t>2026-08-22T03:18:19.799115+00:00</t>
         </is>
       </c>
       <c r="AD16" t="inlineStr">
@@ -4965,7 +4965,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>2026-08-22T03:14:28.093214+00:00</t>
+          <t>2026-08-22T03:18:16.380281+00:00</t>
         </is>
       </c>
       <c r="AD17" t="inlineStr">
@@ -5051,7 +5051,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>2026-08-22T03:14:31.054273+00:00</t>
+          <t>2026-08-22T03:18:20.905590+00:00</t>
         </is>
       </c>
       <c r="AD18" t="inlineStr">
@@ -5137,7 +5137,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>2026-08-22T03:14:30.704245+00:00</t>
+          <t>2026-08-22T03:18:20.301539+00:00</t>
         </is>
       </c>
       <c r="AD19" t="inlineStr">
@@ -5226,7 +5226,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>2026-08-22T03:14:26.754309+00:00</t>
+          <t>2026-08-22T03:18:14.352957+00:00</t>
         </is>
       </c>
       <c r="AD20" t="inlineStr">
@@ -5308,7 +5308,7 @@
         <v>0.07819827777494104</v>
       </c>
       <c r="W21" t="n">
-        <v>1.071721934408579</v>
+        <v>1.071721809401515</v>
       </c>
       <c r="X21" t="n">
         <v>0.00269</v>
@@ -5318,7 +5318,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>2026-08-22T03:14:29.983721+00:00</t>
+          <t>2026-08-22T03:18:19.223232+00:00</t>
         </is>
       </c>
       <c r="AD21" t="inlineStr">
@@ -5410,7 +5410,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>2026-08-22T03:14:28.994127+00:00</t>
+          <t>2026-08-22T03:18:17.675638+00:00</t>
         </is>
       </c>
       <c r="AD22" t="inlineStr">
@@ -5499,7 +5499,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>2026-08-22T03:14:30.172067+00:00</t>
+          <t>2026-08-22T03:18:19.522740+00:00</t>
         </is>
       </c>
       <c r="AD23" t="inlineStr">
@@ -5591,7 +5591,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>2026-08-22T03:14:27.715414+00:00</t>
+          <t>2026-08-22T03:18:15.774314+00:00</t>
         </is>
       </c>
       <c r="AD24" t="inlineStr">
@@ -5680,7 +5680,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>2026-08-22T03:14:27.484444+00:00</t>
+          <t>2026-08-22T03:18:15.440460+00:00</t>
         </is>
       </c>
       <c r="AD25" t="inlineStr">
@@ -5772,7 +5772,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>2026-08-22T03:14:29.203156+00:00</t>
+          <t>2026-08-22T03:18:17.978769+00:00</t>
         </is>
       </c>
       <c r="AD26" t="inlineStr">
@@ -5854,7 +5854,7 @@
         <v>-0.1456296261876776</v>
       </c>
       <c r="W27" t="n">
-        <v>-0.253548447765114</v>
+        <v>-0.2535483859208238</v>
       </c>
       <c r="X27" t="n">
         <v>0.00148</v>
@@ -5864,7 +5864,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>2026-08-22T03:14:28.288018+00:00</t>
+          <t>2026-08-22T03:18:16.708893+00:00</t>
         </is>
       </c>
       <c r="AD27" t="inlineStr">
@@ -5950,7 +5950,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>2026-08-22T03:14:27.302041+00:00</t>
+          <t>2026-08-22T03:18:15.181675+00:00</t>
         </is>
       </c>
       <c r="AD28" t="inlineStr">
@@ -6042,7 +6042,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>2026-08-22T03:14:29.401623+00:00</t>
+          <t>2026-08-22T03:18:18.285936+00:00</t>
         </is>
       </c>
       <c r="AD29" t="inlineStr">
@@ -6134,7 +6134,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>2026-08-22T03:14:30.882803+00:00</t>
+          <t>2026-08-22T03:18:20.566542+00:00</t>
         </is>
       </c>
       <c r="AD30" t="inlineStr">
@@ -6213,7 +6213,7 @@
         <v>-0.05779410309686361</v>
       </c>
       <c r="W31" t="n">
-        <v>-0.3646448542401906</v>
+        <v>-0.3646448121864612</v>
       </c>
       <c r="X31" t="n">
         <v>0.40498</v>
@@ -6223,7 +6223,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>2026-08-22T03:14:28.520889+00:00</t>
+          <t>2026-08-22T03:18:17.057713+00:00</t>
         </is>
       </c>
       <c r="AD31" t="inlineStr">

--- a/reports/investment_dashboard.xlsx
+++ b/reports/investment_dashboard.xlsx
@@ -3594,7 +3594,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>2026-08-22T03:18:17.357579+00:00</t>
+          <t>2026-08-22T03:21:42.469103+00:00</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
@@ -3676,7 +3676,7 @@
         <v>1.317802614597143</v>
       </c>
       <c r="W3" t="n">
-        <v>7.362826272720001</v>
+        <v>7.362826824630407</v>
       </c>
       <c r="X3" t="n">
         <v>0.00243</v>
@@ -3686,7 +3686,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>2026-08-22T03:18:14.083925+00:00</t>
+          <t>2026-08-22T03:21:36.321523+00:00</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
@@ -3778,7 +3778,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>2026-08-22T03:18:14.619724+00:00</t>
+          <t>2026-08-22T03:21:37.117440+00:00</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
@@ -3870,7 +3870,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>2026-08-22T03:18:18.544411+00:00</t>
+          <t>2026-08-22T03:21:44.422288+00:00</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
@@ -3962,7 +3962,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>2026-08-22T03:18:12.810467+00:00</t>
+          <t>2026-08-22T03:21:34.317705+00:00</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr">
@@ -4054,7 +4054,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>2026-08-22T03:18:14.930623+00:00</t>
+          <t>2026-08-22T03:21:38.202309+00:00</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>2026-08-22T03:18:18.811915+00:00</t>
+          <t>2026-08-22T03:21:44.946623+00:00</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr">
@@ -4228,7 +4228,7 @@
         <v>0.144129303232654</v>
       </c>
       <c r="W9" t="n">
-        <v>0.2287461792392489</v>
+        <v>0.2287460719461247</v>
       </c>
       <c r="X9" t="n">
         <v>0.03991</v>
@@ -4238,7 +4238,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>2026-08-22T03:18:12.544404+00:00</t>
+          <t>2026-08-22T03:21:33.943490+00:00</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr">
@@ -4327,7 +4327,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>2026-08-22T03:18:21.166229+00:00</t>
+          <t>2026-08-22T03:21:48.353921+00:00</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr">
@@ -4419,7 +4419,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>2026-08-22T03:18:13.056644+00:00</t>
+          <t>2026-08-22T03:21:34.674902+00:00</t>
         </is>
       </c>
       <c r="AD11" t="inlineStr">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>2026-08-22T03:18:16.069649+00:00</t>
+          <t>2026-08-22T03:21:40.410764+00:00</t>
         </is>
       </c>
       <c r="AD12" t="inlineStr">
@@ -4593,7 +4593,7 @@
         <v>0.3342865245955684</v>
       </c>
       <c r="W13" t="n">
-        <v>2.097116404241915</v>
+        <v>2.097116106946919</v>
       </c>
       <c r="X13" t="n">
         <v>0.00331</v>
@@ -4603,7 +4603,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>2026-08-22T03:18:13.724578+00:00</t>
+          <t>2026-08-22T03:21:35.901428+00:00</t>
         </is>
       </c>
       <c r="AD13" t="inlineStr">
@@ -4695,7 +4695,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>2026-08-22T03:18:20.045192+00:00</t>
+          <t>2026-08-22T03:21:46.750341+00:00</t>
         </is>
       </c>
       <c r="AD14" t="inlineStr">
@@ -4774,7 +4774,7 @@
         <v>-0.1089169343844046</v>
       </c>
       <c r="V15" t="n">
-        <v>0.1072405701495147</v>
+        <v>0.1072406716938052</v>
       </c>
       <c r="W15" t="n">
         <v>0.2815942361128876</v>
@@ -4787,7 +4787,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>2026-08-22T03:18:13.415914+00:00</t>
+          <t>2026-08-22T03:21:35.466687+00:00</t>
         </is>
       </c>
       <c r="AD15" t="inlineStr">
@@ -4873,7 +4873,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>2026-08-22T03:18:19.799115+00:00</t>
+          <t>2026-08-22T03:21:46.328268+00:00</t>
         </is>
       </c>
       <c r="AD16" t="inlineStr">
@@ -4965,7 +4965,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>2026-08-22T03:18:16.380281+00:00</t>
+          <t>2026-08-22T03:21:40.965250+00:00</t>
         </is>
       </c>
       <c r="AD17" t="inlineStr">
@@ -5051,7 +5051,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>2026-08-22T03:18:20.905590+00:00</t>
+          <t>2026-08-22T03:21:47.996489+00:00</t>
         </is>
       </c>
       <c r="AD18" t="inlineStr">
@@ -5137,7 +5137,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>2026-08-22T03:18:20.301539+00:00</t>
+          <t>2026-08-22T03:21:47.146656+00:00</t>
         </is>
       </c>
       <c r="AD19" t="inlineStr">
@@ -5226,7 +5226,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>2026-08-22T03:18:14.352957+00:00</t>
+          <t>2026-08-22T03:21:36.752763+00:00</t>
         </is>
       </c>
       <c r="AD20" t="inlineStr">
@@ -5308,7 +5308,7 @@
         <v>0.07819827777494104</v>
       </c>
       <c r="W21" t="n">
-        <v>1.071721809401515</v>
+        <v>1.071721934408579</v>
       </c>
       <c r="X21" t="n">
         <v>0.00269</v>
@@ -5318,7 +5318,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>2026-08-22T03:18:19.223232+00:00</t>
+          <t>2026-08-22T03:21:45.537320+00:00</t>
         </is>
       </c>
       <c r="AD21" t="inlineStr">
@@ -5410,7 +5410,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>2026-08-22T03:18:17.675638+00:00</t>
+          <t>2026-08-22T03:21:42.948373+00:00</t>
         </is>
       </c>
       <c r="AD22" t="inlineStr">
@@ -5499,7 +5499,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>2026-08-22T03:18:19.522740+00:00</t>
+          <t>2026-08-22T03:21:45.962355+00:00</t>
         </is>
       </c>
       <c r="AD23" t="inlineStr">
@@ -5591,7 +5591,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>2026-08-22T03:18:15.774314+00:00</t>
+          <t>2026-08-22T03:21:39.945888+00:00</t>
         </is>
       </c>
       <c r="AD24" t="inlineStr">
@@ -5680,7 +5680,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>2026-08-22T03:18:15.440460+00:00</t>
+          <t>2026-08-22T03:21:39.410057+00:00</t>
         </is>
       </c>
       <c r="AD25" t="inlineStr">
@@ -5772,7 +5772,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>2026-08-22T03:18:17.978769+00:00</t>
+          <t>2026-08-22T03:21:43.376205+00:00</t>
         </is>
       </c>
       <c r="AD26" t="inlineStr">
@@ -5864,7 +5864,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>2026-08-22T03:18:16.708893+00:00</t>
+          <t>2026-08-22T03:21:41.451636+00:00</t>
         </is>
       </c>
       <c r="AD27" t="inlineStr">
@@ -5950,7 +5950,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>2026-08-22T03:18:15.181675+00:00</t>
+          <t>2026-08-22T03:21:38.985536+00:00</t>
         </is>
       </c>
       <c r="AD28" t="inlineStr">
@@ -6042,7 +6042,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>2026-08-22T03:18:18.285936+00:00</t>
+          <t>2026-08-22T03:21:44.062630+00:00</t>
         </is>
       </c>
       <c r="AD29" t="inlineStr">
@@ -6134,7 +6134,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>2026-08-22T03:18:20.566542+00:00</t>
+          <t>2026-08-22T03:21:47.638801+00:00</t>
         </is>
       </c>
       <c r="AD30" t="inlineStr">
@@ -6223,7 +6223,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>2026-08-22T03:18:17.057713+00:00</t>
+          <t>2026-08-22T03:21:42.024330+00:00</t>
         </is>
       </c>
       <c r="AD31" t="inlineStr">

--- a/reports/investment_dashboard.xlsx
+++ b/reports/investment_dashboard.xlsx
@@ -525,16 +525,16 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>MU</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Taiwan Semiconductor Manufacturing Company Limited</t>
+          <t>Micron Technology, Inc.</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>55.67</v>
+        <v>57.27</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>418.9500122070312</v>
+        <v>966.780029296875</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -550,19 +550,24 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>100</v>
+        <v>84.2</v>
       </c>
       <c r="I2" t="n">
-        <v>100</v>
+        <v>88.2</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Revenue Growth; Earnings Fcf; Balance Sheet; Valuation</t>
+          <t>Revenue Growth; Earnings Fcf; Balance Sheet</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
           <t>Industry Growth; Competitive Advantage; Catalysts; Inflation Resilience</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>High market sensitivity / beta</t>
         </is>
       </c>
     </row>
@@ -572,16 +577,16 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>MU</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Micron Technology, Inc.</t>
+          <t>Taiwan Semiconductor Manufacturing Company Limited</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>55.05</v>
+        <v>55.67</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -589,7 +594,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>966.780029296875</v>
+        <v>418.9500122070312</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -597,24 +602,19 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="I3" t="n">
         <v>100</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Revenue Growth; Earnings Fcf; Balance Sheet</t>
+          <t>Revenue Growth; Earnings Fcf; Balance Sheet; Valuation</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
           <t>Industry Growth; Competitive Advantage; Catalysts; Inflation Resilience</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>High market sensitivity / beta</t>
         </is>
       </c>
     </row>
@@ -883,7 +883,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>50.09</v>
+        <v>50.06</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -2115,7 +2115,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>MU</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -2128,19 +2128,19 @@
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>8.84</v>
+        <v>9.02</v>
       </c>
       <c r="F2" t="n">
-        <v>8.68</v>
+        <v>7.04</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>5.46</v>
+        <v>7.71</v>
       </c>
       <c r="I2" t="n">
-        <v>2.69</v>
+        <v>3.5</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -2149,13 +2149,13 @@
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>55.67</v>
+        <v>57.27</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>MU</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -2168,19 +2168,19 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>9.02</v>
+        <v>8.84</v>
       </c>
       <c r="F3" t="n">
-        <v>4.82</v>
+        <v>8.68</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>7.71</v>
+        <v>5.46</v>
       </c>
       <c r="I3" t="n">
-        <v>3.5</v>
+        <v>2.69</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -2189,7 +2189,7 @@
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>55.05</v>
+        <v>55.67</v>
       </c>
     </row>
     <row r="4">
@@ -2411,7 +2411,7 @@
         <v>9.029999999999999</v>
       </c>
       <c r="F9" t="n">
-        <v>3.15</v>
+        <v>3.12</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -2429,7 +2429,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>50.09</v>
+        <v>50.06</v>
       </c>
     </row>
     <row r="10">
@@ -3514,12 +3514,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>MU</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Taiwan Semiconductor Manufacturing Company Limited</t>
+          <t>Micron Technology, Inc.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -3532,69 +3532,60 @@
           <t>Semiconductors</t>
         </is>
       </c>
-      <c r="E2" t="n">
-        <v>2172873342976</v>
-      </c>
       <c r="F2" t="n">
-        <v>418.9500122070312</v>
+        <v>966.780029296875</v>
       </c>
       <c r="G2" t="n">
-        <v>4440492343296</v>
+        <v>90273996800</v>
       </c>
       <c r="H2" t="n">
-        <v>0.36</v>
+        <v>3.457</v>
       </c>
       <c r="I2" t="n">
-        <v>13.49</v>
+        <v>44.23</v>
       </c>
       <c r="J2" t="n">
-        <v>0.774</v>
+        <v>13.685</v>
       </c>
       <c r="K2" t="n">
-        <v>730826014720</v>
+        <v>7639499776</v>
       </c>
       <c r="M2" t="n">
-        <v>3518010228736</v>
+        <v>26022000640</v>
       </c>
       <c r="N2" t="n">
-        <v>1068558516224</v>
+        <v>6376000000</v>
       </c>
       <c r="O2" t="n">
-        <v>0.6423</v>
+        <v>0.7256899999999999</v>
       </c>
       <c r="P2" t="n">
-        <v>0.60344005</v>
+        <v>0.80370003</v>
       </c>
       <c r="Q2" t="n">
-        <v>31.05634</v>
-      </c>
-      <c r="R2" t="n">
-        <v>0.48933163</v>
-      </c>
-      <c r="S2" t="n">
-        <v>2.97317459861974</v>
+        <v>21.858015</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.005365445487747644</v>
+        <v>0.007608338867642228</v>
       </c>
       <c r="U2" t="n">
-        <v>0.03809732083456407</v>
+        <v>0.2875215850577266</v>
       </c>
       <c r="V2" t="n">
-        <v>0.1684963370842598</v>
+        <v>1.317802614597143</v>
       </c>
       <c r="W2" t="n">
-        <v>0.8632971696944793</v>
+        <v>7.362826824630407</v>
       </c>
       <c r="X2" t="n">
-        <v>0.00013</v>
+        <v>0.00243</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.155</v>
+        <v>0.79989</v>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>2026-08-22T03:21:42.469103+00:00</t>
+          <t>2026-08-22T03:39:09.596279+00:00</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
@@ -3606,12 +3597,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>MU</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Micron Technology, Inc.</t>
+          <t>Taiwan Semiconductor Manufacturing Company Limited</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -3625,68 +3616,68 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1091874717696</v>
+        <v>2172873342976</v>
       </c>
       <c r="F3" t="n">
-        <v>966.780029296875</v>
+        <v>418.9500122070312</v>
       </c>
       <c r="G3" t="n">
-        <v>90273996800</v>
+        <v>4440492343296</v>
       </c>
       <c r="H3" t="n">
-        <v>3.457</v>
+        <v>0.36</v>
       </c>
       <c r="I3" t="n">
-        <v>44.23</v>
+        <v>13.49</v>
       </c>
       <c r="J3" t="n">
-        <v>13.685</v>
+        <v>0.774</v>
       </c>
       <c r="K3" t="n">
-        <v>7639499776</v>
+        <v>730826014720</v>
       </c>
       <c r="M3" t="n">
-        <v>26022000640</v>
+        <v>3518010228736</v>
       </c>
       <c r="N3" t="n">
-        <v>6376000000</v>
+        <v>1068558516224</v>
       </c>
       <c r="O3" t="n">
-        <v>0.7256899999999999</v>
+        <v>0.6423</v>
       </c>
       <c r="P3" t="n">
-        <v>0.80370003</v>
+        <v>0.60344005</v>
       </c>
       <c r="Q3" t="n">
-        <v>21.858015</v>
+        <v>31.05634</v>
       </c>
       <c r="R3" t="n">
-        <v>12.0951185</v>
+        <v>0.48933163</v>
       </c>
       <c r="S3" t="n">
-        <v>142.924896879531</v>
+        <v>2.97317459861974</v>
       </c>
       <c r="T3" t="n">
-        <v>0.007608338867642228</v>
+        <v>-0.005365445487747644</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2875215850577266</v>
+        <v>0.03809732083456407</v>
       </c>
       <c r="V3" t="n">
-        <v>1.317802614597143</v>
+        <v>0.1684963370842598</v>
       </c>
       <c r="W3" t="n">
-        <v>7.362826824630407</v>
+        <v>0.8632971696944793</v>
       </c>
       <c r="X3" t="n">
-        <v>0.00243</v>
+        <v>0.00013</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.79989</v>
+        <v>0.155</v>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>2026-08-22T03:21:36.321523+00:00</t>
+          <t>2026-08-22T03:39:14.292211+00:00</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
@@ -3778,7 +3769,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>2026-08-22T03:21:37.117440+00:00</t>
+          <t>2026-08-22T03:39:10.465796+00:00</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
@@ -3870,7 +3861,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>2026-08-22T03:21:44.422288+00:00</t>
+          <t>2026-08-22T03:39:15.931795+00:00</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
@@ -3962,7 +3953,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>2026-08-22T03:21:34.317705+00:00</t>
+          <t>2026-08-22T03:39:07.881315+00:00</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr">
@@ -4044,7 +4035,7 @@
         <v>0.1898762435729664</v>
       </c>
       <c r="W7" t="n">
-        <v>2.446494406067634</v>
+        <v>2.446494647256825</v>
       </c>
       <c r="X7" t="n">
         <v>0.00202</v>
@@ -4054,7 +4045,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>2026-08-22T03:21:38.202309+00:00</t>
+          <t>2026-08-22T03:39:10.872177+00:00</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr">
@@ -4146,7 +4137,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>2026-08-22T03:21:44.946623+00:00</t>
+          <t>2026-08-22T03:39:16.359634+00:00</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr">
@@ -4189,7 +4180,7 @@
         <v>0.852</v>
       </c>
       <c r="I9" t="n">
-        <v>6.53</v>
+        <v>6.46</v>
       </c>
       <c r="J9" t="n">
         <v>2.145</v>
@@ -4210,7 +4201,7 @@
         <v>0.65596</v>
       </c>
       <c r="Q9" t="n">
-        <v>32.88208</v>
+        <v>33.23839</v>
       </c>
       <c r="R9" t="n">
         <v>20.51644</v>
@@ -4228,7 +4219,7 @@
         <v>0.144129303232654</v>
       </c>
       <c r="W9" t="n">
-        <v>0.2287460719461247</v>
+        <v>0.2287461792392489</v>
       </c>
       <c r="X9" t="n">
         <v>0.03991</v>
@@ -4238,7 +4229,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>2026-08-22T03:21:33.943490+00:00</t>
+          <t>2026-08-22T03:39:07.530474+00:00</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr">
@@ -4327,7 +4318,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>2026-08-22T03:21:48.353921+00:00</t>
+          <t>2026-08-22T03:39:19.570935+00:00</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr">
@@ -4419,7 +4410,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>2026-08-22T03:21:34.674902+00:00</t>
+          <t>2026-08-22T03:39:08.249133+00:00</t>
         </is>
       </c>
       <c r="AD11" t="inlineStr">
@@ -4501,7 +4492,7 @@
         <v>0.1400655521483041</v>
       </c>
       <c r="W12" t="n">
-        <v>0.731182362414351</v>
+        <v>0.7311824950356518</v>
       </c>
       <c r="X12" t="n">
         <v>0.01596</v>
@@ -4511,7 +4502,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>2026-08-22T03:21:40.410764+00:00</t>
+          <t>2026-08-22T03:39:12.671855+00:00</t>
         </is>
       </c>
       <c r="AD12" t="inlineStr">
@@ -4603,7 +4594,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>2026-08-22T03:21:35.901428+00:00</t>
+          <t>2026-08-22T03:39:09.181710+00:00</t>
         </is>
       </c>
       <c r="AD13" t="inlineStr">
@@ -4695,7 +4686,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>2026-08-22T03:21:46.750341+00:00</t>
+          <t>2026-08-22T03:39:17.969751+00:00</t>
         </is>
       </c>
       <c r="AD14" t="inlineStr">
@@ -4787,7 +4778,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>2026-08-22T03:21:35.466687+00:00</t>
+          <t>2026-08-22T03:39:08.779000+00:00</t>
         </is>
       </c>
       <c r="AD15" t="inlineStr">
@@ -4873,7 +4864,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>2026-08-22T03:21:46.328268+00:00</t>
+          <t>2026-08-22T03:39:17.569403+00:00</t>
         </is>
       </c>
       <c r="AD16" t="inlineStr">
@@ -4965,7 +4956,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>2026-08-22T03:21:40.965250+00:00</t>
+          <t>2026-08-22T03:39:13.070293+00:00</t>
         </is>
       </c>
       <c r="AD17" t="inlineStr">
@@ -5051,7 +5042,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>2026-08-22T03:21:47.996489+00:00</t>
+          <t>2026-08-22T03:39:19.184722+00:00</t>
         </is>
       </c>
       <c r="AD18" t="inlineStr">
@@ -5137,7 +5128,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>2026-08-22T03:21:47.146656+00:00</t>
+          <t>2026-08-22T03:39:18.392496+00:00</t>
         </is>
       </c>
       <c r="AD19" t="inlineStr">
@@ -5226,7 +5217,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>2026-08-22T03:21:36.752763+00:00</t>
+          <t>2026-08-22T03:39:10.083875+00:00</t>
         </is>
       </c>
       <c r="AD20" t="inlineStr">
@@ -5269,7 +5260,7 @@
         <v>0.241</v>
       </c>
       <c r="I21" t="n">
-        <v>4.42</v>
+        <v>4.37</v>
       </c>
       <c r="J21" t="n">
         <v>0.53</v>
@@ -5290,7 +5281,7 @@
         <v>0.20362</v>
       </c>
       <c r="Q21" t="n">
-        <v>59.26471</v>
+        <v>59.942795</v>
       </c>
       <c r="R21" t="n">
         <v>8.784945499999999</v>
@@ -5318,7 +5309,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>2026-08-22T03:21:45.537320+00:00</t>
+          <t>2026-08-22T03:39:16.750767+00:00</t>
         </is>
       </c>
       <c r="AD21" t="inlineStr">
@@ -5410,7 +5401,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>2026-08-22T03:21:42.948373+00:00</t>
+          <t>2026-08-22T03:39:14.706831+00:00</t>
         </is>
       </c>
       <c r="AD22" t="inlineStr">
@@ -5499,7 +5490,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>2026-08-22T03:21:45.962355+00:00</t>
+          <t>2026-08-22T03:39:17.148821+00:00</t>
         </is>
       </c>
       <c r="AD23" t="inlineStr">
@@ -5581,7 +5572,7 @@
         <v>0.2176838288473297</v>
       </c>
       <c r="W24" t="n">
-        <v>-0.03376181497550057</v>
+        <v>-0.03376187393524122</v>
       </c>
       <c r="X24" t="n">
         <v>0.00090000004</v>
@@ -5591,7 +5582,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>2026-08-22T03:21:39.945888+00:00</t>
+          <t>2026-08-22T03:39:12.197594+00:00</t>
         </is>
       </c>
       <c r="AD24" t="inlineStr">
@@ -5680,7 +5671,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>2026-08-22T03:21:39.410057+00:00</t>
+          <t>2026-08-22T03:39:11.708023+00:00</t>
         </is>
       </c>
       <c r="AD25" t="inlineStr">
@@ -5772,7 +5763,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>2026-08-22T03:21:43.376205+00:00</t>
+          <t>2026-08-22T03:39:15.100463+00:00</t>
         </is>
       </c>
       <c r="AD26" t="inlineStr">
@@ -5854,7 +5845,7 @@
         <v>-0.1456296261876776</v>
       </c>
       <c r="W27" t="n">
-        <v>-0.2535483859208238</v>
+        <v>-0.253548447765114</v>
       </c>
       <c r="X27" t="n">
         <v>0.00148</v>
@@ -5864,7 +5855,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>2026-08-22T03:21:41.451636+00:00</t>
+          <t>2026-08-22T03:39:13.486202+00:00</t>
         </is>
       </c>
       <c r="AD27" t="inlineStr">
@@ -5950,7 +5941,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>2026-08-22T03:21:38.985536+00:00</t>
+          <t>2026-08-22T03:39:11.262513+00:00</t>
         </is>
       </c>
       <c r="AD28" t="inlineStr">
@@ -6042,7 +6033,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>2026-08-22T03:21:44.062630+00:00</t>
+          <t>2026-08-22T03:39:15.538615+00:00</t>
         </is>
       </c>
       <c r="AD29" t="inlineStr">
@@ -6134,7 +6125,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>2026-08-22T03:21:47.638801+00:00</t>
+          <t>2026-08-22T03:39:18.797686+00:00</t>
         </is>
       </c>
       <c r="AD30" t="inlineStr">
@@ -6223,7 +6214,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>2026-08-22T03:21:42.024330+00:00</t>
+          <t>2026-08-22T03:39:13.885380+00:00</t>
         </is>
       </c>
       <c r="AD31" t="inlineStr">
@@ -6251,7 +6242,7 @@
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
@@ -6308,22 +6299,27 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>MU</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>100</v>
+        <v>84.2</v>
       </c>
       <c r="C2" t="n">
-        <v>100</v>
+        <v>88.2</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MODERATE</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>price_to_sales, price_to_fcf</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -6337,11 +6333,11 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>MU</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="C3" t="n">
         <v>100</v>
@@ -6352,7 +6348,7 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -7289,11 +7285,11 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>MU</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>55.67</v>
+        <v>57.27</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -7306,7 +7302,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>100</v>
+        <v>84.2</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>

--- a/reports/investment_dashboard.xlsx
+++ b/reports/investment_dashboard.xlsx
@@ -3349,7 +3349,7 @@
     <col width="23" customWidth="1" min="20" max="20"/>
     <col width="23" customWidth="1" min="21" max="21"/>
     <col width="22" customWidth="1" min="22" max="22"/>
-    <col width="22" customWidth="1" min="23" max="23"/>
+    <col width="21" customWidth="1" min="23" max="23"/>
     <col width="18" customWidth="1" min="24" max="24"/>
     <col width="24" customWidth="1" min="25" max="25"/>
     <col width="17" customWidth="1" min="26" max="26"/>
@@ -3585,7 +3585,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>2026-08-22T03:39:09.596279+00:00</t>
+          <t>2026-08-22T03:40:39.713577+00:00</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
@@ -3677,7 +3677,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>2026-08-22T03:39:14.292211+00:00</t>
+          <t>2026-08-22T03:40:44.926761+00:00</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
@@ -3769,7 +3769,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>2026-08-22T03:39:10.465796+00:00</t>
+          <t>2026-08-22T03:40:40.640485+00:00</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
@@ -3861,7 +3861,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>2026-08-22T03:39:15.931795+00:00</t>
+          <t>2026-08-22T03:40:46.811059+00:00</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
@@ -3953,7 +3953,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>2026-08-22T03:39:07.881315+00:00</t>
+          <t>2026-08-22T03:40:37.854214+00:00</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr">
@@ -4045,7 +4045,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>2026-08-22T03:39:10.872177+00:00</t>
+          <t>2026-08-22T03:40:41.180623+00:00</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr">
@@ -4137,7 +4137,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>2026-08-22T03:39:16.359634+00:00</t>
+          <t>2026-08-22T03:40:47.284377+00:00</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr">
@@ -4229,7 +4229,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>2026-08-22T03:39:07.530474+00:00</t>
+          <t>2026-08-22T03:40:37.430390+00:00</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr">
@@ -4318,7 +4318,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>2026-08-22T03:39:19.570935+00:00</t>
+          <t>2026-08-22T03:40:50.752898+00:00</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr">
@@ -4410,7 +4410,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>2026-08-22T03:39:08.249133+00:00</t>
+          <t>2026-08-22T03:40:38.272525+00:00</t>
         </is>
       </c>
       <c r="AD11" t="inlineStr">
@@ -4492,7 +4492,7 @@
         <v>0.1400655521483041</v>
       </c>
       <c r="W12" t="n">
-        <v>0.7311824950356518</v>
+        <v>0.731182362414351</v>
       </c>
       <c r="X12" t="n">
         <v>0.01596</v>
@@ -4502,7 +4502,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>2026-08-22T03:39:12.671855+00:00</t>
+          <t>2026-08-22T03:40:43.134617+00:00</t>
         </is>
       </c>
       <c r="AD12" t="inlineStr">
@@ -4594,7 +4594,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>2026-08-22T03:39:09.181710+00:00</t>
+          <t>2026-08-22T03:40:39.216069+00:00</t>
         </is>
       </c>
       <c r="AD13" t="inlineStr">
@@ -4686,7 +4686,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>2026-08-22T03:39:17.969751+00:00</t>
+          <t>2026-08-22T03:40:49.087805+00:00</t>
         </is>
       </c>
       <c r="AD14" t="inlineStr">
@@ -4778,7 +4778,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>2026-08-22T03:39:08.779000+00:00</t>
+          <t>2026-08-22T03:40:38.714917+00:00</t>
         </is>
       </c>
       <c r="AD15" t="inlineStr">
@@ -4864,7 +4864,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>2026-08-22T03:39:17.569403+00:00</t>
+          <t>2026-08-22T03:40:48.641217+00:00</t>
         </is>
       </c>
       <c r="AD16" t="inlineStr">
@@ -4956,7 +4956,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>2026-08-22T03:39:13.070293+00:00</t>
+          <t>2026-08-22T03:40:43.580395+00:00</t>
         </is>
       </c>
       <c r="AD17" t="inlineStr">
@@ -5042,7 +5042,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>2026-08-22T03:39:19.184722+00:00</t>
+          <t>2026-08-22T03:40:50.346729+00:00</t>
         </is>
       </c>
       <c r="AD18" t="inlineStr">
@@ -5128,7 +5128,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>2026-08-22T03:39:18.392496+00:00</t>
+          <t>2026-08-22T03:40:49.533734+00:00</t>
         </is>
       </c>
       <c r="AD19" t="inlineStr">
@@ -5217,7 +5217,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>2026-08-22T03:39:10.083875+00:00</t>
+          <t>2026-08-22T03:40:40.181639+00:00</t>
         </is>
       </c>
       <c r="AD20" t="inlineStr">
@@ -5299,7 +5299,7 @@
         <v>0.07819827777494104</v>
       </c>
       <c r="W21" t="n">
-        <v>1.071721934408579</v>
+        <v>1.071721809401515</v>
       </c>
       <c r="X21" t="n">
         <v>0.00269</v>
@@ -5309,7 +5309,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>2026-08-22T03:39:16.750767+00:00</t>
+          <t>2026-08-22T03:40:47.770398+00:00</t>
         </is>
       </c>
       <c r="AD21" t="inlineStr">
@@ -5401,7 +5401,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>2026-08-22T03:39:14.706831+00:00</t>
+          <t>2026-08-22T03:40:45.457727+00:00</t>
         </is>
       </c>
       <c r="AD22" t="inlineStr">
@@ -5490,7 +5490,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>2026-08-22T03:39:17.148821+00:00</t>
+          <t>2026-08-22T03:40:48.240630+00:00</t>
         </is>
       </c>
       <c r="AD23" t="inlineStr">
@@ -5572,7 +5572,7 @@
         <v>0.2176838288473297</v>
       </c>
       <c r="W24" t="n">
-        <v>-0.03376187393524122</v>
+        <v>-0.0337617560157526</v>
       </c>
       <c r="X24" t="n">
         <v>0.00090000004</v>
@@ -5582,7 +5582,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>2026-08-22T03:39:12.197594+00:00</t>
+          <t>2026-08-22T03:40:42.537405+00:00</t>
         </is>
       </c>
       <c r="AD24" t="inlineStr">
@@ -5671,7 +5671,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>2026-08-22T03:39:11.708023+00:00</t>
+          <t>2026-08-22T03:40:42.041554+00:00</t>
         </is>
       </c>
       <c r="AD25" t="inlineStr">
@@ -5763,7 +5763,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>2026-08-22T03:39:15.100463+00:00</t>
+          <t>2026-08-22T03:40:45.890756+00:00</t>
         </is>
       </c>
       <c r="AD26" t="inlineStr">
@@ -5855,7 +5855,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>2026-08-22T03:39:13.486202+00:00</t>
+          <t>2026-08-22T03:40:44.009748+00:00</t>
         </is>
       </c>
       <c r="AD27" t="inlineStr">
@@ -5941,7 +5941,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>2026-08-22T03:39:11.262513+00:00</t>
+          <t>2026-08-22T03:40:41.639460+00:00</t>
         </is>
       </c>
       <c r="AD28" t="inlineStr">
@@ -6033,7 +6033,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>2026-08-22T03:39:15.538615+00:00</t>
+          <t>2026-08-22T03:40:46.357193+00:00</t>
         </is>
       </c>
       <c r="AD29" t="inlineStr">
@@ -6125,7 +6125,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>2026-08-22T03:39:18.797686+00:00</t>
+          <t>2026-08-22T03:40:49.946030+00:00</t>
         </is>
       </c>
       <c r="AD30" t="inlineStr">
@@ -6214,7 +6214,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>2026-08-22T03:39:13.885380+00:00</t>
+          <t>2026-08-22T03:40:44.469402+00:00</t>
         </is>
       </c>
       <c r="AD31" t="inlineStr">

--- a/reports/investment_dashboard.xlsx
+++ b/reports/investment_dashboard.xlsx
@@ -3349,7 +3349,7 @@
     <col width="23" customWidth="1" min="20" max="20"/>
     <col width="23" customWidth="1" min="21" max="21"/>
     <col width="22" customWidth="1" min="22" max="22"/>
-    <col width="21" customWidth="1" min="23" max="23"/>
+    <col width="22" customWidth="1" min="23" max="23"/>
     <col width="18" customWidth="1" min="24" max="24"/>
     <col width="24" customWidth="1" min="25" max="25"/>
     <col width="17" customWidth="1" min="26" max="26"/>
@@ -3575,7 +3575,7 @@
         <v>1.317802614597143</v>
       </c>
       <c r="W2" t="n">
-        <v>7.362826824630407</v>
+        <v>7.362826272720001</v>
       </c>
       <c r="X2" t="n">
         <v>0.00243</v>
@@ -3585,7 +3585,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>2026-08-22T03:40:39.713577+00:00</t>
+          <t>2026-08-22T03:48:40.386171+00:00</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
@@ -3667,7 +3667,7 @@
         <v>0.1684963370842598</v>
       </c>
       <c r="W3" t="n">
-        <v>0.8632971696944793</v>
+        <v>0.8632972961454419</v>
       </c>
       <c r="X3" t="n">
         <v>0.00013</v>
@@ -3677,7 +3677,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>2026-08-22T03:40:44.926761+00:00</t>
+          <t>2026-08-22T03:48:43.597709+00:00</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
@@ -3769,7 +3769,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>2026-08-22T03:40:40.640485+00:00</t>
+          <t>2026-08-22T03:48:40.946328+00:00</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
@@ -3861,7 +3861,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>2026-08-22T03:40:46.811059+00:00</t>
+          <t>2026-08-22T03:48:44.788885+00:00</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
@@ -3953,7 +3953,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>2026-08-22T03:40:37.854214+00:00</t>
+          <t>2026-08-22T03:48:39.183355+00:00</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr">
@@ -4045,7 +4045,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>2026-08-22T03:40:41.180623+00:00</t>
+          <t>2026-08-22T03:48:41.288517+00:00</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr">
@@ -4137,7 +4137,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>2026-08-22T03:40:47.284377+00:00</t>
+          <t>2026-08-22T03:48:45.066415+00:00</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr">
@@ -4229,7 +4229,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>2026-08-22T03:40:37.430390+00:00</t>
+          <t>2026-08-22T03:48:38.927421+00:00</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr">
@@ -4318,7 +4318,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>2026-08-22T03:40:50.752898+00:00</t>
+          <t>2026-08-22T03:48:47.624196+00:00</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr">
@@ -4410,7 +4410,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>2026-08-22T03:40:38.272525+00:00</t>
+          <t>2026-08-22T03:48:39.450675+00:00</t>
         </is>
       </c>
       <c r="AD11" t="inlineStr">
@@ -4492,7 +4492,7 @@
         <v>0.1400655521483041</v>
       </c>
       <c r="W12" t="n">
-        <v>0.731182362414351</v>
+        <v>0.7311824950356518</v>
       </c>
       <c r="X12" t="n">
         <v>0.01596</v>
@@ -4502,7 +4502,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>2026-08-22T03:40:43.134617+00:00</t>
+          <t>2026-08-22T03:48:42.448193+00:00</t>
         </is>
       </c>
       <c r="AD12" t="inlineStr">
@@ -4594,7 +4594,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>2026-08-22T03:40:39.216069+00:00</t>
+          <t>2026-08-22T03:48:40.029242+00:00</t>
         </is>
       </c>
       <c r="AD13" t="inlineStr">
@@ -4686,7 +4686,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>2026-08-22T03:40:49.087805+00:00</t>
+          <t>2026-08-22T03:48:46.346790+00:00</t>
         </is>
       </c>
       <c r="AD14" t="inlineStr">
@@ -4778,7 +4778,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>2026-08-22T03:40:38.714917+00:00</t>
+          <t>2026-08-22T03:48:39.738255+00:00</t>
         </is>
       </c>
       <c r="AD15" t="inlineStr">
@@ -4864,7 +4864,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>2026-08-22T03:40:48.641217+00:00</t>
+          <t>2026-08-22T03:48:45.897047+00:00</t>
         </is>
       </c>
       <c r="AD16" t="inlineStr">
@@ -4956,7 +4956,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>2026-08-22T03:40:43.580395+00:00</t>
+          <t>2026-08-22T03:48:42.696669+00:00</t>
         </is>
       </c>
       <c r="AD17" t="inlineStr">
@@ -5042,7 +5042,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>2026-08-22T03:40:50.346729+00:00</t>
+          <t>2026-08-22T03:48:47.361615+00:00</t>
         </is>
       </c>
       <c r="AD18" t="inlineStr">
@@ -5128,7 +5128,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>2026-08-22T03:40:49.533734+00:00</t>
+          <t>2026-08-22T03:48:46.622661+00:00</t>
         </is>
       </c>
       <c r="AD19" t="inlineStr">
@@ -5217,7 +5217,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>2026-08-22T03:40:40.181639+00:00</t>
+          <t>2026-08-22T03:48:40.688384+00:00</t>
         </is>
       </c>
       <c r="AD20" t="inlineStr">
@@ -5299,7 +5299,7 @@
         <v>0.07819827777494104</v>
       </c>
       <c r="W21" t="n">
-        <v>1.071721809401515</v>
+        <v>1.071721934408579</v>
       </c>
       <c r="X21" t="n">
         <v>0.00269</v>
@@ -5309,7 +5309,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>2026-08-22T03:40:47.770398+00:00</t>
+          <t>2026-08-22T03:48:45.336616+00:00</t>
         </is>
       </c>
       <c r="AD21" t="inlineStr">
@@ -5401,7 +5401,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>2026-08-22T03:40:45.457727+00:00</t>
+          <t>2026-08-22T03:48:43.928452+00:00</t>
         </is>
       </c>
       <c r="AD22" t="inlineStr">
@@ -5490,7 +5490,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>2026-08-22T03:40:48.240630+00:00</t>
+          <t>2026-08-22T03:48:45.630249+00:00</t>
         </is>
       </c>
       <c r="AD23" t="inlineStr">
@@ -5572,7 +5572,7 @@
         <v>0.2176838288473297</v>
       </c>
       <c r="W24" t="n">
-        <v>-0.0337617560157526</v>
+        <v>-0.03376181497550057</v>
       </c>
       <c r="X24" t="n">
         <v>0.00090000004</v>
@@ -5582,7 +5582,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>2026-08-22T03:40:42.537405+00:00</t>
+          <t>2026-08-22T03:48:42.176421+00:00</t>
         </is>
       </c>
       <c r="AD24" t="inlineStr">
@@ -5671,7 +5671,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>2026-08-22T03:40:42.041554+00:00</t>
+          <t>2026-08-22T03:48:41.875535+00:00</t>
         </is>
       </c>
       <c r="AD25" t="inlineStr">
@@ -5763,7 +5763,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>2026-08-22T03:40:45.890756+00:00</t>
+          <t>2026-08-22T03:48:44.202301+00:00</t>
         </is>
       </c>
       <c r="AD26" t="inlineStr">
@@ -5845,7 +5845,7 @@
         <v>-0.1456296261876776</v>
       </c>
       <c r="W27" t="n">
-        <v>-0.253548447765114</v>
+        <v>-0.2535483859208238</v>
       </c>
       <c r="X27" t="n">
         <v>0.00148</v>
@@ -5855,7 +5855,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>2026-08-22T03:40:44.009748+00:00</t>
+          <t>2026-08-22T03:48:42.966437+00:00</t>
         </is>
       </c>
       <c r="AD27" t="inlineStr">
@@ -5941,7 +5941,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>2026-08-22T03:40:41.639460+00:00</t>
+          <t>2026-08-22T03:48:41.587467+00:00</t>
         </is>
       </c>
       <c r="AD28" t="inlineStr">
@@ -6033,7 +6033,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>2026-08-22T03:40:46.357193+00:00</t>
+          <t>2026-08-22T03:48:44.495431+00:00</t>
         </is>
       </c>
       <c r="AD29" t="inlineStr">
@@ -6125,7 +6125,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>2026-08-22T03:40:49.946030+00:00</t>
+          <t>2026-08-22T03:48:47.021627+00:00</t>
         </is>
       </c>
       <c r="AD30" t="inlineStr">
@@ -6214,7 +6214,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>2026-08-22T03:40:44.469402+00:00</t>
+          <t>2026-08-22T03:48:43.288740+00:00</t>
         </is>
       </c>
       <c r="AD31" t="inlineStr">

--- a/reports/investment_dashboard.xlsx
+++ b/reports/investment_dashboard.xlsx
@@ -586,7 +586,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>55.67</v>
+        <v>55.66</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -827,16 +827,16 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>DELL</t>
+          <t>NVDA</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Dell Technologies Inc.</t>
+          <t>NVIDIA Corporation</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>50.47</v>
+        <v>50.09</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -844,11 +844,11 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>442.0799865722656</v>
+        <v>214.7200012207031</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="H8" t="n">
@@ -859,12 +859,17 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Revenue Growth; Momentum</t>
+          <t>Revenue Growth; Earnings Fcf; Balance Sheet</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Industry Growth; Competitive Advantage; Catalysts; Inflation Resilience</t>
+          <t>Industry Growth; Valuation; Competitive Advantage; Catalysts; Inflation Resilience</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>Excessive price-to-sales valuation; High market sensitivity / beta</t>
         </is>
       </c>
     </row>
@@ -874,28 +879,28 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>NVDA</t>
+          <t>DELL</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>NVIDIA Corporation</t>
+          <t>Dell Technologies Inc.</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>50.06</v>
+        <v>49.5</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RESEARCH</t>
+          <t>REJECT</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>214.7200012207031</v>
+        <v>442.0799865722656</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="H9" t="n">
@@ -906,17 +911,17 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Revenue Growth; Earnings Fcf; Balance Sheet</t>
+          <t>Revenue Growth; Momentum</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Industry Growth; Valuation; Competitive Advantage; Catalysts; Inflation Resilience</t>
+          <t>Industry Growth; Competitive Advantage; Catalysts; Inflation Resilience</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Excessive price-to-sales valuation; High market sensitivity / beta</t>
+          <t>Very high earnings multiple</t>
         </is>
       </c>
     </row>
@@ -935,7 +940,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>48.3</v>
+        <v>48.25</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -1034,7 +1039,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>46.99</v>
+        <v>46.98</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -1081,7 +1086,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>45.78</v>
+        <v>45.64</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -1284,7 +1289,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>42.92</v>
+        <v>42.93</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -1430,7 +1435,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>42.76</v>
+        <v>42.73</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -1581,7 +1586,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>42.01</v>
+        <v>41.99</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -1633,7 +1638,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>41.9</v>
+        <v>41.89</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -1977,7 +1982,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>30.94</v>
+        <v>30.88</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -2171,7 +2176,7 @@
         <v>8.84</v>
       </c>
       <c r="F3" t="n">
-        <v>8.68</v>
+        <v>8.67</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -2189,7 +2194,7 @@
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>55.67</v>
+        <v>55.66</v>
       </c>
     </row>
     <row r="4">
@@ -2355,32 +2360,32 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>DELL</t>
+          <t>NVDA</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>15</v>
       </c>
       <c r="C8" t="n">
-        <v>11.48</v>
+        <v>15</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>6.33</v>
+        <v>9.029999999999999</v>
       </c>
       <c r="F8" t="n">
-        <v>5.94</v>
+        <v>3.15</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>8.18</v>
+        <v>4.47</v>
       </c>
       <c r="I8" t="n">
-        <v>3.54</v>
+        <v>3.44</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -2389,38 +2394,38 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>50.47</v>
+        <v>50.09</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>NVDA</t>
+          <t>DELL</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>15</v>
       </c>
       <c r="C9" t="n">
-        <v>15</v>
+        <v>11.48</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>9.029999999999999</v>
+        <v>6.33</v>
       </c>
       <c r="F9" t="n">
-        <v>3.12</v>
+        <v>4.97</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>4.47</v>
+        <v>8.18</v>
       </c>
       <c r="I9" t="n">
-        <v>3.44</v>
+        <v>3.54</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -2429,7 +2434,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>50.06</v>
+        <v>49.5</v>
       </c>
     </row>
     <row r="10">
@@ -2451,7 +2456,7 @@
         <v>9.699999999999999</v>
       </c>
       <c r="F10" t="n">
-        <v>7.17</v>
+        <v>7.12</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -2469,7 +2474,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>48.3</v>
+        <v>48.25</v>
       </c>
     </row>
     <row r="11">
@@ -2531,7 +2536,7 @@
         <v>8.34</v>
       </c>
       <c r="F12" t="n">
-        <v>4.4</v>
+        <v>4.39</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -2549,7 +2554,7 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>46.99</v>
+        <v>46.98</v>
       </c>
     </row>
     <row r="13">
@@ -2568,10 +2573,10 @@
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>7.93</v>
+        <v>7.78</v>
       </c>
       <c r="F13" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -2589,7 +2594,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>45.78</v>
+        <v>45.64</v>
       </c>
     </row>
     <row r="14">
@@ -2731,7 +2736,7 @@
         <v>6.64</v>
       </c>
       <c r="F17" t="n">
-        <v>6.51</v>
+        <v>6.52</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -2749,7 +2754,7 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>42.92</v>
+        <v>42.93</v>
       </c>
     </row>
     <row r="18">
@@ -2851,7 +2856,7 @@
         <v>4.02</v>
       </c>
       <c r="F20" t="n">
-        <v>6.89</v>
+        <v>6.86</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -2869,7 +2874,7 @@
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>42.76</v>
+        <v>42.73</v>
       </c>
     </row>
     <row r="21">
@@ -2971,7 +2976,7 @@
         <v>2.23</v>
       </c>
       <c r="F23" t="n">
-        <v>9.9</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -2989,7 +2994,7 @@
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>42.01</v>
+        <v>41.99</v>
       </c>
     </row>
     <row r="24">
@@ -3011,7 +3016,7 @@
         <v>6.87</v>
       </c>
       <c r="F24" t="n">
-        <v>3.07</v>
+        <v>3.06</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -3029,7 +3034,7 @@
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>41.9</v>
+        <v>41.89</v>
       </c>
     </row>
     <row r="25">
@@ -3291,7 +3296,7 @@
         <v>0.8</v>
       </c>
       <c r="F31" t="n">
-        <v>6.57</v>
+        <v>6.51</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -3309,7 +3314,7 @@
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>30.94</v>
+        <v>30.88</v>
       </c>
     </row>
   </sheetData>
@@ -3578,14 +3583,14 @@
         <v>7.362826272720001</v>
       </c>
       <c r="X2" t="n">
-        <v>0.00243</v>
+        <v>0.00242</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.79989</v>
+        <v>0.7999000000000001</v>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>2026-08-22T03:48:40.386171+00:00</t>
+          <t>2026-08-22T13:18:15.909203+00:00</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
@@ -3628,7 +3633,7 @@
         <v>0.36</v>
       </c>
       <c r="I3" t="n">
-        <v>13.49</v>
+        <v>13.41</v>
       </c>
       <c r="J3" t="n">
         <v>0.774</v>
@@ -3649,7 +3654,7 @@
         <v>0.60344005</v>
       </c>
       <c r="Q3" t="n">
-        <v>31.05634</v>
+        <v>31.241611</v>
       </c>
       <c r="R3" t="n">
         <v>0.48933163</v>
@@ -3667,17 +3672,17 @@
         <v>0.1684963370842598</v>
       </c>
       <c r="W3" t="n">
-        <v>0.8632972961454419</v>
+        <v>0.8632971696944793</v>
       </c>
       <c r="X3" t="n">
         <v>0.00013</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.155</v>
+        <v>0.15498</v>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>2026-08-22T03:48:43.597709+00:00</t>
+          <t>2026-08-22T13:18:19.660011+00:00</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
@@ -3720,7 +3725,7 @@
         <v>1.57</v>
       </c>
       <c r="I4" t="n">
-        <v>2.49</v>
+        <v>2.51</v>
       </c>
       <c r="J4" t="n">
         <v>3.432</v>
@@ -3741,7 +3746,7 @@
         <v>0.35661998</v>
       </c>
       <c r="Q4" t="n">
-        <v>92.5984</v>
+        <v>91.86056000000001</v>
       </c>
       <c r="R4" t="n">
         <v>32.2041</v>
@@ -3765,11 +3770,11 @@
         <v>0.108789995</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.7415</v>
+        <v>0.74186</v>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>2026-08-22T03:48:40.946328+00:00</t>
+          <t>2026-08-22T13:18:16.606575+00:00</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
@@ -3812,7 +3817,7 @@
         <v>0.377</v>
       </c>
       <c r="I5" t="n">
-        <v>3.24</v>
+        <v>3.17</v>
       </c>
       <c r="J5" t="n">
         <v>0.357</v>
@@ -3833,7 +3838,7 @@
         <v>0.45393002</v>
       </c>
       <c r="Q5" t="n">
-        <v>58.225307</v>
+        <v>59.511036</v>
       </c>
       <c r="R5" t="n">
         <v>22.572294</v>
@@ -3861,7 +3866,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>2026-08-22T03:48:44.788885+00:00</t>
+          <t>2026-08-22T13:18:20.952402+00:00</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
@@ -3953,7 +3958,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>2026-08-22T03:48:39.183355+00:00</t>
+          <t>2026-08-22T13:18:14.597170+00:00</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr">
@@ -3996,7 +4001,7 @@
         <v>1.039</v>
       </c>
       <c r="I7" t="n">
-        <v>7.14</v>
+        <v>7.29</v>
       </c>
       <c r="J7" t="n">
         <v>3.858</v>
@@ -4017,7 +4022,7 @@
         <v>0.33161</v>
       </c>
       <c r="Q7" t="n">
-        <v>52.62465</v>
+        <v>51.541836</v>
       </c>
       <c r="R7" t="n">
         <v>13.159287</v>
@@ -4045,7 +4050,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>2026-08-22T03:48:41.288517+00:00</t>
+          <t>2026-08-22T13:18:16.911485+00:00</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr">
@@ -4057,12 +4062,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>DELL</t>
+          <t>NVDA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Dell Technologies Inc.</t>
+          <t>NVIDIA Corporation</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -4072,72 +4077,72 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Computer Hardware</t>
+          <t>Semiconductors</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>285646618624</v>
+        <v>5200733011968</v>
       </c>
       <c r="F8" t="n">
-        <v>442.0799865722656</v>
+        <v>214.7200012207031</v>
       </c>
       <c r="G8" t="n">
-        <v>134001999872</v>
+        <v>253491003392</v>
       </c>
       <c r="H8" t="n">
-        <v>0.875</v>
+        <v>0.852</v>
       </c>
       <c r="I8" t="n">
-        <v>12.78</v>
+        <v>6.53</v>
       </c>
       <c r="J8" t="n">
-        <v>2.825</v>
+        <v>2.145</v>
       </c>
       <c r="K8" t="n">
-        <v>5434124800</v>
+        <v>46335873024</v>
       </c>
       <c r="M8" t="n">
-        <v>11580999680</v>
+        <v>53171998720</v>
       </c>
       <c r="N8" t="n">
-        <v>31924000768</v>
+        <v>12814000128</v>
       </c>
       <c r="O8" t="n">
-        <v>0.19212</v>
+        <v>0.74144995</v>
       </c>
       <c r="P8" t="n">
-        <v>0.08857000600000001</v>
+        <v>0.65596</v>
       </c>
       <c r="Q8" t="n">
-        <v>34.59155</v>
+        <v>32.88208</v>
       </c>
       <c r="R8" t="n">
-        <v>2.1316593</v>
+        <v>20.51644</v>
       </c>
       <c r="S8" t="n">
-        <v>52.56534016738077</v>
+        <v>112.2398839722787</v>
       </c>
       <c r="T8" t="n">
-        <v>0.0006337681915646876</v>
+        <v>0.01254363714389073</v>
       </c>
       <c r="U8" t="n">
-        <v>0.5000864673161829</v>
+        <v>-0.001670682268214541</v>
       </c>
       <c r="V8" t="n">
-        <v>2.73072935680286</v>
+        <v>0.144129303232654</v>
       </c>
       <c r="W8" t="n">
-        <v>2.50241270126798</v>
+        <v>0.2287461792392489</v>
       </c>
       <c r="X8" t="n">
-        <v>0.07491</v>
+        <v>0.03991</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.75601995</v>
+        <v>0.71262</v>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>2026-08-22T03:48:45.066415+00:00</t>
+          <t>2026-08-22T13:18:14.332541+00:00</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr">
@@ -4149,12 +4154,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>NVDA</t>
+          <t>DELL</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>NVIDIA Corporation</t>
+          <t>Dell Technologies Inc.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -4164,72 +4169,72 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Semiconductors</t>
+          <t>Computer Hardware</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5200733011968</v>
+        <v>285646618624</v>
       </c>
       <c r="F9" t="n">
-        <v>214.7200012207031</v>
+        <v>442.0799865722656</v>
       </c>
       <c r="G9" t="n">
-        <v>253491003392</v>
+        <v>134001999872</v>
       </c>
       <c r="H9" t="n">
-        <v>0.852</v>
+        <v>0.875</v>
       </c>
       <c r="I9" t="n">
-        <v>6.46</v>
+        <v>0.49</v>
       </c>
       <c r="J9" t="n">
-        <v>2.145</v>
+        <v>2.825</v>
       </c>
       <c r="K9" t="n">
-        <v>46335873024</v>
+        <v>5434124800</v>
       </c>
       <c r="M9" t="n">
-        <v>53171998720</v>
+        <v>11580999680</v>
       </c>
       <c r="N9" t="n">
-        <v>12814000128</v>
+        <v>31924000768</v>
       </c>
       <c r="O9" t="n">
-        <v>0.74144995</v>
+        <v>0.19212</v>
       </c>
       <c r="P9" t="n">
-        <v>0.65596</v>
+        <v>0.08857000600000001</v>
       </c>
       <c r="Q9" t="n">
-        <v>33.23839</v>
+        <v>902.20404</v>
       </c>
       <c r="R9" t="n">
-        <v>20.51644</v>
+        <v>2.1316593</v>
       </c>
       <c r="S9" t="n">
-        <v>112.2398839722787</v>
+        <v>52.56534016738077</v>
       </c>
       <c r="T9" t="n">
-        <v>0.01254363714389073</v>
+        <v>0.0006337681915646876</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.001670682268214541</v>
+        <v>0.5000864673161829</v>
       </c>
       <c r="V9" t="n">
-        <v>0.144129303232654</v>
+        <v>2.73072935680286</v>
       </c>
       <c r="W9" t="n">
-        <v>0.2287461792392489</v>
+        <v>2.50241270126798</v>
       </c>
       <c r="X9" t="n">
-        <v>0.03991</v>
+        <v>0.07491</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.71266</v>
+        <v>0.75602996</v>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>2026-08-22T03:48:38.927421+00:00</t>
+          <t>2026-08-22T13:18:21.264830+00:00</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr">
@@ -4272,7 +4277,7 @@
         <v>0.173</v>
       </c>
       <c r="I10" t="n">
-        <v>0.62</v>
+        <v>0.6</v>
       </c>
       <c r="K10" t="n">
         <v>511553632</v>
@@ -4290,7 +4295,7 @@
         <v>0.07274</v>
       </c>
       <c r="Q10" t="n">
-        <v>26.435482</v>
+        <v>27.316664</v>
       </c>
       <c r="R10" t="n">
         <v>5.0779395</v>
@@ -4318,7 +4323,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>2026-08-22T03:48:47.624196+00:00</t>
+          <t>2026-08-22T13:18:23.680623+00:00</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr">
@@ -4361,7 +4366,7 @@
         <v>0.501</v>
       </c>
       <c r="I11" t="n">
-        <v>3.98</v>
+        <v>3.93</v>
       </c>
       <c r="J11" t="n">
         <v>1.595</v>
@@ -4382,7 +4387,7 @@
         <v>0.1725</v>
       </c>
       <c r="Q11" t="n">
-        <v>118.907036</v>
+        <v>120.419846</v>
       </c>
       <c r="R11" t="n">
         <v>18.704</v>
@@ -4403,14 +4408,14 @@
         <v>1.890782362663681</v>
       </c>
       <c r="X11" t="n">
-        <v>0.0043</v>
+        <v>0.00429</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.75376</v>
+        <v>0.75372005</v>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>2026-08-22T03:48:39.450675+00:00</t>
+          <t>2026-08-22T13:18:14.892918+00:00</t>
         </is>
       </c>
       <c r="AD11" t="inlineStr">
@@ -4453,7 +4458,7 @@
         <v>0.242</v>
       </c>
       <c r="I12" t="n">
-        <v>20.17</v>
+        <v>19.93</v>
       </c>
       <c r="J12" t="n">
         <v>2.94</v>
@@ -4474,7 +4479,7 @@
         <v>0.34033</v>
       </c>
       <c r="Q12" t="n">
-        <v>17.095688</v>
+        <v>17.301556</v>
       </c>
       <c r="R12" t="n">
         <v>9.458282000000001</v>
@@ -4498,11 +4503,11 @@
         <v>0.01596</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.8107499500000001</v>
+        <v>0.81073</v>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>2026-08-22T03:48:42.448193+00:00</t>
+          <t>2026-08-22T13:18:18.257768+00:00</t>
         </is>
       </c>
       <c r="AD12" t="inlineStr">
@@ -4545,19 +4550,19 @@
         <v>0.248</v>
       </c>
       <c r="I13" t="n">
-        <v>11.52</v>
+        <v>11.57</v>
       </c>
       <c r="J13" t="n">
         <v>0.428</v>
       </c>
       <c r="K13" t="n">
-        <v>3195375104</v>
+        <v>3075375104</v>
       </c>
       <c r="M13" t="n">
         <v>9233000448</v>
       </c>
       <c r="N13" t="n">
-        <v>6544000000</v>
+        <v>7345999872</v>
       </c>
       <c r="O13" t="n">
         <v>0.49398</v>
@@ -4566,13 +4571,13 @@
         <v>0.33736</v>
       </c>
       <c r="Q13" t="n">
-        <v>42.73611</v>
+        <v>42.55143</v>
       </c>
       <c r="R13" t="n">
         <v>12.67575</v>
       </c>
       <c r="S13" t="n">
-        <v>122.3274534218816</v>
+        <v>127.1006254461765</v>
       </c>
       <c r="T13" t="n">
         <v>-0.1102569665921038</v>
@@ -4584,17 +4589,17 @@
         <v>0.3342865245955684</v>
       </c>
       <c r="W13" t="n">
-        <v>2.097116106946919</v>
+        <v>2.097116404241915</v>
       </c>
       <c r="X13" t="n">
         <v>0.00331</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.8653999999999999</v>
+        <v>0.86535</v>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>2026-08-22T03:48:40.029242+00:00</t>
+          <t>2026-08-22T13:18:15.560000+00:00</t>
         </is>
       </c>
       <c r="AD13" t="inlineStr">
@@ -4637,7 +4642,7 @@
         <v>0.356</v>
       </c>
       <c r="I14" t="n">
-        <v>0.52</v>
+        <v>0.49</v>
       </c>
       <c r="J14" t="n">
         <v>14.985</v>
@@ -4658,7 +4663,7 @@
         <v>0.00666</v>
       </c>
       <c r="Q14" t="n">
-        <v>453.1154</v>
+        <v>480.85712</v>
       </c>
       <c r="R14" t="n">
         <v>21.328741</v>
@@ -4686,7 +4691,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>2026-08-22T03:48:46.346790+00:00</t>
+          <t>2026-08-22T13:18:22.523323+00:00</t>
         </is>
       </c>
       <c r="AD14" t="inlineStr">
@@ -4729,7 +4734,7 @@
         <v>0.479</v>
       </c>
       <c r="I15" t="n">
-        <v>6.08</v>
+        <v>6.01</v>
       </c>
       <c r="J15" t="n">
         <v>0.854</v>
@@ -4750,7 +4755,7 @@
         <v>0.48988</v>
       </c>
       <c r="Q15" t="n">
-        <v>60.60033</v>
+        <v>61.306156</v>
       </c>
       <c r="R15" t="n">
         <v>23.22839</v>
@@ -4765,7 +4770,7 @@
         <v>-0.1089169343844046</v>
       </c>
       <c r="V15" t="n">
-        <v>0.1072406716938052</v>
+        <v>0.1072405701495147</v>
       </c>
       <c r="W15" t="n">
         <v>0.2815942361128876</v>
@@ -4774,11 +4779,11 @@
         <v>0.01948</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.80177003</v>
+        <v>0.80174005</v>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>2026-08-22T03:48:39.738255+00:00</t>
+          <t>2026-08-22T13:18:15.226556+00:00</t>
         </is>
       </c>
       <c r="AD15" t="inlineStr">
@@ -4860,11 +4865,11 @@
         <v>0.02962</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.81992996</v>
+        <v>0.81998</v>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>2026-08-22T03:48:45.897047+00:00</t>
+          <t>2026-08-22T13:18:22.186618+00:00</t>
         </is>
       </c>
       <c r="AD16" t="inlineStr">
@@ -4907,7 +4912,7 @@
         <v>0.196</v>
       </c>
       <c r="I17" t="n">
-        <v>12.36</v>
+        <v>12.44</v>
       </c>
       <c r="J17" t="n">
         <v>2.423</v>
@@ -4928,7 +4933,7 @@
         <v>0.13689</v>
       </c>
       <c r="Q17" t="n">
-        <v>20.924759</v>
+        <v>20.790194</v>
       </c>
       <c r="R17" t="n">
         <v>3.5964112</v>
@@ -4952,11 +4957,11 @@
         <v>0.088690005</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.68791</v>
+        <v>0.6879</v>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>2026-08-22T03:48:42.696669+00:00</t>
+          <t>2026-08-22T13:18:18.560097+00:00</t>
         </is>
       </c>
       <c r="AD17" t="inlineStr">
@@ -5038,11 +5043,11 @@
         <v>0.02641</v>
       </c>
       <c r="Y18" t="n">
-        <v>0.96408</v>
+        <v>0.96402</v>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>2026-08-22T03:48:47.361615+00:00</t>
+          <t>2026-08-22T13:18:23.410921+00:00</t>
         </is>
       </c>
       <c r="AD18" t="inlineStr">
@@ -5085,10 +5090,10 @@
         <v>0.359</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.62</v>
+        <v>-0.59</v>
       </c>
       <c r="K19" t="n">
-        <v>691048256</v>
+        <v>692851968</v>
       </c>
       <c r="M19" t="n">
         <v>4162798080</v>
@@ -5106,7 +5111,7 @@
         <v>41.54724</v>
       </c>
       <c r="S19" t="n">
-        <v>151.0476435150717</v>
+        <v>150.6544189017877</v>
       </c>
       <c r="T19" t="n">
         <v>0.08982081446690615</v>
@@ -5124,11 +5129,11 @@
         <v>0.00616</v>
       </c>
       <c r="Y19" t="n">
-        <v>0.90910006</v>
+        <v>0.90915</v>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>2026-08-22T03:48:46.622661+00:00</t>
+          <t>2026-08-22T13:18:22.788532+00:00</t>
         </is>
       </c>
       <c r="AD19" t="inlineStr">
@@ -5171,7 +5176,7 @@
         <v>0.36</v>
       </c>
       <c r="I20" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="J20" t="n">
         <v>1.806</v>
@@ -5192,7 +5197,7 @@
         <v>0.16982001</v>
       </c>
       <c r="Q20" t="n">
-        <v>37.107475</v>
+        <v>37.45755</v>
       </c>
       <c r="R20" t="n">
         <v>5.329536</v>
@@ -5217,7 +5222,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>2026-08-22T03:48:40.688384+00:00</t>
+          <t>2026-08-22T13:18:16.214764+00:00</t>
         </is>
       </c>
       <c r="AD20" t="inlineStr">
@@ -5305,11 +5310,11 @@
         <v>0.00269</v>
       </c>
       <c r="Y21" t="n">
-        <v>0.84406996</v>
+        <v>0.8440800000000001</v>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>2026-08-22T03:48:45.336616+00:00</t>
+          <t>2026-08-22T13:18:21.559033+00:00</t>
         </is>
       </c>
       <c r="AD21" t="inlineStr">
@@ -5401,7 +5406,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>2026-08-22T03:48:43.928452+00:00</t>
+          <t>2026-08-22T13:18:20.004228+00:00</t>
         </is>
       </c>
       <c r="AD22" t="inlineStr">
@@ -5444,7 +5449,7 @@
         <v>0.9320000000000001</v>
       </c>
       <c r="I23" t="n">
-        <v>3.33</v>
+        <v>3.26</v>
       </c>
       <c r="J23" t="n">
         <v>4.094</v>
@@ -5465,7 +5470,7 @@
         <v>0.13382</v>
       </c>
       <c r="Q23" t="n">
-        <v>11.183184</v>
+        <v>11.423313</v>
       </c>
       <c r="R23" t="n">
         <v>0.6166835000000001</v>
@@ -5490,7 +5495,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>2026-08-22T03:48:45.630249+00:00</t>
+          <t>2026-08-22T13:18:21.843909+00:00</t>
         </is>
       </c>
       <c r="AD23" t="inlineStr">
@@ -5533,7 +5538,7 @@
         <v>0.177</v>
       </c>
       <c r="I24" t="n">
-        <v>18.02</v>
+        <v>17.93</v>
       </c>
       <c r="J24" t="n">
         <v>0.317</v>
@@ -5554,7 +5559,7 @@
         <v>0.45111</v>
       </c>
       <c r="Q24" t="n">
-        <v>26.81687</v>
+        <v>26.951477</v>
       </c>
       <c r="R24" t="n">
         <v>10.813438</v>
@@ -5578,11 +5583,11 @@
         <v>0.00090000004</v>
       </c>
       <c r="Y24" t="n">
-        <v>0.75908</v>
+        <v>0.75907</v>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>2026-08-22T03:48:42.176421+00:00</t>
+          <t>2026-08-22T13:18:17.966588+00:00</t>
         </is>
       </c>
       <c r="AD24" t="inlineStr">
@@ -5667,11 +5672,11 @@
         <v>0.0076</v>
       </c>
       <c r="Y25" t="n">
-        <v>0.84957004</v>
+        <v>0.84946</v>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>2026-08-22T03:48:41.875535+00:00</t>
+          <t>2026-08-22T13:18:17.601334+00:00</t>
         </is>
       </c>
       <c r="AD25" t="inlineStr">
@@ -5714,7 +5719,7 @@
         <v>0.224</v>
       </c>
       <c r="I26" t="n">
-        <v>0.95</v>
+        <v>0.97</v>
       </c>
       <c r="J26" t="n">
         <v>1.083</v>
@@ -5735,7 +5740,7 @@
         <v>0.07603</v>
       </c>
       <c r="Q26" t="n">
-        <v>256.1263</v>
+        <v>250.84537</v>
       </c>
       <c r="R26" t="n">
         <v>50.40059</v>
@@ -5759,11 +5764,11 @@
         <v>0.0007</v>
       </c>
       <c r="Y26" t="n">
-        <v>0.96259004</v>
+        <v>0.96261</v>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>2026-08-22T03:48:44.202301+00:00</t>
+          <t>2026-08-22T13:18:20.285917+00:00</t>
         </is>
       </c>
       <c r="AD26" t="inlineStr">
@@ -5806,7 +5811,7 @@
         <v>0.28</v>
       </c>
       <c r="I27" t="n">
-        <v>26.73</v>
+        <v>26.56</v>
       </c>
       <c r="J27" t="n">
         <v>-0.134</v>
@@ -5827,7 +5832,7 @@
         <v>0.34827</v>
       </c>
       <c r="Q27" t="n">
-        <v>20.572392</v>
+        <v>20.704067</v>
       </c>
       <c r="R27" t="n">
         <v>6.137534</v>
@@ -5845,17 +5850,17 @@
         <v>-0.1456296261876776</v>
       </c>
       <c r="W27" t="n">
-        <v>-0.2535483859208238</v>
+        <v>-0.253548447765114</v>
       </c>
       <c r="X27" t="n">
         <v>0.00148</v>
       </c>
       <c r="Y27" t="n">
-        <v>0.79107004</v>
+        <v>0.79103994</v>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>2026-08-22T03:48:42.966437+00:00</t>
+          <t>2026-08-22T13:18:18.955562+00:00</t>
         </is>
       </c>
       <c r="AD27" t="inlineStr">
@@ -5934,14 +5939,14 @@
         <v>0.8543206113126569</v>
       </c>
       <c r="X28" t="n">
-        <v>0.0147</v>
+        <v>0.014680001</v>
       </c>
       <c r="Y28" t="n">
         <v>0.76635003</v>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>2026-08-22T03:48:41.587467+00:00</t>
+          <t>2026-08-22T13:18:17.265895+00:00</t>
         </is>
       </c>
       <c r="AD28" t="inlineStr">
@@ -5984,7 +5989,7 @@
         <v>0.276</v>
       </c>
       <c r="I29" t="n">
-        <v>2.91</v>
+        <v>2.92</v>
       </c>
       <c r="J29" t="n">
         <v>-0.804</v>
@@ -6005,7 +6010,7 @@
         <v>0.14479999</v>
       </c>
       <c r="Q29" t="n">
-        <v>81.45704000000001</v>
+        <v>81.17807999999999</v>
       </c>
       <c r="R29" t="n">
         <v>24.406502</v>
@@ -6023,17 +6028,17 @@
         <v>1.979740667578479</v>
       </c>
       <c r="W29" t="n">
-        <v>2.335838148861586</v>
+        <v>2.335837790700546</v>
       </c>
       <c r="X29" t="n">
         <v>0.00494</v>
       </c>
       <c r="Y29" t="n">
-        <v>0.82133</v>
+        <v>0.82137</v>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>2026-08-22T03:48:44.495431+00:00</t>
+          <t>2026-08-22T13:18:20.652315+00:00</t>
         </is>
       </c>
       <c r="AD29" t="inlineStr">
@@ -6076,7 +6081,7 @@
         <v>0.24</v>
       </c>
       <c r="I30" t="n">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="J30" t="n">
         <v>-0.219</v>
@@ -6097,7 +6102,7 @@
         <v>0.04063</v>
       </c>
       <c r="Q30" t="n">
-        <v>81.31645</v>
+        <v>79.80124000000001</v>
       </c>
       <c r="R30" t="n">
         <v>9.016465999999999</v>
@@ -6125,7 +6130,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>2026-08-22T03:48:47.021627+00:00</t>
+          <t>2026-08-22T13:18:23.099018+00:00</t>
         </is>
       </c>
       <c r="AD30" t="inlineStr">
@@ -6168,7 +6173,7 @@
         <v>0.206</v>
       </c>
       <c r="I31" t="n">
-        <v>6.01</v>
+        <v>5.83</v>
       </c>
       <c r="J31" t="n">
         <v>0.219</v>
@@ -6189,7 +6194,7 @@
         <v>0.36202</v>
       </c>
       <c r="Q31" t="n">
-        <v>24.371048</v>
+        <v>25.123499</v>
       </c>
       <c r="R31" t="n">
         <v>6.2636786</v>
@@ -6210,11 +6215,11 @@
         <v>0.40498</v>
       </c>
       <c r="Y31" t="n">
-        <v>0.45830002</v>
+        <v>0.45828</v>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>2026-08-22T03:48:43.288740+00:00</t>
+          <t>2026-08-22T13:18:19.318775+00:00</t>
         </is>
       </c>
       <c r="AD31" t="inlineStr">
@@ -6478,7 +6483,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>DELL</t>
+          <t>NVDA</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -6507,7 +6512,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>NVDA</t>
+          <t>DELL</t>
         </is>
       </c>
       <c r="B9" t="n">

--- a/reports/investment_dashboard.xlsx
+++ b/reports/investment_dashboard.xlsx
@@ -525,16 +525,16 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>MU</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Micron Technology, Inc.</t>
+          <t>Taiwan Semiconductor Manufacturing Company Limited</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>57.27</v>
+        <v>55.66</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>966.780029296875</v>
+        <v>418.9500122070312</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -550,24 +550,19 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>84.2</v>
+        <v>100</v>
       </c>
       <c r="I2" t="n">
-        <v>88.2</v>
+        <v>100</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Revenue Growth; Earnings Fcf; Balance Sheet</t>
+          <t>Revenue Growth; Earnings Fcf; Balance Sheet; Valuation</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
           <t>Industry Growth; Competitive Advantage; Catalysts; Inflation Resilience</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>High market sensitivity / beta</t>
         </is>
       </c>
     </row>
@@ -577,16 +572,16 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>MU</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Taiwan Semiconductor Manufacturing Company Limited</t>
+          <t>Micron Technology, Inc.</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>55.66</v>
+        <v>55.05</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -594,7 +589,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>418.9500122070312</v>
+        <v>966.780029296875</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -602,19 +597,24 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="I3" t="n">
         <v>100</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Revenue Growth; Earnings Fcf; Balance Sheet; Valuation</t>
+          <t>Revenue Growth; Earnings Fcf; Balance Sheet</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
           <t>Industry Growth; Competitive Advantage; Catalysts; Inflation Resilience</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>High market sensitivity / beta</t>
         </is>
       </c>
     </row>
@@ -2120,7 +2120,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>MU</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -2133,19 +2133,19 @@
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>9.02</v>
+        <v>8.84</v>
       </c>
       <c r="F2" t="n">
-        <v>7.04</v>
+        <v>8.67</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>7.71</v>
+        <v>5.46</v>
       </c>
       <c r="I2" t="n">
-        <v>3.5</v>
+        <v>2.69</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -2154,13 +2154,13 @@
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>57.27</v>
+        <v>55.66</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>MU</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -2173,19 +2173,19 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>8.84</v>
+        <v>9.02</v>
       </c>
       <c r="F3" t="n">
-        <v>8.67</v>
+        <v>4.82</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>5.46</v>
+        <v>7.71</v>
       </c>
       <c r="I3" t="n">
-        <v>2.69</v>
+        <v>3.5</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -2194,7 +2194,7 @@
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>55.66</v>
+        <v>55.05</v>
       </c>
     </row>
     <row r="4">
@@ -3354,7 +3354,7 @@
     <col width="23" customWidth="1" min="20" max="20"/>
     <col width="23" customWidth="1" min="21" max="21"/>
     <col width="22" customWidth="1" min="22" max="22"/>
-    <col width="22" customWidth="1" min="23" max="23"/>
+    <col width="21" customWidth="1" min="23" max="23"/>
     <col width="18" customWidth="1" min="24" max="24"/>
     <col width="24" customWidth="1" min="25" max="25"/>
     <col width="17" customWidth="1" min="26" max="26"/>
@@ -3519,12 +3519,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>MU</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Micron Technology, Inc.</t>
+          <t>Taiwan Semiconductor Manufacturing Company Limited</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -3537,60 +3537,69 @@
           <t>Semiconductors</t>
         </is>
       </c>
+      <c r="E2" t="n">
+        <v>2172873342976</v>
+      </c>
       <c r="F2" t="n">
-        <v>966.780029296875</v>
+        <v>418.9500122070312</v>
       </c>
       <c r="G2" t="n">
-        <v>90273996800</v>
+        <v>4440492343296</v>
       </c>
       <c r="H2" t="n">
-        <v>3.457</v>
+        <v>0.36</v>
       </c>
       <c r="I2" t="n">
-        <v>44.23</v>
+        <v>13.41</v>
       </c>
       <c r="J2" t="n">
-        <v>13.685</v>
+        <v>0.774</v>
       </c>
       <c r="K2" t="n">
-        <v>7639499776</v>
+        <v>730826014720</v>
       </c>
       <c r="M2" t="n">
-        <v>26022000640</v>
+        <v>3518010228736</v>
       </c>
       <c r="N2" t="n">
-        <v>6376000000</v>
+        <v>1068558516224</v>
       </c>
       <c r="O2" t="n">
-        <v>0.7256899999999999</v>
+        <v>0.6423</v>
       </c>
       <c r="P2" t="n">
-        <v>0.80370003</v>
+        <v>0.60344005</v>
       </c>
       <c r="Q2" t="n">
-        <v>21.858015</v>
+        <v>31.241611</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0.48933163</v>
+      </c>
+      <c r="S2" t="n">
+        <v>2.97317459861974</v>
       </c>
       <c r="T2" t="n">
-        <v>0.007608338867642228</v>
+        <v>-0.005365445487747644</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2875215850577266</v>
+        <v>0.03809732083456407</v>
       </c>
       <c r="V2" t="n">
-        <v>1.317802614597143</v>
+        <v>0.1684963370842598</v>
       </c>
       <c r="W2" t="n">
-        <v>7.362826272720001</v>
+        <v>0.8632971696944793</v>
       </c>
       <c r="X2" t="n">
-        <v>0.00242</v>
+        <v>0.00013</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.7999000000000001</v>
+        <v>0.15498</v>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>2026-08-22T13:18:15.909203+00:00</t>
+          <t>2026-08-22T13:32:15.180961+00:00</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
@@ -3602,12 +3611,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>MU</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Taiwan Semiconductor Manufacturing Company Limited</t>
+          <t>Micron Technology, Inc.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -3621,68 +3630,68 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2172873342976</v>
+        <v>1091874717696</v>
       </c>
       <c r="F3" t="n">
-        <v>418.9500122070312</v>
+        <v>966.780029296875</v>
       </c>
       <c r="G3" t="n">
-        <v>4440492343296</v>
+        <v>90273996800</v>
       </c>
       <c r="H3" t="n">
-        <v>0.36</v>
+        <v>3.457</v>
       </c>
       <c r="I3" t="n">
-        <v>13.41</v>
+        <v>44.23</v>
       </c>
       <c r="J3" t="n">
-        <v>0.774</v>
+        <v>13.685</v>
       </c>
       <c r="K3" t="n">
-        <v>730826014720</v>
+        <v>7639499776</v>
       </c>
       <c r="M3" t="n">
-        <v>3518010228736</v>
+        <v>26022000640</v>
       </c>
       <c r="N3" t="n">
-        <v>1068558516224</v>
+        <v>6376000000</v>
       </c>
       <c r="O3" t="n">
-        <v>0.6423</v>
+        <v>0.7256899999999999</v>
       </c>
       <c r="P3" t="n">
-        <v>0.60344005</v>
+        <v>0.80370003</v>
       </c>
       <c r="Q3" t="n">
-        <v>31.241611</v>
+        <v>21.858015</v>
       </c>
       <c r="R3" t="n">
-        <v>0.48933163</v>
+        <v>12.0951185</v>
       </c>
       <c r="S3" t="n">
-        <v>2.97317459861974</v>
+        <v>142.924896879531</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.005365445487747644</v>
+        <v>0.007608338867642228</v>
       </c>
       <c r="U3" t="n">
-        <v>0.03809732083456407</v>
+        <v>0.2875215850577266</v>
       </c>
       <c r="V3" t="n">
-        <v>0.1684963370842598</v>
+        <v>1.317802614597143</v>
       </c>
       <c r="W3" t="n">
-        <v>0.8632971696944793</v>
+        <v>7.362827376540883</v>
       </c>
       <c r="X3" t="n">
-        <v>0.00013</v>
+        <v>0.00242</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.15498</v>
+        <v>0.7999000000000001</v>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>2026-08-22T13:18:19.660011+00:00</t>
+          <t>2026-08-22T13:32:12.101074+00:00</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
@@ -3774,7 +3783,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>2026-08-22T13:18:16.606575+00:00</t>
+          <t>2026-08-22T13:32:12.596342+00:00</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
@@ -3866,7 +3875,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>2026-08-22T13:18:20.952402+00:00</t>
+          <t>2026-08-22T13:32:16.356918+00:00</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
@@ -3958,7 +3967,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>2026-08-22T13:18:14.597170+00:00</t>
+          <t>2026-08-22T13:32:10.905049+00:00</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr">
@@ -4050,7 +4059,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>2026-08-22T13:18:16.911485+00:00</t>
+          <t>2026-08-22T13:32:12.878000+00:00</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr">
@@ -4142,7 +4151,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>2026-08-22T13:18:14.332541+00:00</t>
+          <t>2026-08-22T13:32:10.658878+00:00</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr">
@@ -4234,7 +4243,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>2026-08-22T13:18:21.264830+00:00</t>
+          <t>2026-08-22T13:32:16.618828+00:00</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr">
@@ -4323,7 +4332,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>2026-08-22T13:18:23.680623+00:00</t>
+          <t>2026-08-22T13:32:18.698682+00:00</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr">
@@ -4415,7 +4424,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>2026-08-22T13:18:14.892918+00:00</t>
+          <t>2026-08-22T13:32:11.147857+00:00</t>
         </is>
       </c>
       <c r="AD11" t="inlineStr">
@@ -4507,7 +4516,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>2026-08-22T13:18:18.257768+00:00</t>
+          <t>2026-08-22T13:32:13.976160+00:00</t>
         </is>
       </c>
       <c r="AD12" t="inlineStr">
@@ -4589,7 +4598,7 @@
         <v>0.3342865245955684</v>
       </c>
       <c r="W13" t="n">
-        <v>2.097116404241915</v>
+        <v>2.097116106946919</v>
       </c>
       <c r="X13" t="n">
         <v>0.00331</v>
@@ -4599,7 +4608,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>2026-08-22T13:18:15.560000+00:00</t>
+          <t>2026-08-22T13:32:11.714983+00:00</t>
         </is>
       </c>
       <c r="AD13" t="inlineStr">
@@ -4691,7 +4700,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>2026-08-22T13:18:22.523323+00:00</t>
+          <t>2026-08-22T13:32:17.654081+00:00</t>
         </is>
       </c>
       <c r="AD14" t="inlineStr">
@@ -4734,7 +4743,7 @@
         <v>0.479</v>
       </c>
       <c r="I15" t="n">
-        <v>6.01</v>
+        <v>6.08</v>
       </c>
       <c r="J15" t="n">
         <v>0.854</v>
@@ -4755,7 +4764,7 @@
         <v>0.48988</v>
       </c>
       <c r="Q15" t="n">
-        <v>61.306156</v>
+        <v>60.60033</v>
       </c>
       <c r="R15" t="n">
         <v>23.22839</v>
@@ -4783,7 +4792,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>2026-08-22T13:18:15.226556+00:00</t>
+          <t>2026-08-22T13:32:11.421107+00:00</t>
         </is>
       </c>
       <c r="AD15" t="inlineStr">
@@ -4869,7 +4878,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>2026-08-22T13:18:22.186618+00:00</t>
+          <t>2026-08-22T13:32:17.392002+00:00</t>
         </is>
       </c>
       <c r="AD16" t="inlineStr">
@@ -4961,7 +4970,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>2026-08-22T13:18:18.560097+00:00</t>
+          <t>2026-08-22T13:32:14.227196+00:00</t>
         </is>
       </c>
       <c r="AD17" t="inlineStr">
@@ -5047,7 +5056,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>2026-08-22T13:18:23.410921+00:00</t>
+          <t>2026-08-22T13:32:18.432365+00:00</t>
         </is>
       </c>
       <c r="AD18" t="inlineStr">
@@ -5133,7 +5142,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>2026-08-22T13:18:22.788532+00:00</t>
+          <t>2026-08-22T13:32:17.915490+00:00</t>
         </is>
       </c>
       <c r="AD19" t="inlineStr">
@@ -5222,7 +5231,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>2026-08-22T13:18:16.214764+00:00</t>
+          <t>2026-08-22T13:32:12.344436+00:00</t>
         </is>
       </c>
       <c r="AD20" t="inlineStr">
@@ -5265,7 +5274,7 @@
         <v>0.241</v>
       </c>
       <c r="I21" t="n">
-        <v>4.37</v>
+        <v>4.43</v>
       </c>
       <c r="J21" t="n">
         <v>0.53</v>
@@ -5286,7 +5295,7 @@
         <v>0.20362</v>
       </c>
       <c r="Q21" t="n">
-        <v>59.942795</v>
+        <v>59.13093</v>
       </c>
       <c r="R21" t="n">
         <v>8.784945499999999</v>
@@ -5314,7 +5323,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>2026-08-22T13:18:21.559033+00:00</t>
+          <t>2026-08-22T13:32:16.891173+00:00</t>
         </is>
       </c>
       <c r="AD21" t="inlineStr">
@@ -5406,7 +5415,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>2026-08-22T13:18:20.004228+00:00</t>
+          <t>2026-08-22T13:32:15.542191+00:00</t>
         </is>
       </c>
       <c r="AD22" t="inlineStr">
@@ -5495,7 +5504,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>2026-08-22T13:18:21.843909+00:00</t>
+          <t>2026-08-22T13:32:17.135064+00:00</t>
         </is>
       </c>
       <c r="AD23" t="inlineStr">
@@ -5577,7 +5586,7 @@
         <v>0.2176838288473297</v>
       </c>
       <c r="W24" t="n">
-        <v>-0.03376181497550057</v>
+        <v>-0.0337617560157526</v>
       </c>
       <c r="X24" t="n">
         <v>0.00090000004</v>
@@ -5587,7 +5596,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>2026-08-22T13:18:17.966588+00:00</t>
+          <t>2026-08-22T13:32:13.675475+00:00</t>
         </is>
       </c>
       <c r="AD24" t="inlineStr">
@@ -5676,7 +5685,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>2026-08-22T13:18:17.601334+00:00</t>
+          <t>2026-08-22T13:32:13.379423+00:00</t>
         </is>
       </c>
       <c r="AD25" t="inlineStr">
@@ -5768,7 +5777,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>2026-08-22T13:18:20.285917+00:00</t>
+          <t>2026-08-22T13:32:15.793688+00:00</t>
         </is>
       </c>
       <c r="AD26" t="inlineStr">
@@ -5860,7 +5869,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>2026-08-22T13:18:18.955562+00:00</t>
+          <t>2026-08-22T13:32:14.496181+00:00</t>
         </is>
       </c>
       <c r="AD27" t="inlineStr">
@@ -5946,7 +5955,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>2026-08-22T13:18:17.265895+00:00</t>
+          <t>2026-08-22T13:32:13.127905+00:00</t>
         </is>
       </c>
       <c r="AD28" t="inlineStr">
@@ -6028,7 +6037,7 @@
         <v>1.979740667578479</v>
       </c>
       <c r="W29" t="n">
-        <v>2.335837790700546</v>
+        <v>2.335838148861586</v>
       </c>
       <c r="X29" t="n">
         <v>0.00494</v>
@@ -6038,7 +6047,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>2026-08-22T13:18:20.652315+00:00</t>
+          <t>2026-08-22T13:32:16.075473+00:00</t>
         </is>
       </c>
       <c r="AD29" t="inlineStr">
@@ -6130,7 +6139,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>2026-08-22T13:18:23.099018+00:00</t>
+          <t>2026-08-22T13:32:18.175205+00:00</t>
         </is>
       </c>
       <c r="AD30" t="inlineStr">
@@ -6219,7 +6228,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>2026-08-22T13:18:19.318775+00:00</t>
+          <t>2026-08-22T13:32:14.800056+00:00</t>
         </is>
       </c>
       <c r="AD31" t="inlineStr">
@@ -6247,7 +6256,7 @@
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
@@ -6304,27 +6313,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>MU</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>84.2</v>
+        <v>100</v>
       </c>
       <c r="C2" t="n">
-        <v>88.2</v>
+        <v>100</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>MODERATE</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>price_to_sales, price_to_fcf</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -6338,11 +6342,11 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>MU</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="C3" t="n">
         <v>100</v>
@@ -6353,7 +6357,7 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -7290,11 +7294,11 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>MU</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>57.27</v>
+        <v>55.66</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -7307,7 +7311,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>84.2</v>
+        <v>100</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>

--- a/reports/investment_dashboard.xlsx
+++ b/reports/investment_dashboard.xlsx
@@ -525,16 +525,16 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>MU</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Taiwan Semiconductor Manufacturing Company Limited</t>
+          <t>Micron Technology, Inc.</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>55.66</v>
+        <v>57.27</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>418.9500122070312</v>
+        <v>966.780029296875</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -550,19 +550,24 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>100</v>
+        <v>84.2</v>
       </c>
       <c r="I2" t="n">
-        <v>100</v>
+        <v>88.2</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Revenue Growth; Earnings Fcf; Balance Sheet; Valuation</t>
+          <t>Revenue Growth; Earnings Fcf; Balance Sheet</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
           <t>Industry Growth; Competitive Advantage; Catalysts; Inflation Resilience</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>High market sensitivity / beta</t>
         </is>
       </c>
     </row>
@@ -572,16 +577,16 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>MU</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Micron Technology, Inc.</t>
+          <t>Taiwan Semiconductor Manufacturing Company Limited</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>55.05</v>
+        <v>55.66</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -589,7 +594,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>966.780029296875</v>
+        <v>418.9500122070312</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -597,24 +602,19 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="I3" t="n">
         <v>100</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Revenue Growth; Earnings Fcf; Balance Sheet</t>
+          <t>Revenue Growth; Earnings Fcf; Balance Sheet; Valuation</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
           <t>Industry Growth; Competitive Advantage; Catalysts; Inflation Resilience</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>High market sensitivity / beta</t>
         </is>
       </c>
     </row>
@@ -2120,7 +2120,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>MU</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -2133,19 +2133,19 @@
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>8.84</v>
+        <v>9.02</v>
       </c>
       <c r="F2" t="n">
-        <v>8.67</v>
+        <v>7.04</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>5.46</v>
+        <v>7.71</v>
       </c>
       <c r="I2" t="n">
-        <v>2.69</v>
+        <v>3.5</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -2154,13 +2154,13 @@
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>55.66</v>
+        <v>57.27</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>MU</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -2173,19 +2173,19 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>9.02</v>
+        <v>8.84</v>
       </c>
       <c r="F3" t="n">
-        <v>4.82</v>
+        <v>8.67</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>7.71</v>
+        <v>5.46</v>
       </c>
       <c r="I3" t="n">
-        <v>3.5</v>
+        <v>2.69</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -2194,7 +2194,7 @@
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>55.05</v>
+        <v>55.66</v>
       </c>
     </row>
     <row r="4">
@@ -3354,7 +3354,7 @@
     <col width="23" customWidth="1" min="20" max="20"/>
     <col width="23" customWidth="1" min="21" max="21"/>
     <col width="22" customWidth="1" min="22" max="22"/>
-    <col width="21" customWidth="1" min="23" max="23"/>
+    <col width="22" customWidth="1" min="23" max="23"/>
     <col width="18" customWidth="1" min="24" max="24"/>
     <col width="24" customWidth="1" min="25" max="25"/>
     <col width="17" customWidth="1" min="26" max="26"/>
@@ -3519,12 +3519,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>MU</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Taiwan Semiconductor Manufacturing Company Limited</t>
+          <t>Micron Technology, Inc.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -3537,69 +3537,60 @@
           <t>Semiconductors</t>
         </is>
       </c>
-      <c r="E2" t="n">
-        <v>2172873342976</v>
-      </c>
       <c r="F2" t="n">
-        <v>418.9500122070312</v>
+        <v>966.780029296875</v>
       </c>
       <c r="G2" t="n">
-        <v>4440492343296</v>
+        <v>90273996800</v>
       </c>
       <c r="H2" t="n">
-        <v>0.36</v>
+        <v>3.457</v>
       </c>
       <c r="I2" t="n">
-        <v>13.41</v>
+        <v>44.23</v>
       </c>
       <c r="J2" t="n">
-        <v>0.774</v>
+        <v>13.685</v>
       </c>
       <c r="K2" t="n">
-        <v>730826014720</v>
+        <v>7639499776</v>
       </c>
       <c r="M2" t="n">
-        <v>3518010228736</v>
+        <v>26022000640</v>
       </c>
       <c r="N2" t="n">
-        <v>1068558516224</v>
+        <v>6376000000</v>
       </c>
       <c r="O2" t="n">
-        <v>0.6423</v>
+        <v>0.7256899999999999</v>
       </c>
       <c r="P2" t="n">
-        <v>0.60344005</v>
+        <v>0.80370003</v>
       </c>
       <c r="Q2" t="n">
-        <v>31.241611</v>
-      </c>
-      <c r="R2" t="n">
-        <v>0.48933163</v>
-      </c>
-      <c r="S2" t="n">
-        <v>2.97317459861974</v>
+        <v>21.858015</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.005365445487747644</v>
+        <v>0.007608338867642228</v>
       </c>
       <c r="U2" t="n">
-        <v>0.03809732083456407</v>
+        <v>0.2875215850577266</v>
       </c>
       <c r="V2" t="n">
-        <v>0.1684963370842598</v>
+        <v>1.317802614597143</v>
       </c>
       <c r="W2" t="n">
-        <v>0.8632971696944793</v>
+        <v>7.362826824630407</v>
       </c>
       <c r="X2" t="n">
-        <v>0.00013</v>
+        <v>0.00242</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.15498</v>
+        <v>0.7999000000000001</v>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>2026-08-22T13:32:15.180961+00:00</t>
+          <t>2026-08-22T13:40:04.132239+00:00</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
@@ -3611,12 +3602,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>MU</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Micron Technology, Inc.</t>
+          <t>Taiwan Semiconductor Manufacturing Company Limited</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -3630,68 +3621,68 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1091874717696</v>
+        <v>2172873342976</v>
       </c>
       <c r="F3" t="n">
-        <v>966.780029296875</v>
+        <v>418.9500122070312</v>
       </c>
       <c r="G3" t="n">
-        <v>90273996800</v>
+        <v>4440492343296</v>
       </c>
       <c r="H3" t="n">
-        <v>3.457</v>
+        <v>0.36</v>
       </c>
       <c r="I3" t="n">
-        <v>44.23</v>
+        <v>13.41</v>
       </c>
       <c r="J3" t="n">
-        <v>13.685</v>
+        <v>0.774</v>
       </c>
       <c r="K3" t="n">
-        <v>7639499776</v>
+        <v>730826014720</v>
       </c>
       <c r="M3" t="n">
-        <v>26022000640</v>
+        <v>3518010228736</v>
       </c>
       <c r="N3" t="n">
-        <v>6376000000</v>
+        <v>1068558516224</v>
       </c>
       <c r="O3" t="n">
-        <v>0.7256899999999999</v>
+        <v>0.6423</v>
       </c>
       <c r="P3" t="n">
-        <v>0.80370003</v>
+        <v>0.60344005</v>
       </c>
       <c r="Q3" t="n">
-        <v>21.858015</v>
+        <v>31.241611</v>
       </c>
       <c r="R3" t="n">
-        <v>12.0951185</v>
+        <v>0.48933163</v>
       </c>
       <c r="S3" t="n">
-        <v>142.924896879531</v>
+        <v>2.97317459861974</v>
       </c>
       <c r="T3" t="n">
-        <v>0.007608338867642228</v>
+        <v>-0.005365445487747644</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2875215850577266</v>
+        <v>0.03809732083456407</v>
       </c>
       <c r="V3" t="n">
-        <v>1.317802614597143</v>
+        <v>0.1684963370842598</v>
       </c>
       <c r="W3" t="n">
-        <v>7.362827376540883</v>
+        <v>0.8632972961454419</v>
       </c>
       <c r="X3" t="n">
-        <v>0.00242</v>
+        <v>0.00013</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.7999000000000001</v>
+        <v>0.15498</v>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>2026-08-22T13:32:12.101074+00:00</t>
+          <t>2026-08-22T13:40:08.436878+00:00</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
@@ -3783,7 +3774,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>2026-08-22T13:32:12.596342+00:00</t>
+          <t>2026-08-22T13:40:04.813255+00:00</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
@@ -3875,7 +3866,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>2026-08-22T13:32:16.356918+00:00</t>
+          <t>2026-08-22T13:40:10.709198+00:00</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
@@ -3918,7 +3909,7 @@
         <v>0.928</v>
       </c>
       <c r="I6" t="n">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="J6" t="n">
         <v>2.154</v>
@@ -3939,7 +3930,7 @@
         <v>0.47120997</v>
       </c>
       <c r="Q6" t="n">
-        <v>148.71074</v>
+        <v>153.79488</v>
       </c>
       <c r="R6" t="n">
         <v>70.24212</v>
@@ -3967,7 +3958,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>2026-08-22T13:32:10.905049+00:00</t>
+          <t>2026-08-22T13:40:02.711506+00:00</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr">
@@ -4059,7 +4050,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>2026-08-22T13:32:12.878000+00:00</t>
+          <t>2026-08-22T13:40:05.178919+00:00</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr">
@@ -4151,7 +4142,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>2026-08-22T13:32:10.658878+00:00</t>
+          <t>2026-08-22T13:40:02.416594+00:00</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr">
@@ -4243,7 +4234,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>2026-08-22T13:32:16.618828+00:00</t>
+          <t>2026-08-22T13:40:11.287004+00:00</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr">
@@ -4332,7 +4323,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>2026-08-22T13:32:18.698682+00:00</t>
+          <t>2026-08-22T13:40:14.603067+00:00</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr">
@@ -4424,7 +4415,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>2026-08-22T13:32:11.147857+00:00</t>
+          <t>2026-08-22T13:40:02.982076+00:00</t>
         </is>
       </c>
       <c r="AD11" t="inlineStr">
@@ -4516,7 +4507,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>2026-08-22T13:32:13.976160+00:00</t>
+          <t>2026-08-22T13:40:06.488419+00:00</t>
         </is>
       </c>
       <c r="AD12" t="inlineStr">
@@ -4608,7 +4599,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>2026-08-22T13:32:11.714983+00:00</t>
+          <t>2026-08-22T13:40:03.769214+00:00</t>
         </is>
       </c>
       <c r="AD13" t="inlineStr">
@@ -4700,7 +4691,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>2026-08-22T13:32:17.654081+00:00</t>
+          <t>2026-08-22T13:40:13.002731+00:00</t>
         </is>
       </c>
       <c r="AD14" t="inlineStr">
@@ -4743,7 +4734,7 @@
         <v>0.479</v>
       </c>
       <c r="I15" t="n">
-        <v>6.08</v>
+        <v>6.01</v>
       </c>
       <c r="J15" t="n">
         <v>0.854</v>
@@ -4764,7 +4755,7 @@
         <v>0.48988</v>
       </c>
       <c r="Q15" t="n">
-        <v>60.60033</v>
+        <v>61.306156</v>
       </c>
       <c r="R15" t="n">
         <v>23.22839</v>
@@ -4782,7 +4773,7 @@
         <v>0.1072405701495147</v>
       </c>
       <c r="W15" t="n">
-        <v>0.2815942361128876</v>
+        <v>0.2815941000710358</v>
       </c>
       <c r="X15" t="n">
         <v>0.01948</v>
@@ -4792,7 +4783,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>2026-08-22T13:32:11.421107+00:00</t>
+          <t>2026-08-22T13:40:03.401554+00:00</t>
         </is>
       </c>
       <c r="AD15" t="inlineStr">
@@ -4878,7 +4869,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>2026-08-22T13:32:17.392002+00:00</t>
+          <t>2026-08-22T13:40:12.575920+00:00</t>
         </is>
       </c>
       <c r="AD16" t="inlineStr">
@@ -4970,7 +4961,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>2026-08-22T13:32:14.227196+00:00</t>
+          <t>2026-08-22T13:40:06.830155+00:00</t>
         </is>
       </c>
       <c r="AD17" t="inlineStr">
@@ -5056,7 +5047,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>2026-08-22T13:32:18.432365+00:00</t>
+          <t>2026-08-22T13:40:14.020449+00:00</t>
         </is>
       </c>
       <c r="AD18" t="inlineStr">
@@ -5142,7 +5133,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>2026-08-22T13:32:17.915490+00:00</t>
+          <t>2026-08-22T13:40:13.310577+00:00</t>
         </is>
       </c>
       <c r="AD19" t="inlineStr">
@@ -5231,7 +5222,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>2026-08-22T13:32:12.344436+00:00</t>
+          <t>2026-08-22T13:40:04.481477+00:00</t>
         </is>
       </c>
       <c r="AD20" t="inlineStr">
@@ -5274,7 +5265,7 @@
         <v>0.241</v>
       </c>
       <c r="I21" t="n">
-        <v>4.43</v>
+        <v>4.37</v>
       </c>
       <c r="J21" t="n">
         <v>0.53</v>
@@ -5295,7 +5286,7 @@
         <v>0.20362</v>
       </c>
       <c r="Q21" t="n">
-        <v>59.13093</v>
+        <v>59.942795</v>
       </c>
       <c r="R21" t="n">
         <v>8.784945499999999</v>
@@ -5323,7 +5314,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>2026-08-22T13:32:16.891173+00:00</t>
+          <t>2026-08-22T13:40:11.611213+00:00</t>
         </is>
       </c>
       <c r="AD21" t="inlineStr">
@@ -5415,7 +5406,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>2026-08-22T13:32:15.542191+00:00</t>
+          <t>2026-08-22T13:40:08.821278+00:00</t>
         </is>
       </c>
       <c r="AD22" t="inlineStr">
@@ -5504,7 +5495,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>2026-08-22T13:32:17.135064+00:00</t>
+          <t>2026-08-22T13:40:12.273134+00:00</t>
         </is>
       </c>
       <c r="AD23" t="inlineStr">
@@ -5586,7 +5577,7 @@
         <v>0.2176838288473297</v>
       </c>
       <c r="W24" t="n">
-        <v>-0.0337617560157526</v>
+        <v>-0.03376187393524122</v>
       </c>
       <c r="X24" t="n">
         <v>0.00090000004</v>
@@ -5596,7 +5587,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>2026-08-22T13:32:13.675475+00:00</t>
+          <t>2026-08-22T13:40:06.165324+00:00</t>
         </is>
       </c>
       <c r="AD24" t="inlineStr">
@@ -5685,7 +5676,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>2026-08-22T13:32:13.379423+00:00</t>
+          <t>2026-08-22T13:40:05.806219+00:00</t>
         </is>
       </c>
       <c r="AD25" t="inlineStr">
@@ -5777,7 +5768,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>2026-08-22T13:32:15.793688+00:00</t>
+          <t>2026-08-22T13:40:09.573919+00:00</t>
         </is>
       </c>
       <c r="AD26" t="inlineStr">
@@ -5859,7 +5850,7 @@
         <v>-0.1456296261876776</v>
       </c>
       <c r="W27" t="n">
-        <v>-0.253548447765114</v>
+        <v>-0.2535483859208238</v>
       </c>
       <c r="X27" t="n">
         <v>0.00148</v>
@@ -5869,7 +5860,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>2026-08-22T13:32:14.496181+00:00</t>
+          <t>2026-08-22T13:40:07.189185+00:00</t>
         </is>
       </c>
       <c r="AD27" t="inlineStr">
@@ -5955,7 +5946,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>2026-08-22T13:32:13.127905+00:00</t>
+          <t>2026-08-22T13:40:05.480311+00:00</t>
         </is>
       </c>
       <c r="AD28" t="inlineStr">
@@ -6047,7 +6038,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>2026-08-22T13:32:16.075473+00:00</t>
+          <t>2026-08-22T13:40:09.931066+00:00</t>
         </is>
       </c>
       <c r="AD29" t="inlineStr">
@@ -6139,7 +6130,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>2026-08-22T13:32:18.175205+00:00</t>
+          <t>2026-08-22T13:40:13.735878+00:00</t>
         </is>
       </c>
       <c r="AD30" t="inlineStr">
@@ -6228,7 +6219,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>2026-08-22T13:32:14.800056+00:00</t>
+          <t>2026-08-22T13:40:08.068309+00:00</t>
         </is>
       </c>
       <c r="AD31" t="inlineStr">
@@ -6256,7 +6247,7 @@
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
@@ -6313,22 +6304,27 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>MU</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>100</v>
+        <v>84.2</v>
       </c>
       <c r="C2" t="n">
-        <v>100</v>
+        <v>88.2</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MODERATE</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>price_to_sales, price_to_fcf</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -6342,11 +6338,11 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>MU</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="C3" t="n">
         <v>100</v>
@@ -6357,7 +6353,7 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -7294,11 +7290,11 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>MU</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>55.66</v>
+        <v>57.27</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -7311,7 +7307,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>100</v>
+        <v>84.2</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>

--- a/reports/investment_dashboard.xlsx
+++ b/reports/investment_dashboard.xlsx
@@ -525,16 +525,16 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>MU</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Micron Technology, Inc.</t>
+          <t>Taiwan Semiconductor Manufacturing Company Limited</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>57.27</v>
+        <v>55.66</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>966.780029296875</v>
+        <v>418.9500122070312</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -550,24 +550,19 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>84.2</v>
+        <v>100</v>
       </c>
       <c r="I2" t="n">
-        <v>88.2</v>
+        <v>100</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Revenue Growth; Earnings Fcf; Balance Sheet</t>
+          <t>Revenue Growth; Earnings Fcf; Balance Sheet; Valuation</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
           <t>Industry Growth; Competitive Advantage; Catalysts; Inflation Resilience</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>High market sensitivity / beta</t>
         </is>
       </c>
     </row>
@@ -577,16 +572,16 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>MU</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Taiwan Semiconductor Manufacturing Company Limited</t>
+          <t>Micron Technology, Inc.</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>55.66</v>
+        <v>55.05</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -594,7 +589,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>418.9500122070312</v>
+        <v>966.780029296875</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -602,19 +597,24 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="I3" t="n">
         <v>100</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Revenue Growth; Earnings Fcf; Balance Sheet; Valuation</t>
+          <t>Revenue Growth; Earnings Fcf; Balance Sheet</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
           <t>Industry Growth; Competitive Advantage; Catalysts; Inflation Resilience</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>High market sensitivity / beta</t>
         </is>
       </c>
     </row>
@@ -2120,7 +2120,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>MU</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -2133,19 +2133,19 @@
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>9.02</v>
+        <v>8.84</v>
       </c>
       <c r="F2" t="n">
-        <v>7.04</v>
+        <v>8.67</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>7.71</v>
+        <v>5.46</v>
       </c>
       <c r="I2" t="n">
-        <v>3.5</v>
+        <v>2.69</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -2154,13 +2154,13 @@
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>57.27</v>
+        <v>55.66</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>MU</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -2173,19 +2173,19 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>8.84</v>
+        <v>9.02</v>
       </c>
       <c r="F3" t="n">
-        <v>8.67</v>
+        <v>4.82</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>5.46</v>
+        <v>7.71</v>
       </c>
       <c r="I3" t="n">
-        <v>2.69</v>
+        <v>3.5</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -2194,7 +2194,7 @@
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>55.66</v>
+        <v>55.05</v>
       </c>
     </row>
     <row r="4">
@@ -3354,7 +3354,7 @@
     <col width="23" customWidth="1" min="20" max="20"/>
     <col width="23" customWidth="1" min="21" max="21"/>
     <col width="22" customWidth="1" min="22" max="22"/>
-    <col width="22" customWidth="1" min="23" max="23"/>
+    <col width="21" customWidth="1" min="23" max="23"/>
     <col width="18" customWidth="1" min="24" max="24"/>
     <col width="24" customWidth="1" min="25" max="25"/>
     <col width="17" customWidth="1" min="26" max="26"/>
@@ -3519,12 +3519,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>MU</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Micron Technology, Inc.</t>
+          <t>Taiwan Semiconductor Manufacturing Company Limited</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -3537,60 +3537,69 @@
           <t>Semiconductors</t>
         </is>
       </c>
+      <c r="E2" t="n">
+        <v>2172873342976</v>
+      </c>
       <c r="F2" t="n">
-        <v>966.780029296875</v>
+        <v>418.9500122070312</v>
       </c>
       <c r="G2" t="n">
-        <v>90273996800</v>
+        <v>4440492343296</v>
       </c>
       <c r="H2" t="n">
-        <v>3.457</v>
+        <v>0.36</v>
       </c>
       <c r="I2" t="n">
-        <v>44.23</v>
+        <v>13.41</v>
       </c>
       <c r="J2" t="n">
-        <v>13.685</v>
+        <v>0.774</v>
       </c>
       <c r="K2" t="n">
-        <v>7639499776</v>
+        <v>730826014720</v>
       </c>
       <c r="M2" t="n">
-        <v>26022000640</v>
+        <v>3518010228736</v>
       </c>
       <c r="N2" t="n">
-        <v>6376000000</v>
+        <v>1068558516224</v>
       </c>
       <c r="O2" t="n">
-        <v>0.7256899999999999</v>
+        <v>0.6423</v>
       </c>
       <c r="P2" t="n">
-        <v>0.80370003</v>
+        <v>0.60344005</v>
       </c>
       <c r="Q2" t="n">
-        <v>21.858015</v>
+        <v>31.241611</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0.48933163</v>
+      </c>
+      <c r="S2" t="n">
+        <v>2.97317459861974</v>
       </c>
       <c r="T2" t="n">
-        <v>0.007608338867642228</v>
+        <v>-0.005365445487747644</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2875215850577266</v>
+        <v>0.03809732083456407</v>
       </c>
       <c r="V2" t="n">
-        <v>1.317802614597143</v>
+        <v>0.1684963370842598</v>
       </c>
       <c r="W2" t="n">
-        <v>7.362826824630407</v>
+        <v>0.8632971696944793</v>
       </c>
       <c r="X2" t="n">
-        <v>0.00242</v>
+        <v>0.00013</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.7999000000000001</v>
+        <v>0.15498</v>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>2026-08-22T13:40:04.132239+00:00</t>
+          <t>2026-08-22T16:00:21.878355+00:00</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
@@ -3602,12 +3611,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>MU</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Taiwan Semiconductor Manufacturing Company Limited</t>
+          <t>Micron Technology, Inc.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -3621,68 +3630,68 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2172873342976</v>
+        <v>1091874717696</v>
       </c>
       <c r="F3" t="n">
-        <v>418.9500122070312</v>
+        <v>966.780029296875</v>
       </c>
       <c r="G3" t="n">
-        <v>4440492343296</v>
+        <v>90273996800</v>
       </c>
       <c r="H3" t="n">
-        <v>0.36</v>
+        <v>3.457</v>
       </c>
       <c r="I3" t="n">
-        <v>13.41</v>
+        <v>44.23</v>
       </c>
       <c r="J3" t="n">
-        <v>0.774</v>
+        <v>13.685</v>
       </c>
       <c r="K3" t="n">
-        <v>730826014720</v>
+        <v>7639499776</v>
       </c>
       <c r="M3" t="n">
-        <v>3518010228736</v>
+        <v>26022000640</v>
       </c>
       <c r="N3" t="n">
-        <v>1068558516224</v>
+        <v>6376000000</v>
       </c>
       <c r="O3" t="n">
-        <v>0.6423</v>
+        <v>0.7256899999999999</v>
       </c>
       <c r="P3" t="n">
-        <v>0.60344005</v>
+        <v>0.80370003</v>
       </c>
       <c r="Q3" t="n">
-        <v>31.241611</v>
+        <v>21.858015</v>
       </c>
       <c r="R3" t="n">
-        <v>0.48933163</v>
+        <v>12.0951185</v>
       </c>
       <c r="S3" t="n">
-        <v>2.97317459861974</v>
+        <v>142.924896879531</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.005365445487747644</v>
+        <v>0.007608338867642228</v>
       </c>
       <c r="U3" t="n">
-        <v>0.03809732083456407</v>
+        <v>0.2875215850577266</v>
       </c>
       <c r="V3" t="n">
-        <v>0.1684963370842598</v>
+        <v>1.317802614597143</v>
       </c>
       <c r="W3" t="n">
-        <v>0.8632972961454419</v>
+        <v>7.362826824630407</v>
       </c>
       <c r="X3" t="n">
-        <v>0.00013</v>
+        <v>0.00242</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.15498</v>
+        <v>0.7999000000000001</v>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>2026-08-22T13:40:08.436878+00:00</t>
+          <t>2026-08-22T16:00:18.634716+00:00</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
@@ -3774,7 +3783,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>2026-08-22T13:40:04.813255+00:00</t>
+          <t>2026-08-22T16:00:19.188294+00:00</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
@@ -3866,7 +3875,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>2026-08-22T13:40:10.709198+00:00</t>
+          <t>2026-08-22T16:00:23.128658+00:00</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
@@ -3958,7 +3967,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>2026-08-22T13:40:02.711506+00:00</t>
+          <t>2026-08-22T16:00:17.215402+00:00</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr">
@@ -4040,7 +4049,7 @@
         <v>0.1898762435729664</v>
       </c>
       <c r="W7" t="n">
-        <v>2.446494647256825</v>
+        <v>2.446494406067634</v>
       </c>
       <c r="X7" t="n">
         <v>0.00202</v>
@@ -4050,7 +4059,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>2026-08-22T13:40:05.178919+00:00</t>
+          <t>2026-08-22T16:00:19.537401+00:00</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr">
@@ -4142,7 +4151,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>2026-08-22T13:40:02.416594+00:00</t>
+          <t>2026-08-22T16:00:16.918016+00:00</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr">
@@ -4234,7 +4243,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>2026-08-22T13:40:11.287004+00:00</t>
+          <t>2026-08-22T16:00:23.395440+00:00</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr">
@@ -4323,7 +4332,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>2026-08-22T13:40:14.603067+00:00</t>
+          <t>2026-08-22T16:00:25.776244+00:00</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr">
@@ -4415,7 +4424,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>2026-08-22T13:40:02.982076+00:00</t>
+          <t>2026-08-22T16:00:17.520292+00:00</t>
         </is>
       </c>
       <c r="AD11" t="inlineStr">
@@ -4507,7 +4516,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>2026-08-22T13:40:06.488419+00:00</t>
+          <t>2026-08-22T16:00:20.641257+00:00</t>
         </is>
       </c>
       <c r="AD12" t="inlineStr">
@@ -4599,7 +4608,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>2026-08-22T13:40:03.769214+00:00</t>
+          <t>2026-08-22T16:00:18.237784+00:00</t>
         </is>
       </c>
       <c r="AD13" t="inlineStr">
@@ -4691,7 +4700,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>2026-08-22T13:40:13.002731+00:00</t>
+          <t>2026-08-22T16:00:24.566446+00:00</t>
         </is>
       </c>
       <c r="AD14" t="inlineStr">
@@ -4770,10 +4779,10 @@
         <v>-0.1089169343844046</v>
       </c>
       <c r="V15" t="n">
-        <v>0.1072405701495147</v>
+        <v>0.1072406716938052</v>
       </c>
       <c r="W15" t="n">
-        <v>0.2815941000710358</v>
+        <v>0.2815942361128876</v>
       </c>
       <c r="X15" t="n">
         <v>0.01948</v>
@@ -4783,7 +4792,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>2026-08-22T13:40:03.401554+00:00</t>
+          <t>2026-08-22T16:00:17.872203+00:00</t>
         </is>
       </c>
       <c r="AD15" t="inlineStr">
@@ -4869,7 +4878,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>2026-08-22T13:40:12.575920+00:00</t>
+          <t>2026-08-22T16:00:24.215652+00:00</t>
         </is>
       </c>
       <c r="AD16" t="inlineStr">
@@ -4961,7 +4970,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>2026-08-22T13:40:06.830155+00:00</t>
+          <t>2026-08-22T16:00:20.958528+00:00</t>
         </is>
       </c>
       <c r="AD17" t="inlineStr">
@@ -5047,7 +5056,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>2026-08-22T13:40:14.020449+00:00</t>
+          <t>2026-08-22T16:00:25.531902+00:00</t>
         </is>
       </c>
       <c r="AD18" t="inlineStr">
@@ -5133,7 +5142,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>2026-08-22T13:40:13.310577+00:00</t>
+          <t>2026-08-22T16:00:24.856936+00:00</t>
         </is>
       </c>
       <c r="AD19" t="inlineStr">
@@ -5222,7 +5231,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>2026-08-22T13:40:04.481477+00:00</t>
+          <t>2026-08-22T16:00:18.936786+00:00</t>
         </is>
       </c>
       <c r="AD20" t="inlineStr">
@@ -5265,7 +5274,7 @@
         <v>0.241</v>
       </c>
       <c r="I21" t="n">
-        <v>4.37</v>
+        <v>4.43</v>
       </c>
       <c r="J21" t="n">
         <v>0.53</v>
@@ -5286,7 +5295,7 @@
         <v>0.20362</v>
       </c>
       <c r="Q21" t="n">
-        <v>59.942795</v>
+        <v>59.13093</v>
       </c>
       <c r="R21" t="n">
         <v>8.784945499999999</v>
@@ -5314,7 +5323,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>2026-08-22T13:40:11.611213+00:00</t>
+          <t>2026-08-22T16:00:23.664526+00:00</t>
         </is>
       </c>
       <c r="AD21" t="inlineStr">
@@ -5406,7 +5415,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>2026-08-22T13:40:08.821278+00:00</t>
+          <t>2026-08-22T16:00:22.198202+00:00</t>
         </is>
       </c>
       <c r="AD22" t="inlineStr">
@@ -5495,7 +5504,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>2026-08-22T13:40:12.273134+00:00</t>
+          <t>2026-08-22T16:00:23.911346+00:00</t>
         </is>
       </c>
       <c r="AD23" t="inlineStr">
@@ -5577,7 +5586,7 @@
         <v>0.2176838288473297</v>
       </c>
       <c r="W24" t="n">
-        <v>-0.03376187393524122</v>
+        <v>-0.0337617560157526</v>
       </c>
       <c r="X24" t="n">
         <v>0.00090000004</v>
@@ -5587,7 +5596,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>2026-08-22T13:40:06.165324+00:00</t>
+          <t>2026-08-22T16:00:20.379764+00:00</t>
         </is>
       </c>
       <c r="AD24" t="inlineStr">
@@ -5676,7 +5685,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>2026-08-22T13:40:05.806219+00:00</t>
+          <t>2026-08-22T16:00:20.071529+00:00</t>
         </is>
       </c>
       <c r="AD25" t="inlineStr">
@@ -5768,7 +5777,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>2026-08-22T13:40:09.573919+00:00</t>
+          <t>2026-08-22T16:00:22.457078+00:00</t>
         </is>
       </c>
       <c r="AD26" t="inlineStr">
@@ -5860,7 +5869,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>2026-08-22T13:40:07.189185+00:00</t>
+          <t>2026-08-22T16:00:21.225528+00:00</t>
         </is>
       </c>
       <c r="AD27" t="inlineStr">
@@ -5946,7 +5955,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>2026-08-22T13:40:05.480311+00:00</t>
+          <t>2026-08-22T16:00:19.827297+00:00</t>
         </is>
       </c>
       <c r="AD28" t="inlineStr">
@@ -6038,7 +6047,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>2026-08-22T13:40:09.931066+00:00</t>
+          <t>2026-08-22T16:00:22.819514+00:00</t>
         </is>
       </c>
       <c r="AD29" t="inlineStr">
@@ -6130,7 +6139,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>2026-08-22T13:40:13.735878+00:00</t>
+          <t>2026-08-22T16:00:25.224799+00:00</t>
         </is>
       </c>
       <c r="AD30" t="inlineStr">
@@ -6219,7 +6228,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>2026-08-22T13:40:08.068309+00:00</t>
+          <t>2026-08-22T16:00:21.583920+00:00</t>
         </is>
       </c>
       <c r="AD31" t="inlineStr">
@@ -6247,7 +6256,7 @@
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
@@ -6304,27 +6313,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>MU</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>84.2</v>
+        <v>100</v>
       </c>
       <c r="C2" t="n">
-        <v>88.2</v>
+        <v>100</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>MODERATE</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>price_to_sales, price_to_fcf</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -6338,11 +6342,11 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>MU</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="C3" t="n">
         <v>100</v>
@@ -6353,7 +6357,7 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -7290,11 +7294,11 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>MU</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>57.27</v>
+        <v>55.66</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -7307,7 +7311,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>84.2</v>
+        <v>100</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>

--- a/reports/investment_dashboard.xlsx
+++ b/reports/investment_dashboard.xlsx
@@ -525,16 +525,16 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>MU</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Taiwan Semiconductor Manufacturing Company Limited</t>
+          <t>Micron Technology, Inc.</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>55.66</v>
+        <v>57.27</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>418.9500122070312</v>
+        <v>966.780029296875</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -550,19 +550,24 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>100</v>
+        <v>84.2</v>
       </c>
       <c r="I2" t="n">
-        <v>100</v>
+        <v>88.2</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Revenue Growth; Earnings Fcf; Balance Sheet; Valuation</t>
+          <t>Revenue Growth; Earnings Fcf; Balance Sheet</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
           <t>Industry Growth; Competitive Advantage; Catalysts; Inflation Resilience</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>High market sensitivity / beta</t>
         </is>
       </c>
     </row>
@@ -572,16 +577,16 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>MU</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Micron Technology, Inc.</t>
+          <t>Taiwan Semiconductor Manufacturing Company Limited</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>55.05</v>
+        <v>55.66</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -589,7 +594,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>966.780029296875</v>
+        <v>418.9500122070312</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -597,24 +602,19 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="I3" t="n">
         <v>100</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Revenue Growth; Earnings Fcf; Balance Sheet</t>
+          <t>Revenue Growth; Earnings Fcf; Balance Sheet; Valuation</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
           <t>Industry Growth; Competitive Advantage; Catalysts; Inflation Resilience</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>High market sensitivity / beta</t>
         </is>
       </c>
     </row>
@@ -2120,7 +2120,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>MU</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -2133,19 +2133,19 @@
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>8.84</v>
+        <v>9.02</v>
       </c>
       <c r="F2" t="n">
-        <v>8.67</v>
+        <v>7.04</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>5.46</v>
+        <v>7.71</v>
       </c>
       <c r="I2" t="n">
-        <v>2.69</v>
+        <v>3.5</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -2154,13 +2154,13 @@
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>55.66</v>
+        <v>57.27</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>MU</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -2173,19 +2173,19 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>9.02</v>
+        <v>8.84</v>
       </c>
       <c r="F3" t="n">
-        <v>4.82</v>
+        <v>8.67</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>7.71</v>
+        <v>5.46</v>
       </c>
       <c r="I3" t="n">
-        <v>3.5</v>
+        <v>2.69</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -2194,7 +2194,7 @@
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>55.05</v>
+        <v>55.66</v>
       </c>
     </row>
     <row r="4">
@@ -3354,7 +3354,7 @@
     <col width="23" customWidth="1" min="20" max="20"/>
     <col width="23" customWidth="1" min="21" max="21"/>
     <col width="22" customWidth="1" min="22" max="22"/>
-    <col width="21" customWidth="1" min="23" max="23"/>
+    <col width="22" customWidth="1" min="23" max="23"/>
     <col width="18" customWidth="1" min="24" max="24"/>
     <col width="24" customWidth="1" min="25" max="25"/>
     <col width="17" customWidth="1" min="26" max="26"/>
@@ -3519,12 +3519,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>MU</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Taiwan Semiconductor Manufacturing Company Limited</t>
+          <t>Micron Technology, Inc.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -3537,69 +3537,60 @@
           <t>Semiconductors</t>
         </is>
       </c>
-      <c r="E2" t="n">
-        <v>2172873342976</v>
-      </c>
       <c r="F2" t="n">
-        <v>418.9500122070312</v>
+        <v>966.780029296875</v>
       </c>
       <c r="G2" t="n">
-        <v>4440492343296</v>
+        <v>90273996800</v>
       </c>
       <c r="H2" t="n">
-        <v>0.36</v>
+        <v>3.457</v>
       </c>
       <c r="I2" t="n">
-        <v>13.41</v>
+        <v>44.23</v>
       </c>
       <c r="J2" t="n">
-        <v>0.774</v>
+        <v>13.685</v>
       </c>
       <c r="K2" t="n">
-        <v>730826014720</v>
+        <v>7639499776</v>
       </c>
       <c r="M2" t="n">
-        <v>3518010228736</v>
+        <v>26022000640</v>
       </c>
       <c r="N2" t="n">
-        <v>1068558516224</v>
+        <v>6376000000</v>
       </c>
       <c r="O2" t="n">
-        <v>0.6423</v>
+        <v>0.7256899999999999</v>
       </c>
       <c r="P2" t="n">
-        <v>0.60344005</v>
+        <v>0.80370003</v>
       </c>
       <c r="Q2" t="n">
-        <v>31.241611</v>
-      </c>
-      <c r="R2" t="n">
-        <v>0.48933163</v>
-      </c>
-      <c r="S2" t="n">
-        <v>2.97317459861974</v>
+        <v>21.858015</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.005365445487747644</v>
+        <v>0.007608338867642228</v>
       </c>
       <c r="U2" t="n">
-        <v>0.03809732083456407</v>
+        <v>0.2875215850577266</v>
       </c>
       <c r="V2" t="n">
-        <v>0.1684963370842598</v>
+        <v>1.317802614597143</v>
       </c>
       <c r="W2" t="n">
-        <v>0.8632971696944793</v>
+        <v>7.362826272720001</v>
       </c>
       <c r="X2" t="n">
-        <v>0.00013</v>
+        <v>0.00242</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.15498</v>
+        <v>0.7999000000000001</v>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>2026-08-22T16:00:21.878355+00:00</t>
+          <t>2026-08-22T16:20:05.784972+00:00</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
@@ -3611,12 +3602,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>MU</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Micron Technology, Inc.</t>
+          <t>Taiwan Semiconductor Manufacturing Company Limited</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -3630,68 +3621,68 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1091874717696</v>
+        <v>2172873342976</v>
       </c>
       <c r="F3" t="n">
-        <v>966.780029296875</v>
+        <v>418.9500122070312</v>
       </c>
       <c r="G3" t="n">
-        <v>90273996800</v>
+        <v>4440492343296</v>
       </c>
       <c r="H3" t="n">
-        <v>3.457</v>
+        <v>0.36</v>
       </c>
       <c r="I3" t="n">
-        <v>44.23</v>
+        <v>13.41</v>
       </c>
       <c r="J3" t="n">
-        <v>13.685</v>
+        <v>0.774</v>
       </c>
       <c r="K3" t="n">
-        <v>7639499776</v>
+        <v>730826014720</v>
       </c>
       <c r="M3" t="n">
-        <v>26022000640</v>
+        <v>3518010228736</v>
       </c>
       <c r="N3" t="n">
-        <v>6376000000</v>
+        <v>1068558516224</v>
       </c>
       <c r="O3" t="n">
-        <v>0.7256899999999999</v>
+        <v>0.6423</v>
       </c>
       <c r="P3" t="n">
-        <v>0.80370003</v>
+        <v>0.60344005</v>
       </c>
       <c r="Q3" t="n">
-        <v>21.858015</v>
+        <v>31.241611</v>
       </c>
       <c r="R3" t="n">
-        <v>12.0951185</v>
+        <v>0.48933163</v>
       </c>
       <c r="S3" t="n">
-        <v>142.924896879531</v>
+        <v>2.97317459861974</v>
       </c>
       <c r="T3" t="n">
-        <v>0.007608338867642228</v>
+        <v>-0.005365445487747644</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2875215850577266</v>
+        <v>0.03809732083456407</v>
       </c>
       <c r="V3" t="n">
-        <v>1.317802614597143</v>
+        <v>0.1684963370842598</v>
       </c>
       <c r="W3" t="n">
-        <v>7.362826824630407</v>
+        <v>0.8632972961454419</v>
       </c>
       <c r="X3" t="n">
-        <v>0.00242</v>
+        <v>0.00013</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.7999000000000001</v>
+        <v>0.15498</v>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>2026-08-22T16:00:18.634716+00:00</t>
+          <t>2026-08-22T16:20:11.893528+00:00</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
@@ -3783,7 +3774,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>2026-08-22T16:00:19.188294+00:00</t>
+          <t>2026-08-22T16:20:06.796108+00:00</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
@@ -3875,7 +3866,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>2026-08-22T16:00:23.128658+00:00</t>
+          <t>2026-08-22T16:20:14.160317+00:00</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
@@ -3967,7 +3958,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>2026-08-22T16:00:17.215402+00:00</t>
+          <t>2026-08-22T16:20:03.502036+00:00</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr">
@@ -4049,7 +4040,7 @@
         <v>0.1898762435729664</v>
       </c>
       <c r="W7" t="n">
-        <v>2.446494406067634</v>
+        <v>2.446494647256825</v>
       </c>
       <c r="X7" t="n">
         <v>0.00202</v>
@@ -4059,7 +4050,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>2026-08-22T16:00:19.537401+00:00</t>
+          <t>2026-08-22T16:20:07.395159+00:00</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr">
@@ -4151,7 +4142,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>2026-08-22T16:00:16.918016+00:00</t>
+          <t>2026-08-22T16:20:02.893623+00:00</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr">
@@ -4243,7 +4234,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>2026-08-22T16:00:23.395440+00:00</t>
+          <t>2026-08-22T16:20:14.729930+00:00</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr">
@@ -4332,7 +4323,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>2026-08-22T16:00:25.776244+00:00</t>
+          <t>2026-08-22T16:20:19.227351+00:00</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr">
@@ -4424,7 +4415,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>2026-08-22T16:00:17.520292+00:00</t>
+          <t>2026-08-22T16:20:04.028627+00:00</t>
         </is>
       </c>
       <c r="AD11" t="inlineStr">
@@ -4506,7 +4497,7 @@
         <v>0.1400655521483041</v>
       </c>
       <c r="W12" t="n">
-        <v>0.7311824950356518</v>
+        <v>0.7311826276569731</v>
       </c>
       <c r="X12" t="n">
         <v>0.01596</v>
@@ -4516,7 +4507,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>2026-08-22T16:00:20.641257+00:00</t>
+          <t>2026-08-22T16:20:09.717486+00:00</t>
         </is>
       </c>
       <c r="AD12" t="inlineStr">
@@ -4608,7 +4599,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>2026-08-22T16:00:18.237784+00:00</t>
+          <t>2026-08-22T16:20:05.125014+00:00</t>
         </is>
       </c>
       <c r="AD13" t="inlineStr">
@@ -4700,7 +4691,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>2026-08-22T16:00:24.566446+00:00</t>
+          <t>2026-08-22T16:20:16.933511+00:00</t>
         </is>
       </c>
       <c r="AD14" t="inlineStr">
@@ -4792,7 +4783,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>2026-08-22T16:00:17.872203+00:00</t>
+          <t>2026-08-22T16:20:04.543500+00:00</t>
         </is>
       </c>
       <c r="AD15" t="inlineStr">
@@ -4878,7 +4869,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>2026-08-22T16:00:24.215652+00:00</t>
+          <t>2026-08-22T16:20:16.416525+00:00</t>
         </is>
       </c>
       <c r="AD16" t="inlineStr">
@@ -4970,7 +4961,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>2026-08-22T16:00:20.958528+00:00</t>
+          <t>2026-08-22T16:20:10.236722+00:00</t>
         </is>
       </c>
       <c r="AD17" t="inlineStr">
@@ -5056,7 +5047,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>2026-08-22T16:00:25.531902+00:00</t>
+          <t>2026-08-22T16:20:18.640093+00:00</t>
         </is>
       </c>
       <c r="AD18" t="inlineStr">
@@ -5142,7 +5133,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>2026-08-22T16:00:24.856936+00:00</t>
+          <t>2026-08-22T16:20:17.586838+00:00</t>
         </is>
       </c>
       <c r="AD19" t="inlineStr">
@@ -5231,7 +5222,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>2026-08-22T16:00:18.936786+00:00</t>
+          <t>2026-08-22T16:20:06.314169+00:00</t>
         </is>
       </c>
       <c r="AD20" t="inlineStr">
@@ -5323,7 +5314,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>2026-08-22T16:00:23.664526+00:00</t>
+          <t>2026-08-22T16:20:15.395829+00:00</t>
         </is>
       </c>
       <c r="AD21" t="inlineStr">
@@ -5415,7 +5406,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>2026-08-22T16:00:22.198202+00:00</t>
+          <t>2026-08-22T16:20:12.450065+00:00</t>
         </is>
       </c>
       <c r="AD22" t="inlineStr">
@@ -5504,7 +5495,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>2026-08-22T16:00:23.911346+00:00</t>
+          <t>2026-08-22T16:20:15.913983+00:00</t>
         </is>
       </c>
       <c r="AD23" t="inlineStr">
@@ -5586,7 +5577,7 @@
         <v>0.2176838288473297</v>
       </c>
       <c r="W24" t="n">
-        <v>-0.0337617560157526</v>
+        <v>-0.03376187393524122</v>
       </c>
       <c r="X24" t="n">
         <v>0.00090000004</v>
@@ -5596,7 +5587,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>2026-08-22T16:00:20.379764+00:00</t>
+          <t>2026-08-22T16:20:09.156758+00:00</t>
         </is>
       </c>
       <c r="AD24" t="inlineStr">
@@ -5685,7 +5676,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>2026-08-22T16:00:20.071529+00:00</t>
+          <t>2026-08-22T16:20:08.501099+00:00</t>
         </is>
       </c>
       <c r="AD25" t="inlineStr">
@@ -5777,7 +5768,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>2026-08-22T16:00:22.457078+00:00</t>
+          <t>2026-08-22T16:20:12.928451+00:00</t>
         </is>
       </c>
       <c r="AD26" t="inlineStr">
@@ -5859,7 +5850,7 @@
         <v>-0.1456296261876776</v>
       </c>
       <c r="W27" t="n">
-        <v>-0.2535483859208238</v>
+        <v>-0.253548447765114</v>
       </c>
       <c r="X27" t="n">
         <v>0.00148</v>
@@ -5869,7 +5860,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>2026-08-22T16:00:21.225528+00:00</t>
+          <t>2026-08-22T16:20:10.784973+00:00</t>
         </is>
       </c>
       <c r="AD27" t="inlineStr">
@@ -5955,7 +5946,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>2026-08-22T16:00:19.827297+00:00</t>
+          <t>2026-08-22T16:20:07.968925+00:00</t>
         </is>
       </c>
       <c r="AD28" t="inlineStr">
@@ -6037,7 +6028,7 @@
         <v>1.979740667578479</v>
       </c>
       <c r="W29" t="n">
-        <v>2.335838148861586</v>
+        <v>2.335837790700546</v>
       </c>
       <c r="X29" t="n">
         <v>0.00494</v>
@@ -6047,7 +6038,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>2026-08-22T16:00:22.819514+00:00</t>
+          <t>2026-08-22T16:20:13.604668+00:00</t>
         </is>
       </c>
       <c r="AD29" t="inlineStr">
@@ -6139,7 +6130,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>2026-08-22T16:00:25.224799+00:00</t>
+          <t>2026-08-22T16:20:18.134197+00:00</t>
         </is>
       </c>
       <c r="AD30" t="inlineStr">
@@ -6228,7 +6219,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>2026-08-22T16:00:21.583920+00:00</t>
+          <t>2026-08-22T16:20:11.356493+00:00</t>
         </is>
       </c>
       <c r="AD31" t="inlineStr">
@@ -6256,7 +6247,7 @@
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
@@ -6313,22 +6304,27 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>MU</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>100</v>
+        <v>84.2</v>
       </c>
       <c r="C2" t="n">
-        <v>100</v>
+        <v>88.2</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MODERATE</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>price_to_sales, price_to_fcf</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -6342,11 +6338,11 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>MU</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="C3" t="n">
         <v>100</v>
@@ -6357,7 +6353,7 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -7294,11 +7290,11 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>MU</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>55.66</v>
+        <v>57.27</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -7311,7 +7307,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>100</v>
+        <v>84.2</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>

--- a/reports/investment_dashboard.xlsx
+++ b/reports/investment_dashboard.xlsx
@@ -525,16 +525,16 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>MU</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Micron Technology, Inc.</t>
+          <t>Taiwan Semiconductor Manufacturing Company Limited</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>57.27</v>
+        <v>55.66</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>966.780029296875</v>
+        <v>418.9500122070312</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -550,24 +550,19 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>84.2</v>
+        <v>100</v>
       </c>
       <c r="I2" t="n">
-        <v>88.2</v>
+        <v>100</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Revenue Growth; Earnings Fcf; Balance Sheet</t>
+          <t>Revenue Growth; Earnings Fcf; Balance Sheet; Valuation</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
           <t>Industry Growth; Competitive Advantage; Catalysts; Inflation Resilience</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>High market sensitivity / beta</t>
         </is>
       </c>
     </row>
@@ -577,16 +572,16 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>MU</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Taiwan Semiconductor Manufacturing Company Limited</t>
+          <t>Micron Technology, Inc.</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>55.66</v>
+        <v>55.05</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -594,7 +589,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>418.9500122070312</v>
+        <v>966.780029296875</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -602,19 +597,24 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="I3" t="n">
         <v>100</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Revenue Growth; Earnings Fcf; Balance Sheet; Valuation</t>
+          <t>Revenue Growth; Earnings Fcf; Balance Sheet</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
           <t>Industry Growth; Competitive Advantage; Catalysts; Inflation Resilience</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>High market sensitivity / beta</t>
         </is>
       </c>
     </row>
@@ -1332,7 +1332,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>MongoDB, Inc. Class A Common Stock</t>
+          <t>MongoDB, Inc.</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>ACM Research, Inc. Class A Common Stock</t>
+          <t>ACM Research, Inc.</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -2120,7 +2120,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>MU</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -2133,19 +2133,19 @@
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>9.02</v>
+        <v>8.84</v>
       </c>
       <c r="F2" t="n">
-        <v>7.04</v>
+        <v>8.67</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>7.71</v>
+        <v>5.46</v>
       </c>
       <c r="I2" t="n">
-        <v>3.5</v>
+        <v>2.69</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -2154,13 +2154,13 @@
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>57.27</v>
+        <v>55.66</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>MU</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -2173,19 +2173,19 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>8.84</v>
+        <v>9.02</v>
       </c>
       <c r="F3" t="n">
-        <v>8.67</v>
+        <v>4.82</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>5.46</v>
+        <v>7.71</v>
       </c>
       <c r="I3" t="n">
-        <v>2.69</v>
+        <v>3.5</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -2194,7 +2194,7 @@
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>55.66</v>
+        <v>55.05</v>
       </c>
     </row>
     <row r="4">
@@ -3519,12 +3519,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>MU</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Micron Technology, Inc.</t>
+          <t>Taiwan Semiconductor Manufacturing Company Limited</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -3537,60 +3537,69 @@
           <t>Semiconductors</t>
         </is>
       </c>
+      <c r="E2" t="n">
+        <v>2172873342976</v>
+      </c>
       <c r="F2" t="n">
-        <v>966.780029296875</v>
+        <v>418.9500122070312</v>
       </c>
       <c r="G2" t="n">
-        <v>90273996800</v>
+        <v>4440492343296</v>
       </c>
       <c r="H2" t="n">
-        <v>3.457</v>
+        <v>0.36</v>
       </c>
       <c r="I2" t="n">
-        <v>44.23</v>
+        <v>13.41</v>
       </c>
       <c r="J2" t="n">
-        <v>13.685</v>
+        <v>0.774</v>
       </c>
       <c r="K2" t="n">
-        <v>7639499776</v>
+        <v>730826014720</v>
       </c>
       <c r="M2" t="n">
-        <v>26022000640</v>
+        <v>3518010228736</v>
       </c>
       <c r="N2" t="n">
-        <v>6376000000</v>
+        <v>1068558516224</v>
       </c>
       <c r="O2" t="n">
-        <v>0.7256899999999999</v>
+        <v>0.6423</v>
       </c>
       <c r="P2" t="n">
-        <v>0.80370003</v>
+        <v>0.60344005</v>
       </c>
       <c r="Q2" t="n">
-        <v>21.858015</v>
+        <v>31.241611</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0.48933163</v>
+      </c>
+      <c r="S2" t="n">
+        <v>2.97317459861974</v>
       </c>
       <c r="T2" t="n">
-        <v>0.007608338867642228</v>
+        <v>-0.005365445487747644</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2875215850577266</v>
+        <v>0.03809732083456407</v>
       </c>
       <c r="V2" t="n">
-        <v>1.317802614597143</v>
+        <v>0.1684963370842598</v>
       </c>
       <c r="W2" t="n">
-        <v>7.362826272720001</v>
+        <v>0.8632971696944793</v>
       </c>
       <c r="X2" t="n">
-        <v>0.00242</v>
+        <v>0.00013</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.7999000000000001</v>
+        <v>0.15498</v>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>2026-08-22T16:20:05.784972+00:00</t>
+          <t>2026-08-22T16:24:06.222084+00:00</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
@@ -3602,12 +3611,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>MU</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Taiwan Semiconductor Manufacturing Company Limited</t>
+          <t>Micron Technology, Inc.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -3621,68 +3630,68 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2172873342976</v>
+        <v>1091874717696</v>
       </c>
       <c r="F3" t="n">
-        <v>418.9500122070312</v>
+        <v>966.780029296875</v>
       </c>
       <c r="G3" t="n">
-        <v>4440492343296</v>
+        <v>90273996800</v>
       </c>
       <c r="H3" t="n">
-        <v>0.36</v>
+        <v>3.457</v>
       </c>
       <c r="I3" t="n">
-        <v>13.41</v>
+        <v>44.23</v>
       </c>
       <c r="J3" t="n">
-        <v>0.774</v>
+        <v>13.685</v>
       </c>
       <c r="K3" t="n">
-        <v>730826014720</v>
+        <v>7639499776</v>
       </c>
       <c r="M3" t="n">
-        <v>3518010228736</v>
+        <v>26022000640</v>
       </c>
       <c r="N3" t="n">
-        <v>1068558516224</v>
+        <v>6376000000</v>
       </c>
       <c r="O3" t="n">
-        <v>0.6423</v>
+        <v>0.7256899999999999</v>
       </c>
       <c r="P3" t="n">
-        <v>0.60344005</v>
+        <v>0.80370003</v>
       </c>
       <c r="Q3" t="n">
-        <v>31.241611</v>
+        <v>21.858015</v>
       </c>
       <c r="R3" t="n">
-        <v>0.48933163</v>
+        <v>12.0951185</v>
       </c>
       <c r="S3" t="n">
-        <v>2.97317459861974</v>
+        <v>142.924896879531</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.005365445487747644</v>
+        <v>0.007608338867642228</v>
       </c>
       <c r="U3" t="n">
-        <v>0.03809732083456407</v>
+        <v>0.2875215850577266</v>
       </c>
       <c r="V3" t="n">
-        <v>0.1684963370842598</v>
+        <v>1.317802614597143</v>
       </c>
       <c r="W3" t="n">
-        <v>0.8632972961454419</v>
+        <v>7.362827376540883</v>
       </c>
       <c r="X3" t="n">
-        <v>0.00013</v>
+        <v>0.00242</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.15498</v>
+        <v>0.7999000000000001</v>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>2026-08-22T16:20:11.893528+00:00</t>
+          <t>2026-08-22T16:24:01.595238+00:00</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
@@ -3774,7 +3783,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>2026-08-22T16:20:06.796108+00:00</t>
+          <t>2026-08-22T16:24:02.395876+00:00</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
@@ -3866,7 +3875,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>2026-08-22T16:20:14.160317+00:00</t>
+          <t>2026-08-22T16:24:07.871915+00:00</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
@@ -3958,7 +3967,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>2026-08-22T16:20:03.502036+00:00</t>
+          <t>2026-08-22T16:23:59.902585+00:00</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr">
@@ -4050,7 +4059,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>2026-08-22T16:20:07.395159+00:00</t>
+          <t>2026-08-22T16:24:02.798144+00:00</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr">
@@ -4142,7 +4151,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>2026-08-22T16:20:02.893623+00:00</t>
+          <t>2026-08-22T16:23:59.276360+00:00</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr">
@@ -4234,7 +4243,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>2026-08-22T16:20:14.729930+00:00</t>
+          <t>2026-08-22T16:24:08.293844+00:00</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr">
@@ -4323,7 +4332,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>2026-08-22T16:20:19.227351+00:00</t>
+          <t>2026-08-22T16:24:11.756563+00:00</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr">
@@ -4415,7 +4424,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>2026-08-22T16:20:04.028627+00:00</t>
+          <t>2026-08-22T16:24:00.270283+00:00</t>
         </is>
       </c>
       <c r="AD11" t="inlineStr">
@@ -4497,7 +4506,7 @@
         <v>0.1400655521483041</v>
       </c>
       <c r="W12" t="n">
-        <v>0.7311826276569731</v>
+        <v>0.7311824950356518</v>
       </c>
       <c r="X12" t="n">
         <v>0.01596</v>
@@ -4507,7 +4516,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>2026-08-22T16:20:09.717486+00:00</t>
+          <t>2026-08-22T16:24:04.438022+00:00</t>
         </is>
       </c>
       <c r="AD12" t="inlineStr">
@@ -4589,7 +4598,7 @@
         <v>0.3342865245955684</v>
       </c>
       <c r="W13" t="n">
-        <v>2.097116106946919</v>
+        <v>2.097116404241915</v>
       </c>
       <c r="X13" t="n">
         <v>0.00331</v>
@@ -4599,7 +4608,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>2026-08-22T16:20:05.125014+00:00</t>
+          <t>2026-08-22T16:24:01.133186+00:00</t>
         </is>
       </c>
       <c r="AD13" t="inlineStr">
@@ -4691,7 +4700,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>2026-08-22T16:20:16.933511+00:00</t>
+          <t>2026-08-22T16:24:09.962637+00:00</t>
         </is>
       </c>
       <c r="AD14" t="inlineStr">
@@ -4770,10 +4779,10 @@
         <v>-0.1089169343844046</v>
       </c>
       <c r="V15" t="n">
-        <v>0.1072406716938052</v>
+        <v>0.1072405701495147</v>
       </c>
       <c r="W15" t="n">
-        <v>0.2815942361128876</v>
+        <v>0.2815943721547682</v>
       </c>
       <c r="X15" t="n">
         <v>0.01948</v>
@@ -4783,7 +4792,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>2026-08-22T16:20:04.543500+00:00</t>
+          <t>2026-08-22T16:24:00.682967+00:00</t>
         </is>
       </c>
       <c r="AD15" t="inlineStr">
@@ -4869,7 +4878,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>2026-08-22T16:20:16.416525+00:00</t>
+          <t>2026-08-22T16:24:09.590959+00:00</t>
         </is>
       </c>
       <c r="AD16" t="inlineStr">
@@ -4961,7 +4970,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>2026-08-22T16:20:10.236722+00:00</t>
+          <t>2026-08-22T16:24:04.826338+00:00</t>
         </is>
       </c>
       <c r="AD17" t="inlineStr">
@@ -4978,7 +4987,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>MongoDB, Inc. Class A Common Stock</t>
+          <t>MongoDB, Inc.</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -5047,7 +5056,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>2026-08-22T16:20:18.640093+00:00</t>
+          <t>2026-08-22T16:24:11.367411+00:00</t>
         </is>
       </c>
       <c r="AD18" t="inlineStr">
@@ -5133,7 +5142,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>2026-08-22T16:20:17.586838+00:00</t>
+          <t>2026-08-22T16:24:10.361098+00:00</t>
         </is>
       </c>
       <c r="AD19" t="inlineStr">
@@ -5150,7 +5159,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>ACM Research, Inc. Class A Common Stock</t>
+          <t>ACM Research, Inc.</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -5222,7 +5231,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>2026-08-22T16:20:06.314169+00:00</t>
+          <t>2026-08-22T16:24:02.026046+00:00</t>
         </is>
       </c>
       <c r="AD20" t="inlineStr">
@@ -5304,7 +5313,7 @@
         <v>0.07819827777494104</v>
       </c>
       <c r="W21" t="n">
-        <v>1.071721934408579</v>
+        <v>1.071721809401515</v>
       </c>
       <c r="X21" t="n">
         <v>0.00269</v>
@@ -5314,7 +5323,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>2026-08-22T16:20:15.395829+00:00</t>
+          <t>2026-08-22T16:24:08.757284+00:00</t>
         </is>
       </c>
       <c r="AD21" t="inlineStr">
@@ -5406,7 +5415,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>2026-08-22T16:20:12.450065+00:00</t>
+          <t>2026-08-22T16:24:06.621911+00:00</t>
         </is>
       </c>
       <c r="AD22" t="inlineStr">
@@ -5495,7 +5504,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>2026-08-22T16:20:15.913983+00:00</t>
+          <t>2026-08-22T16:24:09.142355+00:00</t>
         </is>
       </c>
       <c r="AD23" t="inlineStr">
@@ -5577,7 +5586,7 @@
         <v>0.2176838288473297</v>
       </c>
       <c r="W24" t="n">
-        <v>-0.03376187393524122</v>
+        <v>-0.03376181497550057</v>
       </c>
       <c r="X24" t="n">
         <v>0.00090000004</v>
@@ -5587,7 +5596,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>2026-08-22T16:20:09.156758+00:00</t>
+          <t>2026-08-22T16:24:04.002219+00:00</t>
         </is>
       </c>
       <c r="AD24" t="inlineStr">
@@ -5676,7 +5685,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>2026-08-22T16:20:08.501099+00:00</t>
+          <t>2026-08-22T16:24:03.534425+00:00</t>
         </is>
       </c>
       <c r="AD25" t="inlineStr">
@@ -5768,7 +5777,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>2026-08-22T16:20:12.928451+00:00</t>
+          <t>2026-08-22T16:24:07.064206+00:00</t>
         </is>
       </c>
       <c r="AD26" t="inlineStr">
@@ -5850,7 +5859,7 @@
         <v>-0.1456296261876776</v>
       </c>
       <c r="W27" t="n">
-        <v>-0.253548447765114</v>
+        <v>-0.2535483859208238</v>
       </c>
       <c r="X27" t="n">
         <v>0.00148</v>
@@ -5860,7 +5869,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>2026-08-22T16:20:10.784973+00:00</t>
+          <t>2026-08-22T16:24:05.294281+00:00</t>
         </is>
       </c>
       <c r="AD27" t="inlineStr">
@@ -5946,7 +5955,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>2026-08-22T16:20:07.968925+00:00</t>
+          <t>2026-08-22T16:24:03.176923+00:00</t>
         </is>
       </c>
       <c r="AD28" t="inlineStr">
@@ -6038,7 +6047,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>2026-08-22T16:20:13.604668+00:00</t>
+          <t>2026-08-22T16:24:07.483527+00:00</t>
         </is>
       </c>
       <c r="AD29" t="inlineStr">
@@ -6130,7 +6139,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>2026-08-22T16:20:18.134197+00:00</t>
+          <t>2026-08-22T16:24:10.923917+00:00</t>
         </is>
       </c>
       <c r="AD30" t="inlineStr">
@@ -6219,7 +6228,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>2026-08-22T16:20:11.356493+00:00</t>
+          <t>2026-08-22T16:24:05.804244+00:00</t>
         </is>
       </c>
       <c r="AD31" t="inlineStr">
@@ -6247,7 +6256,7 @@
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
@@ -6304,27 +6313,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>MU</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>84.2</v>
+        <v>100</v>
       </c>
       <c r="C2" t="n">
-        <v>88.2</v>
+        <v>100</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>MODERATE</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>price_to_sales, price_to_fcf</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -6338,11 +6342,11 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>MU</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="C3" t="n">
         <v>100</v>
@@ -6353,7 +6357,7 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -7290,11 +7294,11 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>MU</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>57.27</v>
+        <v>55.66</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -7307,7 +7311,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>84.2</v>
+        <v>100</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>

--- a/reports/investment_dashboard.xlsx
+++ b/reports/investment_dashboard.xlsx
@@ -3589,7 +3589,7 @@
         <v>0.1684963370842598</v>
       </c>
       <c r="W2" t="n">
-        <v>0.8632971696944793</v>
+        <v>0.8632972961454419</v>
       </c>
       <c r="X2" t="n">
         <v>0.00013</v>
@@ -3599,7 +3599,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>2026-08-22T16:24:06.222084+00:00</t>
+          <t>2026-08-22T16:33:30.258808+00:00</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
@@ -3681,7 +3681,7 @@
         <v>1.317802614597143</v>
       </c>
       <c r="W3" t="n">
-        <v>7.362827376540883</v>
+        <v>7.362826824630407</v>
       </c>
       <c r="X3" t="n">
         <v>0.00242</v>
@@ -3691,7 +3691,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>2026-08-22T16:24:01.595238+00:00</t>
+          <t>2026-08-22T16:33:28.051937+00:00</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
@@ -3783,7 +3783,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>2026-08-22T16:24:02.395876+00:00</t>
+          <t>2026-08-22T16:33:28.400990+00:00</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
@@ -3875,7 +3875,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>2026-08-22T16:24:07.871915+00:00</t>
+          <t>2026-08-22T16:33:31.044646+00:00</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
@@ -3967,7 +3967,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>2026-08-22T16:23:59.902585+00:00</t>
+          <t>2026-08-22T16:33:27.145095+00:00</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr">
@@ -4059,7 +4059,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>2026-08-22T16:24:02.798144+00:00</t>
+          <t>2026-08-22T16:33:28.634967+00:00</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr">
@@ -4151,7 +4151,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>2026-08-22T16:23:59.276360+00:00</t>
+          <t>2026-08-22T16:33:26.951789+00:00</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr">
@@ -4243,7 +4243,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>2026-08-22T16:24:08.293844+00:00</t>
+          <t>2026-08-22T16:33:31.225811+00:00</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr">
@@ -4332,7 +4332,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>2026-08-22T16:24:11.756563+00:00</t>
+          <t>2026-08-22T16:33:32.685648+00:00</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr">
@@ -4424,7 +4424,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>2026-08-22T16:24:00.270283+00:00</t>
+          <t>2026-08-22T16:33:27.339916+00:00</t>
         </is>
       </c>
       <c r="AD11" t="inlineStr">
@@ -4506,7 +4506,7 @@
         <v>0.1400655521483041</v>
       </c>
       <c r="W12" t="n">
-        <v>0.7311824950356518</v>
+        <v>0.731182362414351</v>
       </c>
       <c r="X12" t="n">
         <v>0.01596</v>
@@ -4516,7 +4516,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>2026-08-22T16:24:04.438022+00:00</t>
+          <t>2026-08-22T16:33:29.405438+00:00</t>
         </is>
       </c>
       <c r="AD12" t="inlineStr">
@@ -4608,7 +4608,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>2026-08-22T16:24:01.133186+00:00</t>
+          <t>2026-08-22T16:33:27.794530+00:00</t>
         </is>
       </c>
       <c r="AD13" t="inlineStr">
@@ -4700,7 +4700,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>2026-08-22T16:24:09.962637+00:00</t>
+          <t>2026-08-22T16:33:31.942032+00:00</t>
         </is>
       </c>
       <c r="AD14" t="inlineStr">
@@ -4782,7 +4782,7 @@
         <v>0.1072405701495147</v>
       </c>
       <c r="W15" t="n">
-        <v>0.2815943721547682</v>
+        <v>0.2815942361128876</v>
       </c>
       <c r="X15" t="n">
         <v>0.01948</v>
@@ -4792,7 +4792,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>2026-08-22T16:24:00.682967+00:00</t>
+          <t>2026-08-22T16:33:27.562377+00:00</t>
         </is>
       </c>
       <c r="AD15" t="inlineStr">
@@ -4878,7 +4878,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>2026-08-22T16:24:09.590959+00:00</t>
+          <t>2026-08-22T16:33:31.763603+00:00</t>
         </is>
       </c>
       <c r="AD16" t="inlineStr">
@@ -4970,7 +4970,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>2026-08-22T16:24:04.826338+00:00</t>
+          <t>2026-08-22T16:33:29.604628+00:00</t>
         </is>
       </c>
       <c r="AD17" t="inlineStr">
@@ -5056,7 +5056,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>2026-08-22T16:24:11.367411+00:00</t>
+          <t>2026-08-22T16:33:32.492445+00:00</t>
         </is>
       </c>
       <c r="AD18" t="inlineStr">
@@ -5142,7 +5142,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>2026-08-22T16:24:10.361098+00:00</t>
+          <t>2026-08-22T16:33:32.117238+00:00</t>
         </is>
       </c>
       <c r="AD19" t="inlineStr">
@@ -5231,7 +5231,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>2026-08-22T16:24:02.026046+00:00</t>
+          <t>2026-08-22T16:33:28.229359+00:00</t>
         </is>
       </c>
       <c r="AD20" t="inlineStr">
@@ -5313,7 +5313,7 @@
         <v>0.07819827777494104</v>
       </c>
       <c r="W21" t="n">
-        <v>1.071721809401515</v>
+        <v>1.071721934408579</v>
       </c>
       <c r="X21" t="n">
         <v>0.00269</v>
@@ -5323,7 +5323,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>2026-08-22T16:24:08.757284+00:00</t>
+          <t>2026-08-22T16:33:31.415114+00:00</t>
         </is>
       </c>
       <c r="AD21" t="inlineStr">
@@ -5415,7 +5415,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>2026-08-22T16:24:06.621911+00:00</t>
+          <t>2026-08-22T16:33:30.484849+00:00</t>
         </is>
       </c>
       <c r="AD22" t="inlineStr">
@@ -5504,7 +5504,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>2026-08-22T16:24:09.142355+00:00</t>
+          <t>2026-08-22T16:33:31.591860+00:00</t>
         </is>
       </c>
       <c r="AD23" t="inlineStr">
@@ -5586,7 +5586,7 @@
         <v>0.2176838288473297</v>
       </c>
       <c r="W24" t="n">
-        <v>-0.03376181497550057</v>
+        <v>-0.03376187393524122</v>
       </c>
       <c r="X24" t="n">
         <v>0.00090000004</v>
@@ -5596,7 +5596,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>2026-08-22T16:24:04.002219+00:00</t>
+          <t>2026-08-22T16:33:29.216752+00:00</t>
         </is>
       </c>
       <c r="AD24" t="inlineStr">
@@ -5685,7 +5685,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>2026-08-22T16:24:03.534425+00:00</t>
+          <t>2026-08-22T16:33:28.984687+00:00</t>
         </is>
       </c>
       <c r="AD25" t="inlineStr">
@@ -5777,7 +5777,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>2026-08-22T16:24:07.064206+00:00</t>
+          <t>2026-08-22T16:33:30.668611+00:00</t>
         </is>
       </c>
       <c r="AD26" t="inlineStr">
@@ -5869,7 +5869,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>2026-08-22T16:24:05.294281+00:00</t>
+          <t>2026-08-22T16:33:29.799214+00:00</t>
         </is>
       </c>
       <c r="AD27" t="inlineStr">
@@ -5955,7 +5955,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>2026-08-22T16:24:03.176923+00:00</t>
+          <t>2026-08-22T16:33:28.809340+00:00</t>
         </is>
       </c>
       <c r="AD28" t="inlineStr">
@@ -6047,7 +6047,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>2026-08-22T16:24:07.483527+00:00</t>
+          <t>2026-08-22T16:33:30.876809+00:00</t>
         </is>
       </c>
       <c r="AD29" t="inlineStr">
@@ -6139,7 +6139,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>2026-08-22T16:24:10.923917+00:00</t>
+          <t>2026-08-22T16:33:32.297622+00:00</t>
         </is>
       </c>
       <c r="AD30" t="inlineStr">
@@ -6228,7 +6228,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>2026-08-22T16:24:05.804244+00:00</t>
+          <t>2026-08-22T16:33:30.013780+00:00</t>
         </is>
       </c>
       <c r="AD31" t="inlineStr">

--- a/reports/investment_dashboard.xlsx
+++ b/reports/investment_dashboard.xlsx
@@ -525,16 +525,16 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>MU</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Taiwan Semiconductor Manufacturing Company Limited</t>
+          <t>Micron Technology, Inc.</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>55.66</v>
+        <v>57.27</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>418.9500122070312</v>
+        <v>966.780029296875</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -550,19 +550,24 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>100</v>
+        <v>84.2</v>
       </c>
       <c r="I2" t="n">
-        <v>100</v>
+        <v>88.2</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Revenue Growth; Earnings Fcf; Balance Sheet; Valuation</t>
+          <t>Revenue Growth; Earnings Fcf; Balance Sheet</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
           <t>Industry Growth; Competitive Advantage; Catalysts; Inflation Resilience</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>High market sensitivity / beta</t>
         </is>
       </c>
     </row>
@@ -572,16 +577,16 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>MU</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Micron Technology, Inc.</t>
+          <t>Taiwan Semiconductor Manufacturing Company Limited</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>55.05</v>
+        <v>55.66</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -589,7 +594,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>966.780029296875</v>
+        <v>418.9500122070312</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -597,24 +602,19 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="I3" t="n">
         <v>100</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Revenue Growth; Earnings Fcf; Balance Sheet</t>
+          <t>Revenue Growth; Earnings Fcf; Balance Sheet; Valuation</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
           <t>Industry Growth; Competitive Advantage; Catalysts; Inflation Resilience</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>High market sensitivity / beta</t>
         </is>
       </c>
     </row>
@@ -1332,7 +1332,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>MongoDB, Inc.</t>
+          <t>MongoDB, Inc. Class A Common Stock</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>ACM Research, Inc.</t>
+          <t>ACM Research, Inc. Class A Common Stock</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -2120,7 +2120,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>MU</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -2133,19 +2133,19 @@
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>8.84</v>
+        <v>9.02</v>
       </c>
       <c r="F2" t="n">
-        <v>8.67</v>
+        <v>7.04</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>5.46</v>
+        <v>7.71</v>
       </c>
       <c r="I2" t="n">
-        <v>2.69</v>
+        <v>3.5</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -2154,13 +2154,13 @@
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>55.66</v>
+        <v>57.27</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>MU</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -2173,19 +2173,19 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>9.02</v>
+        <v>8.84</v>
       </c>
       <c r="F3" t="n">
-        <v>4.82</v>
+        <v>8.67</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>7.71</v>
+        <v>5.46</v>
       </c>
       <c r="I3" t="n">
-        <v>3.5</v>
+        <v>2.69</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -2194,7 +2194,7 @@
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>55.05</v>
+        <v>55.66</v>
       </c>
     </row>
     <row r="4">
@@ -3519,12 +3519,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>MU</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Taiwan Semiconductor Manufacturing Company Limited</t>
+          <t>Micron Technology, Inc.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -3537,69 +3537,60 @@
           <t>Semiconductors</t>
         </is>
       </c>
-      <c r="E2" t="n">
-        <v>2172873342976</v>
-      </c>
       <c r="F2" t="n">
-        <v>418.9500122070312</v>
+        <v>966.780029296875</v>
       </c>
       <c r="G2" t="n">
-        <v>4440492343296</v>
+        <v>90273996800</v>
       </c>
       <c r="H2" t="n">
-        <v>0.36</v>
+        <v>3.457</v>
       </c>
       <c r="I2" t="n">
-        <v>13.41</v>
+        <v>44.28</v>
       </c>
       <c r="J2" t="n">
-        <v>0.774</v>
+        <v>13.685</v>
       </c>
       <c r="K2" t="n">
-        <v>730826014720</v>
+        <v>7639499776</v>
       </c>
       <c r="M2" t="n">
-        <v>3518010228736</v>
+        <v>26022000640</v>
       </c>
       <c r="N2" t="n">
-        <v>1068558516224</v>
+        <v>6376000000</v>
       </c>
       <c r="O2" t="n">
-        <v>0.6423</v>
+        <v>0.7256899999999999</v>
       </c>
       <c r="P2" t="n">
-        <v>0.60344005</v>
+        <v>0.80370003</v>
       </c>
       <c r="Q2" t="n">
-        <v>31.241611</v>
-      </c>
-      <c r="R2" t="n">
-        <v>0.48933163</v>
-      </c>
-      <c r="S2" t="n">
-        <v>2.97317459861974</v>
+        <v>21.833334</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.005365445487747644</v>
+        <v>0.007608338867642228</v>
       </c>
       <c r="U2" t="n">
-        <v>0.03809732083456407</v>
+        <v>0.2875215850577266</v>
       </c>
       <c r="V2" t="n">
-        <v>0.1684963370842598</v>
+        <v>1.317802614597143</v>
       </c>
       <c r="W2" t="n">
-        <v>0.8632972961454419</v>
+        <v>7.362826824630407</v>
       </c>
       <c r="X2" t="n">
-        <v>0.00013</v>
+        <v>0.00242</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.15498</v>
+        <v>0.7999000000000001</v>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>2026-08-22T16:33:30.258808+00:00</t>
+          <t>2026-08-22T18:42:19.966766+00:00</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
@@ -3611,12 +3602,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>MU</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Micron Technology, Inc.</t>
+          <t>Taiwan Semiconductor Manufacturing Company Limited</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -3630,68 +3621,68 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1091874717696</v>
+        <v>2172873342976</v>
       </c>
       <c r="F3" t="n">
-        <v>966.780029296875</v>
+        <v>418.9500122070312</v>
       </c>
       <c r="G3" t="n">
-        <v>90273996800</v>
+        <v>4440492343296</v>
       </c>
       <c r="H3" t="n">
-        <v>3.457</v>
+        <v>0.36</v>
       </c>
       <c r="I3" t="n">
-        <v>44.23</v>
+        <v>13.41</v>
       </c>
       <c r="J3" t="n">
-        <v>13.685</v>
+        <v>0.774</v>
       </c>
       <c r="K3" t="n">
-        <v>7639499776</v>
+        <v>730826014720</v>
       </c>
       <c r="M3" t="n">
-        <v>26022000640</v>
+        <v>3518010228736</v>
       </c>
       <c r="N3" t="n">
-        <v>6376000000</v>
+        <v>1068558516224</v>
       </c>
       <c r="O3" t="n">
-        <v>0.7256899999999999</v>
+        <v>0.6423</v>
       </c>
       <c r="P3" t="n">
-        <v>0.80370003</v>
+        <v>0.60344005</v>
       </c>
       <c r="Q3" t="n">
-        <v>21.858015</v>
+        <v>31.241611</v>
       </c>
       <c r="R3" t="n">
-        <v>12.0951185</v>
+        <v>0.48933163</v>
       </c>
       <c r="S3" t="n">
-        <v>142.924896879531</v>
+        <v>2.97317459861974</v>
       </c>
       <c r="T3" t="n">
-        <v>0.007608338867642228</v>
+        <v>-0.005365445487747644</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2875215850577266</v>
+        <v>0.03809732083456407</v>
       </c>
       <c r="V3" t="n">
-        <v>1.317802614597143</v>
+        <v>0.1684963370842598</v>
       </c>
       <c r="W3" t="n">
-        <v>7.362826824630407</v>
+        <v>0.8632971696944793</v>
       </c>
       <c r="X3" t="n">
-        <v>0.00242</v>
+        <v>0.00013</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.7999000000000001</v>
+        <v>0.15498</v>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>2026-08-22T16:33:28.051937+00:00</t>
+          <t>2026-08-22T18:42:23.478393+00:00</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
@@ -3783,7 +3774,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>2026-08-22T16:33:28.400990+00:00</t>
+          <t>2026-08-22T18:42:20.630483+00:00</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
@@ -3875,7 +3866,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>2026-08-22T16:33:31.044646+00:00</t>
+          <t>2026-08-22T18:42:24.671941+00:00</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
@@ -3967,7 +3958,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>2026-08-22T16:33:27.145095+00:00</t>
+          <t>2026-08-22T18:42:18.676964+00:00</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr">
@@ -4049,7 +4040,7 @@
         <v>0.1898762435729664</v>
       </c>
       <c r="W7" t="n">
-        <v>2.446494647256825</v>
+        <v>2.446494406067634</v>
       </c>
       <c r="X7" t="n">
         <v>0.00202</v>
@@ -4059,7 +4050,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>2026-08-22T16:33:28.634967+00:00</t>
+          <t>2026-08-22T18:42:20.980941+00:00</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr">
@@ -4151,7 +4142,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>2026-08-22T16:33:26.951789+00:00</t>
+          <t>2026-08-22T18:42:18.380731+00:00</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr">
@@ -4243,7 +4234,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>2026-08-22T16:33:31.225811+00:00</t>
+          <t>2026-08-22T18:42:24.965603+00:00</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr">
@@ -4332,7 +4323,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>2026-08-22T16:33:32.685648+00:00</t>
+          <t>2026-08-22T18:42:27.424328+00:00</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr">
@@ -4424,7 +4415,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>2026-08-22T16:33:27.339916+00:00</t>
+          <t>2026-08-22T18:42:18.986872+00:00</t>
         </is>
       </c>
       <c r="AD11" t="inlineStr">
@@ -4506,7 +4497,7 @@
         <v>0.1400655521483041</v>
       </c>
       <c r="W12" t="n">
-        <v>0.731182362414351</v>
+        <v>0.7311824950356518</v>
       </c>
       <c r="X12" t="n">
         <v>0.01596</v>
@@ -4516,7 +4507,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>2026-08-22T16:33:29.405438+00:00</t>
+          <t>2026-08-22T18:42:22.259015+00:00</t>
         </is>
       </c>
       <c r="AD12" t="inlineStr">
@@ -4598,7 +4589,7 @@
         <v>0.3342865245955684</v>
       </c>
       <c r="W13" t="n">
-        <v>2.097116404241915</v>
+        <v>2.097116106946919</v>
       </c>
       <c r="X13" t="n">
         <v>0.00331</v>
@@ -4608,7 +4599,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>2026-08-22T16:33:27.794530+00:00</t>
+          <t>2026-08-22T18:42:19.646526+00:00</t>
         </is>
       </c>
       <c r="AD13" t="inlineStr">
@@ -4700,7 +4691,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>2026-08-22T16:33:31.942032+00:00</t>
+          <t>2026-08-22T18:42:26.201035+00:00</t>
         </is>
       </c>
       <c r="AD14" t="inlineStr">
@@ -4779,7 +4770,7 @@
         <v>-0.1089169343844046</v>
       </c>
       <c r="V15" t="n">
-        <v>0.1072405701495147</v>
+        <v>0.1072406716938052</v>
       </c>
       <c r="W15" t="n">
         <v>0.2815942361128876</v>
@@ -4792,7 +4783,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>2026-08-22T16:33:27.562377+00:00</t>
+          <t>2026-08-22T18:42:19.320133+00:00</t>
         </is>
       </c>
       <c r="AD15" t="inlineStr">
@@ -4878,7 +4869,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>2026-08-22T16:33:31.763603+00:00</t>
+          <t>2026-08-22T18:42:25.875223+00:00</t>
         </is>
       </c>
       <c r="AD16" t="inlineStr">
@@ -4970,7 +4961,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>2026-08-22T16:33:29.604628+00:00</t>
+          <t>2026-08-22T18:42:22.512817+00:00</t>
         </is>
       </c>
       <c r="AD17" t="inlineStr">
@@ -4987,7 +4978,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>MongoDB, Inc.</t>
+          <t>MongoDB, Inc. Class A Common Stock</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -5056,7 +5047,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>2026-08-22T16:33:32.492445+00:00</t>
+          <t>2026-08-22T18:42:27.150084+00:00</t>
         </is>
       </c>
       <c r="AD18" t="inlineStr">
@@ -5142,7 +5133,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>2026-08-22T16:33:32.117238+00:00</t>
+          <t>2026-08-22T18:42:26.469655+00:00</t>
         </is>
       </c>
       <c r="AD19" t="inlineStr">
@@ -5159,7 +5150,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>ACM Research, Inc.</t>
+          <t>ACM Research, Inc. Class A Common Stock</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -5231,7 +5222,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>2026-08-22T16:33:28.229359+00:00</t>
+          <t>2026-08-22T18:42:20.372808+00:00</t>
         </is>
       </c>
       <c r="AD20" t="inlineStr">
@@ -5323,7 +5314,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>2026-08-22T16:33:31.415114+00:00</t>
+          <t>2026-08-22T18:42:25.322877+00:00</t>
         </is>
       </c>
       <c r="AD21" t="inlineStr">
@@ -5405,7 +5396,7 @@
         <v>0.2131482647002914</v>
       </c>
       <c r="W22" t="n">
-        <v>1.414165403503707</v>
+        <v>1.414165201818253</v>
       </c>
       <c r="X22" t="n">
         <v>0.00016000001</v>
@@ -5415,7 +5406,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>2026-08-22T16:33:30.484849+00:00</t>
+          <t>2026-08-22T18:42:23.791501+00:00</t>
         </is>
       </c>
       <c r="AD22" t="inlineStr">
@@ -5504,7 +5495,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>2026-08-22T16:33:31.591860+00:00</t>
+          <t>2026-08-22T18:42:25.580722+00:00</t>
         </is>
       </c>
       <c r="AD23" t="inlineStr">
@@ -5596,7 +5587,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>2026-08-22T16:33:29.216752+00:00</t>
+          <t>2026-08-22T18:42:21.879096+00:00</t>
         </is>
       </c>
       <c r="AD24" t="inlineStr">
@@ -5685,7 +5676,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>2026-08-22T16:33:28.984687+00:00</t>
+          <t>2026-08-22T18:42:21.570980+00:00</t>
         </is>
       </c>
       <c r="AD25" t="inlineStr">
@@ -5777,7 +5768,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>2026-08-22T16:33:30.668611+00:00</t>
+          <t>2026-08-22T18:42:24.075539+00:00</t>
         </is>
       </c>
       <c r="AD26" t="inlineStr">
@@ -5859,7 +5850,7 @@
         <v>-0.1456296261876776</v>
       </c>
       <c r="W27" t="n">
-        <v>-0.2535483859208238</v>
+        <v>-0.253548447765114</v>
       </c>
       <c r="X27" t="n">
         <v>0.00148</v>
@@ -5869,7 +5860,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>2026-08-22T16:33:29.799214+00:00</t>
+          <t>2026-08-22T18:42:22.829864+00:00</t>
         </is>
       </c>
       <c r="AD27" t="inlineStr">
@@ -5955,7 +5946,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>2026-08-22T16:33:28.809340+00:00</t>
+          <t>2026-08-22T18:42:21.276095+00:00</t>
         </is>
       </c>
       <c r="AD28" t="inlineStr">
@@ -6047,7 +6038,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>2026-08-22T16:33:30.876809+00:00</t>
+          <t>2026-08-22T18:42:24.375423+00:00</t>
         </is>
       </c>
       <c r="AD29" t="inlineStr">
@@ -6139,7 +6130,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>2026-08-22T16:33:32.297622+00:00</t>
+          <t>2026-08-22T18:42:26.804397+00:00</t>
         </is>
       </c>
       <c r="AD30" t="inlineStr">
@@ -6228,7 +6219,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>2026-08-22T16:33:30.013780+00:00</t>
+          <t>2026-08-22T18:42:23.165500+00:00</t>
         </is>
       </c>
       <c r="AD31" t="inlineStr">
@@ -6256,7 +6247,7 @@
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
@@ -6313,22 +6304,27 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>MU</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>100</v>
+        <v>84.2</v>
       </c>
       <c r="C2" t="n">
-        <v>100</v>
+        <v>88.2</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MODERATE</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>price_to_sales, price_to_fcf</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -6342,11 +6338,11 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>MU</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="C3" t="n">
         <v>100</v>
@@ -6357,7 +6353,7 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -7294,11 +7290,11 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>MU</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>55.66</v>
+        <v>57.27</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -7311,7 +7307,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>100</v>
+        <v>84.2</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>

--- a/reports/investment_dashboard.xlsx
+++ b/reports/investment_dashboard.xlsx
@@ -1332,7 +1332,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>MongoDB, Inc. Class A Common Stock</t>
+          <t>MongoDB, Inc.</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>ACM Research, Inc. Class A Common Stock</t>
+          <t>ACM Research, Inc.</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -3354,7 +3354,7 @@
     <col width="23" customWidth="1" min="20" max="20"/>
     <col width="23" customWidth="1" min="21" max="21"/>
     <col width="22" customWidth="1" min="22" max="22"/>
-    <col width="22" customWidth="1" min="23" max="23"/>
+    <col width="21" customWidth="1" min="23" max="23"/>
     <col width="18" customWidth="1" min="24" max="24"/>
     <col width="24" customWidth="1" min="25" max="25"/>
     <col width="17" customWidth="1" min="26" max="26"/>
@@ -3580,7 +3580,7 @@
         <v>1.317802614597143</v>
       </c>
       <c r="W2" t="n">
-        <v>7.362826824630407</v>
+        <v>7.362827376540883</v>
       </c>
       <c r="X2" t="n">
         <v>0.00242</v>
@@ -3590,7 +3590,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>2026-08-22T18:42:19.966766+00:00</t>
+          <t>2026-08-23T12:46:34.756820+00:00</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
@@ -3672,7 +3672,7 @@
         <v>0.1684963370842598</v>
       </c>
       <c r="W3" t="n">
-        <v>0.8632971696944793</v>
+        <v>0.8632972961454419</v>
       </c>
       <c r="X3" t="n">
         <v>0.00013</v>
@@ -3682,7 +3682,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>2026-08-22T18:42:23.478393+00:00</t>
+          <t>2026-08-23T12:46:40.376261+00:00</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
@@ -3774,7 +3774,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>2026-08-22T18:42:20.630483+00:00</t>
+          <t>2026-08-23T12:46:35.606899+00:00</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
@@ -3866,7 +3866,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>2026-08-22T18:42:24.671941+00:00</t>
+          <t>2026-08-23T12:46:42.252644+00:00</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
@@ -3958,7 +3958,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>2026-08-22T18:42:18.676964+00:00</t>
+          <t>2026-08-23T12:46:32.598774+00:00</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr">
@@ -4040,7 +4040,7 @@
         <v>0.1898762435729664</v>
       </c>
       <c r="W7" t="n">
-        <v>2.446494406067634</v>
+        <v>2.446494888446049</v>
       </c>
       <c r="X7" t="n">
         <v>0.00202</v>
@@ -4050,7 +4050,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>2026-08-22T18:42:20.980941+00:00</t>
+          <t>2026-08-23T12:46:36.072628+00:00</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr">
@@ -4142,7 +4142,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>2026-08-22T18:42:18.380731+00:00</t>
+          <t>2026-08-23T12:46:32.172202+00:00</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr">
@@ -4234,7 +4234,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>2026-08-22T18:42:24.965603+00:00</t>
+          <t>2026-08-23T12:46:42.701353+00:00</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr">
@@ -4323,7 +4323,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>2026-08-22T18:42:27.424328+00:00</t>
+          <t>2026-08-23T12:46:46.290710+00:00</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr">
@@ -4415,7 +4415,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>2026-08-22T18:42:18.986872+00:00</t>
+          <t>2026-08-23T12:46:33.064796+00:00</t>
         </is>
       </c>
       <c r="AD11" t="inlineStr">
@@ -4507,7 +4507,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>2026-08-22T18:42:22.259015+00:00</t>
+          <t>2026-08-23T12:46:38.287389+00:00</t>
         </is>
       </c>
       <c r="AD12" t="inlineStr">
@@ -4599,7 +4599,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>2026-08-22T18:42:19.646526+00:00</t>
+          <t>2026-08-23T12:46:34.259013+00:00</t>
         </is>
       </c>
       <c r="AD13" t="inlineStr">
@@ -4691,7 +4691,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>2026-08-22T18:42:26.201035+00:00</t>
+          <t>2026-08-23T12:46:44.442035+00:00</t>
         </is>
       </c>
       <c r="AD14" t="inlineStr">
@@ -4770,7 +4770,7 @@
         <v>-0.1089169343844046</v>
       </c>
       <c r="V15" t="n">
-        <v>0.1072406716938052</v>
+        <v>0.1072405701495147</v>
       </c>
       <c r="W15" t="n">
         <v>0.2815942361128876</v>
@@ -4783,7 +4783,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>2026-08-22T18:42:19.320133+00:00</t>
+          <t>2026-08-23T12:46:33.767017+00:00</t>
         </is>
       </c>
       <c r="AD15" t="inlineStr">
@@ -4869,7 +4869,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>2026-08-22T18:42:25.875223+00:00</t>
+          <t>2026-08-23T12:46:44.017519+00:00</t>
         </is>
       </c>
       <c r="AD16" t="inlineStr">
@@ -4961,7 +4961,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>2026-08-22T18:42:22.512817+00:00</t>
+          <t>2026-08-23T12:46:38.752527+00:00</t>
         </is>
       </c>
       <c r="AD17" t="inlineStr">
@@ -4978,7 +4978,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>MongoDB, Inc. Class A Common Stock</t>
+          <t>MongoDB, Inc.</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -5047,7 +5047,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>2026-08-22T18:42:27.150084+00:00</t>
+          <t>2026-08-23T12:46:45.782825+00:00</t>
         </is>
       </c>
       <c r="AD18" t="inlineStr">
@@ -5133,7 +5133,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>2026-08-22T18:42:26.469655+00:00</t>
+          <t>2026-08-23T12:46:44.913628+00:00</t>
         </is>
       </c>
       <c r="AD19" t="inlineStr">
@@ -5150,7 +5150,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>ACM Research, Inc. Class A Common Stock</t>
+          <t>ACM Research, Inc.</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -5222,7 +5222,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>2026-08-22T18:42:20.372808+00:00</t>
+          <t>2026-08-23T12:46:35.190761+00:00</t>
         </is>
       </c>
       <c r="AD20" t="inlineStr">
@@ -5304,7 +5304,7 @@
         <v>0.07819827777494104</v>
       </c>
       <c r="W21" t="n">
-        <v>1.071721934408579</v>
+        <v>1.071721809401515</v>
       </c>
       <c r="X21" t="n">
         <v>0.00269</v>
@@ -5314,7 +5314,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>2026-08-22T18:42:25.322877+00:00</t>
+          <t>2026-08-23T12:46:43.158249+00:00</t>
         </is>
       </c>
       <c r="AD21" t="inlineStr">
@@ -5357,7 +5357,7 @@
         <v>0.213</v>
       </c>
       <c r="I22" t="n">
-        <v>29.41</v>
+        <v>29.63</v>
       </c>
       <c r="J22" t="n">
         <v>0.285</v>
@@ -5378,7 +5378,7 @@
         <v>0.37057</v>
       </c>
       <c r="Q22" t="n">
-        <v>59.97144</v>
+        <v>59.526157</v>
       </c>
       <c r="R22" t="n">
         <v>19.176569</v>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>2026-08-22T18:42:23.791501+00:00</t>
+          <t>2026-08-23T12:46:40.857485+00:00</t>
         </is>
       </c>
       <c r="AD22" t="inlineStr">
@@ -5495,7 +5495,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>2026-08-22T18:42:25.580722+00:00</t>
+          <t>2026-08-23T12:46:43.583893+00:00</t>
         </is>
       </c>
       <c r="AD23" t="inlineStr">
@@ -5577,7 +5577,7 @@
         <v>0.2176838288473297</v>
       </c>
       <c r="W24" t="n">
-        <v>-0.03376187393524122</v>
+        <v>-0.0337617560157526</v>
       </c>
       <c r="X24" t="n">
         <v>0.00090000004</v>
@@ -5587,7 +5587,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>2026-08-22T18:42:21.879096+00:00</t>
+          <t>2026-08-23T12:46:37.722958+00:00</t>
         </is>
       </c>
       <c r="AD24" t="inlineStr">
@@ -5676,7 +5676,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>2026-08-22T18:42:21.570980+00:00</t>
+          <t>2026-08-23T12:46:37.182944+00:00</t>
         </is>
       </c>
       <c r="AD25" t="inlineStr">
@@ -5768,7 +5768,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>2026-08-22T18:42:24.075539+00:00</t>
+          <t>2026-08-23T12:46:41.349959+00:00</t>
         </is>
       </c>
       <c r="AD26" t="inlineStr">
@@ -5860,7 +5860,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>2026-08-22T18:42:22.829864+00:00</t>
+          <t>2026-08-23T12:46:39.310895+00:00</t>
         </is>
       </c>
       <c r="AD27" t="inlineStr">
@@ -5946,7 +5946,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>2026-08-22T18:42:21.276095+00:00</t>
+          <t>2026-08-23T12:46:36.700585+00:00</t>
         </is>
       </c>
       <c r="AD28" t="inlineStr">
@@ -6028,7 +6028,7 @@
         <v>1.979740667578479</v>
       </c>
       <c r="W29" t="n">
-        <v>2.335837790700546</v>
+        <v>2.335838148861586</v>
       </c>
       <c r="X29" t="n">
         <v>0.00494</v>
@@ -6038,7 +6038,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>2026-08-22T18:42:24.375423+00:00</t>
+          <t>2026-08-23T12:46:41.823756+00:00</t>
         </is>
       </c>
       <c r="AD29" t="inlineStr">
@@ -6130,7 +6130,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>2026-08-22T18:42:26.804397+00:00</t>
+          <t>2026-08-23T12:46:45.362879+00:00</t>
         </is>
       </c>
       <c r="AD30" t="inlineStr">
@@ -6209,7 +6209,7 @@
         <v>-0.05779410309686361</v>
       </c>
       <c r="W31" t="n">
-        <v>-0.3646448121864612</v>
+        <v>-0.3646448542401906</v>
       </c>
       <c r="X31" t="n">
         <v>0.40498</v>
@@ -6219,7 +6219,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>2026-08-22T18:42:23.165500+00:00</t>
+          <t>2026-08-23T12:46:39.842246+00:00</t>
         </is>
       </c>
       <c r="AD31" t="inlineStr">

--- a/reports/investment_dashboard.xlsx
+++ b/reports/investment_dashboard.xlsx
@@ -525,16 +525,16 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>MU</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Micron Technology, Inc.</t>
+          <t>Taiwan Semiconductor Manufacturing Company Limited</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>57.27</v>
+        <v>55.66</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>966.780029296875</v>
+        <v>418.9500122070312</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -550,24 +550,19 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>84.2</v>
+        <v>100</v>
       </c>
       <c r="I2" t="n">
-        <v>88.2</v>
+        <v>100</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Revenue Growth; Earnings Fcf; Balance Sheet</t>
+          <t>Revenue Growth; Earnings Fcf; Balance Sheet; Valuation</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
           <t>Industry Growth; Competitive Advantage; Catalysts; Inflation Resilience</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>High market sensitivity / beta</t>
         </is>
       </c>
     </row>
@@ -577,16 +572,16 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>MU</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Taiwan Semiconductor Manufacturing Company Limited</t>
+          <t>Micron Technology, Inc.</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>55.66</v>
+        <v>55.05</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -594,7 +589,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>418.9500122070312</v>
+        <v>966.780029296875</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -602,19 +597,24 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="I3" t="n">
         <v>100</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Revenue Growth; Earnings Fcf; Balance Sheet; Valuation</t>
+          <t>Revenue Growth; Earnings Fcf; Balance Sheet</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
           <t>Industry Growth; Competitive Advantage; Catalysts; Inflation Resilience</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>High market sensitivity / beta</t>
         </is>
       </c>
     </row>
@@ -2120,7 +2120,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>MU</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -2133,19 +2133,19 @@
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>9.02</v>
+        <v>8.84</v>
       </c>
       <c r="F2" t="n">
-        <v>7.04</v>
+        <v>8.67</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>7.71</v>
+        <v>5.46</v>
       </c>
       <c r="I2" t="n">
-        <v>3.5</v>
+        <v>2.69</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -2154,13 +2154,13 @@
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>57.27</v>
+        <v>55.66</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>MU</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -2173,19 +2173,19 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>8.84</v>
+        <v>9.02</v>
       </c>
       <c r="F3" t="n">
-        <v>8.67</v>
+        <v>4.82</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>5.46</v>
+        <v>7.71</v>
       </c>
       <c r="I3" t="n">
-        <v>2.69</v>
+        <v>3.5</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -2194,7 +2194,7 @@
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>55.66</v>
+        <v>55.05</v>
       </c>
     </row>
     <row r="4">
@@ -3519,12 +3519,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>MU</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Micron Technology, Inc.</t>
+          <t>Taiwan Semiconductor Manufacturing Company Limited</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -3537,60 +3537,69 @@
           <t>Semiconductors</t>
         </is>
       </c>
+      <c r="E2" t="n">
+        <v>2172873342976</v>
+      </c>
       <c r="F2" t="n">
-        <v>966.780029296875</v>
+        <v>418.9500122070312</v>
       </c>
       <c r="G2" t="n">
-        <v>90273996800</v>
+        <v>4440492343296</v>
       </c>
       <c r="H2" t="n">
-        <v>3.457</v>
+        <v>0.36</v>
       </c>
       <c r="I2" t="n">
-        <v>44.28</v>
+        <v>13.41</v>
       </c>
       <c r="J2" t="n">
-        <v>13.685</v>
+        <v>0.774</v>
       </c>
       <c r="K2" t="n">
-        <v>7639499776</v>
+        <v>730826014720</v>
       </c>
       <c r="M2" t="n">
-        <v>26022000640</v>
+        <v>3518010228736</v>
       </c>
       <c r="N2" t="n">
-        <v>6376000000</v>
+        <v>1068558516224</v>
       </c>
       <c r="O2" t="n">
-        <v>0.7256899999999999</v>
+        <v>0.6423</v>
       </c>
       <c r="P2" t="n">
-        <v>0.80370003</v>
+        <v>0.60344005</v>
       </c>
       <c r="Q2" t="n">
-        <v>21.833334</v>
+        <v>31.241611</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0.48933163</v>
+      </c>
+      <c r="S2" t="n">
+        <v>2.97317459861974</v>
       </c>
       <c r="T2" t="n">
-        <v>0.007608338867642228</v>
+        <v>-0.005365445487747644</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2875215850577266</v>
+        <v>0.03809732083456407</v>
       </c>
       <c r="V2" t="n">
-        <v>1.317802614597143</v>
+        <v>0.1684963370842598</v>
       </c>
       <c r="W2" t="n">
-        <v>7.362827376540883</v>
+        <v>0.8632972961454419</v>
       </c>
       <c r="X2" t="n">
-        <v>0.00242</v>
+        <v>0.00013</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.7999000000000001</v>
+        <v>0.15498</v>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>2026-08-23T12:46:34.756820+00:00</t>
+          <t>2026-08-23T20:12:03.576225+00:00</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
@@ -3602,12 +3611,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>MU</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Taiwan Semiconductor Manufacturing Company Limited</t>
+          <t>Micron Technology, Inc.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -3621,68 +3630,68 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2172873342976</v>
+        <v>1091874717696</v>
       </c>
       <c r="F3" t="n">
-        <v>418.9500122070312</v>
+        <v>966.780029296875</v>
       </c>
       <c r="G3" t="n">
-        <v>4440492343296</v>
+        <v>90273996800</v>
       </c>
       <c r="H3" t="n">
-        <v>0.36</v>
+        <v>3.457</v>
       </c>
       <c r="I3" t="n">
-        <v>13.41</v>
+        <v>44.28</v>
       </c>
       <c r="J3" t="n">
-        <v>0.774</v>
+        <v>13.685</v>
       </c>
       <c r="K3" t="n">
-        <v>730826014720</v>
+        <v>7639499776</v>
       </c>
       <c r="M3" t="n">
-        <v>3518010228736</v>
+        <v>26022000640</v>
       </c>
       <c r="N3" t="n">
-        <v>1068558516224</v>
+        <v>6376000000</v>
       </c>
       <c r="O3" t="n">
-        <v>0.6423</v>
+        <v>0.7256899999999999</v>
       </c>
       <c r="P3" t="n">
-        <v>0.60344005</v>
+        <v>0.80370003</v>
       </c>
       <c r="Q3" t="n">
-        <v>31.241611</v>
+        <v>21.833334</v>
       </c>
       <c r="R3" t="n">
-        <v>0.48933163</v>
+        <v>12.0951185</v>
       </c>
       <c r="S3" t="n">
-        <v>2.97317459861974</v>
+        <v>142.924896879531</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.005365445487747644</v>
+        <v>0.007608338867642228</v>
       </c>
       <c r="U3" t="n">
-        <v>0.03809732083456407</v>
+        <v>0.2875215850577266</v>
       </c>
       <c r="V3" t="n">
-        <v>0.1684963370842598</v>
+        <v>1.317802614597143</v>
       </c>
       <c r="W3" t="n">
-        <v>0.8632972961454419</v>
+        <v>7.362826824630407</v>
       </c>
       <c r="X3" t="n">
-        <v>0.00013</v>
+        <v>0.00242</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.15498</v>
+        <v>0.7999000000000001</v>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>2026-08-23T12:46:40.376261+00:00</t>
+          <t>2026-08-23T20:11:58.832054+00:00</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
@@ -3774,7 +3783,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>2026-08-23T12:46:35.606899+00:00</t>
+          <t>2026-08-23T20:11:59.697853+00:00</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
@@ -3866,7 +3875,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>2026-08-23T12:46:42.252644+00:00</t>
+          <t>2026-08-23T20:12:05.223434+00:00</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
@@ -3958,7 +3967,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>2026-08-23T12:46:32.598774+00:00</t>
+          <t>2026-08-23T20:11:57.134125+00:00</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr">
@@ -4040,7 +4049,7 @@
         <v>0.1898762435729664</v>
       </c>
       <c r="W7" t="n">
-        <v>2.446494888446049</v>
+        <v>2.446494406067634</v>
       </c>
       <c r="X7" t="n">
         <v>0.00202</v>
@@ -4050,7 +4059,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>2026-08-23T12:46:36.072628+00:00</t>
+          <t>2026-08-23T20:12:00.109249+00:00</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr">
@@ -4142,7 +4151,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>2026-08-23T12:46:32.172202+00:00</t>
+          <t>2026-08-23T20:11:56.666713+00:00</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr">
@@ -4224,7 +4233,7 @@
         <v>2.73072935680286</v>
       </c>
       <c r="W9" t="n">
-        <v>2.50241270126798</v>
+        <v>2.502412912969455</v>
       </c>
       <c r="X9" t="n">
         <v>0.07491</v>
@@ -4234,7 +4243,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>2026-08-23T12:46:42.701353+00:00</t>
+          <t>2026-08-23T20:12:05.657235+00:00</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr">
@@ -4323,7 +4332,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>2026-08-23T12:46:46.290710+00:00</t>
+          <t>2026-08-23T20:12:08.975397+00:00</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr">
@@ -4415,7 +4424,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>2026-08-23T12:46:33.064796+00:00</t>
+          <t>2026-08-23T20:11:57.494039+00:00</t>
         </is>
       </c>
       <c r="AD11" t="inlineStr">
@@ -4507,7 +4516,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>2026-08-23T12:46:38.287389+00:00</t>
+          <t>2026-08-23T20:12:01.757721+00:00</t>
         </is>
       </c>
       <c r="AD12" t="inlineStr">
@@ -4599,7 +4608,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>2026-08-23T12:46:34.259013+00:00</t>
+          <t>2026-08-23T20:11:58.346310+00:00</t>
         </is>
       </c>
       <c r="AD13" t="inlineStr">
@@ -4691,7 +4700,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>2026-08-23T12:46:44.442035+00:00</t>
+          <t>2026-08-23T20:12:07.273696+00:00</t>
         </is>
       </c>
       <c r="AD14" t="inlineStr">
@@ -4783,7 +4792,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>2026-08-23T12:46:33.767017+00:00</t>
+          <t>2026-08-23T20:11:57.895418+00:00</t>
         </is>
       </c>
       <c r="AD15" t="inlineStr">
@@ -4869,7 +4878,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>2026-08-23T12:46:44.017519+00:00</t>
+          <t>2026-08-23T20:12:06.841266+00:00</t>
         </is>
       </c>
       <c r="AD16" t="inlineStr">
@@ -4961,7 +4970,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>2026-08-23T12:46:38.752527+00:00</t>
+          <t>2026-08-23T20:12:02.164243+00:00</t>
         </is>
       </c>
       <c r="AD17" t="inlineStr">
@@ -5047,7 +5056,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>2026-08-23T12:46:45.782825+00:00</t>
+          <t>2026-08-23T20:12:08.495046+00:00</t>
         </is>
       </c>
       <c r="AD18" t="inlineStr">
@@ -5133,7 +5142,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>2026-08-23T12:46:44.913628+00:00</t>
+          <t>2026-08-23T20:12:07.698463+00:00</t>
         </is>
       </c>
       <c r="AD19" t="inlineStr">
@@ -5222,7 +5231,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>2026-08-23T12:46:35.190761+00:00</t>
+          <t>2026-08-23T20:11:59.195654+00:00</t>
         </is>
       </c>
       <c r="AD20" t="inlineStr">
@@ -5314,7 +5323,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>2026-08-23T12:46:43.158249+00:00</t>
+          <t>2026-08-23T20:12:06.122351+00:00</t>
         </is>
       </c>
       <c r="AD21" t="inlineStr">
@@ -5396,7 +5405,7 @@
         <v>0.2131482647002914</v>
       </c>
       <c r="W22" t="n">
-        <v>1.414165201818253</v>
+        <v>1.414165403503707</v>
       </c>
       <c r="X22" t="n">
         <v>0.00016000001</v>
@@ -5406,7 +5415,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>2026-08-23T12:46:40.857485+00:00</t>
+          <t>2026-08-23T20:12:03.968820+00:00</t>
         </is>
       </c>
       <c r="AD22" t="inlineStr">
@@ -5495,7 +5504,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>2026-08-23T12:46:43.583893+00:00</t>
+          <t>2026-08-23T20:12:06.473519+00:00</t>
         </is>
       </c>
       <c r="AD23" t="inlineStr">
@@ -5587,7 +5596,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>2026-08-23T12:46:37.722958+00:00</t>
+          <t>2026-08-23T20:12:01.401118+00:00</t>
         </is>
       </c>
       <c r="AD24" t="inlineStr">
@@ -5676,7 +5685,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>2026-08-23T12:46:37.182944+00:00</t>
+          <t>2026-08-23T20:12:00.959029+00:00</t>
         </is>
       </c>
       <c r="AD25" t="inlineStr">
@@ -5768,7 +5777,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>2026-08-23T12:46:41.349959+00:00</t>
+          <t>2026-08-23T20:12:04.324820+00:00</t>
         </is>
       </c>
       <c r="AD26" t="inlineStr">
@@ -5850,7 +5859,7 @@
         <v>-0.1456296261876776</v>
       </c>
       <c r="W27" t="n">
-        <v>-0.253548447765114</v>
+        <v>-0.2535483859208238</v>
       </c>
       <c r="X27" t="n">
         <v>0.00148</v>
@@ -5860,7 +5869,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>2026-08-23T12:46:39.310895+00:00</t>
+          <t>2026-08-23T20:12:02.619577+00:00</t>
         </is>
       </c>
       <c r="AD27" t="inlineStr">
@@ -5946,7 +5955,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>2026-08-23T12:46:36.700585+00:00</t>
+          <t>2026-08-23T20:12:00.524396+00:00</t>
         </is>
       </c>
       <c r="AD28" t="inlineStr">
@@ -6038,7 +6047,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>2026-08-23T12:46:41.823756+00:00</t>
+          <t>2026-08-23T20:12:04.874710+00:00</t>
         </is>
       </c>
       <c r="AD29" t="inlineStr">
@@ -6130,7 +6139,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>2026-08-23T12:46:45.362879+00:00</t>
+          <t>2026-08-23T20:12:08.074931+00:00</t>
         </is>
       </c>
       <c r="AD30" t="inlineStr">
@@ -6209,7 +6218,7 @@
         <v>-0.05779410309686361</v>
       </c>
       <c r="W31" t="n">
-        <v>-0.3646448542401906</v>
+        <v>-0.3646448121864612</v>
       </c>
       <c r="X31" t="n">
         <v>0.40498</v>
@@ -6219,7 +6228,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>2026-08-23T12:46:39.842246+00:00</t>
+          <t>2026-08-23T20:12:03.151676+00:00</t>
         </is>
       </c>
       <c r="AD31" t="inlineStr">
@@ -6247,7 +6256,7 @@
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
@@ -6304,27 +6313,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>MU</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>84.2</v>
+        <v>100</v>
       </c>
       <c r="C2" t="n">
-        <v>88.2</v>
+        <v>100</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>MODERATE</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>price_to_sales, price_to_fcf</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -6338,11 +6342,11 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>MU</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="C3" t="n">
         <v>100</v>
@@ -6353,7 +6357,7 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -7290,11 +7294,11 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>MU</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>57.27</v>
+        <v>55.66</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -7307,7 +7311,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>84.2</v>
+        <v>100</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>

--- a/reports/investment_dashboard.xlsx
+++ b/reports/investment_dashboard.xlsx
@@ -525,16 +525,16 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>MU</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Taiwan Semiconductor Manufacturing Company Limited</t>
+          <t>Micron Technology, Inc.</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>55.66</v>
+        <v>57.27</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>418.9500122070312</v>
+        <v>966.780029296875</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -550,19 +550,24 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>100</v>
+        <v>84.2</v>
       </c>
       <c r="I2" t="n">
-        <v>100</v>
+        <v>88.2</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Revenue Growth; Earnings Fcf; Balance Sheet; Valuation</t>
+          <t>Revenue Growth; Earnings Fcf; Balance Sheet</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
           <t>Industry Growth; Competitive Advantage; Catalysts; Inflation Resilience</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>High market sensitivity / beta</t>
         </is>
       </c>
     </row>
@@ -572,16 +577,16 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>MU</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Micron Technology, Inc.</t>
+          <t>Taiwan Semiconductor Manufacturing Company Limited</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>55.05</v>
+        <v>55.66</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -589,7 +594,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>966.780029296875</v>
+        <v>418.9500122070312</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -597,24 +602,19 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="I3" t="n">
         <v>100</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Revenue Growth; Earnings Fcf; Balance Sheet</t>
+          <t>Revenue Growth; Earnings Fcf; Balance Sheet; Valuation</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
           <t>Industry Growth; Competitive Advantage; Catalysts; Inflation Resilience</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>High market sensitivity / beta</t>
         </is>
       </c>
     </row>
@@ -2120,7 +2120,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>MU</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -2133,19 +2133,19 @@
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>8.84</v>
+        <v>9.02</v>
       </c>
       <c r="F2" t="n">
-        <v>8.67</v>
+        <v>7.04</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>5.46</v>
+        <v>7.71</v>
       </c>
       <c r="I2" t="n">
-        <v>2.69</v>
+        <v>3.5</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -2154,13 +2154,13 @@
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>55.66</v>
+        <v>57.27</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>MU</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -2173,19 +2173,19 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>9.02</v>
+        <v>8.84</v>
       </c>
       <c r="F3" t="n">
-        <v>4.82</v>
+        <v>8.67</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>7.71</v>
+        <v>5.46</v>
       </c>
       <c r="I3" t="n">
-        <v>3.5</v>
+        <v>2.69</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -2194,7 +2194,7 @@
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>55.05</v>
+        <v>55.66</v>
       </c>
     </row>
     <row r="4">
@@ -3354,7 +3354,7 @@
     <col width="23" customWidth="1" min="20" max="20"/>
     <col width="23" customWidth="1" min="21" max="21"/>
     <col width="22" customWidth="1" min="22" max="22"/>
-    <col width="21" customWidth="1" min="23" max="23"/>
+    <col width="22" customWidth="1" min="23" max="23"/>
     <col width="18" customWidth="1" min="24" max="24"/>
     <col width="24" customWidth="1" min="25" max="25"/>
     <col width="17" customWidth="1" min="26" max="26"/>
@@ -3519,12 +3519,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>MU</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Taiwan Semiconductor Manufacturing Company Limited</t>
+          <t>Micron Technology, Inc.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -3537,69 +3537,60 @@
           <t>Semiconductors</t>
         </is>
       </c>
-      <c r="E2" t="n">
-        <v>2172873342976</v>
-      </c>
       <c r="F2" t="n">
-        <v>418.9500122070312</v>
+        <v>966.780029296875</v>
       </c>
       <c r="G2" t="n">
-        <v>4440492343296</v>
+        <v>90273996800</v>
       </c>
       <c r="H2" t="n">
-        <v>0.36</v>
+        <v>3.457</v>
       </c>
       <c r="I2" t="n">
-        <v>13.41</v>
+        <v>44.28</v>
       </c>
       <c r="J2" t="n">
-        <v>0.774</v>
+        <v>13.685</v>
       </c>
       <c r="K2" t="n">
-        <v>730826014720</v>
+        <v>7639499776</v>
       </c>
       <c r="M2" t="n">
-        <v>3518010228736</v>
+        <v>26022000640</v>
       </c>
       <c r="N2" t="n">
-        <v>1068558516224</v>
+        <v>6376000000</v>
       </c>
       <c r="O2" t="n">
-        <v>0.6423</v>
+        <v>0.7256899999999999</v>
       </c>
       <c r="P2" t="n">
-        <v>0.60344005</v>
+        <v>0.80370003</v>
       </c>
       <c r="Q2" t="n">
-        <v>31.241611</v>
-      </c>
-      <c r="R2" t="n">
-        <v>0.48933163</v>
-      </c>
-      <c r="S2" t="n">
-        <v>2.97317459861974</v>
+        <v>21.833334</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.005365445487747644</v>
+        <v>0.007608338867642228</v>
       </c>
       <c r="U2" t="n">
-        <v>0.03809732083456407</v>
+        <v>0.2875215850577266</v>
       </c>
       <c r="V2" t="n">
-        <v>0.1684963370842598</v>
+        <v>1.317802614597143</v>
       </c>
       <c r="W2" t="n">
-        <v>0.8632972961454419</v>
+        <v>7.362826824630407</v>
       </c>
       <c r="X2" t="n">
-        <v>0.00013</v>
+        <v>0.00242</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.15498</v>
+        <v>0.7999000000000001</v>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>2026-08-23T20:12:03.576225+00:00</t>
+          <t>2026-08-23T20:56:25.624226+00:00</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
@@ -3611,12 +3602,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>MU</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Micron Technology, Inc.</t>
+          <t>Taiwan Semiconductor Manufacturing Company Limited</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -3630,68 +3621,68 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1091874717696</v>
+        <v>2172873342976</v>
       </c>
       <c r="F3" t="n">
-        <v>966.780029296875</v>
+        <v>418.9500122070312</v>
       </c>
       <c r="G3" t="n">
-        <v>90273996800</v>
+        <v>4440492343296</v>
       </c>
       <c r="H3" t="n">
-        <v>3.457</v>
+        <v>0.36</v>
       </c>
       <c r="I3" t="n">
-        <v>44.28</v>
+        <v>13.41</v>
       </c>
       <c r="J3" t="n">
-        <v>13.685</v>
+        <v>0.774</v>
       </c>
       <c r="K3" t="n">
-        <v>7639499776</v>
+        <v>730826014720</v>
       </c>
       <c r="M3" t="n">
-        <v>26022000640</v>
+        <v>3518010228736</v>
       </c>
       <c r="N3" t="n">
-        <v>6376000000</v>
+        <v>1068558516224</v>
       </c>
       <c r="O3" t="n">
-        <v>0.7256899999999999</v>
+        <v>0.6423</v>
       </c>
       <c r="P3" t="n">
-        <v>0.80370003</v>
+        <v>0.60344005</v>
       </c>
       <c r="Q3" t="n">
-        <v>21.833334</v>
+        <v>31.241611</v>
       </c>
       <c r="R3" t="n">
-        <v>12.0951185</v>
+        <v>0.48933163</v>
       </c>
       <c r="S3" t="n">
-        <v>142.924896879531</v>
+        <v>2.97317459861974</v>
       </c>
       <c r="T3" t="n">
-        <v>0.007608338867642228</v>
+        <v>-0.005365445487747644</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2875215850577266</v>
+        <v>0.03809732083456407</v>
       </c>
       <c r="V3" t="n">
-        <v>1.317802614597143</v>
+        <v>0.1684963370842598</v>
       </c>
       <c r="W3" t="n">
-        <v>7.362826824630407</v>
+        <v>0.8632972961454419</v>
       </c>
       <c r="X3" t="n">
-        <v>0.00242</v>
+        <v>0.00013</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.7999000000000001</v>
+        <v>0.15498</v>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>2026-08-23T20:11:58.832054+00:00</t>
+          <t>2026-08-23T20:56:32.173215+00:00</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
@@ -3783,7 +3774,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>2026-08-23T20:11:59.697853+00:00</t>
+          <t>2026-08-23T20:56:26.768557+00:00</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
@@ -3875,7 +3866,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>2026-08-23T20:12:05.223434+00:00</t>
+          <t>2026-08-23T20:56:34.515332+00:00</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
@@ -3967,7 +3958,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>2026-08-23T20:11:57.134125+00:00</t>
+          <t>2026-08-23T20:56:22.980204+00:00</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr">
@@ -4049,7 +4040,7 @@
         <v>0.1898762435729664</v>
       </c>
       <c r="W7" t="n">
-        <v>2.446494406067634</v>
+        <v>2.446494647256825</v>
       </c>
       <c r="X7" t="n">
         <v>0.00202</v>
@@ -4059,7 +4050,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>2026-08-23T20:12:00.109249+00:00</t>
+          <t>2026-08-23T20:56:27.340323+00:00</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr">
@@ -4151,7 +4142,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>2026-08-23T20:11:56.666713+00:00</t>
+          <t>2026-08-23T20:56:22.446230+00:00</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr">
@@ -4233,7 +4224,7 @@
         <v>2.73072935680286</v>
       </c>
       <c r="W9" t="n">
-        <v>2.502412912969455</v>
+        <v>2.50241270126798</v>
       </c>
       <c r="X9" t="n">
         <v>0.07491</v>
@@ -4243,7 +4234,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>2026-08-23T20:12:05.657235+00:00</t>
+          <t>2026-08-23T20:56:35.167598+00:00</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr">
@@ -4332,7 +4323,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>2026-08-23T20:12:08.975397+00:00</t>
+          <t>2026-08-23T20:56:39.783791+00:00</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr">
@@ -4424,7 +4415,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>2026-08-23T20:11:57.494039+00:00</t>
+          <t>2026-08-23T20:56:23.639104+00:00</t>
         </is>
       </c>
       <c r="AD11" t="inlineStr">
@@ -4506,7 +4497,7 @@
         <v>0.1400655521483041</v>
       </c>
       <c r="W12" t="n">
-        <v>0.7311824950356518</v>
+        <v>0.731182362414351</v>
       </c>
       <c r="X12" t="n">
         <v>0.01596</v>
@@ -4516,7 +4507,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>2026-08-23T20:12:01.757721+00:00</t>
+          <t>2026-08-23T20:56:29.748489+00:00</t>
         </is>
       </c>
       <c r="AD12" t="inlineStr">
@@ -4608,7 +4599,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>2026-08-23T20:11:58.346310+00:00</t>
+          <t>2026-08-23T20:56:24.947651+00:00</t>
         </is>
       </c>
       <c r="AD13" t="inlineStr">
@@ -4700,7 +4691,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>2026-08-23T20:12:07.273696+00:00</t>
+          <t>2026-08-23T20:56:37.377190+00:00</t>
         </is>
       </c>
       <c r="AD14" t="inlineStr">
@@ -4792,7 +4783,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>2026-08-23T20:11:57.895418+00:00</t>
+          <t>2026-08-23T20:56:24.263797+00:00</t>
         </is>
       </c>
       <c r="AD15" t="inlineStr">
@@ -4878,7 +4869,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>2026-08-23T20:12:06.841266+00:00</t>
+          <t>2026-08-23T20:56:36.821771+00:00</t>
         </is>
       </c>
       <c r="AD16" t="inlineStr">
@@ -4970,7 +4961,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>2026-08-23T20:12:02.164243+00:00</t>
+          <t>2026-08-23T20:56:30.275704+00:00</t>
         </is>
       </c>
       <c r="AD17" t="inlineStr">
@@ -5056,7 +5047,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>2026-08-23T20:12:08.495046+00:00</t>
+          <t>2026-08-23T20:56:39.237748+00:00</t>
         </is>
       </c>
       <c r="AD18" t="inlineStr">
@@ -5142,7 +5133,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>2026-08-23T20:12:07.698463+00:00</t>
+          <t>2026-08-23T20:56:38.052860+00:00</t>
         </is>
       </c>
       <c r="AD19" t="inlineStr">
@@ -5231,7 +5222,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>2026-08-23T20:11:59.195654+00:00</t>
+          <t>2026-08-23T20:56:26.212964+00:00</t>
         </is>
       </c>
       <c r="AD20" t="inlineStr">
@@ -5313,7 +5304,7 @@
         <v>0.07819827777494104</v>
       </c>
       <c r="W21" t="n">
-        <v>1.071721809401515</v>
+        <v>1.071721934408579</v>
       </c>
       <c r="X21" t="n">
         <v>0.00269</v>
@@ -5323,7 +5314,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>2026-08-23T20:12:06.122351+00:00</t>
+          <t>2026-08-23T20:56:35.731092+00:00</t>
         </is>
       </c>
       <c r="AD21" t="inlineStr">
@@ -5415,7 +5406,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>2026-08-23T20:12:03.968820+00:00</t>
+          <t>2026-08-23T20:56:32.782436+00:00</t>
         </is>
       </c>
       <c r="AD22" t="inlineStr">
@@ -5504,7 +5495,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>2026-08-23T20:12:06.473519+00:00</t>
+          <t>2026-08-23T20:56:36.267732+00:00</t>
         </is>
       </c>
       <c r="AD23" t="inlineStr">
@@ -5586,7 +5577,7 @@
         <v>0.2176838288473297</v>
       </c>
       <c r="W24" t="n">
-        <v>-0.0337617560157526</v>
+        <v>-0.03376187393524122</v>
       </c>
       <c r="X24" t="n">
         <v>0.00090000004</v>
@@ -5596,7 +5587,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>2026-08-23T20:12:01.401118+00:00</t>
+          <t>2026-08-23T20:56:29.208767+00:00</t>
         </is>
       </c>
       <c r="AD24" t="inlineStr">
@@ -5685,7 +5676,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>2026-08-23T20:12:00.959029+00:00</t>
+          <t>2026-08-23T20:56:28.592420+00:00</t>
         </is>
       </c>
       <c r="AD25" t="inlineStr">
@@ -5777,7 +5768,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>2026-08-23T20:12:04.324820+00:00</t>
+          <t>2026-08-23T20:56:33.381399+00:00</t>
         </is>
       </c>
       <c r="AD26" t="inlineStr">
@@ -5859,7 +5850,7 @@
         <v>-0.1456296261876776</v>
       </c>
       <c r="W27" t="n">
-        <v>-0.2535483859208238</v>
+        <v>-0.253548447765114</v>
       </c>
       <c r="X27" t="n">
         <v>0.00148</v>
@@ -5869,7 +5860,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>2026-08-23T20:12:02.619577+00:00</t>
+          <t>2026-08-23T20:56:30.906132+00:00</t>
         </is>
       </c>
       <c r="AD27" t="inlineStr">
@@ -5955,7 +5946,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>2026-08-23T20:12:00.524396+00:00</t>
+          <t>2026-08-23T20:56:27.970675+00:00</t>
         </is>
       </c>
       <c r="AD28" t="inlineStr">
@@ -6037,7 +6028,7 @@
         <v>1.979740667578479</v>
       </c>
       <c r="W29" t="n">
-        <v>2.335838148861586</v>
+        <v>2.335837790700546</v>
       </c>
       <c r="X29" t="n">
         <v>0.00494</v>
@@ -6047,7 +6038,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>2026-08-23T20:12:04.874710+00:00</t>
+          <t>2026-08-23T20:56:33.973242+00:00</t>
         </is>
       </c>
       <c r="AD29" t="inlineStr">
@@ -6139,7 +6130,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>2026-08-23T20:12:08.074931+00:00</t>
+          <t>2026-08-23T20:56:38.692117+00:00</t>
         </is>
       </c>
       <c r="AD30" t="inlineStr">
@@ -6228,7 +6219,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>2026-08-23T20:12:03.151676+00:00</t>
+          <t>2026-08-23T20:56:31.555283+00:00</t>
         </is>
       </c>
       <c r="AD31" t="inlineStr">
@@ -6256,7 +6247,7 @@
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
@@ -6313,22 +6304,27 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>MU</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>100</v>
+        <v>84.2</v>
       </c>
       <c r="C2" t="n">
-        <v>100</v>
+        <v>88.2</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MODERATE</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>price_to_sales, price_to_fcf</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -6342,11 +6338,11 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>MU</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="C3" t="n">
         <v>100</v>
@@ -6357,7 +6353,7 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -7294,11 +7290,11 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>MU</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>55.66</v>
+        <v>57.27</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -7311,7 +7307,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>100</v>
+        <v>84.2</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>

--- a/reports/investment_dashboard.xlsx
+++ b/reports/investment_dashboard.xlsx
@@ -525,16 +525,16 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>MU</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Micron Technology, Inc.</t>
+          <t>Taiwan Semiconductor Manufacturing Company Limited</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>57.27</v>
+        <v>55.66</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>966.780029296875</v>
+        <v>418.9500122070312</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -550,24 +550,19 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>84.2</v>
+        <v>100</v>
       </c>
       <c r="I2" t="n">
-        <v>88.2</v>
+        <v>100</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Revenue Growth; Earnings Fcf; Balance Sheet</t>
+          <t>Revenue Growth; Earnings Fcf; Balance Sheet; Valuation</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
           <t>Industry Growth; Competitive Advantage; Catalysts; Inflation Resilience</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>High market sensitivity / beta</t>
         </is>
       </c>
     </row>
@@ -577,16 +572,16 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>MU</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Taiwan Semiconductor Manufacturing Company Limited</t>
+          <t>Micron Technology, Inc.</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>55.66</v>
+        <v>55.05</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -594,7 +589,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>418.9500122070312</v>
+        <v>966.780029296875</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -602,19 +597,24 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="I3" t="n">
         <v>100</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Revenue Growth; Earnings Fcf; Balance Sheet; Valuation</t>
+          <t>Revenue Growth; Earnings Fcf; Balance Sheet</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
           <t>Industry Growth; Competitive Advantage; Catalysts; Inflation Resilience</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>High market sensitivity / beta</t>
         </is>
       </c>
     </row>
@@ -2120,7 +2120,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>MU</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -2133,19 +2133,19 @@
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>9.02</v>
+        <v>8.84</v>
       </c>
       <c r="F2" t="n">
-        <v>7.04</v>
+        <v>8.67</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>7.71</v>
+        <v>5.46</v>
       </c>
       <c r="I2" t="n">
-        <v>3.5</v>
+        <v>2.69</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -2154,13 +2154,13 @@
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>57.27</v>
+        <v>55.66</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>MU</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -2173,19 +2173,19 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>8.84</v>
+        <v>9.02</v>
       </c>
       <c r="F3" t="n">
-        <v>8.67</v>
+        <v>4.82</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>5.46</v>
+        <v>7.71</v>
       </c>
       <c r="I3" t="n">
-        <v>2.69</v>
+        <v>3.5</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -2194,7 +2194,7 @@
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>55.66</v>
+        <v>55.05</v>
       </c>
     </row>
     <row r="4">
@@ -3519,12 +3519,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>MU</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Micron Technology, Inc.</t>
+          <t>Taiwan Semiconductor Manufacturing Company Limited</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -3537,60 +3537,69 @@
           <t>Semiconductors</t>
         </is>
       </c>
+      <c r="E2" t="n">
+        <v>2172873342976</v>
+      </c>
       <c r="F2" t="n">
-        <v>966.780029296875</v>
+        <v>418.9500122070312</v>
       </c>
       <c r="G2" t="n">
-        <v>90273996800</v>
+        <v>4440492343296</v>
       </c>
       <c r="H2" t="n">
-        <v>3.457</v>
+        <v>0.36</v>
       </c>
       <c r="I2" t="n">
-        <v>44.28</v>
+        <v>13.41</v>
       </c>
       <c r="J2" t="n">
-        <v>13.685</v>
+        <v>0.774</v>
       </c>
       <c r="K2" t="n">
-        <v>7639499776</v>
+        <v>730826014720</v>
       </c>
       <c r="M2" t="n">
-        <v>26022000640</v>
+        <v>3518010228736</v>
       </c>
       <c r="N2" t="n">
-        <v>6376000000</v>
+        <v>1068558516224</v>
       </c>
       <c r="O2" t="n">
-        <v>0.7256899999999999</v>
+        <v>0.6423</v>
       </c>
       <c r="P2" t="n">
-        <v>0.80370003</v>
+        <v>0.60344005</v>
       </c>
       <c r="Q2" t="n">
-        <v>21.833334</v>
+        <v>31.241611</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0.48933163</v>
+      </c>
+      <c r="S2" t="n">
+        <v>2.97317459861974</v>
       </c>
       <c r="T2" t="n">
-        <v>0.007608338867642228</v>
+        <v>-0.005365445487747644</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2875215850577266</v>
+        <v>0.03809732083456407</v>
       </c>
       <c r="V2" t="n">
-        <v>1.317802614597143</v>
+        <v>0.1684963370842598</v>
       </c>
       <c r="W2" t="n">
-        <v>7.362826824630407</v>
+        <v>0.8632972961454419</v>
       </c>
       <c r="X2" t="n">
-        <v>0.00242</v>
+        <v>0.00013</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.7999000000000001</v>
+        <v>0.15498</v>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>2026-08-23T20:56:25.624226+00:00</t>
+          <t>2026-08-23T21:04:23.151921+00:00</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
@@ -3602,12 +3611,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>MU</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Taiwan Semiconductor Manufacturing Company Limited</t>
+          <t>Micron Technology, Inc.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -3621,68 +3630,68 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2172873342976</v>
+        <v>1091874717696</v>
       </c>
       <c r="F3" t="n">
-        <v>418.9500122070312</v>
+        <v>966.780029296875</v>
       </c>
       <c r="G3" t="n">
-        <v>4440492343296</v>
+        <v>90273996800</v>
       </c>
       <c r="H3" t="n">
-        <v>0.36</v>
+        <v>3.457</v>
       </c>
       <c r="I3" t="n">
-        <v>13.41</v>
+        <v>44.28</v>
       </c>
       <c r="J3" t="n">
-        <v>0.774</v>
+        <v>13.685</v>
       </c>
       <c r="K3" t="n">
-        <v>730826014720</v>
+        <v>7639499776</v>
       </c>
       <c r="M3" t="n">
-        <v>3518010228736</v>
+        <v>26022000640</v>
       </c>
       <c r="N3" t="n">
-        <v>1068558516224</v>
+        <v>6376000000</v>
       </c>
       <c r="O3" t="n">
-        <v>0.6423</v>
+        <v>0.7256899999999999</v>
       </c>
       <c r="P3" t="n">
-        <v>0.60344005</v>
+        <v>0.80370003</v>
       </c>
       <c r="Q3" t="n">
-        <v>31.241611</v>
+        <v>21.833334</v>
       </c>
       <c r="R3" t="n">
-        <v>0.48933163</v>
+        <v>12.0951185</v>
       </c>
       <c r="S3" t="n">
-        <v>2.97317459861974</v>
+        <v>142.924896879531</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.005365445487747644</v>
+        <v>0.007608338867642228</v>
       </c>
       <c r="U3" t="n">
-        <v>0.03809732083456407</v>
+        <v>0.2875215850577266</v>
       </c>
       <c r="V3" t="n">
-        <v>0.1684963370842598</v>
+        <v>1.317802614597143</v>
       </c>
       <c r="W3" t="n">
-        <v>0.8632972961454419</v>
+        <v>7.362827376540883</v>
       </c>
       <c r="X3" t="n">
-        <v>0.00013</v>
+        <v>0.00242</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.15498</v>
+        <v>0.7999000000000001</v>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>2026-08-23T20:56:32.173215+00:00</t>
+          <t>2026-08-23T21:04:19.791860+00:00</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
@@ -3774,7 +3783,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>2026-08-23T20:56:26.768557+00:00</t>
+          <t>2026-08-23T21:04:20.399434+00:00</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
@@ -3866,7 +3875,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>2026-08-23T20:56:34.515332+00:00</t>
+          <t>2026-08-23T21:04:24.433284+00:00</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
@@ -3958,7 +3967,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>2026-08-23T20:56:22.980204+00:00</t>
+          <t>2026-08-23T21:04:18.311436+00:00</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr">
@@ -4040,7 +4049,7 @@
         <v>0.1898762435729664</v>
       </c>
       <c r="W7" t="n">
-        <v>2.446494647256825</v>
+        <v>2.446494888446049</v>
       </c>
       <c r="X7" t="n">
         <v>0.00202</v>
@@ -4050,7 +4059,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>2026-08-23T20:56:27.340323+00:00</t>
+          <t>2026-08-23T21:04:20.731674+00:00</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr">
@@ -4132,7 +4141,7 @@
         <v>0.144129303232654</v>
       </c>
       <c r="W8" t="n">
-        <v>0.2287461792392489</v>
+        <v>0.2287460719461247</v>
       </c>
       <c r="X8" t="n">
         <v>0.03991</v>
@@ -4142,7 +4151,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>2026-08-23T20:56:22.446230+00:00</t>
+          <t>2026-08-23T21:04:18.001839+00:00</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr">
@@ -4234,7 +4243,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>2026-08-23T20:56:35.167598+00:00</t>
+          <t>2026-08-23T21:04:24.705796+00:00</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr">
@@ -4323,7 +4332,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>2026-08-23T20:56:39.783791+00:00</t>
+          <t>2026-08-23T21:04:26.909921+00:00</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr">
@@ -4415,7 +4424,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>2026-08-23T20:56:23.639104+00:00</t>
+          <t>2026-08-23T21:04:18.580078+00:00</t>
         </is>
       </c>
       <c r="AD11" t="inlineStr">
@@ -4497,7 +4506,7 @@
         <v>0.1400655521483041</v>
       </c>
       <c r="W12" t="n">
-        <v>0.731182362414351</v>
+        <v>0.7311824950356518</v>
       </c>
       <c r="X12" t="n">
         <v>0.01596</v>
@@ -4507,7 +4516,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>2026-08-23T20:56:29.748489+00:00</t>
+          <t>2026-08-23T21:04:21.921530+00:00</t>
         </is>
       </c>
       <c r="AD12" t="inlineStr">
@@ -4599,7 +4608,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>2026-08-23T20:56:24.947651+00:00</t>
+          <t>2026-08-23T21:04:19.358155+00:00</t>
         </is>
       </c>
       <c r="AD13" t="inlineStr">
@@ -4691,7 +4700,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>2026-08-23T20:56:37.377190+00:00</t>
+          <t>2026-08-23T21:04:25.856589+00:00</t>
         </is>
       </c>
       <c r="AD14" t="inlineStr">
@@ -4773,7 +4782,7 @@
         <v>0.1072405701495147</v>
       </c>
       <c r="W15" t="n">
-        <v>0.2815942361128876</v>
+        <v>0.2815943721547682</v>
       </c>
       <c r="X15" t="n">
         <v>0.01948</v>
@@ -4783,7 +4792,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>2026-08-23T20:56:24.263797+00:00</t>
+          <t>2026-08-23T21:04:18.948271+00:00</t>
         </is>
       </c>
       <c r="AD15" t="inlineStr">
@@ -4869,7 +4878,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>2026-08-23T20:56:36.821771+00:00</t>
+          <t>2026-08-23T21:04:25.573334+00:00</t>
         </is>
       </c>
       <c r="AD16" t="inlineStr">
@@ -4961,7 +4970,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>2026-08-23T20:56:30.275704+00:00</t>
+          <t>2026-08-23T21:04:22.170682+00:00</t>
         </is>
       </c>
       <c r="AD17" t="inlineStr">
@@ -5047,7 +5056,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>2026-08-23T20:56:39.237748+00:00</t>
+          <t>2026-08-23T21:04:26.662166+00:00</t>
         </is>
       </c>
       <c r="AD18" t="inlineStr">
@@ -5133,7 +5142,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>2026-08-23T20:56:38.052860+00:00</t>
+          <t>2026-08-23T21:04:26.106824+00:00</t>
         </is>
       </c>
       <c r="AD19" t="inlineStr">
@@ -5222,7 +5231,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>2026-08-23T20:56:26.212964+00:00</t>
+          <t>2026-08-23T21:04:20.038475+00:00</t>
         </is>
       </c>
       <c r="AD20" t="inlineStr">
@@ -5304,7 +5313,7 @@
         <v>0.07819827777494104</v>
       </c>
       <c r="W21" t="n">
-        <v>1.071721934408579</v>
+        <v>1.071721809401515</v>
       </c>
       <c r="X21" t="n">
         <v>0.00269</v>
@@ -5314,7 +5323,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>2026-08-23T20:56:35.731092+00:00</t>
+          <t>2026-08-23T21:04:24.977873+00:00</t>
         </is>
       </c>
       <c r="AD21" t="inlineStr">
@@ -5396,7 +5405,7 @@
         <v>0.2131482647002914</v>
       </c>
       <c r="W22" t="n">
-        <v>1.414165403503707</v>
+        <v>1.414165201818253</v>
       </c>
       <c r="X22" t="n">
         <v>0.00016000001</v>
@@ -5406,7 +5415,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>2026-08-23T20:56:32.782436+00:00</t>
+          <t>2026-08-23T21:04:23.465604+00:00</t>
         </is>
       </c>
       <c r="AD22" t="inlineStr">
@@ -5495,7 +5504,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>2026-08-23T20:56:36.267732+00:00</t>
+          <t>2026-08-23T21:04:25.240738+00:00</t>
         </is>
       </c>
       <c r="AD23" t="inlineStr">
@@ -5577,7 +5586,7 @@
         <v>0.2176838288473297</v>
       </c>
       <c r="W24" t="n">
-        <v>-0.03376187393524122</v>
+        <v>-0.03376181497550057</v>
       </c>
       <c r="X24" t="n">
         <v>0.00090000004</v>
@@ -5587,7 +5596,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>2026-08-23T20:56:29.208767+00:00</t>
+          <t>2026-08-23T21:04:21.633654+00:00</t>
         </is>
       </c>
       <c r="AD24" t="inlineStr">
@@ -5676,7 +5685,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>2026-08-23T20:56:28.592420+00:00</t>
+          <t>2026-08-23T21:04:21.310373+00:00</t>
         </is>
       </c>
       <c r="AD25" t="inlineStr">
@@ -5768,7 +5777,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>2026-08-23T20:56:33.381399+00:00</t>
+          <t>2026-08-23T21:04:23.707653+00:00</t>
         </is>
       </c>
       <c r="AD26" t="inlineStr">
@@ -5850,7 +5859,7 @@
         <v>-0.1456296261876776</v>
       </c>
       <c r="W27" t="n">
-        <v>-0.253548447765114</v>
+        <v>-0.2535483859208238</v>
       </c>
       <c r="X27" t="n">
         <v>0.00148</v>
@@ -5860,7 +5869,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>2026-08-23T20:56:30.906132+00:00</t>
+          <t>2026-08-23T21:04:22.537691+00:00</t>
         </is>
       </c>
       <c r="AD27" t="inlineStr">
@@ -5946,7 +5955,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>2026-08-23T20:56:27.970675+00:00</t>
+          <t>2026-08-23T21:04:21.001880+00:00</t>
         </is>
       </c>
       <c r="AD28" t="inlineStr">
@@ -6028,7 +6037,7 @@
         <v>1.979740667578479</v>
       </c>
       <c r="W29" t="n">
-        <v>2.335837790700546</v>
+        <v>2.335838507022704</v>
       </c>
       <c r="X29" t="n">
         <v>0.00494</v>
@@ -6038,7 +6047,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>2026-08-23T20:56:33.973242+00:00</t>
+          <t>2026-08-23T21:04:24.026199+00:00</t>
         </is>
       </c>
       <c r="AD29" t="inlineStr">
@@ -6130,7 +6139,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>2026-08-23T20:56:38.692117+00:00</t>
+          <t>2026-08-23T21:04:26.405839+00:00</t>
         </is>
       </c>
       <c r="AD30" t="inlineStr">
@@ -6209,7 +6218,7 @@
         <v>-0.05779410309686361</v>
       </c>
       <c r="W31" t="n">
-        <v>-0.3646448121864612</v>
+        <v>-0.3646448542401906</v>
       </c>
       <c r="X31" t="n">
         <v>0.40498</v>
@@ -6219,7 +6228,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>2026-08-23T20:56:31.555283+00:00</t>
+          <t>2026-08-23T21:04:22.835465+00:00</t>
         </is>
       </c>
       <c r="AD31" t="inlineStr">
@@ -6247,7 +6256,7 @@
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
@@ -6304,27 +6313,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>MU</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>84.2</v>
+        <v>100</v>
       </c>
       <c r="C2" t="n">
-        <v>88.2</v>
+        <v>100</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>MODERATE</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>price_to_sales, price_to_fcf</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -6338,11 +6342,11 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>MU</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="C3" t="n">
         <v>100</v>
@@ -6353,7 +6357,7 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -7290,11 +7294,11 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>MU</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>57.27</v>
+        <v>55.66</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -7307,7 +7311,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>84.2</v>
+        <v>100</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>

--- a/reports/investment_dashboard.xlsx
+++ b/reports/investment_dashboard.xlsx
@@ -3589,7 +3589,7 @@
         <v>0.1684963370842598</v>
       </c>
       <c r="W2" t="n">
-        <v>0.8632972961454419</v>
+        <v>0.8632971696944793</v>
       </c>
       <c r="X2" t="n">
         <v>0.00013</v>
@@ -3599,7 +3599,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>2026-08-23T21:04:23.151921+00:00</t>
+          <t>2026-08-23T21:18:30.592402+00:00</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
@@ -3681,7 +3681,7 @@
         <v>1.317802614597143</v>
       </c>
       <c r="W3" t="n">
-        <v>7.362827376540883</v>
+        <v>7.362826824630407</v>
       </c>
       <c r="X3" t="n">
         <v>0.00242</v>
@@ -3691,7 +3691,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>2026-08-23T21:04:19.791860+00:00</t>
+          <t>2026-08-23T21:18:25.640064+00:00</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
@@ -3783,7 +3783,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>2026-08-23T21:04:20.399434+00:00</t>
+          <t>2026-08-23T21:18:26.534719+00:00</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
@@ -3875,7 +3875,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>2026-08-23T21:04:24.433284+00:00</t>
+          <t>2026-08-23T21:18:32.563117+00:00</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
@@ -3967,7 +3967,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>2026-08-23T21:04:18.311436+00:00</t>
+          <t>2026-08-23T21:18:23.592789+00:00</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr">
@@ -4049,7 +4049,7 @@
         <v>0.1898762435729664</v>
       </c>
       <c r="W7" t="n">
-        <v>2.446494888446049</v>
+        <v>2.446494406067634</v>
       </c>
       <c r="X7" t="n">
         <v>0.00202</v>
@@ -4059,7 +4059,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>2026-08-23T21:04:20.731674+00:00</t>
+          <t>2026-08-23T21:18:26.947671+00:00</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr">
@@ -4151,7 +4151,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>2026-08-23T21:04:18.001839+00:00</t>
+          <t>2026-08-23T21:18:23.163377+00:00</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr">
@@ -4243,7 +4243,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>2026-08-23T21:04:24.705796+00:00</t>
+          <t>2026-08-23T21:18:33.017641+00:00</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr">
@@ -4332,7 +4332,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>2026-08-23T21:04:26.909921+00:00</t>
+          <t>2026-08-23T21:18:36.738640+00:00</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr">
@@ -4424,7 +4424,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>2026-08-23T21:04:18.580078+00:00</t>
+          <t>2026-08-23T21:18:24.049900+00:00</t>
         </is>
       </c>
       <c r="AD11" t="inlineStr">
@@ -4506,7 +4506,7 @@
         <v>0.1400655521483041</v>
       </c>
       <c r="W12" t="n">
-        <v>0.7311824950356518</v>
+        <v>0.731182362414351</v>
       </c>
       <c r="X12" t="n">
         <v>0.01596</v>
@@ -4516,7 +4516,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>2026-08-23T21:04:21.921530+00:00</t>
+          <t>2026-08-23T21:18:28.669566+00:00</t>
         </is>
       </c>
       <c r="AD12" t="inlineStr">
@@ -4608,7 +4608,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>2026-08-23T21:04:19.358155+00:00</t>
+          <t>2026-08-23T21:18:25.054872+00:00</t>
         </is>
       </c>
       <c r="AD13" t="inlineStr">
@@ -4700,7 +4700,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>2026-08-23T21:04:25.856589+00:00</t>
+          <t>2026-08-23T21:18:34.907399+00:00</t>
         </is>
       </c>
       <c r="AD14" t="inlineStr">
@@ -4782,7 +4782,7 @@
         <v>0.1072405701495147</v>
       </c>
       <c r="W15" t="n">
-        <v>0.2815943721547682</v>
+        <v>0.2815942361128876</v>
       </c>
       <c r="X15" t="n">
         <v>0.01948</v>
@@ -4792,7 +4792,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>2026-08-23T21:04:18.948271+00:00</t>
+          <t>2026-08-23T21:18:24.488209+00:00</t>
         </is>
       </c>
       <c r="AD15" t="inlineStr">
@@ -4878,7 +4878,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>2026-08-23T21:04:25.573334+00:00</t>
+          <t>2026-08-23T21:18:34.478048+00:00</t>
         </is>
       </c>
       <c r="AD16" t="inlineStr">
@@ -4970,7 +4970,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>2026-08-23T21:04:22.170682+00:00</t>
+          <t>2026-08-23T21:18:29.036884+00:00</t>
         </is>
       </c>
       <c r="AD17" t="inlineStr">
@@ -5056,7 +5056,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>2026-08-23T21:04:26.662166+00:00</t>
+          <t>2026-08-23T21:18:36.218976+00:00</t>
         </is>
       </c>
       <c r="AD18" t="inlineStr">
@@ -5142,7 +5142,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>2026-08-23T21:04:26.106824+00:00</t>
+          <t>2026-08-23T21:18:35.264942+00:00</t>
         </is>
       </c>
       <c r="AD19" t="inlineStr">
@@ -5231,7 +5231,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>2026-08-23T21:04:20.038475+00:00</t>
+          <t>2026-08-23T21:18:26.053078+00:00</t>
         </is>
       </c>
       <c r="AD20" t="inlineStr">
@@ -5313,7 +5313,7 @@
         <v>0.07819827777494104</v>
       </c>
       <c r="W21" t="n">
-        <v>1.071721809401515</v>
+        <v>1.071721934408579</v>
       </c>
       <c r="X21" t="n">
         <v>0.00269</v>
@@ -5323,7 +5323,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>2026-08-23T21:04:24.977873+00:00</t>
+          <t>2026-08-23T21:18:33.403568+00:00</t>
         </is>
       </c>
       <c r="AD21" t="inlineStr">
@@ -5405,7 +5405,7 @@
         <v>0.2131482647002914</v>
       </c>
       <c r="W22" t="n">
-        <v>1.414165201818253</v>
+        <v>1.414165403503707</v>
       </c>
       <c r="X22" t="n">
         <v>0.00016000001</v>
@@ -5415,7 +5415,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>2026-08-23T21:04:23.465604+00:00</t>
+          <t>2026-08-23T21:18:31.127094+00:00</t>
         </is>
       </c>
       <c r="AD22" t="inlineStr">
@@ -5504,7 +5504,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>2026-08-23T21:04:25.240738+00:00</t>
+          <t>2026-08-23T21:18:33.859128+00:00</t>
         </is>
       </c>
       <c r="AD23" t="inlineStr">
@@ -5586,7 +5586,7 @@
         <v>0.2176838288473297</v>
       </c>
       <c r="W24" t="n">
-        <v>-0.03376181497550057</v>
+        <v>-0.03376187393524122</v>
       </c>
       <c r="X24" t="n">
         <v>0.00090000004</v>
@@ -5596,7 +5596,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>2026-08-23T21:04:21.633654+00:00</t>
+          <t>2026-08-23T21:18:28.182003+00:00</t>
         </is>
       </c>
       <c r="AD24" t="inlineStr">
@@ -5685,7 +5685,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>2026-08-23T21:04:21.310373+00:00</t>
+          <t>2026-08-23T21:18:27.673777+00:00</t>
         </is>
       </c>
       <c r="AD25" t="inlineStr">
@@ -5777,7 +5777,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>2026-08-23T21:04:23.707653+00:00</t>
+          <t>2026-08-23T21:18:31.636981+00:00</t>
         </is>
       </c>
       <c r="AD26" t="inlineStr">
@@ -5869,7 +5869,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>2026-08-23T21:04:22.537691+00:00</t>
+          <t>2026-08-23T21:18:29.606174+00:00</t>
         </is>
       </c>
       <c r="AD27" t="inlineStr">
@@ -5955,7 +5955,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>2026-08-23T21:04:21.001880+00:00</t>
+          <t>2026-08-23T21:18:27.311000+00:00</t>
         </is>
       </c>
       <c r="AD28" t="inlineStr">
@@ -6037,7 +6037,7 @@
         <v>1.979740667578479</v>
       </c>
       <c r="W29" t="n">
-        <v>2.335838507022704</v>
+        <v>2.335837790700546</v>
       </c>
       <c r="X29" t="n">
         <v>0.00494</v>
@@ -6047,7 +6047,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>2026-08-23T21:04:24.026199+00:00</t>
+          <t>2026-08-23T21:18:32.113041+00:00</t>
         </is>
       </c>
       <c r="AD29" t="inlineStr">
@@ -6139,7 +6139,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>2026-08-23T21:04:26.405839+00:00</t>
+          <t>2026-08-23T21:18:35.782008+00:00</t>
         </is>
       </c>
       <c r="AD30" t="inlineStr">
@@ -6218,7 +6218,7 @@
         <v>-0.05779410309686361</v>
       </c>
       <c r="W31" t="n">
-        <v>-0.3646448542401906</v>
+        <v>-0.3646448121864612</v>
       </c>
       <c r="X31" t="n">
         <v>0.40498</v>
@@ -6228,7 +6228,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>2026-08-23T21:04:22.835465+00:00</t>
+          <t>2026-08-23T21:18:30.033937+00:00</t>
         </is>
       </c>
       <c r="AD31" t="inlineStr">

--- a/reports/investment_dashboard.xlsx
+++ b/reports/investment_dashboard.xlsx
@@ -3589,7 +3589,7 @@
         <v>0.1684963370842598</v>
       </c>
       <c r="W2" t="n">
-        <v>0.8632971696944793</v>
+        <v>0.8632972961454419</v>
       </c>
       <c r="X2" t="n">
         <v>0.00013</v>
@@ -3599,7 +3599,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>2026-08-23T21:18:30.592402+00:00</t>
+          <t>2026-08-23T22:31:06.786822+00:00</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
@@ -3681,7 +3681,7 @@
         <v>1.317802614597143</v>
       </c>
       <c r="W3" t="n">
-        <v>7.362826824630407</v>
+        <v>7.362826272720001</v>
       </c>
       <c r="X3" t="n">
         <v>0.00242</v>
@@ -3691,7 +3691,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>2026-08-23T21:18:25.640064+00:00</t>
+          <t>2026-08-23T22:31:02.307015+00:00</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
@@ -3783,7 +3783,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>2026-08-23T21:18:26.534719+00:00</t>
+          <t>2026-08-23T22:31:03.035007+00:00</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
@@ -3875,7 +3875,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>2026-08-23T21:18:32.563117+00:00</t>
+          <t>2026-08-23T22:31:08.408785+00:00</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
@@ -3967,7 +3967,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>2026-08-23T21:18:23.592789+00:00</t>
+          <t>2026-08-23T22:31:00.486813+00:00</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr">
@@ -4049,7 +4049,7 @@
         <v>0.1898762435729664</v>
       </c>
       <c r="W7" t="n">
-        <v>2.446494406067634</v>
+        <v>2.446494647256825</v>
       </c>
       <c r="X7" t="n">
         <v>0.00202</v>
@@ -4059,7 +4059,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>2026-08-23T21:18:26.947671+00:00</t>
+          <t>2026-08-23T22:31:03.525589+00:00</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr">
@@ -4141,7 +4141,7 @@
         <v>0.144129303232654</v>
       </c>
       <c r="W8" t="n">
-        <v>0.2287460719461247</v>
+        <v>0.2287461792392489</v>
       </c>
       <c r="X8" t="n">
         <v>0.03991</v>
@@ -4151,7 +4151,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>2026-08-23T21:18:23.163377+00:00</t>
+          <t>2026-08-23T22:31:00.113774+00:00</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr">
@@ -4243,7 +4243,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>2026-08-23T21:18:33.017641+00:00</t>
+          <t>2026-08-23T22:31:08.906181+00:00</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr">
@@ -4332,7 +4332,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>2026-08-23T21:18:36.738640+00:00</t>
+          <t>2026-08-23T22:31:12.040330+00:00</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr">
@@ -4424,7 +4424,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>2026-08-23T21:18:24.049900+00:00</t>
+          <t>2026-08-23T22:31:00.974142+00:00</t>
         </is>
       </c>
       <c r="AD11" t="inlineStr">
@@ -4516,7 +4516,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>2026-08-23T21:18:28.669566+00:00</t>
+          <t>2026-08-23T22:31:05.228552+00:00</t>
         </is>
       </c>
       <c r="AD12" t="inlineStr">
@@ -4608,7 +4608,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>2026-08-23T21:18:25.054872+00:00</t>
+          <t>2026-08-23T22:31:01.868332+00:00</t>
         </is>
       </c>
       <c r="AD13" t="inlineStr">
@@ -4700,7 +4700,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>2026-08-23T21:18:34.907399+00:00</t>
+          <t>2026-08-23T22:31:10.451262+00:00</t>
         </is>
       </c>
       <c r="AD14" t="inlineStr">
@@ -4782,7 +4782,7 @@
         <v>0.1072405701495147</v>
       </c>
       <c r="W15" t="n">
-        <v>0.2815942361128876</v>
+        <v>0.2815941000710358</v>
       </c>
       <c r="X15" t="n">
         <v>0.01948</v>
@@ -4792,7 +4792,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>2026-08-23T21:18:24.488209+00:00</t>
+          <t>2026-08-23T22:31:01.403710+00:00</t>
         </is>
       </c>
       <c r="AD15" t="inlineStr">
@@ -4878,7 +4878,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>2026-08-23T21:18:34.478048+00:00</t>
+          <t>2026-08-23T22:31:10.088146+00:00</t>
         </is>
       </c>
       <c r="AD16" t="inlineStr">
@@ -4970,7 +4970,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>2026-08-23T21:18:29.036884+00:00</t>
+          <t>2026-08-23T22:31:05.581704+00:00</t>
         </is>
       </c>
       <c r="AD17" t="inlineStr">
@@ -5056,7 +5056,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>2026-08-23T21:18:36.218976+00:00</t>
+          <t>2026-08-23T22:31:11.614867+00:00</t>
         </is>
       </c>
       <c r="AD18" t="inlineStr">
@@ -5142,7 +5142,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>2026-08-23T21:18:35.264942+00:00</t>
+          <t>2026-08-23T22:31:10.807436+00:00</t>
         </is>
       </c>
       <c r="AD19" t="inlineStr">
@@ -5231,7 +5231,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>2026-08-23T21:18:26.053078+00:00</t>
+          <t>2026-08-23T22:31:02.664056+00:00</t>
         </is>
       </c>
       <c r="AD20" t="inlineStr">
@@ -5313,7 +5313,7 @@
         <v>0.07819827777494104</v>
       </c>
       <c r="W21" t="n">
-        <v>1.071721934408579</v>
+        <v>1.071721809401515</v>
       </c>
       <c r="X21" t="n">
         <v>0.00269</v>
@@ -5323,7 +5323,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>2026-08-23T21:18:33.403568+00:00</t>
+          <t>2026-08-23T22:31:09.281737+00:00</t>
         </is>
       </c>
       <c r="AD21" t="inlineStr">
@@ -5415,7 +5415,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>2026-08-23T21:18:31.127094+00:00</t>
+          <t>2026-08-23T22:31:07.225873+00:00</t>
         </is>
       </c>
       <c r="AD22" t="inlineStr">
@@ -5504,7 +5504,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>2026-08-23T21:18:33.859128+00:00</t>
+          <t>2026-08-23T22:31:09.736522+00:00</t>
         </is>
       </c>
       <c r="AD23" t="inlineStr">
@@ -5596,7 +5596,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>2026-08-23T21:18:28.182003+00:00</t>
+          <t>2026-08-23T22:31:04.780624+00:00</t>
         </is>
       </c>
       <c r="AD24" t="inlineStr">
@@ -5685,7 +5685,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>2026-08-23T21:18:27.673777+00:00</t>
+          <t>2026-08-23T22:31:04.379199+00:00</t>
         </is>
       </c>
       <c r="AD25" t="inlineStr">
@@ -5777,7 +5777,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>2026-08-23T21:18:31.636981+00:00</t>
+          <t>2026-08-23T22:31:07.651415+00:00</t>
         </is>
       </c>
       <c r="AD26" t="inlineStr">
@@ -5859,7 +5859,7 @@
         <v>-0.1456296261876776</v>
       </c>
       <c r="W27" t="n">
-        <v>-0.2535483859208238</v>
+        <v>-0.253548447765114</v>
       </c>
       <c r="X27" t="n">
         <v>0.00148</v>
@@ -5869,7 +5869,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>2026-08-23T21:18:29.606174+00:00</t>
+          <t>2026-08-23T22:31:05.945866+00:00</t>
         </is>
       </c>
       <c r="AD27" t="inlineStr">
@@ -5955,7 +5955,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>2026-08-23T21:18:27.311000+00:00</t>
+          <t>2026-08-23T22:31:03.899151+00:00</t>
         </is>
       </c>
       <c r="AD28" t="inlineStr">
@@ -6047,7 +6047,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>2026-08-23T21:18:32.113041+00:00</t>
+          <t>2026-08-23T22:31:08.044042+00:00</t>
         </is>
       </c>
       <c r="AD29" t="inlineStr">
@@ -6139,7 +6139,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>2026-08-23T21:18:35.782008+00:00</t>
+          <t>2026-08-23T22:31:11.240760+00:00</t>
         </is>
       </c>
       <c r="AD30" t="inlineStr">
@@ -6228,7 +6228,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>2026-08-23T21:18:30.033937+00:00</t>
+          <t>2026-08-23T22:31:06.347958+00:00</t>
         </is>
       </c>
       <c r="AD31" t="inlineStr">

--- a/reports/investment_dashboard.xlsx
+++ b/reports/investment_dashboard.xlsx
@@ -3589,7 +3589,7 @@
         <v>0.1684963370842598</v>
       </c>
       <c r="W2" t="n">
-        <v>0.8632972961454419</v>
+        <v>0.8632971696944793</v>
       </c>
       <c r="X2" t="n">
         <v>0.00013</v>
@@ -3599,7 +3599,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>2026-08-23T22:31:06.786822+00:00</t>
+          <t>2026-08-23T22:52:49.436918+00:00</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
@@ -3681,7 +3681,7 @@
         <v>1.317802614597143</v>
       </c>
       <c r="W3" t="n">
-        <v>7.362826272720001</v>
+        <v>7.362827376540883</v>
       </c>
       <c r="X3" t="n">
         <v>0.00242</v>
@@ -3691,7 +3691,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>2026-08-23T22:31:02.307015+00:00</t>
+          <t>2026-08-23T22:52:46.169677+00:00</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
@@ -3783,7 +3783,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>2026-08-23T22:31:03.035007+00:00</t>
+          <t>2026-08-23T22:52:46.743683+00:00</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
@@ -3875,7 +3875,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>2026-08-23T22:31:08.408785+00:00</t>
+          <t>2026-08-23T22:52:50.577334+00:00</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
@@ -3967,7 +3967,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>2026-08-23T22:31:00.486813+00:00</t>
+          <t>2026-08-23T22:52:44.958695+00:00</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr">
@@ -4049,7 +4049,7 @@
         <v>0.1898762435729664</v>
       </c>
       <c r="W7" t="n">
-        <v>2.446494647256825</v>
+        <v>2.446494406067634</v>
       </c>
       <c r="X7" t="n">
         <v>0.00202</v>
@@ -4059,7 +4059,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>2026-08-23T22:31:03.525589+00:00</t>
+          <t>2026-08-23T22:52:47.043984+00:00</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr">
@@ -4141,7 +4141,7 @@
         <v>0.144129303232654</v>
       </c>
       <c r="W8" t="n">
-        <v>0.2287461792392489</v>
+        <v>0.2287460719461247</v>
       </c>
       <c r="X8" t="n">
         <v>0.03991</v>
@@ -4151,7 +4151,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>2026-08-23T22:31:00.113774+00:00</t>
+          <t>2026-08-23T22:52:44.710006+00:00</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr">
@@ -4233,7 +4233,7 @@
         <v>2.73072935680286</v>
       </c>
       <c r="W9" t="n">
-        <v>2.50241270126798</v>
+        <v>2.502412912969455</v>
       </c>
       <c r="X9" t="n">
         <v>0.07491</v>
@@ -4243,7 +4243,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>2026-08-23T22:31:08.906181+00:00</t>
+          <t>2026-08-23T22:52:50.848312+00:00</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr">
@@ -4332,7 +4332,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>2026-08-23T22:31:12.040330+00:00</t>
+          <t>2026-08-23T22:52:53.001946+00:00</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr">
@@ -4424,7 +4424,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>2026-08-23T22:31:00.974142+00:00</t>
+          <t>2026-08-23T22:52:45.208810+00:00</t>
         </is>
       </c>
       <c r="AD11" t="inlineStr">
@@ -4516,7 +4516,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>2026-08-23T22:31:05.228552+00:00</t>
+          <t>2026-08-23T22:52:48.203924+00:00</t>
         </is>
       </c>
       <c r="AD12" t="inlineStr">
@@ -4598,7 +4598,7 @@
         <v>0.3342865245955684</v>
       </c>
       <c r="W13" t="n">
-        <v>2.097116106946919</v>
+        <v>2.097116404241915</v>
       </c>
       <c r="X13" t="n">
         <v>0.00331</v>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>2026-08-23T22:31:01.868332+00:00</t>
+          <t>2026-08-23T22:52:45.836092+00:00</t>
         </is>
       </c>
       <c r="AD13" t="inlineStr">
@@ -4700,7 +4700,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>2026-08-23T22:31:10.451262+00:00</t>
+          <t>2026-08-23T22:52:51.908319+00:00</t>
         </is>
       </c>
       <c r="AD14" t="inlineStr">
@@ -4779,10 +4779,10 @@
         <v>-0.1089169343844046</v>
       </c>
       <c r="V15" t="n">
-        <v>0.1072405701495147</v>
+        <v>0.1072406716938052</v>
       </c>
       <c r="W15" t="n">
-        <v>0.2815941000710358</v>
+        <v>0.2815942361128876</v>
       </c>
       <c r="X15" t="n">
         <v>0.01948</v>
@@ -4792,7 +4792,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>2026-08-23T22:31:01.403710+00:00</t>
+          <t>2026-08-23T22:52:45.509730+00:00</t>
         </is>
       </c>
       <c r="AD15" t="inlineStr">
@@ -4878,7 +4878,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>2026-08-23T22:31:10.088146+00:00</t>
+          <t>2026-08-23T22:52:51.611934+00:00</t>
         </is>
       </c>
       <c r="AD16" t="inlineStr">
@@ -4970,7 +4970,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>2026-08-23T22:31:05.581704+00:00</t>
+          <t>2026-08-23T22:52:48.464770+00:00</t>
         </is>
       </c>
       <c r="AD17" t="inlineStr">
@@ -5056,7 +5056,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>2026-08-23T22:31:11.614867+00:00</t>
+          <t>2026-08-23T22:52:52.742446+00:00</t>
         </is>
       </c>
       <c r="AD18" t="inlineStr">
@@ -5142,7 +5142,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>2026-08-23T22:31:10.807436+00:00</t>
+          <t>2026-08-23T22:52:52.158191+00:00</t>
         </is>
       </c>
       <c r="AD19" t="inlineStr">
@@ -5231,7 +5231,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>2026-08-23T22:31:02.664056+00:00</t>
+          <t>2026-08-23T22:52:46.426423+00:00</t>
         </is>
       </c>
       <c r="AD20" t="inlineStr">
@@ -5313,7 +5313,7 @@
         <v>0.07819827777494104</v>
       </c>
       <c r="W21" t="n">
-        <v>1.071721809401515</v>
+        <v>1.071721934408579</v>
       </c>
       <c r="X21" t="n">
         <v>0.00269</v>
@@ -5323,7 +5323,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>2026-08-23T22:31:09.281737+00:00</t>
+          <t>2026-08-23T22:52:51.112085+00:00</t>
         </is>
       </c>
       <c r="AD21" t="inlineStr">
@@ -5405,7 +5405,7 @@
         <v>0.2131482647002914</v>
       </c>
       <c r="W22" t="n">
-        <v>1.414165403503707</v>
+        <v>1.414165201818253</v>
       </c>
       <c r="X22" t="n">
         <v>0.00016000001</v>
@@ -5415,7 +5415,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>2026-08-23T22:31:07.225873+00:00</t>
+          <t>2026-08-23T22:52:49.775274+00:00</t>
         </is>
       </c>
       <c r="AD22" t="inlineStr">
@@ -5504,7 +5504,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>2026-08-23T22:31:09.736522+00:00</t>
+          <t>2026-08-23T22:52:51.366758+00:00</t>
         </is>
       </c>
       <c r="AD23" t="inlineStr">
@@ -5596,7 +5596,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>2026-08-23T22:31:04.780624+00:00</t>
+          <t>2026-08-23T22:52:47.945866+00:00</t>
         </is>
       </c>
       <c r="AD24" t="inlineStr">
@@ -5685,7 +5685,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>2026-08-23T22:31:04.379199+00:00</t>
+          <t>2026-08-23T22:52:47.617165+00:00</t>
         </is>
       </c>
       <c r="AD25" t="inlineStr">
@@ -5777,7 +5777,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>2026-08-23T22:31:07.651415+00:00</t>
+          <t>2026-08-23T22:52:50.038323+00:00</t>
         </is>
       </c>
       <c r="AD26" t="inlineStr">
@@ -5869,7 +5869,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>2026-08-23T22:31:05.945866+00:00</t>
+          <t>2026-08-23T22:52:48.723984+00:00</t>
         </is>
       </c>
       <c r="AD27" t="inlineStr">
@@ -5955,7 +5955,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>2026-08-23T22:31:03.899151+00:00</t>
+          <t>2026-08-23T22:52:47.297537+00:00</t>
         </is>
       </c>
       <c r="AD28" t="inlineStr">
@@ -6037,7 +6037,7 @@
         <v>1.979740667578479</v>
       </c>
       <c r="W29" t="n">
-        <v>2.335837790700546</v>
+        <v>2.335838507022704</v>
       </c>
       <c r="X29" t="n">
         <v>0.00494</v>
@@ -6047,7 +6047,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>2026-08-23T22:31:08.044042+00:00</t>
+          <t>2026-08-23T22:52:50.328049+00:00</t>
         </is>
       </c>
       <c r="AD29" t="inlineStr">
@@ -6139,7 +6139,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>2026-08-23T22:31:11.240760+00:00</t>
+          <t>2026-08-23T22:52:52.485572+00:00</t>
         </is>
       </c>
       <c r="AD30" t="inlineStr">
@@ -6228,7 +6228,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>2026-08-23T22:31:06.347958+00:00</t>
+          <t>2026-08-23T22:52:49.066750+00:00</t>
         </is>
       </c>
       <c r="AD31" t="inlineStr">

--- a/reports/investment_dashboard.xlsx
+++ b/reports/investment_dashboard.xlsx
@@ -525,16 +525,16 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>MU</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Taiwan Semiconductor Manufacturing Company Limited</t>
+          <t>Micron Technology, Inc.</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>55.66</v>
+        <v>57.16</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>418.9500122070312</v>
+        <v>910.4299926757812</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -550,19 +550,24 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>100</v>
+        <v>84.2</v>
       </c>
       <c r="I2" t="n">
-        <v>100</v>
+        <v>88.2</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Revenue Growth; Earnings Fcf; Balance Sheet; Valuation</t>
+          <t>Revenue Growth; Earnings Fcf; Balance Sheet</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
           <t>Industry Growth; Competitive Advantage; Catalysts; Inflation Resilience</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>High market sensitivity / beta</t>
         </is>
       </c>
     </row>
@@ -572,16 +577,16 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>MU</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Micron Technology, Inc.</t>
+          <t>Taiwan Semiconductor Manufacturing Company Limited</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>55.05</v>
+        <v>55.45</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -589,7 +594,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>966.780029296875</v>
+        <v>410.1199951171875</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -597,24 +602,19 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="I3" t="n">
         <v>100</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Revenue Growth; Earnings Fcf; Balance Sheet</t>
+          <t>Revenue Growth; Earnings Fcf; Balance Sheet; Valuation</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
           <t>Industry Growth; Competitive Advantage; Catalysts; Inflation Resilience</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>High market sensitivity / beta</t>
         </is>
       </c>
     </row>
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>52.57</v>
+        <v>52.62</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>230.5700073242188</v>
+        <v>222.6100006103516</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -685,7 +685,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>52.11</v>
+        <v>52.22</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -693,7 +693,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>188.6499938964844</v>
+        <v>188.1499938964844</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -737,7 +737,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>52.08</v>
+        <v>51.62</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -745,7 +745,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>179.9400024414062</v>
+        <v>175.8899993896484</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -760,7 +760,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Revenue Growth; Earnings Fcf; Balance Sheet; Momentum</t>
+          <t>Revenue Growth; Earnings Fcf; Balance Sheet</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -789,7 +789,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>51.21</v>
+        <v>50.96</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>375.739990234375</v>
+        <v>364.8999938964844</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -836,19 +836,19 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>50.09</v>
+        <v>49.6</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RESEARCH</t>
+          <t>REJECT</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>214.7200012207031</v>
+        <v>208.4799957275391</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="H8" t="n">
@@ -864,12 +864,12 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Industry Growth; Valuation; Competitive Advantage; Catalysts; Inflation Resilience</t>
+          <t>Industry Growth; Valuation; Competitive Advantage; Momentum; Catalysts; Inflation Resilience</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Excessive price-to-sales valuation; High market sensitivity / beta</t>
+          <t>High market sensitivity / beta</t>
         </is>
       </c>
     </row>
@@ -888,7 +888,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>49.5</v>
+        <v>49.47</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>442.0799865722656</v>
+        <v>433.1900024414062</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -940,7 +940,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>48.25</v>
+        <v>48.19</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -948,7 +948,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>16.38999938964844</v>
+        <v>16.56999969482422</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -978,16 +978,16 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>GOOGL</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Advanced Micro Devices, Inc.</t>
+          <t>Alphabet Inc.</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>47.21</v>
+        <v>47.19</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -995,11 +995,11 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>473.25</v>
+        <v>348.0599975585938</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="H11" t="n">
@@ -1010,17 +1010,12 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Revenue Growth; Earnings Fcf; Balance Sheet</t>
+          <t>Earnings Fcf; Balance Sheet</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Industry Growth; Valuation; Competitive Advantage; Catalysts; Inflation Resilience</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>Very high earnings multiple; High market sensitivity / beta</t>
+          <t>Industry Growth; Competitive Advantage; Catalysts; Inflation Resilience</t>
         </is>
       </c>
     </row>
@@ -1030,16 +1025,16 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Alphabet Inc.</t>
+          <t>Advanced Micro Devices, Inc.</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>46.98</v>
+        <v>47.18</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -1047,11 +1042,11 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>344.8200073242188</v>
+        <v>456.7449951171875</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="H12" t="n">
@@ -1062,12 +1057,17 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Earnings Fcf; Balance Sheet</t>
+          <t>Revenue Growth; Earnings Fcf; Balance Sheet</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Industry Growth; Competitive Advantage; Catalysts; Inflation Resilience</t>
+          <t>Industry Growth; Valuation; Competitive Advantage; Catalysts; Inflation Resilience</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>Very high earnings multiple; High market sensitivity / beta</t>
         </is>
       </c>
     </row>
@@ -1086,7 +1086,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>45.64</v>
+        <v>45.53</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -1094,7 +1094,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>492.3200073242188</v>
+        <v>484.1900024414062</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -1133,7 +1133,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>45.04</v>
+        <v>44.68</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -1141,7 +1141,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>235.6199951171875</v>
+        <v>225.7700042724609</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -1185,7 +1185,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>44.39</v>
+        <v>44.02</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>368.4500122070312</v>
+        <v>358.760009765625</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -1237,7 +1237,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>43.33</v>
+        <v>43.19</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -1245,7 +1245,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>332.7799987792969</v>
+        <v>322.7799987792969</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1289,7 +1289,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>42.93</v>
+        <v>43.13</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -1297,7 +1297,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>258.6300048828125</v>
+        <v>262.0700073242188</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1327,16 +1327,16 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>MDB</t>
+          <t>ACMR</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>MongoDB, Inc.</t>
+          <t>ACM Research, Inc.</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>42.91</v>
+        <v>42.6</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>430.8299865722656</v>
+        <v>77.34500122070312</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1352,19 +1352,24 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>88.2</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="I18" t="n">
-        <v>88.2</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Balance Sheet; Momentum</t>
+          <t>Revenue Growth</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Industry Growth; Valuation; Competitive Advantage; Catalysts; Inflation Resilience</t>
+          <t>Industry Growth; Competitive Advantage; Catalysts; Inflation Resilience</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>Negative free cash flow / unprofitable growth</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1388,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>42.82</v>
+        <v>42.48</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -1391,7 +1396,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>293.1400146484375</v>
+        <v>280.3500061035156</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1426,16 +1431,16 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>ACMR</t>
+          <t>MDB</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>ACM Research, Inc.</t>
+          <t>MongoDB, Inc.</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>42.73</v>
+        <v>42.41</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -1443,7 +1448,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>79.41000366210938</v>
+        <v>402.6900024414062</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1451,24 +1456,19 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>94.09999999999999</v>
+        <v>88.2</v>
       </c>
       <c r="I20" t="n">
-        <v>94.09999999999999</v>
+        <v>88.2</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Revenue Growth</t>
+          <t>Balance Sheet</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Industry Growth; Competitive Advantage; Catalysts; Inflation Resilience</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>Negative free cash flow / unprofitable growth</t>
+          <t>Industry Growth; Valuation; Competitive Advantage; Catalysts; Inflation Resilience</t>
         </is>
       </c>
     </row>
@@ -1487,7 +1487,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>42.25</v>
+        <v>42.29</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -1495,7 +1495,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>261.9500122070312</v>
+        <v>254.9700012207031</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1530,16 +1530,16 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>ASML</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>ASML Holding N.V.</t>
+          <t>Microsoft Corporation</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>42.2</v>
+        <v>42.15</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -1547,7 +1547,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1763.760009765625</v>
+        <v>487.3099975585938</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Earnings Fcf; Balance Sheet</t>
+          <t>Earnings Fcf</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1577,16 +1577,16 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>SMCI</t>
+          <t>ASML</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Super Micro Computer, Inc.</t>
+          <t>ASML Holding N.V.</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>41.99</v>
+        <v>42.08</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -1594,7 +1594,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>37.2400016784668</v>
+        <v>1740.130004882812</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1602,24 +1602,19 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>94.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="I23" t="n">
-        <v>94.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Revenue Growth; Valuation</t>
+          <t>Earnings Fcf; Balance Sheet</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Industry Growth; Balance Sheet; Competitive Advantage; Catalysts; Inflation Resilience</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>Negative free cash flow / unprofitable growth</t>
+          <t>Industry Growth; Valuation; Competitive Advantage; Catalysts; Inflation Resilience</t>
         </is>
       </c>
     </row>
@@ -1629,16 +1624,16 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>PANW</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Microsoft Corporation</t>
+          <t>Palo Alto Networks, Inc.</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>41.89</v>
+        <v>41.48</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -1646,27 +1641,32 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>483.239990234375</v>
+        <v>350.8999938964844</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>100</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="I24" t="n">
-        <v>100</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Earnings Fcf</t>
+          <t>Revenue Growth; Momentum</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
           <t>Industry Growth; Valuation; Competitive Advantage; Catalysts; Inflation Resilience</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>Excessive price-to-sales valuation; Very high earnings multiple</t>
         </is>
       </c>
     </row>
@@ -1676,16 +1676,16 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>PANW</t>
+          <t>SMCI</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Palo Alto Networks, Inc.</t>
+          <t>Super Micro Computer, Inc.</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>41.52</v>
+        <v>41.07</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -1693,11 +1693,11 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>357.8699951171875</v>
+        <v>35.16999816894531</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="H25" t="n">
@@ -1708,17 +1708,17 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Revenue Growth; Momentum</t>
+          <t>Revenue Growth; Valuation</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>Industry Growth; Valuation; Competitive Advantage; Catalysts; Inflation Resilience</t>
+          <t>Industry Growth; Balance Sheet; Competitive Advantage; Momentum; Catalysts; Inflation Resilience</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>Excessive price-to-sales valuation; Very high earnings multiple</t>
+          <t>Negative free cash flow / unprofitable growth</t>
         </is>
       </c>
     </row>
@@ -1737,7 +1737,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>39.96</v>
+        <v>40.24</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>243.3200073242188</v>
+        <v>238.7799987792969</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1789,7 +1789,7 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>39.3</v>
+        <v>39.57</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -1797,7 +1797,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>549.9000244140625</v>
+        <v>559.02001953125</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1836,7 +1836,7 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>39.29</v>
+        <v>39.37</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>191.9499969482422</v>
+        <v>190.6799926757812</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1888,7 +1888,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>38.72</v>
+        <v>38.81</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -1896,7 +1896,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>237.0399932861328</v>
+        <v>229.2899932861328</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1940,7 +1940,7 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>36.58</v>
+        <v>36.5</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -1948,7 +1948,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>128.4799957275391</v>
+        <v>128.0500030517578</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1963,7 +1963,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>Earnings Fcf; Industry Growth; Valuation; Competitive Advantage; Catalysts; Inflation Resilience</t>
+          <t>Earnings Fcf; Industry Growth; Competitive Advantage; Catalysts; Inflation Resilience</t>
         </is>
       </c>
     </row>
@@ -1982,7 +1982,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>30.88</v>
+        <v>31.5</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -1990,7 +1990,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>146.4700012207031</v>
+        <v>142.4499969482422</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -2120,7 +2120,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>MU</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -2133,19 +2133,19 @@
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>8.84</v>
+        <v>9.02</v>
       </c>
       <c r="F2" t="n">
-        <v>8.67</v>
+        <v>7.36</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>5.46</v>
+        <v>7.28</v>
       </c>
       <c r="I2" t="n">
-        <v>2.69</v>
+        <v>3.5</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -2154,13 +2154,13 @@
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>55.66</v>
+        <v>57.16</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>MU</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -2173,19 +2173,19 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>9.02</v>
+        <v>8.84</v>
       </c>
       <c r="F3" t="n">
-        <v>4.82</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>7.71</v>
+        <v>5.21</v>
       </c>
       <c r="I3" t="n">
-        <v>3.5</v>
+        <v>2.69</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -2194,7 +2194,7 @@
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>55.05</v>
+        <v>55.45</v>
       </c>
     </row>
     <row r="4">
@@ -2216,13 +2216,13 @@
         <v>9.91</v>
       </c>
       <c r="F4" t="n">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>6.66</v>
+        <v>6.65</v>
       </c>
       <c r="I4" t="n">
         <v>3.56</v>
@@ -2234,7 +2234,7 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>52.57</v>
+        <v>52.62</v>
       </c>
     </row>
     <row r="5">
@@ -2262,7 +2262,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>7.63</v>
+        <v>7.74</v>
       </c>
       <c r="I5" t="n">
         <v>3.64</v>
@@ -2274,7 +2274,7 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>52.11</v>
+        <v>52.22</v>
       </c>
     </row>
     <row r="6">
@@ -2296,13 +2296,13 @@
         <v>9.890000000000001</v>
       </c>
       <c r="F6" t="n">
-        <v>0.66</v>
+        <v>0.68</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>8.18</v>
+        <v>7.7</v>
       </c>
       <c r="I6" t="n">
         <v>3.35</v>
@@ -2314,7 +2314,7 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>52.08</v>
+        <v>51.62</v>
       </c>
     </row>
     <row r="7">
@@ -2336,13 +2336,13 @@
         <v>8.9</v>
       </c>
       <c r="F7" t="n">
-        <v>2.85</v>
+        <v>2.93</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>5.71</v>
+        <v>5.38</v>
       </c>
       <c r="I7" t="n">
         <v>3.75</v>
@@ -2354,7 +2354,7 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>51.21</v>
+        <v>50.96</v>
       </c>
     </row>
     <row r="8">
@@ -2376,13 +2376,13 @@
         <v>9.029999999999999</v>
       </c>
       <c r="F8" t="n">
-        <v>3.15</v>
+        <v>3.27</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>4.47</v>
+        <v>3.86</v>
       </c>
       <c r="I8" t="n">
         <v>3.44</v>
@@ -2394,7 +2394,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>50.09</v>
+        <v>49.6</v>
       </c>
     </row>
     <row r="9">
@@ -2416,13 +2416,13 @@
         <v>6.33</v>
       </c>
       <c r="F9" t="n">
-        <v>4.97</v>
+        <v>4.98</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>8.18</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="I9" t="n">
         <v>3.54</v>
@@ -2434,7 +2434,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>49.5</v>
+        <v>49.47</v>
       </c>
     </row>
     <row r="10">
@@ -2456,7 +2456,7 @@
         <v>9.699999999999999</v>
       </c>
       <c r="F10" t="n">
-        <v>7.12</v>
+        <v>7.06</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -2474,38 +2474,38 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>48.25</v>
+        <v>48.19</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>GOOGL</t>
         </is>
       </c>
       <c r="B11" t="n">
+        <v>10.95</v>
+      </c>
+      <c r="C11" t="n">
         <v>15</v>
       </c>
-      <c r="C11" t="n">
-        <v>12.88</v>
-      </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>8.77</v>
+        <v>8.34</v>
       </c>
       <c r="F11" t="n">
-        <v>1.34</v>
+        <v>4.35</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>5.77</v>
+        <v>5.02</v>
       </c>
       <c r="I11" t="n">
-        <v>3.45</v>
+        <v>3.53</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -2514,38 +2514,38 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>47.21</v>
+        <v>47.19</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>10.95</v>
+        <v>15</v>
       </c>
       <c r="C12" t="n">
-        <v>15</v>
+        <v>12.88</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>8.34</v>
+        <v>8.77</v>
       </c>
       <c r="F12" t="n">
-        <v>4.39</v>
+        <v>1.39</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>4.77</v>
+        <v>5.69</v>
       </c>
       <c r="I12" t="n">
-        <v>3.53</v>
+        <v>3.45</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -2554,7 +2554,7 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>46.98</v>
+        <v>47.18</v>
       </c>
     </row>
     <row r="13">
@@ -2576,13 +2576,13 @@
         <v>7.78</v>
       </c>
       <c r="F13" t="n">
-        <v>1.89</v>
+        <v>1.99</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>6.2</v>
+        <v>5.99</v>
       </c>
       <c r="I13" t="n">
         <v>3.59</v>
@@ -2594,7 +2594,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>45.64</v>
+        <v>45.53</v>
       </c>
     </row>
     <row r="14">
@@ -2616,13 +2616,13 @@
         <v>8.98</v>
       </c>
       <c r="F14" t="n">
-        <v>0.83</v>
+        <v>0.87</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>6.45</v>
+        <v>6.05</v>
       </c>
       <c r="I14" t="n">
         <v>3.67</v>
@@ -2634,7 +2634,7 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>45.04</v>
+        <v>44.68</v>
       </c>
     </row>
     <row r="15">
@@ -2656,13 +2656,13 @@
         <v>6.16</v>
       </c>
       <c r="F15" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>3.67</v>
+        <v>3.27</v>
       </c>
       <c r="I15" t="n">
         <v>3.53</v>
@@ -2674,7 +2674,7 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>44.39</v>
+        <v>44.02</v>
       </c>
     </row>
     <row r="16">
@@ -2696,13 +2696,13 @@
         <v>7.58</v>
       </c>
       <c r="F16" t="n">
-        <v>0.97</v>
+        <v>1</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>9.279999999999999</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="I16" t="n">
         <v>3.56</v>
@@ -2714,7 +2714,7 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>43.33</v>
+        <v>43.19</v>
       </c>
     </row>
     <row r="17">
@@ -2736,13 +2736,13 @@
         <v>6.64</v>
       </c>
       <c r="F17" t="n">
-        <v>6.52</v>
+        <v>6.49</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>4.8</v>
+        <v>5.03</v>
       </c>
       <c r="I17" t="n">
         <v>3.47</v>
@@ -2754,38 +2754,38 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>42.93</v>
+        <v>43.13</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>MDB</t>
+          <t>ACMR</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>11.32</v>
+        <v>15</v>
       </c>
       <c r="C18" t="n">
-        <v>7.5</v>
+        <v>7.83</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>9.880000000000001</v>
+        <v>4.02</v>
       </c>
       <c r="F18" t="n">
-        <v>1.69</v>
+        <v>6.97</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>8.779999999999999</v>
+        <v>5.15</v>
       </c>
       <c r="I18" t="n">
-        <v>3.74</v>
+        <v>3.63</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2794,7 +2794,7 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>42.91</v>
+        <v>42.6</v>
       </c>
     </row>
     <row r="19">
@@ -2816,13 +2816,13 @@
         <v>7.71</v>
       </c>
       <c r="F19" t="n">
-        <v>0.58</v>
+        <v>0.6</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>8.390000000000001</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="I19" t="n">
         <v>3.64</v>
@@ -2834,38 +2834,38 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>42.82</v>
+        <v>42.48</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ACMR</t>
+          <t>MDB</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>15</v>
+        <v>11.32</v>
       </c>
       <c r="C20" t="n">
-        <v>7.83</v>
+        <v>7.5</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>4.02</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="F20" t="n">
-        <v>6.86</v>
+        <v>2</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>5.39</v>
+        <v>7.97</v>
       </c>
       <c r="I20" t="n">
-        <v>3.63</v>
+        <v>3.74</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2874,7 +2874,7 @@
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>42.73</v>
+        <v>42.41</v>
       </c>
     </row>
     <row r="21">
@@ -2896,13 +2896,13 @@
         <v>7.41</v>
       </c>
       <c r="F21" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>3.63</v>
+        <v>3.52</v>
       </c>
       <c r="I21" t="n">
         <v>3.56</v>
@@ -2914,38 +2914,38 @@
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>42.25</v>
+        <v>42.29</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ASML</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>9.859999999999999</v>
+        <v>8.51</v>
       </c>
       <c r="C22" t="n">
-        <v>14.28</v>
+        <v>14.63</v>
       </c>
       <c r="D22" t="n">
         <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>8.960000000000001</v>
+        <v>6.87</v>
       </c>
       <c r="F22" t="n">
-        <v>0.5600000000000001</v>
+        <v>3.03</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>5.79</v>
+        <v>5.66</v>
       </c>
       <c r="I22" t="n">
-        <v>2.75</v>
+        <v>3.45</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2954,38 +2954,38 @@
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>42.2</v>
+        <v>42.15</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>SMCI</t>
+          <t>ASML</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>15</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="C23" t="n">
-        <v>7.23</v>
+        <v>14.28</v>
       </c>
       <c r="D23" t="n">
         <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>2.23</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="F23" t="n">
-        <v>9.880000000000001</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>4.11</v>
+        <v>5.67</v>
       </c>
       <c r="I23" t="n">
-        <v>3.54</v>
+        <v>2.75</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2994,38 +2994,38 @@
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>41.99</v>
+        <v>42.08</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>PANW</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>8.51</v>
+        <v>13.54</v>
       </c>
       <c r="C24" t="n">
-        <v>14.63</v>
+        <v>7.5</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>6.87</v>
+        <v>7.97</v>
       </c>
       <c r="F24" t="n">
-        <v>3.06</v>
+        <v>0.58</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>5.37</v>
+        <v>8.32</v>
       </c>
       <c r="I24" t="n">
-        <v>3.45</v>
+        <v>3.57</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -3034,38 +3034,38 @@
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>41.89</v>
+        <v>41.48</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>PANW</t>
+          <t>SMCI</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>13.54</v>
+        <v>15</v>
       </c>
       <c r="C25" t="n">
-        <v>7.5</v>
+        <v>7.23</v>
       </c>
       <c r="D25" t="n">
         <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>7.97</v>
+        <v>2.23</v>
       </c>
       <c r="F25" t="n">
-        <v>0.57</v>
+        <v>9.93</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>8.369999999999999</v>
+        <v>3.14</v>
       </c>
       <c r="I25" t="n">
-        <v>3.57</v>
+        <v>3.54</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -3074,7 +3074,7 @@
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>41.52</v>
+        <v>41.07</v>
       </c>
     </row>
     <row r="26">
@@ -3096,13 +3096,13 @@
         <v>9.449999999999999</v>
       </c>
       <c r="F26" t="n">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>5.04</v>
+        <v>5.31</v>
       </c>
       <c r="I26" t="n">
         <v>3.7</v>
@@ -3114,7 +3114,7 @@
         <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>39.96</v>
+        <v>40.24</v>
       </c>
     </row>
     <row r="27">
@@ -3136,13 +3136,13 @@
         <v>7.23</v>
       </c>
       <c r="F27" t="n">
-        <v>5.82</v>
+        <v>5.74</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>0.38</v>
+        <v>0.73</v>
       </c>
       <c r="I27" t="n">
         <v>3.49</v>
@@ -3154,7 +3154,7 @@
         <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>39.3</v>
+        <v>39.57</v>
       </c>
     </row>
     <row r="28">
@@ -3176,13 +3176,13 @@
         <v>9.24</v>
       </c>
       <c r="F28" t="n">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>7.16</v>
+        <v>7.23</v>
       </c>
       <c r="I28" t="n">
         <v>3.48</v>
@@ -3194,7 +3194,7 @@
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>39.29</v>
+        <v>39.37</v>
       </c>
     </row>
     <row r="29">
@@ -3216,13 +3216,13 @@
         <v>7.11</v>
       </c>
       <c r="F29" t="n">
-        <v>0.57</v>
+        <v>0.58</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>7.87</v>
+        <v>7.95</v>
       </c>
       <c r="I29" t="n">
         <v>3.53</v>
@@ -3234,7 +3234,7 @@
         <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>38.72</v>
+        <v>38.81</v>
       </c>
     </row>
     <row r="30">
@@ -3256,13 +3256,13 @@
         <v>6.78</v>
       </c>
       <c r="F30" t="n">
-        <v>3.99</v>
+        <v>4.01</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>5.68</v>
+        <v>5.58</v>
       </c>
       <c r="I30" t="n">
         <v>3.57</v>
@@ -3274,7 +3274,7 @@
         <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>36.58</v>
+        <v>36.5</v>
       </c>
     </row>
     <row r="31">
@@ -3296,13 +3296,13 @@
         <v>0.8</v>
       </c>
       <c r="F31" t="n">
-        <v>6.51</v>
+        <v>6.67</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>1.85</v>
+        <v>2.31</v>
       </c>
       <c r="I31" t="n">
         <v>3.58</v>
@@ -3314,7 +3314,7 @@
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>30.88</v>
+        <v>31.5</v>
       </c>
     </row>
   </sheetData>
@@ -3348,11 +3348,11 @@
     <col width="15" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="18" customWidth="1" min="16" max="16"/>
-    <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="11" customWidth="1" min="17" max="17"/>
     <col width="16" customWidth="1" min="18" max="18"/>
     <col width="19" customWidth="1" min="19" max="19"/>
     <col width="23" customWidth="1" min="20" max="20"/>
-    <col width="23" customWidth="1" min="21" max="21"/>
+    <col width="22" customWidth="1" min="21" max="21"/>
     <col width="22" customWidth="1" min="22" max="22"/>
     <col width="22" customWidth="1" min="23" max="23"/>
     <col width="18" customWidth="1" min="24" max="24"/>
@@ -3519,12 +3519,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>MU</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Taiwan Semiconductor Manufacturing Company Limited</t>
+          <t>Micron Technology, Inc.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -3537,69 +3537,60 @@
           <t>Semiconductors</t>
         </is>
       </c>
-      <c r="E2" t="n">
-        <v>2172873342976</v>
-      </c>
       <c r="F2" t="n">
-        <v>418.9500122070312</v>
+        <v>910.4299926757812</v>
       </c>
       <c r="G2" t="n">
-        <v>4440492343296</v>
+        <v>90273996800</v>
       </c>
       <c r="H2" t="n">
-        <v>0.36</v>
+        <v>3.457</v>
       </c>
       <c r="I2" t="n">
-        <v>13.41</v>
+        <v>44.28</v>
       </c>
       <c r="J2" t="n">
-        <v>0.774</v>
+        <v>13.685</v>
       </c>
       <c r="K2" t="n">
-        <v>730826014720</v>
+        <v>7639499776</v>
       </c>
       <c r="M2" t="n">
-        <v>3518010228736</v>
+        <v>26022000640</v>
       </c>
       <c r="N2" t="n">
-        <v>1068558516224</v>
+        <v>6376000000</v>
       </c>
       <c r="O2" t="n">
-        <v>0.6423</v>
+        <v>0.7256899999999999</v>
       </c>
       <c r="P2" t="n">
-        <v>0.60344005</v>
+        <v>0.80370003</v>
       </c>
       <c r="Q2" t="n">
-        <v>31.241611</v>
-      </c>
-      <c r="R2" t="n">
-        <v>0.48933163</v>
-      </c>
-      <c r="S2" t="n">
-        <v>2.97317459861974</v>
+        <v>20.560751</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.005365445487747644</v>
+        <v>-0.01142300818916231</v>
       </c>
       <c r="U2" t="n">
-        <v>0.03809732083456407</v>
+        <v>0.2124767079710355</v>
       </c>
       <c r="V2" t="n">
-        <v>0.1684963370842598</v>
+        <v>1.127548792894937</v>
       </c>
       <c r="W2" t="n">
-        <v>0.8632971696944793</v>
+        <v>6.748905897439427</v>
       </c>
       <c r="X2" t="n">
-        <v>0.00013</v>
+        <v>0.00242</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.15498</v>
+        <v>0.7999000000000001</v>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>2026-08-23T22:52:49.436918+00:00</t>
+          <t>2026-08-24T23:41:55.651157+00:00</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
@@ -3611,12 +3602,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>MU</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Micron Technology, Inc.</t>
+          <t>Taiwan Semiconductor Manufacturing Company Limited</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -3630,68 +3621,68 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1091874717696</v>
+        <v>2127076655104</v>
       </c>
       <c r="F3" t="n">
-        <v>966.780029296875</v>
+        <v>410.1199951171875</v>
       </c>
       <c r="G3" t="n">
-        <v>90273996800</v>
+        <v>4440492343296</v>
       </c>
       <c r="H3" t="n">
-        <v>3.457</v>
+        <v>0.36</v>
       </c>
       <c r="I3" t="n">
-        <v>44.28</v>
+        <v>13.41</v>
       </c>
       <c r="J3" t="n">
-        <v>13.685</v>
+        <v>0.774</v>
       </c>
       <c r="K3" t="n">
-        <v>7639499776</v>
+        <v>730826014720</v>
       </c>
       <c r="M3" t="n">
-        <v>26022000640</v>
+        <v>3518010228736</v>
       </c>
       <c r="N3" t="n">
-        <v>6376000000</v>
+        <v>1068558516224</v>
       </c>
       <c r="O3" t="n">
-        <v>0.7256899999999999</v>
+        <v>0.6423</v>
       </c>
       <c r="P3" t="n">
-        <v>0.80370003</v>
+        <v>0.60344005</v>
       </c>
       <c r="Q3" t="n">
-        <v>21.833334</v>
+        <v>30.583147</v>
       </c>
       <c r="R3" t="n">
-        <v>12.0951185</v>
+        <v>0.4790182</v>
       </c>
       <c r="S3" t="n">
-        <v>142.924896879531</v>
+        <v>2.910510316082471</v>
       </c>
       <c r="T3" t="n">
-        <v>0.007608338867642228</v>
+        <v>0.01663318062062324</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2875215850577266</v>
+        <v>0.0162178201380454</v>
       </c>
       <c r="V3" t="n">
-        <v>1.317802614597143</v>
+        <v>0.1125350905877338</v>
       </c>
       <c r="W3" t="n">
-        <v>7.362827376540883</v>
+        <v>0.7797145067036872</v>
       </c>
       <c r="X3" t="n">
-        <v>0.00242</v>
+        <v>0.00013</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.7999000000000001</v>
+        <v>0.15498</v>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>2026-08-23T22:52:46.169677+00:00</t>
+          <t>2026-08-24T23:42:02.320528+00:00</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
@@ -3722,10 +3713,10 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>42996211712</v>
+        <v>41511845888</v>
       </c>
       <c r="F4" t="n">
-        <v>230.5700073242188</v>
+        <v>222.6100006103516</v>
       </c>
       <c r="G4" t="n">
         <v>1335116032</v>
@@ -3755,25 +3746,25 @@
         <v>0.35661998</v>
       </c>
       <c r="Q4" t="n">
-        <v>91.86056000000001</v>
+        <v>88.68925</v>
       </c>
       <c r="R4" t="n">
-        <v>32.2041</v>
+        <v>31.092314</v>
       </c>
       <c r="S4" t="n">
-        <v>171.4293280532914</v>
+        <v>165.5110430309258</v>
       </c>
       <c r="T4" t="n">
-        <v>0.01007580062517777</v>
+        <v>0.04438192345649994</v>
       </c>
       <c r="U4" t="n">
-        <v>0.05567512228478999</v>
+        <v>0.01922987444631796</v>
       </c>
       <c r="V4" t="n">
-        <v>0.7646563666145272</v>
+        <v>0.7943737303816445</v>
       </c>
       <c r="W4" t="n">
-        <v>1.079830471358389</v>
+        <v>0.9520343635848012</v>
       </c>
       <c r="X4" t="n">
         <v>0.108789995</v>
@@ -3783,7 +3774,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>2026-08-23T22:52:46.743683+00:00</t>
+          <t>2026-08-24T23:41:56.684819+00:00</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
@@ -3814,10 +3805,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>237930037248</v>
+        <v>237299417088</v>
       </c>
       <c r="F5" t="n">
-        <v>188.6499938964844</v>
+        <v>188.1499938964844</v>
       </c>
       <c r="G5" t="n">
         <v>10540800000</v>
@@ -3847,25 +3838,25 @@
         <v>0.45393002</v>
       </c>
       <c r="Q5" t="n">
-        <v>59.511036</v>
+        <v>59.35331</v>
       </c>
       <c r="R5" t="n">
-        <v>22.572294</v>
+        <v>22.512468</v>
       </c>
       <c r="S5" t="n">
-        <v>61.14076020603871</v>
+        <v>60.97871006546119</v>
       </c>
       <c r="T5" t="n">
-        <v>0.07880139054194135</v>
+        <v>0.08138391836464787</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2247613801957697</v>
+        <v>0.2215152592845022</v>
       </c>
       <c r="V5" t="n">
-        <v>0.3746994080728259</v>
+        <v>0.4168988885409695</v>
       </c>
       <c r="W5" t="n">
-        <v>0.428841896846748</v>
+        <v>0.4120074588854361</v>
       </c>
       <c r="X5" t="n">
         <v>0.17241</v>
@@ -3875,7 +3866,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>2026-08-23T22:52:50.577334+00:00</t>
+          <t>2026-08-24T23:42:04.472032+00:00</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
@@ -3906,10 +3897,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>432406331392</v>
+        <v>422673940480</v>
       </c>
       <c r="F6" t="n">
-        <v>179.9400024414062</v>
+        <v>175.8899993896484</v>
       </c>
       <c r="G6" t="n">
         <v>6155940864</v>
@@ -3939,25 +3930,25 @@
         <v>0.47120997</v>
       </c>
       <c r="Q6" t="n">
-        <v>153.79488</v>
+        <v>150.33334</v>
       </c>
       <c r="R6" t="n">
-        <v>70.24212</v>
+        <v>68.66114</v>
       </c>
       <c r="S6" t="n">
-        <v>200.2711443511633</v>
+        <v>195.7635390648473</v>
       </c>
       <c r="T6" t="n">
-        <v>0.4444890654429585</v>
+        <v>0.4309307029756004</v>
       </c>
       <c r="U6" t="n">
-        <v>0.3145820866638545</v>
+        <v>0.2849941051670306</v>
       </c>
       <c r="V6" t="n">
-        <v>0.3339758562947623</v>
+        <v>0.3005766951003199</v>
       </c>
       <c r="W6" t="n">
-        <v>0.1521322248679389</v>
+        <v>0.1080382594368936</v>
       </c>
       <c r="X6" t="n">
         <v>0.03477</v>
@@ -3967,7 +3958,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>2026-08-23T22:52:44.958695+00:00</t>
+          <t>2026-08-24T23:41:53.187485+00:00</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr">
@@ -3998,10 +3989,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>58743472128</v>
+        <v>57048739840</v>
       </c>
       <c r="F7" t="n">
-        <v>375.739990234375</v>
+        <v>364.8999938964844</v>
       </c>
       <c r="G7" t="n">
         <v>4464031232</v>
@@ -4031,25 +4022,25 @@
         <v>0.33161</v>
       </c>
       <c r="Q7" t="n">
-        <v>51.541836</v>
+        <v>50.05487</v>
       </c>
       <c r="R7" t="n">
-        <v>13.159287</v>
+        <v>12.779646</v>
       </c>
       <c r="S7" t="n">
-        <v>134.307248874099</v>
+        <v>130.4325233440278</v>
       </c>
       <c r="T7" t="n">
-        <v>0.01699777763368582</v>
+        <v>0.04280972763463753</v>
       </c>
       <c r="U7" t="n">
-        <v>0.04826466821541975</v>
+        <v>0.01802251816504241</v>
       </c>
       <c r="V7" t="n">
-        <v>0.1898762435729664</v>
+        <v>0.1237118992363824</v>
       </c>
       <c r="W7" t="n">
-        <v>2.446494406067634</v>
+        <v>2.172889130452521</v>
       </c>
       <c r="X7" t="n">
         <v>0.00202</v>
@@ -4059,7 +4050,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>2026-08-23T22:52:47.043984+00:00</t>
+          <t>2026-08-24T23:41:57.226569+00:00</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr">
@@ -4090,10 +4081,10 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5200733011968</v>
+        <v>5049593888768</v>
       </c>
       <c r="F8" t="n">
-        <v>214.7200012207031</v>
+        <v>208.4799957275391</v>
       </c>
       <c r="G8" t="n">
         <v>253491003392</v>
@@ -4123,25 +4114,25 @@
         <v>0.65596</v>
       </c>
       <c r="Q8" t="n">
-        <v>32.88208</v>
+        <v>31.92649</v>
       </c>
       <c r="R8" t="n">
-        <v>20.51644</v>
+        <v>19.92021</v>
       </c>
       <c r="S8" t="n">
-        <v>112.2398839722787</v>
+        <v>108.9780672990131</v>
       </c>
       <c r="T8" t="n">
-        <v>0.01254363714389073</v>
+        <v>0.007928831070801889</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.001670682268214541</v>
+        <v>-0.03068325860585119</v>
       </c>
       <c r="V8" t="n">
-        <v>0.144129303232654</v>
+        <v>0.09964313567363581</v>
       </c>
       <c r="W8" t="n">
-        <v>0.2287460719461247</v>
+        <v>0.1728617934376302</v>
       </c>
       <c r="X8" t="n">
         <v>0.03991</v>
@@ -4151,7 +4142,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>2026-08-23T22:52:44.710006+00:00</t>
+          <t>2026-08-24T23:41:52.684207+00:00</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr">
@@ -4182,10 +4173,10 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>285646618624</v>
+        <v>279902420992</v>
       </c>
       <c r="F9" t="n">
-        <v>442.0799865722656</v>
+        <v>433.1900024414062</v>
       </c>
       <c r="G9" t="n">
         <v>134001999872</v>
@@ -4215,25 +4206,25 @@
         <v>0.08857000600000001</v>
       </c>
       <c r="Q9" t="n">
-        <v>902.20404</v>
+        <v>884.0612</v>
       </c>
       <c r="R9" t="n">
-        <v>2.1316593</v>
+        <v>2.0887928</v>
       </c>
       <c r="S9" t="n">
-        <v>52.56534016738077</v>
+        <v>51.50827985989574</v>
       </c>
       <c r="T9" t="n">
-        <v>0.0006337681915646876</v>
+        <v>-0.009851422991071446</v>
       </c>
       <c r="U9" t="n">
-        <v>0.5000864673161829</v>
+        <v>0.4699205577649306</v>
       </c>
       <c r="V9" t="n">
-        <v>2.73072935680286</v>
+        <v>2.559731672884073</v>
       </c>
       <c r="W9" t="n">
-        <v>2.502412912969455</v>
+        <v>2.353027819007263</v>
       </c>
       <c r="X9" t="n">
         <v>0.07491</v>
@@ -4243,7 +4234,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>2026-08-23T22:52:50.848312+00:00</t>
+          <t>2026-08-24T23:42:05.010572+00:00</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr">
@@ -4274,10 +4265,10 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>8491990528</v>
+        <v>8585252352</v>
       </c>
       <c r="F10" t="n">
-        <v>16.38999938964844</v>
+        <v>16.56999969482422</v>
       </c>
       <c r="G10" t="n">
         <v>1672329984</v>
@@ -4304,25 +4295,25 @@
         <v>0.07274</v>
       </c>
       <c r="Q10" t="n">
-        <v>27.316664</v>
+        <v>27.616665</v>
       </c>
       <c r="R10" t="n">
-        <v>5.0779395</v>
+        <v>5.133707</v>
       </c>
       <c r="S10" t="n">
-        <v>16.60039142875248</v>
+        <v>16.78270236970969</v>
       </c>
       <c r="T10" t="n">
-        <v>0.5317756711973327</v>
+        <v>0.5285977363079994</v>
       </c>
       <c r="U10" t="n">
-        <v>0.4995424457478865</v>
+        <v>0.5160109087076308</v>
       </c>
       <c r="V10" t="n">
-        <v>0.4620873625222328</v>
+        <v>0.5342592039062499</v>
       </c>
       <c r="W10" t="n">
-        <v>0.5050504015546731</v>
+        <v>0.4834377423139571</v>
       </c>
       <c r="X10" t="n">
         <v>0.09236999999999999</v>
@@ -4332,7 +4323,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>2026-08-23T22:52:53.001946+00:00</t>
+          <t>2026-08-24T23:42:10.047782+00:00</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr">
@@ -4344,87 +4335,87 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>GOOGL</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Advanced Micro Devices, Inc.</t>
+          <t>Alphabet Inc.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Semiconductors</t>
+          <t>Internet Content &amp; Information</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>772568776704</v>
+        <v>4256751157248</v>
       </c>
       <c r="F11" t="n">
-        <v>473.25</v>
+        <v>348.0599975585938</v>
       </c>
       <c r="G11" t="n">
-        <v>41305001984</v>
+        <v>445865984000</v>
       </c>
       <c r="H11" t="n">
-        <v>0.501</v>
+        <v>0.242</v>
       </c>
       <c r="I11" t="n">
-        <v>3.93</v>
+        <v>19.93</v>
       </c>
       <c r="J11" t="n">
-        <v>1.595</v>
+        <v>2.94</v>
       </c>
       <c r="K11" t="n">
-        <v>8841499648</v>
+        <v>22665000960</v>
       </c>
       <c r="M11" t="n">
-        <v>13111000064</v>
+        <v>242473992192</v>
       </c>
       <c r="N11" t="n">
-        <v>4276000000</v>
+        <v>120790999040</v>
       </c>
       <c r="O11" t="n">
-        <v>0.55724</v>
+        <v>0.60897</v>
       </c>
       <c r="P11" t="n">
-        <v>0.1725</v>
+        <v>0.34033</v>
       </c>
       <c r="Q11" t="n">
-        <v>120.419846</v>
+        <v>17.464125</v>
       </c>
       <c r="R11" t="n">
-        <v>18.704</v>
+        <v>9.547153</v>
       </c>
       <c r="S11" t="n">
-        <v>87.37983458255972</v>
+        <v>187.8116468982493</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.1431753021617514</v>
+        <v>0.08857199033333196</v>
       </c>
       <c r="U11" t="n">
-        <v>0.01227779109425398</v>
+        <v>-0.09061313206295496</v>
       </c>
       <c r="V11" t="n">
-        <v>1.327039442211227</v>
+        <v>0.1064609321422796</v>
       </c>
       <c r="W11" t="n">
-        <v>1.890782362663681</v>
+        <v>0.6936919304075204</v>
       </c>
       <c r="X11" t="n">
-        <v>0.00429</v>
+        <v>0.01596</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.75372005</v>
+        <v>0.81073</v>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>2026-08-23T22:52:45.208810+00:00</t>
+          <t>2026-08-24T23:41:59.692825+00:00</t>
         </is>
       </c>
       <c r="AD11" t="inlineStr">
@@ -4436,87 +4427,87 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Alphabet Inc.</t>
+          <t>Advanced Micro Devices, Inc.</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Internet Content &amp; Information</t>
+          <t>Semiconductors</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4217126256640</v>
+        <v>745624764416</v>
       </c>
       <c r="F12" t="n">
-        <v>344.8200073242188</v>
+        <v>456.7449951171875</v>
       </c>
       <c r="G12" t="n">
-        <v>445865984000</v>
+        <v>41305001984</v>
       </c>
       <c r="H12" t="n">
-        <v>0.242</v>
+        <v>0.501</v>
       </c>
       <c r="I12" t="n">
-        <v>19.93</v>
+        <v>3.93</v>
       </c>
       <c r="J12" t="n">
-        <v>2.94</v>
+        <v>1.595</v>
       </c>
       <c r="K12" t="n">
-        <v>22665000960</v>
+        <v>8841499648</v>
       </c>
       <c r="M12" t="n">
-        <v>242473992192</v>
+        <v>13111000064</v>
       </c>
       <c r="N12" t="n">
-        <v>120790999040</v>
+        <v>4276000000</v>
       </c>
       <c r="O12" t="n">
-        <v>0.60897</v>
+        <v>0.55724</v>
       </c>
       <c r="P12" t="n">
-        <v>0.34033</v>
+        <v>0.1725</v>
       </c>
       <c r="Q12" t="n">
-        <v>17.301556</v>
+        <v>116.2201</v>
       </c>
       <c r="R12" t="n">
-        <v>9.458282000000001</v>
+        <v>18.051682</v>
       </c>
       <c r="S12" t="n">
-        <v>186.063361042099</v>
+        <v>84.33238637120398</v>
       </c>
       <c r="T12" t="n">
-        <v>0.007980388247400327</v>
+        <v>-0.1249257889929509</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.09907835240442464</v>
+        <v>-0.0230262762798048</v>
       </c>
       <c r="V12" t="n">
-        <v>0.1400655521483041</v>
+        <v>1.282013535076157</v>
       </c>
       <c r="W12" t="n">
-        <v>0.731182362414351</v>
+        <v>1.722609740539637</v>
       </c>
       <c r="X12" t="n">
-        <v>0.01596</v>
+        <v>0.00429</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.81073</v>
+        <v>0.75372005</v>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>2026-08-23T22:52:48.203924+00:00</t>
+          <t>2026-08-24T23:41:53.768141+00:00</t>
         </is>
       </c>
       <c r="AD12" t="inlineStr">
@@ -4547,10 +4538,10 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>390882099200</v>
+        <v>384427229184</v>
       </c>
       <c r="F13" t="n">
-        <v>492.3200073242188</v>
+        <v>484.1900024414062</v>
       </c>
       <c r="G13" t="n">
         <v>30837000192</v>
@@ -4580,25 +4571,25 @@
         <v>0.33736</v>
       </c>
       <c r="Q13" t="n">
-        <v>42.55143</v>
+        <v>41.848747</v>
       </c>
       <c r="R13" t="n">
-        <v>12.67575</v>
+        <v>12.466428</v>
       </c>
       <c r="S13" t="n">
-        <v>127.1006254461765</v>
+        <v>125.0017367585479</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.1102569665921038</v>
+        <v>-0.09611606402754613</v>
       </c>
       <c r="U13" t="n">
-        <v>0.140425846569036</v>
+        <v>0.1215932426464699</v>
       </c>
       <c r="V13" t="n">
-        <v>0.3342865245955684</v>
+        <v>0.2928508474863543</v>
       </c>
       <c r="W13" t="n">
-        <v>2.097116404241915</v>
+        <v>1.996295596499046</v>
       </c>
       <c r="X13" t="n">
         <v>0.00331</v>
@@ -4608,7 +4599,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>2026-08-23T22:52:45.836092+00:00</t>
+          <t>2026-08-24T23:41:55.017445+00:00</t>
         </is>
       </c>
       <c r="AD13" t="inlineStr">
@@ -4639,10 +4630,10 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>84605255680</v>
+        <v>81068367872</v>
       </c>
       <c r="F14" t="n">
-        <v>235.6199951171875</v>
+        <v>225.7700042724609</v>
       </c>
       <c r="G14" t="n">
         <v>3966725120</v>
@@ -4672,25 +4663,25 @@
         <v>0.00666</v>
       </c>
       <c r="Q14" t="n">
-        <v>480.85712</v>
+        <v>460.7551</v>
       </c>
       <c r="R14" t="n">
-        <v>21.328741</v>
+        <v>20.437103</v>
       </c>
       <c r="S14" t="n">
-        <v>80.46819643983029</v>
+        <v>77.10425668653359</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.04129881181114814</v>
+        <v>-0.08543302392346452</v>
       </c>
       <c r="U14" t="n">
-        <v>0.05982362070352409</v>
+        <v>0.01551815776621002</v>
       </c>
       <c r="V14" t="n">
-        <v>0.9537313275152979</v>
+        <v>0.9520145004666292</v>
       </c>
       <c r="W14" t="n">
-        <v>0.824390292314225</v>
+        <v>0.7205456650829558</v>
       </c>
       <c r="X14" t="n">
         <v>0.00619</v>
@@ -4700,7 +4691,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>2026-08-23T22:52:51.908319+00:00</t>
+          <t>2026-08-24T23:42:07.307540+00:00</t>
         </is>
       </c>
       <c r="AD14" t="inlineStr">
@@ -4731,10 +4722,10 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1752930451456</v>
+        <v>1706829545472</v>
       </c>
       <c r="F15" t="n">
-        <v>368.4500122070312</v>
+        <v>358.760009765625</v>
       </c>
       <c r="G15" t="n">
         <v>75464998912</v>
@@ -4764,25 +4755,25 @@
         <v>0.48988</v>
       </c>
       <c r="Q15" t="n">
-        <v>61.306156</v>
+        <v>59.693844</v>
       </c>
       <c r="R15" t="n">
-        <v>23.22839</v>
+        <v>22.617498</v>
       </c>
       <c r="S15" t="n">
-        <v>64.41696332366014</v>
+        <v>62.72283999578242</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.07146993655918366</v>
+        <v>-0.06064097938793045</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.1089169343844046</v>
+        <v>-0.132351855799088</v>
       </c>
       <c r="V15" t="n">
-        <v>0.1072406716938052</v>
+        <v>0.08246379532588</v>
       </c>
       <c r="W15" t="n">
-        <v>0.2815942361128876</v>
+        <v>0.2292131574770397</v>
       </c>
       <c r="X15" t="n">
         <v>0.01948</v>
@@ -4792,7 +4783,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>2026-08-23T22:52:45.509730+00:00</t>
+          <t>2026-08-24T23:41:54.412556+00:00</t>
         </is>
       </c>
       <c r="AD15" t="inlineStr">
@@ -4823,10 +4814,10 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>115341549568</v>
+        <v>111875547136</v>
       </c>
       <c r="F16" t="n">
-        <v>332.7799987792969</v>
+        <v>322.7799987792969</v>
       </c>
       <c r="G16" t="n">
         <v>5032822784</v>
@@ -4853,22 +4844,22 @@
         <v>-0.22173999</v>
       </c>
       <c r="R16" t="n">
-        <v>22.917864</v>
+        <v>22.229185</v>
       </c>
       <c r="S16" t="n">
-        <v>66.3073873057683</v>
+        <v>64.31485671707644</v>
       </c>
       <c r="T16" t="n">
-        <v>0.24264381608771</v>
+        <v>0.2041334093825102</v>
       </c>
       <c r="U16" t="n">
-        <v>0.9325203523628396</v>
+        <v>0.8744483420421558</v>
       </c>
       <c r="V16" t="n">
-        <v>0.8570312748130948</v>
+        <v>0.8711883987205615</v>
       </c>
       <c r="W16" t="n">
-        <v>0.7093692793255157</v>
+        <v>0.6400589542368125</v>
       </c>
       <c r="X16" t="n">
         <v>0.02962</v>
@@ -4878,7 +4869,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>2026-08-23T22:52:51.611934+00:00</t>
+          <t>2026-08-24T23:42:06.633040+00:00</t>
         </is>
       </c>
       <c r="AD16" t="inlineStr">
@@ -4909,10 +4900,10 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2789664358400</v>
+        <v>2826769268736</v>
       </c>
       <c r="F17" t="n">
-        <v>258.6300048828125</v>
+        <v>262.0700073242188</v>
       </c>
       <c r="G17" t="n">
         <v>775680032768</v>
@@ -4942,25 +4933,25 @@
         <v>0.13689</v>
       </c>
       <c r="Q17" t="n">
-        <v>20.790194</v>
+        <v>21.066721</v>
       </c>
       <c r="R17" t="n">
-        <v>3.5964112</v>
+        <v>3.6442466</v>
       </c>
       <c r="S17" t="n">
-        <v>866.5908796125428</v>
+        <v>878.1172758935854</v>
       </c>
       <c r="T17" t="n">
-        <v>0.05627934831854198</v>
+        <v>0.1290767594463185</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.02887504592189505</v>
+        <v>-0.01595824528055845</v>
       </c>
       <c r="V17" t="n">
-        <v>0.2624719521246743</v>
+        <v>0.247299065075093</v>
       </c>
       <c r="W17" t="n">
-        <v>0.1652624845186366</v>
+        <v>0.1452106778452436</v>
       </c>
       <c r="X17" t="n">
         <v>0.088690005</v>
@@ -4970,7 +4961,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>2026-08-23T22:52:48.464770+00:00</t>
+          <t>2026-08-24T23:42:00.253171+00:00</t>
         </is>
       </c>
       <c r="AD17" t="inlineStr">
@@ -4982,12 +4973,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>MDB</t>
+          <t>ACMR</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>MongoDB, Inc.</t>
+          <t>ACM Research, Inc.</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -4997,66 +4988,69 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Software - Infrastructure</t>
+          <t>Semiconductor Equipment &amp; Materials</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>34652487680</v>
+        <v>5387017216</v>
       </c>
       <c r="F18" t="n">
-        <v>430.8299865722656</v>
+        <v>77.34500122070312</v>
       </c>
       <c r="G18" t="n">
-        <v>2602398976</v>
+        <v>1037772032</v>
       </c>
       <c r="H18" t="n">
-        <v>0.252</v>
+        <v>0.36</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.39</v>
+        <v>2.12</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1.806</v>
       </c>
       <c r="K18" t="n">
-        <v>517605376</v>
+        <v>-186610256</v>
       </c>
       <c r="M18" t="n">
-        <v>2427152896</v>
+        <v>1439374976</v>
       </c>
       <c r="N18" t="n">
-        <v>58635000</v>
+        <v>349319008</v>
       </c>
       <c r="O18" t="n">
-        <v>0.71970004</v>
+        <v>0.43835</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.03607</v>
+        <v>0.16982001</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>36.483494</v>
       </c>
       <c r="R18" t="n">
-        <v>13.315594</v>
-      </c>
-      <c r="S18" t="n">
-        <v>66.94769661743236</v>
+        <v>5.1909447</v>
       </c>
       <c r="T18" t="n">
-        <v>0.4126962811023474</v>
+        <v>-0.08272057043839431</v>
       </c>
       <c r="U18" t="n">
-        <v>0.3210375620822583</v>
+        <v>0.05446493292009436</v>
       </c>
       <c r="V18" t="n">
-        <v>0.2105705943951726</v>
+        <v>0.1615108195567321</v>
       </c>
       <c r="W18" t="n">
-        <v>1.032600362925348</v>
+        <v>1.533409743896125</v>
       </c>
       <c r="X18" t="n">
-        <v>0.02641</v>
+        <v>0.12675999</v>
       </c>
       <c r="Y18" t="n">
-        <v>0.96402</v>
+        <v>0.78052</v>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>2026-08-23T22:52:52.742446+00:00</t>
+          <t>2026-08-24T23:41:56.198991+00:00</t>
         </is>
       </c>
       <c r="AD18" t="inlineStr">
@@ -5087,10 +5081,10 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>104381210624</v>
+        <v>99826950144</v>
       </c>
       <c r="F19" t="n">
-        <v>293.1400146484375</v>
+        <v>280.3500061035156</v>
       </c>
       <c r="G19" t="n">
         <v>2512349952</v>
@@ -5117,22 +5111,22 @@
         <v>-0.07902000000000001</v>
       </c>
       <c r="R19" t="n">
-        <v>41.54724</v>
+        <v>39.734493</v>
       </c>
       <c r="S19" t="n">
-        <v>150.6544189017877</v>
+        <v>144.0812103517039</v>
       </c>
       <c r="T19" t="n">
-        <v>0.08982081446690615</v>
+        <v>0.06942594938307689</v>
       </c>
       <c r="U19" t="n">
-        <v>0.3560624375790442</v>
+        <v>0.296896000731846</v>
       </c>
       <c r="V19" t="n">
-        <v>0.5216985858451444</v>
+        <v>0.5826465342073299</v>
       </c>
       <c r="W19" t="n">
-        <v>0.5206723460674603</v>
+        <v>0.429117646532641</v>
       </c>
       <c r="X19" t="n">
         <v>0.00616</v>
@@ -5142,7 +5136,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>2026-08-23T22:52:52.158191+00:00</t>
+          <t>2026-08-24T23:42:07.850261+00:00</t>
         </is>
       </c>
       <c r="AD19" t="inlineStr">
@@ -5154,12 +5148,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ACMR</t>
+          <t>MDB</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>ACM Research, Inc.</t>
+          <t>MongoDB, Inc.</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -5169,69 +5163,66 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Semiconductor Equipment &amp; Materials</t>
+          <t>Software - Infrastructure</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5530843136</v>
+        <v>32389132288</v>
       </c>
       <c r="F20" t="n">
-        <v>79.41000366210938</v>
+        <v>402.6900024414062</v>
       </c>
       <c r="G20" t="n">
-        <v>1037772032</v>
+        <v>2602398976</v>
       </c>
       <c r="H20" t="n">
-        <v>0.36</v>
+        <v>0.252</v>
       </c>
       <c r="I20" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="J20" t="n">
-        <v>1.806</v>
+        <v>-0.39</v>
       </c>
       <c r="K20" t="n">
-        <v>-186610256</v>
+        <v>517605376</v>
       </c>
       <c r="M20" t="n">
-        <v>1439374976</v>
+        <v>2427152896</v>
       </c>
       <c r="N20" t="n">
-        <v>349319008</v>
+        <v>58635000</v>
       </c>
       <c r="O20" t="n">
-        <v>0.43835</v>
+        <v>0.71970004</v>
       </c>
       <c r="P20" t="n">
-        <v>0.16982001</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>37.45755</v>
+        <v>-0.03607</v>
       </c>
       <c r="R20" t="n">
-        <v>5.329536</v>
+        <v>12.445875</v>
+      </c>
+      <c r="S20" t="n">
+        <v>62.57495341006659</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.1128365348349486</v>
+        <v>0.350311852971217</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0826176593599568</v>
+        <v>0.2347530016016277</v>
       </c>
       <c r="V20" t="n">
-        <v>0.2151492810448359</v>
+        <v>0.1687079327104049</v>
       </c>
       <c r="W20" t="n">
-        <v>2.10074196679292</v>
+        <v>0.8382635210871647</v>
       </c>
       <c r="X20" t="n">
-        <v>0.12675999</v>
+        <v>0.02641</v>
       </c>
       <c r="Y20" t="n">
-        <v>0.78052</v>
+        <v>0.96402</v>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>2026-08-23T22:52:46.426423+00:00</t>
+          <t>2026-08-24T23:42:09.248135+00:00</t>
         </is>
       </c>
       <c r="AD20" t="inlineStr">
@@ -5262,10 +5253,10 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100847656960</v>
+        <v>98160435200</v>
       </c>
       <c r="F21" t="n">
-        <v>261.9500122070312</v>
+        <v>254.9700012207031</v>
       </c>
       <c r="G21" t="n">
         <v>11479600128</v>
@@ -5295,25 +5286,25 @@
         <v>0.20362</v>
       </c>
       <c r="Q21" t="n">
-        <v>59.13093</v>
+        <v>57.555305</v>
       </c>
       <c r="R21" t="n">
-        <v>8.784945499999999</v>
+        <v>8.5508585</v>
       </c>
       <c r="S21" t="n">
-        <v>37.39894335610229</v>
+        <v>36.40239809747136</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.1301965432935455</v>
+        <v>-0.1218831309968894</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1998884785081102</v>
+        <v>-0.2212085279452035</v>
       </c>
       <c r="V21" t="n">
-        <v>0.07819827777494104</v>
+        <v>0.04649740841847994</v>
       </c>
       <c r="W21" t="n">
-        <v>1.071721934408579</v>
+        <v>1.026282952520625</v>
       </c>
       <c r="X21" t="n">
         <v>0.00269</v>
@@ -5323,7 +5314,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>2026-08-23T22:52:51.112085+00:00</t>
+          <t>2026-08-24T23:42:05.554067+00:00</t>
         </is>
       </c>
       <c r="AD21" t="inlineStr">
@@ -5335,12 +5326,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ASML</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>ASML Holding N.V.</t>
+          <t>Microsoft Corporation</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -5350,72 +5341,72 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Semiconductor Equipment &amp; Materials</t>
+          <t>Software - Infrastructure</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>677460246528</v>
+        <v>3618542714880</v>
       </c>
       <c r="F22" t="n">
-        <v>1763.760009765625</v>
+        <v>487.3099975585938</v>
       </c>
       <c r="G22" t="n">
-        <v>35327500288</v>
+        <v>331839012864</v>
       </c>
       <c r="H22" t="n">
-        <v>0.213</v>
+        <v>0.177</v>
       </c>
       <c r="I22" t="n">
-        <v>29.63</v>
+        <v>17.93</v>
       </c>
       <c r="J22" t="n">
-        <v>0.285</v>
+        <v>0.317</v>
       </c>
       <c r="K22" t="n">
-        <v>8437675008</v>
+        <v>16545500160</v>
       </c>
       <c r="M22" t="n">
-        <v>7581499904</v>
+        <v>76842999808</v>
       </c>
       <c r="N22" t="n">
-        <v>1984400000</v>
+        <v>128812998656</v>
       </c>
       <c r="O22" t="n">
-        <v>0.5273300400000001</v>
+        <v>0.67944</v>
       </c>
       <c r="P22" t="n">
-        <v>0.37057</v>
+        <v>0.45111</v>
       </c>
       <c r="Q22" t="n">
-        <v>59.526157</v>
+        <v>27.17847</v>
       </c>
       <c r="R22" t="n">
-        <v>19.176569</v>
+        <v>10.904512</v>
       </c>
       <c r="S22" t="n">
-        <v>80.28991942515925</v>
+        <v>218.702528173074</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.0198788191730831</v>
+        <v>0.2790865460674004</v>
       </c>
       <c r="U22" t="n">
-        <v>0.08153658248673468</v>
+        <v>0.1664174202192839</v>
       </c>
       <c r="V22" t="n">
-        <v>0.2131482647002914</v>
+        <v>0.231741813437734</v>
       </c>
       <c r="W22" t="n">
-        <v>1.414165201818253</v>
+        <v>-0.03136756513099537</v>
       </c>
       <c r="X22" t="n">
-        <v>0.00016000001</v>
+        <v>0.00090000004</v>
       </c>
       <c r="Y22" t="n">
-        <v>0.20382</v>
+        <v>0.75907</v>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>2026-08-23T22:52:49.775274+00:00</t>
+          <t>2026-08-24T23:41:58.940174+00:00</t>
         </is>
       </c>
       <c r="AD22" t="inlineStr">
@@ -5427,12 +5418,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>SMCI</t>
+          <t>ASML</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Super Micro Computer, Inc.</t>
+          <t>ASML Holding N.V.</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -5442,69 +5433,72 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Computer Hardware</t>
+          <t>Semiconductor Equipment &amp; Materials</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>24089552896</v>
+        <v>668383903744</v>
       </c>
       <c r="F23" t="n">
-        <v>37.2400016784668</v>
+        <v>1740.130004882812</v>
       </c>
       <c r="G23" t="n">
-        <v>39063072768</v>
+        <v>35327500288</v>
       </c>
       <c r="H23" t="n">
-        <v>0.9320000000000001</v>
+        <v>0.213</v>
       </c>
       <c r="I23" t="n">
-        <v>3.26</v>
+        <v>29.63</v>
       </c>
       <c r="J23" t="n">
-        <v>4.094</v>
+        <v>0.285</v>
       </c>
       <c r="K23" t="n">
-        <v>-8231267840</v>
+        <v>8437675008</v>
       </c>
       <c r="M23" t="n">
-        <v>7521474048</v>
+        <v>7581499904</v>
       </c>
       <c r="N23" t="n">
-        <v>9311492096</v>
+        <v>1984400000</v>
       </c>
       <c r="O23" t="n">
-        <v>0.108219996</v>
+        <v>0.5273300400000001</v>
       </c>
       <c r="P23" t="n">
-        <v>0.13382</v>
+        <v>0.37057</v>
       </c>
       <c r="Q23" t="n">
-        <v>11.423313</v>
+        <v>58.728657</v>
       </c>
       <c r="R23" t="n">
-        <v>0.6166835000000001</v>
+        <v>18.91965</v>
+      </c>
+      <c r="S23" t="n">
+        <v>79.2142270365102</v>
       </c>
       <c r="T23" t="n">
-        <v>0.2185864636538672</v>
+        <v>-0.008371471746108972</v>
       </c>
       <c r="U23" t="n">
-        <v>0.0466554177061127</v>
+        <v>0.06704667763369399</v>
       </c>
       <c r="V23" t="n">
-        <v>0.1579602566902212</v>
+        <v>0.188213228050349</v>
       </c>
       <c r="W23" t="n">
-        <v>-0.1198298163616878</v>
+        <v>1.320326857563086</v>
       </c>
       <c r="X23" t="n">
-        <v>0.12878999</v>
+        <v>0.00016000001</v>
       </c>
       <c r="Y23" t="n">
-        <v>0.70522004</v>
+        <v>0.20382</v>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>2026-08-23T22:52:51.366758+00:00</t>
+          <t>2026-08-24T23:42:02.915537+00:00</t>
         </is>
       </c>
       <c r="AD23" t="inlineStr">
@@ -5516,12 +5510,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>PANW</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Microsoft Corporation</t>
+          <t>Palo Alto Networks, Inc.</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -5535,68 +5529,65 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>3588320657408</v>
+        <v>285983506432</v>
       </c>
       <c r="F24" t="n">
-        <v>483.239990234375</v>
+        <v>350.8999938964844</v>
       </c>
       <c r="G24" t="n">
-        <v>331839012864</v>
+        <v>10606499840</v>
       </c>
       <c r="H24" t="n">
-        <v>0.177</v>
+        <v>0.311</v>
       </c>
       <c r="I24" t="n">
-        <v>17.93</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0.317</v>
+        <v>1.15</v>
       </c>
       <c r="K24" t="n">
-        <v>16545500160</v>
+        <v>3579375104</v>
       </c>
       <c r="M24" t="n">
-        <v>76842999808</v>
+        <v>3111000064</v>
       </c>
       <c r="N24" t="n">
-        <v>128812998656</v>
+        <v>2130000000</v>
       </c>
       <c r="O24" t="n">
-        <v>0.67944</v>
+        <v>0.71963996</v>
       </c>
       <c r="P24" t="n">
-        <v>0.45111</v>
+        <v>-0.02465</v>
       </c>
       <c r="Q24" t="n">
-        <v>26.951477</v>
+        <v>305.13043</v>
       </c>
       <c r="R24" t="n">
-        <v>10.813438</v>
+        <v>26.963043</v>
       </c>
       <c r="S24" t="n">
-        <v>216.8759253396907</v>
+        <v>79.8976072981034</v>
       </c>
       <c r="T24" t="n">
-        <v>0.2403281430304072</v>
+        <v>0.08372705962544025</v>
       </c>
       <c r="U24" t="n">
-        <v>0.156675515749495</v>
+        <v>0.3466114512949008</v>
       </c>
       <c r="V24" t="n">
-        <v>0.2176838288473297</v>
+        <v>1.359784808997822</v>
       </c>
       <c r="W24" t="n">
-        <v>-0.03376187393524122</v>
+        <v>0.887776978044025</v>
       </c>
       <c r="X24" t="n">
-        <v>0.00090000004</v>
+        <v>0.0076</v>
       </c>
       <c r="Y24" t="n">
-        <v>0.75907</v>
+        <v>0.84946</v>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>2026-08-23T22:52:47.945866+00:00</t>
+          <t>2026-08-24T23:41:58.381156+00:00</t>
         </is>
       </c>
       <c r="AD24" t="inlineStr">
@@ -5608,12 +5599,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>PANW</t>
+          <t>SMCI</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Palo Alto Networks, Inc.</t>
+          <t>Super Micro Computer, Inc.</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -5623,69 +5614,69 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Software - Infrastructure</t>
+          <t>Computer Hardware</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>291664035840</v>
+        <v>22750523392</v>
       </c>
       <c r="F25" t="n">
-        <v>357.8699951171875</v>
+        <v>35.16999816894531</v>
       </c>
       <c r="G25" t="n">
-        <v>10606499840</v>
+        <v>39063072768</v>
       </c>
       <c r="H25" t="n">
-        <v>0.311</v>
+        <v>0.9320000000000001</v>
       </c>
       <c r="I25" t="n">
-        <v>1.15</v>
+        <v>3.26</v>
+      </c>
+      <c r="J25" t="n">
+        <v>4.094</v>
       </c>
       <c r="K25" t="n">
-        <v>3579375104</v>
+        <v>-8231267840</v>
       </c>
       <c r="M25" t="n">
-        <v>3111000064</v>
+        <v>7521474048</v>
       </c>
       <c r="N25" t="n">
-        <v>2130000000</v>
+        <v>9311492096</v>
       </c>
       <c r="O25" t="n">
-        <v>0.71963996</v>
+        <v>0.108219996</v>
       </c>
       <c r="P25" t="n">
-        <v>-0.02465</v>
+        <v>0.13382</v>
       </c>
       <c r="Q25" t="n">
-        <v>311.1913</v>
+        <v>10.788343</v>
       </c>
       <c r="R25" t="n">
-        <v>27.498613</v>
-      </c>
-      <c r="S25" t="n">
-        <v>81.48462437313751</v>
+        <v>0.58240485</v>
       </c>
       <c r="T25" t="n">
-        <v>0.0673765104394457</v>
+        <v>0.1684384625654953</v>
       </c>
       <c r="U25" t="n">
-        <v>0.3733594809973666</v>
+        <v>-0.01152343004523171</v>
       </c>
       <c r="V25" t="n">
-        <v>1.370156845470078</v>
+        <v>0.08482418739413089</v>
       </c>
       <c r="W25" t="n">
-        <v>0.9521600524718539</v>
+        <v>-0.1984959591420548</v>
       </c>
       <c r="X25" t="n">
-        <v>0.0076</v>
+        <v>0.12878999</v>
       </c>
       <c r="Y25" t="n">
-        <v>0.84946</v>
+        <v>0.70522004</v>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>2026-08-23T22:52:47.617165+00:00</t>
+          <t>2026-08-24T23:42:06.041992+00:00</t>
         </is>
       </c>
       <c r="AD25" t="inlineStr">
@@ -5716,10 +5707,10 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>259865427968</v>
+        <v>255016697856</v>
       </c>
       <c r="F26" t="n">
-        <v>243.3200073242188</v>
+        <v>238.7799987792969</v>
       </c>
       <c r="G26" t="n">
         <v>5155999744</v>
@@ -5749,25 +5740,25 @@
         <v>0.07603</v>
       </c>
       <c r="Q26" t="n">
-        <v>250.84537</v>
+        <v>246.16495</v>
       </c>
       <c r="R26" t="n">
-        <v>50.40059</v>
+        <v>49.460186</v>
       </c>
       <c r="S26" t="n">
-        <v>194.728688047447</v>
+        <v>191.0953195736607</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.1414255025951249</v>
+        <v>-0.08165074492887803</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.2061596699230962</v>
+        <v>-0.220971612111847</v>
       </c>
       <c r="V26" t="n">
-        <v>0.9169621581911946</v>
+        <v>0.9014173857118781</v>
       </c>
       <c r="W26" t="n">
-        <v>0.8256303237752955</v>
+        <v>0.7312935176144866</v>
       </c>
       <c r="X26" t="n">
         <v>0.0007</v>
@@ -5777,7 +5768,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>2026-08-23T22:52:50.038323+00:00</t>
+          <t>2026-08-24T23:42:03.504552+00:00</t>
         </is>
       </c>
       <c r="AD26" t="inlineStr">
@@ -5808,10 +5799,10 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1400873680896</v>
+        <v>1424106979328</v>
       </c>
       <c r="F27" t="n">
-        <v>549.9000244140625</v>
+        <v>559.02001953125</v>
       </c>
       <c r="G27" t="n">
         <v>228246994944</v>
@@ -5841,25 +5832,25 @@
         <v>0.34827</v>
       </c>
       <c r="Q27" t="n">
-        <v>20.704067</v>
+        <v>21.047441</v>
       </c>
       <c r="R27" t="n">
-        <v>6.137534</v>
+        <v>6.239324</v>
       </c>
       <c r="S27" t="n">
-        <v>64.99480598629961</v>
+        <v>66.07273595571971</v>
       </c>
       <c r="T27" t="n">
-        <v>-0.1232041720771622</v>
+        <v>-0.0607704812946972</v>
       </c>
       <c r="U27" t="n">
-        <v>-0.09807350747934629</v>
+        <v>-0.08311521534867206</v>
       </c>
       <c r="V27" t="n">
-        <v>-0.1456296261876776</v>
+        <v>-0.1458725259845354</v>
       </c>
       <c r="W27" t="n">
-        <v>-0.253548447765114</v>
+        <v>-0.2569426776396064</v>
       </c>
       <c r="X27" t="n">
         <v>0.00148</v>
@@ -5869,7 +5860,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>2026-08-23T22:52:48.723984+00:00</t>
+          <t>2026-08-24T23:42:00.891769+00:00</t>
         </is>
       </c>
       <c r="AD27" t="inlineStr">
@@ -5900,10 +5891,10 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>195454861312</v>
+        <v>194161672192</v>
       </c>
       <c r="F28" t="n">
-        <v>191.9499969482422</v>
+        <v>190.6799926757812</v>
       </c>
       <c r="G28" t="n">
         <v>5094199808</v>
@@ -5930,22 +5921,22 @@
         <v>-0.022079999</v>
       </c>
       <c r="R28" t="n">
-        <v>38.36812</v>
+        <v>38.11426</v>
       </c>
       <c r="S28" t="n">
-        <v>101.4630434160035</v>
+        <v>100.7917328998725</v>
       </c>
       <c r="T28" t="n">
-        <v>0.01873473523830382</v>
+        <v>0.0403753488966101</v>
       </c>
       <c r="U28" t="n">
-        <v>0.1572663949066291</v>
+        <v>0.1496095400523765</v>
       </c>
       <c r="V28" t="n">
-        <v>0.8188277849765093</v>
+        <v>0.9627379277496741</v>
       </c>
       <c r="W28" t="n">
-        <v>0.8543206113126569</v>
+        <v>0.8136249978411652</v>
       </c>
       <c r="X28" t="n">
         <v>0.014680001</v>
@@ -5955,7 +5946,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>2026-08-23T22:52:47.297537+00:00</t>
+          <t>2026-08-24T23:41:57.743307+00:00</t>
         </is>
       </c>
       <c r="AD28" t="inlineStr">
@@ -5986,10 +5977,10 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>212753924096</v>
+        <v>205797965824</v>
       </c>
       <c r="F29" t="n">
-        <v>237.0399932861328</v>
+        <v>229.2899932861328</v>
       </c>
       <c r="G29" t="n">
         <v>8717100032</v>
@@ -6019,25 +6010,25 @@
         <v>0.14479999</v>
       </c>
       <c r="Q29" t="n">
-        <v>81.17807999999999</v>
+        <v>78.52397000000001</v>
       </c>
       <c r="R29" t="n">
-        <v>24.406502</v>
+        <v>23.608536</v>
       </c>
       <c r="S29" t="n">
-        <v>93.7365797670566</v>
+        <v>90.6718760715072</v>
       </c>
       <c r="T29" t="n">
-        <v>0.1234655060180694</v>
+        <v>0.1805076369757792</v>
       </c>
       <c r="U29" t="n">
-        <v>0.2076527324190676</v>
+        <v>0.1681686413739329</v>
       </c>
       <c r="V29" t="n">
-        <v>1.979740667578479</v>
+        <v>1.887032565299141</v>
       </c>
       <c r="W29" t="n">
-        <v>2.335838507022704</v>
+        <v>2.147650680557031</v>
       </c>
       <c r="X29" t="n">
         <v>0.00494</v>
@@ -6047,7 +6038,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>2026-08-23T22:52:50.328049+00:00</t>
+          <t>2026-08-24T23:42:04.032508+00:00</t>
         </is>
       </c>
       <c r="AD29" t="inlineStr">
@@ -6078,10 +6069,10 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>132830584832</v>
+        <v>132386037760</v>
       </c>
       <c r="F30" t="n">
-        <v>128.4799957275391</v>
+        <v>128.0500030517578</v>
       </c>
       <c r="G30" t="n">
         <v>14732000256</v>
@@ -6111,25 +6102,25 @@
         <v>0.04063</v>
       </c>
       <c r="Q30" t="n">
-        <v>79.80124000000001</v>
+        <v>79.534164</v>
       </c>
       <c r="R30" t="n">
-        <v>9.016465999999999</v>
+        <v>8.986291</v>
       </c>
       <c r="S30" t="n">
-        <v>25.79547720861104</v>
+        <v>25.70914691142508</v>
       </c>
       <c r="T30" t="n">
-        <v>0.3459040117300543</v>
+        <v>0.2963150904451679</v>
       </c>
       <c r="U30" t="n">
-        <v>0.2580044960614081</v>
+        <v>0.2537942474826844</v>
       </c>
       <c r="V30" t="n">
-        <v>0.1966097833747986</v>
+        <v>0.2280618315362024</v>
       </c>
       <c r="W30" t="n">
-        <v>-0.2674778054883237</v>
+        <v>-0.2779814003670369</v>
       </c>
       <c r="X30" t="n">
         <v>0.00176</v>
@@ -6139,7 +6130,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>2026-08-23T22:52:52.485572+00:00</t>
+          <t>2026-08-24T23:42:08.489276+00:00</t>
         </is>
       </c>
       <c r="AD30" t="inlineStr">
@@ -6170,10 +6161,10 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>421902581760</v>
+        <v>410323091456</v>
       </c>
       <c r="F31" t="n">
-        <v>146.4700012207031</v>
+        <v>142.4499969482422</v>
       </c>
       <c r="G31" t="n">
         <v>67356999680</v>
@@ -6203,22 +6194,22 @@
         <v>0.36202</v>
       </c>
       <c r="Q31" t="n">
-        <v>25.123499</v>
+        <v>24.433962</v>
       </c>
       <c r="R31" t="n">
-        <v>6.2636786</v>
+        <v>6.0917664</v>
       </c>
       <c r="T31" t="n">
-        <v>0.1639383779654544</v>
+        <v>0.2388033706810304</v>
       </c>
       <c r="U31" t="n">
-        <v>-0.2348002668577091</v>
+        <v>-0.2558018792758237</v>
       </c>
       <c r="V31" t="n">
-        <v>-0.05779410309686361</v>
+        <v>-0.03130182031897633</v>
       </c>
       <c r="W31" t="n">
-        <v>-0.3646448121864612</v>
+        <v>-0.3904742535260926</v>
       </c>
       <c r="X31" t="n">
         <v>0.40498</v>
@@ -6228,7 +6219,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>2026-08-23T22:52:49.066750+00:00</t>
+          <t>2026-08-24T23:42:01.600223+00:00</t>
         </is>
       </c>
       <c r="AD31" t="inlineStr">
@@ -6256,7 +6247,7 @@
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
@@ -6313,22 +6304,27 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>MU</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>100</v>
+        <v>84.2</v>
       </c>
       <c r="C2" t="n">
-        <v>100</v>
+        <v>88.2</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MODERATE</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>price_to_sales, price_to_fcf</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -6342,11 +6338,11 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>MU</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="C3" t="n">
         <v>100</v>
@@ -6357,7 +6353,7 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -6579,7 +6575,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>GOOGL</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -6608,7 +6604,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -6787,14 +6783,14 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>MDB</t>
+          <t>ACMR</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>88.2</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="C18" t="n">
-        <v>88.2</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -6803,7 +6799,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>eps_growth, pe_ratio</t>
+          <t>price_to_fcf</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -6855,14 +6851,14 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ACMR</t>
+          <t>MDB</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>94.09999999999999</v>
+        <v>88.2</v>
       </c>
       <c r="C20" t="n">
-        <v>94.09999999999999</v>
+        <v>88.2</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -6871,7 +6867,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>price_to_fcf</t>
+          <t>eps_growth, pe_ratio</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -6918,7 +6914,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ASML</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -6947,23 +6943,18 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>SMCI</t>
+          <t>ASML</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>94.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="C23" t="n">
-        <v>94.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
           <t>HIGH</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>price_to_fcf</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -6981,18 +6972,23 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>PANW</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>100</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="C24" t="n">
-        <v>100</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
           <t>HIGH</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>eps_growth</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -7010,7 +7006,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>PANW</t>
+          <t>SMCI</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -7026,7 +7022,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>eps_growth</t>
+          <t>price_to_fcf</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -7294,11 +7290,11 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>MU</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>55.66</v>
+        <v>57.16</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -7311,7 +7307,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>100</v>
+        <v>84.2</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>

--- a/reports/investment_dashboard.xlsx
+++ b/reports/investment_dashboard.xlsx
@@ -525,16 +525,16 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>MU</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Micron Technology, Inc.</t>
+          <t>Taiwan Semiconductor Manufacturing Company Limited</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>57.16</v>
+        <v>55.59</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>910.4299926757812</v>
+        <v>417.4100036621094</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -550,24 +550,19 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>84.2</v>
+        <v>100</v>
       </c>
       <c r="I2" t="n">
-        <v>88.2</v>
+        <v>100</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Revenue Growth; Earnings Fcf; Balance Sheet</t>
+          <t>Revenue Growth; Earnings Fcf; Balance Sheet; Valuation</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
           <t>Industry Growth; Competitive Advantage; Catalysts; Inflation Resilience</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>High market sensitivity / beta</t>
         </is>
       </c>
     </row>
@@ -577,16 +572,16 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>MU</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Taiwan Semiconductor Manufacturing Company Limited</t>
+          <t>Micron Technology, Inc.</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>55.45</v>
+        <v>54.08</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -594,7 +589,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>410.1199951171875</v>
+        <v>932.969970703125</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -602,19 +597,24 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="I3" t="n">
         <v>100</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Revenue Growth; Earnings Fcf; Balance Sheet; Valuation</t>
+          <t>Revenue Growth; Earnings Fcf; Balance Sheet</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
           <t>Industry Growth; Competitive Advantage; Catalysts; Inflation Resilience</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>High market sensitivity / beta</t>
         </is>
       </c>
     </row>
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>52.62</v>
+        <v>52.7</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>222.6100006103516</v>
+        <v>226.5099945068359</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -685,7 +685,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>52.22</v>
+        <v>52.21</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -693,7 +693,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>188.1499938964844</v>
+        <v>190.9400024414062</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -737,7 +737,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>51.62</v>
+        <v>51.59</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -745,7 +745,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>175.8899993896484</v>
+        <v>172.7299957275391</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>50.96</v>
+        <v>50.75</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>364.8999938964844</v>
+        <v>366.4299926757812</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -827,24 +827,24 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>NVDA</t>
+          <t>DELL</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>NVIDIA Corporation</t>
+          <t>Dell Technologies Inc.</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>49.6</v>
+        <v>50.52</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>REJECT</t>
+          <t>RESEARCH</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>208.4799957275391</v>
+        <v>451.5</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -859,17 +859,12 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Revenue Growth; Earnings Fcf; Balance Sheet</t>
+          <t>Revenue Growth; Momentum</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Industry Growth; Valuation; Competitive Advantage; Momentum; Catalysts; Inflation Resilience</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>High market sensitivity / beta</t>
+          <t>Industry Growth; Competitive Advantage; Catalysts; Inflation Resilience</t>
         </is>
       </c>
     </row>
@@ -879,16 +874,16 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>DELL</t>
+          <t>NVDA</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Dell Technologies Inc.</t>
+          <t>NVIDIA Corporation</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>49.47</v>
+        <v>49.84</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -896,11 +891,11 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>433.1900024414062</v>
+        <v>213.0500030517578</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="H9" t="n">
@@ -911,17 +906,17 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Revenue Growth; Momentum</t>
+          <t>Revenue Growth; Earnings Fcf; Balance Sheet</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Industry Growth; Competitive Advantage; Catalysts; Inflation Resilience</t>
+          <t>Industry Growth; Valuation; Competitive Advantage; Catalysts; Inflation Resilience</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Very high earnings multiple</t>
+          <t>Excessive price-to-sales valuation; High market sensitivity / beta</t>
         </is>
       </c>
     </row>
@@ -940,7 +935,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>48.19</v>
+        <v>48.16</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -948,7 +943,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>16.56999969482422</v>
+        <v>16.65999984741211</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -978,12 +973,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Alphabet Inc.</t>
+          <t>Advanced Micro Devices, Inc.</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -995,11 +990,11 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>348.0599975585938</v>
+        <v>479.1799926757812</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="H11" t="n">
@@ -1010,12 +1005,17 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Earnings Fcf; Balance Sheet</t>
+          <t>Revenue Growth; Earnings Fcf; Balance Sheet</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Industry Growth; Competitive Advantage; Catalysts; Inflation Resilience</t>
+          <t>Industry Growth; Valuation; Competitive Advantage; Catalysts; Inflation Resilience</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>Very high earnings multiple; High market sensitivity / beta</t>
         </is>
       </c>
     </row>
@@ -1025,16 +1025,16 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>GOOGL</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Advanced Micro Devices, Inc.</t>
+          <t>Alphabet Inc.</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>47.18</v>
+        <v>47.15</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -1042,11 +1042,11 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>456.7449951171875</v>
+        <v>346.9599914550781</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="H12" t="n">
@@ -1057,17 +1057,12 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Revenue Growth; Earnings Fcf; Balance Sheet</t>
+          <t>Earnings Fcf; Balance Sheet</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Industry Growth; Valuation; Competitive Advantage; Catalysts; Inflation Resilience</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>Very high earnings multiple; High market sensitivity / beta</t>
+          <t>Industry Growth; Competitive Advantage; Catalysts; Inflation Resilience</t>
         </is>
       </c>
     </row>
@@ -1086,7 +1081,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>45.53</v>
+        <v>45.22</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -1094,7 +1089,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>484.1900024414062</v>
+        <v>480.0400085449219</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -1133,7 +1128,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>44.68</v>
+        <v>44.55</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -1141,7 +1136,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>225.7700042724609</v>
+        <v>222.9900054931641</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -1185,7 +1180,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>44.02</v>
+        <v>43.88</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -1193,7 +1188,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>358.760009765625</v>
+        <v>356.739990234375</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -1228,16 +1223,16 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>SNOW</t>
+          <t>MDB</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Snowflake Inc.</t>
+          <t>MongoDB, Inc.</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>43.19</v>
+        <v>43.51</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -1245,7 +1240,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>322.7799987792969</v>
+        <v>404.9200134277344</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1260,17 +1255,12 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Revenue Growth; Momentum</t>
+          <t>Balance Sheet; Momentum</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
           <t>Industry Growth; Valuation; Competitive Advantage; Catalysts; Inflation Resilience</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>Excessive price-to-sales valuation</t>
         </is>
       </c>
     </row>
@@ -1289,7 +1279,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>43.13</v>
+        <v>43.23</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -1297,7 +1287,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>262.0700073242188</v>
+        <v>261.0599975585938</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1327,16 +1317,16 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>ACMR</t>
+          <t>SNOW</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>ACM Research, Inc.</t>
+          <t>Snowflake Inc.</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>42.6</v>
+        <v>43.11</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -1344,7 +1334,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>77.34500122070312</v>
+        <v>317.0199890136719</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1352,24 +1342,24 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>94.09999999999999</v>
+        <v>88.2</v>
       </c>
       <c r="I18" t="n">
-        <v>94.09999999999999</v>
+        <v>88.2</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Revenue Growth</t>
+          <t>Revenue Growth; Momentum</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Industry Growth; Competitive Advantage; Catalysts; Inflation Resilience</t>
+          <t>Industry Growth; Valuation; Competitive Advantage; Catalysts; Inflation Resilience</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>Negative free cash flow / unprofitable growth</t>
+          <t>Excessive price-to-sales valuation</t>
         </is>
       </c>
     </row>
@@ -1379,16 +1369,16 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>NET</t>
+          <t>SMCI</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Cloudflare, Inc.</t>
+          <t>Super Micro Computer, Inc.</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>42.48</v>
+        <v>42.57</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -1396,7 +1386,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>280.3500061035156</v>
+        <v>38.45999908447266</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1404,24 +1394,24 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>88.2</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="I19" t="n">
-        <v>88.2</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Revenue Growth; Momentum</t>
+          <t>Revenue Growth; Valuation</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Industry Growth; Valuation; Competitive Advantage; Catalysts; Inflation Resilience</t>
+          <t>Industry Growth; Balance Sheet; Competitive Advantage; Catalysts; Inflation Resilience</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>Excessive price-to-sales valuation</t>
+          <t>Negative free cash flow / unprofitable growth</t>
         </is>
       </c>
     </row>
@@ -1431,16 +1421,16 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>MDB</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>MongoDB, Inc.</t>
+          <t>Microsoft Corporation</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>42.41</v>
+        <v>42.54</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -1448,7 +1438,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>402.6900024414062</v>
+        <v>491.7099914550781</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1456,14 +1446,14 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>88.2</v>
+        <v>100</v>
       </c>
       <c r="I20" t="n">
-        <v>88.2</v>
+        <v>100</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Balance Sheet</t>
+          <t>Earnings Fcf</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1478,16 +1468,16 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>VRT</t>
+          <t>NET</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Vertiv Holdings Co</t>
+          <t>Cloudflare, Inc.</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>42.29</v>
+        <v>42.34</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -1495,7 +1485,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>254.9700012207031</v>
+        <v>277.5799865722656</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1503,24 +1493,24 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>100</v>
+        <v>88.2</v>
       </c>
       <c r="I21" t="n">
-        <v>100</v>
+        <v>88.2</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Earnings Fcf</t>
+          <t>Revenue Growth</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>Industry Growth; Valuation; Competitive Advantage; Momentum; Catalysts; Inflation Resilience</t>
+          <t>Industry Growth; Valuation; Competitive Advantage; Catalysts; Inflation Resilience</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>High market sensitivity / beta</t>
+          <t>Excessive price-to-sales valuation</t>
         </is>
       </c>
     </row>
@@ -1530,16 +1520,16 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>ACMR</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Microsoft Corporation</t>
+          <t>ACM Research, Inc.</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>42.15</v>
+        <v>42.29</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -1547,7 +1537,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>487.3099975585938</v>
+        <v>79.76999664306641</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1555,19 +1545,24 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>100</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="I22" t="n">
-        <v>100</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Earnings Fcf</t>
+          <t>Revenue Growth</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Industry Growth; Valuation; Competitive Advantage; Catalysts; Inflation Resilience</t>
+          <t>Industry Growth; Competitive Advantage; Catalysts; Inflation Resilience</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>Negative free cash flow / unprofitable growth</t>
         </is>
       </c>
     </row>
@@ -1577,16 +1572,16 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>ASML</t>
+          <t>VRT</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>ASML Holding N.V.</t>
+          <t>Vertiv Holdings Co</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>42.08</v>
+        <v>42.27</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -1594,7 +1589,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1740.130004882812</v>
+        <v>255.75</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1609,12 +1604,17 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Earnings Fcf; Balance Sheet</t>
+          <t>Earnings Fcf</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Industry Growth; Valuation; Competitive Advantage; Catalysts; Inflation Resilience</t>
+          <t>Industry Growth; Valuation; Competitive Advantage; Momentum; Catalysts; Inflation Resilience</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>High market sensitivity / beta</t>
         </is>
       </c>
     </row>
@@ -1624,16 +1624,16 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>PANW</t>
+          <t>ASML</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Palo Alto Networks, Inc.</t>
+          <t>ASML Holding N.V.</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>41.48</v>
+        <v>42.05</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -1641,32 +1641,27 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>350.8999938964844</v>
+        <v>1744.160034179688</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>94.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="I24" t="n">
-        <v>94.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Revenue Growth; Momentum</t>
+          <t>Earnings Fcf; Balance Sheet</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
           <t>Industry Growth; Valuation; Competitive Advantage; Catalysts; Inflation Resilience</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>Excessive price-to-sales valuation; Very high earnings multiple</t>
         </is>
       </c>
     </row>
@@ -1676,16 +1671,16 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>SMCI</t>
+          <t>PANW</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Super Micro Computer, Inc.</t>
+          <t>Palo Alto Networks, Inc.</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>41.07</v>
+        <v>41.24</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -1693,11 +1688,11 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>35.16999816894531</v>
+        <v>339.8999938964844</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="H25" t="n">
@@ -1708,17 +1703,17 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Revenue Growth; Valuation</t>
+          <t>Revenue Growth; Momentum</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>Industry Growth; Balance Sheet; Competitive Advantage; Momentum; Catalysts; Inflation Resilience</t>
+          <t>Industry Growth; Valuation; Competitive Advantage; Catalysts; Inflation Resilience</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>Negative free cash flow / unprofitable growth</t>
+          <t>Excessive price-to-sales valuation; Very high earnings multiple</t>
         </is>
       </c>
     </row>
@@ -1737,7 +1732,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>40.24</v>
+        <v>40.28</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -1745,7 +1740,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>238.7799987792969</v>
+        <v>241.5599975585938</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1789,7 +1784,7 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>39.57</v>
+        <v>39.81</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -1797,7 +1792,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>559.02001953125</v>
+        <v>570.0499877929688</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1836,7 +1831,7 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>39.37</v>
+        <v>39.04</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -1844,7 +1839,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>190.6799926757812</v>
+        <v>185.3800048828125</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1888,7 +1883,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>38.81</v>
+        <v>38.99</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -1896,7 +1891,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>229.2899932861328</v>
+        <v>240.3800048828125</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1911,7 +1906,7 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Revenue Growth</t>
+          <t>Revenue Growth; Momentum</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -1940,7 +1935,7 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>36.5</v>
+        <v>36.72</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -1948,7 +1943,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>128.0500030517578</v>
+        <v>127</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1982,7 +1977,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>31.5</v>
+        <v>31.77</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -1990,7 +1985,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>142.4499969482422</v>
+        <v>144.7599945068359</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -2120,7 +2115,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>MU</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -2133,19 +2128,19 @@
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>9.02</v>
+        <v>8.84</v>
       </c>
       <c r="F2" t="n">
-        <v>7.36</v>
+        <v>8.68</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>7.28</v>
+        <v>5.38</v>
       </c>
       <c r="I2" t="n">
-        <v>3.5</v>
+        <v>2.69</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -2154,13 +2149,13 @@
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>57.16</v>
+        <v>55.59</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>MU</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -2173,19 +2168,19 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>8.84</v>
+        <v>9.02</v>
       </c>
       <c r="F3" t="n">
-        <v>8.710000000000001</v>
+        <v>4.95</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>5.21</v>
+        <v>6.61</v>
       </c>
       <c r="I3" t="n">
-        <v>2.69</v>
+        <v>3.5</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -2194,7 +2189,7 @@
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>55.45</v>
+        <v>54.08</v>
       </c>
     </row>
     <row r="4">
@@ -2216,13 +2211,13 @@
         <v>9.91</v>
       </c>
       <c r="F4" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>6.65</v>
+        <v>6.75</v>
       </c>
       <c r="I4" t="n">
         <v>3.56</v>
@@ -2234,7 +2229,7 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>52.62</v>
+        <v>52.7</v>
       </c>
     </row>
     <row r="5">
@@ -2256,16 +2251,16 @@
         <v>10</v>
       </c>
       <c r="F5" t="n">
-        <v>0.84</v>
+        <v>0.83</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>7.74</v>
+        <v>7.75</v>
       </c>
       <c r="I5" t="n">
-        <v>3.64</v>
+        <v>3.63</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -2274,7 +2269,7 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>52.22</v>
+        <v>52.21</v>
       </c>
     </row>
     <row r="6">
@@ -2296,13 +2291,13 @@
         <v>9.890000000000001</v>
       </c>
       <c r="F6" t="n">
-        <v>0.68</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>7.7</v>
+        <v>7.66</v>
       </c>
       <c r="I6" t="n">
         <v>3.35</v>
@@ -2314,7 +2309,7 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>51.62</v>
+        <v>51.59</v>
       </c>
     </row>
     <row r="7">
@@ -2336,13 +2331,13 @@
         <v>8.9</v>
       </c>
       <c r="F7" t="n">
-        <v>2.93</v>
+        <v>2.92</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>5.38</v>
+        <v>5.18</v>
       </c>
       <c r="I7" t="n">
         <v>3.75</v>
@@ -2354,38 +2349,38 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>50.96</v>
+        <v>50.75</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>NVDA</t>
+          <t>DELL</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>15</v>
       </c>
       <c r="C8" t="n">
-        <v>15</v>
+        <v>11.48</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>9.029999999999999</v>
+        <v>6.33</v>
       </c>
       <c r="F8" t="n">
-        <v>3.27</v>
+        <v>5.84</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>3.86</v>
+        <v>8.33</v>
       </c>
       <c r="I8" t="n">
-        <v>3.44</v>
+        <v>3.54</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -2394,38 +2389,38 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>49.6</v>
+        <v>50.52</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>DELL</t>
+          <t>NVDA</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>15</v>
       </c>
       <c r="C9" t="n">
-        <v>11.48</v>
+        <v>15</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>6.33</v>
+        <v>9.029999999999999</v>
       </c>
       <c r="F9" t="n">
-        <v>4.98</v>
+        <v>3.18</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>8.140000000000001</v>
+        <v>4.19</v>
       </c>
       <c r="I9" t="n">
-        <v>3.54</v>
+        <v>3.44</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -2434,7 +2429,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>49.47</v>
+        <v>49.84</v>
       </c>
     </row>
     <row r="10">
@@ -2456,7 +2451,7 @@
         <v>9.699999999999999</v>
       </c>
       <c r="F10" t="n">
-        <v>7.06</v>
+        <v>7.03</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -2474,38 +2469,38 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>48.19</v>
+        <v>48.16</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>10.95</v>
+        <v>15</v>
       </c>
       <c r="C11" t="n">
-        <v>15</v>
+        <v>12.88</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>8.34</v>
+        <v>8.77</v>
       </c>
       <c r="F11" t="n">
-        <v>4.35</v>
+        <v>1.32</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>5.02</v>
+        <v>5.77</v>
       </c>
       <c r="I11" t="n">
-        <v>3.53</v>
+        <v>3.45</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -2520,32 +2515,32 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>GOOGL</t>
         </is>
       </c>
       <c r="B12" t="n">
+        <v>10.95</v>
+      </c>
+      <c r="C12" t="n">
         <v>15</v>
       </c>
-      <c r="C12" t="n">
-        <v>12.88</v>
-      </c>
       <c r="D12" t="n">
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>8.77</v>
+        <v>8.34</v>
       </c>
       <c r="F12" t="n">
-        <v>1.39</v>
+        <v>4.36</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>5.69</v>
+        <v>4.97</v>
       </c>
       <c r="I12" t="n">
-        <v>3.45</v>
+        <v>3.53</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -2554,7 +2549,7 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>47.18</v>
+        <v>47.15</v>
       </c>
     </row>
     <row r="13">
@@ -2576,16 +2571,16 @@
         <v>7.78</v>
       </c>
       <c r="F13" t="n">
-        <v>1.99</v>
+        <v>2.04</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>5.99</v>
+        <v>5.64</v>
       </c>
       <c r="I13" t="n">
-        <v>3.59</v>
+        <v>3.58</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -2594,7 +2589,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>45.53</v>
+        <v>45.22</v>
       </c>
     </row>
     <row r="14">
@@ -2616,13 +2611,13 @@
         <v>8.98</v>
       </c>
       <c r="F14" t="n">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>6.05</v>
+        <v>5.91</v>
       </c>
       <c r="I14" t="n">
         <v>3.67</v>
@@ -2634,7 +2629,7 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>44.68</v>
+        <v>44.55</v>
       </c>
     </row>
     <row r="15">
@@ -2662,7 +2657,7 @@
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>3.27</v>
+        <v>3.13</v>
       </c>
       <c r="I15" t="n">
         <v>3.53</v>
@@ -2674,17 +2669,17 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>44.02</v>
+        <v>43.88</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>SNOW</t>
+          <t>MDB</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>14.44</v>
+        <v>11.32</v>
       </c>
       <c r="C16" t="n">
         <v>7.5</v>
@@ -2693,19 +2688,19 @@
         <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>7.58</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="F16" t="n">
-        <v>1</v>
+        <v>1.98</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>9.109999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="I16" t="n">
-        <v>3.56</v>
+        <v>3.73</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -2714,7 +2709,7 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>43.19</v>
+        <v>43.51</v>
       </c>
     </row>
     <row r="17">
@@ -2736,13 +2731,13 @@
         <v>6.64</v>
       </c>
       <c r="F17" t="n">
-        <v>6.49</v>
+        <v>6.5</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>5.03</v>
+        <v>5.12</v>
       </c>
       <c r="I17" t="n">
         <v>3.47</v>
@@ -2754,38 +2749,38 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>43.13</v>
+        <v>43.23</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ACMR</t>
+          <t>SNOW</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>15</v>
+        <v>14.44</v>
       </c>
       <c r="C18" t="n">
-        <v>7.83</v>
+        <v>7.5</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>4.02</v>
+        <v>7.58</v>
       </c>
       <c r="F18" t="n">
-        <v>6.97</v>
+        <v>1.02</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>5.15</v>
+        <v>9.01</v>
       </c>
       <c r="I18" t="n">
-        <v>3.63</v>
+        <v>3.56</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2794,38 +2789,38 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>42.6</v>
+        <v>43.11</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>NET</t>
+          <t>SMCI</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>15</v>
       </c>
       <c r="C19" t="n">
-        <v>7.5</v>
+        <v>7.23</v>
       </c>
       <c r="D19" t="n">
         <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>7.71</v>
+        <v>2.23</v>
       </c>
       <c r="F19" t="n">
-        <v>0.6</v>
+        <v>9.85</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>8.029999999999999</v>
+        <v>4.72</v>
       </c>
       <c r="I19" t="n">
-        <v>3.64</v>
+        <v>3.54</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2834,38 +2829,38 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>42.48</v>
+        <v>42.57</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>MDB</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>11.32</v>
+        <v>8.51</v>
       </c>
       <c r="C20" t="n">
-        <v>7.5</v>
+        <v>14.63</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>9.880000000000001</v>
+        <v>6.87</v>
       </c>
       <c r="F20" t="n">
-        <v>2</v>
+        <v>2.98</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>7.97</v>
+        <v>6.1</v>
       </c>
       <c r="I20" t="n">
-        <v>3.74</v>
+        <v>3.45</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2874,38 +2869,38 @@
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>42.41</v>
+        <v>42.54</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>VRT</t>
+          <t>NET</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>10.91</v>
+        <v>15</v>
       </c>
       <c r="C21" t="n">
-        <v>13.39</v>
+        <v>7.5</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>7.41</v>
+        <v>7.71</v>
       </c>
       <c r="F21" t="n">
-        <v>3.5</v>
+        <v>0.61</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>3.52</v>
+        <v>7.89</v>
       </c>
       <c r="I21" t="n">
-        <v>3.56</v>
+        <v>3.63</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2914,38 +2909,38 @@
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>42.29</v>
+        <v>42.34</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>ACMR</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>8.51</v>
+        <v>15</v>
       </c>
       <c r="C22" t="n">
-        <v>14.63</v>
+        <v>7.83</v>
       </c>
       <c r="D22" t="n">
         <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>6.87</v>
+        <v>4.02</v>
       </c>
       <c r="F22" t="n">
-        <v>3.03</v>
+        <v>6.84</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>5.66</v>
+        <v>4.97</v>
       </c>
       <c r="I22" t="n">
-        <v>3.45</v>
+        <v>3.63</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2954,38 +2949,38 @@
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>42.15</v>
+        <v>42.29</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ASML</t>
+          <t>VRT</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>9.859999999999999</v>
+        <v>10.91</v>
       </c>
       <c r="C23" t="n">
-        <v>14.28</v>
+        <v>13.39</v>
       </c>
       <c r="D23" t="n">
         <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>8.960000000000001</v>
+        <v>7.41</v>
       </c>
       <c r="F23" t="n">
-        <v>0.5600000000000001</v>
+        <v>3.48</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>5.67</v>
+        <v>3.52</v>
       </c>
       <c r="I23" t="n">
-        <v>2.75</v>
+        <v>3.56</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2994,38 +2989,38 @@
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>42.08</v>
+        <v>42.27</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>PANW</t>
+          <t>ASML</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>13.54</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="C24" t="n">
-        <v>7.5</v>
+        <v>14.28</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>7.97</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="F24" t="n">
-        <v>0.58</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>8.32</v>
+        <v>5.64</v>
       </c>
       <c r="I24" t="n">
-        <v>3.57</v>
+        <v>2.75</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -3034,38 +3029,38 @@
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>41.48</v>
+        <v>42.05</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>SMCI</t>
+          <t>PANW</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>15</v>
+        <v>13.54</v>
       </c>
       <c r="C25" t="n">
-        <v>7.23</v>
+        <v>7.5</v>
       </c>
       <c r="D25" t="n">
         <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>2.23</v>
+        <v>7.97</v>
       </c>
       <c r="F25" t="n">
-        <v>9.93</v>
+        <v>0.6</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>3.14</v>
+        <v>8.06</v>
       </c>
       <c r="I25" t="n">
-        <v>3.54</v>
+        <v>3.57</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -3074,7 +3069,7 @@
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>41.07</v>
+        <v>41.24</v>
       </c>
     </row>
     <row r="26">
@@ -3096,13 +3091,13 @@
         <v>9.449999999999999</v>
       </c>
       <c r="F26" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>5.31</v>
+        <v>5.36</v>
       </c>
       <c r="I26" t="n">
         <v>3.7</v>
@@ -3114,7 +3109,7 @@
         <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>40.24</v>
+        <v>40.28</v>
       </c>
     </row>
     <row r="27">
@@ -3136,13 +3131,13 @@
         <v>7.23</v>
       </c>
       <c r="F27" t="n">
-        <v>5.74</v>
+        <v>5.64</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>0.73</v>
+        <v>1.07</v>
       </c>
       <c r="I27" t="n">
         <v>3.49</v>
@@ -3154,7 +3149,7 @@
         <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>39.57</v>
+        <v>39.81</v>
       </c>
     </row>
     <row r="28">
@@ -3176,13 +3171,13 @@
         <v>9.24</v>
       </c>
       <c r="F28" t="n">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>7.23</v>
+        <v>6.89</v>
       </c>
       <c r="I28" t="n">
         <v>3.48</v>
@@ -3194,7 +3189,7 @@
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>39.37</v>
+        <v>39.04</v>
       </c>
     </row>
     <row r="29">
@@ -3216,13 +3211,13 @@
         <v>7.11</v>
       </c>
       <c r="F29" t="n">
-        <v>0.58</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>7.95</v>
+        <v>8.15</v>
       </c>
       <c r="I29" t="n">
         <v>3.53</v>
@@ -3234,7 +3229,7 @@
         <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>38.81</v>
+        <v>38.99</v>
       </c>
     </row>
     <row r="30">
@@ -3256,13 +3251,13 @@
         <v>6.78</v>
       </c>
       <c r="F30" t="n">
-        <v>4.01</v>
+        <v>4.05</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>5.58</v>
+        <v>5.76</v>
       </c>
       <c r="I30" t="n">
         <v>3.57</v>
@@ -3274,7 +3269,7 @@
         <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>36.5</v>
+        <v>36.72</v>
       </c>
     </row>
     <row r="31">
@@ -3296,13 +3291,13 @@
         <v>0.8</v>
       </c>
       <c r="F31" t="n">
-        <v>6.67</v>
+        <v>6.57</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>2.31</v>
+        <v>2.68</v>
       </c>
       <c r="I31" t="n">
         <v>3.58</v>
@@ -3314,7 +3309,7 @@
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>31.5</v>
+        <v>31.77</v>
       </c>
     </row>
   </sheetData>
@@ -3352,8 +3347,8 @@
     <col width="16" customWidth="1" min="18" max="18"/>
     <col width="19" customWidth="1" min="19" max="19"/>
     <col width="23" customWidth="1" min="20" max="20"/>
-    <col width="22" customWidth="1" min="21" max="21"/>
-    <col width="22" customWidth="1" min="22" max="22"/>
+    <col width="23" customWidth="1" min="21" max="21"/>
+    <col width="21" customWidth="1" min="22" max="22"/>
     <col width="22" customWidth="1" min="23" max="23"/>
     <col width="18" customWidth="1" min="24" max="24"/>
     <col width="24" customWidth="1" min="25" max="25"/>
@@ -3519,12 +3514,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>MU</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Micron Technology, Inc.</t>
+          <t>Taiwan Semiconductor Manufacturing Company Limited</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -3537,60 +3532,69 @@
           <t>Semiconductors</t>
         </is>
       </c>
+      <c r="E2" t="n">
+        <v>2164886077440</v>
+      </c>
       <c r="F2" t="n">
-        <v>910.4299926757812</v>
+        <v>417.4100036621094</v>
       </c>
       <c r="G2" t="n">
-        <v>90273996800</v>
+        <v>4440492343296</v>
       </c>
       <c r="H2" t="n">
-        <v>3.457</v>
+        <v>0.36</v>
       </c>
       <c r="I2" t="n">
-        <v>44.28</v>
+        <v>13.41</v>
       </c>
       <c r="J2" t="n">
-        <v>13.685</v>
+        <v>0.774</v>
       </c>
       <c r="K2" t="n">
-        <v>7639499776</v>
+        <v>730826014720</v>
       </c>
       <c r="M2" t="n">
-        <v>26022000640</v>
+        <v>3518010228736</v>
       </c>
       <c r="N2" t="n">
-        <v>6376000000</v>
+        <v>1068558516224</v>
       </c>
       <c r="O2" t="n">
-        <v>0.7256899999999999</v>
+        <v>0.6423</v>
       </c>
       <c r="P2" t="n">
-        <v>0.80370003</v>
+        <v>0.60344005</v>
       </c>
       <c r="Q2" t="n">
-        <v>20.560751</v>
+        <v>31.126772</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0.48753288</v>
+      </c>
+      <c r="S2" t="n">
+        <v>2.962245505545432</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.01142300818916231</v>
+        <v>0.03470414683054357</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2124767079710355</v>
+        <v>0.01471556274845898</v>
       </c>
       <c r="V2" t="n">
-        <v>1.127548792894937</v>
+        <v>0.133840746405375</v>
       </c>
       <c r="W2" t="n">
-        <v>6.748905897439427</v>
+        <v>0.7913594096526697</v>
       </c>
       <c r="X2" t="n">
-        <v>0.00242</v>
+        <v>0.00013</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.7999000000000001</v>
+        <v>0.15493</v>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>2026-08-24T23:41:55.651157+00:00</t>
+          <t>2026-08-25T23:44:59.127707+00:00</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
@@ -3602,12 +3606,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>MU</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Taiwan Semiconductor Manufacturing Company Limited</t>
+          <t>Micron Technology, Inc.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -3621,68 +3625,68 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2127076655104</v>
+        <v>1053689905152</v>
       </c>
       <c r="F3" t="n">
-        <v>410.1199951171875</v>
+        <v>932.969970703125</v>
       </c>
       <c r="G3" t="n">
-        <v>4440492343296</v>
+        <v>90273996800</v>
       </c>
       <c r="H3" t="n">
-        <v>0.36</v>
+        <v>3.457</v>
       </c>
       <c r="I3" t="n">
-        <v>13.41</v>
+        <v>44.25</v>
       </c>
       <c r="J3" t="n">
-        <v>0.774</v>
+        <v>13.685</v>
       </c>
       <c r="K3" t="n">
-        <v>730826014720</v>
+        <v>7639499776</v>
       </c>
       <c r="M3" t="n">
-        <v>3518010228736</v>
+        <v>26022000640</v>
       </c>
       <c r="N3" t="n">
-        <v>1068558516224</v>
+        <v>6376000000</v>
       </c>
       <c r="O3" t="n">
-        <v>0.6423</v>
+        <v>0.7256899999999999</v>
       </c>
       <c r="P3" t="n">
-        <v>0.60344005</v>
+        <v>0.80370003</v>
       </c>
       <c r="Q3" t="n">
-        <v>30.583147</v>
+        <v>21.084066</v>
       </c>
       <c r="R3" t="n">
-        <v>0.4790182</v>
+        <v>11.672131</v>
       </c>
       <c r="S3" t="n">
-        <v>2.910510316082471</v>
+        <v>137.9265575034425</v>
       </c>
       <c r="T3" t="n">
-        <v>0.01663318062062324</v>
+        <v>0.01305169481163082</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0162178201380454</v>
+        <v>0.04156075280455829</v>
       </c>
       <c r="V3" t="n">
-        <v>0.1125350905877338</v>
+        <v>1.217510665558717</v>
       </c>
       <c r="W3" t="n">
-        <v>0.7797145067036872</v>
+        <v>7.026691786103124</v>
       </c>
       <c r="X3" t="n">
-        <v>0.00013</v>
+        <v>0.00242</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.15498</v>
+        <v>0.7998100500000001</v>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>2026-08-24T23:42:02.320528+00:00</t>
+          <t>2026-08-25T23:44:52.674132+00:00</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
@@ -3713,10 +3717,10 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>41511845888</v>
+        <v>42239107072</v>
       </c>
       <c r="F4" t="n">
-        <v>222.6100006103516</v>
+        <v>226.5099945068359</v>
       </c>
       <c r="G4" t="n">
         <v>1335116032</v>
@@ -3725,7 +3729,7 @@
         <v>1.57</v>
       </c>
       <c r="I4" t="n">
-        <v>2.51</v>
+        <v>2.52</v>
       </c>
       <c r="J4" t="n">
         <v>3.432</v>
@@ -3746,35 +3750,35 @@
         <v>0.35661998</v>
       </c>
       <c r="Q4" t="n">
-        <v>88.68925</v>
+        <v>89.88491999999999</v>
       </c>
       <c r="R4" t="n">
-        <v>31.092314</v>
+        <v>31.637032</v>
       </c>
       <c r="S4" t="n">
-        <v>165.5110430309258</v>
+        <v>168.4106914215203</v>
       </c>
       <c r="T4" t="n">
-        <v>0.04438192345649994</v>
+        <v>0.06267886930759103</v>
       </c>
       <c r="U4" t="n">
-        <v>0.01922987444631796</v>
+        <v>0.02197254615862865</v>
       </c>
       <c r="V4" t="n">
-        <v>0.7943737303816445</v>
+        <v>0.8259571860899382</v>
       </c>
       <c r="W4" t="n">
-        <v>0.9520343635848012</v>
+        <v>0.9626547727179577</v>
       </c>
       <c r="X4" t="n">
         <v>0.108789995</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.74186</v>
+        <v>0.74177</v>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>2026-08-24T23:41:56.684819+00:00</t>
+          <t>2026-08-25T23:44:53.857324+00:00</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
@@ -3805,10 +3809,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>237299417088</v>
+        <v>240818241536</v>
       </c>
       <c r="F5" t="n">
-        <v>188.1499938964844</v>
+        <v>190.9400024414062</v>
       </c>
       <c r="G5" t="n">
         <v>10540800000</v>
@@ -3817,7 +3821,7 @@
         <v>0.377</v>
       </c>
       <c r="I5" t="n">
-        <v>3.17</v>
+        <v>3.16</v>
       </c>
       <c r="J5" t="n">
         <v>0.357</v>
@@ -3838,35 +3842,35 @@
         <v>0.45393002</v>
       </c>
       <c r="Q5" t="n">
-        <v>59.35331</v>
+        <v>60.42405</v>
       </c>
       <c r="R5" t="n">
-        <v>22.512468</v>
+        <v>22.846296</v>
       </c>
       <c r="S5" t="n">
-        <v>60.97871006546119</v>
+        <v>61.88294058746992</v>
       </c>
       <c r="T5" t="n">
-        <v>0.08138391836464787</v>
+        <v>0.09741937130353229</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2215152592845022</v>
+        <v>0.208404588819511</v>
       </c>
       <c r="V5" t="n">
-        <v>0.4168988885409695</v>
+        <v>0.49839128921081</v>
       </c>
       <c r="W5" t="n">
-        <v>0.4120074588854361</v>
+        <v>0.4352075471827954</v>
       </c>
       <c r="X5" t="n">
         <v>0.17241</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.73608</v>
+        <v>0.73283994</v>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>2026-08-24T23:42:04.472032+00:00</t>
+          <t>2026-08-25T23:45:01.664633+00:00</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
@@ -3897,10 +3901,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>422673940480</v>
+        <v>415080284160</v>
       </c>
       <c r="F6" t="n">
-        <v>175.8899993896484</v>
+        <v>172.7299957275391</v>
       </c>
       <c r="G6" t="n">
         <v>6155940864</v>
@@ -3909,7 +3913,7 @@
         <v>0.928</v>
       </c>
       <c r="I6" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="J6" t="n">
         <v>2.154</v>
@@ -3930,35 +3934,35 @@
         <v>0.47120997</v>
       </c>
       <c r="Q6" t="n">
-        <v>150.33334</v>
+        <v>146.38136</v>
       </c>
       <c r="R6" t="n">
-        <v>68.66114</v>
+        <v>67.4276</v>
       </c>
       <c r="S6" t="n">
-        <v>195.7635390648473</v>
+        <v>192.2464993487078</v>
       </c>
       <c r="T6" t="n">
-        <v>0.4309307029756004</v>
+        <v>0.4052228953838191</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2849941051670306</v>
+        <v>0.2644947877721477</v>
       </c>
       <c r="V6" t="n">
-        <v>0.3005766951003199</v>
+        <v>0.3225879606056874</v>
       </c>
       <c r="W6" t="n">
-        <v>0.1080382594368936</v>
+        <v>0.09900106725119362</v>
       </c>
       <c r="X6" t="n">
         <v>0.03477</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.64834</v>
+        <v>0.64827</v>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>2026-08-24T23:41:53.187485+00:00</t>
+          <t>2026-08-25T23:44:49.725077+00:00</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr">
@@ -3989,10 +3993,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>57048739840</v>
+        <v>57287942144</v>
       </c>
       <c r="F7" t="n">
-        <v>364.8999938964844</v>
+        <v>366.4299926757812</v>
       </c>
       <c r="G7" t="n">
         <v>4464031232</v>
@@ -4001,7 +4005,7 @@
         <v>1.039</v>
       </c>
       <c r="I7" t="n">
-        <v>7.29</v>
+        <v>7.3</v>
       </c>
       <c r="J7" t="n">
         <v>3.858</v>
@@ -4022,35 +4026,35 @@
         <v>0.33161</v>
       </c>
       <c r="Q7" t="n">
-        <v>50.05487</v>
+        <v>50.19589</v>
       </c>
       <c r="R7" t="n">
-        <v>12.779646</v>
+        <v>12.833231</v>
       </c>
       <c r="S7" t="n">
-        <v>130.4325233440278</v>
+        <v>130.9794199133109</v>
       </c>
       <c r="T7" t="n">
-        <v>0.04280972763463753</v>
+        <v>0.04718215196186981</v>
       </c>
       <c r="U7" t="n">
-        <v>0.01802251816504241</v>
+        <v>-0.05835951358837577</v>
       </c>
       <c r="V7" t="n">
-        <v>0.1237118992363824</v>
+        <v>0.1509211258328167</v>
       </c>
       <c r="W7" t="n">
-        <v>2.172889130452521</v>
+        <v>2.138020274911799</v>
       </c>
       <c r="X7" t="n">
         <v>0.00202</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.00457</v>
+        <v>1.0044999</v>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>2026-08-24T23:41:57.226569+00:00</t>
+          <t>2026-08-25T23:44:54.397196+00:00</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr">
@@ -4062,12 +4066,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>NVDA</t>
+          <t>DELL</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>NVIDIA Corporation</t>
+          <t>Dell Technologies Inc.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -4077,72 +4081,72 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Semiconductors</t>
+          <t>Computer Hardware</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5049593888768</v>
+        <v>291733307392</v>
       </c>
       <c r="F8" t="n">
-        <v>208.4799957275391</v>
+        <v>451.5</v>
       </c>
       <c r="G8" t="n">
-        <v>253491003392</v>
+        <v>134001999872</v>
       </c>
       <c r="H8" t="n">
-        <v>0.852</v>
+        <v>0.875</v>
       </c>
       <c r="I8" t="n">
-        <v>6.53</v>
+        <v>12.56</v>
       </c>
       <c r="J8" t="n">
-        <v>2.145</v>
+        <v>2.825</v>
       </c>
       <c r="K8" t="n">
-        <v>46335873024</v>
+        <v>5434124800</v>
       </c>
       <c r="M8" t="n">
-        <v>53171998720</v>
+        <v>11580999680</v>
       </c>
       <c r="N8" t="n">
-        <v>12814000128</v>
+        <v>31924000768</v>
       </c>
       <c r="O8" t="n">
-        <v>0.74144995</v>
+        <v>0.19212</v>
       </c>
       <c r="P8" t="n">
-        <v>0.65596</v>
+        <v>0.08857000600000001</v>
       </c>
       <c r="Q8" t="n">
-        <v>31.92649</v>
+        <v>35.947453</v>
       </c>
       <c r="R8" t="n">
-        <v>19.92021</v>
+        <v>2.1770818</v>
       </c>
       <c r="S8" t="n">
-        <v>108.9780672990131</v>
+        <v>53.68542647235485</v>
       </c>
       <c r="T8" t="n">
-        <v>0.007928831070801889</v>
+        <v>0.03200000000000003</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.03068325860585119</v>
+        <v>0.4823852705245668</v>
       </c>
       <c r="V8" t="n">
-        <v>0.09964313567363581</v>
+        <v>2.807666754214015</v>
       </c>
       <c r="W8" t="n">
-        <v>0.1728617934376302</v>
+        <v>2.490218142880296</v>
       </c>
       <c r="X8" t="n">
-        <v>0.03991</v>
+        <v>0.07491</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.71262</v>
+        <v>0.75588</v>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>2026-08-24T23:41:52.684207+00:00</t>
+          <t>2026-08-25T23:45:02.223851+00:00</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr">
@@ -4154,12 +4158,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>DELL</t>
+          <t>NVDA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Dell Technologies Inc.</t>
+          <t>NVIDIA Corporation</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -4169,72 +4173,72 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Computer Hardware</t>
+          <t>Semiconductors</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>279902420992</v>
+        <v>5160284192768</v>
       </c>
       <c r="F9" t="n">
-        <v>433.1900024414062</v>
+        <v>213.0500030517578</v>
       </c>
       <c r="G9" t="n">
-        <v>134001999872</v>
+        <v>253491003392</v>
       </c>
       <c r="H9" t="n">
-        <v>0.875</v>
+        <v>0.852</v>
       </c>
       <c r="I9" t="n">
-        <v>0.49</v>
+        <v>6.53</v>
       </c>
       <c r="J9" t="n">
-        <v>2.825</v>
+        <v>2.145</v>
       </c>
       <c r="K9" t="n">
-        <v>5434124800</v>
+        <v>46335873024</v>
       </c>
       <c r="M9" t="n">
-        <v>11580999680</v>
+        <v>53171998720</v>
       </c>
       <c r="N9" t="n">
-        <v>31924000768</v>
+        <v>12814000128</v>
       </c>
       <c r="O9" t="n">
-        <v>0.19212</v>
+        <v>0.74144995</v>
       </c>
       <c r="P9" t="n">
-        <v>0.08857000600000001</v>
+        <v>0.65596</v>
       </c>
       <c r="Q9" t="n">
-        <v>884.0612</v>
+        <v>32.62634</v>
       </c>
       <c r="R9" t="n">
-        <v>2.0887928</v>
+        <v>20.356873</v>
       </c>
       <c r="S9" t="n">
-        <v>51.50827985989574</v>
+        <v>111.3669357237576</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.009851422991071446</v>
+        <v>0.03002323933385975</v>
       </c>
       <c r="U9" t="n">
-        <v>0.4699205577649306</v>
+        <v>-0.007268423517560629</v>
       </c>
       <c r="V9" t="n">
-        <v>2.559731672884073</v>
+        <v>0.1135987674078007</v>
       </c>
       <c r="W9" t="n">
-        <v>2.353027819007263</v>
+        <v>0.1864399218446351</v>
       </c>
       <c r="X9" t="n">
-        <v>0.07491</v>
+        <v>0.03991</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.75602996</v>
+        <v>0.71185</v>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>2026-08-24T23:42:05.010572+00:00</t>
+          <t>2026-08-25T23:44:49.156368+00:00</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr">
@@ -4265,10 +4269,10 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>8585252352</v>
+        <v>8631883776</v>
       </c>
       <c r="F10" t="n">
-        <v>16.56999969482422</v>
+        <v>16.65999984741211</v>
       </c>
       <c r="G10" t="n">
         <v>1672329984</v>
@@ -4295,35 +4299,35 @@
         <v>0.07274</v>
       </c>
       <c r="Q10" t="n">
-        <v>27.616665</v>
+        <v>27.766665</v>
       </c>
       <c r="R10" t="n">
-        <v>5.133707</v>
+        <v>5.161591</v>
       </c>
       <c r="S10" t="n">
-        <v>16.78270236970969</v>
+        <v>16.87385884106087</v>
       </c>
       <c r="T10" t="n">
-        <v>0.5285977363079994</v>
+        <v>0.5369003332933329</v>
       </c>
       <c r="U10" t="n">
-        <v>0.5160109087076308</v>
+        <v>0.5022542487093149</v>
       </c>
       <c r="V10" t="n">
-        <v>0.5342592039062499</v>
+        <v>0.6381513984691323</v>
       </c>
       <c r="W10" t="n">
-        <v>0.4834377423139571</v>
+        <v>0.5104261333399276</v>
       </c>
       <c r="X10" t="n">
         <v>0.09236999999999999</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.91146004</v>
+        <v>0.91143</v>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>2026-08-24T23:42:10.047782+00:00</t>
+          <t>2026-08-25T23:45:07.140555+00:00</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr">
@@ -4335,87 +4339,87 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Alphabet Inc.</t>
+          <t>Advanced Micro Devices, Inc.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Internet Content &amp; Information</t>
+          <t>Semiconductors</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4256751157248</v>
+        <v>782249361408</v>
       </c>
       <c r="F11" t="n">
-        <v>348.0599975585938</v>
+        <v>479.1799926757812</v>
       </c>
       <c r="G11" t="n">
-        <v>445865984000</v>
+        <v>41305001984</v>
       </c>
       <c r="H11" t="n">
-        <v>0.242</v>
+        <v>0.501</v>
       </c>
       <c r="I11" t="n">
-        <v>19.93</v>
+        <v>3.93</v>
       </c>
       <c r="J11" t="n">
-        <v>2.94</v>
+        <v>1.595</v>
       </c>
       <c r="K11" t="n">
-        <v>22665000960</v>
+        <v>8841499648</v>
       </c>
       <c r="M11" t="n">
-        <v>242473992192</v>
+        <v>13111000064</v>
       </c>
       <c r="N11" t="n">
-        <v>120790999040</v>
+        <v>4276000000</v>
       </c>
       <c r="O11" t="n">
-        <v>0.60897</v>
+        <v>0.55724</v>
       </c>
       <c r="P11" t="n">
-        <v>0.34033</v>
+        <v>0.1725</v>
       </c>
       <c r="Q11" t="n">
-        <v>17.464125</v>
+        <v>121.92875</v>
       </c>
       <c r="R11" t="n">
-        <v>9.547153</v>
+        <v>18.93837</v>
       </c>
       <c r="S11" t="n">
-        <v>187.8116468982493</v>
+        <v>88.47473760686621</v>
       </c>
       <c r="T11" t="n">
-        <v>0.08857199033333196</v>
+        <v>-0.08194275032277476</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.09061313206295496</v>
+        <v>-0.04903852280124332</v>
       </c>
       <c r="V11" t="n">
-        <v>0.1064609321422796</v>
+        <v>1.437334576803009</v>
       </c>
       <c r="W11" t="n">
-        <v>0.6936919304075204</v>
+        <v>1.933276144009865</v>
       </c>
       <c r="X11" t="n">
-        <v>0.01596</v>
+        <v>0.00425</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.81073</v>
+        <v>0.75365996</v>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>2026-08-24T23:41:59.692825+00:00</t>
+          <t>2026-08-25T23:44:50.453971+00:00</t>
         </is>
       </c>
       <c r="AD11" t="inlineStr">
@@ -4427,87 +4431,87 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>GOOGL</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Advanced Micro Devices, Inc.</t>
+          <t>Alphabet Inc.</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Semiconductors</t>
+          <t>Internet Content &amp; Information</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>745624764416</v>
+        <v>4243298189312</v>
       </c>
       <c r="F12" t="n">
-        <v>456.7449951171875</v>
+        <v>346.9599914550781</v>
       </c>
       <c r="G12" t="n">
-        <v>41305001984</v>
+        <v>445865984000</v>
       </c>
       <c r="H12" t="n">
-        <v>0.501</v>
+        <v>0.242</v>
       </c>
       <c r="I12" t="n">
-        <v>3.93</v>
+        <v>19.94</v>
       </c>
       <c r="J12" t="n">
-        <v>1.595</v>
+        <v>2.94</v>
       </c>
       <c r="K12" t="n">
-        <v>8841499648</v>
+        <v>22665000960</v>
       </c>
       <c r="M12" t="n">
-        <v>13111000064</v>
+        <v>242473992192</v>
       </c>
       <c r="N12" t="n">
-        <v>4276000000</v>
+        <v>120790999040</v>
       </c>
       <c r="O12" t="n">
-        <v>0.55724</v>
+        <v>0.60897</v>
       </c>
       <c r="P12" t="n">
-        <v>0.1725</v>
+        <v>0.34033</v>
       </c>
       <c r="Q12" t="n">
-        <v>116.2201</v>
+        <v>17.4002</v>
       </c>
       <c r="R12" t="n">
-        <v>18.051682</v>
+        <v>9.516980999999999</v>
       </c>
       <c r="S12" t="n">
-        <v>84.33238637120398</v>
+        <v>187.2180899882036</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.1249257889929509</v>
+        <v>0.08513167589937809</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.0230262762798048</v>
+        <v>-0.1072638518099384</v>
       </c>
       <c r="V12" t="n">
-        <v>1.282013535076157</v>
+        <v>0.1153219631662308</v>
       </c>
       <c r="W12" t="n">
-        <v>1.722609740539637</v>
+        <v>0.6689037745617639</v>
       </c>
       <c r="X12" t="n">
-        <v>0.00429</v>
+        <v>0.01596</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.75372005</v>
+        <v>0.81035006</v>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>2026-08-24T23:41:53.768141+00:00</t>
+          <t>2026-08-25T23:44:56.718881+00:00</t>
         </is>
       </c>
       <c r="AD12" t="inlineStr">
@@ -4538,10 +4542,10 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>384427229184</v>
+        <v>380958507008</v>
       </c>
       <c r="F13" t="n">
-        <v>484.1900024414062</v>
+        <v>480.0400085449219</v>
       </c>
       <c r="G13" t="n">
         <v>30837000192</v>
@@ -4571,35 +4575,35 @@
         <v>0.33736</v>
       </c>
       <c r="Q13" t="n">
-        <v>41.848747</v>
+        <v>41.490063</v>
       </c>
       <c r="R13" t="n">
-        <v>12.466428</v>
+        <v>12.353942</v>
       </c>
       <c r="S13" t="n">
-        <v>125.0017367585479</v>
+        <v>123.8738346137044</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.09611606402754613</v>
+        <v>-0.1038632558293222</v>
       </c>
       <c r="U13" t="n">
-        <v>0.1215932426464699</v>
+        <v>0.05641651120348978</v>
       </c>
       <c r="V13" t="n">
-        <v>0.2928508474863543</v>
+        <v>0.2880491350104883</v>
       </c>
       <c r="W13" t="n">
-        <v>1.996295596499046</v>
+        <v>1.979783535953246</v>
       </c>
       <c r="X13" t="n">
         <v>0.00331</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.86535</v>
+        <v>0.86283</v>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>2026-08-24T23:41:55.017445+00:00</t>
+          <t>2026-08-25T23:44:51.879989+00:00</t>
         </is>
       </c>
       <c r="AD13" t="inlineStr">
@@ -4630,10 +4634,10 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>81068367872</v>
+        <v>80070139904</v>
       </c>
       <c r="F14" t="n">
-        <v>225.7700042724609</v>
+        <v>222.9900054931641</v>
       </c>
       <c r="G14" t="n">
         <v>3966725120</v>
@@ -4642,7 +4646,7 @@
         <v>0.356</v>
       </c>
       <c r="I14" t="n">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="J14" t="n">
         <v>14.985</v>
@@ -4663,25 +4667,25 @@
         <v>0.00666</v>
       </c>
       <c r="Q14" t="n">
-        <v>460.7551</v>
+        <v>445.98</v>
       </c>
       <c r="R14" t="n">
-        <v>20.437103</v>
+        <v>20.185452</v>
       </c>
       <c r="S14" t="n">
-        <v>77.10425668653359</v>
+        <v>76.15484044075602</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.08543302392346452</v>
+        <v>-0.0966944626839904</v>
       </c>
       <c r="U14" t="n">
-        <v>0.01551815776621002</v>
+        <v>-0.002950987799381632</v>
       </c>
       <c r="V14" t="n">
-        <v>0.9520145004666292</v>
+        <v>1.173074210742595</v>
       </c>
       <c r="W14" t="n">
-        <v>0.7205456650829558</v>
+        <v>0.736952773110682</v>
       </c>
       <c r="X14" t="n">
         <v>0.00619</v>
@@ -4691,7 +4695,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>2026-08-24T23:42:07.307540+00:00</t>
+          <t>2026-08-25T23:45:04.894691+00:00</t>
         </is>
       </c>
       <c r="AD14" t="inlineStr">
@@ -4722,10 +4726,10 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1706829545472</v>
+        <v>1697219084288</v>
       </c>
       <c r="F15" t="n">
-        <v>358.760009765625</v>
+        <v>356.739990234375</v>
       </c>
       <c r="G15" t="n">
         <v>75464998912</v>
@@ -4734,7 +4738,7 @@
         <v>0.479</v>
       </c>
       <c r="I15" t="n">
-        <v>6.01</v>
+        <v>6.03</v>
       </c>
       <c r="J15" t="n">
         <v>0.854</v>
@@ -4755,35 +4759,35 @@
         <v>0.48988</v>
       </c>
       <c r="Q15" t="n">
-        <v>59.693844</v>
+        <v>59.16086</v>
       </c>
       <c r="R15" t="n">
-        <v>22.617498</v>
+        <v>22.490149</v>
       </c>
       <c r="S15" t="n">
-        <v>62.72283999578242</v>
+        <v>62.36967325998923</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.06064097938793045</v>
+        <v>-0.06593009611454637</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.132351855799088</v>
+        <v>-0.1533267524098848</v>
       </c>
       <c r="V15" t="n">
-        <v>0.08246379532588</v>
+        <v>0.08389571930187634</v>
       </c>
       <c r="W15" t="n">
-        <v>0.2292131574770397</v>
+        <v>0.2213365095285857</v>
       </c>
       <c r="X15" t="n">
         <v>0.01948</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.80174005</v>
+        <v>0.80134004</v>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>2026-08-24T23:41:54.412556+00:00</t>
+          <t>2026-08-25T23:44:51.058964+00:00</t>
         </is>
       </c>
       <c r="AD15" t="inlineStr">
@@ -4795,12 +4799,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>SNOW</t>
+          <t>MDB</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Snowflake Inc.</t>
+          <t>MongoDB, Inc.</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -4810,66 +4814,66 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Software - Application</t>
+          <t>Software - Infrastructure</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>111875547136</v>
+        <v>32568498176</v>
       </c>
       <c r="F16" t="n">
-        <v>322.7799987792969</v>
+        <v>404.9200134277344</v>
       </c>
       <c r="G16" t="n">
-        <v>5032822784</v>
+        <v>2602398976</v>
       </c>
       <c r="H16" t="n">
-        <v>0.335</v>
+        <v>0.252</v>
       </c>
       <c r="I16" t="n">
-        <v>-3.53</v>
+        <v>-0.36</v>
       </c>
       <c r="K16" t="n">
-        <v>1739497728</v>
+        <v>517605376</v>
       </c>
       <c r="M16" t="n">
-        <v>2954998016</v>
+        <v>2427152896</v>
       </c>
       <c r="N16" t="n">
-        <v>2772094976</v>
+        <v>58635000</v>
       </c>
       <c r="O16" t="n">
-        <v>0.67144996</v>
+        <v>0.71970004</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.22173999</v>
+        <v>-0.03607</v>
       </c>
       <c r="R16" t="n">
-        <v>22.229185</v>
+        <v>12.514798</v>
       </c>
       <c r="S16" t="n">
-        <v>64.31485671707644</v>
+        <v>62.92148359757376</v>
       </c>
       <c r="T16" t="n">
-        <v>0.2041334093825102</v>
+        <v>0.3577895908063724</v>
       </c>
       <c r="U16" t="n">
-        <v>0.8744483420421558</v>
+        <v>0.3174556869582659</v>
       </c>
       <c r="V16" t="n">
-        <v>0.8711883987205615</v>
+        <v>0.3259980348506211</v>
       </c>
       <c r="W16" t="n">
-        <v>0.6400589542368125</v>
+        <v>0.8536898411560356</v>
       </c>
       <c r="X16" t="n">
-        <v>0.02962</v>
+        <v>0.02641</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.81998</v>
+        <v>0.96112</v>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>2026-08-24T23:42:06.633040+00:00</t>
+          <t>2026-08-25T23:45:06.572589+00:00</t>
         </is>
       </c>
       <c r="AD16" t="inlineStr">
@@ -4900,10 +4904,10 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2826769268736</v>
+        <v>2815874826240</v>
       </c>
       <c r="F17" t="n">
-        <v>262.0700073242188</v>
+        <v>261.0599975585938</v>
       </c>
       <c r="G17" t="n">
         <v>775680032768</v>
@@ -4912,7 +4916,7 @@
         <v>0.196</v>
       </c>
       <c r="I17" t="n">
-        <v>12.44</v>
+        <v>12.42</v>
       </c>
       <c r="J17" t="n">
         <v>2.423</v>
@@ -4933,35 +4937,35 @@
         <v>0.13689</v>
       </c>
       <c r="Q17" t="n">
-        <v>21.066721</v>
+        <v>21.019323</v>
       </c>
       <c r="R17" t="n">
-        <v>3.6442466</v>
+        <v>3.6302016</v>
       </c>
       <c r="S17" t="n">
-        <v>878.1172758935854</v>
+        <v>874.732989007219</v>
       </c>
       <c r="T17" t="n">
-        <v>0.1290767594463185</v>
+        <v>0.1247253322653736</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.01595824528055845</v>
+        <v>-0.01594485600693796</v>
       </c>
       <c r="V17" t="n">
-        <v>0.247299065075093</v>
+        <v>0.2717883379204353</v>
       </c>
       <c r="W17" t="n">
-        <v>0.1452106778452436</v>
+        <v>0.145301372126208</v>
       </c>
       <c r="X17" t="n">
         <v>0.088690005</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.6879</v>
+        <v>0.68723</v>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>2026-08-24T23:42:00.253171+00:00</t>
+          <t>2026-08-25T23:44:57.275831+00:00</t>
         </is>
       </c>
       <c r="AD17" t="inlineStr">
@@ -4973,12 +4977,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ACMR</t>
+          <t>SNOW</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>ACM Research, Inc.</t>
+          <t>Snowflake Inc.</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -4988,69 +4992,66 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Semiconductor Equipment &amp; Materials</t>
+          <t>Software - Application</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5387017216</v>
+        <v>109879132160</v>
       </c>
       <c r="F18" t="n">
-        <v>77.34500122070312</v>
+        <v>317.0199890136719</v>
       </c>
       <c r="G18" t="n">
-        <v>1037772032</v>
+        <v>5032822784</v>
       </c>
       <c r="H18" t="n">
-        <v>0.36</v>
+        <v>0.335</v>
       </c>
       <c r="I18" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="J18" t="n">
-        <v>1.806</v>
+        <v>-3.52</v>
       </c>
       <c r="K18" t="n">
-        <v>-186610256</v>
+        <v>1739497728</v>
       </c>
       <c r="M18" t="n">
-        <v>1439374976</v>
+        <v>2954998016</v>
       </c>
       <c r="N18" t="n">
-        <v>349319008</v>
+        <v>2772094976</v>
       </c>
       <c r="O18" t="n">
-        <v>0.43835</v>
+        <v>0.67144996</v>
       </c>
       <c r="P18" t="n">
-        <v>0.16982001</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>36.483494</v>
+        <v>-0.22173999</v>
       </c>
       <c r="R18" t="n">
-        <v>5.1909447</v>
+        <v>21.832506</v>
+      </c>
+      <c r="S18" t="n">
+        <v>63.16716049197392</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.08272057043839431</v>
+        <v>0.1826456461276966</v>
       </c>
       <c r="U18" t="n">
-        <v>0.05446493292009436</v>
+        <v>0.7850223993173411</v>
       </c>
       <c r="V18" t="n">
-        <v>0.1615108195567321</v>
+        <v>1.011548075737035</v>
       </c>
       <c r="W18" t="n">
-        <v>1.533409743896125</v>
+        <v>0.6284158667585058</v>
       </c>
       <c r="X18" t="n">
-        <v>0.12675999</v>
+        <v>0.02962</v>
       </c>
       <c r="Y18" t="n">
-        <v>0.78052</v>
+        <v>0.81942004</v>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>2026-08-24T23:41:56.198991+00:00</t>
+          <t>2026-08-25T23:45:03.993300+00:00</t>
         </is>
       </c>
       <c r="AD18" t="inlineStr">
@@ -5062,12 +5063,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>NET</t>
+          <t>SMCI</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Cloudflare, Inc.</t>
+          <t>Super Micro Computer, Inc.</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -5077,66 +5078,69 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Software - Infrastructure</t>
+          <t>Computer Hardware</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>99826950144</v>
+        <v>24878735360</v>
       </c>
       <c r="F19" t="n">
-        <v>280.3500061035156</v>
+        <v>38.45999908447266</v>
       </c>
       <c r="G19" t="n">
-        <v>2512349952</v>
+        <v>39063072768</v>
       </c>
       <c r="H19" t="n">
-        <v>0.359</v>
+        <v>0.9320000000000001</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.59</v>
+        <v>3.26</v>
+      </c>
+      <c r="J19" t="n">
+        <v>4.094</v>
       </c>
       <c r="K19" t="n">
-        <v>692851968</v>
+        <v>-8231267840</v>
       </c>
       <c r="M19" t="n">
-        <v>4162798080</v>
+        <v>7521474048</v>
       </c>
       <c r="N19" t="n">
-        <v>3529349888</v>
+        <v>9311492096</v>
       </c>
       <c r="O19" t="n">
-        <v>0.72577006</v>
+        <v>0.108219996</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.07902000000000001</v>
+        <v>0.13382</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>11.797545</v>
       </c>
       <c r="R19" t="n">
-        <v>39.734493</v>
-      </c>
-      <c r="S19" t="n">
-        <v>144.0812103517039</v>
+        <v>0.6368863</v>
       </c>
       <c r="T19" t="n">
-        <v>0.06942594938307689</v>
+        <v>0.2777408171778477</v>
       </c>
       <c r="U19" t="n">
-        <v>0.296896000731846</v>
+        <v>0.03665769989991308</v>
       </c>
       <c r="V19" t="n">
-        <v>0.5826465342073299</v>
+        <v>0.2523608020528563</v>
       </c>
       <c r="W19" t="n">
-        <v>0.429117646532641</v>
+        <v>-0.1272974960108844</v>
       </c>
       <c r="X19" t="n">
-        <v>0.00616</v>
+        <v>0.12878999</v>
       </c>
       <c r="Y19" t="n">
-        <v>0.90915</v>
+        <v>0.70528</v>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>2026-08-24T23:42:07.850261+00:00</t>
+          <t>2026-08-25T23:45:03.369591+00:00</t>
         </is>
       </c>
       <c r="AD19" t="inlineStr">
@@ -5148,12 +5152,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>MDB</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>MongoDB, Inc.</t>
+          <t>Microsoft Corporation</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -5167,62 +5171,68 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>32389132288</v>
+        <v>3651215032320</v>
       </c>
       <c r="F20" t="n">
-        <v>402.6900024414062</v>
+        <v>491.7099914550781</v>
       </c>
       <c r="G20" t="n">
-        <v>2602398976</v>
+        <v>331839012864</v>
       </c>
       <c r="H20" t="n">
-        <v>0.252</v>
+        <v>0.177</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.39</v>
+        <v>17.93</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0.317</v>
       </c>
       <c r="K20" t="n">
-        <v>517605376</v>
+        <v>16545500160</v>
       </c>
       <c r="M20" t="n">
-        <v>2427152896</v>
+        <v>76842999808</v>
       </c>
       <c r="N20" t="n">
-        <v>58635000</v>
+        <v>128812998656</v>
       </c>
       <c r="O20" t="n">
-        <v>0.71970004</v>
+        <v>0.67944</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.03607</v>
+        <v>0.45111</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>27.42387</v>
       </c>
       <c r="R20" t="n">
-        <v>12.445875</v>
+        <v>11.002971</v>
       </c>
       <c r="S20" t="n">
-        <v>62.57495341006659</v>
+        <v>220.677223233607</v>
       </c>
       <c r="T20" t="n">
-        <v>0.350311852971217</v>
+        <v>0.2906356072891438</v>
       </c>
       <c r="U20" t="n">
-        <v>0.2347530016016277</v>
+        <v>0.1841348949382575</v>
       </c>
       <c r="V20" t="n">
-        <v>0.1687079327104049</v>
+        <v>0.2841122091195314</v>
       </c>
       <c r="W20" t="n">
-        <v>0.8382635210871647</v>
+        <v>-0.01686510460742252</v>
       </c>
       <c r="X20" t="n">
-        <v>0.02641</v>
+        <v>0.00090000004</v>
       </c>
       <c r="Y20" t="n">
-        <v>0.96402</v>
+        <v>0.75867</v>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>2026-08-24T23:42:09.248135+00:00</t>
+          <t>2026-08-25T23:44:56.193806+00:00</t>
         </is>
       </c>
       <c r="AD20" t="inlineStr">
@@ -5234,87 +5244,81 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>VRT</t>
+          <t>NET</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Vertiv Holdings Co</t>
+          <t>Cloudflare, Inc.</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Electrical Equipment &amp; Parts</t>
+          <t>Software - Infrastructure</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>98160435200</v>
+        <v>98840600576</v>
       </c>
       <c r="F21" t="n">
-        <v>254.9700012207031</v>
+        <v>277.5799865722656</v>
       </c>
       <c r="G21" t="n">
-        <v>11479600128</v>
+        <v>2512349952</v>
       </c>
       <c r="H21" t="n">
-        <v>0.241</v>
+        <v>0.359</v>
       </c>
       <c r="I21" t="n">
-        <v>4.43</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0.53</v>
+        <v>-0.59</v>
       </c>
       <c r="K21" t="n">
-        <v>2696537600</v>
+        <v>692851968</v>
       </c>
       <c r="M21" t="n">
-        <v>3110599936</v>
+        <v>4162798080</v>
       </c>
       <c r="N21" t="n">
-        <v>3338200064</v>
+        <v>3529349888</v>
       </c>
       <c r="O21" t="n">
-        <v>0.38039002</v>
+        <v>0.72577006</v>
       </c>
       <c r="P21" t="n">
-        <v>0.20362</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>57.555305</v>
+        <v>-0.07902000000000001</v>
       </c>
       <c r="R21" t="n">
-        <v>8.5508585</v>
+        <v>39.341892</v>
       </c>
       <c r="S21" t="n">
-        <v>36.40239809747136</v>
+        <v>142.6576024043277</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.1218831309968894</v>
+        <v>0.05885940505447462</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.2212085279452035</v>
+        <v>0.2759951969252914</v>
       </c>
       <c r="V21" t="n">
-        <v>0.04649740841847994</v>
+        <v>0.7328171692474872</v>
       </c>
       <c r="W21" t="n">
-        <v>1.026282952520625</v>
+        <v>0.4170919933268895</v>
       </c>
       <c r="X21" t="n">
-        <v>0.00269</v>
+        <v>0.00616</v>
       </c>
       <c r="Y21" t="n">
-        <v>0.8440800000000001</v>
+        <v>0.90181</v>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>2026-08-24T23:42:05.554067+00:00</t>
+          <t>2026-08-25T23:45:05.399915+00:00</t>
         </is>
       </c>
       <c r="AD21" t="inlineStr">
@@ -5326,12 +5330,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>ACMR</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Microsoft Corporation</t>
+          <t>ACM Research, Inc.</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -5341,72 +5345,69 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Software - Infrastructure</t>
+          <t>Semiconductor Equipment &amp; Materials</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>3618542714880</v>
+        <v>5555916288</v>
       </c>
       <c r="F22" t="n">
-        <v>487.3099975585938</v>
+        <v>79.76999664306641</v>
       </c>
       <c r="G22" t="n">
-        <v>331839012864</v>
+        <v>1037772032</v>
       </c>
       <c r="H22" t="n">
-        <v>0.177</v>
+        <v>0.36</v>
       </c>
       <c r="I22" t="n">
-        <v>17.93</v>
+        <v>2.12</v>
       </c>
       <c r="J22" t="n">
-        <v>0.317</v>
+        <v>1.806</v>
       </c>
       <c r="K22" t="n">
-        <v>16545500160</v>
+        <v>-186610256</v>
       </c>
       <c r="M22" t="n">
-        <v>76842999808</v>
+        <v>1439374976</v>
       </c>
       <c r="N22" t="n">
-        <v>128812998656</v>
+        <v>349319008</v>
       </c>
       <c r="O22" t="n">
-        <v>0.67944</v>
+        <v>0.43835</v>
       </c>
       <c r="P22" t="n">
-        <v>0.45111</v>
+        <v>0.16982001</v>
       </c>
       <c r="Q22" t="n">
-        <v>27.17847</v>
+        <v>37.627357</v>
       </c>
       <c r="R22" t="n">
-        <v>10.904512</v>
-      </c>
-      <c r="S22" t="n">
-        <v>218.702528173074</v>
+        <v>5.3536963</v>
       </c>
       <c r="T22" t="n">
-        <v>0.2790865460674004</v>
+        <v>-0.05396113695713289</v>
       </c>
       <c r="U22" t="n">
-        <v>0.1664174202192839</v>
+        <v>-0.07737685070838396</v>
       </c>
       <c r="V22" t="n">
-        <v>0.231741813437734</v>
+        <v>0.224969184253502</v>
       </c>
       <c r="W22" t="n">
-        <v>-0.03136756513099537</v>
+        <v>1.769791623480893</v>
       </c>
       <c r="X22" t="n">
-        <v>0.00090000004</v>
+        <v>0.12675999</v>
       </c>
       <c r="Y22" t="n">
-        <v>0.75907</v>
+        <v>0.78046995</v>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>2026-08-24T23:41:58.940174+00:00</t>
+          <t>2026-08-25T23:44:53.303395+00:00</t>
         </is>
       </c>
       <c r="AD22" t="inlineStr">
@@ -5418,87 +5419,87 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ASML</t>
+          <t>VRT</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>ASML Holding N.V.</t>
+          <t>Vertiv Holdings Co</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Semiconductor Equipment &amp; Materials</t>
+          <t>Electrical Equipment &amp; Parts</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>668383903744</v>
+        <v>98460721152</v>
       </c>
       <c r="F23" t="n">
-        <v>1740.130004882812</v>
+        <v>255.75</v>
       </c>
       <c r="G23" t="n">
-        <v>35327500288</v>
+        <v>11479600128</v>
       </c>
       <c r="H23" t="n">
-        <v>0.213</v>
+        <v>0.241</v>
       </c>
       <c r="I23" t="n">
-        <v>29.63</v>
+        <v>4.41</v>
       </c>
       <c r="J23" t="n">
-        <v>0.285</v>
+        <v>0.53</v>
       </c>
       <c r="K23" t="n">
-        <v>8437675008</v>
+        <v>2696537600</v>
       </c>
       <c r="M23" t="n">
-        <v>7581499904</v>
+        <v>3110599936</v>
       </c>
       <c r="N23" t="n">
-        <v>1984400000</v>
+        <v>3338200064</v>
       </c>
       <c r="O23" t="n">
-        <v>0.5273300400000001</v>
+        <v>0.38039002</v>
       </c>
       <c r="P23" t="n">
-        <v>0.37057</v>
+        <v>0.20362</v>
       </c>
       <c r="Q23" t="n">
-        <v>58.728657</v>
+        <v>57.9932</v>
       </c>
       <c r="R23" t="n">
-        <v>18.91965</v>
+        <v>8.577017</v>
       </c>
       <c r="S23" t="n">
-        <v>79.2142270365102</v>
+        <v>36.51375792126911</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.008371471746108972</v>
+        <v>-0.1191968146356578</v>
       </c>
       <c r="U23" t="n">
-        <v>0.06704667763369399</v>
+        <v>-0.2102645435334196</v>
       </c>
       <c r="V23" t="n">
-        <v>0.188213228050349</v>
+        <v>0.04255600645730628</v>
       </c>
       <c r="W23" t="n">
-        <v>1.320326857563086</v>
+        <v>1.047926180569005</v>
       </c>
       <c r="X23" t="n">
-        <v>0.00016000001</v>
+        <v>0.00269</v>
       </c>
       <c r="Y23" t="n">
-        <v>0.20382</v>
+        <v>0.84405</v>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>2026-08-24T23:42:02.915537+00:00</t>
+          <t>2026-08-25T23:45:02.812959+00:00</t>
         </is>
       </c>
       <c r="AD23" t="inlineStr">
@@ -5510,12 +5511,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>PANW</t>
+          <t>ASML</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Palo Alto Networks, Inc.</t>
+          <t>ASML Holding N.V.</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -5525,69 +5526,72 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Software - Infrastructure</t>
+          <t>Semiconductor Equipment &amp; Materials</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>285983506432</v>
+        <v>669931864064</v>
       </c>
       <c r="F24" t="n">
-        <v>350.8999938964844</v>
+        <v>1744.160034179688</v>
       </c>
       <c r="G24" t="n">
-        <v>10606499840</v>
+        <v>35327500288</v>
       </c>
       <c r="H24" t="n">
-        <v>0.311</v>
+        <v>0.213</v>
       </c>
       <c r="I24" t="n">
-        <v>1.15</v>
+        <v>29.76</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0.285</v>
       </c>
       <c r="K24" t="n">
-        <v>3579375104</v>
+        <v>8437675008</v>
       </c>
       <c r="M24" t="n">
-        <v>3111000064</v>
+        <v>7581499904</v>
       </c>
       <c r="N24" t="n">
-        <v>2130000000</v>
+        <v>1984400000</v>
       </c>
       <c r="O24" t="n">
-        <v>0.71963996</v>
+        <v>0.5273300400000001</v>
       </c>
       <c r="P24" t="n">
-        <v>-0.02465</v>
+        <v>0.37057</v>
       </c>
       <c r="Q24" t="n">
-        <v>305.13043</v>
+        <v>58.60753</v>
       </c>
       <c r="R24" t="n">
-        <v>26.963043</v>
+        <v>18.963467</v>
       </c>
       <c r="S24" t="n">
-        <v>79.8976072981034</v>
+        <v>79.39768519512999</v>
       </c>
       <c r="T24" t="n">
-        <v>0.08372705962544025</v>
+        <v>-0.006074923781723141</v>
       </c>
       <c r="U24" t="n">
-        <v>0.3466114512949008</v>
+        <v>0.07008803937532648</v>
       </c>
       <c r="V24" t="n">
-        <v>1.359784808997822</v>
+        <v>0.1778210552954782</v>
       </c>
       <c r="W24" t="n">
-        <v>0.887776978044025</v>
+        <v>1.327026100903341</v>
       </c>
       <c r="X24" t="n">
-        <v>0.0076</v>
+        <v>0.00016000001</v>
       </c>
       <c r="Y24" t="n">
-        <v>0.84946</v>
+        <v>0.20382999</v>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>2026-08-24T23:41:58.381156+00:00</t>
+          <t>2026-08-25T23:44:59.758374+00:00</t>
         </is>
       </c>
       <c r="AD24" t="inlineStr">
@@ -5599,12 +5603,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>SMCI</t>
+          <t>PANW</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Super Micro Computer, Inc.</t>
+          <t>Palo Alto Networks, Inc.</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -5614,69 +5618,69 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Computer Hardware</t>
+          <t>Software - Infrastructure</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>22750523392</v>
+        <v>277018509312</v>
       </c>
       <c r="F25" t="n">
-        <v>35.16999816894531</v>
+        <v>339.8999938964844</v>
       </c>
       <c r="G25" t="n">
-        <v>39063072768</v>
+        <v>10606499840</v>
       </c>
       <c r="H25" t="n">
-        <v>0.9320000000000001</v>
+        <v>0.311</v>
       </c>
       <c r="I25" t="n">
-        <v>3.26</v>
-      </c>
-      <c r="J25" t="n">
-        <v>4.094</v>
+        <v>1.16</v>
       </c>
       <c r="K25" t="n">
-        <v>-8231267840</v>
+        <v>3579375104</v>
       </c>
       <c r="M25" t="n">
-        <v>7521474048</v>
+        <v>3111000064</v>
       </c>
       <c r="N25" t="n">
-        <v>9311492096</v>
+        <v>2130000000</v>
       </c>
       <c r="O25" t="n">
-        <v>0.108219996</v>
+        <v>0.71963996</v>
       </c>
       <c r="P25" t="n">
-        <v>0.13382</v>
+        <v>-0.02465</v>
       </c>
       <c r="Q25" t="n">
-        <v>10.788343</v>
+        <v>293.01724</v>
       </c>
       <c r="R25" t="n">
-        <v>0.58240485</v>
+        <v>26.117805</v>
+      </c>
+      <c r="S25" t="n">
+        <v>77.39298097101589</v>
       </c>
       <c r="T25" t="n">
-        <v>0.1684384625654953</v>
+        <v>0.04975442393654794</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.01152343004523171</v>
+        <v>0.3238558671722858</v>
       </c>
       <c r="V25" t="n">
-        <v>0.08482418739413089</v>
+        <v>1.358124013707292</v>
       </c>
       <c r="W25" t="n">
-        <v>-0.1984959591420548</v>
+        <v>0.8417772325972708</v>
       </c>
       <c r="X25" t="n">
-        <v>0.12878999</v>
+        <v>0.0076</v>
       </c>
       <c r="Y25" t="n">
-        <v>0.70522004</v>
+        <v>0.84933</v>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>2026-08-24T23:42:06.041992+00:00</t>
+          <t>2026-08-25T23:44:55.563891+00:00</t>
         </is>
       </c>
       <c r="AD25" t="inlineStr">
@@ -5707,10 +5711,10 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>255016697856</v>
+        <v>257985740800</v>
       </c>
       <c r="F26" t="n">
-        <v>238.7799987792969</v>
+        <v>241.5599975585938</v>
       </c>
       <c r="G26" t="n">
         <v>5155999744</v>
@@ -5719,7 +5723,7 @@
         <v>0.224</v>
       </c>
       <c r="I26" t="n">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="J26" t="n">
         <v>1.083</v>
@@ -5740,35 +5744,35 @@
         <v>0.07603</v>
       </c>
       <c r="Q26" t="n">
-        <v>246.16495</v>
+        <v>246.48979</v>
       </c>
       <c r="R26" t="n">
-        <v>49.460186</v>
+        <v>50.036026</v>
       </c>
       <c r="S26" t="n">
-        <v>191.0953195736607</v>
+        <v>193.3201551039677</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.08165074492887803</v>
+        <v>-0.07095885355976195</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.220971612111847</v>
+        <v>-0.2479920408423657</v>
       </c>
       <c r="V26" t="n">
-        <v>0.9014173857118781</v>
+        <v>0.9515269020910384</v>
       </c>
       <c r="W26" t="n">
-        <v>0.7312935176144866</v>
+        <v>0.7532297844300104</v>
       </c>
       <c r="X26" t="n">
         <v>0.0007</v>
       </c>
       <c r="Y26" t="n">
-        <v>0.96261</v>
+        <v>0.96186996</v>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>2026-08-24T23:42:03.504552+00:00</t>
+          <t>2026-08-25T23:45:00.256605+00:00</t>
         </is>
       </c>
       <c r="AD26" t="inlineStr">
@@ -5799,10 +5803,10 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1424106979328</v>
+        <v>1452205801472</v>
       </c>
       <c r="F27" t="n">
-        <v>559.02001953125</v>
+        <v>570.0499877929688</v>
       </c>
       <c r="G27" t="n">
         <v>228246994944</v>
@@ -5811,7 +5815,7 @@
         <v>0.28</v>
       </c>
       <c r="I27" t="n">
-        <v>26.56</v>
+        <v>26.55</v>
       </c>
       <c r="J27" t="n">
         <v>-0.134</v>
@@ -5832,35 +5836,35 @@
         <v>0.34827</v>
       </c>
       <c r="Q27" t="n">
-        <v>21.047441</v>
+        <v>21.47081</v>
       </c>
       <c r="R27" t="n">
-        <v>6.239324</v>
+        <v>6.362431</v>
       </c>
       <c r="S27" t="n">
-        <v>66.07273595571971</v>
+        <v>67.37640631415255</v>
       </c>
       <c r="T27" t="n">
-        <v>-0.0607704812946972</v>
+        <v>-0.04223863731802591</v>
       </c>
       <c r="U27" t="n">
-        <v>-0.08311521534867206</v>
+        <v>-0.06820016862728395</v>
       </c>
       <c r="V27" t="n">
-        <v>-0.1458725259845354</v>
+        <v>-0.1038575283287057</v>
       </c>
       <c r="W27" t="n">
-        <v>-0.2569426776396064</v>
+        <v>-0.2407827733099394</v>
       </c>
       <c r="X27" t="n">
         <v>0.00148</v>
       </c>
       <c r="Y27" t="n">
-        <v>0.79103994</v>
+        <v>0.79033</v>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>2026-08-24T23:42:00.891769+00:00</t>
+          <t>2026-08-25T23:44:58.005827+00:00</t>
         </is>
       </c>
       <c r="AD27" t="inlineStr">
@@ -5891,10 +5895,10 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>194161672192</v>
+        <v>188764913664</v>
       </c>
       <c r="F28" t="n">
-        <v>190.6799926757812</v>
+        <v>185.3800048828125</v>
       </c>
       <c r="G28" t="n">
         <v>5094199808</v>
@@ -5921,32 +5925,32 @@
         <v>-0.022079999</v>
       </c>
       <c r="R28" t="n">
-        <v>38.11426</v>
+        <v>37.05487</v>
       </c>
       <c r="S28" t="n">
-        <v>100.7917328998725</v>
+        <v>97.99020859315256</v>
       </c>
       <c r="T28" t="n">
-        <v>0.0403753488966101</v>
+        <v>0.01145791203351343</v>
       </c>
       <c r="U28" t="n">
-        <v>0.1496095400523765</v>
+        <v>0.1041918442560559</v>
       </c>
       <c r="V28" t="n">
-        <v>0.9627379277496741</v>
+        <v>1.116633025869426</v>
       </c>
       <c r="W28" t="n">
-        <v>0.8136249978411652</v>
+        <v>0.7704558969139306</v>
       </c>
       <c r="X28" t="n">
-        <v>0.014680001</v>
+        <v>0.01467</v>
       </c>
       <c r="Y28" t="n">
-        <v>0.76635003</v>
+        <v>0.76632005</v>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>2026-08-24T23:41:57.743307+00:00</t>
+          <t>2026-08-25T23:44:54.986103+00:00</t>
         </is>
       </c>
       <c r="AD28" t="inlineStr">
@@ -5977,10 +5981,10 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>205797965824</v>
+        <v>216030625792</v>
       </c>
       <c r="F29" t="n">
-        <v>229.2899932861328</v>
+        <v>240.3800048828125</v>
       </c>
       <c r="G29" t="n">
         <v>8717100032</v>
@@ -5989,7 +5993,7 @@
         <v>0.276</v>
       </c>
       <c r="I29" t="n">
-        <v>2.92</v>
+        <v>2.91</v>
       </c>
       <c r="J29" t="n">
         <v>-0.804</v>
@@ -6010,35 +6014,35 @@
         <v>0.14479999</v>
       </c>
       <c r="Q29" t="n">
-        <v>78.52397000000001</v>
+        <v>82.60481</v>
       </c>
       <c r="R29" t="n">
-        <v>23.608536</v>
+        <v>24.782396</v>
       </c>
       <c r="S29" t="n">
-        <v>90.6718760715072</v>
+        <v>95.18025142296156</v>
       </c>
       <c r="T29" t="n">
-        <v>0.1805076369757792</v>
+        <v>0.2376049537683742</v>
       </c>
       <c r="U29" t="n">
-        <v>0.1681686413739329</v>
+        <v>0.1545150694814081</v>
       </c>
       <c r="V29" t="n">
-        <v>1.887032565299141</v>
+        <v>2.092424028873406</v>
       </c>
       <c r="W29" t="n">
-        <v>2.147650680557031</v>
+        <v>2.302154522205557</v>
       </c>
       <c r="X29" t="n">
         <v>0.00494</v>
       </c>
       <c r="Y29" t="n">
-        <v>0.82137</v>
+        <v>0.82125</v>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>2026-08-24T23:42:04.032508+00:00</t>
+          <t>2026-08-25T23:45:01.001094+00:00</t>
         </is>
       </c>
       <c r="AD29" t="inlineStr">
@@ -6069,10 +6073,10 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>132386037760</v>
+        <v>131300474880</v>
       </c>
       <c r="F30" t="n">
-        <v>128.0500030517578</v>
+        <v>127</v>
       </c>
       <c r="G30" t="n">
         <v>14732000256</v>
@@ -6081,7 +6085,7 @@
         <v>0.24</v>
       </c>
       <c r="I30" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="J30" t="n">
         <v>-0.219</v>
@@ -6102,35 +6106,35 @@
         <v>0.04063</v>
       </c>
       <c r="Q30" t="n">
-        <v>79.534164</v>
+        <v>79.375</v>
       </c>
       <c r="R30" t="n">
-        <v>8.986291</v>
+        <v>8.912603000000001</v>
       </c>
       <c r="S30" t="n">
-        <v>25.70914691142508</v>
+        <v>25.49833241742153</v>
       </c>
       <c r="T30" t="n">
-        <v>0.2963150904451679</v>
+        <v>0.2856853772974302</v>
       </c>
       <c r="U30" t="n">
-        <v>0.2537942474826844</v>
+        <v>0.2710168367424073</v>
       </c>
       <c r="V30" t="n">
-        <v>0.2280618315362024</v>
+        <v>0.2599205967760663</v>
       </c>
       <c r="W30" t="n">
-        <v>-0.2779814003670369</v>
+        <v>-0.2783599152039051</v>
       </c>
       <c r="X30" t="n">
         <v>0.00176</v>
       </c>
       <c r="Y30" t="n">
-        <v>0.85102</v>
+        <v>0.85085</v>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>2026-08-24T23:42:08.489276+00:00</t>
+          <t>2026-08-25T23:45:05.999518+00:00</t>
         </is>
       </c>
       <c r="AD30" t="inlineStr">
@@ -6161,10 +6165,10 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>410323091456</v>
+        <v>416976961536</v>
       </c>
       <c r="F31" t="n">
-        <v>142.4499969482422</v>
+        <v>144.7599945068359</v>
       </c>
       <c r="G31" t="n">
         <v>67356999680</v>
@@ -6194,32 +6198,32 @@
         <v>0.36202</v>
       </c>
       <c r="Q31" t="n">
-        <v>24.433962</v>
+        <v>24.830189</v>
       </c>
       <c r="R31" t="n">
-        <v>6.0917664</v>
+        <v>6.1905513</v>
       </c>
       <c r="T31" t="n">
-        <v>0.2388033706810304</v>
+        <v>0.2588920531882728</v>
       </c>
       <c r="U31" t="n">
-        <v>-0.2558018792758237</v>
+        <v>-0.2475726919466725</v>
       </c>
       <c r="V31" t="n">
-        <v>-0.03130182031897633</v>
+        <v>0.03156861753690055</v>
       </c>
       <c r="W31" t="n">
-        <v>-0.3904742535260926</v>
+        <v>-0.3780641367460406</v>
       </c>
       <c r="X31" t="n">
         <v>0.40498</v>
       </c>
       <c r="Y31" t="n">
-        <v>0.45828</v>
+        <v>0.45811</v>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>2026-08-24T23:42:01.600223+00:00</t>
+          <t>2026-08-25T23:44:58.547404+00:00</t>
         </is>
       </c>
       <c r="AD31" t="inlineStr">
@@ -6247,7 +6251,7 @@
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
@@ -6304,27 +6308,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>MU</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>84.2</v>
+        <v>100</v>
       </c>
       <c r="C2" t="n">
-        <v>88.2</v>
+        <v>100</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>MODERATE</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>price_to_sales, price_to_fcf</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -6338,11 +6337,11 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>MU</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="C3" t="n">
         <v>100</v>
@@ -6353,7 +6352,7 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -6483,7 +6482,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>NVDA</t>
+          <t>DELL</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -6512,7 +6511,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>DELL</t>
+          <t>NVDA</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -6575,7 +6574,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -6604,7 +6603,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>GOOGL</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -6720,7 +6719,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>SNOW</t>
+          <t>MDB</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -6783,14 +6782,14 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ACMR</t>
+          <t>SNOW</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>94.09999999999999</v>
+        <v>88.2</v>
       </c>
       <c r="C18" t="n">
-        <v>94.09999999999999</v>
+        <v>88.2</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -6799,7 +6798,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>price_to_fcf</t>
+          <t>eps_growth, pe_ratio</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -6817,14 +6816,14 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>NET</t>
+          <t>SMCI</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>88.2</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="C19" t="n">
-        <v>88.2</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -6833,7 +6832,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>eps_growth, pe_ratio</t>
+          <t>price_to_fcf</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -6851,23 +6850,18 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>MDB</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>88.2</v>
+        <v>100</v>
       </c>
       <c r="C20" t="n">
-        <v>88.2</v>
+        <v>100</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
           <t>HIGH</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>eps_growth, pe_ratio</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -6885,18 +6879,23 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>VRT</t>
+          <t>NET</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>100</v>
+        <v>88.2</v>
       </c>
       <c r="C21" t="n">
-        <v>100</v>
+        <v>88.2</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
           <t>HIGH</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>eps_growth, pe_ratio</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -6914,18 +6913,23 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>ACMR</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>100</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="C22" t="n">
-        <v>100</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
           <t>HIGH</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>price_to_fcf</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -6943,7 +6947,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ASML</t>
+          <t>VRT</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -6972,23 +6976,18 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>PANW</t>
+          <t>ASML</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>94.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="C24" t="n">
-        <v>94.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
           <t>HIGH</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>eps_growth</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -7006,7 +7005,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>SMCI</t>
+          <t>PANW</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -7022,7 +7021,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>price_to_fcf</t>
+          <t>eps_growth</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -7290,11 +7289,11 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>MU</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>57.16</v>
+        <v>55.59</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -7307,7 +7306,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>84.2</v>
+        <v>100</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>

--- a/reports/investment_dashboard.xlsx
+++ b/reports/investment_dashboard.xlsx
@@ -525,16 +525,16 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>MU</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Taiwan Semiconductor Manufacturing Company Limited</t>
+          <t>Micron Technology, Inc.</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>55.59</v>
+        <v>56.33</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>417.4100036621094</v>
+        <v>940.4349975585938</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -550,19 +550,24 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>100</v>
+        <v>84.2</v>
       </c>
       <c r="I2" t="n">
-        <v>100</v>
+        <v>88.2</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Revenue Growth; Earnings Fcf; Balance Sheet; Valuation</t>
+          <t>Revenue Growth; Earnings Fcf; Balance Sheet</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
           <t>Industry Growth; Competitive Advantage; Catalysts; Inflation Resilience</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>High market sensitivity / beta</t>
         </is>
       </c>
     </row>
@@ -572,16 +577,16 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>MU</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Micron Technology, Inc.</t>
+          <t>Taiwan Semiconductor Manufacturing Company Limited</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>54.08</v>
+        <v>55.33</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -589,7 +594,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>932.969970703125</v>
+        <v>417.7999877929688</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -597,24 +602,19 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="I3" t="n">
         <v>100</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Revenue Growth; Earnings Fcf; Balance Sheet</t>
+          <t>Revenue Growth; Earnings Fcf; Balance Sheet; Valuation</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
           <t>Industry Growth; Competitive Advantage; Catalysts; Inflation Resilience</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>High market sensitivity / beta</t>
         </is>
       </c>
     </row>
@@ -624,16 +624,16 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>CRDO</t>
+          <t>ANET</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Credo Technology Group Holding Ltd</t>
+          <t>Arista Networks, Inc.</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>52.7</v>
+        <v>53.03</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -641,11 +641,11 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>226.5099945068359</v>
+        <v>202.4400024414062</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -656,7 +656,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Revenue Growth; Earnings Fcf; Balance Sheet</t>
+          <t>Revenue Growth; Earnings Fcf; Balance Sheet; Momentum</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -666,7 +666,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Excessive price-to-sales valuation; High market sensitivity / beta</t>
+          <t>Excessive price-to-sales valuation</t>
         </is>
       </c>
     </row>
@@ -676,16 +676,16 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ANET</t>
+          <t>CRDO</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Arista Networks, Inc.</t>
+          <t>Credo Technology Group Holding Ltd</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>52.21</v>
+        <v>52.81</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -693,11 +693,11 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>190.9400024414062</v>
+        <v>225.9149932861328</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -718,7 +718,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Excessive price-to-sales valuation</t>
+          <t>Excessive price-to-sales valuation; High market sensitivity / beta</t>
         </is>
       </c>
     </row>
@@ -737,7 +737,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>51.59</v>
+        <v>52.07</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -745,7 +745,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>172.7299957275391</v>
+        <v>178.3600006103516</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -760,7 +760,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Revenue Growth; Earnings Fcf; Balance Sheet</t>
+          <t>Revenue Growth; Earnings Fcf; Balance Sheet; Momentum</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -789,7 +789,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>50.75</v>
+        <v>50.84</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>366.4299926757812</v>
+        <v>362.7699890136719</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -836,7 +836,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>50.52</v>
+        <v>50.71</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -844,7 +844,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>451.5</v>
+        <v>467.5199890136719</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -883,7 +883,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>49.84</v>
+        <v>49.87</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>213.0500030517578</v>
+        <v>210.5899963378906</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>48.16</v>
+        <v>48.11</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -943,7 +943,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>16.65999984741211</v>
+        <v>16.81500053405762</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -982,7 +982,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>47.19</v>
+        <v>47.53</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -990,7 +990,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>479.1799926757812</v>
+        <v>482.0350036621094</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>47.15</v>
+        <v>46.91</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -1042,7 +1042,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>346.9599914550781</v>
+        <v>341.7049865722656</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>45.22</v>
+        <v>45.37</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -1089,7 +1089,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>480.0400085449219</v>
+        <v>479.5299987792969</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -1128,7 +1128,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>44.55</v>
+        <v>44.75</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>222.9900054931641</v>
+        <v>229.8000030517578</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -1180,7 +1180,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>43.88</v>
+        <v>43.76</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>356.739990234375</v>
+        <v>353.760009765625</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -1232,7 +1232,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>43.51</v>
+        <v>43.44</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>404.9200134277344</v>
+        <v>406.1000061035156</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1270,16 +1270,16 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>AMZN</t>
+          <t>SNOW</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Amazon.com, Inc.</t>
+          <t>Snowflake Inc.</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>43.23</v>
+        <v>43.02</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -1287,7 +1287,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>261.0599975585938</v>
+        <v>316.3800048828125</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1295,19 +1295,24 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>100</v>
+        <v>88.2</v>
       </c>
       <c r="I17" t="n">
-        <v>100</v>
+        <v>88.2</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Earnings Fcf</t>
+          <t>Revenue Growth; Momentum</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Industry Growth; Competitive Advantage; Catalysts; Inflation Resilience</t>
+          <t>Industry Growth; Valuation; Competitive Advantage; Catalysts; Inflation Resilience</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>Excessive price-to-sales valuation</t>
         </is>
       </c>
     </row>
@@ -1317,16 +1322,16 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>SNOW</t>
+          <t>AMZN</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Snowflake Inc.</t>
+          <t>Amazon.com, Inc.</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>43.11</v>
+        <v>42.95</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -1334,7 +1339,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>317.0199890136719</v>
+        <v>259.9446105957031</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1342,24 +1347,19 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>88.2</v>
+        <v>100</v>
       </c>
       <c r="I18" t="n">
-        <v>88.2</v>
+        <v>100</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Revenue Growth; Momentum</t>
+          <t>Earnings Fcf</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Industry Growth; Valuation; Competitive Advantage; Catalysts; Inflation Resilience</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>Excessive price-to-sales valuation</t>
+          <t>Industry Growth; Competitive Advantage; Catalysts; Inflation Resilience</t>
         </is>
       </c>
     </row>
@@ -1369,16 +1369,16 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>SMCI</t>
+          <t>NET</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Super Micro Computer, Inc.</t>
+          <t>Cloudflare, Inc.</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>42.57</v>
+        <v>42.79</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -1386,7 +1386,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>38.45999908447266</v>
+        <v>285.1300048828125</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1394,24 +1394,24 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>94.09999999999999</v>
+        <v>88.2</v>
       </c>
       <c r="I19" t="n">
-        <v>94.09999999999999</v>
+        <v>88.2</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Revenue Growth; Valuation</t>
+          <t>Revenue Growth; Momentum</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Industry Growth; Balance Sheet; Competitive Advantage; Catalysts; Inflation Resilience</t>
+          <t>Industry Growth; Valuation; Competitive Advantage; Catalysts; Inflation Resilience</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>Negative free cash flow / unprofitable growth</t>
+          <t>Excessive price-to-sales valuation</t>
         </is>
       </c>
     </row>
@@ -1430,7 +1430,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>42.54</v>
+        <v>42.59</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>491.7099914550781</v>
+        <v>496.1099853515625</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1468,16 +1468,16 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>NET</t>
+          <t>ASML</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Cloudflare, Inc.</t>
+          <t>ASML Holding N.V.</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>42.34</v>
+        <v>42.39</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>277.5799865722656</v>
+        <v>1743.030029296875</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1493,24 +1493,19 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>88.2</v>
+        <v>100</v>
       </c>
       <c r="I21" t="n">
-        <v>88.2</v>
+        <v>100</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Revenue Growth</t>
+          <t>Earnings Fcf; Balance Sheet</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
           <t>Industry Growth; Valuation; Competitive Advantage; Catalysts; Inflation Resilience</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>Excessive price-to-sales valuation</t>
         </is>
       </c>
     </row>
@@ -1520,16 +1515,16 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>ACMR</t>
+          <t>VRT</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>ACM Research, Inc.</t>
+          <t>Vertiv Holdings Co</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>42.29</v>
+        <v>42.28</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -1537,7 +1532,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>79.76999664306641</v>
+        <v>264.7049865722656</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1545,24 +1540,24 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>94.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="I22" t="n">
-        <v>94.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Revenue Growth</t>
+          <t>Earnings Fcf</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Industry Growth; Competitive Advantage; Catalysts; Inflation Resilience</t>
+          <t>Industry Growth; Valuation; Competitive Advantage; Momentum; Catalysts; Inflation Resilience</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>Negative free cash flow / unprofitable growth</t>
+          <t>High market sensitivity / beta</t>
         </is>
       </c>
     </row>
@@ -1572,16 +1567,16 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>VRT</t>
+          <t>ACMR</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Vertiv Holdings Co</t>
+          <t>ACM Research, Inc.</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>42.27</v>
+        <v>42.1</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -1589,7 +1584,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>255.75</v>
+        <v>78.97100067138672</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1597,24 +1592,24 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>100</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="I23" t="n">
-        <v>100</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Earnings Fcf</t>
+          <t>Revenue Growth</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Industry Growth; Valuation; Competitive Advantage; Momentum; Catalysts; Inflation Resilience</t>
+          <t>Industry Growth; Competitive Advantage; Catalysts; Inflation Resilience</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>High market sensitivity / beta</t>
+          <t>Negative free cash flow / unprofitable growth</t>
         </is>
       </c>
     </row>
@@ -1624,16 +1619,16 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>ASML</t>
+          <t>SMCI</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>ASML Holding N.V.</t>
+          <t>Super Micro Computer, Inc.</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>42.05</v>
+        <v>41.92</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -1641,7 +1636,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1744.160034179688</v>
+        <v>37.42990112304688</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1649,19 +1644,24 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>100</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="I24" t="n">
-        <v>100</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Earnings Fcf; Balance Sheet</t>
+          <t>Revenue Growth; Valuation</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>Industry Growth; Valuation; Competitive Advantage; Catalysts; Inflation Resilience</t>
+          <t>Industry Growth; Balance Sheet; Competitive Advantage; Catalysts; Inflation Resilience</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>Negative free cash flow / unprofitable growth</t>
         </is>
       </c>
     </row>
@@ -1680,7 +1680,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>41.24</v>
+        <v>41.54</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>339.8999938964844</v>
+        <v>340.3299865722656</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1732,7 +1732,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>40.28</v>
+        <v>40.35</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -1740,7 +1740,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>241.5599975585938</v>
+        <v>252.0249938964844</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1784,7 +1784,7 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>39.81</v>
+        <v>39.76</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -1792,7 +1792,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>570.0499877929688</v>
+        <v>577.719970703125</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1831,7 +1831,7 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>39.04</v>
+        <v>39.58</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -1839,7 +1839,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>185.3800048828125</v>
+        <v>190.4199981689453</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1883,7 +1883,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>38.99</v>
+        <v>39.54</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -1891,7 +1891,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>240.3800048828125</v>
+        <v>243.7200012207031</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>36.72</v>
+        <v>36.01</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -1943,7 +1943,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>127</v>
+        <v>125.8249969482422</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1977,7 +1977,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>31.77</v>
+        <v>31.52</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -1985,7 +1985,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>144.7599945068359</v>
+        <v>148.9600067138672</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -2115,7 +2115,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>MU</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -2128,19 +2128,19 @@
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>8.84</v>
+        <v>9.02</v>
       </c>
       <c r="F2" t="n">
-        <v>8.68</v>
+        <v>7.18</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>5.38</v>
+        <v>6.63</v>
       </c>
       <c r="I2" t="n">
-        <v>2.69</v>
+        <v>3.5</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -2149,13 +2149,13 @@
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>55.59</v>
+        <v>56.33</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>MU</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -2168,19 +2168,19 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>9.02</v>
+        <v>8.84</v>
       </c>
       <c r="F3" t="n">
-        <v>4.95</v>
+        <v>8.68</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>6.61</v>
+        <v>5.12</v>
       </c>
       <c r="I3" t="n">
-        <v>3.5</v>
+        <v>2.69</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -2189,13 +2189,13 @@
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>54.08</v>
+        <v>55.33</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CRDO</t>
+          <t>ANET</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -2208,19 +2208,19 @@
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>9.91</v>
+        <v>10</v>
       </c>
       <c r="F4" t="n">
-        <v>2.48</v>
+        <v>0.78</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>6.75</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>3.56</v>
+        <v>3.63</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -2229,13 +2229,13 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>52.7</v>
+        <v>53.03</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ANET</t>
+          <t>CRDO</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -2248,19 +2248,19 @@
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>10</v>
+        <v>9.91</v>
       </c>
       <c r="F5" t="n">
-        <v>0.83</v>
+        <v>2.49</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>7.75</v>
+        <v>6.85</v>
       </c>
       <c r="I5" t="n">
-        <v>3.63</v>
+        <v>3.56</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -2269,7 +2269,7 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>52.21</v>
+        <v>52.81</v>
       </c>
     </row>
     <row r="6">
@@ -2291,13 +2291,13 @@
         <v>9.890000000000001</v>
       </c>
       <c r="F6" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.67</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>7.66</v>
+        <v>8.16</v>
       </c>
       <c r="I6" t="n">
         <v>3.35</v>
@@ -2309,7 +2309,7 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>51.59</v>
+        <v>52.07</v>
       </c>
     </row>
     <row r="7">
@@ -2331,13 +2331,13 @@
         <v>8.9</v>
       </c>
       <c r="F7" t="n">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>5.18</v>
+        <v>5.23</v>
       </c>
       <c r="I7" t="n">
         <v>3.75</v>
@@ -2349,7 +2349,7 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>50.75</v>
+        <v>50.84</v>
       </c>
     </row>
     <row r="8">
@@ -2371,13 +2371,13 @@
         <v>6.33</v>
       </c>
       <c r="F8" t="n">
-        <v>5.84</v>
+        <v>5.75</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>8.33</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="I8" t="n">
         <v>3.54</v>
@@ -2389,7 +2389,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>50.52</v>
+        <v>50.71</v>
       </c>
     </row>
     <row r="9">
@@ -2411,13 +2411,13 @@
         <v>9.029999999999999</v>
       </c>
       <c r="F9" t="n">
-        <v>3.18</v>
+        <v>3.23</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>4.19</v>
+        <v>4.17</v>
       </c>
       <c r="I9" t="n">
         <v>3.44</v>
@@ -2429,7 +2429,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>49.84</v>
+        <v>49.87</v>
       </c>
     </row>
     <row r="10">
@@ -2451,7 +2451,7 @@
         <v>9.699999999999999</v>
       </c>
       <c r="F10" t="n">
-        <v>7.03</v>
+        <v>6.98</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -2469,7 +2469,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>48.16</v>
+        <v>48.11</v>
       </c>
     </row>
     <row r="11">
@@ -2491,13 +2491,13 @@
         <v>8.77</v>
       </c>
       <c r="F11" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>5.77</v>
+        <v>6.12</v>
       </c>
       <c r="I11" t="n">
         <v>3.45</v>
@@ -2509,7 +2509,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>47.19</v>
+        <v>47.53</v>
       </c>
     </row>
     <row r="12">
@@ -2531,13 +2531,13 @@
         <v>8.34</v>
       </c>
       <c r="F12" t="n">
-        <v>4.36</v>
+        <v>4.43</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>4.97</v>
+        <v>4.66</v>
       </c>
       <c r="I12" t="n">
         <v>3.53</v>
@@ -2549,7 +2549,7 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>47.15</v>
+        <v>46.91</v>
       </c>
     </row>
     <row r="13">
@@ -2571,13 +2571,13 @@
         <v>7.78</v>
       </c>
       <c r="F13" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>5.64</v>
+        <v>5.78</v>
       </c>
       <c r="I13" t="n">
         <v>3.58</v>
@@ -2589,7 +2589,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>45.22</v>
+        <v>45.37</v>
       </c>
     </row>
     <row r="14">
@@ -2611,13 +2611,13 @@
         <v>8.98</v>
       </c>
       <c r="F14" t="n">
-        <v>0.88</v>
+        <v>0.86</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>5.91</v>
+        <v>6.13</v>
       </c>
       <c r="I14" t="n">
         <v>3.67</v>
@@ -2629,7 +2629,7 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>44.55</v>
+        <v>44.75</v>
       </c>
     </row>
     <row r="15">
@@ -2651,13 +2651,13 @@
         <v>6.16</v>
       </c>
       <c r="F15" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>3.13</v>
+        <v>3</v>
       </c>
       <c r="I15" t="n">
         <v>3.53</v>
@@ -2669,7 +2669,7 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>43.88</v>
+        <v>43.76</v>
       </c>
     </row>
     <row r="16">
@@ -2691,13 +2691,13 @@
         <v>9.880000000000001</v>
       </c>
       <c r="F16" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>9.1</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="I16" t="n">
         <v>3.73</v>
@@ -2709,38 +2709,38 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>43.51</v>
+        <v>43.44</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>AMZN</t>
+          <t>SNOW</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>9.220000000000001</v>
+        <v>14.44</v>
       </c>
       <c r="C17" t="n">
-        <v>12.28</v>
+        <v>7.5</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>6.64</v>
+        <v>7.58</v>
       </c>
       <c r="F17" t="n">
-        <v>6.5</v>
+        <v>1.03</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>5.12</v>
+        <v>8.91</v>
       </c>
       <c r="I17" t="n">
-        <v>3.47</v>
+        <v>3.56</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2749,38 +2749,38 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>43.23</v>
+        <v>43.02</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>SNOW</t>
+          <t>AMZN</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>14.44</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="C18" t="n">
-        <v>7.5</v>
+        <v>12.28</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>7.58</v>
+        <v>6.64</v>
       </c>
       <c r="F18" t="n">
-        <v>1.02</v>
+        <v>6.51</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>9.01</v>
+        <v>4.83</v>
       </c>
       <c r="I18" t="n">
-        <v>3.56</v>
+        <v>3.47</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2789,38 +2789,38 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>43.11</v>
+        <v>42.95</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>SMCI</t>
+          <t>NET</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>15</v>
       </c>
       <c r="C19" t="n">
-        <v>7.23</v>
+        <v>7.5</v>
       </c>
       <c r="D19" t="n">
         <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>2.23</v>
+        <v>7.71</v>
       </c>
       <c r="F19" t="n">
-        <v>9.85</v>
+        <v>0.59</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>4.72</v>
+        <v>8.35</v>
       </c>
       <c r="I19" t="n">
-        <v>3.54</v>
+        <v>3.64</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2829,7 +2829,7 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>42.57</v>
+        <v>42.79</v>
       </c>
     </row>
     <row r="20">
@@ -2851,13 +2851,13 @@
         <v>6.87</v>
       </c>
       <c r="F20" t="n">
-        <v>2.98</v>
+        <v>2.95</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>6.1</v>
+        <v>6.18</v>
       </c>
       <c r="I20" t="n">
         <v>3.45</v>
@@ -2869,38 +2869,38 @@
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>42.54</v>
+        <v>42.59</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>NET</t>
+          <t>ASML</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>15</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="C21" t="n">
-        <v>7.5</v>
+        <v>14.28</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>7.71</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="F21" t="n">
-        <v>0.61</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>7.89</v>
+        <v>5.97</v>
       </c>
       <c r="I21" t="n">
-        <v>3.63</v>
+        <v>2.76</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2909,38 +2909,38 @@
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>42.34</v>
+        <v>42.39</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ACMR</t>
+          <t>VRT</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>15</v>
+        <v>10.91</v>
       </c>
       <c r="C22" t="n">
-        <v>7.83</v>
+        <v>13.39</v>
       </c>
       <c r="D22" t="n">
         <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>4.02</v>
+        <v>7.41</v>
       </c>
       <c r="F22" t="n">
-        <v>6.84</v>
+        <v>3.3</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>4.97</v>
+        <v>3.71</v>
       </c>
       <c r="I22" t="n">
-        <v>3.63</v>
+        <v>3.56</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2949,38 +2949,38 @@
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>42.29</v>
+        <v>42.28</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>VRT</t>
+          <t>ACMR</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>10.91</v>
+        <v>15</v>
       </c>
       <c r="C23" t="n">
-        <v>13.39</v>
+        <v>7.83</v>
       </c>
       <c r="D23" t="n">
         <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>7.41</v>
+        <v>4.02</v>
       </c>
       <c r="F23" t="n">
-        <v>3.48</v>
+        <v>6.88</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>3.52</v>
+        <v>4.74</v>
       </c>
       <c r="I23" t="n">
-        <v>3.56</v>
+        <v>3.63</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2989,38 +2989,38 @@
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>42.27</v>
+        <v>42.1</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ASML</t>
+          <t>SMCI</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>9.859999999999999</v>
+        <v>15</v>
       </c>
       <c r="C24" t="n">
-        <v>14.28</v>
+        <v>7.23</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>8.960000000000001</v>
+        <v>2.23</v>
       </c>
       <c r="F24" t="n">
-        <v>0.5600000000000001</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>5.64</v>
+        <v>4.04</v>
       </c>
       <c r="I24" t="n">
-        <v>2.75</v>
+        <v>3.54</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -3029,7 +3029,7 @@
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>42.05</v>
+        <v>41.92</v>
       </c>
     </row>
     <row r="25">
@@ -3051,13 +3051,13 @@
         <v>7.97</v>
       </c>
       <c r="F25" t="n">
-        <v>0.6</v>
+        <v>0.59</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>8.06</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="I25" t="n">
         <v>3.57</v>
@@ -3069,7 +3069,7 @@
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>41.24</v>
+        <v>41.54</v>
       </c>
     </row>
     <row r="26">
@@ -3091,13 +3091,13 @@
         <v>9.449999999999999</v>
       </c>
       <c r="F26" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>5.36</v>
+        <v>5.44</v>
       </c>
       <c r="I26" t="n">
         <v>3.7</v>
@@ -3109,7 +3109,7 @@
         <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>40.28</v>
+        <v>40.35</v>
       </c>
     </row>
     <row r="27">
@@ -3131,13 +3131,13 @@
         <v>7.23</v>
       </c>
       <c r="F27" t="n">
-        <v>5.64</v>
+        <v>5.58</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="I27" t="n">
         <v>3.49</v>
@@ -3149,7 +3149,7 @@
         <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>39.81</v>
+        <v>39.76</v>
       </c>
     </row>
     <row r="28">
@@ -3171,13 +3171,13 @@
         <v>9.24</v>
       </c>
       <c r="F28" t="n">
-        <v>0.46</v>
+        <v>0.45</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>6.89</v>
+        <v>7.44</v>
       </c>
       <c r="I28" t="n">
         <v>3.48</v>
@@ -3189,7 +3189,7 @@
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>39.04</v>
+        <v>39.58</v>
       </c>
     </row>
     <row r="29">
@@ -3211,13 +3211,13 @@
         <v>7.11</v>
       </c>
       <c r="F29" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.55</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>8.15</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="I29" t="n">
         <v>3.53</v>
@@ -3229,7 +3229,7 @@
         <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>38.99</v>
+        <v>39.54</v>
       </c>
     </row>
     <row r="30">
@@ -3251,13 +3251,13 @@
         <v>6.78</v>
       </c>
       <c r="F30" t="n">
-        <v>4.05</v>
+        <v>4.09</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>5.76</v>
+        <v>5.01</v>
       </c>
       <c r="I30" t="n">
         <v>3.57</v>
@@ -3269,7 +3269,7 @@
         <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>36.72</v>
+        <v>36.01</v>
       </c>
     </row>
     <row r="31">
@@ -3291,13 +3291,13 @@
         <v>0.8</v>
       </c>
       <c r="F31" t="n">
-        <v>6.57</v>
+        <v>6.41</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>2.68</v>
+        <v>2.59</v>
       </c>
       <c r="I31" t="n">
         <v>3.58</v>
@@ -3309,7 +3309,7 @@
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>31.77</v>
+        <v>31.52</v>
       </c>
     </row>
   </sheetData>
@@ -3343,13 +3343,13 @@
     <col width="15" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="18" customWidth="1" min="16" max="16"/>
-    <col width="11" customWidth="1" min="17" max="17"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
     <col width="16" customWidth="1" min="18" max="18"/>
     <col width="19" customWidth="1" min="19" max="19"/>
-    <col width="23" customWidth="1" min="20" max="20"/>
+    <col width="22" customWidth="1" min="20" max="20"/>
     <col width="23" customWidth="1" min="21" max="21"/>
-    <col width="21" customWidth="1" min="22" max="22"/>
-    <col width="22" customWidth="1" min="23" max="23"/>
+    <col width="22" customWidth="1" min="22" max="22"/>
+    <col width="23" customWidth="1" min="23" max="23"/>
     <col width="18" customWidth="1" min="24" max="24"/>
     <col width="24" customWidth="1" min="25" max="25"/>
     <col width="17" customWidth="1" min="26" max="26"/>
@@ -3514,12 +3514,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>MU</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Taiwan Semiconductor Manufacturing Company Limited</t>
+          <t>Micron Technology, Inc.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -3532,69 +3532,60 @@
           <t>Semiconductors</t>
         </is>
       </c>
-      <c r="E2" t="n">
-        <v>2164886077440</v>
-      </c>
       <c r="F2" t="n">
-        <v>417.4100036621094</v>
+        <v>940.4349975585938</v>
       </c>
       <c r="G2" t="n">
-        <v>4440492343296</v>
+        <v>90273996800</v>
       </c>
       <c r="H2" t="n">
-        <v>0.36</v>
+        <v>3.457</v>
       </c>
       <c r="I2" t="n">
-        <v>13.41</v>
+        <v>44.22</v>
       </c>
       <c r="J2" t="n">
-        <v>0.774</v>
+        <v>13.685</v>
       </c>
       <c r="K2" t="n">
-        <v>730826014720</v>
+        <v>7639499776</v>
       </c>
       <c r="M2" t="n">
-        <v>3518010228736</v>
+        <v>26022000640</v>
       </c>
       <c r="N2" t="n">
-        <v>1068558516224</v>
+        <v>6376000000</v>
       </c>
       <c r="O2" t="n">
-        <v>0.6423</v>
+        <v>0.7256899999999999</v>
       </c>
       <c r="P2" t="n">
-        <v>0.60344005</v>
+        <v>0.80370003</v>
       </c>
       <c r="Q2" t="n">
-        <v>31.126772</v>
-      </c>
-      <c r="R2" t="n">
-        <v>0.48753288</v>
-      </c>
-      <c r="S2" t="n">
-        <v>2.962245505545432</v>
+        <v>21.267185</v>
       </c>
       <c r="T2" t="n">
-        <v>0.03470414683054357</v>
+        <v>0.04469560631633174</v>
       </c>
       <c r="U2" t="n">
-        <v>0.01471556274845898</v>
+        <v>0.01310806359242367</v>
       </c>
       <c r="V2" t="n">
-        <v>0.133840746405375</v>
+        <v>1.251081869711045</v>
       </c>
       <c r="W2" t="n">
-        <v>0.7913594096526697</v>
+        <v>7.085359143926503</v>
       </c>
       <c r="X2" t="n">
-        <v>0.00013</v>
+        <v>0.00242</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.15493</v>
+        <v>0.79987</v>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>2026-08-25T23:44:59.127707+00:00</t>
+          <t>2026-08-26T19:35:27.798452+00:00</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
@@ -3606,12 +3597,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>MU</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Micron Technology, Inc.</t>
+          <t>Taiwan Semiconductor Manufacturing Company Limited</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -3625,68 +3616,68 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1053689905152</v>
+        <v>2166908780544</v>
       </c>
       <c r="F3" t="n">
-        <v>932.969970703125</v>
+        <v>417.7999877929688</v>
       </c>
       <c r="G3" t="n">
-        <v>90273996800</v>
+        <v>4440492343296</v>
       </c>
       <c r="H3" t="n">
-        <v>3.457</v>
+        <v>0.36</v>
       </c>
       <c r="I3" t="n">
-        <v>44.25</v>
+        <v>13.44</v>
       </c>
       <c r="J3" t="n">
-        <v>13.685</v>
+        <v>0.774</v>
       </c>
       <c r="K3" t="n">
-        <v>7639499776</v>
+        <v>730826014720</v>
       </c>
       <c r="M3" t="n">
-        <v>26022000640</v>
+        <v>3518010228736</v>
       </c>
       <c r="N3" t="n">
-        <v>6376000000</v>
+        <v>1068558516224</v>
       </c>
       <c r="O3" t="n">
-        <v>0.7256899999999999</v>
+        <v>0.6423</v>
       </c>
       <c r="P3" t="n">
-        <v>0.80370003</v>
+        <v>0.60344005</v>
       </c>
       <c r="Q3" t="n">
-        <v>21.084066</v>
+        <v>31.08631</v>
       </c>
       <c r="R3" t="n">
-        <v>11.672131</v>
+        <v>0.4879884</v>
       </c>
       <c r="S3" t="n">
-        <v>137.9265575034425</v>
+        <v>2.965013199994261</v>
       </c>
       <c r="T3" t="n">
-        <v>0.01305169481163082</v>
+        <v>0.04688163478604768</v>
       </c>
       <c r="U3" t="n">
-        <v>0.04156075280455829</v>
+        <v>-0.009347774506349715</v>
       </c>
       <c r="V3" t="n">
-        <v>1.217510665558717</v>
+        <v>0.08868034762461519</v>
       </c>
       <c r="W3" t="n">
-        <v>7.026691786103124</v>
+        <v>0.7695234161047211</v>
       </c>
       <c r="X3" t="n">
-        <v>0.00242</v>
+        <v>0.00013</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.7998100500000001</v>
+        <v>0.15493</v>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>2026-08-25T23:44:52.674132+00:00</t>
+          <t>2026-08-26T19:35:31.598850+00:00</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
@@ -3698,12 +3689,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CRDO</t>
+          <t>ANET</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Credo Technology Group Holding Ltd</t>
+          <t>Arista Networks, Inc.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -3713,72 +3704,72 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Semiconductors</t>
+          <t>Computer Hardware</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>42239107072</v>
+        <v>255322324992</v>
       </c>
       <c r="F4" t="n">
-        <v>226.5099945068359</v>
+        <v>202.4400024414062</v>
       </c>
       <c r="G4" t="n">
-        <v>1335116032</v>
+        <v>10540800000</v>
       </c>
       <c r="H4" t="n">
-        <v>1.57</v>
+        <v>0.377</v>
       </c>
       <c r="I4" t="n">
-        <v>2.52</v>
+        <v>3.15</v>
       </c>
       <c r="J4" t="n">
-        <v>3.432</v>
+        <v>0.357</v>
       </c>
       <c r="K4" t="n">
-        <v>250810128</v>
+        <v>3891512576</v>
       </c>
       <c r="M4" t="n">
-        <v>1443286016</v>
+        <v>13343299584</v>
       </c>
       <c r="N4" t="n">
-        <v>25448000</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>0.68035007</v>
+        <v>0.63004</v>
       </c>
       <c r="P4" t="n">
-        <v>0.35661998</v>
+        <v>0.45393002</v>
       </c>
       <c r="Q4" t="n">
-        <v>89.88491999999999</v>
+        <v>64.26666</v>
       </c>
       <c r="R4" t="n">
-        <v>31.637032</v>
+        <v>24.222292</v>
       </c>
       <c r="S4" t="n">
-        <v>168.4106914215203</v>
+        <v>65.61004750868368</v>
       </c>
       <c r="T4" t="n">
-        <v>0.06267886930759103</v>
+        <v>0.1855235942473756</v>
       </c>
       <c r="U4" t="n">
-        <v>0.02197254615862865</v>
+        <v>0.3119046441857201</v>
       </c>
       <c r="V4" t="n">
-        <v>0.8259571860899382</v>
+        <v>0.5721052708289811</v>
       </c>
       <c r="W4" t="n">
-        <v>0.9626547727179577</v>
+        <v>0.5077083190569849</v>
       </c>
       <c r="X4" t="n">
-        <v>0.108789995</v>
+        <v>0.17247999</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.74177</v>
+        <v>0.73305</v>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>2026-08-25T23:44:53.857324+00:00</t>
+          <t>2026-08-26T19:35:33.190402+00:00</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
@@ -3790,12 +3781,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ANET</t>
+          <t>CRDO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Arista Networks, Inc.</t>
+          <t>Credo Technology Group Holding Ltd</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -3805,72 +3796,72 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Computer Hardware</t>
+          <t>Semiconductors</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>240818241536</v>
+        <v>42128154624</v>
       </c>
       <c r="F5" t="n">
-        <v>190.9400024414062</v>
+        <v>225.9149932861328</v>
       </c>
       <c r="G5" t="n">
-        <v>10540800000</v>
+        <v>1335116032</v>
       </c>
       <c r="H5" t="n">
-        <v>0.377</v>
+        <v>1.57</v>
       </c>
       <c r="I5" t="n">
-        <v>3.16</v>
+        <v>2.51</v>
       </c>
       <c r="J5" t="n">
-        <v>0.357</v>
+        <v>3.432</v>
       </c>
       <c r="K5" t="n">
-        <v>3891512576</v>
+        <v>250810128</v>
       </c>
       <c r="M5" t="n">
-        <v>13343299584</v>
+        <v>1443286016</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>25448000</v>
       </c>
       <c r="O5" t="n">
-        <v>0.63004</v>
+        <v>0.68035007</v>
       </c>
       <c r="P5" t="n">
-        <v>0.45393002</v>
+        <v>0.35661998</v>
       </c>
       <c r="Q5" t="n">
-        <v>60.42405</v>
+        <v>90.00597399999999</v>
       </c>
       <c r="R5" t="n">
-        <v>22.846296</v>
+        <v>31.553928</v>
       </c>
       <c r="S5" t="n">
-        <v>61.88294058746992</v>
+        <v>167.9683151551201</v>
       </c>
       <c r="T5" t="n">
-        <v>0.09741937130353229</v>
+        <v>0.08539922143080592</v>
       </c>
       <c r="U5" t="n">
-        <v>0.208404588819511</v>
+        <v>0.0211770449264197</v>
       </c>
       <c r="V5" t="n">
-        <v>0.49839128921081</v>
+        <v>0.8696928731492419</v>
       </c>
       <c r="W5" t="n">
-        <v>0.4352075471827954</v>
+        <v>0.8810574201198889</v>
       </c>
       <c r="X5" t="n">
-        <v>0.17241</v>
+        <v>0.10795</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.73283994</v>
+        <v>0.73627</v>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>2026-08-25T23:45:01.664633+00:00</t>
+          <t>2026-08-26T19:35:28.466330+00:00</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
@@ -3901,10 +3892,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>415080284160</v>
+        <v>428649152512</v>
       </c>
       <c r="F6" t="n">
-        <v>172.7299957275391</v>
+        <v>178.3600006103516</v>
       </c>
       <c r="G6" t="n">
         <v>6155940864</v>
@@ -3913,7 +3904,7 @@
         <v>0.928</v>
       </c>
       <c r="I6" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="J6" t="n">
         <v>2.154</v>
@@ -3934,35 +3925,35 @@
         <v>0.47120997</v>
       </c>
       <c r="Q6" t="n">
-        <v>146.38136</v>
+        <v>152.45854</v>
       </c>
       <c r="R6" t="n">
-        <v>67.4276</v>
+        <v>69.62533999999999</v>
       </c>
       <c r="S6" t="n">
-        <v>192.2464993487078</v>
+        <v>198.5309882544491</v>
       </c>
       <c r="T6" t="n">
-        <v>0.4052228953838191</v>
+        <v>0.3560404642718344</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2644947877721477</v>
+        <v>0.3460116821690029</v>
       </c>
       <c r="V6" t="n">
-        <v>0.3225879606056874</v>
+        <v>0.3843527295871054</v>
       </c>
       <c r="W6" t="n">
-        <v>0.09900106725119362</v>
+        <v>0.1087213652267676</v>
       </c>
       <c r="X6" t="n">
         <v>0.03477</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.64827</v>
+        <v>0.64858</v>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>2026-08-25T23:44:49.725077+00:00</t>
+          <t>2026-08-26T19:35:26.290183+00:00</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr">
@@ -3993,10 +3984,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>57287942144</v>
+        <v>56715730944</v>
       </c>
       <c r="F7" t="n">
-        <v>366.4299926757812</v>
+        <v>362.7699890136719</v>
       </c>
       <c r="G7" t="n">
         <v>4464031232</v>
@@ -4005,7 +3996,7 @@
         <v>1.039</v>
       </c>
       <c r="I7" t="n">
-        <v>7.3</v>
+        <v>7.29</v>
       </c>
       <c r="J7" t="n">
         <v>3.858</v>
@@ -4026,35 +4017,35 @@
         <v>0.33161</v>
       </c>
       <c r="Q7" t="n">
-        <v>50.19589</v>
+        <v>49.762688</v>
       </c>
       <c r="R7" t="n">
-        <v>12.833231</v>
+        <v>12.705048</v>
       </c>
       <c r="S7" t="n">
-        <v>130.9794199133109</v>
+        <v>129.6711534921589</v>
       </c>
       <c r="T7" t="n">
-        <v>0.04718215196186981</v>
+        <v>0.08363951644081369</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.05835951358837577</v>
+        <v>-0.03474974862359081</v>
       </c>
       <c r="V7" t="n">
-        <v>0.1509211258328167</v>
+        <v>0.102759113321057</v>
       </c>
       <c r="W7" t="n">
-        <v>2.138020274911799</v>
+        <v>2.066340512011734</v>
       </c>
       <c r="X7" t="n">
         <v>0.00202</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.0044999</v>
+        <v>1.00462</v>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>2026-08-25T23:44:54.397196+00:00</t>
+          <t>2026-08-26T19:35:28.828354+00:00</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr">
@@ -4085,10 +4076,10 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>291733307392</v>
+        <v>302084489216</v>
       </c>
       <c r="F8" t="n">
-        <v>451.5</v>
+        <v>467.5199890136719</v>
       </c>
       <c r="G8" t="n">
         <v>134001999872</v>
@@ -4097,7 +4088,7 @@
         <v>0.875</v>
       </c>
       <c r="I8" t="n">
-        <v>12.56</v>
+        <v>12.55</v>
       </c>
       <c r="J8" t="n">
         <v>2.825</v>
@@ -4118,35 +4109,35 @@
         <v>0.08857000600000001</v>
       </c>
       <c r="Q8" t="n">
-        <v>35.947453</v>
+        <v>37.252586</v>
       </c>
       <c r="R8" t="n">
-        <v>2.1770818</v>
+        <v>2.2543283</v>
       </c>
       <c r="S8" t="n">
-        <v>53.68542647235485</v>
+        <v>55.59027448467874</v>
       </c>
       <c r="T8" t="n">
-        <v>0.03200000000000003</v>
+        <v>0.09512540114591572</v>
       </c>
       <c r="U8" t="n">
-        <v>0.4823852705245668</v>
+        <v>0.5337761349093098</v>
       </c>
       <c r="V8" t="n">
-        <v>2.807666754214015</v>
+        <v>2.921702621122898</v>
       </c>
       <c r="W8" t="n">
-        <v>2.490218142880296</v>
+        <v>2.614609163193061</v>
       </c>
       <c r="X8" t="n">
         <v>0.07491</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.75588</v>
+        <v>0.75615</v>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>2026-08-25T23:45:02.223851+00:00</t>
+          <t>2026-08-26T19:35:33.586639+00:00</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr">
@@ -4177,10 +4168,10 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5160284192768</v>
+        <v>5100700434432</v>
       </c>
       <c r="F9" t="n">
-        <v>213.0500030517578</v>
+        <v>210.5899963378906</v>
       </c>
       <c r="G9" t="n">
         <v>253491003392</v>
@@ -4189,7 +4180,7 @@
         <v>0.852</v>
       </c>
       <c r="I9" t="n">
-        <v>6.53</v>
+        <v>6.54</v>
       </c>
       <c r="J9" t="n">
         <v>2.145</v>
@@ -4210,35 +4201,35 @@
         <v>0.65596</v>
       </c>
       <c r="Q9" t="n">
-        <v>32.62634</v>
+        <v>32.200306</v>
       </c>
       <c r="R9" t="n">
-        <v>20.356873</v>
+        <v>20.12182</v>
       </c>
       <c r="S9" t="n">
-        <v>111.3669357237576</v>
+        <v>110.0810258131978</v>
       </c>
       <c r="T9" t="n">
-        <v>0.03002323933385975</v>
+        <v>0.07165030901552893</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.007268423517560629</v>
+        <v>-0.008299935890130561</v>
       </c>
       <c r="V9" t="n">
-        <v>0.1135987674078007</v>
+        <v>0.09332038999234893</v>
       </c>
       <c r="W9" t="n">
-        <v>0.1864399218446351</v>
+        <v>0.160095031922475</v>
       </c>
       <c r="X9" t="n">
         <v>0.03991</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.71185</v>
+        <v>0.71202004</v>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>2026-08-25T23:44:49.156368+00:00</t>
+          <t>2026-08-26T19:35:26.004677+00:00</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr">
@@ -4269,10 +4260,10 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>8631883776</v>
+        <v>8712192000</v>
       </c>
       <c r="F10" t="n">
-        <v>16.65999984741211</v>
+        <v>16.81500053405762</v>
       </c>
       <c r="G10" t="n">
         <v>1672329984</v>
@@ -4299,35 +4290,35 @@
         <v>0.07274</v>
       </c>
       <c r="Q10" t="n">
-        <v>27.766665</v>
+        <v>28.025</v>
       </c>
       <c r="R10" t="n">
-        <v>5.161591</v>
+        <v>5.209613</v>
       </c>
       <c r="S10" t="n">
-        <v>16.87385884106087</v>
+        <v>17.03084770591561</v>
       </c>
       <c r="T10" t="n">
-        <v>0.5369003332933329</v>
+        <v>0.4470740705389074</v>
       </c>
       <c r="U10" t="n">
-        <v>0.5022542487093149</v>
+        <v>0.5067204985631648</v>
       </c>
       <c r="V10" t="n">
-        <v>0.6381513984691323</v>
+        <v>0.6648514751452654</v>
       </c>
       <c r="W10" t="n">
-        <v>0.5104261333399276</v>
+        <v>0.5540666366285691</v>
       </c>
       <c r="X10" t="n">
         <v>0.09236999999999999</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.91143</v>
+        <v>0.91159</v>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>2026-08-25T23:45:07.140555+00:00</t>
+          <t>2026-08-26T19:35:36.286185+00:00</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr">
@@ -4358,10 +4349,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>782249361408</v>
+        <v>786910085120</v>
       </c>
       <c r="F11" t="n">
-        <v>479.1799926757812</v>
+        <v>482.0350036621094</v>
       </c>
       <c r="G11" t="n">
         <v>41305001984</v>
@@ -4391,35 +4382,35 @@
         <v>0.1725</v>
       </c>
       <c r="Q11" t="n">
-        <v>121.92875</v>
+        <v>122.65521</v>
       </c>
       <c r="R11" t="n">
-        <v>18.93837</v>
+        <v>19.051205</v>
       </c>
       <c r="S11" t="n">
-        <v>88.47473760686621</v>
+        <v>89.00187936986502</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.08194275032277476</v>
+        <v>-0.02609356142316788</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.04903852280124332</v>
+        <v>-0.0272531070144425</v>
       </c>
       <c r="V11" t="n">
-        <v>1.437334576803009</v>
+        <v>1.254185427970365</v>
       </c>
       <c r="W11" t="n">
-        <v>1.933276144009865</v>
+        <v>1.89302015237177</v>
       </c>
       <c r="X11" t="n">
         <v>0.00425</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.75365996</v>
+        <v>0.75384</v>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>2026-08-25T23:44:50.453971+00:00</t>
+          <t>2026-08-26T19:35:26.607815+00:00</t>
         </is>
       </c>
       <c r="AD11" t="inlineStr">
@@ -4450,10 +4441,10 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4243298189312</v>
+        <v>4179029917696</v>
       </c>
       <c r="F12" t="n">
-        <v>346.9599914550781</v>
+        <v>341.7049865722656</v>
       </c>
       <c r="G12" t="n">
         <v>445865984000</v>
@@ -4462,7 +4453,7 @@
         <v>0.242</v>
       </c>
       <c r="I12" t="n">
-        <v>19.94</v>
+        <v>19.92</v>
       </c>
       <c r="J12" t="n">
         <v>2.94</v>
@@ -4483,35 +4474,35 @@
         <v>0.34033</v>
       </c>
       <c r="Q12" t="n">
-        <v>17.4002</v>
+        <v>17.153864</v>
       </c>
       <c r="R12" t="n">
-        <v>9.516980999999999</v>
+        <v>9.372839000000001</v>
       </c>
       <c r="S12" t="n">
-        <v>187.2180899882036</v>
+        <v>184.3825166860262</v>
       </c>
       <c r="T12" t="n">
-        <v>0.08513167589937809</v>
+        <v>0.0463773552391531</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.1072638518099384</v>
+        <v>-0.1206720029528235</v>
       </c>
       <c r="V12" t="n">
-        <v>0.1153219631662308</v>
+        <v>0.1005138619474426</v>
       </c>
       <c r="W12" t="n">
-        <v>0.6689037745617639</v>
+        <v>0.6543391169511197</v>
       </c>
       <c r="X12" t="n">
         <v>0.01596</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.81035006</v>
+        <v>0.81044</v>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>2026-08-25T23:44:56.718881+00:00</t>
+          <t>2026-08-26T19:35:30.186512+00:00</t>
         </is>
       </c>
       <c r="AD12" t="inlineStr">
@@ -4542,10 +4533,10 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>380958507008</v>
+        <v>380553789440</v>
       </c>
       <c r="F13" t="n">
-        <v>480.0400085449219</v>
+        <v>479.5299987792969</v>
       </c>
       <c r="G13" t="n">
         <v>30837000192</v>
@@ -4575,35 +4566,35 @@
         <v>0.33736</v>
       </c>
       <c r="Q13" t="n">
-        <v>41.490063</v>
+        <v>41.44598</v>
       </c>
       <c r="R13" t="n">
-        <v>12.353942</v>
+        <v>12.340817</v>
       </c>
       <c r="S13" t="n">
-        <v>123.8738346137044</v>
+        <v>123.7422351975962</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.1038632558293222</v>
+        <v>-0.07128644345885427</v>
       </c>
       <c r="U13" t="n">
-        <v>0.05641651120348978</v>
+        <v>0.0709264487206942</v>
       </c>
       <c r="V13" t="n">
-        <v>0.2880491350104883</v>
+        <v>0.2717687020321928</v>
       </c>
       <c r="W13" t="n">
-        <v>1.979783535953246</v>
+        <v>1.931021046026384</v>
       </c>
       <c r="X13" t="n">
         <v>0.00331</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.86283</v>
+        <v>0.8631</v>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>2026-08-25T23:44:51.879989+00:00</t>
+          <t>2026-08-26T19:35:27.435476+00:00</t>
         </is>
       </c>
       <c r="AD13" t="inlineStr">
@@ -4634,10 +4625,10 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>80070139904</v>
+        <v>82515435520</v>
       </c>
       <c r="F14" t="n">
-        <v>222.9900054931641</v>
+        <v>229.8000030517578</v>
       </c>
       <c r="G14" t="n">
         <v>3966725120</v>
@@ -4646,7 +4637,7 @@
         <v>0.356</v>
       </c>
       <c r="I14" t="n">
-        <v>0.5</v>
+        <v>0.49</v>
       </c>
       <c r="J14" t="n">
         <v>14.985</v>
@@ -4667,35 +4658,35 @@
         <v>0.00666</v>
       </c>
       <c r="Q14" t="n">
-        <v>445.98</v>
+        <v>468.97958</v>
       </c>
       <c r="R14" t="n">
-        <v>20.185452</v>
+        <v>20.801905</v>
       </c>
       <c r="S14" t="n">
-        <v>76.15484044075602</v>
+        <v>78.48056508280398</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.0966944626839904</v>
+        <v>-0.08758833282432332</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.002950987799381632</v>
+        <v>0.03602184563864586</v>
       </c>
       <c r="V14" t="n">
-        <v>1.173074210742595</v>
+        <v>1.200517115581857</v>
       </c>
       <c r="W14" t="n">
-        <v>0.736952773110682</v>
+        <v>0.8193334454397108</v>
       </c>
       <c r="X14" t="n">
         <v>0.00619</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.92804</v>
+        <v>0.9282899999999999</v>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>2026-08-25T23:45:04.894691+00:00</t>
+          <t>2026-08-26T19:35:34.892476+00:00</t>
         </is>
       </c>
       <c r="AD14" t="inlineStr">
@@ -4726,10 +4717,10 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1697219084288</v>
+        <v>1682993971200</v>
       </c>
       <c r="F15" t="n">
-        <v>356.739990234375</v>
+        <v>353.760009765625</v>
       </c>
       <c r="G15" t="n">
         <v>75464998912</v>
@@ -4738,7 +4729,7 @@
         <v>0.479</v>
       </c>
       <c r="I15" t="n">
-        <v>6.03</v>
+        <v>5.99</v>
       </c>
       <c r="J15" t="n">
         <v>0.854</v>
@@ -4759,35 +4750,35 @@
         <v>0.48988</v>
       </c>
       <c r="Q15" t="n">
-        <v>59.16086</v>
+        <v>59.056763</v>
       </c>
       <c r="R15" t="n">
-        <v>22.490149</v>
+        <v>22.30165</v>
       </c>
       <c r="S15" t="n">
-        <v>62.36967325998923</v>
+        <v>61.84692657183427</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.06593009611454637</v>
+        <v>-0.07687487960241302</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.1533267524098848</v>
+        <v>-0.1601006951045902</v>
       </c>
       <c r="V15" t="n">
-        <v>0.08389571930187634</v>
+        <v>0.09085738489331074</v>
       </c>
       <c r="W15" t="n">
-        <v>0.2213365095285857</v>
+        <v>0.1957721766741856</v>
       </c>
       <c r="X15" t="n">
         <v>0.01948</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.80134004</v>
+        <v>0.80146</v>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>2026-08-25T23:44:51.058964+00:00</t>
+          <t>2026-08-26T19:35:27.004689+00:00</t>
         </is>
       </c>
       <c r="AD15" t="inlineStr">
@@ -4818,10 +4809,10 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>32568498176</v>
+        <v>32663406592</v>
       </c>
       <c r="F16" t="n">
-        <v>404.9200134277344</v>
+        <v>406.1000061035156</v>
       </c>
       <c r="G16" t="n">
         <v>2602398976</v>
@@ -4848,32 +4839,32 @@
         <v>-0.03607</v>
       </c>
       <c r="R16" t="n">
-        <v>12.514798</v>
+        <v>12.551268</v>
       </c>
       <c r="S16" t="n">
-        <v>62.92148359757376</v>
+        <v>63.10484416606987</v>
       </c>
       <c r="T16" t="n">
-        <v>0.3577895908063724</v>
+        <v>0.3112266872488625</v>
       </c>
       <c r="U16" t="n">
-        <v>0.3174556869582659</v>
+        <v>0.3791347479729481</v>
       </c>
       <c r="V16" t="n">
-        <v>0.3259980348506211</v>
+        <v>0.2994783956138904</v>
       </c>
       <c r="W16" t="n">
-        <v>0.8536898411560356</v>
+        <v>0.8946534153305201</v>
       </c>
       <c r="X16" t="n">
         <v>0.02641</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.96112</v>
+        <v>0.9611299599999999</v>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>2026-08-25T23:45:06.572589+00:00</t>
+          <t>2026-08-26T19:35:35.864618+00:00</t>
         </is>
       </c>
       <c r="AD16" t="inlineStr">
@@ -4885,87 +4876,81 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>AMZN</t>
+          <t>SNOW</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Amazon.com, Inc.</t>
+          <t>Snowflake Inc.</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Internet Retail</t>
+          <t>Software - Application</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2815874826240</v>
+        <v>109657309184</v>
       </c>
       <c r="F17" t="n">
-        <v>261.0599975585938</v>
+        <v>316.3800048828125</v>
       </c>
       <c r="G17" t="n">
-        <v>775680032768</v>
+        <v>5032822784</v>
       </c>
       <c r="H17" t="n">
-        <v>0.196</v>
+        <v>0.335</v>
       </c>
       <c r="I17" t="n">
-        <v>12.42</v>
-      </c>
-      <c r="J17" t="n">
-        <v>2.423</v>
+        <v>-3.52</v>
       </c>
       <c r="K17" t="n">
-        <v>3219124992</v>
+        <v>1739497728</v>
       </c>
       <c r="M17" t="n">
-        <v>122988003328</v>
+        <v>2954998016</v>
       </c>
       <c r="N17" t="n">
-        <v>251635007488</v>
+        <v>2772094976</v>
       </c>
       <c r="O17" t="n">
-        <v>0.5077</v>
+        <v>0.67144996</v>
       </c>
       <c r="P17" t="n">
-        <v>0.13689</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>21.019323</v>
+        <v>-0.22173999</v>
       </c>
       <c r="R17" t="n">
-        <v>3.6302016</v>
+        <v>21.788431</v>
       </c>
       <c r="S17" t="n">
-        <v>874.732989007219</v>
+        <v>63.03963921245202</v>
       </c>
       <c r="T17" t="n">
-        <v>0.1247253322653736</v>
+        <v>0.1592407640218212</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.01594485600693796</v>
+        <v>0.8052037818047075</v>
       </c>
       <c r="V17" t="n">
-        <v>0.2717883379204353</v>
+        <v>0.9643611677549742</v>
       </c>
       <c r="W17" t="n">
-        <v>0.145301372126208</v>
+        <v>0.6278878052326928</v>
       </c>
       <c r="X17" t="n">
-        <v>0.088690005</v>
+        <v>0.02962</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.68723</v>
+        <v>0.81926</v>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>2026-08-25T23:44:57.275831+00:00</t>
+          <t>2026-08-26T19:35:34.547859+00:00</t>
         </is>
       </c>
       <c r="AD17" t="inlineStr">
@@ -4977,81 +4962,87 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>SNOW</t>
+          <t>AMZN</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Snowflake Inc.</t>
+          <t>Amazon.com, Inc.</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Software - Application</t>
+          <t>Internet Retail</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>109879132160</v>
+        <v>2803843989504</v>
       </c>
       <c r="F18" t="n">
-        <v>317.0199890136719</v>
+        <v>259.9446105957031</v>
       </c>
       <c r="G18" t="n">
-        <v>5032822784</v>
+        <v>775680032768</v>
       </c>
       <c r="H18" t="n">
-        <v>0.335</v>
+        <v>0.196</v>
       </c>
       <c r="I18" t="n">
-        <v>-3.52</v>
+        <v>12.43</v>
+      </c>
+      <c r="J18" t="n">
+        <v>2.423</v>
       </c>
       <c r="K18" t="n">
-        <v>1739497728</v>
+        <v>3219124992</v>
       </c>
       <c r="M18" t="n">
-        <v>2954998016</v>
+        <v>122988003328</v>
       </c>
       <c r="N18" t="n">
-        <v>2772094976</v>
+        <v>251635007488</v>
       </c>
       <c r="O18" t="n">
-        <v>0.67144996</v>
+        <v>0.5077</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.22173999</v>
+        <v>0.13689</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>20.91268</v>
       </c>
       <c r="R18" t="n">
-        <v>21.832506</v>
+        <v>3.6146915</v>
       </c>
       <c r="S18" t="n">
-        <v>63.16716049197392</v>
+        <v>870.9956887265843</v>
       </c>
       <c r="T18" t="n">
-        <v>0.1826456461276966</v>
+        <v>0.1234046902691341</v>
       </c>
       <c r="U18" t="n">
-        <v>0.7850223993173411</v>
+        <v>-0.04379398653858824</v>
       </c>
       <c r="V18" t="n">
-        <v>1.011548075737035</v>
+        <v>0.246378086107683</v>
       </c>
       <c r="W18" t="n">
-        <v>0.6284158667585058</v>
+        <v>0.1365685932619147</v>
       </c>
       <c r="X18" t="n">
-        <v>0.02962</v>
+        <v>0.088690005</v>
       </c>
       <c r="Y18" t="n">
-        <v>0.81942004</v>
+        <v>0.68727</v>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>2026-08-25T23:45:03.993300+00:00</t>
+          <t>2026-08-26T19:35:30.475525+00:00</t>
         </is>
       </c>
       <c r="AD18" t="inlineStr">
@@ -5063,12 +5054,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>SMCI</t>
+          <t>NET</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Super Micro Computer, Inc.</t>
+          <t>Cloudflare, Inc.</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -5078,69 +5069,66 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Computer Hardware</t>
+          <t>Software - Infrastructure</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>24878735360</v>
+        <v>101529010176</v>
       </c>
       <c r="F19" t="n">
-        <v>38.45999908447266</v>
+        <v>285.1300048828125</v>
       </c>
       <c r="G19" t="n">
-        <v>39063072768</v>
+        <v>2512349952</v>
       </c>
       <c r="H19" t="n">
-        <v>0.9320000000000001</v>
+        <v>0.359</v>
       </c>
       <c r="I19" t="n">
-        <v>3.26</v>
-      </c>
-      <c r="J19" t="n">
-        <v>4.094</v>
+        <v>-0.58</v>
       </c>
       <c r="K19" t="n">
-        <v>-8231267840</v>
+        <v>692851968</v>
       </c>
       <c r="M19" t="n">
-        <v>7521474048</v>
+        <v>4162798080</v>
       </c>
       <c r="N19" t="n">
-        <v>9311492096</v>
+        <v>3529349888</v>
       </c>
       <c r="O19" t="n">
-        <v>0.108219996</v>
+        <v>0.72577006</v>
       </c>
       <c r="P19" t="n">
-        <v>0.13382</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>11.797545</v>
+        <v>-0.07902000000000001</v>
       </c>
       <c r="R19" t="n">
-        <v>0.6368863</v>
+        <v>40.41197</v>
+      </c>
+      <c r="S19" t="n">
+        <v>146.5378101892034</v>
       </c>
       <c r="T19" t="n">
-        <v>0.2777408171778477</v>
+        <v>0.07349128650194836</v>
       </c>
       <c r="U19" t="n">
-        <v>0.03665769989991308</v>
+        <v>0.3628238372010764</v>
       </c>
       <c r="V19" t="n">
-        <v>0.2523608020528563</v>
+        <v>0.7406141818714294</v>
       </c>
       <c r="W19" t="n">
-        <v>-0.1272974960108844</v>
+        <v>0.4360614479995002</v>
       </c>
       <c r="X19" t="n">
-        <v>0.12878999</v>
+        <v>0.00616</v>
       </c>
       <c r="Y19" t="n">
-        <v>0.70528</v>
+        <v>0.90191</v>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>2026-08-25T23:45:03.369591+00:00</t>
+          <t>2026-08-26T19:35:35.186219+00:00</t>
         </is>
       </c>
       <c r="AD19" t="inlineStr">
@@ -5171,10 +5159,10 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>3651215032320</v>
+        <v>3683367780352</v>
       </c>
       <c r="F20" t="n">
-        <v>491.7099914550781</v>
+        <v>496.1099853515625</v>
       </c>
       <c r="G20" t="n">
         <v>331839012864</v>
@@ -5183,7 +5171,7 @@
         <v>0.177</v>
       </c>
       <c r="I20" t="n">
-        <v>17.93</v>
+        <v>17.95</v>
       </c>
       <c r="J20" t="n">
         <v>0.317</v>
@@ -5204,35 +5192,35 @@
         <v>0.45111</v>
       </c>
       <c r="Q20" t="n">
-        <v>27.42387</v>
+        <v>27.63454</v>
       </c>
       <c r="R20" t="n">
-        <v>11.002971</v>
+        <v>11.099864</v>
       </c>
       <c r="S20" t="n">
-        <v>220.677223233607</v>
+        <v>222.6205158340768</v>
       </c>
       <c r="T20" t="n">
-        <v>0.2906356072891438</v>
+        <v>0.2774194582586049</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1841348949382575</v>
+        <v>0.2044585141116562</v>
       </c>
       <c r="V20" t="n">
-        <v>0.2841122091195314</v>
+        <v>0.2805152771044099</v>
       </c>
       <c r="W20" t="n">
-        <v>-0.01686510460742252</v>
+        <v>-0.003681343152454719</v>
       </c>
       <c r="X20" t="n">
         <v>0.00090000004</v>
       </c>
       <c r="Y20" t="n">
-        <v>0.75867</v>
+        <v>0.75881</v>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>2026-08-25T23:44:56.193806+00:00</t>
+          <t>2026-08-26T19:35:29.857994+00:00</t>
         </is>
       </c>
       <c r="AD20" t="inlineStr">
@@ -5244,12 +5232,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>NET</t>
+          <t>ASML</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Cloudflare, Inc.</t>
+          <t>ASML Holding N.V.</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -5259,66 +5247,72 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Software - Infrastructure</t>
+          <t>Semiconductor Equipment &amp; Materials</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>98840600576</v>
+        <v>669497819136</v>
       </c>
       <c r="F21" t="n">
-        <v>277.5799865722656</v>
+        <v>1743.030029296875</v>
       </c>
       <c r="G21" t="n">
-        <v>2512349952</v>
+        <v>35327500288</v>
       </c>
       <c r="H21" t="n">
-        <v>0.359</v>
+        <v>0.213</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.59</v>
+        <v>29.65</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0.285</v>
       </c>
       <c r="K21" t="n">
-        <v>692851968</v>
+        <v>8437675008</v>
       </c>
       <c r="M21" t="n">
-        <v>4162798080</v>
+        <v>7581499904</v>
       </c>
       <c r="N21" t="n">
-        <v>3529349888</v>
+        <v>1984400000</v>
       </c>
       <c r="O21" t="n">
-        <v>0.72577006</v>
+        <v>0.5273300400000001</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.07902000000000001</v>
+        <v>0.37057</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>58.78685</v>
       </c>
       <c r="R21" t="n">
-        <v>39.341892</v>
+        <v>18.95118</v>
       </c>
       <c r="S21" t="n">
-        <v>142.6576024043277</v>
+        <v>79.3462439002723</v>
       </c>
       <c r="T21" t="n">
-        <v>0.05885940505447462</v>
+        <v>0.0543867634453512</v>
       </c>
       <c r="U21" t="n">
-        <v>0.2759951969252914</v>
+        <v>0.09225674229723846</v>
       </c>
       <c r="V21" t="n">
-        <v>0.7328171692474872</v>
+        <v>0.1677768897011251</v>
       </c>
       <c r="W21" t="n">
-        <v>0.4170919933268895</v>
+        <v>1.298886982662355</v>
       </c>
       <c r="X21" t="n">
-        <v>0.00616</v>
+        <v>0.00016000001</v>
       </c>
       <c r="Y21" t="n">
-        <v>0.90181</v>
+        <v>0.20384</v>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>2026-08-25T23:45:05.399915+00:00</t>
+          <t>2026-08-26T19:35:31.979027+00:00</t>
         </is>
       </c>
       <c r="AD21" t="inlineStr">
@@ -5330,84 +5324,87 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ACMR</t>
+          <t>VRT</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>ACM Research, Inc.</t>
+          <t>Vertiv Holdings Co</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Semiconductor Equipment &amp; Materials</t>
+          <t>Electrical Equipment &amp; Parts</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5555916288</v>
+        <v>101908283392</v>
       </c>
       <c r="F22" t="n">
-        <v>79.76999664306641</v>
+        <v>264.7049865722656</v>
       </c>
       <c r="G22" t="n">
-        <v>1037772032</v>
+        <v>11479600128</v>
       </c>
       <c r="H22" t="n">
-        <v>0.36</v>
+        <v>0.241</v>
       </c>
       <c r="I22" t="n">
-        <v>2.12</v>
+        <v>4.42</v>
       </c>
       <c r="J22" t="n">
-        <v>1.806</v>
+        <v>0.53</v>
       </c>
       <c r="K22" t="n">
-        <v>-186610256</v>
+        <v>2696537600</v>
       </c>
       <c r="M22" t="n">
-        <v>1439374976</v>
+        <v>3110599936</v>
       </c>
       <c r="N22" t="n">
-        <v>349319008</v>
+        <v>3338200064</v>
       </c>
       <c r="O22" t="n">
-        <v>0.43835</v>
+        <v>0.38039002</v>
       </c>
       <c r="P22" t="n">
-        <v>0.16982001</v>
+        <v>0.20362</v>
       </c>
       <c r="Q22" t="n">
-        <v>37.627357</v>
+        <v>59.888004</v>
       </c>
       <c r="R22" t="n">
-        <v>5.3536963</v>
+        <v>8.877337000000001</v>
+      </c>
+      <c r="S22" t="n">
+        <v>37.79227235399944</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.05396113695713289</v>
+        <v>-0.07960715940669838</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.07737685070838396</v>
+        <v>-0.1720555715333105</v>
       </c>
       <c r="V22" t="n">
-        <v>0.224969184253502</v>
+        <v>0.04611132820037822</v>
       </c>
       <c r="W22" t="n">
-        <v>1.769791623480893</v>
+        <v>1.071418583977279</v>
       </c>
       <c r="X22" t="n">
-        <v>0.12675999</v>
+        <v>0.00269</v>
       </c>
       <c r="Y22" t="n">
-        <v>0.78046995</v>
+        <v>0.84448</v>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>2026-08-25T23:44:53.303395+00:00</t>
+          <t>2026-08-26T19:35:33.916981+00:00</t>
         </is>
       </c>
       <c r="AD22" t="inlineStr">
@@ -5419,87 +5416,84 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>VRT</t>
+          <t>ACMR</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Vertiv Holdings Co</t>
+          <t>ACM Research, Inc.</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Electrical Equipment &amp; Parts</t>
+          <t>Semiconductor Equipment &amp; Materials</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>98460721152</v>
+        <v>5500267008</v>
       </c>
       <c r="F23" t="n">
-        <v>255.75</v>
+        <v>78.97100067138672</v>
       </c>
       <c r="G23" t="n">
-        <v>11479600128</v>
+        <v>1037772032</v>
       </c>
       <c r="H23" t="n">
-        <v>0.241</v>
+        <v>0.36</v>
       </c>
       <c r="I23" t="n">
-        <v>4.41</v>
+        <v>2.12</v>
       </c>
       <c r="J23" t="n">
-        <v>0.53</v>
+        <v>1.806</v>
       </c>
       <c r="K23" t="n">
-        <v>2696537600</v>
+        <v>-186610256</v>
       </c>
       <c r="M23" t="n">
-        <v>3110599936</v>
+        <v>1439374976</v>
       </c>
       <c r="N23" t="n">
-        <v>3338200064</v>
+        <v>349319008</v>
       </c>
       <c r="O23" t="n">
-        <v>0.38039002</v>
+        <v>0.43835</v>
       </c>
       <c r="P23" t="n">
-        <v>0.20362</v>
+        <v>0.16982001</v>
       </c>
       <c r="Q23" t="n">
-        <v>57.9932</v>
+        <v>37.250473</v>
       </c>
       <c r="R23" t="n">
-        <v>8.577017</v>
-      </c>
-      <c r="S23" t="n">
-        <v>36.51375792126911</v>
+        <v>5.3000727</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.1191968146356578</v>
+        <v>-0.01249219124755718</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.2102645435334196</v>
+        <v>-0.1090816649914247</v>
       </c>
       <c r="V23" t="n">
-        <v>0.04255600645730628</v>
+        <v>0.1654515670264696</v>
       </c>
       <c r="W23" t="n">
-        <v>1.047926180569005</v>
+        <v>1.640287565170934</v>
       </c>
       <c r="X23" t="n">
-        <v>0.00269</v>
+        <v>0.12675999</v>
       </c>
       <c r="Y23" t="n">
-        <v>0.84405</v>
+        <v>0.78055</v>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>2026-08-25T23:45:02.812959+00:00</t>
+          <t>2026-08-26T19:35:28.144524+00:00</t>
         </is>
       </c>
       <c r="AD23" t="inlineStr">
@@ -5511,12 +5505,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ASML</t>
+          <t>SMCI</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>ASML Holding N.V.</t>
+          <t>Super Micro Computer, Inc.</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -5526,72 +5520,69 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Semiconductor Equipment &amp; Materials</t>
+          <t>Computer Hardware</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>669931864064</v>
+        <v>24212393984</v>
       </c>
       <c r="F24" t="n">
-        <v>1744.160034179688</v>
+        <v>37.42990112304688</v>
       </c>
       <c r="G24" t="n">
-        <v>35327500288</v>
+        <v>39063072768</v>
       </c>
       <c r="H24" t="n">
-        <v>0.213</v>
+        <v>0.9320000000000001</v>
       </c>
       <c r="I24" t="n">
-        <v>29.76</v>
+        <v>3.26</v>
       </c>
       <c r="J24" t="n">
-        <v>0.285</v>
+        <v>4.094</v>
       </c>
       <c r="K24" t="n">
-        <v>8437675008</v>
+        <v>-8231267840</v>
       </c>
       <c r="M24" t="n">
-        <v>7581499904</v>
+        <v>7521474048</v>
       </c>
       <c r="N24" t="n">
-        <v>1984400000</v>
+        <v>9311492096</v>
       </c>
       <c r="O24" t="n">
-        <v>0.5273300400000001</v>
+        <v>0.108219996</v>
       </c>
       <c r="P24" t="n">
-        <v>0.37057</v>
+        <v>0.13382</v>
       </c>
       <c r="Q24" t="n">
-        <v>58.60753</v>
+        <v>11.4815645</v>
       </c>
       <c r="R24" t="n">
-        <v>18.963467</v>
-      </c>
-      <c r="S24" t="n">
-        <v>79.39768519512999</v>
+        <v>0.6198282000000001</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.006074923781723141</v>
+        <v>0.2556156254148931</v>
       </c>
       <c r="U24" t="n">
-        <v>0.07008803937532648</v>
+        <v>-0.0199030513483841</v>
       </c>
       <c r="V24" t="n">
-        <v>0.1778210552954782</v>
+        <v>0.2023739843276351</v>
       </c>
       <c r="W24" t="n">
-        <v>1.327026100903341</v>
+        <v>-0.1562240620368144</v>
       </c>
       <c r="X24" t="n">
-        <v>0.00016000001</v>
+        <v>0.12878999</v>
       </c>
       <c r="Y24" t="n">
-        <v>0.20382999</v>
+        <v>0.70584</v>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>2026-08-25T23:44:59.758374+00:00</t>
+          <t>2026-08-26T19:35:34.244980+00:00</t>
         </is>
       </c>
       <c r="AD24" t="inlineStr">
@@ -5622,10 +5613,10 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>277018509312</v>
+        <v>277368930304</v>
       </c>
       <c r="F25" t="n">
-        <v>339.8999938964844</v>
+        <v>340.3299865722656</v>
       </c>
       <c r="G25" t="n">
         <v>10606499840</v>
@@ -5652,35 +5643,35 @@
         <v>-0.02465</v>
       </c>
       <c r="Q25" t="n">
-        <v>293.01724</v>
+        <v>293.38794</v>
       </c>
       <c r="R25" t="n">
-        <v>26.117805</v>
+        <v>26.150845</v>
       </c>
       <c r="S25" t="n">
-        <v>77.39298097101589</v>
+        <v>77.49088101831978</v>
       </c>
       <c r="T25" t="n">
-        <v>0.04975442393654794</v>
+        <v>0.07251348391825996</v>
       </c>
       <c r="U25" t="n">
-        <v>0.3238558671722858</v>
+        <v>0.3697025190174488</v>
       </c>
       <c r="V25" t="n">
-        <v>1.358124013707292</v>
+        <v>1.40227282396385</v>
       </c>
       <c r="W25" t="n">
-        <v>0.8417772325972708</v>
+        <v>0.847310397138507</v>
       </c>
       <c r="X25" t="n">
         <v>0.0076</v>
       </c>
       <c r="Y25" t="n">
-        <v>0.84933</v>
+        <v>0.84953004</v>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>2026-08-25T23:44:55.563891+00:00</t>
+          <t>2026-08-26T19:35:29.451215+00:00</t>
         </is>
       </c>
       <c r="AD25" t="inlineStr">
@@ -5711,10 +5702,10 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>257985740800</v>
+        <v>269162332160</v>
       </c>
       <c r="F26" t="n">
-        <v>241.5599975585938</v>
+        <v>252.0249938964844</v>
       </c>
       <c r="G26" t="n">
         <v>5155999744</v>
@@ -5723,7 +5714,7 @@
         <v>0.224</v>
       </c>
       <c r="I26" t="n">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="J26" t="n">
         <v>1.083</v>
@@ -5744,35 +5735,35 @@
         <v>0.07603</v>
       </c>
       <c r="Q26" t="n">
-        <v>246.48979</v>
+        <v>254.5707</v>
       </c>
       <c r="R26" t="n">
-        <v>50.036026</v>
+        <v>52.203712</v>
       </c>
       <c r="S26" t="n">
-        <v>193.3201551039677</v>
+        <v>201.6952705989125</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.07095885355976195</v>
+        <v>-0.05371153605303758</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.2479920408423657</v>
+        <v>-0.1674374780791316</v>
       </c>
       <c r="V26" t="n">
-        <v>0.9515269020910384</v>
+        <v>0.9667940931553007</v>
       </c>
       <c r="W26" t="n">
-        <v>0.7532297844300104</v>
+        <v>0.796841606779054</v>
       </c>
       <c r="X26" t="n">
         <v>0.0007</v>
       </c>
       <c r="Y26" t="n">
-        <v>0.96186996</v>
+        <v>0.96185</v>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>2026-08-25T23:45:00.256605+00:00</t>
+          <t>2026-08-26T19:35:32.355807+00:00</t>
         </is>
       </c>
       <c r="AD26" t="inlineStr">
@@ -5803,10 +5794,10 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1452205801472</v>
+        <v>1471745228800</v>
       </c>
       <c r="F27" t="n">
-        <v>570.0499877929688</v>
+        <v>577.719970703125</v>
       </c>
       <c r="G27" t="n">
         <v>228246994944</v>
@@ -5815,7 +5806,7 @@
         <v>0.28</v>
       </c>
       <c r="I27" t="n">
-        <v>26.55</v>
+        <v>26.56</v>
       </c>
       <c r="J27" t="n">
         <v>-0.134</v>
@@ -5836,35 +5827,35 @@
         <v>0.34827</v>
       </c>
       <c r="Q27" t="n">
-        <v>21.47081</v>
+        <v>21.751505</v>
       </c>
       <c r="R27" t="n">
-        <v>6.362431</v>
+        <v>6.4480376</v>
       </c>
       <c r="S27" t="n">
-        <v>67.37640631415255</v>
+        <v>68.28295578080717</v>
       </c>
       <c r="T27" t="n">
-        <v>-0.04223863731802591</v>
+        <v>-0.02719454518135012</v>
       </c>
       <c r="U27" t="n">
-        <v>-0.06820016862728395</v>
+        <v>-0.08973431938931742</v>
       </c>
       <c r="V27" t="n">
-        <v>-0.1038575283287057</v>
+        <v>-0.09471213622504215</v>
       </c>
       <c r="W27" t="n">
-        <v>-0.2407827733099394</v>
+        <v>-0.2313838002561468</v>
       </c>
       <c r="X27" t="n">
         <v>0.00148</v>
       </c>
       <c r="Y27" t="n">
-        <v>0.79033</v>
+        <v>0.79038</v>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>2026-08-25T23:44:58.005827+00:00</t>
+          <t>2026-08-26T19:35:30.811396+00:00</t>
         </is>
       </c>
       <c r="AD27" t="inlineStr">
@@ -5895,10 +5886,10 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>188764913664</v>
+        <v>193876557824</v>
       </c>
       <c r="F28" t="n">
-        <v>185.3800048828125</v>
+        <v>190.4199981689453</v>
       </c>
       <c r="G28" t="n">
         <v>5094199808</v>
@@ -5925,32 +5916,32 @@
         <v>-0.022079999</v>
       </c>
       <c r="R28" t="n">
-        <v>37.05487</v>
+        <v>38.058296</v>
       </c>
       <c r="S28" t="n">
-        <v>97.99020859315256</v>
+        <v>100.6437264941749</v>
       </c>
       <c r="T28" t="n">
-        <v>0.01145791203351343</v>
+        <v>0.05724278232000191</v>
       </c>
       <c r="U28" t="n">
-        <v>0.1041918442560559</v>
+        <v>0.1802405013704915</v>
       </c>
       <c r="V28" t="n">
-        <v>1.116633025869426</v>
+        <v>1.174675211065757</v>
       </c>
       <c r="W28" t="n">
-        <v>0.7704558969139306</v>
+        <v>0.8239463159561695</v>
       </c>
       <c r="X28" t="n">
         <v>0.01467</v>
       </c>
       <c r="Y28" t="n">
-        <v>0.76632005</v>
+        <v>0.76657</v>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>2026-08-25T23:44:54.986103+00:00</t>
+          <t>2026-08-26T19:35:29.158946+00:00</t>
         </is>
       </c>
       <c r="AD28" t="inlineStr">
@@ -5981,10 +5972,10 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>216030625792</v>
+        <v>219032289280</v>
       </c>
       <c r="F29" t="n">
-        <v>240.3800048828125</v>
+        <v>243.7200012207031</v>
       </c>
       <c r="G29" t="n">
         <v>8717100032</v>
@@ -6014,35 +6005,35 @@
         <v>0.14479999</v>
       </c>
       <c r="Q29" t="n">
-        <v>82.60481</v>
+        <v>83.75257999999999</v>
       </c>
       <c r="R29" t="n">
-        <v>24.782396</v>
+        <v>25.126738</v>
       </c>
       <c r="S29" t="n">
-        <v>95.18025142296156</v>
+        <v>96.50274486308169</v>
       </c>
       <c r="T29" t="n">
-        <v>0.2376049537683742</v>
+        <v>0.2883649816554943</v>
       </c>
       <c r="U29" t="n">
-        <v>0.1545150694814081</v>
+        <v>0.2268753680737328</v>
       </c>
       <c r="V29" t="n">
-        <v>2.092424028873406</v>
+        <v>2.111393914129264</v>
       </c>
       <c r="W29" t="n">
-        <v>2.302154522205557</v>
+        <v>2.288974769459367</v>
       </c>
       <c r="X29" t="n">
         <v>0.00494</v>
       </c>
       <c r="Y29" t="n">
-        <v>0.82125</v>
+        <v>0.82141995</v>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>2026-08-25T23:45:01.001094+00:00</t>
+          <t>2026-08-26T19:35:32.781834+00:00</t>
         </is>
       </c>
       <c r="AD29" t="inlineStr">
@@ -6073,10 +6064,10 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>131300474880</v>
+        <v>130085683200</v>
       </c>
       <c r="F30" t="n">
-        <v>127</v>
+        <v>125.8249969482422</v>
       </c>
       <c r="G30" t="n">
         <v>14732000256</v>
@@ -6106,35 +6097,35 @@
         <v>0.04063</v>
       </c>
       <c r="Q30" t="n">
-        <v>79.375</v>
+        <v>78.640625</v>
       </c>
       <c r="R30" t="n">
-        <v>8.912603000000001</v>
+        <v>8.830144000000001</v>
       </c>
       <c r="S30" t="n">
-        <v>25.49833241742153</v>
+        <v>25.26242190679415</v>
       </c>
       <c r="T30" t="n">
-        <v>0.2856853772974302</v>
+        <v>0.1919761259789707</v>
       </c>
       <c r="U30" t="n">
-        <v>0.2710168367424073</v>
+        <v>0.2321288049755126</v>
       </c>
       <c r="V30" t="n">
-        <v>0.2599205967760663</v>
+        <v>0.2276807451541731</v>
       </c>
       <c r="W30" t="n">
-        <v>-0.2783599152039051</v>
+        <v>-0.2724019153515419</v>
       </c>
       <c r="X30" t="n">
         <v>0.00176</v>
       </c>
       <c r="Y30" t="n">
-        <v>0.85085</v>
+        <v>0.8513700400000001</v>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>2026-08-25T23:45:05.999518+00:00</t>
+          <t>2026-08-26T19:35:35.492361+00:00</t>
         </is>
       </c>
       <c r="AD30" t="inlineStr">
@@ -6165,10 +6156,10 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>416976961536</v>
+        <v>429074972672</v>
       </c>
       <c r="F31" t="n">
-        <v>144.7599945068359</v>
+        <v>148.9600067138672</v>
       </c>
       <c r="G31" t="n">
         <v>67356999680</v>
@@ -6198,32 +6189,32 @@
         <v>0.36202</v>
       </c>
       <c r="Q31" t="n">
-        <v>24.830189</v>
+        <v>25.550602</v>
       </c>
       <c r="R31" t="n">
-        <v>6.1905513</v>
+        <v>6.3697333</v>
       </c>
       <c r="T31" t="n">
-        <v>0.2588920531882728</v>
+        <v>0.2423686807186241</v>
       </c>
       <c r="U31" t="n">
-        <v>-0.2475726919466725</v>
+        <v>-0.2172275727891279</v>
       </c>
       <c r="V31" t="n">
-        <v>0.03156861753690055</v>
+        <v>0.0264150733113595</v>
       </c>
       <c r="W31" t="n">
-        <v>-0.3780641367460406</v>
+        <v>-0.3567405546600753</v>
       </c>
       <c r="X31" t="n">
         <v>0.40498</v>
       </c>
       <c r="Y31" t="n">
-        <v>0.45811</v>
+        <v>0.45823002</v>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>2026-08-25T23:44:58.547404+00:00</t>
+          <t>2026-08-26T19:35:31.262850+00:00</t>
         </is>
       </c>
       <c r="AD31" t="inlineStr">
@@ -6251,7 +6242,7 @@
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
@@ -6308,22 +6299,27 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>MU</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>100</v>
+        <v>84.2</v>
       </c>
       <c r="C2" t="n">
-        <v>100</v>
+        <v>88.2</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MODERATE</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>price_to_sales, price_to_fcf</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -6337,11 +6333,11 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>MU</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="C3" t="n">
         <v>100</v>
@@ -6352,7 +6348,7 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -6366,7 +6362,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CRDO</t>
+          <t>ANET</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -6395,7 +6391,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ANET</t>
+          <t>CRDO</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -6753,18 +6749,23 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>AMZN</t>
+          <t>SNOW</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>100</v>
+        <v>88.2</v>
       </c>
       <c r="C17" t="n">
-        <v>100</v>
+        <v>88.2</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
           <t>HIGH</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>eps_growth, pe_ratio</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -6782,23 +6783,18 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>SNOW</t>
+          <t>AMZN</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>88.2</v>
+        <v>100</v>
       </c>
       <c r="C18" t="n">
-        <v>88.2</v>
+        <v>100</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
           <t>HIGH</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>eps_growth, pe_ratio</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -6816,14 +6812,14 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>SMCI</t>
+          <t>NET</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>94.09999999999999</v>
+        <v>88.2</v>
       </c>
       <c r="C19" t="n">
-        <v>94.09999999999999</v>
+        <v>88.2</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -6832,7 +6828,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>price_to_fcf</t>
+          <t>eps_growth, pe_ratio</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -6879,23 +6875,18 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>NET</t>
+          <t>ASML</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>88.2</v>
+        <v>100</v>
       </c>
       <c r="C21" t="n">
-        <v>88.2</v>
+        <v>100</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
           <t>HIGH</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>eps_growth, pe_ratio</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -6913,23 +6904,18 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ACMR</t>
+          <t>VRT</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>94.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="C22" t="n">
-        <v>94.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
           <t>HIGH</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>price_to_fcf</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -6947,18 +6933,23 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>VRT</t>
+          <t>ACMR</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>100</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="C23" t="n">
-        <v>100</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
           <t>HIGH</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>price_to_fcf</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -6976,18 +6967,23 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ASML</t>
+          <t>SMCI</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>100</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="C24" t="n">
-        <v>100</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
           <t>HIGH</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>price_to_fcf</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -7289,11 +7285,11 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>MU</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>55.59</v>
+        <v>56.33</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -7306,7 +7302,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>100</v>
+        <v>84.2</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>

--- a/reports/investment_dashboard.xlsx
+++ b/reports/investment_dashboard.xlsx
@@ -525,16 +525,16 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>MU</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Taiwan Semiconductor Manufacturing Company Limited</t>
+          <t>Micron Technology, Inc.</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>55.66</v>
+        <v>56.32</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>418.9500122070312</v>
+        <v>938.4000244140625</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -550,19 +550,24 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>100</v>
+        <v>84.2</v>
       </c>
       <c r="I2" t="n">
-        <v>100</v>
+        <v>88.2</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Revenue Growth; Earnings Fcf; Balance Sheet; Valuation</t>
+          <t>Revenue Growth; Earnings Fcf; Balance Sheet</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
           <t>Industry Growth; Competitive Advantage; Catalysts; Inflation Resilience</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>High market sensitivity / beta</t>
         </is>
       </c>
     </row>
@@ -572,16 +577,16 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>MU</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Micron Technology, Inc.</t>
+          <t>Taiwan Semiconductor Manufacturing Company Limited</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>55.05</v>
+        <v>55.33</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -589,7 +594,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>966.780029296875</v>
+        <v>417.6900024414062</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -597,24 +602,19 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="I3" t="n">
         <v>100</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Revenue Growth; Earnings Fcf; Balance Sheet</t>
+          <t>Revenue Growth; Earnings Fcf; Balance Sheet; Valuation</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
           <t>Industry Growth; Competitive Advantage; Catalysts; Inflation Resilience</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>High market sensitivity / beta</t>
         </is>
       </c>
     </row>
@@ -624,16 +624,16 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>CRDO</t>
+          <t>ANET</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Credo Technology Group Holding Ltd</t>
+          <t>Arista Networks, Inc.</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>52.57</v>
+        <v>53.02</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -641,11 +641,11 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>230.5700073242188</v>
+        <v>202.25</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -656,7 +656,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Revenue Growth; Earnings Fcf; Balance Sheet</t>
+          <t>Revenue Growth; Earnings Fcf; Balance Sheet; Momentum</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -666,7 +666,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Excessive price-to-sales valuation; High market sensitivity / beta</t>
+          <t>Excessive price-to-sales valuation</t>
         </is>
       </c>
     </row>
@@ -676,16 +676,16 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ANET</t>
+          <t>CRDO</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Arista Networks, Inc.</t>
+          <t>Credo Technology Group Holding Ltd</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>52.11</v>
+        <v>52.8</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -693,11 +693,11 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>188.6499938964844</v>
+        <v>226.4900054931641</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -718,7 +718,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Excessive price-to-sales valuation</t>
+          <t>Excessive price-to-sales valuation; High market sensitivity / beta</t>
         </is>
       </c>
     </row>
@@ -737,7 +737,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>52.08</v>
+        <v>51.96</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -745,7 +745,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>179.9400024414062</v>
+        <v>177.5</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>51.21</v>
+        <v>50.85</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>375.739990234375</v>
+        <v>363.1000061035156</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -827,16 +827,16 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>NVDA</t>
+          <t>DELL</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>NVIDIA Corporation</t>
+          <t>Dell Technologies Inc.</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>50.09</v>
+        <v>50.69</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -844,11 +844,11 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>214.7200012207031</v>
+        <v>463.8200073242188</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="H8" t="n">
@@ -859,17 +859,12 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Revenue Growth; Earnings Fcf; Balance Sheet</t>
+          <t>Revenue Growth; Momentum</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Industry Growth; Valuation; Competitive Advantage; Catalysts; Inflation Resilience</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>Excessive price-to-sales valuation; High market sensitivity / beta</t>
+          <t>Industry Growth; Competitive Advantage; Catalysts; Inflation Resilience</t>
         </is>
       </c>
     </row>
@@ -879,16 +874,16 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>DELL</t>
+          <t>NVDA</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Dell Technologies Inc.</t>
+          <t>NVIDIA Corporation</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>49.5</v>
+        <v>49.77</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -896,11 +891,11 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>442.0799865722656</v>
+        <v>209.6600036621094</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="H9" t="n">
@@ -911,17 +906,17 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Revenue Growth; Momentum</t>
+          <t>Revenue Growth; Earnings Fcf; Balance Sheet</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Industry Growth; Competitive Advantage; Catalysts; Inflation Resilience</t>
+          <t>Industry Growth; Valuation; Competitive Advantage; Catalysts; Inflation Resilience</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Very high earnings multiple</t>
+          <t>Excessive price-to-sales valuation; High market sensitivity / beta</t>
         </is>
       </c>
     </row>
@@ -940,7 +935,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>48.25</v>
+        <v>48.13</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -948,7 +943,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>16.38999938964844</v>
+        <v>16.76000022888184</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -987,7 +982,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>47.21</v>
+        <v>47.52</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -995,7 +990,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>473.25</v>
+        <v>480.9299926757812</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -1039,7 +1034,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>46.98</v>
+        <v>46.92</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -1047,7 +1042,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>344.8200073242188</v>
+        <v>342</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -1086,7 +1081,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>45.64</v>
+        <v>45.38</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -1094,7 +1089,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>492.3200073242188</v>
+        <v>479.760009765625</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -1133,7 +1128,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>45.04</v>
+        <v>44.67</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -1141,7 +1136,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>235.6199951171875</v>
+        <v>227.6699981689453</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -1185,7 +1180,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>44.39</v>
+        <v>43.83</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -1193,7 +1188,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>368.4500122070312</v>
+        <v>355.5899963378906</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -1228,16 +1223,16 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>SNOW</t>
+          <t>MDB</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Snowflake Inc.</t>
+          <t>MongoDB, Inc.</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>43.33</v>
+        <v>43.45</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -1245,7 +1240,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>332.7799987792969</v>
+        <v>406.1099853515625</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1260,17 +1255,12 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Revenue Growth; Momentum</t>
+          <t>Balance Sheet; Momentum</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
           <t>Industry Growth; Valuation; Competitive Advantage; Catalysts; Inflation Resilience</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>Excessive price-to-sales valuation</t>
         </is>
       </c>
     </row>
@@ -1280,16 +1270,16 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>AMZN</t>
+          <t>SNOW</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Amazon.com, Inc.</t>
+          <t>Snowflake Inc.</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>42.93</v>
+        <v>43</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -1297,7 +1287,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>258.6300048828125</v>
+        <v>315.3699951171875</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1305,19 +1295,24 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>100</v>
+        <v>88.2</v>
       </c>
       <c r="I17" t="n">
-        <v>100</v>
+        <v>88.2</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Earnings Fcf</t>
+          <t>Revenue Growth; Momentum</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Industry Growth; Competitive Advantage; Catalysts; Inflation Resilience</t>
+          <t>Industry Growth; Valuation; Competitive Advantage; Catalysts; Inflation Resilience</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>Excessive price-to-sales valuation</t>
         </is>
       </c>
     </row>
@@ -1327,16 +1322,16 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>MDB</t>
+          <t>AMZN</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>MongoDB, Inc.</t>
+          <t>Amazon.com, Inc.</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>42.91</v>
+        <v>42.97</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -1344,7 +1339,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>430.8299865722656</v>
+        <v>260.2799987792969</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1352,19 +1347,19 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>88.2</v>
+        <v>100</v>
       </c>
       <c r="I18" t="n">
-        <v>88.2</v>
+        <v>100</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Balance Sheet; Momentum</t>
+          <t>Earnings Fcf</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Industry Growth; Valuation; Competitive Advantage; Catalysts; Inflation Resilience</t>
+          <t>Industry Growth; Competitive Advantage; Catalysts; Inflation Resilience</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1378,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>42.82</v>
+        <v>42.78</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -1391,7 +1386,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>293.1400146484375</v>
+        <v>284.8900146484375</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1426,16 +1421,16 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>ACMR</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>ACM Research, Inc.</t>
+          <t>Microsoft Corporation</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>42.73</v>
+        <v>42.59</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -1443,7 +1438,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>79.41000366210938</v>
+        <v>496.3699951171875</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1451,24 +1446,19 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>94.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="I20" t="n">
-        <v>94.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Revenue Growth</t>
+          <t>Earnings Fcf</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Industry Growth; Competitive Advantage; Catalysts; Inflation Resilience</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>Negative free cash flow / unprofitable growth</t>
+          <t>Industry Growth; Valuation; Competitive Advantage; Catalysts; Inflation Resilience</t>
         </is>
       </c>
     </row>
@@ -1478,16 +1468,16 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>VRT</t>
+          <t>ASML</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Vertiv Holdings Co</t>
+          <t>ASML Holding N.V.</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>42.25</v>
+        <v>42.42</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -1495,7 +1485,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>261.9500122070312</v>
+        <v>1745.640014648438</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1510,17 +1500,12 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Earnings Fcf</t>
+          <t>Earnings Fcf; Balance Sheet</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>Industry Growth; Valuation; Competitive Advantage; Momentum; Catalysts; Inflation Resilience</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>High market sensitivity / beta</t>
+          <t>Industry Growth; Valuation; Competitive Advantage; Catalysts; Inflation Resilience</t>
         </is>
       </c>
     </row>
@@ -1530,16 +1515,16 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>ASML</t>
+          <t>VRT</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>ASML Holding N.V.</t>
+          <t>Vertiv Holdings Co</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>42.2</v>
+        <v>42.27</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -1547,7 +1532,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1763.760009765625</v>
+        <v>263.8099975585938</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1562,12 +1547,17 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Earnings Fcf; Balance Sheet</t>
+          <t>Earnings Fcf</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Industry Growth; Valuation; Competitive Advantage; Catalysts; Inflation Resilience</t>
+          <t>Industry Growth; Valuation; Competitive Advantage; Momentum; Catalysts; Inflation Resilience</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>High market sensitivity / beta</t>
         </is>
       </c>
     </row>
@@ -1577,16 +1567,16 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>SMCI</t>
+          <t>ACMR</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Super Micro Computer, Inc.</t>
+          <t>ACM Research, Inc.</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>41.99</v>
+        <v>42.13</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -1594,7 +1584,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>37.2400016784668</v>
+        <v>79.11000061035156</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1609,12 +1599,12 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Revenue Growth; Valuation</t>
+          <t>Revenue Growth</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Industry Growth; Balance Sheet; Competitive Advantage; Catalysts; Inflation Resilience</t>
+          <t>Industry Growth; Competitive Advantage; Catalysts; Inflation Resilience</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -1629,16 +1619,16 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>SMCI</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Microsoft Corporation</t>
+          <t>Super Micro Computer, Inc.</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>41.89</v>
+        <v>41.9</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -1646,7 +1636,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>483.239990234375</v>
+        <v>37.38999938964844</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1654,19 +1644,24 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>100</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="I24" t="n">
-        <v>100</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Earnings Fcf</t>
+          <t>Revenue Growth; Valuation</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>Industry Growth; Valuation; Competitive Advantage; Catalysts; Inflation Resilience</t>
+          <t>Industry Growth; Balance Sheet; Competitive Advantage; Catalysts; Inflation Resilience</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>Negative free cash flow / unprofitable growth</t>
         </is>
       </c>
     </row>
@@ -1693,7 +1688,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>357.8699951171875</v>
+        <v>339.3099975585938</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1737,7 +1732,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>39.96</v>
+        <v>40.34</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -1745,7 +1740,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>243.3200073242188</v>
+        <v>251.0599975585938</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1789,7 +1784,7 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>39.3</v>
+        <v>39.74</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -1797,7 +1792,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>549.9000244140625</v>
+        <v>576.1400146484375</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1827,16 +1822,16 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>CRWD</t>
+          <t>MRVL</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>CrowdStrike Holdings, Inc.</t>
+          <t>Marvell Technology, Inc.</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>39.29</v>
+        <v>39.6</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -1844,22 +1839,22 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>191.9499969482422</v>
+        <v>245.1100006103516</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>88.2</v>
+        <v>100</v>
       </c>
       <c r="I28" t="n">
-        <v>88.2</v>
+        <v>100</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Balance Sheet</t>
+          <t>Revenue Growth; Momentum</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -1869,7 +1864,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>Excessive price-to-sales valuation</t>
+          <t>Excessive price-to-sales valuation; High market sensitivity / beta</t>
         </is>
       </c>
     </row>
@@ -1879,16 +1874,16 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>MRVL</t>
+          <t>CRWD</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Marvell Technology, Inc.</t>
+          <t>CrowdStrike Holdings, Inc.</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>38.72</v>
+        <v>39.52</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -1896,22 +1891,22 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>237.0399932861328</v>
+        <v>189.1799926757812</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>100</v>
+        <v>88.2</v>
       </c>
       <c r="I29" t="n">
-        <v>100</v>
+        <v>88.2</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Revenue Growth</t>
+          <t>Balance Sheet</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -1921,7 +1916,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>Excessive price-to-sales valuation; High market sensitivity / beta</t>
+          <t>Excessive price-to-sales valuation</t>
         </is>
       </c>
     </row>
@@ -1940,7 +1935,7 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>36.58</v>
+        <v>36</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -1948,7 +1943,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>128.4799957275391</v>
+        <v>125.8000030517578</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1963,7 +1958,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>Earnings Fcf; Industry Growth; Valuation; Competitive Advantage; Catalysts; Inflation Resilience</t>
+          <t>Earnings Fcf; Industry Growth; Competitive Advantage; Catalysts; Inflation Resilience</t>
         </is>
       </c>
     </row>
@@ -1982,7 +1977,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>30.88</v>
+        <v>31.51</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -1990,7 +1985,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>146.4700012207031</v>
+        <v>148.8699951171875</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -2120,7 +2115,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>MU</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -2133,19 +2128,19 @@
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>8.84</v>
+        <v>9.02</v>
       </c>
       <c r="F2" t="n">
-        <v>8.67</v>
+        <v>7.19</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>5.46</v>
+        <v>6.61</v>
       </c>
       <c r="I2" t="n">
-        <v>2.69</v>
+        <v>3.5</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -2154,13 +2149,13 @@
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>55.66</v>
+        <v>56.32</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>MU</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -2173,19 +2168,19 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>9.02</v>
+        <v>8.84</v>
       </c>
       <c r="F3" t="n">
-        <v>4.82</v>
+        <v>8.68</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>7.71</v>
+        <v>5.12</v>
       </c>
       <c r="I3" t="n">
-        <v>3.5</v>
+        <v>2.69</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -2194,13 +2189,13 @@
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>55.05</v>
+        <v>55.33</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CRDO</t>
+          <t>ANET</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -2213,19 +2208,19 @@
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>9.91</v>
+        <v>10</v>
       </c>
       <c r="F4" t="n">
-        <v>2.44</v>
+        <v>0.78</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>6.66</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>3.56</v>
+        <v>3.63</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -2234,13 +2229,13 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>52.57</v>
+        <v>53.02</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ANET</t>
+          <t>CRDO</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -2253,19 +2248,19 @@
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>10</v>
+        <v>9.91</v>
       </c>
       <c r="F5" t="n">
-        <v>0.84</v>
+        <v>2.46</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>7.63</v>
+        <v>6.87</v>
       </c>
       <c r="I5" t="n">
-        <v>3.64</v>
+        <v>3.56</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -2274,7 +2269,7 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>52.11</v>
+        <v>52.8</v>
       </c>
     </row>
     <row r="6">
@@ -2296,13 +2291,13 @@
         <v>9.890000000000001</v>
       </c>
       <c r="F6" t="n">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>8.18</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="I6" t="n">
         <v>3.35</v>
@@ -2314,7 +2309,7 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>52.08</v>
+        <v>51.96</v>
       </c>
     </row>
     <row r="7">
@@ -2336,13 +2331,13 @@
         <v>8.9</v>
       </c>
       <c r="F7" t="n">
-        <v>2.85</v>
+        <v>2.95</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>5.71</v>
+        <v>5.25</v>
       </c>
       <c r="I7" t="n">
         <v>3.75</v>
@@ -2354,38 +2349,38 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>51.21</v>
+        <v>50.85</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>NVDA</t>
+          <t>DELL</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>15</v>
       </c>
       <c r="C8" t="n">
-        <v>15</v>
+        <v>11.48</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>9.029999999999999</v>
+        <v>6.33</v>
       </c>
       <c r="F8" t="n">
-        <v>3.15</v>
+        <v>5.77</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>4.47</v>
+        <v>8.57</v>
       </c>
       <c r="I8" t="n">
-        <v>3.44</v>
+        <v>3.54</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -2394,38 +2389,38 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>50.09</v>
+        <v>50.69</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>DELL</t>
+          <t>NVDA</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>15</v>
       </c>
       <c r="C9" t="n">
-        <v>11.48</v>
+        <v>15</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>6.33</v>
+        <v>9.029999999999999</v>
       </c>
       <c r="F9" t="n">
-        <v>4.97</v>
+        <v>3.22</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>8.18</v>
+        <v>4.08</v>
       </c>
       <c r="I9" t="n">
-        <v>3.54</v>
+        <v>3.44</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -2434,7 +2429,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>49.5</v>
+        <v>49.77</v>
       </c>
     </row>
     <row r="10">
@@ -2456,7 +2451,7 @@
         <v>9.699999999999999</v>
       </c>
       <c r="F10" t="n">
-        <v>7.12</v>
+        <v>7</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -2474,7 +2469,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>48.25</v>
+        <v>48.13</v>
       </c>
     </row>
     <row r="11">
@@ -2496,13 +2491,13 @@
         <v>8.77</v>
       </c>
       <c r="F11" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>5.77</v>
+        <v>6.1</v>
       </c>
       <c r="I11" t="n">
         <v>3.45</v>
@@ -2514,7 +2509,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>47.21</v>
+        <v>47.52</v>
       </c>
     </row>
     <row r="12">
@@ -2536,13 +2531,13 @@
         <v>8.34</v>
       </c>
       <c r="F12" t="n">
-        <v>4.39</v>
+        <v>4.42</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>4.77</v>
+        <v>4.68</v>
       </c>
       <c r="I12" t="n">
         <v>3.53</v>
@@ -2554,7 +2549,7 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>46.98</v>
+        <v>46.92</v>
       </c>
     </row>
     <row r="13">
@@ -2576,16 +2571,16 @@
         <v>7.78</v>
       </c>
       <c r="F13" t="n">
-        <v>1.89</v>
+        <v>2.05</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>6.2</v>
+        <v>5.79</v>
       </c>
       <c r="I13" t="n">
-        <v>3.59</v>
+        <v>3.58</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -2594,7 +2589,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>45.64</v>
+        <v>45.38</v>
       </c>
     </row>
     <row r="14">
@@ -2616,13 +2611,13 @@
         <v>8.98</v>
       </c>
       <c r="F14" t="n">
-        <v>0.83</v>
+        <v>0.86</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>6.45</v>
+        <v>6.05</v>
       </c>
       <c r="I14" t="n">
         <v>3.67</v>
@@ -2634,7 +2629,7 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>45.04</v>
+        <v>44.67</v>
       </c>
     </row>
     <row r="15">
@@ -2656,13 +2651,13 @@
         <v>6.16</v>
       </c>
       <c r="F15" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>3.67</v>
+        <v>3.07</v>
       </c>
       <c r="I15" t="n">
         <v>3.53</v>
@@ -2674,17 +2669,17 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>44.39</v>
+        <v>43.83</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>SNOW</t>
+          <t>MDB</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>14.44</v>
+        <v>11.32</v>
       </c>
       <c r="C16" t="n">
         <v>7.5</v>
@@ -2693,19 +2688,19 @@
         <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>7.58</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="F16" t="n">
-        <v>0.97</v>
+        <v>1.97</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>9.279999999999999</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="I16" t="n">
-        <v>3.56</v>
+        <v>3.73</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -2714,38 +2709,38 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>43.33</v>
+        <v>43.45</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>AMZN</t>
+          <t>SNOW</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>9.220000000000001</v>
+        <v>14.44</v>
       </c>
       <c r="C17" t="n">
-        <v>12.28</v>
+        <v>7.5</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>6.64</v>
+        <v>7.58</v>
       </c>
       <c r="F17" t="n">
-        <v>6.52</v>
+        <v>1.03</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>4.8</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="I17" t="n">
-        <v>3.47</v>
+        <v>3.56</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2754,38 +2749,38 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>42.93</v>
+        <v>43</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>MDB</t>
+          <t>AMZN</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>11.32</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="C18" t="n">
-        <v>7.5</v>
+        <v>12.28</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>9.880000000000001</v>
+        <v>6.64</v>
       </c>
       <c r="F18" t="n">
-        <v>1.69</v>
+        <v>6.5</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>8.779999999999999</v>
+        <v>4.86</v>
       </c>
       <c r="I18" t="n">
-        <v>3.74</v>
+        <v>3.47</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2794,7 +2789,7 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>42.91</v>
+        <v>42.97</v>
       </c>
     </row>
     <row r="19">
@@ -2816,13 +2811,13 @@
         <v>7.71</v>
       </c>
       <c r="F19" t="n">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>8.390000000000001</v>
+        <v>8.34</v>
       </c>
       <c r="I19" t="n">
         <v>3.64</v>
@@ -2834,38 +2829,38 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>42.82</v>
+        <v>42.78</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ACMR</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>15</v>
+        <v>8.51</v>
       </c>
       <c r="C20" t="n">
-        <v>7.83</v>
+        <v>14.63</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>4.02</v>
+        <v>6.87</v>
       </c>
       <c r="F20" t="n">
-        <v>6.86</v>
+        <v>2.94</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>5.39</v>
+        <v>6.19</v>
       </c>
       <c r="I20" t="n">
-        <v>3.63</v>
+        <v>3.45</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2874,38 +2869,38 @@
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>42.73</v>
+        <v>42.59</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>VRT</t>
+          <t>ASML</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>10.91</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="C21" t="n">
-        <v>13.39</v>
+        <v>14.28</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>7.41</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="F21" t="n">
-        <v>3.35</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>3.63</v>
+        <v>6</v>
       </c>
       <c r="I21" t="n">
-        <v>3.56</v>
+        <v>2.76</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2914,38 +2909,38 @@
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>42.25</v>
+        <v>42.42</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ASML</t>
+          <t>VRT</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>9.859999999999999</v>
+        <v>10.91</v>
       </c>
       <c r="C22" t="n">
-        <v>14.28</v>
+        <v>13.39</v>
       </c>
       <c r="D22" t="n">
         <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>8.960000000000001</v>
+        <v>7.41</v>
       </c>
       <c r="F22" t="n">
-        <v>0.5600000000000001</v>
+        <v>3.32</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>5.79</v>
+        <v>3.68</v>
       </c>
       <c r="I22" t="n">
-        <v>2.75</v>
+        <v>3.56</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2954,38 +2949,38 @@
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>42.2</v>
+        <v>42.27</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>SMCI</t>
+          <t>ACMR</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>15</v>
       </c>
       <c r="C23" t="n">
-        <v>7.23</v>
+        <v>7.83</v>
       </c>
       <c r="D23" t="n">
         <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>2.23</v>
+        <v>4.02</v>
       </c>
       <c r="F23" t="n">
-        <v>9.880000000000001</v>
+        <v>6.88</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>4.11</v>
+        <v>4.77</v>
       </c>
       <c r="I23" t="n">
-        <v>3.54</v>
+        <v>3.63</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2994,38 +2989,38 @@
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>41.99</v>
+        <v>42.13</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>SMCI</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>8.51</v>
+        <v>15</v>
       </c>
       <c r="C24" t="n">
-        <v>14.63</v>
+        <v>7.23</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>6.87</v>
+        <v>2.23</v>
       </c>
       <c r="F24" t="n">
-        <v>3.06</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>5.37</v>
+        <v>4.02</v>
       </c>
       <c r="I24" t="n">
-        <v>3.45</v>
+        <v>3.54</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -3034,7 +3029,7 @@
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>41.89</v>
+        <v>41.9</v>
       </c>
     </row>
     <row r="25">
@@ -3056,13 +3051,13 @@
         <v>7.97</v>
       </c>
       <c r="F25" t="n">
-        <v>0.57</v>
+        <v>0.6</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>8.369999999999999</v>
+        <v>8.34</v>
       </c>
       <c r="I25" t="n">
         <v>3.57</v>
@@ -3102,7 +3097,7 @@
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>5.04</v>
+        <v>5.42</v>
       </c>
       <c r="I26" t="n">
         <v>3.7</v>
@@ -3114,7 +3109,7 @@
         <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>39.96</v>
+        <v>40.34</v>
       </c>
     </row>
     <row r="27">
@@ -3136,13 +3131,13 @@
         <v>7.23</v>
       </c>
       <c r="F27" t="n">
-        <v>5.82</v>
+        <v>5.59</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>0.38</v>
+        <v>1.05</v>
       </c>
       <c r="I27" t="n">
         <v>3.49</v>
@@ -3154,38 +3149,38 @@
         <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>39.3</v>
+        <v>39.74</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>CRWD</t>
+          <t>MRVL</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>11.47</v>
+        <v>12.23</v>
       </c>
       <c r="C28" t="n">
-        <v>7.5</v>
+        <v>7.41</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>9.24</v>
+        <v>7.11</v>
       </c>
       <c r="F28" t="n">
-        <v>0.44</v>
+        <v>0.55</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>7.16</v>
+        <v>8.77</v>
       </c>
       <c r="I28" t="n">
-        <v>3.48</v>
+        <v>3.53</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3194,38 +3189,38 @@
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>39.29</v>
+        <v>39.6</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>MRVL</t>
+          <t>CRWD</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>12.23</v>
+        <v>11.47</v>
       </c>
       <c r="C29" t="n">
-        <v>7.41</v>
+        <v>7.5</v>
       </c>
       <c r="D29" t="n">
         <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>7.11</v>
+        <v>9.24</v>
       </c>
       <c r="F29" t="n">
-        <v>0.57</v>
+        <v>0.45</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>7.87</v>
+        <v>7.38</v>
       </c>
       <c r="I29" t="n">
-        <v>3.53</v>
+        <v>3.48</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3234,7 +3229,7 @@
         <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>38.72</v>
+        <v>39.52</v>
       </c>
     </row>
     <row r="30">
@@ -3256,13 +3251,13 @@
         <v>6.78</v>
       </c>
       <c r="F30" t="n">
-        <v>3.99</v>
+        <v>4.09</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>5.68</v>
+        <v>5</v>
       </c>
       <c r="I30" t="n">
         <v>3.57</v>
@@ -3274,7 +3269,7 @@
         <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>36.58</v>
+        <v>36</v>
       </c>
     </row>
     <row r="31">
@@ -3296,13 +3291,13 @@
         <v>0.8</v>
       </c>
       <c r="F31" t="n">
-        <v>6.51</v>
+        <v>6.41</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>1.85</v>
+        <v>2.58</v>
       </c>
       <c r="I31" t="n">
         <v>3.58</v>
@@ -3314,7 +3309,7 @@
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>30.88</v>
+        <v>31.51</v>
       </c>
     </row>
   </sheetData>
@@ -3348,10 +3343,10 @@
     <col width="15" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="18" customWidth="1" min="16" max="16"/>
-    <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="11" customWidth="1" min="17" max="17"/>
     <col width="16" customWidth="1" min="18" max="18"/>
     <col width="19" customWidth="1" min="19" max="19"/>
-    <col width="23" customWidth="1" min="20" max="20"/>
+    <col width="22" customWidth="1" min="20" max="20"/>
     <col width="23" customWidth="1" min="21" max="21"/>
     <col width="22" customWidth="1" min="22" max="22"/>
     <col width="22" customWidth="1" min="23" max="23"/>
@@ -3519,12 +3514,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>MU</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Taiwan Semiconductor Manufacturing Company Limited</t>
+          <t>Micron Technology, Inc.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -3537,69 +3532,60 @@
           <t>Semiconductors</t>
         </is>
       </c>
-      <c r="E2" t="n">
-        <v>2172873342976</v>
-      </c>
       <c r="F2" t="n">
-        <v>418.9500122070312</v>
+        <v>938.4000244140625</v>
       </c>
       <c r="G2" t="n">
-        <v>4440492343296</v>
+        <v>90273996800</v>
       </c>
       <c r="H2" t="n">
-        <v>0.36</v>
+        <v>3.457</v>
       </c>
       <c r="I2" t="n">
-        <v>13.41</v>
+        <v>44.22</v>
       </c>
       <c r="J2" t="n">
-        <v>0.774</v>
+        <v>13.685</v>
       </c>
       <c r="K2" t="n">
-        <v>730826014720</v>
+        <v>7639499776</v>
       </c>
       <c r="M2" t="n">
-        <v>3518010228736</v>
+        <v>26022000640</v>
       </c>
       <c r="N2" t="n">
-        <v>1068558516224</v>
+        <v>6376000000</v>
       </c>
       <c r="O2" t="n">
-        <v>0.6423</v>
+        <v>0.7256899999999999</v>
       </c>
       <c r="P2" t="n">
-        <v>0.60344005</v>
+        <v>0.80370003</v>
       </c>
       <c r="Q2" t="n">
-        <v>31.241611</v>
-      </c>
-      <c r="R2" t="n">
-        <v>0.48933163</v>
-      </c>
-      <c r="S2" t="n">
-        <v>2.97317459861974</v>
+        <v>21.221167</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.005365445487747644</v>
+        <v>0.04243502742615601</v>
       </c>
       <c r="U2" t="n">
-        <v>0.03809732083456407</v>
+        <v>0.01091583583902134</v>
       </c>
       <c r="V2" t="n">
-        <v>0.1684963370842598</v>
+        <v>1.246210835388741</v>
       </c>
       <c r="W2" t="n">
-        <v>0.8632972961454419</v>
+        <v>7.067864058049175</v>
       </c>
       <c r="X2" t="n">
-        <v>0.00013</v>
+        <v>0.00242</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.15498</v>
+        <v>0.79987</v>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>2026-08-23T21:04:23.151921+00:00</t>
+          <t>2026-08-27T00:34:38.466961+00:00</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
@@ -3611,12 +3597,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>MU</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Micron Technology, Inc.</t>
+          <t>Taiwan Semiconductor Manufacturing Company Limited</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -3630,68 +3616,68 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1091874717696</v>
+        <v>2166338355200</v>
       </c>
       <c r="F3" t="n">
-        <v>966.780029296875</v>
+        <v>417.6900024414062</v>
       </c>
       <c r="G3" t="n">
-        <v>90273996800</v>
+        <v>4440492343296</v>
       </c>
       <c r="H3" t="n">
-        <v>3.457</v>
+        <v>0.36</v>
       </c>
       <c r="I3" t="n">
-        <v>44.28</v>
+        <v>13.45</v>
       </c>
       <c r="J3" t="n">
-        <v>13.685</v>
+        <v>0.774</v>
       </c>
       <c r="K3" t="n">
-        <v>7639499776</v>
+        <v>730826014720</v>
       </c>
       <c r="M3" t="n">
-        <v>26022000640</v>
+        <v>3518010228736</v>
       </c>
       <c r="N3" t="n">
-        <v>6376000000</v>
+        <v>1068558516224</v>
       </c>
       <c r="O3" t="n">
-        <v>0.7256899999999999</v>
+        <v>0.6423</v>
       </c>
       <c r="P3" t="n">
-        <v>0.80370003</v>
+        <v>0.60344005</v>
       </c>
       <c r="Q3" t="n">
-        <v>21.833334</v>
+        <v>31.05502</v>
       </c>
       <c r="R3" t="n">
-        <v>12.0951185</v>
+        <v>0.48785993</v>
       </c>
       <c r="S3" t="n">
-        <v>142.924896879531</v>
+        <v>2.964232678594488</v>
       </c>
       <c r="T3" t="n">
-        <v>0.007608338867642228</v>
+        <v>0.04660604443657346</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2875215850577266</v>
+        <v>-0.009608562530477482</v>
       </c>
       <c r="V3" t="n">
-        <v>1.317802614597143</v>
+        <v>0.08839375381353065</v>
       </c>
       <c r="W3" t="n">
-        <v>7.362827376540883</v>
+        <v>0.7690575911628716</v>
       </c>
       <c r="X3" t="n">
-        <v>0.00242</v>
+        <v>0.00013</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.7999000000000001</v>
+        <v>0.15493</v>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>2026-08-23T21:04:19.791860+00:00</t>
+          <t>2026-08-27T00:34:41.669974+00:00</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
@@ -3703,12 +3689,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CRDO</t>
+          <t>ANET</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Credo Technology Group Holding Ltd</t>
+          <t>Arista Networks, Inc.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -3718,72 +3704,72 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Semiconductors</t>
+          <t>Computer Hardware</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>42996211712</v>
+        <v>255082692608</v>
       </c>
       <c r="F4" t="n">
-        <v>230.5700073242188</v>
+        <v>202.25</v>
       </c>
       <c r="G4" t="n">
-        <v>1335116032</v>
+        <v>10540800000</v>
       </c>
       <c r="H4" t="n">
-        <v>1.57</v>
+        <v>0.377</v>
       </c>
       <c r="I4" t="n">
-        <v>2.51</v>
+        <v>3.15</v>
       </c>
       <c r="J4" t="n">
-        <v>3.432</v>
+        <v>0.357</v>
       </c>
       <c r="K4" t="n">
-        <v>250810128</v>
+        <v>3891512576</v>
       </c>
       <c r="M4" t="n">
-        <v>1443286016</v>
+        <v>13343299584</v>
       </c>
       <c r="N4" t="n">
-        <v>25448000</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>0.68035007</v>
+        <v>0.63004</v>
       </c>
       <c r="P4" t="n">
-        <v>0.35661998</v>
+        <v>0.45393002</v>
       </c>
       <c r="Q4" t="n">
-        <v>91.86056000000001</v>
+        <v>64.206345</v>
       </c>
       <c r="R4" t="n">
-        <v>32.2041</v>
+        <v>24.199556</v>
       </c>
       <c r="S4" t="n">
-        <v>171.4293280532914</v>
+        <v>65.54846929730184</v>
       </c>
       <c r="T4" t="n">
-        <v>0.01007580062517777</v>
+        <v>0.1844109071571998</v>
       </c>
       <c r="U4" t="n">
-        <v>0.05567512228478999</v>
+        <v>0.310673340677118</v>
       </c>
       <c r="V4" t="n">
-        <v>0.7646563666145272</v>
+        <v>0.5706297529668847</v>
       </c>
       <c r="W4" t="n">
-        <v>1.079830471358389</v>
+        <v>0.5062932417101436</v>
       </c>
       <c r="X4" t="n">
-        <v>0.108789995</v>
+        <v>0.17247999</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.74186</v>
+        <v>0.73305</v>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>2026-08-23T21:04:20.399434+00:00</t>
+          <t>2026-08-27T00:34:42.843660+00:00</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
@@ -3795,12 +3781,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ANET</t>
+          <t>CRDO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Arista Networks, Inc.</t>
+          <t>Credo Technology Group Holding Ltd</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -3810,72 +3796,72 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Computer Hardware</t>
+          <t>Semiconductors</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>237930037248</v>
+        <v>42565324800</v>
       </c>
       <c r="F5" t="n">
-        <v>188.6499938964844</v>
+        <v>226.4900054931641</v>
       </c>
       <c r="G5" t="n">
-        <v>10540800000</v>
+        <v>1335116032</v>
       </c>
       <c r="H5" t="n">
-        <v>0.377</v>
+        <v>1.57</v>
       </c>
       <c r="I5" t="n">
-        <v>3.17</v>
+        <v>2.51</v>
       </c>
       <c r="J5" t="n">
-        <v>0.357</v>
+        <v>3.432</v>
       </c>
       <c r="K5" t="n">
-        <v>3891512576</v>
+        <v>250810128</v>
       </c>
       <c r="M5" t="n">
-        <v>13343299584</v>
+        <v>1443286016</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>25448000</v>
       </c>
       <c r="O5" t="n">
-        <v>0.63004</v>
+        <v>0.68035007</v>
       </c>
       <c r="P5" t="n">
-        <v>0.45393002</v>
+        <v>0.35661998</v>
       </c>
       <c r="Q5" t="n">
-        <v>59.511036</v>
+        <v>90.23506</v>
       </c>
       <c r="R5" t="n">
-        <v>22.572294</v>
+        <v>31.881367</v>
       </c>
       <c r="S5" t="n">
-        <v>61.14076020603871</v>
+        <v>169.7113475417548</v>
       </c>
       <c r="T5" t="n">
-        <v>0.07880139054194135</v>
+        <v>0.08816184374615799</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2247613801957697</v>
+        <v>0.02377620515846823</v>
       </c>
       <c r="V5" t="n">
-        <v>0.3746994080728259</v>
+        <v>0.8744517260691917</v>
       </c>
       <c r="W5" t="n">
-        <v>0.428841896846748</v>
+        <v>0.8858451987571647</v>
       </c>
       <c r="X5" t="n">
-        <v>0.17241</v>
+        <v>0.10795</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.73608</v>
+        <v>0.73627</v>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>2026-08-23T21:04:24.433284+00:00</t>
+          <t>2026-08-27T00:34:39.009148+00:00</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
@@ -3906,10 +3892,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>432406331392</v>
+        <v>426542858240</v>
       </c>
       <c r="F6" t="n">
-        <v>179.9400024414062</v>
+        <v>177.5</v>
       </c>
       <c r="G6" t="n">
         <v>6155940864</v>
@@ -3939,35 +3925,35 @@
         <v>0.47120997</v>
       </c>
       <c r="Q6" t="n">
-        <v>153.79488</v>
+        <v>151.70941</v>
       </c>
       <c r="R6" t="n">
-        <v>70.24212</v>
+        <v>69.28963</v>
       </c>
       <c r="S6" t="n">
-        <v>200.2711443511633</v>
+        <v>197.5554475799271</v>
       </c>
       <c r="T6" t="n">
-        <v>0.4444890654429585</v>
+        <v>0.3495020272739402</v>
       </c>
       <c r="U6" t="n">
-        <v>0.3145820866638545</v>
+        <v>0.3395216010732165</v>
       </c>
       <c r="V6" t="n">
-        <v>0.3339758562947623</v>
+        <v>0.3776777789910486</v>
       </c>
       <c r="W6" t="n">
-        <v>0.1521322248679389</v>
+        <v>0.1033754297729554</v>
       </c>
       <c r="X6" t="n">
         <v>0.03477</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.64834</v>
+        <v>0.64858</v>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>2026-08-23T21:04:18.311436+00:00</t>
+          <t>2026-08-27T00:34:37.231816+00:00</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr">
@@ -3998,10 +3984,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>58743472128</v>
+        <v>56767328256</v>
       </c>
       <c r="F7" t="n">
-        <v>375.739990234375</v>
+        <v>363.1000061035156</v>
       </c>
       <c r="G7" t="n">
         <v>4464031232</v>
@@ -4031,35 +4017,35 @@
         <v>0.33161</v>
       </c>
       <c r="Q7" t="n">
-        <v>51.541836</v>
+        <v>49.807957</v>
       </c>
       <c r="R7" t="n">
-        <v>13.159287</v>
+        <v>12.716606</v>
       </c>
       <c r="S7" t="n">
-        <v>134.307248874099</v>
+        <v>129.7891222259259</v>
       </c>
       <c r="T7" t="n">
-        <v>0.01699777763368582</v>
+        <v>0.08462531893408998</v>
       </c>
       <c r="U7" t="n">
-        <v>0.04826466821541975</v>
+        <v>-0.03387164655181729</v>
       </c>
       <c r="V7" t="n">
-        <v>0.1898762435729664</v>
+        <v>0.1037623091873037</v>
       </c>
       <c r="W7" t="n">
-        <v>2.446494888446049</v>
+        <v>2.069130006189561</v>
       </c>
       <c r="X7" t="n">
         <v>0.00202</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.00457</v>
+        <v>1.00462</v>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>2026-08-23T21:04:20.731674+00:00</t>
+          <t>2026-08-27T00:34:39.309114+00:00</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr">
@@ -4071,12 +4057,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>NVDA</t>
+          <t>DELL</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>NVIDIA Corporation</t>
+          <t>Dell Technologies Inc.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -4086,72 +4072,72 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Semiconductors</t>
+          <t>Computer Hardware</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5200733011968</v>
+        <v>299693768704</v>
       </c>
       <c r="F8" t="n">
-        <v>214.7200012207031</v>
+        <v>463.8200073242188</v>
       </c>
       <c r="G8" t="n">
-        <v>253491003392</v>
+        <v>134001999872</v>
       </c>
       <c r="H8" t="n">
-        <v>0.852</v>
+        <v>0.875</v>
       </c>
       <c r="I8" t="n">
-        <v>6.53</v>
+        <v>12.55</v>
       </c>
       <c r="J8" t="n">
-        <v>2.145</v>
+        <v>2.825</v>
       </c>
       <c r="K8" t="n">
-        <v>46335873024</v>
+        <v>5434124800</v>
       </c>
       <c r="M8" t="n">
-        <v>53171998720</v>
+        <v>11580999680</v>
       </c>
       <c r="N8" t="n">
-        <v>12814000128</v>
+        <v>31924000768</v>
       </c>
       <c r="O8" t="n">
-        <v>0.74144995</v>
+        <v>0.19212</v>
       </c>
       <c r="P8" t="n">
-        <v>0.65596</v>
+        <v>0.08857000600000001</v>
       </c>
       <c r="Q8" t="n">
-        <v>32.88208</v>
+        <v>36.957767</v>
       </c>
       <c r="R8" t="n">
-        <v>20.51644</v>
+        <v>2.2364874</v>
       </c>
       <c r="S8" t="n">
-        <v>112.2398839722787</v>
+        <v>55.15032866083605</v>
       </c>
       <c r="T8" t="n">
-        <v>0.01254363714389073</v>
+        <v>0.08645851197088117</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.001670682268214541</v>
+        <v>0.521637737090519</v>
       </c>
       <c r="V8" t="n">
-        <v>0.144129303232654</v>
+        <v>2.890666027542702</v>
       </c>
       <c r="W8" t="n">
-        <v>0.2287460719461247</v>
+        <v>2.586002079856828</v>
       </c>
       <c r="X8" t="n">
-        <v>0.03991</v>
+        <v>0.07491</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.71262</v>
+        <v>0.75615</v>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>2026-08-23T21:04:18.001839+00:00</t>
+          <t>2026-08-27T00:34:43.138674+00:00</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr">
@@ -4163,12 +4149,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>DELL</t>
+          <t>NVDA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Dell Technologies Inc.</t>
+          <t>NVIDIA Corporation</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -4178,72 +4164,72 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Computer Hardware</t>
+          <t>Semiconductors</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>285646618624</v>
+        <v>5078174924800</v>
       </c>
       <c r="F9" t="n">
-        <v>442.0799865722656</v>
+        <v>209.6600036621094</v>
       </c>
       <c r="G9" t="n">
-        <v>134001999872</v>
+        <v>253491003392</v>
       </c>
       <c r="H9" t="n">
-        <v>0.875</v>
+        <v>0.852</v>
       </c>
       <c r="I9" t="n">
-        <v>0.49</v>
+        <v>6.44</v>
       </c>
       <c r="J9" t="n">
-        <v>2.825</v>
+        <v>2.145</v>
       </c>
       <c r="K9" t="n">
-        <v>5434124800</v>
+        <v>46335873024</v>
       </c>
       <c r="M9" t="n">
-        <v>11580999680</v>
+        <v>53171998720</v>
       </c>
       <c r="N9" t="n">
-        <v>31924000768</v>
+        <v>12814000128</v>
       </c>
       <c r="O9" t="n">
-        <v>0.19212</v>
+        <v>0.74144995</v>
       </c>
       <c r="P9" t="n">
-        <v>0.08857000600000001</v>
+        <v>0.65596</v>
       </c>
       <c r="Q9" t="n">
-        <v>902.20404</v>
+        <v>32.5559</v>
       </c>
       <c r="R9" t="n">
-        <v>2.1316593</v>
+        <v>20.032959</v>
       </c>
       <c r="S9" t="n">
-        <v>52.56534016738077</v>
+        <v>109.5948903815781</v>
       </c>
       <c r="T9" t="n">
-        <v>0.0006337681915646876</v>
+        <v>0.06691776257118565</v>
       </c>
       <c r="U9" t="n">
-        <v>0.5000864673161829</v>
+        <v>-0.01267941170679843</v>
       </c>
       <c r="V9" t="n">
-        <v>2.73072935680286</v>
+        <v>0.08849214566613828</v>
       </c>
       <c r="W9" t="n">
-        <v>2.50241270126798</v>
+        <v>0.1549719021363523</v>
       </c>
       <c r="X9" t="n">
-        <v>0.07491</v>
+        <v>0.03991</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.75602996</v>
+        <v>0.71202004</v>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>2026-08-23T21:04:24.705796+00:00</t>
+          <t>2026-08-27T00:34:36.952567+00:00</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr">
@@ -4274,10 +4260,10 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>8491990528</v>
+        <v>8683695104</v>
       </c>
       <c r="F10" t="n">
-        <v>16.38999938964844</v>
+        <v>16.76000022888184</v>
       </c>
       <c r="G10" t="n">
         <v>1672329984</v>
@@ -4304,35 +4290,35 @@
         <v>0.07274</v>
       </c>
       <c r="Q10" t="n">
-        <v>27.316664</v>
+        <v>27.933332</v>
       </c>
       <c r="R10" t="n">
-        <v>5.0779395</v>
+        <v>5.1925726</v>
       </c>
       <c r="S10" t="n">
-        <v>16.60039142875248</v>
+        <v>16.97514114023532</v>
       </c>
       <c r="T10" t="n">
-        <v>0.5317756711973327</v>
+        <v>0.4423408256406751</v>
       </c>
       <c r="U10" t="n">
-        <v>0.4995424457478865</v>
+        <v>0.5017921557380944</v>
       </c>
       <c r="V10" t="n">
-        <v>0.4620873625222328</v>
+        <v>0.6594059005810615</v>
       </c>
       <c r="W10" t="n">
-        <v>0.5050504015546731</v>
+        <v>0.5489834289828155</v>
       </c>
       <c r="X10" t="n">
         <v>0.09236999999999999</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.91146004</v>
+        <v>0.91159</v>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>2026-08-23T21:04:26.909921+00:00</t>
+          <t>2026-08-27T00:34:45.352446+00:00</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr">
@@ -4363,10 +4349,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>772568776704</v>
+        <v>785106206720</v>
       </c>
       <c r="F11" t="n">
-        <v>473.25</v>
+        <v>480.9299926757812</v>
       </c>
       <c r="G11" t="n">
         <v>41305001984</v>
@@ -4396,35 +4382,35 @@
         <v>0.1725</v>
       </c>
       <c r="Q11" t="n">
-        <v>120.419846</v>
+        <v>122.37404</v>
       </c>
       <c r="R11" t="n">
-        <v>18.704</v>
+        <v>19.007534</v>
       </c>
       <c r="S11" t="n">
-        <v>87.37983458255972</v>
+        <v>88.79785533866935</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.1431753021617514</v>
+        <v>-0.02832613230724723</v>
       </c>
       <c r="U11" t="n">
-        <v>0.01227779109425398</v>
+        <v>-0.02948301977077639</v>
       </c>
       <c r="V11" t="n">
-        <v>1.327039442211227</v>
+        <v>1.249017961615839</v>
       </c>
       <c r="W11" t="n">
-        <v>1.890782362663681</v>
+        <v>1.886388229321053</v>
       </c>
       <c r="X11" t="n">
-        <v>0.00429</v>
+        <v>0.00425</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.75372005</v>
+        <v>0.75384</v>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>2026-08-23T21:04:18.580078+00:00</t>
+          <t>2026-08-27T00:34:37.497329+00:00</t>
         </is>
       </c>
       <c r="AD11" t="inlineStr">
@@ -4455,10 +4441,10 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4217126256640</v>
+        <v>4182637805568</v>
       </c>
       <c r="F12" t="n">
-        <v>344.8200073242188</v>
+        <v>342</v>
       </c>
       <c r="G12" t="n">
         <v>445865984000</v>
@@ -4467,7 +4453,7 @@
         <v>0.242</v>
       </c>
       <c r="I12" t="n">
-        <v>19.93</v>
+        <v>19.92</v>
       </c>
       <c r="J12" t="n">
         <v>2.94</v>
@@ -4488,35 +4474,35 @@
         <v>0.34033</v>
       </c>
       <c r="Q12" t="n">
-        <v>17.301556</v>
+        <v>17.168674</v>
       </c>
       <c r="R12" t="n">
-        <v>9.458282000000001</v>
+        <v>9.380931</v>
       </c>
       <c r="S12" t="n">
-        <v>186.063361042099</v>
+        <v>184.5416999076977</v>
       </c>
       <c r="T12" t="n">
-        <v>0.007980388247400327</v>
+        <v>0.04728075256258513</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.09907835240442464</v>
+        <v>-0.1199128288795566</v>
       </c>
       <c r="V12" t="n">
-        <v>0.1400655521483041</v>
+        <v>0.1014639984085435</v>
       </c>
       <c r="W12" t="n">
-        <v>0.7311824950356518</v>
+        <v>0.6557672800620484</v>
       </c>
       <c r="X12" t="n">
         <v>0.01596</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.81073</v>
+        <v>0.81044</v>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>2026-08-23T21:04:21.921530+00:00</t>
+          <t>2026-08-27T00:34:40.447126+00:00</t>
         </is>
       </c>
       <c r="AD12" t="inlineStr">
@@ -4547,10 +4533,10 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>390882099200</v>
+        <v>380736307200</v>
       </c>
       <c r="F13" t="n">
-        <v>492.3200073242188</v>
+        <v>479.760009765625</v>
       </c>
       <c r="G13" t="n">
         <v>30837000192</v>
@@ -4580,35 +4566,35 @@
         <v>0.33736</v>
       </c>
       <c r="Q13" t="n">
-        <v>42.55143</v>
+        <v>41.465862</v>
       </c>
       <c r="R13" t="n">
-        <v>12.67575</v>
+        <v>12.346736</v>
       </c>
       <c r="S13" t="n">
-        <v>127.1006254461765</v>
+        <v>123.8015833271179</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.1102569665921038</v>
+        <v>-0.07084097743649875</v>
       </c>
       <c r="U13" t="n">
-        <v>0.140425846569036</v>
+        <v>0.07144012846832659</v>
       </c>
       <c r="V13" t="n">
-        <v>0.3342865245955684</v>
+        <v>0.2723787176188721</v>
       </c>
       <c r="W13" t="n">
-        <v>2.097116106946919</v>
+        <v>1.932426937302136</v>
       </c>
       <c r="X13" t="n">
         <v>0.00331</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.86535</v>
+        <v>0.8631</v>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>2026-08-23T21:04:19.358155+00:00</t>
+          <t>2026-08-27T00:34:38.117605+00:00</t>
         </is>
       </c>
       <c r="AD13" t="inlineStr">
@@ -4639,10 +4625,10 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>84605255680</v>
+        <v>81750605824</v>
       </c>
       <c r="F14" t="n">
-        <v>235.6199951171875</v>
+        <v>227.6699981689453</v>
       </c>
       <c r="G14" t="n">
         <v>3966725120</v>
@@ -4672,35 +4658,35 @@
         <v>0.00666</v>
       </c>
       <c r="Q14" t="n">
-        <v>480.85712</v>
+        <v>464.63263</v>
       </c>
       <c r="R14" t="n">
-        <v>21.328741</v>
+        <v>20.609093</v>
       </c>
       <c r="S14" t="n">
-        <v>80.46819643983029</v>
+        <v>77.75313431356759</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.04129881181114814</v>
+        <v>-0.09604543152062561</v>
       </c>
       <c r="U14" t="n">
-        <v>0.05982362070352409</v>
+        <v>0.02641901030093829</v>
       </c>
       <c r="V14" t="n">
-        <v>0.9537313275152979</v>
+        <v>1.180120631079434</v>
       </c>
       <c r="W14" t="n">
-        <v>0.824390292314225</v>
+        <v>0.8024701335563864</v>
       </c>
       <c r="X14" t="n">
         <v>0.00619</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.92804</v>
+        <v>0.9282899999999999</v>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>2026-08-23T21:04:25.856589+00:00</t>
+          <t>2026-08-27T00:34:44.224129+00:00</t>
         </is>
       </c>
       <c r="AD14" t="inlineStr">
@@ -4731,10 +4717,10 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1752930451456</v>
+        <v>1691748007936</v>
       </c>
       <c r="F15" t="n">
-        <v>368.4500122070312</v>
+        <v>355.5899963378906</v>
       </c>
       <c r="G15" t="n">
         <v>75464998912</v>
@@ -4743,7 +4729,7 @@
         <v>0.479</v>
       </c>
       <c r="I15" t="n">
-        <v>6.01</v>
+        <v>5.99</v>
       </c>
       <c r="J15" t="n">
         <v>0.854</v>
@@ -4764,35 +4750,35 @@
         <v>0.48988</v>
       </c>
       <c r="Q15" t="n">
-        <v>61.306156</v>
+        <v>59.36394</v>
       </c>
       <c r="R15" t="n">
-        <v>23.22839</v>
+        <v>22.41765</v>
       </c>
       <c r="S15" t="n">
-        <v>64.41696332366014</v>
+        <v>62.16862128761064</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.07146993655918366</v>
+        <v>-0.07209958977819608</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.1089169343844046</v>
+        <v>-0.1557559291401385</v>
       </c>
       <c r="V15" t="n">
-        <v>0.1072405701495147</v>
+        <v>0.09650034710357902</v>
       </c>
       <c r="W15" t="n">
-        <v>0.2815943721547682</v>
+        <v>0.2019577349749262</v>
       </c>
       <c r="X15" t="n">
         <v>0.01948</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.80174005</v>
+        <v>0.80146</v>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>2026-08-23T21:04:18.948271+00:00</t>
+          <t>2026-08-27T00:34:37.806390+00:00</t>
         </is>
       </c>
       <c r="AD15" t="inlineStr">
@@ -4804,12 +4790,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>SNOW</t>
+          <t>MDB</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Snowflake Inc.</t>
+          <t>MongoDB, Inc.</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -4819,66 +4805,66 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Software - Application</t>
+          <t>Software - Infrastructure</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>115341549568</v>
+        <v>32664209408</v>
       </c>
       <c r="F16" t="n">
-        <v>332.7799987792969</v>
+        <v>406.1099853515625</v>
       </c>
       <c r="G16" t="n">
-        <v>5032822784</v>
+        <v>2602398976</v>
       </c>
       <c r="H16" t="n">
-        <v>0.335</v>
+        <v>0.252</v>
       </c>
       <c r="I16" t="n">
-        <v>-3.53</v>
+        <v>-0.37</v>
       </c>
       <c r="K16" t="n">
-        <v>1739497728</v>
+        <v>517605376</v>
       </c>
       <c r="M16" t="n">
-        <v>2954998016</v>
+        <v>2427152896</v>
       </c>
       <c r="N16" t="n">
-        <v>2772094976</v>
+        <v>58635000</v>
       </c>
       <c r="O16" t="n">
-        <v>0.67144996</v>
+        <v>0.71970004</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.22173999</v>
+        <v>-0.03607</v>
       </c>
       <c r="R16" t="n">
-        <v>22.917864</v>
+        <v>12.551577</v>
       </c>
       <c r="S16" t="n">
-        <v>66.3073873057683</v>
+        <v>63.10639518550904</v>
       </c>
       <c r="T16" t="n">
-        <v>0.24264381608771</v>
+        <v>0.3112589085149573</v>
       </c>
       <c r="U16" t="n">
-        <v>0.9325203523628396</v>
+        <v>0.3791686379693362</v>
       </c>
       <c r="V16" t="n">
-        <v>0.8570312748130948</v>
+        <v>0.2995103281848004</v>
       </c>
       <c r="W16" t="n">
-        <v>0.7093692793255157</v>
+        <v>0.8946999733608334</v>
       </c>
       <c r="X16" t="n">
-        <v>0.02962</v>
+        <v>0.02641</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.81998</v>
+        <v>0.9611299599999999</v>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>2026-08-23T21:04:25.573334+00:00</t>
+          <t>2026-08-27T00:34:45.065728+00:00</t>
         </is>
       </c>
       <c r="AD16" t="inlineStr">
@@ -4890,87 +4876,81 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>AMZN</t>
+          <t>SNOW</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Amazon.com, Inc.</t>
+          <t>Snowflake Inc.</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Internet Retail</t>
+          <t>Software - Application</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2789664358400</v>
+        <v>109307240448</v>
       </c>
       <c r="F17" t="n">
-        <v>258.6300048828125</v>
+        <v>315.3699951171875</v>
       </c>
       <c r="G17" t="n">
-        <v>775680032768</v>
+        <v>5032822784</v>
       </c>
       <c r="H17" t="n">
-        <v>0.196</v>
+        <v>0.335</v>
       </c>
       <c r="I17" t="n">
-        <v>12.44</v>
-      </c>
-      <c r="J17" t="n">
-        <v>2.423</v>
+        <v>-3.5</v>
       </c>
       <c r="K17" t="n">
-        <v>3219124992</v>
+        <v>1739497728</v>
       </c>
       <c r="M17" t="n">
-        <v>122988003328</v>
+        <v>2954998016</v>
       </c>
       <c r="N17" t="n">
-        <v>251635007488</v>
+        <v>2772094976</v>
       </c>
       <c r="O17" t="n">
-        <v>0.5077</v>
+        <v>0.67144996</v>
       </c>
       <c r="P17" t="n">
-        <v>0.13689</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>20.790194</v>
+        <v>-0.22173999</v>
       </c>
       <c r="R17" t="n">
-        <v>3.5964112</v>
+        <v>21.718874</v>
       </c>
       <c r="S17" t="n">
-        <v>866.5908796125428</v>
+        <v>62.8383921913349</v>
       </c>
       <c r="T17" t="n">
-        <v>0.05627934831854198</v>
+        <v>0.155540010262726</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.02887504592189505</v>
+        <v>0.7994408593050975</v>
       </c>
       <c r="V17" t="n">
-        <v>0.2624719521246743</v>
+        <v>0.9580901521028253</v>
       </c>
       <c r="W17" t="n">
-        <v>0.1652624845186366</v>
+        <v>0.6226909452691944</v>
       </c>
       <c r="X17" t="n">
-        <v>0.088690005</v>
+        <v>0.02962</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.6879</v>
+        <v>0.81926</v>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>2026-08-23T21:04:22.170682+00:00</t>
+          <t>2026-08-27T00:34:43.956209+00:00</t>
         </is>
       </c>
       <c r="AD17" t="inlineStr">
@@ -4982,81 +4962,87 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>MDB</t>
+          <t>AMZN</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>MongoDB, Inc.</t>
+          <t>Amazon.com, Inc.</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Software - Infrastructure</t>
+          <t>Internet Retail</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>34652487680</v>
+        <v>2807461576704</v>
       </c>
       <c r="F18" t="n">
-        <v>430.8299865722656</v>
+        <v>260.2799987792969</v>
       </c>
       <c r="G18" t="n">
-        <v>2602398976</v>
+        <v>775680032768</v>
       </c>
       <c r="H18" t="n">
-        <v>0.252</v>
+        <v>0.196</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.39</v>
+        <v>12.43</v>
+      </c>
+      <c r="J18" t="n">
+        <v>2.423</v>
       </c>
       <c r="K18" t="n">
-        <v>517605376</v>
+        <v>3219124992</v>
       </c>
       <c r="M18" t="n">
-        <v>2427152896</v>
+        <v>122988003328</v>
       </c>
       <c r="N18" t="n">
-        <v>58635000</v>
+        <v>251635007488</v>
       </c>
       <c r="O18" t="n">
-        <v>0.71970004</v>
+        <v>0.5077</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.03607</v>
+        <v>0.13689</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>20.939661</v>
       </c>
       <c r="R18" t="n">
-        <v>13.315594</v>
+        <v>3.6193552</v>
       </c>
       <c r="S18" t="n">
-        <v>66.94769661743236</v>
+        <v>872.119468389999</v>
       </c>
       <c r="T18" t="n">
-        <v>0.4126962811023474</v>
+        <v>0.1248541400486338</v>
       </c>
       <c r="U18" t="n">
-        <v>0.3210375620822583</v>
+        <v>-0.04256026141052616</v>
       </c>
       <c r="V18" t="n">
-        <v>0.2105705943951726</v>
+        <v>0.2479861997801025</v>
       </c>
       <c r="W18" t="n">
-        <v>1.032600362925348</v>
+        <v>0.1380350274963091</v>
       </c>
       <c r="X18" t="n">
-        <v>0.02641</v>
+        <v>0.088690005</v>
       </c>
       <c r="Y18" t="n">
-        <v>0.96402</v>
+        <v>0.68727</v>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>2026-08-23T21:04:26.662166+00:00</t>
+          <t>2026-08-27T00:34:40.730542+00:00</t>
         </is>
       </c>
       <c r="AD18" t="inlineStr">
@@ -5087,10 +5073,10 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>104381210624</v>
+        <v>101443551232</v>
       </c>
       <c r="F19" t="n">
-        <v>293.1400146484375</v>
+        <v>284.8900146484375</v>
       </c>
       <c r="G19" t="n">
         <v>2512349952</v>
@@ -5099,7 +5085,7 @@
         <v>0.359</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.59</v>
+        <v>-0.58</v>
       </c>
       <c r="K19" t="n">
         <v>692851968</v>
@@ -5117,32 +5103,32 @@
         <v>-0.07902000000000001</v>
       </c>
       <c r="R19" t="n">
-        <v>41.54724</v>
+        <v>40.377953</v>
       </c>
       <c r="S19" t="n">
-        <v>150.6544189017877</v>
+        <v>146.4144664621924</v>
       </c>
       <c r="T19" t="n">
-        <v>0.08982081446690615</v>
+        <v>0.07258774278141633</v>
       </c>
       <c r="U19" t="n">
-        <v>0.3560624375790442</v>
+        <v>0.3616767660177536</v>
       </c>
       <c r="V19" t="n">
-        <v>0.5216985858451444</v>
+        <v>0.7391491294451318</v>
       </c>
       <c r="W19" t="n">
-        <v>0.5206723460674603</v>
+        <v>0.4348527336671593</v>
       </c>
       <c r="X19" t="n">
         <v>0.00616</v>
       </c>
       <c r="Y19" t="n">
-        <v>0.90915</v>
+        <v>0.90191</v>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>2026-08-23T21:04:26.106824+00:00</t>
+          <t>2026-08-27T00:34:44.491319+00:00</t>
         </is>
       </c>
       <c r="AD19" t="inlineStr">
@@ -5154,12 +5140,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ACMR</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>ACM Research, Inc.</t>
+          <t>Microsoft Corporation</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -5169,69 +5155,72 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Semiconductor Equipment &amp; Materials</t>
+          <t>Software - Infrastructure</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5530843136</v>
+        <v>3685818040320</v>
       </c>
       <c r="F20" t="n">
-        <v>79.41000366210938</v>
+        <v>496.3699951171875</v>
       </c>
       <c r="G20" t="n">
-        <v>1037772032</v>
+        <v>331839012864</v>
       </c>
       <c r="H20" t="n">
-        <v>0.36</v>
+        <v>0.177</v>
       </c>
       <c r="I20" t="n">
-        <v>2.12</v>
+        <v>17.95</v>
       </c>
       <c r="J20" t="n">
-        <v>1.806</v>
+        <v>0.317</v>
       </c>
       <c r="K20" t="n">
-        <v>-186610256</v>
+        <v>16545500160</v>
       </c>
       <c r="M20" t="n">
-        <v>1439374976</v>
+        <v>76842999808</v>
       </c>
       <c r="N20" t="n">
-        <v>349319008</v>
+        <v>128812998656</v>
       </c>
       <c r="O20" t="n">
-        <v>0.43835</v>
+        <v>0.67944</v>
       </c>
       <c r="P20" t="n">
-        <v>0.16982001</v>
+        <v>0.45111</v>
       </c>
       <c r="Q20" t="n">
-        <v>37.45755</v>
+        <v>27.652924</v>
       </c>
       <c r="R20" t="n">
-        <v>5.329536</v>
+        <v>11.107247</v>
+      </c>
+      <c r="S20" t="n">
+        <v>222.7686080612265</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.1128365348349486</v>
+        <v>0.2780889499917965</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0826176593599568</v>
+        <v>0.2050897672313394</v>
       </c>
       <c r="V20" t="n">
-        <v>0.2151492810448359</v>
+        <v>0.2811864922651715</v>
       </c>
       <c r="W20" t="n">
-        <v>2.10074196679292</v>
+        <v>-0.00315917551200473</v>
       </c>
       <c r="X20" t="n">
-        <v>0.12675999</v>
+        <v>0.00090000004</v>
       </c>
       <c r="Y20" t="n">
-        <v>0.78052</v>
+        <v>0.75881</v>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>2026-08-23T21:04:20.038475+00:00</t>
+          <t>2026-08-27T00:34:40.175406+00:00</t>
         </is>
       </c>
       <c r="AD20" t="inlineStr">
@@ -5243,87 +5232,87 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>VRT</t>
+          <t>ASML</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Vertiv Holdings Co</t>
+          <t>ASML Holding N.V.</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Electrical Equipment &amp; Parts</t>
+          <t>Semiconductor Equipment &amp; Materials</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100847656960</v>
+        <v>670500323328</v>
       </c>
       <c r="F21" t="n">
-        <v>261.9500122070312</v>
+        <v>1745.640014648438</v>
       </c>
       <c r="G21" t="n">
-        <v>11479600128</v>
+        <v>35327500288</v>
       </c>
       <c r="H21" t="n">
-        <v>0.241</v>
+        <v>0.213</v>
       </c>
       <c r="I21" t="n">
-        <v>4.43</v>
+        <v>29.65</v>
       </c>
       <c r="J21" t="n">
-        <v>0.53</v>
+        <v>0.285</v>
       </c>
       <c r="K21" t="n">
-        <v>2696537600</v>
+        <v>8437675008</v>
       </c>
       <c r="M21" t="n">
-        <v>3110599936</v>
+        <v>7581499904</v>
       </c>
       <c r="N21" t="n">
-        <v>3338200064</v>
+        <v>1984400000</v>
       </c>
       <c r="O21" t="n">
-        <v>0.38039002</v>
+        <v>0.5273300400000001</v>
       </c>
       <c r="P21" t="n">
-        <v>0.20362</v>
+        <v>0.37057</v>
       </c>
       <c r="Q21" t="n">
-        <v>59.13093</v>
+        <v>58.874874</v>
       </c>
       <c r="R21" t="n">
-        <v>8.784945499999999</v>
+        <v>18.979557</v>
       </c>
       <c r="S21" t="n">
-        <v>37.39894335610229</v>
+        <v>79.46505674753763</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.1301965432935455</v>
+        <v>0.05596558535961482</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1998884785081102</v>
+        <v>0.09389227011352697</v>
       </c>
       <c r="V21" t="n">
-        <v>0.07819827777494104</v>
+        <v>0.1695255958287856</v>
       </c>
       <c r="W21" t="n">
-        <v>1.071721809401515</v>
+        <v>1.302329484682044</v>
       </c>
       <c r="X21" t="n">
-        <v>0.00269</v>
+        <v>0.00016000001</v>
       </c>
       <c r="Y21" t="n">
-        <v>0.8440800000000001</v>
+        <v>0.20384</v>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>2026-08-23T21:04:24.977873+00:00</t>
+          <t>2026-08-27T00:34:41.973115+00:00</t>
         </is>
       </c>
       <c r="AD21" t="inlineStr">
@@ -5335,87 +5324,87 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ASML</t>
+          <t>VRT</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>ASML Holding N.V.</t>
+          <t>Vertiv Holdings Co</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Semiconductor Equipment &amp; Materials</t>
+          <t>Electrical Equipment &amp; Parts</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>677460246528</v>
+        <v>101563727872</v>
       </c>
       <c r="F22" t="n">
-        <v>1763.760009765625</v>
+        <v>263.8099975585938</v>
       </c>
       <c r="G22" t="n">
-        <v>35327500288</v>
+        <v>11479600128</v>
       </c>
       <c r="H22" t="n">
-        <v>0.213</v>
+        <v>0.241</v>
       </c>
       <c r="I22" t="n">
-        <v>29.63</v>
+        <v>4.42</v>
       </c>
       <c r="J22" t="n">
-        <v>0.285</v>
+        <v>0.53</v>
       </c>
       <c r="K22" t="n">
-        <v>8437675008</v>
+        <v>2696537600</v>
       </c>
       <c r="M22" t="n">
-        <v>7581499904</v>
+        <v>3110599936</v>
       </c>
       <c r="N22" t="n">
-        <v>1984400000</v>
+        <v>3338200064</v>
       </c>
       <c r="O22" t="n">
-        <v>0.5273300400000001</v>
+        <v>0.38039002</v>
       </c>
       <c r="P22" t="n">
-        <v>0.37057</v>
+        <v>0.20362</v>
       </c>
       <c r="Q22" t="n">
-        <v>59.526157</v>
+        <v>59.68552</v>
       </c>
       <c r="R22" t="n">
-        <v>19.176569</v>
+        <v>8.847322</v>
       </c>
       <c r="S22" t="n">
-        <v>80.28991942515925</v>
+        <v>37.66449534098838</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.0198788191730831</v>
+        <v>-0.08271908219765178</v>
       </c>
       <c r="U22" t="n">
-        <v>0.08153658248673468</v>
+        <v>-0.1748549187500137</v>
       </c>
       <c r="V22" t="n">
-        <v>0.2131482647002914</v>
+        <v>0.04257434101346913</v>
       </c>
       <c r="W22" t="n">
-        <v>1.414165201818253</v>
+        <v>1.064414949858474</v>
       </c>
       <c r="X22" t="n">
-        <v>0.00016000001</v>
+        <v>0.00269</v>
       </c>
       <c r="Y22" t="n">
-        <v>0.20382</v>
+        <v>0.84448</v>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>2026-08-23T21:04:23.465604+00:00</t>
+          <t>2026-08-27T00:34:43.432233+00:00</t>
         </is>
       </c>
       <c r="AD22" t="inlineStr">
@@ -5427,12 +5416,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>SMCI</t>
+          <t>ACMR</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Super Micro Computer, Inc.</t>
+          <t>ACM Research, Inc.</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -5442,69 +5431,69 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Computer Hardware</t>
+          <t>Semiconductor Equipment &amp; Materials</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>24089552896</v>
+        <v>5509948416</v>
       </c>
       <c r="F23" t="n">
-        <v>37.2400016784668</v>
+        <v>79.11000061035156</v>
       </c>
       <c r="G23" t="n">
-        <v>39063072768</v>
+        <v>1037772032</v>
       </c>
       <c r="H23" t="n">
-        <v>0.9320000000000001</v>
+        <v>0.36</v>
       </c>
       <c r="I23" t="n">
-        <v>3.26</v>
+        <v>2.12</v>
       </c>
       <c r="J23" t="n">
-        <v>4.094</v>
+        <v>1.806</v>
       </c>
       <c r="K23" t="n">
-        <v>-8231267840</v>
+        <v>-186610256</v>
       </c>
       <c r="M23" t="n">
-        <v>7521474048</v>
+        <v>1439374976</v>
       </c>
       <c r="N23" t="n">
-        <v>9311492096</v>
+        <v>349319008</v>
       </c>
       <c r="O23" t="n">
-        <v>0.108219996</v>
+        <v>0.43835</v>
       </c>
       <c r="P23" t="n">
-        <v>0.13382</v>
+        <v>0.16982001</v>
       </c>
       <c r="Q23" t="n">
-        <v>11.423313</v>
+        <v>37.31604</v>
       </c>
       <c r="R23" t="n">
-        <v>0.6166835000000001</v>
+        <v>5.3094015</v>
       </c>
       <c r="T23" t="n">
-        <v>0.2185864636538672</v>
+        <v>-0.01075404023038729</v>
       </c>
       <c r="U23" t="n">
-        <v>0.0466554177061127</v>
+        <v>-0.1075135248749766</v>
       </c>
       <c r="V23" t="n">
-        <v>0.1579602566902212</v>
+        <v>0.1675029237942185</v>
       </c>
       <c r="W23" t="n">
-        <v>-0.1198298163616878</v>
+        <v>1.644934838312825</v>
       </c>
       <c r="X23" t="n">
-        <v>0.12878999</v>
+        <v>0.12675999</v>
       </c>
       <c r="Y23" t="n">
-        <v>0.70522004</v>
+        <v>0.78055</v>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>2026-08-23T21:04:25.240738+00:00</t>
+          <t>2026-08-27T00:34:38.740928+00:00</t>
         </is>
       </c>
       <c r="AD23" t="inlineStr">
@@ -5516,12 +5505,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>SMCI</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Microsoft Corporation</t>
+          <t>Super Micro Computer, Inc.</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -5531,72 +5520,69 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Software - Infrastructure</t>
+          <t>Computer Hardware</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>3588320657408</v>
+        <v>24186580992</v>
       </c>
       <c r="F24" t="n">
-        <v>483.239990234375</v>
+        <v>37.38999938964844</v>
       </c>
       <c r="G24" t="n">
-        <v>331839012864</v>
+        <v>39063072768</v>
       </c>
       <c r="H24" t="n">
-        <v>0.177</v>
+        <v>0.9320000000000001</v>
       </c>
       <c r="I24" t="n">
-        <v>17.93</v>
+        <v>3.26</v>
       </c>
       <c r="J24" t="n">
-        <v>0.317</v>
+        <v>4.094</v>
       </c>
       <c r="K24" t="n">
-        <v>16545500160</v>
+        <v>-8231267840</v>
       </c>
       <c r="M24" t="n">
-        <v>76842999808</v>
+        <v>7521474048</v>
       </c>
       <c r="N24" t="n">
-        <v>128812998656</v>
+        <v>9311492096</v>
       </c>
       <c r="O24" t="n">
-        <v>0.67944</v>
+        <v>0.108219996</v>
       </c>
       <c r="P24" t="n">
-        <v>0.45111</v>
+        <v>0.13382</v>
       </c>
       <c r="Q24" t="n">
-        <v>26.951477</v>
+        <v>11.469325</v>
       </c>
       <c r="R24" t="n">
-        <v>10.813438</v>
-      </c>
-      <c r="S24" t="n">
-        <v>216.8759253396907</v>
+        <v>0.6191674</v>
       </c>
       <c r="T24" t="n">
-        <v>0.2403281430304072</v>
+        <v>0.254277090221559</v>
       </c>
       <c r="U24" t="n">
-        <v>0.156675515749495</v>
+        <v>-0.02094787289416267</v>
       </c>
       <c r="V24" t="n">
-        <v>0.2176838288473297</v>
+        <v>0.2010922067987515</v>
       </c>
       <c r="W24" t="n">
-        <v>-0.03376181497550057</v>
+        <v>-0.1571235600721937</v>
       </c>
       <c r="X24" t="n">
-        <v>0.00090000004</v>
+        <v>0.12878999</v>
       </c>
       <c r="Y24" t="n">
-        <v>0.75907</v>
+        <v>0.70584</v>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>2026-08-23T21:04:21.633654+00:00</t>
+          <t>2026-08-27T00:34:43.686622+00:00</t>
         </is>
       </c>
       <c r="AD24" t="inlineStr">
@@ -5627,10 +5613,10 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>291664035840</v>
+        <v>276537638912</v>
       </c>
       <c r="F25" t="n">
-        <v>357.8699951171875</v>
+        <v>339.3099975585938</v>
       </c>
       <c r="G25" t="n">
         <v>10606499840</v>
@@ -5657,35 +5643,35 @@
         <v>-0.02465</v>
       </c>
       <c r="Q25" t="n">
-        <v>311.1913</v>
+        <v>295.0522</v>
       </c>
       <c r="R25" t="n">
-        <v>27.498613</v>
+        <v>26.07247</v>
       </c>
       <c r="S25" t="n">
-        <v>81.48462437313751</v>
+        <v>77.25863618008782</v>
       </c>
       <c r="T25" t="n">
-        <v>0.0673765104394457</v>
+        <v>0.06929909784070731</v>
       </c>
       <c r="U25" t="n">
-        <v>0.3733594809973666</v>
+        <v>0.3655974398985982</v>
       </c>
       <c r="V25" t="n">
-        <v>1.370156845470078</v>
+        <v>1.3950730708273</v>
       </c>
       <c r="W25" t="n">
-        <v>0.9521600524718539</v>
+        <v>0.8417738990799586</v>
       </c>
       <c r="X25" t="n">
         <v>0.0076</v>
       </c>
       <c r="Y25" t="n">
-        <v>0.84946</v>
+        <v>0.84953004</v>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>2026-08-23T21:04:21.310373+00:00</t>
+          <t>2026-08-27T00:34:39.862580+00:00</t>
         </is>
       </c>
       <c r="AD25" t="inlineStr">
@@ -5716,10 +5702,10 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>259865427968</v>
+        <v>268131729408</v>
       </c>
       <c r="F26" t="n">
-        <v>243.3200073242188</v>
+        <v>251.0599975585938</v>
       </c>
       <c r="G26" t="n">
         <v>5155999744</v>
@@ -5728,7 +5714,7 @@
         <v>0.224</v>
       </c>
       <c r="I26" t="n">
-        <v>0.97</v>
+        <v>0.99</v>
       </c>
       <c r="J26" t="n">
         <v>1.083</v>
@@ -5749,35 +5735,35 @@
         <v>0.07603</v>
       </c>
       <c r="Q26" t="n">
-        <v>250.84537</v>
+        <v>253.59595</v>
       </c>
       <c r="R26" t="n">
-        <v>50.40059</v>
+        <v>52.00383</v>
       </c>
       <c r="S26" t="n">
-        <v>194.728688047447</v>
+        <v>200.9229942581759</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.1414255025951249</v>
+        <v>-0.05733484693256097</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.2061596699230962</v>
+        <v>-0.1706253356495145</v>
       </c>
       <c r="V26" t="n">
-        <v>0.9169621581911946</v>
+        <v>0.9592632960389664</v>
       </c>
       <c r="W26" t="n">
-        <v>0.8256303237752955</v>
+        <v>0.7899615527673336</v>
       </c>
       <c r="X26" t="n">
         <v>0.0007</v>
       </c>
       <c r="Y26" t="n">
-        <v>0.96261</v>
+        <v>0.96185</v>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>2026-08-23T21:04:23.707653+00:00</t>
+          <t>2026-08-27T00:34:42.252890+00:00</t>
         </is>
       </c>
       <c r="AD26" t="inlineStr">
@@ -5808,10 +5794,10 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1400873680896</v>
+        <v>1467720269824</v>
       </c>
       <c r="F27" t="n">
-        <v>549.9000244140625</v>
+        <v>576.1400146484375</v>
       </c>
       <c r="G27" t="n">
         <v>228246994944</v>
@@ -5841,35 +5827,35 @@
         <v>0.34827</v>
       </c>
       <c r="Q27" t="n">
-        <v>20.704067</v>
+        <v>21.692019</v>
       </c>
       <c r="R27" t="n">
-        <v>6.137534</v>
+        <v>6.4304037</v>
       </c>
       <c r="S27" t="n">
-        <v>64.99480598629961</v>
+        <v>68.09621415569461</v>
       </c>
       <c r="T27" t="n">
-        <v>-0.1232041720771622</v>
+        <v>-0.02985498613253124</v>
       </c>
       <c r="U27" t="n">
-        <v>-0.09807350747934629</v>
+        <v>-0.09222372575639304</v>
       </c>
       <c r="V27" t="n">
-        <v>-0.1456296261876776</v>
+        <v>-0.09718792919419572</v>
       </c>
       <c r="W27" t="n">
-        <v>-0.2535483859208238</v>
+        <v>-0.2334858217892405</v>
       </c>
       <c r="X27" t="n">
         <v>0.00148</v>
       </c>
       <c r="Y27" t="n">
-        <v>0.79103994</v>
+        <v>0.79038</v>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>2026-08-23T21:04:22.537691+00:00</t>
+          <t>2026-08-27T00:34:41.011552+00:00</t>
         </is>
       </c>
       <c r="AD27" t="inlineStr">
@@ -5881,12 +5867,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>CRWD</t>
+          <t>MRVL</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>CrowdStrike Holdings, Inc.</t>
+          <t>Marvell Technology, Inc.</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -5896,66 +5882,72 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Software - Infrastructure</t>
+          <t>Semiconductors</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>195454861312</v>
+        <v>220281487360</v>
       </c>
       <c r="F28" t="n">
-        <v>191.9499969482422</v>
+        <v>245.1100006103516</v>
       </c>
       <c r="G28" t="n">
-        <v>5094199808</v>
+        <v>8717100032</v>
       </c>
       <c r="H28" t="n">
-        <v>0.256</v>
+        <v>0.276</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.04</v>
+        <v>2.91</v>
+      </c>
+      <c r="J28" t="n">
+        <v>-0.804</v>
       </c>
       <c r="K28" t="n">
-        <v>1926365056</v>
+        <v>2269700096</v>
       </c>
       <c r="M28" t="n">
-        <v>4552800768</v>
+        <v>3843599872</v>
       </c>
       <c r="N28" t="n">
-        <v>821342976</v>
+        <v>5277199872</v>
       </c>
       <c r="O28" t="n">
-        <v>0.75136</v>
+        <v>0.5150299699999999</v>
       </c>
       <c r="P28" t="n">
-        <v>-0.022079999</v>
+        <v>0.14479999</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>84.23023999999999</v>
       </c>
       <c r="R28" t="n">
-        <v>38.36812</v>
+        <v>25.270042</v>
       </c>
       <c r="S28" t="n">
-        <v>101.4630434160035</v>
+        <v>97.05312510151121</v>
       </c>
       <c r="T28" t="n">
-        <v>0.01873473523830382</v>
+        <v>0.2957128666430866</v>
       </c>
       <c r="U28" t="n">
-        <v>0.1572663949066291</v>
+        <v>0.2338725615919328</v>
       </c>
       <c r="V28" t="n">
-        <v>0.8188277849765093</v>
+        <v>2.129139013505327</v>
       </c>
       <c r="W28" t="n">
-        <v>0.8543206113126569</v>
+        <v>2.30773265924773</v>
       </c>
       <c r="X28" t="n">
-        <v>0.014680001</v>
+        <v>0.00494</v>
       </c>
       <c r="Y28" t="n">
-        <v>0.76635003</v>
+        <v>0.82141995</v>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>2026-08-23T21:04:21.001880+00:00</t>
+          <t>2026-08-27T00:34:42.558687+00:00</t>
         </is>
       </c>
       <c r="AD28" t="inlineStr">
@@ -5967,12 +5959,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>MRVL</t>
+          <t>CRWD</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Marvell Technology, Inc.</t>
+          <t>CrowdStrike Holdings, Inc.</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -5982,72 +5974,66 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Semiconductors</t>
+          <t>Software - Infrastructure</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>212753924096</v>
+        <v>192634273792</v>
       </c>
       <c r="F29" t="n">
-        <v>237.0399932861328</v>
+        <v>189.1799926757812</v>
       </c>
       <c r="G29" t="n">
-        <v>8717100032</v>
+        <v>5094199808</v>
       </c>
       <c r="H29" t="n">
-        <v>0.276</v>
+        <v>0.256</v>
       </c>
       <c r="I29" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="J29" t="n">
-        <v>-0.804</v>
+        <v>-0.04</v>
       </c>
       <c r="K29" t="n">
-        <v>2269700096</v>
+        <v>1926365056</v>
       </c>
       <c r="M29" t="n">
-        <v>3843599872</v>
+        <v>4552800768</v>
       </c>
       <c r="N29" t="n">
-        <v>5277199872</v>
+        <v>821342976</v>
       </c>
       <c r="O29" t="n">
-        <v>0.5150299699999999</v>
+        <v>0.75136</v>
       </c>
       <c r="P29" t="n">
-        <v>0.14479999</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>81.17807999999999</v>
+        <v>-0.022079999</v>
       </c>
       <c r="R29" t="n">
-        <v>24.406502</v>
+        <v>37.814434</v>
       </c>
       <c r="S29" t="n">
-        <v>93.7365797670566</v>
+        <v>99.99884144077829</v>
       </c>
       <c r="T29" t="n">
-        <v>0.1234655060180694</v>
+        <v>0.05035807026091588</v>
       </c>
       <c r="U29" t="n">
-        <v>0.2076527324190676</v>
+        <v>0.1725548343238212</v>
       </c>
       <c r="V29" t="n">
-        <v>1.979740667578479</v>
+        <v>1.16051383498394</v>
       </c>
       <c r="W29" t="n">
-        <v>2.335838507022704</v>
+        <v>0.8120688688772375</v>
       </c>
       <c r="X29" t="n">
-        <v>0.00494</v>
+        <v>0.01467</v>
       </c>
       <c r="Y29" t="n">
-        <v>0.82137</v>
+        <v>0.76657</v>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>2026-08-23T21:04:24.026199+00:00</t>
+          <t>2026-08-27T00:34:39.589372+00:00</t>
         </is>
       </c>
       <c r="AD29" t="inlineStr">
@@ -6078,10 +6064,10 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>132830584832</v>
+        <v>130059845632</v>
       </c>
       <c r="F30" t="n">
-        <v>128.4799957275391</v>
+        <v>125.8000030517578</v>
       </c>
       <c r="G30" t="n">
         <v>14732000256</v>
@@ -6090,7 +6076,7 @@
         <v>0.24</v>
       </c>
       <c r="I30" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="J30" t="n">
         <v>-0.219</v>
@@ -6111,35 +6097,35 @@
         <v>0.04063</v>
       </c>
       <c r="Q30" t="n">
-        <v>79.80124000000001</v>
+        <v>78.625</v>
       </c>
       <c r="R30" t="n">
-        <v>9.016465999999999</v>
+        <v>8.828390000000001</v>
       </c>
       <c r="S30" t="n">
-        <v>25.79547720861104</v>
+        <v>25.25740429434207</v>
       </c>
       <c r="T30" t="n">
-        <v>0.3459040117300543</v>
+        <v>0.1917393516604557</v>
       </c>
       <c r="U30" t="n">
-        <v>0.2580044960614081</v>
+        <v>0.2318840547227496</v>
       </c>
       <c r="V30" t="n">
-        <v>0.1966097833747986</v>
+        <v>0.2274368784646881</v>
       </c>
       <c r="W30" t="n">
-        <v>-0.2674778054883237</v>
+        <v>-0.27254644554547</v>
       </c>
       <c r="X30" t="n">
         <v>0.00176</v>
       </c>
       <c r="Y30" t="n">
-        <v>0.85102</v>
+        <v>0.8513700400000001</v>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>2026-08-23T21:04:26.405839+00:00</t>
+          <t>2026-08-27T00:34:44.768559+00:00</t>
         </is>
       </c>
       <c r="AD30" t="inlineStr">
@@ -6170,10 +6156,10 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>421902581760</v>
+        <v>428815712256</v>
       </c>
       <c r="F31" t="n">
-        <v>146.4700012207031</v>
+        <v>148.8699951171875</v>
       </c>
       <c r="G31" t="n">
         <v>67356999680</v>
@@ -6203,32 +6189,32 @@
         <v>0.36202</v>
       </c>
       <c r="Q31" t="n">
-        <v>25.123499</v>
+        <v>25.535162</v>
       </c>
       <c r="R31" t="n">
-        <v>6.2636786</v>
+        <v>6.3663125</v>
       </c>
       <c r="T31" t="n">
-        <v>0.1639383779654544</v>
+        <v>0.2416179584873133</v>
       </c>
       <c r="U31" t="n">
-        <v>-0.2348002668577091</v>
+        <v>-0.2177005762318938</v>
       </c>
       <c r="V31" t="n">
-        <v>-0.05779410309686361</v>
+        <v>0.02579484468997983</v>
       </c>
       <c r="W31" t="n">
-        <v>-0.3646448542401906</v>
+        <v>-0.3571292126698538</v>
       </c>
       <c r="X31" t="n">
         <v>0.40498</v>
       </c>
       <c r="Y31" t="n">
-        <v>0.45828</v>
+        <v>0.45823002</v>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>2026-08-23T21:04:22.835465+00:00</t>
+          <t>2026-08-27T00:34:41.321823+00:00</t>
         </is>
       </c>
       <c r="AD31" t="inlineStr">
@@ -6256,7 +6242,7 @@
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
@@ -6313,22 +6299,27 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>MU</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>100</v>
+        <v>84.2</v>
       </c>
       <c r="C2" t="n">
-        <v>100</v>
+        <v>88.2</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MODERATE</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>price_to_sales, price_to_fcf</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -6342,11 +6333,11 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>MU</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="C3" t="n">
         <v>100</v>
@@ -6357,7 +6348,7 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -6371,7 +6362,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CRDO</t>
+          <t>ANET</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -6400,7 +6391,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ANET</t>
+          <t>CRDO</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -6487,7 +6478,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>NVDA</t>
+          <t>DELL</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -6516,7 +6507,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>DELL</t>
+          <t>NVDA</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -6724,7 +6715,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>SNOW</t>
+          <t>MDB</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -6758,18 +6749,23 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>AMZN</t>
+          <t>SNOW</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>100</v>
+        <v>88.2</v>
       </c>
       <c r="C17" t="n">
-        <v>100</v>
+        <v>88.2</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
           <t>HIGH</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>eps_growth, pe_ratio</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -6787,23 +6783,18 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>MDB</t>
+          <t>AMZN</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>88.2</v>
+        <v>100</v>
       </c>
       <c r="C18" t="n">
-        <v>88.2</v>
+        <v>100</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
           <t>HIGH</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>eps_growth, pe_ratio</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -6855,23 +6846,18 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ACMR</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>94.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="C20" t="n">
-        <v>94.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
           <t>HIGH</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>price_to_fcf</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -6889,7 +6875,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>VRT</t>
+          <t>ASML</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -6918,7 +6904,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ASML</t>
+          <t>VRT</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -6947,7 +6933,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>SMCI</t>
+          <t>ACMR</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -6981,18 +6967,23 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>SMCI</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>100</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="C24" t="n">
-        <v>100</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
           <t>HIGH</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>price_to_fcf</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -7102,23 +7093,18 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>CRWD</t>
+          <t>MRVL</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>88.2</v>
+        <v>100</v>
       </c>
       <c r="C28" t="n">
-        <v>88.2</v>
+        <v>100</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
           <t>HIGH</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>eps_growth, pe_ratio</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -7136,18 +7122,23 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>MRVL</t>
+          <t>CRWD</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>100</v>
+        <v>88.2</v>
       </c>
       <c r="C29" t="n">
-        <v>100</v>
+        <v>88.2</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
           <t>HIGH</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>eps_growth, pe_ratio</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -7294,11 +7285,11 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>MU</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>55.66</v>
+        <v>56.32</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -7311,7 +7302,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>100</v>
+        <v>84.2</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>

--- a/reports/investment_dashboard.xlsx
+++ b/reports/investment_dashboard.xlsx
@@ -534,7 +534,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>56.32</v>
+        <v>56.77</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>938.4000244140625</v>
+        <v>923.614990234375</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -586,7 +586,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>55.33</v>
+        <v>55.57</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>417.6900024414062</v>
+        <v>424.6000061035156</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -624,16 +624,16 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ANET</t>
+          <t>CRDO</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Arista Networks, Inc.</t>
+          <t>Credo Technology Group Holding Ltd</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>53.02</v>
+        <v>53.52</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -641,11 +641,11 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>202.25</v>
+        <v>236.8000030517578</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -656,7 +656,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Revenue Growth; Earnings Fcf; Balance Sheet; Momentum</t>
+          <t>Revenue Growth; Earnings Fcf; Balance Sheet</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -666,7 +666,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Excessive price-to-sales valuation</t>
+          <t>Excessive price-to-sales valuation; High market sensitivity / beta</t>
         </is>
       </c>
     </row>
@@ -676,16 +676,16 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>CRDO</t>
+          <t>ANET</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Credo Technology Group Holding Ltd</t>
+          <t>Arista Networks, Inc.</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>52.8</v>
+        <v>52.98</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -693,11 +693,11 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>226.4900054931641</v>
+        <v>201.4949951171875</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -708,7 +708,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Revenue Growth; Earnings Fcf; Balance Sheet</t>
+          <t>Revenue Growth; Earnings Fcf; Balance Sheet; Momentum</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -718,7 +718,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Excessive price-to-sales valuation; High market sensitivity / beta</t>
+          <t>Excessive price-to-sales valuation</t>
         </is>
       </c>
     </row>
@@ -737,7 +737,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>51.96</v>
+        <v>52.27</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -745,7 +745,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>177.5</v>
+        <v>184.8099975585938</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -780,16 +780,16 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>TER</t>
+          <t>DELL</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Teradyne, Inc.</t>
+          <t>Dell Technologies Inc.</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>50.85</v>
+        <v>51.15</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>363.1000061035156</v>
+        <v>467.1600036621094</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -812,12 +812,12 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Revenue Growth; Earnings Fcf; Balance Sheet</t>
+          <t>Revenue Growth; Momentum</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Industry Growth; Valuation; Competitive Advantage; Catalysts; Inflation Resilience</t>
+          <t>Industry Growth; Competitive Advantage; Catalysts; Inflation Resilience</t>
         </is>
       </c>
     </row>
@@ -827,16 +827,16 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>DELL</t>
+          <t>TER</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Dell Technologies Inc.</t>
+          <t>Teradyne, Inc.</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>50.69</v>
+        <v>50.8</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -844,7 +844,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>463.8200073242188</v>
+        <v>363.7049865722656</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -859,12 +859,12 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Revenue Growth; Momentum</t>
+          <t>Revenue Growth; Earnings Fcf; Balance Sheet</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Industry Growth; Competitive Advantage; Catalysts; Inflation Resilience</t>
+          <t>Industry Growth; Valuation; Competitive Advantage; Catalysts; Inflation Resilience</t>
         </is>
       </c>
     </row>
@@ -883,15 +883,15 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>49.77</v>
+        <v>50.79</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>REJECT</t>
+          <t>RESEARCH</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>209.6600036621094</v>
+        <v>224.8000030517578</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>48.13</v>
+        <v>47.65</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -943,7 +943,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>16.76000022888184</v>
+        <v>18.23999977111816</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -982,7 +982,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>47.52</v>
+        <v>47.62</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -990,7 +990,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>480.9299926757812</v>
+        <v>474.5299987792969</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>46.92</v>
+        <v>46.7</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -1042,7 +1042,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>342</v>
+        <v>339.3399963378906</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>45.38</v>
+        <v>45.33</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -1089,7 +1089,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>479.760009765625</v>
+        <v>471.7850036621094</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -1128,7 +1128,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>44.67</v>
+        <v>45.11</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>227.6699981689453</v>
+        <v>242.0399932861328</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -1180,7 +1180,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>43.83</v>
+        <v>44.19</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>355.5899963378906</v>
+        <v>366.9609985351562</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -1232,7 +1232,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>43.45</v>
+        <v>43.58</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>406.1099853515625</v>
+        <v>431.2349853515625</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1279,7 +1279,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>43</v>
+        <v>43.13</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -1287,7 +1287,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>315.3699951171875</v>
+        <v>329.1499938964844</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1322,16 +1322,16 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>AMZN</t>
+          <t>NET</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Amazon.com, Inc.</t>
+          <t>Cloudflare, Inc.</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>42.97</v>
+        <v>42.84</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -1339,7 +1339,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>260.2799987792969</v>
+        <v>300.3500061035156</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1347,19 +1347,24 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>100</v>
+        <v>88.2</v>
       </c>
       <c r="I18" t="n">
-        <v>100</v>
+        <v>88.2</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Earnings Fcf</t>
+          <t>Revenue Growth; Momentum</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Industry Growth; Competitive Advantage; Catalysts; Inflation Resilience</t>
+          <t>Industry Growth; Valuation; Competitive Advantage; Catalysts; Inflation Resilience</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>Excessive price-to-sales valuation</t>
         </is>
       </c>
     </row>
@@ -1369,16 +1374,16 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>NET</t>
+          <t>AMZN</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Cloudflare, Inc.</t>
+          <t>Amazon.com, Inc.</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>42.78</v>
+        <v>42.64</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -1386,7 +1391,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>284.8900146484375</v>
+        <v>256.8200073242188</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1394,24 +1399,19 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>88.2</v>
+        <v>100</v>
       </c>
       <c r="I19" t="n">
-        <v>88.2</v>
+        <v>100</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Revenue Growth; Momentum</t>
+          <t>Earnings Fcf</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Industry Growth; Valuation; Competitive Advantage; Catalysts; Inflation Resilience</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>Excessive price-to-sales valuation</t>
+          <t>Industry Growth; Competitive Advantage; Catalysts; Inflation Resilience</t>
         </is>
       </c>
     </row>
@@ -1430,7 +1430,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>42.59</v>
+        <v>42.39</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>496.3699951171875</v>
+        <v>504.1950073242188</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1468,16 +1468,16 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>ASML</t>
+          <t>VRT</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>ASML Holding N.V.</t>
+          <t>Vertiv Holdings Co</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>42.42</v>
+        <v>42.39</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1745.640014648438</v>
+        <v>264.9200134277344</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1500,12 +1500,17 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Earnings Fcf; Balance Sheet</t>
+          <t>Earnings Fcf</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>Industry Growth; Valuation; Competitive Advantage; Catalysts; Inflation Resilience</t>
+          <t>Industry Growth; Valuation; Competitive Advantage; Momentum; Catalysts; Inflation Resilience</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>High market sensitivity / beta</t>
         </is>
       </c>
     </row>
@@ -1515,16 +1520,16 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>VRT</t>
+          <t>ACMR</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Vertiv Holdings Co</t>
+          <t>ACM Research, Inc.</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>42.27</v>
+        <v>42.36</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -1532,7 +1537,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>263.8099975585938</v>
+        <v>78.95999908447266</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1540,24 +1545,24 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>100</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="I22" t="n">
-        <v>100</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Earnings Fcf</t>
+          <t>Revenue Growth</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Industry Growth; Valuation; Competitive Advantage; Momentum; Catalysts; Inflation Resilience</t>
+          <t>Industry Growth; Competitive Advantage; Catalysts; Inflation Resilience</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>High market sensitivity / beta</t>
+          <t>Negative free cash flow / unprofitable growth</t>
         </is>
       </c>
     </row>
@@ -1567,16 +1572,16 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>ACMR</t>
+          <t>ASML</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>ACM Research, Inc.</t>
+          <t>ASML Holding N.V.</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>42.13</v>
+        <v>42.35</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -1584,7 +1589,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>79.11000061035156</v>
+        <v>1726.2900390625</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1592,24 +1597,19 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>94.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="I23" t="n">
-        <v>94.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Revenue Growth</t>
+          <t>Earnings Fcf; Balance Sheet</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Industry Growth; Competitive Advantage; Catalysts; Inflation Resilience</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>Negative free cash flow / unprofitable growth</t>
+          <t>Industry Growth; Valuation; Competitive Advantage; Catalysts; Inflation Resilience</t>
         </is>
       </c>
     </row>
@@ -1619,16 +1619,16 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>SMCI</t>
+          <t>PANW</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Super Micro Computer, Inc.</t>
+          <t>Palo Alto Networks, Inc.</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>41.9</v>
+        <v>42.07</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -1636,11 +1636,11 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>37.38999938964844</v>
+        <v>373.25</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="H24" t="n">
@@ -1651,17 +1651,17 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Revenue Growth; Valuation</t>
+          <t>Revenue Growth; Momentum</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>Industry Growth; Balance Sheet; Competitive Advantage; Catalysts; Inflation Resilience</t>
+          <t>Industry Growth; Valuation; Competitive Advantage; Catalysts; Inflation Resilience</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>Negative free cash flow / unprofitable growth</t>
+          <t>Excessive price-to-sales valuation; Very high earnings multiple</t>
         </is>
       </c>
     </row>
@@ -1671,16 +1671,16 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>PANW</t>
+          <t>SMCI</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Palo Alto Networks, Inc.</t>
+          <t>Super Micro Computer, Inc.</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>41.52</v>
+        <v>41.78</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -1688,11 +1688,11 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>339.3099975585938</v>
+        <v>38.2400016784668</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="H25" t="n">
@@ -1703,17 +1703,17 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Revenue Growth; Momentum</t>
+          <t>Revenue Growth; Valuation</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>Industry Growth; Valuation; Competitive Advantage; Catalysts; Inflation Resilience</t>
+          <t>Industry Growth; Balance Sheet; Competitive Advantage; Momentum; Catalysts; Inflation Resilience</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>Excessive price-to-sales valuation; Very high earnings multiple</t>
+          <t>Negative free cash flow / unprofitable growth</t>
         </is>
       </c>
     </row>
@@ -1732,7 +1732,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>40.34</v>
+        <v>40.8</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -1740,7 +1740,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>251.0599975585938</v>
+        <v>256.1849975585938</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1775,16 +1775,16 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>META</t>
+          <t>CRWD</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Meta Platforms, Inc.</t>
+          <t>CrowdStrike Holdings, Inc.</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>39.74</v>
+        <v>40.78</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -1792,27 +1792,32 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>576.1400146484375</v>
+        <v>221.3370971679688</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>100</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="I27" t="n">
-        <v>100</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Revenue Growth</t>
+          <t>Balance Sheet; Momentum</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>Industry Growth; Competitive Advantage; Momentum; Catalysts; Inflation Resilience</t>
+          <t>Industry Growth; Valuation; Competitive Advantage; Catalysts; Inflation Resilience</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>Excessive price-to-sales valuation; Very high earnings multiple</t>
         </is>
       </c>
     </row>
@@ -1831,7 +1836,7 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>39.6</v>
+        <v>39.89</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -1839,7 +1844,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>245.1100006103516</v>
+        <v>244.4250030517578</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1874,16 +1879,16 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>CRWD</t>
+          <t>META</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>CrowdStrike Holdings, Inc.</t>
+          <t>Meta Platforms, Inc.</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>39.52</v>
+        <v>39.59</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -1891,7 +1896,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>189.1799926757812</v>
+        <v>571.531005859375</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1899,24 +1904,19 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>88.2</v>
+        <v>100</v>
       </c>
       <c r="I29" t="n">
-        <v>88.2</v>
+        <v>100</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Balance Sheet</t>
+          <t>Revenue Growth</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>Industry Growth; Valuation; Competitive Advantage; Catalysts; Inflation Resilience</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>Excessive price-to-sales valuation</t>
+          <t>Industry Growth; Competitive Advantage; Momentum; Catalysts; Inflation Resilience</t>
         </is>
       </c>
     </row>
@@ -1935,7 +1935,7 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>36</v>
+        <v>36.39</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -1943,7 +1943,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>125.8000030517578</v>
+        <v>137.522705078125</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1958,7 +1958,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>Earnings Fcf; Industry Growth; Competitive Advantage; Catalysts; Inflation Resilience</t>
+          <t>Earnings Fcf; Industry Growth; Valuation; Competitive Advantage; Catalysts; Inflation Resilience</t>
         </is>
       </c>
     </row>
@@ -1977,7 +1977,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>31.51</v>
+        <v>31.47</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -1985,7 +1985,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>148.8699951171875</v>
+        <v>149.4049987792969</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -2131,13 +2131,13 @@
         <v>9.02</v>
       </c>
       <c r="F2" t="n">
-        <v>7.19</v>
+        <v>7.31</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>6.61</v>
+        <v>6.94</v>
       </c>
       <c r="I2" t="n">
         <v>3.5</v>
@@ -2149,7 +2149,7 @@
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>56.32</v>
+        <v>56.77</v>
       </c>
     </row>
     <row r="3">
@@ -2171,13 +2171,13 @@
         <v>8.84</v>
       </c>
       <c r="F3" t="n">
-        <v>8.68</v>
+        <v>8.65</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>5.12</v>
+        <v>5.39</v>
       </c>
       <c r="I3" t="n">
         <v>2.69</v>
@@ -2189,13 +2189,13 @@
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>55.33</v>
+        <v>55.57</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ANET</t>
+          <t>CRDO</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -2208,19 +2208,19 @@
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>10</v>
+        <v>9.91</v>
       </c>
       <c r="F4" t="n">
-        <v>0.78</v>
+        <v>2.36</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>8.609999999999999</v>
+        <v>7.71</v>
       </c>
       <c r="I4" t="n">
-        <v>3.63</v>
+        <v>3.54</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -2229,13 +2229,13 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>53.02</v>
+        <v>53.52</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CRDO</t>
+          <t>ANET</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -2248,19 +2248,19 @@
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>9.91</v>
+        <v>10</v>
       </c>
       <c r="F5" t="n">
-        <v>2.46</v>
+        <v>0.78</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>6.87</v>
+        <v>8.57</v>
       </c>
       <c r="I5" t="n">
-        <v>3.56</v>
+        <v>3.63</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -2269,7 +2269,7 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>52.8</v>
+        <v>52.98</v>
       </c>
     </row>
     <row r="6">
@@ -2291,13 +2291,13 @@
         <v>9.890000000000001</v>
       </c>
       <c r="F6" t="n">
-        <v>0.67</v>
+        <v>0.64</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>8.050000000000001</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="I6" t="n">
         <v>3.35</v>
@@ -2309,38 +2309,38 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>51.96</v>
+        <v>52.27</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>TER</t>
+          <t>DELL</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>15</v>
       </c>
       <c r="C7" t="n">
-        <v>15</v>
+        <v>11.48</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>8.9</v>
+        <v>6.33</v>
       </c>
       <c r="F7" t="n">
-        <v>2.95</v>
+        <v>5.75</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>5.25</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="I7" t="n">
-        <v>3.75</v>
+        <v>3.54</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -2349,38 +2349,38 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>50.85</v>
+        <v>51.15</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>DELL</t>
+          <t>TER</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>15</v>
       </c>
       <c r="C8" t="n">
-        <v>11.48</v>
+        <v>15</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>6.33</v>
+        <v>8.9</v>
       </c>
       <c r="F8" t="n">
-        <v>5.77</v>
+        <v>2.94</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>8.57</v>
+        <v>5.21</v>
       </c>
       <c r="I8" t="n">
-        <v>3.54</v>
+        <v>3.75</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -2389,7 +2389,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>50.69</v>
+        <v>50.8</v>
       </c>
     </row>
     <row r="9">
@@ -2411,13 +2411,13 @@
         <v>9.029999999999999</v>
       </c>
       <c r="F9" t="n">
-        <v>3.22</v>
+        <v>2.95</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>4.08</v>
+        <v>5.37</v>
       </c>
       <c r="I9" t="n">
         <v>3.44</v>
@@ -2429,7 +2429,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>49.77</v>
+        <v>50.79</v>
       </c>
     </row>
     <row r="10">
@@ -2451,7 +2451,7 @@
         <v>9.699999999999999</v>
       </c>
       <c r="F10" t="n">
-        <v>7</v>
+        <v>6.52</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -2469,7 +2469,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>48.13</v>
+        <v>47.65</v>
       </c>
     </row>
     <row r="11">
@@ -2491,13 +2491,13 @@
         <v>8.77</v>
       </c>
       <c r="F11" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>6.1</v>
+        <v>6.18</v>
       </c>
       <c r="I11" t="n">
         <v>3.45</v>
@@ -2509,7 +2509,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>47.52</v>
+        <v>47.62</v>
       </c>
     </row>
     <row r="12">
@@ -2531,13 +2531,13 @@
         <v>8.34</v>
       </c>
       <c r="F12" t="n">
+        <v>4.46</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="n">
         <v>4.42</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" t="n">
-        <v>4.68</v>
       </c>
       <c r="I12" t="n">
         <v>3.53</v>
@@ -2549,7 +2549,7 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>46.92</v>
+        <v>46.7</v>
       </c>
     </row>
     <row r="13">
@@ -2571,13 +2571,13 @@
         <v>7.78</v>
       </c>
       <c r="F13" t="n">
-        <v>2.05</v>
+        <v>2.16</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>5.79</v>
+        <v>5.63</v>
       </c>
       <c r="I13" t="n">
         <v>3.58</v>
@@ -2589,7 +2589,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>45.38</v>
+        <v>45.33</v>
       </c>
     </row>
     <row r="14">
@@ -2611,13 +2611,13 @@
         <v>8.98</v>
       </c>
       <c r="F14" t="n">
-        <v>0.86</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>6.05</v>
+        <v>6.54</v>
       </c>
       <c r="I14" t="n">
         <v>3.67</v>
@@ -2629,7 +2629,7 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>44.67</v>
+        <v>45.11</v>
       </c>
     </row>
     <row r="15">
@@ -2651,13 +2651,13 @@
         <v>6.16</v>
       </c>
       <c r="F15" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>3.07</v>
+        <v>3.47</v>
       </c>
       <c r="I15" t="n">
         <v>3.53</v>
@@ -2669,7 +2669,7 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>43.83</v>
+        <v>44.19</v>
       </c>
     </row>
     <row r="16">
@@ -2691,13 +2691,13 @@
         <v>9.880000000000001</v>
       </c>
       <c r="F16" t="n">
-        <v>1.97</v>
+        <v>1.69</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>9.050000000000001</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="I16" t="n">
         <v>3.73</v>
@@ -2709,7 +2709,7 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>43.45</v>
+        <v>43.58</v>
       </c>
     </row>
     <row r="17">
@@ -2731,13 +2731,13 @@
         <v>7.58</v>
       </c>
       <c r="F17" t="n">
-        <v>1.03</v>
+        <v>0.99</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>8.890000000000001</v>
+        <v>9.06</v>
       </c>
       <c r="I17" t="n">
         <v>3.56</v>
@@ -2749,38 +2749,38 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>43</v>
+        <v>43.13</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>AMZN</t>
+          <t>NET</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>9.220000000000001</v>
+        <v>15</v>
       </c>
       <c r="C18" t="n">
-        <v>12.28</v>
+        <v>7.5</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>6.64</v>
+        <v>7.71</v>
       </c>
       <c r="F18" t="n">
-        <v>6.5</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>4.86</v>
+        <v>8.43</v>
       </c>
       <c r="I18" t="n">
-        <v>3.47</v>
+        <v>3.64</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2789,38 +2789,38 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>42.97</v>
+        <v>42.84</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>NET</t>
+          <t>AMZN</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>15</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="C19" t="n">
-        <v>7.5</v>
+        <v>12.28</v>
       </c>
       <c r="D19" t="n">
         <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>7.71</v>
+        <v>6.64</v>
       </c>
       <c r="F19" t="n">
-        <v>0.59</v>
+        <v>6.53</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>8.34</v>
+        <v>4.5</v>
       </c>
       <c r="I19" t="n">
-        <v>3.64</v>
+        <v>3.47</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2829,7 +2829,7 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>42.78</v>
+        <v>42.64</v>
       </c>
     </row>
     <row r="20">
@@ -2851,13 +2851,13 @@
         <v>6.87</v>
       </c>
       <c r="F20" t="n">
-        <v>2.94</v>
+        <v>2.87</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>6.19</v>
+        <v>6.06</v>
       </c>
       <c r="I20" t="n">
         <v>3.45</v>
@@ -2869,38 +2869,38 @@
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>42.59</v>
+        <v>42.39</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ASML</t>
+          <t>VRT</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>9.859999999999999</v>
+        <v>10.91</v>
       </c>
       <c r="C21" t="n">
-        <v>14.28</v>
+        <v>13.39</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>8.960000000000001</v>
+        <v>7.41</v>
       </c>
       <c r="F21" t="n">
-        <v>0.5600000000000001</v>
+        <v>3.29</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>6</v>
+        <v>3.83</v>
       </c>
       <c r="I21" t="n">
-        <v>2.76</v>
+        <v>3.56</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2909,38 +2909,38 @@
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>42.42</v>
+        <v>42.39</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>VRT</t>
+          <t>ACMR</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>10.91</v>
+        <v>15</v>
       </c>
       <c r="C22" t="n">
-        <v>13.39</v>
+        <v>7.83</v>
       </c>
       <c r="D22" t="n">
         <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>7.41</v>
+        <v>4.02</v>
       </c>
       <c r="F22" t="n">
-        <v>3.32</v>
+        <v>6.88</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>3.68</v>
+        <v>5</v>
       </c>
       <c r="I22" t="n">
-        <v>3.56</v>
+        <v>3.63</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2949,38 +2949,38 @@
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>42.27</v>
+        <v>42.36</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ACMR</t>
+          <t>ASML</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>15</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="C23" t="n">
-        <v>7.83</v>
+        <v>14.28</v>
       </c>
       <c r="D23" t="n">
         <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>4.02</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="F23" t="n">
-        <v>6.88</v>
+        <v>0.57</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>4.77</v>
+        <v>5.92</v>
       </c>
       <c r="I23" t="n">
-        <v>3.63</v>
+        <v>2.76</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2989,38 +2989,38 @@
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>42.13</v>
+        <v>42.35</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>SMCI</t>
+          <t>PANW</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>15</v>
+        <v>13.54</v>
       </c>
       <c r="C24" t="n">
-        <v>7.23</v>
+        <v>7.5</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>2.23</v>
+        <v>7.97</v>
       </c>
       <c r="F24" t="n">
-        <v>9.880000000000001</v>
+        <v>0.54</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>4.02</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="I24" t="n">
-        <v>3.54</v>
+        <v>3.57</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -3029,38 +3029,38 @@
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>41.9</v>
+        <v>42.07</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>PANW</t>
+          <t>SMCI</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>13.54</v>
+        <v>15</v>
       </c>
       <c r="C25" t="n">
-        <v>7.5</v>
+        <v>7.23</v>
       </c>
       <c r="D25" t="n">
         <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>7.97</v>
+        <v>2.23</v>
       </c>
       <c r="F25" t="n">
-        <v>0.6</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>8.34</v>
+        <v>3.92</v>
       </c>
       <c r="I25" t="n">
-        <v>3.57</v>
+        <v>3.54</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -3069,7 +3069,7 @@
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>41.52</v>
+        <v>41.78</v>
       </c>
     </row>
     <row r="26">
@@ -3091,13 +3091,13 @@
         <v>9.449999999999999</v>
       </c>
       <c r="F26" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>5.42</v>
+        <v>5.89</v>
       </c>
       <c r="I26" t="n">
         <v>3.7</v>
@@ -3109,38 +3109,38 @@
         <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>40.34</v>
+        <v>40.8</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>META</t>
+          <t>CRWD</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>12.38</v>
+        <v>11.47</v>
       </c>
       <c r="C27" t="n">
-        <v>10</v>
+        <v>7.5</v>
       </c>
       <c r="D27" t="n">
         <v>0</v>
       </c>
       <c r="E27" t="n">
-        <v>7.23</v>
+        <v>9.24</v>
       </c>
       <c r="F27" t="n">
-        <v>5.59</v>
+        <v>0.29</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>1.05</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I27" t="n">
-        <v>3.49</v>
+        <v>3.48</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3149,7 +3149,7 @@
         <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>39.74</v>
+        <v>40.78</v>
       </c>
     </row>
     <row r="28">
@@ -3177,7 +3177,7 @@
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>8.77</v>
+        <v>9.06</v>
       </c>
       <c r="I28" t="n">
         <v>3.53</v>
@@ -3189,38 +3189,38 @@
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>39.6</v>
+        <v>39.89</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>CRWD</t>
+          <t>META</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>11.47</v>
+        <v>12.38</v>
       </c>
       <c r="C29" t="n">
-        <v>7.5</v>
+        <v>10</v>
       </c>
       <c r="D29" t="n">
         <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>9.24</v>
+        <v>7.23</v>
       </c>
       <c r="F29" t="n">
-        <v>0.45</v>
+        <v>5.63</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>7.38</v>
+        <v>0.86</v>
       </c>
       <c r="I29" t="n">
-        <v>3.48</v>
+        <v>3.49</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3229,7 +3229,7 @@
         <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>39.52</v>
+        <v>39.59</v>
       </c>
     </row>
     <row r="30">
@@ -3251,13 +3251,13 @@
         <v>6.78</v>
       </c>
       <c r="F30" t="n">
-        <v>4.09</v>
+        <v>3.67</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>5</v>
+        <v>5.81</v>
       </c>
       <c r="I30" t="n">
         <v>3.57</v>
@@ -3269,7 +3269,7 @@
         <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>36</v>
+        <v>36.39</v>
       </c>
     </row>
     <row r="31">
@@ -3291,13 +3291,13 @@
         <v>0.8</v>
       </c>
       <c r="F31" t="n">
-        <v>6.41</v>
+        <v>6.39</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="I31" t="n">
         <v>3.58</v>
@@ -3309,7 +3309,7 @@
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>31.51</v>
+        <v>31.47</v>
       </c>
     </row>
   </sheetData>
@@ -3346,9 +3346,9 @@
     <col width="11" customWidth="1" min="17" max="17"/>
     <col width="16" customWidth="1" min="18" max="18"/>
     <col width="19" customWidth="1" min="19" max="19"/>
-    <col width="22" customWidth="1" min="20" max="20"/>
+    <col width="23" customWidth="1" min="20" max="20"/>
     <col width="23" customWidth="1" min="21" max="21"/>
-    <col width="22" customWidth="1" min="22" max="22"/>
+    <col width="21" customWidth="1" min="22" max="22"/>
     <col width="22" customWidth="1" min="23" max="23"/>
     <col width="18" customWidth="1" min="24" max="24"/>
     <col width="24" customWidth="1" min="25" max="25"/>
@@ -3533,7 +3533,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>938.4000244140625</v>
+        <v>923.614990234375</v>
       </c>
       <c r="G2" t="n">
         <v>90273996800</v>
@@ -3542,7 +3542,7 @@
         <v>3.457</v>
       </c>
       <c r="I2" t="n">
-        <v>44.22</v>
+        <v>44.48</v>
       </c>
       <c r="J2" t="n">
         <v>13.685</v>
@@ -3563,29 +3563,29 @@
         <v>0.80370003</v>
       </c>
       <c r="Q2" t="n">
-        <v>21.221167</v>
+        <v>20.764727</v>
       </c>
       <c r="T2" t="n">
-        <v>0.04243502742615601</v>
+        <v>0.1256321612334348</v>
       </c>
       <c r="U2" t="n">
-        <v>0.01091583583902134</v>
+        <v>0.0002566657577935949</v>
       </c>
       <c r="V2" t="n">
-        <v>1.246210835388741</v>
+        <v>1.154184432539791</v>
       </c>
       <c r="W2" t="n">
-        <v>7.067864058049175</v>
+        <v>6.856453213664718</v>
       </c>
       <c r="X2" t="n">
-        <v>0.00242</v>
+        <v>0.00238</v>
       </c>
       <c r="Y2" t="n">
         <v>0.79987</v>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>2026-08-27T00:34:38.466961+00:00</t>
+          <t>2026-08-27T14:43:59.378693+00:00</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
@@ -3616,10 +3616,10 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2166338355200</v>
+        <v>2202176847872</v>
       </c>
       <c r="F3" t="n">
-        <v>417.6900024414062</v>
+        <v>424.6000061035156</v>
       </c>
       <c r="G3" t="n">
         <v>4440492343296</v>
@@ -3628,7 +3628,7 @@
         <v>0.36</v>
       </c>
       <c r="I3" t="n">
-        <v>13.45</v>
+        <v>13.41</v>
       </c>
       <c r="J3" t="n">
         <v>0.774</v>
@@ -3649,25 +3649,25 @@
         <v>0.60344005</v>
       </c>
       <c r="Q3" t="n">
-        <v>31.05502</v>
+        <v>31.66294</v>
       </c>
       <c r="R3" t="n">
-        <v>0.48785993</v>
+        <v>0.4959308</v>
       </c>
       <c r="S3" t="n">
-        <v>2.964232678594488</v>
+        <v>3.013271015969123</v>
       </c>
       <c r="T3" t="n">
-        <v>0.04660604443657346</v>
+        <v>0.08230738126957671</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.009608562530477482</v>
+        <v>0.00172852670241852</v>
       </c>
       <c r="V3" t="n">
-        <v>0.08839375381353065</v>
+        <v>0.1007494875724653</v>
       </c>
       <c r="W3" t="n">
-        <v>0.7690575911628716</v>
+        <v>0.7940400775703229</v>
       </c>
       <c r="X3" t="n">
         <v>0.00013</v>
@@ -3677,7 +3677,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>2026-08-27T00:34:41.669974+00:00</t>
+          <t>2026-08-27T14:44:03.592961+00:00</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
@@ -3689,12 +3689,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ANET</t>
+          <t>CRDO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Arista Networks, Inc.</t>
+          <t>Credo Technology Group Holding Ltd</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -3704,72 +3704,72 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Computer Hardware</t>
+          <t>Semiconductors</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>255082692608</v>
+        <v>44502929408</v>
       </c>
       <c r="F4" t="n">
-        <v>202.25</v>
+        <v>236.8000030517578</v>
       </c>
       <c r="G4" t="n">
-        <v>10540800000</v>
+        <v>1335116032</v>
       </c>
       <c r="H4" t="n">
-        <v>0.377</v>
+        <v>1.57</v>
       </c>
       <c r="I4" t="n">
-        <v>3.15</v>
+        <v>2.51</v>
       </c>
       <c r="J4" t="n">
-        <v>0.357</v>
+        <v>3.432</v>
       </c>
       <c r="K4" t="n">
-        <v>3891512576</v>
+        <v>250810128</v>
       </c>
       <c r="M4" t="n">
-        <v>13343299584</v>
+        <v>1443286016</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>25448000</v>
       </c>
       <c r="O4" t="n">
-        <v>0.63004</v>
+        <v>0.68035007</v>
       </c>
       <c r="P4" t="n">
-        <v>0.45393002</v>
+        <v>0.35661998</v>
       </c>
       <c r="Q4" t="n">
-        <v>64.206345</v>
+        <v>94.34263</v>
       </c>
       <c r="R4" t="n">
-        <v>24.199556</v>
+        <v>33.33263</v>
       </c>
       <c r="S4" t="n">
-        <v>65.54846929730184</v>
+        <v>177.4367317734473</v>
       </c>
       <c r="T4" t="n">
-        <v>0.1844109071571998</v>
+        <v>0.2315373650670862</v>
       </c>
       <c r="U4" t="n">
-        <v>0.310673340677118</v>
+        <v>0.0649876166026051</v>
       </c>
       <c r="V4" t="n">
-        <v>0.5706297529668847</v>
+        <v>0.9180301701584876</v>
       </c>
       <c r="W4" t="n">
-        <v>0.5062932417101436</v>
+        <v>0.9294385771592979</v>
       </c>
       <c r="X4" t="n">
-        <v>0.17247999</v>
+        <v>0.09436</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.73305</v>
+        <v>0.73627</v>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>2026-08-27T00:34:42.843660+00:00</t>
+          <t>2026-08-27T14:44:00.144680+00:00</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
@@ -3781,12 +3781,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CRDO</t>
+          <t>ANET</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Credo Technology Group Holding Ltd</t>
+          <t>Arista Networks, Inc.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -3796,72 +3796,72 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Semiconductors</t>
+          <t>Computer Hardware</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>42565324800</v>
+        <v>254130470912</v>
       </c>
       <c r="F5" t="n">
-        <v>226.4900054931641</v>
+        <v>201.4949951171875</v>
       </c>
       <c r="G5" t="n">
-        <v>1335116032</v>
+        <v>10540800000</v>
       </c>
       <c r="H5" t="n">
-        <v>1.57</v>
+        <v>0.377</v>
       </c>
       <c r="I5" t="n">
-        <v>2.51</v>
+        <v>3.16</v>
       </c>
       <c r="J5" t="n">
-        <v>3.432</v>
+        <v>0.357</v>
       </c>
       <c r="K5" t="n">
-        <v>250810128</v>
+        <v>3891512576</v>
       </c>
       <c r="M5" t="n">
-        <v>1443286016</v>
+        <v>13343299584</v>
       </c>
       <c r="N5" t="n">
-        <v>25448000</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>0.68035007</v>
+        <v>0.63004</v>
       </c>
       <c r="P5" t="n">
-        <v>0.35661998</v>
+        <v>0.45393002</v>
       </c>
       <c r="Q5" t="n">
-        <v>90.23506</v>
+        <v>63.764236</v>
       </c>
       <c r="R5" t="n">
-        <v>31.881367</v>
+        <v>24.10922</v>
       </c>
       <c r="S5" t="n">
-        <v>169.7113475417548</v>
+        <v>65.30377737419909</v>
       </c>
       <c r="T5" t="n">
-        <v>0.08816184374615799</v>
+        <v>0.1872900073412296</v>
       </c>
       <c r="U5" t="n">
-        <v>0.02377620515846823</v>
+        <v>0.2977071525264661</v>
       </c>
       <c r="V5" t="n">
-        <v>0.8744517260691917</v>
+        <v>0.5162540149193733</v>
       </c>
       <c r="W5" t="n">
-        <v>0.8858451987571647</v>
+        <v>0.5119305819578537</v>
       </c>
       <c r="X5" t="n">
-        <v>0.10795</v>
+        <v>0.17247999</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.73627</v>
+        <v>0.73305</v>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>2026-08-27T00:34:39.009148+00:00</t>
+          <t>2026-08-27T14:44:05.320159+00:00</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
@@ -3892,10 +3892,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>426542858240</v>
+        <v>444109225984</v>
       </c>
       <c r="F6" t="n">
-        <v>177.5</v>
+        <v>184.8099975585938</v>
       </c>
       <c r="G6" t="n">
         <v>6155940864</v>
@@ -3925,25 +3925,25 @@
         <v>0.47120997</v>
       </c>
       <c r="Q6" t="n">
-        <v>151.70941</v>
+        <v>157.95728</v>
       </c>
       <c r="R6" t="n">
-        <v>69.28963</v>
+        <v>72.143196</v>
       </c>
       <c r="S6" t="n">
-        <v>197.5554475799271</v>
+        <v>205.6913982235243</v>
       </c>
       <c r="T6" t="n">
-        <v>0.3495020272739402</v>
+        <v>0.49607382324015</v>
       </c>
       <c r="U6" t="n">
-        <v>0.3395216010732165</v>
+        <v>0.2893121409250441</v>
       </c>
       <c r="V6" t="n">
-        <v>0.3776777789910486</v>
+        <v>0.3772262776378634</v>
       </c>
       <c r="W6" t="n">
-        <v>0.1033754297729554</v>
+        <v>0.1792368307752403</v>
       </c>
       <c r="X6" t="n">
         <v>0.03477</v>
@@ -3953,7 +3953,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>2026-08-27T00:34:37.231816+00:00</t>
+          <t>2026-08-27T14:43:57.558862+00:00</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr">
@@ -3965,12 +3965,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>TER</t>
+          <t>DELL</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Teradyne, Inc.</t>
+          <t>Dell Technologies Inc.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -3980,72 +3980,72 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Semiconductor Equipment &amp; Materials</t>
+          <t>Computer Hardware</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>56767328256</v>
+        <v>301851901952</v>
       </c>
       <c r="F7" t="n">
-        <v>363.1000061035156</v>
+        <v>467.1600036621094</v>
       </c>
       <c r="G7" t="n">
-        <v>4464031232</v>
+        <v>134001999872</v>
       </c>
       <c r="H7" t="n">
-        <v>1.039</v>
+        <v>0.875</v>
       </c>
       <c r="I7" t="n">
-        <v>7.29</v>
+        <v>12.57</v>
       </c>
       <c r="J7" t="n">
-        <v>3.858</v>
+        <v>2.825</v>
       </c>
       <c r="K7" t="n">
-        <v>437381248</v>
+        <v>5434124800</v>
       </c>
       <c r="M7" t="n">
-        <v>354828992</v>
+        <v>11580999680</v>
       </c>
       <c r="N7" t="n">
-        <v>100127000</v>
+        <v>31924000768</v>
       </c>
       <c r="O7" t="n">
-        <v>0.5924199999999999</v>
+        <v>0.19212</v>
       </c>
       <c r="P7" t="n">
-        <v>0.33161</v>
+        <v>0.08857000600000001</v>
       </c>
       <c r="Q7" t="n">
-        <v>49.807957</v>
+        <v>37.16468</v>
       </c>
       <c r="R7" t="n">
-        <v>12.716606</v>
+        <v>2.2525926</v>
       </c>
       <c r="S7" t="n">
-        <v>129.7891222259259</v>
+        <v>55.54747324757798</v>
       </c>
       <c r="T7" t="n">
-        <v>0.08462531893408998</v>
+        <v>0.1914307482534894</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.03387164655181729</v>
+        <v>0.4758933103739844</v>
       </c>
       <c r="V7" t="n">
-        <v>0.1037623091873037</v>
+        <v>2.801261827107127</v>
       </c>
       <c r="W7" t="n">
-        <v>2.069130006189561</v>
+        <v>2.570664423673745</v>
       </c>
       <c r="X7" t="n">
-        <v>0.00202</v>
+        <v>0.07491</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.00462</v>
+        <v>0.75618</v>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>2026-08-27T00:34:39.309114+00:00</t>
+          <t>2026-08-27T14:44:05.616488+00:00</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr">
@@ -4057,12 +4057,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>DELL</t>
+          <t>TER</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Dell Technologies Inc.</t>
+          <t>Teradyne, Inc.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -4072,72 +4072,72 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Computer Hardware</t>
+          <t>Semiconductor Equipment &amp; Materials</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>299693768704</v>
+        <v>56861913088</v>
       </c>
       <c r="F8" t="n">
-        <v>463.8200073242188</v>
+        <v>363.7049865722656</v>
       </c>
       <c r="G8" t="n">
-        <v>134001999872</v>
+        <v>4464031232</v>
       </c>
       <c r="H8" t="n">
-        <v>0.875</v>
+        <v>1.039</v>
       </c>
       <c r="I8" t="n">
-        <v>12.55</v>
+        <v>7.26</v>
       </c>
       <c r="J8" t="n">
-        <v>2.825</v>
+        <v>3.858</v>
       </c>
       <c r="K8" t="n">
-        <v>5434124800</v>
+        <v>437381248</v>
       </c>
       <c r="M8" t="n">
-        <v>11580999680</v>
+        <v>354828992</v>
       </c>
       <c r="N8" t="n">
-        <v>31924000768</v>
+        <v>100127000</v>
       </c>
       <c r="O8" t="n">
-        <v>0.19212</v>
+        <v>0.5924199999999999</v>
       </c>
       <c r="P8" t="n">
-        <v>0.08857000600000001</v>
+        <v>0.33161</v>
       </c>
       <c r="Q8" t="n">
-        <v>36.957767</v>
+        <v>50.097103</v>
       </c>
       <c r="R8" t="n">
-        <v>2.2364874</v>
+        <v>12.737795</v>
       </c>
       <c r="S8" t="n">
-        <v>55.15032866083605</v>
+        <v>130.005374825763</v>
       </c>
       <c r="T8" t="n">
-        <v>0.08645851197088117</v>
+        <v>0.13427411038617</v>
       </c>
       <c r="U8" t="n">
-        <v>0.521637737090519</v>
+        <v>-0.04951001601046368</v>
       </c>
       <c r="V8" t="n">
-        <v>2.890666027542702</v>
+        <v>0.06132180276838639</v>
       </c>
       <c r="W8" t="n">
-        <v>2.586002079856828</v>
+        <v>2.116813846967488</v>
       </c>
       <c r="X8" t="n">
-        <v>0.07491</v>
+        <v>0.00202</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.75615</v>
+        <v>1.00462</v>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>2026-08-27T00:34:43.138674+00:00</t>
+          <t>2026-08-27T14:44:00.563465+00:00</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr">
@@ -4168,10 +4168,10 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5078174924800</v>
+        <v>5445365268480</v>
       </c>
       <c r="F9" t="n">
-        <v>209.6600036621094</v>
+        <v>224.8000030517578</v>
       </c>
       <c r="G9" t="n">
         <v>253491003392</v>
@@ -4180,7 +4180,7 @@
         <v>0.852</v>
       </c>
       <c r="I9" t="n">
-        <v>6.44</v>
+        <v>6.52</v>
       </c>
       <c r="J9" t="n">
         <v>2.145</v>
@@ -4201,25 +4201,25 @@
         <v>0.65596</v>
       </c>
       <c r="Q9" t="n">
-        <v>32.5559</v>
+        <v>34.481598</v>
       </c>
       <c r="R9" t="n">
-        <v>20.032959</v>
+        <v>21.478674</v>
       </c>
       <c r="S9" t="n">
-        <v>109.5948903815781</v>
+        <v>117.5194274565526</v>
       </c>
       <c r="T9" t="n">
-        <v>0.06691776257118565</v>
+        <v>0.1410588768071743</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.01267941170679843</v>
+        <v>0.05046445774189645</v>
       </c>
       <c r="V9" t="n">
-        <v>0.08849214566613828</v>
+        <v>0.1509214367724905</v>
       </c>
       <c r="W9" t="n">
-        <v>0.1549719021363523</v>
+        <v>0.2395341452801176</v>
       </c>
       <c r="X9" t="n">
         <v>0.03991</v>
@@ -4229,7 +4229,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>2026-08-27T00:34:36.952567+00:00</t>
+          <t>2026-08-27T14:43:57.233780+00:00</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr">
@@ -4260,10 +4260,10 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>8683695104</v>
+        <v>9450513408</v>
       </c>
       <c r="F10" t="n">
-        <v>16.76000022888184</v>
+        <v>18.23999977111816</v>
       </c>
       <c r="G10" t="n">
         <v>1672329984</v>
@@ -4290,25 +4290,25 @@
         <v>0.07274</v>
       </c>
       <c r="Q10" t="n">
-        <v>27.933332</v>
+        <v>30.399998</v>
       </c>
       <c r="R10" t="n">
-        <v>5.1925726</v>
+        <v>5.6511054</v>
       </c>
       <c r="S10" t="n">
-        <v>16.97514114023532</v>
+        <v>18.47413998616669</v>
       </c>
       <c r="T10" t="n">
-        <v>0.4423408256406751</v>
+        <v>0.4963084822800812</v>
       </c>
       <c r="U10" t="n">
-        <v>0.5017921557380944</v>
+        <v>0.5751295242911063</v>
       </c>
       <c r="V10" t="n">
-        <v>0.6594059005810615</v>
+        <v>0.8350101148007094</v>
       </c>
       <c r="W10" t="n">
-        <v>0.5489834289828155</v>
+        <v>0.6373428374309795</v>
       </c>
       <c r="X10" t="n">
         <v>0.09236999999999999</v>
@@ -4318,7 +4318,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>2026-08-27T00:34:45.352446+00:00</t>
+          <t>2026-08-27T14:44:08.754770+00:00</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr">
@@ -4349,10 +4349,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>785106206720</v>
+        <v>774658392064</v>
       </c>
       <c r="F11" t="n">
-        <v>480.9299926757812</v>
+        <v>474.5299987792969</v>
       </c>
       <c r="G11" t="n">
         <v>41305001984</v>
@@ -4361,7 +4361,7 @@
         <v>0.501</v>
       </c>
       <c r="I11" t="n">
-        <v>3.93</v>
+        <v>3.94</v>
       </c>
       <c r="J11" t="n">
         <v>1.595</v>
@@ -4382,25 +4382,25 @@
         <v>0.1725</v>
       </c>
       <c r="Q11" t="n">
-        <v>122.37404</v>
+        <v>120.43909</v>
       </c>
       <c r="R11" t="n">
-        <v>19.007534</v>
+        <v>18.754591</v>
       </c>
       <c r="S11" t="n">
-        <v>88.79785533866935</v>
+        <v>87.61617631678946</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.02832613230724723</v>
+        <v>0.04379482617560004</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.02948301977077639</v>
+        <v>-0.08407810576968278</v>
       </c>
       <c r="V11" t="n">
-        <v>1.249017961615839</v>
+        <v>1.25045052359732</v>
       </c>
       <c r="W11" t="n">
-        <v>1.886388229321053</v>
+        <v>1.839286692488436</v>
       </c>
       <c r="X11" t="n">
         <v>0.00425</v>
@@ -4410,7 +4410,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>2026-08-27T00:34:37.497329+00:00</t>
+          <t>2026-08-27T14:43:58.004431+00:00</t>
         </is>
       </c>
       <c r="AD11" t="inlineStr">
@@ -4441,10 +4441,10 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4182637805568</v>
+        <v>4150167339008</v>
       </c>
       <c r="F12" t="n">
-        <v>342</v>
+        <v>339.3399963378906</v>
       </c>
       <c r="G12" t="n">
         <v>445865984000</v>
@@ -4453,7 +4453,7 @@
         <v>0.242</v>
       </c>
       <c r="I12" t="n">
-        <v>19.92</v>
+        <v>19.94</v>
       </c>
       <c r="J12" t="n">
         <v>2.94</v>
@@ -4474,25 +4474,25 @@
         <v>0.34033</v>
       </c>
       <c r="Q12" t="n">
-        <v>17.168674</v>
+        <v>17.018305</v>
       </c>
       <c r="R12" t="n">
-        <v>9.380931</v>
+        <v>9.307968000000001</v>
       </c>
       <c r="S12" t="n">
-        <v>184.5416999076977</v>
+        <v>183.1090740447072</v>
       </c>
       <c r="T12" t="n">
-        <v>0.04728075256258513</v>
+        <v>0.01687095090639623</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.1199128288795566</v>
+        <v>-0.1296678678371707</v>
       </c>
       <c r="V12" t="n">
-        <v>0.1014639984085435</v>
+        <v>0.085911530503884</v>
       </c>
       <c r="W12" t="n">
-        <v>0.6557672800620484</v>
+        <v>0.6401969535640104</v>
       </c>
       <c r="X12" t="n">
         <v>0.01596</v>
@@ -4502,7 +4502,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>2026-08-27T00:34:40.447126+00:00</t>
+          <t>2026-08-27T14:44:02.004564+00:00</t>
         </is>
       </c>
       <c r="AD12" t="inlineStr">
@@ -4533,10 +4533,10 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>380736307200</v>
+        <v>374411329536</v>
       </c>
       <c r="F13" t="n">
-        <v>479.760009765625</v>
+        <v>471.7850036621094</v>
       </c>
       <c r="G13" t="n">
         <v>30837000192</v>
@@ -4545,7 +4545,7 @@
         <v>0.248</v>
       </c>
       <c r="I13" t="n">
-        <v>11.57</v>
+        <v>11.61</v>
       </c>
       <c r="J13" t="n">
         <v>0.428</v>
@@ -4566,35 +4566,35 @@
         <v>0.33736</v>
       </c>
       <c r="Q13" t="n">
-        <v>41.465862</v>
+        <v>40.63652</v>
       </c>
       <c r="R13" t="n">
-        <v>12.346736</v>
+        <v>12.141626</v>
       </c>
       <c r="S13" t="n">
-        <v>123.8015833271179</v>
+        <v>121.7449309025817</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.07084097743649875</v>
+        <v>-0.008753097916871289</v>
       </c>
       <c r="U13" t="n">
-        <v>0.07144012846832659</v>
+        <v>0.05027910833708016</v>
       </c>
       <c r="V13" t="n">
-        <v>0.2723787176188721</v>
+        <v>0.1973075732160994</v>
       </c>
       <c r="W13" t="n">
-        <v>1.932426937302136</v>
+        <v>1.885786464938176</v>
       </c>
       <c r="X13" t="n">
         <v>0.00331</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.8631</v>
+        <v>0.86310995</v>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>2026-08-27T00:34:38.117605+00:00</t>
+          <t>2026-08-27T14:43:58.926476+00:00</t>
         </is>
       </c>
       <c r="AD13" t="inlineStr">
@@ -4625,10 +4625,10 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>81750605824</v>
+        <v>86910509056</v>
       </c>
       <c r="F14" t="n">
-        <v>227.6699981689453</v>
+        <v>242.0399932861328</v>
       </c>
       <c r="G14" t="n">
         <v>3966725120</v>
@@ -4637,7 +4637,7 @@
         <v>0.356</v>
       </c>
       <c r="I14" t="n">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="J14" t="n">
         <v>14.985</v>
@@ -4658,25 +4658,25 @@
         <v>0.00666</v>
       </c>
       <c r="Q14" t="n">
-        <v>464.63263</v>
+        <v>484.08</v>
       </c>
       <c r="R14" t="n">
-        <v>20.609093</v>
+        <v>21.90989</v>
       </c>
       <c r="S14" t="n">
-        <v>77.75313431356759</v>
+        <v>82.66072667938373</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.09604543152062561</v>
+        <v>-0.03523601492597594</v>
       </c>
       <c r="U14" t="n">
-        <v>0.02641901030093829</v>
+        <v>0.0745870510710791</v>
       </c>
       <c r="V14" t="n">
-        <v>1.180120631079434</v>
+        <v>1.193782192234185</v>
       </c>
       <c r="W14" t="n">
-        <v>0.8024701335563864</v>
+        <v>0.8373946795439899</v>
       </c>
       <c r="X14" t="n">
         <v>0.00619</v>
@@ -4686,7 +4686,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>2026-08-27T00:34:44.224129+00:00</t>
+          <t>2026-08-27T14:44:07.159805+00:00</t>
         </is>
       </c>
       <c r="AD14" t="inlineStr">
@@ -4717,10 +4717,10 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1691748007936</v>
+        <v>1745846403072</v>
       </c>
       <c r="F15" t="n">
-        <v>355.5899963378906</v>
+        <v>366.9609985351562</v>
       </c>
       <c r="G15" t="n">
         <v>75464998912</v>
@@ -4729,7 +4729,7 @@
         <v>0.479</v>
       </c>
       <c r="I15" t="n">
-        <v>5.99</v>
+        <v>6.01</v>
       </c>
       <c r="J15" t="n">
         <v>0.854</v>
@@ -4750,25 +4750,25 @@
         <v>0.48988</v>
       </c>
       <c r="Q15" t="n">
-        <v>59.36394</v>
+        <v>61.0584</v>
       </c>
       <c r="R15" t="n">
-        <v>22.41765</v>
+        <v>23.143282</v>
       </c>
       <c r="S15" t="n">
-        <v>62.16862128761064</v>
+        <v>64.15663760192022</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.07209958977819608</v>
+        <v>-0.03662021210481714</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.1557559291401385</v>
+        <v>-0.1383989134488648</v>
       </c>
       <c r="V15" t="n">
-        <v>0.09650034710357902</v>
+        <v>0.1083409245445435</v>
       </c>
       <c r="W15" t="n">
-        <v>0.2019577349749262</v>
+        <v>0.2311399127759233</v>
       </c>
       <c r="X15" t="n">
         <v>0.01948</v>
@@ -4778,7 +4778,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>2026-08-27T00:34:37.806390+00:00</t>
+          <t>2026-08-27T14:43:58.416337+00:00</t>
         </is>
       </c>
       <c r="AD15" t="inlineStr">
@@ -4809,10 +4809,10 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>32664209408</v>
+        <v>34685063168</v>
       </c>
       <c r="F16" t="n">
-        <v>406.1099853515625</v>
+        <v>431.2349853515625</v>
       </c>
       <c r="G16" t="n">
         <v>2602398976</v>
@@ -4839,22 +4839,22 @@
         <v>-0.03607</v>
       </c>
       <c r="R16" t="n">
-        <v>12.551577</v>
+        <v>13.328112</v>
       </c>
       <c r="S16" t="n">
-        <v>63.10639518550904</v>
+        <v>67.01063160518642</v>
       </c>
       <c r="T16" t="n">
-        <v>0.3112589085149573</v>
+        <v>0.3883040117519498</v>
       </c>
       <c r="U16" t="n">
-        <v>0.3791686379693362</v>
+        <v>0.3241064696929745</v>
       </c>
       <c r="V16" t="n">
-        <v>0.2995103281848004</v>
+        <v>0.3690434576371553</v>
       </c>
       <c r="W16" t="n">
-        <v>0.8946999733608334</v>
+        <v>0.4583529507927036</v>
       </c>
       <c r="X16" t="n">
         <v>0.02641</v>
@@ -4864,7 +4864,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>2026-08-27T00:34:45.065728+00:00</t>
+          <t>2026-08-27T14:44:08.393508+00:00</t>
         </is>
       </c>
       <c r="AD16" t="inlineStr">
@@ -4895,10 +4895,10 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>109307240448</v>
+        <v>114083389440</v>
       </c>
       <c r="F17" t="n">
-        <v>315.3699951171875</v>
+        <v>329.1499938964844</v>
       </c>
       <c r="G17" t="n">
         <v>5032822784</v>
@@ -4907,7 +4907,7 @@
         <v>0.335</v>
       </c>
       <c r="I17" t="n">
-        <v>-3.5</v>
+        <v>-3.53</v>
       </c>
       <c r="K17" t="n">
         <v>1739497728</v>
@@ -4925,22 +4925,22 @@
         <v>-0.22173999</v>
       </c>
       <c r="R17" t="n">
-        <v>21.718874</v>
+        <v>22.667873</v>
       </c>
       <c r="S17" t="n">
-        <v>62.8383921913349</v>
+        <v>65.58409798624353</v>
       </c>
       <c r="T17" t="n">
-        <v>0.155540010262726</v>
+        <v>0.2174508497197702</v>
       </c>
       <c r="U17" t="n">
-        <v>0.7994408593050975</v>
+        <v>0.3760451425411409</v>
       </c>
       <c r="V17" t="n">
-        <v>0.9580901521028253</v>
+        <v>0.9452158905298933</v>
       </c>
       <c r="W17" t="n">
-        <v>0.6226909452691944</v>
+        <v>0.6425470078298094</v>
       </c>
       <c r="X17" t="n">
         <v>0.02962</v>
@@ -4950,7 +4950,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>2026-08-27T00:34:43.956209+00:00</t>
+          <t>2026-08-27T14:44:06.743871+00:00</t>
         </is>
       </c>
       <c r="AD17" t="inlineStr">
@@ -4962,87 +4962,81 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>AMZN</t>
+          <t>NET</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Amazon.com, Inc.</t>
+          <t>Cloudflare, Inc.</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Internet Retail</t>
+          <t>Software - Infrastructure</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2807461576704</v>
+        <v>106948542464</v>
       </c>
       <c r="F18" t="n">
-        <v>260.2799987792969</v>
+        <v>300.3500061035156</v>
       </c>
       <c r="G18" t="n">
-        <v>775680032768</v>
+        <v>2512349952</v>
       </c>
       <c r="H18" t="n">
-        <v>0.196</v>
+        <v>0.359</v>
       </c>
       <c r="I18" t="n">
-        <v>12.43</v>
-      </c>
-      <c r="J18" t="n">
-        <v>2.423</v>
+        <v>-0.57</v>
       </c>
       <c r="K18" t="n">
-        <v>3219124992</v>
+        <v>692851968</v>
       </c>
       <c r="M18" t="n">
-        <v>122988003328</v>
+        <v>4162798080</v>
       </c>
       <c r="N18" t="n">
-        <v>251635007488</v>
+        <v>3529349888</v>
       </c>
       <c r="O18" t="n">
-        <v>0.5077</v>
+        <v>0.72577006</v>
       </c>
       <c r="P18" t="n">
-        <v>0.13689</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>20.939661</v>
+        <v>-0.07902000000000001</v>
       </c>
       <c r="R18" t="n">
-        <v>3.6193552</v>
+        <v>42.569126</v>
       </c>
       <c r="S18" t="n">
-        <v>872.119468389999</v>
+        <v>154.3598739752732</v>
       </c>
       <c r="T18" t="n">
-        <v>0.1248541400486338</v>
+        <v>0.1372586109891705</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.04256026141052616</v>
+        <v>0.3166893397916455</v>
       </c>
       <c r="V18" t="n">
-        <v>0.2479861997801025</v>
+        <v>0.7482537879410271</v>
       </c>
       <c r="W18" t="n">
-        <v>0.1380350274963091</v>
+        <v>0.4634086828336175</v>
       </c>
       <c r="X18" t="n">
-        <v>0.088690005</v>
+        <v>0.00616</v>
       </c>
       <c r="Y18" t="n">
-        <v>0.68727</v>
+        <v>0.90191</v>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>2026-08-27T00:34:40.730542+00:00</t>
+          <t>2026-08-27T14:44:07.601223+00:00</t>
         </is>
       </c>
       <c r="AD18" t="inlineStr">
@@ -5054,81 +5048,87 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>NET</t>
+          <t>AMZN</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Cloudflare, Inc.</t>
+          <t>Amazon.com, Inc.</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Software - Infrastructure</t>
+          <t>Internet Retail</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>101443551232</v>
+        <v>2770140921856</v>
       </c>
       <c r="F19" t="n">
-        <v>284.8900146484375</v>
+        <v>256.8200073242188</v>
       </c>
       <c r="G19" t="n">
-        <v>2512349952</v>
+        <v>775680032768</v>
       </c>
       <c r="H19" t="n">
-        <v>0.359</v>
+        <v>0.196</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.58</v>
+        <v>12.44</v>
+      </c>
+      <c r="J19" t="n">
+        <v>2.423</v>
       </c>
       <c r="K19" t="n">
-        <v>692851968</v>
+        <v>3219124992</v>
       </c>
       <c r="M19" t="n">
-        <v>4162798080</v>
+        <v>122988003328</v>
       </c>
       <c r="N19" t="n">
-        <v>3529349888</v>
+        <v>251635007488</v>
       </c>
       <c r="O19" t="n">
-        <v>0.72577006</v>
+        <v>0.5077</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.07902000000000001</v>
+        <v>0.13689</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>20.644695</v>
       </c>
       <c r="R19" t="n">
-        <v>40.377953</v>
+        <v>3.5712419</v>
       </c>
       <c r="S19" t="n">
-        <v>146.4144664621924</v>
+        <v>860.5260524956964</v>
       </c>
       <c r="T19" t="n">
-        <v>0.07258774278141633</v>
+        <v>0.112449132137372</v>
       </c>
       <c r="U19" t="n">
-        <v>0.3616767660177536</v>
+        <v>-0.06270070319628196</v>
       </c>
       <c r="V19" t="n">
-        <v>0.7391491294451318</v>
+        <v>0.2192366505335253</v>
       </c>
       <c r="W19" t="n">
-        <v>0.4348527336671593</v>
+        <v>0.1208974022230735</v>
       </c>
       <c r="X19" t="n">
-        <v>0.00616</v>
+        <v>0.0887</v>
       </c>
       <c r="Y19" t="n">
-        <v>0.90191</v>
+        <v>0.68727</v>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>2026-08-27T00:34:44.491319+00:00</t>
+          <t>2026-08-27T14:44:02.346615+00:00</t>
         </is>
       </c>
       <c r="AD19" t="inlineStr">
@@ -5159,10 +5159,10 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>3685818040320</v>
+        <v>3743923044352</v>
       </c>
       <c r="F20" t="n">
-        <v>496.3699951171875</v>
+        <v>504.1950073242188</v>
       </c>
       <c r="G20" t="n">
         <v>331839012864</v>
@@ -5171,7 +5171,7 @@
         <v>0.177</v>
       </c>
       <c r="I20" t="n">
-        <v>17.95</v>
+        <v>17.97</v>
       </c>
       <c r="J20" t="n">
         <v>0.317</v>
@@ -5192,25 +5192,25 @@
         <v>0.45111</v>
       </c>
       <c r="Q20" t="n">
-        <v>27.652924</v>
+        <v>28.057598</v>
       </c>
       <c r="R20" t="n">
-        <v>11.107247</v>
+        <v>11.282348</v>
       </c>
       <c r="S20" t="n">
-        <v>222.7686080612265</v>
+        <v>226.2804392824109</v>
       </c>
       <c r="T20" t="n">
-        <v>0.2780889499917965</v>
+        <v>0.2842104134029855</v>
       </c>
       <c r="U20" t="n">
-        <v>0.2050897672313394</v>
+        <v>0.18303514463473</v>
       </c>
       <c r="V20" t="n">
-        <v>0.2811864922651715</v>
+        <v>0.2637000847261934</v>
       </c>
       <c r="W20" t="n">
-        <v>-0.00315917551200473</v>
+        <v>0.003163998002835955</v>
       </c>
       <c r="X20" t="n">
         <v>0.00090000004</v>
@@ -5220,7 +5220,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>2026-08-27T00:34:40.175406+00:00</t>
+          <t>2026-08-27T14:44:01.670727+00:00</t>
         </is>
       </c>
       <c r="AD20" t="inlineStr">
@@ -5232,87 +5232,87 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ASML</t>
+          <t>VRT</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>ASML Holding N.V.</t>
+          <t>Vertiv Holdings Co</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Semiconductor Equipment &amp; Materials</t>
+          <t>Electrical Equipment &amp; Parts</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>670500323328</v>
+        <v>101991071744</v>
       </c>
       <c r="F21" t="n">
-        <v>1745.640014648438</v>
+        <v>264.9200134277344</v>
       </c>
       <c r="G21" t="n">
-        <v>35327500288</v>
+        <v>11479600128</v>
       </c>
       <c r="H21" t="n">
-        <v>0.213</v>
+        <v>0.241</v>
       </c>
       <c r="I21" t="n">
-        <v>29.65</v>
+        <v>4.56</v>
       </c>
       <c r="J21" t="n">
-        <v>0.285</v>
+        <v>0.53</v>
       </c>
       <c r="K21" t="n">
-        <v>8437675008</v>
+        <v>2696537600</v>
       </c>
       <c r="M21" t="n">
-        <v>7581499904</v>
+        <v>3110599936</v>
       </c>
       <c r="N21" t="n">
-        <v>1984400000</v>
+        <v>3338200064</v>
       </c>
       <c r="O21" t="n">
-        <v>0.5273300400000001</v>
+        <v>0.38039002</v>
       </c>
       <c r="P21" t="n">
-        <v>0.37057</v>
+        <v>0.20362</v>
       </c>
       <c r="Q21" t="n">
-        <v>58.874874</v>
+        <v>58.096497</v>
       </c>
       <c r="R21" t="n">
-        <v>18.979557</v>
+        <v>8.884549</v>
       </c>
       <c r="S21" t="n">
-        <v>79.46505674753763</v>
+        <v>37.82297407757266</v>
       </c>
       <c r="T21" t="n">
-        <v>0.05596558535961482</v>
+        <v>-0.01721317767058816</v>
       </c>
       <c r="U21" t="n">
-        <v>0.09389227011352697</v>
+        <v>-0.1566135634361057</v>
       </c>
       <c r="V21" t="n">
-        <v>0.1695255958287856</v>
+        <v>0.0108630910272951</v>
       </c>
       <c r="W21" t="n">
-        <v>1.302329484682044</v>
+        <v>1.050976853768209</v>
       </c>
       <c r="X21" t="n">
-        <v>0.00016000001</v>
+        <v>0.00269</v>
       </c>
       <c r="Y21" t="n">
-        <v>0.20384</v>
+        <v>0.84448</v>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>2026-08-27T00:34:41.973115+00:00</t>
+          <t>2026-08-27T14:44:06.049229+00:00</t>
         </is>
       </c>
       <c r="AD21" t="inlineStr">
@@ -5324,87 +5324,84 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>VRT</t>
+          <t>ACMR</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Vertiv Holdings Co</t>
+          <t>ACM Research, Inc.</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Electrical Equipment &amp; Parts</t>
+          <t>Semiconductor Equipment &amp; Materials</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>101563727872</v>
+        <v>5499500544</v>
       </c>
       <c r="F22" t="n">
-        <v>263.8099975585938</v>
+        <v>78.95999908447266</v>
       </c>
       <c r="G22" t="n">
-        <v>11479600128</v>
+        <v>1037772032</v>
       </c>
       <c r="H22" t="n">
-        <v>0.241</v>
+        <v>0.36</v>
       </c>
       <c r="I22" t="n">
-        <v>4.42</v>
+        <v>2.12</v>
       </c>
       <c r="J22" t="n">
-        <v>0.53</v>
+        <v>1.806</v>
       </c>
       <c r="K22" t="n">
-        <v>2696537600</v>
+        <v>-186610256</v>
       </c>
       <c r="M22" t="n">
-        <v>3110599936</v>
+        <v>1439374976</v>
       </c>
       <c r="N22" t="n">
-        <v>3338200064</v>
+        <v>349319008</v>
       </c>
       <c r="O22" t="n">
-        <v>0.38039002</v>
+        <v>0.43835</v>
       </c>
       <c r="P22" t="n">
-        <v>0.20362</v>
+        <v>0.16982001</v>
       </c>
       <c r="Q22" t="n">
-        <v>59.68552</v>
+        <v>37.245285</v>
       </c>
       <c r="R22" t="n">
-        <v>8.847322</v>
-      </c>
-      <c r="S22" t="n">
-        <v>37.66449534098838</v>
+        <v>5.299334</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.08271908219765178</v>
+        <v>0.09636216002343279</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1748549187500137</v>
+        <v>-0.1496877173650309</v>
       </c>
       <c r="V22" t="n">
-        <v>0.04257434101346913</v>
+        <v>0.1532057496239345</v>
       </c>
       <c r="W22" t="n">
-        <v>1.064414949858474</v>
+        <v>1.762771143990741</v>
       </c>
       <c r="X22" t="n">
-        <v>0.00269</v>
+        <v>0.12675999</v>
       </c>
       <c r="Y22" t="n">
-        <v>0.84448</v>
+        <v>0.78055</v>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>2026-08-27T00:34:43.432233+00:00</t>
+          <t>2026-08-27T14:43:59.750321+00:00</t>
         </is>
       </c>
       <c r="AD22" t="inlineStr">
@@ -5416,12 +5413,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ACMR</t>
+          <t>ASML</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>ACM Research, Inc.</t>
+          <t>ASML Holding N.V.</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -5435,65 +5432,68 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5509948416</v>
+        <v>663068016640</v>
       </c>
       <c r="F23" t="n">
-        <v>79.11000061035156</v>
+        <v>1726.2900390625</v>
       </c>
       <c r="G23" t="n">
-        <v>1037772032</v>
+        <v>35327500288</v>
       </c>
       <c r="H23" t="n">
-        <v>0.36</v>
+        <v>0.213</v>
       </c>
       <c r="I23" t="n">
-        <v>2.12</v>
+        <v>29.68</v>
       </c>
       <c r="J23" t="n">
-        <v>1.806</v>
+        <v>0.285</v>
       </c>
       <c r="K23" t="n">
-        <v>-186610256</v>
+        <v>8437675008</v>
       </c>
       <c r="M23" t="n">
-        <v>1439374976</v>
+        <v>7581499904</v>
       </c>
       <c r="N23" t="n">
-        <v>349319008</v>
+        <v>1984400000</v>
       </c>
       <c r="O23" t="n">
-        <v>0.43835</v>
+        <v>0.5273300400000001</v>
       </c>
       <c r="P23" t="n">
-        <v>0.16982001</v>
+        <v>0.37057</v>
       </c>
       <c r="Q23" t="n">
-        <v>37.31604</v>
+        <v>58.16341</v>
       </c>
       <c r="R23" t="n">
-        <v>5.3094015</v>
+        <v>18.769175</v>
+      </c>
+      <c r="S23" t="n">
+        <v>78.58420903996969</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.01075404023038729</v>
+        <v>0.09055250785693425</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.1075135248749766</v>
+        <v>0.0764447389708085</v>
       </c>
       <c r="V23" t="n">
-        <v>0.1675029237942185</v>
+        <v>0.1348095086431742</v>
       </c>
       <c r="W23" t="n">
-        <v>1.644934838312825</v>
+        <v>1.256701897826153</v>
       </c>
       <c r="X23" t="n">
-        <v>0.12675999</v>
+        <v>0.00016000001</v>
       </c>
       <c r="Y23" t="n">
-        <v>0.78055</v>
+        <v>0.20384</v>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>2026-08-27T00:34:38.740928+00:00</t>
+          <t>2026-08-27T14:44:04.027839+00:00</t>
         </is>
       </c>
       <c r="AD23" t="inlineStr">
@@ -5505,12 +5505,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>SMCI</t>
+          <t>PANW</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Super Micro Computer, Inc.</t>
+          <t>Palo Alto Networks, Inc.</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -5520,69 +5520,69 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Computer Hardware</t>
+          <t>Software - Infrastructure</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>24186580992</v>
+        <v>304308781056</v>
       </c>
       <c r="F24" t="n">
-        <v>37.38999938964844</v>
+        <v>373.25</v>
       </c>
       <c r="G24" t="n">
-        <v>39063072768</v>
+        <v>10606499840</v>
       </c>
       <c r="H24" t="n">
-        <v>0.9320000000000001</v>
+        <v>0.311</v>
       </c>
       <c r="I24" t="n">
-        <v>3.26</v>
-      </c>
-      <c r="J24" t="n">
-        <v>4.094</v>
+        <v>1.15</v>
       </c>
       <c r="K24" t="n">
-        <v>-8231267840</v>
+        <v>3579375104</v>
       </c>
       <c r="M24" t="n">
-        <v>7521474048</v>
+        <v>3111000064</v>
       </c>
       <c r="N24" t="n">
-        <v>9311492096</v>
+        <v>2130000000</v>
       </c>
       <c r="O24" t="n">
-        <v>0.108219996</v>
+        <v>0.71963996</v>
       </c>
       <c r="P24" t="n">
-        <v>0.13382</v>
+        <v>-0.02465</v>
       </c>
       <c r="Q24" t="n">
-        <v>11.469325</v>
+        <v>324.68262</v>
       </c>
       <c r="R24" t="n">
-        <v>0.6191674</v>
+        <v>28.690783</v>
+      </c>
+      <c r="S24" t="n">
+        <v>85.01729274362188</v>
       </c>
       <c r="T24" t="n">
-        <v>0.254277090221559</v>
+        <v>0.1700626959247649</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.02094787289416267</v>
+        <v>0.4479963374642624</v>
       </c>
       <c r="V24" t="n">
-        <v>0.2010922067987515</v>
+        <v>1.576981561980035</v>
       </c>
       <c r="W24" t="n">
-        <v>-0.1571235600721937</v>
+        <v>0.9894994871579654</v>
       </c>
       <c r="X24" t="n">
-        <v>0.12878999</v>
+        <v>0.0076</v>
       </c>
       <c r="Y24" t="n">
-        <v>0.70584</v>
+        <v>0.84949994</v>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>2026-08-27T00:34:43.686622+00:00</t>
+          <t>2026-08-27T14:44:01.199251+00:00</t>
         </is>
       </c>
       <c r="AD24" t="inlineStr">
@@ -5594,12 +5594,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>PANW</t>
+          <t>SMCI</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Palo Alto Networks, Inc.</t>
+          <t>Super Micro Computer, Inc.</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -5609,69 +5609,69 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Software - Infrastructure</t>
+          <t>Computer Hardware</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>276537638912</v>
+        <v>24739723264</v>
       </c>
       <c r="F25" t="n">
-        <v>339.3099975585938</v>
+        <v>38.2400016784668</v>
       </c>
       <c r="G25" t="n">
-        <v>10606499840</v>
+        <v>39063072768</v>
       </c>
       <c r="H25" t="n">
-        <v>0.311</v>
+        <v>0.9320000000000001</v>
       </c>
       <c r="I25" t="n">
-        <v>1.15</v>
+        <v>3.26</v>
+      </c>
+      <c r="J25" t="n">
+        <v>4.094</v>
       </c>
       <c r="K25" t="n">
-        <v>3579375104</v>
+        <v>-8231267840</v>
       </c>
       <c r="M25" t="n">
-        <v>3111000064</v>
+        <v>7521474048</v>
       </c>
       <c r="N25" t="n">
-        <v>2130000000</v>
+        <v>9311492096</v>
       </c>
       <c r="O25" t="n">
-        <v>0.71963996</v>
+        <v>0.108219996</v>
       </c>
       <c r="P25" t="n">
-        <v>-0.02465</v>
+        <v>0.13382</v>
       </c>
       <c r="Q25" t="n">
-        <v>295.0522</v>
+        <v>11.731626</v>
       </c>
       <c r="R25" t="n">
-        <v>26.07247</v>
-      </c>
-      <c r="S25" t="n">
-        <v>77.25863618008782</v>
+        <v>0.6332432</v>
       </c>
       <c r="T25" t="n">
-        <v>0.06929909784070731</v>
+        <v>0.3441125009838433</v>
       </c>
       <c r="U25" t="n">
-        <v>0.3655974398985982</v>
+        <v>-0.07409195193998608</v>
       </c>
       <c r="V25" t="n">
-        <v>1.3950730708273</v>
+        <v>0.1380953397340021</v>
       </c>
       <c r="W25" t="n">
-        <v>0.8417738990799586</v>
+        <v>-0.1456657034754569</v>
       </c>
       <c r="X25" t="n">
-        <v>0.0076</v>
+        <v>0.12878999</v>
       </c>
       <c r="Y25" t="n">
-        <v>0.84953004</v>
+        <v>0.70584</v>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>2026-08-27T00:34:39.862580+00:00</t>
+          <t>2026-08-27T14:44:06.387065+00:00</t>
         </is>
       </c>
       <c r="AD25" t="inlineStr">
@@ -5702,10 +5702,10 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>268131729408</v>
+        <v>273605214208</v>
       </c>
       <c r="F26" t="n">
-        <v>251.0599975585938</v>
+        <v>256.1849975585938</v>
       </c>
       <c r="G26" t="n">
         <v>5155999744</v>
@@ -5714,7 +5714,7 @@
         <v>0.224</v>
       </c>
       <c r="I26" t="n">
-        <v>0.99</v>
+        <v>0.98</v>
       </c>
       <c r="J26" t="n">
         <v>1.083</v>
@@ -5735,25 +5735,25 @@
         <v>0.07603</v>
       </c>
       <c r="Q26" t="n">
-        <v>253.59595</v>
+        <v>261.41327</v>
       </c>
       <c r="R26" t="n">
-        <v>52.00383</v>
+        <v>53.065407</v>
       </c>
       <c r="S26" t="n">
-        <v>200.9229942581759</v>
+        <v>205.0245191223564</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.05733484693256097</v>
+        <v>0.04676387925368974</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.1706253356495145</v>
+        <v>-0.2358844932340578</v>
       </c>
       <c r="V26" t="n">
-        <v>0.9592632960389664</v>
+        <v>0.9446256784305895</v>
       </c>
       <c r="W26" t="n">
-        <v>0.7899615527673336</v>
+        <v>0.8213066322250082</v>
       </c>
       <c r="X26" t="n">
         <v>0.0007</v>
@@ -5763,7 +5763,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>2026-08-27T00:34:42.252890+00:00</t>
+          <t>2026-08-27T14:44:04.450434+00:00</t>
         </is>
       </c>
       <c r="AD26" t="inlineStr">
@@ -5775,87 +5775,84 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>META</t>
+          <t>CRWD</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Meta Platforms, Inc.</t>
+          <t>CrowdStrike Holdings, Inc.</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Internet Content &amp; Information</t>
+          <t>Software - Infrastructure</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1467720269824</v>
+        <v>225371324416</v>
       </c>
       <c r="F27" t="n">
-        <v>576.1400146484375</v>
+        <v>221.3370971679688</v>
       </c>
       <c r="G27" t="n">
-        <v>228246994944</v>
+        <v>5094199808</v>
       </c>
       <c r="H27" t="n">
-        <v>0.28</v>
+        <v>0.256</v>
       </c>
       <c r="I27" t="n">
-        <v>26.56</v>
-      </c>
-      <c r="J27" t="n">
-        <v>-0.134</v>
+        <v>0.06</v>
       </c>
       <c r="K27" t="n">
-        <v>21553625088</v>
+        <v>1926365056</v>
       </c>
       <c r="M27" t="n">
-        <v>90259996672</v>
+        <v>4552800768</v>
       </c>
       <c r="N27" t="n">
-        <v>112317997056</v>
+        <v>821342976</v>
       </c>
       <c r="O27" t="n">
-        <v>0.81747</v>
+        <v>0.75136</v>
       </c>
       <c r="P27" t="n">
-        <v>0.34827</v>
+        <v>-0.022079999</v>
       </c>
       <c r="Q27" t="n">
-        <v>21.692019</v>
+        <v>3688.8335</v>
       </c>
       <c r="R27" t="n">
-        <v>6.4304037</v>
+        <v>44.240772</v>
       </c>
       <c r="S27" t="n">
-        <v>68.09621415569461</v>
+        <v>116.993050571615</v>
       </c>
       <c r="T27" t="n">
-        <v>-0.02985498613253124</v>
+        <v>0.2174757615650582</v>
       </c>
       <c r="U27" t="n">
-        <v>-0.09222372575639304</v>
+        <v>0.3194461828194859</v>
       </c>
       <c r="V27" t="n">
-        <v>-0.09718792919419572</v>
+        <v>1.436895198649435</v>
       </c>
       <c r="W27" t="n">
-        <v>-0.2334858217892405</v>
+        <v>1.0949537856645</v>
       </c>
       <c r="X27" t="n">
-        <v>0.00148</v>
+        <v>0.01467</v>
       </c>
       <c r="Y27" t="n">
-        <v>0.79038</v>
+        <v>0.76657</v>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>2026-08-27T00:34:41.011552+00:00</t>
+          <t>2026-08-27T14:44:00.899887+00:00</t>
         </is>
       </c>
       <c r="AD27" t="inlineStr">
@@ -5886,10 +5883,10 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220281487360</v>
+        <v>219665891328</v>
       </c>
       <c r="F28" t="n">
-        <v>245.1100006103516</v>
+        <v>244.4250030517578</v>
       </c>
       <c r="G28" t="n">
         <v>8717100032</v>
@@ -5898,7 +5895,7 @@
         <v>0.276</v>
       </c>
       <c r="I28" t="n">
-        <v>2.91</v>
+        <v>2.97</v>
       </c>
       <c r="J28" t="n">
         <v>-0.804</v>
@@ -5919,25 +5916,25 @@
         <v>0.14479999</v>
       </c>
       <c r="Q28" t="n">
-        <v>84.23023999999999</v>
+        <v>82.29798</v>
       </c>
       <c r="R28" t="n">
-        <v>25.270042</v>
+        <v>25.199423</v>
       </c>
       <c r="S28" t="n">
-        <v>97.05312510151121</v>
+        <v>96.78190158916925</v>
       </c>
       <c r="T28" t="n">
-        <v>0.2957128666430866</v>
+        <v>0.4009571923058692</v>
       </c>
       <c r="U28" t="n">
-        <v>0.2338725615919328</v>
+        <v>0.1936010535580535</v>
       </c>
       <c r="V28" t="n">
-        <v>2.129139013505327</v>
+        <v>2.022833487051142</v>
       </c>
       <c r="W28" t="n">
-        <v>2.30773265924773</v>
+        <v>2.275114079046758</v>
       </c>
       <c r="X28" t="n">
         <v>0.00494</v>
@@ -5947,7 +5944,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>2026-08-27T00:34:42.558687+00:00</t>
+          <t>2026-08-27T14:44:04.936838+00:00</t>
         </is>
       </c>
       <c r="AD28" t="inlineStr">
@@ -5959,81 +5956,87 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>CRWD</t>
+          <t>META</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>CrowdStrike Holdings, Inc.</t>
+          <t>Meta Platforms, Inc.</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Software - Infrastructure</t>
+          <t>Internet Content &amp; Information</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>192634273792</v>
+        <v>1455978708992</v>
       </c>
       <c r="F29" t="n">
-        <v>189.1799926757812</v>
+        <v>571.531005859375</v>
       </c>
       <c r="G29" t="n">
-        <v>5094199808</v>
+        <v>228246994944</v>
       </c>
       <c r="H29" t="n">
-        <v>0.256</v>
+        <v>0.28</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.04</v>
+        <v>26.56</v>
+      </c>
+      <c r="J29" t="n">
+        <v>-0.134</v>
       </c>
       <c r="K29" t="n">
-        <v>1926365056</v>
+        <v>21553625088</v>
       </c>
       <c r="M29" t="n">
-        <v>4552800768</v>
+        <v>90259996672</v>
       </c>
       <c r="N29" t="n">
-        <v>821342976</v>
+        <v>112317997056</v>
       </c>
       <c r="O29" t="n">
-        <v>0.75136</v>
+        <v>0.81747</v>
       </c>
       <c r="P29" t="n">
-        <v>-0.022079999</v>
+        <v>0.34827</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>21.518488</v>
       </c>
       <c r="R29" t="n">
-        <v>37.814434</v>
+        <v>6.378961</v>
       </c>
       <c r="S29" t="n">
-        <v>99.99884144077829</v>
+        <v>67.55145378317903</v>
       </c>
       <c r="T29" t="n">
-        <v>0.05035807026091588</v>
+        <v>-0.03686990154415115</v>
       </c>
       <c r="U29" t="n">
-        <v>0.1725548343238212</v>
+        <v>-0.09952819288634152</v>
       </c>
       <c r="V29" t="n">
-        <v>1.16051383498394</v>
+        <v>-0.1241253145406794</v>
       </c>
       <c r="W29" t="n">
-        <v>0.8120688688772375</v>
+        <v>-0.2327809291088164</v>
       </c>
       <c r="X29" t="n">
-        <v>0.01467</v>
+        <v>0.00148</v>
       </c>
       <c r="Y29" t="n">
-        <v>0.76657</v>
+        <v>0.79038</v>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>2026-08-27T00:34:39.589372+00:00</t>
+          <t>2026-08-27T14:44:02.751389+00:00</t>
         </is>
       </c>
       <c r="AD29" t="inlineStr">
@@ -6064,10 +6067,10 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>130059845632</v>
+        <v>142179500032</v>
       </c>
       <c r="F30" t="n">
-        <v>125.8000030517578</v>
+        <v>137.522705078125</v>
       </c>
       <c r="G30" t="n">
         <v>14732000256</v>
@@ -6097,25 +6100,25 @@
         <v>0.04063</v>
       </c>
       <c r="Q30" t="n">
-        <v>78.625</v>
+        <v>85.95169</v>
       </c>
       <c r="R30" t="n">
-        <v>8.828390000000001</v>
+        <v>9.651066</v>
       </c>
       <c r="S30" t="n">
-        <v>25.25740429434207</v>
+        <v>27.61102088984867</v>
       </c>
       <c r="T30" t="n">
-        <v>0.1917393516604557</v>
+        <v>0.2431992556823022</v>
       </c>
       <c r="U30" t="n">
-        <v>0.2318840547227496</v>
+        <v>0.2648091679595752</v>
       </c>
       <c r="V30" t="n">
-        <v>0.2274368784646881</v>
+        <v>0.3194157214711124</v>
       </c>
       <c r="W30" t="n">
-        <v>-0.27254644554547</v>
+        <v>-0.2256429735686207</v>
       </c>
       <c r="X30" t="n">
         <v>0.00176</v>
@@ -6125,7 +6128,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>2026-08-27T00:34:44.768559+00:00</t>
+          <t>2026-08-27T14:44:08.083524+00:00</t>
         </is>
       </c>
       <c r="AD30" t="inlineStr">
@@ -6156,10 +6159,10 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>428815712256</v>
+        <v>430356758528</v>
       </c>
       <c r="F31" t="n">
-        <v>148.8699951171875</v>
+        <v>149.4049987792969</v>
       </c>
       <c r="G31" t="n">
         <v>67356999680</v>
@@ -6168,7 +6171,7 @@
         <v>0.206</v>
       </c>
       <c r="I31" t="n">
-        <v>5.83</v>
+        <v>5.84</v>
       </c>
       <c r="J31" t="n">
         <v>0.219</v>
@@ -6189,22 +6192,22 @@
         <v>0.36202</v>
       </c>
       <c r="Q31" t="n">
-        <v>25.535162</v>
+        <v>25.583048</v>
       </c>
       <c r="R31" t="n">
-        <v>6.3663125</v>
+        <v>6.389191</v>
       </c>
       <c r="T31" t="n">
-        <v>0.2416179584873133</v>
+        <v>0.2454568182689785</v>
       </c>
       <c r="U31" t="n">
-        <v>-0.2177005762318938</v>
+        <v>-0.2639922678418849</v>
       </c>
       <c r="V31" t="n">
-        <v>0.02579484468997983</v>
+        <v>0.01729939871589337</v>
       </c>
       <c r="W31" t="n">
-        <v>-0.3571292126698538</v>
+        <v>-0.3591965229590346</v>
       </c>
       <c r="X31" t="n">
         <v>0.40498</v>
@@ -6214,7 +6217,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>2026-08-27T00:34:41.321823+00:00</t>
+          <t>2026-08-27T14:44:03.194980+00:00</t>
         </is>
       </c>
       <c r="AD31" t="inlineStr">
@@ -6362,7 +6365,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ANET</t>
+          <t>CRDO</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -6391,7 +6394,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CRDO</t>
+          <t>ANET</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -6449,7 +6452,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>TER</t>
+          <t>DELL</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -6478,7 +6481,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>DELL</t>
+          <t>TER</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -6783,18 +6786,23 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>AMZN</t>
+          <t>NET</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>100</v>
+        <v>88.2</v>
       </c>
       <c r="C18" t="n">
-        <v>100</v>
+        <v>88.2</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
           <t>HIGH</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>eps_growth, pe_ratio</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -6812,23 +6820,18 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>NET</t>
+          <t>AMZN</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>88.2</v>
+        <v>100</v>
       </c>
       <c r="C19" t="n">
-        <v>88.2</v>
+        <v>100</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
           <t>HIGH</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>eps_growth, pe_ratio</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -6875,7 +6878,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ASML</t>
+          <t>VRT</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -6904,18 +6907,23 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>VRT</t>
+          <t>ACMR</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>100</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="C22" t="n">
-        <v>100</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
           <t>HIGH</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>price_to_fcf</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -6933,23 +6941,18 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ACMR</t>
+          <t>ASML</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>94.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="C23" t="n">
-        <v>94.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
           <t>HIGH</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>price_to_fcf</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -6967,7 +6970,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>SMCI</t>
+          <t>PANW</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -6983,7 +6986,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>price_to_fcf</t>
+          <t>eps_growth</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -7001,7 +7004,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>PANW</t>
+          <t>SMCI</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -7017,7 +7020,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>eps_growth</t>
+          <t>price_to_fcf</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -7064,18 +7067,23 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>META</t>
+          <t>CRWD</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>100</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="C27" t="n">
-        <v>100</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
           <t>HIGH</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>eps_growth</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -7122,23 +7130,18 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>CRWD</t>
+          <t>META</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>88.2</v>
+        <v>100</v>
       </c>
       <c r="C29" t="n">
-        <v>88.2</v>
+        <v>100</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
           <t>HIGH</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>eps_growth, pe_ratio</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -7289,7 +7292,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>56.32</v>
+        <v>56.77</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/reports/investment_dashboard.xlsx
+++ b/reports/investment_dashboard.xlsx
@@ -534,7 +534,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>56.77</v>
+        <v>56.69</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>923.614990234375</v>
+        <v>915.5549926757812</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -586,7 +586,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>55.57</v>
+        <v>55.59</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>424.6000061035156</v>
+        <v>425.5849914550781</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>53.52</v>
+        <v>53.55</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>236.8000030517578</v>
+        <v>237.7100067138672</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -685,7 +685,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>52.98</v>
+        <v>53.01</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -693,7 +693,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>201.4949951171875</v>
+        <v>201.9745025634766</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -737,7 +737,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>52.27</v>
+        <v>52.36</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -745,7 +745,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>184.8099975585938</v>
+        <v>185.7799987792969</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>51.15</v>
+        <v>51.14</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>467.1600036621094</v>
+        <v>465.3349914550781</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -827,16 +827,16 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>TER</t>
+          <t>NVDA</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Teradyne, Inc.</t>
+          <t>NVIDIA Corporation</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>50.8</v>
+        <v>50.98</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -844,11 +844,11 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>363.7049865722656</v>
+        <v>227.2279968261719</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="H8" t="n">
@@ -865,6 +865,11 @@
       <c r="K8" t="inlineStr">
         <is>
           <t>Industry Growth; Valuation; Competitive Advantage; Catalysts; Inflation Resilience</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>Excessive price-to-sales valuation; High market sensitivity / beta</t>
         </is>
       </c>
     </row>
@@ -874,16 +879,16 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>NVDA</t>
+          <t>TER</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>NVIDIA Corporation</t>
+          <t>Teradyne, Inc.</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>50.79</v>
+        <v>50.9</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -891,11 +896,11 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>224.8000030517578</v>
+        <v>367.1300048828125</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="H9" t="n">
@@ -912,11 +917,6 @@
       <c r="K9" t="inlineStr">
         <is>
           <t>Industry Growth; Valuation; Competitive Advantage; Catalysts; Inflation Resilience</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>Excessive price-to-sales valuation; High market sensitivity / beta</t>
         </is>
       </c>
     </row>
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>47.65</v>
+        <v>47.66</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -943,7 +943,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>18.23999977111816</v>
+        <v>18.20499992370605</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -982,7 +982,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>47.62</v>
+        <v>47.61</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -990,7 +990,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>474.5299987792969</v>
+        <v>473.7550048828125</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>46.7</v>
+        <v>46.73</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -1042,7 +1042,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>339.3399963378906</v>
+        <v>340.5849914550781</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>45.33</v>
+        <v>45.4</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -1089,7 +1089,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>471.7850036621094</v>
+        <v>475.6700134277344</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -1128,7 +1128,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>45.11</v>
+        <v>45.16</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>242.0399932861328</v>
+        <v>243.3049926757812</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -1180,7 +1180,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>44.19</v>
+        <v>44.26</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>366.9609985351562</v>
+        <v>368.135009765625</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -1232,7 +1232,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>43.58</v>
+        <v>43.73</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>431.2349853515625</v>
+        <v>436.6099853515625</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1279,7 +1279,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>43.13</v>
+        <v>43.18</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -1287,7 +1287,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>329.1499938964844</v>
+        <v>330.7349853515625</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1331,7 +1331,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>42.84</v>
+        <v>42.91</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -1339,7 +1339,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>300.3500061035156</v>
+        <v>302.2799987792969</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1383,7 +1383,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>42.64</v>
+        <v>42.62</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -1391,7 +1391,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>256.8200073242188</v>
+        <v>256.3999938964844</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1421,16 +1421,16 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>ACMR</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Microsoft Corporation</t>
+          <t>ACM Research, Inc.</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>42.39</v>
+        <v>42.52</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>504.1950073242188</v>
+        <v>80.23500061035156</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1446,19 +1446,24 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>100</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="I20" t="n">
-        <v>100</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Earnings Fcf</t>
+          <t>Revenue Growth</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Industry Growth; Valuation; Competitive Advantage; Catalysts; Inflation Resilience</t>
+          <t>Industry Growth; Competitive Advantage; Catalysts; Inflation Resilience</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>Negative free cash flow / unprofitable growth</t>
         </is>
       </c>
     </row>
@@ -1485,7 +1490,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>264.9200134277344</v>
+        <v>264.8500061035156</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1520,16 +1525,16 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>ACMR</t>
+          <t>ASML</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>ACM Research, Inc.</t>
+          <t>ASML Holding N.V.</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>42.36</v>
+        <v>42.38</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -1537,7 +1542,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>78.95999908447266</v>
+        <v>1730.25</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1545,24 +1550,19 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>94.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="I22" t="n">
-        <v>94.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Revenue Growth</t>
+          <t>Earnings Fcf; Balance Sheet</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Industry Growth; Competitive Advantage; Catalysts; Inflation Resilience</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>Negative free cash flow / unprofitable growth</t>
+          <t>Industry Growth; Valuation; Competitive Advantage; Catalysts; Inflation Resilience</t>
         </is>
       </c>
     </row>
@@ -1572,16 +1572,16 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>ASML</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>ASML Holding N.V.</t>
+          <t>Microsoft Corporation</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>42.35</v>
+        <v>42.25</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1726.2900390625</v>
+        <v>499.8349914550781</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Earnings Fcf; Balance Sheet</t>
+          <t>Earnings Fcf</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -1628,7 +1628,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>42.07</v>
+        <v>42.16</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -1636,7 +1636,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>373.25</v>
+        <v>379.6650085449219</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1680,7 +1680,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>41.78</v>
+        <v>41.72</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>38.2400016784668</v>
+        <v>38.125</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1723,16 +1723,16 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>ARM</t>
+          <t>CRWD</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Arm Holdings plc</t>
+          <t>CrowdStrike Holdings, Inc.</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>40.8</v>
+        <v>40.84</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -1740,7 +1740,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>256.1849975585938</v>
+        <v>222.4600067138672</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1748,14 +1748,14 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>100</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="I26" t="n">
-        <v>100</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Balance Sheet</t>
+          <t>Balance Sheet; Momentum</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -1765,7 +1765,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>Excessive price-to-sales valuation; Very high earnings multiple; High market sensitivity / beta</t>
+          <t>Excessive price-to-sales valuation; Very high earnings multiple</t>
         </is>
       </c>
     </row>
@@ -1775,16 +1775,16 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>CRWD</t>
+          <t>ARM</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>CrowdStrike Holdings, Inc.</t>
+          <t>Arm Holdings plc</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>40.78</v>
+        <v>40.72</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -1792,7 +1792,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>221.3370971679688</v>
+        <v>251.1199951171875</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1800,14 +1800,14 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>94.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="I27" t="n">
-        <v>94.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Balance Sheet; Momentum</t>
+          <t>Balance Sheet</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -1817,7 +1817,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>Excessive price-to-sales valuation; Very high earnings multiple</t>
+          <t>Excessive price-to-sales valuation; Very high earnings multiple; High market sensitivity / beta</t>
         </is>
       </c>
     </row>
@@ -1836,7 +1836,7 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>39.89</v>
+        <v>39.85</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>244.4250030517578</v>
+        <v>243.5</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1888,7 +1888,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>39.59</v>
+        <v>39.63</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -1896,7 +1896,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>571.531005859375</v>
+        <v>573.61962890625</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>36.39</v>
+        <v>36.23</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -1943,7 +1943,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>137.522705078125</v>
+        <v>135.7825012207031</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1977,7 +1977,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>31.47</v>
+        <v>31.42</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -1985,7 +1985,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>149.4049987792969</v>
+        <v>147.8899993896484</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -2131,13 +2131,13 @@
         <v>9.02</v>
       </c>
       <c r="F2" t="n">
-        <v>7.31</v>
+        <v>7.32</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>6.94</v>
+        <v>6.85</v>
       </c>
       <c r="I2" t="n">
         <v>3.5</v>
@@ -2149,7 +2149,7 @@
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>56.77</v>
+        <v>56.69</v>
       </c>
     </row>
     <row r="3">
@@ -2171,13 +2171,13 @@
         <v>8.84</v>
       </c>
       <c r="F3" t="n">
-        <v>8.65</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>5.39</v>
+        <v>5.42</v>
       </c>
       <c r="I3" t="n">
         <v>2.69</v>
@@ -2189,7 +2189,7 @@
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>55.57</v>
+        <v>55.59</v>
       </c>
     </row>
     <row r="4">
@@ -2211,13 +2211,13 @@
         <v>9.91</v>
       </c>
       <c r="F4" t="n">
-        <v>2.36</v>
+        <v>2.35</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>7.71</v>
+        <v>7.75</v>
       </c>
       <c r="I4" t="n">
         <v>3.54</v>
@@ -2229,7 +2229,7 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>53.52</v>
+        <v>53.55</v>
       </c>
     </row>
     <row r="5">
@@ -2257,7 +2257,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>8.57</v>
+        <v>8.6</v>
       </c>
       <c r="I5" t="n">
         <v>3.63</v>
@@ -2269,7 +2269,7 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>52.98</v>
+        <v>53.01</v>
       </c>
     </row>
     <row r="6">
@@ -2297,7 +2297,7 @@
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>8.390000000000001</v>
+        <v>8.48</v>
       </c>
       <c r="I6" t="n">
         <v>3.35</v>
@@ -2309,7 +2309,7 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>52.27</v>
+        <v>52.36</v>
       </c>
     </row>
     <row r="7">
@@ -2331,13 +2331,13 @@
         <v>6.33</v>
       </c>
       <c r="F7" t="n">
-        <v>5.75</v>
+        <v>5.76</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>9.050000000000001</v>
+        <v>9.029999999999999</v>
       </c>
       <c r="I7" t="n">
         <v>3.54</v>
@@ -2349,13 +2349,13 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>51.15</v>
+        <v>51.14</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>TER</t>
+          <t>NVDA</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -2368,19 +2368,19 @@
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>8.9</v>
+        <v>9.029999999999999</v>
       </c>
       <c r="F8" t="n">
-        <v>2.94</v>
+        <v>2.91</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>5.21</v>
+        <v>5.6</v>
       </c>
       <c r="I8" t="n">
-        <v>3.75</v>
+        <v>3.44</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -2389,13 +2389,13 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>50.8</v>
+        <v>50.98</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>NVDA</t>
+          <t>TER</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -2408,19 +2408,19 @@
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>9.029999999999999</v>
+        <v>8.9</v>
       </c>
       <c r="F9" t="n">
-        <v>2.95</v>
+        <v>2.91</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>5.37</v>
+        <v>5.34</v>
       </c>
       <c r="I9" t="n">
-        <v>3.44</v>
+        <v>3.75</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -2429,7 +2429,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>50.79</v>
+        <v>50.9</v>
       </c>
     </row>
     <row r="10">
@@ -2451,7 +2451,7 @@
         <v>9.699999999999999</v>
       </c>
       <c r="F10" t="n">
-        <v>6.52</v>
+        <v>6.53</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -2469,7 +2469,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>47.65</v>
+        <v>47.66</v>
       </c>
     </row>
     <row r="11">
@@ -2497,7 +2497,7 @@
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>6.18</v>
+        <v>6.17</v>
       </c>
       <c r="I11" t="n">
         <v>3.45</v>
@@ -2509,7 +2509,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>47.62</v>
+        <v>47.61</v>
       </c>
     </row>
     <row r="12">
@@ -2531,13 +2531,13 @@
         <v>8.34</v>
       </c>
       <c r="F12" t="n">
-        <v>4.46</v>
+        <v>4.44</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>4.42</v>
+        <v>4.47</v>
       </c>
       <c r="I12" t="n">
         <v>3.53</v>
@@ -2549,7 +2549,7 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>46.7</v>
+        <v>46.73</v>
       </c>
     </row>
     <row r="13">
@@ -2571,13 +2571,13 @@
         <v>7.78</v>
       </c>
       <c r="F13" t="n">
-        <v>2.16</v>
+        <v>2.11</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>5.63</v>
+        <v>5.75</v>
       </c>
       <c r="I13" t="n">
         <v>3.58</v>
@@ -2589,7 +2589,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>45.33</v>
+        <v>45.4</v>
       </c>
     </row>
     <row r="14">
@@ -2617,7 +2617,7 @@
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>6.54</v>
+        <v>6.59</v>
       </c>
       <c r="I14" t="n">
         <v>3.67</v>
@@ -2629,7 +2629,7 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>45.11</v>
+        <v>45.16</v>
       </c>
     </row>
     <row r="15">
@@ -2657,7 +2657,7 @@
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>3.47</v>
+        <v>3.54</v>
       </c>
       <c r="I15" t="n">
         <v>3.53</v>
@@ -2669,7 +2669,7 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>44.19</v>
+        <v>44.26</v>
       </c>
     </row>
     <row r="16">
@@ -2691,13 +2691,13 @@
         <v>9.880000000000001</v>
       </c>
       <c r="F16" t="n">
-        <v>1.69</v>
+        <v>1.63</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>9.460000000000001</v>
+        <v>9.67</v>
       </c>
       <c r="I16" t="n">
         <v>3.73</v>
@@ -2709,7 +2709,7 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>43.58</v>
+        <v>43.73</v>
       </c>
     </row>
     <row r="17">
@@ -2731,13 +2731,13 @@
         <v>7.58</v>
       </c>
       <c r="F17" t="n">
-        <v>0.99</v>
+        <v>0.98</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>9.06</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="I17" t="n">
         <v>3.56</v>
@@ -2749,7 +2749,7 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>43.13</v>
+        <v>43.18</v>
       </c>
     </row>
     <row r="18">
@@ -2777,7 +2777,7 @@
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>8.43</v>
+        <v>8.5</v>
       </c>
       <c r="I18" t="n">
         <v>3.64</v>
@@ -2789,7 +2789,7 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>42.84</v>
+        <v>42.91</v>
       </c>
     </row>
     <row r="19">
@@ -2811,13 +2811,13 @@
         <v>6.64</v>
       </c>
       <c r="F19" t="n">
-        <v>6.53</v>
+        <v>6.54</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>4.5</v>
+        <v>4.47</v>
       </c>
       <c r="I19" t="n">
         <v>3.47</v>
@@ -2829,38 +2829,38 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>42.64</v>
+        <v>42.62</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>ACMR</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>8.51</v>
+        <v>15</v>
       </c>
       <c r="C20" t="n">
-        <v>14.63</v>
+        <v>7.83</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>6.87</v>
+        <v>4.02</v>
       </c>
       <c r="F20" t="n">
-        <v>2.87</v>
+        <v>6.81</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>6.06</v>
+        <v>5.23</v>
       </c>
       <c r="I20" t="n">
-        <v>3.45</v>
+        <v>3.63</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2869,7 +2869,7 @@
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>42.39</v>
+        <v>42.52</v>
       </c>
     </row>
     <row r="21">
@@ -2915,32 +2915,32 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ACMR</t>
+          <t>ASML</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>15</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="C22" t="n">
-        <v>7.83</v>
+        <v>14.28</v>
       </c>
       <c r="D22" t="n">
         <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>4.02</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="F22" t="n">
-        <v>6.88</v>
+        <v>0.57</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>5</v>
+        <v>5.95</v>
       </c>
       <c r="I22" t="n">
-        <v>3.63</v>
+        <v>2.76</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2949,38 +2949,38 @@
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>42.36</v>
+        <v>42.38</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ASML</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>9.859999999999999</v>
+        <v>8.51</v>
       </c>
       <c r="C23" t="n">
-        <v>14.28</v>
+        <v>14.63</v>
       </c>
       <c r="D23" t="n">
         <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>8.960000000000001</v>
+        <v>6.87</v>
       </c>
       <c r="F23" t="n">
-        <v>0.57</v>
+        <v>2.91</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>5.92</v>
+        <v>5.88</v>
       </c>
       <c r="I23" t="n">
-        <v>2.76</v>
+        <v>3.45</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2989,7 +2989,7 @@
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>42.35</v>
+        <v>42.25</v>
       </c>
     </row>
     <row r="24">
@@ -3011,13 +3011,13 @@
         <v>7.97</v>
       </c>
       <c r="F24" t="n">
-        <v>0.54</v>
+        <v>0.53</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>8.949999999999999</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="I24" t="n">
         <v>3.57</v>
@@ -3029,7 +3029,7 @@
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>42.07</v>
+        <v>42.16</v>
       </c>
     </row>
     <row r="25">
@@ -3057,7 +3057,7 @@
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>3.92</v>
+        <v>3.86</v>
       </c>
       <c r="I25" t="n">
         <v>3.54</v>
@@ -3069,38 +3069,38 @@
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>41.78</v>
+        <v>41.72</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ARM</t>
+          <t>CRWD</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>10.28</v>
+        <v>11.47</v>
       </c>
       <c r="C26" t="n">
-        <v>11.27</v>
+        <v>7.5</v>
       </c>
       <c r="D26" t="n">
         <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>9.449999999999999</v>
+        <v>9.24</v>
       </c>
       <c r="F26" t="n">
-        <v>0.21</v>
+        <v>0.29</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>5.89</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="I26" t="n">
-        <v>3.7</v>
+        <v>3.48</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3109,38 +3109,38 @@
         <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>40.8</v>
+        <v>40.84</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>CRWD</t>
+          <t>ARM</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>11.47</v>
+        <v>10.28</v>
       </c>
       <c r="C27" t="n">
-        <v>7.5</v>
+        <v>11.27</v>
       </c>
       <c r="D27" t="n">
         <v>0</v>
       </c>
       <c r="E27" t="n">
-        <v>9.24</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="F27" t="n">
-        <v>0.29</v>
+        <v>0.22</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>8.800000000000001</v>
+        <v>5.8</v>
       </c>
       <c r="I27" t="n">
-        <v>3.48</v>
+        <v>3.7</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3149,7 +3149,7 @@
         <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>40.78</v>
+        <v>40.72</v>
       </c>
     </row>
     <row r="28">
@@ -3177,7 +3177,7 @@
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>9.06</v>
+        <v>9.02</v>
       </c>
       <c r="I28" t="n">
         <v>3.53</v>
@@ -3189,7 +3189,7 @@
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>39.89</v>
+        <v>39.85</v>
       </c>
     </row>
     <row r="29">
@@ -3211,13 +3211,13 @@
         <v>7.23</v>
       </c>
       <c r="F29" t="n">
-        <v>5.63</v>
+        <v>5.62</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>0.86</v>
+        <v>0.91</v>
       </c>
       <c r="I29" t="n">
         <v>3.49</v>
@@ -3229,7 +3229,7 @@
         <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>39.59</v>
+        <v>39.63</v>
       </c>
     </row>
     <row r="30">
@@ -3251,13 +3251,13 @@
         <v>6.78</v>
       </c>
       <c r="F30" t="n">
-        <v>3.67</v>
+        <v>3.73</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>5.81</v>
+        <v>5.59</v>
       </c>
       <c r="I30" t="n">
         <v>3.57</v>
@@ -3269,7 +3269,7 @@
         <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>36.39</v>
+        <v>36.23</v>
       </c>
     </row>
     <row r="31">
@@ -3291,13 +3291,13 @@
         <v>0.8</v>
       </c>
       <c r="F31" t="n">
-        <v>6.39</v>
+        <v>6.45</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>2.56</v>
+        <v>2.45</v>
       </c>
       <c r="I31" t="n">
         <v>3.58</v>
@@ -3309,7 +3309,7 @@
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>31.47</v>
+        <v>31.42</v>
       </c>
     </row>
   </sheetData>
@@ -3343,13 +3343,13 @@
     <col width="15" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="18" customWidth="1" min="16" max="16"/>
-    <col width="11" customWidth="1" min="17" max="17"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
     <col width="16" customWidth="1" min="18" max="18"/>
     <col width="19" customWidth="1" min="19" max="19"/>
-    <col width="23" customWidth="1" min="20" max="20"/>
+    <col width="24" customWidth="1" min="20" max="20"/>
     <col width="23" customWidth="1" min="21" max="21"/>
-    <col width="21" customWidth="1" min="22" max="22"/>
-    <col width="22" customWidth="1" min="23" max="23"/>
+    <col width="22" customWidth="1" min="22" max="22"/>
+    <col width="23" customWidth="1" min="23" max="23"/>
     <col width="18" customWidth="1" min="24" max="24"/>
     <col width="24" customWidth="1" min="25" max="25"/>
     <col width="17" customWidth="1" min="26" max="26"/>
@@ -3533,7 +3533,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>923.614990234375</v>
+        <v>915.5549926757812</v>
       </c>
       <c r="G2" t="n">
         <v>90273996800</v>
@@ -3542,7 +3542,7 @@
         <v>3.457</v>
       </c>
       <c r="I2" t="n">
-        <v>44.48</v>
+        <v>44.2</v>
       </c>
       <c r="J2" t="n">
         <v>13.685</v>
@@ -3563,19 +3563,19 @@
         <v>0.80370003</v>
       </c>
       <c r="Q2" t="n">
-        <v>20.764727</v>
+        <v>20.711765</v>
       </c>
       <c r="T2" t="n">
-        <v>0.1256321612334348</v>
+        <v>0.1158092452269353</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0002566657577935949</v>
+        <v>-0.008472151302580389</v>
       </c>
       <c r="V2" t="n">
-        <v>1.154184432539791</v>
+        <v>1.135385775685353</v>
       </c>
       <c r="W2" t="n">
-        <v>6.856453213664718</v>
+        <v>6.787893773221825</v>
       </c>
       <c r="X2" t="n">
         <v>0.00238</v>
@@ -3585,7 +3585,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>2026-08-27T14:43:59.378693+00:00</t>
+          <t>2026-08-27T16:09:03.515813+00:00</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
@@ -3616,10 +3616,10 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2202176847872</v>
+        <v>2207285510144</v>
       </c>
       <c r="F3" t="n">
-        <v>424.6000061035156</v>
+        <v>425.5849914550781</v>
       </c>
       <c r="G3" t="n">
         <v>4440492343296</v>
@@ -3649,25 +3649,25 @@
         <v>0.60344005</v>
       </c>
       <c r="Q3" t="n">
-        <v>31.66294</v>
+        <v>31.736391</v>
       </c>
       <c r="R3" t="n">
-        <v>0.4959308</v>
+        <v>0.49708125</v>
       </c>
       <c r="S3" t="n">
-        <v>3.013271015969123</v>
+        <v>3.020261273799446</v>
       </c>
       <c r="T3" t="n">
-        <v>0.08230738126957671</v>
+        <v>0.08481811349075952</v>
       </c>
       <c r="U3" t="n">
-        <v>0.00172852670241852</v>
+        <v>0.004052332427479266</v>
       </c>
       <c r="V3" t="n">
-        <v>0.1007494875724653</v>
+        <v>0.1033030017161616</v>
       </c>
       <c r="W3" t="n">
-        <v>0.7940400775703229</v>
+        <v>0.7982018843793695</v>
       </c>
       <c r="X3" t="n">
         <v>0.00013</v>
@@ -3677,7 +3677,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>2026-08-27T14:44:03.592961+00:00</t>
+          <t>2026-08-27T16:09:07.900545+00:00</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
@@ -3708,10 +3708,10 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>44502929408</v>
+        <v>44673953792</v>
       </c>
       <c r="F4" t="n">
-        <v>236.8000030517578</v>
+        <v>237.7100067138672</v>
       </c>
       <c r="G4" t="n">
         <v>1335116032</v>
@@ -3741,25 +3741,25 @@
         <v>0.35661998</v>
       </c>
       <c r="Q4" t="n">
-        <v>94.34263</v>
+        <v>94.705185</v>
       </c>
       <c r="R4" t="n">
-        <v>33.33263</v>
+        <v>33.460728</v>
       </c>
       <c r="S4" t="n">
-        <v>177.4367317734473</v>
+        <v>178.1186196436214</v>
       </c>
       <c r="T4" t="n">
-        <v>0.2315373650670862</v>
+        <v>0.2362700656489802</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0649876166026051</v>
+        <v>0.06908027968841468</v>
       </c>
       <c r="V4" t="n">
-        <v>0.9180301701584876</v>
+        <v>0.9254010082344439</v>
       </c>
       <c r="W4" t="n">
-        <v>0.9294385771592979</v>
+        <v>0.9368532568400507</v>
       </c>
       <c r="X4" t="n">
         <v>0.09436</v>
@@ -3769,7 +3769,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>2026-08-27T14:44:00.144680+00:00</t>
+          <t>2026-08-27T16:09:04.268933+00:00</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
@@ -3800,10 +3800,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>254130470912</v>
+        <v>254735237120</v>
       </c>
       <c r="F5" t="n">
-        <v>201.4949951171875</v>
+        <v>201.9745025634766</v>
       </c>
       <c r="G5" t="n">
         <v>10540800000</v>
@@ -3833,25 +3833,25 @@
         <v>0.45393002</v>
       </c>
       <c r="Q5" t="n">
-        <v>63.764236</v>
+        <v>63.91598</v>
       </c>
       <c r="R5" t="n">
-        <v>24.10922</v>
+        <v>24.166594</v>
       </c>
       <c r="S5" t="n">
-        <v>65.30377737419909</v>
+        <v>65.45918383792986</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1872900073412296</v>
+        <v>0.1901154591550258</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2977071525264661</v>
+        <v>0.3007953693944687</v>
       </c>
       <c r="V5" t="n">
-        <v>0.5162540149193733</v>
+        <v>0.5198623183921056</v>
       </c>
       <c r="W5" t="n">
-        <v>0.5119305819578537</v>
+        <v>0.5155285967467536</v>
       </c>
       <c r="X5" t="n">
         <v>0.17247999</v>
@@ -3861,7 +3861,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>2026-08-27T14:44:05.320159+00:00</t>
+          <t>2026-08-27T16:09:09.536052+00:00</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
@@ -3892,10 +3892,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>444109225984</v>
+        <v>446440177664</v>
       </c>
       <c r="F6" t="n">
-        <v>184.8099975585938</v>
+        <v>185.7799987792969</v>
       </c>
       <c r="G6" t="n">
         <v>6155940864</v>
@@ -3925,25 +3925,25 @@
         <v>0.47120997</v>
       </c>
       <c r="Q6" t="n">
-        <v>157.95728</v>
+        <v>158.78633</v>
       </c>
       <c r="R6" t="n">
-        <v>72.143196</v>
+        <v>72.52184</v>
       </c>
       <c r="S6" t="n">
-        <v>205.6913982235243</v>
+        <v>206.7709900946194</v>
       </c>
       <c r="T6" t="n">
-        <v>0.49607382324015</v>
+        <v>0.50392617675985</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2893121409250441</v>
+        <v>0.296079276724438</v>
       </c>
       <c r="V6" t="n">
-        <v>0.3772262776378634</v>
+        <v>0.384454843127507</v>
       </c>
       <c r="W6" t="n">
-        <v>0.1792368307752403</v>
+        <v>0.1854262208540287</v>
       </c>
       <c r="X6" t="n">
         <v>0.03477</v>
@@ -3953,7 +3953,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>2026-08-27T14:43:57.558862+00:00</t>
+          <t>2026-08-27T16:09:01.980456+00:00</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr">
@@ -3984,10 +3984,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>301851901952</v>
+        <v>300672679936</v>
       </c>
       <c r="F7" t="n">
-        <v>467.1600036621094</v>
+        <v>465.3349914550781</v>
       </c>
       <c r="G7" t="n">
         <v>134001999872</v>
@@ -4017,25 +4017,25 @@
         <v>0.08857000600000001</v>
       </c>
       <c r="Q7" t="n">
-        <v>37.16468</v>
+        <v>37.01949</v>
       </c>
       <c r="R7" t="n">
-        <v>2.2525926</v>
+        <v>2.2437925</v>
       </c>
       <c r="S7" t="n">
-        <v>55.54747324757798</v>
+        <v>55.33047013127118</v>
       </c>
       <c r="T7" t="n">
-        <v>0.1914307482534894</v>
+        <v>0.1867762923018885</v>
       </c>
       <c r="U7" t="n">
-        <v>0.4758933103739844</v>
+        <v>0.4701275699711385</v>
       </c>
       <c r="V7" t="n">
-        <v>2.801261827107127</v>
+        <v>2.786411777483422</v>
       </c>
       <c r="W7" t="n">
-        <v>2.570664423673745</v>
+        <v>2.556715228303137</v>
       </c>
       <c r="X7" t="n">
         <v>0.07491</v>
@@ -4045,7 +4045,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>2026-08-27T14:44:05.616488+00:00</t>
+          <t>2026-08-27T16:09:09.848736+00:00</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr">
@@ -4057,12 +4057,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>TER</t>
+          <t>NVDA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Teradyne, Inc.</t>
+          <t>NVIDIA Corporation</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -4072,72 +4072,72 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Semiconductor Equipment &amp; Materials</t>
+          <t>Semiconductors</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>56861913088</v>
+        <v>5503689162752</v>
       </c>
       <c r="F8" t="n">
-        <v>363.7049865722656</v>
+        <v>227.2279968261719</v>
       </c>
       <c r="G8" t="n">
-        <v>4464031232</v>
+        <v>253491003392</v>
       </c>
       <c r="H8" t="n">
-        <v>1.039</v>
+        <v>0.852</v>
       </c>
       <c r="I8" t="n">
-        <v>7.26</v>
+        <v>6.52</v>
       </c>
       <c r="J8" t="n">
-        <v>3.858</v>
+        <v>2.145</v>
       </c>
       <c r="K8" t="n">
-        <v>437381248</v>
+        <v>46335873024</v>
       </c>
       <c r="M8" t="n">
-        <v>354828992</v>
+        <v>53171998720</v>
       </c>
       <c r="N8" t="n">
-        <v>100127000</v>
+        <v>12814000128</v>
       </c>
       <c r="O8" t="n">
-        <v>0.5924199999999999</v>
+        <v>0.74144995</v>
       </c>
       <c r="P8" t="n">
-        <v>0.33161</v>
+        <v>0.65596</v>
       </c>
       <c r="Q8" t="n">
-        <v>50.097103</v>
+        <v>34.85092</v>
       </c>
       <c r="R8" t="n">
-        <v>12.737795</v>
+        <v>21.711765</v>
       </c>
       <c r="S8" t="n">
-        <v>130.005374825763</v>
+        <v>118.7781475467469</v>
       </c>
       <c r="T8" t="n">
-        <v>0.13427411038617</v>
+        <v>0.1533830930505784</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.04951001601046368</v>
+        <v>0.06181019230157681</v>
       </c>
       <c r="V8" t="n">
-        <v>0.06132180276838639</v>
+        <v>0.1633521754085567</v>
       </c>
       <c r="W8" t="n">
-        <v>2.116813846967488</v>
+        <v>0.2529219617705865</v>
       </c>
       <c r="X8" t="n">
-        <v>0.00202</v>
+        <v>0.03991</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.00462</v>
+        <v>0.71202004</v>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>2026-08-27T14:44:00.563465+00:00</t>
+          <t>2026-08-27T16:09:01.636136+00:00</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr">
@@ -4149,12 +4149,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>NVDA</t>
+          <t>TER</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>NVIDIA Corporation</t>
+          <t>Teradyne, Inc.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -4164,72 +4164,72 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Semiconductors</t>
+          <t>Semiconductor Equipment &amp; Materials</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5445365268480</v>
+        <v>57397379072</v>
       </c>
       <c r="F9" t="n">
-        <v>224.8000030517578</v>
+        <v>367.1300048828125</v>
       </c>
       <c r="G9" t="n">
-        <v>253491003392</v>
+        <v>4464031232</v>
       </c>
       <c r="H9" t="n">
-        <v>0.852</v>
+        <v>1.039</v>
       </c>
       <c r="I9" t="n">
-        <v>6.52</v>
+        <v>7.26</v>
       </c>
       <c r="J9" t="n">
-        <v>2.145</v>
+        <v>3.858</v>
       </c>
       <c r="K9" t="n">
-        <v>46335873024</v>
+        <v>437381248</v>
       </c>
       <c r="M9" t="n">
-        <v>53171998720</v>
+        <v>354828992</v>
       </c>
       <c r="N9" t="n">
-        <v>12814000128</v>
+        <v>100127000</v>
       </c>
       <c r="O9" t="n">
-        <v>0.74144995</v>
+        <v>0.5924199999999999</v>
       </c>
       <c r="P9" t="n">
-        <v>0.65596</v>
+        <v>0.33161</v>
       </c>
       <c r="Q9" t="n">
-        <v>34.481598</v>
+        <v>50.56887</v>
       </c>
       <c r="R9" t="n">
-        <v>21.478674</v>
+        <v>12.857746</v>
       </c>
       <c r="S9" t="n">
-        <v>117.5194274565526</v>
+        <v>131.2296293781667</v>
       </c>
       <c r="T9" t="n">
-        <v>0.1410588768071743</v>
+        <v>0.1449555960426223</v>
       </c>
       <c r="U9" t="n">
-        <v>0.05046445774189645</v>
+        <v>-0.04055922974317461</v>
       </c>
       <c r="V9" t="n">
-        <v>0.1509214367724905</v>
+        <v>0.07131629484869251</v>
       </c>
       <c r="W9" t="n">
-        <v>0.2395341452801176</v>
+        <v>2.146164955394781</v>
       </c>
       <c r="X9" t="n">
-        <v>0.03991</v>
+        <v>0.00202</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.71202004</v>
+        <v>1.00462</v>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>2026-08-27T14:43:57.233780+00:00</t>
+          <t>2026-08-27T16:09:04.676179+00:00</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr">
@@ -4260,10 +4260,10 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>9450513408</v>
+        <v>9432379392</v>
       </c>
       <c r="F10" t="n">
-        <v>18.23999977111816</v>
+        <v>18.20499992370605</v>
       </c>
       <c r="G10" t="n">
         <v>1672329984</v>
@@ -4290,25 +4290,25 @@
         <v>0.07274</v>
       </c>
       <c r="Q10" t="n">
-        <v>30.399998</v>
+        <v>30.341665</v>
       </c>
       <c r="R10" t="n">
-        <v>5.6511054</v>
+        <v>5.640262</v>
       </c>
       <c r="S10" t="n">
-        <v>18.47413998616669</v>
+        <v>18.43869108136838</v>
       </c>
       <c r="T10" t="n">
-        <v>0.4963084822800812</v>
+        <v>0.4934372887922298</v>
       </c>
       <c r="U10" t="n">
-        <v>0.5751295242911063</v>
+        <v>0.5721070849437224</v>
       </c>
       <c r="V10" t="n">
-        <v>0.8350101148007094</v>
+        <v>0.8314890032423969</v>
       </c>
       <c r="W10" t="n">
-        <v>0.6373428374309795</v>
+        <v>0.6342010199863251</v>
       </c>
       <c r="X10" t="n">
         <v>0.09236999999999999</v>
@@ -4318,7 +4318,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>2026-08-27T14:44:08.754770+00:00</t>
+          <t>2026-08-27T16:09:12.690213+00:00</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr">
@@ -4349,10 +4349,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>774658392064</v>
+        <v>773393219584</v>
       </c>
       <c r="F11" t="n">
-        <v>474.5299987792969</v>
+        <v>473.7550048828125</v>
       </c>
       <c r="G11" t="n">
         <v>41305001984</v>
@@ -4382,25 +4382,25 @@
         <v>0.1725</v>
       </c>
       <c r="Q11" t="n">
-        <v>120.43909</v>
+        <v>120.242386</v>
       </c>
       <c r="R11" t="n">
-        <v>18.754591</v>
+        <v>18.72396</v>
       </c>
       <c r="S11" t="n">
-        <v>87.61617631678946</v>
+        <v>87.47308153305714</v>
       </c>
       <c r="T11" t="n">
-        <v>0.04379482617560004</v>
+        <v>0.04209011915697314</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.08407810576968278</v>
+        <v>-0.08557397300570768</v>
       </c>
       <c r="V11" t="n">
-        <v>1.25045052359732</v>
+        <v>1.246775128101536</v>
       </c>
       <c r="W11" t="n">
-        <v>1.839286692488436</v>
+        <v>1.834649620306049</v>
       </c>
       <c r="X11" t="n">
         <v>0.00425</v>
@@ -4410,7 +4410,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>2026-08-27T14:43:58.004431+00:00</t>
+          <t>2026-08-27T16:09:02.306122+00:00</t>
         </is>
       </c>
       <c r="AD11" t="inlineStr">
@@ -4441,10 +4441,10 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4150167339008</v>
+        <v>4165332369408</v>
       </c>
       <c r="F12" t="n">
-        <v>339.3399963378906</v>
+        <v>340.5849914550781</v>
       </c>
       <c r="G12" t="n">
         <v>445865984000</v>
@@ -4474,25 +4474,25 @@
         <v>0.34033</v>
       </c>
       <c r="Q12" t="n">
-        <v>17.018305</v>
+        <v>17.08049</v>
       </c>
       <c r="R12" t="n">
-        <v>9.307968000000001</v>
+        <v>9.34198</v>
       </c>
       <c r="S12" t="n">
-        <v>183.1090740447072</v>
+        <v>183.7781686733271</v>
       </c>
       <c r="T12" t="n">
-        <v>0.01687095090639623</v>
+        <v>0.02060172058386045</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.1296678678371707</v>
+        <v>-0.126474730374544</v>
       </c>
       <c r="V12" t="n">
-        <v>0.085911530503884</v>
+        <v>0.08989549481487824</v>
       </c>
       <c r="W12" t="n">
-        <v>0.6401969535640104</v>
+        <v>0.6462146267544695</v>
       </c>
       <c r="X12" t="n">
         <v>0.01596</v>
@@ -4502,7 +4502,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>2026-08-27T14:44:02.004564+00:00</t>
+          <t>2026-08-27T16:09:06.196637+00:00</t>
         </is>
       </c>
       <c r="AD12" t="inlineStr">
@@ -4533,10 +4533,10 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>374411329536</v>
+        <v>377490505728</v>
       </c>
       <c r="F13" t="n">
-        <v>471.7850036621094</v>
+        <v>475.6700134277344</v>
       </c>
       <c r="G13" t="n">
         <v>30837000192</v>
@@ -4566,25 +4566,25 @@
         <v>0.33736</v>
       </c>
       <c r="Q13" t="n">
-        <v>40.63652</v>
+        <v>40.97072</v>
       </c>
       <c r="R13" t="n">
-        <v>12.141626</v>
+        <v>12.24148</v>
       </c>
       <c r="S13" t="n">
-        <v>121.7449309025817</v>
+        <v>122.74616687799</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.008753097916871289</v>
+        <v>-0.0005904732788559741</v>
       </c>
       <c r="U13" t="n">
-        <v>0.05027910833708016</v>
+        <v>0.05892784570865572</v>
       </c>
       <c r="V13" t="n">
-        <v>0.1973075732160994</v>
+        <v>0.2071670464471154</v>
       </c>
       <c r="W13" t="n">
-        <v>1.885786464938176</v>
+        <v>1.909550333286604</v>
       </c>
       <c r="X13" t="n">
         <v>0.00331</v>
@@ -4594,7 +4594,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>2026-08-27T14:43:58.926476+00:00</t>
+          <t>2026-08-27T16:09:03.120421+00:00</t>
         </is>
       </c>
       <c r="AD13" t="inlineStr">
@@ -4625,10 +4625,10 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>86910509056</v>
+        <v>87364739072</v>
       </c>
       <c r="F14" t="n">
-        <v>242.0399932861328</v>
+        <v>243.3049926757812</v>
       </c>
       <c r="G14" t="n">
         <v>3966725120</v>
@@ -4658,25 +4658,25 @@
         <v>0.00666</v>
       </c>
       <c r="Q14" t="n">
-        <v>484.08</v>
+        <v>486.61</v>
       </c>
       <c r="R14" t="n">
-        <v>21.90989</v>
+        <v>22.024399</v>
       </c>
       <c r="S14" t="n">
-        <v>82.66072667938373</v>
+        <v>83.09274558722323</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.03523601492597594</v>
+        <v>-0.03019376618144431</v>
       </c>
       <c r="U14" t="n">
-        <v>0.0745870510710791</v>
+        <v>0.08020327979953557</v>
       </c>
       <c r="V14" t="n">
-        <v>1.193782192234185</v>
+        <v>1.205247789702275</v>
       </c>
       <c r="W14" t="n">
-        <v>0.8373946795439899</v>
+        <v>0.8469976510058952</v>
       </c>
       <c r="X14" t="n">
         <v>0.00619</v>
@@ -4686,7 +4686,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>2026-08-27T14:44:07.159805+00:00</t>
+          <t>2026-08-27T16:09:11.290104+00:00</t>
         </is>
       </c>
       <c r="AD14" t="inlineStr">
@@ -4717,10 +4717,10 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1745846403072</v>
+        <v>1751431905280</v>
       </c>
       <c r="F15" t="n">
-        <v>366.9609985351562</v>
+        <v>368.135009765625</v>
       </c>
       <c r="G15" t="n">
         <v>75464998912</v>
@@ -4750,25 +4750,25 @@
         <v>0.48988</v>
       </c>
       <c r="Q15" t="n">
-        <v>61.0584</v>
+        <v>61.253742</v>
       </c>
       <c r="R15" t="n">
-        <v>23.143282</v>
+        <v>23.208532</v>
       </c>
       <c r="S15" t="n">
-        <v>64.15663760192022</v>
+        <v>64.36189451361236</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.03662021210481714</v>
+        <v>-0.03353808976835526</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.1383989134488648</v>
+        <v>-0.1356424097445666</v>
       </c>
       <c r="V15" t="n">
-        <v>0.1083409245445435</v>
+        <v>0.1118868182438673</v>
       </c>
       <c r="W15" t="n">
-        <v>0.2311399127759233</v>
+        <v>0.2350786749049967</v>
       </c>
       <c r="X15" t="n">
         <v>0.01948</v>
@@ -4778,7 +4778,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>2026-08-27T14:43:58.416337+00:00</t>
+          <t>2026-08-27T16:09:02.697030+00:00</t>
         </is>
       </c>
       <c r="AD15" t="inlineStr">
@@ -4809,10 +4809,10 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>34685063168</v>
+        <v>35117383680</v>
       </c>
       <c r="F16" t="n">
-        <v>431.2349853515625</v>
+        <v>436.6099853515625</v>
       </c>
       <c r="G16" t="n">
         <v>2602398976</v>
@@ -4839,22 +4839,22 @@
         <v>-0.03607</v>
       </c>
       <c r="R16" t="n">
-        <v>13.328112</v>
+        <v>13.494235</v>
       </c>
       <c r="S16" t="n">
-        <v>67.01063160518642</v>
+        <v>67.84586348654926</v>
       </c>
       <c r="T16" t="n">
-        <v>0.3883040117519498</v>
+        <v>0.4056081134984333</v>
       </c>
       <c r="U16" t="n">
-        <v>0.3241064696929745</v>
+        <v>0.3406104003024022</v>
       </c>
       <c r="V16" t="n">
-        <v>0.3690434576371553</v>
+        <v>0.3861074919450411</v>
       </c>
       <c r="W16" t="n">
-        <v>0.4583529507927036</v>
+        <v>0.4765301566706552</v>
       </c>
       <c r="X16" t="n">
         <v>0.02641</v>
@@ -4864,7 +4864,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>2026-08-27T14:44:08.393508+00:00</t>
+          <t>2026-08-27T16:09:12.265824+00:00</t>
         </is>
       </c>
       <c r="AD16" t="inlineStr">
@@ -4895,10 +4895,10 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>114083389440</v>
+        <v>114632744960</v>
       </c>
       <c r="F17" t="n">
-        <v>329.1499938964844</v>
+        <v>330.7349853515625</v>
       </c>
       <c r="G17" t="n">
         <v>5032822784</v>
@@ -4925,22 +4925,22 @@
         <v>-0.22173999</v>
       </c>
       <c r="R17" t="n">
-        <v>22.667873</v>
+        <v>22.777027</v>
       </c>
       <c r="S17" t="n">
-        <v>65.58409798624353</v>
+        <v>65.89991071261693</v>
       </c>
       <c r="T17" t="n">
-        <v>0.2174508497197702</v>
+        <v>0.2233133720638851</v>
       </c>
       <c r="U17" t="n">
-        <v>0.3760451425411409</v>
+        <v>0.3826713610833639</v>
       </c>
       <c r="V17" t="n">
-        <v>0.9452158905298933</v>
+        <v>0.954582898343789</v>
       </c>
       <c r="W17" t="n">
-        <v>0.6425470078298094</v>
+        <v>0.6504565415386059</v>
       </c>
       <c r="X17" t="n">
         <v>0.02962</v>
@@ -4950,7 +4950,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>2026-08-27T14:44:06.743871+00:00</t>
+          <t>2026-08-27T16:09:10.938406+00:00</t>
         </is>
       </c>
       <c r="AD17" t="inlineStr">
@@ -4981,10 +4981,10 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>106948542464</v>
+        <v>107635777536</v>
       </c>
       <c r="F18" t="n">
-        <v>300.3500061035156</v>
+        <v>302.2799987792969</v>
       </c>
       <c r="G18" t="n">
         <v>2512349952</v>
@@ -5011,22 +5011,22 @@
         <v>-0.07902000000000001</v>
       </c>
       <c r="R18" t="n">
-        <v>42.569126</v>
+        <v>42.84267</v>
       </c>
       <c r="S18" t="n">
-        <v>154.3598739752732</v>
+        <v>155.3517670545175</v>
       </c>
       <c r="T18" t="n">
-        <v>0.1372586109891705</v>
+        <v>0.1445664210277087</v>
       </c>
       <c r="U18" t="n">
-        <v>0.3166893397916455</v>
+        <v>0.3251501379619017</v>
       </c>
       <c r="V18" t="n">
-        <v>0.7482537879410271</v>
+        <v>0.7594877381243681</v>
       </c>
       <c r="W18" t="n">
-        <v>0.4634086828336175</v>
+        <v>0.4728122719201784</v>
       </c>
       <c r="X18" t="n">
         <v>0.00616</v>
@@ -5036,7 +5036,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>2026-08-27T14:44:07.601223+00:00</t>
+          <t>2026-08-27T16:09:11.639252+00:00</t>
         </is>
       </c>
       <c r="AD18" t="inlineStr">
@@ -5067,10 +5067,10 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2770140921856</v>
+        <v>2765610549248</v>
       </c>
       <c r="F19" t="n">
-        <v>256.8200073242188</v>
+        <v>256.3999938964844</v>
       </c>
       <c r="G19" t="n">
         <v>775680032768</v>
@@ -5100,25 +5100,25 @@
         <v>0.13689</v>
       </c>
       <c r="Q19" t="n">
-        <v>20.644695</v>
+        <v>20.610933</v>
       </c>
       <c r="R19" t="n">
-        <v>3.5712419</v>
+        <v>3.5654013</v>
       </c>
       <c r="S19" t="n">
-        <v>860.5260524956964</v>
+        <v>859.1187220505416</v>
       </c>
       <c r="T19" t="n">
-        <v>0.112449132137372</v>
+        <v>0.1106297895634141</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.06270070319628196</v>
+        <v>-0.06423359891794023</v>
       </c>
       <c r="V19" t="n">
-        <v>0.2192366505335253</v>
+        <v>0.2172426634990046</v>
       </c>
       <c r="W19" t="n">
-        <v>0.1208974022230735</v>
+        <v>0.1190642430196633</v>
       </c>
       <c r="X19" t="n">
         <v>0.0887</v>
@@ -5128,7 +5128,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>2026-08-27T14:44:02.346615+00:00</t>
+          <t>2026-08-27T16:09:06.883781+00:00</t>
         </is>
       </c>
       <c r="AD19" t="inlineStr">
@@ -5140,12 +5140,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>ACMR</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Microsoft Corporation</t>
+          <t>ACM Research, Inc.</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -5155,72 +5155,69 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Software - Infrastructure</t>
+          <t>Semiconductor Equipment &amp; Materials</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>3743923044352</v>
+        <v>5588303360</v>
       </c>
       <c r="F20" t="n">
-        <v>504.1950073242188</v>
+        <v>80.23500061035156</v>
       </c>
       <c r="G20" t="n">
-        <v>331839012864</v>
+        <v>1037772032</v>
       </c>
       <c r="H20" t="n">
-        <v>0.177</v>
+        <v>0.36</v>
       </c>
       <c r="I20" t="n">
-        <v>17.97</v>
+        <v>2.12</v>
       </c>
       <c r="J20" t="n">
-        <v>0.317</v>
+        <v>1.806</v>
       </c>
       <c r="K20" t="n">
-        <v>16545500160</v>
+        <v>-186610256</v>
       </c>
       <c r="M20" t="n">
-        <v>76842999808</v>
+        <v>1439374976</v>
       </c>
       <c r="N20" t="n">
-        <v>128812998656</v>
+        <v>349319008</v>
       </c>
       <c r="O20" t="n">
-        <v>0.67944</v>
+        <v>0.43835</v>
       </c>
       <c r="P20" t="n">
-        <v>0.45111</v>
+        <v>0.16982001</v>
       </c>
       <c r="Q20" t="n">
-        <v>28.057598</v>
+        <v>37.8467</v>
       </c>
       <c r="R20" t="n">
-        <v>11.282348</v>
-      </c>
-      <c r="S20" t="n">
-        <v>226.2804392824109</v>
+        <v>5.3849044</v>
       </c>
       <c r="T20" t="n">
-        <v>0.2842104134029855</v>
+        <v>0.1140655977533434</v>
       </c>
       <c r="U20" t="n">
-        <v>0.18303514463473</v>
+        <v>-0.1359573542646804</v>
       </c>
       <c r="V20" t="n">
-        <v>0.2637000847261934</v>
+        <v>0.1718270655746839</v>
       </c>
       <c r="W20" t="n">
-        <v>0.003163998002835955</v>
+        <v>1.807382814014621</v>
       </c>
       <c r="X20" t="n">
-        <v>0.00090000004</v>
+        <v>0.12675999</v>
       </c>
       <c r="Y20" t="n">
-        <v>0.75881</v>
+        <v>0.78055</v>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>2026-08-27T14:44:01.670727+00:00</t>
+          <t>2026-08-27T16:09:03.937893+00:00</t>
         </is>
       </c>
       <c r="AD20" t="inlineStr">
@@ -5251,10 +5248,10 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>101991071744</v>
+        <v>101964120064</v>
       </c>
       <c r="F21" t="n">
-        <v>264.9200134277344</v>
+        <v>264.8500061035156</v>
       </c>
       <c r="G21" t="n">
         <v>11479600128</v>
@@ -5284,25 +5281,25 @@
         <v>0.20362</v>
       </c>
       <c r="Q21" t="n">
-        <v>58.096497</v>
+        <v>58.081142</v>
       </c>
       <c r="R21" t="n">
-        <v>8.884549</v>
+        <v>8.882201</v>
       </c>
       <c r="S21" t="n">
-        <v>37.82297407757266</v>
+        <v>37.81297915667855</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.01721317767058816</v>
+        <v>-0.01747288728942176</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1566135634361057</v>
+        <v>-0.1568364353397504</v>
       </c>
       <c r="V21" t="n">
-        <v>0.0108630910272951</v>
+        <v>0.01059596202017077</v>
       </c>
       <c r="W21" t="n">
-        <v>1.050976853768209</v>
+        <v>1.050434866019872</v>
       </c>
       <c r="X21" t="n">
         <v>0.00269</v>
@@ -5312,7 +5309,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>2026-08-27T14:44:06.049229+00:00</t>
+          <t>2026-08-27T16:09:10.180635+00:00</t>
         </is>
       </c>
       <c r="AD21" t="inlineStr">
@@ -5324,12 +5321,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ACMR</t>
+          <t>ASML</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>ACM Research, Inc.</t>
+          <t>ASML Holding N.V.</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -5343,65 +5340,68 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5499500544</v>
+        <v>664589041664</v>
       </c>
       <c r="F22" t="n">
-        <v>78.95999908447266</v>
+        <v>1730.25</v>
       </c>
       <c r="G22" t="n">
-        <v>1037772032</v>
+        <v>35327500288</v>
       </c>
       <c r="H22" t="n">
-        <v>0.36</v>
+        <v>0.213</v>
       </c>
       <c r="I22" t="n">
-        <v>2.12</v>
+        <v>29.68</v>
       </c>
       <c r="J22" t="n">
-        <v>1.806</v>
+        <v>0.285</v>
       </c>
       <c r="K22" t="n">
-        <v>-186610256</v>
+        <v>8437675008</v>
       </c>
       <c r="M22" t="n">
-        <v>1439374976</v>
+        <v>7581499904</v>
       </c>
       <c r="N22" t="n">
-        <v>349319008</v>
+        <v>1984400000</v>
       </c>
       <c r="O22" t="n">
-        <v>0.43835</v>
+        <v>0.5273300400000001</v>
       </c>
       <c r="P22" t="n">
-        <v>0.16982001</v>
+        <v>0.37057</v>
       </c>
       <c r="Q22" t="n">
-        <v>37.245285</v>
+        <v>58.296833</v>
       </c>
       <c r="R22" t="n">
-        <v>5.299334</v>
+        <v>18.81223</v>
+      </c>
+      <c r="S22" t="n">
+        <v>78.76447493342469</v>
       </c>
       <c r="T22" t="n">
-        <v>0.09636216002343279</v>
+        <v>0.09305414155329239</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1496877173650309</v>
+        <v>0.07891401065821091</v>
       </c>
       <c r="V22" t="n">
-        <v>0.1532057496239345</v>
+        <v>0.1374126640944859</v>
       </c>
       <c r="W22" t="n">
-        <v>1.762771143990741</v>
+        <v>1.261878397495278</v>
       </c>
       <c r="X22" t="n">
-        <v>0.12675999</v>
+        <v>0.00016000001</v>
       </c>
       <c r="Y22" t="n">
-        <v>0.78055</v>
+        <v>0.20384</v>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>2026-08-27T14:43:59.750321+00:00</t>
+          <t>2026-08-27T16:09:08.380197+00:00</t>
         </is>
       </c>
       <c r="AD22" t="inlineStr">
@@ -5413,12 +5413,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ASML</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>ASML Holding N.V.</t>
+          <t>Microsoft Corporation</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -5428,72 +5428,72 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Semiconductor Equipment &amp; Materials</t>
+          <t>Software - Infrastructure</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>663068016640</v>
+        <v>3711547473920</v>
       </c>
       <c r="F23" t="n">
-        <v>1726.2900390625</v>
+        <v>499.8349914550781</v>
       </c>
       <c r="G23" t="n">
-        <v>35327500288</v>
+        <v>331839012864</v>
       </c>
       <c r="H23" t="n">
-        <v>0.213</v>
+        <v>0.177</v>
       </c>
       <c r="I23" t="n">
-        <v>29.68</v>
+        <v>17.97</v>
       </c>
       <c r="J23" t="n">
-        <v>0.285</v>
+        <v>0.317</v>
       </c>
       <c r="K23" t="n">
-        <v>8437675008</v>
+        <v>16545500160</v>
       </c>
       <c r="M23" t="n">
-        <v>7581499904</v>
+        <v>76842999808</v>
       </c>
       <c r="N23" t="n">
-        <v>1984400000</v>
+        <v>128812998656</v>
       </c>
       <c r="O23" t="n">
-        <v>0.5273300400000001</v>
+        <v>0.67944</v>
       </c>
       <c r="P23" t="n">
-        <v>0.37057</v>
+        <v>0.45111</v>
       </c>
       <c r="Q23" t="n">
-        <v>58.16341</v>
+        <v>27.81497</v>
       </c>
       <c r="R23" t="n">
-        <v>18.769175</v>
+        <v>11.184783</v>
       </c>
       <c r="S23" t="n">
-        <v>78.58420903996969</v>
+        <v>224.3236794311572</v>
       </c>
       <c r="T23" t="n">
-        <v>0.09055250785693425</v>
+        <v>0.2731052304868204</v>
       </c>
       <c r="U23" t="n">
-        <v>0.0764447389708085</v>
+        <v>0.1728048727569254</v>
       </c>
       <c r="V23" t="n">
-        <v>0.1348095086431742</v>
+        <v>0.2527722644518891</v>
       </c>
       <c r="W23" t="n">
-        <v>1.256701897826153</v>
+        <v>-0.005510781480655758</v>
       </c>
       <c r="X23" t="n">
-        <v>0.00016000001</v>
+        <v>0.00090000004</v>
       </c>
       <c r="Y23" t="n">
-        <v>0.20384</v>
+        <v>0.75881</v>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>2026-08-27T14:44:04.027839+00:00</t>
+          <t>2026-08-27T16:09:05.794501+00:00</t>
         </is>
       </c>
       <c r="AD23" t="inlineStr">
@@ -5524,10 +5524,10 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>304308781056</v>
+        <v>309426978816</v>
       </c>
       <c r="F24" t="n">
-        <v>373.25</v>
+        <v>379.6650085449219</v>
       </c>
       <c r="G24" t="n">
         <v>10606499840</v>
@@ -5554,25 +5554,25 @@
         <v>-0.02465</v>
       </c>
       <c r="Q24" t="n">
-        <v>324.68262</v>
+        <v>330.1435</v>
       </c>
       <c r="R24" t="n">
-        <v>28.690783</v>
+        <v>29.173336</v>
       </c>
       <c r="S24" t="n">
-        <v>85.01729274362188</v>
+        <v>86.44720651663782</v>
       </c>
       <c r="T24" t="n">
-        <v>0.1700626959247649</v>
+        <v>0.1901724405796923</v>
       </c>
       <c r="U24" t="n">
-        <v>0.4479963374642624</v>
+        <v>0.472882898423</v>
       </c>
       <c r="V24" t="n">
-        <v>1.576981561980035</v>
+        <v>1.621271873407251</v>
       </c>
       <c r="W24" t="n">
-        <v>0.9894994871579654</v>
+        <v>1.023692805872596</v>
       </c>
       <c r="X24" t="n">
         <v>0.0076</v>
@@ -5582,7 +5582,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>2026-08-27T14:44:01.199251+00:00</t>
+          <t>2026-08-27T16:09:05.381261+00:00</t>
         </is>
       </c>
       <c r="AD24" t="inlineStr">
@@ -5613,10 +5613,10 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>24739723264</v>
+        <v>24662034432</v>
       </c>
       <c r="F25" t="n">
-        <v>38.2400016784668</v>
+        <v>38.125</v>
       </c>
       <c r="G25" t="n">
         <v>39063072768</v>
@@ -5646,22 +5646,22 @@
         <v>0.13382</v>
       </c>
       <c r="Q25" t="n">
-        <v>11.731626</v>
+        <v>11.694785</v>
       </c>
       <c r="R25" t="n">
-        <v>0.6332432</v>
+        <v>0.63133883</v>
       </c>
       <c r="T25" t="n">
-        <v>0.3441125009838433</v>
+        <v>0.340070262833305</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.07409195193998608</v>
+        <v>-0.07687649626422899</v>
       </c>
       <c r="V25" t="n">
-        <v>0.1380953397340021</v>
+        <v>0.1346726705765802</v>
       </c>
       <c r="W25" t="n">
-        <v>-0.1456657034754569</v>
+        <v>-0.1482349993373711</v>
       </c>
       <c r="X25" t="n">
         <v>0.12878999</v>
@@ -5671,7 +5671,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>2026-08-27T14:44:06.387065+00:00</t>
+          <t>2026-08-27T16:09:10.554938+00:00</t>
         </is>
       </c>
       <c r="AD25" t="inlineStr">
@@ -5683,12 +5683,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ARM</t>
+          <t>CRWD</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Arm Holdings plc</t>
+          <t>CrowdStrike Holdings, Inc.</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -5698,72 +5698,69 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Semiconductors</t>
+          <t>Software - Infrastructure</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>273605214208</v>
+        <v>226521956352</v>
       </c>
       <c r="F26" t="n">
-        <v>256.1849975585938</v>
+        <v>222.4600067138672</v>
       </c>
       <c r="G26" t="n">
-        <v>5155999744</v>
+        <v>5094199808</v>
       </c>
       <c r="H26" t="n">
-        <v>0.224</v>
+        <v>0.256</v>
       </c>
       <c r="I26" t="n">
-        <v>0.98</v>
-      </c>
-      <c r="J26" t="n">
-        <v>1.083</v>
+        <v>0.06</v>
       </c>
       <c r="K26" t="n">
-        <v>1334499968</v>
+        <v>1926365056</v>
       </c>
       <c r="M26" t="n">
-        <v>3888000000</v>
+        <v>4552800768</v>
       </c>
       <c r="N26" t="n">
-        <v>485000000</v>
+        <v>821342976</v>
       </c>
       <c r="O26" t="n">
-        <v>0.97537005</v>
+        <v>0.75136</v>
       </c>
       <c r="P26" t="n">
-        <v>0.07603</v>
+        <v>-0.022079999</v>
       </c>
       <c r="Q26" t="n">
-        <v>261.41327</v>
+        <v>3707.6667</v>
       </c>
       <c r="R26" t="n">
-        <v>53.065407</v>
+        <v>44.46664</v>
       </c>
       <c r="S26" t="n">
-        <v>205.0245191223564</v>
+        <v>117.5903578848972</v>
       </c>
       <c r="T26" t="n">
-        <v>0.04676387925368974</v>
+        <v>0.2236523816258331</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.2358844932340578</v>
+        <v>0.3261401294418311</v>
       </c>
       <c r="V26" t="n">
-        <v>0.9446256784305895</v>
+        <v>1.449258299620444</v>
       </c>
       <c r="W26" t="n">
-        <v>0.8213066322250082</v>
+        <v>1.105582115186476</v>
       </c>
       <c r="X26" t="n">
-        <v>0.0007</v>
+        <v>0.01467</v>
       </c>
       <c r="Y26" t="n">
-        <v>0.96185</v>
+        <v>0.76657</v>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>2026-08-27T14:44:04.450434+00:00</t>
+          <t>2026-08-27T16:09:04.974925+00:00</t>
         </is>
       </c>
       <c r="AD26" t="inlineStr">
@@ -5775,12 +5772,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>CRWD</t>
+          <t>ARM</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>CrowdStrike Holdings, Inc.</t>
+          <t>Arm Holdings plc</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -5790,69 +5787,72 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Software - Infrastructure</t>
+          <t>Semiconductors</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>225371324416</v>
+        <v>268195807232</v>
       </c>
       <c r="F27" t="n">
-        <v>221.3370971679688</v>
+        <v>251.1199951171875</v>
       </c>
       <c r="G27" t="n">
-        <v>5094199808</v>
+        <v>5155999744</v>
       </c>
       <c r="H27" t="n">
-        <v>0.256</v>
+        <v>0.224</v>
       </c>
       <c r="I27" t="n">
-        <v>0.06</v>
+        <v>0.98</v>
+      </c>
+      <c r="J27" t="n">
+        <v>1.083</v>
       </c>
       <c r="K27" t="n">
-        <v>1926365056</v>
+        <v>1334499968</v>
       </c>
       <c r="M27" t="n">
-        <v>4552800768</v>
+        <v>3888000000</v>
       </c>
       <c r="N27" t="n">
-        <v>821342976</v>
+        <v>485000000</v>
       </c>
       <c r="O27" t="n">
-        <v>0.75136</v>
+        <v>0.97537005</v>
       </c>
       <c r="P27" t="n">
-        <v>-0.022079999</v>
+        <v>0.07603</v>
       </c>
       <c r="Q27" t="n">
-        <v>3688.8335</v>
+        <v>256.24487</v>
       </c>
       <c r="R27" t="n">
-        <v>44.240772</v>
+        <v>52.01626</v>
       </c>
       <c r="S27" t="n">
-        <v>116.993050571615</v>
+        <v>200.9710106130179</v>
       </c>
       <c r="T27" t="n">
-        <v>0.2174757615650582</v>
+        <v>0.02606843785578672</v>
       </c>
       <c r="U27" t="n">
-        <v>0.3194461828194859</v>
+        <v>-0.2509917280220773</v>
       </c>
       <c r="V27" t="n">
-        <v>1.436895198649435</v>
+        <v>0.9061787205574241</v>
       </c>
       <c r="W27" t="n">
-        <v>1.0949537856645</v>
+        <v>0.7852978002220368</v>
       </c>
       <c r="X27" t="n">
-        <v>0.01467</v>
+        <v>0.0007</v>
       </c>
       <c r="Y27" t="n">
-        <v>0.76657</v>
+        <v>0.96185</v>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>2026-08-27T14:44:00.899887+00:00</t>
+          <t>2026-08-27T16:09:08.695270+00:00</t>
         </is>
       </c>
       <c r="AD27" t="inlineStr">
@@ -5883,10 +5883,10 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>219665891328</v>
+        <v>218834583552</v>
       </c>
       <c r="F28" t="n">
-        <v>244.4250030517578</v>
+        <v>243.5</v>
       </c>
       <c r="G28" t="n">
         <v>8717100032</v>
@@ -5916,25 +5916,25 @@
         <v>0.14479999</v>
       </c>
       <c r="Q28" t="n">
-        <v>82.29798</v>
+        <v>81.98653400000001</v>
       </c>
       <c r="R28" t="n">
-        <v>25.199423</v>
+        <v>25.104057</v>
       </c>
       <c r="S28" t="n">
-        <v>96.78190158916925</v>
+        <v>96.41563832052638</v>
       </c>
       <c r="T28" t="n">
-        <v>0.4009571923058692</v>
+        <v>0.3956554037732509</v>
       </c>
       <c r="U28" t="n">
-        <v>0.1936010535580535</v>
+        <v>0.189083984504816</v>
       </c>
       <c r="V28" t="n">
-        <v>2.022833487051142</v>
+        <v>2.011394146903351</v>
       </c>
       <c r="W28" t="n">
-        <v>2.275114079046758</v>
+        <v>2.262719389443954</v>
       </c>
       <c r="X28" t="n">
         <v>0.00494</v>
@@ -5944,7 +5944,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>2026-08-27T14:44:04.936838+00:00</t>
+          <t>2026-08-27T16:09:09.210813+00:00</t>
         </is>
       </c>
       <c r="AD28" t="inlineStr">
@@ -5975,10 +5975,10 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1455978708992</v>
+        <v>1461299576832</v>
       </c>
       <c r="F29" t="n">
-        <v>571.531005859375</v>
+        <v>573.61962890625</v>
       </c>
       <c r="G29" t="n">
         <v>228246994944</v>
@@ -6008,25 +6008,25 @@
         <v>0.34827</v>
       </c>
       <c r="Q29" t="n">
-        <v>21.518488</v>
+        <v>21.597124</v>
       </c>
       <c r="R29" t="n">
-        <v>6.378961</v>
+        <v>6.402273</v>
       </c>
       <c r="S29" t="n">
-        <v>67.55145378317903</v>
+        <v>67.79832027632233</v>
       </c>
       <c r="T29" t="n">
-        <v>-0.03686990154415115</v>
+        <v>-0.03335020497449759</v>
       </c>
       <c r="U29" t="n">
-        <v>-0.09952819288634152</v>
+        <v>-0.09623747698446183</v>
       </c>
       <c r="V29" t="n">
-        <v>-0.1241253145406794</v>
+        <v>-0.1209245694527549</v>
       </c>
       <c r="W29" t="n">
-        <v>-0.2327809291088164</v>
+        <v>-0.2299771767016204</v>
       </c>
       <c r="X29" t="n">
         <v>0.00148</v>
@@ -6036,7 +6036,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>2026-08-27T14:44:02.751389+00:00</t>
+          <t>2026-08-27T16:09:07.223487+00:00</t>
         </is>
       </c>
       <c r="AD29" t="inlineStr">
@@ -6067,10 +6067,10 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>142179500032</v>
+        <v>140380372992</v>
       </c>
       <c r="F30" t="n">
-        <v>137.522705078125</v>
+        <v>135.7825012207031</v>
       </c>
       <c r="G30" t="n">
         <v>14732000256</v>
@@ -6100,25 +6100,25 @@
         <v>0.04063</v>
       </c>
       <c r="Q30" t="n">
-        <v>85.95169</v>
+        <v>84.86405999999999</v>
       </c>
       <c r="R30" t="n">
-        <v>9.651066</v>
+        <v>9.528942000000001</v>
       </c>
       <c r="S30" t="n">
-        <v>27.61102088984867</v>
+        <v>27.26163343051908</v>
       </c>
       <c r="T30" t="n">
-        <v>0.2431992556823022</v>
+        <v>0.2274678887123656</v>
       </c>
       <c r="U30" t="n">
-        <v>0.2648091679595752</v>
+        <v>0.2488043504879045</v>
       </c>
       <c r="V30" t="n">
-        <v>0.3194157214711124</v>
+        <v>0.3027199160276204</v>
       </c>
       <c r="W30" t="n">
-        <v>-0.2256429735686207</v>
+        <v>-0.2354416397863344</v>
       </c>
       <c r="X30" t="n">
         <v>0.00176</v>
@@ -6128,7 +6128,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>2026-08-27T14:44:08.083524+00:00</t>
+          <t>2026-08-27T16:09:11.940172+00:00</t>
         </is>
       </c>
       <c r="AD30" t="inlineStr">
@@ -6159,10 +6159,10 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>430356758528</v>
+        <v>426021650432</v>
       </c>
       <c r="F31" t="n">
-        <v>149.4049987792969</v>
+        <v>147.8899993896484</v>
       </c>
       <c r="G31" t="n">
         <v>67356999680</v>
@@ -6192,22 +6192,22 @@
         <v>0.36202</v>
       </c>
       <c r="Q31" t="n">
-        <v>25.583048</v>
+        <v>25.32534</v>
       </c>
       <c r="R31" t="n">
-        <v>6.389191</v>
+        <v>6.324831</v>
       </c>
       <c r="T31" t="n">
-        <v>0.2454568182689785</v>
+        <v>0.2328276135239733</v>
       </c>
       <c r="U31" t="n">
-        <v>-0.2639922678418849</v>
+        <v>-0.2714555473446226</v>
       </c>
       <c r="V31" t="n">
-        <v>0.01729939871589337</v>
+        <v>0.006983760144649853</v>
       </c>
       <c r="W31" t="n">
-        <v>-0.3591965229590346</v>
+        <v>-0.3656944104764112</v>
       </c>
       <c r="X31" t="n">
         <v>0.40498</v>
@@ -6217,7 +6217,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>2026-08-27T14:44:03.194980+00:00</t>
+          <t>2026-08-27T16:09:07.560885+00:00</t>
         </is>
       </c>
       <c r="AD31" t="inlineStr">
@@ -6481,7 +6481,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>TER</t>
+          <t>NVDA</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -6510,7 +6510,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>NVDA</t>
+          <t>TER</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -6849,18 +6849,23 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>ACMR</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>100</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="C20" t="n">
-        <v>100</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
           <t>HIGH</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>price_to_fcf</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -6907,23 +6912,18 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ACMR</t>
+          <t>ASML</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>94.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="C22" t="n">
-        <v>94.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
           <t>HIGH</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>price_to_fcf</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -6941,7 +6941,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ASML</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -7038,18 +7038,23 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ARM</t>
+          <t>CRWD</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>100</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="C26" t="n">
-        <v>100</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
           <t>HIGH</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>eps_growth</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -7067,23 +7072,18 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>CRWD</t>
+          <t>ARM</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>94.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="C27" t="n">
-        <v>94.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
           <t>HIGH</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>eps_growth</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -7292,7 +7292,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>56.77</v>
+        <v>56.69</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/reports/investment_dashboard.xlsx
+++ b/reports/investment_dashboard.xlsx
@@ -534,7 +534,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>56.69</v>
+        <v>56.68</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>915.5549926757812</v>
+        <v>912.260009765625</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -586,7 +586,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>55.59</v>
+        <v>55.57</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>425.5849914550781</v>
+        <v>425.1000061035156</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>53.55</v>
+        <v>53.45</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>237.7100067138672</v>
+        <v>234.6399993896484</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -685,7 +685,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>53.01</v>
+        <v>52.89</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -693,7 +693,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>201.9745025634766</v>
+        <v>199.7149963378906</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -737,7 +737,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>52.36</v>
+        <v>52.37</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -745,7 +745,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>185.7799987792969</v>
+        <v>185.8999938964844</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>465.3349914550781</v>
+        <v>464.0498962402344</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -836,7 +836,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>50.98</v>
+        <v>50.9</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -844,7 +844,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>227.2279968261719</v>
+        <v>226.1300048828125</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>50.9</v>
+        <v>50.83</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>367.1300048828125</v>
+        <v>364.6549987792969</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>47.66</v>
+        <v>47.68</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -943,7 +943,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>18.20499992370605</v>
+        <v>18.14500045776367</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -982,7 +982,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>47.61</v>
+        <v>47.56</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -990,7 +990,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>473.7550048828125</v>
+        <v>471.2699890136719</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>46.73</v>
+        <v>46.74</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -1042,7 +1042,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>340.5849914550781</v>
+        <v>340.8099975585938</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>45.4</v>
+        <v>45.39</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -1089,7 +1089,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>475.6700134277344</v>
+        <v>475.2000122070312</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -1128,7 +1128,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>45.16</v>
+        <v>45.08</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>243.3049926757812</v>
+        <v>240.8500061035156</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -1180,7 +1180,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>44.26</v>
+        <v>44.24</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>368.135009765625</v>
+        <v>367.8999938964844</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -1232,7 +1232,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>43.73</v>
+        <v>43.82</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>436.6099853515625</v>
+        <v>444.2250061035156</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1279,7 +1279,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>43.18</v>
+        <v>43.22</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -1287,7 +1287,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>330.7349853515625</v>
+        <v>331.8399963378906</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1331,7 +1331,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>42.91</v>
+        <v>43.04</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -1339,7 +1339,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>302.2799987792969</v>
+        <v>306.125</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1383,7 +1383,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>42.62</v>
+        <v>42.54</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -1391,7 +1391,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>256.3999938964844</v>
+        <v>255.3699035644531</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1421,16 +1421,16 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>ACMR</t>
+          <t>VRT</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>ACM Research, Inc.</t>
+          <t>Vertiv Holdings Co</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>42.52</v>
+        <v>42.45</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>80.23500061035156</v>
+        <v>267.7550048828125</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1446,24 +1446,24 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>94.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="I20" t="n">
-        <v>94.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Revenue Growth</t>
+          <t>Earnings Fcf</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Industry Growth; Competitive Advantage; Catalysts; Inflation Resilience</t>
+          <t>Industry Growth; Valuation; Competitive Advantage; Momentum; Catalysts; Inflation Resilience</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>Negative free cash flow / unprofitable growth</t>
+          <t>High market sensitivity / beta</t>
         </is>
       </c>
     </row>
@@ -1473,16 +1473,16 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>VRT</t>
+          <t>ACMR</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Vertiv Holdings Co</t>
+          <t>ACM Research, Inc.</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>42.39</v>
+        <v>42.43</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -1490,7 +1490,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>264.8500061035156</v>
+        <v>79.52999877929688</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1498,24 +1498,24 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>100</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="I21" t="n">
-        <v>100</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Earnings Fcf</t>
+          <t>Revenue Growth</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>Industry Growth; Valuation; Competitive Advantage; Momentum; Catalysts; Inflation Resilience</t>
+          <t>Industry Growth; Competitive Advantage; Catalysts; Inflation Resilience</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>High market sensitivity / beta</t>
+          <t>Negative free cash flow / unprofitable growth</t>
         </is>
       </c>
     </row>
@@ -1525,16 +1525,16 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>ASML</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>ASML Holding N.V.</t>
+          <t>Microsoft Corporation</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>42.38</v>
+        <v>42.35</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -1542,7 +1542,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1730.25</v>
+        <v>502.9700012207031</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1557,7 +1557,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Earnings Fcf; Balance Sheet</t>
+          <t>Earnings Fcf</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1572,16 +1572,16 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>ASML</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Microsoft Corporation</t>
+          <t>ASML Holding N.V.</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>42.25</v>
+        <v>42.32</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>499.8349914550781</v>
+        <v>1723.60498046875</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Earnings Fcf</t>
+          <t>Earnings Fcf; Balance Sheet</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -1628,7 +1628,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>42.16</v>
+        <v>42.24</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -1636,7 +1636,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>379.6650085449219</v>
+        <v>386.5599975585938</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1680,7 +1680,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>41.72</v>
+        <v>41.75</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>38.125</v>
+        <v>38.17499923706055</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1732,7 +1732,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>40.84</v>
+        <v>41.04</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -1740,7 +1740,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>222.4600067138672</v>
+        <v>226.4199981689453</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1784,7 +1784,7 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>40.72</v>
+        <v>40.71</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -1792,7 +1792,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>251.1199951171875</v>
+        <v>250.75</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1836,7 +1836,7 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>39.85</v>
+        <v>39.89</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>243.5</v>
+        <v>244.3000030517578</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1888,7 +1888,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>39.63</v>
+        <v>39.56</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -1896,7 +1896,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>573.61962890625</v>
+        <v>569.1900024414062</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>36.23</v>
+        <v>36.37</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -1943,7 +1943,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>135.7825012207031</v>
+        <v>137.4299926757812</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1977,7 +1977,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>31.42</v>
+        <v>31.47</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -1985,7 +1985,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>147.8899993896484</v>
+        <v>149.5950012207031</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -2131,13 +2131,13 @@
         <v>9.02</v>
       </c>
       <c r="F2" t="n">
-        <v>7.32</v>
+        <v>7.34</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>6.85</v>
+        <v>6.82</v>
       </c>
       <c r="I2" t="n">
         <v>3.5</v>
@@ -2149,7 +2149,7 @@
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>56.69</v>
+        <v>56.68</v>
       </c>
     </row>
     <row r="3">
@@ -2177,7 +2177,7 @@
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>5.42</v>
+        <v>5.4</v>
       </c>
       <c r="I3" t="n">
         <v>2.69</v>
@@ -2189,7 +2189,7 @@
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>55.59</v>
+        <v>55.57</v>
       </c>
     </row>
     <row r="4">
@@ -2211,13 +2211,13 @@
         <v>9.91</v>
       </c>
       <c r="F4" t="n">
-        <v>2.35</v>
+        <v>2.38</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>7.75</v>
+        <v>7.62</v>
       </c>
       <c r="I4" t="n">
         <v>3.54</v>
@@ -2229,7 +2229,7 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>53.55</v>
+        <v>53.45</v>
       </c>
     </row>
     <row r="5">
@@ -2251,13 +2251,13 @@
         <v>10</v>
       </c>
       <c r="F5" t="n">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>8.6</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="I5" t="n">
         <v>3.63</v>
@@ -2269,7 +2269,7 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>53.01</v>
+        <v>52.89</v>
       </c>
     </row>
     <row r="6">
@@ -2297,7 +2297,7 @@
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>8.48</v>
+        <v>8.49</v>
       </c>
       <c r="I6" t="n">
         <v>3.35</v>
@@ -2309,7 +2309,7 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>52.36</v>
+        <v>52.37</v>
       </c>
     </row>
     <row r="7">
@@ -2331,13 +2331,13 @@
         <v>6.33</v>
       </c>
       <c r="F7" t="n">
-        <v>5.76</v>
+        <v>5.77</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>9.029999999999999</v>
+        <v>9.02</v>
       </c>
       <c r="I7" t="n">
         <v>3.54</v>
@@ -2371,13 +2371,13 @@
         <v>9.029999999999999</v>
       </c>
       <c r="F8" t="n">
-        <v>2.91</v>
+        <v>2.93</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="I8" t="n">
         <v>3.44</v>
@@ -2389,7 +2389,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>50.98</v>
+        <v>50.9</v>
       </c>
     </row>
     <row r="9">
@@ -2411,13 +2411,13 @@
         <v>8.9</v>
       </c>
       <c r="F9" t="n">
-        <v>2.91</v>
+        <v>2.93</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>5.34</v>
+        <v>5.25</v>
       </c>
       <c r="I9" t="n">
         <v>3.75</v>
@@ -2429,7 +2429,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>50.9</v>
+        <v>50.83</v>
       </c>
     </row>
     <row r="10">
@@ -2451,7 +2451,7 @@
         <v>9.699999999999999</v>
       </c>
       <c r="F10" t="n">
-        <v>6.53</v>
+        <v>6.55</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -2469,7 +2469,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>47.66</v>
+        <v>47.68</v>
       </c>
     </row>
     <row r="11">
@@ -2497,7 +2497,7 @@
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>6.17</v>
+        <v>6.12</v>
       </c>
       <c r="I11" t="n">
         <v>3.45</v>
@@ -2509,7 +2509,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>47.61</v>
+        <v>47.56</v>
       </c>
     </row>
     <row r="12">
@@ -2537,7 +2537,7 @@
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>4.47</v>
+        <v>4.48</v>
       </c>
       <c r="I12" t="n">
         <v>3.53</v>
@@ -2549,7 +2549,7 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>46.73</v>
+        <v>46.74</v>
       </c>
     </row>
     <row r="13">
@@ -2577,7 +2577,7 @@
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>5.75</v>
+        <v>5.74</v>
       </c>
       <c r="I13" t="n">
         <v>3.58</v>
@@ -2589,7 +2589,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>45.4</v>
+        <v>45.39</v>
       </c>
     </row>
     <row r="14">
@@ -2611,13 +2611,13 @@
         <v>8.98</v>
       </c>
       <c r="F14" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.82</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>6.59</v>
+        <v>6.5</v>
       </c>
       <c r="I14" t="n">
         <v>3.67</v>
@@ -2629,7 +2629,7 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>45.16</v>
+        <v>45.08</v>
       </c>
     </row>
     <row r="15">
@@ -2657,7 +2657,7 @@
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>3.54</v>
+        <v>3.52</v>
       </c>
       <c r="I15" t="n">
         <v>3.53</v>
@@ -2669,7 +2669,7 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>44.26</v>
+        <v>44.24</v>
       </c>
     </row>
     <row r="16">
@@ -2691,13 +2691,13 @@
         <v>9.880000000000001</v>
       </c>
       <c r="F16" t="n">
-        <v>1.63</v>
+        <v>1.55</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>9.67</v>
+        <v>9.84</v>
       </c>
       <c r="I16" t="n">
         <v>3.73</v>
@@ -2709,7 +2709,7 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>43.73</v>
+        <v>43.82</v>
       </c>
     </row>
     <row r="17">
@@ -2737,7 +2737,7 @@
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>9.119999999999999</v>
+        <v>9.16</v>
       </c>
       <c r="I17" t="n">
         <v>3.56</v>
@@ -2749,7 +2749,7 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>43.18</v>
+        <v>43.22</v>
       </c>
     </row>
     <row r="18">
@@ -2771,13 +2771,13 @@
         <v>7.71</v>
       </c>
       <c r="F18" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.55</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>8.5</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="I18" t="n">
         <v>3.64</v>
@@ -2789,7 +2789,7 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>42.91</v>
+        <v>43.04</v>
       </c>
     </row>
     <row r="19">
@@ -2817,7 +2817,7 @@
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>4.47</v>
+        <v>4.39</v>
       </c>
       <c r="I19" t="n">
         <v>3.47</v>
@@ -2829,38 +2829,38 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>42.62</v>
+        <v>42.54</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ACMR</t>
+          <t>VRT</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>15</v>
+        <v>10.91</v>
       </c>
       <c r="C20" t="n">
-        <v>7.83</v>
+        <v>13.39</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>4.02</v>
+        <v>7.41</v>
       </c>
       <c r="F20" t="n">
-        <v>6.81</v>
+        <v>3.24</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>5.23</v>
+        <v>3.94</v>
       </c>
       <c r="I20" t="n">
-        <v>3.63</v>
+        <v>3.56</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2869,38 +2869,38 @@
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>42.52</v>
+        <v>42.45</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>VRT</t>
+          <t>ACMR</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>10.91</v>
+        <v>15</v>
       </c>
       <c r="C21" t="n">
-        <v>13.39</v>
+        <v>7.83</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>7.41</v>
+        <v>4.02</v>
       </c>
       <c r="F21" t="n">
-        <v>3.29</v>
+        <v>6.85</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>3.83</v>
+        <v>5.1</v>
       </c>
       <c r="I21" t="n">
-        <v>3.56</v>
+        <v>3.63</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2909,38 +2909,38 @@
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>42.39</v>
+        <v>42.43</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ASML</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>9.859999999999999</v>
+        <v>8.51</v>
       </c>
       <c r="C22" t="n">
-        <v>14.28</v>
+        <v>14.63</v>
       </c>
       <c r="D22" t="n">
         <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>8.960000000000001</v>
+        <v>6.87</v>
       </c>
       <c r="F22" t="n">
-        <v>0.57</v>
+        <v>2.88</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>5.95</v>
+        <v>6.01</v>
       </c>
       <c r="I22" t="n">
-        <v>2.76</v>
+        <v>3.45</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2949,38 +2949,38 @@
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>42.38</v>
+        <v>42.35</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>ASML</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>8.51</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="C23" t="n">
-        <v>14.63</v>
+        <v>14.28</v>
       </c>
       <c r="D23" t="n">
         <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>6.87</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="F23" t="n">
-        <v>2.91</v>
+        <v>0.57</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>5.88</v>
+        <v>5.89</v>
       </c>
       <c r="I23" t="n">
-        <v>3.45</v>
+        <v>2.76</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2989,7 +2989,7 @@
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>42.25</v>
+        <v>42.32</v>
       </c>
     </row>
     <row r="24">
@@ -3011,13 +3011,13 @@
         <v>7.97</v>
       </c>
       <c r="F24" t="n">
-        <v>0.53</v>
+        <v>0.52</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>9.050000000000001</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="I24" t="n">
         <v>3.57</v>
@@ -3029,7 +3029,7 @@
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>42.16</v>
+        <v>42.24</v>
       </c>
     </row>
     <row r="25">
@@ -3057,7 +3057,7 @@
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>3.86</v>
+        <v>3.89</v>
       </c>
       <c r="I25" t="n">
         <v>3.54</v>
@@ -3069,7 +3069,7 @@
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>41.72</v>
+        <v>41.75</v>
       </c>
     </row>
     <row r="26">
@@ -3091,13 +3091,13 @@
         <v>9.24</v>
       </c>
       <c r="F26" t="n">
-        <v>0.29</v>
+        <v>0.28</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>8.859999999999999</v>
+        <v>9.07</v>
       </c>
       <c r="I26" t="n">
         <v>3.48</v>
@@ -3109,7 +3109,7 @@
         <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>40.84</v>
+        <v>41.04</v>
       </c>
     </row>
     <row r="27">
@@ -3137,7 +3137,7 @@
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>5.8</v>
+        <v>5.79</v>
       </c>
       <c r="I27" t="n">
         <v>3.7</v>
@@ -3149,7 +3149,7 @@
         <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>40.72</v>
+        <v>40.71</v>
       </c>
     </row>
     <row r="28">
@@ -3177,7 +3177,7 @@
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>9.02</v>
+        <v>9.06</v>
       </c>
       <c r="I28" t="n">
         <v>3.53</v>
@@ -3189,7 +3189,7 @@
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>39.85</v>
+        <v>39.89</v>
       </c>
     </row>
     <row r="29">
@@ -3211,13 +3211,13 @@
         <v>7.23</v>
       </c>
       <c r="F29" t="n">
-        <v>5.62</v>
+        <v>5.65</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>0.91</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="I29" t="n">
         <v>3.49</v>
@@ -3229,7 +3229,7 @@
         <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>39.63</v>
+        <v>39.56</v>
       </c>
     </row>
     <row r="30">
@@ -3251,13 +3251,13 @@
         <v>6.78</v>
       </c>
       <c r="F30" t="n">
-        <v>3.73</v>
+        <v>3.67</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>5.59</v>
+        <v>5.79</v>
       </c>
       <c r="I30" t="n">
         <v>3.57</v>
@@ -3269,7 +3269,7 @@
         <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>36.23</v>
+        <v>36.37</v>
       </c>
     </row>
     <row r="31">
@@ -3291,13 +3291,13 @@
         <v>0.8</v>
       </c>
       <c r="F31" t="n">
-        <v>6.45</v>
+        <v>6.38</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>2.45</v>
+        <v>2.57</v>
       </c>
       <c r="I31" t="n">
         <v>3.58</v>
@@ -3309,7 +3309,7 @@
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>31.42</v>
+        <v>31.47</v>
       </c>
     </row>
   </sheetData>
@@ -3343,12 +3343,12 @@
     <col width="15" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="18" customWidth="1" min="16" max="16"/>
-    <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="11" customWidth="1" min="17" max="17"/>
     <col width="16" customWidth="1" min="18" max="18"/>
     <col width="19" customWidth="1" min="19" max="19"/>
-    <col width="24" customWidth="1" min="20" max="20"/>
-    <col width="23" customWidth="1" min="21" max="21"/>
-    <col width="22" customWidth="1" min="22" max="22"/>
+    <col width="23" customWidth="1" min="20" max="20"/>
+    <col width="22" customWidth="1" min="21" max="21"/>
+    <col width="21" customWidth="1" min="22" max="22"/>
     <col width="23" customWidth="1" min="23" max="23"/>
     <col width="18" customWidth="1" min="24" max="24"/>
     <col width="24" customWidth="1" min="25" max="25"/>
@@ -3533,7 +3533,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>915.5549926757812</v>
+        <v>912.260009765625</v>
       </c>
       <c r="G2" t="n">
         <v>90273996800</v>
@@ -3563,19 +3563,19 @@
         <v>0.80370003</v>
       </c>
       <c r="Q2" t="n">
-        <v>20.711765</v>
+        <v>20.639366</v>
       </c>
       <c r="T2" t="n">
-        <v>0.1158092452269353</v>
+        <v>0.1117935690267848</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.008472151302580389</v>
+        <v>-0.01204055226433332</v>
       </c>
       <c r="V2" t="n">
-        <v>1.135385775685353</v>
+        <v>1.127700754366305</v>
       </c>
       <c r="W2" t="n">
-        <v>6.787893773221825</v>
+        <v>6.759865486377861</v>
       </c>
       <c r="X2" t="n">
         <v>0.00238</v>
@@ -3585,7 +3585,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>2026-08-27T16:09:03.515813+00:00</t>
+          <t>2026-08-27T18:37:24.150743+00:00</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
@@ -3616,10 +3616,10 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2207285510144</v>
+        <v>2204770238464</v>
       </c>
       <c r="F3" t="n">
-        <v>425.5849914550781</v>
+        <v>425.1000061035156</v>
       </c>
       <c r="G3" t="n">
         <v>4440492343296</v>
@@ -3649,25 +3649,25 @@
         <v>0.60344005</v>
       </c>
       <c r="Q3" t="n">
-        <v>31.736391</v>
+        <v>31.700224</v>
       </c>
       <c r="R3" t="n">
-        <v>0.49708125</v>
+        <v>0.49651483</v>
       </c>
       <c r="S3" t="n">
-        <v>3.020261273799446</v>
+        <v>3.016819590513221</v>
       </c>
       <c r="T3" t="n">
-        <v>0.08481811349075952</v>
+        <v>0.08358188358435736</v>
       </c>
       <c r="U3" t="n">
-        <v>0.004052332427479266</v>
+        <v>0.002908141059817071</v>
       </c>
       <c r="V3" t="n">
-        <v>0.1033030017161616</v>
+        <v>0.1020457069221468</v>
       </c>
       <c r="W3" t="n">
-        <v>0.7982018843793695</v>
+        <v>0.7961527012770839</v>
       </c>
       <c r="X3" t="n">
         <v>0.00013</v>
@@ -3677,7 +3677,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>2026-08-27T16:09:07.900545+00:00</t>
+          <t>2026-08-27T18:37:28.298591+00:00</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
@@ -3708,10 +3708,10 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>44673953792</v>
+        <v>44096991232</v>
       </c>
       <c r="F4" t="n">
-        <v>237.7100067138672</v>
+        <v>234.6399993896484</v>
       </c>
       <c r="G4" t="n">
         <v>1335116032</v>
@@ -3741,25 +3741,25 @@
         <v>0.35661998</v>
       </c>
       <c r="Q4" t="n">
-        <v>94.705185</v>
+        <v>93.48206999999999</v>
       </c>
       <c r="R4" t="n">
-        <v>33.460728</v>
+        <v>33.028584</v>
       </c>
       <c r="S4" t="n">
-        <v>178.1186196436214</v>
+        <v>175.8182238637508</v>
       </c>
       <c r="T4" t="n">
-        <v>0.2362700656489802</v>
+        <v>0.2203037283091169</v>
       </c>
       <c r="U4" t="n">
-        <v>0.06908027968841468</v>
+        <v>0.0552731861874165</v>
       </c>
       <c r="V4" t="n">
-        <v>0.9254010082344439</v>
+        <v>0.9005345952506061</v>
       </c>
       <c r="W4" t="n">
-        <v>0.9368532568400507</v>
+        <v>0.9118389389043597</v>
       </c>
       <c r="X4" t="n">
         <v>0.09436</v>
@@ -3769,7 +3769,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>2026-08-27T16:09:04.268933+00:00</t>
+          <t>2026-08-27T18:37:24.949586+00:00</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
@@ -3800,10 +3800,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>254735237120</v>
+        <v>251885486080</v>
       </c>
       <c r="F5" t="n">
-        <v>201.9745025634766</v>
+        <v>199.7149963378906</v>
       </c>
       <c r="G5" t="n">
         <v>10540800000</v>
@@ -3833,25 +3833,25 @@
         <v>0.45393002</v>
       </c>
       <c r="Q5" t="n">
-        <v>63.91598</v>
+        <v>63.200947</v>
       </c>
       <c r="R5" t="n">
-        <v>24.166594</v>
+        <v>23.89624</v>
       </c>
       <c r="S5" t="n">
-        <v>65.45918383792986</v>
+        <v>64.72688476800647</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1901154591550258</v>
+        <v>0.1768015346002088</v>
       </c>
       <c r="U5" t="n">
-        <v>0.3007953693944687</v>
+        <v>0.2862432591129422</v>
       </c>
       <c r="V5" t="n">
-        <v>0.5198623183921056</v>
+        <v>0.5028594872086933</v>
       </c>
       <c r="W5" t="n">
-        <v>0.5155285967467536</v>
+        <v>0.4985742472821393</v>
       </c>
       <c r="X5" t="n">
         <v>0.17247999</v>
@@ -3861,7 +3861,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>2026-08-27T16:09:09.536052+00:00</t>
+          <t>2026-08-27T18:37:29.986370+00:00</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
@@ -3892,10 +3892,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>446440177664</v>
+        <v>446728536064</v>
       </c>
       <c r="F6" t="n">
-        <v>185.7799987792969</v>
+        <v>185.8999938964844</v>
       </c>
       <c r="G6" t="n">
         <v>6155940864</v>
@@ -3925,25 +3925,25 @@
         <v>0.47120997</v>
       </c>
       <c r="Q6" t="n">
-        <v>158.78633</v>
+        <v>158.88889</v>
       </c>
       <c r="R6" t="n">
-        <v>72.52184</v>
+        <v>72.56869</v>
       </c>
       <c r="S6" t="n">
-        <v>206.7709900946194</v>
+        <v>206.9045447226596</v>
       </c>
       <c r="T6" t="n">
-        <v>0.50392617675985</v>
+        <v>0.5048975611877078</v>
       </c>
       <c r="U6" t="n">
-        <v>0.296079276724438</v>
+        <v>0.2969164130454454</v>
       </c>
       <c r="V6" t="n">
-        <v>0.384454843127507</v>
+        <v>0.3853490611393138</v>
       </c>
       <c r="W6" t="n">
-        <v>0.1854262208540287</v>
+        <v>0.1861918864758565</v>
       </c>
       <c r="X6" t="n">
         <v>0.03477</v>
@@ -3953,7 +3953,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>2026-08-27T16:09:01.980456+00:00</t>
+          <t>2026-08-27T18:37:22.422361+00:00</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr">
@@ -3984,10 +3984,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>300672679936</v>
+        <v>299842306048</v>
       </c>
       <c r="F7" t="n">
-        <v>465.3349914550781</v>
+        <v>464.0498962402344</v>
       </c>
       <c r="G7" t="n">
         <v>134001999872</v>
@@ -4017,25 +4017,25 @@
         <v>0.08857000600000001</v>
       </c>
       <c r="Q7" t="n">
-        <v>37.01949</v>
+        <v>36.917255</v>
       </c>
       <c r="R7" t="n">
-        <v>2.2437925</v>
+        <v>2.2375958</v>
       </c>
       <c r="S7" t="n">
-        <v>55.33047013127118</v>
+        <v>55.1776628405737</v>
       </c>
       <c r="T7" t="n">
-        <v>0.1867762923018885</v>
+        <v>0.1834988243221902</v>
       </c>
       <c r="U7" t="n">
-        <v>0.4701275699711385</v>
+        <v>0.4660675832087586</v>
       </c>
       <c r="V7" t="n">
-        <v>2.786411777483422</v>
+        <v>2.775955010324226</v>
       </c>
       <c r="W7" t="n">
-        <v>2.556715228303137</v>
+        <v>2.546892804018727</v>
       </c>
       <c r="X7" t="n">
         <v>0.07491</v>
@@ -4045,7 +4045,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>2026-08-27T16:09:09.848736+00:00</t>
+          <t>2026-08-27T18:37:30.446342+00:00</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr">
@@ -4076,10 +4076,10 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5503689162752</v>
+        <v>5477336875008</v>
       </c>
       <c r="F8" t="n">
-        <v>227.2279968261719</v>
+        <v>226.1300048828125</v>
       </c>
       <c r="G8" t="n">
         <v>253491003392</v>
@@ -4109,25 +4109,25 @@
         <v>0.65596</v>
       </c>
       <c r="Q8" t="n">
-        <v>34.85092</v>
+        <v>34.684048</v>
       </c>
       <c r="R8" t="n">
-        <v>21.711765</v>
+        <v>21.607618</v>
       </c>
       <c r="S8" t="n">
-        <v>118.7781475467469</v>
+        <v>118.2094243086987</v>
       </c>
       <c r="T8" t="n">
-        <v>0.1533830930505784</v>
+        <v>0.1478098126385468</v>
       </c>
       <c r="U8" t="n">
-        <v>0.06181019230157681</v>
+        <v>0.05667940272983274</v>
       </c>
       <c r="V8" t="n">
-        <v>0.1633521754085567</v>
+        <v>0.1577307232383589</v>
       </c>
       <c r="W8" t="n">
-        <v>0.2529219617705865</v>
+        <v>0.2468676980403361</v>
       </c>
       <c r="X8" t="n">
         <v>0.03991</v>
@@ -4137,7 +4137,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>2026-08-27T16:09:01.636136+00:00</t>
+          <t>2026-08-27T18:37:22.042775+00:00</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr">
@@ -4168,10 +4168,10 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>57397379072</v>
+        <v>57010438144</v>
       </c>
       <c r="F9" t="n">
-        <v>367.1300048828125</v>
+        <v>364.6549987792969</v>
       </c>
       <c r="G9" t="n">
         <v>4464031232</v>
@@ -4201,25 +4201,25 @@
         <v>0.33161</v>
       </c>
       <c r="Q9" t="n">
-        <v>50.56887</v>
+        <v>50.22796</v>
       </c>
       <c r="R9" t="n">
-        <v>12.857746</v>
+        <v>12.771066</v>
       </c>
       <c r="S9" t="n">
-        <v>131.2296293781667</v>
+        <v>130.3449528407766</v>
       </c>
       <c r="T9" t="n">
-        <v>0.1449555960426223</v>
+        <v>0.1372368804629345</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.04055922974317461</v>
+        <v>-0.04702729754140689</v>
       </c>
       <c r="V9" t="n">
-        <v>0.07131629484869251</v>
+        <v>0.06409401845264417</v>
       </c>
       <c r="W9" t="n">
-        <v>2.146164955394781</v>
+        <v>2.124955091412798</v>
       </c>
       <c r="X9" t="n">
         <v>0.00202</v>
@@ -4229,7 +4229,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>2026-08-27T16:09:04.676179+00:00</t>
+          <t>2026-08-27T18:37:25.314125+00:00</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr">
@@ -4260,10 +4260,10 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>9432379392</v>
+        <v>9401291776</v>
       </c>
       <c r="F10" t="n">
-        <v>18.20499992370605</v>
+        <v>18.14500045776367</v>
       </c>
       <c r="G10" t="n">
         <v>1672329984</v>
@@ -4290,25 +4290,25 @@
         <v>0.07274</v>
       </c>
       <c r="Q10" t="n">
-        <v>30.341665</v>
+        <v>30.241667</v>
       </c>
       <c r="R10" t="n">
-        <v>5.640262</v>
+        <v>5.6216726</v>
       </c>
       <c r="S10" t="n">
-        <v>18.43869108136838</v>
+        <v>18.37792010046759</v>
       </c>
       <c r="T10" t="n">
-        <v>0.4934372887922298</v>
+        <v>0.4885152651656715</v>
       </c>
       <c r="U10" t="n">
-        <v>0.5721070849437224</v>
+        <v>0.566925783878292</v>
       </c>
       <c r="V10" t="n">
-        <v>0.8314890032423969</v>
+        <v>0.8254528394118881</v>
       </c>
       <c r="W10" t="n">
-        <v>0.6342010199863251</v>
+        <v>0.6288150716835186</v>
       </c>
       <c r="X10" t="n">
         <v>0.09236999999999999</v>
@@ -4318,7 +4318,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>2026-08-27T16:09:12.690213+00:00</t>
+          <t>2026-08-27T18:37:34.330376+00:00</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr">
@@ -4349,10 +4349,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>773393219584</v>
+        <v>769336475648</v>
       </c>
       <c r="F11" t="n">
-        <v>473.7550048828125</v>
+        <v>471.2699890136719</v>
       </c>
       <c r="G11" t="n">
         <v>41305001984</v>
@@ -4382,25 +4382,25 @@
         <v>0.1725</v>
       </c>
       <c r="Q11" t="n">
-        <v>120.242386</v>
+        <v>119.61167</v>
       </c>
       <c r="R11" t="n">
-        <v>18.72396</v>
+        <v>18.625746</v>
       </c>
       <c r="S11" t="n">
-        <v>87.47308153305714</v>
+        <v>87.01425168546248</v>
       </c>
       <c r="T11" t="n">
-        <v>0.04209011915697314</v>
+        <v>0.03662398063286343</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.08557397300570768</v>
+        <v>-0.09037046732200127</v>
       </c>
       <c r="V11" t="n">
-        <v>1.246775128101536</v>
+        <v>1.234989982213517</v>
       </c>
       <c r="W11" t="n">
-        <v>1.834649620306049</v>
+        <v>1.819780860678577</v>
       </c>
       <c r="X11" t="n">
         <v>0.00425</v>
@@ -4410,7 +4410,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>2026-08-27T16:09:02.306122+00:00</t>
+          <t>2026-08-27T18:37:22.840566+00:00</t>
         </is>
       </c>
       <c r="AD11" t="inlineStr">
@@ -4441,10 +4441,10 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4165332369408</v>
+        <v>4168084094976</v>
       </c>
       <c r="F12" t="n">
-        <v>340.5849914550781</v>
+        <v>340.8099975585938</v>
       </c>
       <c r="G12" t="n">
         <v>445865984000</v>
@@ -4474,25 +4474,25 @@
         <v>0.34033</v>
       </c>
       <c r="Q12" t="n">
-        <v>17.08049</v>
+        <v>17.091774</v>
       </c>
       <c r="R12" t="n">
-        <v>9.34198</v>
+        <v>9.3482895</v>
       </c>
       <c r="S12" t="n">
-        <v>183.7781686733271</v>
+        <v>183.8995772526982</v>
       </c>
       <c r="T12" t="n">
-        <v>0.02060172058386045</v>
+        <v>0.02127597700193928</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.126474730374544</v>
+        <v>-0.1258976394217068</v>
       </c>
       <c r="V12" t="n">
-        <v>0.08989549481487824</v>
+        <v>0.09061563639367964</v>
       </c>
       <c r="W12" t="n">
-        <v>0.6462146267544695</v>
+        <v>0.6473021918204871</v>
       </c>
       <c r="X12" t="n">
         <v>0.01596</v>
@@ -4502,7 +4502,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>2026-08-27T16:09:06.196637+00:00</t>
+          <t>2026-08-27T18:37:26.820357+00:00</t>
         </is>
       </c>
       <c r="AD12" t="inlineStr">
@@ -4533,10 +4533,10 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>377490505728</v>
+        <v>377061965824</v>
       </c>
       <c r="F13" t="n">
-        <v>475.6700134277344</v>
+        <v>475.2000122070312</v>
       </c>
       <c r="G13" t="n">
         <v>30837000192</v>
@@ -4566,25 +4566,25 @@
         <v>0.33736</v>
       </c>
       <c r="Q13" t="n">
-        <v>40.97072</v>
+        <v>40.924206</v>
       </c>
       <c r="R13" t="n">
-        <v>12.24148</v>
+        <v>12.227583</v>
       </c>
       <c r="S13" t="n">
-        <v>122.74616687799</v>
+        <v>122.6068213056589</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.0005904732788559741</v>
+        <v>-0.001577972352334256</v>
       </c>
       <c r="U13" t="n">
-        <v>0.05892784570865572</v>
+        <v>0.05788153762517356</v>
       </c>
       <c r="V13" t="n">
-        <v>0.2071670464471154</v>
+        <v>0.2059742658021169</v>
       </c>
       <c r="W13" t="n">
-        <v>1.909550333286604</v>
+        <v>1.906675457490908</v>
       </c>
       <c r="X13" t="n">
         <v>0.00331</v>
@@ -4594,7 +4594,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>2026-08-27T16:09:03.120421+00:00</t>
+          <t>2026-08-27T18:37:23.696963+00:00</t>
         </is>
       </c>
       <c r="AD13" t="inlineStr">
@@ -4625,10 +4625,10 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>87364739072</v>
+        <v>86483214336</v>
       </c>
       <c r="F14" t="n">
-        <v>243.3049926757812</v>
+        <v>240.8500061035156</v>
       </c>
       <c r="G14" t="n">
         <v>3966725120</v>
@@ -4658,25 +4658,25 @@
         <v>0.00666</v>
       </c>
       <c r="Q14" t="n">
-        <v>486.61</v>
+        <v>481.7</v>
       </c>
       <c r="R14" t="n">
-        <v>22.024399</v>
+        <v>21.80217</v>
       </c>
       <c r="S14" t="n">
-        <v>83.09274558722323</v>
+        <v>82.25432597542853</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.03019376618144431</v>
+        <v>-0.03997926731539225</v>
       </c>
       <c r="U14" t="n">
-        <v>0.08020327979953557</v>
+        <v>0.06930385468679678</v>
       </c>
       <c r="V14" t="n">
-        <v>1.205247789702275</v>
+        <v>1.182996484241182</v>
       </c>
       <c r="W14" t="n">
-        <v>0.8469976510058952</v>
+        <v>0.8283611471579535</v>
       </c>
       <c r="X14" t="n">
         <v>0.00619</v>
@@ -4686,7 +4686,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>2026-08-27T16:09:11.290104+00:00</t>
+          <t>2026-08-27T18:37:32.345733+00:00</t>
         </is>
       </c>
       <c r="AD14" t="inlineStr">
@@ -4717,10 +4717,10 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1751431905280</v>
+        <v>1750313730048</v>
       </c>
       <c r="F15" t="n">
-        <v>368.135009765625</v>
+        <v>367.8999938964844</v>
       </c>
       <c r="G15" t="n">
         <v>75464998912</v>
@@ -4750,25 +4750,25 @@
         <v>0.48988</v>
       </c>
       <c r="Q15" t="n">
-        <v>61.253742</v>
+        <v>61.214638</v>
       </c>
       <c r="R15" t="n">
-        <v>23.208532</v>
+        <v>23.193716</v>
       </c>
       <c r="S15" t="n">
-        <v>64.36189451361236</v>
+        <v>64.32080363470764</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.03353808976835526</v>
+        <v>-0.03415507505853188</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.1356424097445666</v>
+        <v>-0.1361942120587543</v>
       </c>
       <c r="V15" t="n">
-        <v>0.1118868182438673</v>
+        <v>0.1111769942932956</v>
       </c>
       <c r="W15" t="n">
-        <v>0.2350786749049967</v>
+        <v>0.2342902057821479</v>
       </c>
       <c r="X15" t="n">
         <v>0.01948</v>
@@ -4778,7 +4778,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>2026-08-27T16:09:02.697030+00:00</t>
+          <t>2026-08-27T18:37:23.247722+00:00</t>
         </is>
       </c>
       <c r="AD15" t="inlineStr">
@@ -4809,10 +4809,10 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>35117383680</v>
+        <v>35729874944</v>
       </c>
       <c r="F16" t="n">
-        <v>436.6099853515625</v>
+        <v>444.2250061035156</v>
       </c>
       <c r="G16" t="n">
         <v>2602398976</v>
@@ -4839,22 +4839,22 @@
         <v>-0.03607</v>
       </c>
       <c r="R16" t="n">
-        <v>13.494235</v>
+        <v>13.729591</v>
       </c>
       <c r="S16" t="n">
-        <v>67.84586348654926</v>
+        <v>69.02918053154069</v>
       </c>
       <c r="T16" t="n">
-        <v>0.4056081134984333</v>
+        <v>0.43012366585069</v>
       </c>
       <c r="U16" t="n">
-        <v>0.3406104003024022</v>
+        <v>0.3639923117590693</v>
       </c>
       <c r="V16" t="n">
-        <v>0.3861074919450411</v>
+        <v>0.4102829292225463</v>
       </c>
       <c r="W16" t="n">
-        <v>0.4765301566706552</v>
+        <v>0.5022826775958877</v>
       </c>
       <c r="X16" t="n">
         <v>0.02641</v>
@@ -4864,7 +4864,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>2026-08-27T16:09:12.265824+00:00</t>
+          <t>2026-08-27T18:37:33.888521+00:00</t>
         </is>
       </c>
       <c r="AD16" t="inlineStr">
@@ -4895,10 +4895,10 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>114632744960</v>
+        <v>115015745536</v>
       </c>
       <c r="F17" t="n">
-        <v>330.7349853515625</v>
+        <v>331.8399963378906</v>
       </c>
       <c r="G17" t="n">
         <v>5032822784</v>
@@ -4925,22 +4925,22 @@
         <v>-0.22173999</v>
       </c>
       <c r="R17" t="n">
-        <v>22.777027</v>
+        <v>22.853128</v>
       </c>
       <c r="S17" t="n">
-        <v>65.89991071261693</v>
+        <v>66.120089543457</v>
       </c>
       <c r="T17" t="n">
-        <v>0.2233133720638851</v>
+        <v>0.2274005559897578</v>
       </c>
       <c r="U17" t="n">
-        <v>0.3826713610833639</v>
+        <v>0.3872909722891584</v>
       </c>
       <c r="V17" t="n">
-        <v>0.954582898343789</v>
+        <v>0.9611133099180682</v>
       </c>
       <c r="W17" t="n">
-        <v>0.6504565415386059</v>
+        <v>0.6559708435980589</v>
       </c>
       <c r="X17" t="n">
         <v>0.02962</v>
@@ -4950,7 +4950,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>2026-08-27T16:09:10.938406+00:00</t>
+          <t>2026-08-27T18:37:31.829046+00:00</t>
         </is>
       </c>
       <c r="AD17" t="inlineStr">
@@ -4981,10 +4981,10 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>107635777536</v>
+        <v>109004898304</v>
       </c>
       <c r="F18" t="n">
-        <v>302.2799987792969</v>
+        <v>306.125</v>
       </c>
       <c r="G18" t="n">
         <v>2512349952</v>
@@ -5011,22 +5011,22 @@
         <v>-0.07902000000000001</v>
       </c>
       <c r="R18" t="n">
-        <v>42.84267</v>
+        <v>43.387627</v>
       </c>
       <c r="S18" t="n">
-        <v>155.3517670545175</v>
+        <v>157.3278324064744</v>
       </c>
       <c r="T18" t="n">
-        <v>0.1445664210277087</v>
+        <v>0.1591253045257879</v>
       </c>
       <c r="U18" t="n">
-        <v>0.3251501379619017</v>
+        <v>0.3420060461220662</v>
       </c>
       <c r="V18" t="n">
-        <v>0.7594877381243681</v>
+        <v>0.7818684200359087</v>
       </c>
       <c r="W18" t="n">
-        <v>0.4728122719201784</v>
+        <v>0.4915464422465927</v>
       </c>
       <c r="X18" t="n">
         <v>0.00616</v>
@@ -5036,7 +5036,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>2026-08-27T16:09:11.639252+00:00</t>
+          <t>2026-08-27T18:37:33.081801+00:00</t>
         </is>
       </c>
       <c r="AD18" t="inlineStr">
@@ -5067,10 +5067,10 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2765610549248</v>
+        <v>2754499837952</v>
       </c>
       <c r="F19" t="n">
-        <v>256.3999938964844</v>
+        <v>255.3699035644531</v>
       </c>
       <c r="G19" t="n">
         <v>775680032768</v>
@@ -5100,25 +5100,25 @@
         <v>0.13689</v>
       </c>
       <c r="Q19" t="n">
-        <v>20.610933</v>
+        <v>20.528128</v>
       </c>
       <c r="R19" t="n">
-        <v>3.5654013</v>
+        <v>3.5510774</v>
       </c>
       <c r="S19" t="n">
-        <v>859.1187220505416</v>
+        <v>855.6672526842972</v>
       </c>
       <c r="T19" t="n">
-        <v>0.1106297895634141</v>
+        <v>0.1061678198445026</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.06423359891794023</v>
+        <v>-0.06799305268447764</v>
       </c>
       <c r="V19" t="n">
-        <v>0.2172426634990046</v>
+        <v>0.2123523751633796</v>
       </c>
       <c r="W19" t="n">
-        <v>0.1190642430196633</v>
+        <v>0.1145683877735753</v>
       </c>
       <c r="X19" t="n">
         <v>0.0887</v>
@@ -5128,7 +5128,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>2026-08-27T16:09:06.883781+00:00</t>
+          <t>2026-08-27T18:37:27.157206+00:00</t>
         </is>
       </c>
       <c r="AD19" t="inlineStr">
@@ -5140,84 +5140,87 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ACMR</t>
+          <t>VRT</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>ACM Research, Inc.</t>
+          <t>Vertiv Holdings Co</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Semiconductor Equipment &amp; Materials</t>
+          <t>Electrical Equipment &amp; Parts</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5588303360</v>
+        <v>103082508288</v>
       </c>
       <c r="F20" t="n">
-        <v>80.23500061035156</v>
+        <v>267.7550048828125</v>
       </c>
       <c r="G20" t="n">
-        <v>1037772032</v>
+        <v>11479600128</v>
       </c>
       <c r="H20" t="n">
-        <v>0.36</v>
+        <v>0.241</v>
       </c>
       <c r="I20" t="n">
-        <v>2.12</v>
+        <v>4.43</v>
       </c>
       <c r="J20" t="n">
-        <v>1.806</v>
+        <v>0.53</v>
       </c>
       <c r="K20" t="n">
-        <v>-186610256</v>
+        <v>2696537600</v>
       </c>
       <c r="M20" t="n">
-        <v>1439374976</v>
+        <v>3110599936</v>
       </c>
       <c r="N20" t="n">
-        <v>349319008</v>
+        <v>3338200064</v>
       </c>
       <c r="O20" t="n">
-        <v>0.43835</v>
+        <v>0.38039002</v>
       </c>
       <c r="P20" t="n">
-        <v>0.16982001</v>
+        <v>0.20362</v>
       </c>
       <c r="Q20" t="n">
-        <v>37.8467</v>
+        <v>60.44131</v>
       </c>
       <c r="R20" t="n">
-        <v>5.3849044</v>
+        <v>8.979626</v>
+      </c>
+      <c r="S20" t="n">
+        <v>38.22772888017582</v>
       </c>
       <c r="T20" t="n">
-        <v>0.1140655977533434</v>
+        <v>-0.00669607023345109</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1359573542646804</v>
+        <v>-0.1475882228812304</v>
       </c>
       <c r="V20" t="n">
-        <v>0.1718270655746839</v>
+        <v>0.02168065134762154</v>
       </c>
       <c r="W20" t="n">
-        <v>1.807382814014621</v>
+        <v>1.072925239821928</v>
       </c>
       <c r="X20" t="n">
-        <v>0.12675999</v>
+        <v>0.00269</v>
       </c>
       <c r="Y20" t="n">
-        <v>0.78055</v>
+        <v>0.84448</v>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>2026-08-27T16:09:03.937893+00:00</t>
+          <t>2026-08-27T18:37:30.859676+00:00</t>
         </is>
       </c>
       <c r="AD20" t="inlineStr">
@@ -5229,87 +5232,84 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>VRT</t>
+          <t>ACMR</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Vertiv Holdings Co</t>
+          <t>ACM Research, Inc.</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Electrical Equipment &amp; Parts</t>
+          <t>Semiconductor Equipment &amp; Materials</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>101964120064</v>
+        <v>5539201024</v>
       </c>
       <c r="F21" t="n">
-        <v>264.8500061035156</v>
+        <v>79.52999877929688</v>
       </c>
       <c r="G21" t="n">
-        <v>11479600128</v>
+        <v>1037772032</v>
       </c>
       <c r="H21" t="n">
-        <v>0.241</v>
+        <v>0.36</v>
       </c>
       <c r="I21" t="n">
-        <v>4.56</v>
+        <v>2.12</v>
       </c>
       <c r="J21" t="n">
-        <v>0.53</v>
+        <v>1.806</v>
       </c>
       <c r="K21" t="n">
-        <v>2696537600</v>
+        <v>-186610256</v>
       </c>
       <c r="M21" t="n">
-        <v>3110599936</v>
+        <v>1439374976</v>
       </c>
       <c r="N21" t="n">
-        <v>3338200064</v>
+        <v>349319008</v>
       </c>
       <c r="O21" t="n">
-        <v>0.38039002</v>
+        <v>0.43835</v>
       </c>
       <c r="P21" t="n">
-        <v>0.20362</v>
+        <v>0.16982001</v>
       </c>
       <c r="Q21" t="n">
-        <v>58.081142</v>
+        <v>37.514153</v>
       </c>
       <c r="R21" t="n">
-        <v>8.882201</v>
-      </c>
-      <c r="S21" t="n">
-        <v>37.81297915667855</v>
+        <v>5.3375893</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.01747288728942176</v>
+        <v>0.1042766243582363</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1568364353397504</v>
+        <v>-0.1435494480232506</v>
       </c>
       <c r="V21" t="n">
-        <v>0.01059596202017077</v>
+        <v>0.1615305588055045</v>
       </c>
       <c r="W21" t="n">
-        <v>1.050434866019872</v>
+        <v>1.782715150160993</v>
       </c>
       <c r="X21" t="n">
-        <v>0.00269</v>
+        <v>0.12675999</v>
       </c>
       <c r="Y21" t="n">
-        <v>0.84448</v>
+        <v>0.78055</v>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>2026-08-27T16:09:10.180635+00:00</t>
+          <t>2026-08-27T18:37:24.493957+00:00</t>
         </is>
       </c>
       <c r="AD21" t="inlineStr">
@@ -5321,12 +5321,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ASML</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>ASML Holding N.V.</t>
+          <t>Microsoft Corporation</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -5336,72 +5336,72 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Semiconductor Equipment &amp; Materials</t>
+          <t>Software - Infrastructure</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>664589041664</v>
+        <v>3734826647552</v>
       </c>
       <c r="F22" t="n">
-        <v>1730.25</v>
+        <v>502.9700012207031</v>
       </c>
       <c r="G22" t="n">
-        <v>35327500288</v>
+        <v>331839012864</v>
       </c>
       <c r="H22" t="n">
-        <v>0.213</v>
+        <v>0.177</v>
       </c>
       <c r="I22" t="n">
-        <v>29.68</v>
+        <v>17.97</v>
       </c>
       <c r="J22" t="n">
-        <v>0.285</v>
+        <v>0.317</v>
       </c>
       <c r="K22" t="n">
-        <v>8437675008</v>
+        <v>16545500160</v>
       </c>
       <c r="M22" t="n">
-        <v>7581499904</v>
+        <v>76842999808</v>
       </c>
       <c r="N22" t="n">
-        <v>1984400000</v>
+        <v>128812998656</v>
       </c>
       <c r="O22" t="n">
-        <v>0.5273300400000001</v>
+        <v>0.67944</v>
       </c>
       <c r="P22" t="n">
-        <v>0.37057</v>
+        <v>0.45111</v>
       </c>
       <c r="Q22" t="n">
-        <v>58.296833</v>
+        <v>27.989428</v>
       </c>
       <c r="R22" t="n">
-        <v>18.81223</v>
+        <v>11.254935</v>
       </c>
       <c r="S22" t="n">
-        <v>78.76447493342469</v>
+        <v>225.7306585739382</v>
       </c>
       <c r="T22" t="n">
-        <v>0.09305414155329239</v>
+        <v>0.2810902603436249</v>
       </c>
       <c r="U22" t="n">
-        <v>0.07891401065821091</v>
+        <v>0.1801608098003926</v>
       </c>
       <c r="V22" t="n">
-        <v>0.1374126640944859</v>
+        <v>0.2606297641273871</v>
       </c>
       <c r="W22" t="n">
-        <v>1.261878397495278</v>
+        <v>0.0007268045960038272</v>
       </c>
       <c r="X22" t="n">
-        <v>0.00016000001</v>
+        <v>0.00090000004</v>
       </c>
       <c r="Y22" t="n">
-        <v>0.20384</v>
+        <v>0.75881</v>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>2026-08-27T16:09:08.380197+00:00</t>
+          <t>2026-08-27T18:37:26.445383+00:00</t>
         </is>
       </c>
       <c r="AD22" t="inlineStr">
@@ -5413,12 +5413,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>ASML</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Microsoft Corporation</t>
+          <t>ASML Holding N.V.</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -5428,72 +5428,72 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Software - Infrastructure</t>
+          <t>Semiconductor Equipment &amp; Materials</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>3711547473920</v>
+        <v>662036676608</v>
       </c>
       <c r="F23" t="n">
-        <v>499.8349914550781</v>
+        <v>1723.60498046875</v>
       </c>
       <c r="G23" t="n">
-        <v>331839012864</v>
+        <v>35327500288</v>
       </c>
       <c r="H23" t="n">
-        <v>0.177</v>
+        <v>0.213</v>
       </c>
       <c r="I23" t="n">
-        <v>17.97</v>
+        <v>29.68</v>
       </c>
       <c r="J23" t="n">
-        <v>0.317</v>
+        <v>0.285</v>
       </c>
       <c r="K23" t="n">
-        <v>16545500160</v>
+        <v>8437675008</v>
       </c>
       <c r="M23" t="n">
-        <v>76842999808</v>
+        <v>7581499904</v>
       </c>
       <c r="N23" t="n">
-        <v>128812998656</v>
+        <v>1984400000</v>
       </c>
       <c r="O23" t="n">
-        <v>0.67944</v>
+        <v>0.5273300400000001</v>
       </c>
       <c r="P23" t="n">
-        <v>0.45111</v>
+        <v>0.37057</v>
       </c>
       <c r="Q23" t="n">
-        <v>27.81497</v>
+        <v>58.072945</v>
       </c>
       <c r="R23" t="n">
-        <v>11.184783</v>
+        <v>18.73998</v>
       </c>
       <c r="S23" t="n">
-        <v>224.3236794311572</v>
+        <v>78.46197868255226</v>
       </c>
       <c r="T23" t="n">
-        <v>0.2731052304868204</v>
+        <v>0.08885627065640733</v>
       </c>
       <c r="U23" t="n">
-        <v>0.1728048727569254</v>
+        <v>0.07477044488831464</v>
       </c>
       <c r="V23" t="n">
-        <v>0.2527722644518891</v>
+        <v>0.1330444344351887</v>
       </c>
       <c r="W23" t="n">
-        <v>-0.005510781480655758</v>
+        <v>1.253191840601018</v>
       </c>
       <c r="X23" t="n">
-        <v>0.00090000004</v>
+        <v>0.00016000001</v>
       </c>
       <c r="Y23" t="n">
-        <v>0.75881</v>
+        <v>0.20384</v>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>2026-08-27T16:09:05.794501+00:00</t>
+          <t>2026-08-27T18:37:28.763120+00:00</t>
         </is>
       </c>
       <c r="AD23" t="inlineStr">
@@ -5524,10 +5524,10 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>309426978816</v>
+        <v>315046395904</v>
       </c>
       <c r="F24" t="n">
-        <v>379.6650085449219</v>
+        <v>386.5599975585938</v>
       </c>
       <c r="G24" t="n">
         <v>10606499840</v>
@@ -5554,25 +5554,25 @@
         <v>-0.02465</v>
       </c>
       <c r="Q24" t="n">
-        <v>330.1435</v>
+        <v>336.13913</v>
       </c>
       <c r="R24" t="n">
-        <v>29.173336</v>
+        <v>29.703144</v>
       </c>
       <c r="S24" t="n">
-        <v>86.44720651663782</v>
+        <v>88.01715013101906</v>
       </c>
       <c r="T24" t="n">
-        <v>0.1901724405796923</v>
+        <v>0.2117868262024882</v>
       </c>
       <c r="U24" t="n">
-        <v>0.472882898423</v>
+        <v>0.4996315088413608</v>
       </c>
       <c r="V24" t="n">
-        <v>1.621271873407251</v>
+        <v>1.668876051728181</v>
       </c>
       <c r="W24" t="n">
-        <v>1.023692805872596</v>
+        <v>1.060444519487225</v>
       </c>
       <c r="X24" t="n">
         <v>0.0076</v>
@@ -5582,7 +5582,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>2026-08-27T16:09:05.381261+00:00</t>
+          <t>2026-08-27T18:37:26.063260+00:00</t>
         </is>
       </c>
       <c r="AD24" t="inlineStr">
@@ -5613,10 +5613,10 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>24662034432</v>
+        <v>24694376448</v>
       </c>
       <c r="F25" t="n">
-        <v>38.125</v>
+        <v>38.17499923706055</v>
       </c>
       <c r="G25" t="n">
         <v>39063072768</v>
@@ -5646,22 +5646,22 @@
         <v>0.13382</v>
       </c>
       <c r="Q25" t="n">
-        <v>11.694785</v>
+        <v>11.710122</v>
       </c>
       <c r="R25" t="n">
-        <v>0.63133883</v>
+        <v>0.6321667399999999</v>
       </c>
       <c r="T25" t="n">
-        <v>0.340070262833305</v>
+        <v>0.3418277052136116</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.07687649626422899</v>
+        <v>-0.07566586096194849</v>
       </c>
       <c r="V25" t="n">
-        <v>0.1346726705765802</v>
+        <v>0.1361607431757219</v>
       </c>
       <c r="W25" t="n">
-        <v>-0.1482349993373711</v>
+        <v>-0.147117947529161</v>
       </c>
       <c r="X25" t="n">
         <v>0.12878999</v>
@@ -5671,7 +5671,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>2026-08-27T16:09:10.554938+00:00</t>
+          <t>2026-08-27T18:37:31.457520+00:00</t>
         </is>
       </c>
       <c r="AD25" t="inlineStr">
@@ -5702,10 +5702,10 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>226521956352</v>
+        <v>230554255360</v>
       </c>
       <c r="F26" t="n">
-        <v>222.4600067138672</v>
+        <v>226.4199981689453</v>
       </c>
       <c r="G26" t="n">
         <v>5094199808</v>
@@ -5732,25 +5732,25 @@
         <v>-0.022079999</v>
       </c>
       <c r="Q26" t="n">
-        <v>3707.6667</v>
+        <v>3773.6667</v>
       </c>
       <c r="R26" t="n">
-        <v>44.46664</v>
+        <v>45.25819</v>
       </c>
       <c r="S26" t="n">
-        <v>117.5903578848972</v>
+        <v>119.6835743266306</v>
       </c>
       <c r="T26" t="n">
-        <v>0.2236523816258331</v>
+        <v>0.245434512476242</v>
       </c>
       <c r="U26" t="n">
-        <v>0.3261401294418311</v>
+        <v>0.3497466358804489</v>
       </c>
       <c r="V26" t="n">
-        <v>1.449258299620444</v>
+        <v>1.49285733605422</v>
       </c>
       <c r="W26" t="n">
-        <v>1.105582115186476</v>
+        <v>1.143063401406288</v>
       </c>
       <c r="X26" t="n">
         <v>0.01467</v>
@@ -5760,7 +5760,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>2026-08-27T16:09:04.974925+00:00</t>
+          <t>2026-08-27T18:37:25.691165+00:00</t>
         </is>
       </c>
       <c r="AD26" t="inlineStr">
@@ -5791,10 +5791,10 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>268195807232</v>
+        <v>267800641536</v>
       </c>
       <c r="F27" t="n">
-        <v>251.1199951171875</v>
+        <v>250.75</v>
       </c>
       <c r="G27" t="n">
         <v>5155999744</v>
@@ -5824,25 +5824,25 @@
         <v>0.07603</v>
       </c>
       <c r="Q27" t="n">
-        <v>256.24487</v>
+        <v>255.86734</v>
       </c>
       <c r="R27" t="n">
-        <v>52.01626</v>
+        <v>51.939613</v>
       </c>
       <c r="S27" t="n">
-        <v>200.9710106130179</v>
+        <v>200.6748954346921</v>
       </c>
       <c r="T27" t="n">
-        <v>0.02606843785578672</v>
+        <v>0.02455664939095459</v>
       </c>
       <c r="U27" t="n">
-        <v>-0.2509917280220773</v>
+        <v>-0.2520953016472502</v>
       </c>
       <c r="V27" t="n">
-        <v>0.9061787205574241</v>
+        <v>0.9033701954188191</v>
       </c>
       <c r="W27" t="n">
-        <v>0.7852978002220368</v>
+        <v>0.7826673785843672</v>
       </c>
       <c r="X27" t="n">
         <v>0.0007</v>
@@ -5852,7 +5852,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>2026-08-27T16:09:08.695270+00:00</t>
+          <t>2026-08-27T18:37:29.132514+00:00</t>
         </is>
       </c>
       <c r="AD27" t="inlineStr">
@@ -5883,10 +5883,10 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>218834583552</v>
+        <v>219531067392</v>
       </c>
       <c r="F28" t="n">
-        <v>243.5</v>
+        <v>244.3000030517578</v>
       </c>
       <c r="G28" t="n">
         <v>8717100032</v>
@@ -5895,7 +5895,7 @@
         <v>0.276</v>
       </c>
       <c r="I28" t="n">
-        <v>2.97</v>
+        <v>2.92</v>
       </c>
       <c r="J28" t="n">
         <v>-0.804</v>
@@ -5916,25 +5916,25 @@
         <v>0.14479999</v>
       </c>
       <c r="Q28" t="n">
-        <v>81.98653400000001</v>
+        <v>83.655815</v>
       </c>
       <c r="R28" t="n">
-        <v>25.104057</v>
+        <v>25.186535</v>
       </c>
       <c r="S28" t="n">
-        <v>96.41563832052638</v>
+        <v>96.72249993683747</v>
       </c>
       <c r="T28" t="n">
-        <v>0.3956554037732509</v>
+        <v>0.4002407367597842</v>
       </c>
       <c r="U28" t="n">
-        <v>0.189083984504816</v>
+        <v>0.1929906408350017</v>
       </c>
       <c r="V28" t="n">
-        <v>2.011394146903351</v>
+        <v>2.021287596977853</v>
       </c>
       <c r="W28" t="n">
-        <v>2.262719389443954</v>
+        <v>2.273438836953542</v>
       </c>
       <c r="X28" t="n">
         <v>0.00494</v>
@@ -5944,7 +5944,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>2026-08-27T16:09:09.210813+00:00</t>
+          <t>2026-08-27T18:37:29.568626+00:00</t>
         </is>
       </c>
       <c r="AD28" t="inlineStr">
@@ -5975,10 +5975,10 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1461299576832</v>
+        <v>1450015064064</v>
       </c>
       <c r="F29" t="n">
-        <v>573.61962890625</v>
+        <v>569.1900024414062</v>
       </c>
       <c r="G29" t="n">
         <v>228246994944</v>
@@ -6008,25 +6008,25 @@
         <v>0.34827</v>
       </c>
       <c r="Q29" t="n">
-        <v>21.597124</v>
+        <v>21.430347</v>
       </c>
       <c r="R29" t="n">
-        <v>6.402273</v>
+        <v>6.3528333</v>
       </c>
       <c r="S29" t="n">
-        <v>67.79832027632233</v>
+        <v>67.27476506359467</v>
       </c>
       <c r="T29" t="n">
-        <v>-0.03335020497449759</v>
+        <v>-0.04081490335388405</v>
       </c>
       <c r="U29" t="n">
-        <v>-0.09623747698446183</v>
+        <v>-0.1032165449733257</v>
       </c>
       <c r="V29" t="n">
-        <v>-0.1209245694527549</v>
+        <v>-0.1277129162829321</v>
       </c>
       <c r="W29" t="n">
-        <v>-0.2299771767016204</v>
+        <v>-0.2359234124897758</v>
       </c>
       <c r="X29" t="n">
         <v>0.00148</v>
@@ -6036,7 +6036,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>2026-08-27T16:09:07.223487+00:00</t>
+          <t>2026-08-27T18:37:27.525567+00:00</t>
         </is>
       </c>
       <c r="AD29" t="inlineStr">
@@ -6067,10 +6067,10 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>140380372992</v>
+        <v>142083653632</v>
       </c>
       <c r="F30" t="n">
-        <v>135.7825012207031</v>
+        <v>137.4299926757812</v>
       </c>
       <c r="G30" t="n">
         <v>14732000256</v>
@@ -6100,25 +6100,25 @@
         <v>0.04063</v>
       </c>
       <c r="Q30" t="n">
-        <v>84.86405999999999</v>
+        <v>85.893745</v>
       </c>
       <c r="R30" t="n">
-        <v>9.528942000000001</v>
+        <v>9.64456</v>
       </c>
       <c r="S30" t="n">
-        <v>27.26163343051908</v>
+        <v>27.59240767942086</v>
       </c>
       <c r="T30" t="n">
-        <v>0.2274678887123656</v>
+        <v>0.2423611396088814</v>
       </c>
       <c r="U30" t="n">
-        <v>0.2488043504879045</v>
+        <v>0.2639564833326891</v>
       </c>
       <c r="V30" t="n">
-        <v>0.3027199160276204</v>
+        <v>0.3185262232521948</v>
       </c>
       <c r="W30" t="n">
-        <v>-0.2354416397863344</v>
+        <v>-0.226165014639231</v>
       </c>
       <c r="X30" t="n">
         <v>0.00176</v>
@@ -6128,7 +6128,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>2026-08-27T16:09:11.940172+00:00</t>
+          <t>2026-08-27T18:37:33.457796+00:00</t>
         </is>
       </c>
       <c r="AD30" t="inlineStr">
@@ -6159,10 +6159,10 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>426021650432</v>
+        <v>430904082432</v>
       </c>
       <c r="F31" t="n">
-        <v>147.8899993896484</v>
+        <v>149.5950012207031</v>
       </c>
       <c r="G31" t="n">
         <v>67356999680</v>
@@ -6192,22 +6192,22 @@
         <v>0.36202</v>
       </c>
       <c r="Q31" t="n">
-        <v>25.32534</v>
+        <v>25.615582</v>
       </c>
       <c r="R31" t="n">
-        <v>6.324831</v>
+        <v>6.397317</v>
       </c>
       <c r="T31" t="n">
-        <v>0.2328276135239733</v>
+        <v>0.2470406999199981</v>
       </c>
       <c r="U31" t="n">
-        <v>-0.2714555473446226</v>
+        <v>-0.2630562665892729</v>
       </c>
       <c r="V31" t="n">
-        <v>0.006983760144649853</v>
+        <v>0.01859312630851995</v>
       </c>
       <c r="W31" t="n">
-        <v>-0.3656944104764112</v>
+        <v>-0.3583815535820681</v>
       </c>
       <c r="X31" t="n">
         <v>0.40498</v>
@@ -6217,7 +6217,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>2026-08-27T16:09:07.560885+00:00</t>
+          <t>2026-08-27T18:37:27.950175+00:00</t>
         </is>
       </c>
       <c r="AD31" t="inlineStr">
@@ -6849,23 +6849,18 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ACMR</t>
+          <t>VRT</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>94.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="C20" t="n">
-        <v>94.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
           <t>HIGH</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>price_to_fcf</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -6883,18 +6878,23 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>VRT</t>
+          <t>ACMR</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>100</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="C21" t="n">
-        <v>100</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
           <t>HIGH</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>price_to_fcf</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -6912,7 +6912,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ASML</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -6941,7 +6941,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>ASML</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -7292,7 +7292,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>56.69</v>
+        <v>56.68</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/reports/investment_dashboard.xlsx
+++ b/reports/investment_dashboard.xlsx
@@ -534,7 +534,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>56.68</v>
+        <v>56.69</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>912.260009765625</v>
+        <v>914.239990234375</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -586,7 +586,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>55.57</v>
+        <v>55.58</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>425.1000061035156</v>
+        <v>425.2799987792969</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>53.45</v>
+        <v>53.47</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>234.6399993896484</v>
+        <v>235.4750061035156</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -685,7 +685,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>52.89</v>
+        <v>52.9</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -693,7 +693,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>199.7149963378906</v>
+        <v>199.9700012207031</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -745,7 +745,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>185.8999938964844</v>
+        <v>185.8500061035156</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>464.0498962402344</v>
+        <v>465.375</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -836,7 +836,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>50.9</v>
+        <v>50.93</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -844,7 +844,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>226.1300048828125</v>
+        <v>226.5599975585938</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>50.83</v>
+        <v>50.85</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>364.6549987792969</v>
+        <v>365.1449890136719</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>47.68</v>
+        <v>47.69</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -943,7 +943,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>18.14500045776367</v>
+        <v>18.13999938964844</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -982,7 +982,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>47.56</v>
+        <v>47.57</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -990,7 +990,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>471.2699890136719</v>
+        <v>471.7000122070312</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>46.74</v>
+        <v>46.73</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -1042,7 +1042,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>340.8099975585938</v>
+        <v>340.5599975585938</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -1089,7 +1089,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>475.2000122070312</v>
+        <v>475.25</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -1128,7 +1128,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>45.08</v>
+        <v>45.07</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>240.8500061035156</v>
+        <v>240.6450042724609</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -1180,7 +1180,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>44.24</v>
+        <v>44.27</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>367.8999938964844</v>
+        <v>368.3500061035156</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>444.2250061035156</v>
+        <v>443.6000061035156</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1279,7 +1279,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>43.22</v>
+        <v>43.17</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -1287,7 +1287,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>331.8399963378906</v>
+        <v>330.5101013183594</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1331,7 +1331,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>43.04</v>
+        <v>43.05</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -1339,7 +1339,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>306.125</v>
+        <v>306.4700012207031</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1391,7 +1391,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>255.3699035644531</v>
+        <v>255.3849945068359</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1421,12 +1421,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>VRT</t>
+          <t>ACMR</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Vertiv Holdings Co</t>
+          <t>ACM Research, Inc.</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1438,7 +1438,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>267.7550048828125</v>
+        <v>79.61499786376953</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1446,24 +1446,24 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>100</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="I20" t="n">
-        <v>100</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Earnings Fcf</t>
+          <t>Revenue Growth</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Industry Growth; Valuation; Competitive Advantage; Momentum; Catalysts; Inflation Resilience</t>
+          <t>Industry Growth; Competitive Advantage; Catalysts; Inflation Resilience</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>High market sensitivity / beta</t>
+          <t>Negative free cash flow / unprofitable growth</t>
         </is>
       </c>
     </row>
@@ -1473,12 +1473,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>ACMR</t>
+          <t>VRT</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>ACM Research, Inc.</t>
+          <t>Vertiv Holdings Co</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1490,7 +1490,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>79.52999877929688</v>
+        <v>267.3599853515625</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1498,24 +1498,24 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>94.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="I21" t="n">
-        <v>94.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Revenue Growth</t>
+          <t>Earnings Fcf</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>Industry Growth; Competitive Advantage; Catalysts; Inflation Resilience</t>
+          <t>Industry Growth; Valuation; Competitive Advantage; Momentum; Catalysts; Inflation Resilience</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>Negative free cash flow / unprofitable growth</t>
+          <t>High market sensitivity / beta</t>
         </is>
       </c>
     </row>
@@ -1525,16 +1525,16 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>ASML</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Microsoft Corporation</t>
+          <t>ASML Holding N.V.</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>42.35</v>
+        <v>42.33</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -1542,7 +1542,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>502.9700012207031</v>
+        <v>1724.660034179688</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1557,7 +1557,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Earnings Fcf</t>
+          <t>Earnings Fcf; Balance Sheet</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1572,16 +1572,16 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>ASML</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>ASML Holding N.V.</t>
+          <t>Microsoft Corporation</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>42.32</v>
+        <v>42.33</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1723.60498046875</v>
+        <v>502.3200073242188</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Earnings Fcf; Balance Sheet</t>
+          <t>Earnings Fcf</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -1636,7 +1636,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>386.5599975585938</v>
+        <v>385.8999938964844</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1680,7 +1680,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>41.75</v>
+        <v>41.79</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>38.17499923706055</v>
+        <v>38.27500152587891</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1732,7 +1732,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>41.04</v>
+        <v>41</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -1740,7 +1740,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>226.4199981689453</v>
+        <v>225.75</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1784,7 +1784,7 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>40.71</v>
+        <v>40.72</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -1792,7 +1792,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>250.75</v>
+        <v>250.8950042724609</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>244.3000030517578</v>
+        <v>244.1999969482422</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1888,7 +1888,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>39.56</v>
+        <v>39.57</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -1896,7 +1896,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>569.1900024414062</v>
+        <v>569.5599975585938</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>36.37</v>
+        <v>36.38</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -1943,7 +1943,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>137.4299926757812</v>
+        <v>137.3999938964844</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1977,7 +1977,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>31.47</v>
+        <v>31.48</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -1985,7 +1985,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>149.5950012207031</v>
+        <v>149.7100067138672</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -2131,13 +2131,13 @@
         <v>9.02</v>
       </c>
       <c r="F2" t="n">
-        <v>7.34</v>
+        <v>7.33</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>6.82</v>
+        <v>6.84</v>
       </c>
       <c r="I2" t="n">
         <v>3.5</v>
@@ -2149,7 +2149,7 @@
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>56.68</v>
+        <v>56.69</v>
       </c>
     </row>
     <row r="3">
@@ -2177,7 +2177,7 @@
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>5.4</v>
+        <v>5.41</v>
       </c>
       <c r="I3" t="n">
         <v>2.69</v>
@@ -2189,7 +2189,7 @@
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>55.57</v>
+        <v>55.58</v>
       </c>
     </row>
     <row r="4">
@@ -2211,13 +2211,13 @@
         <v>9.91</v>
       </c>
       <c r="F4" t="n">
-        <v>2.38</v>
+        <v>2.37</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>7.62</v>
+        <v>7.65</v>
       </c>
       <c r="I4" t="n">
         <v>3.54</v>
@@ -2229,7 +2229,7 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>53.45</v>
+        <v>53.47</v>
       </c>
     </row>
     <row r="5">
@@ -2257,7 +2257,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>8.470000000000001</v>
+        <v>8.48</v>
       </c>
       <c r="I5" t="n">
         <v>3.63</v>
@@ -2269,7 +2269,7 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>52.89</v>
+        <v>52.9</v>
       </c>
     </row>
     <row r="6">
@@ -2331,13 +2331,13 @@
         <v>6.33</v>
       </c>
       <c r="F7" t="n">
-        <v>5.77</v>
+        <v>5.76</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>9.02</v>
+        <v>9.029999999999999</v>
       </c>
       <c r="I7" t="n">
         <v>3.54</v>
@@ -2371,13 +2371,13 @@
         <v>9.029999999999999</v>
       </c>
       <c r="F8" t="n">
-        <v>2.93</v>
+        <v>2.92</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>5.5</v>
+        <v>5.54</v>
       </c>
       <c r="I8" t="n">
         <v>3.44</v>
@@ -2389,7 +2389,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>50.9</v>
+        <v>50.93</v>
       </c>
     </row>
     <row r="9">
@@ -2417,7 +2417,7 @@
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>5.25</v>
+        <v>5.27</v>
       </c>
       <c r="I9" t="n">
         <v>3.75</v>
@@ -2429,7 +2429,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>50.83</v>
+        <v>50.85</v>
       </c>
     </row>
     <row r="10">
@@ -2451,7 +2451,7 @@
         <v>9.699999999999999</v>
       </c>
       <c r="F10" t="n">
-        <v>6.55</v>
+        <v>6.56</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -2469,7 +2469,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>47.68</v>
+        <v>47.69</v>
       </c>
     </row>
     <row r="11">
@@ -2497,7 +2497,7 @@
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>6.12</v>
+        <v>6.13</v>
       </c>
       <c r="I11" t="n">
         <v>3.45</v>
@@ -2509,7 +2509,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>47.56</v>
+        <v>47.57</v>
       </c>
     </row>
     <row r="12">
@@ -2537,7 +2537,7 @@
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>4.48</v>
+        <v>4.47</v>
       </c>
       <c r="I12" t="n">
         <v>3.53</v>
@@ -2549,7 +2549,7 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>46.74</v>
+        <v>46.73</v>
       </c>
     </row>
     <row r="13">
@@ -2617,7 +2617,7 @@
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>6.5</v>
+        <v>6.49</v>
       </c>
       <c r="I14" t="n">
         <v>3.67</v>
@@ -2629,7 +2629,7 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>45.08</v>
+        <v>45.07</v>
       </c>
     </row>
     <row r="15">
@@ -2657,7 +2657,7 @@
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>3.52</v>
+        <v>3.55</v>
       </c>
       <c r="I15" t="n">
         <v>3.53</v>
@@ -2669,7 +2669,7 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>44.24</v>
+        <v>44.27</v>
       </c>
     </row>
     <row r="16">
@@ -2691,13 +2691,13 @@
         <v>9.880000000000001</v>
       </c>
       <c r="F16" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>9.84</v>
+        <v>9.83</v>
       </c>
       <c r="I16" t="n">
         <v>3.73</v>
@@ -2737,7 +2737,7 @@
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>9.16</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="I17" t="n">
         <v>3.56</v>
@@ -2749,7 +2749,7 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>43.22</v>
+        <v>43.17</v>
       </c>
     </row>
     <row r="18">
@@ -2777,7 +2777,7 @@
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>8.640000000000001</v>
+        <v>8.65</v>
       </c>
       <c r="I18" t="n">
         <v>3.64</v>
@@ -2789,7 +2789,7 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>43.04</v>
+        <v>43.05</v>
       </c>
     </row>
     <row r="19">
@@ -2835,32 +2835,32 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>VRT</t>
+          <t>ACMR</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>10.91</v>
+        <v>15</v>
       </c>
       <c r="C20" t="n">
-        <v>13.39</v>
+        <v>7.83</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>7.41</v>
+        <v>4.02</v>
       </c>
       <c r="F20" t="n">
-        <v>3.24</v>
+        <v>6.85</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>3.94</v>
+        <v>5.12</v>
       </c>
       <c r="I20" t="n">
-        <v>3.56</v>
+        <v>3.63</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2875,32 +2875,32 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ACMR</t>
+          <t>VRT</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>15</v>
+        <v>10.91</v>
       </c>
       <c r="C21" t="n">
-        <v>7.83</v>
+        <v>13.39</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>4.02</v>
+        <v>7.41</v>
       </c>
       <c r="F21" t="n">
-        <v>6.85</v>
+        <v>3.24</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>5.1</v>
+        <v>3.92</v>
       </c>
       <c r="I21" t="n">
-        <v>3.63</v>
+        <v>3.56</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2915,32 +2915,32 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>ASML</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>8.51</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="C22" t="n">
-        <v>14.63</v>
+        <v>14.28</v>
       </c>
       <c r="D22" t="n">
         <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>6.87</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="F22" t="n">
-        <v>2.88</v>
+        <v>0.57</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>6.01</v>
+        <v>5.9</v>
       </c>
       <c r="I22" t="n">
-        <v>3.45</v>
+        <v>2.76</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2949,38 +2949,38 @@
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>42.35</v>
+        <v>42.33</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ASML</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>9.859999999999999</v>
+        <v>8.51</v>
       </c>
       <c r="C23" t="n">
-        <v>14.28</v>
+        <v>14.63</v>
       </c>
       <c r="D23" t="n">
         <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>8.960000000000001</v>
+        <v>6.87</v>
       </c>
       <c r="F23" t="n">
-        <v>0.57</v>
+        <v>2.89</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>5.89</v>
+        <v>5.98</v>
       </c>
       <c r="I23" t="n">
-        <v>2.76</v>
+        <v>3.45</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2989,7 +2989,7 @@
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>42.32</v>
+        <v>42.33</v>
       </c>
     </row>
     <row r="24">
@@ -3051,13 +3051,13 @@
         <v>2.23</v>
       </c>
       <c r="F25" t="n">
-        <v>9.859999999999999</v>
+        <v>9.85</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>3.89</v>
+        <v>3.94</v>
       </c>
       <c r="I25" t="n">
         <v>3.54</v>
@@ -3069,7 +3069,7 @@
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>41.75</v>
+        <v>41.79</v>
       </c>
     </row>
     <row r="26">
@@ -3097,7 +3097,7 @@
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>9.07</v>
+        <v>9.029999999999999</v>
       </c>
       <c r="I26" t="n">
         <v>3.48</v>
@@ -3109,7 +3109,7 @@
         <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>41.04</v>
+        <v>41</v>
       </c>
     </row>
     <row r="27">
@@ -3137,7 +3137,7 @@
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>5.79</v>
+        <v>5.8</v>
       </c>
       <c r="I27" t="n">
         <v>3.7</v>
@@ -3149,7 +3149,7 @@
         <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>40.71</v>
+        <v>40.72</v>
       </c>
     </row>
     <row r="28">
@@ -3217,7 +3217,7 @@
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.82</v>
       </c>
       <c r="I29" t="n">
         <v>3.49</v>
@@ -3229,7 +3229,7 @@
         <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>39.56</v>
+        <v>39.57</v>
       </c>
     </row>
     <row r="30">
@@ -3251,7 +3251,7 @@
         <v>6.78</v>
       </c>
       <c r="F30" t="n">
-        <v>3.67</v>
+        <v>3.68</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -3269,7 +3269,7 @@
         <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>36.37</v>
+        <v>36.38</v>
       </c>
     </row>
     <row r="31">
@@ -3297,7 +3297,7 @@
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>2.57</v>
+        <v>2.58</v>
       </c>
       <c r="I31" t="n">
         <v>3.58</v>
@@ -3309,7 +3309,7 @@
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>31.47</v>
+        <v>31.48</v>
       </c>
     </row>
   </sheetData>
@@ -3349,7 +3349,7 @@
     <col width="23" customWidth="1" min="20" max="20"/>
     <col width="22" customWidth="1" min="21" max="21"/>
     <col width="21" customWidth="1" min="22" max="22"/>
-    <col width="23" customWidth="1" min="23" max="23"/>
+    <col width="24" customWidth="1" min="23" max="23"/>
     <col width="18" customWidth="1" min="24" max="24"/>
     <col width="24" customWidth="1" min="25" max="25"/>
     <col width="17" customWidth="1" min="26" max="26"/>
@@ -3533,7 +3533,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>912.260009765625</v>
+        <v>914.239990234375</v>
       </c>
       <c r="G2" t="n">
         <v>90273996800</v>
@@ -3563,19 +3563,19 @@
         <v>0.80370003</v>
       </c>
       <c r="Q2" t="n">
-        <v>20.639366</v>
+        <v>20.683485</v>
       </c>
       <c r="T2" t="n">
-        <v>0.1117935690267848</v>
+        <v>0.114206619613668</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.01204055226433332</v>
+        <v>-0.00989627279412375</v>
       </c>
       <c r="V2" t="n">
-        <v>1.127700754366305</v>
+        <v>1.132318742540611</v>
       </c>
       <c r="W2" t="n">
-        <v>6.759865486377861</v>
+        <v>6.77670809960623</v>
       </c>
       <c r="X2" t="n">
         <v>0.00238</v>
@@ -3585,7 +3585,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>2026-08-27T18:37:24.150743+00:00</t>
+          <t>2026-08-27T18:45:19.530064+00:00</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
@@ -3616,10 +3616,10 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2204770238464</v>
+        <v>2205651828736</v>
       </c>
       <c r="F3" t="n">
-        <v>425.1000061035156</v>
+        <v>425.2799987792969</v>
       </c>
       <c r="G3" t="n">
         <v>4440492343296</v>
@@ -3649,25 +3649,25 @@
         <v>0.60344005</v>
       </c>
       <c r="Q3" t="n">
-        <v>31.700224</v>
+        <v>31.7129</v>
       </c>
       <c r="R3" t="n">
-        <v>0.49651483</v>
+        <v>0.49671334</v>
       </c>
       <c r="S3" t="n">
-        <v>3.016819590513221</v>
+        <v>3.018025883467007</v>
       </c>
       <c r="T3" t="n">
-        <v>0.08358188358435736</v>
+        <v>0.08404068574821077</v>
       </c>
       <c r="U3" t="n">
-        <v>0.002908141059817071</v>
+        <v>0.003332784948973266</v>
       </c>
       <c r="V3" t="n">
-        <v>0.1020457069221468</v>
+        <v>0.102512326900444</v>
       </c>
       <c r="W3" t="n">
-        <v>0.7961527012770839</v>
+        <v>0.7969132148648814</v>
       </c>
       <c r="X3" t="n">
         <v>0.00013</v>
@@ -3677,7 +3677,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>2026-08-27T18:37:28.298591+00:00</t>
+          <t>2026-08-27T18:45:23.593836+00:00</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
@@ -3708,10 +3708,10 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>44096991232</v>
+        <v>44253917184</v>
       </c>
       <c r="F4" t="n">
-        <v>234.6399993896484</v>
+        <v>235.4750061035156</v>
       </c>
       <c r="G4" t="n">
         <v>1335116032</v>
@@ -3741,25 +3741,25 @@
         <v>0.35661998</v>
       </c>
       <c r="Q4" t="n">
-        <v>93.48206999999999</v>
+        <v>93.81474</v>
       </c>
       <c r="R4" t="n">
-        <v>33.028584</v>
+        <v>33.146122</v>
       </c>
       <c r="S4" t="n">
-        <v>175.8182238637508</v>
+        <v>176.4439001602041</v>
       </c>
       <c r="T4" t="n">
-        <v>0.2203037283091169</v>
+        <v>0.2246463885918728</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0552731861874165</v>
+        <v>0.05902855695848119</v>
       </c>
       <c r="V4" t="n">
-        <v>0.9005345952506061</v>
+        <v>0.9072979738352427</v>
       </c>
       <c r="W4" t="n">
-        <v>0.9118389389043597</v>
+        <v>0.918642545936283</v>
       </c>
       <c r="X4" t="n">
         <v>0.09436</v>
@@ -3769,7 +3769,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>2026-08-27T18:37:24.949586+00:00</t>
+          <t>2026-08-27T18:45:20.246622+00:00</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
@@ -3800,10 +3800,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>251885486080</v>
+        <v>252207104000</v>
       </c>
       <c r="F5" t="n">
-        <v>199.7149963378906</v>
+        <v>199.9700012207031</v>
       </c>
       <c r="G5" t="n">
         <v>10540800000</v>
@@ -3833,25 +3833,25 @@
         <v>0.45393002</v>
       </c>
       <c r="Q5" t="n">
-        <v>63.200947</v>
+        <v>63.281643</v>
       </c>
       <c r="R5" t="n">
-        <v>23.89624</v>
+        <v>23.926752</v>
       </c>
       <c r="S5" t="n">
-        <v>64.72688476800647</v>
+        <v>64.80953076071981</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1768015346002088</v>
+        <v>0.1783041265083125</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2862432591129422</v>
+        <v>0.2878855910237794</v>
       </c>
       <c r="V5" t="n">
-        <v>0.5028594872086933</v>
+        <v>0.5047784042376926</v>
       </c>
       <c r="W5" t="n">
-        <v>0.4985742472821393</v>
+        <v>0.5004876927285065</v>
       </c>
       <c r="X5" t="n">
         <v>0.17247999</v>
@@ -3861,7 +3861,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>2026-08-27T18:37:29.986370+00:00</t>
+          <t>2026-08-27T18:45:25.062145+00:00</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
@@ -3892,10 +3892,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>446728536064</v>
+        <v>446560337920</v>
       </c>
       <c r="F6" t="n">
-        <v>185.8999938964844</v>
+        <v>185.8500061035156</v>
       </c>
       <c r="G6" t="n">
         <v>6155940864</v>
@@ -3925,25 +3925,25 @@
         <v>0.47120997</v>
       </c>
       <c r="Q6" t="n">
-        <v>158.88889</v>
+        <v>158.82907</v>
       </c>
       <c r="R6" t="n">
-        <v>72.56869</v>
+        <v>72.54917</v>
       </c>
       <c r="S6" t="n">
-        <v>206.9045447226596</v>
+        <v>206.8266429151902</v>
       </c>
       <c r="T6" t="n">
-        <v>0.5048975611877078</v>
+        <v>0.5044929000247294</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2969164130454454</v>
+        <v>0.2965676772128385</v>
       </c>
       <c r="V6" t="n">
-        <v>0.3853490611393138</v>
+        <v>0.3849765461079457</v>
       </c>
       <c r="W6" t="n">
-        <v>0.1861918864758565</v>
+        <v>0.1858729240423485</v>
       </c>
       <c r="X6" t="n">
         <v>0.03477</v>
@@ -3953,7 +3953,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>2026-08-27T18:37:22.422361+00:00</t>
+          <t>2026-08-27T18:45:18.076344+00:00</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr">
@@ -3984,10 +3984,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>299842306048</v>
+        <v>300698533888</v>
       </c>
       <c r="F7" t="n">
-        <v>464.0498962402344</v>
+        <v>465.375</v>
       </c>
       <c r="G7" t="n">
         <v>134001999872</v>
@@ -4017,25 +4017,25 @@
         <v>0.08857000600000001</v>
       </c>
       <c r="Q7" t="n">
-        <v>36.917255</v>
+        <v>37.022675</v>
       </c>
       <c r="R7" t="n">
-        <v>2.2375958</v>
+        <v>2.2439854</v>
       </c>
       <c r="S7" t="n">
-        <v>55.1776628405737</v>
+        <v>55.33522783429633</v>
       </c>
       <c r="T7" t="n">
-        <v>0.1834988243221902</v>
+        <v>0.1868783288851557</v>
       </c>
       <c r="U7" t="n">
-        <v>0.4660675832087586</v>
+        <v>0.4702539685141325</v>
       </c>
       <c r="V7" t="n">
-        <v>2.775955010324226</v>
+        <v>2.786737325375744</v>
       </c>
       <c r="W7" t="n">
-        <v>2.546892804018727</v>
+        <v>2.557021442207762</v>
       </c>
       <c r="X7" t="n">
         <v>0.07491</v>
@@ -4045,7 +4045,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>2026-08-27T18:37:30.446342+00:00</t>
+          <t>2026-08-27T18:45:25.392621+00:00</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr">
@@ -4076,10 +4076,10 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5477336875008</v>
+        <v>5486782971904</v>
       </c>
       <c r="F8" t="n">
-        <v>226.1300048828125</v>
+        <v>226.5599975585938</v>
       </c>
       <c r="G8" t="n">
         <v>253491003392</v>
@@ -4109,25 +4109,25 @@
         <v>0.65596</v>
       </c>
       <c r="Q8" t="n">
-        <v>34.684048</v>
+        <v>34.743866</v>
       </c>
       <c r="R8" t="n">
-        <v>21.607618</v>
+        <v>21.647749</v>
       </c>
       <c r="S8" t="n">
-        <v>118.2094243086987</v>
+        <v>118.413285729225</v>
       </c>
       <c r="T8" t="n">
-        <v>0.1478098126385468</v>
+        <v>0.1499924058458491</v>
       </c>
       <c r="U8" t="n">
-        <v>0.05667940272983274</v>
+        <v>0.05868870885467992</v>
       </c>
       <c r="V8" t="n">
-        <v>0.1577307232383589</v>
+        <v>0.1599321813410879</v>
       </c>
       <c r="W8" t="n">
-        <v>0.2468676980403361</v>
+        <v>0.2492386526516157</v>
       </c>
       <c r="X8" t="n">
         <v>0.03991</v>
@@ -4137,7 +4137,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>2026-08-27T18:37:22.042775+00:00</t>
+          <t>2026-08-27T18:45:17.679154+00:00</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr">
@@ -4168,10 +4168,10 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>57010438144</v>
+        <v>57087041536</v>
       </c>
       <c r="F9" t="n">
-        <v>364.6549987792969</v>
+        <v>365.1449890136719</v>
       </c>
       <c r="G9" t="n">
         <v>4464031232</v>
@@ -4201,25 +4201,25 @@
         <v>0.33161</v>
       </c>
       <c r="Q9" t="n">
-        <v>50.22796</v>
+        <v>50.295452</v>
       </c>
       <c r="R9" t="n">
-        <v>12.771066</v>
+        <v>12.788226</v>
       </c>
       <c r="S9" t="n">
-        <v>130.3449528407766</v>
+        <v>130.520093847279</v>
       </c>
       <c r="T9" t="n">
-        <v>0.1372368804629345</v>
+        <v>0.1387649959898389</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.04702729754140689</v>
+        <v>-0.04574677946433736</v>
       </c>
       <c r="V9" t="n">
-        <v>0.06409401845264417</v>
+        <v>0.06552385125143756</v>
       </c>
       <c r="W9" t="n">
-        <v>2.124955091412798</v>
+        <v>2.129154326543427</v>
       </c>
       <c r="X9" t="n">
         <v>0.00202</v>
@@ -4229,7 +4229,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>2026-08-27T18:37:25.314125+00:00</t>
+          <t>2026-08-27T18:45:20.642832+00:00</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr">
@@ -4260,10 +4260,10 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>9401291776</v>
+        <v>9398701056</v>
       </c>
       <c r="F10" t="n">
-        <v>18.14500045776367</v>
+        <v>18.13999938964844</v>
       </c>
       <c r="G10" t="n">
         <v>1672329984</v>
@@ -4290,25 +4290,25 @@
         <v>0.07274</v>
       </c>
       <c r="Q10" t="n">
-        <v>30.241667</v>
+        <v>30.233332</v>
       </c>
       <c r="R10" t="n">
-        <v>5.6216726</v>
+        <v>5.6201234</v>
       </c>
       <c r="S10" t="n">
-        <v>18.37792010046759</v>
+        <v>18.3728556852471</v>
       </c>
       <c r="T10" t="n">
-        <v>0.4885152651656715</v>
+        <v>0.488105005256944</v>
       </c>
       <c r="U10" t="n">
-        <v>0.566925783878292</v>
+        <v>0.5664939127083279</v>
       </c>
       <c r="V10" t="n">
-        <v>0.8254528394118881</v>
+        <v>0.8249497138257358</v>
       </c>
       <c r="W10" t="n">
-        <v>0.6288150716835186</v>
+        <v>0.6283661427821623</v>
       </c>
       <c r="X10" t="n">
         <v>0.09236999999999999</v>
@@ -4318,7 +4318,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>2026-08-27T18:37:34.330376+00:00</t>
+          <t>2026-08-27T18:45:28.501244+00:00</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr">
@@ -4349,10 +4349,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>769336475648</v>
+        <v>770038497280</v>
       </c>
       <c r="F11" t="n">
-        <v>471.2699890136719</v>
+        <v>471.7000122070312</v>
       </c>
       <c r="G11" t="n">
         <v>41305001984</v>
@@ -4382,25 +4382,25 @@
         <v>0.1725</v>
       </c>
       <c r="Q11" t="n">
-        <v>119.61167</v>
+        <v>119.72081</v>
       </c>
       <c r="R11" t="n">
-        <v>18.625746</v>
+        <v>18.642742</v>
       </c>
       <c r="S11" t="n">
-        <v>87.01425168546248</v>
+        <v>87.09365242741228</v>
       </c>
       <c r="T11" t="n">
-        <v>0.03662398063286343</v>
+        <v>0.03756987654148602</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.09037046732200127</v>
+        <v>-0.08954045097142715</v>
       </c>
       <c r="V11" t="n">
-        <v>1.234989982213517</v>
+        <v>1.23702935996233</v>
       </c>
       <c r="W11" t="n">
-        <v>1.819780860678577</v>
+        <v>1.822353846861764</v>
       </c>
       <c r="X11" t="n">
         <v>0.00425</v>
@@ -4410,7 +4410,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>2026-08-27T18:37:22.840566+00:00</t>
+          <t>2026-08-27T18:45:18.431024+00:00</t>
         </is>
       </c>
       <c r="AD11" t="inlineStr">
@@ -4441,10 +4441,10 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4168084094976</v>
+        <v>4165026709504</v>
       </c>
       <c r="F12" t="n">
-        <v>340.8099975585938</v>
+        <v>340.5599975585938</v>
       </c>
       <c r="G12" t="n">
         <v>445865984000</v>
@@ -4474,25 +4474,25 @@
         <v>0.34033</v>
       </c>
       <c r="Q12" t="n">
-        <v>17.091774</v>
+        <v>17.079237</v>
       </c>
       <c r="R12" t="n">
-        <v>9.3482895</v>
+        <v>9.341431999999999</v>
       </c>
       <c r="S12" t="n">
-        <v>183.8995772526982</v>
+        <v>183.7646826865169</v>
       </c>
       <c r="T12" t="n">
-        <v>0.02127597700193928</v>
+        <v>0.02052682352616264</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.1258976394217068</v>
+        <v>-0.1265388341980044</v>
       </c>
       <c r="V12" t="n">
-        <v>0.09061563639367964</v>
+        <v>0.0898156190495536</v>
       </c>
       <c r="W12" t="n">
-        <v>0.6473021918204871</v>
+        <v>0.6460938189707899</v>
       </c>
       <c r="X12" t="n">
         <v>0.01596</v>
@@ -4502,7 +4502,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>2026-08-27T18:37:26.820357+00:00</t>
+          <t>2026-08-27T18:45:22.063586+00:00</t>
         </is>
       </c>
       <c r="AD12" t="inlineStr">
@@ -4533,10 +4533,10 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>377061965824</v>
+        <v>377157189632</v>
       </c>
       <c r="F13" t="n">
-        <v>475.2000122070312</v>
+        <v>475.25</v>
       </c>
       <c r="G13" t="n">
         <v>30837000192</v>
@@ -4566,25 +4566,25 @@
         <v>0.33736</v>
       </c>
       <c r="Q13" t="n">
-        <v>40.924206</v>
+        <v>40.93454</v>
       </c>
       <c r="R13" t="n">
-        <v>12.227583</v>
+        <v>12.230671</v>
       </c>
       <c r="S13" t="n">
-        <v>122.6068213056589</v>
+        <v>122.6377846206301</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.001577972352334256</v>
+        <v>-0.001472945179919583</v>
       </c>
       <c r="U13" t="n">
-        <v>0.05788153762517356</v>
+        <v>0.05799281953159152</v>
       </c>
       <c r="V13" t="n">
-        <v>0.2059742658021169</v>
+        <v>0.2061011260512247</v>
       </c>
       <c r="W13" t="n">
-        <v>1.906675457490908</v>
+        <v>1.906981219879931</v>
       </c>
       <c r="X13" t="n">
         <v>0.00331</v>
@@ -4594,7 +4594,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>2026-08-27T18:37:23.696963+00:00</t>
+          <t>2026-08-27T18:45:19.162964+00:00</t>
         </is>
       </c>
       <c r="AD13" t="inlineStr">
@@ -4625,10 +4625,10 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>86483214336</v>
+        <v>86409609216</v>
       </c>
       <c r="F14" t="n">
-        <v>240.8500061035156</v>
+        <v>240.6450042724609</v>
       </c>
       <c r="G14" t="n">
         <v>3966725120</v>
@@ -4658,25 +4658,25 @@
         <v>0.00666</v>
       </c>
       <c r="Q14" t="n">
-        <v>481.7</v>
+        <v>481.29</v>
       </c>
       <c r="R14" t="n">
-        <v>21.80217</v>
+        <v>21.783613</v>
       </c>
       <c r="S14" t="n">
-        <v>82.25432597542853</v>
+        <v>82.18432002594544</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.03997926731539225</v>
+        <v>-0.04079639832250637</v>
       </c>
       <c r="U14" t="n">
-        <v>0.06930385468679678</v>
+        <v>0.06839370628484742</v>
       </c>
       <c r="V14" t="n">
-        <v>1.182996484241182</v>
+        <v>1.181138405498751</v>
       </c>
       <c r="W14" t="n">
-        <v>0.8283611471579535</v>
+        <v>0.8268049197404812</v>
       </c>
       <c r="X14" t="n">
         <v>0.00619</v>
@@ -4686,7 +4686,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>2026-08-27T18:37:32.345733+00:00</t>
+          <t>2026-08-27T18:45:26.949964+00:00</t>
         </is>
       </c>
       <c r="AD14" t="inlineStr">
@@ -4717,10 +4717,10 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1750313730048</v>
+        <v>1752454791168</v>
       </c>
       <c r="F15" t="n">
-        <v>367.8999938964844</v>
+        <v>368.3500061035156</v>
       </c>
       <c r="G15" t="n">
         <v>75464998912</v>
@@ -4750,25 +4750,25 @@
         <v>0.48988</v>
       </c>
       <c r="Q15" t="n">
-        <v>61.214638</v>
+        <v>61.289516</v>
       </c>
       <c r="R15" t="n">
-        <v>23.193716</v>
+        <v>23.222088</v>
       </c>
       <c r="S15" t="n">
-        <v>64.32080363470764</v>
+        <v>64.39948368474967</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.03415507505853188</v>
+        <v>-0.03297366159418391</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.1361942120587543</v>
+        <v>-0.1351376120165505</v>
       </c>
       <c r="V15" t="n">
-        <v>0.1111769942932956</v>
+        <v>0.1125361767339046</v>
       </c>
       <c r="W15" t="n">
-        <v>0.2342902057821479</v>
+        <v>0.2357999792772172</v>
       </c>
       <c r="X15" t="n">
         <v>0.01948</v>
@@ -4778,7 +4778,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>2026-08-27T18:37:23.247722+00:00</t>
+          <t>2026-08-27T18:45:18.802472+00:00</t>
         </is>
       </c>
       <c r="AD15" t="inlineStr">
@@ -4809,10 +4809,10 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>35729874944</v>
+        <v>35679604736</v>
       </c>
       <c r="F16" t="n">
-        <v>444.2250061035156</v>
+        <v>443.6000061035156</v>
       </c>
       <c r="G16" t="n">
         <v>2602398976</v>
@@ -4839,22 +4839,22 @@
         <v>-0.03607</v>
       </c>
       <c r="R16" t="n">
-        <v>13.729591</v>
+        <v>13.710275</v>
       </c>
       <c r="S16" t="n">
-        <v>69.02918053154069</v>
+        <v>68.93205980920878</v>
       </c>
       <c r="T16" t="n">
-        <v>0.43012366585069</v>
+        <v>0.4281115609964479</v>
       </c>
       <c r="U16" t="n">
-        <v>0.3639923117590693</v>
+        <v>0.3620732500602986</v>
       </c>
       <c r="V16" t="n">
-        <v>0.4102829292225463</v>
+        <v>0.4082987391867456</v>
       </c>
       <c r="W16" t="n">
-        <v>0.5022826775958877</v>
+        <v>0.5001690490054282</v>
       </c>
       <c r="X16" t="n">
         <v>0.02641</v>
@@ -4864,7 +4864,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>2026-08-27T18:37:33.888521+00:00</t>
+          <t>2026-08-27T18:45:28.011182+00:00</t>
         </is>
       </c>
       <c r="AD16" t="inlineStr">
@@ -4895,10 +4895,10 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>115015745536</v>
+        <v>114554798080</v>
       </c>
       <c r="F17" t="n">
-        <v>331.8399963378906</v>
+        <v>330.5101013183594</v>
       </c>
       <c r="G17" t="n">
         <v>5032822784</v>
@@ -4925,22 +4925,22 @@
         <v>-0.22173999</v>
       </c>
       <c r="R17" t="n">
-        <v>22.853128</v>
+        <v>22.76154</v>
       </c>
       <c r="S17" t="n">
-        <v>66.120089543457</v>
+        <v>65.85510072020054</v>
       </c>
       <c r="T17" t="n">
-        <v>0.2274005559897578</v>
+        <v>0.2224815772518285</v>
       </c>
       <c r="U17" t="n">
-        <v>0.3872909722891584</v>
+        <v>0.3817312104308879</v>
       </c>
       <c r="V17" t="n">
-        <v>0.9611133099180682</v>
+        <v>0.9532538750929158</v>
       </c>
       <c r="W17" t="n">
-        <v>0.6559708435980589</v>
+        <v>0.6493343097212094</v>
       </c>
       <c r="X17" t="n">
         <v>0.02962</v>
@@ -4950,7 +4950,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>2026-08-27T18:37:31.829046+00:00</t>
+          <t>2026-08-27T18:45:26.581197+00:00</t>
         </is>
       </c>
       <c r="AD17" t="inlineStr">
@@ -4981,10 +4981,10 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>109004898304</v>
+        <v>109127753728</v>
       </c>
       <c r="F18" t="n">
-        <v>306.125</v>
+        <v>306.4700012207031</v>
       </c>
       <c r="G18" t="n">
         <v>2512349952</v>
@@ -5011,22 +5011,22 @@
         <v>-0.07902000000000001</v>
       </c>
       <c r="R18" t="n">
-        <v>43.387627</v>
+        <v>43.436527</v>
       </c>
       <c r="S18" t="n">
-        <v>157.3278324064744</v>
+        <v>157.5051508376462</v>
       </c>
       <c r="T18" t="n">
-        <v>0.1591253045257879</v>
+        <v>0.1604316324800852</v>
       </c>
       <c r="U18" t="n">
-        <v>0.3420060461220662</v>
+        <v>0.3435184796838566</v>
       </c>
       <c r="V18" t="n">
-        <v>0.7818684200359087</v>
+        <v>0.7838765761160875</v>
       </c>
       <c r="W18" t="n">
-        <v>0.4915464422465927</v>
+        <v>0.4932274070267004</v>
       </c>
       <c r="X18" t="n">
         <v>0.00616</v>
@@ -5036,7 +5036,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>2026-08-27T18:37:33.081801+00:00</t>
+          <t>2026-08-27T18:45:27.298564+00:00</t>
         </is>
       </c>
       <c r="AD18" t="inlineStr">
@@ -5067,10 +5067,10 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2754499837952</v>
+        <v>2754662629376</v>
       </c>
       <c r="F19" t="n">
-        <v>255.3699035644531</v>
+        <v>255.3849945068359</v>
       </c>
       <c r="G19" t="n">
         <v>775680032768</v>
@@ -5100,25 +5100,25 @@
         <v>0.13689</v>
       </c>
       <c r="Q19" t="n">
-        <v>20.528128</v>
+        <v>20.52934</v>
       </c>
       <c r="R19" t="n">
-        <v>3.5510774</v>
+        <v>3.5512872</v>
       </c>
       <c r="S19" t="n">
-        <v>855.6672526842972</v>
+        <v>855.7178227691508</v>
       </c>
       <c r="T19" t="n">
-        <v>0.1061678198445026</v>
+        <v>0.1062331882164289</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.06799305268447764</v>
+        <v>-0.06793797625242359</v>
       </c>
       <c r="V19" t="n">
-        <v>0.2123523751633796</v>
+        <v>0.2124240184525297</v>
       </c>
       <c r="W19" t="n">
-        <v>0.1145683877735753</v>
+        <v>0.11463425257239</v>
       </c>
       <c r="X19" t="n">
         <v>0.0887</v>
@@ -5128,7 +5128,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>2026-08-27T18:37:27.157206+00:00</t>
+          <t>2026-08-27T18:45:22.406672+00:00</t>
         </is>
       </c>
       <c r="AD19" t="inlineStr">
@@ -5140,87 +5140,84 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>VRT</t>
+          <t>ACMR</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Vertiv Holdings Co</t>
+          <t>ACM Research, Inc.</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Electrical Equipment &amp; Parts</t>
+          <t>Semiconductor Equipment &amp; Materials</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103082508288</v>
+        <v>5545120768</v>
       </c>
       <c r="F20" t="n">
-        <v>267.7550048828125</v>
+        <v>79.61499786376953</v>
       </c>
       <c r="G20" t="n">
-        <v>11479600128</v>
+        <v>1037772032</v>
       </c>
       <c r="H20" t="n">
-        <v>0.241</v>
+        <v>0.36</v>
       </c>
       <c r="I20" t="n">
-        <v>4.43</v>
+        <v>2.12</v>
       </c>
       <c r="J20" t="n">
-        <v>0.53</v>
+        <v>1.806</v>
       </c>
       <c r="K20" t="n">
-        <v>2696537600</v>
+        <v>-186610256</v>
       </c>
       <c r="M20" t="n">
-        <v>3110599936</v>
+        <v>1439374976</v>
       </c>
       <c r="N20" t="n">
-        <v>3338200064</v>
+        <v>349319008</v>
       </c>
       <c r="O20" t="n">
-        <v>0.38039002</v>
+        <v>0.43835</v>
       </c>
       <c r="P20" t="n">
-        <v>0.20362</v>
+        <v>0.16982001</v>
       </c>
       <c r="Q20" t="n">
-        <v>60.44131</v>
+        <v>37.554245</v>
       </c>
       <c r="R20" t="n">
-        <v>8.979626</v>
-      </c>
-      <c r="S20" t="n">
-        <v>38.22772888017582</v>
+        <v>5.3432937</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.00669607023345109</v>
+        <v>0.1054568394156448</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1475882228812304</v>
+        <v>-0.1426341014379182</v>
       </c>
       <c r="V20" t="n">
-        <v>0.02168065134762154</v>
+        <v>0.1627719650119783</v>
       </c>
       <c r="W20" t="n">
-        <v>1.072925239821928</v>
+        <v>1.785689225902756</v>
       </c>
       <c r="X20" t="n">
-        <v>0.00269</v>
+        <v>0.12675999</v>
       </c>
       <c r="Y20" t="n">
-        <v>0.84448</v>
+        <v>0.78055</v>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>2026-08-27T18:37:30.859676+00:00</t>
+          <t>2026-08-27T18:45:19.863427+00:00</t>
         </is>
       </c>
       <c r="AD20" t="inlineStr">
@@ -5232,84 +5229,87 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ACMR</t>
+          <t>VRT</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>ACM Research, Inc.</t>
+          <t>Vertiv Holdings Co</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Semiconductor Equipment &amp; Materials</t>
+          <t>Electrical Equipment &amp; Parts</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5539201024</v>
+        <v>102930432000</v>
       </c>
       <c r="F21" t="n">
-        <v>79.52999877929688</v>
+        <v>267.3599853515625</v>
       </c>
       <c r="G21" t="n">
-        <v>1037772032</v>
+        <v>11479600128</v>
       </c>
       <c r="H21" t="n">
-        <v>0.36</v>
+        <v>0.241</v>
       </c>
       <c r="I21" t="n">
-        <v>2.12</v>
+        <v>4.43</v>
       </c>
       <c r="J21" t="n">
-        <v>1.806</v>
+        <v>0.53</v>
       </c>
       <c r="K21" t="n">
-        <v>-186610256</v>
+        <v>2696537600</v>
       </c>
       <c r="M21" t="n">
-        <v>1439374976</v>
+        <v>3110599936</v>
       </c>
       <c r="N21" t="n">
-        <v>349319008</v>
+        <v>3338200064</v>
       </c>
       <c r="O21" t="n">
-        <v>0.43835</v>
+        <v>0.38039002</v>
       </c>
       <c r="P21" t="n">
-        <v>0.16982001</v>
+        <v>0.20362</v>
       </c>
       <c r="Q21" t="n">
-        <v>37.514153</v>
+        <v>60.352142</v>
       </c>
       <c r="R21" t="n">
-        <v>5.3375893</v>
+        <v>8.966378000000001</v>
+      </c>
+      <c r="S21" t="n">
+        <v>38.17133200738606</v>
       </c>
       <c r="T21" t="n">
-        <v>0.1042766243582363</v>
+        <v>-0.008161493645039264</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1435494480232506</v>
+        <v>-0.1488457877987446</v>
       </c>
       <c r="V21" t="n">
-        <v>0.1615305588055045</v>
+        <v>0.02017336369800637</v>
       </c>
       <c r="W21" t="n">
-        <v>1.782715150160993</v>
+        <v>1.069867048783038</v>
       </c>
       <c r="X21" t="n">
-        <v>0.12675999</v>
+        <v>0.00269</v>
       </c>
       <c r="Y21" t="n">
-        <v>0.78055</v>
+        <v>0.84448</v>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>2026-08-27T18:37:24.493957+00:00</t>
+          <t>2026-08-27T18:45:25.733666+00:00</t>
         </is>
       </c>
       <c r="AD21" t="inlineStr">
@@ -5321,12 +5321,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>ASML</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Microsoft Corporation</t>
+          <t>ASML Holding N.V.</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -5336,72 +5336,72 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Software - Infrastructure</t>
+          <t>Semiconductor Equipment &amp; Materials</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>3734826647552</v>
+        <v>662441951232</v>
       </c>
       <c r="F22" t="n">
-        <v>502.9700012207031</v>
+        <v>1724.660034179688</v>
       </c>
       <c r="G22" t="n">
-        <v>331839012864</v>
+        <v>35327500288</v>
       </c>
       <c r="H22" t="n">
-        <v>0.177</v>
+        <v>0.213</v>
       </c>
       <c r="I22" t="n">
-        <v>17.97</v>
+        <v>29.68</v>
       </c>
       <c r="J22" t="n">
-        <v>0.317</v>
+        <v>0.285</v>
       </c>
       <c r="K22" t="n">
-        <v>16545500160</v>
+        <v>8437675008</v>
       </c>
       <c r="M22" t="n">
-        <v>76842999808</v>
+        <v>7581499904</v>
       </c>
       <c r="N22" t="n">
-        <v>128812998656</v>
+        <v>1984400000</v>
       </c>
       <c r="O22" t="n">
-        <v>0.67944</v>
+        <v>0.5273300400000001</v>
       </c>
       <c r="P22" t="n">
-        <v>0.45111</v>
+        <v>0.37057</v>
       </c>
       <c r="Q22" t="n">
-        <v>27.989428</v>
+        <v>58.10849</v>
       </c>
       <c r="R22" t="n">
-        <v>11.254935</v>
+        <v>18.751453</v>
       </c>
       <c r="S22" t="n">
-        <v>225.7306585739382</v>
+        <v>78.51001023432639</v>
       </c>
       <c r="T22" t="n">
-        <v>0.2810902603436249</v>
+        <v>0.08952278175497774</v>
       </c>
       <c r="U22" t="n">
-        <v>0.1801608098003926</v>
+        <v>0.07542833376606484</v>
       </c>
       <c r="V22" t="n">
-        <v>0.2606297641273871</v>
+        <v>0.1337379940087302</v>
       </c>
       <c r="W22" t="n">
-        <v>0.0007268045960038272</v>
+        <v>1.254571065214441</v>
       </c>
       <c r="X22" t="n">
-        <v>0.00090000004</v>
+        <v>0.00016000001</v>
       </c>
       <c r="Y22" t="n">
-        <v>0.75881</v>
+        <v>0.20384</v>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>2026-08-27T18:37:26.445383+00:00</t>
+          <t>2026-08-27T18:45:23.986635+00:00</t>
         </is>
       </c>
       <c r="AD22" t="inlineStr">
@@ -5413,12 +5413,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ASML</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>ASML Holding N.V.</t>
+          <t>Microsoft Corporation</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -5428,72 +5428,72 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Semiconductor Equipment &amp; Materials</t>
+          <t>Software - Infrastructure</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>662036676608</v>
+        <v>3729851416576</v>
       </c>
       <c r="F23" t="n">
-        <v>1723.60498046875</v>
+        <v>502.3200073242188</v>
       </c>
       <c r="G23" t="n">
-        <v>35327500288</v>
+        <v>331839012864</v>
       </c>
       <c r="H23" t="n">
-        <v>0.213</v>
+        <v>0.177</v>
       </c>
       <c r="I23" t="n">
-        <v>29.68</v>
+        <v>17.97</v>
       </c>
       <c r="J23" t="n">
-        <v>0.285</v>
+        <v>0.317</v>
       </c>
       <c r="K23" t="n">
-        <v>8437675008</v>
+        <v>16545500160</v>
       </c>
       <c r="M23" t="n">
-        <v>7581499904</v>
+        <v>76842999808</v>
       </c>
       <c r="N23" t="n">
-        <v>1984400000</v>
+        <v>128812998656</v>
       </c>
       <c r="O23" t="n">
-        <v>0.5273300400000001</v>
+        <v>0.67944</v>
       </c>
       <c r="P23" t="n">
-        <v>0.37057</v>
+        <v>0.45111</v>
       </c>
       <c r="Q23" t="n">
-        <v>58.072945</v>
+        <v>27.952143</v>
       </c>
       <c r="R23" t="n">
-        <v>18.73998</v>
+        <v>11.240391</v>
       </c>
       <c r="S23" t="n">
-        <v>78.46197868255226</v>
+        <v>225.4299586296701</v>
       </c>
       <c r="T23" t="n">
-        <v>0.08885627065640733</v>
+        <v>0.2794346927192179</v>
       </c>
       <c r="U23" t="n">
-        <v>0.07477044488831464</v>
+        <v>0.1786356744615483</v>
       </c>
       <c r="V23" t="n">
-        <v>0.1330444344351887</v>
+        <v>0.2590006378367125</v>
       </c>
       <c r="W23" t="n">
-        <v>1.253191840601018</v>
+        <v>-0.0005665068060966005</v>
       </c>
       <c r="X23" t="n">
-        <v>0.00016000001</v>
+        <v>0.00090000004</v>
       </c>
       <c r="Y23" t="n">
-        <v>0.20384</v>
+        <v>0.75881</v>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>2026-08-27T18:37:28.763120+00:00</t>
+          <t>2026-08-27T18:45:21.737734+00:00</t>
         </is>
       </c>
       <c r="AD23" t="inlineStr">
@@ -5524,10 +5524,10 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>315046395904</v>
+        <v>314508509184</v>
       </c>
       <c r="F24" t="n">
-        <v>386.5599975585938</v>
+        <v>385.8999938964844</v>
       </c>
       <c r="G24" t="n">
         <v>10606499840</v>
@@ -5554,25 +5554,25 @@
         <v>-0.02465</v>
       </c>
       <c r="Q24" t="n">
-        <v>336.13913</v>
+        <v>335.56522</v>
       </c>
       <c r="R24" t="n">
-        <v>29.703144</v>
+        <v>29.652431</v>
       </c>
       <c r="S24" t="n">
-        <v>88.01715013101906</v>
+        <v>87.86687621326206</v>
       </c>
       <c r="T24" t="n">
-        <v>0.2117868262024882</v>
+        <v>0.2097178492052802</v>
       </c>
       <c r="U24" t="n">
-        <v>0.4996315088413608</v>
+        <v>0.4970710724436451</v>
       </c>
       <c r="V24" t="n">
-        <v>1.668876051728181</v>
+        <v>1.664319274050766</v>
       </c>
       <c r="W24" t="n">
-        <v>1.060444519487225</v>
+        <v>1.056926563834742</v>
       </c>
       <c r="X24" t="n">
         <v>0.0076</v>
@@ -5582,7 +5582,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>2026-08-27T18:37:26.063260+00:00</t>
+          <t>2026-08-27T18:45:21.379411+00:00</t>
         </is>
       </c>
       <c r="AD24" t="inlineStr">
@@ -5613,10 +5613,10 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>24694376448</v>
+        <v>24759066624</v>
       </c>
       <c r="F25" t="n">
-        <v>38.17499923706055</v>
+        <v>38.27500152587891</v>
       </c>
       <c r="G25" t="n">
         <v>39063072768</v>
@@ -5646,22 +5646,22 @@
         <v>0.13382</v>
       </c>
       <c r="Q25" t="n">
-        <v>11.710122</v>
+        <v>11.740798</v>
       </c>
       <c r="R25" t="n">
-        <v>0.6321667399999999</v>
+        <v>0.6338228</v>
       </c>
       <c r="T25" t="n">
-        <v>0.3418277052136116</v>
+        <v>0.3453427240584839</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.07566586096194849</v>
+        <v>-0.0732444979918343</v>
       </c>
       <c r="V25" t="n">
-        <v>0.1361607431757219</v>
+        <v>0.1391370019066676</v>
       </c>
       <c r="W25" t="n">
-        <v>-0.147117947529161</v>
+        <v>-0.144883758687151</v>
       </c>
       <c r="X25" t="n">
         <v>0.12878999</v>
@@ -5671,7 +5671,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>2026-08-27T18:37:31.457520+00:00</t>
+          <t>2026-08-27T18:45:26.101825+00:00</t>
         </is>
       </c>
       <c r="AD25" t="inlineStr">
@@ -5702,10 +5702,10 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>230554255360</v>
+        <v>229872025600</v>
       </c>
       <c r="F26" t="n">
-        <v>226.4199981689453</v>
+        <v>225.75</v>
       </c>
       <c r="G26" t="n">
         <v>5094199808</v>
@@ -5732,25 +5732,25 @@
         <v>-0.022079999</v>
       </c>
       <c r="Q26" t="n">
-        <v>3773.6667</v>
+        <v>3762.5</v>
       </c>
       <c r="R26" t="n">
-        <v>45.25819</v>
+        <v>45.124268</v>
       </c>
       <c r="S26" t="n">
-        <v>119.6835743266306</v>
+        <v>119.3294203941374</v>
       </c>
       <c r="T26" t="n">
-        <v>0.245434512476242</v>
+        <v>0.2417491540730601</v>
       </c>
       <c r="U26" t="n">
-        <v>0.3497466358804489</v>
+        <v>0.34575260804769</v>
       </c>
       <c r="V26" t="n">
-        <v>1.49285733605422</v>
+        <v>1.485480735647431</v>
       </c>
       <c r="W26" t="n">
-        <v>1.143063401406288</v>
+        <v>1.136721874304055</v>
       </c>
       <c r="X26" t="n">
         <v>0.01467</v>
@@ -5760,7 +5760,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>2026-08-27T18:37:25.691165+00:00</t>
+          <t>2026-08-27T18:45:21.016181+00:00</t>
         </is>
       </c>
       <c r="AD26" t="inlineStr">
@@ -5791,10 +5791,10 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>267800641536</v>
+        <v>267955519488</v>
       </c>
       <c r="F27" t="n">
-        <v>250.75</v>
+        <v>250.8950042724609</v>
       </c>
       <c r="G27" t="n">
         <v>5155999744</v>
@@ -5824,25 +5824,25 @@
         <v>0.07603</v>
       </c>
       <c r="Q27" t="n">
-        <v>255.86734</v>
+        <v>256.01532</v>
       </c>
       <c r="R27" t="n">
-        <v>51.939613</v>
+        <v>51.969654</v>
       </c>
       <c r="S27" t="n">
-        <v>200.6748954346921</v>
+        <v>200.7909523516751</v>
       </c>
       <c r="T27" t="n">
-        <v>0.02455664939095459</v>
+        <v>0.02514913230836213</v>
       </c>
       <c r="U27" t="n">
-        <v>-0.2520953016472502</v>
+        <v>-0.251662801640651</v>
       </c>
       <c r="V27" t="n">
-        <v>0.9033701954188191</v>
+        <v>0.9044708806049031</v>
       </c>
       <c r="W27" t="n">
-        <v>0.7826673785843672</v>
+        <v>0.7836982634747818</v>
       </c>
       <c r="X27" t="n">
         <v>0.0007</v>
@@ -5852,7 +5852,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>2026-08-27T18:37:29.132514+00:00</t>
+          <t>2026-08-27T18:45:24.266747+00:00</t>
         </is>
       </c>
       <c r="AD27" t="inlineStr">
@@ -5883,10 +5883,10 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>219531067392</v>
+        <v>219463663616</v>
       </c>
       <c r="F28" t="n">
-        <v>244.3000030517578</v>
+        <v>244.1999969482422</v>
       </c>
       <c r="G28" t="n">
         <v>8717100032</v>
@@ -5916,25 +5916,25 @@
         <v>0.14479999</v>
       </c>
       <c r="Q28" t="n">
-        <v>83.655815</v>
+        <v>83.630135</v>
       </c>
       <c r="R28" t="n">
-        <v>25.186535</v>
+        <v>25.176224</v>
       </c>
       <c r="S28" t="n">
-        <v>96.72249993683747</v>
+        <v>96.692802719959</v>
       </c>
       <c r="T28" t="n">
-        <v>0.4002407367597842</v>
+        <v>0.3996675373397356</v>
       </c>
       <c r="U28" t="n">
-        <v>0.1929906408350017</v>
+        <v>0.1925022808512515</v>
       </c>
       <c r="V28" t="n">
-        <v>2.021287596977853</v>
+        <v>2.020051094389128</v>
       </c>
       <c r="W28" t="n">
-        <v>2.273438836953542</v>
+        <v>2.272098829343672</v>
       </c>
       <c r="X28" t="n">
         <v>0.00494</v>
@@ -5944,7 +5944,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>2026-08-27T18:37:29.568626+00:00</t>
+          <t>2026-08-27T18:45:24.686675+00:00</t>
         </is>
       </c>
       <c r="AD28" t="inlineStr">
@@ -5975,10 +5975,10 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1450015064064</v>
+        <v>1450957602816</v>
       </c>
       <c r="F29" t="n">
-        <v>569.1900024414062</v>
+        <v>569.5599975585938</v>
       </c>
       <c r="G29" t="n">
         <v>228246994944</v>
@@ -6008,25 +6008,25 @@
         <v>0.34827</v>
       </c>
       <c r="Q29" t="n">
-        <v>21.430347</v>
+        <v>21.444277</v>
       </c>
       <c r="R29" t="n">
-        <v>6.3528333</v>
+        <v>6.3569627</v>
       </c>
       <c r="S29" t="n">
-        <v>67.27476506359467</v>
+        <v>67.31849500452812</v>
       </c>
       <c r="T29" t="n">
-        <v>-0.04081490335388405</v>
+        <v>-0.04019139661498172</v>
       </c>
       <c r="U29" t="n">
-        <v>-0.1032165449733257</v>
+        <v>-0.1026336016712451</v>
       </c>
       <c r="V29" t="n">
-        <v>-0.1277129162829321</v>
+        <v>-0.1271458965524789</v>
       </c>
       <c r="W29" t="n">
-        <v>-0.2359234124897758</v>
+        <v>-0.2354267963351629</v>
       </c>
       <c r="X29" t="n">
         <v>0.00148</v>
@@ -6036,7 +6036,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>2026-08-27T18:37:27.525567+00:00</t>
+          <t>2026-08-27T18:45:22.785172+00:00</t>
         </is>
       </c>
       <c r="AD29" t="inlineStr">
@@ -6067,10 +6067,10 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>142083653632</v>
+        <v>142052638720</v>
       </c>
       <c r="F30" t="n">
-        <v>137.4299926757812</v>
+        <v>137.3999938964844</v>
       </c>
       <c r="G30" t="n">
         <v>14732000256</v>
@@ -6100,25 +6100,25 @@
         <v>0.04063</v>
       </c>
       <c r="Q30" t="n">
-        <v>85.893745</v>
+        <v>85.87499</v>
       </c>
       <c r="R30" t="n">
-        <v>9.64456</v>
+        <v>9.642454000000001</v>
       </c>
       <c r="S30" t="n">
-        <v>27.59240767942086</v>
+        <v>27.58638463543114</v>
       </c>
       <c r="T30" t="n">
-        <v>0.2423611396088814</v>
+        <v>0.2420899519524717</v>
       </c>
       <c r="U30" t="n">
-        <v>0.2639564833326891</v>
+        <v>0.2636805817565766</v>
       </c>
       <c r="V30" t="n">
-        <v>0.3185262232521948</v>
+        <v>0.3182384099706954</v>
       </c>
       <c r="W30" t="n">
-        <v>-0.226165014639231</v>
+        <v>-0.2263339304958505</v>
       </c>
       <c r="X30" t="n">
         <v>0.00176</v>
@@ -6128,7 +6128,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>2026-08-27T18:37:33.457796+00:00</t>
+          <t>2026-08-27T18:45:27.674997+00:00</t>
         </is>
       </c>
       <c r="AD30" t="inlineStr">
@@ -6159,10 +6159,10 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>430904082432</v>
+        <v>431235334144</v>
       </c>
       <c r="F31" t="n">
-        <v>149.5950012207031</v>
+        <v>149.7100067138672</v>
       </c>
       <c r="G31" t="n">
         <v>67356999680</v>
@@ -6192,22 +6192,22 @@
         <v>0.36202</v>
       </c>
       <c r="Q31" t="n">
-        <v>25.615582</v>
+        <v>25.635275</v>
       </c>
       <c r="R31" t="n">
-        <v>6.397317</v>
+        <v>6.402235</v>
       </c>
       <c r="T31" t="n">
-        <v>0.2470406999199981</v>
+        <v>0.2479993986032407</v>
       </c>
       <c r="U31" t="n">
-        <v>-0.2630562665892729</v>
+        <v>-0.262489719734074</v>
       </c>
       <c r="V31" t="n">
-        <v>0.01859312630851995</v>
+        <v>0.0193761992980499</v>
       </c>
       <c r="W31" t="n">
-        <v>-0.3583815535820681</v>
+        <v>-0.3578883328275487</v>
       </c>
       <c r="X31" t="n">
         <v>0.40498</v>
@@ -6217,7 +6217,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>2026-08-27T18:37:27.950175+00:00</t>
+          <t>2026-08-27T18:45:23.181568+00:00</t>
         </is>
       </c>
       <c r="AD31" t="inlineStr">
@@ -6849,18 +6849,23 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>VRT</t>
+          <t>ACMR</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>100</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="C20" t="n">
-        <v>100</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
           <t>HIGH</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>price_to_fcf</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -6878,23 +6883,18 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ACMR</t>
+          <t>VRT</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>94.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="C21" t="n">
-        <v>94.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
           <t>HIGH</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>price_to_fcf</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -6912,7 +6912,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>ASML</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -6941,7 +6941,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ASML</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -7292,7 +7292,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>56.68</v>
+        <v>56.69</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/reports/investment_dashboard.xlsx
+++ b/reports/investment_dashboard.xlsx
@@ -534,7 +534,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>56.69</v>
+        <v>56.7</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>914.239990234375</v>
+        <v>916.1649780273438</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -586,7 +586,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>55.58</v>
+        <v>55.57</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>425.2799987792969</v>
+        <v>424.6199951171875</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>53.47</v>
+        <v>53.51</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>235.4750061035156</v>
+        <v>236.5500030517578</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -685,7 +685,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>52.9</v>
+        <v>52.89</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -693,7 +693,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>199.9700012207031</v>
+        <v>199.7100067138672</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>465.375</v>
+        <v>464.1300048828125</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -836,7 +836,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>50.93</v>
+        <v>50.85</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -844,7 +844,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>226.5599975585938</v>
+        <v>225.5700073242188</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>50.85</v>
+        <v>50.83</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>365.1449890136719</v>
+        <v>364.739990234375</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>47.69</v>
+        <v>47.65</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -943,7 +943,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>18.13999938964844</v>
+        <v>18.2450008392334</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -990,7 +990,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>471.7000122070312</v>
+        <v>471.1799926757812</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>46.73</v>
+        <v>46.74</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -1042,7 +1042,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>340.5599975585938</v>
+        <v>340.8099975585938</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>45.39</v>
+        <v>45.38</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -1089,7 +1089,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>475.25</v>
+        <v>474.7149963378906</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -1128,7 +1128,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>45.07</v>
+        <v>45.1</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>240.6450042724609</v>
+        <v>241.7700042724609</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>368.3500061035156</v>
+        <v>368.4400024414062</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>443.6000061035156</v>
+        <v>445.1400146484375</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1279,7 +1279,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>43.17</v>
+        <v>43.18</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -1287,7 +1287,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>330.5101013183594</v>
+        <v>330.9049987792969</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1339,7 +1339,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>306.4700012207031</v>
+        <v>306.3900146484375</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1391,7 +1391,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>255.3849945068359</v>
+        <v>255.3549957275391</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1430,7 +1430,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>42.45</v>
+        <v>42.44</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>79.61499786376953</v>
+        <v>79.55999755859375</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1482,7 +1482,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>42.43</v>
+        <v>42.44</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -1490,7 +1490,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>267.3599853515625</v>
+        <v>267.4024963378906</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1525,16 +1525,16 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>ASML</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>ASML Holding N.V.</t>
+          <t>Microsoft Corporation</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>42.33</v>
+        <v>42.37</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -1542,7 +1542,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1724.660034179688</v>
+        <v>503.3150024414062</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1557,7 +1557,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Earnings Fcf; Balance Sheet</t>
+          <t>Earnings Fcf</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1572,16 +1572,16 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>ASML</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Microsoft Corporation</t>
+          <t>ASML Holding N.V.</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>42.33</v>
+        <v>42.32</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>502.3200073242188</v>
+        <v>1723.364990234375</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Earnings Fcf</t>
+          <t>Earnings Fcf; Balance Sheet</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -1636,7 +1636,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>385.8999938964844</v>
+        <v>386.1400146484375</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1680,7 +1680,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>41.79</v>
+        <v>41.72</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>38.27500152587891</v>
+        <v>38.1150016784668</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1732,7 +1732,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>41</v>
+        <v>41.04</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -1740,7 +1740,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>225.75</v>
+        <v>226.5200042724609</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1792,7 +1792,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>250.8950042724609</v>
+        <v>251.0399932861328</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1836,7 +1836,7 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>39.89</v>
+        <v>39.87</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>244.1999969482422</v>
+        <v>243.8099975585938</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1888,7 +1888,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>39.57</v>
+        <v>39.56</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -1896,7 +1896,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>569.5599975585938</v>
+        <v>569.135009765625</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>36.38</v>
+        <v>36.41</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -1943,7 +1943,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>137.3999938964844</v>
+        <v>137.7649993896484</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1985,7 +1985,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>149.7100067138672</v>
+        <v>149.8500061035156</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -2131,13 +2131,13 @@
         <v>9.02</v>
       </c>
       <c r="F2" t="n">
-        <v>7.33</v>
+        <v>7.32</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>6.84</v>
+        <v>6.86</v>
       </c>
       <c r="I2" t="n">
         <v>3.5</v>
@@ -2149,7 +2149,7 @@
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>56.69</v>
+        <v>56.7</v>
       </c>
     </row>
     <row r="3">
@@ -2171,13 +2171,13 @@
         <v>8.84</v>
       </c>
       <c r="F3" t="n">
-        <v>8.640000000000001</v>
+        <v>8.65</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>5.41</v>
+        <v>5.39</v>
       </c>
       <c r="I3" t="n">
         <v>2.69</v>
@@ -2189,7 +2189,7 @@
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>55.58</v>
+        <v>55.57</v>
       </c>
     </row>
     <row r="4">
@@ -2211,13 +2211,13 @@
         <v>9.91</v>
       </c>
       <c r="F4" t="n">
-        <v>2.37</v>
+        <v>2.36</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>7.65</v>
+        <v>7.7</v>
       </c>
       <c r="I4" t="n">
         <v>3.54</v>
@@ -2229,7 +2229,7 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>53.47</v>
+        <v>53.51</v>
       </c>
     </row>
     <row r="5">
@@ -2257,7 +2257,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>8.48</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="I5" t="n">
         <v>3.63</v>
@@ -2269,7 +2269,7 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>52.9</v>
+        <v>52.89</v>
       </c>
     </row>
     <row r="6">
@@ -2331,13 +2331,13 @@
         <v>6.33</v>
       </c>
       <c r="F7" t="n">
-        <v>5.76</v>
+        <v>5.77</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>9.029999999999999</v>
+        <v>9.02</v>
       </c>
       <c r="I7" t="n">
         <v>3.54</v>
@@ -2371,13 +2371,13 @@
         <v>9.029999999999999</v>
       </c>
       <c r="F8" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>5.54</v>
+        <v>5.44</v>
       </c>
       <c r="I8" t="n">
         <v>3.44</v>
@@ -2389,7 +2389,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>50.93</v>
+        <v>50.85</v>
       </c>
     </row>
     <row r="9">
@@ -2417,7 +2417,7 @@
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>5.27</v>
+        <v>5.25</v>
       </c>
       <c r="I9" t="n">
         <v>3.75</v>
@@ -2429,7 +2429,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>50.85</v>
+        <v>50.83</v>
       </c>
     </row>
     <row r="10">
@@ -2451,7 +2451,7 @@
         <v>9.699999999999999</v>
       </c>
       <c r="F10" t="n">
-        <v>6.56</v>
+        <v>6.52</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -2469,7 +2469,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>47.69</v>
+        <v>47.65</v>
       </c>
     </row>
     <row r="11">
@@ -2491,13 +2491,13 @@
         <v>8.77</v>
       </c>
       <c r="F11" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>6.13</v>
+        <v>6.12</v>
       </c>
       <c r="I11" t="n">
         <v>3.45</v>
@@ -2537,7 +2537,7 @@
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>4.47</v>
+        <v>4.48</v>
       </c>
       <c r="I12" t="n">
         <v>3.53</v>
@@ -2549,7 +2549,7 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>46.73</v>
+        <v>46.74</v>
       </c>
     </row>
     <row r="13">
@@ -2571,13 +2571,13 @@
         <v>7.78</v>
       </c>
       <c r="F13" t="n">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>5.74</v>
+        <v>5.72</v>
       </c>
       <c r="I13" t="n">
         <v>3.58</v>
@@ -2589,7 +2589,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>45.39</v>
+        <v>45.38</v>
       </c>
     </row>
     <row r="14">
@@ -2611,13 +2611,13 @@
         <v>8.98</v>
       </c>
       <c r="F14" t="n">
-        <v>0.82</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>6.49</v>
+        <v>6.53</v>
       </c>
       <c r="I14" t="n">
         <v>3.67</v>
@@ -2629,7 +2629,7 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>45.07</v>
+        <v>45.1</v>
       </c>
     </row>
     <row r="15">
@@ -2691,13 +2691,13 @@
         <v>9.880000000000001</v>
       </c>
       <c r="F16" t="n">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>9.83</v>
+        <v>9.85</v>
       </c>
       <c r="I16" t="n">
         <v>3.73</v>
@@ -2737,7 +2737,7 @@
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>9.109999999999999</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="I17" t="n">
         <v>3.56</v>
@@ -2749,7 +2749,7 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>43.17</v>
+        <v>43.18</v>
       </c>
     </row>
     <row r="18">
@@ -2857,7 +2857,7 @@
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>5.12</v>
+        <v>5.11</v>
       </c>
       <c r="I20" t="n">
         <v>3.63</v>
@@ -2869,7 +2869,7 @@
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>42.45</v>
+        <v>42.44</v>
       </c>
     </row>
     <row r="21">
@@ -2897,7 +2897,7 @@
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>3.92</v>
+        <v>3.93</v>
       </c>
       <c r="I21" t="n">
         <v>3.56</v>
@@ -2909,38 +2909,38 @@
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>42.43</v>
+        <v>42.44</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ASML</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>9.859999999999999</v>
+        <v>8.51</v>
       </c>
       <c r="C22" t="n">
-        <v>14.28</v>
+        <v>14.63</v>
       </c>
       <c r="D22" t="n">
         <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>8.960000000000001</v>
+        <v>6.87</v>
       </c>
       <c r="F22" t="n">
-        <v>0.57</v>
+        <v>2.88</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>5.9</v>
+        <v>6.03</v>
       </c>
       <c r="I22" t="n">
-        <v>2.76</v>
+        <v>3.45</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2949,38 +2949,38 @@
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>42.33</v>
+        <v>42.37</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>ASML</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>8.51</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="C23" t="n">
-        <v>14.63</v>
+        <v>14.28</v>
       </c>
       <c r="D23" t="n">
         <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>6.87</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="F23" t="n">
-        <v>2.89</v>
+        <v>0.57</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>5.98</v>
+        <v>5.89</v>
       </c>
       <c r="I23" t="n">
-        <v>3.45</v>
+        <v>2.76</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2989,7 +2989,7 @@
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>42.33</v>
+        <v>42.32</v>
       </c>
     </row>
     <row r="24">
@@ -3051,13 +3051,13 @@
         <v>2.23</v>
       </c>
       <c r="F25" t="n">
-        <v>9.85</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>3.94</v>
+        <v>3.86</v>
       </c>
       <c r="I25" t="n">
         <v>3.54</v>
@@ -3069,7 +3069,7 @@
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>41.79</v>
+        <v>41.72</v>
       </c>
     </row>
     <row r="26">
@@ -3097,7 +3097,7 @@
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>9.029999999999999</v>
+        <v>9.07</v>
       </c>
       <c r="I26" t="n">
         <v>3.48</v>
@@ -3109,7 +3109,7 @@
         <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>41</v>
+        <v>41.04</v>
       </c>
     </row>
     <row r="27">
@@ -3177,7 +3177,7 @@
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>9.06</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="I28" t="n">
         <v>3.53</v>
@@ -3189,7 +3189,7 @@
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>39.89</v>
+        <v>39.87</v>
       </c>
     </row>
     <row r="29">
@@ -3217,7 +3217,7 @@
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>0.82</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="I29" t="n">
         <v>3.49</v>
@@ -3229,7 +3229,7 @@
         <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>39.57</v>
+        <v>39.56</v>
       </c>
     </row>
     <row r="30">
@@ -3251,13 +3251,13 @@
         <v>6.78</v>
       </c>
       <c r="F30" t="n">
-        <v>3.68</v>
+        <v>3.66</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>5.79</v>
+        <v>5.84</v>
       </c>
       <c r="I30" t="n">
         <v>3.57</v>
@@ -3269,7 +3269,7 @@
         <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>36.38</v>
+        <v>36.41</v>
       </c>
     </row>
     <row r="31">
@@ -3291,13 +3291,13 @@
         <v>0.8</v>
       </c>
       <c r="F31" t="n">
-        <v>6.38</v>
+        <v>6.37</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>2.58</v>
+        <v>2.59</v>
       </c>
       <c r="I31" t="n">
         <v>3.58</v>
@@ -3347,9 +3347,9 @@
     <col width="16" customWidth="1" min="18" max="18"/>
     <col width="19" customWidth="1" min="19" max="19"/>
     <col width="23" customWidth="1" min="20" max="20"/>
-    <col width="22" customWidth="1" min="21" max="21"/>
+    <col width="23" customWidth="1" min="21" max="21"/>
     <col width="21" customWidth="1" min="22" max="22"/>
-    <col width="24" customWidth="1" min="23" max="23"/>
+    <col width="22" customWidth="1" min="23" max="23"/>
     <col width="18" customWidth="1" min="24" max="24"/>
     <col width="24" customWidth="1" min="25" max="25"/>
     <col width="17" customWidth="1" min="26" max="26"/>
@@ -3533,7 +3533,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>914.239990234375</v>
+        <v>916.1649780273438</v>
       </c>
       <c r="G2" t="n">
         <v>90273996800</v>
@@ -3563,19 +3563,19 @@
         <v>0.80370003</v>
       </c>
       <c r="Q2" t="n">
-        <v>20.683485</v>
+        <v>20.727827</v>
       </c>
       <c r="T2" t="n">
-        <v>0.114206619613668</v>
+        <v>0.1165526492825861</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.00989627279412375</v>
+        <v>-0.007811549298102127</v>
       </c>
       <c r="V2" t="n">
-        <v>1.132318742540611</v>
+        <v>1.136808469082825</v>
       </c>
       <c r="W2" t="n">
-        <v>6.77670809960623</v>
+        <v>6.793081924800167</v>
       </c>
       <c r="X2" t="n">
         <v>0.00238</v>
@@ -3585,7 +3585,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>2026-08-27T18:45:19.530064+00:00</t>
+          <t>2026-08-27T18:56:27.637791+00:00</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
@@ -3616,10 +3616,10 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2205651828736</v>
+        <v>2202280656896</v>
       </c>
       <c r="F3" t="n">
-        <v>425.2799987792969</v>
+        <v>424.6199951171875</v>
       </c>
       <c r="G3" t="n">
         <v>4440492343296</v>
@@ -3649,25 +3649,25 @@
         <v>0.60344005</v>
       </c>
       <c r="Q3" t="n">
-        <v>31.7129</v>
+        <v>31.664429</v>
       </c>
       <c r="R3" t="n">
-        <v>0.49671334</v>
+        <v>0.49595416</v>
       </c>
       <c r="S3" t="n">
-        <v>3.018025883467007</v>
+        <v>3.013413059385627</v>
       </c>
       <c r="T3" t="n">
-        <v>0.08404068574821077</v>
+        <v>0.08235833335796672</v>
       </c>
       <c r="U3" t="n">
-        <v>0.003332784948973266</v>
+        <v>0.001775685357453538</v>
       </c>
       <c r="V3" t="n">
-        <v>0.102512326900444</v>
+        <v>0.1008013078650705</v>
       </c>
       <c r="W3" t="n">
-        <v>0.7969132148648814</v>
+        <v>0.7941245360986389</v>
       </c>
       <c r="X3" t="n">
         <v>0.00013</v>
@@ -3677,7 +3677,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>2026-08-27T18:45:23.593836+00:00</t>
+          <t>2026-08-27T18:56:32.637696+00:00</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
@@ -3708,10 +3708,10 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>44253917184</v>
+        <v>44455948288</v>
       </c>
       <c r="F4" t="n">
-        <v>235.4750061035156</v>
+        <v>236.5500030517578</v>
       </c>
       <c r="G4" t="n">
         <v>1335116032</v>
@@ -3741,25 +3741,25 @@
         <v>0.35661998</v>
       </c>
       <c r="Q4" t="n">
-        <v>93.81474</v>
+        <v>94.24303</v>
       </c>
       <c r="R4" t="n">
-        <v>33.146122</v>
+        <v>33.297443</v>
       </c>
       <c r="S4" t="n">
-        <v>176.4439001602041</v>
+        <v>177.2494142979745</v>
       </c>
       <c r="T4" t="n">
-        <v>0.2246463885918728</v>
+        <v>0.230237177831871</v>
       </c>
       <c r="U4" t="n">
-        <v>0.05902855695848119</v>
+        <v>0.0638632631367293</v>
       </c>
       <c r="V4" t="n">
-        <v>0.9072979738352427</v>
+        <v>0.9160052227921025</v>
       </c>
       <c r="W4" t="n">
-        <v>0.918642545936283</v>
+        <v>0.9274015854444608</v>
       </c>
       <c r="X4" t="n">
         <v>0.09436</v>
@@ -3769,7 +3769,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>2026-08-27T18:45:20.246622+00:00</t>
+          <t>2026-08-27T18:56:28.519501+00:00</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
@@ -3800,10 +3800,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>252207104000</v>
+        <v>251879194624</v>
       </c>
       <c r="F5" t="n">
-        <v>199.9700012207031</v>
+        <v>199.7100067138672</v>
       </c>
       <c r="G5" t="n">
         <v>10540800000</v>
@@ -3833,25 +3833,25 @@
         <v>0.45393002</v>
       </c>
       <c r="Q5" t="n">
-        <v>63.281643</v>
+        <v>63.199368</v>
       </c>
       <c r="R5" t="n">
-        <v>23.926752</v>
+        <v>23.895643</v>
       </c>
       <c r="S5" t="n">
-        <v>64.80953076071981</v>
+        <v>64.72526805576999</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1783041265083125</v>
+        <v>0.1767721337173731</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2878855910237794</v>
+        <v>0.2862111239684446</v>
       </c>
       <c r="V5" t="n">
-        <v>0.5047784042376926</v>
+        <v>0.5028219401844902</v>
       </c>
       <c r="W5" t="n">
-        <v>0.5004876927285065</v>
+        <v>0.4985368073191807</v>
       </c>
       <c r="X5" t="n">
         <v>0.17247999</v>
@@ -3861,7 +3861,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>2026-08-27T18:45:25.062145+00:00</t>
+          <t>2026-08-27T18:56:34.461249+00:00</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
@@ -3892,7 +3892,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>446560337920</v>
+        <v>446608408576</v>
       </c>
       <c r="F6" t="n">
         <v>185.8500061035156</v>
@@ -3925,13 +3925,13 @@
         <v>0.47120997</v>
       </c>
       <c r="Q6" t="n">
-        <v>158.82907</v>
+        <v>158.84616</v>
       </c>
       <c r="R6" t="n">
         <v>72.54917</v>
       </c>
       <c r="S6" t="n">
-        <v>206.8266429151902</v>
+        <v>206.848907078751</v>
       </c>
       <c r="T6" t="n">
         <v>0.5044929000247294</v>
@@ -3953,7 +3953,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>2026-08-27T18:45:18.076344+00:00</t>
+          <t>2026-08-27T18:56:25.788709+00:00</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr">
@@ -3984,10 +3984,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>300698533888</v>
+        <v>299894079488</v>
       </c>
       <c r="F7" t="n">
-        <v>465.375</v>
+        <v>464.1300048828125</v>
       </c>
       <c r="G7" t="n">
         <v>134001999872</v>
@@ -4017,25 +4017,25 @@
         <v>0.08857000600000001</v>
       </c>
       <c r="Q7" t="n">
-        <v>37.022675</v>
+        <v>36.92363</v>
       </c>
       <c r="R7" t="n">
-        <v>2.2439854</v>
+        <v>2.237982</v>
       </c>
       <c r="S7" t="n">
-        <v>55.33522783429633</v>
+        <v>55.18719030670771</v>
       </c>
       <c r="T7" t="n">
-        <v>0.1868783288851557</v>
+        <v>0.1837031309820503</v>
       </c>
       <c r="U7" t="n">
-        <v>0.4702539685141325</v>
+        <v>0.4663206695362638</v>
       </c>
       <c r="V7" t="n">
-        <v>2.786737325375744</v>
+        <v>2.776606851069723</v>
       </c>
       <c r="W7" t="n">
-        <v>2.557021442207762</v>
+        <v>2.547505515638265</v>
       </c>
       <c r="X7" t="n">
         <v>0.07491</v>
@@ -4045,7 +4045,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>2026-08-27T18:45:25.392621+00:00</t>
+          <t>2026-08-27T18:56:34.924336+00:00</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr">
@@ -4076,10 +4076,10 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5486782971904</v>
+        <v>5462804135936</v>
       </c>
       <c r="F8" t="n">
-        <v>226.5599975585938</v>
+        <v>225.5700073242188</v>
       </c>
       <c r="G8" t="n">
         <v>253491003392</v>
@@ -4109,25 +4109,25 @@
         <v>0.65596</v>
       </c>
       <c r="Q8" t="n">
-        <v>34.743866</v>
+        <v>34.592022</v>
       </c>
       <c r="R8" t="n">
-        <v>21.647749</v>
+        <v>21.553156</v>
       </c>
       <c r="S8" t="n">
-        <v>118.413285729225</v>
+        <v>117.8957852613784</v>
       </c>
       <c r="T8" t="n">
-        <v>0.1499924058458491</v>
+        <v>0.1449673296467799</v>
       </c>
       <c r="U8" t="n">
-        <v>0.05868870885467992</v>
+        <v>0.05406259879860897</v>
       </c>
       <c r="V8" t="n">
-        <v>0.1599321813410879</v>
+        <v>0.1548636716993186</v>
       </c>
       <c r="W8" t="n">
-        <v>0.2492386526516157</v>
+        <v>0.2437800087114501</v>
       </c>
       <c r="X8" t="n">
         <v>0.03991</v>
@@ -4137,7 +4137,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>2026-08-27T18:45:17.679154+00:00</t>
+          <t>2026-08-27T18:56:25.382433+00:00</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr">
@@ -4168,10 +4168,10 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>57087041536</v>
+        <v>57023725568</v>
       </c>
       <c r="F9" t="n">
-        <v>365.1449890136719</v>
+        <v>364.739990234375</v>
       </c>
       <c r="G9" t="n">
         <v>4464031232</v>
@@ -4201,25 +4201,25 @@
         <v>0.33161</v>
       </c>
       <c r="Q9" t="n">
-        <v>50.295452</v>
+        <v>50.239666</v>
       </c>
       <c r="R9" t="n">
-        <v>12.788226</v>
+        <v>12.774043</v>
       </c>
       <c r="S9" t="n">
-        <v>130.520093847279</v>
+        <v>130.3753323416371</v>
       </c>
       <c r="T9" t="n">
-        <v>0.1387649959898389</v>
+        <v>0.1375019403621889</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.04574677946433736</v>
+        <v>-0.0468051847583576</v>
       </c>
       <c r="V9" t="n">
-        <v>0.06552385125143756</v>
+        <v>0.06434203068138356</v>
       </c>
       <c r="W9" t="n">
-        <v>2.129154326543427</v>
+        <v>2.125683435960829</v>
       </c>
       <c r="X9" t="n">
         <v>0.00202</v>
@@ -4229,7 +4229,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>2026-08-27T18:45:20.642832+00:00</t>
+          <t>2026-08-27T18:56:28.985200+00:00</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr">
@@ -4260,10 +4260,10 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>9398701056</v>
+        <v>9453104128</v>
       </c>
       <c r="F10" t="n">
-        <v>18.13999938964844</v>
+        <v>18.2450008392334</v>
       </c>
       <c r="G10" t="n">
         <v>1672329984</v>
@@ -4290,25 +4290,25 @@
         <v>0.07274</v>
       </c>
       <c r="Q10" t="n">
-        <v>30.233332</v>
+        <v>30.408333</v>
       </c>
       <c r="R10" t="n">
-        <v>5.6201234</v>
+        <v>5.6526546</v>
       </c>
       <c r="S10" t="n">
-        <v>18.3728556852471</v>
+        <v>18.47920440138719</v>
       </c>
       <c r="T10" t="n">
-        <v>0.488105005256944</v>
+        <v>0.4967187421888086</v>
       </c>
       <c r="U10" t="n">
-        <v>0.5664939127083279</v>
+        <v>0.5755613954610703</v>
       </c>
       <c r="V10" t="n">
-        <v>0.8249497138257358</v>
+        <v>0.8355132403868617</v>
       </c>
       <c r="W10" t="n">
-        <v>0.6283661427821623</v>
+        <v>0.6377917663323356</v>
       </c>
       <c r="X10" t="n">
         <v>0.09236999999999999</v>
@@ -4318,7 +4318,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>2026-08-27T18:45:28.501244+00:00</t>
+          <t>2026-08-27T18:56:38.769857+00:00</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr">
@@ -4349,10 +4349,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>770038497280</v>
+        <v>769189543936</v>
       </c>
       <c r="F11" t="n">
-        <v>471.7000122070312</v>
+        <v>471.1799926757812</v>
       </c>
       <c r="G11" t="n">
         <v>41305001984</v>
@@ -4382,25 +4382,25 @@
         <v>0.1725</v>
       </c>
       <c r="Q11" t="n">
-        <v>119.72081</v>
+        <v>119.58883</v>
       </c>
       <c r="R11" t="n">
-        <v>18.642742</v>
+        <v>18.622189</v>
       </c>
       <c r="S11" t="n">
-        <v>87.09365242741228</v>
+        <v>86.99763327027846</v>
       </c>
       <c r="T11" t="n">
-        <v>0.03756987654148602</v>
+        <v>0.0364260211527323</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.08954045097142715</v>
+        <v>-0.09054417523611968</v>
       </c>
       <c r="V11" t="n">
-        <v>1.23702935996233</v>
+        <v>1.234563176097468</v>
       </c>
       <c r="W11" t="n">
-        <v>1.822353846861764</v>
+        <v>1.819242379644285</v>
       </c>
       <c r="X11" t="n">
         <v>0.00425</v>
@@ -4410,7 +4410,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>2026-08-27T18:45:18.431024+00:00</t>
+          <t>2026-08-27T18:56:26.264454+00:00</t>
         </is>
       </c>
       <c r="AD11" t="inlineStr">
@@ -4441,10 +4441,10 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4165026709504</v>
+        <v>4167717355520</v>
       </c>
       <c r="F12" t="n">
-        <v>340.5599975585938</v>
+        <v>340.8099975585938</v>
       </c>
       <c r="G12" t="n">
         <v>445865984000</v>
@@ -4474,25 +4474,25 @@
         <v>0.34033</v>
       </c>
       <c r="Q12" t="n">
-        <v>17.079237</v>
+        <v>17.090271</v>
       </c>
       <c r="R12" t="n">
-        <v>9.341431999999999</v>
+        <v>9.3482895</v>
       </c>
       <c r="S12" t="n">
-        <v>183.7646826865169</v>
+        <v>183.8833963817313</v>
       </c>
       <c r="T12" t="n">
-        <v>0.02052682352616264</v>
+        <v>0.02127597700193928</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.1265388341980044</v>
+        <v>-0.1258976394217068</v>
       </c>
       <c r="V12" t="n">
-        <v>0.0898156190495536</v>
+        <v>0.09061563639367964</v>
       </c>
       <c r="W12" t="n">
-        <v>0.6460938189707899</v>
+        <v>0.6473023133143463</v>
       </c>
       <c r="X12" t="n">
         <v>0.01596</v>
@@ -4502,7 +4502,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>2026-08-27T18:45:22.063586+00:00</t>
+          <t>2026-08-27T18:56:30.848036+00:00</t>
         </is>
       </c>
       <c r="AD12" t="inlineStr">
@@ -4533,10 +4533,10 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>377157189632</v>
+        <v>376732614656</v>
       </c>
       <c r="F13" t="n">
-        <v>475.25</v>
+        <v>474.7149963378906</v>
       </c>
       <c r="G13" t="n">
         <v>30837000192</v>
@@ -4566,25 +4566,25 @@
         <v>0.33736</v>
       </c>
       <c r="Q13" t="n">
-        <v>40.93454</v>
+        <v>40.88846</v>
       </c>
       <c r="R13" t="n">
-        <v>12.230671</v>
+        <v>12.216902</v>
       </c>
       <c r="S13" t="n">
-        <v>122.6377846206301</v>
+        <v>122.4997282985094</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.001472945179919583</v>
+        <v>-0.002597018049028565</v>
       </c>
       <c r="U13" t="n">
-        <v>0.05799281953159152</v>
+        <v>0.05680180420716252</v>
       </c>
       <c r="V13" t="n">
-        <v>0.2061011260512247</v>
+        <v>0.2047433806134304</v>
       </c>
       <c r="W13" t="n">
-        <v>1.906981219879931</v>
+        <v>1.903709011992588</v>
       </c>
       <c r="X13" t="n">
         <v>0.00331</v>
@@ -4594,7 +4594,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>2026-08-27T18:45:19.162964+00:00</t>
+          <t>2026-08-27T18:56:27.123584+00:00</t>
         </is>
       </c>
       <c r="AD13" t="inlineStr">
@@ -4625,10 +4625,10 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>86409609216</v>
+        <v>86813564928</v>
       </c>
       <c r="F14" t="n">
-        <v>240.6450042724609</v>
+        <v>241.7700042724609</v>
       </c>
       <c r="G14" t="n">
         <v>3966725120</v>
@@ -4658,25 +4658,25 @@
         <v>0.00666</v>
       </c>
       <c r="Q14" t="n">
-        <v>481.29</v>
+        <v>483.54</v>
       </c>
       <c r="R14" t="n">
-        <v>21.783613</v>
+        <v>21.88545</v>
       </c>
       <c r="S14" t="n">
-        <v>82.18432002594544</v>
+        <v>82.56852296138899</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.04079639832250637</v>
+        <v>-0.03631218284855697</v>
       </c>
       <c r="U14" t="n">
-        <v>0.06839370628484742</v>
+        <v>0.07338837851253088</v>
       </c>
       <c r="V14" t="n">
-        <v>1.181138405498751</v>
+        <v>1.191335088008761</v>
       </c>
       <c r="W14" t="n">
-        <v>0.8268049197404812</v>
+        <v>0.8353451158726277</v>
       </c>
       <c r="X14" t="n">
         <v>0.00619</v>
@@ -4686,7 +4686,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>2026-08-27T18:45:26.949964+00:00</t>
+          <t>2026-08-27T18:56:36.826917+00:00</t>
         </is>
       </c>
       <c r="AD14" t="inlineStr">
@@ -4717,10 +4717,10 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1752454791168</v>
+        <v>1752882872320</v>
       </c>
       <c r="F15" t="n">
-        <v>368.3500061035156</v>
+        <v>368.4400024414062</v>
       </c>
       <c r="G15" t="n">
         <v>75464998912</v>
@@ -4750,25 +4750,25 @@
         <v>0.48988</v>
       </c>
       <c r="Q15" t="n">
-        <v>61.289516</v>
+        <v>61.30449</v>
       </c>
       <c r="R15" t="n">
-        <v>23.222088</v>
+        <v>23.22776</v>
       </c>
       <c r="S15" t="n">
-        <v>64.39948368474967</v>
+        <v>64.41521487810364</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.03297366159418391</v>
+        <v>-0.0327373949248253</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.1351376120165505</v>
+        <v>-0.1349263063387762</v>
       </c>
       <c r="V15" t="n">
-        <v>0.1125361767339046</v>
+        <v>0.112807994787435</v>
       </c>
       <c r="W15" t="n">
-        <v>0.2357999792772172</v>
+        <v>0.2361019134991729</v>
       </c>
       <c r="X15" t="n">
         <v>0.01948</v>
@@ -4778,7 +4778,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>2026-08-27T18:45:18.802472+00:00</t>
+          <t>2026-08-27T18:56:26.677264+00:00</t>
         </is>
       </c>
       <c r="AD15" t="inlineStr">
@@ -4809,10 +4809,10 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>35679604736</v>
+        <v>35803467776</v>
       </c>
       <c r="F16" t="n">
-        <v>443.6000061035156</v>
+        <v>445.1400146484375</v>
       </c>
       <c r="G16" t="n">
         <v>2602398976</v>
@@ -4839,22 +4839,22 @@
         <v>-0.03607</v>
       </c>
       <c r="R16" t="n">
-        <v>13.710275</v>
+        <v>13.757871</v>
       </c>
       <c r="S16" t="n">
-        <v>68.93205980920878</v>
+        <v>69.17135995125368</v>
       </c>
       <c r="T16" t="n">
-        <v>0.4281115609964479</v>
+        <v>0.4330694148665468</v>
       </c>
       <c r="U16" t="n">
-        <v>0.3620732500602986</v>
+        <v>0.3668018443232413</v>
       </c>
       <c r="V16" t="n">
-        <v>0.4082987391867456</v>
+        <v>0.4131878105625566</v>
       </c>
       <c r="W16" t="n">
-        <v>0.5001690490054282</v>
+        <v>0.5053770587495865</v>
       </c>
       <c r="X16" t="n">
         <v>0.02641</v>
@@ -4864,7 +4864,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>2026-08-27T18:45:28.011182+00:00</t>
+          <t>2026-08-27T18:56:38.321002+00:00</t>
         </is>
       </c>
       <c r="AD16" t="inlineStr">
@@ -4895,10 +4895,10 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>114554798080</v>
+        <v>114691670016</v>
       </c>
       <c r="F17" t="n">
-        <v>330.5101013183594</v>
+        <v>330.9049987792969</v>
       </c>
       <c r="G17" t="n">
         <v>5032822784</v>
@@ -4925,22 +4925,22 @@
         <v>-0.22173999</v>
       </c>
       <c r="R17" t="n">
-        <v>22.76154</v>
+        <v>22.788736</v>
       </c>
       <c r="S17" t="n">
-        <v>65.85510072020054</v>
+        <v>65.93378546568587</v>
       </c>
       <c r="T17" t="n">
-        <v>0.2224815772518285</v>
+        <v>0.2239422130053923</v>
       </c>
       <c r="U17" t="n">
-        <v>0.3817312104308879</v>
+        <v>0.3833821195695821</v>
       </c>
       <c r="V17" t="n">
-        <v>0.9532538750929158</v>
+        <v>0.9555876464141666</v>
       </c>
       <c r="W17" t="n">
-        <v>0.6493343097212094</v>
+        <v>0.6513049542750309</v>
       </c>
       <c r="X17" t="n">
         <v>0.02962</v>
@@ -4950,7 +4950,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>2026-08-27T18:45:26.581197+00:00</t>
+          <t>2026-08-27T18:56:36.308126+00:00</t>
         </is>
       </c>
       <c r="AD17" t="inlineStr">
@@ -4981,10 +4981,10 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>109127753728</v>
+        <v>109099270144</v>
       </c>
       <c r="F18" t="n">
-        <v>306.4700012207031</v>
+        <v>306.3900146484375</v>
       </c>
       <c r="G18" t="n">
         <v>2512349952</v>
@@ -5011,22 +5011,22 @@
         <v>-0.07902000000000001</v>
       </c>
       <c r="R18" t="n">
-        <v>43.436527</v>
+        <v>43.42519</v>
       </c>
       <c r="S18" t="n">
-        <v>157.5051508376462</v>
+        <v>157.4640402031737</v>
       </c>
       <c r="T18" t="n">
-        <v>0.1604316324800852</v>
+        <v>0.1601287677681691</v>
       </c>
       <c r="U18" t="n">
-        <v>0.3435184796838566</v>
+        <v>0.3431678305582084</v>
       </c>
       <c r="V18" t="n">
-        <v>0.7838765761160875</v>
+        <v>0.7834109965419038</v>
       </c>
       <c r="W18" t="n">
-        <v>0.4932274070267004</v>
+        <v>0.4928376848959033</v>
       </c>
       <c r="X18" t="n">
         <v>0.00616</v>
@@ -5036,7 +5036,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>2026-08-27T18:45:27.298564+00:00</t>
+          <t>2026-08-27T18:56:37.445537+00:00</t>
         </is>
       </c>
       <c r="AD18" t="inlineStr">
@@ -5067,10 +5067,10 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2754662629376</v>
+        <v>2754338881536</v>
       </c>
       <c r="F19" t="n">
-        <v>255.3849945068359</v>
+        <v>255.3549957275391</v>
       </c>
       <c r="G19" t="n">
         <v>775680032768</v>
@@ -5100,25 +5100,25 @@
         <v>0.13689</v>
       </c>
       <c r="Q19" t="n">
-        <v>20.52934</v>
+        <v>20.52693</v>
       </c>
       <c r="R19" t="n">
-        <v>3.5512872</v>
+        <v>3.55087</v>
       </c>
       <c r="S19" t="n">
-        <v>855.7178227691508</v>
+        <v>855.6172526326061</v>
       </c>
       <c r="T19" t="n">
-        <v>0.1062331882164289</v>
+        <v>0.1061032446176351</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.06793797625242359</v>
+        <v>-0.06804746084839763</v>
       </c>
       <c r="V19" t="n">
-        <v>0.2124240184525297</v>
+        <v>0.2122816011557969</v>
       </c>
       <c r="W19" t="n">
-        <v>0.11463425257239</v>
+        <v>0.1145033221431992</v>
       </c>
       <c r="X19" t="n">
         <v>0.0887</v>
@@ -5128,7 +5128,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>2026-08-27T18:45:22.406672+00:00</t>
+          <t>2026-08-27T18:56:31.196787+00:00</t>
         </is>
       </c>
       <c r="AD19" t="inlineStr">
@@ -5159,10 +5159,10 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5545120768</v>
+        <v>5541289984</v>
       </c>
       <c r="F20" t="n">
-        <v>79.61499786376953</v>
+        <v>79.55999755859375</v>
       </c>
       <c r="G20" t="n">
         <v>1037772032</v>
@@ -5192,22 +5192,22 @@
         <v>0.16982001</v>
       </c>
       <c r="Q20" t="n">
-        <v>37.554245</v>
+        <v>37.5283</v>
       </c>
       <c r="R20" t="n">
-        <v>5.3432937</v>
+        <v>5.3396025</v>
       </c>
       <c r="T20" t="n">
-        <v>0.1054568394156448</v>
+        <v>0.1046931583862167</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1426341014379182</v>
+        <v>-0.1432263941884488</v>
       </c>
       <c r="V20" t="n">
-        <v>0.1627719650119783</v>
+        <v>0.1619686890634575</v>
       </c>
       <c r="W20" t="n">
-        <v>1.785689225902756</v>
+        <v>1.783764792546471</v>
       </c>
       <c r="X20" t="n">
         <v>0.12675999</v>
@@ -5217,7 +5217,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>2026-08-27T18:45:19.863427+00:00</t>
+          <t>2026-08-27T18:56:28.059677+00:00</t>
         </is>
       </c>
       <c r="AD20" t="inlineStr">
@@ -5248,10 +5248,10 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>102930432000</v>
+        <v>102946791424</v>
       </c>
       <c r="F21" t="n">
-        <v>267.3599853515625</v>
+        <v>267.4024963378906</v>
       </c>
       <c r="G21" t="n">
         <v>11479600128</v>
@@ -5281,25 +5281,25 @@
         <v>0.20362</v>
       </c>
       <c r="Q21" t="n">
-        <v>60.352142</v>
+        <v>60.36174</v>
       </c>
       <c r="R21" t="n">
-        <v>8.966378000000001</v>
+        <v>8.967803</v>
       </c>
       <c r="S21" t="n">
-        <v>38.17133200738606</v>
+        <v>38.1773988332297</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.008161493645039264</v>
+        <v>-0.008003788545198232</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1488457877987446</v>
+        <v>-0.1487104518956159</v>
       </c>
       <c r="V21" t="n">
-        <v>0.02017336369800637</v>
+        <v>0.0203355741195077</v>
       </c>
       <c r="W21" t="n">
-        <v>1.069867048783038</v>
+        <v>1.070195918884233</v>
       </c>
       <c r="X21" t="n">
         <v>0.00269</v>
@@ -5309,7 +5309,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>2026-08-27T18:45:25.733666+00:00</t>
+          <t>2026-08-27T18:56:35.394069+00:00</t>
         </is>
       </c>
       <c r="AD21" t="inlineStr">
@@ -5321,12 +5321,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ASML</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>ASML Holding N.V.</t>
+          <t>Microsoft Corporation</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -5336,72 +5336,72 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Semiconductor Equipment &amp; Materials</t>
+          <t>Software - Infrastructure</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>662441951232</v>
+        <v>3737425805312</v>
       </c>
       <c r="F22" t="n">
-        <v>1724.660034179688</v>
+        <v>503.3150024414062</v>
       </c>
       <c r="G22" t="n">
-        <v>35327500288</v>
+        <v>331839012864</v>
       </c>
       <c r="H22" t="n">
-        <v>0.213</v>
+        <v>0.177</v>
       </c>
       <c r="I22" t="n">
-        <v>29.68</v>
+        <v>17.97</v>
       </c>
       <c r="J22" t="n">
-        <v>0.285</v>
+        <v>0.317</v>
       </c>
       <c r="K22" t="n">
-        <v>8437675008</v>
+        <v>16545500160</v>
       </c>
       <c r="M22" t="n">
-        <v>7581499904</v>
+        <v>76842999808</v>
       </c>
       <c r="N22" t="n">
-        <v>1984400000</v>
+        <v>128812998656</v>
       </c>
       <c r="O22" t="n">
-        <v>0.5273300400000001</v>
+        <v>0.67944</v>
       </c>
       <c r="P22" t="n">
-        <v>0.37057</v>
+        <v>0.45111</v>
       </c>
       <c r="Q22" t="n">
-        <v>58.10849</v>
+        <v>28.008905</v>
       </c>
       <c r="R22" t="n">
-        <v>18.751453</v>
+        <v>11.262768</v>
       </c>
       <c r="S22" t="n">
-        <v>78.51001023432639</v>
+        <v>225.8877500933764</v>
       </c>
       <c r="T22" t="n">
-        <v>0.08952278175497774</v>
+        <v>0.2819689960586313</v>
       </c>
       <c r="U22" t="n">
-        <v>0.07542833376606484</v>
+        <v>0.1809703151764965</v>
       </c>
       <c r="V22" t="n">
-        <v>0.1337379940087302</v>
+        <v>0.2614944654145874</v>
       </c>
       <c r="W22" t="n">
-        <v>1.254571065214441</v>
+        <v>0.001413231158896355</v>
       </c>
       <c r="X22" t="n">
-        <v>0.00016000001</v>
+        <v>0.00090000004</v>
       </c>
       <c r="Y22" t="n">
-        <v>0.20384</v>
+        <v>0.75881</v>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>2026-08-27T18:45:23.986635+00:00</t>
+          <t>2026-08-27T18:56:30.330439+00:00</t>
         </is>
       </c>
       <c r="AD22" t="inlineStr">
@@ -5413,12 +5413,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>ASML</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Microsoft Corporation</t>
+          <t>ASML Holding N.V.</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -5428,72 +5428,72 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Software - Infrastructure</t>
+          <t>Semiconductor Equipment &amp; Materials</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>3729851416576</v>
+        <v>661944467456</v>
       </c>
       <c r="F23" t="n">
-        <v>502.3200073242188</v>
+        <v>1723.364990234375</v>
       </c>
       <c r="G23" t="n">
-        <v>331839012864</v>
+        <v>35327500288</v>
       </c>
       <c r="H23" t="n">
-        <v>0.177</v>
+        <v>0.213</v>
       </c>
       <c r="I23" t="n">
-        <v>17.97</v>
+        <v>29.68</v>
       </c>
       <c r="J23" t="n">
-        <v>0.317</v>
+        <v>0.285</v>
       </c>
       <c r="K23" t="n">
-        <v>16545500160</v>
+        <v>8437675008</v>
       </c>
       <c r="M23" t="n">
-        <v>76842999808</v>
+        <v>7581499904</v>
       </c>
       <c r="N23" t="n">
-        <v>128812998656</v>
+        <v>1984400000</v>
       </c>
       <c r="O23" t="n">
-        <v>0.67944</v>
+        <v>0.5273300400000001</v>
       </c>
       <c r="P23" t="n">
-        <v>0.45111</v>
+        <v>0.37057</v>
       </c>
       <c r="Q23" t="n">
-        <v>27.952143</v>
+        <v>58.064857</v>
       </c>
       <c r="R23" t="n">
-        <v>11.240391</v>
+        <v>18.737371</v>
       </c>
       <c r="S23" t="n">
-        <v>225.4299586296701</v>
+        <v>78.45105041713406</v>
       </c>
       <c r="T23" t="n">
-        <v>0.2794346927192179</v>
+        <v>0.08870466116667131</v>
       </c>
       <c r="U23" t="n">
-        <v>0.1786356744615483</v>
+        <v>0.07462079667199428</v>
       </c>
       <c r="V23" t="n">
-        <v>0.2590006378367125</v>
+        <v>0.1328866723014872</v>
       </c>
       <c r="W23" t="n">
-        <v>-0.0005665068060966005</v>
+        <v>1.252878112081987</v>
       </c>
       <c r="X23" t="n">
-        <v>0.00090000004</v>
+        <v>0.00016000001</v>
       </c>
       <c r="Y23" t="n">
-        <v>0.75881</v>
+        <v>0.20384</v>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>2026-08-27T18:45:21.737734+00:00</t>
+          <t>2026-08-27T18:56:33.129796+00:00</t>
         </is>
       </c>
       <c r="AD23" t="inlineStr">
@@ -5524,10 +5524,10 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>314508509184</v>
+        <v>314704101376</v>
       </c>
       <c r="F24" t="n">
-        <v>385.8999938964844</v>
+        <v>386.1400146484375</v>
       </c>
       <c r="G24" t="n">
         <v>10606499840</v>
@@ -5554,25 +5554,25 @@
         <v>-0.02465</v>
       </c>
       <c r="Q24" t="n">
-        <v>335.56522</v>
+        <v>335.77393</v>
       </c>
       <c r="R24" t="n">
-        <v>29.652431</v>
+        <v>29.670872</v>
       </c>
       <c r="S24" t="n">
-        <v>87.86687621326206</v>
+        <v>87.92152044202183</v>
       </c>
       <c r="T24" t="n">
-        <v>0.2097178492052802</v>
+        <v>0.2104702653556034</v>
       </c>
       <c r="U24" t="n">
-        <v>0.4970710724436451</v>
+        <v>0.4980022155641906</v>
       </c>
       <c r="V24" t="n">
-        <v>1.664319274050766</v>
+        <v>1.66597641819618</v>
       </c>
       <c r="W24" t="n">
-        <v>1.056926563834742</v>
+        <v>1.058205923949727</v>
       </c>
       <c r="X24" t="n">
         <v>0.0076</v>
@@ -5582,7 +5582,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>2026-08-27T18:45:21.379411+00:00</t>
+          <t>2026-08-27T18:56:29.858142+00:00</t>
         </is>
       </c>
       <c r="AD24" t="inlineStr">
@@ -5613,10 +5613,10 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>24759066624</v>
+        <v>24655566848</v>
       </c>
       <c r="F25" t="n">
-        <v>38.27500152587891</v>
+        <v>38.1150016784668</v>
       </c>
       <c r="G25" t="n">
         <v>39063072768</v>
@@ -5646,22 +5646,22 @@
         <v>0.13382</v>
       </c>
       <c r="Q25" t="n">
-        <v>11.740798</v>
+        <v>11.691718</v>
       </c>
       <c r="R25" t="n">
-        <v>0.6338228</v>
+        <v>0.63117325</v>
       </c>
       <c r="T25" t="n">
-        <v>0.3453427240584839</v>
+        <v>0.3397188279909471</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.0732444979918343</v>
+        <v>-0.07711858637846403</v>
       </c>
       <c r="V25" t="n">
-        <v>0.1391370019066676</v>
+        <v>0.1343751014698165</v>
       </c>
       <c r="W25" t="n">
-        <v>-0.144883758687151</v>
+        <v>-0.1484583756087771</v>
       </c>
       <c r="X25" t="n">
         <v>0.12878999</v>
@@ -5671,7 +5671,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>2026-08-27T18:45:26.101825+00:00</t>
+          <t>2026-08-27T18:56:35.872091+00:00</t>
         </is>
       </c>
       <c r="AD25" t="inlineStr">
@@ -5702,10 +5702,10 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>229872025600</v>
+        <v>230656098304</v>
       </c>
       <c r="F26" t="n">
-        <v>225.75</v>
+        <v>226.5200042724609</v>
       </c>
       <c r="G26" t="n">
         <v>5094199808</v>
@@ -5732,25 +5732,25 @@
         <v>-0.022079999</v>
       </c>
       <c r="Q26" t="n">
-        <v>3762.5</v>
+        <v>3775.3335</v>
       </c>
       <c r="R26" t="n">
-        <v>45.124268</v>
+        <v>45.27818</v>
       </c>
       <c r="S26" t="n">
-        <v>119.3294203941374</v>
+        <v>119.7364422623746</v>
       </c>
       <c r="T26" t="n">
-        <v>0.2417491540730601</v>
+        <v>0.2459846010452018</v>
       </c>
       <c r="U26" t="n">
-        <v>0.34575260804769</v>
+        <v>0.350342797451332</v>
       </c>
       <c r="V26" t="n">
-        <v>1.485480735647431</v>
+        <v>1.493958391397455</v>
       </c>
       <c r="W26" t="n">
-        <v>1.136721874304055</v>
+        <v>1.14400995834514</v>
       </c>
       <c r="X26" t="n">
         <v>0.01467</v>
@@ -5760,7 +5760,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>2026-08-27T18:45:21.016181+00:00</t>
+          <t>2026-08-27T18:56:29.474358+00:00</t>
         </is>
       </c>
       <c r="AD26" t="inlineStr">
@@ -5791,10 +5791,10 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>267955519488</v>
+        <v>268110364672</v>
       </c>
       <c r="F27" t="n">
-        <v>250.8950042724609</v>
+        <v>251.0399932861328</v>
       </c>
       <c r="G27" t="n">
         <v>5155999744</v>
@@ -5824,25 +5824,25 @@
         <v>0.07603</v>
       </c>
       <c r="Q27" t="n">
-        <v>256.01532</v>
+        <v>256.16324</v>
       </c>
       <c r="R27" t="n">
-        <v>51.969654</v>
+        <v>51.999687</v>
       </c>
       <c r="S27" t="n">
-        <v>200.7909523516751</v>
+        <v>200.9069847141428</v>
       </c>
       <c r="T27" t="n">
-        <v>0.02514913230836213</v>
+        <v>0.02574155287883539</v>
       </c>
       <c r="U27" t="n">
-        <v>-0.251662801640651</v>
+        <v>-0.251230347145996</v>
       </c>
       <c r="V27" t="n">
-        <v>0.9044708806049031</v>
+        <v>0.9055714499659648</v>
       </c>
       <c r="W27" t="n">
-        <v>0.7836982634747818</v>
+        <v>0.7847290398852542</v>
       </c>
       <c r="X27" t="n">
         <v>0.0007</v>
@@ -5852,7 +5852,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>2026-08-27T18:45:24.266747+00:00</t>
+          <t>2026-08-27T18:56:33.535883+00:00</t>
         </is>
       </c>
       <c r="AD27" t="inlineStr">
@@ -5883,10 +5883,10 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>219463663616</v>
+        <v>219140128768</v>
       </c>
       <c r="F28" t="n">
-        <v>244.1999969482422</v>
+        <v>243.8099975585938</v>
       </c>
       <c r="G28" t="n">
         <v>8717100032</v>
@@ -5916,25 +5916,25 @@
         <v>0.14479999</v>
       </c>
       <c r="Q28" t="n">
-        <v>83.630135</v>
+        <v>83.50684</v>
       </c>
       <c r="R28" t="n">
-        <v>25.176224</v>
+        <v>25.139109</v>
       </c>
       <c r="S28" t="n">
-        <v>96.692802719959</v>
+        <v>96.5502575226573</v>
       </c>
       <c r="T28" t="n">
-        <v>0.3996675373397356</v>
+        <v>0.3974321995342689</v>
       </c>
       <c r="U28" t="n">
-        <v>0.1925022808512515</v>
+        <v>0.1905977961358609</v>
       </c>
       <c r="V28" t="n">
-        <v>2.020051094389128</v>
+        <v>2.015227924453673</v>
       </c>
       <c r="W28" t="n">
-        <v>2.272098829343672</v>
+        <v>2.266873126795511</v>
       </c>
       <c r="X28" t="n">
         <v>0.00494</v>
@@ -5944,7 +5944,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>2026-08-27T18:45:24.686675+00:00</t>
+          <t>2026-08-27T18:56:34.001261+00:00</t>
         </is>
       </c>
       <c r="AD28" t="inlineStr">
@@ -5975,10 +5975,10 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1450957602816</v>
+        <v>1449874948096</v>
       </c>
       <c r="F29" t="n">
-        <v>569.5599975585938</v>
+        <v>569.135009765625</v>
       </c>
       <c r="G29" t="n">
         <v>228246994944</v>
@@ -6008,25 +6008,25 @@
         <v>0.34827</v>
       </c>
       <c r="Q29" t="n">
-        <v>21.444277</v>
+        <v>21.428276</v>
       </c>
       <c r="R29" t="n">
-        <v>6.3569627</v>
+        <v>6.352219</v>
       </c>
       <c r="S29" t="n">
-        <v>67.31849500452812</v>
+        <v>67.26826425607723</v>
       </c>
       <c r="T29" t="n">
-        <v>-0.04019139661498172</v>
+        <v>-0.0409075756685906</v>
       </c>
       <c r="U29" t="n">
-        <v>-0.1026336016712451</v>
+        <v>-0.1033031883113618</v>
       </c>
       <c r="V29" t="n">
-        <v>-0.1271458965524789</v>
+        <v>-0.1277972744705423</v>
       </c>
       <c r="W29" t="n">
-        <v>-0.2354267963351629</v>
+        <v>-0.2359973594586448</v>
       </c>
       <c r="X29" t="n">
         <v>0.00148</v>
@@ -6036,7 +6036,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>2026-08-27T18:45:22.785172+00:00</t>
+          <t>2026-08-27T18:56:31.661173+00:00</t>
         </is>
       </c>
       <c r="AD29" t="inlineStr">
@@ -6067,10 +6067,10 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>142052638720</v>
+        <v>142429995008</v>
       </c>
       <c r="F30" t="n">
-        <v>137.3999938964844</v>
+        <v>137.7649993896484</v>
       </c>
       <c r="G30" t="n">
         <v>14732000256</v>
@@ -6100,25 +6100,25 @@
         <v>0.04063</v>
       </c>
       <c r="Q30" t="n">
-        <v>85.87499</v>
+        <v>86.10312999999999</v>
       </c>
       <c r="R30" t="n">
-        <v>9.642454000000001</v>
+        <v>9.668068999999999</v>
       </c>
       <c r="S30" t="n">
-        <v>27.58638463543114</v>
+        <v>27.65966659484539</v>
       </c>
       <c r="T30" t="n">
-        <v>0.2420899519524717</v>
+        <v>0.245389585690506</v>
       </c>
       <c r="U30" t="n">
-        <v>0.2636805817565766</v>
+        <v>0.267037571381288</v>
       </c>
       <c r="V30" t="n">
-        <v>0.3182384099706954</v>
+        <v>0.3217403334227564</v>
       </c>
       <c r="W30" t="n">
-        <v>-0.2263339304958505</v>
+        <v>-0.2242786730155888</v>
       </c>
       <c r="X30" t="n">
         <v>0.00176</v>
@@ -6128,7 +6128,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>2026-08-27T18:45:27.674997+00:00</t>
+          <t>2026-08-27T18:56:37.840528+00:00</t>
         </is>
       </c>
       <c r="AD30" t="inlineStr">
@@ -6159,10 +6159,10 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>431235334144</v>
+        <v>431638609920</v>
       </c>
       <c r="F31" t="n">
-        <v>149.7100067138672</v>
+        <v>149.8500061035156</v>
       </c>
       <c r="G31" t="n">
         <v>67356999680</v>
@@ -6192,22 +6192,22 @@
         <v>0.36202</v>
       </c>
       <c r="Q31" t="n">
-        <v>25.635275</v>
+        <v>25.659246</v>
       </c>
       <c r="R31" t="n">
-        <v>6.402235</v>
+        <v>6.408222</v>
       </c>
       <c r="T31" t="n">
-        <v>0.2479993986032407</v>
+        <v>0.249166449209417</v>
       </c>
       <c r="U31" t="n">
-        <v>-0.262489719734074</v>
+        <v>-0.2618000464693201</v>
       </c>
       <c r="V31" t="n">
-        <v>0.0193761992980499</v>
+        <v>0.02032945585622126</v>
       </c>
       <c r="W31" t="n">
-        <v>-0.3578883328275487</v>
+        <v>-0.357287870350367</v>
       </c>
       <c r="X31" t="n">
         <v>0.40498</v>
@@ -6217,7 +6217,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>2026-08-27T18:45:23.181568+00:00</t>
+          <t>2026-08-27T18:56:32.140292+00:00</t>
         </is>
       </c>
       <c r="AD31" t="inlineStr">
@@ -6912,7 +6912,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ASML</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -6941,7 +6941,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>ASML</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -7292,7 +7292,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>56.69</v>
+        <v>56.7</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/reports/investment_dashboard.xlsx
+++ b/reports/investment_dashboard.xlsx
@@ -525,16 +525,16 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>MU</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Micron Technology, Inc.</t>
+          <t>Taiwan Semiconductor Manufacturing Company Limited</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>56.7</v>
+        <v>55.57</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>916.1649780273438</v>
+        <v>424.6400146484375</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -550,24 +550,19 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>84.2</v>
+        <v>100</v>
       </c>
       <c r="I2" t="n">
-        <v>88.2</v>
+        <v>100</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Revenue Growth; Earnings Fcf; Balance Sheet</t>
+          <t>Revenue Growth; Earnings Fcf; Balance Sheet; Valuation</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
           <t>Industry Growth; Competitive Advantage; Catalysts; Inflation Resilience</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>High market sensitivity / beta</t>
         </is>
       </c>
     </row>
@@ -577,16 +572,16 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>MU</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Taiwan Semiconductor Manufacturing Company Limited</t>
+          <t>Micron Technology, Inc.</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>55.57</v>
+        <v>54.4</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -594,7 +589,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>424.6199951171875</v>
+        <v>917.35498046875</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -602,19 +597,24 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="I3" t="n">
         <v>100</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Revenue Growth; Earnings Fcf; Balance Sheet; Valuation</t>
+          <t>Revenue Growth; Earnings Fcf; Balance Sheet</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
           <t>Industry Growth; Competitive Advantage; Catalysts; Inflation Resilience</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>High market sensitivity / beta</t>
         </is>
       </c>
     </row>
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>53.51</v>
+        <v>53.52</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>236.5500030517578</v>
+        <v>237.0549926757812</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -685,7 +685,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>52.89</v>
+        <v>52.93</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -693,7 +693,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>199.7100067138672</v>
+        <v>200.5</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -737,7 +737,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>52.37</v>
+        <v>52.38</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -745,7 +745,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>185.8500061035156</v>
+        <v>185.9900054931641</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>51.14</v>
+        <v>51.15</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>464.1300048828125</v>
+        <v>466.2699890136719</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -836,7 +836,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>50.85</v>
+        <v>50.91</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -844,7 +844,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>225.5700073242188</v>
+        <v>226.3699951171875</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>50.83</v>
+        <v>50.82</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>364.739990234375</v>
+        <v>364.4974975585938</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>47.65</v>
+        <v>47.64</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -943,7 +943,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>18.2450008392334</v>
+        <v>18.29500007629395</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -982,7 +982,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>47.57</v>
+        <v>47.56</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -990,7 +990,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>471.1799926757812</v>
+        <v>470.8500061035156</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -1042,7 +1042,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>340.8099975585938</v>
+        <v>340.8699951171875</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>45.38</v>
+        <v>45.42</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -1089,7 +1089,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>474.7149963378906</v>
+        <v>476.8150024414062</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -1128,7 +1128,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>45.1</v>
+        <v>45.13</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>241.7700042724609</v>
+        <v>242.5149993896484</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -1180,7 +1180,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>44.27</v>
+        <v>44.3</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>368.4400024414062</v>
+        <v>369.0799865722656</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>445.1400146484375</v>
+        <v>445.3099975585938</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1279,7 +1279,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>43.18</v>
+        <v>43.2</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -1287,7 +1287,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>330.9049987792969</v>
+        <v>331.3800048828125</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1331,7 +1331,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>43.05</v>
+        <v>43.03</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -1339,7 +1339,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>306.3900146484375</v>
+        <v>305.9150085449219</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1383,7 +1383,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>42.54</v>
+        <v>42.56</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -1391,7 +1391,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>255.3549957275391</v>
+        <v>255.6943969726562</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1430,7 +1430,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>42.44</v>
+        <v>42.49</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>79.55999755859375</v>
+        <v>80.02999877929688</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1482,7 +1482,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>42.44</v>
+        <v>42.48</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -1490,7 +1490,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>267.4024963378906</v>
+        <v>268.9800109863281</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1534,7 +1534,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>42.37</v>
+        <v>42.43</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -1542,7 +1542,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>503.3150024414062</v>
+        <v>505.2099914550781</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1581,7 +1581,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>42.32</v>
+        <v>42.35</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1723.364990234375</v>
+        <v>1726.535034179688</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1636,7 +1636,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>386.1400146484375</v>
+        <v>385.9349975585938</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1680,7 +1680,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>41.72</v>
+        <v>41.89</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>38.1150016784668</v>
+        <v>38.47499847412109</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1708,7 +1708,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>Industry Growth; Balance Sheet; Competitive Advantage; Momentum; Catalysts; Inflation Resilience</t>
+          <t>Industry Growth; Balance Sheet; Competitive Advantage; Catalysts; Inflation Resilience</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -1732,7 +1732,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>41.04</v>
+        <v>41.01</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -1740,7 +1740,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>226.5200042724609</v>
+        <v>225.8300018310547</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1784,7 +1784,7 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>40.72</v>
+        <v>40.73</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -1792,7 +1792,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>251.0399932861328</v>
+        <v>251.4698944091797</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>243.8099975585938</v>
+        <v>243.9799957275391</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1888,7 +1888,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>39.56</v>
+        <v>39.57</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -1896,7 +1896,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>569.135009765625</v>
+        <v>570.10498046875</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>36.41</v>
+        <v>36.46</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -1943,7 +1943,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>137.7649993896484</v>
+        <v>138.2400054931641</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1977,7 +1977,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>31.48</v>
+        <v>31.52</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -1985,7 +1985,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>149.8500061035156</v>
+        <v>151.0399932861328</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -2115,7 +2115,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>MU</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -2128,19 +2128,19 @@
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>9.02</v>
+        <v>8.84</v>
       </c>
       <c r="F2" t="n">
-        <v>7.32</v>
+        <v>8.65</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>6.86</v>
+        <v>5.39</v>
       </c>
       <c r="I2" t="n">
-        <v>3.5</v>
+        <v>2.69</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -2149,13 +2149,13 @@
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>56.7</v>
+        <v>55.57</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>MU</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -2168,19 +2168,19 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>8.84</v>
+        <v>9.02</v>
       </c>
       <c r="F3" t="n">
-        <v>8.65</v>
+        <v>5.01</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>5.39</v>
+        <v>6.87</v>
       </c>
       <c r="I3" t="n">
-        <v>2.69</v>
+        <v>3.5</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -2189,7 +2189,7 @@
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>55.57</v>
+        <v>54.4</v>
       </c>
     </row>
     <row r="4">
@@ -2211,13 +2211,13 @@
         <v>9.91</v>
       </c>
       <c r="F4" t="n">
-        <v>2.36</v>
+        <v>2.35</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>7.7</v>
+        <v>7.72</v>
       </c>
       <c r="I4" t="n">
         <v>3.54</v>
@@ -2229,7 +2229,7 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>53.51</v>
+        <v>53.52</v>
       </c>
     </row>
     <row r="5">
@@ -2257,7 +2257,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>8.470000000000001</v>
+        <v>8.51</v>
       </c>
       <c r="I5" t="n">
         <v>3.63</v>
@@ -2269,7 +2269,7 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>52.89</v>
+        <v>52.93</v>
       </c>
     </row>
     <row r="6">
@@ -2297,7 +2297,7 @@
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>8.49</v>
+        <v>8.5</v>
       </c>
       <c r="I6" t="n">
         <v>3.35</v>
@@ -2309,7 +2309,7 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>52.37</v>
+        <v>52.38</v>
       </c>
     </row>
     <row r="7">
@@ -2331,13 +2331,13 @@
         <v>6.33</v>
       </c>
       <c r="F7" t="n">
-        <v>5.77</v>
+        <v>5.76</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>9.02</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="I7" t="n">
         <v>3.54</v>
@@ -2349,7 +2349,7 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>51.14</v>
+        <v>51.15</v>
       </c>
     </row>
     <row r="8">
@@ -2371,13 +2371,13 @@
         <v>9.029999999999999</v>
       </c>
       <c r="F8" t="n">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>5.44</v>
+        <v>5.52</v>
       </c>
       <c r="I8" t="n">
         <v>3.44</v>
@@ -2389,7 +2389,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>50.85</v>
+        <v>50.91</v>
       </c>
     </row>
     <row r="9">
@@ -2417,7 +2417,7 @@
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>5.25</v>
+        <v>5.24</v>
       </c>
       <c r="I9" t="n">
         <v>3.75</v>
@@ -2429,7 +2429,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>50.83</v>
+        <v>50.82</v>
       </c>
     </row>
     <row r="10">
@@ -2451,7 +2451,7 @@
         <v>9.699999999999999</v>
       </c>
       <c r="F10" t="n">
-        <v>6.52</v>
+        <v>6.51</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -2469,7 +2469,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>47.65</v>
+        <v>47.64</v>
       </c>
     </row>
     <row r="11">
@@ -2497,7 +2497,7 @@
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>6.12</v>
+        <v>6.11</v>
       </c>
       <c r="I11" t="n">
         <v>3.45</v>
@@ -2509,7 +2509,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>47.57</v>
+        <v>47.56</v>
       </c>
     </row>
     <row r="12">
@@ -2571,13 +2571,13 @@
         <v>7.78</v>
       </c>
       <c r="F13" t="n">
-        <v>2.12</v>
+        <v>2.09</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>5.72</v>
+        <v>5.79</v>
       </c>
       <c r="I13" t="n">
         <v>3.58</v>
@@ -2589,7 +2589,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>45.38</v>
+        <v>45.42</v>
       </c>
     </row>
     <row r="14">
@@ -2617,7 +2617,7 @@
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>6.53</v>
+        <v>6.56</v>
       </c>
       <c r="I14" t="n">
         <v>3.67</v>
@@ -2629,7 +2629,7 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>45.1</v>
+        <v>45.13</v>
       </c>
     </row>
     <row r="15">
@@ -2657,7 +2657,7 @@
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>3.55</v>
+        <v>3.58</v>
       </c>
       <c r="I15" t="n">
         <v>3.53</v>
@@ -2669,7 +2669,7 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>44.27</v>
+        <v>44.3</v>
       </c>
     </row>
     <row r="16">
@@ -2737,7 +2737,7 @@
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>9.119999999999999</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="I17" t="n">
         <v>3.56</v>
@@ -2749,7 +2749,7 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>43.18</v>
+        <v>43.2</v>
       </c>
     </row>
     <row r="18">
@@ -2777,7 +2777,7 @@
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>8.65</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="I18" t="n">
         <v>3.64</v>
@@ -2789,7 +2789,7 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>43.05</v>
+        <v>43.03</v>
       </c>
     </row>
     <row r="19">
@@ -2817,7 +2817,7 @@
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>4.39</v>
+        <v>4.41</v>
       </c>
       <c r="I19" t="n">
         <v>3.47</v>
@@ -2829,7 +2829,7 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>42.54</v>
+        <v>42.56</v>
       </c>
     </row>
     <row r="20">
@@ -2851,13 +2851,13 @@
         <v>4.02</v>
       </c>
       <c r="F20" t="n">
-        <v>6.85</v>
+        <v>6.82</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>5.11</v>
+        <v>5.19</v>
       </c>
       <c r="I20" t="n">
         <v>3.63</v>
@@ -2869,7 +2869,7 @@
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>42.44</v>
+        <v>42.49</v>
       </c>
     </row>
     <row r="21">
@@ -2891,13 +2891,13 @@
         <v>7.41</v>
       </c>
       <c r="F21" t="n">
-        <v>3.24</v>
+        <v>3.21</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>3.93</v>
+        <v>4</v>
       </c>
       <c r="I21" t="n">
         <v>3.56</v>
@@ -2909,7 +2909,7 @@
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>42.44</v>
+        <v>42.48</v>
       </c>
     </row>
     <row r="22">
@@ -2931,13 +2931,13 @@
         <v>6.87</v>
       </c>
       <c r="F22" t="n">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>6.03</v>
+        <v>6.11</v>
       </c>
       <c r="I22" t="n">
         <v>3.45</v>
@@ -2949,7 +2949,7 @@
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>42.37</v>
+        <v>42.43</v>
       </c>
     </row>
     <row r="23">
@@ -2977,7 +2977,7 @@
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>5.89</v>
+        <v>5.92</v>
       </c>
       <c r="I23" t="n">
         <v>2.76</v>
@@ -2989,7 +2989,7 @@
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>42.32</v>
+        <v>42.35</v>
       </c>
     </row>
     <row r="24">
@@ -3051,13 +3051,13 @@
         <v>2.23</v>
       </c>
       <c r="F25" t="n">
-        <v>9.859999999999999</v>
+        <v>9.85</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>3.86</v>
+        <v>4.04</v>
       </c>
       <c r="I25" t="n">
         <v>3.54</v>
@@ -3069,7 +3069,7 @@
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>41.72</v>
+        <v>41.89</v>
       </c>
     </row>
     <row r="26">
@@ -3097,7 +3097,7 @@
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>9.07</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="I26" t="n">
         <v>3.48</v>
@@ -3109,7 +3109,7 @@
         <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>41.04</v>
+        <v>41.01</v>
       </c>
     </row>
     <row r="27">
@@ -3137,7 +3137,7 @@
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>5.8</v>
+        <v>5.81</v>
       </c>
       <c r="I27" t="n">
         <v>3.7</v>
@@ -3149,7 +3149,7 @@
         <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>40.72</v>
+        <v>40.73</v>
       </c>
     </row>
     <row r="28">
@@ -3211,13 +3211,13 @@
         <v>7.23</v>
       </c>
       <c r="F29" t="n">
-        <v>5.65</v>
+        <v>5.64</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.83</v>
       </c>
       <c r="I29" t="n">
         <v>3.49</v>
@@ -3229,7 +3229,7 @@
         <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>39.56</v>
+        <v>39.57</v>
       </c>
     </row>
     <row r="30">
@@ -3251,13 +3251,13 @@
         <v>6.78</v>
       </c>
       <c r="F30" t="n">
-        <v>3.66</v>
+        <v>3.65</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>5.84</v>
+        <v>5.9</v>
       </c>
       <c r="I30" t="n">
         <v>3.57</v>
@@ -3269,7 +3269,7 @@
         <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>36.41</v>
+        <v>36.46</v>
       </c>
     </row>
     <row r="31">
@@ -3291,13 +3291,13 @@
         <v>0.8</v>
       </c>
       <c r="F31" t="n">
-        <v>6.37</v>
+        <v>6.33</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>2.59</v>
+        <v>2.67</v>
       </c>
       <c r="I31" t="n">
         <v>3.58</v>
@@ -3309,7 +3309,7 @@
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>31.48</v>
+        <v>31.52</v>
       </c>
     </row>
   </sheetData>
@@ -3514,12 +3514,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>MU</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Micron Technology, Inc.</t>
+          <t>Taiwan Semiconductor Manufacturing Company Limited</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -3532,60 +3532,69 @@
           <t>Semiconductors</t>
         </is>
       </c>
+      <c r="E2" t="n">
+        <v>2202384465920</v>
+      </c>
       <c r="F2" t="n">
-        <v>916.1649780273438</v>
+        <v>424.6400146484375</v>
       </c>
       <c r="G2" t="n">
-        <v>90273996800</v>
+        <v>4440492343296</v>
       </c>
       <c r="H2" t="n">
-        <v>3.457</v>
+        <v>0.36</v>
       </c>
       <c r="I2" t="n">
-        <v>44.2</v>
+        <v>13.41</v>
       </c>
       <c r="J2" t="n">
-        <v>13.685</v>
+        <v>0.774</v>
       </c>
       <c r="K2" t="n">
-        <v>7639499776</v>
+        <v>730826014720</v>
       </c>
       <c r="M2" t="n">
-        <v>26022000640</v>
+        <v>3518010228736</v>
       </c>
       <c r="N2" t="n">
-        <v>6376000000</v>
+        <v>1068558516224</v>
       </c>
       <c r="O2" t="n">
-        <v>0.7256899999999999</v>
+        <v>0.6423</v>
       </c>
       <c r="P2" t="n">
-        <v>0.80370003</v>
+        <v>0.60344005</v>
       </c>
       <c r="Q2" t="n">
-        <v>20.727827</v>
+        <v>31.665922</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0.49597755</v>
+      </c>
+      <c r="S2" t="n">
+        <v>3.013555102802129</v>
       </c>
       <c r="T2" t="n">
-        <v>0.1165526492825861</v>
+        <v>0.0824093632358045</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.007811549298102127</v>
+        <v>0.001822916010435272</v>
       </c>
       <c r="V2" t="n">
-        <v>1.136808469082825</v>
+        <v>0.100853207272626</v>
       </c>
       <c r="W2" t="n">
-        <v>6.793081924800167</v>
+        <v>0.7942091235712727</v>
       </c>
       <c r="X2" t="n">
-        <v>0.00238</v>
+        <v>0.00013</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.79987</v>
+        <v>0.15493</v>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>2026-08-27T18:56:27.637791+00:00</t>
+          <t>2026-08-27T19:10:22.074363+00:00</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
@@ -3597,12 +3606,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>MU</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Taiwan Semiconductor Manufacturing Company Limited</t>
+          <t>Micron Technology, Inc.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -3616,68 +3625,68 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2202280656896</v>
+        <v>1035907629056</v>
       </c>
       <c r="F3" t="n">
-        <v>424.6199951171875</v>
+        <v>917.35498046875</v>
       </c>
       <c r="G3" t="n">
-        <v>4440492343296</v>
+        <v>90273996800</v>
       </c>
       <c r="H3" t="n">
-        <v>0.36</v>
+        <v>3.457</v>
       </c>
       <c r="I3" t="n">
-        <v>13.41</v>
+        <v>44.2</v>
       </c>
       <c r="J3" t="n">
-        <v>0.774</v>
+        <v>13.685</v>
       </c>
       <c r="K3" t="n">
-        <v>730826014720</v>
+        <v>7639499776</v>
       </c>
       <c r="M3" t="n">
-        <v>3518010228736</v>
+        <v>26022000640</v>
       </c>
       <c r="N3" t="n">
-        <v>1068558516224</v>
+        <v>6376000000</v>
       </c>
       <c r="O3" t="n">
-        <v>0.6423</v>
+        <v>0.7256899999999999</v>
       </c>
       <c r="P3" t="n">
-        <v>0.60344005</v>
+        <v>0.80370003</v>
       </c>
       <c r="Q3" t="n">
-        <v>31.664429</v>
+        <v>20.751696</v>
       </c>
       <c r="R3" t="n">
-        <v>0.49595416</v>
+        <v>11.476776</v>
       </c>
       <c r="S3" t="n">
-        <v>3.013413059385627</v>
+        <v>135.5988820512009</v>
       </c>
       <c r="T3" t="n">
-        <v>0.08235833335796672</v>
+        <v>0.1180029343409232</v>
       </c>
       <c r="U3" t="n">
-        <v>0.001775685357453538</v>
+        <v>-0.006522800320584277</v>
       </c>
       <c r="V3" t="n">
-        <v>0.1008013078650705</v>
+        <v>1.139583959694245</v>
       </c>
       <c r="W3" t="n">
-        <v>0.7941245360986389</v>
+        <v>6.803204829179007</v>
       </c>
       <c r="X3" t="n">
-        <v>0.00013</v>
+        <v>0.00238</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.15493</v>
+        <v>0.79987</v>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>2026-08-27T18:56:32.637696+00:00</t>
+          <t>2026-08-27T19:10:17.194924+00:00</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
@@ -3708,10 +3717,10 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>44455948288</v>
+        <v>44550852608</v>
       </c>
       <c r="F4" t="n">
-        <v>236.5500030517578</v>
+        <v>237.0549926757812</v>
       </c>
       <c r="G4" t="n">
         <v>1335116032</v>
@@ -3741,25 +3750,25 @@
         <v>0.35661998</v>
       </c>
       <c r="Q4" t="n">
-        <v>94.24303</v>
+        <v>94.44422</v>
       </c>
       <c r="R4" t="n">
-        <v>33.297443</v>
+        <v>33.368526</v>
       </c>
       <c r="S4" t="n">
-        <v>177.2494142979745</v>
+        <v>177.6278053970771</v>
       </c>
       <c r="T4" t="n">
-        <v>0.230237177831871</v>
+        <v>0.2328635020841563</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0638632631367293</v>
+        <v>0.06613441047273771</v>
       </c>
       <c r="V4" t="n">
-        <v>0.9160052227921025</v>
+        <v>0.9200955324289746</v>
       </c>
       <c r="W4" t="n">
-        <v>0.9274015854444608</v>
+        <v>0.9315162241653185</v>
       </c>
       <c r="X4" t="n">
         <v>0.09436</v>
@@ -3769,7 +3778,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>2026-08-27T18:56:28.519501+00:00</t>
+          <t>2026-08-27T19:10:18.055631+00:00</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
@@ -3800,10 +3809,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>251879194624</v>
+        <v>252875554816</v>
       </c>
       <c r="F5" t="n">
-        <v>199.7100067138672</v>
+        <v>200.5</v>
       </c>
       <c r="G5" t="n">
         <v>10540800000</v>
@@ -3833,25 +3842,25 @@
         <v>0.45393002</v>
       </c>
       <c r="Q5" t="n">
-        <v>63.199368</v>
+        <v>63.449364</v>
       </c>
       <c r="R5" t="n">
-        <v>23.895643</v>
+        <v>23.990168</v>
       </c>
       <c r="S5" t="n">
-        <v>64.72526805576999</v>
+        <v>64.98130222565675</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1767721337173731</v>
+        <v>0.1814270936777762</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2862111239684446</v>
+        <v>0.2912989919686706</v>
       </c>
       <c r="V5" t="n">
-        <v>0.5028219401844902</v>
+        <v>0.5087666560379116</v>
       </c>
       <c r="W5" t="n">
-        <v>0.4985368073191807</v>
+        <v>0.5044645724636743</v>
       </c>
       <c r="X5" t="n">
         <v>0.17247999</v>
@@ -3861,7 +3870,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>2026-08-27T18:56:34.461249+00:00</t>
+          <t>2026-08-27T19:10:23.861872+00:00</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
@@ -3892,10 +3901,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>446608408576</v>
+        <v>446944837632</v>
       </c>
       <c r="F6" t="n">
-        <v>185.8500061035156</v>
+        <v>185.9900054931641</v>
       </c>
       <c r="G6" t="n">
         <v>6155940864</v>
@@ -3925,25 +3934,25 @@
         <v>0.47120997</v>
       </c>
       <c r="Q6" t="n">
-        <v>158.84616</v>
+        <v>158.96582</v>
       </c>
       <c r="R6" t="n">
-        <v>72.54917</v>
+        <v>72.60382</v>
       </c>
       <c r="S6" t="n">
-        <v>206.848907078751</v>
+        <v>207.0047258703519</v>
       </c>
       <c r="T6" t="n">
-        <v>0.5044929000247294</v>
+        <v>0.5056262230315445</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2965676772128385</v>
+        <v>0.29754437173792</v>
       </c>
       <c r="V6" t="n">
-        <v>0.3849765461079457</v>
+        <v>0.3860198383584958</v>
       </c>
       <c r="W6" t="n">
-        <v>0.1858729240423485</v>
+        <v>0.1867662330556075</v>
       </c>
       <c r="X6" t="n">
         <v>0.03477</v>
@@ -3953,7 +3962,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>2026-08-27T18:56:25.788709+00:00</t>
+          <t>2026-08-27T19:10:14.937151+00:00</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr">
@@ -3984,10 +3993,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>299894079488</v>
+        <v>301276823552</v>
       </c>
       <c r="F7" t="n">
-        <v>464.1300048828125</v>
+        <v>466.2699890136719</v>
       </c>
       <c r="G7" t="n">
         <v>134001999872</v>
@@ -4017,25 +4026,25 @@
         <v>0.08857000600000001</v>
       </c>
       <c r="Q7" t="n">
-        <v>36.92363</v>
+        <v>37.093876</v>
       </c>
       <c r="R7" t="n">
-        <v>2.237982</v>
+        <v>2.248301</v>
       </c>
       <c r="S7" t="n">
-        <v>55.18719030670771</v>
+        <v>55.44164601298814</v>
       </c>
       <c r="T7" t="n">
-        <v>0.1837031309820503</v>
+        <v>0.1891608818046668</v>
       </c>
       <c r="U7" t="n">
-        <v>0.4663206695362638</v>
+        <v>0.473081497171941</v>
       </c>
       <c r="V7" t="n">
-        <v>2.776606851069723</v>
+        <v>2.794019814344581</v>
       </c>
       <c r="W7" t="n">
-        <v>2.547505515638265</v>
+        <v>2.563861735907643</v>
       </c>
       <c r="X7" t="n">
         <v>0.07491</v>
@@ -4045,7 +4054,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>2026-08-27T18:56:34.924336+00:00</t>
+          <t>2026-08-27T19:10:24.268246+00:00</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr">
@@ -4076,10 +4085,10 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5462804135936</v>
+        <v>5482907435008</v>
       </c>
       <c r="F8" t="n">
-        <v>225.5700073242188</v>
+        <v>226.3699951171875</v>
       </c>
       <c r="G8" t="n">
         <v>253491003392</v>
@@ -4109,25 +4118,25 @@
         <v>0.65596</v>
       </c>
       <c r="Q8" t="n">
-        <v>34.592022</v>
+        <v>34.719326</v>
       </c>
       <c r="R8" t="n">
-        <v>21.553156</v>
+        <v>21.629593</v>
       </c>
       <c r="S8" t="n">
-        <v>117.8957852613784</v>
+        <v>118.3296456326201</v>
       </c>
       <c r="T8" t="n">
-        <v>0.1449673296467799</v>
+        <v>0.1490279753768169</v>
       </c>
       <c r="U8" t="n">
-        <v>0.05406259879860897</v>
+        <v>0.05780084938460894</v>
       </c>
       <c r="V8" t="n">
-        <v>0.1548636716993186</v>
+        <v>0.1589594149714932</v>
       </c>
       <c r="W8" t="n">
-        <v>0.2437800087114501</v>
+        <v>0.2481909902378594</v>
       </c>
       <c r="X8" t="n">
         <v>0.03991</v>
@@ -4137,7 +4146,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>2026-08-27T18:56:25.382433+00:00</t>
+          <t>2026-08-27T19:10:14.483161+00:00</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr">
@@ -4168,10 +4177,10 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>57023725568</v>
+        <v>56985812992</v>
       </c>
       <c r="F9" t="n">
-        <v>364.739990234375</v>
+        <v>364.4974975585938</v>
       </c>
       <c r="G9" t="n">
         <v>4464031232</v>
@@ -4201,25 +4210,25 @@
         <v>0.33161</v>
       </c>
       <c r="Q9" t="n">
-        <v>50.239666</v>
+        <v>50.206264</v>
       </c>
       <c r="R9" t="n">
-        <v>12.774043</v>
+        <v>12.76555</v>
       </c>
       <c r="S9" t="n">
-        <v>130.3753323416371</v>
+        <v>130.2886514970116</v>
       </c>
       <c r="T9" t="n">
-        <v>0.1375019403621889</v>
+        <v>0.1367456868758423</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0468051847583576</v>
+        <v>-0.04743890403092832</v>
       </c>
       <c r="V9" t="n">
-        <v>0.06434203068138356</v>
+        <v>0.06363441661690827</v>
       </c>
       <c r="W9" t="n">
-        <v>2.125683435960829</v>
+        <v>2.123605365663288</v>
       </c>
       <c r="X9" t="n">
         <v>0.00202</v>
@@ -4229,7 +4238,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>2026-08-27T18:56:28.985200+00:00</t>
+          <t>2026-08-27T19:10:18.609464+00:00</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr">
@@ -4260,10 +4269,10 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>9453104128</v>
+        <v>9479010304</v>
       </c>
       <c r="F10" t="n">
-        <v>18.2450008392334</v>
+        <v>18.29500007629395</v>
       </c>
       <c r="G10" t="n">
         <v>1672329984</v>
@@ -4290,25 +4299,25 @@
         <v>0.07274</v>
       </c>
       <c r="Q10" t="n">
-        <v>30.408333</v>
+        <v>30.491665</v>
       </c>
       <c r="R10" t="n">
-        <v>5.6526546</v>
+        <v>5.6681457</v>
       </c>
       <c r="S10" t="n">
-        <v>18.47920440138719</v>
+        <v>18.52984655184698</v>
       </c>
       <c r="T10" t="n">
-        <v>0.4967187421888086</v>
+        <v>0.5008204024662222</v>
       </c>
       <c r="U10" t="n">
-        <v>0.5755613954610703</v>
+        <v>0.5798791188971637</v>
       </c>
       <c r="V10" t="n">
-        <v>0.8355132403868617</v>
+        <v>0.8405433449312543</v>
       </c>
       <c r="W10" t="n">
-        <v>0.6377917663323356</v>
+        <v>0.6422800280486394</v>
       </c>
       <c r="X10" t="n">
         <v>0.09236999999999999</v>
@@ -4318,7 +4327,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>2026-08-27T18:56:38.769857+00:00</t>
+          <t>2026-08-27T19:10:27.840175+00:00</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr">
@@ -4349,10 +4358,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>769189543936</v>
+        <v>768650838016</v>
       </c>
       <c r="F11" t="n">
-        <v>471.1799926757812</v>
+        <v>470.8500061035156</v>
       </c>
       <c r="G11" t="n">
         <v>41305001984</v>
@@ -4382,25 +4391,25 @@
         <v>0.1725</v>
       </c>
       <c r="Q11" t="n">
-        <v>119.58883</v>
+        <v>119.50507</v>
       </c>
       <c r="R11" t="n">
-        <v>18.622189</v>
+        <v>18.609146</v>
       </c>
       <c r="S11" t="n">
-        <v>86.99763327027846</v>
+        <v>86.93670402281511</v>
       </c>
       <c r="T11" t="n">
-        <v>0.0364260211527323</v>
+        <v>0.03570016972558476</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.09054417523611968</v>
+        <v>-0.09118110425455395</v>
       </c>
       <c r="V11" t="n">
-        <v>1.234563176097468</v>
+        <v>1.232998220338621</v>
       </c>
       <c r="W11" t="n">
-        <v>1.819242379644285</v>
+        <v>1.817267949185212</v>
       </c>
       <c r="X11" t="n">
         <v>0.00425</v>
@@ -4410,7 +4419,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>2026-08-27T18:56:26.264454+00:00</t>
+          <t>2026-08-27T19:10:15.476657+00:00</t>
         </is>
       </c>
       <c r="AD11" t="inlineStr">
@@ -4441,10 +4450,10 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4167717355520</v>
+        <v>4168940257280</v>
       </c>
       <c r="F12" t="n">
-        <v>340.8099975585938</v>
+        <v>340.8699951171875</v>
       </c>
       <c r="G12" t="n">
         <v>445865984000</v>
@@ -4474,25 +4483,25 @@
         <v>0.34033</v>
       </c>
       <c r="Q12" t="n">
-        <v>17.090271</v>
+        <v>17.095285</v>
       </c>
       <c r="R12" t="n">
-        <v>9.3482895</v>
+        <v>9.349935</v>
       </c>
       <c r="S12" t="n">
-        <v>183.8833963817313</v>
+        <v>183.9373518949986</v>
       </c>
       <c r="T12" t="n">
-        <v>0.02127597700193928</v>
+        <v>0.02145576652017378</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.1258976394217068</v>
+        <v>-0.1257437589370631</v>
       </c>
       <c r="V12" t="n">
-        <v>0.09061563639367964</v>
+        <v>0.09080763274360049</v>
       </c>
       <c r="W12" t="n">
-        <v>0.6473023133143463</v>
+        <v>0.6475921895038983</v>
       </c>
       <c r="X12" t="n">
         <v>0.01596</v>
@@ -4502,7 +4511,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>2026-08-27T18:56:30.848036+00:00</t>
+          <t>2026-08-27T19:10:20.367109+00:00</t>
         </is>
       </c>
       <c r="AD12" t="inlineStr">
@@ -4533,10 +4542,10 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>376732614656</v>
+        <v>378399162368</v>
       </c>
       <c r="F13" t="n">
-        <v>474.7149963378906</v>
+        <v>476.8150024414062</v>
       </c>
       <c r="G13" t="n">
         <v>30837000192</v>
@@ -4566,25 +4575,25 @@
         <v>0.33736</v>
       </c>
       <c r="Q13" t="n">
-        <v>40.88846</v>
+        <v>41.06934</v>
       </c>
       <c r="R13" t="n">
-        <v>12.216902</v>
+        <v>12.270946</v>
       </c>
       <c r="S13" t="n">
-        <v>122.4997282985094</v>
+        <v>123.0416289303485</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.002597018049028565</v>
+        <v>0.001815213217983835</v>
       </c>
       <c r="U13" t="n">
-        <v>0.05680180420716252</v>
+        <v>0.06147679921714055</v>
       </c>
       <c r="V13" t="n">
-        <v>0.2047433806134304</v>
+        <v>0.210072827696365</v>
       </c>
       <c r="W13" t="n">
-        <v>1.903709011992588</v>
+        <v>1.916553662460941</v>
       </c>
       <c r="X13" t="n">
         <v>0.00331</v>
@@ -4594,7 +4603,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>2026-08-27T18:56:27.123584+00:00</t>
+          <t>2026-08-27T19:10:16.663342+00:00</t>
         </is>
       </c>
       <c r="AD13" t="inlineStr">
@@ -4625,10 +4634,10 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>86813564928</v>
+        <v>87081074688</v>
       </c>
       <c r="F14" t="n">
-        <v>241.7700042724609</v>
+        <v>242.5149993896484</v>
       </c>
       <c r="G14" t="n">
         <v>3966725120</v>
@@ -4658,25 +4667,25 @@
         <v>0.00666</v>
       </c>
       <c r="Q14" t="n">
-        <v>483.54</v>
+        <v>485.03</v>
       </c>
       <c r="R14" t="n">
-        <v>21.88545</v>
+        <v>21.952888</v>
       </c>
       <c r="S14" t="n">
-        <v>82.56852296138899</v>
+        <v>82.82295192971064</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.03631218284855697</v>
+        <v>-0.03334265517521573</v>
       </c>
       <c r="U14" t="n">
-        <v>0.07338837851253088</v>
+        <v>0.07669593977615441</v>
       </c>
       <c r="V14" t="n">
-        <v>1.191335088008761</v>
+        <v>1.198087513503399</v>
       </c>
       <c r="W14" t="n">
-        <v>0.8353451158726277</v>
+        <v>0.8410005864666479</v>
       </c>
       <c r="X14" t="n">
         <v>0.00619</v>
@@ -4686,7 +4695,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>2026-08-27T18:56:36.826917+00:00</t>
+          <t>2026-08-27T19:10:26.019124+00:00</t>
         </is>
       </c>
       <c r="AD14" t="inlineStr">
@@ -4717,10 +4726,10 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1752882872320</v>
+        <v>1755975254016</v>
       </c>
       <c r="F15" t="n">
-        <v>368.4400024414062</v>
+        <v>369.0799865722656</v>
       </c>
       <c r="G15" t="n">
         <v>75464998912</v>
@@ -4750,25 +4759,25 @@
         <v>0.48988</v>
       </c>
       <c r="Q15" t="n">
-        <v>61.30449</v>
+        <v>61.412643</v>
       </c>
       <c r="R15" t="n">
-        <v>23.22776</v>
+        <v>23.268738</v>
       </c>
       <c r="S15" t="n">
-        <v>64.41521487810364</v>
+        <v>64.52885420596661</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.0327373949248253</v>
+        <v>-0.0310572496813124</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.1349263063387762</v>
+        <v>-0.1334236643012707</v>
       </c>
       <c r="V15" t="n">
-        <v>0.112807994787435</v>
+        <v>0.1147409538924133</v>
       </c>
       <c r="W15" t="n">
-        <v>0.2361019134991729</v>
+        <v>0.2382489086497031</v>
       </c>
       <c r="X15" t="n">
         <v>0.01948</v>
@@ -4778,7 +4787,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>2026-08-27T18:56:26.677264+00:00</t>
+          <t>2026-08-27T19:10:16.154303+00:00</t>
         </is>
       </c>
       <c r="AD15" t="inlineStr">
@@ -4809,10 +4818,10 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>35803467776</v>
+        <v>35817140224</v>
       </c>
       <c r="F16" t="n">
-        <v>445.1400146484375</v>
+        <v>445.3099975585938</v>
       </c>
       <c r="G16" t="n">
         <v>2602398976</v>
@@ -4839,22 +4848,22 @@
         <v>-0.03607</v>
       </c>
       <c r="R16" t="n">
-        <v>13.757871</v>
+        <v>13.763124</v>
       </c>
       <c r="S16" t="n">
-        <v>69.17135995125368</v>
+        <v>69.19777476190664</v>
       </c>
       <c r="T16" t="n">
-        <v>0.4330694148665468</v>
+        <v>0.4336166523684086</v>
       </c>
       <c r="U16" t="n">
-        <v>0.3668018443232413</v>
+        <v>0.3673237766309636</v>
       </c>
       <c r="V16" t="n">
-        <v>0.4131878105625566</v>
+        <v>0.413727455997098</v>
       </c>
       <c r="W16" t="n">
-        <v>0.5053770587495865</v>
+        <v>0.5059519079316597</v>
       </c>
       <c r="X16" t="n">
         <v>0.02641</v>
@@ -4864,7 +4873,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>2026-08-27T18:56:38.321002+00:00</t>
+          <t>2026-08-27T19:10:27.454223+00:00</t>
         </is>
       </c>
       <c r="AD16" t="inlineStr">
@@ -4895,10 +4904,10 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>114691670016</v>
+        <v>114856312832</v>
       </c>
       <c r="F17" t="n">
-        <v>330.9049987792969</v>
+        <v>331.3800048828125</v>
       </c>
       <c r="G17" t="n">
         <v>5032822784</v>
@@ -4925,22 +4934,22 @@
         <v>-0.22173999</v>
       </c>
       <c r="R17" t="n">
-        <v>22.788736</v>
+        <v>22.82145</v>
       </c>
       <c r="S17" t="n">
-        <v>65.93378546568587</v>
+        <v>66.02843509548981</v>
       </c>
       <c r="T17" t="n">
-        <v>0.2239422130053923</v>
+        <v>0.2256991523797527</v>
       </c>
       <c r="U17" t="n">
-        <v>0.3833821195695821</v>
+        <v>0.3853679310644644</v>
       </c>
       <c r="V17" t="n">
-        <v>0.9555876464141666</v>
+        <v>0.9583948450706792</v>
       </c>
       <c r="W17" t="n">
-        <v>0.6513049542750309</v>
+        <v>0.6536753625037968</v>
       </c>
       <c r="X17" t="n">
         <v>0.02962</v>
@@ -4950,7 +4959,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>2026-08-27T18:56:36.308126+00:00</t>
+          <t>2026-08-27T19:10:25.625429+00:00</t>
         </is>
       </c>
       <c r="AD17" t="inlineStr">
@@ -4981,10 +4990,10 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>109099270144</v>
+        <v>108930129920</v>
       </c>
       <c r="F18" t="n">
-        <v>306.3900146484375</v>
+        <v>305.9150085449219</v>
       </c>
       <c r="G18" t="n">
         <v>2512349952</v>
@@ -5011,22 +5020,22 @@
         <v>-0.07902000000000001</v>
       </c>
       <c r="R18" t="n">
-        <v>43.42519</v>
+        <v>43.357864</v>
       </c>
       <c r="S18" t="n">
-        <v>157.4640402031737</v>
+        <v>157.2199184689333</v>
       </c>
       <c r="T18" t="n">
-        <v>0.1601287677681691</v>
+        <v>0.1583301835480329</v>
       </c>
       <c r="U18" t="n">
-        <v>0.3431678305582084</v>
+        <v>0.3410854751058185</v>
       </c>
       <c r="V18" t="n">
-        <v>0.7834109965419038</v>
+        <v>0.7806461182236391</v>
       </c>
       <c r="W18" t="n">
-        <v>0.4928376848959033</v>
+        <v>0.490523291547617</v>
       </c>
       <c r="X18" t="n">
         <v>0.00616</v>
@@ -5036,7 +5045,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>2026-08-27T18:56:37.445537+00:00</t>
+          <t>2026-08-27T19:10:26.510322+00:00</t>
         </is>
       </c>
       <c r="AD18" t="inlineStr">
@@ -5067,10 +5076,10 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2754338881536</v>
+        <v>2757999722496</v>
       </c>
       <c r="F19" t="n">
-        <v>255.3549957275391</v>
+        <v>255.6943969726562</v>
       </c>
       <c r="G19" t="n">
         <v>775680032768</v>
@@ -5100,25 +5109,25 @@
         <v>0.13689</v>
       </c>
       <c r="Q19" t="n">
-        <v>20.52693</v>
+        <v>20.554213</v>
       </c>
       <c r="R19" t="n">
-        <v>3.55087</v>
+        <v>3.5555894</v>
       </c>
       <c r="S19" t="n">
-        <v>855.6172526326061</v>
+        <v>856.7544687919965</v>
       </c>
       <c r="T19" t="n">
-        <v>0.1061032446176351</v>
+        <v>0.1075734050794728</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.06804746084839763</v>
+        <v>-0.06680877017278741</v>
       </c>
       <c r="V19" t="n">
-        <v>0.2122816011557969</v>
+        <v>0.2138928869804295</v>
       </c>
       <c r="W19" t="n">
-        <v>0.1145033221431992</v>
+        <v>0.1159846474415156</v>
       </c>
       <c r="X19" t="n">
         <v>0.0887</v>
@@ -5128,7 +5137,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>2026-08-27T18:56:31.196787+00:00</t>
+          <t>2026-08-27T19:10:20.757478+00:00</t>
         </is>
       </c>
       <c r="AD19" t="inlineStr">
@@ -5159,10 +5168,10 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5541289984</v>
+        <v>5574025216</v>
       </c>
       <c r="F20" t="n">
-        <v>79.55999755859375</v>
+        <v>80.02999877929688</v>
       </c>
       <c r="G20" t="n">
         <v>1037772032</v>
@@ -5192,22 +5201,22 @@
         <v>0.16982001</v>
       </c>
       <c r="Q20" t="n">
-        <v>37.5283</v>
+        <v>37.75</v>
       </c>
       <c r="R20" t="n">
-        <v>5.3396025</v>
+        <v>5.371146</v>
       </c>
       <c r="T20" t="n">
-        <v>0.1046931583862167</v>
+        <v>0.1112191406496215</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1432263941884488</v>
+        <v>-0.138164998349402</v>
       </c>
       <c r="V20" t="n">
-        <v>0.1619686890634575</v>
+        <v>0.1688330269095772</v>
       </c>
       <c r="W20" t="n">
-        <v>1.783764792546471</v>
+        <v>1.800209901782223</v>
       </c>
       <c r="X20" t="n">
         <v>0.12675999</v>
@@ -5217,7 +5226,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>2026-08-27T18:56:28.059677+00:00</t>
+          <t>2026-08-27T19:10:17.581832+00:00</t>
         </is>
       </c>
       <c r="AD20" t="inlineStr">
@@ -5248,10 +5257,10 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>102946791424</v>
+        <v>103490592768</v>
       </c>
       <c r="F21" t="n">
-        <v>267.4024963378906</v>
+        <v>268.9800109863281</v>
       </c>
       <c r="G21" t="n">
         <v>11479600128</v>
@@ -5281,25 +5290,25 @@
         <v>0.20362</v>
       </c>
       <c r="Q21" t="n">
-        <v>60.36174</v>
+        <v>60.68059</v>
       </c>
       <c r="R21" t="n">
-        <v>8.967803</v>
+        <v>9.017353999999999</v>
       </c>
       <c r="S21" t="n">
-        <v>38.1773988332297</v>
+        <v>38.37906534958015</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.008003788545198232</v>
+        <v>-0.002151604754112468</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1487104518956159</v>
+        <v>-0.1436883531845422</v>
       </c>
       <c r="V21" t="n">
-        <v>0.0203355741195077</v>
+        <v>0.02635494318501386</v>
       </c>
       <c r="W21" t="n">
-        <v>1.070195918884233</v>
+        <v>1.082409081485411</v>
       </c>
       <c r="X21" t="n">
         <v>0.00269</v>
@@ -5309,7 +5318,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>2026-08-27T18:56:35.394069+00:00</t>
+          <t>2026-08-27T19:10:24.746982+00:00</t>
         </is>
       </c>
       <c r="AD21" t="inlineStr">
@@ -5340,10 +5349,10 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>3737425805312</v>
+        <v>3751459946496</v>
       </c>
       <c r="F22" t="n">
-        <v>503.3150024414062</v>
+        <v>505.2099914550781</v>
       </c>
       <c r="G22" t="n">
         <v>331839012864</v>
@@ -5373,25 +5382,25 @@
         <v>0.45111</v>
       </c>
       <c r="Q22" t="n">
-        <v>28.008905</v>
+        <v>28.11408</v>
       </c>
       <c r="R22" t="n">
-        <v>11.262768</v>
+        <v>11.30506</v>
       </c>
       <c r="S22" t="n">
-        <v>225.8877500933764</v>
+        <v>226.7359650792207</v>
       </c>
       <c r="T22" t="n">
-        <v>0.2819689960586313</v>
+        <v>0.2867956297802874</v>
       </c>
       <c r="U22" t="n">
-        <v>0.1809703151764965</v>
+        <v>0.1854166872533802</v>
       </c>
       <c r="V22" t="n">
-        <v>0.2614944654145874</v>
+        <v>0.2662440122017344</v>
       </c>
       <c r="W22" t="n">
-        <v>0.001413231158896355</v>
+        <v>0.005183506916361935</v>
       </c>
       <c r="X22" t="n">
         <v>0.00090000004</v>
@@ -5401,7 +5410,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>2026-08-27T18:56:30.330439+00:00</t>
+          <t>2026-08-27T19:10:19.910153+00:00</t>
         </is>
       </c>
       <c r="AD22" t="inlineStr">
@@ -5432,10 +5441,10 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>661944467456</v>
+        <v>663162126336</v>
       </c>
       <c r="F23" t="n">
-        <v>1723.364990234375</v>
+        <v>1726.535034179688</v>
       </c>
       <c r="G23" t="n">
         <v>35327500288</v>
@@ -5465,25 +5474,25 @@
         <v>0.37057</v>
       </c>
       <c r="Q23" t="n">
-        <v>58.064857</v>
+        <v>58.171665</v>
       </c>
       <c r="R23" t="n">
-        <v>18.737371</v>
+        <v>18.77184</v>
       </c>
       <c r="S23" t="n">
-        <v>78.45105041713406</v>
+        <v>78.5953625503752</v>
       </c>
       <c r="T23" t="n">
-        <v>0.08870466116667131</v>
+        <v>0.09070727909086118</v>
       </c>
       <c r="U23" t="n">
-        <v>0.07462079667199428</v>
+        <v>0.0765975080298904</v>
       </c>
       <c r="V23" t="n">
-        <v>0.1328866723014872</v>
+        <v>0.1349705608315461</v>
       </c>
       <c r="W23" t="n">
-        <v>1.252878112081987</v>
+        <v>1.257021988920565</v>
       </c>
       <c r="X23" t="n">
         <v>0.00016000001</v>
@@ -5493,7 +5502,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>2026-08-27T18:56:33.129796+00:00</t>
+          <t>2026-08-27T19:10:22.551781+00:00</t>
         </is>
       </c>
       <c r="AD23" t="inlineStr">
@@ -5524,10 +5533,10 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>314704101376</v>
+        <v>314537017344</v>
       </c>
       <c r="F24" t="n">
-        <v>386.1400146484375</v>
+        <v>385.9349975585938</v>
       </c>
       <c r="G24" t="n">
         <v>10606499840</v>
@@ -5554,25 +5563,25 @@
         <v>-0.02465</v>
       </c>
       <c r="Q24" t="n">
-        <v>335.77393</v>
+        <v>335.59564</v>
       </c>
       <c r="R24" t="n">
-        <v>29.670872</v>
+        <v>29.655119</v>
       </c>
       <c r="S24" t="n">
-        <v>87.92152044202183</v>
+        <v>87.87484077667654</v>
       </c>
       <c r="T24" t="n">
-        <v>0.2104702653556034</v>
+        <v>0.2098275785535855</v>
       </c>
       <c r="U24" t="n">
-        <v>0.4980022155641906</v>
+        <v>0.4972068666151983</v>
       </c>
       <c r="V24" t="n">
-        <v>1.66597641819618</v>
+        <v>1.664560945294859</v>
       </c>
       <c r="W24" t="n">
-        <v>1.058205923949727</v>
+        <v>1.057113140573698</v>
       </c>
       <c r="X24" t="n">
         <v>0.0076</v>
@@ -5582,7 +5591,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>2026-08-27T18:56:29.858142+00:00</t>
+          <t>2026-08-27T19:10:19.464625+00:00</t>
         </is>
       </c>
       <c r="AD24" t="inlineStr">
@@ -5613,10 +5622,10 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>24655566848</v>
+        <v>24888438784</v>
       </c>
       <c r="F25" t="n">
-        <v>38.1150016784668</v>
+        <v>38.47499847412109</v>
       </c>
       <c r="G25" t="n">
         <v>39063072768</v>
@@ -5646,22 +5655,22 @@
         <v>0.13382</v>
       </c>
       <c r="Q25" t="n">
-        <v>11.691718</v>
+        <v>11.802147</v>
       </c>
       <c r="R25" t="n">
-        <v>0.63117325</v>
+        <v>0.6371347000000001</v>
       </c>
       <c r="T25" t="n">
-        <v>0.3397188279909471</v>
+        <v>0.3523724935797106</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.07711858637846403</v>
+        <v>-0.06840195678271199</v>
       </c>
       <c r="V25" t="n">
-        <v>0.1343751014698165</v>
+        <v>0.1450892923032348</v>
       </c>
       <c r="W25" t="n">
-        <v>-0.1484583756087771</v>
+        <v>-0.1404155514543107</v>
       </c>
       <c r="X25" t="n">
         <v>0.12878999</v>
@@ -5671,7 +5680,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>2026-08-27T18:56:35.872091+00:00</t>
+          <t>2026-08-27T19:10:25.202653+00:00</t>
         </is>
       </c>
       <c r="AD25" t="inlineStr">
@@ -5702,10 +5711,10 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>230656098304</v>
+        <v>229953486848</v>
       </c>
       <c r="F26" t="n">
-        <v>226.5200042724609</v>
+        <v>225.8300018310547</v>
       </c>
       <c r="G26" t="n">
         <v>5094199808</v>
@@ -5732,25 +5741,25 @@
         <v>-0.022079999</v>
       </c>
       <c r="Q26" t="n">
-        <v>3775.3335</v>
+        <v>3763.8335</v>
       </c>
       <c r="R26" t="n">
-        <v>45.27818</v>
+        <v>45.140255</v>
       </c>
       <c r="S26" t="n">
-        <v>119.7364422623746</v>
+        <v>119.3717079386224</v>
       </c>
       <c r="T26" t="n">
-        <v>0.2459846010452018</v>
+        <v>0.2421892081418815</v>
       </c>
       <c r="U26" t="n">
-        <v>0.350342797451332</v>
+        <v>0.3462295191120994</v>
       </c>
       <c r="V26" t="n">
-        <v>1.493958391397455</v>
+        <v>1.486361546322527</v>
       </c>
       <c r="W26" t="n">
-        <v>1.14400995834514</v>
+        <v>1.137479090970274</v>
       </c>
       <c r="X26" t="n">
         <v>0.01467</v>
@@ -5760,7 +5769,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>2026-08-27T18:56:29.474358+00:00</t>
+          <t>2026-08-27T19:10:19.012182+00:00</t>
         </is>
       </c>
       <c r="AD26" t="inlineStr">
@@ -5791,10 +5800,10 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>268110364672</v>
+        <v>268569493504</v>
       </c>
       <c r="F27" t="n">
-        <v>251.0399932861328</v>
+        <v>251.4698944091797</v>
       </c>
       <c r="G27" t="n">
         <v>5155999744</v>
@@ -5824,25 +5833,25 @@
         <v>0.07603</v>
       </c>
       <c r="Q27" t="n">
-        <v>256.16324</v>
+        <v>256.60193</v>
       </c>
       <c r="R27" t="n">
-        <v>51.999687</v>
+        <v>52.088734</v>
       </c>
       <c r="S27" t="n">
-        <v>200.9069847141428</v>
+        <v>201.2510303065065</v>
       </c>
       <c r="T27" t="n">
-        <v>0.02574155287883539</v>
+        <v>0.02749811540804115</v>
       </c>
       <c r="U27" t="n">
-        <v>-0.251230347145996</v>
+        <v>-0.2499480936275359</v>
       </c>
       <c r="V27" t="n">
-        <v>0.9055714499659648</v>
+        <v>0.9088347041417755</v>
       </c>
       <c r="W27" t="n">
-        <v>0.7847290398852542</v>
+        <v>0.7877853537758721</v>
       </c>
       <c r="X27" t="n">
         <v>0.0007</v>
@@ -5852,7 +5861,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>2026-08-27T18:56:33.535883+00:00</t>
+          <t>2026-08-27T19:10:23.019520+00:00</t>
         </is>
       </c>
       <c r="AD27" t="inlineStr">
@@ -5883,10 +5892,10 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>219140128768</v>
+        <v>219265957888</v>
       </c>
       <c r="F28" t="n">
-        <v>243.8099975585938</v>
+        <v>243.9799957275391</v>
       </c>
       <c r="G28" t="n">
         <v>8717100032</v>
@@ -5916,25 +5925,25 @@
         <v>0.14479999</v>
       </c>
       <c r="Q28" t="n">
-        <v>83.50684</v>
+        <v>83.554794</v>
       </c>
       <c r="R28" t="n">
-        <v>25.139109</v>
+        <v>25.155605</v>
       </c>
       <c r="S28" t="n">
-        <v>96.5502575226573</v>
+        <v>96.6056961774037</v>
       </c>
       <c r="T28" t="n">
-        <v>0.3974321995342689</v>
+        <v>0.39840656858199</v>
       </c>
       <c r="U28" t="n">
-        <v>0.1905977961358609</v>
+        <v>0.1914279484976187</v>
       </c>
       <c r="V28" t="n">
-        <v>2.015227924453673</v>
+        <v>2.017330027810736</v>
       </c>
       <c r="W28" t="n">
-        <v>2.266873126795511</v>
+        <v>2.269150976167124</v>
       </c>
       <c r="X28" t="n">
         <v>0.00494</v>
@@ -5944,7 +5953,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>2026-08-27T18:56:34.001261+00:00</t>
+          <t>2026-08-27T19:10:23.450534+00:00</t>
         </is>
       </c>
       <c r="AD28" t="inlineStr">
@@ -5975,10 +5984,10 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1449874948096</v>
+        <v>1452460736512</v>
       </c>
       <c r="F29" t="n">
-        <v>569.135009765625</v>
+        <v>570.10498046875</v>
       </c>
       <c r="G29" t="n">
         <v>228246994944</v>
@@ -6008,25 +6017,25 @@
         <v>0.34827</v>
       </c>
       <c r="Q29" t="n">
-        <v>21.428276</v>
+        <v>21.466492</v>
       </c>
       <c r="R29" t="n">
-        <v>6.352219</v>
+        <v>6.3635483</v>
       </c>
       <c r="S29" t="n">
-        <v>67.26826425607723</v>
+        <v>67.38823425673571</v>
       </c>
       <c r="T29" t="n">
-        <v>-0.0409075756685906</v>
+        <v>-0.03927300471929396</v>
       </c>
       <c r="U29" t="n">
-        <v>-0.1033031883113618</v>
+        <v>-0.1017749575365905</v>
       </c>
       <c r="V29" t="n">
-        <v>-0.1277972744705423</v>
+        <v>-0.1263107069824991</v>
       </c>
       <c r="W29" t="n">
-        <v>-0.2359973594586448</v>
+        <v>-0.2346952152351088</v>
       </c>
       <c r="X29" t="n">
         <v>0.00148</v>
@@ -6036,7 +6045,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>2026-08-27T18:56:31.661173+00:00</t>
+          <t>2026-08-27T19:10:21.154513+00:00</t>
         </is>
       </c>
       <c r="AD29" t="inlineStr">
@@ -6067,10 +6076,10 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>142429995008</v>
+        <v>142921089024</v>
       </c>
       <c r="F30" t="n">
-        <v>137.7649993896484</v>
+        <v>138.2400054931641</v>
       </c>
       <c r="G30" t="n">
         <v>14732000256</v>
@@ -6100,25 +6109,25 @@
         <v>0.04063</v>
       </c>
       <c r="Q30" t="n">
-        <v>86.10312999999999</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="R30" t="n">
-        <v>9.668068999999999</v>
+        <v>9.701404999999999</v>
       </c>
       <c r="S30" t="n">
-        <v>27.65966659484539</v>
+        <v>27.75503623063398</v>
       </c>
       <c r="T30" t="n">
-        <v>0.245389585690506</v>
+        <v>0.2496836201483048</v>
       </c>
       <c r="U30" t="n">
-        <v>0.267037571381288</v>
+        <v>0.2714062468972476</v>
       </c>
       <c r="V30" t="n">
-        <v>0.3217403334227564</v>
+        <v>0.3262976210387702</v>
       </c>
       <c r="W30" t="n">
-        <v>-0.2242786730155888</v>
+        <v>-0.2216040287548745</v>
       </c>
       <c r="X30" t="n">
         <v>0.00176</v>
@@ -6128,7 +6137,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>2026-08-27T18:56:37.840528+00:00</t>
+          <t>2026-08-27T19:10:26.954003+00:00</t>
         </is>
       </c>
       <c r="AD30" t="inlineStr">
@@ -6159,10 +6168,10 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>431638609920</v>
+        <v>434951127040</v>
       </c>
       <c r="F31" t="n">
-        <v>149.8500061035156</v>
+        <v>151.0399932861328</v>
       </c>
       <c r="G31" t="n">
         <v>67356999680</v>
@@ -6192,22 +6201,22 @@
         <v>0.36202</v>
       </c>
       <c r="Q31" t="n">
-        <v>25.659246</v>
+        <v>25.856163</v>
       </c>
       <c r="R31" t="n">
-        <v>6.408222</v>
+        <v>6.4574003</v>
       </c>
       <c r="T31" t="n">
-        <v>0.249166449209417</v>
+        <v>0.2590863157624272</v>
       </c>
       <c r="U31" t="n">
-        <v>-0.2618000464693201</v>
+        <v>-0.2559378613032863</v>
       </c>
       <c r="V31" t="n">
-        <v>0.02032945585622126</v>
+        <v>0.02843208465209157</v>
       </c>
       <c r="W31" t="n">
-        <v>-0.357287870350367</v>
+        <v>-0.3521839296204266</v>
       </c>
       <c r="X31" t="n">
         <v>0.40498</v>
@@ -6217,7 +6226,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>2026-08-27T18:56:32.140292+00:00</t>
+          <t>2026-08-27T19:10:21.582339+00:00</t>
         </is>
       </c>
       <c r="AD31" t="inlineStr">
@@ -6245,7 +6254,7 @@
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
@@ -6302,27 +6311,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>MU</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>84.2</v>
+        <v>100</v>
       </c>
       <c r="C2" t="n">
-        <v>88.2</v>
+        <v>100</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>MODERATE</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>price_to_sales, price_to_fcf</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -6336,11 +6340,11 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>MU</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="C3" t="n">
         <v>100</v>
@@ -6351,7 +6355,7 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -7288,11 +7292,11 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>MU</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>56.7</v>
+        <v>55.57</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -7305,7 +7309,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>84.2</v>
+        <v>100</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>

--- a/reports/investment_dashboard.xlsx
+++ b/reports/investment_dashboard.xlsx
@@ -534,7 +534,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>55.57</v>
+        <v>55.59</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>424.6400146484375</v>
+        <v>425.6600036621094</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -581,7 +581,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>54.4</v>
+        <v>54.41</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -589,7 +589,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>917.35498046875</v>
+        <v>919.1599731445312</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>53.52</v>
+        <v>53.49</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>237.0549926757812</v>
+        <v>236.1399993896484</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -685,7 +685,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>52.93</v>
+        <v>52.92</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -693,7 +693,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>200.5</v>
+        <v>200.3200073242188</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -737,7 +737,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>52.38</v>
+        <v>52.42</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -745,7 +745,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>185.9900054931641</v>
+        <v>186.3549957275391</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>51.15</v>
+        <v>51.16</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>466.2699890136719</v>
+        <v>466.6199951171875</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -836,7 +836,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>50.91</v>
+        <v>50.98</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -844,7 +844,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>226.3699951171875</v>
+        <v>227.2749938964844</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>50.82</v>
+        <v>50.84</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>364.4974975585938</v>
+        <v>364.9800109863281</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>47.64</v>
+        <v>47.65</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -943,7 +943,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>18.29500007629395</v>
+        <v>18.2549991607666</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -982,7 +982,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>47.56</v>
+        <v>47.59</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -990,7 +990,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>470.8500061035156</v>
+        <v>472.9599914550781</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>46.74</v>
+        <v>46.73</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -1042,7 +1042,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>340.8699951171875</v>
+        <v>340.5799865722656</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>45.42</v>
+        <v>45.43</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -1089,7 +1089,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>476.8150024414062</v>
+        <v>477.2999877929688</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -1128,7 +1128,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>45.13</v>
+        <v>45.18</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>242.5149993896484</v>
+        <v>243.8099975585938</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -1232,7 +1232,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>43.82</v>
+        <v>43.81</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>445.3099975585938</v>
+        <v>444.0700073242188</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1279,7 +1279,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>43.2</v>
+        <v>43.18</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -1287,7 +1287,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>331.3800048828125</v>
+        <v>330.7699890136719</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1331,7 +1331,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>43.03</v>
+        <v>43.05</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -1339,7 +1339,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>305.9150085449219</v>
+        <v>306.3900146484375</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1383,7 +1383,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>42.56</v>
+        <v>42.57</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -1391,7 +1391,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>255.6943969726562</v>
+        <v>255.8200073242188</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>80.02999877929688</v>
+        <v>79.97000122070312</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1490,7 +1490,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>268.9800109863281</v>
+        <v>268.8800048828125</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1534,7 +1534,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>42.43</v>
+        <v>42.45</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -1542,7 +1542,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>505.2099914550781</v>
+        <v>505.7349853515625</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1581,7 +1581,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>42.35</v>
+        <v>42.34</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1726.535034179688</v>
+        <v>1725.64501953125</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1628,7 +1628,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>42.24</v>
+        <v>42.25</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -1636,7 +1636,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>385.9349975585938</v>
+        <v>386.8299865722656</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1680,7 +1680,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>41.89</v>
+        <v>41.81</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>38.47499847412109</v>
+        <v>38.31499862670898</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1708,7 +1708,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>Industry Growth; Balance Sheet; Competitive Advantage; Catalysts; Inflation Resilience</t>
+          <t>Industry Growth; Balance Sheet; Competitive Advantage; Momentum; Catalysts; Inflation Resilience</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -1732,7 +1732,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>41.01</v>
+        <v>41.08</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -1740,7 +1740,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>225.8300018310547</v>
+        <v>227.2550048828125</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1784,7 +1784,7 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>40.73</v>
+        <v>40.72</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -1792,7 +1792,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>251.4698944091797</v>
+        <v>251</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1836,7 +1836,7 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>39.87</v>
+        <v>39.81</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>243.9799957275391</v>
+        <v>242.5399932861328</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1896,7 +1896,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>570.10498046875</v>
+        <v>569.5</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>36.46</v>
+        <v>36.49</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -1943,7 +1943,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>138.2400054931641</v>
+        <v>138.5399932861328</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1977,7 +1977,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>31.52</v>
+        <v>31.51</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -1985,7 +1985,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>151.0399932861328</v>
+        <v>150.7449951171875</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -2131,13 +2131,13 @@
         <v>8.84</v>
       </c>
       <c r="F2" t="n">
-        <v>8.65</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>5.39</v>
+        <v>5.42</v>
       </c>
       <c r="I2" t="n">
         <v>2.69</v>
@@ -2149,7 +2149,7 @@
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>55.57</v>
+        <v>55.59</v>
       </c>
     </row>
     <row r="3">
@@ -2171,13 +2171,13 @@
         <v>9.02</v>
       </c>
       <c r="F3" t="n">
-        <v>5.01</v>
+        <v>5</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>6.87</v>
+        <v>6.89</v>
       </c>
       <c r="I3" t="n">
         <v>3.5</v>
@@ -2189,7 +2189,7 @@
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>54.4</v>
+        <v>54.41</v>
       </c>
     </row>
     <row r="4">
@@ -2211,13 +2211,13 @@
         <v>9.91</v>
       </c>
       <c r="F4" t="n">
-        <v>2.35</v>
+        <v>2.36</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>7.72</v>
+        <v>7.68</v>
       </c>
       <c r="I4" t="n">
         <v>3.54</v>
@@ -2229,7 +2229,7 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>53.52</v>
+        <v>53.49</v>
       </c>
     </row>
     <row r="5">
@@ -2257,7 +2257,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>8.51</v>
+        <v>8.5</v>
       </c>
       <c r="I5" t="n">
         <v>3.63</v>
@@ -2269,7 +2269,7 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>52.93</v>
+        <v>52.92</v>
       </c>
     </row>
     <row r="6">
@@ -2297,7 +2297,7 @@
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>8.5</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="I6" t="n">
         <v>3.35</v>
@@ -2309,7 +2309,7 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>52.38</v>
+        <v>52.42</v>
       </c>
     </row>
     <row r="7">
@@ -2337,7 +2337,7 @@
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>9.039999999999999</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="I7" t="n">
         <v>3.54</v>
@@ -2349,7 +2349,7 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>51.15</v>
+        <v>51.16</v>
       </c>
     </row>
     <row r="8">
@@ -2371,13 +2371,13 @@
         <v>9.029999999999999</v>
       </c>
       <c r="F8" t="n">
-        <v>2.92</v>
+        <v>2.91</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>5.52</v>
+        <v>5.6</v>
       </c>
       <c r="I8" t="n">
         <v>3.44</v>
@@ -2389,7 +2389,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>50.91</v>
+        <v>50.98</v>
       </c>
     </row>
     <row r="9">
@@ -2417,7 +2417,7 @@
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>5.24</v>
+        <v>5.26</v>
       </c>
       <c r="I9" t="n">
         <v>3.75</v>
@@ -2429,7 +2429,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>50.82</v>
+        <v>50.84</v>
       </c>
     </row>
     <row r="10">
@@ -2451,7 +2451,7 @@
         <v>9.699999999999999</v>
       </c>
       <c r="F10" t="n">
-        <v>6.51</v>
+        <v>6.52</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -2469,7 +2469,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>47.64</v>
+        <v>47.65</v>
       </c>
     </row>
     <row r="11">
@@ -2491,13 +2491,13 @@
         <v>8.77</v>
       </c>
       <c r="F11" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>6.11</v>
+        <v>6.15</v>
       </c>
       <c r="I11" t="n">
         <v>3.45</v>
@@ -2509,7 +2509,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>47.56</v>
+        <v>47.59</v>
       </c>
     </row>
     <row r="12">
@@ -2537,7 +2537,7 @@
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>4.48</v>
+        <v>4.47</v>
       </c>
       <c r="I12" t="n">
         <v>3.53</v>
@@ -2549,7 +2549,7 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>46.74</v>
+        <v>46.73</v>
       </c>
     </row>
     <row r="13">
@@ -2577,7 +2577,7 @@
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>5.79</v>
+        <v>5.8</v>
       </c>
       <c r="I13" t="n">
         <v>3.58</v>
@@ -2589,7 +2589,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>45.42</v>
+        <v>45.43</v>
       </c>
     </row>
     <row r="14">
@@ -2617,7 +2617,7 @@
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>6.56</v>
+        <v>6.61</v>
       </c>
       <c r="I14" t="n">
         <v>3.67</v>
@@ -2629,7 +2629,7 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>45.13</v>
+        <v>45.18</v>
       </c>
     </row>
     <row r="15">
@@ -2691,13 +2691,13 @@
         <v>9.880000000000001</v>
       </c>
       <c r="F16" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>9.85</v>
+        <v>9.83</v>
       </c>
       <c r="I16" t="n">
         <v>3.73</v>
@@ -2709,7 +2709,7 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>43.82</v>
+        <v>43.81</v>
       </c>
     </row>
     <row r="17">
@@ -2737,7 +2737,7 @@
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>9.140000000000001</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="I17" t="n">
         <v>3.56</v>
@@ -2749,7 +2749,7 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>43.2</v>
+        <v>43.18</v>
       </c>
     </row>
     <row r="18">
@@ -2777,7 +2777,7 @@
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>8.630000000000001</v>
+        <v>8.65</v>
       </c>
       <c r="I18" t="n">
         <v>3.64</v>
@@ -2789,7 +2789,7 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>43.03</v>
+        <v>43.05</v>
       </c>
     </row>
     <row r="19">
@@ -2817,7 +2817,7 @@
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>4.41</v>
+        <v>4.42</v>
       </c>
       <c r="I19" t="n">
         <v>3.47</v>
@@ -2829,7 +2829,7 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>42.56</v>
+        <v>42.57</v>
       </c>
     </row>
     <row r="20">
@@ -2851,13 +2851,13 @@
         <v>4.02</v>
       </c>
       <c r="F20" t="n">
-        <v>6.82</v>
+        <v>6.83</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>5.19</v>
+        <v>5.18</v>
       </c>
       <c r="I20" t="n">
         <v>3.63</v>
@@ -2937,7 +2937,7 @@
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>6.11</v>
+        <v>6.13</v>
       </c>
       <c r="I22" t="n">
         <v>3.45</v>
@@ -2949,7 +2949,7 @@
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>42.43</v>
+        <v>42.45</v>
       </c>
     </row>
     <row r="23">
@@ -2977,7 +2977,7 @@
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>5.92</v>
+        <v>5.91</v>
       </c>
       <c r="I23" t="n">
         <v>2.76</v>
@@ -2989,7 +2989,7 @@
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>42.35</v>
+        <v>42.34</v>
       </c>
     </row>
     <row r="24">
@@ -3017,7 +3017,7 @@
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>9.140000000000001</v>
+        <v>9.15</v>
       </c>
       <c r="I24" t="n">
         <v>3.57</v>
@@ -3029,7 +3029,7 @@
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>42.24</v>
+        <v>42.25</v>
       </c>
     </row>
     <row r="25">
@@ -3057,7 +3057,7 @@
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>4.04</v>
+        <v>3.96</v>
       </c>
       <c r="I25" t="n">
         <v>3.54</v>
@@ -3069,7 +3069,7 @@
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>41.89</v>
+        <v>41.81</v>
       </c>
     </row>
     <row r="26">
@@ -3097,7 +3097,7 @@
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>9.039999999999999</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="I26" t="n">
         <v>3.48</v>
@@ -3109,7 +3109,7 @@
         <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>41.01</v>
+        <v>41.08</v>
       </c>
     </row>
     <row r="27">
@@ -3137,7 +3137,7 @@
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>5.81</v>
+        <v>5.8</v>
       </c>
       <c r="I27" t="n">
         <v>3.7</v>
@@ -3149,7 +3149,7 @@
         <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>40.73</v>
+        <v>40.72</v>
       </c>
     </row>
     <row r="28">
@@ -3177,7 +3177,7 @@
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>9.039999999999999</v>
+        <v>8.98</v>
       </c>
       <c r="I28" t="n">
         <v>3.53</v>
@@ -3189,7 +3189,7 @@
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>39.87</v>
+        <v>39.81</v>
       </c>
     </row>
     <row r="29">
@@ -3211,13 +3211,13 @@
         <v>7.23</v>
       </c>
       <c r="F29" t="n">
-        <v>5.64</v>
+        <v>5.65</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>0.83</v>
+        <v>0.82</v>
       </c>
       <c r="I29" t="n">
         <v>3.49</v>
@@ -3251,13 +3251,13 @@
         <v>6.78</v>
       </c>
       <c r="F30" t="n">
-        <v>3.65</v>
+        <v>3.64</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>5.9</v>
+        <v>5.94</v>
       </c>
       <c r="I30" t="n">
         <v>3.57</v>
@@ -3269,7 +3269,7 @@
         <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>36.46</v>
+        <v>36.49</v>
       </c>
     </row>
     <row r="31">
@@ -3291,13 +3291,13 @@
         <v>0.8</v>
       </c>
       <c r="F31" t="n">
-        <v>6.33</v>
+        <v>6.34</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>2.67</v>
+        <v>2.65</v>
       </c>
       <c r="I31" t="n">
         <v>3.58</v>
@@ -3309,7 +3309,7 @@
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>31.52</v>
+        <v>31.51</v>
       </c>
     </row>
   </sheetData>
@@ -3347,7 +3347,7 @@
     <col width="16" customWidth="1" min="18" max="18"/>
     <col width="19" customWidth="1" min="19" max="19"/>
     <col width="23" customWidth="1" min="20" max="20"/>
-    <col width="23" customWidth="1" min="21" max="21"/>
+    <col width="22" customWidth="1" min="21" max="21"/>
     <col width="21" customWidth="1" min="22" max="22"/>
     <col width="22" customWidth="1" min="23" max="23"/>
     <col width="18" customWidth="1" min="24" max="24"/>
@@ -3533,10 +3533,10 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2202384465920</v>
+        <v>2207700484096</v>
       </c>
       <c r="F2" t="n">
-        <v>424.6400146484375</v>
+        <v>425.6600036621094</v>
       </c>
       <c r="G2" t="n">
         <v>4440492343296</v>
@@ -3566,25 +3566,25 @@
         <v>0.60344005</v>
       </c>
       <c r="Q2" t="n">
-        <v>31.665922</v>
+        <v>31.742357</v>
       </c>
       <c r="R2" t="n">
-        <v>0.49597755</v>
+        <v>0.4971221</v>
       </c>
       <c r="S2" t="n">
-        <v>3.013555102802129</v>
+        <v>3.020829088769962</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0824093632358045</v>
+        <v>0.08500931995375582</v>
       </c>
       <c r="U2" t="n">
-        <v>0.001822916010435272</v>
+        <v>0.004229303380267613</v>
       </c>
       <c r="V2" t="n">
-        <v>0.100853207272626</v>
+        <v>0.103497466264594</v>
       </c>
       <c r="W2" t="n">
-        <v>0.7942091235712727</v>
+        <v>0.7985188295131107</v>
       </c>
       <c r="X2" t="n">
         <v>0.00013</v>
@@ -3594,7 +3594,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>2026-08-27T19:10:22.074363+00:00</t>
+          <t>2026-08-27T19:31:13.383951+00:00</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
@@ -3625,10 +3625,10 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1035907629056</v>
+        <v>1037838909440</v>
       </c>
       <c r="F3" t="n">
-        <v>917.35498046875</v>
+        <v>919.1599731445312</v>
       </c>
       <c r="G3" t="n">
         <v>90273996800</v>
@@ -3658,25 +3658,25 @@
         <v>0.80370003</v>
       </c>
       <c r="Q3" t="n">
-        <v>20.751696</v>
+        <v>20.790384</v>
       </c>
       <c r="R3" t="n">
-        <v>11.476776</v>
+        <v>11.499358</v>
       </c>
       <c r="S3" t="n">
-        <v>135.5988820512009</v>
+        <v>135.8516839938186</v>
       </c>
       <c r="T3" t="n">
-        <v>0.1180029343409232</v>
+        <v>0.1202027230279112</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.006522800320584277</v>
+        <v>-0.0045680291500384</v>
       </c>
       <c r="V3" t="n">
-        <v>1.139583959694245</v>
+        <v>1.14379381679285</v>
       </c>
       <c r="W3" t="n">
-        <v>6.803204829179007</v>
+        <v>6.818558457669792</v>
       </c>
       <c r="X3" t="n">
         <v>0.00238</v>
@@ -3686,7 +3686,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>2026-08-27T19:10:17.194924+00:00</t>
+          <t>2026-08-27T19:31:08.578666+00:00</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
@@ -3717,10 +3717,10 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>44550852608</v>
+        <v>44378894336</v>
       </c>
       <c r="F4" t="n">
-        <v>237.0549926757812</v>
+        <v>236.1399993896484</v>
       </c>
       <c r="G4" t="n">
         <v>1335116032</v>
@@ -3750,25 +3750,25 @@
         <v>0.35661998</v>
       </c>
       <c r="Q4" t="n">
-        <v>94.44422</v>
+        <v>94.07968</v>
       </c>
       <c r="R4" t="n">
-        <v>33.368526</v>
+        <v>33.239727</v>
       </c>
       <c r="S4" t="n">
-        <v>177.6278053970771</v>
+        <v>176.9421940409041</v>
       </c>
       <c r="T4" t="n">
-        <v>0.2328635020841563</v>
+        <v>0.228104851720407</v>
       </c>
       <c r="U4" t="n">
-        <v>0.06613441047273771</v>
+        <v>0.06201930698267155</v>
       </c>
       <c r="V4" t="n">
-        <v>0.9200955324289746</v>
+        <v>0.9126842794489163</v>
       </c>
       <c r="W4" t="n">
-        <v>0.9315162241653185</v>
+        <v>0.9240608891933821</v>
       </c>
       <c r="X4" t="n">
         <v>0.09436</v>
@@ -3778,7 +3778,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>2026-08-27T19:10:18.055631+00:00</t>
+          <t>2026-08-27T19:31:09.368855+00:00</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
@@ -3809,10 +3809,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>252875554816</v>
+        <v>252648538112</v>
       </c>
       <c r="F5" t="n">
-        <v>200.5</v>
+        <v>200.3200073242188</v>
       </c>
       <c r="G5" t="n">
         <v>10540800000</v>
@@ -3842,25 +3842,25 @@
         <v>0.45393002</v>
       </c>
       <c r="Q5" t="n">
-        <v>63.449364</v>
+        <v>63.392406</v>
       </c>
       <c r="R5" t="n">
-        <v>23.990168</v>
+        <v>23.96863</v>
       </c>
       <c r="S5" t="n">
-        <v>64.98130222565675</v>
+        <v>64.92296585912408</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1814270936777762</v>
+        <v>0.1803665040327311</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2912989919686706</v>
+        <v>0.2901397682240419</v>
       </c>
       <c r="V5" t="n">
-        <v>0.5087666560379116</v>
+        <v>0.5074122074217033</v>
       </c>
       <c r="W5" t="n">
-        <v>0.5044645724636743</v>
+        <v>0.5031139859099794</v>
       </c>
       <c r="X5" t="n">
         <v>0.17247999</v>
@@ -3870,7 +3870,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>2026-08-27T19:10:23.861872+00:00</t>
+          <t>2026-08-27T19:31:15.122950+00:00</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
@@ -3901,10 +3901,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>446944837632</v>
+        <v>447821938688</v>
       </c>
       <c r="F6" t="n">
-        <v>185.9900054931641</v>
+        <v>186.3549957275391</v>
       </c>
       <c r="G6" t="n">
         <v>6155940864</v>
@@ -3934,25 +3934,25 @@
         <v>0.47120997</v>
       </c>
       <c r="Q6" t="n">
-        <v>158.96582</v>
+        <v>159.27779</v>
       </c>
       <c r="R6" t="n">
-        <v>72.60382</v>
+        <v>72.74045</v>
       </c>
       <c r="S6" t="n">
-        <v>207.0047258703519</v>
+        <v>207.4109595895282</v>
       </c>
       <c r="T6" t="n">
-        <v>0.5056262230315445</v>
+        <v>0.5085808918405932</v>
       </c>
       <c r="U6" t="n">
-        <v>0.29754437173792</v>
+        <v>0.3000906968648904</v>
       </c>
       <c r="V6" t="n">
-        <v>0.3860198383584958</v>
+        <v>0.3887397893811839</v>
       </c>
       <c r="W6" t="n">
-        <v>0.1867662330556075</v>
+        <v>0.1890951651097939</v>
       </c>
       <c r="X6" t="n">
         <v>0.03477</v>
@@ -3962,7 +3962,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>2026-08-27T19:10:14.937151+00:00</t>
+          <t>2026-08-27T19:31:06.543065+00:00</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr">
@@ -3993,10 +3993,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>301276823552</v>
+        <v>301502955520</v>
       </c>
       <c r="F7" t="n">
-        <v>466.2699890136719</v>
+        <v>466.6199951171875</v>
       </c>
       <c r="G7" t="n">
         <v>134001999872</v>
@@ -4026,25 +4026,25 @@
         <v>0.08857000600000001</v>
       </c>
       <c r="Q7" t="n">
-        <v>37.093876</v>
+        <v>37.12172</v>
       </c>
       <c r="R7" t="n">
-        <v>2.248301</v>
+        <v>2.2499886</v>
       </c>
       <c r="S7" t="n">
-        <v>55.44164601298814</v>
+        <v>55.48325933184309</v>
       </c>
       <c r="T7" t="n">
-        <v>0.1891608818046668</v>
+        <v>0.1900535267882613</v>
       </c>
       <c r="U7" t="n">
-        <v>0.473081497171941</v>
+        <v>0.4741872674920014</v>
       </c>
       <c r="V7" t="n">
-        <v>2.794019814344581</v>
+        <v>2.796867799681765</v>
       </c>
       <c r="W7" t="n">
-        <v>2.563861735907643</v>
+        <v>2.56653653685992</v>
       </c>
       <c r="X7" t="n">
         <v>0.07491</v>
@@ -4054,7 +4054,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>2026-08-27T19:10:24.268246+00:00</t>
+          <t>2026-08-27T19:31:15.575478+00:00</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr">
@@ -4085,10 +4085,10 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5482907435008</v>
+        <v>5505190723584</v>
       </c>
       <c r="F8" t="n">
-        <v>226.3699951171875</v>
+        <v>227.2749938964844</v>
       </c>
       <c r="G8" t="n">
         <v>253491003392</v>
@@ -4118,25 +4118,25 @@
         <v>0.65596</v>
       </c>
       <c r="Q8" t="n">
-        <v>34.719326</v>
+        <v>34.860428</v>
       </c>
       <c r="R8" t="n">
-        <v>21.629593</v>
+        <v>21.717499</v>
       </c>
       <c r="S8" t="n">
-        <v>118.3296456326201</v>
+        <v>118.810553558202</v>
       </c>
       <c r="T8" t="n">
-        <v>0.1490279753768169</v>
+        <v>0.1536216447566994</v>
       </c>
       <c r="U8" t="n">
-        <v>0.05780084938460894</v>
+        <v>0.06202980418463322</v>
       </c>
       <c r="V8" t="n">
-        <v>0.1589594149714932</v>
+        <v>0.1635927889982092</v>
       </c>
       <c r="W8" t="n">
-        <v>0.2481909902378594</v>
+        <v>0.2531812063212786</v>
       </c>
       <c r="X8" t="n">
         <v>0.03991</v>
@@ -4146,7 +4146,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>2026-08-27T19:10:14.483161+00:00</t>
+          <t>2026-08-27T19:31:06.056129+00:00</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr">
@@ -4177,10 +4177,10 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>56985812992</v>
+        <v>57061249024</v>
       </c>
       <c r="F9" t="n">
-        <v>364.4974975585938</v>
+        <v>364.9800109863281</v>
       </c>
       <c r="G9" t="n">
         <v>4464031232</v>
@@ -4210,25 +4210,25 @@
         <v>0.33161</v>
       </c>
       <c r="Q9" t="n">
-        <v>50.206264</v>
+        <v>50.272728</v>
       </c>
       <c r="R9" t="n">
-        <v>12.76555</v>
+        <v>12.782449</v>
       </c>
       <c r="S9" t="n">
-        <v>130.2886514970116</v>
+        <v>130.4611235276369</v>
       </c>
       <c r="T9" t="n">
-        <v>0.1367456868758423</v>
+        <v>0.138250484745541</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.04743890403092832</v>
+        <v>-0.04617792549850763</v>
       </c>
       <c r="V9" t="n">
-        <v>0.06363441661690827</v>
+        <v>0.06504243146380206</v>
       </c>
       <c r="W9" t="n">
-        <v>2.123605365663288</v>
+        <v>2.127740322808319</v>
       </c>
       <c r="X9" t="n">
         <v>0.00202</v>
@@ -4238,7 +4238,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>2026-08-27T19:10:18.609464+00:00</t>
+          <t>2026-08-27T19:31:09.853556+00:00</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr">
@@ -4269,10 +4269,10 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>9479010304</v>
+        <v>9458284544</v>
       </c>
       <c r="F10" t="n">
-        <v>18.29500007629395</v>
+        <v>18.2549991607666</v>
       </c>
       <c r="G10" t="n">
         <v>1672329984</v>
@@ -4299,25 +4299,25 @@
         <v>0.07274</v>
       </c>
       <c r="Q10" t="n">
-        <v>30.491665</v>
+        <v>30.424997</v>
       </c>
       <c r="R10" t="n">
-        <v>5.6681457</v>
+        <v>5.6557527</v>
       </c>
       <c r="S10" t="n">
-        <v>18.52984655184698</v>
+        <v>18.48933123008303</v>
       </c>
       <c r="T10" t="n">
-        <v>0.5008204024662222</v>
+        <v>0.4975389490696434</v>
       </c>
       <c r="U10" t="n">
-        <v>0.5798791188971637</v>
+        <v>0.576424808379816</v>
       </c>
       <c r="V10" t="n">
-        <v>0.8405433449312543</v>
+        <v>0.8365191077867895</v>
       </c>
       <c r="W10" t="n">
-        <v>0.6422800280486394</v>
+        <v>0.6386892817026288</v>
       </c>
       <c r="X10" t="n">
         <v>0.09236999999999999</v>
@@ -4327,7 +4327,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>2026-08-27T19:10:27.840175+00:00</t>
+          <t>2026-08-27T19:31:18.915719+00:00</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr">
@@ -4358,10 +4358,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>768650838016</v>
+        <v>772065198080</v>
       </c>
       <c r="F11" t="n">
-        <v>470.8500061035156</v>
+        <v>472.9599914550781</v>
       </c>
       <c r="G11" t="n">
         <v>41305001984</v>
@@ -4391,25 +4391,25 @@
         <v>0.1725</v>
       </c>
       <c r="Q11" t="n">
-        <v>119.50507</v>
+        <v>120.03591</v>
       </c>
       <c r="R11" t="n">
-        <v>18.609146</v>
+        <v>18.693726</v>
       </c>
       <c r="S11" t="n">
-        <v>86.93670402281511</v>
+        <v>87.32287833712076</v>
       </c>
       <c r="T11" t="n">
-        <v>0.03570016972558476</v>
+        <v>0.04034137639098589</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.09118110425455395</v>
+        <v>-0.08710848126976301</v>
       </c>
       <c r="V11" t="n">
-        <v>1.232998220338621</v>
+        <v>1.243004790316118</v>
       </c>
       <c r="W11" t="n">
-        <v>1.817267949185212</v>
+        <v>1.829892763939702</v>
       </c>
       <c r="X11" t="n">
         <v>0.00425</v>
@@ -4419,7 +4419,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>2026-08-27T19:10:15.476657+00:00</t>
+          <t>2026-08-27T19:31:06.935233+00:00</t>
         </is>
       </c>
       <c r="AD11" t="inlineStr">
@@ -4450,10 +4450,10 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4168940257280</v>
+        <v>4165515870208</v>
       </c>
       <c r="F12" t="n">
-        <v>340.8699951171875</v>
+        <v>340.5799865722656</v>
       </c>
       <c r="G12" t="n">
         <v>445865984000</v>
@@ -4483,25 +4483,25 @@
         <v>0.34033</v>
       </c>
       <c r="Q12" t="n">
-        <v>17.095285</v>
+        <v>17.081244</v>
       </c>
       <c r="R12" t="n">
-        <v>9.349935</v>
+        <v>9.342529000000001</v>
       </c>
       <c r="S12" t="n">
-        <v>183.9373518949986</v>
+        <v>183.7862648918238</v>
       </c>
       <c r="T12" t="n">
-        <v>0.02145576652017378</v>
+        <v>0.02058672288244123</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.1257437589370631</v>
+        <v>-0.1264875667934054</v>
       </c>
       <c r="V12" t="n">
-        <v>0.09080763274360049</v>
+        <v>0.08987947884422121</v>
       </c>
       <c r="W12" t="n">
-        <v>0.6475921895038983</v>
+        <v>0.6461905571083069</v>
       </c>
       <c r="X12" t="n">
         <v>0.01596</v>
@@ -4511,7 +4511,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>2026-08-27T19:10:20.367109+00:00</t>
+          <t>2026-08-27T19:31:11.499635+00:00</t>
         </is>
       </c>
       <c r="AD12" t="inlineStr">
@@ -4542,10 +4542,10 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>378399162368</v>
+        <v>378784055296</v>
       </c>
       <c r="F13" t="n">
-        <v>476.8150024414062</v>
+        <v>477.2999877929688</v>
       </c>
       <c r="G13" t="n">
         <v>30837000192</v>
@@ -4575,25 +4575,25 @@
         <v>0.33736</v>
       </c>
       <c r="Q13" t="n">
-        <v>41.06934</v>
+        <v>41.11111</v>
       </c>
       <c r="R13" t="n">
-        <v>12.270946</v>
+        <v>12.283427</v>
       </c>
       <c r="S13" t="n">
-        <v>123.0416289303485</v>
+        <v>123.1667820954045</v>
       </c>
       <c r="T13" t="n">
-        <v>0.001815213217983835</v>
+        <v>0.002834194795525269</v>
       </c>
       <c r="U13" t="n">
-        <v>0.06147679921714055</v>
+        <v>0.06255646469747966</v>
       </c>
       <c r="V13" t="n">
-        <v>0.210072827696365</v>
+        <v>0.2113036354367919</v>
       </c>
       <c r="W13" t="n">
-        <v>1.916553662460941</v>
+        <v>1.919520464519896</v>
       </c>
       <c r="X13" t="n">
         <v>0.00331</v>
@@ -4603,7 +4603,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>2026-08-27T19:10:16.663342+00:00</t>
+          <t>2026-08-27T19:31:08.079723+00:00</t>
         </is>
       </c>
       <c r="AD13" t="inlineStr">
@@ -4634,10 +4634,10 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>87081074688</v>
+        <v>87546077184</v>
       </c>
       <c r="F14" t="n">
-        <v>242.5149993896484</v>
+        <v>243.8099975585938</v>
       </c>
       <c r="G14" t="n">
         <v>3966725120</v>
@@ -4667,25 +4667,25 @@
         <v>0.00666</v>
       </c>
       <c r="Q14" t="n">
-        <v>485.03</v>
+        <v>487.62</v>
       </c>
       <c r="R14" t="n">
-        <v>21.952888</v>
+        <v>22.064684</v>
       </c>
       <c r="S14" t="n">
-        <v>82.82295192971064</v>
+        <v>83.26521656081894</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.03334265517521573</v>
+        <v>-0.02818083221706402</v>
       </c>
       <c r="U14" t="n">
-        <v>0.07669593977615441</v>
+        <v>0.08244535434444966</v>
       </c>
       <c r="V14" t="n">
-        <v>1.198087513503399</v>
+        <v>1.20982501144098</v>
       </c>
       <c r="W14" t="n">
-        <v>0.8410005864666479</v>
+        <v>0.8508312872253709</v>
       </c>
       <c r="X14" t="n">
         <v>0.00619</v>
@@ -4695,7 +4695,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>2026-08-27T19:10:26.019124+00:00</t>
+          <t>2026-08-27T19:31:17.258344+00:00</t>
         </is>
       </c>
       <c r="AD14" t="inlineStr">
@@ -4726,7 +4726,7 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1755975254016</v>
+        <v>1755927674880</v>
       </c>
       <c r="F15" t="n">
         <v>369.0799865722656</v>
@@ -4759,13 +4759,13 @@
         <v>0.48988</v>
       </c>
       <c r="Q15" t="n">
-        <v>61.412643</v>
+        <v>61.410976</v>
       </c>
       <c r="R15" t="n">
-        <v>23.268738</v>
+        <v>23.270945</v>
       </c>
       <c r="S15" t="n">
-        <v>64.52885420596661</v>
+        <v>64.52710576041012</v>
       </c>
       <c r="T15" t="n">
         <v>-0.0310572496813124</v>
@@ -4787,7 +4787,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>2026-08-27T19:10:16.154303+00:00</t>
+          <t>2026-08-27T19:31:07.521984+00:00</t>
         </is>
       </c>
       <c r="AD15" t="inlineStr">
@@ -4818,10 +4818,10 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>35817140224</v>
+        <v>35717406720</v>
       </c>
       <c r="F16" t="n">
-        <v>445.3099975585938</v>
+        <v>444.0700073242188</v>
       </c>
       <c r="G16" t="n">
         <v>2602398976</v>
@@ -4848,22 +4848,22 @@
         <v>-0.03607</v>
       </c>
       <c r="R16" t="n">
-        <v>13.763124</v>
+        <v>13.7248</v>
       </c>
       <c r="S16" t="n">
-        <v>69.19777476190664</v>
+        <v>69.00509225004649</v>
       </c>
       <c r="T16" t="n">
-        <v>0.4336166523684086</v>
+        <v>0.4296246677767301</v>
       </c>
       <c r="U16" t="n">
-        <v>0.3673237766309636</v>
+        <v>0.3635163882059416</v>
       </c>
       <c r="V16" t="n">
-        <v>0.413727455997098</v>
+        <v>0.4097908539690389</v>
       </c>
       <c r="W16" t="n">
-        <v>0.5059519079316597</v>
+        <v>0.5017585018336348</v>
       </c>
       <c r="X16" t="n">
         <v>0.02641</v>
@@ -4873,7 +4873,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>2026-08-27T19:10:27.454223+00:00</t>
+          <t>2026-08-27T19:31:18.488556+00:00</t>
         </is>
       </c>
       <c r="AD16" t="inlineStr">
@@ -4904,10 +4904,10 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>114856312832</v>
+        <v>114644877312</v>
       </c>
       <c r="F17" t="n">
-        <v>331.3800048828125</v>
+        <v>330.7699890136719</v>
       </c>
       <c r="G17" t="n">
         <v>5032822784</v>
@@ -4934,22 +4934,22 @@
         <v>-0.22173999</v>
       </c>
       <c r="R17" t="n">
-        <v>22.82145</v>
+        <v>22.779438</v>
       </c>
       <c r="S17" t="n">
-        <v>66.02843509548981</v>
+        <v>65.90688534201983</v>
       </c>
       <c r="T17" t="n">
-        <v>0.2256991523797527</v>
+        <v>0.223442842636477</v>
       </c>
       <c r="U17" t="n">
-        <v>0.3853679310644644</v>
+        <v>0.3828176974652868</v>
       </c>
       <c r="V17" t="n">
-        <v>0.9583948450706792</v>
+        <v>0.9547897635451392</v>
       </c>
       <c r="W17" t="n">
-        <v>0.6536753625037968</v>
+        <v>0.6506312192281911</v>
       </c>
       <c r="X17" t="n">
         <v>0.02962</v>
@@ -4959,7 +4959,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>2026-08-27T19:10:25.625429+00:00</t>
+          <t>2026-08-27T19:31:16.860088+00:00</t>
         </is>
       </c>
       <c r="AD17" t="inlineStr">
@@ -4990,10 +4990,10 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>108930129920</v>
+        <v>109099270144</v>
       </c>
       <c r="F18" t="n">
-        <v>305.9150085449219</v>
+        <v>306.3900146484375</v>
       </c>
       <c r="G18" t="n">
         <v>2512349952</v>
@@ -5020,22 +5020,22 @@
         <v>-0.07902000000000001</v>
       </c>
       <c r="R18" t="n">
-        <v>43.357864</v>
+        <v>43.42519</v>
       </c>
       <c r="S18" t="n">
-        <v>157.2199184689333</v>
+        <v>157.4640402031737</v>
       </c>
       <c r="T18" t="n">
-        <v>0.1583301835480329</v>
+        <v>0.1601287677681691</v>
       </c>
       <c r="U18" t="n">
-        <v>0.3410854751058185</v>
+        <v>0.3431678305582084</v>
       </c>
       <c r="V18" t="n">
-        <v>0.7806461182236391</v>
+        <v>0.7834109965419038</v>
       </c>
       <c r="W18" t="n">
-        <v>0.490523291547617</v>
+        <v>0.4928376848959033</v>
       </c>
       <c r="X18" t="n">
         <v>0.00616</v>
@@ -5045,7 +5045,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>2026-08-27T19:10:26.510322+00:00</t>
+          <t>2026-08-27T19:31:17.648954+00:00</t>
         </is>
       </c>
       <c r="AD18" t="inlineStr">
@@ -5076,10 +5076,10 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2757999722496</v>
+        <v>2759354744832</v>
       </c>
       <c r="F19" t="n">
-        <v>255.6943969726562</v>
+        <v>255.8200073242188</v>
       </c>
       <c r="G19" t="n">
         <v>775680032768</v>
@@ -5109,25 +5109,25 @@
         <v>0.13689</v>
       </c>
       <c r="Q19" t="n">
-        <v>20.554213</v>
+        <v>20.56431</v>
       </c>
       <c r="R19" t="n">
-        <v>3.5555894</v>
+        <v>3.5573363</v>
       </c>
       <c r="S19" t="n">
-        <v>856.7544687919965</v>
+        <v>857.1753975659234</v>
       </c>
       <c r="T19" t="n">
-        <v>0.1075734050794728</v>
+        <v>0.1081175025897838</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.06680877017278741</v>
+        <v>-0.06635033823277825</v>
       </c>
       <c r="V19" t="n">
-        <v>0.2138928869804295</v>
+        <v>0.2144892141354164</v>
       </c>
       <c r="W19" t="n">
-        <v>0.1159846474415156</v>
+        <v>0.1165328769903955</v>
       </c>
       <c r="X19" t="n">
         <v>0.0887</v>
@@ -5137,7 +5137,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>2026-08-27T19:10:20.757478+00:00</t>
+          <t>2026-08-27T19:31:11.882822+00:00</t>
         </is>
       </c>
       <c r="AD19" t="inlineStr">
@@ -5168,10 +5168,10 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5574025216</v>
+        <v>5569846784</v>
       </c>
       <c r="F20" t="n">
-        <v>80.02999877929688</v>
+        <v>79.97000122070312</v>
       </c>
       <c r="G20" t="n">
         <v>1037772032</v>
@@ -5201,22 +5201,22 @@
         <v>0.16982001</v>
       </c>
       <c r="Q20" t="n">
-        <v>37.75</v>
+        <v>37.721703</v>
       </c>
       <c r="R20" t="n">
-        <v>5.371146</v>
+        <v>5.36712</v>
       </c>
       <c r="T20" t="n">
-        <v>0.1112191406496215</v>
+        <v>0.1103860725936605</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.138164998349402</v>
+        <v>-0.1388111060190056</v>
       </c>
       <c r="V20" t="n">
-        <v>0.1688330269095772</v>
+        <v>0.167956766393671</v>
       </c>
       <c r="W20" t="n">
-        <v>1.800209901782223</v>
+        <v>1.798110617011267</v>
       </c>
       <c r="X20" t="n">
         <v>0.12675999</v>
@@ -5226,7 +5226,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>2026-08-27T19:10:17.581832+00:00</t>
+          <t>2026-08-27T19:31:08.983706+00:00</t>
         </is>
       </c>
       <c r="AD20" t="inlineStr">
@@ -5257,10 +5257,10 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103490592768</v>
+        <v>103515619328</v>
       </c>
       <c r="F21" t="n">
-        <v>268.9800109863281</v>
+        <v>268.8800048828125</v>
       </c>
       <c r="G21" t="n">
         <v>11479600128</v>
@@ -5290,25 +5290,25 @@
         <v>0.20362</v>
       </c>
       <c r="Q21" t="n">
-        <v>60.68059</v>
+        <v>60.695263</v>
       </c>
       <c r="R21" t="n">
         <v>9.017353999999999</v>
       </c>
       <c r="S21" t="n">
-        <v>38.37906534958015</v>
+        <v>38.38834634755325</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.002151604754112468</v>
+        <v>-0.002522602322080236</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1436883531845422</v>
+        <v>-0.1440067277391385</v>
       </c>
       <c r="V21" t="n">
-        <v>0.02635494318501386</v>
+        <v>0.0259733469529535</v>
       </c>
       <c r="W21" t="n">
-        <v>1.082409081485411</v>
+        <v>1.081634601027083</v>
       </c>
       <c r="X21" t="n">
         <v>0.00269</v>
@@ -5318,7 +5318,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>2026-08-27T19:10:24.746982+00:00</t>
+          <t>2026-08-27T19:31:15.994057+00:00</t>
         </is>
       </c>
       <c r="AD21" t="inlineStr">
@@ -5349,10 +5349,10 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>3751459946496</v>
+        <v>3755358289920</v>
       </c>
       <c r="F22" t="n">
-        <v>505.2099914550781</v>
+        <v>505.7349853515625</v>
       </c>
       <c r="G22" t="n">
         <v>331839012864</v>
@@ -5382,25 +5382,25 @@
         <v>0.45111</v>
       </c>
       <c r="Q22" t="n">
-        <v>28.11408</v>
+        <v>28.143295</v>
       </c>
       <c r="R22" t="n">
-        <v>11.30506</v>
+        <v>11.316808</v>
       </c>
       <c r="S22" t="n">
-        <v>226.7359650792207</v>
+        <v>226.9715785926414</v>
       </c>
       <c r="T22" t="n">
-        <v>0.2867956297802874</v>
+        <v>0.2881328160257766</v>
       </c>
       <c r="U22" t="n">
-        <v>0.1854166872533802</v>
+        <v>0.186648524580679</v>
       </c>
       <c r="V22" t="n">
-        <v>0.2662440122017344</v>
+        <v>0.2675598420331105</v>
       </c>
       <c r="W22" t="n">
-        <v>0.005183506916361935</v>
+        <v>0.006228053174162529</v>
       </c>
       <c r="X22" t="n">
         <v>0.00090000004</v>
@@ -5410,7 +5410,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>2026-08-27T19:10:19.910153+00:00</t>
+          <t>2026-08-27T19:31:11.097926+00:00</t>
         </is>
       </c>
       <c r="AD22" t="inlineStr">
@@ -5441,10 +5441,10 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>663162126336</v>
+        <v>662820225024</v>
       </c>
       <c r="F23" t="n">
-        <v>1726.535034179688</v>
+        <v>1725.64501953125</v>
       </c>
       <c r="G23" t="n">
         <v>35327500288</v>
@@ -5474,25 +5474,25 @@
         <v>0.37057</v>
       </c>
       <c r="Q23" t="n">
-        <v>58.171665</v>
+        <v>58.141678</v>
       </c>
       <c r="R23" t="n">
-        <v>18.77184</v>
+        <v>18.762161</v>
       </c>
       <c r="S23" t="n">
-        <v>78.5953625503752</v>
+        <v>78.55484175386718</v>
       </c>
       <c r="T23" t="n">
-        <v>0.09070727909086118</v>
+        <v>0.09014502843487637</v>
       </c>
       <c r="U23" t="n">
-        <v>0.0765975080298904</v>
+        <v>0.076042530845154</v>
       </c>
       <c r="V23" t="n">
-        <v>0.1349705608315461</v>
+        <v>0.1343854928168879</v>
       </c>
       <c r="W23" t="n">
-        <v>1.257021988920565</v>
+        <v>1.25585851259821</v>
       </c>
       <c r="X23" t="n">
         <v>0.00016000001</v>
@@ -5502,7 +5502,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>2026-08-27T19:10:22.551781+00:00</t>
+          <t>2026-08-27T19:31:13.843574+00:00</t>
         </is>
       </c>
       <c r="AD23" t="inlineStr">
@@ -5533,10 +5533,10 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>314537017344</v>
+        <v>315209416704</v>
       </c>
       <c r="F24" t="n">
-        <v>385.9349975585938</v>
+        <v>386.8299865722656</v>
       </c>
       <c r="G24" t="n">
         <v>10606499840</v>
@@ -5563,25 +5563,25 @@
         <v>-0.02465</v>
       </c>
       <c r="Q24" t="n">
-        <v>335.59564</v>
+        <v>336.31305</v>
       </c>
       <c r="R24" t="n">
-        <v>29.655119</v>
+        <v>29.71928</v>
       </c>
       <c r="S24" t="n">
-        <v>87.87484077667654</v>
+        <v>88.06269461721104</v>
       </c>
       <c r="T24" t="n">
-        <v>0.2098275785535855</v>
+        <v>0.2126331867469142</v>
       </c>
       <c r="U24" t="n">
-        <v>0.4972068666151983</v>
+        <v>0.5006789116623989</v>
       </c>
       <c r="V24" t="n">
-        <v>1.664560945294859</v>
+        <v>1.670740101855896</v>
       </c>
       <c r="W24" t="n">
-        <v>1.057113140573698</v>
+        <v>1.061883616618473</v>
       </c>
       <c r="X24" t="n">
         <v>0.0076</v>
@@ -5591,7 +5591,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>2026-08-27T19:10:19.464625+00:00</t>
+          <t>2026-08-27T19:31:10.666179+00:00</t>
         </is>
       </c>
       <c r="AD24" t="inlineStr">
@@ -5622,10 +5622,10 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>24888438784</v>
+        <v>24784939008</v>
       </c>
       <c r="F25" t="n">
-        <v>38.47499847412109</v>
+        <v>38.31499862670898</v>
       </c>
       <c r="G25" t="n">
         <v>39063072768</v>
@@ -5655,22 +5655,22 @@
         <v>0.13382</v>
       </c>
       <c r="Q25" t="n">
-        <v>11.802147</v>
+        <v>11.753067</v>
       </c>
       <c r="R25" t="n">
-        <v>0.6371347000000001</v>
+        <v>0.6344851</v>
       </c>
       <c r="T25" t="n">
-        <v>0.3523724935797106</v>
+        <v>0.3467485975121738</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.06840195678271199</v>
+        <v>-0.07227604516934161</v>
       </c>
       <c r="V25" t="n">
-        <v>0.1450892923032348</v>
+        <v>0.1403273918663839</v>
       </c>
       <c r="W25" t="n">
-        <v>-0.1404155514543107</v>
+        <v>-0.1439901683759369</v>
       </c>
       <c r="X25" t="n">
         <v>0.12878999</v>
@@ -5680,7 +5680,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>2026-08-27T19:10:25.202653+00:00</t>
+          <t>2026-08-27T19:31:16.420471+00:00</t>
         </is>
       </c>
       <c r="AD25" t="inlineStr">
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>229953486848</v>
+        <v>231404519424</v>
       </c>
       <c r="F26" t="n">
-        <v>225.8300018310547</v>
+        <v>227.2550048828125</v>
       </c>
       <c r="G26" t="n">
         <v>5094199808</v>
@@ -5741,25 +5741,25 @@
         <v>-0.022079999</v>
       </c>
       <c r="Q26" t="n">
-        <v>3763.8335</v>
+        <v>3787.5835</v>
       </c>
       <c r="R26" t="n">
-        <v>45.140255</v>
+        <v>45.4251</v>
       </c>
       <c r="S26" t="n">
-        <v>119.3717079386224</v>
+        <v>120.1249569510464</v>
       </c>
       <c r="T26" t="n">
-        <v>0.2421892081418815</v>
+        <v>0.2500275086250345</v>
       </c>
       <c r="U26" t="n">
-        <v>0.3462295191120994</v>
+        <v>0.3547243212090163</v>
       </c>
       <c r="V26" t="n">
-        <v>1.486361546322527</v>
+        <v>1.502050660977601</v>
       </c>
       <c r="W26" t="n">
-        <v>1.137479090970274</v>
+        <v>1.150966733015196</v>
       </c>
       <c r="X26" t="n">
         <v>0.01467</v>
@@ -5769,7 +5769,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>2026-08-27T19:10:19.012182+00:00</t>
+          <t>2026-08-27T19:31:10.231182+00:00</t>
         </is>
       </c>
       <c r="AD26" t="inlineStr">
@@ -5800,10 +5800,10 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>268569493504</v>
+        <v>268067651584</v>
       </c>
       <c r="F27" t="n">
-        <v>251.4698944091797</v>
+        <v>251</v>
       </c>
       <c r="G27" t="n">
         <v>5155999744</v>
@@ -5833,25 +5833,25 @@
         <v>0.07603</v>
       </c>
       <c r="Q27" t="n">
-        <v>256.60193</v>
+        <v>256.12244</v>
       </c>
       <c r="R27" t="n">
-        <v>52.088734</v>
+        <v>51.9914</v>
       </c>
       <c r="S27" t="n">
-        <v>201.2510303065065</v>
+        <v>200.874977903334</v>
       </c>
       <c r="T27" t="n">
-        <v>0.02749811540804115</v>
+        <v>0.02557814156382698</v>
       </c>
       <c r="U27" t="n">
-        <v>-0.2499480936275359</v>
+        <v>-0.2513496339519833</v>
       </c>
       <c r="V27" t="n">
-        <v>0.9088347041417755</v>
+        <v>0.9052678725827463</v>
       </c>
       <c r="W27" t="n">
-        <v>0.7877853537758721</v>
+        <v>0.784444713956834</v>
       </c>
       <c r="X27" t="n">
         <v>0.0007</v>
@@ -5861,7 +5861,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>2026-08-27T19:10:23.019520+00:00</t>
+          <t>2026-08-27T19:31:14.213096+00:00</t>
         </is>
       </c>
       <c r="AD27" t="inlineStr">
@@ -5892,10 +5892,10 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>219265957888</v>
+        <v>217971818496</v>
       </c>
       <c r="F28" t="n">
-        <v>243.9799957275391</v>
+        <v>242.5399932861328</v>
       </c>
       <c r="G28" t="n">
         <v>8717100032</v>
@@ -5925,25 +5925,25 @@
         <v>0.14479999</v>
       </c>
       <c r="Q28" t="n">
-        <v>83.554794</v>
+        <v>83.06164</v>
       </c>
       <c r="R28" t="n">
-        <v>25.155605</v>
+        <v>25.005083</v>
       </c>
       <c r="S28" t="n">
-        <v>96.6056961774037</v>
+        <v>96.03551538819691</v>
       </c>
       <c r="T28" t="n">
-        <v>0.39840656858199</v>
+        <v>0.3901529866978204</v>
       </c>
       <c r="U28" t="n">
-        <v>0.1914279484976187</v>
+        <v>0.1843959820059391</v>
       </c>
       <c r="V28" t="n">
-        <v>2.017330027810736</v>
+        <v>1.999521343973279</v>
       </c>
       <c r="W28" t="n">
-        <v>2.269150976167124</v>
+        <v>2.249855679314171</v>
       </c>
       <c r="X28" t="n">
         <v>0.00494</v>
@@ -5953,7 +5953,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>2026-08-27T19:10:23.450534+00:00</t>
+          <t>2026-08-27T19:31:14.622829+00:00</t>
         </is>
       </c>
       <c r="AD28" t="inlineStr">
@@ -5984,10 +5984,10 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1452460736512</v>
+        <v>1450269736960</v>
       </c>
       <c r="F29" t="n">
-        <v>570.10498046875</v>
+        <v>569.5</v>
       </c>
       <c r="G29" t="n">
         <v>228246994944</v>
@@ -6017,25 +6017,25 @@
         <v>0.34827</v>
       </c>
       <c r="Q29" t="n">
-        <v>21.466492</v>
+        <v>21.43411</v>
       </c>
       <c r="R29" t="n">
-        <v>6.3635483</v>
+        <v>6.353949</v>
       </c>
       <c r="S29" t="n">
-        <v>67.38823425673571</v>
+        <v>67.28658084376902</v>
       </c>
       <c r="T29" t="n">
-        <v>-0.03927300471929396</v>
+        <v>-0.04029250303602117</v>
       </c>
       <c r="U29" t="n">
-        <v>-0.1017749575365905</v>
+        <v>-0.1027281304185143</v>
       </c>
       <c r="V29" t="n">
-        <v>-0.1263107069824991</v>
+        <v>-0.1272379248052589</v>
       </c>
       <c r="W29" t="n">
-        <v>-0.2346952152351088</v>
+        <v>-0.2355072739847233</v>
       </c>
       <c r="X29" t="n">
         <v>0.00148</v>
@@ -6045,7 +6045,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>2026-08-27T19:10:21.154513+00:00</t>
+          <t>2026-08-27T19:31:12.303864+00:00</t>
         </is>
       </c>
       <c r="AD29" t="inlineStr">
@@ -6076,10 +6076,10 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>142921089024</v>
+        <v>143231238144</v>
       </c>
       <c r="F30" t="n">
-        <v>138.2400054931641</v>
+        <v>138.5399932861328</v>
       </c>
       <c r="G30" t="n">
         <v>14732000256</v>
@@ -6109,25 +6109,25 @@
         <v>0.04063</v>
       </c>
       <c r="Q30" t="n">
-        <v>86.40000000000001</v>
+        <v>86.58749400000001</v>
       </c>
       <c r="R30" t="n">
-        <v>9.701404999999999</v>
+        <v>9.722457</v>
       </c>
       <c r="S30" t="n">
-        <v>27.75503623063398</v>
+        <v>27.81526667053116</v>
       </c>
       <c r="T30" t="n">
-        <v>0.2496836201483048</v>
+        <v>0.2523954967124014</v>
       </c>
       <c r="U30" t="n">
-        <v>0.2714062468972476</v>
+        <v>0.2741652626583706</v>
       </c>
       <c r="V30" t="n">
-        <v>0.3262976210387702</v>
+        <v>0.3291757538537663</v>
       </c>
       <c r="W30" t="n">
-        <v>-0.2216040287548745</v>
+        <v>-0.2199148701886797</v>
       </c>
       <c r="X30" t="n">
         <v>0.00176</v>
@@ -6137,7 +6137,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>2026-08-27T19:10:26.954003+00:00</t>
+          <t>2026-08-27T19:31:18.099324+00:00</t>
         </is>
       </c>
       <c r="AD30" t="inlineStr">
@@ -6168,10 +6168,10 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>434951127040</v>
+        <v>434216599552</v>
       </c>
       <c r="F31" t="n">
-        <v>151.0399932861328</v>
+        <v>150.7449951171875</v>
       </c>
       <c r="G31" t="n">
         <v>67356999680</v>
@@ -6201,22 +6201,22 @@
         <v>0.36202</v>
       </c>
       <c r="Q31" t="n">
-        <v>25.856163</v>
+        <v>25.812498</v>
       </c>
       <c r="R31" t="n">
-        <v>6.4574003</v>
+        <v>6.4464955</v>
       </c>
       <c r="T31" t="n">
-        <v>0.2590863157624272</v>
+        <v>0.2566271779565192</v>
       </c>
       <c r="U31" t="n">
-        <v>-0.2559378613032863</v>
+        <v>-0.2573910987122766</v>
       </c>
       <c r="V31" t="n">
-        <v>0.02843208465209157</v>
+        <v>0.02642344061512936</v>
       </c>
       <c r="W31" t="n">
-        <v>-0.3521839296204266</v>
+        <v>-0.3534492298995104</v>
       </c>
       <c r="X31" t="n">
         <v>0.40498</v>
@@ -6226,7 +6226,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>2026-08-27T19:10:21.582339+00:00</t>
+          <t>2026-08-27T19:31:12.928043+00:00</t>
         </is>
       </c>
       <c r="AD31" t="inlineStr">
@@ -7296,7 +7296,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>55.57</v>
+        <v>55.59</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/reports/investment_dashboard.xlsx
+++ b/reports/investment_dashboard.xlsx
@@ -534,7 +534,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>55.59</v>
+        <v>55.6</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>425.6600036621094</v>
+        <v>426</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -589,7 +589,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>919.1599731445312</v>
+        <v>920.5449829101562</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>53.49</v>
+        <v>53.52</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>236.1399993896484</v>
+        <v>236.9799957275391</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -693,7 +693,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>200.3200073242188</v>
+        <v>200.2200012207031</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -737,7 +737,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>52.42</v>
+        <v>52.41</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -745,7 +745,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>186.3549957275391</v>
+        <v>186.2700042724609</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>466.6199951171875</v>
+        <v>468.1749877929688</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -836,7 +836,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>50.98</v>
+        <v>51.05</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -844,7 +844,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>227.2749938964844</v>
+        <v>228.2599945068359</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>50.84</v>
+        <v>50.9</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>364.9800109863281</v>
+        <v>366.6700134277344</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>47.65</v>
+        <v>47.63</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -943,7 +943,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>18.2549991607666</v>
+        <v>18.32999992370605</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -982,7 +982,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>47.59</v>
+        <v>47.62</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -990,7 +990,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>472.9599914550781</v>
+        <v>474.5328979492188</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>46.73</v>
+        <v>46.74</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -1042,7 +1042,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>340.5799865722656</v>
+        <v>341.0549926757812</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>45.43</v>
+        <v>45.46</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -1089,7 +1089,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>477.2999877929688</v>
+        <v>478.8800048828125</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -1128,7 +1128,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>45.18</v>
+        <v>45.16</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>243.8099975585938</v>
+        <v>243.3099975585938</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -1180,7 +1180,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>44.3</v>
+        <v>44.29</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>369.0799865722656</v>
+        <v>368.8299865722656</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -1232,7 +1232,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>43.81</v>
+        <v>43.82</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>444.0700073242188</v>
+        <v>445.1099853515625</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1270,16 +1270,16 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>SNOW</t>
+          <t>NET</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Snowflake Inc.</t>
+          <t>Cloudflare, Inc.</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>43.18</v>
+        <v>43.16</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -1287,7 +1287,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>330.7699890136719</v>
+        <v>309.239990234375</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1322,16 +1322,16 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>NET</t>
+          <t>SNOW</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Cloudflare, Inc.</t>
+          <t>Snowflake Inc.</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>43.05</v>
+        <v>43.15</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -1339,7 +1339,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>306.3900146484375</v>
+        <v>329.8384094238281</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1383,7 +1383,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>42.57</v>
+        <v>42.65</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -1391,7 +1391,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>255.8200073242188</v>
+        <v>256.9700012207031</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1421,16 +1421,16 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>ACMR</t>
+          <t>VRT</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>ACM Research, Inc.</t>
+          <t>Vertiv Holdings Co</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>42.49</v>
+        <v>42.48</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>79.97000122070312</v>
+        <v>268.9700012207031</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1446,24 +1446,24 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>94.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="I20" t="n">
-        <v>94.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Revenue Growth</t>
+          <t>Earnings Fcf</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Industry Growth; Competitive Advantage; Catalysts; Inflation Resilience</t>
+          <t>Industry Growth; Valuation; Competitive Advantage; Momentum; Catalysts; Inflation Resilience</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>Negative free cash flow / unprofitable growth</t>
+          <t>High market sensitivity / beta</t>
         </is>
       </c>
     </row>
@@ -1473,16 +1473,16 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>VRT</t>
+          <t>ACMR</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Vertiv Holdings Co</t>
+          <t>ACM Research, Inc.</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>42.48</v>
+        <v>42.45</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -1490,7 +1490,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>268.8800048828125</v>
+        <v>79.69000244140625</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1498,24 +1498,24 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>100</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="I21" t="n">
-        <v>100</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Earnings Fcf</t>
+          <t>Revenue Growth</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>Industry Growth; Valuation; Competitive Advantage; Momentum; Catalysts; Inflation Resilience</t>
+          <t>Industry Growth; Competitive Advantage; Catalysts; Inflation Resilience</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>High market sensitivity / beta</t>
+          <t>Negative free cash flow / unprofitable growth</t>
         </is>
       </c>
     </row>
@@ -1534,7 +1534,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>42.45</v>
+        <v>42.41</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -1542,7 +1542,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>505.7349853515625</v>
+        <v>504.8999938964844</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1581,7 +1581,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>42.34</v>
+        <v>42.35</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1725.64501953125</v>
+        <v>1726.380004882812</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1636,7 +1636,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>386.8299865722656</v>
+        <v>387.0700073242188</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1732,7 +1732,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>41.08</v>
+        <v>41.15</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -1740,7 +1740,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>227.2550048828125</v>
+        <v>228.5599975585938</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1784,7 +1784,7 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>40.72</v>
+        <v>40.74</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -1792,7 +1792,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>251</v>
+        <v>252.4799957275391</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1836,7 +1836,7 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>39.81</v>
+        <v>39.76</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>242.5399932861328</v>
+        <v>241.5500030517578</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1888,7 +1888,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>39.57</v>
+        <v>39.56</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -1896,7 +1896,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>569.5</v>
+        <v>569.3599853515625</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>36.49</v>
+        <v>36.48</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -1943,7 +1943,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>138.5399932861328</v>
+        <v>138.5299987792969</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1977,7 +1977,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>31.51</v>
+        <v>31.52</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -1985,7 +1985,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>150.7449951171875</v>
+        <v>151.1755065917969</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -2137,7 +2137,7 @@
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>5.42</v>
+        <v>5.43</v>
       </c>
       <c r="I2" t="n">
         <v>2.69</v>
@@ -2149,7 +2149,7 @@
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>55.59</v>
+        <v>55.6</v>
       </c>
     </row>
     <row r="3">
@@ -2171,13 +2171,13 @@
         <v>9.02</v>
       </c>
       <c r="F3" t="n">
-        <v>5</v>
+        <v>4.99</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>6.89</v>
+        <v>6.9</v>
       </c>
       <c r="I3" t="n">
         <v>3.5</v>
@@ -2211,13 +2211,13 @@
         <v>9.91</v>
       </c>
       <c r="F4" t="n">
-        <v>2.36</v>
+        <v>2.35</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>7.68</v>
+        <v>7.72</v>
       </c>
       <c r="I4" t="n">
         <v>3.54</v>
@@ -2229,7 +2229,7 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>53.49</v>
+        <v>53.52</v>
       </c>
     </row>
     <row r="5">
@@ -2297,7 +2297,7 @@
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>8.539999999999999</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="I6" t="n">
         <v>3.35</v>
@@ -2309,7 +2309,7 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>52.42</v>
+        <v>52.41</v>
       </c>
     </row>
     <row r="7">
@@ -2331,13 +2331,13 @@
         <v>6.33</v>
       </c>
       <c r="F7" t="n">
-        <v>5.76</v>
+        <v>5.75</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>9.050000000000001</v>
+        <v>9.06</v>
       </c>
       <c r="I7" t="n">
         <v>3.54</v>
@@ -2371,13 +2371,13 @@
         <v>9.029999999999999</v>
       </c>
       <c r="F8" t="n">
-        <v>2.91</v>
+        <v>2.89</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>5.6</v>
+        <v>5.69</v>
       </c>
       <c r="I8" t="n">
         <v>3.44</v>
@@ -2389,7 +2389,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>50.98</v>
+        <v>51.05</v>
       </c>
     </row>
     <row r="9">
@@ -2411,13 +2411,13 @@
         <v>8.9</v>
       </c>
       <c r="F9" t="n">
-        <v>2.93</v>
+        <v>2.92</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>5.26</v>
+        <v>5.33</v>
       </c>
       <c r="I9" t="n">
         <v>3.75</v>
@@ -2429,7 +2429,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>50.84</v>
+        <v>50.9</v>
       </c>
     </row>
     <row r="10">
@@ -2451,7 +2451,7 @@
         <v>9.699999999999999</v>
       </c>
       <c r="F10" t="n">
-        <v>6.52</v>
+        <v>6.5</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -2469,7 +2469,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>47.65</v>
+        <v>47.63</v>
       </c>
     </row>
     <row r="11">
@@ -2497,7 +2497,7 @@
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>6.15</v>
+        <v>6.18</v>
       </c>
       <c r="I11" t="n">
         <v>3.45</v>
@@ -2509,7 +2509,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>47.59</v>
+        <v>47.62</v>
       </c>
     </row>
     <row r="12">
@@ -2531,13 +2531,13 @@
         <v>8.34</v>
       </c>
       <c r="F12" t="n">
-        <v>4.44</v>
+        <v>4.43</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>4.47</v>
+        <v>4.49</v>
       </c>
       <c r="I12" t="n">
         <v>3.53</v>
@@ -2549,7 +2549,7 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>46.73</v>
+        <v>46.74</v>
       </c>
     </row>
     <row r="13">
@@ -2571,13 +2571,13 @@
         <v>7.78</v>
       </c>
       <c r="F13" t="n">
-        <v>2.09</v>
+        <v>2.07</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>5.8</v>
+        <v>5.85</v>
       </c>
       <c r="I13" t="n">
         <v>3.58</v>
@@ -2589,7 +2589,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>45.43</v>
+        <v>45.46</v>
       </c>
     </row>
     <row r="14">
@@ -2617,7 +2617,7 @@
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>6.61</v>
+        <v>6.59</v>
       </c>
       <c r="I14" t="n">
         <v>3.67</v>
@@ -2629,7 +2629,7 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>45.18</v>
+        <v>45.16</v>
       </c>
     </row>
     <row r="15">
@@ -2657,7 +2657,7 @@
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>3.58</v>
+        <v>3.57</v>
       </c>
       <c r="I15" t="n">
         <v>3.53</v>
@@ -2669,7 +2669,7 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>44.3</v>
+        <v>44.29</v>
       </c>
     </row>
     <row r="16">
@@ -2691,13 +2691,13 @@
         <v>9.880000000000001</v>
       </c>
       <c r="F16" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>9.83</v>
+        <v>9.85</v>
       </c>
       <c r="I16" t="n">
         <v>3.73</v>
@@ -2709,17 +2709,17 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>43.81</v>
+        <v>43.82</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>SNOW</t>
+          <t>NET</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>14.44</v>
+        <v>15</v>
       </c>
       <c r="C17" t="n">
         <v>7.5</v>
@@ -2728,19 +2728,19 @@
         <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>7.58</v>
+        <v>7.71</v>
       </c>
       <c r="F17" t="n">
-        <v>0.98</v>
+        <v>0.55</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>9.119999999999999</v>
+        <v>8.76</v>
       </c>
       <c r="I17" t="n">
-        <v>3.56</v>
+        <v>3.64</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2749,17 +2749,17 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>43.18</v>
+        <v>43.16</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>NET</t>
+          <t>SNOW</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>15</v>
+        <v>14.44</v>
       </c>
       <c r="C18" t="n">
         <v>7.5</v>
@@ -2768,19 +2768,19 @@
         <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>7.71</v>
+        <v>7.58</v>
       </c>
       <c r="F18" t="n">
-        <v>0.55</v>
+        <v>0.98</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>8.65</v>
+        <v>9.09</v>
       </c>
       <c r="I18" t="n">
-        <v>3.64</v>
+        <v>3.56</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2789,7 +2789,7 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>43.05</v>
+        <v>43.15</v>
       </c>
     </row>
     <row r="19">
@@ -2811,13 +2811,13 @@
         <v>6.64</v>
       </c>
       <c r="F19" t="n">
-        <v>6.54</v>
+        <v>6.53</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>4.42</v>
+        <v>4.51</v>
       </c>
       <c r="I19" t="n">
         <v>3.47</v>
@@ -2829,38 +2829,38 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>42.57</v>
+        <v>42.65</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ACMR</t>
+          <t>VRT</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>15</v>
+        <v>10.91</v>
       </c>
       <c r="C20" t="n">
-        <v>7.83</v>
+        <v>13.39</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>4.02</v>
+        <v>7.41</v>
       </c>
       <c r="F20" t="n">
-        <v>6.83</v>
+        <v>3.21</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>5.18</v>
+        <v>4</v>
       </c>
       <c r="I20" t="n">
-        <v>3.63</v>
+        <v>3.56</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2869,38 +2869,38 @@
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>42.49</v>
+        <v>42.48</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>VRT</t>
+          <t>ACMR</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>10.91</v>
+        <v>15</v>
       </c>
       <c r="C21" t="n">
-        <v>13.39</v>
+        <v>7.83</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>7.41</v>
+        <v>4.02</v>
       </c>
       <c r="F21" t="n">
-        <v>3.21</v>
+        <v>6.84</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>4</v>
+        <v>5.13</v>
       </c>
       <c r="I21" t="n">
-        <v>3.56</v>
+        <v>3.63</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>42.48</v>
+        <v>42.45</v>
       </c>
     </row>
     <row r="22">
@@ -2937,7 +2937,7 @@
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>6.13</v>
+        <v>6.09</v>
       </c>
       <c r="I22" t="n">
         <v>3.45</v>
@@ -2949,7 +2949,7 @@
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>42.45</v>
+        <v>42.41</v>
       </c>
     </row>
     <row r="23">
@@ -2977,7 +2977,7 @@
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>5.91</v>
+        <v>5.92</v>
       </c>
       <c r="I23" t="n">
         <v>2.76</v>
@@ -2989,7 +2989,7 @@
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>42.34</v>
+        <v>42.35</v>
       </c>
     </row>
     <row r="24">
@@ -3097,7 +3097,7 @@
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>9.109999999999999</v>
+        <v>9.18</v>
       </c>
       <c r="I26" t="n">
         <v>3.48</v>
@@ -3109,7 +3109,7 @@
         <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>41.08</v>
+        <v>41.15</v>
       </c>
     </row>
     <row r="27">
@@ -3131,13 +3131,13 @@
         <v>9.449999999999999</v>
       </c>
       <c r="F27" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>5.8</v>
+        <v>5.83</v>
       </c>
       <c r="I27" t="n">
         <v>3.7</v>
@@ -3149,7 +3149,7 @@
         <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>40.72</v>
+        <v>40.74</v>
       </c>
     </row>
     <row r="28">
@@ -3177,7 +3177,7 @@
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>8.98</v>
+        <v>8.93</v>
       </c>
       <c r="I28" t="n">
         <v>3.53</v>
@@ -3189,7 +3189,7 @@
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>39.81</v>
+        <v>39.76</v>
       </c>
     </row>
     <row r="29">
@@ -3217,7 +3217,7 @@
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>0.82</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="I29" t="n">
         <v>3.49</v>
@@ -3229,7 +3229,7 @@
         <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>39.57</v>
+        <v>39.56</v>
       </c>
     </row>
     <row r="30">
@@ -3257,7 +3257,7 @@
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>5.94</v>
+        <v>5.93</v>
       </c>
       <c r="I30" t="n">
         <v>3.57</v>
@@ -3269,7 +3269,7 @@
         <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>36.49</v>
+        <v>36.48</v>
       </c>
     </row>
     <row r="31">
@@ -3291,13 +3291,13 @@
         <v>0.8</v>
       </c>
       <c r="F31" t="n">
-        <v>6.34</v>
+        <v>6.32</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>2.65</v>
+        <v>2.68</v>
       </c>
       <c r="I31" t="n">
         <v>3.58</v>
@@ -3309,7 +3309,7 @@
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>31.51</v>
+        <v>31.52</v>
       </c>
     </row>
   </sheetData>
@@ -3347,7 +3347,7 @@
     <col width="16" customWidth="1" min="18" max="18"/>
     <col width="19" customWidth="1" min="19" max="19"/>
     <col width="23" customWidth="1" min="20" max="20"/>
-    <col width="22" customWidth="1" min="21" max="21"/>
+    <col width="23" customWidth="1" min="21" max="21"/>
     <col width="21" customWidth="1" min="22" max="22"/>
     <col width="22" customWidth="1" min="23" max="23"/>
     <col width="18" customWidth="1" min="24" max="24"/>
@@ -3533,10 +3533,10 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2207700484096</v>
+        <v>2209437974528</v>
       </c>
       <c r="F2" t="n">
-        <v>425.6600036621094</v>
+        <v>426</v>
       </c>
       <c r="G2" t="n">
         <v>4440492343296</v>
@@ -3566,25 +3566,25 @@
         <v>0.60344005</v>
       </c>
       <c r="Q2" t="n">
-        <v>31.742357</v>
+        <v>31.767338</v>
       </c>
       <c r="R2" t="n">
-        <v>0.4971221</v>
+        <v>0.49756598</v>
       </c>
       <c r="S2" t="n">
-        <v>3.020829088769962</v>
+        <v>3.023206522518903</v>
       </c>
       <c r="T2" t="n">
-        <v>0.08500931995375582</v>
+        <v>0.08587597219307286</v>
       </c>
       <c r="U2" t="n">
-        <v>0.004229303380267613</v>
+        <v>0.005031432503544986</v>
       </c>
       <c r="V2" t="n">
-        <v>0.103497466264594</v>
+        <v>0.1043788859285832</v>
       </c>
       <c r="W2" t="n">
-        <v>0.7985188295131107</v>
+        <v>0.7999555142074082</v>
       </c>
       <c r="X2" t="n">
         <v>0.00013</v>
@@ -3594,7 +3594,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>2026-08-27T19:31:13.383951+00:00</t>
+          <t>2026-08-27T19:49:37.912963+00:00</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
@@ -3625,10 +3625,10 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1037838909440</v>
+        <v>1039823273984</v>
       </c>
       <c r="F3" t="n">
-        <v>919.1599731445312</v>
+        <v>920.5449829101562</v>
       </c>
       <c r="G3" t="n">
         <v>90273996800</v>
@@ -3658,25 +3658,25 @@
         <v>0.80370003</v>
       </c>
       <c r="Q3" t="n">
-        <v>20.790384</v>
+        <v>20.830135</v>
       </c>
       <c r="R3" t="n">
-        <v>11.499358</v>
+        <v>11.518937</v>
       </c>
       <c r="S3" t="n">
-        <v>135.8516839938186</v>
+        <v>136.1114345798758</v>
       </c>
       <c r="T3" t="n">
-        <v>0.1202027230279112</v>
+        <v>0.1218906682781442</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.0045680291500384</v>
+        <v>-0.003068091118657468</v>
       </c>
       <c r="V3" t="n">
-        <v>1.14379381679285</v>
+        <v>1.147024130838822</v>
       </c>
       <c r="W3" t="n">
-        <v>6.818558457669792</v>
+        <v>6.830339627578591</v>
       </c>
       <c r="X3" t="n">
         <v>0.00238</v>
@@ -3686,7 +3686,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>2026-08-27T19:31:08.578666+00:00</t>
+          <t>2026-08-27T19:49:31.236307+00:00</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
@@ -3717,10 +3717,10 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>44378894336</v>
+        <v>44536758272</v>
       </c>
       <c r="F4" t="n">
-        <v>236.1399993896484</v>
+        <v>236.9799957275391</v>
       </c>
       <c r="G4" t="n">
         <v>1335116032</v>
@@ -3750,25 +3750,25 @@
         <v>0.35661998</v>
       </c>
       <c r="Q4" t="n">
-        <v>94.07968</v>
+        <v>94.414345</v>
       </c>
       <c r="R4" t="n">
-        <v>33.239727</v>
+        <v>33.357967</v>
       </c>
       <c r="S4" t="n">
-        <v>176.9421940409041</v>
+        <v>177.5716101544352</v>
       </c>
       <c r="T4" t="n">
-        <v>0.228104851720407</v>
+        <v>0.2324734617850179</v>
       </c>
       <c r="U4" t="n">
-        <v>0.06201930698267155</v>
+        <v>0.06579711815799283</v>
       </c>
       <c r="V4" t="n">
-        <v>0.9126842794489163</v>
+        <v>0.9194880729376549</v>
       </c>
       <c r="W4" t="n">
-        <v>0.9240608891933821</v>
+        <v>0.930905151516489</v>
       </c>
       <c r="X4" t="n">
         <v>0.09436</v>
@@ -3778,7 +3778,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>2026-08-27T19:31:09.368855+00:00</t>
+          <t>2026-08-27T19:49:32.522633+00:00</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
@@ -3809,10 +3809,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>252648538112</v>
+        <v>252522414080</v>
       </c>
       <c r="F5" t="n">
-        <v>200.3200073242188</v>
+        <v>200.2200012207031</v>
       </c>
       <c r="G5" t="n">
         <v>10540800000</v>
@@ -3842,25 +3842,25 @@
         <v>0.45393002</v>
       </c>
       <c r="Q5" t="n">
-        <v>63.392406</v>
+        <v>63.36076</v>
       </c>
       <c r="R5" t="n">
-        <v>23.96863</v>
+        <v>23.956665</v>
       </c>
       <c r="S5" t="n">
-        <v>64.92296585912408</v>
+        <v>64.89055583100857</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1803665040327311</v>
+        <v>0.1797772276226239</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2901397682240419</v>
+        <v>0.289495689517506</v>
       </c>
       <c r="V5" t="n">
-        <v>0.5074122074217033</v>
+        <v>0.5066596594197847</v>
       </c>
       <c r="W5" t="n">
-        <v>0.5031139859099794</v>
+        <v>0.5023635837166158</v>
       </c>
       <c r="X5" t="n">
         <v>0.17247999</v>
@@ -3870,7 +3870,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>2026-08-27T19:31:15.122950+00:00</t>
+          <t>2026-08-27T19:49:40.481967+00:00</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
@@ -3901,10 +3901,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>447821938688</v>
+        <v>447713804288</v>
       </c>
       <c r="F6" t="n">
-        <v>186.3549957275391</v>
+        <v>186.2700042724609</v>
       </c>
       <c r="G6" t="n">
         <v>6155940864</v>
@@ -3934,25 +3934,25 @@
         <v>0.47120997</v>
       </c>
       <c r="Q6" t="n">
-        <v>159.27779</v>
+        <v>159.23932</v>
       </c>
       <c r="R6" t="n">
-        <v>72.74045</v>
+        <v>72.72874</v>
       </c>
       <c r="S6" t="n">
-        <v>207.4109595895282</v>
+        <v>207.3608766040131</v>
       </c>
       <c r="T6" t="n">
-        <v>0.5085808918405932</v>
+        <v>0.5078928690451752</v>
       </c>
       <c r="U6" t="n">
-        <v>0.3000906968648904</v>
+        <v>0.2994977607880833</v>
       </c>
       <c r="V6" t="n">
-        <v>0.3887397893811839</v>
+        <v>0.3881064228595965</v>
       </c>
       <c r="W6" t="n">
-        <v>0.1890951651097939</v>
+        <v>0.1885528510821257</v>
       </c>
       <c r="X6" t="n">
         <v>0.03477</v>
@@ -3962,7 +3962,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>2026-08-27T19:31:06.543065+00:00</t>
+          <t>2026-08-27T19:49:28.861374+00:00</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr">
@@ -3993,10 +3993,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>301502955520</v>
+        <v>302507720704</v>
       </c>
       <c r="F7" t="n">
-        <v>466.6199951171875</v>
+        <v>468.1749877929688</v>
       </c>
       <c r="G7" t="n">
         <v>134001999872</v>
@@ -4026,25 +4026,25 @@
         <v>0.08857000600000001</v>
       </c>
       <c r="Q7" t="n">
-        <v>37.12172</v>
+        <v>37.245426</v>
       </c>
       <c r="R7" t="n">
-        <v>2.2499886</v>
+        <v>2.2574866</v>
       </c>
       <c r="S7" t="n">
-        <v>55.48325933184309</v>
+        <v>55.66815850530337</v>
       </c>
       <c r="T7" t="n">
-        <v>0.1900535267882613</v>
+        <v>0.1940193330916937</v>
       </c>
       <c r="U7" t="n">
-        <v>0.4741872674920014</v>
+        <v>0.4790999382469361</v>
       </c>
       <c r="V7" t="n">
-        <v>2.796867799681765</v>
+        <v>2.809520711432647</v>
       </c>
       <c r="W7" t="n">
-        <v>2.56653653685992</v>
+        <v>2.57842229613338</v>
       </c>
       <c r="X7" t="n">
         <v>0.07491</v>
@@ -4054,7 +4054,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>2026-08-27T19:31:15.575478+00:00</t>
+          <t>2026-08-27T19:49:41.143850+00:00</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr">
@@ -4085,10 +4085,10 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5505190723584</v>
+        <v>5529048449024</v>
       </c>
       <c r="F8" t="n">
-        <v>227.2749938964844</v>
+        <v>228.2599945068359</v>
       </c>
       <c r="G8" t="n">
         <v>253491003392</v>
@@ -4118,25 +4118,25 @@
         <v>0.65596</v>
       </c>
       <c r="Q8" t="n">
-        <v>34.860428</v>
+        <v>35.0115</v>
       </c>
       <c r="R8" t="n">
-        <v>21.717499</v>
+        <v>21.812094</v>
       </c>
       <c r="S8" t="n">
-        <v>118.810553558202</v>
+        <v>119.3254402730297</v>
       </c>
       <c r="T8" t="n">
-        <v>0.1536216447566994</v>
+        <v>0.1586213941999561</v>
       </c>
       <c r="U8" t="n">
-        <v>0.06202980418463322</v>
+        <v>0.06663259830376922</v>
       </c>
       <c r="V8" t="n">
-        <v>0.1635927889982092</v>
+        <v>0.1686357529764018</v>
       </c>
       <c r="W8" t="n">
-        <v>0.2531812063212786</v>
+        <v>0.258612336973733</v>
       </c>
       <c r="X8" t="n">
         <v>0.03991</v>
@@ -4146,7 +4146,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>2026-08-27T19:31:06.056129+00:00</t>
+          <t>2026-08-27T19:49:28.359017+00:00</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr">
@@ -4177,10 +4177,10 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>57061249024</v>
+        <v>57325465600</v>
       </c>
       <c r="F9" t="n">
-        <v>364.9800109863281</v>
+        <v>366.6700134277344</v>
       </c>
       <c r="G9" t="n">
         <v>4464031232</v>
@@ -4210,25 +4210,25 @@
         <v>0.33161</v>
       </c>
       <c r="Q9" t="n">
-        <v>50.272728</v>
+        <v>50.50551</v>
       </c>
       <c r="R9" t="n">
-        <v>12.782449</v>
+        <v>12.841637</v>
       </c>
       <c r="S9" t="n">
-        <v>130.4611235276369</v>
+        <v>131.0652110993108</v>
       </c>
       <c r="T9" t="n">
-        <v>0.138250484745541</v>
+        <v>0.1435210366668731</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.04617792549850763</v>
+        <v>-0.04176135038191831</v>
       </c>
       <c r="V9" t="n">
-        <v>0.06504243146380206</v>
+        <v>0.06997400101609319</v>
       </c>
       <c r="W9" t="n">
-        <v>2.127740322808319</v>
+        <v>2.142223208458631</v>
       </c>
       <c r="X9" t="n">
         <v>0.00202</v>
@@ -4238,7 +4238,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>2026-08-27T19:31:09.853556+00:00</t>
+          <t>2026-08-27T19:49:33.087777+00:00</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr">
@@ -4269,10 +4269,10 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>9458284544</v>
+        <v>9499112448</v>
       </c>
       <c r="F10" t="n">
-        <v>18.2549991607666</v>
+        <v>18.32999992370605</v>
       </c>
       <c r="G10" t="n">
         <v>1672329984</v>
@@ -4299,25 +4299,25 @@
         <v>0.07274</v>
       </c>
       <c r="Q10" t="n">
-        <v>30.424997</v>
+        <v>30.556332</v>
       </c>
       <c r="R10" t="n">
-        <v>5.6557527</v>
+        <v>5.6789894</v>
       </c>
       <c r="S10" t="n">
-        <v>18.48933123008303</v>
+        <v>18.56914281081675</v>
       </c>
       <c r="T10" t="n">
-        <v>0.4975389490696434</v>
+        <v>0.5036915959540738</v>
       </c>
       <c r="U10" t="n">
-        <v>0.576424808379816</v>
+        <v>0.5829015582445474</v>
       </c>
       <c r="V10" t="n">
-        <v>0.8365191077867895</v>
+        <v>0.844064456489567</v>
       </c>
       <c r="W10" t="n">
-        <v>0.6386892817026288</v>
+        <v>0.6454218454932941</v>
       </c>
       <c r="X10" t="n">
         <v>0.09236999999999999</v>
@@ -4327,7 +4327,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>2026-08-27T19:31:18.915719+00:00</t>
+          <t>2026-08-27T19:49:48.519429+00:00</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr">
@@ -4358,10 +4358,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>772065198080</v>
+        <v>774663110656</v>
       </c>
       <c r="F11" t="n">
-        <v>472.9599914550781</v>
+        <v>474.5328979492188</v>
       </c>
       <c r="G11" t="n">
         <v>41305001984</v>
@@ -4391,25 +4391,25 @@
         <v>0.1725</v>
       </c>
       <c r="Q11" t="n">
-        <v>120.03591</v>
+        <v>120.43982</v>
       </c>
       <c r="R11" t="n">
-        <v>18.693726</v>
+        <v>18.754705</v>
       </c>
       <c r="S11" t="n">
-        <v>87.32287833712076</v>
+        <v>87.61671000362855</v>
       </c>
       <c r="T11" t="n">
-        <v>0.04034137639098589</v>
+        <v>0.04380120330364767</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.08710848126976301</v>
+        <v>-0.08407250988909909</v>
       </c>
       <c r="V11" t="n">
-        <v>1.243004790316118</v>
+        <v>1.250464272861825</v>
       </c>
       <c r="W11" t="n">
-        <v>1.829892763939702</v>
+        <v>1.839304039283369</v>
       </c>
       <c r="X11" t="n">
         <v>0.00425</v>
@@ -4419,7 +4419,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>2026-08-27T19:31:06.935233+00:00</t>
+          <t>2026-08-27T19:49:29.402353+00:00</t>
         </is>
       </c>
       <c r="AD11" t="inlineStr">
@@ -4450,10 +4450,10 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4165515870208</v>
+        <v>4171080400896</v>
       </c>
       <c r="F12" t="n">
-        <v>340.5799865722656</v>
+        <v>341.0549926757812</v>
       </c>
       <c r="G12" t="n">
         <v>445865984000</v>
@@ -4483,25 +4483,25 @@
         <v>0.34033</v>
       </c>
       <c r="Q12" t="n">
-        <v>17.081244</v>
+        <v>17.104061</v>
       </c>
       <c r="R12" t="n">
-        <v>9.342529000000001</v>
+        <v>9.355146</v>
       </c>
       <c r="S12" t="n">
-        <v>183.7862648918238</v>
+        <v>184.0317769347229</v>
       </c>
       <c r="T12" t="n">
-        <v>0.02058672288244123</v>
+        <v>0.02201013277629671</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.1264875667934054</v>
+        <v>-0.1252692810642706</v>
       </c>
       <c r="V12" t="n">
-        <v>0.08987947884422121</v>
+        <v>0.0913995311812883</v>
       </c>
       <c r="W12" t="n">
-        <v>0.6461905571083069</v>
+        <v>0.648486373612158</v>
       </c>
       <c r="X12" t="n">
         <v>0.01596</v>
@@ -4511,7 +4511,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>2026-08-27T19:31:11.499635+00:00</t>
+          <t>2026-08-27T19:49:35.457146+00:00</t>
         </is>
       </c>
       <c r="AD12" t="inlineStr">
@@ -4542,10 +4542,10 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>378784055296</v>
+        <v>380033957888</v>
       </c>
       <c r="F13" t="n">
-        <v>477.2999877929688</v>
+        <v>478.8800048828125</v>
       </c>
       <c r="G13" t="n">
         <v>30837000192</v>
@@ -4575,25 +4575,25 @@
         <v>0.33736</v>
       </c>
       <c r="Q13" t="n">
-        <v>41.11111</v>
+        <v>41.246773</v>
       </c>
       <c r="R13" t="n">
-        <v>12.283427</v>
+        <v>12.32409</v>
       </c>
       <c r="S13" t="n">
-        <v>123.1667820954045</v>
+        <v>123.5732049055438</v>
       </c>
       <c r="T13" t="n">
-        <v>0.002834194795525269</v>
+        <v>0.006153899816644826</v>
       </c>
       <c r="U13" t="n">
-        <v>0.06255646469747966</v>
+        <v>0.06607386971755735</v>
       </c>
       <c r="V13" t="n">
-        <v>0.2113036354367919</v>
+        <v>0.2153134416256204</v>
       </c>
       <c r="W13" t="n">
-        <v>1.919520464519896</v>
+        <v>1.92918502003229</v>
       </c>
       <c r="X13" t="n">
         <v>0.00331</v>
@@ -4603,7 +4603,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>2026-08-27T19:31:08.079723+00:00</t>
+          <t>2026-08-27T19:49:30.642446+00:00</t>
         </is>
       </c>
       <c r="AD13" t="inlineStr">
@@ -4634,10 +4634,10 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>87546077184</v>
+        <v>87366541312</v>
       </c>
       <c r="F14" t="n">
-        <v>243.8099975585938</v>
+        <v>243.3099975585938</v>
       </c>
       <c r="G14" t="n">
         <v>3966725120</v>
@@ -4667,25 +4667,25 @@
         <v>0.00666</v>
       </c>
       <c r="Q14" t="n">
-        <v>487.62</v>
+        <v>486.62</v>
       </c>
       <c r="R14" t="n">
-        <v>22.064684</v>
+        <v>22.024855</v>
       </c>
       <c r="S14" t="n">
-        <v>83.26521656081894</v>
+        <v>83.09445970062181</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.02818083221706402</v>
+        <v>-0.0301738168721527</v>
       </c>
       <c r="U14" t="n">
-        <v>0.08244535434444966</v>
+        <v>0.08022550002103479</v>
       </c>
       <c r="V14" t="n">
-        <v>1.20982501144098</v>
+        <v>1.205293152547642</v>
       </c>
       <c r="W14" t="n">
-        <v>0.8508312872253709</v>
+        <v>0.8470356444999727</v>
       </c>
       <c r="X14" t="n">
         <v>0.00619</v>
@@ -4695,7 +4695,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>2026-08-27T19:31:17.258344+00:00</t>
+          <t>2026-08-27T19:49:44.726171+00:00</t>
         </is>
       </c>
       <c r="AD14" t="inlineStr">
@@ -4726,10 +4726,10 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1755927674880</v>
+        <v>1754738327552</v>
       </c>
       <c r="F15" t="n">
-        <v>369.0799865722656</v>
+        <v>368.8299865722656</v>
       </c>
       <c r="G15" t="n">
         <v>75464998912</v>
@@ -4759,25 +4759,25 @@
         <v>0.48988</v>
       </c>
       <c r="Q15" t="n">
-        <v>61.410976</v>
+        <v>61.36938</v>
       </c>
       <c r="R15" t="n">
-        <v>23.270945</v>
+        <v>23.252346</v>
       </c>
       <c r="S15" t="n">
-        <v>64.52710576041012</v>
+        <v>64.48339943815232</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.0310572496813124</v>
+        <v>-0.031713572690938</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.1334236643012707</v>
+        <v>-0.1340106484017545</v>
       </c>
       <c r="V15" t="n">
-        <v>0.1147409538924133</v>
+        <v>0.113985873019399</v>
       </c>
       <c r="W15" t="n">
-        <v>0.2382489086497031</v>
+        <v>0.2374101684350483</v>
       </c>
       <c r="X15" t="n">
         <v>0.01948</v>
@@ -4787,7 +4787,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>2026-08-27T19:31:07.521984+00:00</t>
+          <t>2026-08-27T19:49:29.957998+00:00</t>
         </is>
       </c>
       <c r="AD15" t="inlineStr">
@@ -4818,10 +4818,10 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>35717406720</v>
+        <v>35806281728</v>
       </c>
       <c r="F16" t="n">
-        <v>444.0700073242188</v>
+        <v>445.1099853515625</v>
       </c>
       <c r="G16" t="n">
         <v>2602398976</v>
@@ -4848,22 +4848,22 @@
         <v>-0.03607</v>
       </c>
       <c r="R16" t="n">
-        <v>13.7248</v>
+        <v>13.756944</v>
       </c>
       <c r="S16" t="n">
-        <v>69.00509225004649</v>
+        <v>69.17679643265529</v>
       </c>
       <c r="T16" t="n">
-        <v>0.4296246677767301</v>
+        <v>0.432972739516128</v>
       </c>
       <c r="U16" t="n">
-        <v>0.3635163882059416</v>
+        <v>0.366709639405683</v>
       </c>
       <c r="V16" t="n">
-        <v>0.4097908539690389</v>
+        <v>0.4130924764319304</v>
       </c>
       <c r="W16" t="n">
-        <v>0.5017585018336348</v>
+        <v>0.5052755055009042</v>
       </c>
       <c r="X16" t="n">
         <v>0.02641</v>
@@ -4873,7 +4873,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>2026-08-27T19:31:18.488556+00:00</t>
+          <t>2026-08-27T19:49:47.360481+00:00</t>
         </is>
       </c>
       <c r="AD16" t="inlineStr">
@@ -4885,12 +4885,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>SNOW</t>
+          <t>NET</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Snowflake Inc.</t>
+          <t>Cloudflare, Inc.</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -4900,66 +4900,66 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Software - Application</t>
+          <t>Software - Infrastructure</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>114644877312</v>
+        <v>110114086912</v>
       </c>
       <c r="F17" t="n">
-        <v>330.7699890136719</v>
+        <v>309.239990234375</v>
       </c>
       <c r="G17" t="n">
-        <v>5032822784</v>
+        <v>2512349952</v>
       </c>
       <c r="H17" t="n">
-        <v>0.335</v>
+        <v>0.359</v>
       </c>
       <c r="I17" t="n">
-        <v>-3.53</v>
+        <v>-0.57</v>
       </c>
       <c r="K17" t="n">
-        <v>1739497728</v>
+        <v>692851968</v>
       </c>
       <c r="M17" t="n">
-        <v>2954998016</v>
+        <v>4162798080</v>
       </c>
       <c r="N17" t="n">
-        <v>2772094976</v>
+        <v>3529349888</v>
       </c>
       <c r="O17" t="n">
-        <v>0.67144996</v>
+        <v>0.72577006</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.22173999</v>
+        <v>-0.07902000000000001</v>
       </c>
       <c r="R17" t="n">
-        <v>22.779438</v>
+        <v>43.847546</v>
       </c>
       <c r="S17" t="n">
-        <v>65.90688534201983</v>
+        <v>158.9287351378354</v>
       </c>
       <c r="T17" t="n">
-        <v>0.223442842636477</v>
+        <v>0.1709200419827575</v>
       </c>
       <c r="U17" t="n">
-        <v>0.3828176974652868</v>
+        <v>0.355661695703585</v>
       </c>
       <c r="V17" t="n">
-        <v>0.9547897635451392</v>
+        <v>0.799999911182836</v>
       </c>
       <c r="W17" t="n">
-        <v>0.6506312192281911</v>
+        <v>0.5067237476013169</v>
       </c>
       <c r="X17" t="n">
-        <v>0.02962</v>
+        <v>0.00616</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.81926</v>
+        <v>0.90191</v>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>2026-08-27T19:31:16.860088+00:00</t>
+          <t>2026-08-27T19:49:45.832840+00:00</t>
         </is>
       </c>
       <c r="AD17" t="inlineStr">
@@ -4971,12 +4971,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>NET</t>
+          <t>SNOW</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Cloudflare, Inc.</t>
+          <t>Snowflake Inc.</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -4986,66 +4986,66 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Software - Infrastructure</t>
+          <t>Software - Application</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>109099270144</v>
+        <v>114321989632</v>
       </c>
       <c r="F18" t="n">
-        <v>306.3900146484375</v>
+        <v>329.8384094238281</v>
       </c>
       <c r="G18" t="n">
-        <v>2512349952</v>
+        <v>5032822784</v>
       </c>
       <c r="H18" t="n">
-        <v>0.359</v>
+        <v>0.335</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.57</v>
+        <v>-3.53</v>
       </c>
       <c r="K18" t="n">
-        <v>692851968</v>
+        <v>1739497728</v>
       </c>
       <c r="M18" t="n">
-        <v>4162798080</v>
+        <v>2954998016</v>
       </c>
       <c r="N18" t="n">
-        <v>3529349888</v>
+        <v>2772094976</v>
       </c>
       <c r="O18" t="n">
-        <v>0.72577006</v>
+        <v>0.67144996</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.07902000000000001</v>
+        <v>-0.22173999</v>
       </c>
       <c r="R18" t="n">
-        <v>43.42519</v>
+        <v>22.715282</v>
       </c>
       <c r="S18" t="n">
-        <v>157.4640402031737</v>
+        <v>65.72126412803225</v>
       </c>
       <c r="T18" t="n">
-        <v>0.1601287677681691</v>
+        <v>0.219997141939932</v>
       </c>
       <c r="U18" t="n">
-        <v>0.3431678305582084</v>
+        <v>0.378923133912908</v>
       </c>
       <c r="V18" t="n">
-        <v>0.7834109965419038</v>
+        <v>0.9492842996075423</v>
       </c>
       <c r="W18" t="n">
-        <v>0.4928376848959033</v>
+        <v>0.6459823864886274</v>
       </c>
       <c r="X18" t="n">
-        <v>0.00616</v>
+        <v>0.02962</v>
       </c>
       <c r="Y18" t="n">
-        <v>0.90191</v>
+        <v>0.81926</v>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>2026-08-27T19:31:17.648954+00:00</t>
+          <t>2026-08-27T19:49:43.807249+00:00</t>
         </is>
       </c>
       <c r="AD18" t="inlineStr">
@@ -5076,10 +5076,10 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2759354744832</v>
+        <v>2771758874624</v>
       </c>
       <c r="F19" t="n">
-        <v>255.8200073242188</v>
+        <v>256.9700012207031</v>
       </c>
       <c r="G19" t="n">
         <v>775680032768</v>
@@ -5109,25 +5109,25 @@
         <v>0.13689</v>
       </c>
       <c r="Q19" t="n">
-        <v>20.56431</v>
+        <v>20.656754</v>
       </c>
       <c r="R19" t="n">
-        <v>3.5573363</v>
+        <v>3.5733275</v>
       </c>
       <c r="S19" t="n">
-        <v>857.1753975659234</v>
+        <v>861.0286588784932</v>
       </c>
       <c r="T19" t="n">
-        <v>0.1081175025897838</v>
+        <v>0.1130988501313415</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.06635033823277825</v>
+        <v>-0.06215328021641198</v>
       </c>
       <c r="V19" t="n">
-        <v>0.2144892141354164</v>
+        <v>0.2199487370171893</v>
       </c>
       <c r="W19" t="n">
-        <v>0.1165328769903955</v>
+        <v>0.1215520543690272</v>
       </c>
       <c r="X19" t="n">
         <v>0.0887</v>
@@ -5137,7 +5137,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>2026-08-27T19:31:11.882822+00:00</t>
+          <t>2026-08-27T19:49:36.051114+00:00</t>
         </is>
       </c>
       <c r="AD19" t="inlineStr">
@@ -5149,84 +5149,87 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ACMR</t>
+          <t>VRT</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>ACM Research, Inc.</t>
+          <t>Vertiv Holdings Co</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Semiconductor Equipment &amp; Materials</t>
+          <t>Electrical Equipment &amp; Parts</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5569846784</v>
+        <v>103550263296</v>
       </c>
       <c r="F20" t="n">
-        <v>79.97000122070312</v>
+        <v>268.9700012207031</v>
       </c>
       <c r="G20" t="n">
-        <v>1037772032</v>
+        <v>11479600128</v>
       </c>
       <c r="H20" t="n">
-        <v>0.36</v>
+        <v>0.241</v>
       </c>
       <c r="I20" t="n">
-        <v>2.12</v>
+        <v>4.43</v>
       </c>
       <c r="J20" t="n">
-        <v>1.806</v>
+        <v>0.53</v>
       </c>
       <c r="K20" t="n">
-        <v>-186610256</v>
+        <v>2696537600</v>
       </c>
       <c r="M20" t="n">
-        <v>1439374976</v>
+        <v>3110599936</v>
       </c>
       <c r="N20" t="n">
-        <v>349319008</v>
+        <v>3338200064</v>
       </c>
       <c r="O20" t="n">
-        <v>0.43835</v>
+        <v>0.38039002</v>
       </c>
       <c r="P20" t="n">
-        <v>0.16982001</v>
+        <v>0.20362</v>
       </c>
       <c r="Q20" t="n">
-        <v>37.721703</v>
+        <v>60.71558</v>
       </c>
       <c r="R20" t="n">
-        <v>5.36712</v>
+        <v>9.020708000000001</v>
+      </c>
+      <c r="S20" t="n">
+        <v>38.40119392216152</v>
       </c>
       <c r="T20" t="n">
-        <v>0.1103860725936605</v>
+        <v>-0.002188738474678043</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1388111060190056</v>
+        <v>-0.1437202197862839</v>
       </c>
       <c r="V20" t="n">
-        <v>0.167956766393671</v>
+        <v>0.02631674862776157</v>
       </c>
       <c r="W20" t="n">
-        <v>1.798110617011267</v>
+        <v>1.082331587151298</v>
       </c>
       <c r="X20" t="n">
-        <v>0.12675999</v>
+        <v>0.00269</v>
       </c>
       <c r="Y20" t="n">
-        <v>0.78055</v>
+        <v>0.84448</v>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>2026-08-27T19:31:08.983706+00:00</t>
+          <t>2026-08-27T19:49:41.694895+00:00</t>
         </is>
       </c>
       <c r="AD20" t="inlineStr">
@@ -5238,87 +5241,84 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>VRT</t>
+          <t>ACMR</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Vertiv Holdings Co</t>
+          <t>ACM Research, Inc.</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Electrical Equipment &amp; Parts</t>
+          <t>Semiconductor Equipment &amp; Materials</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103515619328</v>
+        <v>5550344704</v>
       </c>
       <c r="F21" t="n">
-        <v>268.8800048828125</v>
+        <v>79.69000244140625</v>
       </c>
       <c r="G21" t="n">
-        <v>11479600128</v>
+        <v>1037772032</v>
       </c>
       <c r="H21" t="n">
-        <v>0.241</v>
+        <v>0.36</v>
       </c>
       <c r="I21" t="n">
-        <v>4.43</v>
+        <v>2.12</v>
       </c>
       <c r="J21" t="n">
-        <v>0.53</v>
+        <v>1.806</v>
       </c>
       <c r="K21" t="n">
-        <v>2696537600</v>
+        <v>-186610256</v>
       </c>
       <c r="M21" t="n">
-        <v>3110599936</v>
+        <v>1439374976</v>
       </c>
       <c r="N21" t="n">
-        <v>3338200064</v>
+        <v>349319008</v>
       </c>
       <c r="O21" t="n">
-        <v>0.38039002</v>
+        <v>0.43835</v>
       </c>
       <c r="P21" t="n">
-        <v>0.20362</v>
+        <v>0.16982001</v>
       </c>
       <c r="Q21" t="n">
-        <v>60.695263</v>
+        <v>37.589626</v>
       </c>
       <c r="R21" t="n">
-        <v>9.017353999999999</v>
-      </c>
-      <c r="S21" t="n">
-        <v>38.38834634755325</v>
+        <v>5.3483276</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.002522602322080236</v>
+        <v>0.1064982804199874</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1440067277391385</v>
+        <v>-0.1418263846907318</v>
       </c>
       <c r="V21" t="n">
-        <v>0.0259733469529535</v>
+        <v>0.1638674020836814</v>
       </c>
       <c r="W21" t="n">
-        <v>1.081634601027083</v>
+        <v>1.788313598815175</v>
       </c>
       <c r="X21" t="n">
-        <v>0.00269</v>
+        <v>0.12675999</v>
       </c>
       <c r="Y21" t="n">
-        <v>0.84448</v>
+        <v>0.78055</v>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>2026-08-27T19:31:15.994057+00:00</t>
+          <t>2026-08-27T19:49:31.812168+00:00</t>
         </is>
       </c>
       <c r="AD21" t="inlineStr">
@@ -5349,10 +5349,10 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>3755358289920</v>
+        <v>3749232246784</v>
       </c>
       <c r="F22" t="n">
-        <v>505.7349853515625</v>
+        <v>504.8999938964844</v>
       </c>
       <c r="G22" t="n">
         <v>331839012864</v>
@@ -5382,25 +5382,25 @@
         <v>0.45111</v>
       </c>
       <c r="Q22" t="n">
-        <v>28.143295</v>
+        <v>28.097385</v>
       </c>
       <c r="R22" t="n">
-        <v>11.316808</v>
+        <v>11.298123</v>
       </c>
       <c r="S22" t="n">
-        <v>226.9715785926414</v>
+        <v>226.6013242590304</v>
       </c>
       <c r="T22" t="n">
-        <v>0.2881328160257766</v>
+        <v>0.2860060501789574</v>
       </c>
       <c r="U22" t="n">
-        <v>0.186648524580679</v>
+        <v>0.1846893139132242</v>
       </c>
       <c r="V22" t="n">
-        <v>0.2675598420331105</v>
+        <v>0.2654670431017452</v>
       </c>
       <c r="W22" t="n">
-        <v>0.006228053174162529</v>
+        <v>0.004566724908180886</v>
       </c>
       <c r="X22" t="n">
         <v>0.00090000004</v>
@@ -5410,7 +5410,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>2026-08-27T19:31:11.097926+00:00</t>
+          <t>2026-08-27T19:49:34.836052+00:00</t>
         </is>
       </c>
       <c r="AD22" t="inlineStr">
@@ -5441,10 +5441,10 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>662820225024</v>
+        <v>663102554112</v>
       </c>
       <c r="F23" t="n">
-        <v>1725.64501953125</v>
+        <v>1726.380004882812</v>
       </c>
       <c r="G23" t="n">
         <v>35327500288</v>
@@ -5474,25 +5474,25 @@
         <v>0.37057</v>
       </c>
       <c r="Q23" t="n">
-        <v>58.141678</v>
+        <v>58.166443</v>
       </c>
       <c r="R23" t="n">
-        <v>18.762161</v>
+        <v>18.770153</v>
       </c>
       <c r="S23" t="n">
-        <v>78.55484175386718</v>
+        <v>78.5883022850837</v>
       </c>
       <c r="T23" t="n">
-        <v>0.09014502843487637</v>
+        <v>0.09060934213665739</v>
       </c>
       <c r="U23" t="n">
-        <v>0.076042530845154</v>
+        <v>0.07650083802239949</v>
       </c>
       <c r="V23" t="n">
-        <v>0.1343854928168879</v>
+        <v>0.1348686493820033</v>
       </c>
       <c r="W23" t="n">
-        <v>1.25585851259821</v>
+        <v>1.256819326058215</v>
       </c>
       <c r="X23" t="n">
         <v>0.00016000001</v>
@@ -5502,7 +5502,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>2026-08-27T19:31:13.843574+00:00</t>
+          <t>2026-08-27T19:49:38.702680+00:00</t>
         </is>
       </c>
       <c r="AD23" t="inlineStr">
@@ -5533,10 +5533,10 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>315209416704</v>
+        <v>315343863808</v>
       </c>
       <c r="F24" t="n">
-        <v>386.8299865722656</v>
+        <v>387.0700073242188</v>
       </c>
       <c r="G24" t="n">
         <v>10606499840</v>
@@ -5563,25 +5563,25 @@
         <v>-0.02465</v>
       </c>
       <c r="Q24" t="n">
-        <v>336.31305</v>
+        <v>336.4565</v>
       </c>
       <c r="R24" t="n">
-        <v>29.71928</v>
+        <v>29.742334</v>
       </c>
       <c r="S24" t="n">
-        <v>88.06269461721104</v>
+        <v>88.10025623064735</v>
       </c>
       <c r="T24" t="n">
-        <v>0.2126331867469142</v>
+        <v>0.2133856028972374</v>
       </c>
       <c r="U24" t="n">
-        <v>0.5006789116623989</v>
+        <v>0.5016100547829443</v>
       </c>
       <c r="V24" t="n">
-        <v>1.670740101855896</v>
+        <v>1.67239724600131</v>
       </c>
       <c r="W24" t="n">
-        <v>1.061883616618473</v>
+        <v>1.063162976733458</v>
       </c>
       <c r="X24" t="n">
         <v>0.0076</v>
@@ -5591,7 +5591,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>2026-08-27T19:31:10.666179+00:00</t>
+          <t>2026-08-27T19:49:34.194101+00:00</t>
         </is>
       </c>
       <c r="AD24" t="inlineStr">
@@ -5680,7 +5680,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>2026-08-27T19:31:16.420471+00:00</t>
+          <t>2026-08-27T19:49:42.267947+00:00</t>
         </is>
       </c>
       <c r="AD25" t="inlineStr">
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>231404519424</v>
+        <v>232733327360</v>
       </c>
       <c r="F26" t="n">
-        <v>227.2550048828125</v>
+        <v>228.5599975585938</v>
       </c>
       <c r="G26" t="n">
         <v>5094199808</v>
@@ -5741,25 +5741,25 @@
         <v>-0.022079999</v>
       </c>
       <c r="Q26" t="n">
-        <v>3787.5835</v>
+        <v>3809.3335</v>
       </c>
       <c r="R26" t="n">
-        <v>45.4251</v>
+        <v>45.685944</v>
       </c>
       <c r="S26" t="n">
-        <v>120.1249569510464</v>
+        <v>120.8147576364674</v>
       </c>
       <c r="T26" t="n">
-        <v>0.2500275086250345</v>
+        <v>0.2572056860390894</v>
       </c>
       <c r="U26" t="n">
-        <v>0.3547243212090163</v>
+        <v>0.3625037112285767</v>
       </c>
       <c r="V26" t="n">
-        <v>1.502050660977601</v>
+        <v>1.516418475621301</v>
       </c>
       <c r="W26" t="n">
-        <v>1.150966733015196</v>
+        <v>1.163318477848633</v>
       </c>
       <c r="X26" t="n">
         <v>0.01467</v>
@@ -5769,7 +5769,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>2026-08-27T19:31:10.231182+00:00</t>
+          <t>2026-08-27T19:49:33.591437+00:00</t>
         </is>
       </c>
       <c r="AD26" t="inlineStr">
@@ -5800,10 +5800,10 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>268067651584</v>
+        <v>269648281600</v>
       </c>
       <c r="F27" t="n">
-        <v>251</v>
+        <v>252.4799957275391</v>
       </c>
       <c r="G27" t="n">
         <v>5155999744</v>
@@ -5833,25 +5833,25 @@
         <v>0.07603</v>
       </c>
       <c r="Q27" t="n">
-        <v>256.12244</v>
+        <v>257.63263</v>
       </c>
       <c r="R27" t="n">
-        <v>51.9914</v>
+        <v>52.297962</v>
       </c>
       <c r="S27" t="n">
-        <v>200.874977903334</v>
+        <v>202.0594140621216</v>
       </c>
       <c r="T27" t="n">
-        <v>0.02557814156382698</v>
+        <v>0.03162535777008957</v>
       </c>
       <c r="U27" t="n">
-        <v>-0.2513496339519833</v>
+        <v>-0.2469352939393473</v>
       </c>
       <c r="V27" t="n">
-        <v>0.9052678725827463</v>
+        <v>0.9165020889621882</v>
       </c>
       <c r="W27" t="n">
-        <v>0.784444713956834</v>
+        <v>0.7949665089874547</v>
       </c>
       <c r="X27" t="n">
         <v>0.0007</v>
@@ -5861,7 +5861,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>2026-08-27T19:31:14.213096+00:00</t>
+          <t>2026-08-27T19:49:39.223496+00:00</t>
         </is>
       </c>
       <c r="AD27" t="inlineStr">
@@ -5892,10 +5892,10 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>217971818496</v>
+        <v>217064128512</v>
       </c>
       <c r="F28" t="n">
-        <v>242.5399932861328</v>
+        <v>241.5500030517578</v>
       </c>
       <c r="G28" t="n">
         <v>8717100032</v>
@@ -5925,25 +5925,25 @@
         <v>0.14479999</v>
       </c>
       <c r="Q28" t="n">
-        <v>83.06164</v>
+        <v>82.71575</v>
       </c>
       <c r="R28" t="n">
-        <v>25.005083</v>
+        <v>24.900957</v>
       </c>
       <c r="S28" t="n">
-        <v>96.03551538819691</v>
+        <v>95.63559912366502</v>
       </c>
       <c r="T28" t="n">
-        <v>0.3901529866978204</v>
+        <v>0.3844787147459181</v>
       </c>
       <c r="U28" t="n">
-        <v>0.1843959820059391</v>
+        <v>0.1795615609278631</v>
       </c>
       <c r="V28" t="n">
-        <v>1.999521343973279</v>
+        <v>1.987278297226078</v>
       </c>
       <c r="W28" t="n">
-        <v>2.249855679314171</v>
+        <v>2.236591207574131</v>
       </c>
       <c r="X28" t="n">
         <v>0.00494</v>
@@ -5953,7 +5953,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>2026-08-27T19:31:14.622829+00:00</t>
+          <t>2026-08-27T19:49:39.791700+00:00</t>
         </is>
       </c>
       <c r="AD28" t="inlineStr">
@@ -5984,10 +5984,10 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1450269736960</v>
+        <v>1450448125952</v>
       </c>
       <c r="F29" t="n">
-        <v>569.5</v>
+        <v>569.3599853515625</v>
       </c>
       <c r="G29" t="n">
         <v>228246994944</v>
@@ -6017,25 +6017,25 @@
         <v>0.34827</v>
       </c>
       <c r="Q29" t="n">
-        <v>21.43411</v>
+        <v>21.436747</v>
       </c>
       <c r="R29" t="n">
-        <v>6.353949</v>
+        <v>6.3547306</v>
       </c>
       <c r="S29" t="n">
-        <v>67.28658084376902</v>
+        <v>67.29485736297502</v>
       </c>
       <c r="T29" t="n">
-        <v>-0.04029250303602117</v>
+        <v>-0.04052845230343161</v>
       </c>
       <c r="U29" t="n">
-        <v>-0.1027281304185143</v>
+        <v>-0.1029487295499845</v>
       </c>
       <c r="V29" t="n">
-        <v>-0.1272379248052589</v>
+        <v>-0.1274524980715064</v>
       </c>
       <c r="W29" t="n">
-        <v>-0.2355072739847233</v>
+        <v>-0.2356952912690724</v>
       </c>
       <c r="X29" t="n">
         <v>0.00148</v>
@@ -6045,7 +6045,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>2026-08-27T19:31:12.303864+00:00</t>
+          <t>2026-08-27T19:49:36.630470+00:00</t>
         </is>
       </c>
       <c r="AD29" t="inlineStr">
@@ -6076,10 +6076,10 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>143231238144</v>
+        <v>143220899840</v>
       </c>
       <c r="F30" t="n">
-        <v>138.5399932861328</v>
+        <v>138.5299987792969</v>
       </c>
       <c r="G30" t="n">
         <v>14732000256</v>
@@ -6109,25 +6109,25 @@
         <v>0.04063</v>
       </c>
       <c r="Q30" t="n">
-        <v>86.58749400000001</v>
+        <v>86.581245</v>
       </c>
       <c r="R30" t="n">
-        <v>9.722457</v>
+        <v>9.721755</v>
       </c>
       <c r="S30" t="n">
-        <v>27.81526667053116</v>
+        <v>27.81325898920126</v>
       </c>
       <c r="T30" t="n">
-        <v>0.2523954967124014</v>
+        <v>0.2523051468065274</v>
       </c>
       <c r="U30" t="n">
-        <v>0.2741652626583706</v>
+        <v>0.2740733422451693</v>
       </c>
       <c r="V30" t="n">
-        <v>0.3291757538537663</v>
+        <v>0.3290798648917206</v>
       </c>
       <c r="W30" t="n">
-        <v>-0.2199148701886797</v>
+        <v>-0.219971146834705</v>
       </c>
       <c r="X30" t="n">
         <v>0.00176</v>
@@ -6137,7 +6137,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>2026-08-27T19:31:18.099324+00:00</t>
+          <t>2026-08-27T19:49:46.482409+00:00</t>
         </is>
       </c>
       <c r="AD30" t="inlineStr">
@@ -6168,10 +6168,10 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>434216599552</v>
+        <v>435456671744</v>
       </c>
       <c r="F31" t="n">
-        <v>150.7449951171875</v>
+        <v>151.1755065917969</v>
       </c>
       <c r="G31" t="n">
         <v>67356999680</v>
@@ -6201,22 +6201,22 @@
         <v>0.36202</v>
       </c>
       <c r="Q31" t="n">
-        <v>25.812498</v>
+        <v>25.886217</v>
       </c>
       <c r="R31" t="n">
-        <v>6.4464955</v>
+        <v>6.464906</v>
       </c>
       <c r="T31" t="n">
-        <v>0.2566271779565192</v>
+        <v>0.2602159698696154</v>
       </c>
       <c r="U31" t="n">
-        <v>-0.2573910987122766</v>
+        <v>-0.2552702876505039</v>
       </c>
       <c r="V31" t="n">
-        <v>0.02642344061512936</v>
+        <v>0.0293547954415323</v>
       </c>
       <c r="W31" t="n">
-        <v>-0.3534492298995104</v>
+        <v>-0.351602750517363</v>
       </c>
       <c r="X31" t="n">
         <v>0.40498</v>
@@ -6226,7 +6226,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>2026-08-27T19:31:12.928043+00:00</t>
+          <t>2026-08-27T19:49:37.264589+00:00</t>
         </is>
       </c>
       <c r="AD31" t="inlineStr">
@@ -6756,7 +6756,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>SNOW</t>
+          <t>NET</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -6790,7 +6790,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>NET</t>
+          <t>SNOW</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -6853,23 +6853,18 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ACMR</t>
+          <t>VRT</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>94.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="C20" t="n">
-        <v>94.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
           <t>HIGH</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>price_to_fcf</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -6887,18 +6882,23 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>VRT</t>
+          <t>ACMR</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>100</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="C21" t="n">
-        <v>100</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
           <t>HIGH</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>price_to_fcf</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -7296,7 +7296,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>55.59</v>
+        <v>55.6</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/reports/investment_dashboard.xlsx
+++ b/reports/investment_dashboard.xlsx
@@ -525,16 +525,16 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>MU</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Taiwan Semiconductor Manufacturing Company Limited</t>
+          <t>Micron Technology, Inc.</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>55.6</v>
+        <v>56.77</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>426</v>
+        <v>935.3900146484375</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -550,19 +550,24 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>100</v>
+        <v>84.2</v>
       </c>
       <c r="I2" t="n">
-        <v>100</v>
+        <v>88.2</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Revenue Growth; Earnings Fcf; Balance Sheet; Valuation</t>
+          <t>Revenue Growth; Earnings Fcf; Balance Sheet</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
           <t>Industry Growth; Competitive Advantage; Catalysts; Inflation Resilience</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>High market sensitivity / beta</t>
         </is>
       </c>
     </row>
@@ -572,16 +577,16 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>MU</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Micron Technology, Inc.</t>
+          <t>Taiwan Semiconductor Manufacturing Company Limited</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>54.41</v>
+        <v>55.69</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -589,7 +594,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>920.5449829101562</v>
+        <v>427.2999877929688</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -597,24 +602,19 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="I3" t="n">
         <v>100</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Revenue Growth; Earnings Fcf; Balance Sheet</t>
+          <t>Revenue Growth; Earnings Fcf; Balance Sheet; Valuation</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
           <t>Industry Growth; Competitive Advantage; Catalysts; Inflation Resilience</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>High market sensitivity / beta</t>
         </is>
       </c>
     </row>
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>53.52</v>
+        <v>53.63</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>236.9799957275391</v>
+        <v>240.2400054931641</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -685,7 +685,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>52.92</v>
+        <v>52.96</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -693,7 +693,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>200.2200012207031</v>
+        <v>201.0899963378906</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -737,7 +737,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>52.41</v>
+        <v>52.38</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -745,7 +745,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>186.2700042724609</v>
+        <v>185.9299926757812</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>51.16</v>
+        <v>51.23</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>468.1749877929688</v>
+        <v>472.260009765625</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -836,7 +836,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>51.05</v>
+        <v>51.22</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -844,7 +844,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>228.2599945068359</v>
+        <v>227.9799957275391</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>50.9</v>
+        <v>51.07</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>366.6700134277344</v>
+        <v>372.0599975585938</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>47.63</v>
+        <v>47.8</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -982,7 +982,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>47.62</v>
+        <v>47.65</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -990,7 +990,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>474.5328979492188</v>
+        <v>476.6700134277344</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -1042,7 +1042,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>341.0549926757812</v>
+        <v>340.6499938964844</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>45.46</v>
+        <v>45.54</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -1089,7 +1089,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>478.8800048828125</v>
+        <v>482.3599853515625</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -1128,7 +1128,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>45.16</v>
+        <v>45.15</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>243.3099975585938</v>
+        <v>242.9299926757812</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -1180,7 +1180,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>44.29</v>
+        <v>44.42</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>368.8299865722656</v>
+        <v>371.5400085449219</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -1232,7 +1232,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>43.82</v>
+        <v>43.8</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>445.1099853515625</v>
+        <v>440.5799865722656</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1270,16 +1270,16 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>NET</t>
+          <t>SNOW</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Cloudflare, Inc.</t>
+          <t>Snowflake Inc.</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>43.16</v>
+        <v>43.13</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -1287,7 +1287,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>309.239990234375</v>
+        <v>329.1099853515625</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1322,16 +1322,16 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>SNOW</t>
+          <t>NET</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Snowflake Inc.</t>
+          <t>Cloudflare, Inc.</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>43.15</v>
+        <v>43.12</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -1339,7 +1339,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>329.8384094238281</v>
+        <v>308.2300109863281</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1374,16 +1374,16 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>AMZN</t>
+          <t>ACMR</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Amazon.com, Inc.</t>
+          <t>ACM Research, Inc.</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>42.65</v>
+        <v>42.61</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -1391,7 +1391,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>256.9700012207031</v>
+        <v>80.48999786376953</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1399,19 +1399,24 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>100</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="I19" t="n">
-        <v>100</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Earnings Fcf</t>
+          <t>Revenue Growth</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
           <t>Industry Growth; Competitive Advantage; Catalysts; Inflation Resilience</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>Negative free cash flow / unprofitable growth</t>
         </is>
       </c>
     </row>
@@ -1421,16 +1426,16 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>VRT</t>
+          <t>AMZN</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Vertiv Holdings Co</t>
+          <t>Amazon.com, Inc.</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>42.48</v>
+        <v>42.59</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -1438,7 +1443,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>268.9700012207031</v>
+        <v>256.260009765625</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1458,12 +1463,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Industry Growth; Valuation; Competitive Advantage; Momentum; Catalysts; Inflation Resilience</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>High market sensitivity / beta</t>
+          <t>Industry Growth; Competitive Advantage; Catalysts; Inflation Resilience</t>
         </is>
       </c>
     </row>
@@ -1473,16 +1473,16 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>ACMR</t>
+          <t>VRT</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>ACM Research, Inc.</t>
+          <t>Vertiv Holdings Co</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>42.45</v>
+        <v>42.49</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -1490,7 +1490,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>79.69000244140625</v>
+        <v>269.2799987792969</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1498,24 +1498,24 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>94.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="I21" t="n">
-        <v>94.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Revenue Growth</t>
+          <t>Earnings Fcf</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>Industry Growth; Competitive Advantage; Catalysts; Inflation Resilience</t>
+          <t>Industry Growth; Valuation; Competitive Advantage; Catalysts; Inflation Resilience</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>Negative free cash flow / unprofitable growth</t>
+          <t>High market sensitivity / beta</t>
         </is>
       </c>
     </row>
@@ -1534,7 +1534,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>42.41</v>
+        <v>42.42</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -1542,7 +1542,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>504.8999938964844</v>
+        <v>505.0599975585938</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1581,7 +1581,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>42.35</v>
+        <v>42.41</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1726.380004882812</v>
+        <v>1735.010009765625</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1628,7 +1628,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>42.25</v>
+        <v>42.2</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -1636,7 +1636,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>387.0700073242188</v>
+        <v>382.8500061035156</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1680,7 +1680,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>41.81</v>
+        <v>41.91</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>38.31499862670898</v>
+        <v>38.45999908447266</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1708,7 +1708,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>Industry Growth; Balance Sheet; Competitive Advantage; Momentum; Catalysts; Inflation Resilience</t>
+          <t>Industry Growth; Balance Sheet; Competitive Advantage; Catalysts; Inflation Resilience</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -1732,7 +1732,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>41.15</v>
+        <v>41.12</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -1740,7 +1740,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>228.5599975585938</v>
+        <v>227.9600067138672</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1784,7 +1784,7 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>40.74</v>
+        <v>40.79</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -1792,7 +1792,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>252.4799957275391</v>
+        <v>255.2100067138672</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1836,7 +1836,7 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>39.76</v>
+        <v>39.75</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>241.5500030517578</v>
+        <v>241.4499969482422</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1888,7 +1888,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>39.56</v>
+        <v>39.57</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -1896,7 +1896,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>569.3599853515625</v>
+        <v>571.0999755859375</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>36.48</v>
+        <v>36.47</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -1943,7 +1943,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>138.5299987792969</v>
+        <v>138.4299926757812</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1977,7 +1977,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>31.52</v>
+        <v>31.59</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -1985,7 +1985,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>151.1755065917969</v>
+        <v>151.9400024414062</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -2115,7 +2115,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>MU</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -2128,19 +2128,19 @@
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>8.84</v>
+        <v>9.02</v>
       </c>
       <c r="F2" t="n">
-        <v>8.640000000000001</v>
+        <v>7.19</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>5.43</v>
+        <v>7.06</v>
       </c>
       <c r="I2" t="n">
-        <v>2.69</v>
+        <v>3.5</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -2149,13 +2149,13 @@
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>55.6</v>
+        <v>56.77</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>MU</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -2168,19 +2168,19 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>9.02</v>
+        <v>8.84</v>
       </c>
       <c r="F3" t="n">
-        <v>4.99</v>
+        <v>8.68</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>6.9</v>
+        <v>5.48</v>
       </c>
       <c r="I3" t="n">
-        <v>3.5</v>
+        <v>2.69</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -2189,7 +2189,7 @@
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>54.41</v>
+        <v>55.69</v>
       </c>
     </row>
     <row r="4">
@@ -2211,13 +2211,13 @@
         <v>9.91</v>
       </c>
       <c r="F4" t="n">
-        <v>2.35</v>
+        <v>2.32</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>7.72</v>
+        <v>7.86</v>
       </c>
       <c r="I4" t="n">
         <v>3.54</v>
@@ -2229,7 +2229,7 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>53.52</v>
+        <v>53.63</v>
       </c>
     </row>
     <row r="5">
@@ -2251,13 +2251,13 @@
         <v>10</v>
       </c>
       <c r="F5" t="n">
-        <v>0.79</v>
+        <v>0.78</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>8.5</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="I5" t="n">
         <v>3.63</v>
@@ -2269,7 +2269,7 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>52.92</v>
+        <v>52.96</v>
       </c>
     </row>
     <row r="6">
@@ -2297,7 +2297,7 @@
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>8.529999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="I6" t="n">
         <v>3.35</v>
@@ -2309,7 +2309,7 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>52.41</v>
+        <v>52.38</v>
       </c>
     </row>
     <row r="7">
@@ -2331,13 +2331,13 @@
         <v>6.33</v>
       </c>
       <c r="F7" t="n">
-        <v>5.75</v>
+        <v>5.77</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>9.06</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="I7" t="n">
         <v>3.54</v>
@@ -2349,7 +2349,7 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>51.16</v>
+        <v>51.23</v>
       </c>
     </row>
     <row r="8">
@@ -2371,13 +2371,13 @@
         <v>9.029999999999999</v>
       </c>
       <c r="F8" t="n">
-        <v>2.89</v>
+        <v>3.08</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>5.69</v>
+        <v>5.67</v>
       </c>
       <c r="I8" t="n">
         <v>3.44</v>
@@ -2389,7 +2389,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>51.05</v>
+        <v>51.22</v>
       </c>
     </row>
     <row r="9">
@@ -2411,13 +2411,13 @@
         <v>8.9</v>
       </c>
       <c r="F9" t="n">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>5.33</v>
+        <v>5.54</v>
       </c>
       <c r="I9" t="n">
         <v>3.75</v>
@@ -2429,7 +2429,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>50.9</v>
+        <v>51.07</v>
       </c>
     </row>
     <row r="10">
@@ -2451,7 +2451,7 @@
         <v>9.699999999999999</v>
       </c>
       <c r="F10" t="n">
-        <v>6.5</v>
+        <v>6.67</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -2469,7 +2469,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>47.63</v>
+        <v>47.8</v>
       </c>
     </row>
     <row r="11">
@@ -2491,13 +2491,13 @@
         <v>8.77</v>
       </c>
       <c r="F11" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>6.18</v>
+        <v>6.22</v>
       </c>
       <c r="I11" t="n">
         <v>3.45</v>
@@ -2509,7 +2509,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>47.62</v>
+        <v>47.65</v>
       </c>
     </row>
     <row r="12">
@@ -2531,13 +2531,13 @@
         <v>8.34</v>
       </c>
       <c r="F12" t="n">
-        <v>4.43</v>
+        <v>4.44</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>4.49</v>
+        <v>4.48</v>
       </c>
       <c r="I12" t="n">
         <v>3.53</v>
@@ -2571,13 +2571,13 @@
         <v>7.78</v>
       </c>
       <c r="F13" t="n">
-        <v>2.07</v>
+        <v>2.04</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>5.85</v>
+        <v>5.96</v>
       </c>
       <c r="I13" t="n">
         <v>3.58</v>
@@ -2589,7 +2589,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>45.46</v>
+        <v>45.54</v>
       </c>
     </row>
     <row r="14">
@@ -2617,7 +2617,7 @@
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>6.59</v>
+        <v>6.58</v>
       </c>
       <c r="I14" t="n">
         <v>3.67</v>
@@ -2629,7 +2629,7 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>45.16</v>
+        <v>45.15</v>
       </c>
     </row>
     <row r="15">
@@ -2651,13 +2651,13 @@
         <v>6.16</v>
       </c>
       <c r="F15" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>3.57</v>
+        <v>3.71</v>
       </c>
       <c r="I15" t="n">
         <v>3.53</v>
@@ -2669,7 +2669,7 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>44.29</v>
+        <v>44.42</v>
       </c>
     </row>
     <row r="16">
@@ -2691,13 +2691,13 @@
         <v>9.880000000000001</v>
       </c>
       <c r="F16" t="n">
-        <v>1.54</v>
+        <v>1.59</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>9.85</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="I16" t="n">
         <v>3.73</v>
@@ -2709,17 +2709,17 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>43.82</v>
+        <v>43.8</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>NET</t>
+          <t>SNOW</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>15</v>
+        <v>14.44</v>
       </c>
       <c r="C17" t="n">
         <v>7.5</v>
@@ -2728,19 +2728,19 @@
         <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>7.71</v>
+        <v>7.58</v>
       </c>
       <c r="F17" t="n">
-        <v>0.55</v>
+        <v>0.99</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>8.76</v>
+        <v>9.06</v>
       </c>
       <c r="I17" t="n">
-        <v>3.64</v>
+        <v>3.56</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2749,17 +2749,17 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>43.16</v>
+        <v>43.13</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>SNOW</t>
+          <t>NET</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>14.44</v>
+        <v>15</v>
       </c>
       <c r="C18" t="n">
         <v>7.5</v>
@@ -2768,19 +2768,19 @@
         <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>7.58</v>
+        <v>7.71</v>
       </c>
       <c r="F18" t="n">
-        <v>0.98</v>
+        <v>0.55</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>9.09</v>
+        <v>8.720000000000001</v>
       </c>
       <c r="I18" t="n">
-        <v>3.56</v>
+        <v>3.64</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2789,38 +2789,38 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>43.15</v>
+        <v>43.12</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>AMZN</t>
+          <t>ACMR</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>9.220000000000001</v>
+        <v>15</v>
       </c>
       <c r="C19" t="n">
-        <v>12.28</v>
+        <v>7.83</v>
       </c>
       <c r="D19" t="n">
         <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>6.64</v>
+        <v>4.02</v>
       </c>
       <c r="F19" t="n">
-        <v>6.53</v>
+        <v>6.86</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>4.51</v>
+        <v>5.27</v>
       </c>
       <c r="I19" t="n">
-        <v>3.47</v>
+        <v>3.63</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2829,38 +2829,38 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>42.65</v>
+        <v>42.61</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>VRT</t>
+          <t>AMZN</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>10.91</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="C20" t="n">
-        <v>13.39</v>
+        <v>12.28</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>7.41</v>
+        <v>6.64</v>
       </c>
       <c r="F20" t="n">
-        <v>3.21</v>
+        <v>6.52</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>4</v>
+        <v>4.46</v>
       </c>
       <c r="I20" t="n">
-        <v>3.56</v>
+        <v>3.47</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2869,38 +2869,38 @@
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>42.48</v>
+        <v>42.59</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ACMR</t>
+          <t>VRT</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>15</v>
+        <v>10.91</v>
       </c>
       <c r="C21" t="n">
-        <v>7.83</v>
+        <v>13.39</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
       </c>
       <c r="E21" t="n">
+        <v>7.41</v>
+      </c>
+      <c r="F21" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" t="n">
         <v>4.02</v>
       </c>
-      <c r="F21" t="n">
-        <v>6.84</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" t="n">
-        <v>5.13</v>
-      </c>
       <c r="I21" t="n">
-        <v>3.63</v>
+        <v>3.56</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>42.45</v>
+        <v>42.49</v>
       </c>
     </row>
     <row r="22">
@@ -2937,7 +2937,7 @@
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>6.09</v>
+        <v>6.1</v>
       </c>
       <c r="I22" t="n">
         <v>3.45</v>
@@ -2949,7 +2949,7 @@
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>42.41</v>
+        <v>42.42</v>
       </c>
     </row>
     <row r="23">
@@ -2971,13 +2971,13 @@
         <v>8.960000000000001</v>
       </c>
       <c r="F23" t="n">
-        <v>0.57</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>5.92</v>
+        <v>5.99</v>
       </c>
       <c r="I23" t="n">
         <v>2.76</v>
@@ -2989,7 +2989,7 @@
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>42.35</v>
+        <v>42.41</v>
       </c>
     </row>
     <row r="24">
@@ -3011,13 +3011,13 @@
         <v>7.97</v>
       </c>
       <c r="F24" t="n">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>9.15</v>
+        <v>9.09</v>
       </c>
       <c r="I24" t="n">
         <v>3.57</v>
@@ -3029,7 +3029,7 @@
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>42.25</v>
+        <v>42.2</v>
       </c>
     </row>
     <row r="25">
@@ -3051,13 +3051,13 @@
         <v>2.23</v>
       </c>
       <c r="F25" t="n">
-        <v>9.85</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>3.96</v>
+        <v>4.03</v>
       </c>
       <c r="I25" t="n">
         <v>3.54</v>
@@ -3069,7 +3069,7 @@
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>41.81</v>
+        <v>41.91</v>
       </c>
     </row>
     <row r="26">
@@ -3097,7 +3097,7 @@
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>9.18</v>
+        <v>9.15</v>
       </c>
       <c r="I26" t="n">
         <v>3.48</v>
@@ -3109,7 +3109,7 @@
         <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>41.15</v>
+        <v>41.12</v>
       </c>
     </row>
     <row r="27">
@@ -3137,7 +3137,7 @@
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>5.83</v>
+        <v>5.88</v>
       </c>
       <c r="I27" t="n">
         <v>3.7</v>
@@ -3149,7 +3149,7 @@
         <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>40.74</v>
+        <v>40.79</v>
       </c>
     </row>
     <row r="28">
@@ -3177,7 +3177,7 @@
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>8.93</v>
+        <v>8.92</v>
       </c>
       <c r="I28" t="n">
         <v>3.53</v>
@@ -3189,7 +3189,7 @@
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>39.76</v>
+        <v>39.75</v>
       </c>
     </row>
     <row r="29">
@@ -3211,13 +3211,13 @@
         <v>7.23</v>
       </c>
       <c r="F29" t="n">
-        <v>5.65</v>
+        <v>5.62</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.85</v>
       </c>
       <c r="I29" t="n">
         <v>3.49</v>
@@ -3229,7 +3229,7 @@
         <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>39.56</v>
+        <v>39.57</v>
       </c>
     </row>
     <row r="30">
@@ -3257,7 +3257,7 @@
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>5.93</v>
+        <v>5.92</v>
       </c>
       <c r="I30" t="n">
         <v>3.57</v>
@@ -3269,7 +3269,7 @@
         <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>36.48</v>
+        <v>36.47</v>
       </c>
     </row>
     <row r="31">
@@ -3291,13 +3291,13 @@
         <v>0.8</v>
       </c>
       <c r="F31" t="n">
-        <v>6.32</v>
+        <v>6.34</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>2.68</v>
+        <v>2.73</v>
       </c>
       <c r="I31" t="n">
         <v>3.58</v>
@@ -3309,7 +3309,7 @@
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>31.52</v>
+        <v>31.59</v>
       </c>
     </row>
   </sheetData>
@@ -3343,11 +3343,11 @@
     <col width="15" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="18" customWidth="1" min="16" max="16"/>
-    <col width="11" customWidth="1" min="17" max="17"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
     <col width="16" customWidth="1" min="18" max="18"/>
     <col width="19" customWidth="1" min="19" max="19"/>
     <col width="23" customWidth="1" min="20" max="20"/>
-    <col width="23" customWidth="1" min="21" max="21"/>
+    <col width="22" customWidth="1" min="21" max="21"/>
     <col width="21" customWidth="1" min="22" max="22"/>
     <col width="22" customWidth="1" min="23" max="23"/>
     <col width="18" customWidth="1" min="24" max="24"/>
@@ -3514,12 +3514,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>MU</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Taiwan Semiconductor Manufacturing Company Limited</t>
+          <t>Micron Technology, Inc.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -3532,69 +3532,60 @@
           <t>Semiconductors</t>
         </is>
       </c>
-      <c r="E2" t="n">
-        <v>2209437974528</v>
-      </c>
       <c r="F2" t="n">
-        <v>426</v>
+        <v>935.3900146484375</v>
       </c>
       <c r="G2" t="n">
-        <v>4440492343296</v>
+        <v>90273996800</v>
       </c>
       <c r="H2" t="n">
-        <v>0.36</v>
+        <v>3.457</v>
       </c>
       <c r="I2" t="n">
-        <v>13.41</v>
+        <v>44.06</v>
       </c>
       <c r="J2" t="n">
-        <v>0.774</v>
+        <v>13.685</v>
       </c>
       <c r="K2" t="n">
-        <v>730826014720</v>
+        <v>7639499776</v>
       </c>
       <c r="M2" t="n">
-        <v>3518010228736</v>
+        <v>26022000640</v>
       </c>
       <c r="N2" t="n">
-        <v>1068558516224</v>
+        <v>6376000000</v>
       </c>
       <c r="O2" t="n">
-        <v>0.6423</v>
+        <v>0.7256899999999999</v>
       </c>
       <c r="P2" t="n">
-        <v>0.60344005</v>
+        <v>0.80370003</v>
       </c>
       <c r="Q2" t="n">
-        <v>31.767338</v>
-      </c>
-      <c r="R2" t="n">
-        <v>0.49756598</v>
-      </c>
-      <c r="S2" t="n">
-        <v>3.023206522518903</v>
+        <v>21.229914</v>
       </c>
       <c r="T2" t="n">
-        <v>0.08587597219307286</v>
+        <v>0.1399826712618766</v>
       </c>
       <c r="U2" t="n">
-        <v>0.005031432503544986</v>
+        <v>0.01300878301894581</v>
       </c>
       <c r="V2" t="n">
-        <v>0.1043788859285832</v>
+        <v>1.181647796120662</v>
       </c>
       <c r="W2" t="n">
-        <v>0.7999555142074082</v>
+        <v>6.956613918478925</v>
       </c>
       <c r="X2" t="n">
-        <v>0.00013</v>
+        <v>0.00238</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.15493</v>
+        <v>0.79987</v>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>2026-08-27T19:49:37.912963+00:00</t>
+          <t>2026-08-28T06:05:53.639739+00:00</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
@@ -3606,12 +3597,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>MU</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Micron Technology, Inc.</t>
+          <t>Taiwan Semiconductor Manufacturing Company Limited</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -3625,68 +3616,68 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1039823273984</v>
+        <v>2216180318208</v>
       </c>
       <c r="F3" t="n">
-        <v>920.5449829101562</v>
+        <v>427.2999877929688</v>
       </c>
       <c r="G3" t="n">
-        <v>90273996800</v>
+        <v>4440492343296</v>
       </c>
       <c r="H3" t="n">
-        <v>3.457</v>
+        <v>0.36</v>
       </c>
       <c r="I3" t="n">
-        <v>44.2</v>
+        <v>13.72</v>
       </c>
       <c r="J3" t="n">
-        <v>13.685</v>
+        <v>0.774</v>
       </c>
       <c r="K3" t="n">
-        <v>7639499776</v>
+        <v>730826014720</v>
       </c>
       <c r="M3" t="n">
-        <v>26022000640</v>
+        <v>3518010228736</v>
       </c>
       <c r="N3" t="n">
-        <v>6376000000</v>
+        <v>1068558516224</v>
       </c>
       <c r="O3" t="n">
-        <v>0.7256899999999999</v>
+        <v>0.6423</v>
       </c>
       <c r="P3" t="n">
-        <v>0.80370003</v>
+        <v>0.60344005</v>
       </c>
       <c r="Q3" t="n">
-        <v>20.830135</v>
+        <v>31.144314</v>
       </c>
       <c r="R3" t="n">
-        <v>11.518937</v>
+        <v>0.49908438</v>
       </c>
       <c r="S3" t="n">
-        <v>136.1114345798758</v>
+        <v>3.032432170681665</v>
       </c>
       <c r="T3" t="n">
-        <v>0.1218906682781442</v>
+        <v>0.08918964709572319</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.003068091118657468</v>
+        <v>0.008098401033602487</v>
       </c>
       <c r="V3" t="n">
-        <v>1.147024130838822</v>
+        <v>0.1077490245917747</v>
       </c>
       <c r="W3" t="n">
-        <v>6.830339627578591</v>
+        <v>0.8054482846213904</v>
       </c>
       <c r="X3" t="n">
-        <v>0.00238</v>
+        <v>0.00013</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.79987</v>
+        <v>0.15493</v>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>2026-08-27T19:49:31.236307+00:00</t>
+          <t>2026-08-28T06:05:59.916108+00:00</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
@@ -3717,10 +3708,10 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>44536758272</v>
+        <v>45149425664</v>
       </c>
       <c r="F4" t="n">
-        <v>236.9799957275391</v>
+        <v>240.2400054931641</v>
       </c>
       <c r="G4" t="n">
         <v>1335116032</v>
@@ -3729,7 +3720,7 @@
         <v>1.57</v>
       </c>
       <c r="I4" t="n">
-        <v>2.51</v>
+        <v>2.67</v>
       </c>
       <c r="J4" t="n">
         <v>3.432</v>
@@ -3750,25 +3741,25 @@
         <v>0.35661998</v>
       </c>
       <c r="Q4" t="n">
-        <v>94.414345</v>
+        <v>89.97752</v>
       </c>
       <c r="R4" t="n">
-        <v>33.357967</v>
+        <v>33.816856</v>
       </c>
       <c r="S4" t="n">
-        <v>177.5716101544352</v>
+        <v>180.0143639494494</v>
       </c>
       <c r="T4" t="n">
-        <v>0.2324734617850179</v>
+        <v>0.2494279541207858</v>
       </c>
       <c r="U4" t="n">
-        <v>0.06579711815799283</v>
+        <v>0.0804587312730709</v>
       </c>
       <c r="V4" t="n">
-        <v>0.9194880729376549</v>
+        <v>0.9458934656948221</v>
       </c>
       <c r="W4" t="n">
-        <v>0.930905151516489</v>
+        <v>0.9574676030479532</v>
       </c>
       <c r="X4" t="n">
         <v>0.09436</v>
@@ -3778,7 +3769,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>2026-08-27T19:49:32.522633+00:00</t>
+          <t>2026-08-28T06:05:54.692792+00:00</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
@@ -3809,10 +3800,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>252522414080</v>
+        <v>253619666944</v>
       </c>
       <c r="F5" t="n">
-        <v>200.2200012207031</v>
+        <v>201.0899963378906</v>
       </c>
       <c r="G5" t="n">
         <v>10540800000</v>
@@ -3821,7 +3812,7 @@
         <v>0.377</v>
       </c>
       <c r="I5" t="n">
-        <v>3.16</v>
+        <v>3.14</v>
       </c>
       <c r="J5" t="n">
         <v>0.357</v>
@@ -3842,25 +3833,25 @@
         <v>0.45393002</v>
       </c>
       <c r="Q5" t="n">
-        <v>63.36076</v>
+        <v>64.0414</v>
       </c>
       <c r="R5" t="n">
-        <v>23.956665</v>
+        <v>24.06076</v>
       </c>
       <c r="S5" t="n">
-        <v>64.89055583100857</v>
+        <v>65.17251633931248</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1797772276226239</v>
+        <v>0.1849035907289216</v>
       </c>
       <c r="U5" t="n">
-        <v>0.289495689517506</v>
+        <v>0.2950988008284381</v>
       </c>
       <c r="V5" t="n">
-        <v>0.5066596594197847</v>
+        <v>0.5132063907102002</v>
       </c>
       <c r="W5" t="n">
-        <v>0.5023635837166158</v>
+        <v>0.5088916477167404</v>
       </c>
       <c r="X5" t="n">
         <v>0.17247999</v>
@@ -3870,7 +3861,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>2026-08-27T19:49:40.481967+00:00</t>
+          <t>2026-08-28T06:06:02.225298+00:00</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
@@ -3901,10 +3892,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>447713804288</v>
+        <v>446800625664</v>
       </c>
       <c r="F6" t="n">
-        <v>186.2700042724609</v>
+        <v>185.9299926757812</v>
       </c>
       <c r="G6" t="n">
         <v>6155940864</v>
@@ -3913,7 +3904,7 @@
         <v>0.928</v>
       </c>
       <c r="I6" t="n">
-        <v>1.17</v>
+        <v>1.23</v>
       </c>
       <c r="J6" t="n">
         <v>2.154</v>
@@ -3934,25 +3925,25 @@
         <v>0.47120997</v>
       </c>
       <c r="Q6" t="n">
-        <v>159.23932</v>
+        <v>151.1626</v>
       </c>
       <c r="R6" t="n">
-        <v>72.72874</v>
+        <v>72.5804</v>
       </c>
       <c r="S6" t="n">
-        <v>207.3608766040131</v>
+        <v>206.9379333796696</v>
       </c>
       <c r="T6" t="n">
-        <v>0.5078928690451752</v>
+        <v>0.5051404072946721</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2994977607880833</v>
+        <v>0.297125697125697</v>
       </c>
       <c r="V6" t="n">
-        <v>0.3881064228595965</v>
+        <v>0.3855726156422654</v>
       </c>
       <c r="W6" t="n">
-        <v>0.1885528510821257</v>
+        <v>0.1863833028813136</v>
       </c>
       <c r="X6" t="n">
         <v>0.03477</v>
@@ -3962,7 +3953,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>2026-08-27T19:49:28.861374+00:00</t>
+          <t>2026-08-28T06:05:51.284618+00:00</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr">
@@ -3993,10 +3984,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>302507720704</v>
+        <v>305147215872</v>
       </c>
       <c r="F7" t="n">
-        <v>468.1749877929688</v>
+        <v>472.260009765625</v>
       </c>
       <c r="G7" t="n">
         <v>134001999872</v>
@@ -4005,7 +3996,7 @@
         <v>0.875</v>
       </c>
       <c r="I7" t="n">
-        <v>12.57</v>
+        <v>12.8</v>
       </c>
       <c r="J7" t="n">
         <v>2.825</v>
@@ -4026,25 +4017,25 @@
         <v>0.08857000600000001</v>
       </c>
       <c r="Q7" t="n">
-        <v>37.245426</v>
+        <v>36.895313</v>
       </c>
       <c r="R7" t="n">
-        <v>2.2574866</v>
+        <v>2.277184</v>
       </c>
       <c r="S7" t="n">
-        <v>55.66815850530337</v>
+        <v>56.15388440692418</v>
       </c>
       <c r="T7" t="n">
-        <v>0.1940193330916937</v>
+        <v>0.2044376496157128</v>
       </c>
       <c r="U7" t="n">
-        <v>0.4790999382469361</v>
+        <v>0.4920057019144415</v>
       </c>
       <c r="V7" t="n">
-        <v>2.809520711432647</v>
+        <v>2.842760368008178</v>
       </c>
       <c r="W7" t="n">
-        <v>2.57842229613338</v>
+        <v>2.60964552267963</v>
       </c>
       <c r="X7" t="n">
         <v>0.07491</v>
@@ -4054,7 +4045,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>2026-08-27T19:49:41.143850+00:00</t>
+          <t>2026-08-28T06:06:02.798169+00:00</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr">
@@ -4085,10 +4076,10 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5529048449024</v>
+        <v>5505032912896</v>
       </c>
       <c r="F8" t="n">
-        <v>228.2599945068359</v>
+        <v>227.9799957275391</v>
       </c>
       <c r="G8" t="n">
         <v>253491003392</v>
@@ -4097,7 +4088,7 @@
         <v>0.852</v>
       </c>
       <c r="I8" t="n">
-        <v>6.52</v>
+        <v>7.09</v>
       </c>
       <c r="J8" t="n">
         <v>2.145</v>
@@ -4118,25 +4109,25 @@
         <v>0.65596</v>
       </c>
       <c r="Q8" t="n">
-        <v>35.0115</v>
+        <v>32.155148</v>
       </c>
       <c r="R8" t="n">
-        <v>21.812094</v>
+        <v>21.716877</v>
       </c>
       <c r="S8" t="n">
-        <v>119.3254402730297</v>
+        <v>118.8071477588137</v>
       </c>
       <c r="T8" t="n">
-        <v>0.1586213941999561</v>
+        <v>0.1572001527040727</v>
       </c>
       <c r="U8" t="n">
-        <v>0.06663259830376922</v>
+        <v>0.06532419633815723</v>
       </c>
       <c r="V8" t="n">
-        <v>0.1686357529764018</v>
+        <v>0.1672022272068816</v>
       </c>
       <c r="W8" t="n">
-        <v>0.258612336973733</v>
+        <v>0.2570684399859056</v>
       </c>
       <c r="X8" t="n">
         <v>0.03991</v>
@@ -4146,7 +4137,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>2026-08-27T19:49:28.359017+00:00</t>
+          <t>2026-08-28T06:05:50.757405+00:00</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr">
@@ -4177,10 +4168,10 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>57325465600</v>
+        <v>58168139776</v>
       </c>
       <c r="F9" t="n">
-        <v>366.6700134277344</v>
+        <v>372.0599975585938</v>
       </c>
       <c r="G9" t="n">
         <v>4464031232</v>
@@ -4189,7 +4180,7 @@
         <v>1.039</v>
       </c>
       <c r="I9" t="n">
-        <v>7.26</v>
+        <v>7.44</v>
       </c>
       <c r="J9" t="n">
         <v>3.858</v>
@@ -4210,25 +4201,25 @@
         <v>0.33161</v>
       </c>
       <c r="Q9" t="n">
-        <v>50.50551</v>
+        <v>50.008064</v>
       </c>
       <c r="R9" t="n">
-        <v>12.841637</v>
+        <v>13.030406</v>
       </c>
       <c r="S9" t="n">
-        <v>131.0652110993108</v>
+        <v>132.991846454286</v>
       </c>
       <c r="T9" t="n">
-        <v>0.1435210366668731</v>
+        <v>0.1603305929851542</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.04176135038191831</v>
+        <v>-0.02767541227442294</v>
       </c>
       <c r="V9" t="n">
-        <v>0.06997400101609319</v>
+        <v>0.08570242896141655</v>
       </c>
       <c r="W9" t="n">
-        <v>2.142223208458631</v>
+        <v>2.188413123565745</v>
       </c>
       <c r="X9" t="n">
         <v>0.00202</v>
@@ -4238,7 +4229,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>2026-08-27T19:49:33.087777+00:00</t>
+          <t>2026-08-28T06:05:55.266776+00:00</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr">
@@ -4269,7 +4260,7 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>9499112448</v>
+        <v>9497144320</v>
       </c>
       <c r="F10" t="n">
         <v>18.32999992370605</v>
@@ -4281,7 +4272,7 @@
         <v>0.173</v>
       </c>
       <c r="I10" t="n">
-        <v>0.6</v>
+        <v>0.66</v>
       </c>
       <c r="K10" t="n">
         <v>511553632</v>
@@ -4299,13 +4290,13 @@
         <v>0.07274</v>
       </c>
       <c r="Q10" t="n">
-        <v>30.556332</v>
+        <v>27.772726</v>
       </c>
       <c r="R10" t="n">
         <v>5.6789894</v>
       </c>
       <c r="S10" t="n">
-        <v>18.56914281081675</v>
+        <v>18.5652954566453</v>
       </c>
       <c r="T10" t="n">
         <v>0.5036915959540738</v>
@@ -4327,7 +4318,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>2026-08-27T19:49:48.519429+00:00</t>
+          <t>2026-08-28T06:06:07.171430+00:00</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr">
@@ -4358,10 +4349,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>774663110656</v>
+        <v>778151854080</v>
       </c>
       <c r="F11" t="n">
-        <v>474.5328979492188</v>
+        <v>476.6700134277344</v>
       </c>
       <c r="G11" t="n">
         <v>41305001984</v>
@@ -4370,7 +4361,7 @@
         <v>0.501</v>
       </c>
       <c r="I11" t="n">
-        <v>3.94</v>
+        <v>3.91</v>
       </c>
       <c r="J11" t="n">
         <v>1.595</v>
@@ -4391,25 +4382,25 @@
         <v>0.1725</v>
       </c>
       <c r="Q11" t="n">
-        <v>120.43982</v>
+        <v>121.910484</v>
       </c>
       <c r="R11" t="n">
-        <v>18.754705</v>
+        <v>18.839167</v>
       </c>
       <c r="S11" t="n">
-        <v>87.61671000362855</v>
+        <v>88.01129729796716</v>
       </c>
       <c r="T11" t="n">
-        <v>0.04380120330364767</v>
+        <v>0.04850208646204179</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.08407250988909909</v>
+        <v>-0.07994752124284621</v>
       </c>
       <c r="V11" t="n">
-        <v>1.250464272861825</v>
+        <v>1.260599507009267</v>
       </c>
       <c r="W11" t="n">
-        <v>1.839304039283369</v>
+        <v>1.852091183518865</v>
       </c>
       <c r="X11" t="n">
         <v>0.00425</v>
@@ -4419,7 +4410,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>2026-08-27T19:49:29.402353+00:00</t>
+          <t>2026-08-28T06:05:51.819478+00:00</t>
         </is>
       </c>
       <c r="AD11" t="inlineStr">
@@ -4450,10 +4441,10 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4171080400896</v>
+        <v>4166127190016</v>
       </c>
       <c r="F12" t="n">
-        <v>341.0549926757812</v>
+        <v>340.6499938964844</v>
       </c>
       <c r="G12" t="n">
         <v>445865984000</v>
@@ -4462,7 +4453,7 @@
         <v>0.242</v>
       </c>
       <c r="I12" t="n">
-        <v>19.94</v>
+        <v>19.86</v>
       </c>
       <c r="J12" t="n">
         <v>2.94</v>
@@ -4483,25 +4474,25 @@
         <v>0.34033</v>
       </c>
       <c r="Q12" t="n">
-        <v>17.104061</v>
+        <v>17.152567</v>
       </c>
       <c r="R12" t="n">
-        <v>9.355146</v>
+        <v>9.3439</v>
       </c>
       <c r="S12" t="n">
-        <v>184.0317769347229</v>
+        <v>183.8132368654442</v>
       </c>
       <c r="T12" t="n">
-        <v>0.02201013277629671</v>
+        <v>0.02079650780351439</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.1252692810642706</v>
+        <v>-0.1263080134710389</v>
       </c>
       <c r="V12" t="n">
-        <v>0.0913995311812883</v>
+        <v>0.09010350711670623</v>
       </c>
       <c r="W12" t="n">
-        <v>0.648486373612158</v>
+        <v>0.6465288154959068</v>
       </c>
       <c r="X12" t="n">
         <v>0.01596</v>
@@ -4511,7 +4502,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>2026-08-27T19:49:35.457146+00:00</t>
+          <t>2026-08-28T06:05:57.554552+00:00</t>
         </is>
       </c>
       <c r="AD12" t="inlineStr">
@@ -4542,10 +4533,10 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>380033957888</v>
+        <v>382799642624</v>
       </c>
       <c r="F13" t="n">
-        <v>478.8800048828125</v>
+        <v>482.3599853515625</v>
       </c>
       <c r="G13" t="n">
         <v>30837000192</v>
@@ -4554,7 +4545,7 @@
         <v>0.248</v>
       </c>
       <c r="I13" t="n">
-        <v>11.61</v>
+        <v>11.67</v>
       </c>
       <c r="J13" t="n">
         <v>0.428</v>
@@ -4575,25 +4566,25 @@
         <v>0.33736</v>
       </c>
       <c r="Q13" t="n">
-        <v>41.246773</v>
+        <v>41.333332</v>
       </c>
       <c r="R13" t="n">
-        <v>12.32409</v>
+        <v>12.413648</v>
       </c>
       <c r="S13" t="n">
-        <v>123.5732049055438</v>
+        <v>124.4725048746444</v>
       </c>
       <c r="T13" t="n">
-        <v>0.006153899816644826</v>
+        <v>0.01346553505765979</v>
       </c>
       <c r="U13" t="n">
-        <v>0.06607386971755735</v>
+        <v>0.07382093830892544</v>
       </c>
       <c r="V13" t="n">
-        <v>0.2153134416256204</v>
+        <v>0.224145021556174</v>
       </c>
       <c r="W13" t="n">
-        <v>1.92918502003229</v>
+        <v>1.950471159681328</v>
       </c>
       <c r="X13" t="n">
         <v>0.00331</v>
@@ -4603,7 +4594,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>2026-08-27T19:49:30.642446+00:00</t>
+          <t>2026-08-28T06:05:53.007319+00:00</t>
         </is>
       </c>
       <c r="AD13" t="inlineStr">
@@ -4634,10 +4625,10 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>87366541312</v>
+        <v>87230087168</v>
       </c>
       <c r="F14" t="n">
-        <v>243.3099975585938</v>
+        <v>242.9299926757812</v>
       </c>
       <c r="G14" t="n">
         <v>3966725120</v>
@@ -4646,7 +4637,7 @@
         <v>0.356</v>
       </c>
       <c r="I14" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="J14" t="n">
         <v>14.985</v>
@@ -4667,25 +4658,25 @@
         <v>0.00666</v>
       </c>
       <c r="Q14" t="n">
-        <v>486.62</v>
+        <v>458.3585</v>
       </c>
       <c r="R14" t="n">
-        <v>22.024855</v>
+        <v>21.990454</v>
       </c>
       <c r="S14" t="n">
-        <v>83.09445970062181</v>
+        <v>82.96467794207538</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.0301738168721527</v>
+        <v>-0.03168850467276074</v>
       </c>
       <c r="U14" t="n">
-        <v>0.08022550002103479</v>
+        <v>0.07853838905697441</v>
       </c>
       <c r="V14" t="n">
-        <v>1.205293152547642</v>
+        <v>1.201848895532271</v>
       </c>
       <c r="W14" t="n">
-        <v>0.8470356444999727</v>
+        <v>0.8441509189618464</v>
       </c>
       <c r="X14" t="n">
         <v>0.00619</v>
@@ -4695,7 +4686,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>2026-08-27T19:49:44.726171+00:00</t>
+          <t>2026-08-28T06:06:04.952226+00:00</t>
         </is>
       </c>
       <c r="AD14" t="inlineStr">
@@ -4726,10 +4717,10 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1754738327552</v>
+        <v>1767631355904</v>
       </c>
       <c r="F15" t="n">
-        <v>368.8299865722656</v>
+        <v>371.5400085449219</v>
       </c>
       <c r="G15" t="n">
         <v>75464998912</v>
@@ -4738,7 +4729,7 @@
         <v>0.479</v>
       </c>
       <c r="I15" t="n">
-        <v>6.01</v>
+        <v>6.28</v>
       </c>
       <c r="J15" t="n">
         <v>0.854</v>
@@ -4759,25 +4750,25 @@
         <v>0.48988</v>
       </c>
       <c r="Q15" t="n">
-        <v>61.36938</v>
+        <v>59.16242</v>
       </c>
       <c r="R15" t="n">
-        <v>23.252346</v>
+        <v>23.423195</v>
       </c>
       <c r="S15" t="n">
-        <v>64.48339943815232</v>
+        <v>64.95719446737999</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.031713572690938</v>
+        <v>-0.02459897358195728</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.1340106484017545</v>
+        <v>-0.127647689162111</v>
       </c>
       <c r="V15" t="n">
-        <v>0.113985873019399</v>
+        <v>0.1221710160474041</v>
       </c>
       <c r="W15" t="n">
-        <v>0.2374101684350483</v>
+        <v>0.2465023137027968</v>
       </c>
       <c r="X15" t="n">
         <v>0.01948</v>
@@ -4787,7 +4778,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>2026-08-27T19:49:29.957998+00:00</t>
+          <t>2026-08-28T06:05:52.404809+00:00</t>
         </is>
       </c>
       <c r="AD15" t="inlineStr">
@@ -4818,10 +4809,10 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>35806281728</v>
+        <v>35436699648</v>
       </c>
       <c r="F16" t="n">
-        <v>445.1099853515625</v>
+        <v>440.5799865722656</v>
       </c>
       <c r="G16" t="n">
         <v>2602398976</v>
@@ -4830,7 +4821,7 @@
         <v>0.252</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.37</v>
+        <v>-0.4</v>
       </c>
       <c r="K16" t="n">
         <v>517605376</v>
@@ -4848,22 +4839,22 @@
         <v>-0.03607</v>
       </c>
       <c r="R16" t="n">
-        <v>13.756944</v>
+        <v>13.616936</v>
       </c>
       <c r="S16" t="n">
-        <v>69.17679643265529</v>
+        <v>68.46277355511856</v>
       </c>
       <c r="T16" t="n">
-        <v>0.432972739516128</v>
+        <v>0.4183890074624725</v>
       </c>
       <c r="U16" t="n">
-        <v>0.366709639405683</v>
+        <v>0.3528002839611608</v>
       </c>
       <c r="V16" t="n">
-        <v>0.4130924764319304</v>
+        <v>0.3987110709278181</v>
       </c>
       <c r="W16" t="n">
-        <v>0.5052755055009042</v>
+        <v>0.4899559296054348</v>
       </c>
       <c r="X16" t="n">
         <v>0.02641</v>
@@ -4873,7 +4864,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>2026-08-27T19:49:47.360481+00:00</t>
+          <t>2026-08-28T06:06:06.639929+00:00</t>
         </is>
       </c>
       <c r="AD16" t="inlineStr">
@@ -4885,12 +4876,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>NET</t>
+          <t>SNOW</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Cloudflare, Inc.</t>
+          <t>Snowflake Inc.</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -4900,66 +4891,66 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Software - Infrastructure</t>
+          <t>Software - Application</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>110114086912</v>
+        <v>114069520384</v>
       </c>
       <c r="F17" t="n">
-        <v>309.239990234375</v>
+        <v>329.1099853515625</v>
       </c>
       <c r="G17" t="n">
-        <v>2512349952</v>
+        <v>5032822784</v>
       </c>
       <c r="H17" t="n">
-        <v>0.359</v>
+        <v>0.335</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.57</v>
+        <v>-3.69</v>
       </c>
       <c r="K17" t="n">
-        <v>692851968</v>
+        <v>1739497728</v>
       </c>
       <c r="M17" t="n">
-        <v>4162798080</v>
+        <v>2954998016</v>
       </c>
       <c r="N17" t="n">
-        <v>3529349888</v>
+        <v>2772094976</v>
       </c>
       <c r="O17" t="n">
-        <v>0.72577006</v>
+        <v>0.67144996</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.07902000000000001</v>
+        <v>-0.22173999</v>
       </c>
       <c r="R17" t="n">
-        <v>43.847546</v>
+        <v>22.665117</v>
       </c>
       <c r="S17" t="n">
-        <v>158.9287351378354</v>
+        <v>65.57612496289504</v>
       </c>
       <c r="T17" t="n">
-        <v>0.1709200419827575</v>
+        <v>0.2173028672257267</v>
       </c>
       <c r="U17" t="n">
-        <v>0.355661695703585</v>
+        <v>0.3758778827358218</v>
       </c>
       <c r="V17" t="n">
-        <v>0.799999911182836</v>
+        <v>0.9449794473921684</v>
       </c>
       <c r="W17" t="n">
-        <v>0.5067237476013169</v>
+        <v>0.6423473544287228</v>
       </c>
       <c r="X17" t="n">
-        <v>0.00616</v>
+        <v>0.02962</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.90191</v>
+        <v>0.81926</v>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>2026-08-27T19:49:45.832840+00:00</t>
+          <t>2026-08-28T06:06:04.419941+00:00</t>
         </is>
       </c>
       <c r="AD17" t="inlineStr">
@@ -4971,12 +4962,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>SNOW</t>
+          <t>NET</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Snowflake Inc.</t>
+          <t>Cloudflare, Inc.</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -4986,66 +4977,66 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Software - Application</t>
+          <t>Software - Infrastructure</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>114321989632</v>
+        <v>109754449920</v>
       </c>
       <c r="F18" t="n">
-        <v>329.8384094238281</v>
+        <v>308.2300109863281</v>
       </c>
       <c r="G18" t="n">
-        <v>5032822784</v>
+        <v>2512349952</v>
       </c>
       <c r="H18" t="n">
-        <v>0.335</v>
+        <v>0.359</v>
       </c>
       <c r="I18" t="n">
-        <v>-3.53</v>
+        <v>-0.62</v>
       </c>
       <c r="K18" t="n">
-        <v>1739497728</v>
+        <v>692851968</v>
       </c>
       <c r="M18" t="n">
-        <v>2954998016</v>
+        <v>4162798080</v>
       </c>
       <c r="N18" t="n">
-        <v>2772094976</v>
+        <v>3529349888</v>
       </c>
       <c r="O18" t="n">
-        <v>0.67144996</v>
+        <v>0.72577006</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.22173999</v>
+        <v>-0.07902000000000001</v>
       </c>
       <c r="R18" t="n">
-        <v>22.715282</v>
+        <v>43.68597</v>
       </c>
       <c r="S18" t="n">
-        <v>65.72126412803225</v>
+        <v>158.4096675611954</v>
       </c>
       <c r="T18" t="n">
-        <v>0.219997141939932</v>
+        <v>0.1670958116733836</v>
       </c>
       <c r="U18" t="n">
-        <v>0.378923133912908</v>
+        <v>0.3512340982929301</v>
       </c>
       <c r="V18" t="n">
-        <v>0.9492842996075423</v>
+        <v>0.7941211030914146</v>
       </c>
       <c r="W18" t="n">
-        <v>0.6459823864886274</v>
+        <v>0.5018027808257604</v>
       </c>
       <c r="X18" t="n">
-        <v>0.02962</v>
+        <v>0.00616</v>
       </c>
       <c r="Y18" t="n">
-        <v>0.81926</v>
+        <v>0.90191</v>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>2026-08-27T19:49:43.807249+00:00</t>
+          <t>2026-08-28T06:06:05.481159+00:00</t>
         </is>
       </c>
       <c r="AD18" t="inlineStr">
@@ -5057,87 +5048,84 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>AMZN</t>
+          <t>ACMR</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Amazon.com, Inc.</t>
+          <t>ACM Research, Inc.</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Internet Retail</t>
+          <t>Semiconductor Equipment &amp; Materials</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2771758874624</v>
+        <v>5606064128</v>
       </c>
       <c r="F19" t="n">
-        <v>256.9700012207031</v>
+        <v>80.48999786376953</v>
       </c>
       <c r="G19" t="n">
-        <v>775680032768</v>
+        <v>1037772032</v>
       </c>
       <c r="H19" t="n">
-        <v>0.196</v>
+        <v>0.36</v>
       </c>
       <c r="I19" t="n">
-        <v>12.44</v>
+        <v>2.16</v>
       </c>
       <c r="J19" t="n">
-        <v>2.423</v>
+        <v>1.806</v>
       </c>
       <c r="K19" t="n">
-        <v>3219124992</v>
+        <v>-186610256</v>
       </c>
       <c r="M19" t="n">
-        <v>122988003328</v>
+        <v>1439374976</v>
       </c>
       <c r="N19" t="n">
-        <v>251635007488</v>
+        <v>349319008</v>
       </c>
       <c r="O19" t="n">
-        <v>0.5077</v>
+        <v>0.43835</v>
       </c>
       <c r="P19" t="n">
-        <v>0.13689</v>
+        <v>0.16982001</v>
       </c>
       <c r="Q19" t="n">
-        <v>20.656754</v>
+        <v>37.263885</v>
       </c>
       <c r="R19" t="n">
-        <v>3.5733275</v>
-      </c>
-      <c r="S19" t="n">
-        <v>861.0286588784932</v>
+        <v>5.402019</v>
       </c>
       <c r="T19" t="n">
-        <v>0.1130988501313415</v>
+        <v>0.1176062429255689</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.06215328021641198</v>
+        <v>-0.133211314508683</v>
       </c>
       <c r="V19" t="n">
-        <v>0.2199487370171893</v>
+        <v>0.1755512841941056</v>
       </c>
       <c r="W19" t="n">
-        <v>0.1215520543690272</v>
+        <v>1.816305041239907</v>
       </c>
       <c r="X19" t="n">
-        <v>0.0887</v>
+        <v>0.12675999</v>
       </c>
       <c r="Y19" t="n">
-        <v>0.68727</v>
+        <v>0.78055</v>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>2026-08-27T19:49:36.051114+00:00</t>
+          <t>2026-08-28T06:05:54.161675+00:00</t>
         </is>
       </c>
       <c r="AD19" t="inlineStr">
@@ -5149,87 +5137,87 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>VRT</t>
+          <t>AMZN</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Vertiv Holdings Co</t>
+          <t>Amazon.com, Inc.</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Electrical Equipment &amp; Parts</t>
+          <t>Internet Retail</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103550263296</v>
+        <v>2764100599808</v>
       </c>
       <c r="F20" t="n">
-        <v>268.9700012207031</v>
+        <v>256.260009765625</v>
       </c>
       <c r="G20" t="n">
-        <v>11479600128</v>
+        <v>775680032768</v>
       </c>
       <c r="H20" t="n">
-        <v>0.241</v>
+        <v>0.196</v>
       </c>
       <c r="I20" t="n">
-        <v>4.43</v>
+        <v>12.25</v>
       </c>
       <c r="J20" t="n">
-        <v>0.53</v>
+        <v>2.423</v>
       </c>
       <c r="K20" t="n">
-        <v>2696537600</v>
+        <v>3219124992</v>
       </c>
       <c r="M20" t="n">
-        <v>3110599936</v>
+        <v>122988003328</v>
       </c>
       <c r="N20" t="n">
-        <v>3338200064</v>
+        <v>251635007488</v>
       </c>
       <c r="O20" t="n">
-        <v>0.38039002</v>
+        <v>0.5077</v>
       </c>
       <c r="P20" t="n">
-        <v>0.20362</v>
+        <v>0.13689</v>
       </c>
       <c r="Q20" t="n">
-        <v>60.71558</v>
+        <v>20.919184</v>
       </c>
       <c r="R20" t="n">
-        <v>9.020708000000001</v>
+        <v>3.5634546</v>
       </c>
       <c r="S20" t="n">
-        <v>38.40119392216152</v>
+        <v>858.6496661910294</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.002188738474678043</v>
+        <v>0.1100234301659901</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1437202197862839</v>
+        <v>-0.06474448990647808</v>
       </c>
       <c r="V20" t="n">
-        <v>0.02631674862776157</v>
+        <v>0.2165780977410052</v>
       </c>
       <c r="W20" t="n">
-        <v>1.082331587151298</v>
+        <v>0.118453278748353</v>
       </c>
       <c r="X20" t="n">
-        <v>0.00269</v>
+        <v>0.0887</v>
       </c>
       <c r="Y20" t="n">
-        <v>0.84448</v>
+        <v>0.68727</v>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>2026-08-27T19:49:41.694895+00:00</t>
+          <t>2026-08-28T06:05:58.127191+00:00</t>
         </is>
       </c>
       <c r="AD20" t="inlineStr">
@@ -5241,84 +5229,87 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ACMR</t>
+          <t>VRT</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>ACM Research, Inc.</t>
+          <t>Vertiv Holdings Co</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Semiconductor Equipment &amp; Materials</t>
+          <t>Electrical Equipment &amp; Parts</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5550344704</v>
+        <v>103669612544</v>
       </c>
       <c r="F21" t="n">
-        <v>79.69000244140625</v>
+        <v>269.2799987792969</v>
       </c>
       <c r="G21" t="n">
-        <v>1037772032</v>
+        <v>11479600128</v>
       </c>
       <c r="H21" t="n">
-        <v>0.36</v>
+        <v>0.241</v>
       </c>
       <c r="I21" t="n">
-        <v>2.12</v>
+        <v>4.52</v>
       </c>
       <c r="J21" t="n">
-        <v>1.806</v>
+        <v>0.53</v>
       </c>
       <c r="K21" t="n">
-        <v>-186610256</v>
+        <v>2696537600</v>
       </c>
       <c r="M21" t="n">
-        <v>1439374976</v>
+        <v>3110599936</v>
       </c>
       <c r="N21" t="n">
-        <v>349319008</v>
+        <v>3338200064</v>
       </c>
       <c r="O21" t="n">
-        <v>0.43835</v>
+        <v>0.38039002</v>
       </c>
       <c r="P21" t="n">
-        <v>0.16982001</v>
+        <v>0.20362</v>
       </c>
       <c r="Q21" t="n">
-        <v>37.589626</v>
+        <v>59.575222</v>
       </c>
       <c r="R21" t="n">
-        <v>5.3483276</v>
+        <v>9.030768</v>
+      </c>
+      <c r="S21" t="n">
+        <v>38.44545410529414</v>
       </c>
       <c r="T21" t="n">
-        <v>0.1064982804199874</v>
+        <v>-0.001038725262772044</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1418263846907318</v>
+        <v>-0.1427333266750271</v>
       </c>
       <c r="V21" t="n">
-        <v>0.1638674020836814</v>
+        <v>0.02749961543437407</v>
       </c>
       <c r="W21" t="n">
-        <v>1.788313598815175</v>
+        <v>1.084731548876657</v>
       </c>
       <c r="X21" t="n">
-        <v>0.12675999</v>
+        <v>0.00269</v>
       </c>
       <c r="Y21" t="n">
-        <v>0.78055</v>
+        <v>0.84448</v>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>2026-08-27T19:49:31.812168+00:00</t>
+          <t>2026-08-28T06:06:03.372533+00:00</t>
         </is>
       </c>
       <c r="AD21" t="inlineStr">
@@ -5349,10 +5340,10 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>3749232246784</v>
+        <v>3750346096640</v>
       </c>
       <c r="F22" t="n">
-        <v>504.8999938964844</v>
+        <v>505.0599975585938</v>
       </c>
       <c r="G22" t="n">
         <v>331839012864</v>
@@ -5382,25 +5373,25 @@
         <v>0.45111</v>
       </c>
       <c r="Q22" t="n">
-        <v>28.097385</v>
+        <v>28.105732</v>
       </c>
       <c r="R22" t="n">
-        <v>11.298123</v>
+        <v>11.301703</v>
       </c>
       <c r="S22" t="n">
-        <v>226.6013242590304</v>
+        <v>226.6686446691255</v>
       </c>
       <c r="T22" t="n">
-        <v>0.2860060501789574</v>
+        <v>0.2864135876715517</v>
       </c>
       <c r="U22" t="n">
-        <v>0.1846893139132242</v>
+        <v>0.1850647439607176</v>
       </c>
       <c r="V22" t="n">
-        <v>0.2654670431017452</v>
+        <v>0.2658680717482547</v>
       </c>
       <c r="W22" t="n">
-        <v>0.004566724908180886</v>
+        <v>0.004885073802539441</v>
       </c>
       <c r="X22" t="n">
         <v>0.00090000004</v>
@@ -5410,7 +5401,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>2026-08-27T19:49:34.836052+00:00</t>
+          <t>2026-08-28T06:05:57.001313+00:00</t>
         </is>
       </c>
       <c r="AD22" t="inlineStr">
@@ -5441,10 +5432,10 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>663102554112</v>
+        <v>666417364992</v>
       </c>
       <c r="F23" t="n">
-        <v>1726.380004882812</v>
+        <v>1735.010009765625</v>
       </c>
       <c r="G23" t="n">
         <v>35327500288</v>
@@ -5474,25 +5465,25 @@
         <v>0.37057</v>
       </c>
       <c r="Q23" t="n">
-        <v>58.166443</v>
+        <v>58.45721</v>
       </c>
       <c r="R23" t="n">
-        <v>18.770153</v>
+        <v>18.863983</v>
       </c>
       <c r="S23" t="n">
-        <v>78.5883022850837</v>
+        <v>78.98116061120518</v>
       </c>
       <c r="T23" t="n">
-        <v>0.09060934213665739</v>
+        <v>0.0960611916259122</v>
       </c>
       <c r="U23" t="n">
-        <v>0.07650083802239949</v>
+        <v>0.08188216047875851</v>
       </c>
       <c r="V23" t="n">
-        <v>0.1348686493820033</v>
+        <v>0.1405417468216266</v>
       </c>
       <c r="W23" t="n">
-        <v>1.256819326058215</v>
+        <v>1.268100945254697</v>
       </c>
       <c r="X23" t="n">
         <v>0.00016000001</v>
@@ -5502,7 +5493,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>2026-08-27T19:49:38.702680+00:00</t>
+          <t>2026-08-28T06:06:00.568591+00:00</t>
         </is>
       </c>
       <c r="AD23" t="inlineStr">
@@ -5533,10 +5524,10 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>315343863808</v>
+        <v>312022761472</v>
       </c>
       <c r="F24" t="n">
-        <v>387.0700073242188</v>
+        <v>382.8500061035156</v>
       </c>
       <c r="G24" t="n">
         <v>10606499840</v>
@@ -5545,7 +5536,7 @@
         <v>0.311</v>
       </c>
       <c r="I24" t="n">
-        <v>1.15</v>
+        <v>1.3</v>
       </c>
       <c r="K24" t="n">
         <v>3579375104</v>
@@ -5563,25 +5554,25 @@
         <v>-0.02465</v>
       </c>
       <c r="Q24" t="n">
-        <v>336.4565</v>
+        <v>294.50003</v>
       </c>
       <c r="R24" t="n">
-        <v>29.742334</v>
+        <v>29.41807</v>
       </c>
       <c r="S24" t="n">
-        <v>88.10025623064735</v>
+        <v>87.17241205687282</v>
       </c>
       <c r="T24" t="n">
-        <v>0.2133856028972374</v>
+        <v>0.20015675894519</v>
       </c>
       <c r="U24" t="n">
-        <v>0.5016100547829443</v>
+        <v>0.4852388657362654</v>
       </c>
       <c r="V24" t="n">
-        <v>1.67239724600131</v>
+        <v>1.643261638935576</v>
       </c>
       <c r="W24" t="n">
-        <v>1.063162976733458</v>
+        <v>1.040669499802728</v>
       </c>
       <c r="X24" t="n">
         <v>0.0076</v>
@@ -5591,7 +5582,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>2026-08-27T19:49:34.194101+00:00</t>
+          <t>2026-08-28T06:05:56.402224+00:00</t>
         </is>
       </c>
       <c r="AD24" t="inlineStr">
@@ -5622,10 +5613,10 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>24784939008</v>
+        <v>24878735360</v>
       </c>
       <c r="F25" t="n">
-        <v>38.31499862670898</v>
+        <v>38.45999908447266</v>
       </c>
       <c r="G25" t="n">
         <v>39063072768</v>
@@ -5634,7 +5625,7 @@
         <v>0.9320000000000001</v>
       </c>
       <c r="I25" t="n">
-        <v>3.26</v>
+        <v>3.35</v>
       </c>
       <c r="J25" t="n">
         <v>4.094</v>
@@ -5655,22 +5646,22 @@
         <v>0.13382</v>
       </c>
       <c r="Q25" t="n">
-        <v>11.753067</v>
+        <v>11.4805975</v>
       </c>
       <c r="R25" t="n">
-        <v>0.6344851</v>
+        <v>0.6368863</v>
       </c>
       <c r="T25" t="n">
-        <v>0.3467485975121738</v>
+        <v>0.3518452742740443</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.07227604516934161</v>
+        <v>-0.06876513813684082</v>
       </c>
       <c r="V25" t="n">
-        <v>0.1403273918663839</v>
+        <v>0.1446428818767584</v>
       </c>
       <c r="W25" t="n">
-        <v>-0.1439901683759369</v>
+        <v>-0.1407506584742148</v>
       </c>
       <c r="X25" t="n">
         <v>0.12878999</v>
@@ -5680,7 +5671,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>2026-08-27T19:49:42.267947+00:00</t>
+          <t>2026-08-28T06:06:03.894138+00:00</t>
         </is>
       </c>
       <c r="AD25" t="inlineStr">
@@ -5711,10 +5702,10 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>232733327360</v>
+        <v>233416196096</v>
       </c>
       <c r="F26" t="n">
-        <v>228.5599975585938</v>
+        <v>227.9600067138672</v>
       </c>
       <c r="G26" t="n">
         <v>5094199808</v>
@@ -5723,7 +5714,7 @@
         <v>0.256</v>
       </c>
       <c r="I26" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="K26" t="n">
         <v>1926365056</v>
@@ -5741,25 +5732,25 @@
         <v>-0.022079999</v>
       </c>
       <c r="Q26" t="n">
-        <v>3809.3335</v>
+        <v>3256.5715</v>
       </c>
       <c r="R26" t="n">
-        <v>45.685944</v>
+        <v>45.819992</v>
       </c>
       <c r="S26" t="n">
-        <v>120.8147576364674</v>
+        <v>121.1692432693297</v>
       </c>
       <c r="T26" t="n">
-        <v>0.2572056860390894</v>
+        <v>0.2539054064205257</v>
       </c>
       <c r="U26" t="n">
-        <v>0.3625037112285767</v>
+        <v>0.3589270146877328</v>
       </c>
       <c r="V26" t="n">
-        <v>1.516418475621301</v>
+        <v>1.509812647554268</v>
       </c>
       <c r="W26" t="n">
-        <v>1.163318477848633</v>
+        <v>1.157639569488458</v>
       </c>
       <c r="X26" t="n">
         <v>0.01467</v>
@@ -5769,7 +5760,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>2026-08-27T19:49:33.591437+00:00</t>
+          <t>2026-08-28T06:05:55.802307+00:00</t>
         </is>
       </c>
       <c r="AD26" t="inlineStr">
@@ -5800,10 +5791,10 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>269648281600</v>
+        <v>272563929088</v>
       </c>
       <c r="F27" t="n">
-        <v>252.4799957275391</v>
+        <v>255.2100067138672</v>
       </c>
       <c r="G27" t="n">
         <v>5155999744</v>
@@ -5812,7 +5803,7 @@
         <v>0.224</v>
       </c>
       <c r="I27" t="n">
-        <v>0.98</v>
+        <v>1</v>
       </c>
       <c r="J27" t="n">
         <v>1.083</v>
@@ -5833,25 +5824,25 @@
         <v>0.07603</v>
       </c>
       <c r="Q27" t="n">
-        <v>257.63263</v>
+        <v>255.21</v>
       </c>
       <c r="R27" t="n">
-        <v>52.297962</v>
+        <v>52.86345</v>
       </c>
       <c r="S27" t="n">
-        <v>202.0594140621216</v>
+        <v>204.2442380096033</v>
       </c>
       <c r="T27" t="n">
-        <v>0.03162535777008957</v>
+        <v>0.04278009718764819</v>
       </c>
       <c r="U27" t="n">
-        <v>-0.2469352939393473</v>
+        <v>-0.2387925699384323</v>
       </c>
       <c r="V27" t="n">
-        <v>0.9165020889621882</v>
+        <v>0.9372248069862874</v>
       </c>
       <c r="W27" t="n">
-        <v>0.7949665089874547</v>
+        <v>0.8143750893603523</v>
       </c>
       <c r="X27" t="n">
         <v>0.0007</v>
@@ -5861,7 +5852,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>2026-08-27T19:49:39.223496+00:00</t>
+          <t>2026-08-28T06:06:01.107925+00:00</t>
         </is>
       </c>
       <c r="AD27" t="inlineStr">
@@ -5892,10 +5883,10 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>217064128512</v>
+        <v>216992235520</v>
       </c>
       <c r="F28" t="n">
-        <v>241.5500030517578</v>
+        <v>241.4499969482422</v>
       </c>
       <c r="G28" t="n">
         <v>8717100032</v>
@@ -5925,25 +5916,25 @@
         <v>0.14479999</v>
       </c>
       <c r="Q28" t="n">
-        <v>82.71575</v>
+        <v>82.688354</v>
       </c>
       <c r="R28" t="n">
-        <v>24.900957</v>
+        <v>24.89271</v>
       </c>
       <c r="S28" t="n">
-        <v>95.63559912366502</v>
+        <v>95.60392401728127</v>
       </c>
       <c r="T28" t="n">
-        <v>0.3844787147459181</v>
+        <v>0.3839055153258693</v>
       </c>
       <c r="U28" t="n">
-        <v>0.1795615609278631</v>
+        <v>0.1790732009441129</v>
       </c>
       <c r="V28" t="n">
-        <v>1.987278297226078</v>
+        <v>1.986041509567837</v>
       </c>
       <c r="W28" t="n">
-        <v>2.236591207574131</v>
+        <v>2.235250869093278</v>
       </c>
       <c r="X28" t="n">
         <v>0.00494</v>
@@ -5953,7 +5944,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>2026-08-27T19:49:39.791700+00:00</t>
+          <t>2026-08-28T06:06:01.698064+00:00</t>
         </is>
       </c>
       <c r="AD28" t="inlineStr">
@@ -5984,10 +5975,10 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1450448125952</v>
+        <v>1454880718848</v>
       </c>
       <c r="F29" t="n">
-        <v>569.3599853515625</v>
+        <v>571.0999755859375</v>
       </c>
       <c r="G29" t="n">
         <v>228246994944</v>
@@ -5996,7 +5987,7 @@
         <v>0.28</v>
       </c>
       <c r="I29" t="n">
-        <v>26.56</v>
+        <v>26.33</v>
       </c>
       <c r="J29" t="n">
         <v>-0.134</v>
@@ -6017,25 +6008,25 @@
         <v>0.34827</v>
       </c>
       <c r="Q29" t="n">
-        <v>21.436747</v>
+        <v>21.690086</v>
       </c>
       <c r="R29" t="n">
-        <v>6.3547306</v>
+        <v>6.3741508</v>
       </c>
       <c r="S29" t="n">
-        <v>67.29485736297502</v>
+        <v>67.50051153381183</v>
       </c>
       <c r="T29" t="n">
-        <v>-0.04052845230343161</v>
+        <v>-0.03759626323833276</v>
       </c>
       <c r="U29" t="n">
-        <v>-0.1029487295499845</v>
+        <v>-0.1002072997156541</v>
       </c>
       <c r="V29" t="n">
-        <v>-0.1274524980715064</v>
+        <v>-0.1247859528778774</v>
       </c>
       <c r="W29" t="n">
-        <v>-0.2356952912690724</v>
+        <v>-0.233359541017046</v>
       </c>
       <c r="X29" t="n">
         <v>0.00148</v>
@@ -6045,7 +6036,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>2026-08-27T19:49:36.630470+00:00</t>
+          <t>2026-08-28T06:05:58.759724+00:00</t>
         </is>
       </c>
       <c r="AD29" t="inlineStr">
@@ -6076,10 +6067,10 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>143220899840</v>
+        <v>143117516800</v>
       </c>
       <c r="F30" t="n">
-        <v>138.5299987792969</v>
+        <v>138.4299926757812</v>
       </c>
       <c r="G30" t="n">
         <v>14732000256</v>
@@ -6088,7 +6079,7 @@
         <v>0.24</v>
       </c>
       <c r="I30" t="n">
-        <v>1.6</v>
+        <v>1.76</v>
       </c>
       <c r="J30" t="n">
         <v>-0.219</v>
@@ -6109,25 +6100,25 @@
         <v>0.04063</v>
       </c>
       <c r="Q30" t="n">
-        <v>86.581245</v>
+        <v>78.65340399999999</v>
       </c>
       <c r="R30" t="n">
-        <v>9.721755</v>
+        <v>9.714738000000001</v>
       </c>
       <c r="S30" t="n">
-        <v>27.81325898920126</v>
+        <v>27.7931821759022</v>
       </c>
       <c r="T30" t="n">
-        <v>0.2523051468065274</v>
+        <v>0.2514010959926369</v>
       </c>
       <c r="U30" t="n">
-        <v>0.2740733422451693</v>
+        <v>0.2731535767671225</v>
       </c>
       <c r="V30" t="n">
-        <v>0.3290798648917206</v>
+        <v>0.3281203896898139</v>
       </c>
       <c r="W30" t="n">
-        <v>-0.219971146834705</v>
+        <v>-0.2205342569691323</v>
       </c>
       <c r="X30" t="n">
         <v>0.00176</v>
@@ -6137,7 +6128,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>2026-08-27T19:49:46.482409+00:00</t>
+          <t>2026-08-28T06:06:06.024445+00:00</t>
         </is>
       </c>
       <c r="AD30" t="inlineStr">
@@ -6168,10 +6159,10 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>435456671744</v>
+        <v>437658779648</v>
       </c>
       <c r="F31" t="n">
-        <v>151.1755065917969</v>
+        <v>151.9400024414062</v>
       </c>
       <c r="G31" t="n">
         <v>67356999680</v>
@@ -6180,7 +6171,7 @@
         <v>0.206</v>
       </c>
       <c r="I31" t="n">
-        <v>5.84</v>
+        <v>5.96</v>
       </c>
       <c r="J31" t="n">
         <v>0.219</v>
@@ -6201,22 +6192,22 @@
         <v>0.36202</v>
       </c>
       <c r="Q31" t="n">
-        <v>25.886217</v>
+        <v>25.493288</v>
       </c>
       <c r="R31" t="n">
-        <v>6.464906</v>
+        <v>6.497599</v>
       </c>
       <c r="T31" t="n">
-        <v>0.2602159698696154</v>
+        <v>0.2665888929726827</v>
       </c>
       <c r="U31" t="n">
-        <v>-0.2552702876505039</v>
+        <v>-0.2515041830280843</v>
       </c>
       <c r="V31" t="n">
-        <v>0.0293547954415323</v>
+        <v>0.03456025158076947</v>
       </c>
       <c r="W31" t="n">
-        <v>-0.351602750517363</v>
+        <v>-0.3483237999961911</v>
       </c>
       <c r="X31" t="n">
         <v>0.40498</v>
@@ -6226,7 +6217,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>2026-08-27T19:49:37.264589+00:00</t>
+          <t>2026-08-28T06:05:59.335968+00:00</t>
         </is>
       </c>
       <c r="AD31" t="inlineStr">
@@ -6254,7 +6245,7 @@
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
@@ -6311,22 +6302,27 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>MU</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>100</v>
+        <v>84.2</v>
       </c>
       <c r="C2" t="n">
-        <v>100</v>
+        <v>88.2</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MODERATE</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>price_to_sales, price_to_fcf</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -6340,11 +6336,11 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>MU</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="C3" t="n">
         <v>100</v>
@@ -6355,7 +6351,7 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -6756,7 +6752,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>NET</t>
+          <t>SNOW</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -6790,7 +6786,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>SNOW</t>
+          <t>NET</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -6824,18 +6820,23 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>AMZN</t>
+          <t>ACMR</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>100</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="C19" t="n">
-        <v>100</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
           <t>HIGH</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>price_to_fcf</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -6853,7 +6854,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>VRT</t>
+          <t>AMZN</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -6882,23 +6883,18 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ACMR</t>
+          <t>VRT</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>94.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="C21" t="n">
-        <v>94.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
           <t>HIGH</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>price_to_fcf</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -7292,11 +7288,11 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>MU</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>55.6</v>
+        <v>56.77</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -7309,7 +7305,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>100</v>
+        <v>84.2</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>

--- a/reports/investment_dashboard.xlsx
+++ b/reports/investment_dashboard.xlsx
@@ -525,16 +525,16 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>MU</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Micron Technology, Inc.</t>
+          <t>Taiwan Semiconductor Manufacturing Company Limited</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>56.77</v>
+        <v>55.79</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>935.3900146484375</v>
+        <v>417.5199890136719</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -550,24 +550,19 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>84.2</v>
+        <v>100</v>
       </c>
       <c r="I2" t="n">
-        <v>88.2</v>
+        <v>100</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Revenue Growth; Earnings Fcf; Balance Sheet</t>
+          <t>Revenue Growth; Earnings Fcf; Balance Sheet; Valuation</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
           <t>Industry Growth; Competitive Advantage; Catalysts; Inflation Resilience</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>High market sensitivity / beta</t>
         </is>
       </c>
     </row>
@@ -577,16 +572,16 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>MU</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Taiwan Semiconductor Manufacturing Company Limited</t>
+          <t>Micron Technology, Inc.</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>55.69</v>
+        <v>54.85</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -594,7 +589,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>427.2999877929688</v>
+        <v>932.8599853515625</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -602,19 +597,24 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="I3" t="n">
         <v>100</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Revenue Growth; Earnings Fcf; Balance Sheet; Valuation</t>
+          <t>Revenue Growth; Earnings Fcf; Balance Sheet</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
           <t>Industry Growth; Competitive Advantage; Catalysts; Inflation Resilience</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>High market sensitivity / beta</t>
         </is>
       </c>
     </row>
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>53.63</v>
+        <v>53.57</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>240.2400054931641</v>
+        <v>232.75</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -685,7 +685,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>52.96</v>
+        <v>52.9</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -693,7 +693,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>201.0899963378906</v>
+        <v>195.3800048828125</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -737,7 +737,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>52.38</v>
+        <v>51.78</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -745,7 +745,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>185.9299926757812</v>
+        <v>186.2899932861328</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -760,7 +760,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Revenue Growth; Earnings Fcf; Balance Sheet; Momentum</t>
+          <t>Revenue Growth; Earnings Fcf; Balance Sheet</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -780,16 +780,16 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>DELL</t>
+          <t>TER</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Dell Technologies Inc.</t>
+          <t>Teradyne, Inc.</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>51.23</v>
+        <v>50.85</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>472.260009765625</v>
+        <v>354.9700012207031</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -812,12 +812,12 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Revenue Growth; Momentum</t>
+          <t>Revenue Growth; Earnings Fcf; Balance Sheet</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Industry Growth; Competitive Advantage; Catalysts; Inflation Resilience</t>
+          <t>Industry Growth; Valuation; Competitive Advantage; Catalysts; Inflation Resilience</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>51.22</v>
+        <v>50.72</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -844,11 +844,11 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>227.9799957275391</v>
+        <v>217.5500030517578</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="H8" t="n">
@@ -869,7 +869,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Excessive price-to-sales valuation; High market sensitivity / beta</t>
+          <t>High market sensitivity / beta</t>
         </is>
       </c>
     </row>
@@ -879,24 +879,24 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>TER</t>
+          <t>DELL</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Teradyne, Inc.</t>
+          <t>Dell Technologies Inc.</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>51.07</v>
+        <v>49.99</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RESEARCH</t>
+          <t>REJECT</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>372.0599975585938</v>
+        <v>456.239990234375</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -911,12 +911,12 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Revenue Growth; Earnings Fcf; Balance Sheet</t>
+          <t>Revenue Growth</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Industry Growth; Valuation; Competitive Advantage; Catalysts; Inflation Resilience</t>
+          <t>Industry Growth; Competitive Advantage; Catalysts; Inflation Resilience</t>
         </is>
       </c>
     </row>
@@ -926,16 +926,16 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>PATH</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>UiPath, Inc.</t>
+          <t>Advanced Micro Devices, Inc.</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>47.8</v>
+        <v>47.76</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -943,27 +943,32 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>18.32999992370605</v>
+        <v>465.5799865722656</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>94.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="I10" t="n">
-        <v>94.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Balance Sheet; Momentum</t>
+          <t>Revenue Growth; Earnings Fcf; Balance Sheet</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Industry Growth; Competitive Advantage; Catalysts; Inflation Resilience</t>
+          <t>Industry Growth; Valuation; Competitive Advantage; Catalysts; Inflation Resilience</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>Very high earnings multiple; High market sensitivity / beta</t>
         </is>
       </c>
     </row>
@@ -973,16 +978,16 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>PATH</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Advanced Micro Devices, Inc.</t>
+          <t>UiPath, Inc.</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>47.65</v>
+        <v>47.68</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -990,32 +995,27 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>476.6700134277344</v>
+        <v>18.14999961853027</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>100</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>100</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Revenue Growth; Earnings Fcf; Balance Sheet</t>
+          <t>Balance Sheet; Momentum</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Industry Growth; Valuation; Competitive Advantage; Catalysts; Inflation Resilience</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>Very high earnings multiple; High market sensitivity / beta</t>
+          <t>Industry Growth; Competitive Advantage; Catalysts; Inflation Resilience</t>
         </is>
       </c>
     </row>
@@ -1025,16 +1025,16 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>MRVL</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Alphabet Inc.</t>
+          <t>Marvell Technology, Inc.</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>46.74</v>
+        <v>47.51</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -1042,7 +1042,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>340.6499938964844</v>
+        <v>216.6199951171875</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -1057,12 +1057,17 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Earnings Fcf; Balance Sheet</t>
+          <t>Revenue Growth; Earnings Fcf; Momentum</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Industry Growth; Competitive Advantage; Catalysts; Inflation Resilience</t>
+          <t>Industry Growth; Valuation; Competitive Advantage; Catalysts; Inflation Resilience</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>Excessive price-to-sales valuation</t>
         </is>
       </c>
     </row>
@@ -1072,16 +1077,16 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>AMAT</t>
+          <t>GOOGL</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Applied Materials, Inc.</t>
+          <t>Alphabet Inc.</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>45.54</v>
+        <v>47.05</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -1089,7 +1094,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>482.3599853515625</v>
+        <v>346.5899963378906</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -1104,12 +1109,12 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Earnings Fcf</t>
+          <t>Earnings Fcf; Balance Sheet</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Industry Growth; Valuation; Competitive Advantage; Catalysts; Inflation Resilience</t>
+          <t>Industry Growth; Competitive Advantage; Catalysts; Inflation Resilience</t>
         </is>
       </c>
     </row>
@@ -1119,16 +1124,16 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>DDOG</t>
+          <t>AMAT</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Datadog, Inc.</t>
+          <t>Applied Materials, Inc.</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>45.15</v>
+        <v>45.81</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -1136,32 +1141,27 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>242.9299926757812</v>
+        <v>461.6700134277344</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="I14" t="n">
         <v>100</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Revenue Growth; Balance Sheet</t>
+          <t>Earnings Fcf</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
           <t>Industry Growth; Valuation; Competitive Advantage; Catalysts; Inflation Resilience</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>Excessive price-to-sales valuation; Very high earnings multiple</t>
         </is>
       </c>
     </row>
@@ -1180,7 +1180,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>44.42</v>
+        <v>44.36</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>371.5400085449219</v>
+        <v>368.7900085449219</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -1223,16 +1223,16 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>MDB</t>
+          <t>DDOG</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>MongoDB, Inc.</t>
+          <t>Datadog, Inc.</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>43.8</v>
+        <v>44.29</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -1240,27 +1240,32 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>440.5799865722656</v>
+        <v>236.9799957275391</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>88.2</v>
+        <v>96</v>
       </c>
       <c r="I16" t="n">
-        <v>88.2</v>
+        <v>100</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Balance Sheet; Momentum</t>
+          <t>Revenue Growth; Balance Sheet</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
           <t>Industry Growth; Valuation; Competitive Advantage; Catalysts; Inflation Resilience</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>Excessive price-to-sales valuation; Very high earnings multiple</t>
         </is>
       </c>
     </row>
@@ -1270,16 +1275,16 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>SNOW</t>
+          <t>ACMR</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Snowflake Inc.</t>
+          <t>ACM Research, Inc.</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>43.13</v>
+        <v>43.55</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -1287,7 +1292,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>329.1099853515625</v>
+        <v>74.41999816894531</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1295,24 +1300,24 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>88.2</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="I17" t="n">
-        <v>88.2</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Revenue Growth; Momentum</t>
+          <t>Revenue Growth</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Industry Growth; Valuation; Competitive Advantage; Catalysts; Inflation Resilience</t>
+          <t>Industry Growth; Competitive Advantage; Catalysts; Inflation Resilience</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>Excessive price-to-sales valuation</t>
+          <t>Negative free cash flow / unprofitable growth</t>
         </is>
       </c>
     </row>
@@ -1322,16 +1327,16 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>NET</t>
+          <t>AMZN</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Cloudflare, Inc.</t>
+          <t>Amazon.com, Inc.</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>43.12</v>
+        <v>43.49</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -1339,7 +1344,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>308.2300109863281</v>
+        <v>266.4299926757812</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1347,24 +1352,19 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>88.2</v>
+        <v>100</v>
       </c>
       <c r="I18" t="n">
-        <v>88.2</v>
+        <v>100</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Revenue Growth; Momentum</t>
+          <t>Earnings Fcf</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Industry Growth; Valuation; Competitive Advantage; Catalysts; Inflation Resilience</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>Excessive price-to-sales valuation</t>
+          <t>Industry Growth; Competitive Advantage; Catalysts; Inflation Resilience</t>
         </is>
       </c>
     </row>
@@ -1374,16 +1374,16 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>ACMR</t>
+          <t>MDB</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>ACM Research, Inc.</t>
+          <t>MongoDB, Inc.</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>42.61</v>
+        <v>43.26</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -1391,7 +1391,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>80.48999786376953</v>
+        <v>446.6199951171875</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1399,24 +1399,19 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>94.09999999999999</v>
+        <v>88.2</v>
       </c>
       <c r="I19" t="n">
-        <v>94.09999999999999</v>
+        <v>88.2</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Revenue Growth</t>
+          <t>Balance Sheet; Momentum</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Industry Growth; Competitive Advantage; Catalysts; Inflation Resilience</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>Negative free cash flow / unprofitable growth</t>
+          <t>Industry Growth; Valuation; Competitive Advantage; Catalysts; Inflation Resilience</t>
         </is>
       </c>
     </row>
@@ -1426,16 +1421,16 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>AMZN</t>
+          <t>VRT</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Amazon.com, Inc.</t>
+          <t>Vertiv Holdings Co</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>42.59</v>
+        <v>43.25</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -1443,7 +1438,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>256.260009765625</v>
+        <v>257.0799865722656</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1463,7 +1458,12 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Industry Growth; Competitive Advantage; Catalysts; Inflation Resilience</t>
+          <t>Industry Growth; Valuation; Competitive Advantage; Catalysts; Inflation Resilience</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>High market sensitivity / beta</t>
         </is>
       </c>
     </row>
@@ -1473,16 +1473,16 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>VRT</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Vertiv Holdings Co</t>
+          <t>Microsoft Corporation</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>42.49</v>
+        <v>42.42</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -1490,7 +1490,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>269.2799987792969</v>
+        <v>513.530029296875</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1511,11 +1511,6 @@
       <c r="K21" t="inlineStr">
         <is>
           <t>Industry Growth; Valuation; Competitive Advantage; Catalysts; Inflation Resilience</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>High market sensitivity / beta</t>
         </is>
       </c>
     </row>
@@ -1525,16 +1520,16 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>ASML</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Microsoft Corporation</t>
+          <t>ASML Holding N.V.</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>42.42</v>
+        <v>42.38</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -1542,7 +1537,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>505.0599975585938</v>
+        <v>1696.160034179688</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1557,7 +1552,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Earnings Fcf</t>
+          <t>Earnings Fcf; Balance Sheet</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1572,16 +1567,16 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>ASML</t>
+          <t>NET</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>ASML Holding N.V.</t>
+          <t>Cloudflare, Inc.</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>42.41</v>
+        <v>42.36</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -1589,7 +1584,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1735.010009765625</v>
+        <v>299.8399963378906</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1597,19 +1592,24 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>100</v>
+        <v>88.2</v>
       </c>
       <c r="I23" t="n">
-        <v>100</v>
+        <v>88.2</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Earnings Fcf; Balance Sheet</t>
+          <t>Revenue Growth</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
           <t>Industry Growth; Valuation; Competitive Advantage; Catalysts; Inflation Resilience</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>Excessive price-to-sales valuation</t>
         </is>
       </c>
     </row>
@@ -1619,16 +1619,16 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>PANW</t>
+          <t>SNOW</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Palo Alto Networks, Inc.</t>
+          <t>Snowflake Inc.</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>42.2</v>
+        <v>42.27</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -1636,18 +1636,18 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>382.8500061035156</v>
+        <v>328</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>94.09999999999999</v>
+        <v>88.2</v>
       </c>
       <c r="I24" t="n">
-        <v>94.09999999999999</v>
+        <v>88.2</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
@@ -1661,7 +1661,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>Excessive price-to-sales valuation; Very high earnings multiple</t>
+          <t>Excessive price-to-sales valuation</t>
         </is>
       </c>
     </row>
@@ -1671,16 +1671,16 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>SMCI</t>
+          <t>PANW</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Super Micro Computer, Inc.</t>
+          <t>Palo Alto Networks, Inc.</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>41.91</v>
+        <v>41.77</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -1688,11 +1688,11 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>38.45999908447266</v>
+        <v>371.5899963378906</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="H25" t="n">
@@ -1703,17 +1703,17 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Revenue Growth; Valuation</t>
+          <t>Revenue Growth; Momentum</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>Industry Growth; Balance Sheet; Competitive Advantage; Catalysts; Inflation Resilience</t>
+          <t>Industry Growth; Valuation; Competitive Advantage; Catalysts; Inflation Resilience</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>Negative free cash flow / unprofitable growth</t>
+          <t>Excessive price-to-sales valuation; Very high earnings multiple</t>
         </is>
       </c>
     </row>
@@ -1723,16 +1723,16 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>CRWD</t>
+          <t>SMCI</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>CrowdStrike Holdings, Inc.</t>
+          <t>Super Micro Computer, Inc.</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>41.12</v>
+        <v>41.75</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -1740,11 +1740,11 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>227.9600067138672</v>
+        <v>37.08000183105469</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="H26" t="n">
@@ -1755,17 +1755,17 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Balance Sheet; Momentum</t>
+          <t>Revenue Growth; Valuation</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>Industry Growth; Valuation; Competitive Advantage; Catalysts; Inflation Resilience</t>
+          <t>Industry Growth; Balance Sheet; Competitive Advantage; Momentum; Catalysts; Inflation Resilience</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>Excessive price-to-sales valuation; Very high earnings multiple</t>
+          <t>Negative free cash flow / unprofitable growth</t>
         </is>
       </c>
     </row>
@@ -1784,7 +1784,7 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>40.79</v>
+        <v>40.9</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -1792,7 +1792,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>255.2100067138672</v>
+        <v>239.0500030517578</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1827,16 +1827,16 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>MRVL</t>
+          <t>CRWD</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Marvell Technology, Inc.</t>
+          <t>CrowdStrike Holdings, Inc.</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>39.75</v>
+        <v>40.37</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>241.4499969482422</v>
+        <v>218.3999938964844</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1852,14 +1852,14 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>100</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="I28" t="n">
-        <v>100</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Revenue Growth; Momentum</t>
+          <t>Balance Sheet; Momentum</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -1869,7 +1869,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>Excessive price-to-sales valuation; High market sensitivity / beta</t>
+          <t>Excessive price-to-sales valuation; Very high earnings multiple</t>
         </is>
       </c>
     </row>
@@ -1888,7 +1888,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>39.57</v>
+        <v>39.74</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -1896,7 +1896,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>571.0999755859375</v>
+        <v>578.02001953125</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>36.47</v>
+        <v>35.73</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -1943,7 +1943,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>138.4299926757812</v>
+        <v>144.7100067138672</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1977,7 +1977,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>31.59</v>
+        <v>31.54</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -1985,7 +1985,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>151.9400024414062</v>
+        <v>150.8500061035156</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -2115,7 +2115,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>MU</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -2128,19 +2128,19 @@
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>9.02</v>
+        <v>8.84</v>
       </c>
       <c r="F2" t="n">
-        <v>7.19</v>
+        <v>8.68</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>7.06</v>
+        <v>5.58</v>
       </c>
       <c r="I2" t="n">
-        <v>3.5</v>
+        <v>2.69</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -2149,13 +2149,13 @@
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>56.77</v>
+        <v>55.79</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>MU</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -2168,19 +2168,19 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>8.84</v>
+        <v>9.02</v>
       </c>
       <c r="F3" t="n">
-        <v>8.68</v>
+        <v>4.95</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>5.48</v>
+        <v>7.38</v>
       </c>
       <c r="I3" t="n">
-        <v>2.69</v>
+        <v>3.5</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -2189,7 +2189,7 @@
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>55.69</v>
+        <v>54.85</v>
       </c>
     </row>
     <row r="4">
@@ -2211,13 +2211,13 @@
         <v>9.91</v>
       </c>
       <c r="F4" t="n">
-        <v>2.32</v>
+        <v>2.4</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>7.86</v>
+        <v>7.72</v>
       </c>
       <c r="I4" t="n">
         <v>3.54</v>
@@ -2229,7 +2229,7 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>53.63</v>
+        <v>53.57</v>
       </c>
     </row>
     <row r="5">
@@ -2251,13 +2251,13 @@
         <v>10</v>
       </c>
       <c r="F5" t="n">
-        <v>0.78</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>8.550000000000001</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="I5" t="n">
         <v>3.63</v>
@@ -2269,7 +2269,7 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>52.96</v>
+        <v>52.9</v>
       </c>
     </row>
     <row r="6">
@@ -2297,7 +2297,7 @@
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>8.5</v>
+        <v>7.9</v>
       </c>
       <c r="I6" t="n">
         <v>3.35</v>
@@ -2309,38 +2309,38 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>52.38</v>
+        <v>51.78</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>DELL</t>
+          <t>TER</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>15</v>
       </c>
       <c r="C7" t="n">
-        <v>11.48</v>
+        <v>15</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>6.33</v>
+        <v>8.9</v>
       </c>
       <c r="F7" t="n">
-        <v>5.77</v>
+        <v>3.08</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>9.109999999999999</v>
+        <v>5.12</v>
       </c>
       <c r="I7" t="n">
-        <v>3.54</v>
+        <v>3.75</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -2349,7 +2349,7 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>51.23</v>
+        <v>50.85</v>
       </c>
     </row>
     <row r="8">
@@ -2368,16 +2368,16 @@
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>9.029999999999999</v>
+        <v>8.08</v>
       </c>
       <c r="F8" t="n">
-        <v>3.08</v>
+        <v>3.91</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>5.67</v>
+        <v>5.29</v>
       </c>
       <c r="I8" t="n">
         <v>3.44</v>
@@ -2389,38 +2389,38 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>51.22</v>
+        <v>50.72</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>TER</t>
+          <t>DELL</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>15</v>
       </c>
       <c r="C9" t="n">
-        <v>15</v>
+        <v>11.48</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>8.9</v>
+        <v>6.33</v>
       </c>
       <c r="F9" t="n">
-        <v>2.88</v>
+        <v>5.82</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>5.54</v>
+        <v>7.82</v>
       </c>
       <c r="I9" t="n">
-        <v>3.75</v>
+        <v>3.54</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -2429,38 +2429,38 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>51.07</v>
+        <v>49.99</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>PATH</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>8.359999999999999</v>
+        <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>9.32</v>
+        <v>12.88</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>9.699999999999999</v>
+        <v>8.77</v>
       </c>
       <c r="F10" t="n">
-        <v>6.67</v>
+        <v>1.36</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>10</v>
+        <v>6.3</v>
       </c>
       <c r="I10" t="n">
-        <v>3.75</v>
+        <v>3.45</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -2469,38 +2469,38 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>47.8</v>
+        <v>47.76</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>PATH</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>15</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="C11" t="n">
-        <v>12.88</v>
+        <v>9.32</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>8.77</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="F11" t="n">
-        <v>1.33</v>
+        <v>6.55</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>6.22</v>
+        <v>10</v>
       </c>
       <c r="I11" t="n">
-        <v>3.45</v>
+        <v>3.75</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -2509,35 +2509,35 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>47.65</v>
+        <v>47.68</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>MRVL</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>10.95</v>
+        <v>15</v>
       </c>
       <c r="C12" t="n">
-        <v>15</v>
+        <v>12.78</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>8.34</v>
+        <v>7.21</v>
       </c>
       <c r="F12" t="n">
-        <v>4.44</v>
+        <v>0.89</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>4.48</v>
+        <v>8.1</v>
       </c>
       <c r="I12" t="n">
         <v>3.53</v>
@@ -2549,17 +2549,17 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>46.74</v>
+        <v>47.51</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AMAT</t>
+          <t>GOOGL</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>11.18</v>
+        <v>10.95</v>
       </c>
       <c r="C13" t="n">
         <v>15</v>
@@ -2568,19 +2568,19 @@
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>7.78</v>
+        <v>8.34</v>
       </c>
       <c r="F13" t="n">
-        <v>2.04</v>
+        <v>4.37</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>5.96</v>
+        <v>4.86</v>
       </c>
       <c r="I13" t="n">
-        <v>3.58</v>
+        <v>3.53</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -2589,38 +2589,38 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>45.54</v>
+        <v>47.05</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>DDOG</t>
+          <t>AMAT</t>
         </is>
       </c>
       <c r="B14" t="n">
+        <v>11.18</v>
+      </c>
+      <c r="C14" t="n">
         <v>15</v>
       </c>
-      <c r="C14" t="n">
-        <v>10.11</v>
-      </c>
       <c r="D14" t="n">
         <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>8.98</v>
+        <v>7.78</v>
       </c>
       <c r="F14" t="n">
-        <v>0.8100000000000001</v>
+        <v>2.28</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>6.58</v>
+        <v>5.99</v>
       </c>
       <c r="I14" t="n">
-        <v>3.67</v>
+        <v>3.58</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -2629,7 +2629,7 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>45.15</v>
+        <v>45.81</v>
       </c>
     </row>
     <row r="15">
@@ -2651,13 +2651,13 @@
         <v>6.16</v>
       </c>
       <c r="F15" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>3.71</v>
+        <v>3.64</v>
       </c>
       <c r="I15" t="n">
         <v>3.53</v>
@@ -2669,38 +2669,38 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>44.42</v>
+        <v>44.36</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>MDB</t>
+          <t>DDOG</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>11.32</v>
+        <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>7.5</v>
+        <v>10.11</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>9.880000000000001</v>
+        <v>8.98</v>
       </c>
       <c r="F16" t="n">
-        <v>1.59</v>
+        <v>0.83</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>9.779999999999999</v>
+        <v>5.7</v>
       </c>
       <c r="I16" t="n">
-        <v>3.73</v>
+        <v>3.67</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -2709,38 +2709,38 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>43.8</v>
+        <v>44.29</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>SNOW</t>
+          <t>ACMR</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>14.44</v>
+        <v>15</v>
       </c>
       <c r="C17" t="n">
-        <v>7.5</v>
+        <v>7.83</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>7.58</v>
+        <v>4.02</v>
       </c>
       <c r="F17" t="n">
-        <v>0.99</v>
+        <v>7.14</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>9.06</v>
+        <v>5.93</v>
       </c>
       <c r="I17" t="n">
-        <v>3.56</v>
+        <v>3.63</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2749,38 +2749,38 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>43.13</v>
+        <v>43.55</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>NET</t>
+          <t>AMZN</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>15</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="C18" t="n">
-        <v>7.5</v>
+        <v>12.28</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>7.71</v>
+        <v>6.64</v>
       </c>
       <c r="F18" t="n">
-        <v>0.55</v>
+        <v>6.46</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>8.720000000000001</v>
+        <v>5.42</v>
       </c>
       <c r="I18" t="n">
-        <v>3.64</v>
+        <v>3.47</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2789,38 +2789,38 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>43.12</v>
+        <v>43.49</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ACMR</t>
+          <t>MDB</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>15</v>
+        <v>11.32</v>
       </c>
       <c r="C19" t="n">
-        <v>7.83</v>
+        <v>7.5</v>
       </c>
       <c r="D19" t="n">
         <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>4.02</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="F19" t="n">
-        <v>6.86</v>
+        <v>1.52</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>5.27</v>
+        <v>9.31</v>
       </c>
       <c r="I19" t="n">
-        <v>3.63</v>
+        <v>3.73</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2829,38 +2829,38 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>42.61</v>
+        <v>43.26</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>AMZN</t>
+          <t>VRT</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>9.220000000000001</v>
+        <v>10.91</v>
       </c>
       <c r="C20" t="n">
-        <v>12.28</v>
+        <v>13.39</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>6.64</v>
+        <v>7.41</v>
       </c>
       <c r="F20" t="n">
-        <v>6.52</v>
+        <v>3.46</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>4.46</v>
+        <v>4.52</v>
       </c>
       <c r="I20" t="n">
-        <v>3.47</v>
+        <v>3.56</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2869,38 +2869,38 @@
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>42.59</v>
+        <v>43.25</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>VRT</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>10.91</v>
+        <v>8.51</v>
       </c>
       <c r="C21" t="n">
-        <v>13.39</v>
+        <v>14.63</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>7.41</v>
+        <v>6.87</v>
       </c>
       <c r="F21" t="n">
-        <v>3.2</v>
+        <v>2.78</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>4.02</v>
+        <v>6.18</v>
       </c>
       <c r="I21" t="n">
-        <v>3.56</v>
+        <v>3.45</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2909,38 +2909,38 @@
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>42.49</v>
+        <v>42.42</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>ASML</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>8.51</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="C22" t="n">
-        <v>14.63</v>
+        <v>14.28</v>
       </c>
       <c r="D22" t="n">
         <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>6.87</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="F22" t="n">
-        <v>2.86</v>
+        <v>0.58</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>6.1</v>
+        <v>5.95</v>
       </c>
       <c r="I22" t="n">
-        <v>3.45</v>
+        <v>2.75</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2949,26 +2949,26 @@
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>42.42</v>
+        <v>42.38</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ASML</t>
+          <t>NET</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>9.859999999999999</v>
+        <v>15</v>
       </c>
       <c r="C23" t="n">
-        <v>14.28</v>
+        <v>7.5</v>
       </c>
       <c r="D23" t="n">
         <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>8.960000000000001</v>
+        <v>7.71</v>
       </c>
       <c r="F23" t="n">
         <v>0.5600000000000001</v>
@@ -2977,10 +2977,10 @@
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>5.99</v>
+        <v>7.95</v>
       </c>
       <c r="I23" t="n">
-        <v>2.76</v>
+        <v>3.64</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2989,17 +2989,17 @@
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>42.41</v>
+        <v>42.36</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>PANW</t>
+          <t>SNOW</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>13.54</v>
+        <v>14.44</v>
       </c>
       <c r="C24" t="n">
         <v>7.5</v>
@@ -3008,19 +3008,19 @@
         <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>7.97</v>
+        <v>7.58</v>
       </c>
       <c r="F24" t="n">
-        <v>0.53</v>
+        <v>0.99</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>9.09</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I24" t="n">
-        <v>3.57</v>
+        <v>3.56</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -3029,38 +3029,38 @@
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>42.2</v>
+        <v>42.27</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>SMCI</t>
+          <t>PANW</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>15</v>
+        <v>13.54</v>
       </c>
       <c r="C25" t="n">
-        <v>7.23</v>
+        <v>7.5</v>
       </c>
       <c r="D25" t="n">
         <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>2.23</v>
+        <v>7.97</v>
       </c>
       <c r="F25" t="n">
-        <v>9.880000000000001</v>
+        <v>0.54</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>4.03</v>
+        <v>8.65</v>
       </c>
       <c r="I25" t="n">
-        <v>3.54</v>
+        <v>3.57</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -3069,38 +3069,38 @@
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>41.91</v>
+        <v>41.77</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>CRWD</t>
+          <t>SMCI</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>11.47</v>
+        <v>15</v>
       </c>
       <c r="C26" t="n">
-        <v>7.5</v>
+        <v>7.23</v>
       </c>
       <c r="D26" t="n">
         <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>9.24</v>
+        <v>2.23</v>
       </c>
       <c r="F26" t="n">
-        <v>0.28</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>9.15</v>
+        <v>3.86</v>
       </c>
       <c r="I26" t="n">
-        <v>3.48</v>
+        <v>3.54</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3109,7 +3109,7 @@
         <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>41.12</v>
+        <v>41.75</v>
       </c>
     </row>
     <row r="27">
@@ -3131,13 +3131,13 @@
         <v>9.449999999999999</v>
       </c>
       <c r="F27" t="n">
-        <v>0.21</v>
+        <v>0.23</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>5.88</v>
+        <v>5.97</v>
       </c>
       <c r="I27" t="n">
         <v>3.7</v>
@@ -3149,38 +3149,38 @@
         <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>40.79</v>
+        <v>40.9</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>MRVL</t>
+          <t>CRWD</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>12.23</v>
+        <v>11.55</v>
       </c>
       <c r="C28" t="n">
-        <v>7.41</v>
+        <v>7.5</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>7.11</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="F28" t="n">
-        <v>0.55</v>
+        <v>0.31</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>8.92</v>
+        <v>8.24</v>
       </c>
       <c r="I28" t="n">
-        <v>3.53</v>
+        <v>3.47</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3189,7 +3189,7 @@
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>39.75</v>
+        <v>40.37</v>
       </c>
     </row>
     <row r="29">
@@ -3211,13 +3211,13 @@
         <v>7.23</v>
       </c>
       <c r="F29" t="n">
-        <v>5.62</v>
+        <v>5.58</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>0.85</v>
+        <v>1.06</v>
       </c>
       <c r="I29" t="n">
         <v>3.49</v>
@@ -3229,7 +3229,7 @@
         <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>39.57</v>
+        <v>39.74</v>
       </c>
     </row>
     <row r="30">
@@ -3251,13 +3251,13 @@
         <v>6.78</v>
       </c>
       <c r="F30" t="n">
-        <v>3.64</v>
+        <v>3.42</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>5.92</v>
+        <v>5.4</v>
       </c>
       <c r="I30" t="n">
         <v>3.57</v>
@@ -3269,7 +3269,7 @@
         <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>36.47</v>
+        <v>35.73</v>
       </c>
     </row>
     <row r="31">
@@ -3291,13 +3291,13 @@
         <v>0.8</v>
       </c>
       <c r="F31" t="n">
-        <v>6.34</v>
+        <v>6.33</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>2.73</v>
+        <v>2.69</v>
       </c>
       <c r="I31" t="n">
         <v>3.58</v>
@@ -3309,7 +3309,7 @@
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>31.59</v>
+        <v>31.54</v>
       </c>
     </row>
   </sheetData>
@@ -3348,8 +3348,8 @@
     <col width="19" customWidth="1" min="19" max="19"/>
     <col width="23" customWidth="1" min="20" max="20"/>
     <col width="22" customWidth="1" min="21" max="21"/>
-    <col width="21" customWidth="1" min="22" max="22"/>
-    <col width="22" customWidth="1" min="23" max="23"/>
+    <col width="22" customWidth="1" min="22" max="22"/>
+    <col width="21" customWidth="1" min="23" max="23"/>
     <col width="18" customWidth="1" min="24" max="24"/>
     <col width="24" customWidth="1" min="25" max="25"/>
     <col width="17" customWidth="1" min="26" max="26"/>
@@ -3514,12 +3514,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>MU</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Micron Technology, Inc.</t>
+          <t>Taiwan Semiconductor Manufacturing Company Limited</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -3532,60 +3532,69 @@
           <t>Semiconductors</t>
         </is>
       </c>
+      <c r="E2" t="n">
+        <v>2165456502784</v>
+      </c>
       <c r="F2" t="n">
-        <v>935.3900146484375</v>
+        <v>417.5199890136719</v>
       </c>
       <c r="G2" t="n">
-        <v>90273996800</v>
+        <v>4440492343296</v>
       </c>
       <c r="H2" t="n">
-        <v>3.457</v>
+        <v>0.36</v>
       </c>
       <c r="I2" t="n">
-        <v>44.06</v>
+        <v>13.42</v>
       </c>
       <c r="J2" t="n">
-        <v>13.685</v>
+        <v>0.774</v>
       </c>
       <c r="K2" t="n">
-        <v>7639499776</v>
+        <v>730826014720</v>
       </c>
       <c r="M2" t="n">
-        <v>26022000640</v>
+        <v>3518010228736</v>
       </c>
       <c r="N2" t="n">
-        <v>6376000000</v>
+        <v>1068558516224</v>
       </c>
       <c r="O2" t="n">
-        <v>0.7256899999999999</v>
+        <v>0.6423</v>
       </c>
       <c r="P2" t="n">
-        <v>0.80370003</v>
+        <v>0.60344005</v>
       </c>
       <c r="Q2" t="n">
-        <v>21.229914</v>
+        <v>31.111773</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0.48766136</v>
+      </c>
+      <c r="S2" t="n">
+        <v>2.963026026945206</v>
       </c>
       <c r="T2" t="n">
-        <v>0.1399826712618766</v>
+        <v>0.1143672406390812</v>
       </c>
       <c r="U2" t="n">
-        <v>0.01300878301894581</v>
+        <v>0.000114110405947887</v>
       </c>
       <c r="V2" t="n">
-        <v>1.181647796120662</v>
+        <v>0.113762876766069</v>
       </c>
       <c r="W2" t="n">
-        <v>6.956613918478925</v>
+        <v>0.7716772783500616</v>
       </c>
       <c r="X2" t="n">
-        <v>0.00238</v>
+        <v>0.00013</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.79987</v>
+        <v>0.15493</v>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>2026-08-28T06:05:53.639739+00:00</t>
+          <t>2026-08-28T22:51:03.998625+00:00</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
@@ -3597,12 +3606,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>MU</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Taiwan Semiconductor Manufacturing Company Limited</t>
+          <t>Micron Technology, Inc.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -3616,68 +3625,68 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2216180318208</v>
+        <v>1053565648896</v>
       </c>
       <c r="F3" t="n">
-        <v>427.2999877929688</v>
+        <v>932.8599853515625</v>
       </c>
       <c r="G3" t="n">
-        <v>4440492343296</v>
+        <v>90273996800</v>
       </c>
       <c r="H3" t="n">
-        <v>0.36</v>
+        <v>3.457</v>
       </c>
       <c r="I3" t="n">
-        <v>13.72</v>
+        <v>44.24</v>
       </c>
       <c r="J3" t="n">
-        <v>0.774</v>
+        <v>13.685</v>
       </c>
       <c r="K3" t="n">
-        <v>730826014720</v>
+        <v>7639499776</v>
       </c>
       <c r="M3" t="n">
-        <v>3518010228736</v>
+        <v>26022000640</v>
       </c>
       <c r="N3" t="n">
-        <v>1068558516224</v>
+        <v>6376000000</v>
       </c>
       <c r="O3" t="n">
-        <v>0.6423</v>
+        <v>0.7256899999999999</v>
       </c>
       <c r="P3" t="n">
-        <v>0.60344005</v>
+        <v>0.80370003</v>
       </c>
       <c r="Q3" t="n">
-        <v>31.144314</v>
+        <v>21.086346</v>
       </c>
       <c r="R3" t="n">
-        <v>0.49908438</v>
+        <v>11.670754</v>
       </c>
       <c r="S3" t="n">
-        <v>3.032432170681665</v>
+        <v>137.9102925306506</v>
       </c>
       <c r="T3" t="n">
-        <v>0.08918964709572319</v>
+        <v>0.2623274497314783</v>
       </c>
       <c r="U3" t="n">
-        <v>0.008098401033602487</v>
+        <v>-0.03913137451813475</v>
       </c>
       <c r="V3" t="n">
-        <v>0.1077490245917747</v>
+        <v>1.246114648857811</v>
       </c>
       <c r="W3" t="n">
-        <v>0.8054482846213904</v>
+        <v>6.658666224370205</v>
       </c>
       <c r="X3" t="n">
-        <v>0.00013</v>
+        <v>0.00238</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.15493</v>
+        <v>0.79977</v>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>2026-08-28T06:05:59.916108+00:00</t>
+          <t>2026-08-28T22:50:58.770573+00:00</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
@@ -3708,10 +3717,10 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>45149425664</v>
+        <v>43741794304</v>
       </c>
       <c r="F4" t="n">
-        <v>240.2400054931641</v>
+        <v>232.75</v>
       </c>
       <c r="G4" t="n">
         <v>1335116032</v>
@@ -3720,7 +3729,7 @@
         <v>1.57</v>
       </c>
       <c r="I4" t="n">
-        <v>2.67</v>
+        <v>2.5</v>
       </c>
       <c r="J4" t="n">
         <v>3.432</v>
@@ -3741,35 +3750,35 @@
         <v>0.35661998</v>
       </c>
       <c r="Q4" t="n">
-        <v>89.97752</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="R4" t="n">
-        <v>33.816856</v>
+        <v>32.762543</v>
       </c>
       <c r="S4" t="n">
-        <v>180.0143639494494</v>
+        <v>174.4020253599966</v>
       </c>
       <c r="T4" t="n">
-        <v>0.2494279541207858</v>
+        <v>0.3116371034251832</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0804587312730709</v>
+        <v>-0.01389653347566167</v>
       </c>
       <c r="V4" t="n">
-        <v>0.9458934656948221</v>
+        <v>1.033106159809553</v>
       </c>
       <c r="W4" t="n">
-        <v>0.9574676030479532</v>
+        <v>0.7656652030638886</v>
       </c>
       <c r="X4" t="n">
         <v>0.09436</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.73627</v>
+        <v>0.73563004</v>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>2026-08-28T06:05:54.692792+00:00</t>
+          <t>2026-08-28T22:50:59.626150+00:00</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
@@ -3800,10 +3809,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>253619666944</v>
+        <v>246418096128</v>
       </c>
       <c r="F5" t="n">
-        <v>201.0899963378906</v>
+        <v>195.3800048828125</v>
       </c>
       <c r="G5" t="n">
         <v>10540800000</v>
@@ -3812,7 +3821,7 @@
         <v>0.377</v>
       </c>
       <c r="I5" t="n">
-        <v>3.14</v>
+        <v>3.16</v>
       </c>
       <c r="J5" t="n">
         <v>0.357</v>
@@ -3833,35 +3842,35 @@
         <v>0.45393002</v>
       </c>
       <c r="Q5" t="n">
-        <v>64.0414</v>
+        <v>61.829113</v>
       </c>
       <c r="R5" t="n">
-        <v>24.06076</v>
+        <v>23.377552</v>
       </c>
       <c r="S5" t="n">
-        <v>65.17251633931248</v>
+        <v>63.32193236319635</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1849035907289216</v>
+        <v>0.2368171385264668</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2950988008284381</v>
+        <v>0.2251834413195413</v>
       </c>
       <c r="V5" t="n">
-        <v>0.5132063907102002</v>
+        <v>0.5000384252039347</v>
       </c>
       <c r="W5" t="n">
-        <v>0.5088916477167404</v>
+        <v>0.4341922558198847</v>
       </c>
       <c r="X5" t="n">
         <v>0.17247999</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.73305</v>
+        <v>0.73299</v>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>2026-08-28T06:06:02.225298+00:00</t>
+          <t>2026-08-28T22:51:05.893818+00:00</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
@@ -3892,10 +3901,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>446800625664</v>
+        <v>447665733632</v>
       </c>
       <c r="F6" t="n">
-        <v>185.9299926757812</v>
+        <v>186.2899932861328</v>
       </c>
       <c r="G6" t="n">
         <v>6155940864</v>
@@ -3904,7 +3913,7 @@
         <v>0.928</v>
       </c>
       <c r="I6" t="n">
-        <v>1.23</v>
+        <v>1.17</v>
       </c>
       <c r="J6" t="n">
         <v>2.154</v>
@@ -3925,35 +3934,35 @@
         <v>0.47120997</v>
       </c>
       <c r="Q6" t="n">
-        <v>151.1626</v>
+        <v>159.22223</v>
       </c>
       <c r="R6" t="n">
-        <v>72.5804</v>
+        <v>72.72093</v>
       </c>
       <c r="S6" t="n">
-        <v>206.9379333796696</v>
+        <v>207.3386124404524</v>
       </c>
       <c r="T6" t="n">
-        <v>0.5051404072946721</v>
+        <v>0.5145527909441692</v>
       </c>
       <c r="U6" t="n">
-        <v>0.297125697125697</v>
+        <v>0.1900472804136464</v>
       </c>
       <c r="V6" t="n">
-        <v>0.3855726156422654</v>
+        <v>0.3703839189382738</v>
       </c>
       <c r="W6" t="n">
-        <v>0.1863833028813136</v>
+        <v>0.178155824935788</v>
       </c>
       <c r="X6" t="n">
         <v>0.03477</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.64858</v>
+        <v>0.64865994</v>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>2026-08-28T06:05:51.284618+00:00</t>
+          <t>2026-08-28T22:50:56.792100+00:00</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr">
@@ -3965,12 +3974,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>DELL</t>
+          <t>TER</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Dell Technologies Inc.</t>
+          <t>Teradyne, Inc.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -3980,72 +3989,72 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Computer Hardware</t>
+          <t>Semiconductor Equipment &amp; Materials</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>305147215872</v>
+        <v>55496278016</v>
       </c>
       <c r="F7" t="n">
-        <v>472.260009765625</v>
+        <v>354.9700012207031</v>
       </c>
       <c r="G7" t="n">
-        <v>134001999872</v>
+        <v>4464031232</v>
       </c>
       <c r="H7" t="n">
-        <v>0.875</v>
+        <v>1.039</v>
       </c>
       <c r="I7" t="n">
-        <v>12.8</v>
+        <v>7.29</v>
       </c>
       <c r="J7" t="n">
-        <v>2.825</v>
+        <v>3.858</v>
       </c>
       <c r="K7" t="n">
-        <v>5434124800</v>
+        <v>437381248</v>
       </c>
       <c r="M7" t="n">
-        <v>11580999680</v>
+        <v>354828992</v>
       </c>
       <c r="N7" t="n">
-        <v>31924000768</v>
+        <v>100127000</v>
       </c>
       <c r="O7" t="n">
-        <v>0.19212</v>
+        <v>0.5924199999999999</v>
       </c>
       <c r="P7" t="n">
-        <v>0.08857000600000001</v>
+        <v>0.33161</v>
       </c>
       <c r="Q7" t="n">
-        <v>36.895313</v>
+        <v>48.69273</v>
       </c>
       <c r="R7" t="n">
-        <v>2.277184</v>
+        <v>12.431875</v>
       </c>
       <c r="S7" t="n">
-        <v>56.15388440692418</v>
+        <v>126.8830757371656</v>
       </c>
       <c r="T7" t="n">
-        <v>0.2044376496157128</v>
+        <v>0.1113302562565048</v>
       </c>
       <c r="U7" t="n">
-        <v>0.4920057019144415</v>
+        <v>-0.05166839374858856</v>
       </c>
       <c r="V7" t="n">
-        <v>2.842760368008178</v>
+        <v>0.06734011770084192</v>
       </c>
       <c r="W7" t="n">
-        <v>2.60964552267963</v>
+        <v>2.018735227611809</v>
       </c>
       <c r="X7" t="n">
-        <v>0.07491</v>
+        <v>0.00202</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.75618</v>
+        <v>1.00471</v>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>2026-08-28T06:06:02.798169+00:00</t>
+          <t>2026-08-28T22:51:00.101902+00:00</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr">
@@ -4076,68 +4085,68 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5505032912896</v>
+        <v>5253179637760</v>
       </c>
       <c r="F8" t="n">
-        <v>227.9799957275391</v>
+        <v>217.5500030517578</v>
       </c>
       <c r="G8" t="n">
-        <v>253491003392</v>
+        <v>302970011648</v>
       </c>
       <c r="H8" t="n">
-        <v>0.852</v>
+        <v>1.059</v>
       </c>
       <c r="I8" t="n">
-        <v>7.09</v>
+        <v>7.91</v>
       </c>
       <c r="J8" t="n">
-        <v>2.145</v>
+        <v>1.278</v>
       </c>
       <c r="K8" t="n">
-        <v>46335873024</v>
+        <v>41809874944</v>
       </c>
       <c r="M8" t="n">
-        <v>53171998720</v>
+        <v>62469001216</v>
       </c>
       <c r="N8" t="n">
-        <v>12814000128</v>
+        <v>38860001280</v>
       </c>
       <c r="O8" t="n">
-        <v>0.74144995</v>
+        <v>0.74674004</v>
       </c>
       <c r="P8" t="n">
-        <v>0.65596</v>
+        <v>0.66236997</v>
       </c>
       <c r="Q8" t="n">
-        <v>32.155148</v>
+        <v>27.503162</v>
       </c>
       <c r="R8" t="n">
-        <v>21.716877</v>
+        <v>17.338943</v>
       </c>
       <c r="S8" t="n">
-        <v>118.8071477588137</v>
+        <v>125.6444714268122</v>
       </c>
       <c r="T8" t="n">
-        <v>0.1572001527040727</v>
+        <v>0.1449397891747799</v>
       </c>
       <c r="U8" t="n">
-        <v>0.06532419633815723</v>
+        <v>0.03155986221998819</v>
       </c>
       <c r="V8" t="n">
-        <v>0.1672022272068816</v>
+        <v>0.1780807440636778</v>
       </c>
       <c r="W8" t="n">
-        <v>0.2570684399859056</v>
+        <v>0.2090789147412515</v>
       </c>
       <c r="X8" t="n">
-        <v>0.03991</v>
+        <v>0.04008</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.71202004</v>
+        <v>0.71496004</v>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>2026-08-28T06:05:50.757405+00:00</t>
+          <t>2026-08-28T22:50:56.364503+00:00</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr">
@@ -4149,12 +4158,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>TER</t>
+          <t>DELL</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Teradyne, Inc.</t>
+          <t>Dell Technologies Inc.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -4164,72 +4173,72 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Semiconductor Equipment &amp; Materials</t>
+          <t>Computer Hardware</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>58168139776</v>
+        <v>294796001280</v>
       </c>
       <c r="F9" t="n">
-        <v>372.0599975585938</v>
+        <v>456.239990234375</v>
       </c>
       <c r="G9" t="n">
-        <v>4464031232</v>
+        <v>134001999872</v>
       </c>
       <c r="H9" t="n">
-        <v>1.039</v>
+        <v>0.875</v>
       </c>
       <c r="I9" t="n">
-        <v>7.44</v>
+        <v>12.56</v>
       </c>
       <c r="J9" t="n">
-        <v>3.858</v>
+        <v>2.825</v>
       </c>
       <c r="K9" t="n">
-        <v>437381248</v>
+        <v>5434124800</v>
       </c>
       <c r="M9" t="n">
-        <v>354828992</v>
+        <v>11580999680</v>
       </c>
       <c r="N9" t="n">
-        <v>100127000</v>
+        <v>31924000768</v>
       </c>
       <c r="O9" t="n">
-        <v>0.5924199999999999</v>
+        <v>0.19212</v>
       </c>
       <c r="P9" t="n">
-        <v>0.33161</v>
+        <v>0.08857000600000001</v>
       </c>
       <c r="Q9" t="n">
-        <v>50.008064</v>
+        <v>36.32484</v>
       </c>
       <c r="R9" t="n">
-        <v>13.030406</v>
+        <v>2.1999373</v>
       </c>
       <c r="S9" t="n">
-        <v>132.991846454286</v>
+        <v>54.24903036455843</v>
       </c>
       <c r="T9" t="n">
-        <v>0.1603305929851542</v>
+        <v>0.2342819287795512</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.02767541227442294</v>
+        <v>0.08572833319716411</v>
       </c>
       <c r="V9" t="n">
-        <v>0.08570242896141655</v>
+        <v>2.774458150107836</v>
       </c>
       <c r="W9" t="n">
-        <v>2.188413123565745</v>
+        <v>2.446876908237777</v>
       </c>
       <c r="X9" t="n">
-        <v>0.00202</v>
+        <v>0.07491</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.00462</v>
+        <v>0.75615996</v>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>2026-08-28T06:05:55.266776+00:00</t>
+          <t>2026-08-28T22:51:06.369837+00:00</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr">
@@ -4241,12 +4250,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>PATH</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>UiPath, Inc.</t>
+          <t>Advanced Micro Devices, Inc.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -4256,69 +4265,72 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Software - Infrastructure</t>
+          <t>Semiconductors</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>9497144320</v>
+        <v>760047665152</v>
       </c>
       <c r="F10" t="n">
-        <v>18.32999992370605</v>
+        <v>465.5799865722656</v>
       </c>
       <c r="G10" t="n">
-        <v>1672329984</v>
+        <v>41305001984</v>
       </c>
       <c r="H10" t="n">
-        <v>0.173</v>
+        <v>0.501</v>
       </c>
       <c r="I10" t="n">
-        <v>0.66</v>
+        <v>3.91</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1.595</v>
       </c>
       <c r="K10" t="n">
-        <v>511553632</v>
+        <v>8841499648</v>
       </c>
       <c r="M10" t="n">
-        <v>1307244032</v>
+        <v>13111000064</v>
       </c>
       <c r="N10" t="n">
-        <v>83003000</v>
+        <v>4276000000</v>
       </c>
       <c r="O10" t="n">
-        <v>0.8305</v>
+        <v>0.55724</v>
       </c>
       <c r="P10" t="n">
-        <v>0.07274</v>
+        <v>0.1725</v>
       </c>
       <c r="Q10" t="n">
-        <v>27.772726</v>
+        <v>119.074165</v>
       </c>
       <c r="R10" t="n">
-        <v>5.6789894</v>
+        <v>18.400862</v>
       </c>
       <c r="S10" t="n">
-        <v>18.5652954566453</v>
+        <v>85.96365949343529</v>
       </c>
       <c r="T10" t="n">
-        <v>0.5036915959540738</v>
+        <v>0.08385322008192486</v>
       </c>
       <c r="U10" t="n">
-        <v>0.5829015582445474</v>
+        <v>-0.09788798954372291</v>
       </c>
       <c r="V10" t="n">
-        <v>0.844064456489567</v>
+        <v>1.285840550443155</v>
       </c>
       <c r="W10" t="n">
-        <v>0.6454218454932941</v>
+        <v>1.761774715359504</v>
       </c>
       <c r="X10" t="n">
-        <v>0.09236999999999999</v>
+        <v>0.00425</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.91159</v>
+        <v>0.75373</v>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>2026-08-28T06:06:07.171430+00:00</t>
+          <t>2026-08-28T22:50:57.225818+00:00</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr">
@@ -4330,12 +4342,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>PATH</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Advanced Micro Devices, Inc.</t>
+          <t>UiPath, Inc.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -4345,72 +4357,69 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Semiconductors</t>
+          <t>Software - Infrastructure</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>778151854080</v>
+        <v>9403882496</v>
       </c>
       <c r="F11" t="n">
-        <v>476.6700134277344</v>
+        <v>18.14999961853027</v>
       </c>
       <c r="G11" t="n">
-        <v>41305001984</v>
+        <v>1672329984</v>
       </c>
       <c r="H11" t="n">
-        <v>0.501</v>
+        <v>0.173</v>
       </c>
       <c r="I11" t="n">
-        <v>3.91</v>
-      </c>
-      <c r="J11" t="n">
-        <v>1.595</v>
+        <v>0.6</v>
       </c>
       <c r="K11" t="n">
-        <v>8841499648</v>
+        <v>511553632</v>
       </c>
       <c r="M11" t="n">
-        <v>13111000064</v>
+        <v>1307244032</v>
       </c>
       <c r="N11" t="n">
-        <v>4276000000</v>
+        <v>83003000</v>
       </c>
       <c r="O11" t="n">
-        <v>0.55724</v>
+        <v>0.8305</v>
       </c>
       <c r="P11" t="n">
-        <v>0.1725</v>
+        <v>0.07274</v>
       </c>
       <c r="Q11" t="n">
-        <v>121.910484</v>
+        <v>30.249998</v>
       </c>
       <c r="R11" t="n">
-        <v>18.839167</v>
+        <v>5.623222</v>
       </c>
       <c r="S11" t="n">
-        <v>88.01129729796716</v>
+        <v>18.38298451568808</v>
       </c>
       <c r="T11" t="n">
-        <v>0.04850208646204179</v>
+        <v>0.4416202858265668</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.07994752124284621</v>
+        <v>0.5486347444539406</v>
       </c>
       <c r="V11" t="n">
-        <v>1.260599507009267</v>
+        <v>0.6946778294942526</v>
       </c>
       <c r="W11" t="n">
-        <v>1.852091183518865</v>
+        <v>0.6119004662162997</v>
       </c>
       <c r="X11" t="n">
-        <v>0.00425</v>
+        <v>0.09236999999999999</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.75384</v>
+        <v>0.91153</v>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>2026-08-28T06:05:51.819478+00:00</t>
+          <t>2026-08-28T22:51:09.946502+00:00</t>
         </is>
       </c>
       <c r="AD11" t="inlineStr">
@@ -4422,87 +4431,87 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>MRVL</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Alphabet Inc.</t>
+          <t>Marvell Technology, Inc.</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Internet Content &amp; Information</t>
+          <t>Semiconductors</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4166127190016</v>
+        <v>194677391360</v>
       </c>
       <c r="F12" t="n">
-        <v>340.6499938964844</v>
+        <v>216.6199951171875</v>
       </c>
       <c r="G12" t="n">
-        <v>445865984000</v>
+        <v>9450300416</v>
       </c>
       <c r="H12" t="n">
-        <v>0.242</v>
+        <v>0.365</v>
       </c>
       <c r="I12" t="n">
-        <v>19.86</v>
+        <v>3.02</v>
       </c>
       <c r="J12" t="n">
-        <v>2.94</v>
+        <v>0.5</v>
       </c>
       <c r="K12" t="n">
-        <v>22665000960</v>
+        <v>2229250048</v>
       </c>
       <c r="M12" t="n">
-        <v>242473992192</v>
+        <v>3932800000</v>
       </c>
       <c r="N12" t="n">
-        <v>120790999040</v>
+        <v>4962899968</v>
       </c>
       <c r="O12" t="n">
-        <v>0.60897</v>
+        <v>0.52216</v>
       </c>
       <c r="P12" t="n">
-        <v>0.34033</v>
+        <v>0.16679001</v>
       </c>
       <c r="Q12" t="n">
-        <v>17.152567</v>
+        <v>71.72848</v>
       </c>
       <c r="R12" t="n">
-        <v>9.3439</v>
+        <v>20.600128</v>
       </c>
       <c r="S12" t="n">
-        <v>183.8132368654442</v>
+        <v>87.32864737836714</v>
       </c>
       <c r="T12" t="n">
-        <v>0.02079650780351439</v>
+        <v>0.3257038140063735</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.1263080134710389</v>
+        <v>0.05694362072151526</v>
       </c>
       <c r="V12" t="n">
-        <v>0.09010350711670623</v>
+        <v>1.734038348041977</v>
       </c>
       <c r="W12" t="n">
-        <v>0.6465288154959068</v>
+        <v>1.810844566604123</v>
       </c>
       <c r="X12" t="n">
-        <v>0.01596</v>
+        <v>0.00494</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.81044</v>
+        <v>0.82141</v>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>2026-08-28T06:05:57.554552+00:00</t>
+          <t>2026-08-28T22:51:05.465346+00:00</t>
         </is>
       </c>
       <c r="AD12" t="inlineStr">
@@ -4514,87 +4523,87 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AMAT</t>
+          <t>GOOGL</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Applied Materials, Inc.</t>
+          <t>Alphabet Inc.</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Semiconductor Equipment &amp; Materials</t>
+          <t>Internet Content &amp; Information</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>382799642624</v>
+        <v>4238773059584</v>
       </c>
       <c r="F13" t="n">
-        <v>482.3599853515625</v>
+        <v>346.5899963378906</v>
       </c>
       <c r="G13" t="n">
-        <v>30837000192</v>
+        <v>445865984000</v>
       </c>
       <c r="H13" t="n">
-        <v>0.248</v>
+        <v>0.242</v>
       </c>
       <c r="I13" t="n">
-        <v>11.67</v>
+        <v>19.93</v>
       </c>
       <c r="J13" t="n">
-        <v>0.428</v>
+        <v>2.94</v>
       </c>
       <c r="K13" t="n">
-        <v>3075375104</v>
+        <v>22665000960</v>
       </c>
       <c r="M13" t="n">
-        <v>9233000448</v>
+        <v>242473992192</v>
       </c>
       <c r="N13" t="n">
-        <v>7345999872</v>
+        <v>120790999040</v>
       </c>
       <c r="O13" t="n">
-        <v>0.49398</v>
+        <v>0.60897</v>
       </c>
       <c r="P13" t="n">
-        <v>0.33736</v>
+        <v>0.34033</v>
       </c>
       <c r="Q13" t="n">
-        <v>41.333332</v>
+        <v>17.390366</v>
       </c>
       <c r="R13" t="n">
-        <v>12.413648</v>
+        <v>9.506831999999999</v>
       </c>
       <c r="S13" t="n">
-        <v>124.4725048746444</v>
+        <v>187.018437240075</v>
       </c>
       <c r="T13" t="n">
-        <v>0.01346553505765979</v>
+        <v>0.0293427731090381</v>
       </c>
       <c r="U13" t="n">
-        <v>0.07382093830892544</v>
+        <v>-0.08819207451527</v>
       </c>
       <c r="V13" t="n">
-        <v>0.224145021556174</v>
+        <v>0.1290295835576318</v>
       </c>
       <c r="W13" t="n">
-        <v>1.950471159681328</v>
+        <v>0.6423112460262883</v>
       </c>
       <c r="X13" t="n">
-        <v>0.00331</v>
+        <v>0.01596</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.86310995</v>
+        <v>0.81044996</v>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>2026-08-28T06:05:53.007319+00:00</t>
+          <t>2026-08-28T22:51:02.101307+00:00</t>
         </is>
       </c>
       <c r="AD13" t="inlineStr">
@@ -4606,12 +4615,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>DDOG</t>
+          <t>AMAT</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Datadog, Inc.</t>
+          <t>Applied Materials, Inc.</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -4621,72 +4630,72 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Software - Application</t>
+          <t>Semiconductor Equipment &amp; Materials</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>87230087168</v>
+        <v>366380154880</v>
       </c>
       <c r="F14" t="n">
-        <v>242.9299926757812</v>
+        <v>461.6700134277344</v>
       </c>
       <c r="G14" t="n">
-        <v>3966725120</v>
+        <v>30837000192</v>
       </c>
       <c r="H14" t="n">
-        <v>0.356</v>
+        <v>0.248</v>
       </c>
       <c r="I14" t="n">
-        <v>0.53</v>
+        <v>11.58</v>
       </c>
       <c r="J14" t="n">
-        <v>14.985</v>
+        <v>0.428</v>
       </c>
       <c r="K14" t="n">
-        <v>1051412352</v>
+        <v>3075375104</v>
       </c>
       <c r="M14" t="n">
-        <v>4985438208</v>
+        <v>9233000448</v>
       </c>
       <c r="N14" t="n">
-        <v>1277800960</v>
+        <v>7345999872</v>
       </c>
       <c r="O14" t="n">
-        <v>0.79536</v>
+        <v>0.49398</v>
       </c>
       <c r="P14" t="n">
-        <v>0.00666</v>
+        <v>0.33736</v>
       </c>
       <c r="Q14" t="n">
-        <v>458.3585</v>
+        <v>39.867878</v>
       </c>
       <c r="R14" t="n">
-        <v>21.990454</v>
+        <v>11.8811865</v>
       </c>
       <c r="S14" t="n">
-        <v>82.96467794207538</v>
+        <v>119.1334853441019</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.03168850467276074</v>
+        <v>0.05891553435360564</v>
       </c>
       <c r="U14" t="n">
-        <v>0.07853838905697441</v>
+        <v>0.02689349912329186</v>
       </c>
       <c r="V14" t="n">
-        <v>1.201848895532271</v>
+        <v>0.231603937484552</v>
       </c>
       <c r="W14" t="n">
-        <v>0.8441509189618464</v>
+        <v>1.808879272617759</v>
       </c>
       <c r="X14" t="n">
-        <v>0.00619</v>
+        <v>0.00331</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.9282899999999999</v>
+        <v>0.86313003</v>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>2026-08-28T06:06:04.952226+00:00</t>
+          <t>2026-08-28T22:50:58.258372+00:00</t>
         </is>
       </c>
       <c r="AD14" t="inlineStr">
@@ -4717,10 +4726,10 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1767631355904</v>
+        <v>1754548011008</v>
       </c>
       <c r="F15" t="n">
-        <v>371.5400085449219</v>
+        <v>368.7900085449219</v>
       </c>
       <c r="G15" t="n">
         <v>75464998912</v>
@@ -4729,7 +4738,7 @@
         <v>0.479</v>
       </c>
       <c r="I15" t="n">
-        <v>6.28</v>
+        <v>6.02</v>
       </c>
       <c r="J15" t="n">
         <v>0.854</v>
@@ -4750,35 +4759,35 @@
         <v>0.48988</v>
       </c>
       <c r="Q15" t="n">
-        <v>59.16242</v>
+        <v>61.2608</v>
       </c>
       <c r="R15" t="n">
-        <v>23.423195</v>
+        <v>23.249825</v>
       </c>
       <c r="S15" t="n">
-        <v>64.95719446737999</v>
+        <v>64.47640565592636</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.02459897358195728</v>
+        <v>-0.004131558514356315</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.127647689162111</v>
+        <v>-0.1732352596283164</v>
       </c>
       <c r="V15" t="n">
-        <v>0.1221710160474041</v>
+        <v>0.150601502821587</v>
       </c>
       <c r="W15" t="n">
-        <v>0.2465023137027968</v>
+        <v>0.2036033468000933</v>
       </c>
       <c r="X15" t="n">
         <v>0.01948</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.80146</v>
+        <v>0.80147004</v>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>2026-08-28T06:05:52.404809+00:00</t>
+          <t>2026-08-28T22:50:57.700886+00:00</t>
         </is>
       </c>
       <c r="AD15" t="inlineStr">
@@ -4790,12 +4799,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>MDB</t>
+          <t>DDOG</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>MongoDB, Inc.</t>
+          <t>Datadog, Inc.</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -4805,66 +4814,72 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Software - Infrastructure</t>
+          <t>Software - Application</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>35436699648</v>
+        <v>85093597184</v>
       </c>
       <c r="F16" t="n">
-        <v>440.5799865722656</v>
+        <v>236.9799957275391</v>
       </c>
       <c r="G16" t="n">
-        <v>2602398976</v>
+        <v>3966725120</v>
       </c>
       <c r="H16" t="n">
-        <v>0.252</v>
+        <v>0.356</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.4</v>
+        <v>0.51</v>
+      </c>
+      <c r="J16" t="n">
+        <v>14.985</v>
       </c>
       <c r="K16" t="n">
-        <v>517605376</v>
+        <v>1051412352</v>
       </c>
       <c r="M16" t="n">
-        <v>2427152896</v>
+        <v>4985438208</v>
       </c>
       <c r="N16" t="n">
-        <v>58635000</v>
+        <v>1277800960</v>
       </c>
       <c r="O16" t="n">
-        <v>0.71970004</v>
+        <v>0.79536</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.03607</v>
+        <v>0.00666</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>464.66666</v>
       </c>
       <c r="R16" t="n">
-        <v>13.616936</v>
+        <v>21.45185</v>
       </c>
       <c r="S16" t="n">
-        <v>68.46277355511856</v>
+        <v>80.93265883945027</v>
       </c>
       <c r="T16" t="n">
-        <v>0.4183890074624725</v>
+        <v>-0.103028066698809</v>
       </c>
       <c r="U16" t="n">
-        <v>0.3528002839611608</v>
+        <v>-0.04192443953947889</v>
       </c>
       <c r="V16" t="n">
-        <v>0.3987110709278181</v>
+        <v>1.034861734419634</v>
       </c>
       <c r="W16" t="n">
-        <v>0.4899559296054348</v>
+        <v>0.6811860417159425</v>
       </c>
       <c r="X16" t="n">
-        <v>0.02641</v>
+        <v>0.00619</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.9611299599999999</v>
+        <v>0.92819</v>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>2026-08-28T06:06:06.639929+00:00</t>
+          <t>2026-08-28T22:51:08.190912+00:00</t>
         </is>
       </c>
       <c r="AD16" t="inlineStr">
@@ -4876,12 +4891,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>SNOW</t>
+          <t>ACMR</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Snowflake Inc.</t>
+          <t>ACM Research, Inc.</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -4891,66 +4906,69 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Software - Application</t>
+          <t>Semiconductor Equipment &amp; Materials</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>114069520384</v>
+        <v>5183293440</v>
       </c>
       <c r="F17" t="n">
-        <v>329.1099853515625</v>
+        <v>74.41999816894531</v>
       </c>
       <c r="G17" t="n">
-        <v>5032822784</v>
+        <v>1037772032</v>
       </c>
       <c r="H17" t="n">
-        <v>0.335</v>
+        <v>0.36</v>
       </c>
       <c r="I17" t="n">
-        <v>-3.69</v>
+        <v>2.12</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1.806</v>
       </c>
       <c r="K17" t="n">
-        <v>1739497728</v>
+        <v>-186610256</v>
       </c>
       <c r="M17" t="n">
-        <v>2954998016</v>
+        <v>1439374976</v>
       </c>
       <c r="N17" t="n">
-        <v>2772094976</v>
+        <v>349319008</v>
       </c>
       <c r="O17" t="n">
-        <v>0.67144996</v>
+        <v>0.43835</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.22173999</v>
+        <v>0.16982001</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>35.103775</v>
       </c>
       <c r="R17" t="n">
-        <v>22.665117</v>
-      </c>
-      <c r="S17" t="n">
-        <v>65.57612496289504</v>
+        <v>4.994636</v>
       </c>
       <c r="T17" t="n">
-        <v>0.2173028672257267</v>
+        <v>0.1396630121128608</v>
       </c>
       <c r="U17" t="n">
-        <v>0.3758778827358218</v>
+        <v>-0.1402495347973027</v>
       </c>
       <c r="V17" t="n">
-        <v>0.9449794473921684</v>
+        <v>0.3046984041805443</v>
       </c>
       <c r="W17" t="n">
-        <v>0.6423473544287228</v>
+        <v>1.540798765543686</v>
       </c>
       <c r="X17" t="n">
-        <v>0.02962</v>
+        <v>0.12675999</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.81926</v>
+        <v>0.78056</v>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>2026-08-28T06:06:04.419941+00:00</t>
+          <t>2026-08-28T22:50:59.195149+00:00</t>
         </is>
       </c>
       <c r="AD17" t="inlineStr">
@@ -4962,81 +4980,87 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>NET</t>
+          <t>AMZN</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Cloudflare, Inc.</t>
+          <t>Amazon.com, Inc.</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Software - Infrastructure</t>
+          <t>Internet Retail</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>109754449920</v>
+        <v>2873797378048</v>
       </c>
       <c r="F18" t="n">
-        <v>308.2300109863281</v>
+        <v>266.4299926757812</v>
       </c>
       <c r="G18" t="n">
-        <v>2512349952</v>
+        <v>775680032768</v>
       </c>
       <c r="H18" t="n">
-        <v>0.359</v>
+        <v>0.196</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.62</v>
+        <v>12.43</v>
+      </c>
+      <c r="J18" t="n">
+        <v>2.423</v>
       </c>
       <c r="K18" t="n">
-        <v>692851968</v>
+        <v>3219124992</v>
       </c>
       <c r="M18" t="n">
-        <v>4162798080</v>
+        <v>122988003328</v>
       </c>
       <c r="N18" t="n">
-        <v>3529349888</v>
+        <v>251635007488</v>
       </c>
       <c r="O18" t="n">
-        <v>0.72577006</v>
+        <v>0.5077</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.07902000000000001</v>
+        <v>0.13689</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>21.434431</v>
       </c>
       <c r="R18" t="n">
-        <v>43.68597</v>
+        <v>3.7048748</v>
       </c>
       <c r="S18" t="n">
-        <v>158.4096675611954</v>
+        <v>892.7262486513603</v>
       </c>
       <c r="T18" t="n">
-        <v>0.1670958116733836</v>
+        <v>0.1755129047012691</v>
       </c>
       <c r="U18" t="n">
-        <v>0.3512340982929301</v>
+        <v>-0.01555580012115021</v>
       </c>
       <c r="V18" t="n">
-        <v>0.7941211030914146</v>
+        <v>0.2814062861778868</v>
       </c>
       <c r="W18" t="n">
-        <v>0.5018027808257604</v>
+        <v>0.1503885390948481</v>
       </c>
       <c r="X18" t="n">
-        <v>0.00616</v>
+        <v>0.0887</v>
       </c>
       <c r="Y18" t="n">
-        <v>0.90191</v>
+        <v>0.68727</v>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>2026-08-28T06:06:05.481159+00:00</t>
+          <t>2026-08-28T22:51:02.541011+00:00</t>
         </is>
       </c>
       <c r="AD18" t="inlineStr">
@@ -5048,12 +5072,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ACMR</t>
+          <t>MDB</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>ACM Research, Inc.</t>
+          <t>MongoDB, Inc.</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -5063,69 +5087,66 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Semiconductor Equipment &amp; Materials</t>
+          <t>Software - Infrastructure</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5606064128</v>
+        <v>35922505728</v>
       </c>
       <c r="F19" t="n">
-        <v>80.48999786376953</v>
+        <v>446.6199951171875</v>
       </c>
       <c r="G19" t="n">
-        <v>1037772032</v>
+        <v>2602398976</v>
       </c>
       <c r="H19" t="n">
-        <v>0.36</v>
+        <v>0.252</v>
       </c>
       <c r="I19" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="J19" t="n">
-        <v>1.806</v>
+        <v>-0.35</v>
       </c>
       <c r="K19" t="n">
-        <v>-186610256</v>
+        <v>517605376</v>
       </c>
       <c r="M19" t="n">
-        <v>1439374976</v>
+        <v>2427152896</v>
       </c>
       <c r="N19" t="n">
-        <v>349319008</v>
+        <v>58635000</v>
       </c>
       <c r="O19" t="n">
-        <v>0.43835</v>
+        <v>0.71970004</v>
       </c>
       <c r="P19" t="n">
-        <v>0.16982001</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>37.263885</v>
+        <v>-0.03607</v>
       </c>
       <c r="R19" t="n">
-        <v>5.402019</v>
+        <v>13.803612</v>
+      </c>
+      <c r="S19" t="n">
+        <v>69.40133814993452</v>
       </c>
       <c r="T19" t="n">
-        <v>0.1176062429255689</v>
+        <v>0.3909062180871057</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.133211314508683</v>
+        <v>0.331008825405614</v>
       </c>
       <c r="V19" t="n">
-        <v>0.1755512841941056</v>
+        <v>0.3268174283384024</v>
       </c>
       <c r="W19" t="n">
-        <v>1.816305041239907</v>
+        <v>0.4040238495683937</v>
       </c>
       <c r="X19" t="n">
-        <v>0.12675999</v>
+        <v>0.02641</v>
       </c>
       <c r="Y19" t="n">
-        <v>0.78055</v>
+        <v>0.9609799999999999</v>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>2026-08-28T06:05:54.161675+00:00</t>
+          <t>2026-08-28T22:51:09.513285+00:00</t>
         </is>
       </c>
       <c r="AD19" t="inlineStr">
@@ -5137,87 +5158,87 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>AMZN</t>
+          <t>VRT</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Amazon.com, Inc.</t>
+          <t>Vertiv Holdings Co</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Internet Retail</t>
+          <t>Electrical Equipment &amp; Parts</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2764100599808</v>
+        <v>98972753920</v>
       </c>
       <c r="F20" t="n">
-        <v>256.260009765625</v>
+        <v>257.0799865722656</v>
       </c>
       <c r="G20" t="n">
-        <v>775680032768</v>
+        <v>11479600128</v>
       </c>
       <c r="H20" t="n">
-        <v>0.196</v>
+        <v>0.241</v>
       </c>
       <c r="I20" t="n">
-        <v>12.25</v>
+        <v>4.42</v>
       </c>
       <c r="J20" t="n">
-        <v>2.423</v>
+        <v>0.53</v>
       </c>
       <c r="K20" t="n">
-        <v>3219124992</v>
+        <v>2696537600</v>
       </c>
       <c r="M20" t="n">
-        <v>122988003328</v>
+        <v>3110599936</v>
       </c>
       <c r="N20" t="n">
-        <v>251635007488</v>
+        <v>3338200064</v>
       </c>
       <c r="O20" t="n">
-        <v>0.5077</v>
+        <v>0.38039002</v>
       </c>
       <c r="P20" t="n">
-        <v>0.13689</v>
+        <v>0.20362</v>
       </c>
       <c r="Q20" t="n">
-        <v>20.919184</v>
+        <v>58.16289</v>
       </c>
       <c r="R20" t="n">
-        <v>3.5634546</v>
+        <v>8.62162</v>
       </c>
       <c r="S20" t="n">
-        <v>858.6496661910294</v>
+        <v>36.70364319043799</v>
       </c>
       <c r="T20" t="n">
-        <v>0.1100234301659901</v>
+        <v>0.1526183389113704</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.06474448990647808</v>
+        <v>-0.1855390000205935</v>
       </c>
       <c r="V20" t="n">
-        <v>0.2165780977410052</v>
+        <v>-0.007851449963671819</v>
       </c>
       <c r="W20" t="n">
-        <v>0.118453278748353</v>
+        <v>0.9173299123032923</v>
       </c>
       <c r="X20" t="n">
-        <v>0.0887</v>
+        <v>0.00269</v>
       </c>
       <c r="Y20" t="n">
-        <v>0.68727</v>
+        <v>0.84446</v>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>2026-08-28T06:05:58.127191+00:00</t>
+          <t>2026-08-28T22:51:06.848598+00:00</t>
         </is>
       </c>
       <c r="AD20" t="inlineStr">
@@ -5229,87 +5250,87 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>VRT</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Vertiv Holdings Co</t>
+          <t>Microsoft Corporation</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Electrical Equipment &amp; Parts</t>
+          <t>Software - Infrastructure</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103669612544</v>
+        <v>3813240733696</v>
       </c>
       <c r="F21" t="n">
-        <v>269.2799987792969</v>
+        <v>513.530029296875</v>
       </c>
       <c r="G21" t="n">
-        <v>11479600128</v>
+        <v>331839012864</v>
       </c>
       <c r="H21" t="n">
-        <v>0.241</v>
+        <v>0.177</v>
       </c>
       <c r="I21" t="n">
-        <v>4.52</v>
+        <v>17.93</v>
       </c>
       <c r="J21" t="n">
-        <v>0.53</v>
+        <v>0.317</v>
       </c>
       <c r="K21" t="n">
-        <v>2696537600</v>
+        <v>16545500160</v>
       </c>
       <c r="M21" t="n">
-        <v>3110599936</v>
+        <v>76842999808</v>
       </c>
       <c r="N21" t="n">
-        <v>3338200064</v>
+        <v>128812998656</v>
       </c>
       <c r="O21" t="n">
-        <v>0.38039002</v>
+        <v>0.67944</v>
       </c>
       <c r="P21" t="n">
-        <v>0.20362</v>
+        <v>0.45111</v>
       </c>
       <c r="Q21" t="n">
-        <v>59.575222</v>
+        <v>28.640827</v>
       </c>
       <c r="R21" t="n">
-        <v>9.030768</v>
+        <v>11.491237</v>
       </c>
       <c r="S21" t="n">
-        <v>38.44545410529414</v>
+        <v>230.4699584068663</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.001038725262772044</v>
+        <v>0.3173983684080277</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1427333266750271</v>
+        <v>0.1427166697123534</v>
       </c>
       <c r="V21" t="n">
-        <v>0.02749961543437407</v>
+        <v>0.2835086809884435</v>
       </c>
       <c r="W21" t="n">
-        <v>1.084731548876657</v>
+        <v>0.015923407485678</v>
       </c>
       <c r="X21" t="n">
-        <v>0.00269</v>
+        <v>0.00090000004</v>
       </c>
       <c r="Y21" t="n">
-        <v>0.84448</v>
+        <v>0.75881</v>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>2026-08-28T06:06:03.372533+00:00</t>
+          <t>2026-08-28T22:51:01.614393+00:00</t>
         </is>
       </c>
       <c r="AD21" t="inlineStr">
@@ -5321,12 +5342,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>ASML</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Microsoft Corporation</t>
+          <t>ASML Holding N.V.</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -5336,72 +5357,72 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Software - Infrastructure</t>
+          <t>Semiconductor Equipment &amp; Materials</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>3750346096640</v>
+        <v>651495079936</v>
       </c>
       <c r="F22" t="n">
-        <v>505.0599975585938</v>
+        <v>1696.160034179688</v>
       </c>
       <c r="G22" t="n">
-        <v>331839012864</v>
+        <v>35327500288</v>
       </c>
       <c r="H22" t="n">
-        <v>0.177</v>
+        <v>0.213</v>
       </c>
       <c r="I22" t="n">
-        <v>17.97</v>
+        <v>29.67</v>
       </c>
       <c r="J22" t="n">
-        <v>0.317</v>
+        <v>0.285</v>
       </c>
       <c r="K22" t="n">
-        <v>16545500160</v>
+        <v>8437675008</v>
       </c>
       <c r="M22" t="n">
-        <v>76842999808</v>
+        <v>7581499904</v>
       </c>
       <c r="N22" t="n">
-        <v>128812998656</v>
+        <v>1984400000</v>
       </c>
       <c r="O22" t="n">
-        <v>0.67944</v>
+        <v>0.5273300400000001</v>
       </c>
       <c r="P22" t="n">
-        <v>0.45111</v>
+        <v>0.37057</v>
       </c>
       <c r="Q22" t="n">
-        <v>28.105732</v>
+        <v>57.16751</v>
       </c>
       <c r="R22" t="n">
-        <v>11.301703</v>
+        <v>18.441584</v>
       </c>
       <c r="S22" t="n">
-        <v>226.6686446691255</v>
+        <v>77.21263017576511</v>
       </c>
       <c r="T22" t="n">
-        <v>0.2864135876715517</v>
+        <v>0.0938099157601533</v>
       </c>
       <c r="U22" t="n">
-        <v>0.1850647439607176</v>
+        <v>0.0530728138986476</v>
       </c>
       <c r="V22" t="n">
-        <v>0.2658680717482547</v>
+        <v>0.1627703588159193</v>
       </c>
       <c r="W22" t="n">
-        <v>0.004885073802539441</v>
+        <v>1.236308349157486</v>
       </c>
       <c r="X22" t="n">
-        <v>0.00090000004</v>
+        <v>0.00016000001</v>
       </c>
       <c r="Y22" t="n">
-        <v>0.75881</v>
+        <v>0.20377001</v>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>2026-08-28T06:05:57.001313+00:00</t>
+          <t>2026-08-28T22:51:04.490576+00:00</t>
         </is>
       </c>
       <c r="AD22" t="inlineStr">
@@ -5413,12 +5434,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ASML</t>
+          <t>NET</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>ASML Holding N.V.</t>
+          <t>Cloudflare, Inc.</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -5428,72 +5449,66 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Semiconductor Equipment &amp; Materials</t>
+          <t>Software - Infrastructure</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>666417364992</v>
+        <v>106766942208</v>
       </c>
       <c r="F23" t="n">
-        <v>1735.010009765625</v>
+        <v>299.8399963378906</v>
       </c>
       <c r="G23" t="n">
-        <v>35327500288</v>
+        <v>2512349952</v>
       </c>
       <c r="H23" t="n">
-        <v>0.213</v>
+        <v>0.359</v>
       </c>
       <c r="I23" t="n">
-        <v>29.68</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0.285</v>
+        <v>-0.59</v>
       </c>
       <c r="K23" t="n">
-        <v>8437675008</v>
+        <v>691946368</v>
       </c>
       <c r="M23" t="n">
-        <v>7581499904</v>
+        <v>4162798080</v>
       </c>
       <c r="N23" t="n">
-        <v>1984400000</v>
+        <v>3529349888</v>
       </c>
       <c r="O23" t="n">
-        <v>0.5273300400000001</v>
+        <v>0.72577006</v>
       </c>
       <c r="P23" t="n">
-        <v>0.37057</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>58.45721</v>
+        <v>-0.07603</v>
       </c>
       <c r="R23" t="n">
-        <v>18.863983</v>
+        <v>42.49684</v>
       </c>
       <c r="S23" t="n">
-        <v>78.98116061120518</v>
+        <v>154.2994473930095</v>
       </c>
       <c r="T23" t="n">
-        <v>0.0960611916259122</v>
+        <v>0.1089577295771063</v>
       </c>
       <c r="U23" t="n">
-        <v>0.08188216047875851</v>
+        <v>0.2399304741393127</v>
       </c>
       <c r="V23" t="n">
-        <v>0.1405417468216266</v>
+        <v>0.7167066875708403</v>
       </c>
       <c r="W23" t="n">
-        <v>1.268100945254697</v>
+        <v>0.4049292423877466</v>
       </c>
       <c r="X23" t="n">
-        <v>0.00016000001</v>
+        <v>0.00616</v>
       </c>
       <c r="Y23" t="n">
-        <v>0.20384</v>
+        <v>0.90196</v>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>2026-08-28T06:06:00.568591+00:00</t>
+          <t>2026-08-28T22:51:08.648322+00:00</t>
         </is>
       </c>
       <c r="AD23" t="inlineStr">
@@ -5505,12 +5520,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>PANW</t>
+          <t>SNOW</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Palo Alto Networks, Inc.</t>
+          <t>Snowflake Inc.</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -5520,69 +5535,66 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Software - Infrastructure</t>
+          <t>Software - Application</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>312022761472</v>
+        <v>113684799488</v>
       </c>
       <c r="F24" t="n">
-        <v>382.8500061035156</v>
+        <v>328</v>
       </c>
       <c r="G24" t="n">
-        <v>10606499840</v>
+        <v>5032822784</v>
       </c>
       <c r="H24" t="n">
-        <v>0.311</v>
+        <v>0.335</v>
       </c>
       <c r="I24" t="n">
-        <v>1.3</v>
+        <v>-3.52</v>
       </c>
       <c r="K24" t="n">
-        <v>3579375104</v>
+        <v>1739497728</v>
       </c>
       <c r="M24" t="n">
-        <v>3111000064</v>
+        <v>2954998016</v>
       </c>
       <c r="N24" t="n">
-        <v>2130000000</v>
+        <v>2772094976</v>
       </c>
       <c r="O24" t="n">
-        <v>0.71963996</v>
+        <v>0.67144996</v>
       </c>
       <c r="P24" t="n">
-        <v>-0.02465</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>294.50003</v>
+        <v>-0.22173999</v>
       </c>
       <c r="R24" t="n">
-        <v>29.41807</v>
+        <v>22.588675</v>
       </c>
       <c r="S24" t="n">
-        <v>87.17241205687282</v>
+        <v>65.35495715692018</v>
       </c>
       <c r="T24" t="n">
-        <v>0.20015675894519</v>
+        <v>0.1594203148693532</v>
       </c>
       <c r="U24" t="n">
-        <v>0.4852388657362654</v>
+        <v>0.2835061478499319</v>
       </c>
       <c r="V24" t="n">
-        <v>1.643261638935576</v>
+        <v>0.8952964557216492</v>
       </c>
       <c r="W24" t="n">
-        <v>1.040669499802728</v>
+        <v>0.3609958506224067</v>
       </c>
       <c r="X24" t="n">
-        <v>0.0076</v>
+        <v>0.02962</v>
       </c>
       <c r="Y24" t="n">
-        <v>0.84949994</v>
+        <v>0.81921</v>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>2026-08-28T06:05:56.402224+00:00</t>
+          <t>2026-08-28T22:51:07.742502+00:00</t>
         </is>
       </c>
       <c r="AD24" t="inlineStr">
@@ -5594,12 +5606,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>SMCI</t>
+          <t>PANW</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Super Micro Computer, Inc.</t>
+          <t>Palo Alto Networks, Inc.</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -5609,69 +5621,69 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Computer Hardware</t>
+          <t>Software - Infrastructure</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>24878735360</v>
+        <v>302845853696</v>
       </c>
       <c r="F25" t="n">
-        <v>38.45999908447266</v>
+        <v>371.5899963378906</v>
       </c>
       <c r="G25" t="n">
-        <v>39063072768</v>
+        <v>10606499840</v>
       </c>
       <c r="H25" t="n">
-        <v>0.9320000000000001</v>
+        <v>0.311</v>
       </c>
       <c r="I25" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="J25" t="n">
-        <v>4.094</v>
+        <v>1.15</v>
       </c>
       <c r="K25" t="n">
-        <v>-8231267840</v>
+        <v>3579375104</v>
       </c>
       <c r="M25" t="n">
-        <v>7521474048</v>
+        <v>3111000064</v>
       </c>
       <c r="N25" t="n">
-        <v>9311492096</v>
+        <v>2130000000</v>
       </c>
       <c r="O25" t="n">
-        <v>0.108219996</v>
+        <v>0.71963996</v>
       </c>
       <c r="P25" t="n">
-        <v>0.13382</v>
+        <v>-0.02465</v>
       </c>
       <c r="Q25" t="n">
-        <v>11.4805975</v>
+        <v>323.12173</v>
       </c>
       <c r="R25" t="n">
-        <v>0.6368863</v>
+        <v>28.552855</v>
+      </c>
+      <c r="S25" t="n">
+        <v>84.60858247507105</v>
       </c>
       <c r="T25" t="n">
-        <v>0.3518452742740443</v>
+        <v>0.182842602442747</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.06876513813684082</v>
+        <v>0.3191451351390586</v>
       </c>
       <c r="V25" t="n">
-        <v>0.1446428818767584</v>
+        <v>1.487215605881191</v>
       </c>
       <c r="W25" t="n">
-        <v>-0.1407506584742148</v>
+        <v>0.9452936238440981</v>
       </c>
       <c r="X25" t="n">
-        <v>0.12878999</v>
+        <v>0.0076</v>
       </c>
       <c r="Y25" t="n">
-        <v>0.70584</v>
+        <v>0.84946</v>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>2026-08-28T06:06:03.894138+00:00</t>
+          <t>2026-08-28T22:51:01.115092+00:00</t>
         </is>
       </c>
       <c r="AD25" t="inlineStr">
@@ -5683,12 +5695,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>CRWD</t>
+          <t>SMCI</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>CrowdStrike Holdings, Inc.</t>
+          <t>Super Micro Computer, Inc.</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -5698,69 +5710,69 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Software - Infrastructure</t>
+          <t>Computer Hardware</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>233416196096</v>
+        <v>23986053120</v>
       </c>
       <c r="F26" t="n">
-        <v>227.9600067138672</v>
+        <v>37.08000183105469</v>
       </c>
       <c r="G26" t="n">
-        <v>5094199808</v>
+        <v>39063072768</v>
       </c>
       <c r="H26" t="n">
-        <v>0.256</v>
+        <v>0.9320000000000001</v>
       </c>
       <c r="I26" t="n">
-        <v>0.07000000000000001</v>
+        <v>3.26</v>
+      </c>
+      <c r="J26" t="n">
+        <v>4.094</v>
       </c>
       <c r="K26" t="n">
-        <v>1926365056</v>
+        <v>-8231267840</v>
       </c>
       <c r="M26" t="n">
-        <v>4552800768</v>
+        <v>7521474048</v>
       </c>
       <c r="N26" t="n">
-        <v>821342976</v>
+        <v>9311492096</v>
       </c>
       <c r="O26" t="n">
-        <v>0.75136</v>
+        <v>0.108219996</v>
       </c>
       <c r="P26" t="n">
-        <v>-0.022079999</v>
+        <v>0.13382</v>
       </c>
       <c r="Q26" t="n">
-        <v>3256.5715</v>
+        <v>11.374234</v>
       </c>
       <c r="R26" t="n">
-        <v>45.819992</v>
-      </c>
-      <c r="S26" t="n">
-        <v>121.1692432693297</v>
+        <v>0.61403394</v>
       </c>
       <c r="T26" t="n">
-        <v>0.2539054064205257</v>
+        <v>0.4428015848359703</v>
       </c>
       <c r="U26" t="n">
-        <v>0.3589270146877328</v>
+        <v>-0.1954870534108103</v>
       </c>
       <c r="V26" t="n">
-        <v>1.509812647554268</v>
+        <v>0.1486989849217821</v>
       </c>
       <c r="W26" t="n">
-        <v>1.157639569488458</v>
+        <v>-0.1566977302335008</v>
       </c>
       <c r="X26" t="n">
-        <v>0.01467</v>
+        <v>0.12878999</v>
       </c>
       <c r="Y26" t="n">
-        <v>0.76657</v>
+        <v>0.70585996</v>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>2026-08-28T06:05:55.802307+00:00</t>
+          <t>2026-08-28T22:51:07.289444+00:00</t>
         </is>
       </c>
       <c r="AD26" t="inlineStr">
@@ -5791,10 +5803,10 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>272563929088</v>
+        <v>255305072640</v>
       </c>
       <c r="F27" t="n">
-        <v>255.2100067138672</v>
+        <v>239.0500030517578</v>
       </c>
       <c r="G27" t="n">
         <v>5155999744</v>
@@ -5803,7 +5815,7 @@
         <v>0.224</v>
       </c>
       <c r="I27" t="n">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="J27" t="n">
         <v>1.083</v>
@@ -5824,35 +5836,35 @@
         <v>0.07603</v>
       </c>
       <c r="Q27" t="n">
-        <v>255.21</v>
+        <v>246.4433</v>
       </c>
       <c r="R27" t="n">
-        <v>52.86345</v>
+        <v>49.516113</v>
       </c>
       <c r="S27" t="n">
-        <v>204.2442380096033</v>
+        <v>191.3114115863358</v>
       </c>
       <c r="T27" t="n">
-        <v>0.04278009718764819</v>
+        <v>0.06296413224482911</v>
       </c>
       <c r="U27" t="n">
-        <v>-0.2387925699384323</v>
+        <v>-0.3233604198535892</v>
       </c>
       <c r="V27" t="n">
-        <v>0.9372248069862874</v>
+        <v>0.8493734582289156</v>
       </c>
       <c r="W27" t="n">
-        <v>0.8143750893603523</v>
+        <v>0.6769554397341</v>
       </c>
       <c r="X27" t="n">
         <v>0.0007</v>
       </c>
       <c r="Y27" t="n">
-        <v>0.96185</v>
+        <v>0.96182996</v>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>2026-08-28T06:06:01.107925+00:00</t>
+          <t>2026-08-28T22:51:04.986785+00:00</t>
         </is>
       </c>
       <c r="AD27" t="inlineStr">
@@ -5864,12 +5876,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>MRVL</t>
+          <t>CRWD</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Marvell Technology, Inc.</t>
+          <t>CrowdStrike Holdings, Inc.</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -5879,72 +5891,69 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Semiconductors</t>
+          <t>Software - Infrastructure</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>216992235520</v>
+        <v>223627362304</v>
       </c>
       <c r="F28" t="n">
-        <v>241.4499969482422</v>
+        <v>218.3999938964844</v>
       </c>
       <c r="G28" t="n">
-        <v>8717100032</v>
+        <v>5396145152</v>
       </c>
       <c r="H28" t="n">
-        <v>0.276</v>
+        <v>0.258</v>
       </c>
       <c r="I28" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="J28" t="n">
-        <v>-0.804</v>
+        <v>0.05</v>
       </c>
       <c r="K28" t="n">
-        <v>2269700096</v>
+        <v>1995385472</v>
       </c>
       <c r="M28" t="n">
-        <v>3843599872</v>
+        <v>5013847040</v>
       </c>
       <c r="N28" t="n">
-        <v>5277199872</v>
+        <v>820179008</v>
       </c>
       <c r="O28" t="n">
-        <v>0.5150299699999999</v>
+        <v>0.75185996</v>
       </c>
       <c r="P28" t="n">
-        <v>0.14479999</v>
+        <v>-0.02259</v>
       </c>
       <c r="Q28" t="n">
-        <v>82.688354</v>
+        <v>4368</v>
       </c>
       <c r="R28" t="n">
-        <v>24.89271</v>
+        <v>41.44206</v>
       </c>
       <c r="S28" t="n">
-        <v>95.60392401728127</v>
+        <v>112.0722614462335</v>
       </c>
       <c r="T28" t="n">
-        <v>0.3839055153258693</v>
+        <v>0.2175269704065586</v>
       </c>
       <c r="U28" t="n">
-        <v>0.1790732009441129</v>
+        <v>0.1950752059999146</v>
       </c>
       <c r="V28" t="n">
-        <v>1.986041509567837</v>
+        <v>1.292311628430275</v>
       </c>
       <c r="W28" t="n">
-        <v>2.235250869093278</v>
+        <v>0.9764705329998586</v>
       </c>
       <c r="X28" t="n">
-        <v>0.00494</v>
+        <v>0.014579999</v>
       </c>
       <c r="Y28" t="n">
-        <v>0.82141995</v>
+        <v>0.76237</v>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>2026-08-28T06:06:01.698064+00:00</t>
+          <t>2026-08-28T22:51:00.572730+00:00</t>
         </is>
       </c>
       <c r="AD28" t="inlineStr">
@@ -5975,10 +5984,10 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1454880718848</v>
+        <v>1472509509632</v>
       </c>
       <c r="F29" t="n">
-        <v>571.0999755859375</v>
+        <v>578.02001953125</v>
       </c>
       <c r="G29" t="n">
         <v>228246994944</v>
@@ -5987,7 +5996,7 @@
         <v>0.28</v>
       </c>
       <c r="I29" t="n">
-        <v>26.33</v>
+        <v>26.56</v>
       </c>
       <c r="J29" t="n">
         <v>-0.134</v>
@@ -6008,35 +6017,35 @@
         <v>0.34827</v>
       </c>
       <c r="Q29" t="n">
-        <v>21.690086</v>
+        <v>21.762802</v>
       </c>
       <c r="R29" t="n">
-        <v>6.3741508</v>
+        <v>6.451386</v>
       </c>
       <c r="S29" t="n">
-        <v>67.50051153381183</v>
+        <v>68.31841528373901</v>
       </c>
       <c r="T29" t="n">
-        <v>-0.03759626323833276</v>
+        <v>-0.01296078620612318</v>
       </c>
       <c r="U29" t="n">
-        <v>-0.1002072997156541</v>
+        <v>-0.08530182408797538</v>
       </c>
       <c r="V29" t="n">
-        <v>-0.1247859528778774</v>
+        <v>-0.1186571598612787</v>
       </c>
       <c r="W29" t="n">
-        <v>-0.233359541017046</v>
+        <v>-0.2279233366030805</v>
       </c>
       <c r="X29" t="n">
         <v>0.00148</v>
       </c>
       <c r="Y29" t="n">
-        <v>0.79038</v>
+        <v>0.79037005</v>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>2026-08-28T06:05:58.759724+00:00</t>
+          <t>2026-08-28T22:51:03.026009+00:00</t>
         </is>
       </c>
       <c r="AD29" t="inlineStr">
@@ -6067,10 +6076,10 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>143117516800</v>
+        <v>149610184704</v>
       </c>
       <c r="F30" t="n">
-        <v>138.4299926757812</v>
+        <v>144.7100067138672</v>
       </c>
       <c r="G30" t="n">
         <v>14732000256</v>
@@ -6079,7 +6088,7 @@
         <v>0.24</v>
       </c>
       <c r="I30" t="n">
-        <v>1.76</v>
+        <v>1.61</v>
       </c>
       <c r="J30" t="n">
         <v>-0.219</v>
@@ -6100,35 +6109,35 @@
         <v>0.04063</v>
       </c>
       <c r="Q30" t="n">
-        <v>78.65340399999999</v>
+        <v>89.88199</v>
       </c>
       <c r="R30" t="n">
-        <v>9.714738000000001</v>
+        <v>10.155457</v>
       </c>
       <c r="S30" t="n">
-        <v>27.7931821759022</v>
+        <v>29.05404741377296</v>
       </c>
       <c r="T30" t="n">
-        <v>0.2514010959926369</v>
+        <v>0.2500864205545481</v>
       </c>
       <c r="U30" t="n">
-        <v>0.2731535767671225</v>
+        <v>0.1635442913733003</v>
       </c>
       <c r="V30" t="n">
-        <v>0.3281203896898139</v>
+        <v>0.3239707472408886</v>
       </c>
       <c r="W30" t="n">
-        <v>-0.2205342569691323</v>
+        <v>-0.2208162515468708</v>
       </c>
       <c r="X30" t="n">
         <v>0.00176</v>
       </c>
       <c r="Y30" t="n">
-        <v>0.8513700400000001</v>
+        <v>0.85128</v>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>2026-08-28T06:06:06.024445+00:00</t>
+          <t>2026-08-28T22:51:09.083412+00:00</t>
         </is>
       </c>
       <c r="AD30" t="inlineStr">
@@ -6159,10 +6168,10 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>437658779648</v>
+        <v>434519080960</v>
       </c>
       <c r="F31" t="n">
-        <v>151.9400024414062</v>
+        <v>150.8500061035156</v>
       </c>
       <c r="G31" t="n">
         <v>67356999680</v>
@@ -6171,7 +6180,7 @@
         <v>0.206</v>
       </c>
       <c r="I31" t="n">
-        <v>5.96</v>
+        <v>5.83</v>
       </c>
       <c r="J31" t="n">
         <v>0.219</v>
@@ -6192,32 +6201,32 @@
         <v>0.36202</v>
       </c>
       <c r="Q31" t="n">
-        <v>25.493288</v>
+        <v>25.874786</v>
       </c>
       <c r="R31" t="n">
-        <v>6.497599</v>
+        <v>6.4509864</v>
       </c>
       <c r="T31" t="n">
-        <v>0.2665888929726827</v>
+        <v>0.281212916939712</v>
       </c>
       <c r="U31" t="n">
-        <v>-0.2515041830280843</v>
+        <v>-0.3295472987237595</v>
       </c>
       <c r="V31" t="n">
-        <v>0.03456025158076947</v>
+        <v>0.01060149055477</v>
       </c>
       <c r="W31" t="n">
-        <v>-0.3483237999961911</v>
+        <v>-0.3651408526453519</v>
       </c>
       <c r="X31" t="n">
         <v>0.40498</v>
       </c>
       <c r="Y31" t="n">
-        <v>0.45823002</v>
+        <v>0.45821</v>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>2026-08-28T06:05:59.335968+00:00</t>
+          <t>2026-08-28T22:51:03.517487+00:00</t>
         </is>
       </c>
       <c r="AD31" t="inlineStr">
@@ -6245,7 +6254,7 @@
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
@@ -6302,27 +6311,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>MU</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>84.2</v>
+        <v>100</v>
       </c>
       <c r="C2" t="n">
-        <v>88.2</v>
+        <v>100</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>MODERATE</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>price_to_sales, price_to_fcf</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -6336,11 +6340,11 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>MU</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="C3" t="n">
         <v>100</v>
@@ -6351,7 +6355,7 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -6452,7 +6456,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>DELL</t>
+          <t>TER</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -6510,7 +6514,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>TER</t>
+          <t>DELL</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -6539,23 +6543,18 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>PATH</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>94.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="C10" t="n">
-        <v>94.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
           <t>HIGH</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>eps_growth</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -6573,18 +6572,23 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>PATH</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>100</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="C11" t="n">
-        <v>100</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
           <t>HIGH</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>eps_growth</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -6602,7 +6606,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>MRVL</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -6631,7 +6635,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AMAT</t>
+          <t>GOOGL</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -6660,11 +6664,11 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>DDOG</t>
+          <t>AMAT</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="C14" t="n">
         <v>100</v>
@@ -6675,7 +6679,7 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -6718,27 +6722,22 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>MDB</t>
+          <t>DDOG</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>88.2</v>
+        <v>96</v>
       </c>
       <c r="C16" t="n">
-        <v>88.2</v>
+        <v>100</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>eps_growth, pe_ratio</t>
-        </is>
-      </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -6752,14 +6751,14 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>SNOW</t>
+          <t>ACMR</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>88.2</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="C17" t="n">
-        <v>88.2</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -6768,7 +6767,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>eps_growth, pe_ratio</t>
+          <t>price_to_fcf</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -6786,23 +6785,18 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>NET</t>
+          <t>AMZN</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>88.2</v>
+        <v>100</v>
       </c>
       <c r="C18" t="n">
-        <v>88.2</v>
+        <v>100</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
           <t>HIGH</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>eps_growth, pe_ratio</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -6820,14 +6814,14 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ACMR</t>
+          <t>MDB</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>94.09999999999999</v>
+        <v>88.2</v>
       </c>
       <c r="C19" t="n">
-        <v>94.09999999999999</v>
+        <v>88.2</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -6836,7 +6830,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>price_to_fcf</t>
+          <t>eps_growth, pe_ratio</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -6854,7 +6848,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>AMZN</t>
+          <t>VRT</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -6883,7 +6877,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>VRT</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -6912,7 +6906,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>ASML</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -6941,18 +6935,23 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ASML</t>
+          <t>NET</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>100</v>
+        <v>88.2</v>
       </c>
       <c r="C23" t="n">
-        <v>100</v>
+        <v>88.2</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
           <t>HIGH</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>eps_growth, pe_ratio</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -6970,14 +6969,14 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>PANW</t>
+          <t>SNOW</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>94.09999999999999</v>
+        <v>88.2</v>
       </c>
       <c r="C24" t="n">
-        <v>94.09999999999999</v>
+        <v>88.2</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -6986,7 +6985,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>eps_growth</t>
+          <t>eps_growth, pe_ratio</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -7004,7 +7003,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>SMCI</t>
+          <t>PANW</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -7020,7 +7019,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>price_to_fcf</t>
+          <t>eps_growth</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -7038,7 +7037,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>CRWD</t>
+          <t>SMCI</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -7054,7 +7053,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>eps_growth</t>
+          <t>price_to_fcf</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -7101,18 +7100,23 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>MRVL</t>
+          <t>CRWD</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>100</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="C28" t="n">
-        <v>100</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
           <t>HIGH</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>eps_growth</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -7288,11 +7292,11 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>MU</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>56.77</v>
+        <v>55.79</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -7305,7 +7309,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>84.2</v>
+        <v>100</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>

--- a/reports/investment_dashboard.xlsx
+++ b/reports/investment_dashboard.xlsx
@@ -534,7 +534,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>55.79</v>
+        <v>55.21</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>417.5199890136719</v>
+        <v>415.3200073242188</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -581,7 +581,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>54.85</v>
+        <v>54.15</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -589,7 +589,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>932.8599853515625</v>
+        <v>958.72998046875</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>53.57</v>
+        <v>52.71</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>232.75</v>
+        <v>226.1900024414062</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -685,7 +685,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>52.9</v>
+        <v>51.86</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -693,7 +693,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>195.3800048828125</v>
+        <v>195.6900024414062</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -708,7 +708,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Revenue Growth; Earnings Fcf; Balance Sheet; Momentum</t>
+          <t>Revenue Growth; Earnings Fcf; Balance Sheet</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -737,7 +737,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>51.78</v>
+        <v>51.64</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -745,7 +745,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>186.2899932861328</v>
+        <v>186.3800048828125</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -780,16 +780,16 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>TER</t>
+          <t>NVDA</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Teradyne, Inc.</t>
+          <t>NVIDIA Corporation</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>50.85</v>
+        <v>50.86</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>354.9700012207031</v>
+        <v>220.7799987792969</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -818,6 +818,11 @@
       <c r="K7" t="inlineStr">
         <is>
           <t>Industry Growth; Valuation; Competitive Advantage; Catalysts; Inflation Resilience</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>High market sensitivity / beta</t>
         </is>
       </c>
     </row>
@@ -827,16 +832,16 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>NVDA</t>
+          <t>TER</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>NVIDIA Corporation</t>
+          <t>Teradyne, Inc.</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>50.72</v>
+        <v>50.31</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -844,7 +849,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>217.5500030517578</v>
+        <v>349.8299865722656</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -865,11 +870,6 @@
       <c r="K8" t="inlineStr">
         <is>
           <t>Industry Growth; Valuation; Competitive Advantage; Catalysts; Inflation Resilience</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>High market sensitivity / beta</t>
         </is>
       </c>
     </row>
@@ -888,7 +888,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>49.99</v>
+        <v>49.01</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>456.239990234375</v>
+        <v>456.010009765625</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -926,16 +926,16 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>PATH</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Advanced Micro Devices, Inc.</t>
+          <t>UiPath, Inc.</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>47.76</v>
+        <v>47.52</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -943,32 +943,27 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>465.5799865722656</v>
+        <v>18.67000007629395</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>100</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="I10" t="n">
-        <v>100</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Revenue Growth; Earnings Fcf; Balance Sheet</t>
+          <t>Balance Sheet; Momentum</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Industry Growth; Valuation; Competitive Advantage; Catalysts; Inflation Resilience</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>Very high earnings multiple; High market sensitivity / beta</t>
+          <t>Industry Growth; Competitive Advantage; Catalysts; Inflation Resilience</t>
         </is>
       </c>
     </row>
@@ -978,16 +973,16 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>PATH</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>UiPath, Inc.</t>
+          <t>Advanced Micro Devices, Inc.</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>47.68</v>
+        <v>47.41</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -995,27 +990,32 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>18.14999961853027</v>
+        <v>470.7200012207031</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>94.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="I11" t="n">
-        <v>94.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Balance Sheet; Momentum</t>
+          <t>Revenue Growth; Earnings Fcf; Balance Sheet</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Industry Growth; Competitive Advantage; Catalysts; Inflation Resilience</t>
+          <t>Industry Growth; Valuation; Competitive Advantage; Catalysts; Inflation Resilience</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>Very high earnings multiple; High market sensitivity / beta</t>
         </is>
       </c>
     </row>
@@ -1025,16 +1025,16 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>MRVL</t>
+          <t>GOOGL</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Marvell Technology, Inc.</t>
+          <t>Alphabet Inc.</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>47.51</v>
+        <v>46.58</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -1042,7 +1042,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>216.6199951171875</v>
+        <v>339.3500061035156</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -1057,17 +1057,12 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Revenue Growth; Earnings Fcf; Momentum</t>
+          <t>Earnings Fcf; Balance Sheet</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Industry Growth; Valuation; Competitive Advantage; Catalysts; Inflation Resilience</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>Excessive price-to-sales valuation</t>
+          <t>Industry Growth; Competitive Advantage; Catalysts; Inflation Resilience</t>
         </is>
       </c>
     </row>
@@ -1077,16 +1072,16 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>MRVL</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Alphabet Inc.</t>
+          <t>Marvell Technology, Inc.</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>47.05</v>
+        <v>46.32</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -1094,11 +1089,11 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>346.5899963378906</v>
+        <v>211.6600036621094</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="H13" t="n">
@@ -1109,12 +1104,17 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Earnings Fcf; Balance Sheet</t>
+          <t>Revenue Growth; Earnings Fcf</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Industry Growth; Competitive Advantage; Catalysts; Inflation Resilience</t>
+          <t>Industry Growth; Valuation; Competitive Advantage; Catalysts; Inflation Resilience</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>Excessive price-to-sales valuation; High market sensitivity / beta</t>
         </is>
       </c>
     </row>
@@ -1133,7 +1133,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>45.81</v>
+        <v>45.04</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -1141,7 +1141,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>461.6700134277344</v>
+        <v>458.3900146484375</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -1180,7 +1180,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>44.36</v>
+        <v>44.44</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>368.7900085449219</v>
+        <v>370.3399963378906</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -1232,7 +1232,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>44.29</v>
+        <v>43.77</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>236.9799957275391</v>
+        <v>237.0399932861328</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1275,16 +1275,16 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>ACMR</t>
+          <t>VRT</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>ACM Research, Inc.</t>
+          <t>Vertiv Holdings Co</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>43.55</v>
+        <v>42.95</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>74.41999816894531</v>
+        <v>258.7200012207031</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1300,24 +1300,24 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>94.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="I17" t="n">
-        <v>94.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Revenue Growth</t>
+          <t>Earnings Fcf</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Industry Growth; Competitive Advantage; Catalysts; Inflation Resilience</t>
+          <t>Industry Growth; Valuation; Competitive Advantage; Catalysts; Inflation Resilience</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>Negative free cash flow / unprofitable growth</t>
+          <t>High market sensitivity / beta</t>
         </is>
       </c>
     </row>
@@ -1327,16 +1327,16 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>AMZN</t>
+          <t>ACMR</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Amazon.com, Inc.</t>
+          <t>ACM Research, Inc.</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>43.49</v>
+        <v>42.82</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>266.4299926757812</v>
+        <v>72.81999969482422</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1352,19 +1352,24 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>100</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="I18" t="n">
-        <v>100</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Earnings Fcf</t>
+          <t>Revenue Growth</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
           <t>Industry Growth; Competitive Advantage; Catalysts; Inflation Resilience</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>Negative free cash flow / unprofitable growth</t>
         </is>
       </c>
     </row>
@@ -1374,16 +1379,16 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>MDB</t>
+          <t>AMZN</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>MongoDB, Inc.</t>
+          <t>Amazon.com, Inc.</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>43.26</v>
+        <v>42.31</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -1391,7 +1396,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>446.6199951171875</v>
+        <v>259.7699890136719</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1399,19 +1404,19 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>88.2</v>
+        <v>100</v>
       </c>
       <c r="I19" t="n">
-        <v>88.2</v>
+        <v>100</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Balance Sheet; Momentum</t>
+          <t>Earnings Fcf</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Industry Growth; Valuation; Competitive Advantage; Catalysts; Inflation Resilience</t>
+          <t>Industry Growth; Competitive Advantage; Catalysts; Inflation Resilience</t>
         </is>
       </c>
     </row>
@@ -1421,16 +1426,16 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>VRT</t>
+          <t>MDB</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Vertiv Holdings Co</t>
+          <t>MongoDB, Inc.</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>43.25</v>
+        <v>42.28</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -1438,7 +1443,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>257.0799865722656</v>
+        <v>453.3699951171875</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1446,24 +1451,19 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>100</v>
+        <v>88.2</v>
       </c>
       <c r="I20" t="n">
-        <v>100</v>
+        <v>88.2</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Earnings Fcf</t>
+          <t>Balance Sheet; Momentum</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
           <t>Industry Growth; Valuation; Competitive Advantage; Catalysts; Inflation Resilience</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>High market sensitivity / beta</t>
         </is>
       </c>
     </row>
@@ -1473,16 +1473,16 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>ASML</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Microsoft Corporation</t>
+          <t>ASML Holding N.V.</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>42.42</v>
+        <v>42.14</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -1490,7 +1490,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>513.530029296875</v>
+        <v>1696.010009765625</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1505,7 +1505,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Earnings Fcf</t>
+          <t>Earnings Fcf; Balance Sheet</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1520,16 +1520,16 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>ASML</t>
+          <t>SNOW</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>ASML Holding N.V.</t>
+          <t>Snowflake Inc.</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>42.38</v>
+        <v>41.81</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -1537,7 +1537,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1696.160034179688</v>
+        <v>331.4299926757812</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1545,19 +1545,24 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>100</v>
+        <v>88.2</v>
       </c>
       <c r="I22" t="n">
-        <v>100</v>
+        <v>88.2</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Earnings Fcf; Balance Sheet</t>
+          <t>Revenue Growth</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
           <t>Industry Growth; Valuation; Competitive Advantage; Catalysts; Inflation Resilience</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>Excessive price-to-sales valuation</t>
         </is>
       </c>
     </row>
@@ -1576,7 +1581,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>42.36</v>
+        <v>41.76</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -1584,7 +1589,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>299.8399963378906</v>
+        <v>305.1099853515625</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1619,16 +1624,16 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>SNOW</t>
+          <t>SMCI</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Snowflake Inc.</t>
+          <t>Super Micro Computer, Inc.</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>42.27</v>
+        <v>41.57</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -1636,7 +1641,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>328</v>
+        <v>37.27999877929688</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1644,24 +1649,24 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>88.2</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="I24" t="n">
-        <v>88.2</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Revenue Growth; Momentum</t>
+          <t>Revenue Growth; Valuation</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>Industry Growth; Valuation; Competitive Advantage; Catalysts; Inflation Resilience</t>
+          <t>Industry Growth; Balance Sheet; Competitive Advantage; Momentum; Catalysts; Inflation Resilience</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>Excessive price-to-sales valuation</t>
+          <t>Negative free cash flow / unprofitable growth</t>
         </is>
       </c>
     </row>
@@ -1680,7 +1685,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>41.77</v>
+        <v>41.4</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -1688,7 +1693,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>371.5899963378906</v>
+        <v>382.1300048828125</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1723,16 +1728,16 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>SMCI</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Super Micro Computer, Inc.</t>
+          <t>Microsoft Corporation</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>41.75</v>
+        <v>41.32</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -1740,7 +1745,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>37.08000183105469</v>
+        <v>507.2900085449219</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1748,24 +1753,19 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>94.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="I26" t="n">
-        <v>94.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Revenue Growth; Valuation</t>
+          <t>Earnings Fcf</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>Industry Growth; Balance Sheet; Competitive Advantage; Momentum; Catalysts; Inflation Resilience</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>Negative free cash flow / unprofitable growth</t>
+          <t>Industry Growth; Valuation; Competitive Advantage; Catalysts; Inflation Resilience</t>
         </is>
       </c>
     </row>
@@ -1784,7 +1784,7 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>40.9</v>
+        <v>40.64</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -1792,7 +1792,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>239.0500030517578</v>
+        <v>241.9100036621094</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1836,7 +1836,7 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>40.37</v>
+        <v>40.25</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>218.3999938964844</v>
+        <v>231</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1888,7 +1888,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>39.74</v>
+        <v>40.16</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -1896,7 +1896,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>578.02001953125</v>
+        <v>572.3400268554688</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>35.73</v>
+        <v>35.86</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -1943,7 +1943,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>144.7100067138672</v>
+        <v>147.9900054931641</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1977,7 +1977,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>31.54</v>
+        <v>31.11</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -1985,7 +1985,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>150.8500061035156</v>
+        <v>149.1199951171875</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -2131,13 +2131,13 @@
         <v>8.84</v>
       </c>
       <c r="F2" t="n">
-        <v>8.68</v>
+        <v>8.69</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>5.58</v>
+        <v>4.99</v>
       </c>
       <c r="I2" t="n">
         <v>2.69</v>
@@ -2149,7 +2149,7 @@
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>55.79</v>
+        <v>55.21</v>
       </c>
     </row>
     <row r="3">
@@ -2171,13 +2171,13 @@
         <v>9.02</v>
       </c>
       <c r="F3" t="n">
-        <v>4.95</v>
+        <v>4.85</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>7.38</v>
+        <v>6.78</v>
       </c>
       <c r="I3" t="n">
         <v>3.5</v>
@@ -2189,7 +2189,7 @@
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>54.85</v>
+        <v>54.15</v>
       </c>
     </row>
     <row r="4">
@@ -2211,13 +2211,13 @@
         <v>9.91</v>
       </c>
       <c r="F4" t="n">
-        <v>2.4</v>
+        <v>2.47</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>7.72</v>
+        <v>6.79</v>
       </c>
       <c r="I4" t="n">
         <v>3.54</v>
@@ -2229,7 +2229,7 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>53.57</v>
+        <v>52.71</v>
       </c>
     </row>
     <row r="5">
@@ -2257,7 +2257,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>8.460000000000001</v>
+        <v>7.42</v>
       </c>
       <c r="I5" t="n">
         <v>3.63</v>
@@ -2269,7 +2269,7 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>52.9</v>
+        <v>51.86</v>
       </c>
     </row>
     <row r="6">
@@ -2297,7 +2297,7 @@
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>7.9</v>
+        <v>7.76</v>
       </c>
       <c r="I6" t="n">
         <v>3.35</v>
@@ -2309,13 +2309,13 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>51.78</v>
+        <v>51.64</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>TER</t>
+          <t>NVDA</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -2328,19 +2328,19 @@
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>8.9</v>
+        <v>8.08</v>
       </c>
       <c r="F7" t="n">
-        <v>3.08</v>
+        <v>3.88</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>5.12</v>
+        <v>5.46</v>
       </c>
       <c r="I7" t="n">
-        <v>3.75</v>
+        <v>3.44</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -2349,13 +2349,13 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>50.85</v>
+        <v>50.86</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>NVDA</t>
+          <t>TER</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -2368,19 +2368,19 @@
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>8.08</v>
+        <v>8.9</v>
       </c>
       <c r="F8" t="n">
-        <v>3.91</v>
+        <v>3.15</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>5.29</v>
+        <v>4.51</v>
       </c>
       <c r="I8" t="n">
-        <v>3.44</v>
+        <v>3.75</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -2389,7 +2389,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>50.72</v>
+        <v>50.31</v>
       </c>
     </row>
     <row r="9">
@@ -2417,7 +2417,7 @@
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>7.82</v>
+        <v>6.84</v>
       </c>
       <c r="I9" t="n">
         <v>3.54</v>
@@ -2429,38 +2429,38 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>49.99</v>
+        <v>49.01</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>PATH</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>15</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="C10" t="n">
-        <v>12.88</v>
+        <v>9.32</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>8.77</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="F10" t="n">
-        <v>1.36</v>
+        <v>6.39</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>6.3</v>
+        <v>10</v>
       </c>
       <c r="I10" t="n">
-        <v>3.45</v>
+        <v>3.75</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -2469,38 +2469,38 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>47.76</v>
+        <v>47.52</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>PATH</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>8.359999999999999</v>
+        <v>15</v>
       </c>
       <c r="C11" t="n">
-        <v>9.32</v>
+        <v>12.88</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>9.699999999999999</v>
+        <v>8.77</v>
       </c>
       <c r="F11" t="n">
-        <v>6.55</v>
+        <v>1.35</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>10</v>
+        <v>5.96</v>
       </c>
       <c r="I11" t="n">
-        <v>3.75</v>
+        <v>3.45</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -2509,35 +2509,35 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>47.68</v>
+        <v>47.41</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>MRVL</t>
+          <t>GOOGL</t>
         </is>
       </c>
       <c r="B12" t="n">
+        <v>10.95</v>
+      </c>
+      <c r="C12" t="n">
         <v>15</v>
       </c>
-      <c r="C12" t="n">
-        <v>12.78</v>
-      </c>
       <c r="D12" t="n">
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>7.21</v>
+        <v>8.34</v>
       </c>
       <c r="F12" t="n">
-        <v>0.89</v>
+        <v>4.46</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>8.1</v>
+        <v>4.3</v>
       </c>
       <c r="I12" t="n">
         <v>3.53</v>
@@ -2549,35 +2549,35 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>47.51</v>
+        <v>46.58</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>MRVL</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>10.95</v>
+        <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>15</v>
+        <v>12.88</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>8.34</v>
+        <v>7.21</v>
       </c>
       <c r="F13" t="n">
-        <v>4.37</v>
+        <v>0.91</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>4.86</v>
+        <v>6.79</v>
       </c>
       <c r="I13" t="n">
         <v>3.53</v>
@@ -2589,7 +2589,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>47.05</v>
+        <v>46.32</v>
       </c>
     </row>
     <row r="14">
@@ -2611,13 +2611,13 @@
         <v>7.78</v>
       </c>
       <c r="F14" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>5.99</v>
+        <v>5.18</v>
       </c>
       <c r="I14" t="n">
         <v>3.58</v>
@@ -2629,7 +2629,7 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>45.81</v>
+        <v>45.04</v>
       </c>
     </row>
     <row r="15">
@@ -2657,7 +2657,7 @@
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>3.64</v>
+        <v>3.72</v>
       </c>
       <c r="I15" t="n">
         <v>3.53</v>
@@ -2669,7 +2669,7 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>44.36</v>
+        <v>44.44</v>
       </c>
     </row>
     <row r="16">
@@ -2697,7 +2697,7 @@
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>5.7</v>
+        <v>5.18</v>
       </c>
       <c r="I16" t="n">
         <v>3.67</v>
@@ -2709,38 +2709,38 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>44.29</v>
+        <v>43.77</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ACMR</t>
+          <t>VRT</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>15</v>
+        <v>10.91</v>
       </c>
       <c r="C17" t="n">
-        <v>7.83</v>
+        <v>13.39</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>4.02</v>
+        <v>7.41</v>
       </c>
       <c r="F17" t="n">
-        <v>7.14</v>
+        <v>3.42</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>5.93</v>
+        <v>4.26</v>
       </c>
       <c r="I17" t="n">
-        <v>3.63</v>
+        <v>3.56</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2749,38 +2749,38 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>43.55</v>
+        <v>42.95</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>AMZN</t>
+          <t>ACMR</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>9.220000000000001</v>
+        <v>15</v>
       </c>
       <c r="C18" t="n">
-        <v>12.28</v>
+        <v>7.83</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>6.64</v>
+        <v>4.02</v>
       </c>
       <c r="F18" t="n">
-        <v>6.46</v>
+        <v>7.23</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>5.42</v>
+        <v>5.11</v>
       </c>
       <c r="I18" t="n">
-        <v>3.47</v>
+        <v>3.63</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2789,38 +2789,38 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>43.49</v>
+        <v>42.82</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>MDB</t>
+          <t>AMZN</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>11.32</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="C19" t="n">
-        <v>7.5</v>
+        <v>12.28</v>
       </c>
       <c r="D19" t="n">
         <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>9.880000000000001</v>
+        <v>6.64</v>
       </c>
       <c r="F19" t="n">
-        <v>1.52</v>
+        <v>6.51</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>9.31</v>
+        <v>4.19</v>
       </c>
       <c r="I19" t="n">
-        <v>3.73</v>
+        <v>3.47</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2829,38 +2829,38 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>43.26</v>
+        <v>42.31</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>VRT</t>
+          <t>MDB</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>10.91</v>
+        <v>11.32</v>
       </c>
       <c r="C20" t="n">
-        <v>13.39</v>
+        <v>7.5</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>7.41</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="F20" t="n">
-        <v>3.46</v>
+        <v>1.45</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>4.52</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="I20" t="n">
-        <v>3.56</v>
+        <v>3.74</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2869,38 +2869,38 @@
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>43.25</v>
+        <v>42.28</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>ASML</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>8.51</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="C21" t="n">
-        <v>14.63</v>
+        <v>14.28</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>6.87</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="F21" t="n">
-        <v>2.78</v>
+        <v>0.58</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>6.18</v>
+        <v>5.71</v>
       </c>
       <c r="I21" t="n">
-        <v>3.45</v>
+        <v>2.75</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2909,38 +2909,38 @@
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>42.42</v>
+        <v>42.14</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ASML</t>
+          <t>SNOW</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>9.859999999999999</v>
+        <v>14.44</v>
       </c>
       <c r="C22" t="n">
-        <v>14.28</v>
+        <v>7.5</v>
       </c>
       <c r="D22" t="n">
         <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>8.960000000000001</v>
+        <v>7.58</v>
       </c>
       <c r="F22" t="n">
-        <v>0.58</v>
+        <v>0.98</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>5.95</v>
+        <v>7.74</v>
       </c>
       <c r="I22" t="n">
-        <v>2.75</v>
+        <v>3.57</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2949,7 +2949,7 @@
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>42.38</v>
+        <v>41.81</v>
       </c>
     </row>
     <row r="23">
@@ -2971,13 +2971,13 @@
         <v>7.71</v>
       </c>
       <c r="F23" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.55</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>7.95</v>
+        <v>7.36</v>
       </c>
       <c r="I23" t="n">
         <v>3.64</v>
@@ -2989,38 +2989,38 @@
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>42.36</v>
+        <v>41.76</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>SNOW</t>
+          <t>SMCI</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>14.44</v>
+        <v>15</v>
       </c>
       <c r="C24" t="n">
-        <v>7.5</v>
+        <v>7.23</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>7.58</v>
+        <v>2.23</v>
       </c>
       <c r="F24" t="n">
-        <v>0.99</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>8.199999999999999</v>
+        <v>3.69</v>
       </c>
       <c r="I24" t="n">
-        <v>3.56</v>
+        <v>3.54</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -3029,7 +3029,7 @@
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>42.27</v>
+        <v>41.57</v>
       </c>
     </row>
     <row r="25">
@@ -3051,13 +3051,13 @@
         <v>7.97</v>
       </c>
       <c r="F25" t="n">
-        <v>0.54</v>
+        <v>0.53</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>8.65</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="I25" t="n">
         <v>3.57</v>
@@ -3069,38 +3069,38 @@
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>41.77</v>
+        <v>41.4</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>SMCI</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>15</v>
+        <v>8.51</v>
       </c>
       <c r="C26" t="n">
-        <v>7.23</v>
+        <v>14.63</v>
       </c>
       <c r="D26" t="n">
         <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>2.23</v>
+        <v>6.87</v>
       </c>
       <c r="F26" t="n">
-        <v>9.890000000000001</v>
+        <v>2.84</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>3.86</v>
+        <v>5.02</v>
       </c>
       <c r="I26" t="n">
-        <v>3.54</v>
+        <v>3.45</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3109,7 +3109,7 @@
         <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>41.75</v>
+        <v>41.32</v>
       </c>
     </row>
     <row r="27">
@@ -3131,13 +3131,13 @@
         <v>9.449999999999999</v>
       </c>
       <c r="F27" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>5.97</v>
+        <v>5.72</v>
       </c>
       <c r="I27" t="n">
         <v>3.7</v>
@@ -3149,7 +3149,7 @@
         <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>40.9</v>
+        <v>40.64</v>
       </c>
     </row>
     <row r="28">
@@ -3171,13 +3171,13 @@
         <v>9.300000000000001</v>
       </c>
       <c r="F28" t="n">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>8.24</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="I28" t="n">
         <v>3.47</v>
@@ -3189,7 +3189,7 @@
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>40.37</v>
+        <v>40.25</v>
       </c>
     </row>
     <row r="29">
@@ -3211,13 +3211,13 @@
         <v>7.23</v>
       </c>
       <c r="F29" t="n">
-        <v>5.58</v>
+        <v>5.62</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>1.06</v>
+        <v>1.44</v>
       </c>
       <c r="I29" t="n">
         <v>3.49</v>
@@ -3229,7 +3229,7 @@
         <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>39.74</v>
+        <v>40.16</v>
       </c>
     </row>
     <row r="30">
@@ -3251,13 +3251,13 @@
         <v>6.78</v>
       </c>
       <c r="F30" t="n">
-        <v>3.42</v>
+        <v>3.31</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>5.4</v>
+        <v>5.64</v>
       </c>
       <c r="I30" t="n">
         <v>3.57</v>
@@ -3269,7 +3269,7 @@
         <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>35.73</v>
+        <v>35.86</v>
       </c>
     </row>
     <row r="31">
@@ -3291,13 +3291,13 @@
         <v>0.8</v>
       </c>
       <c r="F31" t="n">
-        <v>6.33</v>
+        <v>6.4</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>2.69</v>
+        <v>2.19</v>
       </c>
       <c r="I31" t="n">
         <v>3.58</v>
@@ -3309,7 +3309,7 @@
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>31.54</v>
+        <v>31.11</v>
       </c>
     </row>
   </sheetData>
@@ -3343,13 +3343,13 @@
     <col width="15" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="18" customWidth="1" min="16" max="16"/>
-    <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="11" customWidth="1" min="17" max="17"/>
     <col width="16" customWidth="1" min="18" max="18"/>
     <col width="19" customWidth="1" min="19" max="19"/>
-    <col width="23" customWidth="1" min="20" max="20"/>
-    <col width="22" customWidth="1" min="21" max="21"/>
-    <col width="22" customWidth="1" min="22" max="22"/>
-    <col width="21" customWidth="1" min="23" max="23"/>
+    <col width="22" customWidth="1" min="20" max="20"/>
+    <col width="23" customWidth="1" min="21" max="21"/>
+    <col width="21" customWidth="1" min="22" max="22"/>
+    <col width="22" customWidth="1" min="23" max="23"/>
     <col width="18" customWidth="1" min="24" max="24"/>
     <col width="24" customWidth="1" min="25" max="25"/>
     <col width="17" customWidth="1" min="26" max="26"/>
@@ -3533,10 +3533,10 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2165456502784</v>
+        <v>2154046423040</v>
       </c>
       <c r="F2" t="n">
-        <v>417.5199890136719</v>
+        <v>415.3200073242188</v>
       </c>
       <c r="G2" t="n">
         <v>4440492343296</v>
@@ -3545,7 +3545,7 @@
         <v>0.36</v>
       </c>
       <c r="I2" t="n">
-        <v>13.42</v>
+        <v>13.44</v>
       </c>
       <c r="J2" t="n">
         <v>0.774</v>
@@ -3566,35 +3566,35 @@
         <v>0.60344005</v>
       </c>
       <c r="Q2" t="n">
-        <v>31.111773</v>
+        <v>30.901787</v>
       </c>
       <c r="R2" t="n">
-        <v>0.48766136</v>
+        <v>0.4850918</v>
       </c>
       <c r="S2" t="n">
-        <v>2.963026026945206</v>
+        <v>2.947413446776762</v>
       </c>
       <c r="T2" t="n">
-        <v>0.1143672406390812</v>
+        <v>0.02738406264494442</v>
       </c>
       <c r="U2" t="n">
-        <v>0.000114110405947887</v>
+        <v>-0.044389470032138</v>
       </c>
       <c r="V2" t="n">
-        <v>0.113762876766069</v>
+        <v>0.1144900263701596</v>
       </c>
       <c r="W2" t="n">
-        <v>0.7716772783500616</v>
+        <v>0.8188297145954699</v>
       </c>
       <c r="X2" t="n">
         <v>0.00013</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.15493</v>
+        <v>0.15494001</v>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>2026-08-28T22:51:03.998625+00:00</t>
+          <t>2026-08-31T22:50:49.888808+00:00</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
@@ -3625,10 +3625,10 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1053565648896</v>
+        <v>1082783105024</v>
       </c>
       <c r="F3" t="n">
-        <v>932.8599853515625</v>
+        <v>958.72998046875</v>
       </c>
       <c r="G3" t="n">
         <v>90273996800</v>
@@ -3637,7 +3637,7 @@
         <v>3.457</v>
       </c>
       <c r="I3" t="n">
-        <v>44.24</v>
+        <v>44.22</v>
       </c>
       <c r="J3" t="n">
         <v>13.685</v>
@@ -3658,35 +3658,35 @@
         <v>0.80370003</v>
       </c>
       <c r="Q3" t="n">
-        <v>21.086346</v>
+        <v>21.680912</v>
       </c>
       <c r="R3" t="n">
-        <v>11.670754</v>
+        <v>11.994408</v>
       </c>
       <c r="S3" t="n">
-        <v>137.9102925306506</v>
+        <v>141.7348173012107</v>
       </c>
       <c r="T3" t="n">
-        <v>0.2623274497314783</v>
+        <v>0.1648784933009129</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.03913137451813475</v>
+        <v>-0.07399576867898083</v>
       </c>
       <c r="V3" t="n">
-        <v>1.246114648857811</v>
+        <v>1.326261002670978</v>
       </c>
       <c r="W3" t="n">
-        <v>6.658666224370205</v>
+        <v>7.068806989239613</v>
       </c>
       <c r="X3" t="n">
         <v>0.00238</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.79977</v>
+        <v>0.79989</v>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>2026-08-28T22:50:58.770573+00:00</t>
+          <t>2026-08-31T22:50:46.301421+00:00</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
@@ -3717,10 +3717,10 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>43741794304</v>
+        <v>42508943360</v>
       </c>
       <c r="F4" t="n">
-        <v>232.75</v>
+        <v>226.1900024414062</v>
       </c>
       <c r="G4" t="n">
         <v>1335116032</v>
@@ -3729,7 +3729,7 @@
         <v>1.57</v>
       </c>
       <c r="I4" t="n">
-        <v>2.5</v>
+        <v>2.51</v>
       </c>
       <c r="J4" t="n">
         <v>3.432</v>
@@ -3750,35 +3750,35 @@
         <v>0.35661998</v>
       </c>
       <c r="Q4" t="n">
-        <v>93.09999999999999</v>
+        <v>90.11554</v>
       </c>
       <c r="R4" t="n">
-        <v>32.762543</v>
+        <v>31.839138</v>
       </c>
       <c r="S4" t="n">
-        <v>174.4020253599966</v>
+        <v>169.4865502401083</v>
       </c>
       <c r="T4" t="n">
-        <v>0.3116371034251832</v>
+        <v>0.092758087051098</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.01389653347566167</v>
+        <v>0.0003980377508234767</v>
       </c>
       <c r="V4" t="n">
-        <v>1.033106159809553</v>
+        <v>1.014696795266853</v>
       </c>
       <c r="W4" t="n">
-        <v>0.7656652030638886</v>
+        <v>0.8381211806140034</v>
       </c>
       <c r="X4" t="n">
         <v>0.09436</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.73563004</v>
+        <v>0.73555</v>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>2026-08-28T22:50:59.626150+00:00</t>
+          <t>2026-08-31T22:50:46.904788+00:00</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
@@ -3809,10 +3809,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>246418096128</v>
+        <v>246809067520</v>
       </c>
       <c r="F5" t="n">
-        <v>195.3800048828125</v>
+        <v>195.6900024414062</v>
       </c>
       <c r="G5" t="n">
         <v>10540800000</v>
@@ -3821,7 +3821,7 @@
         <v>0.377</v>
       </c>
       <c r="I5" t="n">
-        <v>3.16</v>
+        <v>3.17</v>
       </c>
       <c r="J5" t="n">
         <v>0.357</v>
@@ -3842,35 +3842,35 @@
         <v>0.45393002</v>
       </c>
       <c r="Q5" t="n">
-        <v>61.829113</v>
+        <v>61.73186</v>
       </c>
       <c r="R5" t="n">
-        <v>23.377552</v>
+        <v>23.414642</v>
       </c>
       <c r="S5" t="n">
-        <v>63.32193236319635</v>
+        <v>63.42240008220392</v>
       </c>
       <c r="T5" t="n">
-        <v>0.2368171385264668</v>
+        <v>0.08505681074990323</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2251834413195413</v>
+        <v>0.146531584478875</v>
       </c>
       <c r="V5" t="n">
-        <v>0.5000384252039347</v>
+        <v>0.4658427149169007</v>
       </c>
       <c r="W5" t="n">
-        <v>0.4341922558198847</v>
+        <v>0.4331014138991418</v>
       </c>
       <c r="X5" t="n">
-        <v>0.17247999</v>
+        <v>0.17247</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.73299</v>
+        <v>0.73297</v>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>2026-08-28T22:51:05.893818+00:00</t>
+          <t>2026-08-31T22:50:51.257075+00:00</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
@@ -3901,10 +3901,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>447665733632</v>
+        <v>447882035200</v>
       </c>
       <c r="F6" t="n">
-        <v>186.2899932861328</v>
+        <v>186.3800048828125</v>
       </c>
       <c r="G6" t="n">
         <v>6155940864</v>
@@ -3934,35 +3934,35 @@
         <v>0.47120997</v>
       </c>
       <c r="Q6" t="n">
-        <v>159.22223</v>
+        <v>159.29915</v>
       </c>
       <c r="R6" t="n">
-        <v>72.72093</v>
+        <v>72.75606500000001</v>
       </c>
       <c r="S6" t="n">
-        <v>207.3386124404524</v>
+        <v>207.4387935881448</v>
       </c>
       <c r="T6" t="n">
-        <v>0.5145527909441692</v>
+        <v>0.5145458197662451</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1900472804136464</v>
+        <v>0.1601619169864854</v>
       </c>
       <c r="V6" t="n">
-        <v>0.3703839189382738</v>
+        <v>0.3585538418691643</v>
       </c>
       <c r="W6" t="n">
-        <v>0.178155824935788</v>
+        <v>0.1893305908863816</v>
       </c>
       <c r="X6" t="n">
         <v>0.03477</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.64865994</v>
+        <v>0.6486499999999999</v>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>2026-08-28T22:50:56.792100+00:00</t>
+          <t>2026-08-31T22:50:44.364786+00:00</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr">
@@ -3974,12 +3974,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>TER</t>
+          <t>NVDA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Teradyne, Inc.</t>
+          <t>NVIDIA Corporation</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -3989,72 +3989,72 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Semiconductor Equipment &amp; Materials</t>
+          <t>Semiconductors</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>55496278016</v>
+        <v>5331174293504</v>
       </c>
       <c r="F7" t="n">
-        <v>354.9700012207031</v>
+        <v>220.7799987792969</v>
       </c>
       <c r="G7" t="n">
-        <v>4464031232</v>
+        <v>302970011648</v>
       </c>
       <c r="H7" t="n">
-        <v>1.039</v>
+        <v>1.059</v>
       </c>
       <c r="I7" t="n">
-        <v>7.29</v>
+        <v>7.92</v>
       </c>
       <c r="J7" t="n">
-        <v>3.858</v>
+        <v>1.278</v>
       </c>
       <c r="K7" t="n">
-        <v>437381248</v>
+        <v>41809874944</v>
       </c>
       <c r="M7" t="n">
-        <v>354828992</v>
+        <v>62469001216</v>
       </c>
       <c r="N7" t="n">
-        <v>100127000</v>
+        <v>38860001280</v>
       </c>
       <c r="O7" t="n">
-        <v>0.5924199999999999</v>
+        <v>0.74674004</v>
       </c>
       <c r="P7" t="n">
-        <v>0.33161</v>
+        <v>0.66236997</v>
       </c>
       <c r="Q7" t="n">
-        <v>48.69273</v>
+        <v>27.876263</v>
       </c>
       <c r="R7" t="n">
-        <v>12.431875</v>
+        <v>17.596376</v>
       </c>
       <c r="S7" t="n">
-        <v>126.8830757371656</v>
+        <v>127.5099315806267</v>
       </c>
       <c r="T7" t="n">
-        <v>0.1113302562565048</v>
+        <v>0.09977583451704541</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.05166839374858856</v>
+        <v>-0.0148096147901412</v>
       </c>
       <c r="V7" t="n">
-        <v>0.06734011770084192</v>
+        <v>0.2475268098144381</v>
       </c>
       <c r="W7" t="n">
-        <v>2.018735227611809</v>
+        <v>0.2692276652833767</v>
       </c>
       <c r="X7" t="n">
-        <v>0.00202</v>
+        <v>0.04008</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.00471</v>
+        <v>0.71499</v>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>2026-08-28T22:51:00.101902+00:00</t>
+          <t>2026-08-31T22:50:43.972738+00:00</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr">
@@ -4066,12 +4066,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>NVDA</t>
+          <t>TER</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>NVIDIA Corporation</t>
+          <t>Teradyne, Inc.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -4081,72 +4081,72 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Semiconductors</t>
+          <t>Semiconductor Equipment &amp; Materials</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5253179637760</v>
+        <v>54692683776</v>
       </c>
       <c r="F8" t="n">
-        <v>217.5500030517578</v>
+        <v>349.8299865722656</v>
       </c>
       <c r="G8" t="n">
-        <v>302970011648</v>
+        <v>4464031232</v>
       </c>
       <c r="H8" t="n">
-        <v>1.059</v>
+        <v>1.039</v>
       </c>
       <c r="I8" t="n">
-        <v>7.91</v>
+        <v>7.28</v>
       </c>
       <c r="J8" t="n">
-        <v>1.278</v>
+        <v>3.858</v>
       </c>
       <c r="K8" t="n">
-        <v>41809874944</v>
+        <v>437381248</v>
       </c>
       <c r="M8" t="n">
-        <v>62469001216</v>
+        <v>354828992</v>
       </c>
       <c r="N8" t="n">
-        <v>38860001280</v>
+        <v>100127000</v>
       </c>
       <c r="O8" t="n">
-        <v>0.74674004</v>
+        <v>0.5924199999999999</v>
       </c>
       <c r="P8" t="n">
-        <v>0.66236997</v>
+        <v>0.33161</v>
       </c>
       <c r="Q8" t="n">
-        <v>27.503162</v>
+        <v>48.05357</v>
       </c>
       <c r="R8" t="n">
-        <v>17.338943</v>
+        <v>12.25186</v>
       </c>
       <c r="S8" t="n">
-        <v>125.6444714268122</v>
+        <v>125.0457902026929</v>
       </c>
       <c r="T8" t="n">
-        <v>0.1449397891747799</v>
+        <v>-0.04857356944859204</v>
       </c>
       <c r="U8" t="n">
-        <v>0.03155986221998819</v>
+        <v>-0.0531572646860321</v>
       </c>
       <c r="V8" t="n">
-        <v>0.1780807440636778</v>
+        <v>0.09352906632436575</v>
       </c>
       <c r="W8" t="n">
-        <v>0.2090789147412515</v>
+        <v>1.966217225464943</v>
       </c>
       <c r="X8" t="n">
-        <v>0.04008</v>
+        <v>0.00202</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.71496004</v>
+        <v>1.00471</v>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>2026-08-28T22:50:56.364503+00:00</t>
+          <t>2026-08-31T22:50:47.282848+00:00</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr">
@@ -4177,10 +4177,10 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>294796001280</v>
+        <v>294647398400</v>
       </c>
       <c r="F9" t="n">
-        <v>456.239990234375</v>
+        <v>456.010009765625</v>
       </c>
       <c r="G9" t="n">
         <v>134001999872</v>
@@ -4189,7 +4189,7 @@
         <v>0.875</v>
       </c>
       <c r="I9" t="n">
-        <v>12.56</v>
+        <v>12.55</v>
       </c>
       <c r="J9" t="n">
         <v>2.825</v>
@@ -4210,35 +4210,35 @@
         <v>0.08857000600000001</v>
       </c>
       <c r="Q9" t="n">
-        <v>36.32484</v>
+        <v>36.335457</v>
       </c>
       <c r="R9" t="n">
-        <v>2.1999373</v>
+        <v>2.1988285</v>
       </c>
       <c r="S9" t="n">
-        <v>54.24903036455843</v>
+        <v>54.22168412473707</v>
       </c>
       <c r="T9" t="n">
-        <v>0.2342819287795512</v>
+        <v>0.1249229475748399</v>
       </c>
       <c r="U9" t="n">
-        <v>0.08572833319716411</v>
+        <v>-0.01973655725354495</v>
       </c>
       <c r="V9" t="n">
-        <v>2.774458150107836</v>
+        <v>2.094116833404496</v>
       </c>
       <c r="W9" t="n">
-        <v>2.446876908237777</v>
+        <v>2.780769057304163</v>
       </c>
       <c r="X9" t="n">
         <v>0.07491</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.75615996</v>
+        <v>0.75596</v>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>2026-08-28T22:51:06.369837+00:00</t>
+          <t>2026-08-31T22:50:51.617375+00:00</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr">
@@ -4250,12 +4250,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>PATH</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Advanced Micro Devices, Inc.</t>
+          <t>UiPath, Inc.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -4265,72 +4265,69 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Semiconductors</t>
+          <t>Software - Infrastructure</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>760047665152</v>
+        <v>9673305088</v>
       </c>
       <c r="F10" t="n">
-        <v>465.5799865722656</v>
+        <v>18.67000007629395</v>
       </c>
       <c r="G10" t="n">
-        <v>41305001984</v>
+        <v>1672329984</v>
       </c>
       <c r="H10" t="n">
-        <v>0.501</v>
+        <v>0.173</v>
       </c>
       <c r="I10" t="n">
-        <v>3.91</v>
-      </c>
-      <c r="J10" t="n">
-        <v>1.595</v>
+        <v>0.6</v>
       </c>
       <c r="K10" t="n">
-        <v>8841499648</v>
+        <v>511553632</v>
       </c>
       <c r="M10" t="n">
-        <v>13111000064</v>
+        <v>1307244032</v>
       </c>
       <c r="N10" t="n">
-        <v>4276000000</v>
+        <v>83003000</v>
       </c>
       <c r="O10" t="n">
-        <v>0.55724</v>
+        <v>0.8305</v>
       </c>
       <c r="P10" t="n">
-        <v>0.1725</v>
+        <v>0.07274</v>
       </c>
       <c r="Q10" t="n">
-        <v>119.074165</v>
+        <v>31.116665</v>
       </c>
       <c r="R10" t="n">
-        <v>18.400862</v>
+        <v>5.784328</v>
       </c>
       <c r="S10" t="n">
-        <v>85.96365949343529</v>
+        <v>18.90965967767774</v>
       </c>
       <c r="T10" t="n">
-        <v>0.08385322008192486</v>
+        <v>0.4631661239343101</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.09788798954372291</v>
+        <v>0.4251908040173129</v>
       </c>
       <c r="V10" t="n">
-        <v>1.285840550443155</v>
+        <v>0.7399814420125106</v>
       </c>
       <c r="W10" t="n">
-        <v>1.761774715359504</v>
+        <v>0.6789568586722401</v>
       </c>
       <c r="X10" t="n">
-        <v>0.00425</v>
+        <v>0.09236999999999999</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.75373</v>
+        <v>0.91153</v>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>2026-08-28T22:50:57.225818+00:00</t>
+          <t>2026-08-31T22:50:54.089657+00:00</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr">
@@ -4342,12 +4339,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>PATH</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>UiPath, Inc.</t>
+          <t>Advanced Micro Devices, Inc.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -4357,69 +4354,72 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Software - Infrastructure</t>
+          <t>Semiconductors</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>9403882496</v>
+        <v>768438632448</v>
       </c>
       <c r="F11" t="n">
-        <v>18.14999961853027</v>
+        <v>470.7200012207031</v>
       </c>
       <c r="G11" t="n">
-        <v>1672329984</v>
+        <v>41305001984</v>
       </c>
       <c r="H11" t="n">
-        <v>0.173</v>
+        <v>0.501</v>
       </c>
       <c r="I11" t="n">
-        <v>0.6</v>
+        <v>3.91</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1.595</v>
       </c>
       <c r="K11" t="n">
-        <v>511553632</v>
+        <v>8841499648</v>
       </c>
       <c r="M11" t="n">
-        <v>1307244032</v>
+        <v>13111000064</v>
       </c>
       <c r="N11" t="n">
-        <v>83003000</v>
+        <v>4276000000</v>
       </c>
       <c r="O11" t="n">
-        <v>0.8305</v>
+        <v>0.55724</v>
       </c>
       <c r="P11" t="n">
-        <v>0.07274</v>
+        <v>0.1725</v>
       </c>
       <c r="Q11" t="n">
-        <v>30.249998</v>
+        <v>120.38875</v>
       </c>
       <c r="R11" t="n">
-        <v>5.623222</v>
+        <v>18.60401</v>
       </c>
       <c r="S11" t="n">
-        <v>18.38298451568808</v>
+        <v>86.91270293969026</v>
       </c>
       <c r="T11" t="n">
-        <v>0.4416202858265668</v>
+        <v>-0.01140395410140804</v>
       </c>
       <c r="U11" t="n">
-        <v>0.5486347444539406</v>
+        <v>-0.077254823838803</v>
       </c>
       <c r="V11" t="n">
-        <v>0.6946778294942526</v>
+        <v>1.351131239376256</v>
       </c>
       <c r="W11" t="n">
-        <v>0.6119004662162997</v>
+        <v>1.894422843803598</v>
       </c>
       <c r="X11" t="n">
-        <v>0.09236999999999999</v>
+        <v>0.00424</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.91153</v>
+        <v>0.75394994</v>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>2026-08-28T22:51:09.946502+00:00</t>
+          <t>2026-08-31T22:50:44.833177+00:00</t>
         </is>
       </c>
       <c r="AD11" t="inlineStr">
@@ -4431,87 +4431,87 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>MRVL</t>
+          <t>GOOGL</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Marvell Technology, Inc.</t>
+          <t>Alphabet Inc.</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Semiconductors</t>
+          <t>Internet Content &amp; Information</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>194677391360</v>
+        <v>4150228680704</v>
       </c>
       <c r="F12" t="n">
-        <v>216.6199951171875</v>
+        <v>339.3500061035156</v>
       </c>
       <c r="G12" t="n">
-        <v>9450300416</v>
+        <v>445865984000</v>
       </c>
       <c r="H12" t="n">
-        <v>0.365</v>
+        <v>0.242</v>
       </c>
       <c r="I12" t="n">
-        <v>3.02</v>
+        <v>19.93</v>
       </c>
       <c r="J12" t="n">
-        <v>0.5</v>
+        <v>2.94</v>
       </c>
       <c r="K12" t="n">
-        <v>2229250048</v>
+        <v>22665000960</v>
       </c>
       <c r="M12" t="n">
-        <v>3932800000</v>
+        <v>242473992192</v>
       </c>
       <c r="N12" t="n">
-        <v>4962899968</v>
+        <v>120790999040</v>
       </c>
       <c r="O12" t="n">
-        <v>0.52216</v>
+        <v>0.60897</v>
       </c>
       <c r="P12" t="n">
-        <v>0.16679001</v>
+        <v>0.34033</v>
       </c>
       <c r="Q12" t="n">
-        <v>71.72848</v>
+        <v>17.027096</v>
       </c>
       <c r="R12" t="n">
-        <v>20.600128</v>
+        <v>9.308242999999999</v>
       </c>
       <c r="S12" t="n">
-        <v>87.32864737836714</v>
+        <v>183.1117804948904</v>
       </c>
       <c r="T12" t="n">
-        <v>0.3257038140063735</v>
+        <v>-0.04711762151245436</v>
       </c>
       <c r="U12" t="n">
-        <v>0.05694362072151526</v>
+        <v>-0.09782208148452842</v>
       </c>
       <c r="V12" t="n">
-        <v>1.734038348041977</v>
+        <v>0.08991438545481922</v>
       </c>
       <c r="W12" t="n">
-        <v>1.810844566604123</v>
+        <v>0.5984128597259455</v>
       </c>
       <c r="X12" t="n">
-        <v>0.00494</v>
+        <v>0.01596</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.82141</v>
+        <v>0.81047994</v>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>2026-08-28T22:51:05.465346+00:00</t>
+          <t>2026-08-31T22:50:48.579178+00:00</t>
         </is>
       </c>
       <c r="AD12" t="inlineStr">
@@ -4523,87 +4523,87 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>MRVL</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Alphabet Inc.</t>
+          <t>Marvell Technology, Inc.</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Internet Content &amp; Information</t>
+          <t>Semiconductors</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4238773059584</v>
+        <v>190219829248</v>
       </c>
       <c r="F13" t="n">
-        <v>346.5899963378906</v>
+        <v>211.6600036621094</v>
       </c>
       <c r="G13" t="n">
-        <v>445865984000</v>
+        <v>9450300416</v>
       </c>
       <c r="H13" t="n">
-        <v>0.242</v>
+        <v>0.365</v>
       </c>
       <c r="I13" t="n">
-        <v>19.93</v>
+        <v>3.01</v>
       </c>
       <c r="J13" t="n">
-        <v>2.94</v>
+        <v>0.5</v>
       </c>
       <c r="K13" t="n">
-        <v>22665000960</v>
+        <v>2469100032</v>
       </c>
       <c r="M13" t="n">
-        <v>242473992192</v>
+        <v>3932800000</v>
       </c>
       <c r="N13" t="n">
-        <v>120790999040</v>
+        <v>4962899968</v>
       </c>
       <c r="O13" t="n">
-        <v>0.60897</v>
+        <v>0.52246</v>
       </c>
       <c r="P13" t="n">
-        <v>0.34033</v>
+        <v>0.17253</v>
       </c>
       <c r="Q13" t="n">
-        <v>17.390366</v>
+        <v>70.31894</v>
       </c>
       <c r="R13" t="n">
-        <v>9.506831999999999</v>
+        <v>20.128443</v>
       </c>
       <c r="S13" t="n">
-        <v>187.018437240075</v>
+        <v>77.04014692913017</v>
       </c>
       <c r="T13" t="n">
-        <v>0.0293427731090381</v>
+        <v>0.1284922500384804</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.08819207451527</v>
+        <v>-0.03517189970631596</v>
       </c>
       <c r="V13" t="n">
-        <v>0.1290295835576318</v>
+        <v>1.592951391566251</v>
       </c>
       <c r="W13" t="n">
-        <v>0.6423112460262883</v>
+        <v>2.373802251070248</v>
       </c>
       <c r="X13" t="n">
-        <v>0.01596</v>
+        <v>0.00494</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.81044996</v>
+        <v>0.8214399999999999</v>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>2026-08-28T22:51:02.101307+00:00</t>
+          <t>2026-08-31T22:50:50.930867+00:00</t>
         </is>
       </c>
       <c r="AD13" t="inlineStr">
@@ -4634,10 +4634,10 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>366380154880</v>
+        <v>363777130496</v>
       </c>
       <c r="F14" t="n">
-        <v>461.6700134277344</v>
+        <v>458.3900146484375</v>
       </c>
       <c r="G14" t="n">
         <v>30837000192</v>
@@ -4646,7 +4646,7 @@
         <v>0.248</v>
       </c>
       <c r="I14" t="n">
-        <v>11.58</v>
+        <v>11.59</v>
       </c>
       <c r="J14" t="n">
         <v>0.428</v>
@@ -4667,35 +4667,35 @@
         <v>0.33736</v>
       </c>
       <c r="Q14" t="n">
-        <v>39.867878</v>
+        <v>39.550476</v>
       </c>
       <c r="R14" t="n">
-        <v>11.8811865</v>
+        <v>11.796774</v>
       </c>
       <c r="S14" t="n">
-        <v>119.1334853441019</v>
+        <v>118.2870765985104</v>
       </c>
       <c r="T14" t="n">
-        <v>0.05891553435360564</v>
+        <v>-0.09610543351666145</v>
       </c>
       <c r="U14" t="n">
-        <v>0.02689349912329186</v>
+        <v>0.001550014609317696</v>
       </c>
       <c r="V14" t="n">
-        <v>0.231603937484552</v>
+        <v>0.2340871573637926</v>
       </c>
       <c r="W14" t="n">
-        <v>1.808879272617759</v>
+        <v>1.867164712580105</v>
       </c>
       <c r="X14" t="n">
-        <v>0.00331</v>
+        <v>0.0033000002</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.86313003</v>
+        <v>0.86324</v>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>2026-08-28T22:50:58.258372+00:00</t>
+          <t>2026-08-31T22:50:45.699382+00:00</t>
         </is>
       </c>
       <c r="AD14" t="inlineStr">
@@ -4726,10 +4726,10 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1754548011008</v>
+        <v>1761922252800</v>
       </c>
       <c r="F15" t="n">
-        <v>368.7900085449219</v>
+        <v>370.3399963378906</v>
       </c>
       <c r="G15" t="n">
         <v>75464998912</v>
@@ -4738,7 +4738,7 @@
         <v>0.479</v>
       </c>
       <c r="I15" t="n">
-        <v>6.02</v>
+        <v>6.01</v>
       </c>
       <c r="J15" t="n">
         <v>0.854</v>
@@ -4759,25 +4759,25 @@
         <v>0.48988</v>
       </c>
       <c r="Q15" t="n">
-        <v>61.2608</v>
+        <v>61.62063</v>
       </c>
       <c r="R15" t="n">
-        <v>23.249825</v>
+        <v>23.347542</v>
       </c>
       <c r="S15" t="n">
-        <v>64.47640565592636</v>
+        <v>64.74739545056453</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.004131558514356315</v>
+        <v>-0.04865393161939546</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.1732352596283164</v>
+        <v>-0.1935862625328272</v>
       </c>
       <c r="V15" t="n">
-        <v>0.150601502821587</v>
+        <v>0.1632114344825788</v>
       </c>
       <c r="W15" t="n">
-        <v>0.2036033468000933</v>
+        <v>0.254425111282889</v>
       </c>
       <c r="X15" t="n">
         <v>0.01948</v>
@@ -4787,7 +4787,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>2026-08-28T22:50:57.700886+00:00</t>
+          <t>2026-08-31T22:50:45.280476+00:00</t>
         </is>
       </c>
       <c r="AD15" t="inlineStr">
@@ -4818,10 +4818,10 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>85093597184</v>
+        <v>85115133952</v>
       </c>
       <c r="F16" t="n">
-        <v>236.9799957275391</v>
+        <v>237.0399932861328</v>
       </c>
       <c r="G16" t="n">
         <v>3966725120</v>
@@ -4830,7 +4830,7 @@
         <v>0.356</v>
       </c>
       <c r="I16" t="n">
-        <v>0.51</v>
+        <v>0.5</v>
       </c>
       <c r="J16" t="n">
         <v>14.985</v>
@@ -4851,35 +4851,35 @@
         <v>0.00666</v>
       </c>
       <c r="Q16" t="n">
-        <v>464.66666</v>
+        <v>474.08</v>
       </c>
       <c r="R16" t="n">
-        <v>21.45185</v>
+        <v>21.457281</v>
       </c>
       <c r="S16" t="n">
-        <v>80.93265883945027</v>
+        <v>80.95314249456335</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.103028066698809</v>
+        <v>-0.1154233973716186</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.04192443953947889</v>
+        <v>-0.1457710129078066</v>
       </c>
       <c r="V16" t="n">
-        <v>1.034861734419634</v>
+        <v>1.117184666170715</v>
       </c>
       <c r="W16" t="n">
-        <v>0.6811860417159425</v>
+        <v>0.7342698711465081</v>
       </c>
       <c r="X16" t="n">
         <v>0.00619</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.92819</v>
+        <v>0.92821</v>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>2026-08-28T22:51:08.190912+00:00</t>
+          <t>2026-08-31T22:50:52.838186+00:00</t>
         </is>
       </c>
       <c r="AD16" t="inlineStr">
@@ -4891,84 +4891,87 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ACMR</t>
+          <t>VRT</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>ACM Research, Inc.</t>
+          <t>Vertiv Holdings Co</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Semiconductor Equipment &amp; Materials</t>
+          <t>Electrical Equipment &amp; Parts</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5183293440</v>
+        <v>99604135936</v>
       </c>
       <c r="F17" t="n">
-        <v>74.41999816894531</v>
+        <v>258.7200012207031</v>
       </c>
       <c r="G17" t="n">
-        <v>1037772032</v>
+        <v>11479600128</v>
       </c>
       <c r="H17" t="n">
-        <v>0.36</v>
+        <v>0.241</v>
       </c>
       <c r="I17" t="n">
-        <v>2.12</v>
+        <v>4.42</v>
       </c>
       <c r="J17" t="n">
-        <v>1.806</v>
+        <v>0.53</v>
       </c>
       <c r="K17" t="n">
-        <v>-186610256</v>
+        <v>2696537600</v>
       </c>
       <c r="M17" t="n">
-        <v>1439374976</v>
+        <v>3110599936</v>
       </c>
       <c r="N17" t="n">
-        <v>349319008</v>
+        <v>3338200064</v>
       </c>
       <c r="O17" t="n">
-        <v>0.43835</v>
+        <v>0.38039002</v>
       </c>
       <c r="P17" t="n">
-        <v>0.16982001</v>
+        <v>0.20362</v>
       </c>
       <c r="Q17" t="n">
-        <v>35.103775</v>
+        <v>58.533936</v>
       </c>
       <c r="R17" t="n">
-        <v>4.994636</v>
+        <v>8.6766205</v>
+      </c>
+      <c r="S17" t="n">
+        <v>36.93778864273949</v>
       </c>
       <c r="T17" t="n">
-        <v>0.1396630121128608</v>
+        <v>0.07099388738878831</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1402495347973027</v>
+        <v>-0.1998088656150657</v>
       </c>
       <c r="V17" t="n">
-        <v>0.3046984041805443</v>
+        <v>0.01547892791900263</v>
       </c>
       <c r="W17" t="n">
-        <v>1.540798765543686</v>
+        <v>1.030615386807944</v>
       </c>
       <c r="X17" t="n">
-        <v>0.12675999</v>
+        <v>0.00269</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.78056</v>
+        <v>0.84445</v>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>2026-08-28T22:50:59.195149+00:00</t>
+          <t>2026-08-31T22:50:51.911634+00:00</t>
         </is>
       </c>
       <c r="AD17" t="inlineStr">
@@ -4980,87 +4983,84 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>AMZN</t>
+          <t>ACMR</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Amazon.com, Inc.</t>
+          <t>ACM Research, Inc.</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Internet Retail</t>
+          <t>Semiconductor Equipment &amp; Materials</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2873797378048</v>
+        <v>5071854592</v>
       </c>
       <c r="F18" t="n">
-        <v>266.4299926757812</v>
+        <v>72.81999969482422</v>
       </c>
       <c r="G18" t="n">
-        <v>775680032768</v>
+        <v>1037772032</v>
       </c>
       <c r="H18" t="n">
-        <v>0.196</v>
+        <v>0.36</v>
       </c>
       <c r="I18" t="n">
-        <v>12.43</v>
+        <v>2.12</v>
       </c>
       <c r="J18" t="n">
-        <v>2.423</v>
+        <v>1.806</v>
       </c>
       <c r="K18" t="n">
-        <v>3219124992</v>
+        <v>-186610256</v>
       </c>
       <c r="M18" t="n">
-        <v>122988003328</v>
+        <v>1439374976</v>
       </c>
       <c r="N18" t="n">
-        <v>251635007488</v>
+        <v>349319008</v>
       </c>
       <c r="O18" t="n">
-        <v>0.5077</v>
+        <v>0.43835</v>
       </c>
       <c r="P18" t="n">
-        <v>0.13689</v>
+        <v>0.16982001</v>
       </c>
       <c r="Q18" t="n">
-        <v>21.434431</v>
+        <v>34.34906</v>
       </c>
       <c r="R18" t="n">
-        <v>3.7048748</v>
-      </c>
-      <c r="S18" t="n">
-        <v>892.7262486513603</v>
+        <v>4.8872533</v>
       </c>
       <c r="T18" t="n">
-        <v>0.1755129047012691</v>
+        <v>-0.07200205732108789</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.01555580012115021</v>
+        <v>-0.1124924194227175</v>
       </c>
       <c r="V18" t="n">
-        <v>0.2814062861778868</v>
+        <v>0.3078304471211573</v>
       </c>
       <c r="W18" t="n">
-        <v>0.1503885390948481</v>
+        <v>1.580439456650297</v>
       </c>
       <c r="X18" t="n">
-        <v>0.0887</v>
+        <v>0.12675999</v>
       </c>
       <c r="Y18" t="n">
-        <v>0.68727</v>
+        <v>0.78069</v>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>2026-08-28T22:51:02.541011+00:00</t>
+          <t>2026-08-31T22:50:46.582882+00:00</t>
         </is>
       </c>
       <c r="AD18" t="inlineStr">
@@ -5072,81 +5072,87 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>MDB</t>
+          <t>AMZN</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>MongoDB, Inc.</t>
+          <t>Amazon.com, Inc.</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Software - Infrastructure</t>
+          <t>Internet Retail</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>35922505728</v>
+        <v>2801960484864</v>
       </c>
       <c r="F19" t="n">
-        <v>446.6199951171875</v>
+        <v>259.7699890136719</v>
       </c>
       <c r="G19" t="n">
-        <v>2602398976</v>
+        <v>775680032768</v>
       </c>
       <c r="H19" t="n">
-        <v>0.252</v>
+        <v>0.196</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.35</v>
+        <v>12.44</v>
+      </c>
+      <c r="J19" t="n">
+        <v>2.423</v>
       </c>
       <c r="K19" t="n">
-        <v>517605376</v>
+        <v>3219124992</v>
       </c>
       <c r="M19" t="n">
-        <v>2427152896</v>
+        <v>122988003328</v>
       </c>
       <c r="N19" t="n">
-        <v>58635000</v>
+        <v>251635007488</v>
       </c>
       <c r="O19" t="n">
-        <v>0.71970004</v>
+        <v>0.5077</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.03607</v>
+        <v>0.13689</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>20.881832</v>
       </c>
       <c r="R19" t="n">
-        <v>13.803612</v>
+        <v>3.6122632</v>
       </c>
       <c r="S19" t="n">
-        <v>69.40133814993452</v>
+        <v>870.410590401828</v>
       </c>
       <c r="T19" t="n">
-        <v>0.3909062180871057</v>
+        <v>-0.04348625871756273</v>
       </c>
       <c r="U19" t="n">
-        <v>0.331008825405614</v>
+        <v>-0.00570321019772535</v>
       </c>
       <c r="V19" t="n">
-        <v>0.3268174283384024</v>
+        <v>0.2369999476841518</v>
       </c>
       <c r="W19" t="n">
-        <v>0.4040238495683937</v>
+        <v>0.1343667642518422</v>
       </c>
       <c r="X19" t="n">
-        <v>0.02641</v>
+        <v>0.08866</v>
       </c>
       <c r="Y19" t="n">
-        <v>0.9609799999999999</v>
+        <v>0.6873</v>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>2026-08-28T22:51:09.513285+00:00</t>
+          <t>2026-08-31T22:50:48.860407+00:00</t>
         </is>
       </c>
       <c r="AD19" t="inlineStr">
@@ -5158,87 +5164,81 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>VRT</t>
+          <t>MDB</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Vertiv Holdings Co</t>
+          <t>MongoDB, Inc.</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Electrical Equipment &amp; Parts</t>
+          <t>Software - Infrastructure</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>98972753920</v>
+        <v>36465422336</v>
       </c>
       <c r="F20" t="n">
-        <v>257.0799865722656</v>
+        <v>453.3699951171875</v>
       </c>
       <c r="G20" t="n">
-        <v>11479600128</v>
+        <v>2602398976</v>
       </c>
       <c r="H20" t="n">
-        <v>0.241</v>
+        <v>0.252</v>
       </c>
       <c r="I20" t="n">
-        <v>4.42</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0.53</v>
+        <v>-0.36</v>
       </c>
       <c r="K20" t="n">
-        <v>2696537600</v>
+        <v>517605376</v>
       </c>
       <c r="M20" t="n">
-        <v>3110599936</v>
+        <v>2427152896</v>
       </c>
       <c r="N20" t="n">
-        <v>3338200064</v>
+        <v>58635000</v>
       </c>
       <c r="O20" t="n">
-        <v>0.38039002</v>
+        <v>0.71970004</v>
       </c>
       <c r="P20" t="n">
-        <v>0.20362</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>58.16289</v>
+        <v>-0.03607</v>
       </c>
       <c r="R20" t="n">
-        <v>8.62162</v>
+        <v>14.012234</v>
       </c>
       <c r="S20" t="n">
-        <v>36.70364319043799</v>
+        <v>70.45023878577335</v>
       </c>
       <c r="T20" t="n">
-        <v>0.1526183389113704</v>
+        <v>0.3433980690949849</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1855390000205935</v>
+        <v>0.1225363712886325</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.007851449963671819</v>
+        <v>0.3802477956352626</v>
       </c>
       <c r="W20" t="n">
-        <v>0.9173299123032923</v>
+        <v>0.4364881219210226</v>
       </c>
       <c r="X20" t="n">
-        <v>0.00269</v>
+        <v>0.02641</v>
       </c>
       <c r="Y20" t="n">
-        <v>0.84446</v>
+        <v>0.96919</v>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>2026-08-28T22:51:06.848598+00:00</t>
+          <t>2026-08-31T22:50:53.805242+00:00</t>
         </is>
       </c>
       <c r="AD20" t="inlineStr">
@@ -5250,12 +5250,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>ASML</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Microsoft Corporation</t>
+          <t>ASML Holding N.V.</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -5265,72 +5265,72 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Software - Infrastructure</t>
+          <t>Semiconductor Equipment &amp; Materials</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>3813240733696</v>
+        <v>651437473792</v>
       </c>
       <c r="F21" t="n">
-        <v>513.530029296875</v>
+        <v>1696.010009765625</v>
       </c>
       <c r="G21" t="n">
-        <v>331839012864</v>
+        <v>35327500288</v>
       </c>
       <c r="H21" t="n">
-        <v>0.177</v>
+        <v>0.213</v>
       </c>
       <c r="I21" t="n">
-        <v>17.93</v>
+        <v>29.68</v>
       </c>
       <c r="J21" t="n">
-        <v>0.317</v>
+        <v>0.285</v>
       </c>
       <c r="K21" t="n">
-        <v>16545500160</v>
+        <v>8437675008</v>
       </c>
       <c r="M21" t="n">
-        <v>76842999808</v>
+        <v>7581499904</v>
       </c>
       <c r="N21" t="n">
-        <v>128812998656</v>
+        <v>1984400000</v>
       </c>
       <c r="O21" t="n">
-        <v>0.67944</v>
+        <v>0.5273300400000001</v>
       </c>
       <c r="P21" t="n">
-        <v>0.45111</v>
+        <v>0.37057</v>
       </c>
       <c r="Q21" t="n">
-        <v>28.640827</v>
+        <v>57.143192</v>
       </c>
       <c r="R21" t="n">
-        <v>11.491237</v>
+        <v>18.439955</v>
       </c>
       <c r="S21" t="n">
-        <v>230.4699584068663</v>
+        <v>77.20580292252944</v>
       </c>
       <c r="T21" t="n">
-        <v>0.3173983684080277</v>
+        <v>0.04113567204765189</v>
       </c>
       <c r="U21" t="n">
-        <v>0.1427166697123534</v>
+        <v>0.04275746353594823</v>
       </c>
       <c r="V21" t="n">
-        <v>0.2835086809884435</v>
+        <v>0.1732796814666719</v>
       </c>
       <c r="W21" t="n">
-        <v>0.015923407485678</v>
+        <v>1.298861829835056</v>
       </c>
       <c r="X21" t="n">
-        <v>0.00090000004</v>
+        <v>0.00016000001</v>
       </c>
       <c r="Y21" t="n">
-        <v>0.75881</v>
+        <v>0.20377001</v>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>2026-08-28T22:51:01.614393+00:00</t>
+          <t>2026-08-31T22:50:50.293086+00:00</t>
         </is>
       </c>
       <c r="AD21" t="inlineStr">
@@ -5342,12 +5342,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ASML</t>
+          <t>SNOW</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>ASML Holding N.V.</t>
+          <t>Snowflake Inc.</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -5357,72 +5357,66 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Semiconductor Equipment &amp; Materials</t>
+          <t>Software - Application</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>651495079936</v>
+        <v>114873638912</v>
       </c>
       <c r="F22" t="n">
-        <v>1696.160034179688</v>
+        <v>331.4299926757812</v>
       </c>
       <c r="G22" t="n">
-        <v>35327500288</v>
+        <v>5032822784</v>
       </c>
       <c r="H22" t="n">
-        <v>0.213</v>
+        <v>0.335</v>
       </c>
       <c r="I22" t="n">
-        <v>29.67</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0.285</v>
+        <v>-3.51</v>
       </c>
       <c r="K22" t="n">
-        <v>8437675008</v>
+        <v>1739497728</v>
       </c>
       <c r="M22" t="n">
-        <v>7581499904</v>
+        <v>2954998016</v>
       </c>
       <c r="N22" t="n">
-        <v>1984400000</v>
+        <v>2772094976</v>
       </c>
       <c r="O22" t="n">
-        <v>0.5273300400000001</v>
+        <v>0.67144996</v>
       </c>
       <c r="P22" t="n">
-        <v>0.37057</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>57.16751</v>
+        <v>-0.22173999</v>
       </c>
       <c r="R22" t="n">
-        <v>18.441584</v>
+        <v>22.824892</v>
       </c>
       <c r="S22" t="n">
-        <v>77.21263017576511</v>
+        <v>66.03839548791868</v>
       </c>
       <c r="T22" t="n">
-        <v>0.0938099157601533</v>
+        <v>0.1300804489064171</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0530728138986476</v>
+        <v>0.1830025283534287</v>
       </c>
       <c r="V22" t="n">
-        <v>0.1627703588159193</v>
+        <v>0.967994688372243</v>
       </c>
       <c r="W22" t="n">
-        <v>1.236308349157486</v>
+        <v>0.3887119231968754</v>
       </c>
       <c r="X22" t="n">
-        <v>0.00016000001</v>
+        <v>0.02962</v>
       </c>
       <c r="Y22" t="n">
-        <v>0.20377001</v>
+        <v>0.82328004</v>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>2026-08-28T22:51:04.490576+00:00</t>
+          <t>2026-08-31T22:50:52.548034+00:00</t>
         </is>
       </c>
       <c r="AD22" t="inlineStr">
@@ -5453,10 +5447,10 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>106766942208</v>
+        <v>108643475456</v>
       </c>
       <c r="F23" t="n">
-        <v>299.8399963378906</v>
+        <v>305.1099853515625</v>
       </c>
       <c r="G23" t="n">
         <v>2512349952</v>
@@ -5465,7 +5459,7 @@
         <v>0.359</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.59</v>
+        <v>-0.57</v>
       </c>
       <c r="K23" t="n">
         <v>691946368</v>
@@ -5483,22 +5477,22 @@
         <v>-0.07603</v>
       </c>
       <c r="R23" t="n">
-        <v>42.49684</v>
+        <v>43.243767</v>
       </c>
       <c r="S23" t="n">
-        <v>154.2994473930095</v>
+        <v>157.0114108265686</v>
       </c>
       <c r="T23" t="n">
-        <v>0.1089577295771063</v>
+        <v>0.09366253256945689</v>
       </c>
       <c r="U23" t="n">
-        <v>0.2399304741393127</v>
+        <v>0.1266153795878628</v>
       </c>
       <c r="V23" t="n">
-        <v>0.7167066875708403</v>
+        <v>0.7719378652973015</v>
       </c>
       <c r="W23" t="n">
-        <v>0.4049292423877466</v>
+        <v>0.461884794866859</v>
       </c>
       <c r="X23" t="n">
         <v>0.00616</v>
@@ -5508,7 +5502,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>2026-08-28T22:51:08.648322+00:00</t>
+          <t>2026-08-31T22:50:53.133300+00:00</t>
         </is>
       </c>
       <c r="AD23" t="inlineStr">
@@ -5520,12 +5514,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>SNOW</t>
+          <t>SMCI</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Snowflake Inc.</t>
+          <t>Super Micro Computer, Inc.</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -5535,66 +5529,69 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Software - Application</t>
+          <t>Computer Hardware</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>113684799488</v>
+        <v>24115425280</v>
       </c>
       <c r="F24" t="n">
-        <v>328</v>
+        <v>37.27999877929688</v>
       </c>
       <c r="G24" t="n">
-        <v>5032822784</v>
+        <v>39063072768</v>
       </c>
       <c r="H24" t="n">
-        <v>0.335</v>
+        <v>0.9320000000000001</v>
       </c>
       <c r="I24" t="n">
-        <v>-3.52</v>
+        <v>3.26</v>
+      </c>
+      <c r="J24" t="n">
+        <v>4.094</v>
       </c>
       <c r="K24" t="n">
-        <v>1739497728</v>
+        <v>-8231267840</v>
       </c>
       <c r="M24" t="n">
-        <v>2954998016</v>
+        <v>7521474048</v>
       </c>
       <c r="N24" t="n">
-        <v>2772094976</v>
+        <v>9311492096</v>
       </c>
       <c r="O24" t="n">
-        <v>0.67144996</v>
+        <v>0.108219996</v>
       </c>
       <c r="P24" t="n">
-        <v>-0.22173999</v>
+        <v>0.13382</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>11.435582</v>
       </c>
       <c r="R24" t="n">
-        <v>22.588675</v>
-      </c>
-      <c r="S24" t="n">
-        <v>65.35495715692018</v>
+        <v>0.6173457999999999</v>
       </c>
       <c r="T24" t="n">
-        <v>0.1594203148693532</v>
+        <v>0.312676030987431</v>
       </c>
       <c r="U24" t="n">
-        <v>0.2835061478499319</v>
+        <v>-0.2047782011538319</v>
       </c>
       <c r="V24" t="n">
-        <v>0.8952964557216492</v>
+        <v>0.1509725063845244</v>
       </c>
       <c r="W24" t="n">
-        <v>0.3609958506224067</v>
+        <v>-0.1025518065079799</v>
       </c>
       <c r="X24" t="n">
-        <v>0.02962</v>
+        <v>0.12878999</v>
       </c>
       <c r="Y24" t="n">
-        <v>0.81921</v>
+        <v>0.70587</v>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>2026-08-28T22:51:07.742502+00:00</t>
+          <t>2026-08-31T22:50:52.243724+00:00</t>
         </is>
       </c>
       <c r="AD24" t="inlineStr">
@@ -5625,10 +5622,10 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>302845853696</v>
+        <v>311435952128</v>
       </c>
       <c r="F25" t="n">
-        <v>371.5899963378906</v>
+        <v>382.1300048828125</v>
       </c>
       <c r="G25" t="n">
         <v>10606499840</v>
@@ -5655,35 +5652,35 @@
         <v>-0.02465</v>
       </c>
       <c r="Q25" t="n">
-        <v>323.12173</v>
+        <v>332.28696</v>
       </c>
       <c r="R25" t="n">
-        <v>28.552855</v>
+        <v>29.362745</v>
       </c>
       <c r="S25" t="n">
-        <v>84.60858247507105</v>
+        <v>87.00847021592291</v>
       </c>
       <c r="T25" t="n">
-        <v>0.182842602442747</v>
+        <v>0.1515837035408871</v>
       </c>
       <c r="U25" t="n">
-        <v>0.3191451351390586</v>
+        <v>0.2717318653858791</v>
       </c>
       <c r="V25" t="n">
-        <v>1.487215605881191</v>
+        <v>1.566008659557579</v>
       </c>
       <c r="W25" t="n">
-        <v>0.9452936238440981</v>
+        <v>1.005721164777699</v>
       </c>
       <c r="X25" t="n">
         <v>0.0076</v>
       </c>
       <c r="Y25" t="n">
-        <v>0.84946</v>
+        <v>0.84946996</v>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>2026-08-28T22:51:01.115092+00:00</t>
+          <t>2026-08-31T22:50:47.899293+00:00</t>
         </is>
       </c>
       <c r="AD25" t="inlineStr">
@@ -5695,12 +5692,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>SMCI</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Super Micro Computer, Inc.</t>
+          <t>Microsoft Corporation</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -5710,69 +5707,72 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Computer Hardware</t>
+          <t>Software - Infrastructure</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>23986053120</v>
+        <v>3766905208832</v>
       </c>
       <c r="F26" t="n">
-        <v>37.08000183105469</v>
+        <v>507.2900085449219</v>
       </c>
       <c r="G26" t="n">
-        <v>39063072768</v>
+        <v>331839012864</v>
       </c>
       <c r="H26" t="n">
-        <v>0.9320000000000001</v>
+        <v>0.177</v>
       </c>
       <c r="I26" t="n">
-        <v>3.26</v>
+        <v>17.97</v>
       </c>
       <c r="J26" t="n">
-        <v>4.094</v>
+        <v>0.317</v>
       </c>
       <c r="K26" t="n">
-        <v>-8231267840</v>
+        <v>16545500160</v>
       </c>
       <c r="M26" t="n">
-        <v>7521474048</v>
+        <v>76842999808</v>
       </c>
       <c r="N26" t="n">
-        <v>9311492096</v>
+        <v>128812998656</v>
       </c>
       <c r="O26" t="n">
-        <v>0.108219996</v>
+        <v>0.67944</v>
       </c>
       <c r="P26" t="n">
-        <v>0.13382</v>
+        <v>0.45111</v>
       </c>
       <c r="Q26" t="n">
-        <v>11.374234</v>
+        <v>28.22983</v>
       </c>
       <c r="R26" t="n">
-        <v>0.61403394</v>
+        <v>11.351604</v>
+      </c>
+      <c r="S26" t="n">
+        <v>227.6694673720882</v>
       </c>
       <c r="T26" t="n">
-        <v>0.4428015848359703</v>
+        <v>0.0936585239403942</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.1954870534108103</v>
+        <v>0.1036328261285961</v>
       </c>
       <c r="V26" t="n">
-        <v>0.1486989849217821</v>
+        <v>0.2969032941411813</v>
       </c>
       <c r="W26" t="n">
-        <v>-0.1566977302335008</v>
+        <v>0.009421579553753778</v>
       </c>
       <c r="X26" t="n">
-        <v>0.12878999</v>
+        <v>0.00090000004</v>
       </c>
       <c r="Y26" t="n">
-        <v>0.70585996</v>
+        <v>0.75882006</v>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>2026-08-28T22:51:07.289444+00:00</t>
+          <t>2026-08-31T22:50:48.267338+00:00</t>
         </is>
       </c>
       <c r="AD26" t="inlineStr">
@@ -5803,10 +5803,10 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>255305072640</v>
+        <v>258359541760</v>
       </c>
       <c r="F27" t="n">
-        <v>239.0500030517578</v>
+        <v>241.9100036621094</v>
       </c>
       <c r="G27" t="n">
         <v>5155999744</v>
@@ -5815,7 +5815,7 @@
         <v>0.224</v>
       </c>
       <c r="I27" t="n">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="J27" t="n">
         <v>1.083</v>
@@ -5836,35 +5836,35 @@
         <v>0.07603</v>
       </c>
       <c r="Q27" t="n">
-        <v>246.4433</v>
+        <v>246.84694</v>
       </c>
       <c r="R27" t="n">
-        <v>49.516113</v>
+        <v>50.108524</v>
       </c>
       <c r="S27" t="n">
-        <v>191.3114115863358</v>
+        <v>193.6002607382603</v>
       </c>
       <c r="T27" t="n">
-        <v>0.06296413224482911</v>
+        <v>0.009261968367853868</v>
       </c>
       <c r="U27" t="n">
-        <v>-0.3233604198535892</v>
+        <v>-0.4083160081918629</v>
       </c>
       <c r="V27" t="n">
-        <v>0.8493734582289156</v>
+        <v>0.8980777517032796</v>
       </c>
       <c r="W27" t="n">
-        <v>0.6769554397341</v>
+        <v>0.7490420644366393</v>
       </c>
       <c r="X27" t="n">
         <v>0.0007</v>
       </c>
       <c r="Y27" t="n">
-        <v>0.96182996</v>
+        <v>0.96182</v>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>2026-08-28T22:51:04.986785+00:00</t>
+          <t>2026-08-31T22:50:50.606799+00:00</t>
         </is>
       </c>
       <c r="AD27" t="inlineStr">
@@ -5895,10 +5895,10 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>223627362304</v>
+        <v>236528943104</v>
       </c>
       <c r="F28" t="n">
-        <v>218.3999938964844</v>
+        <v>231</v>
       </c>
       <c r="G28" t="n">
         <v>5396145152</v>
@@ -5907,7 +5907,7 @@
         <v>0.258</v>
       </c>
       <c r="I28" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="K28" t="n">
         <v>1995385472</v>
@@ -5925,35 +5925,35 @@
         <v>-0.02259</v>
       </c>
       <c r="Q28" t="n">
-        <v>4368</v>
+        <v>5775</v>
       </c>
       <c r="R28" t="n">
-        <v>41.44206</v>
+        <v>43.832947</v>
       </c>
       <c r="S28" t="n">
-        <v>112.0722614462335</v>
+        <v>118.5379699426818</v>
       </c>
       <c r="T28" t="n">
-        <v>0.2175269704065586</v>
+        <v>0.2103112190154284</v>
       </c>
       <c r="U28" t="n">
-        <v>0.1950752059999146</v>
+        <v>0.1813288929372465</v>
       </c>
       <c r="V28" t="n">
-        <v>1.292311628430275</v>
+        <v>1.484004443007452</v>
       </c>
       <c r="W28" t="n">
-        <v>0.9764705329998586</v>
+        <v>1.180788230774251</v>
       </c>
       <c r="X28" t="n">
-        <v>0.014579999</v>
+        <v>0.01456</v>
       </c>
       <c r="Y28" t="n">
-        <v>0.76237</v>
+        <v>0.7654300000000001</v>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>2026-08-28T22:51:00.572730+00:00</t>
+          <t>2026-08-31T22:50:47.586780+00:00</t>
         </is>
       </c>
       <c r="AD28" t="inlineStr">
@@ -5984,10 +5984,10 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1472509509632</v>
+        <v>1458039816192</v>
       </c>
       <c r="F29" t="n">
-        <v>578.02001953125</v>
+        <v>572.3400268554688</v>
       </c>
       <c r="G29" t="n">
         <v>228246994944</v>
@@ -5996,7 +5996,7 @@
         <v>0.28</v>
       </c>
       <c r="I29" t="n">
-        <v>26.56</v>
+        <v>26.53</v>
       </c>
       <c r="J29" t="n">
         <v>-0.134</v>
@@ -6017,35 +6017,35 @@
         <v>0.34827</v>
       </c>
       <c r="Q29" t="n">
-        <v>21.762802</v>
+        <v>21.573313</v>
       </c>
       <c r="R29" t="n">
-        <v>6.451386</v>
+        <v>6.3879914</v>
       </c>
       <c r="S29" t="n">
-        <v>68.31841528373901</v>
+        <v>67.64708072257251</v>
       </c>
       <c r="T29" t="n">
-        <v>-0.01296078620612318</v>
+        <v>0.02807566644377779</v>
       </c>
       <c r="U29" t="n">
-        <v>-0.08530182408797538</v>
+        <v>-0.04596311523360996</v>
       </c>
       <c r="V29" t="n">
-        <v>-0.1186571598612787</v>
+        <v>-0.1154293831138969</v>
       </c>
       <c r="W29" t="n">
-        <v>-0.2279233366030805</v>
+        <v>-0.2226670692091168</v>
       </c>
       <c r="X29" t="n">
         <v>0.00148</v>
       </c>
       <c r="Y29" t="n">
-        <v>0.79037005</v>
+        <v>0.79042</v>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>2026-08-28T22:51:03.026009+00:00</t>
+          <t>2026-08-31T22:50:49.201384+00:00</t>
         </is>
       </c>
       <c r="AD29" t="inlineStr">
@@ -6076,10 +6076,10 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>149610184704</v>
+        <v>153001246720</v>
       </c>
       <c r="F30" t="n">
-        <v>144.7100067138672</v>
+        <v>147.9900054931641</v>
       </c>
       <c r="G30" t="n">
         <v>14732000256</v>
@@ -6109,35 +6109,35 @@
         <v>0.04063</v>
       </c>
       <c r="Q30" t="n">
-        <v>89.88199</v>
+        <v>91.91925999999999</v>
       </c>
       <c r="R30" t="n">
-        <v>10.155457</v>
+        <v>10.38564</v>
       </c>
       <c r="S30" t="n">
-        <v>29.05404741377296</v>
+        <v>29.71258598045434</v>
       </c>
       <c r="T30" t="n">
-        <v>0.2500864205545481</v>
+        <v>0.3304863888052649</v>
       </c>
       <c r="U30" t="n">
-        <v>0.1635442913733003</v>
+        <v>0.08928312106814662</v>
       </c>
       <c r="V30" t="n">
-        <v>0.3239707472408886</v>
+        <v>0.3701509357115627</v>
       </c>
       <c r="W30" t="n">
-        <v>-0.2208162515468708</v>
+        <v>-0.1934798141124087</v>
       </c>
       <c r="X30" t="n">
         <v>0.00176</v>
       </c>
       <c r="Y30" t="n">
-        <v>0.85128</v>
+        <v>0.85129</v>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>2026-08-28T22:51:09.083412+00:00</t>
+          <t>2026-08-31T22:50:53.470095+00:00</t>
         </is>
       </c>
       <c r="AD30" t="inlineStr">
@@ -6168,10 +6168,10 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>434519080960</v>
+        <v>429535821824</v>
       </c>
       <c r="F31" t="n">
-        <v>150.8500061035156</v>
+        <v>149.1199951171875</v>
       </c>
       <c r="G31" t="n">
         <v>67356999680</v>
@@ -6180,7 +6180,7 @@
         <v>0.206</v>
       </c>
       <c r="I31" t="n">
-        <v>5.83</v>
+        <v>5.82</v>
       </c>
       <c r="J31" t="n">
         <v>0.219</v>
@@ -6201,32 +6201,32 @@
         <v>0.36202</v>
       </c>
       <c r="Q31" t="n">
-        <v>25.874786</v>
+        <v>25.621992</v>
       </c>
       <c r="R31" t="n">
-        <v>6.4509864</v>
+        <v>6.3770037</v>
       </c>
       <c r="T31" t="n">
-        <v>0.281212916939712</v>
+        <v>0.1482251537980721</v>
       </c>
       <c r="U31" t="n">
-        <v>-0.3295472987237595</v>
+        <v>-0.3969825581621358</v>
       </c>
       <c r="V31" t="n">
-        <v>0.01060149055477</v>
+        <v>0.03274701231595389</v>
       </c>
       <c r="W31" t="n">
-        <v>-0.3651408526453519</v>
+        <v>-0.333040235042808</v>
       </c>
       <c r="X31" t="n">
         <v>0.40498</v>
       </c>
       <c r="Y31" t="n">
-        <v>0.45821</v>
+        <v>0.4582</v>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>2026-08-28T22:51:03.517487+00:00</t>
+          <t>2026-08-31T22:50:49.551411+00:00</t>
         </is>
       </c>
       <c r="AD31" t="inlineStr">
@@ -6456,7 +6456,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>TER</t>
+          <t>NVDA</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -6485,7 +6485,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>NVDA</t>
+          <t>TER</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -6543,18 +6543,23 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>PATH</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>100</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="C10" t="n">
-        <v>100</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
           <t>HIGH</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>eps_growth</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -6572,23 +6577,18 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>PATH</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>94.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="C11" t="n">
-        <v>94.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
           <t>HIGH</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>eps_growth</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -6606,7 +6606,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>MRVL</t>
+          <t>GOOGL</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -6635,7 +6635,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>MRVL</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -6751,23 +6751,18 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ACMR</t>
+          <t>VRT</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>94.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="C17" t="n">
-        <v>94.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
           <t>HIGH</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>price_to_fcf</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -6785,18 +6780,23 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>AMZN</t>
+          <t>ACMR</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>100</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="C18" t="n">
-        <v>100</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
           <t>HIGH</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>price_to_fcf</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -6814,23 +6814,18 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>MDB</t>
+          <t>AMZN</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>88.2</v>
+        <v>100</v>
       </c>
       <c r="C19" t="n">
-        <v>88.2</v>
+        <v>100</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
           <t>HIGH</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>eps_growth, pe_ratio</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -6848,18 +6843,23 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>VRT</t>
+          <t>MDB</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>100</v>
+        <v>88.2</v>
       </c>
       <c r="C20" t="n">
-        <v>100</v>
+        <v>88.2</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
           <t>HIGH</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>eps_growth, pe_ratio</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -6877,7 +6877,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>ASML</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -6906,18 +6906,23 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ASML</t>
+          <t>SNOW</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>100</v>
+        <v>88.2</v>
       </c>
       <c r="C22" t="n">
-        <v>100</v>
+        <v>88.2</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
           <t>HIGH</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>eps_growth, pe_ratio</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -6969,14 +6974,14 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>SNOW</t>
+          <t>SMCI</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>88.2</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="C24" t="n">
-        <v>88.2</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -6985,7 +6990,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>eps_growth, pe_ratio</t>
+          <t>price_to_fcf</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -7037,23 +7042,18 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>SMCI</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>94.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="C26" t="n">
-        <v>94.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
           <t>HIGH</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>price_to_fcf</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -7296,7 +7296,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>55.79</v>
+        <v>55.21</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/reports/investment_dashboard.xlsx
+++ b/reports/investment_dashboard.xlsx
@@ -534,7 +534,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>55.21</v>
+        <v>55.15</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>415.3200073242188</v>
+        <v>414</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -581,7 +581,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>54.15</v>
+        <v>53.88</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -589,7 +589,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>958.72998046875</v>
+        <v>933.4400024414062</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>52.71</v>
+        <v>51.86</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>226.1900024414062</v>
+        <v>206.6300048828125</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -685,7 +685,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>51.86</v>
+        <v>51.35</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -693,7 +693,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>195.6900024414062</v>
+        <v>189.2599945068359</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -737,7 +737,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>51.64</v>
+        <v>51.04</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -745,7 +745,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>186.3800048828125</v>
+        <v>179.9199981689453</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>50.86</v>
+        <v>50.44</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>220.7799987792969</v>
+        <v>217.4400024414062</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -841,15 +841,15 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>50.31</v>
+        <v>49.64</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RESEARCH</t>
+          <t>REJECT</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>349.8299865722656</v>
+        <v>335.4599914550781</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -869,7 +869,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Industry Growth; Valuation; Competitive Advantage; Catalysts; Inflation Resilience</t>
+          <t>Industry Growth; Valuation; Competitive Advantage; Momentum; Catalysts; Inflation Resilience</t>
         </is>
       </c>
     </row>
@@ -888,7 +888,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>49.01</v>
+        <v>48.83</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>456.010009765625</v>
+        <v>425</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>47.52</v>
+        <v>47.69</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -943,7 +943,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>18.67000007629395</v>
+        <v>18.13999938964844</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -982,7 +982,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>47.41</v>
+        <v>47.15</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -990,7 +990,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>470.7200012207031</v>
+        <v>459.6099853515625</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>46.58</v>
+        <v>46.7</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -1042,7 +1042,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>339.3500061035156</v>
+        <v>335.0199890136719</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>46.32</v>
+        <v>45.59</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -1089,7 +1089,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>211.6600036621094</v>
+        <v>210.3899993896484</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -1133,7 +1133,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>45.04</v>
+        <v>44.45</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -1141,7 +1141,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>458.3900146484375</v>
+        <v>441.8500061035156</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -1180,7 +1180,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>44.44</v>
+        <v>44.43</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>370.3399963378906</v>
+        <v>369.6799926757812</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -1232,7 +1232,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>43.77</v>
+        <v>43.64</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>237.0399932861328</v>
+        <v>223.8399963378906</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>42.95</v>
+        <v>42.86</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>258.7200012207031</v>
+        <v>255.9700012207031</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1336,7 +1336,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>42.82</v>
+        <v>42.27</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>72.81999969482422</v>
+        <v>70.04000091552734</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1388,7 +1388,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>42.31</v>
+        <v>42.11</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -1396,7 +1396,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>259.7699890136719</v>
+        <v>254.9199981689453</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Industry Growth; Competitive Advantage; Catalysts; Inflation Resilience</t>
+          <t>Industry Growth; Competitive Advantage; Momentum; Catalysts; Inflation Resilience</t>
         </is>
       </c>
     </row>
@@ -1426,16 +1426,16 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>MDB</t>
+          <t>ASML</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>MongoDB, Inc.</t>
+          <t>ASML Holding N.V.</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>42.28</v>
+        <v>41.77</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -1443,7 +1443,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>453.3699951171875</v>
+        <v>1665.140014648438</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1451,14 +1451,14 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>88.2</v>
+        <v>100</v>
       </c>
       <c r="I20" t="n">
-        <v>88.2</v>
+        <v>100</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Balance Sheet; Momentum</t>
+          <t>Earnings Fcf; Balance Sheet</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1473,16 +1473,16 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>ASML</t>
+          <t>MDB</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>ASML Holding N.V.</t>
+          <t>MongoDB, Inc.</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>42.14</v>
+        <v>41.77</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -1490,7 +1490,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1696.010009765625</v>
+        <v>434.2099914550781</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1498,14 +1498,14 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>100</v>
+        <v>88.2</v>
       </c>
       <c r="I21" t="n">
-        <v>100</v>
+        <v>88.2</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Earnings Fcf; Balance Sheet</t>
+          <t>Balance Sheet</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1529,7 +1529,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>41.81</v>
+        <v>41.62</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -1537,7 +1537,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>331.4299926757812</v>
+        <v>319.7999877929688</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1572,16 +1572,16 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>NET</t>
+          <t>SMCI</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Cloudflare, Inc.</t>
+          <t>Super Micro Computer, Inc.</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>41.76</v>
+        <v>41.43</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>305.1099853515625</v>
+        <v>36.70999908447266</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1597,24 +1597,24 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>88.2</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="I23" t="n">
-        <v>88.2</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Revenue Growth</t>
+          <t>Revenue Growth; Valuation</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Industry Growth; Valuation; Competitive Advantage; Catalysts; Inflation Resilience</t>
+          <t>Industry Growth; Balance Sheet; Competitive Advantage; Momentum; Catalysts; Inflation Resilience</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>Excessive price-to-sales valuation</t>
+          <t>Negative free cash flow / unprofitable growth</t>
         </is>
       </c>
     </row>
@@ -1624,16 +1624,16 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>SMCI</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Super Micro Computer, Inc.</t>
+          <t>Microsoft Corporation</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>41.57</v>
+        <v>41.25</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -1641,7 +1641,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>37.27999877929688</v>
+        <v>501.0199890136719</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1649,24 +1649,19 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>94.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="I24" t="n">
-        <v>94.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Revenue Growth; Valuation</t>
+          <t>Earnings Fcf</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>Industry Growth; Balance Sheet; Competitive Advantage; Momentum; Catalysts; Inflation Resilience</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>Negative free cash flow / unprofitable growth</t>
+          <t>Industry Growth; Valuation; Competitive Advantage; Catalysts; Inflation Resilience</t>
         </is>
       </c>
     </row>
@@ -1676,16 +1671,16 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>PANW</t>
+          <t>NET</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Palo Alto Networks, Inc.</t>
+          <t>Cloudflare, Inc.</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>41.4</v>
+        <v>40.98</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -1693,22 +1688,22 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>382.1300048828125</v>
+        <v>285.510009765625</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>94.09999999999999</v>
+        <v>88.2</v>
       </c>
       <c r="I25" t="n">
-        <v>94.09999999999999</v>
+        <v>88.2</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Revenue Growth; Momentum</t>
+          <t>Revenue Growth</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -1718,7 +1713,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>Excessive price-to-sales valuation; Very high earnings multiple</t>
+          <t>Excessive price-to-sales valuation</t>
         </is>
       </c>
     </row>
@@ -1728,16 +1723,16 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>PANW</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Microsoft Corporation</t>
+          <t>Palo Alto Networks, Inc.</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>41.32</v>
+        <v>40.91</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -1745,27 +1740,32 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>507.2900085449219</v>
+        <v>362.0899963378906</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>100</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="I26" t="n">
-        <v>100</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Earnings Fcf</t>
+          <t>Revenue Growth</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
           <t>Industry Growth; Valuation; Competitive Advantage; Catalysts; Inflation Resilience</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>Excessive price-to-sales valuation; Very high earnings multiple</t>
         </is>
       </c>
     </row>
@@ -1784,7 +1784,7 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>40.64</v>
+        <v>40.52</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -1792,7 +1792,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>241.9100036621094</v>
+        <v>234.8200073242188</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1827,16 +1827,16 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>CRWD</t>
+          <t>META</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>CrowdStrike Holdings, Inc.</t>
+          <t>Meta Platforms, Inc.</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>40.25</v>
+        <v>40.24</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -1844,32 +1844,27 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>231</v>
+        <v>578.5399780273438</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>94.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="I28" t="n">
-        <v>94.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Balance Sheet; Momentum</t>
+          <t>Revenue Growth</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>Industry Growth; Valuation; Competitive Advantage; Catalysts; Inflation Resilience</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>Excessive price-to-sales valuation; Very high earnings multiple</t>
+          <t>Industry Growth; Competitive Advantage; Momentum; Catalysts; Inflation Resilience</t>
         </is>
       </c>
     </row>
@@ -1879,16 +1874,16 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>META</t>
+          <t>CRWD</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Meta Platforms, Inc.</t>
+          <t>CrowdStrike Holdings, Inc.</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>40.16</v>
+        <v>39.63</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -1896,27 +1891,32 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>572.3400268554688</v>
+        <v>215.0700073242188</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>100</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="I29" t="n">
-        <v>100</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Revenue Growth</t>
+          <t>Balance Sheet</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>Industry Growth; Competitive Advantage; Momentum; Catalysts; Inflation Resilience</t>
+          <t>Industry Growth; Valuation; Competitive Advantage; Catalysts; Inflation Resilience</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>Excessive price-to-sales valuation; Very high earnings multiple</t>
         </is>
       </c>
     </row>
@@ -1935,7 +1935,7 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>35.86</v>
+        <v>35.66</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -1943,7 +1943,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>147.9900054931641</v>
+        <v>142.8999938964844</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1977,7 +1977,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>31.11</v>
+        <v>30.79</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -1985,7 +1985,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>149.1199951171875</v>
+        <v>141.3200073242188</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -2131,13 +2131,13 @@
         <v>8.84</v>
       </c>
       <c r="F2" t="n">
-        <v>8.69</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>4.99</v>
+        <v>4.91</v>
       </c>
       <c r="I2" t="n">
         <v>2.69</v>
@@ -2149,7 +2149,7 @@
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>55.21</v>
+        <v>55.15</v>
       </c>
     </row>
     <row r="3">
@@ -2171,13 +2171,13 @@
         <v>9.02</v>
       </c>
       <c r="F3" t="n">
-        <v>4.85</v>
+        <v>4.94</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>6.78</v>
+        <v>6.42</v>
       </c>
       <c r="I3" t="n">
         <v>3.5</v>
@@ -2189,7 +2189,7 @@
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>54.15</v>
+        <v>53.88</v>
       </c>
     </row>
     <row r="4">
@@ -2211,13 +2211,13 @@
         <v>9.91</v>
       </c>
       <c r="F4" t="n">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>6.79</v>
+        <v>5.91</v>
       </c>
       <c r="I4" t="n">
         <v>3.54</v>
@@ -2229,7 +2229,7 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>52.71</v>
+        <v>51.86</v>
       </c>
     </row>
     <row r="5">
@@ -2251,13 +2251,13 @@
         <v>10</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.83</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>7.42</v>
+        <v>6.89</v>
       </c>
       <c r="I5" t="n">
         <v>3.63</v>
@@ -2269,7 +2269,7 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>51.86</v>
+        <v>51.35</v>
       </c>
     </row>
     <row r="6">
@@ -2291,13 +2291,13 @@
         <v>9.890000000000001</v>
       </c>
       <c r="F6" t="n">
-        <v>0.64</v>
+        <v>0.66</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>7.76</v>
+        <v>7.14</v>
       </c>
       <c r="I6" t="n">
         <v>3.35</v>
@@ -2309,7 +2309,7 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>51.64</v>
+        <v>51.04</v>
       </c>
     </row>
     <row r="7">
@@ -2331,13 +2331,13 @@
         <v>8.08</v>
       </c>
       <c r="F7" t="n">
-        <v>3.88</v>
+        <v>3.91</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>5.46</v>
+        <v>5.01</v>
       </c>
       <c r="I7" t="n">
         <v>3.44</v>
@@ -2349,7 +2349,7 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>50.86</v>
+        <v>50.44</v>
       </c>
     </row>
     <row r="8">
@@ -2371,13 +2371,13 @@
         <v>8.9</v>
       </c>
       <c r="F8" t="n">
-        <v>3.15</v>
+        <v>3.37</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>4.51</v>
+        <v>3.62</v>
       </c>
       <c r="I8" t="n">
         <v>3.75</v>
@@ -2389,7 +2389,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>50.31</v>
+        <v>49.64</v>
       </c>
     </row>
     <row r="9">
@@ -2411,13 +2411,13 @@
         <v>6.33</v>
       </c>
       <c r="F9" t="n">
-        <v>5.82</v>
+        <v>6</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>6.84</v>
+        <v>6.48</v>
       </c>
       <c r="I9" t="n">
         <v>3.54</v>
@@ -2429,7 +2429,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>49.01</v>
+        <v>48.83</v>
       </c>
     </row>
     <row r="10">
@@ -2451,7 +2451,7 @@
         <v>9.699999999999999</v>
       </c>
       <c r="F10" t="n">
-        <v>6.39</v>
+        <v>6.56</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -2469,7 +2469,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>47.52</v>
+        <v>47.69</v>
       </c>
     </row>
     <row r="11">
@@ -2491,13 +2491,13 @@
         <v>8.77</v>
       </c>
       <c r="F11" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>5.96</v>
+        <v>5.67</v>
       </c>
       <c r="I11" t="n">
         <v>3.45</v>
@@ -2509,7 +2509,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>47.41</v>
+        <v>47.15</v>
       </c>
     </row>
     <row r="12">
@@ -2531,13 +2531,13 @@
         <v>8.34</v>
       </c>
       <c r="F12" t="n">
-        <v>4.46</v>
+        <v>4.51</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>4.3</v>
+        <v>4.37</v>
       </c>
       <c r="I12" t="n">
         <v>3.53</v>
@@ -2549,7 +2549,7 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>46.58</v>
+        <v>46.7</v>
       </c>
     </row>
     <row r="13">
@@ -2562,13 +2562,13 @@
         <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>12.88</v>
+        <v>12.78</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>7.21</v>
+        <v>7.13</v>
       </c>
       <c r="F13" t="n">
         <v>0.91</v>
@@ -2577,7 +2577,7 @@
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>6.79</v>
+        <v>6.24</v>
       </c>
       <c r="I13" t="n">
         <v>3.53</v>
@@ -2589,7 +2589,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>46.32</v>
+        <v>45.59</v>
       </c>
     </row>
     <row r="14">
@@ -2611,13 +2611,13 @@
         <v>7.78</v>
       </c>
       <c r="F14" t="n">
-        <v>2.32</v>
+        <v>2.53</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>5.18</v>
+        <v>4.38</v>
       </c>
       <c r="I14" t="n">
         <v>3.58</v>
@@ -2629,7 +2629,7 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>45.04</v>
+        <v>44.45</v>
       </c>
     </row>
     <row r="15">
@@ -2657,7 +2657,7 @@
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>3.72</v>
+        <v>3.71</v>
       </c>
       <c r="I15" t="n">
         <v>3.53</v>
@@ -2669,7 +2669,7 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>44.44</v>
+        <v>44.43</v>
       </c>
     </row>
     <row r="16">
@@ -2691,13 +2691,13 @@
         <v>8.98</v>
       </c>
       <c r="F16" t="n">
-        <v>0.83</v>
+        <v>0.88</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>5.18</v>
+        <v>5</v>
       </c>
       <c r="I16" t="n">
         <v>3.67</v>
@@ -2709,7 +2709,7 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>43.77</v>
+        <v>43.64</v>
       </c>
     </row>
     <row r="17">
@@ -2731,13 +2731,13 @@
         <v>7.41</v>
       </c>
       <c r="F17" t="n">
-        <v>3.42</v>
+        <v>3.48</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>4.26</v>
+        <v>4.11</v>
       </c>
       <c r="I17" t="n">
         <v>3.56</v>
@@ -2749,7 +2749,7 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>42.95</v>
+        <v>42.86</v>
       </c>
     </row>
     <row r="18">
@@ -2771,13 +2771,13 @@
         <v>4.02</v>
       </c>
       <c r="F18" t="n">
-        <v>7.23</v>
+        <v>7.39</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>5.11</v>
+        <v>4.4</v>
       </c>
       <c r="I18" t="n">
         <v>3.63</v>
@@ -2789,7 +2789,7 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>42.82</v>
+        <v>42.27</v>
       </c>
     </row>
     <row r="19">
@@ -2811,13 +2811,13 @@
         <v>6.64</v>
       </c>
       <c r="F19" t="n">
-        <v>6.51</v>
+        <v>6.55</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>4.19</v>
+        <v>3.95</v>
       </c>
       <c r="I19" t="n">
         <v>3.47</v>
@@ -2829,38 +2829,38 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>42.31</v>
+        <v>42.11</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>MDB</t>
+          <t>ASML</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>11.32</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="C20" t="n">
-        <v>7.5</v>
+        <v>14.28</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>9.880000000000001</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="F20" t="n">
-        <v>1.45</v>
+        <v>0.59</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>8.390000000000001</v>
+        <v>5.33</v>
       </c>
       <c r="I20" t="n">
-        <v>3.74</v>
+        <v>2.75</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2869,38 +2869,38 @@
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>42.28</v>
+        <v>41.77</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ASML</t>
+          <t>MDB</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>9.859999999999999</v>
+        <v>11.32</v>
       </c>
       <c r="C21" t="n">
-        <v>14.28</v>
+        <v>7.5</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>8.960000000000001</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="F21" t="n">
-        <v>0.58</v>
+        <v>1.66</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>5.71</v>
+        <v>7.67</v>
       </c>
       <c r="I21" t="n">
-        <v>2.75</v>
+        <v>3.74</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>42.14</v>
+        <v>41.77</v>
       </c>
     </row>
     <row r="22">
@@ -2931,13 +2931,13 @@
         <v>7.58</v>
       </c>
       <c r="F22" t="n">
-        <v>0.98</v>
+        <v>1.01</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>7.74</v>
+        <v>7.52</v>
       </c>
       <c r="I22" t="n">
         <v>3.57</v>
@@ -2949,38 +2949,38 @@
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>41.81</v>
+        <v>41.62</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>NET</t>
+          <t>SMCI</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>15</v>
       </c>
       <c r="C23" t="n">
-        <v>7.5</v>
+        <v>7.23</v>
       </c>
       <c r="D23" t="n">
         <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>7.71</v>
+        <v>2.23</v>
       </c>
       <c r="F23" t="n">
-        <v>0.55</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>7.36</v>
+        <v>3.54</v>
       </c>
       <c r="I23" t="n">
-        <v>3.64</v>
+        <v>3.54</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2989,38 +2989,38 @@
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>41.76</v>
+        <v>41.43</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>SMCI</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>15</v>
+        <v>8.51</v>
       </c>
       <c r="C24" t="n">
-        <v>7.23</v>
+        <v>14.63</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>2.23</v>
+        <v>6.87</v>
       </c>
       <c r="F24" t="n">
-        <v>9.880000000000001</v>
+        <v>2.9</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>3.69</v>
+        <v>4.89</v>
       </c>
       <c r="I24" t="n">
-        <v>3.54</v>
+        <v>3.45</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -3029,17 +3029,17 @@
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>41.57</v>
+        <v>41.25</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>PANW</t>
+          <t>NET</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>13.54</v>
+        <v>15</v>
       </c>
       <c r="C25" t="n">
         <v>7.5</v>
@@ -3048,19 +3048,19 @@
         <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>7.97</v>
+        <v>7.71</v>
       </c>
       <c r="F25" t="n">
-        <v>0.53</v>
+        <v>0.59</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>8.289999999999999</v>
+        <v>6.54</v>
       </c>
       <c r="I25" t="n">
-        <v>3.57</v>
+        <v>3.64</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -3069,38 +3069,38 @@
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>41.4</v>
+        <v>40.98</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>PANW</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>8.51</v>
+        <v>13.54</v>
       </c>
       <c r="C26" t="n">
-        <v>14.63</v>
+        <v>7.5</v>
       </c>
       <c r="D26" t="n">
         <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>6.87</v>
+        <v>7.97</v>
       </c>
       <c r="F26" t="n">
-        <v>2.84</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>5.02</v>
+        <v>7.77</v>
       </c>
       <c r="I26" t="n">
-        <v>3.45</v>
+        <v>3.57</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3109,7 +3109,7 @@
         <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>41.32</v>
+        <v>40.91</v>
       </c>
     </row>
     <row r="27">
@@ -3131,13 +3131,13 @@
         <v>9.449999999999999</v>
       </c>
       <c r="F27" t="n">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>5.72</v>
+        <v>5.59</v>
       </c>
       <c r="I27" t="n">
         <v>3.7</v>
@@ -3149,38 +3149,38 @@
         <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>40.64</v>
+        <v>40.52</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>CRWD</t>
+          <t>META</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>11.55</v>
+        <v>12.38</v>
       </c>
       <c r="C28" t="n">
-        <v>7.5</v>
+        <v>10</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>9.300000000000001</v>
+        <v>7.23</v>
       </c>
       <c r="F28" t="n">
-        <v>0.29</v>
+        <v>5.57</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>8.140000000000001</v>
+        <v>1.57</v>
       </c>
       <c r="I28" t="n">
-        <v>3.47</v>
+        <v>3.49</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3189,38 +3189,38 @@
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>40.25</v>
+        <v>40.24</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>META</t>
+          <t>CRWD</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>12.38</v>
+        <v>11.55</v>
       </c>
       <c r="C29" t="n">
-        <v>10</v>
+        <v>7.5</v>
       </c>
       <c r="D29" t="n">
         <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>7.23</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="F29" t="n">
-        <v>5.62</v>
+        <v>0.32</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>1.44</v>
+        <v>7.48</v>
       </c>
       <c r="I29" t="n">
-        <v>3.49</v>
+        <v>3.48</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3229,7 +3229,7 @@
         <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>40.16</v>
+        <v>39.63</v>
       </c>
     </row>
     <row r="30">
@@ -3251,13 +3251,13 @@
         <v>6.78</v>
       </c>
       <c r="F30" t="n">
-        <v>3.31</v>
+        <v>3.48</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>5.64</v>
+        <v>5.27</v>
       </c>
       <c r="I30" t="n">
         <v>3.57</v>
@@ -3269,7 +3269,7 @@
         <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>35.86</v>
+        <v>35.66</v>
       </c>
     </row>
     <row r="31">
@@ -3291,13 +3291,13 @@
         <v>0.8</v>
       </c>
       <c r="F31" t="n">
-        <v>6.4</v>
+        <v>6.72</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>2.19</v>
+        <v>1.55</v>
       </c>
       <c r="I31" t="n">
         <v>3.58</v>
@@ -3309,7 +3309,7 @@
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>31.11</v>
+        <v>30.79</v>
       </c>
     </row>
   </sheetData>
@@ -3343,13 +3343,13 @@
     <col width="15" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="18" customWidth="1" min="16" max="16"/>
-    <col width="11" customWidth="1" min="17" max="17"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
     <col width="16" customWidth="1" min="18" max="18"/>
     <col width="19" customWidth="1" min="19" max="19"/>
-    <col width="22" customWidth="1" min="20" max="20"/>
+    <col width="23" customWidth="1" min="20" max="20"/>
     <col width="23" customWidth="1" min="21" max="21"/>
-    <col width="21" customWidth="1" min="22" max="22"/>
-    <col width="22" customWidth="1" min="23" max="23"/>
+    <col width="23" customWidth="1" min="22" max="22"/>
+    <col width="23" customWidth="1" min="23" max="23"/>
     <col width="18" customWidth="1" min="24" max="24"/>
     <col width="24" customWidth="1" min="25" max="25"/>
     <col width="17" customWidth="1" min="26" max="26"/>
@@ -3533,10 +3533,10 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2154046423040</v>
+        <v>2147200270336</v>
       </c>
       <c r="F2" t="n">
-        <v>415.3200073242188</v>
+        <v>414</v>
       </c>
       <c r="G2" t="n">
         <v>4440492343296</v>
@@ -3545,7 +3545,7 @@
         <v>0.36</v>
       </c>
       <c r="I2" t="n">
-        <v>13.44</v>
+        <v>13.5</v>
       </c>
       <c r="J2" t="n">
         <v>0.774</v>
@@ -3566,25 +3566,25 @@
         <v>0.60344005</v>
       </c>
       <c r="Q2" t="n">
-        <v>30.901787</v>
+        <v>30.666666</v>
       </c>
       <c r="R2" t="n">
-        <v>0.4850918</v>
+        <v>0.48355004</v>
       </c>
       <c r="S2" t="n">
-        <v>2.947413446776762</v>
+        <v>2.938045755197498</v>
       </c>
       <c r="T2" t="n">
-        <v>0.02738406264494442</v>
+        <v>0.02411873840445278</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.044389470032138</v>
+        <v>-0.07101227561025381</v>
       </c>
       <c r="V2" t="n">
-        <v>0.1144900263701596</v>
+        <v>0.1274114960976349</v>
       </c>
       <c r="W2" t="n">
-        <v>0.8188297145954699</v>
+        <v>0.8130490679022422</v>
       </c>
       <c r="X2" t="n">
         <v>0.00013</v>
@@ -3594,7 +3594,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>2026-08-31T22:50:49.888808+00:00</t>
+          <t>2026-09-01T20:23:04.750935+00:00</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
@@ -3625,10 +3625,10 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1082783105024</v>
+        <v>1054220746752</v>
       </c>
       <c r="F3" t="n">
-        <v>958.72998046875</v>
+        <v>933.4400024414062</v>
       </c>
       <c r="G3" t="n">
         <v>90273996800</v>
@@ -3658,35 +3658,35 @@
         <v>0.80370003</v>
       </c>
       <c r="Q3" t="n">
-        <v>21.680912</v>
+        <v>21.109</v>
       </c>
       <c r="R3" t="n">
-        <v>11.994408</v>
+        <v>11.678011</v>
       </c>
       <c r="S3" t="n">
-        <v>141.7348173012107</v>
+        <v>137.9960439378381</v>
       </c>
       <c r="T3" t="n">
-        <v>0.1648784933009129</v>
+        <v>0.1341506010890707</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.07399576867898083</v>
+        <v>-0.1226542222450672</v>
       </c>
       <c r="V3" t="n">
-        <v>1.326261002670978</v>
+        <v>1.263250877901507</v>
       </c>
       <c r="W3" t="n">
-        <v>7.068806989239613</v>
+        <v>6.855963464985801</v>
       </c>
       <c r="X3" t="n">
         <v>0.00238</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.79989</v>
+        <v>0.79999</v>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>2026-08-31T22:50:46.301421+00:00</t>
+          <t>2026-09-01T20:23:01.479622+00:00</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
@@ -3717,10 +3717,10 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>42508943360</v>
+        <v>38832943104</v>
       </c>
       <c r="F4" t="n">
-        <v>226.1900024414062</v>
+        <v>206.6300048828125</v>
       </c>
       <c r="G4" t="n">
         <v>1335116032</v>
@@ -3750,35 +3750,35 @@
         <v>0.35661998</v>
       </c>
       <c r="Q4" t="n">
-        <v>90.11554</v>
+        <v>82.32271</v>
       </c>
       <c r="R4" t="n">
-        <v>31.839138</v>
+        <v>29.08582</v>
       </c>
       <c r="S4" t="n">
-        <v>169.4865502401083</v>
+        <v>154.830043801102</v>
       </c>
       <c r="T4" t="n">
-        <v>0.092758087051098</v>
+        <v>-0.001739217357349387</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0003980377508234767</v>
+        <v>-0.09768556819732532</v>
       </c>
       <c r="V4" t="n">
-        <v>1.014696795266853</v>
+        <v>0.809052728720856</v>
       </c>
       <c r="W4" t="n">
-        <v>0.8381211806140034</v>
+        <v>0.6791678872891889</v>
       </c>
       <c r="X4" t="n">
         <v>0.09436</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.73555</v>
+        <v>0.73853</v>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>2026-08-31T22:50:46.904788+00:00</t>
+          <t>2026-09-01T20:23:02.071712+00:00</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
@@ -3809,10 +3809,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>246809067520</v>
+        <v>238699380736</v>
       </c>
       <c r="F5" t="n">
-        <v>195.6900024414062</v>
+        <v>189.2599945068359</v>
       </c>
       <c r="G5" t="n">
         <v>10540800000</v>
@@ -3821,7 +3821,7 @@
         <v>0.377</v>
       </c>
       <c r="I5" t="n">
-        <v>3.17</v>
+        <v>3.15</v>
       </c>
       <c r="J5" t="n">
         <v>0.357</v>
@@ -3842,35 +3842,35 @@
         <v>0.45393002</v>
       </c>
       <c r="Q5" t="n">
-        <v>61.73186</v>
+        <v>60.082535</v>
       </c>
       <c r="R5" t="n">
-        <v>23.414642</v>
+        <v>22.64528</v>
       </c>
       <c r="S5" t="n">
-        <v>63.42240008220392</v>
+        <v>61.3384580093928</v>
       </c>
       <c r="T5" t="n">
-        <v>0.08505681074990323</v>
+        <v>0.0494038708166511</v>
       </c>
       <c r="U5" t="n">
-        <v>0.146531584478875</v>
+        <v>0.07945013705756976</v>
       </c>
       <c r="V5" t="n">
-        <v>0.4658427149169007</v>
+        <v>0.4637276878568719</v>
       </c>
       <c r="W5" t="n">
-        <v>0.4331014138991418</v>
+        <v>0.3860123784479079</v>
       </c>
       <c r="X5" t="n">
         <v>0.17247</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.73297</v>
+        <v>0.7335</v>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>2026-08-31T22:50:51.257075+00:00</t>
+          <t>2026-09-01T20:23:06.087990+00:00</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
@@ -3901,10 +3901,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>447882035200</v>
+        <v>432358260736</v>
       </c>
       <c r="F6" t="n">
-        <v>186.3800048828125</v>
+        <v>179.9199981689453</v>
       </c>
       <c r="G6" t="n">
         <v>6155940864</v>
@@ -3934,35 +3934,35 @@
         <v>0.47120997</v>
       </c>
       <c r="Q6" t="n">
-        <v>159.29915</v>
+        <v>153.77779</v>
       </c>
       <c r="R6" t="n">
-        <v>72.75606500000001</v>
+        <v>70.234314</v>
       </c>
       <c r="S6" t="n">
-        <v>207.4387935881448</v>
+        <v>200.2488801876025</v>
       </c>
       <c r="T6" t="n">
-        <v>0.5145458197662451</v>
+        <v>0.4620510461433924</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1601619169864854</v>
+        <v>0.18236183435575</v>
       </c>
       <c r="V6" t="n">
-        <v>0.3585538418691643</v>
+        <v>0.2393745294365768</v>
       </c>
       <c r="W6" t="n">
-        <v>0.1893305908863816</v>
+        <v>0.1481079092636162</v>
       </c>
       <c r="X6" t="n">
         <v>0.03477</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.6486499999999999</v>
+        <v>0.6487000000000001</v>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>2026-08-31T22:50:44.364786+00:00</t>
+          <t>2026-09-01T20:23:00.193279+00:00</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr">
@@ -3993,10 +3993,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5331174293504</v>
+        <v>5250523594752</v>
       </c>
       <c r="F7" t="n">
-        <v>220.7799987792969</v>
+        <v>217.4400024414062</v>
       </c>
       <c r="G7" t="n">
         <v>302970011648</v>
@@ -4026,35 +4026,35 @@
         <v>0.66236997</v>
       </c>
       <c r="Q7" t="n">
-        <v>27.876263</v>
+        <v>27.454546</v>
       </c>
       <c r="R7" t="n">
-        <v>17.596376</v>
+        <v>17.330175</v>
       </c>
       <c r="S7" t="n">
-        <v>127.5099315806267</v>
+        <v>125.5809447357719</v>
       </c>
       <c r="T7" t="n">
-        <v>0.09977583451704541</v>
+        <v>0.08313824379280832</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0148096147901412</v>
+        <v>-0.02300768998086622</v>
       </c>
       <c r="V7" t="n">
-        <v>0.2475268098144381</v>
+        <v>0.1930359905499135</v>
       </c>
       <c r="W7" t="n">
-        <v>0.2692276652833767</v>
+        <v>0.250026579236476</v>
       </c>
       <c r="X7" t="n">
         <v>0.04008</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.71499</v>
+        <v>0.715</v>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>2026-08-31T22:50:43.972738+00:00</t>
+          <t>2026-09-01T20:22:59.922900+00:00</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr">
@@ -4085,10 +4085,10 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>54692683776</v>
+        <v>52446068736</v>
       </c>
       <c r="F8" t="n">
-        <v>349.8299865722656</v>
+        <v>335.4599914550781</v>
       </c>
       <c r="G8" t="n">
         <v>4464031232</v>
@@ -4118,35 +4118,35 @@
         <v>0.33161</v>
       </c>
       <c r="Q8" t="n">
-        <v>48.05357</v>
+        <v>46.079666</v>
       </c>
       <c r="R8" t="n">
-        <v>12.25186</v>
+        <v>11.7485895</v>
       </c>
       <c r="S8" t="n">
-        <v>125.0457902026929</v>
+        <v>119.9092758910414</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.04857356944859204</v>
+        <v>-0.08765539115103949</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.0531572646860321</v>
+        <v>-0.1455860739977048</v>
       </c>
       <c r="V8" t="n">
-        <v>0.09352906632436575</v>
+        <v>0.02994415880569301</v>
       </c>
       <c r="W8" t="n">
-        <v>1.966217225464943</v>
+        <v>1.844373676648285</v>
       </c>
       <c r="X8" t="n">
         <v>0.00202</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.00471</v>
+        <v>1.005</v>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>2026-08-31T22:50:47.282848+00:00</t>
+          <t>2026-09-01T20:23:02.435456+00:00</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr">
@@ -4177,10 +4177,10 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>294647398400</v>
+        <v>274610520064</v>
       </c>
       <c r="F9" t="n">
-        <v>456.010009765625</v>
+        <v>425</v>
       </c>
       <c r="G9" t="n">
         <v>134001999872</v>
@@ -4210,35 +4210,35 @@
         <v>0.08857000600000001</v>
       </c>
       <c r="Q9" t="n">
-        <v>36.335457</v>
+        <v>33.86454</v>
       </c>
       <c r="R9" t="n">
-        <v>2.1988285</v>
+        <v>2.0493016</v>
       </c>
       <c r="S9" t="n">
-        <v>54.22168412473707</v>
+        <v>50.53445222016248</v>
       </c>
       <c r="T9" t="n">
-        <v>0.1249229475748399</v>
+        <v>0.04842490840284741</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.01973655725354495</v>
+        <v>-0.02207095631354228</v>
       </c>
       <c r="V9" t="n">
-        <v>2.094116833404496</v>
+        <v>1.780979770980133</v>
       </c>
       <c r="W9" t="n">
-        <v>2.780769057304163</v>
+        <v>2.523665741855378</v>
       </c>
       <c r="X9" t="n">
         <v>0.07491</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.75596</v>
+        <v>0.7561</v>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>2026-08-31T22:50:51.617375+00:00</t>
+          <t>2026-09-01T20:23:06.374543+00:00</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr">
@@ -4269,10 +4269,10 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>9673305088</v>
+        <v>9398701056</v>
       </c>
       <c r="F10" t="n">
-        <v>18.67000007629395</v>
+        <v>18.13999938964844</v>
       </c>
       <c r="G10" t="n">
         <v>1672329984</v>
@@ -4299,25 +4299,25 @@
         <v>0.07274</v>
       </c>
       <c r="Q10" t="n">
-        <v>31.116665</v>
+        <v>30.233332</v>
       </c>
       <c r="R10" t="n">
-        <v>5.784328</v>
+        <v>5.6201234</v>
       </c>
       <c r="S10" t="n">
-        <v>18.90965967767774</v>
+        <v>18.3728556852471</v>
       </c>
       <c r="T10" t="n">
-        <v>0.4631661239343101</v>
+        <v>0.4216300207102781</v>
       </c>
       <c r="U10" t="n">
-        <v>0.4251908040173129</v>
+        <v>0.4893266777620693</v>
       </c>
       <c r="V10" t="n">
-        <v>0.7399814420125106</v>
+        <v>0.6953270759819079</v>
       </c>
       <c r="W10" t="n">
-        <v>0.6789568586722401</v>
+        <v>0.6312949259294358</v>
       </c>
       <c r="X10" t="n">
         <v>0.09236999999999999</v>
@@ -4327,7 +4327,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>2026-08-31T22:50:54.089657+00:00</t>
+          <t>2026-09-01T20:23:08.798606+00:00</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr">
@@ -4358,10 +4358,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>768438632448</v>
+        <v>750301806592</v>
       </c>
       <c r="F11" t="n">
-        <v>470.7200012207031</v>
+        <v>459.6099853515625</v>
       </c>
       <c r="G11" t="n">
         <v>41305001984</v>
@@ -4391,35 +4391,35 @@
         <v>0.1725</v>
       </c>
       <c r="Q11" t="n">
-        <v>120.38875</v>
+        <v>117.54731</v>
       </c>
       <c r="R11" t="n">
-        <v>18.60401</v>
+        <v>18.164913</v>
       </c>
       <c r="S11" t="n">
-        <v>86.91270293969026</v>
+        <v>84.86137380118798</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.01140395410140804</v>
+        <v>-0.03473697103211071</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.077254823838803</v>
+        <v>-0.1187444784386871</v>
       </c>
       <c r="V11" t="n">
-        <v>1.351131239376256</v>
+        <v>1.314016698471816</v>
       </c>
       <c r="W11" t="n">
-        <v>1.894422843803598</v>
+        <v>1.826108169170548</v>
       </c>
       <c r="X11" t="n">
         <v>0.00424</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.75394994</v>
+        <v>0.75398004</v>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>2026-08-31T22:50:44.833177+00:00</t>
+          <t>2026-09-01T20:23:00.433819+00:00</t>
         </is>
       </c>
       <c r="AD11" t="inlineStr">
@@ -4450,10 +4450,10 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4150228680704</v>
+        <v>4097272709120</v>
       </c>
       <c r="F12" t="n">
-        <v>339.3500061035156</v>
+        <v>335.0199890136719</v>
       </c>
       <c r="G12" t="n">
         <v>445865984000</v>
@@ -4462,7 +4462,7 @@
         <v>0.242</v>
       </c>
       <c r="I12" t="n">
-        <v>19.93</v>
+        <v>19.92</v>
       </c>
       <c r="J12" t="n">
         <v>2.94</v>
@@ -4483,35 +4483,35 @@
         <v>0.34033</v>
       </c>
       <c r="Q12" t="n">
-        <v>17.027096</v>
+        <v>16.818272</v>
       </c>
       <c r="R12" t="n">
-        <v>9.308242999999999</v>
+        <v>9.189470999999999</v>
       </c>
       <c r="S12" t="n">
-        <v>183.1117804948904</v>
+        <v>180.7753159309815</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.04711762151245436</v>
+        <v>-0.05927615078680903</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.09782208148452842</v>
+        <v>-0.07359378121038251</v>
       </c>
       <c r="V12" t="n">
-        <v>0.08991438545481922</v>
+        <v>0.09440194836202598</v>
       </c>
       <c r="W12" t="n">
-        <v>0.5984128597259455</v>
+        <v>0.578017530788989</v>
       </c>
       <c r="X12" t="n">
         <v>0.01596</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.81047994</v>
+        <v>0.81052</v>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>2026-08-31T22:50:48.579178+00:00</t>
+          <t>2026-09-01T20:23:03.588293+00:00</t>
         </is>
       </c>
       <c r="AD12" t="inlineStr">
@@ -4542,10 +4542,10 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>190219829248</v>
+        <v>189078470656</v>
       </c>
       <c r="F13" t="n">
-        <v>211.6600036621094</v>
+        <v>210.3899993896484</v>
       </c>
       <c r="G13" t="n">
         <v>9450300416</v>
@@ -4554,56 +4554,56 @@
         <v>0.365</v>
       </c>
       <c r="I13" t="n">
-        <v>3.01</v>
+        <v>3.03</v>
       </c>
       <c r="J13" t="n">
         <v>0.5</v>
       </c>
       <c r="K13" t="n">
-        <v>2469100032</v>
+        <v>2408049920</v>
       </c>
       <c r="M13" t="n">
         <v>3932800000</v>
       </c>
       <c r="N13" t="n">
-        <v>4962899968</v>
+        <v>5286099968</v>
       </c>
       <c r="O13" t="n">
-        <v>0.52246</v>
+        <v>0.52216</v>
       </c>
       <c r="P13" t="n">
-        <v>0.17253</v>
+        <v>0.16679001</v>
       </c>
       <c r="Q13" t="n">
-        <v>70.31894</v>
+        <v>69.43564600000001</v>
       </c>
       <c r="R13" t="n">
-        <v>20.128443</v>
+        <v>20.007668</v>
       </c>
       <c r="S13" t="n">
-        <v>77.04014692913017</v>
+        <v>78.51933179857002</v>
       </c>
       <c r="T13" t="n">
-        <v>0.1284922500384804</v>
+        <v>0.1217210606111392</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.03517189970631596</v>
+        <v>-0.2763097300440246</v>
       </c>
       <c r="V13" t="n">
-        <v>1.592951391566251</v>
+        <v>1.603849312680738</v>
       </c>
       <c r="W13" t="n">
-        <v>2.373802251070248</v>
+        <v>2.353558936137119</v>
       </c>
       <c r="X13" t="n">
         <v>0.00494</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.8214399999999999</v>
+        <v>0.8216899600000001</v>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>2026-08-31T22:50:50.930867+00:00</t>
+          <t>2026-09-01T20:23:05.787116+00:00</t>
         </is>
       </c>
       <c r="AD13" t="inlineStr">
@@ -4634,10 +4634,10 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>363777130496</v>
+        <v>350651023360</v>
       </c>
       <c r="F14" t="n">
-        <v>458.3900146484375</v>
+        <v>441.8500061035156</v>
       </c>
       <c r="G14" t="n">
         <v>30837000192</v>
@@ -4667,35 +4667,35 @@
         <v>0.33736</v>
       </c>
       <c r="Q14" t="n">
-        <v>39.550476</v>
+        <v>38.123383</v>
       </c>
       <c r="R14" t="n">
-        <v>11.796774</v>
+        <v>11.371114</v>
       </c>
       <c r="S14" t="n">
-        <v>118.2870765985104</v>
+        <v>114.0189445196211</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.09610543351666145</v>
+        <v>-0.1287205066543455</v>
       </c>
       <c r="U14" t="n">
-        <v>0.001550014609317696</v>
+        <v>-0.09739311711600507</v>
       </c>
       <c r="V14" t="n">
-        <v>0.2340871573637926</v>
+        <v>0.1899413360623652</v>
       </c>
       <c r="W14" t="n">
-        <v>1.867164712580105</v>
+        <v>1.763709298347</v>
       </c>
       <c r="X14" t="n">
         <v>0.0033000002</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.86324</v>
+        <v>0.8632099600000001</v>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>2026-08-31T22:50:45.699382+00:00</t>
+          <t>2026-09-01T20:23:01.143342+00:00</t>
         </is>
       </c>
       <c r="AD14" t="inlineStr">
@@ -4726,10 +4726,10 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1761922252800</v>
+        <v>1758782291968</v>
       </c>
       <c r="F15" t="n">
-        <v>370.3399963378906</v>
+        <v>369.6799926757812</v>
       </c>
       <c r="G15" t="n">
         <v>75464998912</v>
@@ -4738,7 +4738,7 @@
         <v>0.479</v>
       </c>
       <c r="I15" t="n">
-        <v>6.01</v>
+        <v>6</v>
       </c>
       <c r="J15" t="n">
         <v>0.854</v>
@@ -4759,35 +4759,35 @@
         <v>0.48988</v>
       </c>
       <c r="Q15" t="n">
-        <v>61.62063</v>
+        <v>61.61333</v>
       </c>
       <c r="R15" t="n">
-        <v>23.347542</v>
+        <v>23.305935</v>
       </c>
       <c r="S15" t="n">
-        <v>64.74739545056453</v>
+        <v>64.63200767714507</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.04865393161939546</v>
+        <v>-0.05034937876329959</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.1935862625328272</v>
+        <v>-0.231129298602089</v>
       </c>
       <c r="V15" t="n">
-        <v>0.1632114344825788</v>
+        <v>0.1637970780548021</v>
       </c>
       <c r="W15" t="n">
-        <v>0.254425111282889</v>
+        <v>0.252189529991439</v>
       </c>
       <c r="X15" t="n">
         <v>0.01948</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.80147004</v>
+        <v>0.80154</v>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>2026-08-31T22:50:45.280476+00:00</t>
+          <t>2026-09-01T20:23:00.778752+00:00</t>
         </is>
       </c>
       <c r="AD15" t="inlineStr">
@@ -4818,10 +4818,10 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>85115133952</v>
+        <v>80375349248</v>
       </c>
       <c r="F16" t="n">
-        <v>237.0399932861328</v>
+        <v>223.8399963378906</v>
       </c>
       <c r="G16" t="n">
         <v>3966725120</v>
@@ -4851,35 +4851,35 @@
         <v>0.00666</v>
       </c>
       <c r="Q16" t="n">
-        <v>474.08</v>
+        <v>447.68</v>
       </c>
       <c r="R16" t="n">
-        <v>21.457281</v>
+        <v>20.262394</v>
       </c>
       <c r="S16" t="n">
-        <v>80.95314249456335</v>
+        <v>76.44512554480623</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.1154233973716186</v>
+        <v>-0.1646826311967157</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.1457710129078066</v>
+        <v>-0.1682830146146006</v>
       </c>
       <c r="V16" t="n">
-        <v>1.117184666170715</v>
+        <v>1.014580101775614</v>
       </c>
       <c r="W16" t="n">
-        <v>0.7342698711465081</v>
+        <v>0.6376939444887277</v>
       </c>
       <c r="X16" t="n">
         <v>0.00619</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.92821</v>
+        <v>0.92807</v>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>2026-08-31T22:50:52.838186+00:00</t>
+          <t>2026-09-01T20:23:07.604446+00:00</t>
         </is>
       </c>
       <c r="AD16" t="inlineStr">
@@ -4910,10 +4910,10 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>99604135936</v>
+        <v>98545418240</v>
       </c>
       <c r="F17" t="n">
-        <v>258.7200012207031</v>
+        <v>255.9700012207031</v>
       </c>
       <c r="G17" t="n">
         <v>11479600128</v>
@@ -4943,35 +4943,35 @@
         <v>0.20362</v>
       </c>
       <c r="Q17" t="n">
-        <v>58.533936</v>
+        <v>57.911762</v>
       </c>
       <c r="R17" t="n">
-        <v>8.6766205</v>
+        <v>8.584394</v>
       </c>
       <c r="S17" t="n">
-        <v>36.93778864273949</v>
+        <v>36.54516749182359</v>
       </c>
       <c r="T17" t="n">
-        <v>0.07099388738878831</v>
+        <v>0.05961002384355485</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1998088656150657</v>
+        <v>-0.2345861871854436</v>
       </c>
       <c r="V17" t="n">
-        <v>0.01547892791900263</v>
+        <v>-0.006462781850907096</v>
       </c>
       <c r="W17" t="n">
-        <v>1.030615386807944</v>
+        <v>1.009031464856126</v>
       </c>
       <c r="X17" t="n">
         <v>0.00269</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.84445</v>
+        <v>0.84457</v>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>2026-08-31T22:50:51.911634+00:00</t>
+          <t>2026-09-01T20:23:06.698516+00:00</t>
         </is>
       </c>
       <c r="AD17" t="inlineStr">
@@ -5002,10 +5002,10 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5071854592</v>
+        <v>4878230016</v>
       </c>
       <c r="F18" t="n">
-        <v>72.81999969482422</v>
+        <v>70.04000091552734</v>
       </c>
       <c r="G18" t="n">
         <v>1037772032</v>
@@ -5035,32 +5035,32 @@
         <v>0.16982001</v>
       </c>
       <c r="Q18" t="n">
-        <v>34.34906</v>
+        <v>33.03774</v>
       </c>
       <c r="R18" t="n">
-        <v>4.8872533</v>
+        <v>4.700676</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.07200205732108789</v>
+        <v>-0.1074295931443372</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1124924194227175</v>
+        <v>-0.2380330470982321</v>
       </c>
       <c r="V18" t="n">
-        <v>0.3078304471211573</v>
+        <v>0.2264051859042029</v>
       </c>
       <c r="W18" t="n">
-        <v>1.580439456650297</v>
+        <v>1.48192780367583</v>
       </c>
       <c r="X18" t="n">
         <v>0.12675999</v>
       </c>
       <c r="Y18" t="n">
-        <v>0.78069</v>
+        <v>0.7793099999999999</v>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>2026-08-31T22:50:46.582882+00:00</t>
+          <t>2026-09-01T20:23:01.773461+00:00</t>
         </is>
       </c>
       <c r="AD18" t="inlineStr">
@@ -5091,10 +5091,10 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2801960484864</v>
+        <v>2749647028224</v>
       </c>
       <c r="F19" t="n">
-        <v>259.7699890136719</v>
+        <v>254.9199981689453</v>
       </c>
       <c r="G19" t="n">
         <v>775680032768</v>
@@ -5124,35 +5124,35 @@
         <v>0.13689</v>
       </c>
       <c r="Q19" t="n">
-        <v>20.881832</v>
+        <v>20.491962</v>
       </c>
       <c r="R19" t="n">
-        <v>3.6122632</v>
+        <v>3.5448213</v>
       </c>
       <c r="S19" t="n">
-        <v>870.410590401828</v>
+        <v>854.1597592691425</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.04348625871756273</v>
+        <v>-0.06134468380234348</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.00570321019772535</v>
+        <v>-0.006237294999421272</v>
       </c>
       <c r="V19" t="n">
-        <v>0.2369999476841518</v>
+        <v>0.2232832617475797</v>
       </c>
       <c r="W19" t="n">
-        <v>0.1343667642518422</v>
+        <v>0.1131877649298922</v>
       </c>
       <c r="X19" t="n">
         <v>0.08866</v>
       </c>
       <c r="Y19" t="n">
-        <v>0.6873</v>
+        <v>0.6873500299999999</v>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>2026-08-31T22:50:48.860407+00:00</t>
+          <t>2026-09-01T20:23:03.845484+00:00</t>
         </is>
       </c>
       <c r="AD19" t="inlineStr">
@@ -5164,12 +5164,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>MDB</t>
+          <t>ASML</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>MongoDB, Inc.</t>
+          <t>ASML Holding N.V.</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -5179,66 +5179,72 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Software - Infrastructure</t>
+          <t>Semiconductor Equipment &amp; Materials</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>36465422336</v>
+        <v>639580307456</v>
       </c>
       <c r="F20" t="n">
-        <v>453.3699951171875</v>
+        <v>1665.140014648438</v>
       </c>
       <c r="G20" t="n">
-        <v>2602398976</v>
+        <v>35327500288</v>
       </c>
       <c r="H20" t="n">
-        <v>0.252</v>
+        <v>0.213</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.36</v>
+        <v>29.68</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0.285</v>
       </c>
       <c r="K20" t="n">
-        <v>517605376</v>
+        <v>8437675008</v>
       </c>
       <c r="M20" t="n">
-        <v>2427152896</v>
+        <v>7581499904</v>
       </c>
       <c r="N20" t="n">
-        <v>58635000</v>
+        <v>1984400000</v>
       </c>
       <c r="O20" t="n">
-        <v>0.71970004</v>
+        <v>0.5273300400000001</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.03607</v>
+        <v>0.37057</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>56.1031</v>
       </c>
       <c r="R20" t="n">
-        <v>14.012234</v>
+        <v>18.104319</v>
       </c>
       <c r="S20" t="n">
-        <v>70.45023878577335</v>
+        <v>75.80053828212104</v>
       </c>
       <c r="T20" t="n">
-        <v>0.3433980690949849</v>
+        <v>0.02218539880198733</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1225363712886325</v>
+        <v>-0.02232735627399152</v>
       </c>
       <c r="V20" t="n">
-        <v>0.3802477956352626</v>
+        <v>0.1737887690369853</v>
       </c>
       <c r="W20" t="n">
-        <v>0.4364881219210226</v>
+        <v>1.257019002815477</v>
       </c>
       <c r="X20" t="n">
-        <v>0.02641</v>
+        <v>0.00016000001</v>
       </c>
       <c r="Y20" t="n">
-        <v>0.96919</v>
+        <v>0.20377001</v>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>2026-08-31T22:50:53.805242+00:00</t>
+          <t>2026-09-01T20:23:05.074752+00:00</t>
         </is>
       </c>
       <c r="AD20" t="inlineStr">
@@ -5250,12 +5256,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ASML</t>
+          <t>MDB</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>ASML Holding N.V.</t>
+          <t>MongoDB, Inc.</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -5265,72 +5271,66 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Semiconductor Equipment &amp; Materials</t>
+          <t>Software - Infrastructure</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>651437473792</v>
+        <v>34924347392</v>
       </c>
       <c r="F21" t="n">
-        <v>1696.010009765625</v>
+        <v>434.2099914550781</v>
       </c>
       <c r="G21" t="n">
-        <v>35327500288</v>
+        <v>2602398976</v>
       </c>
       <c r="H21" t="n">
-        <v>0.213</v>
+        <v>0.252</v>
       </c>
       <c r="I21" t="n">
-        <v>29.68</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0.285</v>
+        <v>-0.36</v>
       </c>
       <c r="K21" t="n">
-        <v>8437675008</v>
+        <v>517605376</v>
       </c>
       <c r="M21" t="n">
-        <v>7581499904</v>
+        <v>2427152896</v>
       </c>
       <c r="N21" t="n">
-        <v>1984400000</v>
+        <v>58635000</v>
       </c>
       <c r="O21" t="n">
-        <v>0.5273300400000001</v>
+        <v>0.71970004</v>
       </c>
       <c r="P21" t="n">
-        <v>0.37057</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>57.143192</v>
+        <v>-0.03607</v>
       </c>
       <c r="R21" t="n">
-        <v>18.439955</v>
+        <v>13.420059</v>
       </c>
       <c r="S21" t="n">
-        <v>77.20580292252944</v>
+        <v>67.47292244507136</v>
       </c>
       <c r="T21" t="n">
-        <v>0.04113567204765189</v>
+        <v>0.2866243253520242</v>
       </c>
       <c r="U21" t="n">
-        <v>0.04275746353594823</v>
+        <v>0.08972042555502191</v>
       </c>
       <c r="V21" t="n">
-        <v>0.1732796814666719</v>
+        <v>0.3359895954226169</v>
       </c>
       <c r="W21" t="n">
-        <v>1.298861829835056</v>
+        <v>0.3757802718801986</v>
       </c>
       <c r="X21" t="n">
-        <v>0.00016000001</v>
+        <v>0.02641</v>
       </c>
       <c r="Y21" t="n">
-        <v>0.20377001</v>
+        <v>0.96931</v>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>2026-08-31T22:50:50.293086+00:00</t>
+          <t>2026-09-01T20:23:08.492651+00:00</t>
         </is>
       </c>
       <c r="AD21" t="inlineStr">
@@ -5361,10 +5361,10 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>114873638912</v>
+        <v>110842675200</v>
       </c>
       <c r="F22" t="n">
-        <v>331.4299926757812</v>
+        <v>319.7999877929688</v>
       </c>
       <c r="G22" t="n">
         <v>5032822784</v>
@@ -5391,32 +5391,32 @@
         <v>-0.22173999</v>
       </c>
       <c r="R22" t="n">
-        <v>22.824892</v>
+        <v>22.023958</v>
       </c>
       <c r="S22" t="n">
-        <v>66.03839548791868</v>
+        <v>63.72108075555934</v>
       </c>
       <c r="T22" t="n">
-        <v>0.1300804489064171</v>
+        <v>0.09042549483106432</v>
       </c>
       <c r="U22" t="n">
-        <v>0.1830025283534287</v>
+        <v>0.2246303509766701</v>
       </c>
       <c r="V22" t="n">
-        <v>0.967994688372243</v>
+        <v>0.8775317580878614</v>
       </c>
       <c r="W22" t="n">
-        <v>0.3887119231968754</v>
+        <v>0.3399814920213273</v>
       </c>
       <c r="X22" t="n">
         <v>0.02962</v>
       </c>
       <c r="Y22" t="n">
-        <v>0.82328004</v>
+        <v>0.82354</v>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>2026-08-31T22:50:52.548034+00:00</t>
+          <t>2026-09-01T20:23:07.282770+00:00</t>
         </is>
       </c>
       <c r="AD22" t="inlineStr">
@@ -5428,12 +5428,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>NET</t>
+          <t>SMCI</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Cloudflare, Inc.</t>
+          <t>Super Micro Computer, Inc.</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -5443,66 +5443,69 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Software - Infrastructure</t>
+          <t>Computer Hardware</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>108643475456</v>
+        <v>23746707456</v>
       </c>
       <c r="F23" t="n">
-        <v>305.1099853515625</v>
+        <v>36.70999908447266</v>
       </c>
       <c r="G23" t="n">
-        <v>2512349952</v>
+        <v>39063072768</v>
       </c>
       <c r="H23" t="n">
-        <v>0.359</v>
+        <v>0.9320000000000001</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.57</v>
+        <v>3.26</v>
+      </c>
+      <c r="J23" t="n">
+        <v>4.094</v>
       </c>
       <c r="K23" t="n">
-        <v>691946368</v>
+        <v>-8231267840</v>
       </c>
       <c r="M23" t="n">
-        <v>4162798080</v>
+        <v>7521474048</v>
       </c>
       <c r="N23" t="n">
-        <v>3529349888</v>
+        <v>9311492096</v>
       </c>
       <c r="O23" t="n">
-        <v>0.72577006</v>
+        <v>0.108219996</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.07603</v>
+        <v>0.13382</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>11.2607355</v>
       </c>
       <c r="R23" t="n">
-        <v>43.243767</v>
-      </c>
-      <c r="S23" t="n">
-        <v>157.0114108265686</v>
+        <v>0.6079068</v>
       </c>
       <c r="T23" t="n">
-        <v>0.09366253256945689</v>
+        <v>0.2926056189282595</v>
       </c>
       <c r="U23" t="n">
-        <v>0.1266153795878628</v>
+        <v>-0.2682878129504148</v>
       </c>
       <c r="V23" t="n">
-        <v>0.7719378652973015</v>
+        <v>0.153314457193326</v>
       </c>
       <c r="W23" t="n">
-        <v>0.461884794866859</v>
+        <v>-0.1162735128695982</v>
       </c>
       <c r="X23" t="n">
-        <v>0.00616</v>
+        <v>0.12878999</v>
       </c>
       <c r="Y23" t="n">
-        <v>0.90196</v>
+        <v>0.7059299999999999</v>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>2026-08-31T22:50:53.133300+00:00</t>
+          <t>2026-09-01T20:23:06.960542+00:00</t>
         </is>
       </c>
       <c r="AD23" t="inlineStr">
@@ -5514,12 +5517,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>SMCI</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Super Micro Computer, Inc.</t>
+          <t>Microsoft Corporation</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -5529,69 +5532,72 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Computer Hardware</t>
+          <t>Software - Infrastructure</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>24115425280</v>
+        <v>3720346861568</v>
       </c>
       <c r="F24" t="n">
-        <v>37.27999877929688</v>
+        <v>501.0199890136719</v>
       </c>
       <c r="G24" t="n">
-        <v>39063072768</v>
+        <v>331839012864</v>
       </c>
       <c r="H24" t="n">
-        <v>0.9320000000000001</v>
+        <v>0.177</v>
       </c>
       <c r="I24" t="n">
-        <v>3.26</v>
+        <v>17.96</v>
       </c>
       <c r="J24" t="n">
-        <v>4.094</v>
+        <v>0.317</v>
       </c>
       <c r="K24" t="n">
-        <v>-8231267840</v>
+        <v>16545500160</v>
       </c>
       <c r="M24" t="n">
-        <v>7521474048</v>
+        <v>76842999808</v>
       </c>
       <c r="N24" t="n">
-        <v>9311492096</v>
+        <v>128812998656</v>
       </c>
       <c r="O24" t="n">
-        <v>0.108219996</v>
+        <v>0.67944</v>
       </c>
       <c r="P24" t="n">
-        <v>0.13382</v>
+        <v>0.45111</v>
       </c>
       <c r="Q24" t="n">
-        <v>11.435582</v>
+        <v>27.896437</v>
       </c>
       <c r="R24" t="n">
-        <v>0.6173457999999999</v>
+        <v>11.211301</v>
+      </c>
+      <c r="S24" t="n">
+        <v>224.8555090865262</v>
       </c>
       <c r="T24" t="n">
-        <v>0.312676030987431</v>
+        <v>0.080141087779384</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.2047782011538319</v>
+        <v>0.1374389500552666</v>
       </c>
       <c r="V24" t="n">
-        <v>0.1509725063845244</v>
+        <v>0.2622014726713937</v>
       </c>
       <c r="W24" t="n">
-        <v>-0.1025518065079799</v>
+        <v>-0.003054641545529702</v>
       </c>
       <c r="X24" t="n">
-        <v>0.12878999</v>
+        <v>0.00090000004</v>
       </c>
       <c r="Y24" t="n">
-        <v>0.70587</v>
+        <v>0.75884</v>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>2026-08-31T22:50:52.243724+00:00</t>
+          <t>2026-09-01T20:23:03.262394+00:00</t>
         </is>
       </c>
       <c r="AD24" t="inlineStr">
@@ -5603,12 +5609,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>PANW</t>
+          <t>NET</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Palo Alto Networks, Inc.</t>
+          <t>Cloudflare, Inc.</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -5622,65 +5628,62 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>311435952128</v>
+        <v>101664325632</v>
       </c>
       <c r="F25" t="n">
-        <v>382.1300048828125</v>
+        <v>285.510009765625</v>
       </c>
       <c r="G25" t="n">
-        <v>10606499840</v>
+        <v>2512349952</v>
       </c>
       <c r="H25" t="n">
-        <v>0.311</v>
+        <v>0.359</v>
       </c>
       <c r="I25" t="n">
-        <v>1.15</v>
+        <v>-0.57</v>
       </c>
       <c r="K25" t="n">
-        <v>3579375104</v>
+        <v>691946368</v>
       </c>
       <c r="M25" t="n">
-        <v>3111000064</v>
+        <v>4162798080</v>
       </c>
       <c r="N25" t="n">
-        <v>2130000000</v>
+        <v>3529349888</v>
       </c>
       <c r="O25" t="n">
-        <v>0.71963996</v>
+        <v>0.72577006</v>
       </c>
       <c r="P25" t="n">
-        <v>-0.02465</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>332.28696</v>
+        <v>-0.07603</v>
       </c>
       <c r="R25" t="n">
-        <v>29.362745</v>
+        <v>40.465828</v>
       </c>
       <c r="S25" t="n">
-        <v>87.00847021592291</v>
+        <v>146.9251524881188</v>
       </c>
       <c r="T25" t="n">
-        <v>0.1515837035408871</v>
+        <v>0.02340669052313182</v>
       </c>
       <c r="U25" t="n">
-        <v>0.2717318653858791</v>
+        <v>0.04712831339736878</v>
       </c>
       <c r="V25" t="n">
-        <v>1.566008659557579</v>
+        <v>0.5772290521874681</v>
       </c>
       <c r="W25" t="n">
-        <v>1.005721164777699</v>
+        <v>0.3679747045240982</v>
       </c>
       <c r="X25" t="n">
-        <v>0.0076</v>
+        <v>0.00616</v>
       </c>
       <c r="Y25" t="n">
-        <v>0.84946996</v>
+        <v>0.90198</v>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>2026-08-31T22:50:47.899293+00:00</t>
+          <t>2026-09-01T20:23:07.930391+00:00</t>
         </is>
       </c>
       <c r="AD25" t="inlineStr">
@@ -5692,12 +5695,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>PANW</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Microsoft Corporation</t>
+          <t>Palo Alto Networks, Inc.</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -5711,68 +5714,65 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>3766905208832</v>
+        <v>295103332352</v>
       </c>
       <c r="F26" t="n">
-        <v>507.2900085449219</v>
+        <v>362.0899963378906</v>
       </c>
       <c r="G26" t="n">
-        <v>331839012864</v>
+        <v>10606499840</v>
       </c>
       <c r="H26" t="n">
-        <v>0.177</v>
+        <v>0.311</v>
       </c>
       <c r="I26" t="n">
-        <v>17.97</v>
-      </c>
-      <c r="J26" t="n">
-        <v>0.317</v>
+        <v>1.15</v>
       </c>
       <c r="K26" t="n">
-        <v>16545500160</v>
+        <v>3579375104</v>
       </c>
       <c r="M26" t="n">
-        <v>76842999808</v>
+        <v>3111000064</v>
       </c>
       <c r="N26" t="n">
-        <v>128812998656</v>
+        <v>2130000000</v>
       </c>
       <c r="O26" t="n">
-        <v>0.67944</v>
+        <v>0.71963996</v>
       </c>
       <c r="P26" t="n">
-        <v>0.45111</v>
+        <v>-0.02465</v>
       </c>
       <c r="Q26" t="n">
-        <v>28.22983</v>
+        <v>314.86087</v>
       </c>
       <c r="R26" t="n">
-        <v>11.351604</v>
+        <v>27.822876</v>
       </c>
       <c r="S26" t="n">
-        <v>227.6694673720882</v>
+        <v>82.44548944373504</v>
       </c>
       <c r="T26" t="n">
-        <v>0.0936585239403942</v>
+        <v>0.09119130575932743</v>
       </c>
       <c r="U26" t="n">
-        <v>0.1036328261285961</v>
+        <v>0.2184198306139848</v>
       </c>
       <c r="V26" t="n">
-        <v>0.2969032941411813</v>
+        <v>1.411521885159188</v>
       </c>
       <c r="W26" t="n">
-        <v>0.009421579553753778</v>
+        <v>0.9005353150216655</v>
       </c>
       <c r="X26" t="n">
-        <v>0.00090000004</v>
+        <v>0.0076</v>
       </c>
       <c r="Y26" t="n">
-        <v>0.75882006</v>
+        <v>0.84923</v>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>2026-08-31T22:50:48.267338+00:00</t>
+          <t>2026-09-01T20:23:02.966566+00:00</t>
         </is>
       </c>
       <c r="AD26" t="inlineStr">
@@ -5803,10 +5803,10 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>258359541760</v>
+        <v>250787430400</v>
       </c>
       <c r="F27" t="n">
-        <v>241.9100036621094</v>
+        <v>234.8200073242188</v>
       </c>
       <c r="G27" t="n">
         <v>5155999744</v>
@@ -5836,25 +5836,25 @@
         <v>0.07603</v>
       </c>
       <c r="Q27" t="n">
-        <v>246.84694</v>
+        <v>239.61224</v>
       </c>
       <c r="R27" t="n">
-        <v>50.108524</v>
+        <v>48.639923</v>
       </c>
       <c r="S27" t="n">
-        <v>193.6002607382603</v>
+        <v>187.9261419360334</v>
       </c>
       <c r="T27" t="n">
-        <v>0.009261968367853868</v>
+        <v>-0.02031789005625295</v>
       </c>
       <c r="U27" t="n">
-        <v>-0.4083160081918629</v>
+        <v>-0.4169004685586186</v>
       </c>
       <c r="V27" t="n">
-        <v>0.8980777517032796</v>
+        <v>0.8880759197432126</v>
       </c>
       <c r="W27" t="n">
-        <v>0.7490420644366393</v>
+        <v>0.6977804314163147</v>
       </c>
       <c r="X27" t="n">
         <v>0.0007</v>
@@ -5864,7 +5864,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>2026-08-31T22:50:50.606799+00:00</t>
+          <t>2026-09-01T20:23:05.370668+00:00</t>
         </is>
       </c>
       <c r="AD27" t="inlineStr">
@@ -5876,84 +5876,87 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>CRWD</t>
+          <t>META</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>CrowdStrike Holdings, Inc.</t>
+          <t>Meta Platforms, Inc.</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Software - Infrastructure</t>
+          <t>Internet Content &amp; Information</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>236528943104</v>
+        <v>1473834123264</v>
       </c>
       <c r="F28" t="n">
-        <v>231</v>
+        <v>578.5399780273438</v>
       </c>
       <c r="G28" t="n">
-        <v>5396145152</v>
+        <v>228246994944</v>
       </c>
       <c r="H28" t="n">
-        <v>0.258</v>
+        <v>0.28</v>
       </c>
       <c r="I28" t="n">
-        <v>0.04</v>
+        <v>26.53</v>
+      </c>
+      <c r="J28" t="n">
+        <v>-0.134</v>
       </c>
       <c r="K28" t="n">
-        <v>1995385472</v>
+        <v>21553625088</v>
       </c>
       <c r="M28" t="n">
-        <v>5013847040</v>
+        <v>90259996672</v>
       </c>
       <c r="N28" t="n">
-        <v>820179008</v>
+        <v>112317997056</v>
       </c>
       <c r="O28" t="n">
-        <v>0.75185996</v>
+        <v>0.81747</v>
       </c>
       <c r="P28" t="n">
-        <v>-0.02259</v>
+        <v>0.34827</v>
       </c>
       <c r="Q28" t="n">
-        <v>5775</v>
+        <v>21.807009</v>
       </c>
       <c r="R28" t="n">
-        <v>43.832947</v>
+        <v>6.4571896</v>
       </c>
       <c r="S28" t="n">
-        <v>118.5379699426818</v>
+        <v>68.37987193553619</v>
       </c>
       <c r="T28" t="n">
-        <v>0.2103112190154284</v>
+        <v>0.03921243590574286</v>
       </c>
       <c r="U28" t="n">
-        <v>0.1813288929372465</v>
+        <v>-0.03104563320859699</v>
       </c>
       <c r="V28" t="n">
-        <v>1.484004443007452</v>
+        <v>-0.113207676029062</v>
       </c>
       <c r="W28" t="n">
-        <v>1.180788230774251</v>
+        <v>-0.2142465045289341</v>
       </c>
       <c r="X28" t="n">
-        <v>0.01456</v>
+        <v>0.00148</v>
       </c>
       <c r="Y28" t="n">
-        <v>0.7654300000000001</v>
+        <v>0.79052</v>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>2026-08-31T22:50:47.586780+00:00</t>
+          <t>2026-09-01T20:23:04.100432+00:00</t>
         </is>
       </c>
       <c r="AD28" t="inlineStr">
@@ -5965,87 +5968,84 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>META</t>
+          <t>CRWD</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Meta Platforms, Inc.</t>
+          <t>CrowdStrike Holdings, Inc.</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Internet Content &amp; Information</t>
+          <t>Software - Infrastructure</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1458039816192</v>
+        <v>220217671680</v>
       </c>
       <c r="F29" t="n">
-        <v>572.3400268554688</v>
+        <v>215.0700073242188</v>
       </c>
       <c r="G29" t="n">
-        <v>228246994944</v>
+        <v>5396145152</v>
       </c>
       <c r="H29" t="n">
-        <v>0.28</v>
+        <v>0.258</v>
       </c>
       <c r="I29" t="n">
-        <v>26.53</v>
-      </c>
-      <c r="J29" t="n">
-        <v>-0.134</v>
+        <v>0.05</v>
       </c>
       <c r="K29" t="n">
-        <v>21553625088</v>
+        <v>1995385472</v>
       </c>
       <c r="M29" t="n">
-        <v>90259996672</v>
+        <v>5013847040</v>
       </c>
       <c r="N29" t="n">
-        <v>112317997056</v>
+        <v>820179008</v>
       </c>
       <c r="O29" t="n">
-        <v>0.81747</v>
+        <v>0.75185996</v>
       </c>
       <c r="P29" t="n">
-        <v>0.34827</v>
+        <v>-0.02259</v>
       </c>
       <c r="Q29" t="n">
-        <v>21.573313</v>
+        <v>4301.4</v>
       </c>
       <c r="R29" t="n">
-        <v>6.3879914</v>
+        <v>40.810184</v>
       </c>
       <c r="S29" t="n">
-        <v>67.64708072257251</v>
+        <v>110.3634735093431</v>
       </c>
       <c r="T29" t="n">
-        <v>0.02807566644377779</v>
+        <v>0.126846938260746</v>
       </c>
       <c r="U29" t="n">
-        <v>-0.04596311523360996</v>
+        <v>0.1187723722478518</v>
       </c>
       <c r="V29" t="n">
-        <v>-0.1154293831138969</v>
+        <v>1.235306506367569</v>
       </c>
       <c r="W29" t="n">
-        <v>-0.2226670692091168</v>
+        <v>1.030398877771377</v>
       </c>
       <c r="X29" t="n">
-        <v>0.00148</v>
+        <v>0.01456</v>
       </c>
       <c r="Y29" t="n">
-        <v>0.79042</v>
+        <v>0.76548</v>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>2026-08-31T22:50:49.201384+00:00</t>
+          <t>2026-09-01T20:23:02.712375+00:00</t>
         </is>
       </c>
       <c r="AD29" t="inlineStr">
@@ -6076,10 +6076,10 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>153001246720</v>
+        <v>147738869760</v>
       </c>
       <c r="F30" t="n">
-        <v>147.9900054931641</v>
+        <v>142.8999938964844</v>
       </c>
       <c r="G30" t="n">
         <v>14732000256</v>
@@ -6088,7 +6088,7 @@
         <v>0.24</v>
       </c>
       <c r="I30" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="J30" t="n">
         <v>-0.219</v>
@@ -6109,35 +6109,35 @@
         <v>0.04063</v>
       </c>
       <c r="Q30" t="n">
-        <v>91.91925999999999</v>
+        <v>89.31249</v>
       </c>
       <c r="R30" t="n">
-        <v>10.38564</v>
+        <v>10.028433</v>
       </c>
       <c r="S30" t="n">
-        <v>29.71258598045434</v>
+        <v>28.69064118433312</v>
       </c>
       <c r="T30" t="n">
-        <v>0.3304863888052649</v>
+        <v>0.2847252502359707</v>
       </c>
       <c r="U30" t="n">
-        <v>0.08928312106814662</v>
+        <v>0.1194672321841985</v>
       </c>
       <c r="V30" t="n">
-        <v>0.3701509357115627</v>
+        <v>0.3059769355492556</v>
       </c>
       <c r="W30" t="n">
-        <v>-0.1934798141124087</v>
+        <v>-0.2212195056236285</v>
       </c>
       <c r="X30" t="n">
         <v>0.00176</v>
       </c>
       <c r="Y30" t="n">
-        <v>0.85129</v>
+        <v>0.85097003</v>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>2026-08-31T22:50:53.470095+00:00</t>
+          <t>2026-09-01T20:23:08.240560+00:00</t>
         </is>
       </c>
       <c r="AD30" t="inlineStr">
@@ -6168,10 +6168,10 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>429535821824</v>
+        <v>407068180480</v>
       </c>
       <c r="F31" t="n">
-        <v>149.1199951171875</v>
+        <v>141.3200073242188</v>
       </c>
       <c r="G31" t="n">
         <v>67356999680</v>
@@ -6180,7 +6180,7 @@
         <v>0.206</v>
       </c>
       <c r="I31" t="n">
-        <v>5.82</v>
+        <v>5.83</v>
       </c>
       <c r="J31" t="n">
         <v>0.219</v>
@@ -6201,32 +6201,32 @@
         <v>0.36202</v>
       </c>
       <c r="Q31" t="n">
-        <v>25.621992</v>
+        <v>24.240139</v>
       </c>
       <c r="R31" t="n">
-        <v>6.3770037</v>
+        <v>6.0434427</v>
       </c>
       <c r="T31" t="n">
-        <v>0.1482251537980721</v>
+        <v>0.08816518547413033</v>
       </c>
       <c r="U31" t="n">
-        <v>-0.3969825581621358</v>
+        <v>-0.420182962426185</v>
       </c>
       <c r="V31" t="n">
-        <v>0.03274701231595389</v>
+        <v>-0.04651959579188036</v>
       </c>
       <c r="W31" t="n">
-        <v>-0.333040235042808</v>
+        <v>-0.3679267572759877</v>
       </c>
       <c r="X31" t="n">
         <v>0.40498</v>
       </c>
       <c r="Y31" t="n">
-        <v>0.4582</v>
+        <v>0.45821998</v>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>2026-08-31T22:50:49.551411+00:00</t>
+          <t>2026-09-01T20:23:04.411086+00:00</t>
         </is>
       </c>
       <c r="AD31" t="inlineStr">
@@ -6843,23 +6843,18 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>MDB</t>
+          <t>ASML</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>88.2</v>
+        <v>100</v>
       </c>
       <c r="C20" t="n">
-        <v>88.2</v>
+        <v>100</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
           <t>HIGH</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>eps_growth, pe_ratio</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -6877,18 +6872,23 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ASML</t>
+          <t>MDB</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>100</v>
+        <v>88.2</v>
       </c>
       <c r="C21" t="n">
-        <v>100</v>
+        <v>88.2</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
           <t>HIGH</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>eps_growth, pe_ratio</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -6940,14 +6940,14 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>NET</t>
+          <t>SMCI</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>88.2</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="C23" t="n">
-        <v>88.2</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -6956,7 +6956,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>eps_growth, pe_ratio</t>
+          <t>price_to_fcf</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -6974,23 +6974,18 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>SMCI</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>94.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="C24" t="n">
-        <v>94.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
           <t>HIGH</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>price_to_fcf</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -7008,14 +7003,14 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>PANW</t>
+          <t>NET</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>94.09999999999999</v>
+        <v>88.2</v>
       </c>
       <c r="C25" t="n">
-        <v>94.09999999999999</v>
+        <v>88.2</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -7024,7 +7019,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>eps_growth</t>
+          <t>eps_growth, pe_ratio</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -7042,18 +7037,23 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>PANW</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>100</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="C26" t="n">
-        <v>100</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
           <t>HIGH</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>eps_growth</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -7100,23 +7100,18 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>CRWD</t>
+          <t>META</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>94.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="C28" t="n">
-        <v>94.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
           <t>HIGH</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>eps_growth</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -7134,18 +7129,23 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>META</t>
+          <t>CRWD</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>100</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="C29" t="n">
-        <v>100</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
           <t>HIGH</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>eps_growth</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -7296,7 +7296,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>55.21</v>
+        <v>55.15</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/reports/investment_dashboard.xlsx
+++ b/reports/investment_dashboard.xlsx
@@ -789,7 +789,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>50.44</v>
+        <v>50.43</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -2331,7 +2331,7 @@
         <v>8.08</v>
       </c>
       <c r="F7" t="n">
-        <v>3.91</v>
+        <v>3.9</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -2349,7 +2349,7 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>50.44</v>
+        <v>50.43</v>
       </c>
     </row>
     <row r="8">
@@ -3594,7 +3594,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>2026-09-01T20:23:04.750935+00:00</t>
+          <t>2026-09-01T20:42:43.188308+00:00</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
@@ -3637,7 +3637,7 @@
         <v>3.457</v>
       </c>
       <c r="I3" t="n">
-        <v>44.22</v>
+        <v>44.2</v>
       </c>
       <c r="J3" t="n">
         <v>13.685</v>
@@ -3658,7 +3658,7 @@
         <v>0.80370003</v>
       </c>
       <c r="Q3" t="n">
-        <v>21.109</v>
+        <v>21.118551</v>
       </c>
       <c r="R3" t="n">
         <v>11.678011</v>
@@ -3686,7 +3686,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>2026-09-01T20:23:01.479622+00:00</t>
+          <t>2026-09-01T20:42:37.784545+00:00</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
@@ -3778,7 +3778,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>2026-09-01T20:23:02.071712+00:00</t>
+          <t>2026-09-01T20:42:38.650245+00:00</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
@@ -3870,7 +3870,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>2026-09-01T20:23:06.087990+00:00</t>
+          <t>2026-09-01T20:42:45.192978+00:00</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
@@ -3962,7 +3962,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>2026-09-01T20:23:00.193279+00:00</t>
+          <t>2026-09-01T20:42:35.505701+00:00</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr">
@@ -4005,7 +4005,7 @@
         <v>1.059</v>
       </c>
       <c r="I7" t="n">
-        <v>7.92</v>
+        <v>7.9</v>
       </c>
       <c r="J7" t="n">
         <v>1.278</v>
@@ -4026,7 +4026,7 @@
         <v>0.66236997</v>
       </c>
       <c r="Q7" t="n">
-        <v>27.454546</v>
+        <v>27.52405</v>
       </c>
       <c r="R7" t="n">
         <v>17.330175</v>
@@ -4054,7 +4054,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>2026-09-01T20:22:59.922900+00:00</t>
+          <t>2026-09-01T20:42:35.049839+00:00</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>2026-09-01T20:23:02.435456+00:00</t>
+          <t>2026-09-01T20:42:39.151913+00:00</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr">
@@ -4238,7 +4238,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>2026-09-01T20:23:06.374543+00:00</t>
+          <t>2026-09-01T20:42:45.680098+00:00</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr">
@@ -4327,7 +4327,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>2026-09-01T20:23:08.798606+00:00</t>
+          <t>2026-09-01T20:42:49.472969+00:00</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr">
@@ -4419,7 +4419,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>2026-09-01T20:23:00.433819+00:00</t>
+          <t>2026-09-01T20:42:36.017324+00:00</t>
         </is>
       </c>
       <c r="AD11" t="inlineStr">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>2026-09-01T20:23:03.588293+00:00</t>
+          <t>2026-09-01T20:42:41.077425+00:00</t>
         </is>
       </c>
       <c r="AD12" t="inlineStr">
@@ -4554,7 +4554,7 @@
         <v>0.365</v>
       </c>
       <c r="I13" t="n">
-        <v>3.03</v>
+        <v>3.01</v>
       </c>
       <c r="J13" t="n">
         <v>0.5</v>
@@ -4575,7 +4575,7 @@
         <v>0.16679001</v>
       </c>
       <c r="Q13" t="n">
-        <v>69.43564600000001</v>
+        <v>69.89700999999999</v>
       </c>
       <c r="R13" t="n">
         <v>20.007668</v>
@@ -4590,10 +4590,10 @@
         <v>-0.2763097300440246</v>
       </c>
       <c r="V13" t="n">
-        <v>1.603849312680738</v>
+        <v>1.60384906681578</v>
       </c>
       <c r="W13" t="n">
-        <v>2.353558936137119</v>
+        <v>2.353558732223212</v>
       </c>
       <c r="X13" t="n">
         <v>0.00494</v>
@@ -4603,7 +4603,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>2026-09-01T20:23:05.787116+00:00</t>
+          <t>2026-09-01T20:42:44.689840+00:00</t>
         </is>
       </c>
       <c r="AD13" t="inlineStr">
@@ -4695,7 +4695,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>2026-09-01T20:23:01.143342+00:00</t>
+          <t>2026-09-01T20:42:37.216902+00:00</t>
         </is>
       </c>
       <c r="AD14" t="inlineStr">
@@ -4787,7 +4787,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>2026-09-01T20:23:00.778752+00:00</t>
+          <t>2026-09-01T20:42:36.615544+00:00</t>
         </is>
       </c>
       <c r="AD15" t="inlineStr">
@@ -4879,7 +4879,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>2026-09-01T20:23:07.604446+00:00</t>
+          <t>2026-09-01T20:42:47.622695+00:00</t>
         </is>
       </c>
       <c r="AD16" t="inlineStr">
@@ -4958,10 +4958,10 @@
         <v>-0.2345861871854436</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.006462781850907096</v>
+        <v>-0.006462899538105416</v>
       </c>
       <c r="W17" t="n">
-        <v>1.009031464856126</v>
+        <v>1.009031344553681</v>
       </c>
       <c r="X17" t="n">
         <v>0.00269</v>
@@ -4971,7 +4971,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>2026-09-01T20:23:06.698516+00:00</t>
+          <t>2026-09-01T20:42:46.195269+00:00</t>
         </is>
       </c>
       <c r="AD17" t="inlineStr">
@@ -5060,7 +5060,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>2026-09-01T20:23:01.773461+00:00</t>
+          <t>2026-09-01T20:42:38.234134+00:00</t>
         </is>
       </c>
       <c r="AD18" t="inlineStr">
@@ -5152,7 +5152,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>2026-09-01T20:23:03.845484+00:00</t>
+          <t>2026-09-01T20:42:41.504899+00:00</t>
         </is>
       </c>
       <c r="AD19" t="inlineStr">
@@ -5234,7 +5234,7 @@
         <v>0.1737887690369853</v>
       </c>
       <c r="W20" t="n">
-        <v>1.257019002815477</v>
+        <v>1.257019189539317</v>
       </c>
       <c r="X20" t="n">
         <v>0.00016000001</v>
@@ -5244,7 +5244,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>2026-09-01T20:23:05.074752+00:00</t>
+          <t>2026-09-01T20:42:43.650251+00:00</t>
         </is>
       </c>
       <c r="AD20" t="inlineStr">
@@ -5330,7 +5330,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>2026-09-01T20:23:08.492651+00:00</t>
+          <t>2026-09-01T20:42:49.041249+00:00</t>
         </is>
       </c>
       <c r="AD21" t="inlineStr">
@@ -5416,7 +5416,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>2026-09-01T20:23:07.282770+00:00</t>
+          <t>2026-09-01T20:42:47.163595+00:00</t>
         </is>
       </c>
       <c r="AD22" t="inlineStr">
@@ -5505,7 +5505,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>2026-09-01T20:23:06.960542+00:00</t>
+          <t>2026-09-01T20:42:46.706503+00:00</t>
         </is>
       </c>
       <c r="AD23" t="inlineStr">
@@ -5587,7 +5587,7 @@
         <v>0.2622014726713937</v>
       </c>
       <c r="W24" t="n">
-        <v>-0.003054641545529702</v>
+        <v>-0.003054702084871797</v>
       </c>
       <c r="X24" t="n">
         <v>0.00090000004</v>
@@ -5597,7 +5597,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>2026-09-01T20:23:03.262394+00:00</t>
+          <t>2026-09-01T20:42:40.628870+00:00</t>
         </is>
       </c>
       <c r="AD24" t="inlineStr">
@@ -5683,7 +5683,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>2026-09-01T20:23:07.930391+00:00</t>
+          <t>2026-09-01T20:42:48.118198+00:00</t>
         </is>
       </c>
       <c r="AD25" t="inlineStr">
@@ -5772,7 +5772,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>2026-09-01T20:23:02.966566+00:00</t>
+          <t>2026-09-01T20:42:40.055418+00:00</t>
         </is>
       </c>
       <c r="AD26" t="inlineStr">
@@ -5864,7 +5864,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>2026-09-01T20:23:05.370668+00:00</t>
+          <t>2026-09-01T20:42:44.154580+00:00</t>
         </is>
       </c>
       <c r="AD27" t="inlineStr">
@@ -5946,7 +5946,7 @@
         <v>-0.113207676029062</v>
       </c>
       <c r="W28" t="n">
-        <v>-0.2142465045289341</v>
+        <v>-0.2142464393931921</v>
       </c>
       <c r="X28" t="n">
         <v>0.00148</v>
@@ -5956,7 +5956,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>2026-09-01T20:23:04.100432+00:00</t>
+          <t>2026-09-01T20:42:41.972149+00:00</t>
         </is>
       </c>
       <c r="AD28" t="inlineStr">
@@ -6045,7 +6045,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>2026-09-01T20:23:02.712375+00:00</t>
+          <t>2026-09-01T20:42:39.608887+00:00</t>
         </is>
       </c>
       <c r="AD29" t="inlineStr">
@@ -6137,7 +6137,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>2026-09-01T20:23:08.240560+00:00</t>
+          <t>2026-09-01T20:42:48.605064+00:00</t>
         </is>
       </c>
       <c r="AD30" t="inlineStr">
@@ -6226,7 +6226,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>2026-09-01T20:23:04.411086+00:00</t>
+          <t>2026-09-01T20:42:42.529549+00:00</t>
         </is>
       </c>
       <c r="AD31" t="inlineStr">

--- a/reports/investment_dashboard.xlsx
+++ b/reports/investment_dashboard.xlsx
@@ -789,7 +789,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>50.43</v>
+        <v>50.44</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -1977,7 +1977,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>30.79</v>
+        <v>30.78</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -2331,7 +2331,7 @@
         <v>8.08</v>
       </c>
       <c r="F7" t="n">
-        <v>3.9</v>
+        <v>3.91</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -2349,7 +2349,7 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>50.43</v>
+        <v>50.44</v>
       </c>
     </row>
     <row r="8">
@@ -3291,7 +3291,7 @@
         <v>0.8</v>
       </c>
       <c r="F31" t="n">
-        <v>6.72</v>
+        <v>6.71</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -3309,7 +3309,7 @@
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>30.79</v>
+        <v>30.78</v>
       </c>
     </row>
   </sheetData>
@@ -3594,7 +3594,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>2026-09-01T20:42:43.188308+00:00</t>
+          <t>2026-09-01T22:51:05.450813+00:00</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
@@ -3637,7 +3637,7 @@
         <v>3.457</v>
       </c>
       <c r="I3" t="n">
-        <v>44.2</v>
+        <v>44.22</v>
       </c>
       <c r="J3" t="n">
         <v>13.685</v>
@@ -3658,7 +3658,7 @@
         <v>0.80370003</v>
       </c>
       <c r="Q3" t="n">
-        <v>21.118551</v>
+        <v>21.109</v>
       </c>
       <c r="R3" t="n">
         <v>11.678011</v>
@@ -3686,7 +3686,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>2026-09-01T20:42:37.784545+00:00</t>
+          <t>2026-09-01T22:51:01.011812+00:00</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
@@ -3778,7 +3778,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>2026-09-01T20:42:38.650245+00:00</t>
+          <t>2026-09-01T22:51:01.702897+00:00</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
@@ -3870,7 +3870,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>2026-09-01T20:42:45.192978+00:00</t>
+          <t>2026-09-01T22:51:06.991818+00:00</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
@@ -3962,7 +3962,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>2026-09-01T20:42:35.505701+00:00</t>
+          <t>2026-09-01T22:50:59.183580+00:00</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr">
@@ -4005,7 +4005,7 @@
         <v>1.059</v>
       </c>
       <c r="I7" t="n">
-        <v>7.9</v>
+        <v>7.92</v>
       </c>
       <c r="J7" t="n">
         <v>1.278</v>
@@ -4026,7 +4026,7 @@
         <v>0.66236997</v>
       </c>
       <c r="Q7" t="n">
-        <v>27.52405</v>
+        <v>27.454546</v>
       </c>
       <c r="R7" t="n">
         <v>17.330175</v>
@@ -4054,7 +4054,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>2026-09-01T20:42:35.049839+00:00</t>
+          <t>2026-09-01T22:50:58.848800+00:00</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>2026-09-01T20:42:39.151913+00:00</t>
+          <t>2026-09-01T22:51:02.266347+00:00</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr">
@@ -4238,7 +4238,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>2026-09-01T20:42:45.680098+00:00</t>
+          <t>2026-09-01T22:51:07.418037+00:00</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr">
@@ -4327,7 +4327,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>2026-09-01T20:42:49.472969+00:00</t>
+          <t>2026-09-01T22:51:09.756363+00:00</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr">
@@ -4419,7 +4419,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>2026-09-01T20:42:36.017324+00:00</t>
+          <t>2026-09-01T22:50:59.498930+00:00</t>
         </is>
       </c>
       <c r="AD11" t="inlineStr">
@@ -4462,7 +4462,7 @@
         <v>0.242</v>
       </c>
       <c r="I12" t="n">
-        <v>19.92</v>
+        <v>19.93</v>
       </c>
       <c r="J12" t="n">
         <v>2.94</v>
@@ -4483,7 +4483,7 @@
         <v>0.34033</v>
       </c>
       <c r="Q12" t="n">
-        <v>16.818272</v>
+        <v>16.809834</v>
       </c>
       <c r="R12" t="n">
         <v>9.189470999999999</v>
@@ -4501,7 +4501,7 @@
         <v>0.09440194836202598</v>
       </c>
       <c r="W12" t="n">
-        <v>0.578017530788989</v>
+        <v>0.5780176442046498</v>
       </c>
       <c r="X12" t="n">
         <v>0.01596</v>
@@ -4511,7 +4511,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>2026-09-01T20:42:41.077425+00:00</t>
+          <t>2026-09-01T22:51:03.686712+00:00</t>
         </is>
       </c>
       <c r="AD12" t="inlineStr">
@@ -4554,7 +4554,7 @@
         <v>0.365</v>
       </c>
       <c r="I13" t="n">
-        <v>3.01</v>
+        <v>3.03</v>
       </c>
       <c r="J13" t="n">
         <v>0.5</v>
@@ -4575,7 +4575,7 @@
         <v>0.16679001</v>
       </c>
       <c r="Q13" t="n">
-        <v>69.89700999999999</v>
+        <v>69.43564600000001</v>
       </c>
       <c r="R13" t="n">
         <v>20.007668</v>
@@ -4590,7 +4590,7 @@
         <v>-0.2763097300440246</v>
       </c>
       <c r="V13" t="n">
-        <v>1.60384906681578</v>
+        <v>1.603849312680738</v>
       </c>
       <c r="W13" t="n">
         <v>2.353558732223212</v>
@@ -4603,7 +4603,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>2026-09-01T20:42:44.689840+00:00</t>
+          <t>2026-09-01T22:51:06.513437+00:00</t>
         </is>
       </c>
       <c r="AD13" t="inlineStr">
@@ -4695,7 +4695,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>2026-09-01T20:42:37.216902+00:00</t>
+          <t>2026-09-01T22:51:00.414055+00:00</t>
         </is>
       </c>
       <c r="AD14" t="inlineStr">
@@ -4787,7 +4787,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>2026-09-01T20:42:36.615544+00:00</t>
+          <t>2026-09-01T22:50:59.909576+00:00</t>
         </is>
       </c>
       <c r="AD15" t="inlineStr">
@@ -4879,7 +4879,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>2026-09-01T20:42:47.622695+00:00</t>
+          <t>2026-09-01T22:51:08.571262+00:00</t>
         </is>
       </c>
       <c r="AD16" t="inlineStr">
@@ -4958,7 +4958,7 @@
         <v>-0.2345861871854436</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.006462899538105416</v>
+        <v>-0.006462781850907096</v>
       </c>
       <c r="W17" t="n">
         <v>1.009031344553681</v>
@@ -4971,7 +4971,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>2026-09-01T20:42:46.195269+00:00</t>
+          <t>2026-09-01T22:51:07.697441+00:00</t>
         </is>
       </c>
       <c r="AD17" t="inlineStr">
@@ -5060,7 +5060,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>2026-09-01T20:42:38.234134+00:00</t>
+          <t>2026-09-01T22:51:01.457591+00:00</t>
         </is>
       </c>
       <c r="AD18" t="inlineStr">
@@ -5152,7 +5152,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>2026-09-01T20:42:41.504899+00:00</t>
+          <t>2026-09-01T22:51:04.191830+00:00</t>
         </is>
       </c>
       <c r="AD19" t="inlineStr">
@@ -5244,7 +5244,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>2026-09-01T20:42:43.650251+00:00</t>
+          <t>2026-09-01T22:51:05.757670+00:00</t>
         </is>
       </c>
       <c r="AD20" t="inlineStr">
@@ -5330,7 +5330,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>2026-09-01T20:42:49.041249+00:00</t>
+          <t>2026-09-01T22:51:09.497095+00:00</t>
         </is>
       </c>
       <c r="AD21" t="inlineStr">
@@ -5416,7 +5416,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>2026-09-01T20:42:47.163595+00:00</t>
+          <t>2026-09-01T22:51:08.324365+00:00</t>
         </is>
       </c>
       <c r="AD22" t="inlineStr">
@@ -5505,7 +5505,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>2026-09-01T20:42:46.706503+00:00</t>
+          <t>2026-09-01T22:51:07.977943+00:00</t>
         </is>
       </c>
       <c r="AD23" t="inlineStr">
@@ -5597,7 +5597,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>2026-09-01T20:42:40.628870+00:00</t>
+          <t>2026-09-01T22:51:03.416355+00:00</t>
         </is>
       </c>
       <c r="AD24" t="inlineStr">
@@ -5683,7 +5683,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>2026-09-01T20:42:48.118198+00:00</t>
+          <t>2026-09-01T22:51:08.908930+00:00</t>
         </is>
       </c>
       <c r="AD25" t="inlineStr">
@@ -5772,7 +5772,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>2026-09-01T20:42:40.055418+00:00</t>
+          <t>2026-09-01T22:51:03.066689+00:00</t>
         </is>
       </c>
       <c r="AD26" t="inlineStr">
@@ -5815,7 +5815,7 @@
         <v>0.224</v>
       </c>
       <c r="I27" t="n">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="J27" t="n">
         <v>1.083</v>
@@ -5836,7 +5836,7 @@
         <v>0.07603</v>
       </c>
       <c r="Q27" t="n">
-        <v>239.61224</v>
+        <v>237.19193</v>
       </c>
       <c r="R27" t="n">
         <v>48.639923</v>
@@ -5864,7 +5864,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>2026-09-01T20:42:44.154580+00:00</t>
+          <t>2026-09-01T22:51:06.108727+00:00</t>
         </is>
       </c>
       <c r="AD27" t="inlineStr">
@@ -5907,7 +5907,7 @@
         <v>0.28</v>
       </c>
       <c r="I28" t="n">
-        <v>26.53</v>
+        <v>26.56</v>
       </c>
       <c r="J28" t="n">
         <v>-0.134</v>
@@ -5928,7 +5928,7 @@
         <v>0.34827</v>
       </c>
       <c r="Q28" t="n">
-        <v>21.807009</v>
+        <v>21.78238</v>
       </c>
       <c r="R28" t="n">
         <v>6.4571896</v>
@@ -5946,7 +5946,7 @@
         <v>-0.113207676029062</v>
       </c>
       <c r="W28" t="n">
-        <v>-0.2142464393931921</v>
+        <v>-0.2142465045289341</v>
       </c>
       <c r="X28" t="n">
         <v>0.00148</v>
@@ -5956,7 +5956,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>2026-09-01T20:42:41.972149+00:00</t>
+          <t>2026-09-01T22:51:04.563710+00:00</t>
         </is>
       </c>
       <c r="AD28" t="inlineStr">
@@ -6045,7 +6045,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>2026-09-01T20:42:39.608887+00:00</t>
+          <t>2026-09-01T22:51:02.644547+00:00</t>
         </is>
       </c>
       <c r="AD29" t="inlineStr">
@@ -6137,7 +6137,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>2026-09-01T20:42:48.605064+00:00</t>
+          <t>2026-09-01T22:51:09.233432+00:00</t>
         </is>
       </c>
       <c r="AD30" t="inlineStr">
@@ -6180,7 +6180,7 @@
         <v>0.206</v>
       </c>
       <c r="I31" t="n">
-        <v>5.83</v>
+        <v>5.82</v>
       </c>
       <c r="J31" t="n">
         <v>0.219</v>
@@ -6201,7 +6201,7 @@
         <v>0.36202</v>
       </c>
       <c r="Q31" t="n">
-        <v>24.240139</v>
+        <v>24.281788</v>
       </c>
       <c r="R31" t="n">
         <v>6.0434427</v>
@@ -6216,7 +6216,7 @@
         <v>-0.04651959579188036</v>
       </c>
       <c r="W31" t="n">
-        <v>-0.3679267572759877</v>
+        <v>-0.3679267141388564</v>
       </c>
       <c r="X31" t="n">
         <v>0.40498</v>
@@ -6226,7 +6226,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>2026-09-01T20:42:42.529549+00:00</t>
+          <t>2026-09-01T22:51:05.035567+00:00</t>
         </is>
       </c>
       <c r="AD31" t="inlineStr">

--- a/reports/investment_dashboard.xlsx
+++ b/reports/investment_dashboard.xlsx
@@ -1977,7 +1977,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>30.78</v>
+        <v>30.79</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -3291,7 +3291,7 @@
         <v>0.8</v>
       </c>
       <c r="F31" t="n">
-        <v>6.71</v>
+        <v>6.72</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -3309,7 +3309,7 @@
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>30.78</v>
+        <v>30.79</v>
       </c>
     </row>
   </sheetData>
@@ -3590,11 +3590,11 @@
         <v>0.00013</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.15494001</v>
+        <v>0.15493</v>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>2026-09-01T22:51:05.450813+00:00</t>
+          <t>2026-09-01T23:58:55.903671+00:00</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
@@ -3637,7 +3637,7 @@
         <v>3.457</v>
       </c>
       <c r="I3" t="n">
-        <v>44.22</v>
+        <v>44.2</v>
       </c>
       <c r="J3" t="n">
         <v>13.685</v>
@@ -3658,7 +3658,7 @@
         <v>0.80370003</v>
       </c>
       <c r="Q3" t="n">
-        <v>21.109</v>
+        <v>21.118551</v>
       </c>
       <c r="R3" t="n">
         <v>11.678011</v>
@@ -3676,7 +3676,7 @@
         <v>1.263250877901507</v>
       </c>
       <c r="W3" t="n">
-        <v>6.855963464985801</v>
+        <v>6.855962960553897</v>
       </c>
       <c r="X3" t="n">
         <v>0.00238</v>
@@ -3686,7 +3686,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>2026-09-01T22:51:01.011812+00:00</t>
+          <t>2026-09-01T23:58:52.603853+00:00</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
@@ -3778,7 +3778,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>2026-09-01T22:51:01.702897+00:00</t>
+          <t>2026-09-01T23:58:53.150398+00:00</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
@@ -3870,7 +3870,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>2026-09-01T22:51:06.991818+00:00</t>
+          <t>2026-09-01T23:58:56.982948+00:00</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
@@ -3962,7 +3962,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>2026-09-01T22:50:59.183580+00:00</t>
+          <t>2026-09-01T23:58:51.275937+00:00</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr">
@@ -4054,7 +4054,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>2026-09-01T22:50:58.848800+00:00</t>
+          <t>2026-09-01T23:58:50.995757+00:00</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>2026-09-01T22:51:02.266347+00:00</t>
+          <t>2026-09-01T23:58:53.473847+00:00</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr">
@@ -4189,7 +4189,7 @@
         <v>0.875</v>
       </c>
       <c r="I9" t="n">
-        <v>12.55</v>
+        <v>12.54</v>
       </c>
       <c r="J9" t="n">
         <v>2.825</v>
@@ -4210,7 +4210,7 @@
         <v>0.08857000600000001</v>
       </c>
       <c r="Q9" t="n">
-        <v>33.86454</v>
+        <v>33.89155</v>
       </c>
       <c r="R9" t="n">
         <v>2.0493016</v>
@@ -4228,7 +4228,7 @@
         <v>1.780979770980133</v>
       </c>
       <c r="W9" t="n">
-        <v>2.523665741855378</v>
+        <v>2.523665518965409</v>
       </c>
       <c r="X9" t="n">
         <v>0.07491</v>
@@ -4238,7 +4238,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>2026-09-01T22:51:07.418037+00:00</t>
+          <t>2026-09-01T23:58:57.303098+00:00</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr">
@@ -4323,11 +4323,11 @@
         <v>0.09236999999999999</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.91153</v>
+        <v>0.91133004</v>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>2026-09-01T22:51:09.756363+00:00</t>
+          <t>2026-09-01T23:58:59.544417+00:00</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr">
@@ -4419,7 +4419,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>2026-09-01T22:50:59.498930+00:00</t>
+          <t>2026-09-01T23:58:51.513272+00:00</t>
         </is>
       </c>
       <c r="AD11" t="inlineStr">
@@ -4462,7 +4462,7 @@
         <v>0.242</v>
       </c>
       <c r="I12" t="n">
-        <v>19.93</v>
+        <v>19.92</v>
       </c>
       <c r="J12" t="n">
         <v>2.94</v>
@@ -4483,7 +4483,7 @@
         <v>0.34033</v>
       </c>
       <c r="Q12" t="n">
-        <v>16.809834</v>
+        <v>16.818272</v>
       </c>
       <c r="R12" t="n">
         <v>9.189470999999999</v>
@@ -4501,7 +4501,7 @@
         <v>0.09440194836202598</v>
       </c>
       <c r="W12" t="n">
-        <v>0.5780176442046498</v>
+        <v>0.578017530788989</v>
       </c>
       <c r="X12" t="n">
         <v>0.01596</v>
@@ -4511,7 +4511,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>2026-09-01T22:51:03.686712+00:00</t>
+          <t>2026-09-01T23:58:54.728203+00:00</t>
         </is>
       </c>
       <c r="AD12" t="inlineStr">
@@ -4590,7 +4590,7 @@
         <v>-0.2763097300440246</v>
       </c>
       <c r="V13" t="n">
-        <v>1.603849312680738</v>
+        <v>1.60384906681578</v>
       </c>
       <c r="W13" t="n">
         <v>2.353558732223212</v>
@@ -4603,7 +4603,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>2026-09-01T22:51:06.513437+00:00</t>
+          <t>2026-09-01T23:58:56.703356+00:00</t>
         </is>
       </c>
       <c r="AD13" t="inlineStr">
@@ -4646,7 +4646,7 @@
         <v>0.248</v>
       </c>
       <c r="I14" t="n">
-        <v>11.59</v>
+        <v>11.6</v>
       </c>
       <c r="J14" t="n">
         <v>0.428</v>
@@ -4667,7 +4667,7 @@
         <v>0.33736</v>
       </c>
       <c r="Q14" t="n">
-        <v>38.123383</v>
+        <v>38.090515</v>
       </c>
       <c r="R14" t="n">
         <v>11.371114</v>
@@ -4695,7 +4695,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>2026-09-01T22:51:00.414055+00:00</t>
+          <t>2026-09-01T23:58:52.122287+00:00</t>
         </is>
       </c>
       <c r="AD14" t="inlineStr">
@@ -4787,7 +4787,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>2026-09-01T22:50:59.909576+00:00</t>
+          <t>2026-09-01T23:58:51.805181+00:00</t>
         </is>
       </c>
       <c r="AD15" t="inlineStr">
@@ -4879,7 +4879,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>2026-09-01T22:51:08.571262+00:00</t>
+          <t>2026-09-01T23:58:58.508228+00:00</t>
         </is>
       </c>
       <c r="AD16" t="inlineStr">
@@ -4958,7 +4958,7 @@
         <v>-0.2345861871854436</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.006462781850907096</v>
+        <v>-0.006462899538105416</v>
       </c>
       <c r="W17" t="n">
         <v>1.009031344553681</v>
@@ -4971,7 +4971,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>2026-09-01T22:51:07.697441+00:00</t>
+          <t>2026-09-01T23:58:57.610967+00:00</t>
         </is>
       </c>
       <c r="AD17" t="inlineStr">
@@ -5060,7 +5060,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>2026-09-01T22:51:01.457591+00:00</t>
+          <t>2026-09-01T23:58:52.839603+00:00</t>
         </is>
       </c>
       <c r="AD18" t="inlineStr">
@@ -5152,7 +5152,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>2026-09-01T22:51:04.191830+00:00</t>
+          <t>2026-09-01T23:58:55.017893+00:00</t>
         </is>
       </c>
       <c r="AD19" t="inlineStr">
@@ -5195,7 +5195,7 @@
         <v>0.213</v>
       </c>
       <c r="I20" t="n">
-        <v>29.68</v>
+        <v>29.51</v>
       </c>
       <c r="J20" t="n">
         <v>0.285</v>
@@ -5216,7 +5216,7 @@
         <v>0.37057</v>
       </c>
       <c r="Q20" t="n">
-        <v>56.1031</v>
+        <v>56.426296</v>
       </c>
       <c r="R20" t="n">
         <v>18.104319</v>
@@ -5234,7 +5234,7 @@
         <v>0.1737887690369853</v>
       </c>
       <c r="W20" t="n">
-        <v>1.257019189539317</v>
+        <v>1.257019376263188</v>
       </c>
       <c r="X20" t="n">
         <v>0.00016000001</v>
@@ -5244,7 +5244,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>2026-09-01T22:51:05.757670+00:00</t>
+          <t>2026-09-01T23:58:56.204290+00:00</t>
         </is>
       </c>
       <c r="AD20" t="inlineStr">
@@ -5330,7 +5330,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>2026-09-01T22:51:09.497095+00:00</t>
+          <t>2026-09-01T23:58:59.314378+00:00</t>
         </is>
       </c>
       <c r="AD21" t="inlineStr">
@@ -5416,7 +5416,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>2026-09-01T22:51:08.324365+00:00</t>
+          <t>2026-09-01T23:58:58.272419+00:00</t>
         </is>
       </c>
       <c r="AD22" t="inlineStr">
@@ -5505,7 +5505,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>2026-09-01T22:51:07.977943+00:00</t>
+          <t>2026-09-01T23:58:57.849576+00:00</t>
         </is>
       </c>
       <c r="AD23" t="inlineStr">
@@ -5597,7 +5597,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>2026-09-01T22:51:03.416355+00:00</t>
+          <t>2026-09-01T23:58:54.417532+00:00</t>
         </is>
       </c>
       <c r="AD24" t="inlineStr">
@@ -5640,7 +5640,7 @@
         <v>0.359</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.57</v>
+        <v>-0.58</v>
       </c>
       <c r="K25" t="n">
         <v>691946368</v>
@@ -5683,7 +5683,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>2026-09-01T22:51:08.908930+00:00</t>
+          <t>2026-09-01T23:58:58.760434+00:00</t>
         </is>
       </c>
       <c r="AD25" t="inlineStr">
@@ -5772,7 +5772,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>2026-09-01T22:51:03.066689+00:00</t>
+          <t>2026-09-01T23:58:54.041833+00:00</t>
         </is>
       </c>
       <c r="AD26" t="inlineStr">
@@ -5815,7 +5815,7 @@
         <v>0.224</v>
       </c>
       <c r="I27" t="n">
-        <v>0.99</v>
+        <v>0.98</v>
       </c>
       <c r="J27" t="n">
         <v>1.083</v>
@@ -5836,7 +5836,7 @@
         <v>0.07603</v>
       </c>
       <c r="Q27" t="n">
-        <v>237.19193</v>
+        <v>239.61224</v>
       </c>
       <c r="R27" t="n">
         <v>48.639923</v>
@@ -5864,7 +5864,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>2026-09-01T22:51:06.108727+00:00</t>
+          <t>2026-09-01T23:58:56.442983+00:00</t>
         </is>
       </c>
       <c r="AD27" t="inlineStr">
@@ -5946,7 +5946,7 @@
         <v>-0.113207676029062</v>
       </c>
       <c r="W28" t="n">
-        <v>-0.2142465045289341</v>
+        <v>-0.2142464393931921</v>
       </c>
       <c r="X28" t="n">
         <v>0.00148</v>
@@ -5956,7 +5956,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>2026-09-01T22:51:04.563710+00:00</t>
+          <t>2026-09-01T23:58:55.286720+00:00</t>
         </is>
       </c>
       <c r="AD28" t="inlineStr">
@@ -6045,7 +6045,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>2026-09-01T22:51:02.644547+00:00</t>
+          <t>2026-09-01T23:58:53.764028+00:00</t>
         </is>
       </c>
       <c r="AD29" t="inlineStr">
@@ -6137,7 +6137,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>2026-09-01T22:51:09.233432+00:00</t>
+          <t>2026-09-01T23:58:59.008692+00:00</t>
         </is>
       </c>
       <c r="AD30" t="inlineStr">
@@ -6180,7 +6180,7 @@
         <v>0.206</v>
       </c>
       <c r="I31" t="n">
-        <v>5.82</v>
+        <v>5.83</v>
       </c>
       <c r="J31" t="n">
         <v>0.219</v>
@@ -6201,7 +6201,7 @@
         <v>0.36202</v>
       </c>
       <c r="Q31" t="n">
-        <v>24.281788</v>
+        <v>24.240139</v>
       </c>
       <c r="R31" t="n">
         <v>6.0434427</v>
@@ -6216,7 +6216,7 @@
         <v>-0.04651959579188036</v>
       </c>
       <c r="W31" t="n">
-        <v>-0.3679267141388564</v>
+        <v>-0.3679267572759877</v>
       </c>
       <c r="X31" t="n">
         <v>0.40498</v>
@@ -6226,7 +6226,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>2026-09-01T22:51:05.035567+00:00</t>
+          <t>2026-09-01T23:58:55.592839+00:00</t>
         </is>
       </c>
       <c r="AD31" t="inlineStr">

--- a/reports/investment_dashboard.xlsx
+++ b/reports/investment_dashboard.xlsx
@@ -3594,7 +3594,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>2026-09-01T23:58:55.903671+00:00</t>
+          <t>2026-09-02T00:30:53.915149+00:00</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
@@ -3676,7 +3676,7 @@
         <v>1.263250877901507</v>
       </c>
       <c r="W3" t="n">
-        <v>6.855962960553897</v>
+        <v>6.855963464985801</v>
       </c>
       <c r="X3" t="n">
         <v>0.00238</v>
@@ -3686,7 +3686,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>2026-09-01T23:58:52.603853+00:00</t>
+          <t>2026-09-02T00:30:50.586025+00:00</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
@@ -3778,7 +3778,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>2026-09-01T23:58:53.150398+00:00</t>
+          <t>2026-09-02T00:30:51.168566+00:00</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
@@ -3870,7 +3870,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>2026-09-01T23:58:56.982948+00:00</t>
+          <t>2026-09-02T00:30:55.087228+00:00</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
@@ -3962,7 +3962,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>2026-09-01T23:58:51.275937+00:00</t>
+          <t>2026-09-02T00:30:49.287229+00:00</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr">
@@ -4044,7 +4044,7 @@
         <v>0.1930359905499135</v>
       </c>
       <c r="W7" t="n">
-        <v>0.250026579236476</v>
+        <v>0.2500264695838386</v>
       </c>
       <c r="X7" t="n">
         <v>0.04008</v>
@@ -4054,7 +4054,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>2026-09-01T23:58:50.995757+00:00</t>
+          <t>2026-09-02T00:30:49.000917+00:00</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>2026-09-01T23:58:53.473847+00:00</t>
+          <t>2026-09-02T00:30:51.455477+00:00</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr">
@@ -4238,7 +4238,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>2026-09-01T23:58:57.303098+00:00</t>
+          <t>2026-09-02T00:30:55.355093+00:00</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr">
@@ -4327,7 +4327,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>2026-09-01T23:58:59.544417+00:00</t>
+          <t>2026-09-02T00:30:57.665222+00:00</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr">
@@ -4419,7 +4419,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>2026-09-01T23:58:51.513272+00:00</t>
+          <t>2026-09-02T00:30:49.574611+00:00</t>
         </is>
       </c>
       <c r="AD11" t="inlineStr">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>2026-09-01T23:58:54.728203+00:00</t>
+          <t>2026-09-02T00:30:52.709783+00:00</t>
         </is>
       </c>
       <c r="AD12" t="inlineStr">
@@ -4603,7 +4603,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>2026-09-01T23:58:56.703356+00:00</t>
+          <t>2026-09-02T00:30:54.825872+00:00</t>
         </is>
       </c>
       <c r="AD13" t="inlineStr">
@@ -4695,7 +4695,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>2026-09-01T23:58:52.122287+00:00</t>
+          <t>2026-09-02T00:30:50.259621+00:00</t>
         </is>
       </c>
       <c r="AD14" t="inlineStr">
@@ -4787,7 +4787,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>2026-09-01T23:58:51.805181+00:00</t>
+          <t>2026-09-02T00:30:49.898314+00:00</t>
         </is>
       </c>
       <c r="AD15" t="inlineStr">
@@ -4879,7 +4879,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>2026-09-01T23:58:58.508228+00:00</t>
+          <t>2026-09-02T00:30:56.553227+00:00</t>
         </is>
       </c>
       <c r="AD16" t="inlineStr">
@@ -4961,7 +4961,7 @@
         <v>-0.006462899538105416</v>
       </c>
       <c r="W17" t="n">
-        <v>1.009031344553681</v>
+        <v>1.009031464856126</v>
       </c>
       <c r="X17" t="n">
         <v>0.00269</v>
@@ -4971,7 +4971,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>2026-09-01T23:58:57.610967+00:00</t>
+          <t>2026-09-02T00:30:55.673645+00:00</t>
         </is>
       </c>
       <c r="AD17" t="inlineStr">
@@ -5060,7 +5060,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>2026-09-01T23:58:52.839603+00:00</t>
+          <t>2026-09-02T00:30:50.867553+00:00</t>
         </is>
       </c>
       <c r="AD18" t="inlineStr">
@@ -5152,7 +5152,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>2026-09-01T23:58:55.017893+00:00</t>
+          <t>2026-09-02T00:30:53.004258+00:00</t>
         </is>
       </c>
       <c r="AD19" t="inlineStr">
@@ -5240,11 +5240,11 @@
         <v>0.00016000001</v>
       </c>
       <c r="Y20" t="n">
-        <v>0.20377001</v>
+        <v>0.20381</v>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>2026-09-01T23:58:56.204290+00:00</t>
+          <t>2026-09-02T00:30:54.291474+00:00</t>
         </is>
       </c>
       <c r="AD20" t="inlineStr">
@@ -5330,7 +5330,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>2026-09-01T23:58:59.314378+00:00</t>
+          <t>2026-09-02T00:30:57.377021+00:00</t>
         </is>
       </c>
       <c r="AD21" t="inlineStr">
@@ -5416,7 +5416,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>2026-09-01T23:58:58.272419+00:00</t>
+          <t>2026-09-02T00:30:56.284347+00:00</t>
         </is>
       </c>
       <c r="AD22" t="inlineStr">
@@ -5505,7 +5505,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>2026-09-01T23:58:57.849576+00:00</t>
+          <t>2026-09-02T00:30:56.007732+00:00</t>
         </is>
       </c>
       <c r="AD23" t="inlineStr">
@@ -5597,7 +5597,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>2026-09-01T23:58:54.417532+00:00</t>
+          <t>2026-09-02T00:30:52.402454+00:00</t>
         </is>
       </c>
       <c r="AD24" t="inlineStr">
@@ -5683,7 +5683,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>2026-09-01T23:58:58.760434+00:00</t>
+          <t>2026-09-02T00:30:56.813916+00:00</t>
         </is>
       </c>
       <c r="AD25" t="inlineStr">
@@ -5772,7 +5772,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>2026-09-01T23:58:54.041833+00:00</t>
+          <t>2026-09-02T00:30:52.053889+00:00</t>
         </is>
       </c>
       <c r="AD26" t="inlineStr">
@@ -5815,7 +5815,7 @@
         <v>0.224</v>
       </c>
       <c r="I27" t="n">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="J27" t="n">
         <v>1.083</v>
@@ -5836,7 +5836,7 @@
         <v>0.07603</v>
       </c>
       <c r="Q27" t="n">
-        <v>239.61224</v>
+        <v>237.19193</v>
       </c>
       <c r="R27" t="n">
         <v>48.639923</v>
@@ -5864,7 +5864,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>2026-09-01T23:58:56.442983+00:00</t>
+          <t>2026-09-02T00:30:54.546564+00:00</t>
         </is>
       </c>
       <c r="AD27" t="inlineStr">
@@ -5956,7 +5956,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>2026-09-01T23:58:55.286720+00:00</t>
+          <t>2026-09-02T00:30:53.281481+00:00</t>
         </is>
       </c>
       <c r="AD28" t="inlineStr">
@@ -6045,7 +6045,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>2026-09-01T23:58:53.764028+00:00</t>
+          <t>2026-09-02T00:30:51.804584+00:00</t>
         </is>
       </c>
       <c r="AD29" t="inlineStr">
@@ -6137,7 +6137,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>2026-09-01T23:58:59.008692+00:00</t>
+          <t>2026-09-02T00:30:57.090707+00:00</t>
         </is>
       </c>
       <c r="AD30" t="inlineStr">
@@ -6216,7 +6216,7 @@
         <v>-0.04651959579188036</v>
       </c>
       <c r="W31" t="n">
-        <v>-0.3679267572759877</v>
+        <v>-0.3679267141388564</v>
       </c>
       <c r="X31" t="n">
         <v>0.40498</v>
@@ -6226,7 +6226,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>2026-09-01T23:58:55.592839+00:00</t>
+          <t>2026-09-02T00:30:53.625684+00:00</t>
         </is>
       </c>
       <c r="AD31" t="inlineStr">

--- a/reports/investment_dashboard.xlsx
+++ b/reports/investment_dashboard.xlsx
@@ -3594,7 +3594,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>2026-09-02T00:30:53.915149+00:00</t>
+          <t>2026-09-02T00:36:37.848591+00:00</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
@@ -3676,7 +3676,7 @@
         <v>1.263250877901507</v>
       </c>
       <c r="W3" t="n">
-        <v>6.855963464985801</v>
+        <v>6.855962960553897</v>
       </c>
       <c r="X3" t="n">
         <v>0.00238</v>
@@ -3686,7 +3686,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>2026-09-02T00:30:50.586025+00:00</t>
+          <t>2026-09-02T00:36:34.826555+00:00</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
@@ -3778,7 +3778,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>2026-09-02T00:30:51.168566+00:00</t>
+          <t>2026-09-02T00:36:35.326853+00:00</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
@@ -3870,7 +3870,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>2026-09-02T00:30:55.087228+00:00</t>
+          <t>2026-09-02T00:36:39.193989+00:00</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
@@ -3962,7 +3962,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>2026-09-02T00:30:49.287229+00:00</t>
+          <t>2026-09-02T00:36:33.611166+00:00</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr">
@@ -4044,7 +4044,7 @@
         <v>0.1930359905499135</v>
       </c>
       <c r="W7" t="n">
-        <v>0.2500264695838386</v>
+        <v>0.250026579236476</v>
       </c>
       <c r="X7" t="n">
         <v>0.04008</v>
@@ -4054,7 +4054,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>2026-09-02T00:30:49.000917+00:00</t>
+          <t>2026-09-02T00:36:33.362209+00:00</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr">
@@ -4136,7 +4136,7 @@
         <v>0.02994415880569301</v>
       </c>
       <c r="W8" t="n">
-        <v>1.844373676648285</v>
+        <v>1.84437386065034</v>
       </c>
       <c r="X8" t="n">
         <v>0.00202</v>
@@ -4146,7 +4146,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>2026-09-02T00:30:51.455477+00:00</t>
+          <t>2026-09-02T00:36:35.586293+00:00</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr">
@@ -4228,7 +4228,7 @@
         <v>1.780979770980133</v>
       </c>
       <c r="W9" t="n">
-        <v>2.523665518965409</v>
+        <v>2.523665741855378</v>
       </c>
       <c r="X9" t="n">
         <v>0.07491</v>
@@ -4238,7 +4238,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>2026-09-02T00:30:55.355093+00:00</t>
+          <t>2026-09-02T00:36:39.745979+00:00</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr">
@@ -4327,7 +4327,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>2026-09-02T00:30:57.665222+00:00</t>
+          <t>2026-09-02T00:36:42.145872+00:00</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr">
@@ -4419,7 +4419,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>2026-09-02T00:30:49.574611+00:00</t>
+          <t>2026-09-02T00:36:33.899038+00:00</t>
         </is>
       </c>
       <c r="AD11" t="inlineStr">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>2026-09-02T00:30:52.709783+00:00</t>
+          <t>2026-09-02T00:36:36.715118+00:00</t>
         </is>
       </c>
       <c r="AD12" t="inlineStr">
@@ -4603,7 +4603,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>2026-09-02T00:30:54.825872+00:00</t>
+          <t>2026-09-02T00:36:38.898963+00:00</t>
         </is>
       </c>
       <c r="AD13" t="inlineStr">
@@ -4695,7 +4695,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>2026-09-02T00:30:50.259621+00:00</t>
+          <t>2026-09-02T00:36:34.482153+00:00</t>
         </is>
       </c>
       <c r="AD14" t="inlineStr">
@@ -4787,7 +4787,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>2026-09-02T00:30:49.898314+00:00</t>
+          <t>2026-09-02T00:36:34.208148+00:00</t>
         </is>
       </c>
       <c r="AD15" t="inlineStr">
@@ -4879,7 +4879,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>2026-09-02T00:30:56.553227+00:00</t>
+          <t>2026-09-02T00:36:41.026249+00:00</t>
         </is>
       </c>
       <c r="AD16" t="inlineStr">
@@ -4971,7 +4971,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>2026-09-02T00:30:55.673645+00:00</t>
+          <t>2026-09-02T00:36:40.020567+00:00</t>
         </is>
       </c>
       <c r="AD17" t="inlineStr">
@@ -5060,7 +5060,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>2026-09-02T00:30:50.867553+00:00</t>
+          <t>2026-09-02T00:36:35.058564+00:00</t>
         </is>
       </c>
       <c r="AD18" t="inlineStr">
@@ -5152,7 +5152,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>2026-09-02T00:30:53.004258+00:00</t>
+          <t>2026-09-02T00:36:36.984795+00:00</t>
         </is>
       </c>
       <c r="AD19" t="inlineStr">
@@ -5244,7 +5244,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>2026-09-02T00:30:54.291474+00:00</t>
+          <t>2026-09-02T00:36:38.170050+00:00</t>
         </is>
       </c>
       <c r="AD20" t="inlineStr">
@@ -5330,7 +5330,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>2026-09-02T00:30:57.377021+00:00</t>
+          <t>2026-09-02T00:36:41.863188+00:00</t>
         </is>
       </c>
       <c r="AD21" t="inlineStr">
@@ -5416,7 +5416,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>2026-09-02T00:30:56.284347+00:00</t>
+          <t>2026-09-02T00:36:40.665294+00:00</t>
         </is>
       </c>
       <c r="AD22" t="inlineStr">
@@ -5505,7 +5505,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>2026-09-02T00:30:56.007732+00:00</t>
+          <t>2026-09-02T00:36:40.375382+00:00</t>
         </is>
       </c>
       <c r="AD23" t="inlineStr">
@@ -5597,7 +5597,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>2026-09-02T00:30:52.402454+00:00</t>
+          <t>2026-09-02T00:36:36.420309+00:00</t>
         </is>
       </c>
       <c r="AD24" t="inlineStr">
@@ -5683,7 +5683,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>2026-09-02T00:30:56.813916+00:00</t>
+          <t>2026-09-02T00:36:41.324030+00:00</t>
         </is>
       </c>
       <c r="AD25" t="inlineStr">
@@ -5772,7 +5772,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>2026-09-02T00:30:52.053889+00:00</t>
+          <t>2026-09-02T00:36:36.112055+00:00</t>
         </is>
       </c>
       <c r="AD26" t="inlineStr">
@@ -5864,7 +5864,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>2026-09-02T00:30:54.546564+00:00</t>
+          <t>2026-09-02T00:36:38.517056+00:00</t>
         </is>
       </c>
       <c r="AD27" t="inlineStr">
@@ -5946,7 +5946,7 @@
         <v>-0.113207676029062</v>
       </c>
       <c r="W28" t="n">
-        <v>-0.2142464393931921</v>
+        <v>-0.2142465045289341</v>
       </c>
       <c r="X28" t="n">
         <v>0.00148</v>
@@ -5956,7 +5956,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>2026-09-02T00:30:53.281481+00:00</t>
+          <t>2026-09-02T00:36:37.239041+00:00</t>
         </is>
       </c>
       <c r="AD28" t="inlineStr">
@@ -6045,7 +6045,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>2026-09-02T00:30:51.804584+00:00</t>
+          <t>2026-09-02T00:36:35.833277+00:00</t>
         </is>
       </c>
       <c r="AD29" t="inlineStr">
@@ -6137,7 +6137,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>2026-09-02T00:30:57.090707+00:00</t>
+          <t>2026-09-02T00:36:41.593316+00:00</t>
         </is>
       </c>
       <c r="AD30" t="inlineStr">
@@ -6216,7 +6216,7 @@
         <v>-0.04651959579188036</v>
       </c>
       <c r="W31" t="n">
-        <v>-0.3679267141388564</v>
+        <v>-0.3679267572759877</v>
       </c>
       <c r="X31" t="n">
         <v>0.40498</v>
@@ -6226,7 +6226,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>2026-09-02T00:30:53.625684+00:00</t>
+          <t>2026-09-02T00:36:37.573041+00:00</t>
         </is>
       </c>
       <c r="AD31" t="inlineStr">

--- a/reports/investment_dashboard.xlsx
+++ b/reports/investment_dashboard.xlsx
@@ -3594,7 +3594,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>2026-09-02T00:36:37.848591+00:00</t>
+          <t>2026-09-02T00:48:26.682757+00:00</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
@@ -3686,7 +3686,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>2026-09-02T00:36:34.826555+00:00</t>
+          <t>2026-09-02T00:48:20.954542+00:00</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
@@ -3778,7 +3778,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>2026-09-02T00:36:35.326853+00:00</t>
+          <t>2026-09-02T00:48:21.975282+00:00</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
@@ -3870,7 +3870,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>2026-09-02T00:36:39.193989+00:00</t>
+          <t>2026-09-02T00:48:28.905875+00:00</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
@@ -3962,7 +3962,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>2026-09-02T00:36:33.611166+00:00</t>
+          <t>2026-09-02T00:48:18.756392+00:00</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr">
@@ -4054,7 +4054,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>2026-09-02T00:36:33.362209+00:00</t>
+          <t>2026-09-02T00:48:18.231248+00:00</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr">
@@ -4136,7 +4136,7 @@
         <v>0.02994415880569301</v>
       </c>
       <c r="W8" t="n">
-        <v>1.84437386065034</v>
+        <v>1.844373676648285</v>
       </c>
       <c r="X8" t="n">
         <v>0.00202</v>
@@ -4146,7 +4146,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>2026-09-02T00:36:35.586293+00:00</t>
+          <t>2026-09-02T00:48:22.499663+00:00</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr">
@@ -4238,7 +4238,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>2026-09-02T00:36:39.745979+00:00</t>
+          <t>2026-09-02T00:48:29.482503+00:00</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr">
@@ -4327,7 +4327,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>2026-09-02T00:36:42.145872+00:00</t>
+          <t>2026-09-02T00:48:33.608470+00:00</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr">
@@ -4419,7 +4419,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>2026-09-02T00:36:33.899038+00:00</t>
+          <t>2026-09-02T00:48:19.286750+00:00</t>
         </is>
       </c>
       <c r="AD11" t="inlineStr">
@@ -4501,7 +4501,7 @@
         <v>0.09440194836202598</v>
       </c>
       <c r="W12" t="n">
-        <v>0.578017530788989</v>
+        <v>0.5780174173733443</v>
       </c>
       <c r="X12" t="n">
         <v>0.01596</v>
@@ -4511,7 +4511,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>2026-09-02T00:36:36.715118+00:00</t>
+          <t>2026-09-02T00:48:24.561805+00:00</t>
         </is>
       </c>
       <c r="AD12" t="inlineStr">
@@ -4590,7 +4590,7 @@
         <v>-0.2763097300440246</v>
       </c>
       <c r="V13" t="n">
-        <v>1.60384906681578</v>
+        <v>1.603849312680738</v>
       </c>
       <c r="W13" t="n">
         <v>2.353558732223212</v>
@@ -4603,7 +4603,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>2026-09-02T00:36:38.898963+00:00</t>
+          <t>2026-09-02T00:48:28.424853+00:00</t>
         </is>
       </c>
       <c r="AD13" t="inlineStr">
@@ -4695,7 +4695,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>2026-09-02T00:36:34.482153+00:00</t>
+          <t>2026-09-02T00:48:20.381620+00:00</t>
         </is>
       </c>
       <c r="AD14" t="inlineStr">
@@ -4787,7 +4787,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>2026-09-02T00:36:34.208148+00:00</t>
+          <t>2026-09-02T00:48:19.845082+00:00</t>
         </is>
       </c>
       <c r="AD15" t="inlineStr">
@@ -4879,7 +4879,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>2026-09-02T00:36:41.026249+00:00</t>
+          <t>2026-09-02T00:48:31.568280+00:00</t>
         </is>
       </c>
       <c r="AD16" t="inlineStr">
@@ -4958,7 +4958,7 @@
         <v>-0.2345861871854436</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.006462899538105416</v>
+        <v>-0.006462781850907096</v>
       </c>
       <c r="W17" t="n">
         <v>1.009031464856126</v>
@@ -4971,7 +4971,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>2026-09-02T00:36:40.020567+00:00</t>
+          <t>2026-09-02T00:48:30.040513+00:00</t>
         </is>
       </c>
       <c r="AD17" t="inlineStr">
@@ -5060,7 +5060,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>2026-09-02T00:36:35.058564+00:00</t>
+          <t>2026-09-02T00:48:21.434343+00:00</t>
         </is>
       </c>
       <c r="AD18" t="inlineStr">
@@ -5152,7 +5152,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>2026-09-02T00:36:36.984795+00:00</t>
+          <t>2026-09-02T00:48:25.026902+00:00</t>
         </is>
       </c>
       <c r="AD19" t="inlineStr">
@@ -5234,7 +5234,7 @@
         <v>0.1737887690369853</v>
       </c>
       <c r="W20" t="n">
-        <v>1.257019376263188</v>
+        <v>1.257019189539317</v>
       </c>
       <c r="X20" t="n">
         <v>0.00016000001</v>
@@ -5244,7 +5244,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>2026-09-02T00:36:38.170050+00:00</t>
+          <t>2026-09-02T00:48:27.339930+00:00</t>
         </is>
       </c>
       <c r="AD20" t="inlineStr">
@@ -5330,7 +5330,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>2026-09-02T00:36:41.863188+00:00</t>
+          <t>2026-09-02T00:48:33.084997+00:00</t>
         </is>
       </c>
       <c r="AD21" t="inlineStr">
@@ -5416,7 +5416,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>2026-09-02T00:36:40.665294+00:00</t>
+          <t>2026-09-02T00:48:31.055371+00:00</t>
         </is>
       </c>
       <c r="AD22" t="inlineStr">
@@ -5505,7 +5505,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>2026-09-02T00:36:40.375382+00:00</t>
+          <t>2026-09-02T00:48:30.528746+00:00</t>
         </is>
       </c>
       <c r="AD23" t="inlineStr">
@@ -5587,7 +5587,7 @@
         <v>0.2622014726713937</v>
       </c>
       <c r="W24" t="n">
-        <v>-0.003054702084871797</v>
+        <v>-0.003054641545529702</v>
       </c>
       <c r="X24" t="n">
         <v>0.00090000004</v>
@@ -5597,7 +5597,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>2026-09-02T00:36:36.420309+00:00</t>
+          <t>2026-09-02T00:48:24.025406+00:00</t>
         </is>
       </c>
       <c r="AD24" t="inlineStr">
@@ -5683,7 +5683,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>2026-09-02T00:36:41.324030+00:00</t>
+          <t>2026-09-02T00:48:32.072903+00:00</t>
         </is>
       </c>
       <c r="AD25" t="inlineStr">
@@ -5772,7 +5772,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>2026-09-02T00:36:36.112055+00:00</t>
+          <t>2026-09-02T00:48:23.450308+00:00</t>
         </is>
       </c>
       <c r="AD26" t="inlineStr">
@@ -5860,11 +5860,11 @@
         <v>0.0007</v>
       </c>
       <c r="Y27" t="n">
-        <v>0.96182</v>
+        <v>0.96182996</v>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>2026-09-02T00:36:38.517056+00:00</t>
+          <t>2026-09-02T00:48:27.895461+00:00</t>
         </is>
       </c>
       <c r="AD27" t="inlineStr">
@@ -5946,7 +5946,7 @@
         <v>-0.113207676029062</v>
       </c>
       <c r="W28" t="n">
-        <v>-0.2142465045289341</v>
+        <v>-0.2142464393931921</v>
       </c>
       <c r="X28" t="n">
         <v>0.00148</v>
@@ -5956,7 +5956,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>2026-09-02T00:36:37.239041+00:00</t>
+          <t>2026-09-02T00:48:25.568074+00:00</t>
         </is>
       </c>
       <c r="AD28" t="inlineStr">
@@ -6045,7 +6045,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>2026-09-02T00:36:35.833277+00:00</t>
+          <t>2026-09-02T00:48:22.973110+00:00</t>
         </is>
       </c>
       <c r="AD29" t="inlineStr">
@@ -6137,7 +6137,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>2026-09-02T00:36:41.593316+00:00</t>
+          <t>2026-09-02T00:48:32.642141+00:00</t>
         </is>
       </c>
       <c r="AD30" t="inlineStr">
@@ -6226,7 +6226,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>2026-09-02T00:36:37.573041+00:00</t>
+          <t>2026-09-02T00:48:26.084050+00:00</t>
         </is>
       </c>
       <c r="AD31" t="inlineStr">

--- a/reports/investment_dashboard.xlsx
+++ b/reports/investment_dashboard.xlsx
@@ -3594,7 +3594,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>2026-09-02T00:48:26.682757+00:00</t>
+          <t>2026-09-02T00:50:58.262275+00:00</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
@@ -3676,7 +3676,7 @@
         <v>1.263250877901507</v>
       </c>
       <c r="W3" t="n">
-        <v>6.855962960553897</v>
+        <v>6.855963464985801</v>
       </c>
       <c r="X3" t="n">
         <v>0.00238</v>
@@ -3686,7 +3686,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>2026-09-02T00:48:20.954542+00:00</t>
+          <t>2026-09-02T00:50:54.827815+00:00</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
@@ -3778,7 +3778,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>2026-09-02T00:48:21.975282+00:00</t>
+          <t>2026-09-02T00:50:55.630447+00:00</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
@@ -3870,7 +3870,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>2026-09-02T00:48:28.905875+00:00</t>
+          <t>2026-09-02T00:50:59.492168+00:00</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
@@ -3962,7 +3962,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>2026-09-02T00:48:18.756392+00:00</t>
+          <t>2026-09-02T00:50:53.541501+00:00</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr">
@@ -4054,7 +4054,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>2026-09-02T00:48:18.231248+00:00</t>
+          <t>2026-09-02T00:50:53.192692+00:00</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>2026-09-02T00:48:22.499663+00:00</t>
+          <t>2026-09-02T00:50:55.921994+00:00</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr">
@@ -4228,7 +4228,7 @@
         <v>1.780979770980133</v>
       </c>
       <c r="W9" t="n">
-        <v>2.523665741855378</v>
+        <v>2.523665964745376</v>
       </c>
       <c r="X9" t="n">
         <v>0.07491</v>
@@ -4238,7 +4238,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>2026-09-02T00:48:29.482503+00:00</t>
+          <t>2026-09-02T00:50:59.774095+00:00</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr">
@@ -4327,7 +4327,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>2026-09-02T00:48:33.608470+00:00</t>
+          <t>2026-09-02T00:51:02.061396+00:00</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr">
@@ -4419,7 +4419,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>2026-09-02T00:48:19.286750+00:00</t>
+          <t>2026-09-02T00:50:53.840915+00:00</t>
         </is>
       </c>
       <c r="AD11" t="inlineStr">
@@ -4501,7 +4501,7 @@
         <v>0.09440194836202598</v>
       </c>
       <c r="W12" t="n">
-        <v>0.5780174173733443</v>
+        <v>0.5780176442046498</v>
       </c>
       <c r="X12" t="n">
         <v>0.01596</v>
@@ -4511,7 +4511,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>2026-09-02T00:48:24.561805+00:00</t>
+          <t>2026-09-02T00:50:57.051188+00:00</t>
         </is>
       </c>
       <c r="AD12" t="inlineStr">
@@ -4590,10 +4590,10 @@
         <v>-0.2763097300440246</v>
       </c>
       <c r="V13" t="n">
-        <v>1.603849312680738</v>
+        <v>1.60384906681578</v>
       </c>
       <c r="W13" t="n">
-        <v>2.353558732223212</v>
+        <v>2.353558936137119</v>
       </c>
       <c r="X13" t="n">
         <v>0.00494</v>
@@ -4603,7 +4603,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>2026-09-02T00:48:28.424853+00:00</t>
+          <t>2026-09-02T00:50:59.138204+00:00</t>
         </is>
       </c>
       <c r="AD13" t="inlineStr">
@@ -4695,7 +4695,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>2026-09-02T00:48:20.381620+00:00</t>
+          <t>2026-09-02T00:50:54.532797+00:00</t>
         </is>
       </c>
       <c r="AD14" t="inlineStr">
@@ -4787,7 +4787,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>2026-09-02T00:48:19.845082+00:00</t>
+          <t>2026-09-02T00:50:54.148701+00:00</t>
         </is>
       </c>
       <c r="AD15" t="inlineStr">
@@ -4879,7 +4879,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>2026-09-02T00:48:31.568280+00:00</t>
+          <t>2026-09-02T00:51:00.896612+00:00</t>
         </is>
       </c>
       <c r="AD16" t="inlineStr">
@@ -4961,7 +4961,7 @@
         <v>-0.006462781850907096</v>
       </c>
       <c r="W17" t="n">
-        <v>1.009031464856126</v>
+        <v>1.009031344553681</v>
       </c>
       <c r="X17" t="n">
         <v>0.00269</v>
@@ -4971,7 +4971,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>2026-09-02T00:48:30.040513+00:00</t>
+          <t>2026-09-02T00:51:00.046956+00:00</t>
         </is>
       </c>
       <c r="AD17" t="inlineStr">
@@ -5060,7 +5060,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>2026-09-02T00:48:21.434343+00:00</t>
+          <t>2026-09-02T00:50:55.109105+00:00</t>
         </is>
       </c>
       <c r="AD18" t="inlineStr">
@@ -5152,7 +5152,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>2026-09-02T00:48:25.026902+00:00</t>
+          <t>2026-09-02T00:50:57.334056+00:00</t>
         </is>
       </c>
       <c r="AD19" t="inlineStr">
@@ -5244,7 +5244,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>2026-09-02T00:48:27.339930+00:00</t>
+          <t>2026-09-02T00:50:58.541441+00:00</t>
         </is>
       </c>
       <c r="AD20" t="inlineStr">
@@ -5330,7 +5330,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>2026-09-02T00:48:33.084997+00:00</t>
+          <t>2026-09-02T00:51:01.793045+00:00</t>
         </is>
       </c>
       <c r="AD21" t="inlineStr">
@@ -5416,7 +5416,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>2026-09-02T00:48:31.055371+00:00</t>
+          <t>2026-09-02T00:51:00.629992+00:00</t>
         </is>
       </c>
       <c r="AD22" t="inlineStr">
@@ -5505,7 +5505,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>2026-09-02T00:48:30.528746+00:00</t>
+          <t>2026-09-02T00:51:00.347619+00:00</t>
         </is>
       </c>
       <c r="AD23" t="inlineStr">
@@ -5587,7 +5587,7 @@
         <v>0.2622014726713937</v>
       </c>
       <c r="W24" t="n">
-        <v>-0.003054641545529702</v>
+        <v>-0.003054702084871797</v>
       </c>
       <c r="X24" t="n">
         <v>0.00090000004</v>
@@ -5597,7 +5597,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>2026-09-02T00:48:24.025406+00:00</t>
+          <t>2026-09-02T00:50:56.807885+00:00</t>
         </is>
       </c>
       <c r="AD24" t="inlineStr">
@@ -5683,7 +5683,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>2026-09-02T00:48:32.072903+00:00</t>
+          <t>2026-09-02T00:51:01.152468+00:00</t>
         </is>
       </c>
       <c r="AD25" t="inlineStr">
@@ -5772,7 +5772,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>2026-09-02T00:48:23.450308+00:00</t>
+          <t>2026-09-02T00:50:56.453611+00:00</t>
         </is>
       </c>
       <c r="AD26" t="inlineStr">
@@ -5864,7 +5864,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>2026-09-02T00:48:27.895461+00:00</t>
+          <t>2026-09-02T00:50:58.836068+00:00</t>
         </is>
       </c>
       <c r="AD27" t="inlineStr">
@@ -5956,7 +5956,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>2026-09-02T00:48:25.568074+00:00</t>
+          <t>2026-09-02T00:50:57.637614+00:00</t>
         </is>
       </c>
       <c r="AD28" t="inlineStr">
@@ -6045,7 +6045,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>2026-09-02T00:48:22.973110+00:00</t>
+          <t>2026-09-02T00:50:56.190516+00:00</t>
         </is>
       </c>
       <c r="AD29" t="inlineStr">
@@ -6137,7 +6137,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>2026-09-02T00:48:32.642141+00:00</t>
+          <t>2026-09-02T00:51:01.433413+00:00</t>
         </is>
       </c>
       <c r="AD30" t="inlineStr">
@@ -6226,7 +6226,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>2026-09-02T00:48:26.084050+00:00</t>
+          <t>2026-09-02T00:50:57.939877+00:00</t>
         </is>
       </c>
       <c r="AD31" t="inlineStr">

--- a/reports/investment_dashboard.xlsx
+++ b/reports/investment_dashboard.xlsx
@@ -581,7 +581,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>53.88</v>
+        <v>53.89</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -1336,7 +1336,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>42.27</v>
+        <v>42.16</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -1473,16 +1473,16 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>MDB</t>
+          <t>SNOW</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>MongoDB, Inc.</t>
+          <t>Snowflake Inc.</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>41.77</v>
+        <v>41.62</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -1490,7 +1490,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>434.2099914550781</v>
+        <v>319.7999877929688</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1505,12 +1505,17 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Balance Sheet</t>
+          <t>Revenue Growth</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
           <t>Industry Growth; Valuation; Competitive Advantage; Catalysts; Inflation Resilience</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>Excessive price-to-sales valuation</t>
         </is>
       </c>
     </row>
@@ -1520,16 +1525,16 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>SNOW</t>
+          <t>SMCI</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Snowflake Inc.</t>
+          <t>Super Micro Computer, Inc.</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>41.62</v>
+        <v>41.43</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -1537,7 +1542,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>319.7999877929688</v>
+        <v>36.70999908447266</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1545,24 +1550,24 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>88.2</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="I22" t="n">
-        <v>88.2</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Revenue Growth</t>
+          <t>Revenue Growth; Valuation</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Industry Growth; Valuation; Competitive Advantage; Catalysts; Inflation Resilience</t>
+          <t>Industry Growth; Balance Sheet; Competitive Advantage; Momentum; Catalysts; Inflation Resilience</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>Excessive price-to-sales valuation</t>
+          <t>Negative free cash flow / unprofitable growth</t>
         </is>
       </c>
     </row>
@@ -1572,16 +1577,16 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>SMCI</t>
+          <t>MDB</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Super Micro Computer, Inc.</t>
+          <t>MongoDB, Inc.</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>41.43</v>
+        <v>41.35</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -1589,7 +1594,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>36.70999908447266</v>
+        <v>434.2099914550781</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1604,17 +1609,17 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Revenue Growth; Valuation</t>
+          <t>Balance Sheet</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Industry Growth; Balance Sheet; Competitive Advantage; Momentum; Catalysts; Inflation Resilience</t>
+          <t>Industry Growth; Valuation; Competitive Advantage; Catalysts; Inflation Resilience</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>Negative free cash flow / unprofitable growth</t>
+          <t>Very high earnings multiple</t>
         </is>
       </c>
     </row>
@@ -2171,7 +2176,7 @@
         <v>9.02</v>
       </c>
       <c r="F3" t="n">
-        <v>4.94</v>
+        <v>4.95</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -2189,7 +2194,7 @@
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>53.88</v>
+        <v>53.89</v>
       </c>
     </row>
     <row r="4">
@@ -2771,7 +2776,7 @@
         <v>4.02</v>
       </c>
       <c r="F18" t="n">
-        <v>7.39</v>
+        <v>7.28</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -2789,7 +2794,7 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>42.27</v>
+        <v>42.16</v>
       </c>
     </row>
     <row r="19">
@@ -2875,11 +2880,11 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>MDB</t>
+          <t>SNOW</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>11.32</v>
+        <v>14.44</v>
       </c>
       <c r="C21" t="n">
         <v>7.5</v>
@@ -2888,19 +2893,19 @@
         <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>9.880000000000001</v>
+        <v>7.58</v>
       </c>
       <c r="F21" t="n">
-        <v>1.66</v>
+        <v>1.01</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>7.67</v>
+        <v>7.52</v>
       </c>
       <c r="I21" t="n">
-        <v>3.74</v>
+        <v>3.57</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2909,38 +2914,38 @@
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>41.77</v>
+        <v>41.62</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>SNOW</t>
+          <t>SMCI</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>14.44</v>
+        <v>15</v>
       </c>
       <c r="C22" t="n">
-        <v>7.5</v>
+        <v>7.23</v>
       </c>
       <c r="D22" t="n">
         <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>7.58</v>
+        <v>2.24</v>
       </c>
       <c r="F22" t="n">
-        <v>1.01</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>7.52</v>
+        <v>3.54</v>
       </c>
       <c r="I22" t="n">
-        <v>3.57</v>
+        <v>3.53</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2949,38 +2954,38 @@
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>41.62</v>
+        <v>41.43</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>SMCI</t>
+          <t>MDB</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>15</v>
+        <v>11.32</v>
       </c>
       <c r="C23" t="n">
-        <v>7.23</v>
+        <v>7.5</v>
       </c>
       <c r="D23" t="n">
         <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>2.23</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="F23" t="n">
-        <v>9.890000000000001</v>
+        <v>1.24</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>3.54</v>
+        <v>7.67</v>
       </c>
       <c r="I23" t="n">
-        <v>3.54</v>
+        <v>3.74</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2989,7 +2994,7 @@
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>41.43</v>
+        <v>41.35</v>
       </c>
     </row>
     <row r="24">
@@ -3594,7 +3599,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>2026-09-02T00:50:58.262275+00:00</t>
+          <t>2026-09-02T12:53:11.386229+00:00</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
@@ -3637,7 +3642,7 @@
         <v>3.457</v>
       </c>
       <c r="I3" t="n">
-        <v>44.2</v>
+        <v>44.25</v>
       </c>
       <c r="J3" t="n">
         <v>13.685</v>
@@ -3658,7 +3663,7 @@
         <v>0.80370003</v>
       </c>
       <c r="Q3" t="n">
-        <v>21.118551</v>
+        <v>21.094688</v>
       </c>
       <c r="R3" t="n">
         <v>11.678011</v>
@@ -3676,7 +3681,7 @@
         <v>1.263250877901507</v>
       </c>
       <c r="W3" t="n">
-        <v>6.855963464985801</v>
+        <v>6.855962960553897</v>
       </c>
       <c r="X3" t="n">
         <v>0.00238</v>
@@ -3686,7 +3691,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>2026-09-02T00:50:54.827815+00:00</t>
+          <t>2026-09-02T12:53:08.103911+00:00</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
@@ -3729,7 +3734,7 @@
         <v>1.57</v>
       </c>
       <c r="I4" t="n">
-        <v>2.51</v>
+        <v>2.5</v>
       </c>
       <c r="J4" t="n">
         <v>3.432</v>
@@ -3750,7 +3755,7 @@
         <v>0.35661998</v>
       </c>
       <c r="Q4" t="n">
-        <v>82.32271</v>
+        <v>82.652</v>
       </c>
       <c r="R4" t="n">
         <v>29.08582</v>
@@ -3778,7 +3783,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>2026-09-02T00:50:55.630447+00:00</t>
+          <t>2026-09-02T12:53:08.674025+00:00</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
@@ -3821,7 +3826,7 @@
         <v>0.377</v>
       </c>
       <c r="I5" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="J5" t="n">
         <v>0.357</v>
@@ -3842,7 +3847,7 @@
         <v>0.45393002</v>
       </c>
       <c r="Q5" t="n">
-        <v>60.082535</v>
+        <v>62.05246</v>
       </c>
       <c r="R5" t="n">
         <v>22.64528</v>
@@ -3870,7 +3875,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>2026-09-02T00:50:59.492168+00:00</t>
+          <t>2026-09-02T12:53:12.595669+00:00</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
@@ -3913,7 +3918,7 @@
         <v>0.928</v>
       </c>
       <c r="I6" t="n">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="J6" t="n">
         <v>2.154</v>
@@ -3934,7 +3939,7 @@
         <v>0.47120997</v>
       </c>
       <c r="Q6" t="n">
-        <v>153.77779</v>
+        <v>159.22124</v>
       </c>
       <c r="R6" t="n">
         <v>70.234314</v>
@@ -3962,7 +3967,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>2026-09-02T00:50:53.541501+00:00</t>
+          <t>2026-09-02T12:53:06.911248+00:00</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr">
@@ -4005,7 +4010,7 @@
         <v>1.059</v>
       </c>
       <c r="I7" t="n">
-        <v>7.92</v>
+        <v>7.91</v>
       </c>
       <c r="J7" t="n">
         <v>1.278</v>
@@ -4026,7 +4031,7 @@
         <v>0.66236997</v>
       </c>
       <c r="Q7" t="n">
-        <v>27.454546</v>
+        <v>27.489254</v>
       </c>
       <c r="R7" t="n">
         <v>17.330175</v>
@@ -4054,7 +4059,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>2026-09-02T00:50:53.192692+00:00</t>
+          <t>2026-09-02T12:53:06.618683+00:00</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr">
@@ -4136,7 +4141,7 @@
         <v>0.02994415880569301</v>
       </c>
       <c r="W8" t="n">
-        <v>1.844373676648285</v>
+        <v>1.84437386065034</v>
       </c>
       <c r="X8" t="n">
         <v>0.00202</v>
@@ -4146,7 +4151,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>2026-09-02T00:50:55.921994+00:00</t>
+          <t>2026-09-02T12:53:08.999150+00:00</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr">
@@ -4228,7 +4233,7 @@
         <v>1.780979770980133</v>
       </c>
       <c r="W9" t="n">
-        <v>2.523665964745376</v>
+        <v>2.523665518965409</v>
       </c>
       <c r="X9" t="n">
         <v>0.07491</v>
@@ -4238,7 +4243,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>2026-09-02T00:50:59.774095+00:00</t>
+          <t>2026-09-02T12:53:12.880306+00:00</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr">
@@ -4327,7 +4332,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>2026-09-02T00:51:02.061396+00:00</t>
+          <t>2026-09-02T12:53:15.114086+00:00</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr">
@@ -4419,7 +4424,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>2026-09-02T00:50:53.840915+00:00</t>
+          <t>2026-09-02T12:53:07.143092+00:00</t>
         </is>
       </c>
       <c r="AD11" t="inlineStr">
@@ -4462,7 +4467,7 @@
         <v>0.242</v>
       </c>
       <c r="I12" t="n">
-        <v>19.92</v>
+        <v>19.93</v>
       </c>
       <c r="J12" t="n">
         <v>2.94</v>
@@ -4483,7 +4488,7 @@
         <v>0.34033</v>
       </c>
       <c r="Q12" t="n">
-        <v>16.818272</v>
+        <v>16.809834</v>
       </c>
       <c r="R12" t="n">
         <v>9.189470999999999</v>
@@ -4501,7 +4506,7 @@
         <v>0.09440194836202598</v>
       </c>
       <c r="W12" t="n">
-        <v>0.5780176442046498</v>
+        <v>0.578017530788989</v>
       </c>
       <c r="X12" t="n">
         <v>0.01596</v>
@@ -4511,7 +4516,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>2026-09-02T00:50:57.051188+00:00</t>
+          <t>2026-09-02T12:53:10.255690+00:00</t>
         </is>
       </c>
       <c r="AD12" t="inlineStr">
@@ -4603,7 +4608,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>2026-09-02T00:50:59.138204+00:00</t>
+          <t>2026-09-02T12:53:12.304813+00:00</t>
         </is>
       </c>
       <c r="AD13" t="inlineStr">
@@ -4646,7 +4651,7 @@
         <v>0.248</v>
       </c>
       <c r="I14" t="n">
-        <v>11.6</v>
+        <v>11.58</v>
       </c>
       <c r="J14" t="n">
         <v>0.428</v>
@@ -4667,7 +4672,7 @@
         <v>0.33736</v>
       </c>
       <c r="Q14" t="n">
-        <v>38.090515</v>
+        <v>38.156303</v>
       </c>
       <c r="R14" t="n">
         <v>11.371114</v>
@@ -4691,11 +4696,11 @@
         <v>0.0033000002</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.8632099600000001</v>
+        <v>0.8632300000000001</v>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>2026-09-02T00:50:54.532797+00:00</t>
+          <t>2026-09-02T12:53:07.780422+00:00</t>
         </is>
       </c>
       <c r="AD14" t="inlineStr">
@@ -4738,7 +4743,7 @@
         <v>0.479</v>
       </c>
       <c r="I15" t="n">
-        <v>6</v>
+        <v>5.99</v>
       </c>
       <c r="J15" t="n">
         <v>0.854</v>
@@ -4759,7 +4764,7 @@
         <v>0.48988</v>
       </c>
       <c r="Q15" t="n">
-        <v>61.61333</v>
+        <v>61.716194</v>
       </c>
       <c r="R15" t="n">
         <v>23.305935</v>
@@ -4787,7 +4792,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>2026-09-02T00:50:54.148701+00:00</t>
+          <t>2026-09-02T12:53:07.469160+00:00</t>
         </is>
       </c>
       <c r="AD15" t="inlineStr">
@@ -4830,7 +4835,7 @@
         <v>0.356</v>
       </c>
       <c r="I16" t="n">
-        <v>0.5</v>
+        <v>0.49</v>
       </c>
       <c r="J16" t="n">
         <v>14.985</v>
@@ -4851,7 +4856,7 @@
         <v>0.00666</v>
       </c>
       <c r="Q16" t="n">
-        <v>447.68</v>
+        <v>456.8163</v>
       </c>
       <c r="R16" t="n">
         <v>20.262394</v>
@@ -4879,7 +4884,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>2026-09-02T00:51:00.896612+00:00</t>
+          <t>2026-09-02T12:53:14.056257+00:00</t>
         </is>
       </c>
       <c r="AD16" t="inlineStr">
@@ -4922,7 +4927,7 @@
         <v>0.241</v>
       </c>
       <c r="I17" t="n">
-        <v>4.42</v>
+        <v>4.43</v>
       </c>
       <c r="J17" t="n">
         <v>0.53</v>
@@ -4943,7 +4948,7 @@
         <v>0.20362</v>
       </c>
       <c r="Q17" t="n">
-        <v>57.911762</v>
+        <v>57.78104</v>
       </c>
       <c r="R17" t="n">
         <v>8.584394</v>
@@ -4958,10 +4963,10 @@
         <v>-0.2345861871854436</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.006462781850907096</v>
+        <v>-0.006462899538105416</v>
       </c>
       <c r="W17" t="n">
-        <v>1.009031344553681</v>
+        <v>1.009031585158586</v>
       </c>
       <c r="X17" t="n">
         <v>0.00269</v>
@@ -4971,7 +4976,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>2026-09-02T00:51:00.046956+00:00</t>
+          <t>2026-09-02T12:53:13.233966+00:00</t>
         </is>
       </c>
       <c r="AD17" t="inlineStr">
@@ -5014,7 +5019,7 @@
         <v>0.36</v>
       </c>
       <c r="I18" t="n">
-        <v>2.12</v>
+        <v>2.04</v>
       </c>
       <c r="J18" t="n">
         <v>1.806</v>
@@ -5035,7 +5040,7 @@
         <v>0.16982001</v>
       </c>
       <c r="Q18" t="n">
-        <v>33.03774</v>
+        <v>34.333336</v>
       </c>
       <c r="R18" t="n">
         <v>4.700676</v>
@@ -5060,7 +5065,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>2026-09-02T00:50:55.109105+00:00</t>
+          <t>2026-09-02T12:53:08.398613+00:00</t>
         </is>
       </c>
       <c r="AD18" t="inlineStr">
@@ -5152,7 +5157,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>2026-09-02T00:50:57.334056+00:00</t>
+          <t>2026-09-02T12:53:10.502270+00:00</t>
         </is>
       </c>
       <c r="AD19" t="inlineStr">
@@ -5195,7 +5200,7 @@
         <v>0.213</v>
       </c>
       <c r="I20" t="n">
-        <v>29.51</v>
+        <v>29.47</v>
       </c>
       <c r="J20" t="n">
         <v>0.285</v>
@@ -5216,7 +5221,7 @@
         <v>0.37057</v>
       </c>
       <c r="Q20" t="n">
-        <v>56.426296</v>
+        <v>56.502888</v>
       </c>
       <c r="R20" t="n">
         <v>18.104319</v>
@@ -5234,7 +5239,7 @@
         <v>0.1737887690369853</v>
       </c>
       <c r="W20" t="n">
-        <v>1.257019189539317</v>
+        <v>1.257019376263188</v>
       </c>
       <c r="X20" t="n">
         <v>0.00016000001</v>
@@ -5244,7 +5249,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>2026-09-02T00:50:58.541441+00:00</t>
+          <t>2026-09-02T12:53:11.738600+00:00</t>
         </is>
       </c>
       <c r="AD20" t="inlineStr">
@@ -5256,12 +5261,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>MDB</t>
+          <t>SNOW</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>MongoDB, Inc.</t>
+          <t>Snowflake Inc.</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -5271,66 +5276,66 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Software - Infrastructure</t>
+          <t>Software - Application</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>34924347392</v>
+        <v>110842675200</v>
       </c>
       <c r="F21" t="n">
-        <v>434.2099914550781</v>
+        <v>319.7999877929688</v>
       </c>
       <c r="G21" t="n">
-        <v>2602398976</v>
+        <v>5032822784</v>
       </c>
       <c r="H21" t="n">
-        <v>0.252</v>
+        <v>0.335</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.36</v>
+        <v>-3.52</v>
       </c>
       <c r="K21" t="n">
-        <v>517605376</v>
+        <v>1739497728</v>
       </c>
       <c r="M21" t="n">
-        <v>2427152896</v>
+        <v>2954998016</v>
       </c>
       <c r="N21" t="n">
-        <v>58635000</v>
+        <v>2772094976</v>
       </c>
       <c r="O21" t="n">
-        <v>0.71970004</v>
+        <v>0.67144996</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.03607</v>
+        <v>-0.22173999</v>
       </c>
       <c r="R21" t="n">
-        <v>13.420059</v>
+        <v>22.023958</v>
       </c>
       <c r="S21" t="n">
-        <v>67.47292244507136</v>
+        <v>63.72108075555934</v>
       </c>
       <c r="T21" t="n">
-        <v>0.2866243253520242</v>
+        <v>0.09042549483106432</v>
       </c>
       <c r="U21" t="n">
-        <v>0.08972042555502191</v>
+        <v>0.2246303509766701</v>
       </c>
       <c r="V21" t="n">
-        <v>0.3359895954226169</v>
+        <v>0.8775317580878614</v>
       </c>
       <c r="W21" t="n">
-        <v>0.3757802718801986</v>
+        <v>0.3399814920213273</v>
       </c>
       <c r="X21" t="n">
-        <v>0.02641</v>
+        <v>0.02962</v>
       </c>
       <c r="Y21" t="n">
-        <v>0.96931</v>
+        <v>0.82354</v>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>2026-09-02T00:51:01.793045+00:00</t>
+          <t>2026-09-02T12:53:13.818318+00:00</t>
         </is>
       </c>
       <c r="AD21" t="inlineStr">
@@ -5342,12 +5347,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>SNOW</t>
+          <t>SMCI</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Snowflake Inc.</t>
+          <t>Super Micro Computer, Inc.</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -5357,66 +5362,69 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Software - Application</t>
+          <t>Computer Hardware</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>110842675200</v>
+        <v>24117198848</v>
       </c>
       <c r="F22" t="n">
-        <v>319.7999877929688</v>
+        <v>36.70999908447266</v>
       </c>
       <c r="G22" t="n">
-        <v>5032822784</v>
+        <v>39063072768</v>
       </c>
       <c r="H22" t="n">
-        <v>0.335</v>
+        <v>0.9320000000000001</v>
       </c>
       <c r="I22" t="n">
-        <v>-3.51</v>
+        <v>3.26</v>
+      </c>
+      <c r="J22" t="n">
+        <v>4.347</v>
       </c>
       <c r="K22" t="n">
-        <v>1739497728</v>
+        <v>-8248783872</v>
       </c>
       <c r="M22" t="n">
-        <v>2954998016</v>
+        <v>7544584192</v>
       </c>
       <c r="N22" t="n">
-        <v>2772094976</v>
+        <v>9259886592</v>
       </c>
       <c r="O22" t="n">
-        <v>0.67144996</v>
+        <v>0.108219996</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.22173999</v>
+        <v>0.13382</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>11.2607355</v>
       </c>
       <c r="R22" t="n">
-        <v>22.023958</v>
-      </c>
-      <c r="S22" t="n">
-        <v>63.72108075555934</v>
+        <v>0.6173912</v>
       </c>
       <c r="T22" t="n">
-        <v>0.09042549483106432</v>
+        <v>0.2926056189282595</v>
       </c>
       <c r="U22" t="n">
-        <v>0.2246303509766701</v>
+        <v>-0.2682878129504148</v>
       </c>
       <c r="V22" t="n">
-        <v>0.8775317580878614</v>
+        <v>0.153314457193326</v>
       </c>
       <c r="W22" t="n">
-        <v>0.3399814920213273</v>
+        <v>-0.1162735128695982</v>
       </c>
       <c r="X22" t="n">
-        <v>0.02962</v>
+        <v>0.12726</v>
       </c>
       <c r="Y22" t="n">
-        <v>0.82354</v>
+        <v>0.69504</v>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>2026-09-02T00:51:00.629992+00:00</t>
+          <t>2026-09-02T12:53:13.502676+00:00</t>
         </is>
       </c>
       <c r="AD22" t="inlineStr">
@@ -5428,12 +5436,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>SMCI</t>
+          <t>MDB</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Super Micro Computer, Inc.</t>
+          <t>MongoDB, Inc.</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -5443,69 +5451,69 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Computer Hardware</t>
+          <t>Software - Infrastructure</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>23746707456</v>
+        <v>34924347392</v>
       </c>
       <c r="F23" t="n">
-        <v>36.70999908447266</v>
+        <v>434.2099914550781</v>
       </c>
       <c r="G23" t="n">
-        <v>39063072768</v>
+        <v>2602398976</v>
       </c>
       <c r="H23" t="n">
-        <v>0.9320000000000001</v>
+        <v>0.252</v>
       </c>
       <c r="I23" t="n">
-        <v>3.26</v>
-      </c>
-      <c r="J23" t="n">
-        <v>4.094</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="K23" t="n">
-        <v>-8231267840</v>
+        <v>517605376</v>
       </c>
       <c r="M23" t="n">
-        <v>7521474048</v>
+        <v>2427152896</v>
       </c>
       <c r="N23" t="n">
-        <v>9311492096</v>
+        <v>58635000</v>
       </c>
       <c r="O23" t="n">
-        <v>0.108219996</v>
+        <v>0.71970004</v>
       </c>
       <c r="P23" t="n">
-        <v>0.13382</v>
+        <v>-0.03607</v>
       </c>
       <c r="Q23" t="n">
-        <v>11.2607355</v>
+        <v>629.28986</v>
       </c>
       <c r="R23" t="n">
-        <v>0.6079068</v>
+        <v>13.420059</v>
+      </c>
+      <c r="S23" t="n">
+        <v>67.47292244507136</v>
       </c>
       <c r="T23" t="n">
-        <v>0.2926056189282595</v>
+        <v>0.2866243253520242</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.2682878129504148</v>
+        <v>0.08972042555502191</v>
       </c>
       <c r="V23" t="n">
-        <v>0.153314457193326</v>
+        <v>0.3359895954226169</v>
       </c>
       <c r="W23" t="n">
-        <v>-0.1162735128695982</v>
+        <v>0.3757802718801986</v>
       </c>
       <c r="X23" t="n">
-        <v>0.12878999</v>
+        <v>0.02641</v>
       </c>
       <c r="Y23" t="n">
-        <v>0.7059299999999999</v>
+        <v>0.96931</v>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>2026-09-02T00:51:00.347619+00:00</t>
+          <t>2026-09-02T12:53:14.859182+00:00</t>
         </is>
       </c>
       <c r="AD23" t="inlineStr">
@@ -5548,7 +5556,7 @@
         <v>0.177</v>
       </c>
       <c r="I24" t="n">
-        <v>17.96</v>
+        <v>17.94</v>
       </c>
       <c r="J24" t="n">
         <v>0.317</v>
@@ -5569,7 +5577,7 @@
         <v>0.45111</v>
       </c>
       <c r="Q24" t="n">
-        <v>27.896437</v>
+        <v>27.927534</v>
       </c>
       <c r="R24" t="n">
         <v>11.211301</v>
@@ -5597,7 +5605,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>2026-09-02T00:50:56.807885+00:00</t>
+          <t>2026-09-02T12:53:09.965291+00:00</t>
         </is>
       </c>
       <c r="AD24" t="inlineStr">
@@ -5640,7 +5648,7 @@
         <v>0.359</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.58</v>
+        <v>-0.57</v>
       </c>
       <c r="K25" t="n">
         <v>691946368</v>
@@ -5683,7 +5691,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>2026-09-02T00:51:01.152468+00:00</t>
+          <t>2026-09-02T12:53:14.291416+00:00</t>
         </is>
       </c>
       <c r="AD25" t="inlineStr">
@@ -5726,7 +5734,7 @@
         <v>0.311</v>
       </c>
       <c r="I26" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="K26" t="n">
         <v>3579375104</v>
@@ -5744,7 +5752,7 @@
         <v>-0.02465</v>
       </c>
       <c r="Q26" t="n">
-        <v>314.86087</v>
+        <v>312.14655</v>
       </c>
       <c r="R26" t="n">
         <v>27.822876</v>
@@ -5772,7 +5780,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>2026-09-02T00:50:56.453611+00:00</t>
+          <t>2026-09-02T12:53:09.630573+00:00</t>
         </is>
       </c>
       <c r="AD26" t="inlineStr">
@@ -5857,14 +5865,14 @@
         <v>0.6977804314163147</v>
       </c>
       <c r="X27" t="n">
-        <v>0.0007</v>
+        <v>0.00068999996</v>
       </c>
       <c r="Y27" t="n">
         <v>0.96182996</v>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>2026-09-02T00:50:58.836068+00:00</t>
+          <t>2026-09-02T12:53:11.976325+00:00</t>
         </is>
       </c>
       <c r="AD27" t="inlineStr">
@@ -5907,7 +5915,7 @@
         <v>0.28</v>
       </c>
       <c r="I28" t="n">
-        <v>26.56</v>
+        <v>26.55</v>
       </c>
       <c r="J28" t="n">
         <v>-0.134</v>
@@ -5928,7 +5936,7 @@
         <v>0.34827</v>
       </c>
       <c r="Q28" t="n">
-        <v>21.78238</v>
+        <v>21.790583</v>
       </c>
       <c r="R28" t="n">
         <v>6.4571896</v>
@@ -5956,7 +5964,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>2026-09-02T00:50:57.637614+00:00</t>
+          <t>2026-09-02T12:53:10.750874+00:00</t>
         </is>
       </c>
       <c r="AD28" t="inlineStr">
@@ -5999,7 +6007,7 @@
         <v>0.258</v>
       </c>
       <c r="I29" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="K29" t="n">
         <v>1995385472</v>
@@ -6017,7 +6025,7 @@
         <v>-0.02259</v>
       </c>
       <c r="Q29" t="n">
-        <v>4301.4</v>
+        <v>5376.7505</v>
       </c>
       <c r="R29" t="n">
         <v>40.810184</v>
@@ -6038,14 +6046,14 @@
         <v>1.030398877771377</v>
       </c>
       <c r="X29" t="n">
-        <v>0.01456</v>
+        <v>0.01454</v>
       </c>
       <c r="Y29" t="n">
         <v>0.76548</v>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>2026-09-02T00:50:56.190516+00:00</t>
+          <t>2026-09-02T12:53:09.312547+00:00</t>
         </is>
       </c>
       <c r="AD29" t="inlineStr">
@@ -6130,14 +6138,14 @@
         <v>-0.2212195056236285</v>
       </c>
       <c r="X30" t="n">
-        <v>0.00176</v>
+        <v>0.0017499999</v>
       </c>
       <c r="Y30" t="n">
         <v>0.85097003</v>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>2026-09-02T00:51:01.433413+00:00</t>
+          <t>2026-09-02T12:53:14.583935+00:00</t>
         </is>
       </c>
       <c r="AD30" t="inlineStr">
@@ -6180,7 +6188,7 @@
         <v>0.206</v>
       </c>
       <c r="I31" t="n">
-        <v>5.83</v>
+        <v>5.84</v>
       </c>
       <c r="J31" t="n">
         <v>0.219</v>
@@ -6201,7 +6209,7 @@
         <v>0.36202</v>
       </c>
       <c r="Q31" t="n">
-        <v>24.240139</v>
+        <v>24.198631</v>
       </c>
       <c r="R31" t="n">
         <v>6.0434427</v>
@@ -6216,7 +6224,7 @@
         <v>-0.04651959579188036</v>
       </c>
       <c r="W31" t="n">
-        <v>-0.3679267572759877</v>
+        <v>-0.3679267141388564</v>
       </c>
       <c r="X31" t="n">
         <v>0.40498</v>
@@ -6226,7 +6234,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>2026-09-02T00:50:57.939877+00:00</t>
+          <t>2026-09-02T12:53:11.064265+00:00</t>
         </is>
       </c>
       <c r="AD31" t="inlineStr">
@@ -6872,7 +6880,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>MDB</t>
+          <t>SNOW</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -6906,14 +6914,14 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>SNOW</t>
+          <t>SMCI</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>88.2</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="C22" t="n">
-        <v>88.2</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -6922,7 +6930,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>eps_growth, pe_ratio</t>
+          <t>price_to_fcf</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -6940,7 +6948,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>SMCI</t>
+          <t>MDB</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -6956,7 +6964,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>price_to_fcf</t>
+          <t>eps_growth</t>
         </is>
       </c>
       <c r="G23" t="n">

--- a/reports/investment_dashboard.xlsx
+++ b/reports/investment_dashboard.xlsx
@@ -534,7 +534,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>55.15</v>
+        <v>55.42</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>414</v>
+        <v>412.9500122070312</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -581,7 +581,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>53.89</v>
+        <v>53.86</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -589,7 +589,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>933.4400024414062</v>
+        <v>945.4600219726562</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -624,16 +624,16 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>CRDO</t>
+          <t>NVDA</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Credo Technology Group Holding Ltd</t>
+          <t>NVIDIA Corporation</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>51.86</v>
+        <v>51.51</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -641,11 +641,11 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>206.6300048828125</v>
+        <v>227.2100067138672</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -666,7 +666,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Excessive price-to-sales valuation; High market sensitivity / beta</t>
+          <t>High market sensitivity / beta</t>
         </is>
       </c>
     </row>
@@ -685,7 +685,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>51.35</v>
+        <v>50.96</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -693,7 +693,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>189.2599945068359</v>
+        <v>185.1699981689453</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -728,16 +728,16 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>PLTR</t>
+          <t>CRDO</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Palantir Technologies Inc.</t>
+          <t>Credo Technology Group Holding Ltd</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>51.04</v>
+        <v>50.76</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -745,7 +745,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>179.9199981689453</v>
+        <v>168.6799926757812</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -770,7 +770,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Excessive price-to-sales valuation; Very high earnings multiple</t>
+          <t>Excessive price-to-sales valuation; High market sensitivity / beta</t>
         </is>
       </c>
     </row>
@@ -780,16 +780,16 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>NVDA</t>
+          <t>TER</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>NVIDIA Corporation</t>
+          <t>Teradyne, Inc.</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>50.44</v>
+        <v>50.08</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>217.4400024414062</v>
+        <v>344.4649963378906</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -818,11 +818,6 @@
       <c r="K7" t="inlineStr">
         <is>
           <t>Industry Growth; Valuation; Competitive Advantage; Catalysts; Inflation Resilience</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>High market sensitivity / beta</t>
         </is>
       </c>
     </row>
@@ -832,16 +827,16 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>TER</t>
+          <t>PLTR</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Teradyne, Inc.</t>
+          <t>Palantir Technologies Inc.</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>49.64</v>
+        <v>49.84</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -849,11 +844,11 @@
         </i